--- a/downloads/indicadores/SIC/SIC_datos.xlsx
+++ b/downloads/indicadores/SIC/SIC_datos.xlsx
@@ -687,7 +687,7 @@
       <c r="P6" s="6" t="n"/>
       <c r="Q6" s="6" t="n"/>
       <c r="R6" s="6" t="n">
-        <v>101.939093</v>
+        <v>101.941389</v>
       </c>
       <c r="S6" s="6" t="n">
         <v>99.495265</v>
@@ -759,7 +759,7 @@
       <c r="P7" s="9" t="n"/>
       <c r="Q7" s="9" t="n"/>
       <c r="R7" s="9" t="n">
-        <v>101.677178</v>
+        <v>101.679166</v>
       </c>
       <c r="S7" s="9" t="n">
         <v>99.51222199999999</v>
@@ -831,7 +831,7 @@
       <c r="P8" s="6" t="n"/>
       <c r="Q8" s="6" t="n"/>
       <c r="R8" s="6" t="n">
-        <v>101.414188</v>
+        <v>101.415867</v>
       </c>
       <c r="S8" s="6" t="n">
         <v>99.52595599999999</v>
@@ -903,7 +903,7 @@
       <c r="P9" s="9" t="n"/>
       <c r="Q9" s="9" t="n"/>
       <c r="R9" s="9" t="n">
-        <v>101.145765</v>
+        <v>101.147129</v>
       </c>
       <c r="S9" s="9" t="n">
         <v>99.529944</v>
@@ -975,7 +975,7 @@
       <c r="P10" s="6" t="n"/>
       <c r="Q10" s="6" t="n"/>
       <c r="R10" s="6" t="n">
-        <v>100.866283</v>
+        <v>100.867318</v>
       </c>
       <c r="S10" s="6" t="n">
         <v>99.52073900000001</v>
@@ -1047,7 +1047,7 @@
       <c r="P11" s="9" t="n"/>
       <c r="Q11" s="9" t="n"/>
       <c r="R11" s="9" t="n">
-        <v>100.572182</v>
+        <v>100.572872</v>
       </c>
       <c r="S11" s="9" t="n">
         <v>99.50088</v>
@@ -1119,7 +1119,7 @@
       <c r="P12" s="6" t="n"/>
       <c r="Q12" s="6" t="n"/>
       <c r="R12" s="6" t="n">
-        <v>100.266893</v>
+        <v>100.267224</v>
       </c>
       <c r="S12" s="6" t="n">
         <v>99.48105200000001</v>
@@ -1191,7 +1191,7 @@
       <c r="P13" s="9" t="n"/>
       <c r="Q13" s="9" t="n"/>
       <c r="R13" s="9" t="n">
-        <v>99.963573</v>
+        <v>99.963548</v>
       </c>
       <c r="S13" s="9" t="n">
         <v>99.473849</v>
@@ -1263,7 +1263,7 @@
       <c r="P14" s="6" t="n"/>
       <c r="Q14" s="6" t="n"/>
       <c r="R14" s="6" t="n">
-        <v>99.668307</v>
+        <v>99.667934</v>
       </c>
       <c r="S14" s="6" t="n">
         <v>99.487202</v>
@@ -1335,7 +1335,7 @@
       <c r="P15" s="9" t="n"/>
       <c r="Q15" s="9" t="n"/>
       <c r="R15" s="9" t="n">
-        <v>99.376735</v>
+        <v>99.37602</v>
       </c>
       <c r="S15" s="9" t="n">
         <v>99.52110999999999</v>
@@ -1407,7 +1407,7 @@
       <c r="P16" s="6" t="n"/>
       <c r="Q16" s="6" t="n"/>
       <c r="R16" s="6" t="n">
-        <v>99.08217500000001</v>
+        <v>99.081114</v>
       </c>
       <c r="S16" s="6" t="n">
         <v>99.570081</v>
@@ -1479,7 +1479,7 @@
       <c r="P17" s="9" t="n"/>
       <c r="Q17" s="9" t="n"/>
       <c r="R17" s="9" t="n">
-        <v>98.78179799999999</v>
+        <v>98.780384</v>
       </c>
       <c r="S17" s="9" t="n">
         <v>99.62748000000001</v>
@@ -1557,7 +1557,7 @@
         <v>106.952153</v>
       </c>
       <c r="R18" s="6" t="n">
-        <v>98.48235</v>
+        <v>98.480585</v>
       </c>
       <c r="S18" s="6" t="n">
         <v>99.678867</v>
@@ -1635,7 +1635,7 @@
         <v>106.502529</v>
       </c>
       <c r="R19" s="9" t="n">
-        <v>98.19567499999999</v>
+        <v>98.193574</v>
       </c>
       <c r="S19" s="9" t="n">
         <v>99.712999</v>
@@ -1713,7 +1713,7 @@
         <v>106.051782</v>
       </c>
       <c r="R20" s="6" t="n">
-        <v>97.928355</v>
+        <v>97.92594099999999</v>
       </c>
       <c r="S20" s="6" t="n">
         <v>99.72793900000001</v>
@@ -1791,7 +1791,7 @@
         <v>105.594574</v>
       </c>
       <c r="R21" s="9" t="n">
-        <v>97.68249900000001</v>
+        <v>97.67979800000001</v>
       </c>
       <c r="S21" s="9" t="n">
         <v>99.7273</v>
@@ -1869,7 +1869,7 @@
         <v>105.122658</v>
       </c>
       <c r="R22" s="6" t="n">
-        <v>97.45650500000001</v>
+        <v>97.45354</v>
       </c>
       <c r="S22" s="6" t="n">
         <v>99.71915</v>
@@ -1947,7 +1947,7 @@
         <v>104.64142</v>
       </c>
       <c r="R23" s="9" t="n">
-        <v>97.24387900000001</v>
+        <v>97.24066500000001</v>
       </c>
       <c r="S23" s="9" t="n">
         <v>99.711607</v>
@@ -2025,7 +2025,7 @@
         <v>104.157259</v>
       </c>
       <c r="R24" s="6" t="n">
-        <v>97.040532</v>
+        <v>97.03708</v>
       </c>
       <c r="S24" s="6" t="n">
         <v>99.70895400000001</v>
@@ -2103,7 +2103,7 @@
         <v>103.672064</v>
       </c>
       <c r="R25" s="9" t="n">
-        <v>96.85361</v>
+        <v>96.849934</v>
       </c>
       <c r="S25" s="9" t="n">
         <v>99.709416</v>
@@ -2181,7 +2181,7 @@
         <v>103.183298</v>
       </c>
       <c r="R26" s="6" t="n">
-        <v>96.70961200000001</v>
+        <v>96.705758</v>
       </c>
       <c r="S26" s="6" t="n">
         <v>99.706962</v>
@@ -2259,7 +2259,7 @@
         <v>102.686076</v>
       </c>
       <c r="R27" s="9" t="n">
-        <v>96.651156</v>
+        <v>96.647215</v>
       </c>
       <c r="S27" s="9" t="n">
         <v>99.696932</v>
@@ -2337,7 +2337,7 @@
         <v>102.16971</v>
       </c>
       <c r="R28" s="6" t="n">
-        <v>96.741212</v>
+        <v>96.73735000000001</v>
       </c>
       <c r="S28" s="6" t="n">
         <v>99.67963899999999</v>
@@ -2415,7 +2415,7 @@
         <v>101.580592</v>
       </c>
       <c r="R29" s="9" t="n">
-        <v>97.047342</v>
+        <v>97.043802</v>
       </c>
       <c r="S29" s="9" t="n">
         <v>99.66201599999999</v>
@@ -2493,7 +2493,7 @@
         <v>100.876556</v>
       </c>
       <c r="R30" s="6" t="n">
-        <v>97.61970100000001</v>
+        <v>97.616789</v>
       </c>
       <c r="S30" s="6" t="n">
         <v>99.656966</v>
@@ -2571,7 +2571,7 @@
         <v>100.081219</v>
       </c>
       <c r="R31" s="9" t="n">
-        <v>98.446913</v>
+        <v>98.444929</v>
       </c>
       <c r="S31" s="9" t="n">
         <v>99.676513</v>
@@ -2649,7 +2649,7 @@
         <v>99.2047</v>
       </c>
       <c r="R32" s="6" t="n">
-        <v>99.368572</v>
+        <v>99.367648</v>
       </c>
       <c r="S32" s="6" t="n">
         <v>99.72995400000001</v>
@@ -2727,7 +2727,7 @@
         <v>98.289587</v>
       </c>
       <c r="R33" s="9" t="n">
-        <v>100.19379</v>
+        <v>100.193865</v>
       </c>
       <c r="S33" s="9" t="n">
         <v>99.82688</v>
@@ -2805,7 +2805,7 @@
         <v>97.450121</v>
       </c>
       <c r="R34" s="6" t="n">
-        <v>100.828526</v>
+        <v>100.829396</v>
       </c>
       <c r="S34" s="6" t="n">
         <v>99.96764899999999</v>
@@ -2883,7 +2883,7 @@
         <v>96.787127</v>
       </c>
       <c r="R35" s="9" t="n">
-        <v>101.307262</v>
+        <v>101.308747</v>
       </c>
       <c r="S35" s="9" t="n">
         <v>100.136386</v>
@@ -2961,7 +2961,7 @@
         <v>96.303622</v>
       </c>
       <c r="R36" s="6" t="n">
-        <v>101.705298</v>
+        <v>101.707294</v>
       </c>
       <c r="S36" s="6" t="n">
         <v>100.303258</v>
@@ -3039,7 +3039,7 @@
         <v>96.00009</v>
       </c>
       <c r="R37" s="9" t="n">
-        <v>102.074932</v>
+        <v>102.077392</v>
       </c>
       <c r="S37" s="9" t="n">
         <v>100.438409</v>
@@ -3117,7 +3117,7 @@
         <v>95.833355</v>
       </c>
       <c r="R38" s="6" t="n">
-        <v>102.375824</v>
+        <v>102.378652</v>
       </c>
       <c r="S38" s="6" t="n">
         <v>100.526374</v>
@@ -3195,7 +3195,7 @@
         <v>95.712726</v>
       </c>
       <c r="R39" s="9" t="n">
-        <v>102.563586</v>
+        <v>102.566638</v>
       </c>
       <c r="S39" s="9" t="n">
         <v>100.576221</v>
@@ -3273,7 +3273,7 @@
         <v>95.60773</v>
       </c>
       <c r="R40" s="6" t="n">
-        <v>102.684777</v>
+        <v>102.687969</v>
       </c>
       <c r="S40" s="6" t="n">
         <v>100.619526</v>
@@ -3351,7 +3351,7 @@
         <v>95.505442</v>
       </c>
       <c r="R41" s="9" t="n">
-        <v>102.798247</v>
+        <v>102.801567</v>
       </c>
       <c r="S41" s="9" t="n">
         <v>100.683262</v>
@@ -3429,7 +3429,7 @@
         <v>95.467579</v>
       </c>
       <c r="R42" s="6" t="n">
-        <v>102.897725</v>
+        <v>102.901158</v>
       </c>
       <c r="S42" s="6" t="n">
         <v>100.774942</v>
@@ -3507,7 +3507,7 @@
         <v>95.52218499999999</v>
       </c>
       <c r="R43" s="9" t="n">
-        <v>102.933648</v>
+        <v>102.937119</v>
       </c>
       <c r="S43" s="9" t="n">
         <v>100.875771</v>
@@ -3585,7 +3585,7 @@
         <v>95.697683</v>
       </c>
       <c r="R44" s="6" t="n">
-        <v>102.889904</v>
+        <v>102.89332</v>
       </c>
       <c r="S44" s="6" t="n">
         <v>100.960643</v>
@@ -3663,7 +3663,7 @@
         <v>96.034391</v>
       </c>
       <c r="R45" s="9" t="n">
-        <v>102.779724</v>
+        <v>102.783008</v>
       </c>
       <c r="S45" s="9" t="n">
         <v>101.013305</v>
@@ -3741,7 +3741,7 @@
         <v>96.52513399999999</v>
       </c>
       <c r="R46" s="6" t="n">
-        <v>102.628501</v>
+        <v>102.631606</v>
       </c>
       <c r="S46" s="6" t="n">
         <v>101.026856</v>
@@ -3819,7 +3819,7 @@
         <v>97.10444099999999</v>
       </c>
       <c r="R47" s="9" t="n">
-        <v>102.452495</v>
+        <v>102.455392</v>
       </c>
       <c r="S47" s="9" t="n">
         <v>101.000264</v>
@@ -3897,7 +3897,7 @@
         <v>97.68363100000001</v>
       </c>
       <c r="R48" s="6" t="n">
-        <v>102.25915</v>
+        <v>102.261819</v>
       </c>
       <c r="S48" s="6" t="n">
         <v>100.936882</v>
@@ -3975,7 +3975,7 @@
         <v>98.226795</v>
       </c>
       <c r="R49" s="9" t="n">
-        <v>102.051668</v>
+        <v>102.054093</v>
       </c>
       <c r="S49" s="9" t="n">
         <v>100.842964</v>
@@ -4053,7 +4053,7 @@
         <v>98.73935899999999</v>
       </c>
       <c r="R50" s="6" t="n">
-        <v>101.8218</v>
+        <v>101.823955</v>
       </c>
       <c r="S50" s="6" t="n">
         <v>100.726367</v>
@@ -4131,7 +4131,7 @@
         <v>99.196934</v>
       </c>
       <c r="R51" s="9" t="n">
-        <v>101.554162</v>
+        <v>101.556001</v>
       </c>
       <c r="S51" s="9" t="n">
         <v>100.593533</v>
@@ -4209,7 +4209,7 @@
         <v>99.61892899999999</v>
       </c>
       <c r="R52" s="6" t="n">
-        <v>101.241426</v>
+        <v>101.242898</v>
       </c>
       <c r="S52" s="6" t="n">
         <v>100.448514</v>
@@ -4287,7 +4287,7 @@
         <v>100.00957</v>
       </c>
       <c r="R53" s="9" t="n">
-        <v>100.896087</v>
+        <v>100.897152</v>
       </c>
       <c r="S53" s="9" t="n">
         <v>100.29202</v>
@@ -4365,7 +4365,7 @@
         <v>100.298536</v>
       </c>
       <c r="R54" s="6" t="n">
-        <v>100.535219</v>
+        <v>100.535859</v>
       </c>
       <c r="S54" s="6" t="n">
         <v>100.123622</v>
@@ -4443,7 +4443,7 @@
         <v>100.384109</v>
       </c>
       <c r="R55" s="9" t="n">
-        <v>100.184056</v>
+        <v>100.184283</v>
       </c>
       <c r="S55" s="9" t="n">
         <v>99.944547</v>
@@ -4521,7 +4521,7 @@
         <v>100.242564</v>
       </c>
       <c r="R56" s="6" t="n">
-        <v>99.86263599999999</v>
+        <v>99.86248500000001</v>
       </c>
       <c r="S56" s="6" t="n">
         <v>99.760648</v>
@@ -4599,7 +4599,7 @@
         <v>99.98224500000001</v>
       </c>
       <c r="R57" s="9" t="n">
-        <v>99.580629</v>
+        <v>99.580146</v>
       </c>
       <c r="S57" s="9" t="n">
         <v>99.584147</v>
@@ -4677,7 +4677,7 @@
         <v>99.72409399999999</v>
       </c>
       <c r="R58" s="6" t="n">
-        <v>99.337833</v>
+        <v>99.337064</v>
       </c>
       <c r="S58" s="6" t="n">
         <v>99.42650399999999</v>
@@ -4755,7 +4755,7 @@
         <v>99.507971</v>
       </c>
       <c r="R59" s="9" t="n">
-        <v>99.124133</v>
+        <v>99.12311099999999</v>
       </c>
       <c r="S59" s="9" t="n">
         <v>99.29065300000001</v>
@@ -4833,7 +4833,7 @@
         <v>99.353987</v>
       </c>
       <c r="R60" s="6" t="n">
-        <v>98.925122</v>
+        <v>98.923866</v>
       </c>
       <c r="S60" s="6" t="n">
         <v>99.169594</v>
@@ -4911,7 +4911,7 @@
         <v>99.230988</v>
       </c>
       <c r="R61" s="9" t="n">
-        <v>98.72202799999999</v>
+        <v>98.720533</v>
       </c>
       <c r="S61" s="9" t="n">
         <v>99.053189</v>
@@ -4989,7 +4989,7 @@
         <v>99.061644</v>
       </c>
       <c r="R62" s="6" t="n">
-        <v>98.49393000000001</v>
+        <v>98.492166</v>
       </c>
       <c r="S62" s="6" t="n">
         <v>98.934439</v>
@@ -5067,7 +5067,7 @@
         <v>98.792233</v>
       </c>
       <c r="R63" s="9" t="n">
-        <v>98.226176</v>
+        <v>98.224097</v>
       </c>
       <c r="S63" s="9" t="n">
         <v>98.81493399999999</v>
@@ -5145,7 +5145,7 @@
         <v>98.440395</v>
       </c>
       <c r="R64" s="6" t="n">
-        <v>97.91884899999999</v>
+        <v>97.916408</v>
       </c>
       <c r="S64" s="6" t="n">
         <v>98.706216</v>
@@ -5223,7 +5223,7 @@
         <v>98.03715200000001</v>
       </c>
       <c r="R65" s="9" t="n">
-        <v>97.589376</v>
+        <v>97.58654799999999</v>
       </c>
       <c r="S65" s="9" t="n">
         <v>98.62401</v>
@@ -5301,7 +5301,7 @@
         <v>97.649612</v>
       </c>
       <c r="R66" s="6" t="n">
-        <v>97.27527000000001</v>
+        <v>97.272071</v>
       </c>
       <c r="S66" s="6" t="n">
         <v>98.583417</v>
@@ -5379,7 +5379,7 @@
         <v>97.353213</v>
       </c>
       <c r="R67" s="9" t="n">
-        <v>97.03260400000001</v>
+        <v>97.02912000000001</v>
       </c>
       <c r="S67" s="9" t="n">
         <v>98.594334</v>
@@ -5457,7 +5457,7 @@
         <v>97.164259</v>
       </c>
       <c r="R68" s="6" t="n">
-        <v>96.90470500000001</v>
+        <v>96.90107</v>
       </c>
       <c r="S68" s="6" t="n">
         <v>98.65728799999999</v>
@@ -5535,7 +5535,7 @@
         <v>97.092613</v>
       </c>
       <c r="R69" s="9" t="n">
-        <v>96.92171399999999</v>
+        <v>96.918099</v>
       </c>
       <c r="S69" s="9" t="n">
         <v>98.760068</v>
@@ -5613,7 +5613,7 @@
         <v>97.145049</v>
       </c>
       <c r="R70" s="6" t="n">
-        <v>97.097365</v>
+        <v>97.09395600000001</v>
       </c>
       <c r="S70" s="6" t="n">
         <v>98.88591599999999</v>
@@ -5691,7 +5691,7 @@
         <v>97.349131</v>
       </c>
       <c r="R71" s="9" t="n">
-        <v>97.428268</v>
+        <v>97.425248</v>
       </c>
       <c r="S71" s="9" t="n">
         <v>99.022496</v>
@@ -5769,7 +5769,7 @@
         <v>97.69759999999999</v>
       </c>
       <c r="R72" s="6" t="n">
-        <v>97.888482</v>
+        <v>97.886003</v>
       </c>
       <c r="S72" s="6" t="n">
         <v>99.163076</v>
@@ -5847,7 +5847,7 @@
         <v>98.14623899999999</v>
       </c>
       <c r="R73" s="9" t="n">
-        <v>98.409899</v>
+        <v>98.40803200000001</v>
       </c>
       <c r="S73" s="9" t="n">
         <v>99.301806</v>
@@ -5925,7 +5925,7 @@
         <v>98.630112</v>
       </c>
       <c r="R74" s="6" t="n">
-        <v>98.890839</v>
+        <v>98.889538</v>
       </c>
       <c r="S74" s="6" t="n">
         <v>99.435158</v>
@@ -6003,7 +6003,7 @@
         <v>99.083766</v>
       </c>
       <c r="R75" s="9" t="n">
-        <v>99.298456</v>
+        <v>99.297634</v>
       </c>
       <c r="S75" s="9" t="n">
         <v>99.563045</v>
@@ -6081,7 +6081,7 @@
         <v>99.411209</v>
       </c>
       <c r="R76" s="6" t="n">
-        <v>99.636045</v>
+        <v>99.63561900000001</v>
       </c>
       <c r="S76" s="6" t="n">
         <v>99.689082</v>
@@ -6159,7 +6159,7 @@
         <v>99.565517</v>
       </c>
       <c r="R77" s="9" t="n">
-        <v>99.927035</v>
+        <v>99.926952</v>
       </c>
       <c r="S77" s="9" t="n">
         <v>99.81725900000001</v>
@@ -6239,7 +6239,7 @@
         <v>99.54959599999999</v>
       </c>
       <c r="R78" s="6" t="n">
-        <v>100.200076</v>
+        <v>100.200313</v>
       </c>
       <c r="S78" s="6" t="n">
         <v>99.94747</v>
@@ -6319,7 +6319,7 @@
         <v>99.37104600000001</v>
       </c>
       <c r="R79" s="9" t="n">
-        <v>100.479713</v>
+        <v>100.480278</v>
       </c>
       <c r="S79" s="9" t="n">
         <v>100.078038</v>
@@ -6399,7 +6399,7 @@
         <v>99.10888</v>
       </c>
       <c r="R80" s="6" t="n">
-        <v>100.765946</v>
+        <v>100.766848</v>
       </c>
       <c r="S80" s="6" t="n">
         <v>100.211482</v>
@@ -6479,7 +6479,7 @@
         <v>98.88258</v>
       </c>
       <c r="R81" s="9" t="n">
-        <v>101.050641</v>
+        <v>101.051878</v>
       </c>
       <c r="S81" s="9" t="n">
         <v>100.353426</v>
@@ -6559,7 +6559,7 @@
         <v>98.798497</v>
       </c>
       <c r="R82" s="6" t="n">
-        <v>101.338639</v>
+        <v>101.340214</v>
       </c>
       <c r="S82" s="6" t="n">
         <v>100.509856</v>
@@ -6639,7 +6639,7 @@
         <v>98.901359</v>
       </c>
       <c r="R83" s="9" t="n">
-        <v>101.639309</v>
+        <v>101.641237</v>
       </c>
       <c r="S83" s="9" t="n">
         <v>100.684937</v>
@@ -6719,7 +6719,7 @@
         <v>99.208271</v>
       </c>
       <c r="R84" s="6" t="n">
-        <v>101.95443</v>
+        <v>101.956728</v>
       </c>
       <c r="S84" s="6" t="n">
         <v>100.877104</v>
@@ -6799,7 +6799,7 @@
         <v>99.69279299999999</v>
       </c>
       <c r="R85" s="9" t="n">
-        <v>102.267121</v>
+        <v>102.269787</v>
       </c>
       <c r="S85" s="9" t="n">
         <v>101.075985</v>
@@ -6879,7 +6879,7 @@
         <v>100.323211</v>
       </c>
       <c r="R86" s="6" t="n">
-        <v>102.552632</v>
+        <v>102.555633</v>
       </c>
       <c r="S86" s="6" t="n">
         <v>101.27015</v>
@@ -6959,7 +6959,7 @@
         <v>101.046648</v>
       </c>
       <c r="R87" s="9" t="n">
-        <v>102.782188</v>
+        <v>102.78546</v>
       </c>
       <c r="S87" s="9" t="n">
         <v>101.447219</v>
@@ -7039,7 +7039,7 @@
         <v>101.828367</v>
       </c>
       <c r="R88" s="6" t="n">
-        <v>102.939585</v>
+        <v>102.943042</v>
       </c>
       <c r="S88" s="6" t="n">
         <v>101.595407</v>
@@ -7119,7 +7119,7 @@
         <v>102.663793</v>
       </c>
       <c r="R89" s="9" t="n">
-        <v>103.027697</v>
+        <v>103.031257</v>
       </c>
       <c r="S89" s="9" t="n">
         <v>101.707919</v>
@@ -7201,7 +7201,7 @@
         <v>103.560733</v>
       </c>
       <c r="R90" s="6" t="n">
-        <v>103.061161</v>
+        <v>103.06476</v>
       </c>
       <c r="S90" s="6" t="n">
         <v>101.784681</v>
@@ -7283,7 +7283,7 @@
         <v>104.486584</v>
       </c>
       <c r="R91" s="9" t="n">
-        <v>103.0532</v>
+        <v>103.056789</v>
       </c>
       <c r="S91" s="9" t="n">
         <v>101.83014</v>
@@ -7365,7 +7365,7 @@
         <v>105.377068</v>
       </c>
       <c r="R92" s="6" t="n">
-        <v>103.007634</v>
+        <v>103.01117</v>
       </c>
       <c r="S92" s="6" t="n">
         <v>101.85151</v>
@@ -7447,7 +7447,7 @@
         <v>106.165579</v>
       </c>
       <c r="R93" s="9" t="n">
-        <v>102.922382</v>
+        <v>102.925817</v>
       </c>
       <c r="S93" s="9" t="n">
         <v>101.858534</v>
@@ -7529,7 +7529,7 @@
         <v>106.780635</v>
       </c>
       <c r="R94" s="6" t="n">
-        <v>102.80317</v>
+        <v>102.806465</v>
       </c>
       <c r="S94" s="6" t="n">
         <v>101.86425</v>
@@ -7611,7 +7611,7 @@
         <v>107.143222</v>
       </c>
       <c r="R95" s="9" t="n">
-        <v>102.652046</v>
+        <v>102.655164</v>
       </c>
       <c r="S95" s="9" t="n">
         <v>101.884985</v>
@@ -7693,7 +7693,7 @@
         <v>107.151878</v>
       </c>
       <c r="R96" s="6" t="n">
-        <v>102.468884</v>
+        <v>102.471786</v>
       </c>
       <c r="S96" s="6" t="n">
         <v>101.93854</v>
@@ -7775,7 +7775,7 @@
         <v>106.667278</v>
       </c>
       <c r="R97" s="9" t="n">
-        <v>102.262226</v>
+        <v>102.264885</v>
       </c>
       <c r="S97" s="9" t="n">
         <v>102.041426</v>
@@ -7857,7 +7857,7 @@
         <v>105.635126</v>
       </c>
       <c r="R98" s="6" t="n">
-        <v>102.040322</v>
+        <v>102.04272</v>
       </c>
       <c r="S98" s="6" t="n">
         <v>102.204806</v>
@@ -7939,7 +7939,7 @@
         <v>104.188999</v>
       </c>
       <c r="R99" s="9" t="n">
-        <v>101.80166</v>
+        <v>101.803778</v>
       </c>
       <c r="S99" s="9" t="n">
         <v>102.427555</v>
@@ -8021,7 +8021,7 @@
         <v>102.610306</v>
       </c>
       <c r="R100" s="6" t="n">
-        <v>101.544477</v>
+        <v>101.546291</v>
       </c>
       <c r="S100" s="6" t="n">
         <v>102.683684</v>
@@ -8103,7 +8103,7 @@
         <v>101.243674</v>
       </c>
       <c r="R101" s="9" t="n">
-        <v>101.254362</v>
+        <v>101.255835</v>
       </c>
       <c r="S101" s="9" t="n">
         <v>102.907545</v>
@@ -8185,7 +8185,7 @@
         <v>100.251374</v>
       </c>
       <c r="R102" s="6" t="n">
-        <v>100.905123</v>
+        <v>100.906186</v>
       </c>
       <c r="S102" s="6" t="n">
         <v>102.989028</v>
@@ -8267,7 +8267,7 @@
         <v>99.58345</v>
       </c>
       <c r="R103" s="9" t="n">
-        <v>100.517894</v>
+        <v>100.518501</v>
       </c>
       <c r="S103" s="9" t="n">
         <v>102.810462</v>
@@ -8349,7 +8349,7 @@
         <v>99.105767</v>
       </c>
       <c r="R104" s="6" t="n">
-        <v>100.140475</v>
+        <v>100.140638</v>
       </c>
       <c r="S104" s="6" t="n">
         <v>102.309906</v>
@@ -8431,7 +8431,7 @@
         <v>98.783759</v>
       </c>
       <c r="R105" s="9" t="n">
-        <v>99.808216</v>
+        <v>99.80798900000001</v>
       </c>
       <c r="S105" s="9" t="n">
         <v>101.540482</v>
@@ -8513,7 +8513,7 @@
         <v>98.600138</v>
       </c>
       <c r="R106" s="6" t="n">
-        <v>99.54073099999999</v>
+        <v>99.54019</v>
       </c>
       <c r="S106" s="6" t="n">
         <v>100.653315</v>
@@ -8595,7 +8595,7 @@
         <v>98.480902</v>
       </c>
       <c r="R107" s="9" t="n">
-        <v>99.342063</v>
+        <v>99.34128800000001</v>
       </c>
       <c r="S107" s="9" t="n">
         <v>99.81292500000001</v>
@@ -8677,7 +8677,7 @@
         <v>98.389815</v>
       </c>
       <c r="R108" s="6" t="n">
-        <v>99.207239</v>
+        <v>99.206305</v>
       </c>
       <c r="S108" s="6" t="n">
         <v>99.152598</v>
@@ -8759,7 +8759,7 @@
         <v>98.307175</v>
       </c>
       <c r="R109" s="9" t="n">
-        <v>99.12385500000001</v>
+        <v>99.12282399999999</v>
       </c>
       <c r="S109" s="9" t="n">
         <v>98.73942</v>
@@ -8841,7 +8841,7 @@
         <v>98.21720999999999</v>
       </c>
       <c r="R110" s="6" t="n">
-        <v>99.073103</v>
+        <v>99.072012</v>
       </c>
       <c r="S110" s="6" t="n">
         <v>98.574332</v>
@@ -8923,7 +8923,7 @@
         <v>98.118065</v>
       </c>
       <c r="R111" s="9" t="n">
-        <v>99.03675800000001</v>
+        <v>99.035623</v>
       </c>
       <c r="S111" s="9" t="n">
         <v>98.620761</v>
@@ -9005,7 +9005,7 @@
         <v>98.01443500000001</v>
       </c>
       <c r="R112" s="6" t="n">
-        <v>99.007864</v>
+        <v>99.00669600000001</v>
       </c>
       <c r="S112" s="6" t="n">
         <v>98.82359</v>
@@ -9087,7 +9087,7 @@
         <v>97.906109</v>
       </c>
       <c r="R113" s="9" t="n">
-        <v>98.994766</v>
+        <v>98.993583</v>
       </c>
       <c r="S113" s="9" t="n">
         <v>99.114391</v>
@@ -9169,7 +9169,7 @@
         <v>97.853639</v>
       </c>
       <c r="R114" s="6" t="n">
-        <v>99.01557699999999</v>
+        <v>99.01441800000001</v>
       </c>
       <c r="S114" s="6" t="n">
         <v>99.419799</v>
@@ -9251,7 +9251,7 @@
         <v>97.917035</v>
       </c>
       <c r="R115" s="9" t="n">
-        <v>99.08313800000001</v>
+        <v>99.082059</v>
       </c>
       <c r="S115" s="9" t="n">
         <v>99.682661</v>
@@ -9333,7 +9333,7 @@
         <v>98.129069</v>
       </c>
       <c r="R116" s="6" t="n">
-        <v>99.19528099999999</v>
+        <v>99.194333</v>
       </c>
       <c r="S116" s="6" t="n">
         <v>99.88001300000001</v>
@@ -9415,7 +9415,7 @@
         <v>98.464539</v>
       </c>
       <c r="R117" s="9" t="n">
-        <v>99.340371</v>
+        <v>99.33959400000001</v>
       </c>
       <c r="S117" s="9" t="n">
         <v>100.006662</v>
@@ -9497,7 +9497,7 @@
         <v>98.86287400000001</v>
       </c>
       <c r="R118" s="6" t="n">
-        <v>99.504935</v>
+        <v>99.504352</v>
       </c>
       <c r="S118" s="6" t="n">
         <v>100.057533</v>
@@ -9579,7 +9579,7 @@
         <v>99.246559</v>
       </c>
       <c r="R119" s="9" t="n">
-        <v>99.67598599999999</v>
+        <v>99.67560400000001</v>
       </c>
       <c r="S119" s="9" t="n">
         <v>100.023344</v>
@@ -9661,7 +9661,7 @@
         <v>99.549491</v>
       </c>
       <c r="R120" s="6" t="n">
-        <v>99.841255</v>
+        <v>99.841067</v>
       </c>
       <c r="S120" s="6" t="n">
         <v>99.91336699999999</v>
@@ -9743,7 +9743,7 @@
         <v>99.74402600000001</v>
       </c>
       <c r="R121" s="9" t="n">
-        <v>99.987199</v>
+        <v>99.987183</v>
       </c>
       <c r="S121" s="9" t="n">
         <v>99.788033</v>
@@ -9825,7 +9825,7 @@
         <v>99.808858</v>
       </c>
       <c r="R122" s="6" t="n">
-        <v>100.100111</v>
+        <v>100.100228</v>
       </c>
       <c r="S122" s="6" t="n">
         <v>99.72949199999999</v>
@@ -9907,7 +9907,7 @@
         <v>99.760751</v>
       </c>
       <c r="R123" s="9" t="n">
-        <v>100.167315</v>
+        <v>100.167511</v>
       </c>
       <c r="S123" s="9" t="n">
         <v>99.783154</v>
@@ -9989,7 +9989,7 @@
         <v>99.66736</v>
       </c>
       <c r="R124" s="6" t="n">
-        <v>100.183762</v>
+        <v>100.183978</v>
       </c>
       <c r="S124" s="6" t="n">
         <v>99.939645</v>
@@ -10071,7 +10071,7 @@
         <v>99.593937</v>
       </c>
       <c r="R125" s="9" t="n">
-        <v>100.156052</v>
+        <v>100.156235</v>
       </c>
       <c r="S125" s="9" t="n">
         <v>100.162556</v>
@@ -10153,7 +10153,7 @@
         <v>99.567795</v>
       </c>
       <c r="R126" s="6" t="n">
-        <v>100.108383</v>
+        <v>100.10851</v>
       </c>
       <c r="S126" s="6" t="n">
         <v>100.407028</v>
@@ -10235,7 +10235,7 @@
         <v>99.597928</v>
       </c>
       <c r="R127" s="9" t="n">
-        <v>100.068729</v>
+        <v>100.06881</v>
       </c>
       <c r="S127" s="9" t="n">
         <v>100.618107</v>
@@ -10317,7 +10317,7 @@
         <v>99.67031799999999</v>
       </c>
       <c r="R128" s="6" t="n">
-        <v>100.050125</v>
+        <v>100.050184</v>
       </c>
       <c r="S128" s="6" t="n">
         <v>100.740342</v>
@@ -10399,7 +10399,7 @@
         <v>99.753517</v>
       </c>
       <c r="R129" s="9" t="n">
-        <v>100.052915</v>
+        <v>100.052977</v>
       </c>
       <c r="S129" s="9" t="n">
         <v>100.736183</v>
@@ -10481,7 +10481,7 @@
         <v>99.7894</v>
       </c>
       <c r="R130" s="6" t="n">
-        <v>100.072087</v>
+        <v>100.072171</v>
       </c>
       <c r="S130" s="6" t="n">
         <v>100.605043</v>
@@ -10563,7 +10563,7 @@
         <v>99.704002</v>
       </c>
       <c r="R131" s="9" t="n">
-        <v>100.10163</v>
+        <v>100.101749</v>
       </c>
       <c r="S131" s="9" t="n">
         <v>100.392325</v>
@@ -10645,7 +10645,7 @@
         <v>99.496607</v>
       </c>
       <c r="R132" s="6" t="n">
-        <v>100.134788</v>
+        <v>100.134947</v>
       </c>
       <c r="S132" s="6" t="n">
         <v>100.167236</v>
@@ -10727,7 +10727,7 @@
         <v>99.191838</v>
       </c>
       <c r="R133" s="9" t="n">
-        <v>100.161324</v>
+        <v>100.161514</v>
       </c>
       <c r="S133" s="9" t="n">
         <v>99.971189</v>
@@ -10809,7 +10809,7 @@
         <v>98.88020299999999</v>
       </c>
       <c r="R134" s="6" t="n">
-        <v>100.165749</v>
+        <v>100.165945</v>
       </c>
       <c r="S134" s="6" t="n">
         <v>99.818096</v>
@@ -10891,7 +10891,7 @@
         <v>98.639599</v>
       </c>
       <c r="R135" s="9" t="n">
-        <v>100.132646</v>
+        <v>100.132803</v>
       </c>
       <c r="S135" s="9" t="n">
         <v>99.694985</v>
@@ -10973,7 +10973,7 @@
         <v>98.48047800000001</v>
       </c>
       <c r="R136" s="6" t="n">
-        <v>100.056365</v>
+        <v>100.056433</v>
       </c>
       <c r="S136" s="6" t="n">
         <v>99.579048</v>
@@ -11055,7 +11055,7 @@
         <v>98.427623</v>
       </c>
       <c r="R137" s="9" t="n">
-        <v>99.95037000000001</v>
+        <v>99.95031299999999</v>
       </c>
       <c r="S137" s="9" t="n">
         <v>99.45949400000001</v>
@@ -11137,7 +11137,7 @@
         <v>98.51862300000001</v>
       </c>
       <c r="R138" s="6" t="n">
-        <v>99.839725</v>
+        <v>99.839538</v>
       </c>
       <c r="S138" s="6" t="n">
         <v>99.328642</v>
@@ -11219,7 +11219,7 @@
         <v>98.78081</v>
       </c>
       <c r="R139" s="9" t="n">
-        <v>99.744871</v>
+        <v>99.744573</v>
       </c>
       <c r="S139" s="9" t="n">
         <v>99.193896</v>
@@ -11301,7 +11301,7 @@
         <v>99.19443099999999</v>
       </c>
       <c r="R140" s="6" t="n">
-        <v>99.67775399999999</v>
+        <v>99.67737700000001</v>
       </c>
       <c r="S140" s="6" t="n">
         <v>99.065923</v>
@@ -11383,7 +11383,7 @@
         <v>99.68305700000001</v>
       </c>
       <c r="R141" s="9" t="n">
-        <v>99.641248</v>
+        <v>99.640828</v>
       </c>
       <c r="S141" s="9" t="n">
         <v>98.954705</v>
@@ -11465,7 +11465,7 @@
         <v>100.170586</v>
       </c>
       <c r="R142" s="6" t="n">
-        <v>99.629503</v>
+        <v>99.62907</v>
       </c>
       <c r="S142" s="6" t="n">
         <v>98.864047</v>
@@ -11547,7 +11547,7 @@
         <v>100.590688</v>
       </c>
       <c r="R143" s="9" t="n">
-        <v>99.63114899999999</v>
+        <v>99.630719</v>
       </c>
       <c r="S143" s="9" t="n">
         <v>98.795748</v>
@@ -11629,7 +11629,7 @@
         <v>100.940242</v>
       </c>
       <c r="R144" s="6" t="n">
-        <v>99.632515</v>
+        <v>99.632086</v>
       </c>
       <c r="S144" s="6" t="n">
         <v>98.754431</v>
@@ -11711,7 +11711,7 @@
         <v>101.213714</v>
       </c>
       <c r="R145" s="9" t="n">
-        <v>99.61829899999999</v>
+        <v>99.617853</v>
       </c>
       <c r="S145" s="9" t="n">
         <v>98.736605</v>
@@ -11793,7 +11793,7 @@
         <v>101.427154</v>
       </c>
       <c r="R146" s="6" t="n">
-        <v>99.573066</v>
+        <v>99.57256700000001</v>
       </c>
       <c r="S146" s="6" t="n">
         <v>98.725776</v>
@@ -11875,7 +11875,7 @@
         <v>101.611</v>
       </c>
       <c r="R147" s="9" t="n">
-        <v>99.48729899999999</v>
+        <v>99.486701</v>
       </c>
       <c r="S147" s="9" t="n">
         <v>98.69170099999999</v>
@@ -11957,7 +11957,7 @@
         <v>101.780354</v>
       </c>
       <c r="R148" s="6" t="n">
-        <v>99.36391</v>
+        <v>99.36316600000001</v>
       </c>
       <c r="S148" s="6" t="n">
         <v>98.61841</v>
@@ -12039,7 +12039,7 @@
         <v>101.951922</v>
       </c>
       <c r="R149" s="9" t="n">
-        <v>99.221248</v>
+        <v>99.220337</v>
       </c>
       <c r="S149" s="9" t="n">
         <v>98.504752</v>
@@ -12121,7 +12121,7 @@
         <v>102.114124</v>
       </c>
       <c r="R150" s="6" t="n">
-        <v>99.084107</v>
+        <v>99.083035</v>
       </c>
       <c r="S150" s="6" t="n">
         <v>98.36104899999999</v>
@@ -12203,7 +12203,7 @@
         <v>102.210828</v>
       </c>
       <c r="R151" s="9" t="n">
-        <v>98.972076</v>
+        <v>98.970873</v>
       </c>
       <c r="S151" s="9" t="n">
         <v>98.21176699999999</v>
@@ -12285,7 +12285,7 @@
         <v>102.178211</v>
       </c>
       <c r="R152" s="6" t="n">
-        <v>98.89405600000001</v>
+        <v>98.892762</v>
       </c>
       <c r="S152" s="6" t="n">
         <v>98.09177699999999</v>
@@ -12367,7 +12367,7 @@
         <v>101.995538</v>
       </c>
       <c r="R153" s="9" t="n">
-        <v>98.84835200000001</v>
+        <v>98.847004</v>
       </c>
       <c r="S153" s="9" t="n">
         <v>98.046232</v>
@@ -12449,7 +12449,7 @@
         <v>101.677787</v>
       </c>
       <c r="R154" s="6" t="n">
-        <v>98.826466</v>
+        <v>98.825093</v>
       </c>
       <c r="S154" s="6" t="n">
         <v>98.108315</v>
@@ -12531,7 +12531,7 @@
         <v>101.264903</v>
       </c>
       <c r="R155" s="9" t="n">
-        <v>98.81174300000001</v>
+        <v>98.81035300000001</v>
       </c>
       <c r="S155" s="9" t="n">
         <v>98.286675</v>
@@ -12613,7 +12613,7 @@
         <v>100.84855</v>
       </c>
       <c r="R156" s="6" t="n">
-        <v>98.789278</v>
+        <v>98.787862</v>
       </c>
       <c r="S156" s="6" t="n">
         <v>98.560496</v>
@@ -12695,7 +12695,7 @@
         <v>100.500391</v>
       </c>
       <c r="R157" s="9" t="n">
-        <v>98.75291799999999</v>
+        <v>98.75145999999999</v>
       </c>
       <c r="S157" s="9" t="n">
         <v>98.88110399999999</v>
@@ -12777,7 +12777,7 @@
         <v>100.281196</v>
       </c>
       <c r="R158" s="6" t="n">
-        <v>98.70359000000001</v>
+        <v>98.702074</v>
       </c>
       <c r="S158" s="6" t="n">
         <v>99.20181100000001</v>
@@ -12859,7 +12859,7 @@
         <v>100.194326</v>
       </c>
       <c r="R159" s="9" t="n">
-        <v>98.640694</v>
+        <v>98.639105</v>
       </c>
       <c r="S159" s="9" t="n">
         <v>99.487911</v>
@@ -12941,7 +12941,7 @@
         <v>100.161221</v>
       </c>
       <c r="R160" s="6" t="n">
-        <v>98.558735</v>
+        <v>98.55705</v>
       </c>
       <c r="S160" s="6" t="n">
         <v>99.708549</v>
@@ -13023,7 +13023,7 @@
         <v>100.116365</v>
       </c>
       <c r="R161" s="9" t="n">
-        <v>98.461055</v>
+        <v>98.459255</v>
       </c>
       <c r="S161" s="9" t="n">
         <v>99.849825</v>
@@ -13105,7 +13105,7 @@
         <v>100.037181</v>
       </c>
       <c r="R162" s="6" t="n">
-        <v>98.35937300000001</v>
+        <v>98.357454</v>
       </c>
       <c r="S162" s="6" t="n">
         <v>99.90014499999999</v>
@@ -13187,7 +13187,7 @@
         <v>99.947171</v>
       </c>
       <c r="R163" s="9" t="n">
-        <v>98.264456</v>
+        <v>98.262426</v>
       </c>
       <c r="S163" s="9" t="n">
         <v>99.858999</v>
@@ -13269,7 +13269,7 @@
         <v>99.87590899999999</v>
       </c>
       <c r="R164" s="6" t="n">
-        <v>98.181434</v>
+        <v>98.17930699999999</v>
       </c>
       <c r="S164" s="6" t="n">
         <v>99.73571200000001</v>
@@ -13351,7 +13351,7 @@
         <v>99.820103</v>
       </c>
       <c r="R165" s="9" t="n">
-        <v>98.10794199999999</v>
+        <v>98.105729</v>
       </c>
       <c r="S165" s="9" t="n">
         <v>99.552903</v>
@@ -13433,7 +13433,7 @@
         <v>99.813124</v>
       </c>
       <c r="R166" s="6" t="n">
-        <v>98.04061799999999</v>
+        <v>98.038326</v>
       </c>
       <c r="S166" s="6" t="n">
         <v>99.332207</v>
@@ -13515,7 +13515,7 @@
         <v>99.887991</v>
       </c>
       <c r="R167" s="9" t="n">
-        <v>97.97162899999999</v>
+        <v>97.969256</v>
       </c>
       <c r="S167" s="9" t="n">
         <v>99.087436</v>
@@ -13597,7 +13597,7 @@
         <v>100.053144</v>
       </c>
       <c r="R168" s="6" t="n">
-        <v>97.898585</v>
+        <v>97.896126</v>
       </c>
       <c r="S168" s="6" t="n">
         <v>98.833527</v>
@@ -13679,7 +13679,7 @@
         <v>100.298468</v>
       </c>
       <c r="R169" s="9" t="n">
-        <v>97.822744</v>
+        <v>97.82019699999999</v>
       </c>
       <c r="S169" s="9" t="n">
         <v>98.583482</v>
@@ -13761,7 +13761,7 @@
         <v>100.607789</v>
       </c>
       <c r="R170" s="6" t="n">
-        <v>97.74899600000001</v>
+        <v>97.746363</v>
       </c>
       <c r="S170" s="6" t="n">
         <v>98.339202</v>
@@ -13843,7 +13843,7 @@
         <v>100.97425</v>
       </c>
       <c r="R171" s="9" t="n">
-        <v>97.68316</v>
+        <v>97.680449</v>
       </c>
       <c r="S171" s="9" t="n">
         <v>98.09987099999999</v>
@@ -13925,7 +13925,7 @@
         <v>101.352183</v>
       </c>
       <c r="R172" s="6" t="n">
-        <v>97.629305</v>
+        <v>97.626532</v>
       </c>
       <c r="S172" s="6" t="n">
         <v>97.862959</v>
@@ -14007,7 +14007,7 @@
         <v>101.675228</v>
       </c>
       <c r="R173" s="9" t="n">
-        <v>97.592961</v>
+        <v>97.590146</v>
       </c>
       <c r="S173" s="9" t="n">
         <v>97.626713</v>
@@ -14089,7 +14089,7 @@
         <v>101.873339</v>
       </c>
       <c r="R174" s="6" t="n">
-        <v>97.594255</v>
+        <v>97.591443</v>
       </c>
       <c r="S174" s="6" t="n">
         <v>97.43158699999999</v>
@@ -14171,7 +14171,7 @@
         <v>101.929007</v>
       </c>
       <c r="R175" s="9" t="n">
-        <v>97.641627</v>
+        <v>97.638873</v>
       </c>
       <c r="S175" s="9" t="n">
         <v>97.329741</v>
@@ -14253,7 +14253,7 @@
         <v>101.892081</v>
       </c>
       <c r="R176" s="6" t="n">
-        <v>97.722865</v>
+        <v>97.720208</v>
       </c>
       <c r="S176" s="6" t="n">
         <v>97.35902299999999</v>
@@ -14335,7 +14335,7 @@
         <v>101.831877</v>
       </c>
       <c r="R177" s="9" t="n">
-        <v>97.798485</v>
+        <v>97.795918</v>
       </c>
       <c r="S177" s="9" t="n">
         <v>97.51206500000001</v>
@@ -14417,7 +14417,7 @@
         <v>101.797768</v>
       </c>
       <c r="R178" s="6" t="n">
-        <v>97.85409799999999</v>
+        <v>97.851598</v>
       </c>
       <c r="S178" s="6" t="n">
         <v>97.719644</v>
@@ -14499,7 +14499,7 @@
         <v>101.792885</v>
       </c>
       <c r="R179" s="9" t="n">
-        <v>97.911231</v>
+        <v>97.908799</v>
       </c>
       <c r="S179" s="9" t="n">
         <v>97.915432</v>
@@ -14581,7 +14581,7 @@
         <v>101.815146</v>
       </c>
       <c r="R180" s="6" t="n">
-        <v>98.00146100000001</v>
+        <v>97.999133</v>
       </c>
       <c r="S180" s="6" t="n">
         <v>98.089567</v>
@@ -14663,7 +14663,7 @@
         <v>101.804005</v>
       </c>
       <c r="R181" s="9" t="n">
-        <v>98.173715</v>
+        <v>98.171583</v>
       </c>
       <c r="S181" s="9" t="n">
         <v>98.276551</v>
@@ -14745,7 +14745,7 @@
         <v>101.680889</v>
       </c>
       <c r="R182" s="6" t="n">
-        <v>98.495824</v>
+        <v>98.494057</v>
       </c>
       <c r="S182" s="6" t="n">
         <v>98.555172</v>
@@ -14827,7 +14827,7 @@
         <v>101.396729</v>
       </c>
       <c r="R183" s="9" t="n">
-        <v>99.03205199999999</v>
+        <v>99.030894</v>
       </c>
       <c r="S183" s="9" t="n">
         <v>99.01929699999999</v>
@@ -14909,7 +14909,7 @@
         <v>100.945133</v>
       </c>
       <c r="R184" s="6" t="n">
-        <v>99.817069</v>
+        <v>99.816804</v>
       </c>
       <c r="S184" s="6" t="n">
         <v>99.74650099999999</v>
@@ -14991,7 +14991,7 @@
         <v>100.340606</v>
       </c>
       <c r="R185" s="9" t="n">
-        <v>100.814493</v>
+        <v>100.815363</v>
       </c>
       <c r="S185" s="9" t="n">
         <v>100.745275</v>
@@ -15073,7 +15073,7 @@
         <v>99.656263</v>
       </c>
       <c r="R186" s="6" t="n">
-        <v>101.8613</v>
+        <v>101.863362</v>
       </c>
       <c r="S186" s="6" t="n">
         <v>101.910233</v>
@@ -15155,7 +15155,7 @@
         <v>99.016271</v>
       </c>
       <c r="R187" s="9" t="n">
-        <v>102.73503</v>
+        <v>102.738096</v>
       </c>
       <c r="S187" s="9" t="n">
         <v>103.025198</v>
@@ -15237,7 +15237,7 @@
         <v>98.558041</v>
       </c>
       <c r="R188" s="6" t="n">
-        <v>103.270128</v>
+        <v>103.273818</v>
       </c>
       <c r="S188" s="6" t="n">
         <v>103.833177</v>
@@ -15319,7 +15319,7 @@
         <v>98.295478</v>
       </c>
       <c r="R189" s="9" t="n">
-        <v>103.441168</v>
+        <v>103.445088</v>
       </c>
       <c r="S189" s="9" t="n">
         <v>104.169663</v>
@@ -15401,7 +15401,7 @@
         <v>98.211574</v>
       </c>
       <c r="R190" s="6" t="n">
-        <v>103.352978</v>
+        <v>103.356836</v>
       </c>
       <c r="S190" s="6" t="n">
         <v>104.061384</v>
@@ -15483,7 +15483,7 @@
         <v>98.273008</v>
       </c>
       <c r="R191" s="9" t="n">
-        <v>103.164471</v>
+        <v>103.168145</v>
       </c>
       <c r="S191" s="9" t="n">
         <v>103.681323</v>
@@ -15565,7 +15565,7 @@
         <v>98.4109</v>
       </c>
       <c r="R192" s="6" t="n">
-        <v>102.983103</v>
+        <v>102.986595</v>
       </c>
       <c r="S192" s="6" t="n">
         <v>103.218142</v>
@@ -15647,7 +15647,7 @@
         <v>98.56554800000001</v>
       </c>
       <c r="R193" s="9" t="n">
-        <v>102.890902</v>
+        <v>102.894306</v>
       </c>
       <c r="S193" s="9" t="n">
         <v>102.822576</v>
@@ -15729,7 +15729,7 @@
         <v>98.708696</v>
       </c>
       <c r="R194" s="6" t="n">
-        <v>102.916397</v>
+        <v>102.919843</v>
       </c>
       <c r="S194" s="6" t="n">
         <v>102.583518</v>
@@ -15811,7 +15811,7 @@
         <v>98.85575900000001</v>
       </c>
       <c r="R195" s="9" t="n">
-        <v>103.031675</v>
+        <v>103.035263</v>
       </c>
       <c r="S195" s="9" t="n">
         <v>102.50202</v>
@@ -15893,7 +15893,7 @@
         <v>99.01858199999999</v>
       </c>
       <c r="R196" s="6" t="n">
-        <v>103.147506</v>
+        <v>103.151231</v>
       </c>
       <c r="S196" s="6" t="n">
         <v>102.484636</v>
@@ -15975,7 +15975,7 @@
         <v>99.164647</v>
       </c>
       <c r="R197" s="9" t="n">
-        <v>103.151519</v>
+        <v>103.155249</v>
       </c>
       <c r="S197" s="9" t="n">
         <v>102.421892</v>
@@ -16057,7 +16057,7 @@
         <v>99.27675600000001</v>
       </c>
       <c r="R198" s="6" t="n">
-        <v>103.024948</v>
+        <v>103.028527</v>
       </c>
       <c r="S198" s="6" t="n">
         <v>102.266611</v>
@@ -16139,7 +16139,7 @@
         <v>99.34424</v>
       </c>
       <c r="R199" s="9" t="n">
-        <v>102.803113</v>
+        <v>102.806429</v>
       </c>
       <c r="S199" s="9" t="n">
         <v>102.035458</v>
@@ -16221,7 +16221,7 @@
         <v>99.38457099999999</v>
       </c>
       <c r="R200" s="6" t="n">
-        <v>102.524982</v>
+        <v>102.52797</v>
       </c>
       <c r="S200" s="6" t="n">
         <v>101.746032</v>
@@ -16303,7 +16303,7 @@
         <v>99.390698</v>
       </c>
       <c r="R201" s="9" t="n">
-        <v>102.225146</v>
+        <v>102.227779</v>
       </c>
       <c r="S201" s="9" t="n">
         <v>101.409078</v>
@@ -16385,7 +16385,7 @@
         <v>99.36143</v>
       </c>
       <c r="R202" s="6" t="n">
-        <v>101.943742</v>
+        <v>101.946043</v>
       </c>
       <c r="S202" s="6" t="n">
         <v>101.076805</v>
@@ -16467,7 +16467,7 @@
         <v>99.307081</v>
       </c>
       <c r="R203" s="9" t="n">
-        <v>101.70314</v>
+        <v>101.705157</v>
       </c>
       <c r="S203" s="9" t="n">
         <v>100.804086</v>
@@ -16549,7 +16549,7 @@
         <v>99.246447</v>
       </c>
       <c r="R204" s="6" t="n">
-        <v>101.502802</v>
+        <v>101.504583</v>
       </c>
       <c r="S204" s="6" t="n">
         <v>100.597693</v>
@@ -16631,7 +16631,7 @@
         <v>99.20444999999999</v>
       </c>
       <c r="R205" s="9" t="n">
-        <v>101.335259</v>
+        <v>101.336843</v>
       </c>
       <c r="S205" s="9" t="n">
         <v>100.434192</v>
@@ -16713,7 +16713,7 @@
         <v>99.17540099999999</v>
       </c>
       <c r="R206" s="6" t="n">
-        <v>101.198348</v>
+        <v>101.19977</v>
       </c>
       <c r="S206" s="6" t="n">
         <v>100.318365</v>
@@ -16795,7 +16795,7 @@
         <v>99.171048</v>
       </c>
       <c r="R207" s="9" t="n">
-        <v>101.077062</v>
+        <v>101.078342</v>
       </c>
       <c r="S207" s="9" t="n">
         <v>100.243715</v>
@@ -16877,7 +16877,7 @@
         <v>99.204382</v>
       </c>
       <c r="R208" s="6" t="n">
-        <v>100.943835</v>
+        <v>100.944957</v>
       </c>
       <c r="S208" s="6" t="n">
         <v>100.166131</v>
@@ -16959,7 +16959,7 @@
         <v>99.28100499999999</v>
       </c>
       <c r="R209" s="9" t="n">
-        <v>100.777999</v>
+        <v>100.778926</v>
       </c>
       <c r="S209" s="9" t="n">
         <v>100.037668</v>
@@ -17041,7 +17041,7 @@
         <v>99.403109</v>
       </c>
       <c r="R210" s="6" t="n">
-        <v>100.595372</v>
+        <v>100.596083</v>
       </c>
       <c r="S210" s="6" t="n">
         <v>99.861137</v>
@@ -17123,7 +17123,7 @@
         <v>99.55976699999999</v>
       </c>
       <c r="R211" s="9" t="n">
-        <v>100.418429</v>
+        <v>100.418932</v>
       </c>
       <c r="S211" s="9" t="n">
         <v>99.670991</v>
@@ -17205,7 +17205,7 @@
         <v>99.749802</v>
       </c>
       <c r="R212" s="6" t="n">
-        <v>100.258383</v>
+        <v>100.258698</v>
       </c>
       <c r="S212" s="6" t="n">
         <v>99.49144099999999</v>
@@ -17287,7 +17287,7 @@
         <v>99.990821</v>
       </c>
       <c r="R213" s="9" t="n">
-        <v>100.10798</v>
+        <v>100.108117</v>
       </c>
       <c r="S213" s="9" t="n">
         <v>99.326638</v>
@@ -17369,7 +17369,7 @@
         <v>100.287335</v>
       </c>
       <c r="R214" s="6" t="n">
-        <v>99.96771099999999</v>
+        <v>99.96768299999999</v>
       </c>
       <c r="S214" s="6" t="n">
         <v>99.169569</v>
@@ -17451,7 +17451,7 @@
         <v>100.610424</v>
       </c>
       <c r="R215" s="9" t="n">
-        <v>99.838172</v>
+        <v>99.837991</v>
       </c>
       <c r="S215" s="9" t="n">
         <v>99.016958</v>
@@ -17533,7 +17533,7 @@
         <v>100.902453</v>
       </c>
       <c r="R216" s="6" t="n">
-        <v>99.72147</v>
+        <v>99.721152</v>
       </c>
       <c r="S216" s="6" t="n">
         <v>98.88350199999999</v>
@@ -17615,7 +17615,7 @@
         <v>101.112802</v>
       </c>
       <c r="R217" s="9" t="n">
-        <v>99.62966299999999</v>
+        <v>99.62923600000001</v>
       </c>
       <c r="S217" s="9" t="n">
         <v>98.790536</v>
@@ -17697,7 +17697,7 @@
         <v>101.24229</v>
       </c>
       <c r="R218" s="6" t="n">
-        <v>99.57756999999999</v>
+        <v>99.577082</v>
       </c>
       <c r="S218" s="6" t="n">
         <v>98.740898</v>
@@ -17779,7 +17779,7 @@
         <v>101.278586</v>
       </c>
       <c r="R219" s="9" t="n">
-        <v>99.56864400000001</v>
+        <v>99.568145</v>
       </c>
       <c r="S219" s="9" t="n">
         <v>98.731447</v>
@@ -17861,7 +17861,7 @@
         <v>101.254075</v>
       </c>
       <c r="R220" s="6" t="n">
-        <v>99.589437</v>
+        <v>99.588961</v>
       </c>
       <c r="S220" s="6" t="n">
         <v>98.751868</v>
@@ -17943,7 +17943,7 @@
         <v>101.168014</v>
       </c>
       <c r="R221" s="9" t="n">
-        <v>99.611009</v>
+        <v>99.61055899999999</v>
       </c>
       <c r="S221" s="9" t="n">
         <v>98.778133</v>
@@ -18025,7 +18025,7 @@
         <v>101.020104</v>
       </c>
       <c r="R222" s="6" t="n">
-        <v>99.644571</v>
+        <v>99.644159</v>
       </c>
       <c r="S222" s="6" t="n">
         <v>98.82171099999999</v>
@@ -18107,7 +18107,7 @@
         <v>100.837332</v>
       </c>
       <c r="R223" s="9" t="n">
-        <v>99.704275</v>
+        <v>99.703934</v>
       </c>
       <c r="S223" s="9" t="n">
         <v>98.89967300000001</v>
@@ -18189,7 +18189,7 @@
         <v>100.602289</v>
       </c>
       <c r="R224" s="6" t="n">
-        <v>99.79154200000001</v>
+        <v>99.791303</v>
       </c>
       <c r="S224" s="6" t="n">
         <v>99.02064799999999</v>
@@ -18271,7 +18271,7 @@
         <v>100.282961</v>
       </c>
       <c r="R225" s="9" t="n">
-        <v>99.918818</v>
+        <v>99.918728</v>
       </c>
       <c r="S225" s="9" t="n">
         <v>99.19860799999999</v>
@@ -18353,7 +18353,7 @@
         <v>99.869989</v>
       </c>
       <c r="R226" s="6" t="n">
-        <v>100.105488</v>
+        <v>100.105617</v>
       </c>
       <c r="S226" s="6" t="n">
         <v>99.470375</v>
@@ -18435,7 +18435,7 @@
         <v>99.40459199999999</v>
       </c>
       <c r="R227" s="9" t="n">
-        <v>100.354335</v>
+        <v>100.354757</v>
       </c>
       <c r="S227" s="9" t="n">
         <v>99.86547899999999</v>
@@ -18517,7 +18517,7 @@
         <v>98.941974</v>
       </c>
       <c r="R228" s="6" t="n">
-        <v>100.642772</v>
+        <v>100.643533</v>
       </c>
       <c r="S228" s="6" t="n">
         <v>100.378143</v>
@@ -18599,7 +18599,7 @@
         <v>98.54958499999999</v>
       </c>
       <c r="R229" s="9" t="n">
-        <v>100.940268</v>
+        <v>100.941378</v>
       </c>
       <c r="S229" s="9" t="n">
         <v>100.973718</v>
@@ -18681,7 +18681,7 @@
         <v>98.331613</v>
       </c>
       <c r="R230" s="6" t="n">
-        <v>101.182746</v>
+        <v>101.18414</v>
       </c>
       <c r="S230" s="6" t="n">
         <v>101.564063</v>
@@ -18763,7 +18763,7 @@
         <v>98.265986</v>
       </c>
       <c r="R231" s="9" t="n">
-        <v>101.290946</v>
+        <v>101.292468</v>
       </c>
       <c r="S231" s="9" t="n">
         <v>102.035061</v>
@@ -18845,7 +18845,7 @@
         <v>98.30688000000001</v>
       </c>
       <c r="R232" s="6" t="n">
-        <v>101.25276</v>
+        <v>101.254237</v>
       </c>
       <c r="S232" s="6" t="n">
         <v>102.318363</v>
@@ -18927,7 +18927,7 @@
         <v>98.45351700000001</v>
       </c>
       <c r="R233" s="9" t="n">
-        <v>101.098551</v>
+        <v>101.099846</v>
       </c>
       <c r="S233" s="9" t="n">
         <v>102.404722</v>
@@ -19009,7 +19009,7 @@
         <v>98.69708</v>
       </c>
       <c r="R234" s="6" t="n">
-        <v>100.868658</v>
+        <v>100.869682</v>
       </c>
       <c r="S234" s="6" t="n">
         <v>102.297275</v>
@@ -19091,7 +19091,7 @@
         <v>99.02433000000001</v>
       </c>
       <c r="R235" s="9" t="n">
-        <v>100.591129</v>
+        <v>100.591827</v>
       </c>
       <c r="S235" s="9" t="n">
         <v>102.032139</v>
@@ -19173,7 +19173,7 @@
         <v>99.387246</v>
       </c>
       <c r="R236" s="6" t="n">
-        <v>100.299435</v>
+        <v>100.29979</v>
       </c>
       <c r="S236" s="6" t="n">
         <v>101.681939</v>
@@ -19255,7 +19255,7 @@
         <v>99.712446</v>
       </c>
       <c r="R237" s="9" t="n">
-        <v>100.031519</v>
+        <v>100.031559</v>
       </c>
       <c r="S237" s="9" t="n">
         <v>101.338436</v>
@@ -19337,7 +19337,7 @@
         <v>99.948785</v>
       </c>
       <c r="R238" s="6" t="n">
-        <v>99.81901499999999</v>
+        <v>99.818804</v>
       </c>
       <c r="S238" s="6" t="n">
         <v>101.071253</v>
@@ -19419,7 +19419,7 @@
         <v>100.089676</v>
       </c>
       <c r="R239" s="9" t="n">
-        <v>99.669139</v>
+        <v>99.668752</v>
       </c>
       <c r="S239" s="9" t="n">
         <v>100.888492</v>
@@ -19501,7 +19501,7 @@
         <v>100.159501</v>
       </c>
       <c r="R240" s="6" t="n">
-        <v>99.56666300000001</v>
+        <v>99.56615499999999</v>
       </c>
       <c r="S240" s="6" t="n">
         <v>100.761838</v>
@@ -19583,7 +19583,7 @@
         <v>100.233589</v>
       </c>
       <c r="R241" s="9" t="n">
-        <v>99.50362</v>
+        <v>99.503038</v>
       </c>
       <c r="S241" s="9" t="n">
         <v>100.664811</v>
@@ -19665,7 +19665,7 @@
         <v>100.374955</v>
       </c>
       <c r="R242" s="6" t="n">
-        <v>99.464894</v>
+        <v>99.46426599999999</v>
       </c>
       <c r="S242" s="6" t="n">
         <v>100.562399</v>
@@ -19747,7 +19747,7 @@
         <v>100.60819</v>
       </c>
       <c r="R243" s="9" t="n">
-        <v>99.437659</v>
+        <v>99.436999</v>
       </c>
       <c r="S243" s="9" t="n">
         <v>100.442745</v>
@@ -19829,7 +19829,7 @@
         <v>100.900397</v>
       </c>
       <c r="R244" s="6" t="n">
-        <v>99.405107</v>
+        <v>99.404409</v>
       </c>
       <c r="S244" s="6" t="n">
         <v>100.312095</v>
@@ -19911,7 +19911,7 @@
         <v>101.18183</v>
       </c>
       <c r="R245" s="9" t="n">
-        <v>99.371922</v>
+        <v>99.371184</v>
       </c>
       <c r="S245" s="9" t="n">
         <v>100.183967</v>
@@ -19993,7 +19993,7 @@
         <v>101.383522</v>
       </c>
       <c r="R246" s="6" t="n">
-        <v>99.346295</v>
+        <v>99.345528</v>
       </c>
       <c r="S246" s="6" t="n">
         <v>100.063</v>
@@ -20075,7 +20075,7 @@
         <v>101.491861</v>
       </c>
       <c r="R247" s="9" t="n">
-        <v>99.33412</v>
+        <v>99.333338</v>
       </c>
       <c r="S247" s="9" t="n">
         <v>99.955871</v>
@@ -20157,7 +20157,7 @@
         <v>101.484281</v>
       </c>
       <c r="R248" s="6" t="n">
-        <v>99.34107299999999</v>
+        <v>99.340299</v>
       </c>
       <c r="S248" s="6" t="n">
         <v>99.88304100000001</v>
@@ -20239,7 +20239,7 @@
         <v>101.376545</v>
       </c>
       <c r="R249" s="9" t="n">
-        <v>99.36963299999999</v>
+        <v>99.368892</v>
       </c>
       <c r="S249" s="9" t="n">
         <v>99.88517299999999</v>
@@ -20321,7 +20321,7 @@
         <v>101.227509</v>
       </c>
       <c r="R250" s="6" t="n">
-        <v>99.406792</v>
+        <v>99.40609499999999</v>
       </c>
       <c r="S250" s="6" t="n">
         <v>99.979775</v>
@@ -20403,7 +20403,7 @@
         <v>101.080193</v>
       </c>
       <c r="R251" s="9" t="n">
-        <v>99.429805</v>
+        <v>99.429134</v>
       </c>
       <c r="S251" s="9" t="n">
         <v>100.141688</v>
@@ -20485,7 +20485,7 @@
         <v>100.912205</v>
       </c>
       <c r="R252" s="6" t="n">
-        <v>99.42</v>
+        <v>99.419318</v>
       </c>
       <c r="S252" s="6" t="n">
         <v>100.334746</v>
@@ -20567,7 +20567,7 @@
         <v>100.724512</v>
       </c>
       <c r="R253" s="9" t="n">
-        <v>99.398949</v>
+        <v>99.398242</v>
       </c>
       <c r="S253" s="9" t="n">
         <v>100.544318</v>
@@ -20649,7 +20649,7 @@
         <v>100.516194</v>
       </c>
       <c r="R254" s="6" t="n">
-        <v>99.390896</v>
+        <v>99.39018</v>
       </c>
       <c r="S254" s="6" t="n">
         <v>100.768492</v>
@@ -20731,7 +20731,7 @@
         <v>100.306412</v>
       </c>
       <c r="R255" s="9" t="n">
-        <v>99.398794</v>
+        <v>99.39808600000001</v>
       </c>
       <c r="S255" s="9" t="n">
         <v>100.994481</v>
@@ -20813,7 +20813,7 @@
         <v>100.117372</v>
       </c>
       <c r="R256" s="6" t="n">
-        <v>99.411525</v>
+        <v>99.410833</v>
       </c>
       <c r="S256" s="6" t="n">
         <v>101.194048</v>
@@ -20895,7 +20895,7 @@
         <v>99.989724</v>
       </c>
       <c r="R257" s="9" t="n">
-        <v>99.423292</v>
+        <v>99.422613</v>
       </c>
       <c r="S257" s="9" t="n">
         <v>101.329527</v>
@@ -20977,7 +20977,7 @@
         <v>99.924504</v>
       </c>
       <c r="R258" s="6" t="n">
-        <v>99.426435</v>
+        <v>99.42576</v>
       </c>
       <c r="S258" s="6" t="n">
         <v>101.375454</v>
@@ -21059,7 +21059,7 @@
         <v>99.885246</v>
       </c>
       <c r="R259" s="9" t="n">
-        <v>99.391091</v>
+        <v>99.39037500000001</v>
       </c>
       <c r="S259" s="9" t="n">
         <v>101.311483</v>
@@ -21141,7 +21141,7 @@
         <v>99.872829</v>
       </c>
       <c r="R260" s="6" t="n">
-        <v>99.307951</v>
+        <v>99.307137</v>
       </c>
       <c r="S260" s="6" t="n">
         <v>101.132102</v>
@@ -21223,7 +21223,7 @@
         <v>99.887429</v>
       </c>
       <c r="R261" s="9" t="n">
-        <v>99.19095</v>
+        <v>99.189998</v>
       </c>
       <c r="S261" s="9" t="n">
         <v>100.848417</v>
@@ -21305,7 +21305,7 @@
         <v>99.896699</v>
       </c>
       <c r="R262" s="6" t="n">
-        <v>99.07110299999999</v>
+        <v>99.07001099999999</v>
       </c>
       <c r="S262" s="6" t="n">
         <v>100.490126</v>
@@ -21387,7 +21387,7 @@
         <v>99.85391300000001</v>
       </c>
       <c r="R263" s="9" t="n">
-        <v>98.972967</v>
+        <v>98.97175900000001</v>
       </c>
       <c r="S263" s="9" t="n">
         <v>100.11208</v>
@@ -21469,7 +21469,7 @@
         <v>99.745859</v>
       </c>
       <c r="R264" s="6" t="n">
-        <v>98.90224499999999</v>
+        <v>98.900954</v>
       </c>
       <c r="S264" s="6" t="n">
         <v>99.768366</v>
@@ -21551,7 +21551,7 @@
         <v>99.59824399999999</v>
       </c>
       <c r="R265" s="9" t="n">
-        <v>98.84800799999999</v>
+        <v>98.84665200000001</v>
       </c>
       <c r="S265" s="9" t="n">
         <v>99.471144</v>
@@ -21633,7 +21633,7 @@
         <v>99.466937</v>
       </c>
       <c r="R266" s="6" t="n">
-        <v>98.796525</v>
+        <v>98.795109</v>
       </c>
       <c r="S266" s="6" t="n">
         <v>99.204266</v>
@@ -21715,7 +21715,7 @@
         <v>99.429259</v>
       </c>
       <c r="R267" s="9" t="n">
-        <v>98.726811</v>
+        <v>98.725313</v>
       </c>
       <c r="S267" s="9" t="n">
         <v>98.95381500000001</v>
@@ -21797,7 +21797,7 @@
         <v>99.50279999999999</v>
       </c>
       <c r="R268" s="6" t="n">
-        <v>98.64193400000001</v>
+        <v>98.640336</v>
       </c>
       <c r="S268" s="6" t="n">
         <v>98.72821999999999</v>
@@ -21879,7 +21879,7 @@
         <v>99.655947</v>
       </c>
       <c r="R269" s="9" t="n">
-        <v>98.564362</v>
+        <v>98.562673</v>
       </c>
       <c r="S269" s="9" t="n">
         <v>98.561019</v>
@@ -21961,7 +21961,7 @@
         <v>99.825416</v>
       </c>
       <c r="R270" s="6" t="n">
-        <v>98.518818</v>
+        <v>98.517076</v>
       </c>
       <c r="S270" s="6" t="n">
         <v>98.47472399999999</v>
@@ -22043,7 +22043,7 @@
         <v>99.94861299999999</v>
       </c>
       <c r="R271" s="9" t="n">
-        <v>98.52582700000001</v>
+        <v>98.524092</v>
       </c>
       <c r="S271" s="9" t="n">
         <v>98.45469900000001</v>
@@ -22125,7 +22125,7 @@
         <v>99.987859</v>
       </c>
       <c r="R272" s="6" t="n">
-        <v>98.59760199999999</v>
+        <v>98.595952</v>
       </c>
       <c r="S272" s="6" t="n">
         <v>98.46416600000001</v>
@@ -22207,7 +22207,7 @@
         <v>99.90312299999999</v>
       </c>
       <c r="R273" s="9" t="n">
-        <v>98.73663000000001</v>
+        <v>98.73514299999999</v>
       </c>
       <c r="S273" s="9" t="n">
         <v>98.500895</v>
@@ -22289,7 +22289,7 @@
         <v>99.69028900000001</v>
       </c>
       <c r="R274" s="6" t="n">
-        <v>98.928083</v>
+        <v>98.926821</v>
       </c>
       <c r="S274" s="6" t="n">
         <v>98.579757</v>
@@ -22371,7 +22371,7 @@
         <v>99.38884899999999</v>
       </c>
       <c r="R275" s="9" t="n">
-        <v>99.13712599999999</v>
+        <v>99.136111</v>
       </c>
       <c r="S275" s="9" t="n">
         <v>98.69679600000001</v>
@@ -22453,7 +22453,7 @@
         <v>99.058719</v>
       </c>
       <c r="R276" s="6" t="n">
-        <v>99.337366</v>
+        <v>99.336586</v>
       </c>
       <c r="S276" s="6" t="n">
         <v>98.83392499999999</v>
@@ -22535,7 +22535,7 @@
         <v>98.749514</v>
       </c>
       <c r="R277" s="9" t="n">
-        <v>99.52105400000001</v>
+        <v>99.520489</v>
       </c>
       <c r="S277" s="9" t="n">
         <v>98.99118300000001</v>
@@ -22617,7 +22617,7 @@
         <v>98.480343</v>
       </c>
       <c r="R278" s="6" t="n">
-        <v>99.68986700000001</v>
+        <v>99.689502</v>
       </c>
       <c r="S278" s="6" t="n">
         <v>99.179434</v>
@@ -22699,7 +22699,7 @@
         <v>98.272036</v>
       </c>
       <c r="R279" s="9" t="n">
-        <v>99.84424300000001</v>
+        <v>99.844058</v>
       </c>
       <c r="S279" s="9" t="n">
         <v>99.37867199999999</v>
@@ -22781,7 +22781,7 @@
         <v>98.114341</v>
       </c>
       <c r="R280" s="6" t="n">
-        <v>99.99128899999999</v>
+        <v>99.99127799999999</v>
       </c>
       <c r="S280" s="6" t="n">
         <v>99.568494</v>
@@ -22863,7 +22863,7 @@
         <v>97.99497700000001</v>
       </c>
       <c r="R281" s="9" t="n">
-        <v>100.136879</v>
+        <v>100.137039</v>
       </c>
       <c r="S281" s="9" t="n">
         <v>99.733644</v>
@@ -22945,7 +22945,7 @@
         <v>97.91765700000001</v>
       </c>
       <c r="R282" s="6" t="n">
-        <v>100.27743</v>
+        <v>100.277755</v>
       </c>
       <c r="S282" s="6" t="n">
         <v>99.840013</v>
@@ -23027,7 +23027,7 @@
         <v>97.899818</v>
       </c>
       <c r="R283" s="9" t="n">
-        <v>100.380908</v>
+        <v>100.381355</v>
       </c>
       <c r="S283" s="9" t="n">
         <v>99.8248</v>
@@ -23109,7 +23109,7 @@
         <v>97.95455200000001</v>
       </c>
       <c r="R284" s="6" t="n">
-        <v>100.41847</v>
+        <v>100.418961</v>
       </c>
       <c r="S284" s="6" t="n">
         <v>99.634497</v>
@@ -23191,7 +23191,7 @@
         <v>98.08153299999999</v>
       </c>
       <c r="R285" s="9" t="n">
-        <v>100.399436</v>
+        <v>100.399905</v>
       </c>
       <c r="S285" s="9" t="n">
         <v>99.26326</v>
@@ -23273,7 +23273,7 @@
         <v>98.251891</v>
       </c>
       <c r="R286" s="6" t="n">
-        <v>100.369852</v>
+        <v>100.370286</v>
       </c>
       <c r="S286" s="6" t="n">
         <v>98.773364</v>
@@ -23355,7 +23355,7 @@
         <v>98.442635</v>
       </c>
       <c r="R287" s="9" t="n">
-        <v>100.375279</v>
+        <v>100.375719</v>
       </c>
       <c r="S287" s="9" t="n">
         <v>98.266879</v>
@@ -23437,7 +23437,7 @@
         <v>98.634355</v>
       </c>
       <c r="R288" s="6" t="n">
-        <v>100.422034</v>
+        <v>100.422529</v>
       </c>
       <c r="S288" s="6" t="n">
         <v>97.837084</v>
@@ -23519,7 +23519,7 @@
         <v>98.817407</v>
       </c>
       <c r="R289" s="9" t="n">
-        <v>100.503759</v>
+        <v>100.50435</v>
       </c>
       <c r="S289" s="9" t="n">
         <v>97.54005600000001</v>
@@ -23601,7 +23601,7 @@
         <v>98.992075</v>
       </c>
       <c r="R290" s="6" t="n">
-        <v>100.590902</v>
+        <v>100.591596</v>
       </c>
       <c r="S290" s="6" t="n">
         <v>97.394148</v>
@@ -23683,7 +23683,7 @@
         <v>99.162947</v>
       </c>
       <c r="R291" s="9" t="n">
-        <v>100.656472</v>
+        <v>100.657242</v>
       </c>
       <c r="S291" s="9" t="n">
         <v>97.37935</v>
@@ -23765,7 +23765,7 @@
         <v>99.331231</v>
       </c>
       <c r="R292" s="6" t="n">
-        <v>100.686141</v>
+        <v>100.686946</v>
       </c>
       <c r="S292" s="6" t="n">
         <v>97.457627</v>
@@ -23847,7 +23847,7 @@
         <v>99.48864</v>
       </c>
       <c r="R293" s="9" t="n">
-        <v>100.693179</v>
+        <v>100.693993</v>
       </c>
       <c r="S293" s="9" t="n">
         <v>97.618534</v>
@@ -23931,7 +23931,7 @@
         <v>99.62402400000001</v>
       </c>
       <c r="R294" s="6" t="n">
-        <v>100.696753</v>
+        <v>100.697571</v>
       </c>
       <c r="S294" s="6" t="n">
         <v>97.858414</v>
@@ -24015,7 +24015,7 @@
         <v>99.71603500000001</v>
       </c>
       <c r="R295" s="9" t="n">
-        <v>100.729609</v>
+        <v>100.730465</v>
       </c>
       <c r="S295" s="9" t="n">
         <v>98.157359</v>
@@ -24099,7 +24099,7 @@
         <v>99.74854999999999</v>
       </c>
       <c r="R296" s="6" t="n">
-        <v>100.801052</v>
+        <v>100.801992</v>
       </c>
       <c r="S296" s="6" t="n">
         <v>98.479725</v>
@@ -24183,7 +24183,7 @@
         <v>99.722976</v>
       </c>
       <c r="R297" s="9" t="n">
-        <v>100.901637</v>
+        <v>100.902695</v>
       </c>
       <c r="S297" s="9" t="n">
         <v>98.785933</v>
@@ -24267,7 +24267,7 @@
         <v>99.672467</v>
       </c>
       <c r="R298" s="6" t="n">
-        <v>100.999136</v>
+        <v>101.000309</v>
       </c>
       <c r="S298" s="6" t="n">
         <v>99.057165</v>
@@ -24351,7 +24351,7 @@
         <v>99.62397900000001</v>
       </c>
       <c r="R299" s="9" t="n">
-        <v>101.058624</v>
+        <v>101.059867</v>
       </c>
       <c r="S299" s="9" t="n">
         <v>99.298284</v>
@@ -24435,7 +24435,7 @@
         <v>99.59861100000001</v>
       </c>
       <c r="R300" s="6" t="n">
-        <v>101.070223</v>
+        <v>101.07148</v>
       </c>
       <c r="S300" s="6" t="n">
         <v>99.524815</v>
@@ -24519,7 +24519,7 @@
         <v>99.617704</v>
       </c>
       <c r="R301" s="9" t="n">
-        <v>101.03237</v>
+        <v>101.033582</v>
       </c>
       <c r="S301" s="9" t="n">
         <v>99.751402</v>
@@ -24603,7 +24603,7 @@
         <v>99.685011</v>
       </c>
       <c r="R302" s="6" t="n">
-        <v>100.955224</v>
+        <v>100.956345</v>
       </c>
       <c r="S302" s="6" t="n">
         <v>99.982257</v>
@@ -24687,7 +24687,7 @@
         <v>99.780129</v>
       </c>
       <c r="R303" s="9" t="n">
-        <v>100.847796</v>
+        <v>100.84879</v>
       </c>
       <c r="S303" s="9" t="n">
         <v>100.217709</v>
@@ -24771,7 +24771,7 @@
         <v>99.87445099999999</v>
       </c>
       <c r="R304" s="6" t="n">
-        <v>100.72448</v>
+        <v>100.72533</v>
       </c>
       <c r="S304" s="6" t="n">
         <v>100.453632</v>
@@ -24855,7 +24855,7 @@
         <v>99.939657</v>
       </c>
       <c r="R305" s="9" t="n">
-        <v>100.600453</v>
+        <v>100.601157</v>
       </c>
       <c r="S305" s="9" t="n">
         <v>100.679433</v>
@@ -24939,7 +24939,7 @@
         <v>99.950822</v>
       </c>
       <c r="R306" s="6" t="n">
-        <v>100.491288</v>
+        <v>100.491863</v>
       </c>
       <c r="S306" s="6" t="n">
         <v>100.888662</v>
@@ -25023,7 +25023,7 @@
         <v>99.90555500000001</v>
       </c>
       <c r="R307" s="9" t="n">
-        <v>100.395708</v>
+        <v>100.396171</v>
       </c>
       <c r="S307" s="9" t="n">
         <v>101.078927</v>
@@ -25107,7 +25107,7 @@
         <v>99.820559</v>
       </c>
       <c r="R308" s="6" t="n">
-        <v>100.309547</v>
+        <v>100.309908</v>
       </c>
       <c r="S308" s="6" t="n">
         <v>101.239663</v>
@@ -25191,7 +25191,7 @@
         <v>99.75062800000001</v>
       </c>
       <c r="R309" s="9" t="n">
-        <v>100.223831</v>
+        <v>100.224091</v>
       </c>
       <c r="S309" s="9" t="n">
         <v>101.361087</v>
@@ -25275,7 +25275,7 @@
         <v>99.73730999999999</v>
       </c>
       <c r="R310" s="6" t="n">
-        <v>100.132244</v>
+        <v>100.132397</v>
       </c>
       <c r="S310" s="6" t="n">
         <v>101.436418</v>
@@ -25359,7 +25359,7 @@
         <v>99.786838</v>
       </c>
       <c r="R311" s="9" t="n">
-        <v>100.039561</v>
+        <v>100.039605</v>
       </c>
       <c r="S311" s="9" t="n">
         <v>101.463302</v>
@@ -25443,7 +25443,7 @@
         <v>99.889528</v>
       </c>
       <c r="R312" s="6" t="n">
-        <v>99.955443</v>
+        <v>99.955387</v>
       </c>
       <c r="S312" s="6" t="n">
         <v>101.443607</v>
@@ -25527,7 +25527,7 @@
         <v>100.027822</v>
       </c>
       <c r="R313" s="9" t="n">
-        <v>99.885206</v>
+        <v>99.885068</v>
       </c>
       <c r="S313" s="9" t="n">
         <v>101.377935</v>
@@ -25611,7 +25611,7 @@
         <v>100.192269</v>
       </c>
       <c r="R314" s="6" t="n">
-        <v>99.820717</v>
+        <v>99.820503</v>
       </c>
       <c r="S314" s="6" t="n">
         <v>101.267844</v>
@@ -25695,7 +25695,7 @@
         <v>100.354791</v>
       </c>
       <c r="R315" s="9" t="n">
-        <v>99.74682799999999</v>
+        <v>99.746527</v>
       </c>
       <c r="S315" s="9" t="n">
         <v>101.120158</v>
@@ -25779,7 +25779,7 @@
         <v>100.511062</v>
       </c>
       <c r="R316" s="6" t="n">
-        <v>99.666473</v>
+        <v>99.666077</v>
       </c>
       <c r="S316" s="6" t="n">
         <v>100.942245</v>
@@ -25863,7 +25863,7 @@
         <v>100.645611</v>
       </c>
       <c r="R317" s="9" t="n">
-        <v>99.61056000000001</v>
+        <v>99.61009900000001</v>
       </c>
       <c r="S317" s="9" t="n">
         <v>100.743369</v>
@@ -25947,7 +25947,7 @@
         <v>100.742199</v>
       </c>
       <c r="R318" s="6" t="n">
-        <v>99.61057</v>
+        <v>99.610108</v>
       </c>
       <c r="S318" s="6" t="n">
         <v>100.53797</v>
@@ -26031,7 +26031,7 @@
         <v>100.791261</v>
       </c>
       <c r="R319" s="9" t="n">
-        <v>99.682152</v>
+        <v>99.681774</v>
       </c>
       <c r="S319" s="9" t="n">
         <v>100.340687</v>
@@ -26115,7 +26115,7 @@
         <v>100.802487</v>
       </c>
       <c r="R320" s="6" t="n">
-        <v>99.82080000000001</v>
+        <v>99.82058499999999</v>
       </c>
       <c r="S320" s="6" t="n">
         <v>100.167515</v>
@@ -26199,7 +26199,7 @@
         <v>100.785345</v>
       </c>
       <c r="R321" s="9" t="n">
-        <v>99.987298</v>
+        <v>99.98728</v>
       </c>
       <c r="S321" s="9" t="n">
         <v>100.029391</v>
@@ -26283,7 +26283,7 @@
         <v>100.754254</v>
       </c>
       <c r="R322" s="6" t="n">
-        <v>100.126705</v>
+        <v>100.12685</v>
       </c>
       <c r="S322" s="6" t="n">
         <v>99.930747</v>
@@ -26367,7 +26367,7 @@
         <v>100.756692</v>
       </c>
       <c r="R323" s="9" t="n">
-        <v>100.19683</v>
+        <v>100.197057</v>
       </c>
       <c r="S323" s="9" t="n">
         <v>99.871433</v>
@@ -26451,7 +26451,7 @@
         <v>100.815207</v>
       </c>
       <c r="R324" s="6" t="n">
-        <v>100.174171</v>
+        <v>100.174371</v>
       </c>
       <c r="S324" s="6" t="n">
         <v>99.844551</v>
@@ -26535,7 +26535,7 @@
         <v>100.931193</v>
       </c>
       <c r="R325" s="9" t="n">
-        <v>100.081556</v>
+        <v>100.081647</v>
       </c>
       <c r="S325" s="9" t="n">
         <v>99.842271</v>
@@ -26619,7 +26619,7 @@
         <v>101.096405</v>
       </c>
       <c r="R326" s="6" t="n">
-        <v>99.952275</v>
+        <v>99.952215</v>
       </c>
       <c r="S326" s="6" t="n">
         <v>99.857739</v>
@@ -26703,7 +26703,7 @@
         <v>101.298183</v>
       </c>
       <c r="R327" s="9" t="n">
-        <v>99.81647</v>
+        <v>99.81625</v>
       </c>
       <c r="S327" s="9" t="n">
         <v>99.885796</v>
@@ -26787,7 +26787,7 @@
         <v>101.515987</v>
       </c>
       <c r="R328" s="6" t="n">
-        <v>99.70278399999999</v>
+        <v>99.70243000000001</v>
       </c>
       <c r="S328" s="6" t="n">
         <v>99.923565</v>
@@ -26871,7 +26871,7 @@
         <v>101.722834</v>
       </c>
       <c r="R329" s="9" t="n">
-        <v>99.630548</v>
+        <v>99.63011</v>
       </c>
       <c r="S329" s="9" t="n">
         <v>99.969649</v>
@@ -26955,7 +26955,7 @@
         <v>101.901627</v>
       </c>
       <c r="R330" s="6" t="n">
-        <v>99.60654700000001</v>
+        <v>99.60608000000001</v>
       </c>
       <c r="S330" s="6" t="n">
         <v>100.022128</v>
@@ -27039,7 +27039,7 @@
         <v>102.050419</v>
       </c>
       <c r="R331" s="9" t="n">
-        <v>99.621315</v>
+        <v>99.62086499999999</v>
       </c>
       <c r="S331" s="9" t="n">
         <v>100.078754</v>
@@ -27123,7 +27123,7 @@
         <v>102.181358</v>
       </c>
       <c r="R332" s="6" t="n">
-        <v>99.654983</v>
+        <v>99.654573</v>
       </c>
       <c r="S332" s="6" t="n">
         <v>100.138354</v>
@@ -27207,7 +27207,7 @@
         <v>102.283007</v>
       </c>
       <c r="R333" s="9" t="n">
-        <v>99.68397400000001</v>
+        <v>99.683598</v>
       </c>
       <c r="S333" s="9" t="n">
         <v>100.200897</v>
@@ -27291,7 +27291,7 @@
         <v>102.343454</v>
       </c>
       <c r="R334" s="6" t="n">
-        <v>99.700011</v>
+        <v>99.699654</v>
       </c>
       <c r="S334" s="6" t="n">
         <v>100.264732</v>
@@ -27375,7 +27375,7 @@
         <v>102.341101</v>
       </c>
       <c r="R335" s="9" t="n">
-        <v>99.70149499999999</v>
+        <v>99.70114</v>
       </c>
       <c r="S335" s="9" t="n">
         <v>100.324227</v>
@@ -27459,7 +27459,7 @@
         <v>102.278883</v>
       </c>
       <c r="R336" s="6" t="n">
-        <v>99.686976</v>
+        <v>99.686604</v>
       </c>
       <c r="S336" s="6" t="n">
         <v>100.378952</v>
@@ -27543,7 +27543,7 @@
         <v>102.173165</v>
       </c>
       <c r="R337" s="9" t="n">
-        <v>99.655396</v>
+        <v>99.65498700000001</v>
       </c>
       <c r="S337" s="9" t="n">
         <v>100.431163</v>
@@ -27627,7 +27627,7 @@
         <v>102.041262</v>
       </c>
       <c r="R338" s="6" t="n">
-        <v>99.59702299999999</v>
+        <v>99.59654500000001</v>
       </c>
       <c r="S338" s="6" t="n">
         <v>100.483696</v>
@@ -27711,7 +27711,7 @@
         <v>101.895441</v>
       </c>
       <c r="R339" s="9" t="n">
-        <v>99.513344</v>
+        <v>99.51276799999999</v>
       </c>
       <c r="S339" s="9" t="n">
         <v>100.53866</v>
@@ -27795,7 +27795,7 @@
         <v>101.741623</v>
       </c>
       <c r="R340" s="6" t="n">
-        <v>99.415468</v>
+        <v>99.414777</v>
       </c>
       <c r="S340" s="6" t="n">
         <v>100.595144</v>
@@ -27879,7 +27879,7 @@
         <v>101.602397</v>
       </c>
       <c r="R341" s="9" t="n">
-        <v>99.30570400000001</v>
+        <v>99.304884</v>
       </c>
       <c r="S341" s="9" t="n">
         <v>100.648929</v>
@@ -27963,7 +27963,7 @@
         <v>101.489513</v>
       </c>
       <c r="R342" s="6" t="n">
-        <v>99.18487500000001</v>
+        <v>99.183913</v>
       </c>
       <c r="S342" s="6" t="n">
         <v>100.700815</v>
@@ -28047,7 +28047,7 @@
         <v>101.402357</v>
       </c>
       <c r="R343" s="9" t="n">
-        <v>99.051922</v>
+        <v>99.050804</v>
       </c>
       <c r="S343" s="9" t="n">
         <v>100.755052</v>
@@ -28131,7 +28131,7 @@
         <v>101.315061</v>
       </c>
       <c r="R344" s="6" t="n">
-        <v>98.91911500000001</v>
+        <v>98.917841</v>
       </c>
       <c r="S344" s="6" t="n">
         <v>100.817998</v>
@@ -28215,7 +28215,7 @@
         <v>101.178782</v>
       </c>
       <c r="R345" s="9" t="n">
-        <v>98.805852</v>
+        <v>98.804445</v>
       </c>
       <c r="S345" s="9" t="n">
         <v>100.896708</v>
@@ -28299,7 +28299,7 @@
         <v>100.955255</v>
       </c>
       <c r="R346" s="6" t="n">
-        <v>98.743972</v>
+        <v>98.742493</v>
       </c>
       <c r="S346" s="6" t="n">
         <v>100.997001</v>
@@ -28383,7 +28383,7 @@
         <v>100.609962</v>
       </c>
       <c r="R347" s="9" t="n">
-        <v>98.766938</v>
+        <v>98.765486</v>
       </c>
       <c r="S347" s="9" t="n">
         <v>101.120999</v>
@@ -28467,7 +28467,7 @@
         <v>100.153682</v>
       </c>
       <c r="R348" s="6" t="n">
-        <v>98.91587</v>
+        <v>98.914593</v>
       </c>
       <c r="S348" s="6" t="n">
         <v>101.262206</v>
@@ -28551,7 +28551,7 @@
         <v>99.616022</v>
       </c>
       <c r="R349" s="9" t="n">
-        <v>99.229921</v>
+        <v>99.22901400000001</v>
       </c>
       <c r="S349" s="9" t="n">
         <v>101.403006</v>
@@ -28635,7 +28635,7 @@
         <v>99.035662</v>
       </c>
       <c r="R350" s="6" t="n">
-        <v>99.723906</v>
+        <v>99.72358</v>
       </c>
       <c r="S350" s="6" t="n">
         <v>101.521243</v>
@@ -28719,7 +28719,7 @@
         <v>98.46801499999999</v>
       </c>
       <c r="R351" s="9" t="n">
-        <v>100.336613</v>
+        <v>100.337008</v>
       </c>
       <c r="S351" s="9" t="n">
         <v>101.596483</v>
@@ -28803,7 +28803,7 @@
         <v>97.99027700000001</v>
       </c>
       <c r="R352" s="6" t="n">
-        <v>100.938932</v>
+        <v>100.940035</v>
       </c>
       <c r="S352" s="6" t="n">
         <v>101.609336</v>
@@ -28887,7 +28887,7 @@
         <v>97.629774</v>
       </c>
       <c r="R353" s="9" t="n">
-        <v>101.459956</v>
+        <v>101.461672</v>
       </c>
       <c r="S353" s="9" t="n">
         <v>101.54026</v>
@@ -28971,7 +28971,7 @@
         <v>97.39106099999999</v>
       </c>
       <c r="R354" s="6" t="n">
-        <v>101.860491</v>
+        <v>101.862679</v>
       </c>
       <c r="S354" s="6" t="n">
         <v>101.374288</v>
@@ -29055,7 +29055,7 @@
         <v>97.320742</v>
       </c>
       <c r="R355" s="9" t="n">
-        <v>102.101981</v>
+        <v>102.104454</v>
       </c>
       <c r="S355" s="9" t="n">
         <v>101.109901</v>
@@ -29139,7 +29139,7 @@
         <v>97.448117</v>
       </c>
       <c r="R356" s="6" t="n">
-        <v>102.159621</v>
+        <v>102.162162</v>
       </c>
       <c r="S356" s="6" t="n">
         <v>100.759105</v>
@@ -29223,7 +29223,7 @@
         <v>97.733762</v>
       </c>
       <c r="R357" s="9" t="n">
-        <v>102.061785</v>
+        <v>102.064212</v>
       </c>
       <c r="S357" s="9" t="n">
         <v>100.347056</v>
@@ -29307,7 +29307,7 @@
         <v>98.107777</v>
       </c>
       <c r="R358" s="6" t="n">
-        <v>101.898745</v>
+        <v>101.900981</v>
       </c>
       <c r="S358" s="6" t="n">
         <v>99.92553599999999</v>
@@ -29391,7 +29391,7 @@
         <v>98.502821</v>
       </c>
       <c r="R359" s="9" t="n">
-        <v>101.725517</v>
+        <v>101.72755</v>
       </c>
       <c r="S359" s="9" t="n">
         <v>99.552654</v>
@@ -29475,7 +29475,7 @@
         <v>98.882034</v>
       </c>
       <c r="R360" s="6" t="n">
-        <v>101.556054</v>
+        <v>101.557888</v>
       </c>
       <c r="S360" s="6" t="n">
         <v>99.269113</v>
@@ -29559,7 +29559,7 @@
         <v>99.207392</v>
       </c>
       <c r="R361" s="9" t="n">
-        <v>101.393867</v>
+        <v>101.395511</v>
       </c>
       <c r="S361" s="9" t="n">
         <v>99.091156</v>
@@ -29643,7 +29643,7 @@
         <v>99.463691</v>
       </c>
       <c r="R362" s="6" t="n">
-        <v>101.240218</v>
+        <v>101.241683</v>
       </c>
       <c r="S362" s="6" t="n">
         <v>99.00810799999999</v>
@@ -29727,7 +29727,7 @@
         <v>99.65195300000001</v>
       </c>
       <c r="R363" s="9" t="n">
-        <v>101.073537</v>
+        <v>101.074806</v>
       </c>
       <c r="S363" s="9" t="n">
         <v>98.99659</v>
@@ -29811,7 +29811,7 @@
         <v>99.785927</v>
       </c>
       <c r="R364" s="6" t="n">
-        <v>100.889668</v>
+        <v>100.890722</v>
       </c>
       <c r="S364" s="6" t="n">
         <v>99.032014</v>
@@ -29895,7 +29895,7 @@
         <v>99.86318</v>
       </c>
       <c r="R365" s="9" t="n">
-        <v>100.69928</v>
+        <v>100.700112</v>
       </c>
       <c r="S365" s="9" t="n">
         <v>99.09332499999999</v>
@@ -29979,7 +29979,7 @@
         <v>99.891302</v>
       </c>
       <c r="R366" s="6" t="n">
-        <v>100.524</v>
+        <v>100.524626</v>
       </c>
       <c r="S366" s="6" t="n">
         <v>99.165997</v>
@@ -30063,7 +30063,7 @@
         <v>99.89702</v>
       </c>
       <c r="R367" s="9" t="n">
-        <v>100.378086</v>
+        <v>100.378542</v>
       </c>
       <c r="S367" s="9" t="n">
         <v>99.24155500000001</v>
@@ -30147,7 +30147,7 @@
         <v>99.885969</v>
       </c>
       <c r="R368" s="6" t="n">
-        <v>100.268295</v>
+        <v>100.268622</v>
       </c>
       <c r="S368" s="6" t="n">
         <v>99.314645</v>
@@ -30231,7 +30231,7 @@
         <v>99.85785</v>
       </c>
       <c r="R369" s="9" t="n">
-        <v>100.211656</v>
+        <v>100.211919</v>
       </c>
       <c r="S369" s="9" t="n">
         <v>99.382324</v>
@@ -30315,7 +30315,7 @@
         <v>99.827597</v>
       </c>
       <c r="R370" s="6" t="n">
-        <v>100.208252</v>
+        <v>100.208511</v>
       </c>
       <c r="S370" s="6" t="n">
         <v>99.4427</v>
@@ -30399,7 +30399,7 @@
         <v>99.817001</v>
       </c>
       <c r="R371" s="9" t="n">
-        <v>100.216243</v>
+        <v>100.216513</v>
       </c>
       <c r="S371" s="9" t="n">
         <v>99.495558</v>
@@ -30483,7 +30483,7 @@
         <v>99.846878</v>
       </c>
       <c r="R372" s="6" t="n">
-        <v>100.200928</v>
+        <v>100.201181</v>
       </c>
       <c r="S372" s="6" t="n">
         <v>99.541873</v>
@@ -30567,7 +30567,7 @@
         <v>99.920451</v>
       </c>
       <c r="R373" s="9" t="n">
-        <v>100.136942</v>
+        <v>100.137122</v>
       </c>
       <c r="S373" s="9" t="n">
         <v>99.583828</v>
@@ -30651,7 +30651,7 @@
         <v>100.036883</v>
       </c>
       <c r="R374" s="6" t="n">
-        <v>100.016933</v>
+        <v>100.016973</v>
       </c>
       <c r="S374" s="6" t="n">
         <v>99.62366</v>
@@ -30735,7 +30735,7 @@
         <v>100.171469</v>
       </c>
       <c r="R375" s="9" t="n">
-        <v>99.844623</v>
+        <v>99.84446199999999</v>
       </c>
       <c r="S375" s="9" t="n">
         <v>99.66277599999999</v>
@@ -30819,7 +30819,7 @@
         <v>100.289159</v>
       </c>
       <c r="R376" s="6" t="n">
-        <v>99.650063</v>
+        <v>99.649674</v>
       </c>
       <c r="S376" s="6" t="n">
         <v>99.702611</v>
@@ -30903,7 +30903,7 @@
         <v>100.363929</v>
       </c>
       <c r="R377" s="9" t="n">
-        <v>99.458991</v>
+        <v>99.45838000000001</v>
       </c>
       <c r="S377" s="9" t="n">
         <v>99.743053</v>
@@ -30987,7 +30987,7 @@
         <v>100.382134</v>
       </c>
       <c r="R378" s="6" t="n">
-        <v>99.285921</v>
+        <v>99.28510799999999</v>
       </c>
       <c r="S378" s="6" t="n">
         <v>99.78322199999999</v>
@@ -31071,7 +31071,7 @@
         <v>100.356769</v>
       </c>
       <c r="R379" s="9" t="n">
-        <v>99.15098999999999</v>
+        <v>99.150021</v>
       </c>
       <c r="S379" s="9" t="n">
         <v>99.823808</v>
@@ -31155,7 +31155,7 @@
         <v>100.299063</v>
       </c>
       <c r="R380" s="6" t="n">
-        <v>99.068181</v>
+        <v>99.067115</v>
       </c>
       <c r="S380" s="6" t="n">
         <v>99.86528800000001</v>
@@ -31239,7 +31239,7 @@
         <v>100.216602</v>
       </c>
       <c r="R381" s="9" t="n">
-        <v>99.0489</v>
+        <v>99.047814</v>
       </c>
       <c r="S381" s="9" t="n">
         <v>99.906874</v>
@@ -31323,7 +31323,7 @@
         <v>100.120313</v>
       </c>
       <c r="R382" s="6" t="n">
-        <v>99.11127399999999</v>
+        <v>99.110263</v>
       </c>
       <c r="S382" s="6" t="n">
         <v>99.947003</v>
@@ -31407,7 +31407,7 @@
         <v>100.021428</v>
       </c>
       <c r="R383" s="9" t="n">
-        <v>99.263502</v>
+        <v>99.26267199999999</v>
       </c>
       <c r="S383" s="9" t="n">
         <v>99.984596</v>
@@ -31491,7 +31491,7 @@
         <v>99.923676</v>
       </c>
       <c r="R384" s="6" t="n">
-        <v>99.502</v>
+        <v>99.501452</v>
       </c>
       <c r="S384" s="6" t="n">
         <v>100.019543</v>
@@ -31575,7 +31575,7 @@
         <v>99.83911000000001</v>
       </c>
       <c r="R385" s="9" t="n">
-        <v>99.812977</v>
+        <v>99.812797</v>
       </c>
       <c r="S385" s="9" t="n">
         <v>100.053323</v>
@@ -31659,7 +31659,7 @@
         <v>99.78235599999999</v>
       </c>
       <c r="R386" s="6" t="n">
-        <v>100.138851</v>
+        <v>100.139056</v>
       </c>
       <c r="S386" s="6" t="n">
         <v>100.087282</v>
@@ -31743,7 +31743,7 @@
         <v>99.769779</v>
       </c>
       <c r="R387" s="9" t="n">
-        <v>100.404546</v>
+        <v>100.405066</v>
       </c>
       <c r="S387" s="9" t="n">
         <v>100.12259</v>
@@ -31827,7 +31827,7 @@
         <v>99.786102</v>
       </c>
       <c r="R388" s="6" t="n">
-        <v>100.562091</v>
+        <v>100.562798</v>
       </c>
       <c r="S388" s="6" t="n">
         <v>100.158468</v>
@@ -31911,7 +31911,7 @@
         <v>99.820724</v>
       </c>
       <c r="R389" s="9" t="n">
-        <v>100.608878</v>
+        <v>100.609642</v>
       </c>
       <c r="S389" s="9" t="n">
         <v>100.193584</v>
@@ -31995,7 +31995,7 @@
         <v>99.868849</v>
       </c>
       <c r="R390" s="6" t="n">
-        <v>100.575334</v>
+        <v>100.576061</v>
       </c>
       <c r="S390" s="6" t="n">
         <v>100.227354</v>
@@ -32079,7 +32079,7 @@
         <v>99.92652699999999</v>
       </c>
       <c r="R391" s="9" t="n">
-        <v>100.518144</v>
+        <v>100.518806</v>
       </c>
       <c r="S391" s="9" t="n">
         <v>100.260409</v>
@@ -32163,7 +32163,7 @@
         <v>99.986734</v>
       </c>
       <c r="R392" s="6" t="n">
-        <v>100.497711</v>
+        <v>100.498351</v>
       </c>
       <c r="S392" s="6" t="n">
         <v>100.294262</v>
@@ -32247,7 +32247,7 @@
         <v>100.038167</v>
       </c>
       <c r="R393" s="9" t="n">
-        <v>100.522228</v>
+        <v>100.5229</v>
       </c>
       <c r="S393" s="9" t="n">
         <v>100.330965</v>
@@ -32331,7 +32331,7 @@
         <v>100.082667</v>
       </c>
       <c r="R394" s="6" t="n">
-        <v>100.552005</v>
+        <v>100.552714</v>
       </c>
       <c r="S394" s="6" t="n">
         <v>100.372637</v>
@@ -32415,7 +32415,7 @@
         <v>100.130917</v>
       </c>
       <c r="R395" s="9" t="n">
-        <v>100.529986</v>
+        <v>100.530672</v>
       </c>
       <c r="S395" s="9" t="n">
         <v>100.41905</v>
@@ -32499,7 +32499,7 @@
         <v>100.177558</v>
       </c>
       <c r="R396" s="6" t="n">
-        <v>100.424373</v>
+        <v>100.424936</v>
       </c>
       <c r="S396" s="6" t="n">
         <v>100.468977</v>
@@ -32583,7 +32583,7 @@
         <v>100.225799</v>
       </c>
       <c r="R397" s="9" t="n">
-        <v>100.257545</v>
+        <v>100.257915</v>
       </c>
       <c r="S397" s="9" t="n">
         <v>100.519463</v>
@@ -32667,7 +32667,7 @@
         <v>100.286449</v>
       </c>
       <c r="R398" s="6" t="n">
-        <v>100.053832</v>
+        <v>100.053964</v>
       </c>
       <c r="S398" s="6" t="n">
         <v>100.566435</v>
@@ -32751,7 +32751,7 @@
         <v>100.354497</v>
       </c>
       <c r="R399" s="9" t="n">
-        <v>99.834558</v>
+        <v>99.834435</v>
       </c>
       <c r="S399" s="9" t="n">
         <v>100.604359</v>
@@ -32835,7 +32835,7 @@
         <v>100.420484</v>
       </c>
       <c r="R400" s="6" t="n">
-        <v>99.614092</v>
+        <v>99.61371200000001</v>
       </c>
       <c r="S400" s="6" t="n">
         <v>100.626074</v>
@@ -32919,7 +32919,7 @@
         <v>100.471575</v>
       </c>
       <c r="R401" s="9" t="n">
-        <v>99.397296</v>
+        <v>99.396663</v>
       </c>
       <c r="S401" s="9" t="n">
         <v>100.624014</v>
@@ -33003,7 +33003,7 @@
         <v>100.484887</v>
       </c>
       <c r="R402" s="6" t="n">
-        <v>99.19916499999999</v>
+        <v>99.198302</v>
       </c>
       <c r="S402" s="6" t="n">
         <v>100.592515</v>
@@ -33087,7 +33087,7 @@
         <v>100.445016</v>
       </c>
       <c r="R403" s="9" t="n">
-        <v>99.03298599999999</v>
+        <v>99.03193</v>
       </c>
       <c r="S403" s="9" t="n">
         <v>100.530072</v>
@@ -33171,7 +33171,7 @@
         <v>100.358911</v>
       </c>
       <c r="R404" s="6" t="n">
-        <v>98.908034</v>
+        <v>98.90683300000001</v>
       </c>
       <c r="S404" s="6" t="n">
         <v>100.443625</v>
@@ -33255,7 +33255,7 @@
         <v>100.241392</v>
       </c>
       <c r="R405" s="9" t="n">
-        <v>98.84222800000001</v>
+        <v>98.840951</v>
       </c>
       <c r="S405" s="9" t="n">
         <v>100.353322</v>
@@ -33339,7 +33339,7 @@
         <v>100.116082</v>
       </c>
       <c r="R406" s="6" t="n">
-        <v>98.850426</v>
+        <v>98.849161</v>
       </c>
       <c r="S406" s="6" t="n">
         <v>100.271334</v>
@@ -33423,7 +33423,7 @@
         <v>100.000267</v>
       </c>
       <c r="R407" s="9" t="n">
-        <v>98.91202199999999</v>
+        <v>98.910831</v>
       </c>
       <c r="S407" s="9" t="n">
         <v>100.196468</v>
@@ -33507,7 +33507,7 @@
         <v>99.90637099999999</v>
       </c>
       <c r="R408" s="6" t="n">
-        <v>98.976049</v>
+        <v>98.974934</v>
       </c>
       <c r="S408" s="6" t="n">
         <v>100.120727</v>
@@ -33591,7 +33591,7 @@
         <v>99.83740400000001</v>
       </c>
       <c r="R409" s="9" t="n">
-        <v>99.019975</v>
+        <v>99.018914</v>
       </c>
       <c r="S409" s="9" t="n">
         <v>100.034327</v>
@@ -33675,7 +33675,7 @@
         <v>99.796119</v>
       </c>
       <c r="R410" s="6" t="n">
-        <v>99.029314</v>
+        <v>99.028266</v>
       </c>
       <c r="S410" s="6" t="n">
         <v>99.93434499999999</v>
@@ -33759,7 +33759,7 @@
         <v>99.769999</v>
       </c>
       <c r="R411" s="9" t="n">
-        <v>98.99702000000001</v>
+        <v>98.995935</v>
       </c>
       <c r="S411" s="9" t="n">
         <v>99.83123399999999</v>
@@ -33843,7 +33843,7 @@
         <v>99.74104199999999</v>
       </c>
       <c r="R412" s="6" t="n">
-        <v>98.93616299999999</v>
+        <v>98.935008</v>
       </c>
       <c r="S412" s="6" t="n">
         <v>99.737156</v>
@@ -33927,7 +33927,7 @@
         <v>99.69591800000001</v>
       </c>
       <c r="R413" s="9" t="n">
-        <v>98.863732</v>
+        <v>98.86249100000001</v>
       </c>
       <c r="S413" s="9" t="n">
         <v>99.66248299999999</v>
@@ -34011,7 +34011,7 @@
         <v>99.64142099999999</v>
       </c>
       <c r="R414" s="6" t="n">
-        <v>98.792176</v>
+        <v>98.790852</v>
       </c>
       <c r="S414" s="6" t="n">
         <v>99.603829</v>
@@ -34095,7 +34095,7 @@
         <v>99.60718799999999</v>
       </c>
       <c r="R415" s="9" t="n">
-        <v>98.719301</v>
+        <v>98.717893</v>
       </c>
       <c r="S415" s="9" t="n">
         <v>99.550072</v>
@@ -34179,7 +34179,7 @@
         <v>99.620942</v>
       </c>
       <c r="R416" s="6" t="n">
-        <v>98.63999</v>
+        <v>98.638488</v>
       </c>
       <c r="S416" s="6" t="n">
         <v>99.486009</v>
@@ -34263,7 +34263,7 @@
         <v>99.681202</v>
       </c>
       <c r="R417" s="9" t="n">
-        <v>98.556501</v>
+        <v>98.554901</v>
       </c>
       <c r="S417" s="9" t="n">
         <v>99.397604</v>
@@ -34347,7 +34347,7 @@
         <v>99.777332</v>
       </c>
       <c r="R418" s="6" t="n">
-        <v>98.477706</v>
+        <v>98.47601299999999</v>
       </c>
       <c r="S418" s="6" t="n">
         <v>99.277809</v>
@@ -34431,7 +34431,7 @@
         <v>99.88937199999999</v>
       </c>
       <c r="R419" s="9" t="n">
-        <v>98.413629</v>
+        <v>98.411861</v>
       </c>
       <c r="S419" s="9" t="n">
         <v>99.13395199999999</v>
@@ -34515,7 +34515,7 @@
         <v>99.99125600000001</v>
       </c>
       <c r="R420" s="6" t="n">
-        <v>98.37355100000001</v>
+        <v>98.371735</v>
       </c>
       <c r="S420" s="6" t="n">
         <v>98.995103</v>
@@ -34599,7 +34599,7 @@
         <v>100.0593</v>
       </c>
       <c r="R421" s="9" t="n">
-        <v>98.369148</v>
+        <v>98.36732499999999</v>
       </c>
       <c r="S421" s="9" t="n">
         <v>98.881131</v>
@@ -34683,7 +34683,7 @@
         <v>100.076785</v>
       </c>
       <c r="R422" s="6" t="n">
-        <v>98.407995</v>
+        <v>98.406216</v>
       </c>
       <c r="S422" s="6" t="n">
         <v>98.79669199999999</v>
@@ -34767,7 +34767,7 @@
         <v>100.048877</v>
       </c>
       <c r="R423" s="9" t="n">
-        <v>98.498316</v>
+        <v>98.496641</v>
       </c>
       <c r="S423" s="9" t="n">
         <v>98.73866599999999</v>
@@ -34851,7 +34851,7 @@
         <v>99.99153699999999</v>
       </c>
       <c r="R424" s="6" t="n">
-        <v>98.641334</v>
+        <v>98.639825</v>
       </c>
       <c r="S424" s="6" t="n">
         <v>98.70006600000001</v>
@@ -34935,7 +34935,7 @@
         <v>99.93123900000001</v>
       </c>
       <c r="R425" s="9" t="n">
-        <v>98.83420599999999</v>
+        <v>98.832921</v>
       </c>
       <c r="S425" s="9" t="n">
         <v>98.673069</v>
@@ -35019,7 +35019,7 @@
         <v>99.894961</v>
       </c>
       <c r="R426" s="6" t="n">
-        <v>99.04786</v>
+        <v>99.046823</v>
       </c>
       <c r="S426" s="6" t="n">
         <v>98.650454</v>
@@ -35103,7 +35103,7 @@
         <v>99.89936</v>
       </c>
       <c r="R427" s="9" t="n">
-        <v>99.265129</v>
+        <v>99.26434399999999</v>
       </c>
       <c r="S427" s="9" t="n">
         <v>98.627223</v>
@@ -35187,7 +35187,7 @@
         <v>99.926242</v>
       </c>
       <c r="R428" s="6" t="n">
-        <v>99.475252</v>
+        <v>99.474709</v>
       </c>
       <c r="S428" s="6" t="n">
         <v>98.600488</v>
@@ -35271,7 +35271,7 @@
         <v>99.96231400000001</v>
       </c>
       <c r="R429" s="9" t="n">
-        <v>99.674285</v>
+        <v>99.67397200000001</v>
       </c>
       <c r="S429" s="9" t="n">
         <v>98.56921800000001</v>
@@ -35355,7 +35355,7 @@
         <v>99.989831</v>
       </c>
       <c r="R430" s="6" t="n">
-        <v>99.86826000000001</v>
+        <v>99.86816899999999</v>
       </c>
       <c r="S430" s="6" t="n">
         <v>98.534024</v>
@@ -35439,7 +35439,7 @@
         <v>99.996233</v>
       </c>
       <c r="R431" s="9" t="n">
-        <v>100.060236</v>
+        <v>100.060364</v>
       </c>
       <c r="S431" s="9" t="n">
         <v>98.497089</v>
@@ -35523,7 +35523,7 @@
         <v>99.976822</v>
       </c>
       <c r="R432" s="6" t="n">
-        <v>100.244754</v>
+        <v>100.245093</v>
       </c>
       <c r="S432" s="6" t="n">
         <v>98.462174</v>
@@ -35607,7 +35607,7 @@
         <v>99.93813299999999</v>
       </c>
       <c r="R433" s="9" t="n">
-        <v>100.40549</v>
+        <v>100.406011</v>
       </c>
       <c r="S433" s="9" t="n">
         <v>98.43456999999999</v>
@@ -35691,7 +35691,7 @@
         <v>99.895577</v>
       </c>
       <c r="R434" s="6" t="n">
-        <v>100.526421</v>
+        <v>100.527076</v>
       </c>
       <c r="S434" s="6" t="n">
         <v>98.420711</v>
@@ -35775,7 +35775,7 @@
         <v>99.86329499999999</v>
       </c>
       <c r="R435" s="9" t="n">
-        <v>100.613225</v>
+        <v>100.613973</v>
       </c>
       <c r="S435" s="9" t="n">
         <v>98.429503</v>
@@ -35859,7 +35859,7 @@
         <v>99.84242999999999</v>
       </c>
       <c r="R436" s="6" t="n">
-        <v>100.696911</v>
+        <v>100.697748</v>
       </c>
       <c r="S436" s="6" t="n">
         <v>98.47127</v>
@@ -35943,7 +35943,7 @@
         <v>99.844922</v>
       </c>
       <c r="R437" s="9" t="n">
-        <v>100.799189</v>
+        <v>100.800136</v>
       </c>
       <c r="S437" s="9" t="n">
         <v>98.551306</v>
@@ -36027,7 +36027,7 @@
         <v>99.87924700000001</v>
       </c>
       <c r="R438" s="6" t="n">
-        <v>100.914326</v>
+        <v>100.915398</v>
       </c>
       <c r="S438" s="6" t="n">
         <v>98.66451000000001</v>
@@ -36111,7 +36111,7 @@
         <v>99.943476</v>
       </c>
       <c r="R439" s="9" t="n">
-        <v>101.012718</v>
+        <v>101.013894</v>
       </c>
       <c r="S439" s="9" t="n">
         <v>98.79776099999999</v>
@@ -36195,7 +36195,7 @@
         <v>100.029788</v>
       </c>
       <c r="R440" s="6" t="n">
-        <v>101.088973</v>
+        <v>101.090225</v>
       </c>
       <c r="S440" s="6" t="n">
         <v>98.93394000000001</v>
@@ -36279,7 +36279,7 @@
         <v>100.119538</v>
       </c>
       <c r="R441" s="9" t="n">
-        <v>101.177261</v>
+        <v>101.178604</v>
       </c>
       <c r="S441" s="9" t="n">
         <v>99.059124</v>
@@ -36363,7 +36363,7 @@
         <v>100.203196</v>
       </c>
       <c r="R442" s="6" t="n">
-        <v>101.296184</v>
+        <v>101.297652</v>
       </c>
       <c r="S442" s="6" t="n">
         <v>99.180396</v>
@@ -36447,7 +36447,7 @@
         <v>100.275575</v>
       </c>
       <c r="R443" s="9" t="n">
-        <v>101.430104</v>
+        <v>101.431714</v>
       </c>
       <c r="S443" s="9" t="n">
         <v>99.312623</v>
@@ -36531,7 +36531,7 @@
         <v>100.329573</v>
       </c>
       <c r="R444" s="6" t="n">
-        <v>101.560803</v>
+        <v>101.56255</v>
       </c>
       <c r="S444" s="6" t="n">
         <v>99.467378</v>
@@ -36615,7 +36615,7 @@
         <v>100.357538</v>
       </c>
       <c r="R445" s="9" t="n">
-        <v>101.693418</v>
+        <v>101.695303</v>
       </c>
       <c r="S445" s="9" t="n">
         <v>99.640981</v>
@@ -36699,7 +36699,7 @@
         <v>100.355306</v>
       </c>
       <c r="R446" s="6" t="n">
-        <v>101.832396</v>
+        <v>101.834426</v>
       </c>
       <c r="S446" s="6" t="n">
         <v>99.841348</v>
@@ -36783,7 +36783,7 @@
         <v>100.330027</v>
       </c>
       <c r="R447" s="9" t="n">
-        <v>101.959055</v>
+        <v>101.961214</v>
       </c>
       <c r="S447" s="9" t="n">
         <v>100.073592</v>
@@ -36867,7 +36867,7 @@
         <v>100.295144</v>
       </c>
       <c r="R448" s="6" t="n">
-        <v>102.053259</v>
+        <v>102.055508</v>
       </c>
       <c r="S448" s="6" t="n">
         <v>100.32277</v>
@@ -36951,7 +36951,7 @@
         <v>100.279013</v>
       </c>
       <c r="R449" s="9" t="n">
-        <v>102.06262</v>
+        <v>102.064859</v>
       </c>
       <c r="S449" s="9" t="n">
         <v>100.573691</v>
@@ -37035,7 +37035,7 @@
         <v>100.293886</v>
       </c>
       <c r="R450" s="6" t="n">
-        <v>101.93951</v>
+        <v>101.94158</v>
       </c>
       <c r="S450" s="6" t="n">
         <v>100.805945</v>
@@ -37119,7 +37119,7 @@
         <v>100.340045</v>
       </c>
       <c r="R451" s="9" t="n">
-        <v>101.663717</v>
+        <v>101.665439</v>
       </c>
       <c r="S451" s="9" t="n">
         <v>101.006967</v>
@@ -37203,7 +37203,7 @@
         <v>100.413053</v>
       </c>
       <c r="R452" s="6" t="n">
-        <v>101.281721</v>
+        <v>101.282968</v>
       </c>
       <c r="S452" s="6" t="n">
         <v>101.170061</v>
@@ -37287,7 +37287,7 @@
         <v>100.497417</v>
       </c>
       <c r="R453" s="9" t="n">
-        <v>100.864579</v>
+        <v>100.865309</v>
       </c>
       <c r="S453" s="9" t="n">
         <v>101.295028</v>
@@ -37371,7 +37371,7 @@
         <v>100.578745</v>
       </c>
       <c r="R454" s="6" t="n">
-        <v>100.468807</v>
+        <v>100.469044</v>
       </c>
       <c r="S454" s="6" t="n">
         <v>101.383472</v>
@@ -37455,7 +37455,7 @@
         <v>100.646729</v>
       </c>
       <c r="R455" s="9" t="n">
-        <v>100.125365</v>
+        <v>100.125169</v>
       </c>
       <c r="S455" s="9" t="n">
         <v>101.439476</v>
@@ -37539,7 +37539,7 @@
         <v>100.686671</v>
       </c>
       <c r="R456" s="6" t="n">
-        <v>99.86854700000001</v>
+        <v>99.86801800000001</v>
       </c>
       <c r="S456" s="6" t="n">
         <v>101.465094</v>
@@ -37623,7 +37623,7 @@
         <v>100.686797</v>
       </c>
       <c r="R457" s="9" t="n">
-        <v>99.718109</v>
+        <v>99.71737299999999</v>
       </c>
       <c r="S457" s="9" t="n">
         <v>101.464857</v>
@@ -37707,7 +37707,7 @@
         <v>100.647609</v>
       </c>
       <c r="R458" s="6" t="n">
-        <v>99.66754299999999</v>
+        <v>99.666714</v>
       </c>
       <c r="S458" s="6" t="n">
         <v>101.448346</v>
@@ -37791,7 +37791,7 @@
         <v>100.583365</v>
       </c>
       <c r="R459" s="9" t="n">
-        <v>99.686634</v>
+        <v>99.685793</v>
       </c>
       <c r="S459" s="9" t="n">
         <v>101.426494</v>
@@ -37875,7 +37875,7 @@
         <v>100.516217</v>
       </c>
       <c r="R460" s="6" t="n">
-        <v>99.723964</v>
+        <v>99.723131</v>
       </c>
       <c r="S460" s="6" t="n">
         <v>101.408614</v>
@@ -37959,7 +37959,7 @@
         <v>100.461014</v>
       </c>
       <c r="R461" s="9" t="n">
-        <v>99.753157</v>
+        <v>99.75232200000001</v>
       </c>
       <c r="S461" s="9" t="n">
         <v>101.399908</v>
@@ -38043,7 +38043,7 @@
         <v>100.409692</v>
       </c>
       <c r="R462" s="6" t="n">
-        <v>99.771046</v>
+        <v>99.770194</v>
       </c>
       <c r="S462" s="6" t="n">
         <v>101.398809</v>
@@ -38127,7 +38127,7 @@
         <v>100.359408</v>
       </c>
       <c r="R463" s="9" t="n">
-        <v>99.79062</v>
+        <v>99.789751</v>
       </c>
       <c r="S463" s="9" t="n">
         <v>101.400754</v>
@@ -38211,7 +38211,7 @@
         <v>100.327472</v>
       </c>
       <c r="R464" s="6" t="n">
-        <v>99.83372</v>
+        <v>99.83286099999999</v>
       </c>
       <c r="S464" s="6" t="n">
         <v>101.401412</v>
@@ -38295,7 +38295,7 @@
         <v>100.322226</v>
       </c>
       <c r="R465" s="9" t="n">
-        <v>99.9051</v>
+        <v>99.904284</v>
       </c>
       <c r="S465" s="9" t="n">
         <v>101.400221</v>
@@ -38379,7 +38379,7 @@
         <v>100.330935</v>
       </c>
       <c r="R466" s="6" t="n">
-        <v>99.989377</v>
+        <v>99.98861599999999</v>
       </c>
       <c r="S466" s="6" t="n">
         <v>101.399459</v>
@@ -38463,7 +38463,7 @@
         <v>100.349622</v>
       </c>
       <c r="R467" s="9" t="n">
-        <v>100.031191</v>
+        <v>100.030436</v>
       </c>
       <c r="S467" s="9" t="n">
         <v>101.401538</v>
@@ -38547,7 +38547,7 @@
         <v>100.343164</v>
       </c>
       <c r="R468" s="6" t="n">
-        <v>100.003532</v>
+        <v>100.002699</v>
       </c>
       <c r="S468" s="6" t="n">
         <v>101.406396</v>
@@ -38631,7 +38631,7 @@
         <v>100.279067</v>
       </c>
       <c r="R469" s="9" t="n">
-        <v>99.947812</v>
+        <v>99.946867</v>
       </c>
       <c r="S469" s="9" t="n">
         <v>101.412375</v>
@@ -38715,7 +38715,7 @@
         <v>100.149826</v>
       </c>
       <c r="R470" s="6" t="n">
-        <v>99.898082</v>
+        <v>99.897031</v>
       </c>
       <c r="S470" s="6" t="n">
         <v>101.421455</v>
@@ -38799,7 +38799,7 @@
         <v>99.975212</v>
       </c>
       <c r="R471" s="9" t="n">
-        <v>99.85851599999999</v>
+        <v>99.85736900000001</v>
       </c>
       <c r="S471" s="9" t="n">
         <v>101.436573</v>
@@ -38883,7 +38883,7 @@
         <v>99.811229</v>
       </c>
       <c r="R472" s="6" t="n">
-        <v>99.81680799999999</v>
+        <v>99.815563</v>
       </c>
       <c r="S472" s="6" t="n">
         <v>101.458375</v>
@@ -38967,7 +38967,7 @@
         <v>99.698545</v>
       </c>
       <c r="R473" s="9" t="n">
-        <v>99.742237</v>
+        <v>99.740854</v>
       </c>
       <c r="S473" s="9" t="n">
         <v>101.482151</v>
@@ -39051,7 +39051,7 @@
         <v>99.644536</v>
       </c>
       <c r="R474" s="6" t="n">
-        <v>99.64331900000001</v>
+        <v>99.641769</v>
       </c>
       <c r="S474" s="6" t="n">
         <v>101.500298</v>
@@ -39135,7 +39135,7 @@
         <v>99.62882399999999</v>
       </c>
       <c r="R475" s="9" t="n">
-        <v>99.556048</v>
+        <v>99.554343</v>
       </c>
       <c r="S475" s="9" t="n">
         <v>101.506083</v>
@@ -39219,7 +39219,7 @@
         <v>99.6384</v>
       </c>
       <c r="R476" s="6" t="n">
-        <v>99.494711</v>
+        <v>99.49288199999999</v>
       </c>
       <c r="S476" s="6" t="n">
         <v>101.498742</v>
@@ -39303,7 +39303,7 @@
         <v>99.656881</v>
       </c>
       <c r="R477" s="9" t="n">
-        <v>99.460824</v>
+        <v>99.458901</v>
       </c>
       <c r="S477" s="9" t="n">
         <v>101.479737</v>
@@ -39387,7 +39387,7 @@
         <v>99.669753</v>
       </c>
       <c r="R478" s="6" t="n">
-        <v>99.451318</v>
+        <v>99.449331</v>
       </c>
       <c r="S478" s="6" t="n">
         <v>101.449601</v>
@@ -39471,7 +39471,7 @@
         <v>99.68104700000001</v>
       </c>
       <c r="R479" s="9" t="n">
-        <v>99.452952</v>
+        <v>99.450913</v>
       </c>
       <c r="S479" s="9" t="n">
         <v>101.406674</v>
@@ -39555,7 +39555,7 @@
         <v>99.693533</v>
       </c>
       <c r="R480" s="6" t="n">
-        <v>99.45204</v>
+        <v>99.449946</v>
       </c>
       <c r="S480" s="6" t="n">
         <v>101.348145</v>
@@ -39639,7 +39639,7 @@
         <v>99.714883</v>
       </c>
       <c r="R481" s="9" t="n">
-        <v>99.44546800000001</v>
+        <v>99.443313</v>
       </c>
       <c r="S481" s="9" t="n">
         <v>101.271657</v>
@@ -39723,7 +39723,7 @@
         <v>99.727627</v>
       </c>
       <c r="R482" s="6" t="n">
-        <v>99.42440000000001</v>
+        <v>99.422166</v>
       </c>
       <c r="S482" s="6" t="n">
         <v>101.176706</v>
@@ -39807,7 +39807,7 @@
         <v>99.712333</v>
       </c>
       <c r="R483" s="9" t="n">
-        <v>99.40574599999999</v>
+        <v>99.403437</v>
       </c>
       <c r="S483" s="9" t="n">
         <v>101.063609</v>
@@ -39891,7 +39891,7 @@
         <v>99.65216100000001</v>
       </c>
       <c r="R484" s="6" t="n">
-        <v>99.43335999999999</v>
+        <v>99.431031</v>
       </c>
       <c r="S484" s="6" t="n">
         <v>100.930901</v>
@@ -39975,7 +39975,7 @@
         <v>99.537077</v>
       </c>
       <c r="R485" s="9" t="n">
-        <v>99.56064600000001</v>
+        <v>99.558414</v>
       </c>
       <c r="S485" s="9" t="n">
         <v>100.772422</v>
@@ -40059,7 +40059,7 @@
         <v>99.35934899999999</v>
       </c>
       <c r="R486" s="6" t="n">
-        <v>99.834082</v>
+        <v>99.83211900000001</v>
       </c>
       <c r="S486" s="6" t="n">
         <v>100.579187</v>
@@ -40143,7 +40143,7 @@
         <v>99.12958</v>
       </c>
       <c r="R487" s="9" t="n">
-        <v>100.269794</v>
+        <v>100.268294</v>
       </c>
       <c r="S487" s="9" t="n">
         <v>100.340968</v>
@@ -40227,7 +40227,7 @@
         <v>98.895561</v>
       </c>
       <c r="R488" s="6" t="n">
-        <v>100.810475</v>
+        <v>100.809561</v>
       </c>
       <c r="S488" s="6" t="n">
         <v>100.050202</v>
@@ -40311,7 +40311,7 @@
         <v>98.723353</v>
       </c>
       <c r="R489" s="9" t="n">
-        <v>101.290398</v>
+        <v>101.290001</v>
       </c>
       <c r="S489" s="9" t="n">
         <v>99.710571</v>
@@ -40395,7 +40395,7 @@
         <v>98.620248</v>
       </c>
       <c r="R490" s="6" t="n">
-        <v>101.576942</v>
+        <v>101.576836</v>
       </c>
       <c r="S490" s="6" t="n">
         <v>99.340858</v>
@@ -40479,7 +40479,7 @@
         <v>98.582958</v>
       </c>
       <c r="R491" s="9" t="n">
-        <v>101.655127</v>
+        <v>101.655069</v>
       </c>
       <c r="S491" s="9" t="n">
         <v>98.965486</v>
@@ -40563,7 +40563,7 @@
         <v>98.59928600000001</v>
       </c>
       <c r="R492" s="6" t="n">
-        <v>101.571659</v>
+        <v>101.571462</v>
       </c>
       <c r="S492" s="6" t="n">
         <v>98.605591</v>
@@ -40647,7 +40647,7 @@
         <v>98.672332</v>
       </c>
       <c r="R493" s="9" t="n">
-        <v>101.360391</v>
+        <v>101.359907</v>
       </c>
       <c r="S493" s="9" t="n">
         <v>98.28086500000001</v>
@@ -40731,7 +40731,7 @@
         <v>98.80711599999999</v>
       </c>
       <c r="R494" s="6" t="n">
-        <v>101.061429</v>
+        <v>101.060557</v>
       </c>
       <c r="S494" s="6" t="n">
         <v>98.003405</v>
@@ -40815,7 +40815,7 @@
         <v>99.001842</v>
       </c>
       <c r="R495" s="9" t="n">
-        <v>100.723807</v>
+        <v>100.722506</v>
       </c>
       <c r="S495" s="9" t="n">
         <v>97.779449</v>
@@ -40899,7 +40899,7 @@
         <v>99.247001</v>
       </c>
       <c r="R496" s="6" t="n">
-        <v>100.396042</v>
+        <v>100.394326</v>
       </c>
       <c r="S496" s="6" t="n">
         <v>97.60740199999999</v>
@@ -40983,7 +40983,7 @@
         <v>99.50240700000001</v>
       </c>
       <c r="R497" s="9" t="n">
-        <v>100.129687</v>
+        <v>100.127633</v>
       </c>
       <c r="S497" s="9" t="n">
         <v>97.476136</v>
@@ -41067,7 +41067,7 @@
         <v>99.745301</v>
       </c>
       <c r="R498" s="6" t="n">
-        <v>99.956107</v>
+        <v>99.953828</v>
       </c>
       <c r="S498" s="6" t="n">
         <v>97.37322500000001</v>
@@ -41151,7 +41151,7 @@
         <v>99.97938499999999</v>
       </c>
       <c r="R499" s="9" t="n">
-        <v>99.87389899999999</v>
+        <v>99.871509</v>
       </c>
       <c r="S499" s="9" t="n">
         <v>97.29190699999999</v>
@@ -41235,7 +41235,7 @@
         <v>100.200336</v>
       </c>
       <c r="R500" s="6" t="n">
-        <v>99.852745</v>
+        <v>99.850319</v>
       </c>
       <c r="S500" s="6" t="n">
         <v>97.235022</v>
@@ -41319,7 +41319,7 @@
         <v>100.39602</v>
       </c>
       <c r="R501" s="9" t="n">
-        <v>99.86048</v>
+        <v>99.858057</v>
       </c>
       <c r="S501" s="9" t="n">
         <v>97.20910499999999</v>
@@ -41403,7 +41403,7 @@
         <v>100.557828</v>
       </c>
       <c r="R502" s="6" t="n">
-        <v>99.89606499999999</v>
+        <v>99.893686</v>
       </c>
       <c r="S502" s="6" t="n">
         <v>97.21916899999999</v>
@@ -41487,7 +41487,7 @@
         <v>100.674094</v>
       </c>
       <c r="R503" s="9" t="n">
-        <v>99.955201</v>
+        <v>99.952899</v>
       </c>
       <c r="S503" s="9" t="n">
         <v>97.268539</v>
@@ -41571,7 +41571,7 @@
         <v>100.749093</v>
       </c>
       <c r="R504" s="6" t="n">
-        <v>100.032761</v>
+        <v>100.030564</v>
       </c>
       <c r="S504" s="6" t="n">
         <v>97.35690700000001</v>
@@ -41655,7 +41655,7 @@
         <v>100.78608</v>
       </c>
       <c r="R505" s="9" t="n">
-        <v>100.128484</v>
+        <v>100.126421</v>
       </c>
       <c r="S505" s="9" t="n">
         <v>97.477299</v>
@@ -41739,7 +41739,7 @@
         <v>100.785381</v>
       </c>
       <c r="R506" s="6" t="n">
-        <v>100.238834</v>
+        <v>100.236931</v>
       </c>
       <c r="S506" s="6" t="n">
         <v>97.625405</v>
@@ -41823,7 +41823,7 @@
         <v>100.766194</v>
       </c>
       <c r="R507" s="9" t="n">
-        <v>100.3575</v>
+        <v>100.355775</v>
       </c>
       <c r="S507" s="9" t="n">
         <v>97.79974799999999</v>
@@ -41907,7 +41907,7 @@
         <v>100.744143</v>
       </c>
       <c r="R508" s="6" t="n">
-        <v>100.463508</v>
+        <v>100.461955</v>
       </c>
       <c r="S508" s="6" t="n">
         <v>97.99692899999999</v>
@@ -41991,7 +41991,7 @@
         <v>100.727777</v>
       </c>
       <c r="R509" s="9" t="n">
-        <v>100.541792</v>
+        <v>100.540389</v>
       </c>
       <c r="S509" s="9" t="n">
         <v>98.215255</v>
@@ -42075,7 +42075,7 @@
         <v>100.697338</v>
       </c>
       <c r="R510" s="6" t="n">
-        <v>100.588335</v>
+        <v>100.587053</v>
       </c>
       <c r="S510" s="6" t="n">
         <v>98.44961499999999</v>
@@ -42159,7 +42159,7 @@
         <v>100.641439</v>
       </c>
       <c r="R511" s="9" t="n">
-        <v>100.617982</v>
+        <v>100.616813</v>
       </c>
       <c r="S511" s="9" t="n">
         <v>98.69631</v>
@@ -42243,7 +42243,7 @@
         <v>100.536507</v>
       </c>
       <c r="R512" s="6" t="n">
-        <v>100.638299</v>
+        <v>100.637243</v>
       </c>
       <c r="S512" s="6" t="n">
         <v>98.953272</v>
@@ -42327,7 +42327,7 @@
         <v>100.367753</v>
       </c>
       <c r="R513" s="9" t="n">
-        <v>100.651921</v>
+        <v>100.650982</v>
       </c>
       <c r="S513" s="9" t="n">
         <v>99.219703</v>
@@ -42411,7 +42411,7 @@
         <v>100.16217</v>
       </c>
       <c r="R514" s="6" t="n">
-        <v>100.669074</v>
+        <v>100.66827</v>
       </c>
       <c r="S514" s="6" t="n">
         <v>99.494546</v>
@@ -42495,7 +42495,7 @@
         <v>99.947166</v>
       </c>
       <c r="R515" s="9" t="n">
-        <v>100.678249</v>
+        <v>100.677583</v>
       </c>
       <c r="S515" s="9" t="n">
         <v>99.77865799999999</v>
@@ -42579,7 +42579,7 @@
         <v>99.767995</v>
       </c>
       <c r="R516" s="6" t="n">
-        <v>100.662405</v>
+        <v>100.661862</v>
       </c>
       <c r="S516" s="6" t="n">
         <v>100.068147</v>
@@ -42663,7 +42663,7 @@
         <v>99.65320699999999</v>
       </c>
       <c r="R517" s="9" t="n">
-        <v>100.599822</v>
+        <v>100.599361</v>
       </c>
       <c r="S517" s="9" t="n">
         <v>100.353452</v>
@@ -42747,7 +42747,7 @@
         <v>99.630576</v>
       </c>
       <c r="R518" s="6" t="n">
-        <v>100.49133</v>
+        <v>100.490913</v>
       </c>
       <c r="S518" s="6" t="n">
         <v>100.627366</v>
@@ -42831,7 +42831,7 @@
         <v>99.69457300000001</v>
       </c>
       <c r="R519" s="9" t="n">
-        <v>100.338027</v>
+        <v>100.337616</v>
       </c>
       <c r="S519" s="9" t="n">
         <v>100.883551</v>
@@ -42915,7 +42915,7 @@
         <v>99.801202</v>
       </c>
       <c r="R520" s="6" t="n">
-        <v>100.143876</v>
+        <v>100.143441</v>
       </c>
       <c r="S520" s="6" t="n">
         <v>101.111576</v>
@@ -42999,7 +42999,7 @@
         <v>99.920322</v>
       </c>
       <c r="R521" s="9" t="n">
-        <v>99.924976</v>
+        <v>99.924505</v>
       </c>
       <c r="S521" s="9" t="n">
         <v>101.304374</v>
@@ -43083,7 +43083,7 @@
         <v>100.043416</v>
       </c>
       <c r="R522" s="6" t="n">
-        <v>99.688965</v>
+        <v>99.688456</v>
       </c>
       <c r="S522" s="6" t="n">
         <v>101.456708</v>
@@ -43167,7 +43167,7 @@
         <v>100.138478</v>
       </c>
       <c r="R523" s="9" t="n">
-        <v>99.45135500000001</v>
+        <v>99.45082499999999</v>
       </c>
       <c r="S523" s="9" t="n">
         <v>101.568894</v>
@@ -43251,7 +43251,7 @@
         <v>100.200833</v>
       </c>
       <c r="R524" s="6" t="n">
-        <v>99.225194</v>
+        <v>99.224676</v>
       </c>
       <c r="S524" s="6" t="n">
         <v>101.642235</v>
@@ -43335,7 +43335,7 @@
         <v>100.225158</v>
       </c>
       <c r="R525" s="9" t="n">
-        <v>99.017049</v>
+        <v>99.01658399999999</v>
       </c>
       <c r="S525" s="9" t="n">
         <v>101.679741</v>
@@ -43419,7 +43419,7 @@
         <v>100.210858</v>
       </c>
       <c r="R526" s="6" t="n">
-        <v>98.832632</v>
+        <v>98.832268</v>
       </c>
       <c r="S526" s="6" t="n">
         <v>101.686583</v>
@@ -43503,7 +43503,7 @@
         <v>100.172121</v>
       </c>
       <c r="R527" s="9" t="n">
-        <v>98.68146900000001</v>
+        <v>98.681269</v>
       </c>
       <c r="S527" s="9" t="n">
         <v>101.671325</v>
@@ -43587,7 +43587,7 @@
         <v>100.116177</v>
       </c>
       <c r="R528" s="6" t="n">
-        <v>98.57841000000001</v>
+        <v>98.578451</v>
       </c>
       <c r="S528" s="6" t="n">
         <v>101.643169</v>
@@ -43671,7 +43671,7 @@
         <v>100.053167</v>
       </c>
       <c r="R529" s="9" t="n">
-        <v>98.52924</v>
+        <v>98.52960899999999</v>
       </c>
       <c r="S529" s="9" t="n">
         <v>101.609184</v>
@@ -43755,7 +43755,7 @@
         <v>100.010003</v>
       </c>
       <c r="R530" s="6" t="n">
-        <v>98.51473300000001</v>
+        <v>98.515494</v>
       </c>
       <c r="S530" s="6" t="n">
         <v>101.573961</v>
@@ -43839,7 +43839,7 @@
         <v>100.013716</v>
       </c>
       <c r="R531" s="9" t="n">
-        <v>98.497727</v>
+        <v>98.498902</v>
       </c>
       <c r="S531" s="9" t="n">
         <v>101.539827</v>
@@ -43923,7 +43923,7 @@
         <v>100.069662</v>
       </c>
       <c r="R532" s="6" t="n">
-        <v>98.443996</v>
+        <v>98.445566</v>
       </c>
       <c r="S532" s="6" t="n">
         <v>101.507278</v>
@@ -44007,7 +44007,7 @@
         <v>100.139378</v>
       </c>
       <c r="R533" s="9" t="n">
-        <v>98.37384900000001</v>
+        <v>98.375821</v>
       </c>
       <c r="S533" s="9" t="n">
         <v>101.47548</v>
@@ -44091,7 +44091,7 @@
         <v>100.184547</v>
       </c>
       <c r="R534" s="6" t="n">
-        <v>98.32190900000001</v>
+        <v>98.324331</v>
       </c>
       <c r="S534" s="6" t="n">
         <v>101.443137</v>
@@ -44175,7 +44175,7 @@
         <v>100.189632</v>
       </c>
       <c r="R535" s="9" t="n">
-        <v>98.320988</v>
+        <v>98.323947</v>
       </c>
       <c r="S535" s="9" t="n">
         <v>101.408772</v>
@@ -44259,7 +44259,7 @@
         <v>100.153181</v>
       </c>
       <c r="R536" s="6" t="n">
-        <v>98.394139</v>
+        <v>98.397749</v>
       </c>
       <c r="S536" s="6" t="n">
         <v>101.371526</v>
@@ -44343,7 +44343,7 @@
         <v>100.067761</v>
       </c>
       <c r="R537" s="9" t="n">
-        <v>98.56648199999999</v>
+        <v>98.57089000000001</v>
       </c>
       <c r="S537" s="9" t="n">
         <v>101.332263</v>
@@ -44427,7 +44427,7 @@
         <v>99.93894299999999</v>
       </c>
       <c r="R538" s="6" t="n">
-        <v>98.84993</v>
+        <v>98.855294</v>
       </c>
       <c r="S538" s="6" t="n">
         <v>101.292933</v>
@@ -44511,7 +44511,7 @@
         <v>99.783644</v>
       </c>
       <c r="R539" s="9" t="n">
-        <v>99.230948</v>
+        <v>99.23741200000001</v>
       </c>
       <c r="S539" s="9" t="n">
         <v>101.251642</v>
@@ -44595,7 +44595,7 @@
         <v>99.62483899999999</v>
       </c>
       <c r="R540" s="6" t="n">
-        <v>99.659589</v>
+        <v>99.667238</v>
       </c>
       <c r="S540" s="6" t="n">
         <v>101.204191</v>
@@ -44679,7 +44679,7 @@
         <v>99.472677</v>
       </c>
       <c r="R541" s="9" t="n">
-        <v>100.106184</v>
+        <v>100.115067</v>
       </c>
       <c r="S541" s="9" t="n">
         <v>101.146262</v>
@@ -44763,7 +44763,7 @@
         <v>99.336128</v>
       </c>
       <c r="R542" s="6" t="n">
-        <v>100.522632</v>
+        <v>100.53274</v>
       </c>
       <c r="S542" s="6" t="n">
         <v>101.07655</v>
@@ -44847,7 +44847,7 @@
         <v>99.221727</v>
       </c>
       <c r="R543" s="9" t="n">
-        <v>100.875064</v>
+        <v>100.886346</v>
       </c>
       <c r="S543" s="9" t="n">
         <v>100.994338</v>
@@ -44931,7 +44931,7 @@
         <v>99.14724099999999</v>
       </c>
       <c r="R544" s="6" t="n">
-        <v>101.153039</v>
+        <v>101.165426</v>
       </c>
       <c r="S544" s="6" t="n">
         <v>100.899432</v>
@@ -45015,7 +45015,7 @@
         <v>99.127163</v>
       </c>
       <c r="R545" s="9" t="n">
-        <v>101.343839</v>
+        <v>101.357244</v>
       </c>
       <c r="S545" s="9" t="n">
         <v>100.790091</v>
@@ -45099,7 +45099,7 @@
         <v>99.16571</v>
       </c>
       <c r="R546" s="6" t="n">
-        <v>101.447589</v>
+        <v>101.461922</v>
       </c>
       <c r="S546" s="6" t="n">
         <v>100.664877</v>
@@ -45183,7 +45183,7 @@
         <v>99.251963</v>
       </c>
       <c r="R547" s="9" t="n">
-        <v>101.45805</v>
+        <v>101.473213</v>
       </c>
       <c r="S547" s="9" t="n">
         <v>100.521756</v>
@@ -45267,7 +45267,7 @@
         <v>99.372514</v>
       </c>
       <c r="R548" s="6" t="n">
-        <v>101.380664</v>
+        <v>101.396573</v>
       </c>
       <c r="S548" s="6" t="n">
         <v>100.363351</v>
@@ -45351,7 +45351,7 @@
         <v>99.51421000000001</v>
       </c>
       <c r="R549" s="9" t="n">
-        <v>101.231243</v>
+        <v>101.247851</v>
       </c>
       <c r="S549" s="9" t="n">
         <v>100.191589</v>
@@ -45435,7 +45435,7 @@
         <v>99.654281</v>
       </c>
       <c r="R550" s="6" t="n">
-        <v>101.031533</v>
+        <v>101.048854</v>
       </c>
       <c r="S550" s="6" t="n">
         <v>100.013707</v>
@@ -45519,7 +45519,7 @@
         <v>99.784363</v>
       </c>
       <c r="R551" s="9" t="n">
-        <v>100.816525</v>
+        <v>100.834673</v>
       </c>
       <c r="S551" s="9" t="n">
         <v>99.835679</v>
@@ -45603,7 +45603,7 @@
         <v>99.91254600000001</v>
       </c>
       <c r="R552" s="6" t="n">
-        <v>100.611432</v>
+        <v>100.630632</v>
       </c>
       <c r="S552" s="6" t="n">
         <v>99.665465</v>
@@ -45687,7 +45687,7 @@
         <v>100.047651</v>
       </c>
       <c r="R553" s="9" t="n">
-        <v>100.428222</v>
+        <v>100.448813</v>
       </c>
       <c r="S553" s="9" t="n">
         <v>99.51245299999999</v>
@@ -45771,7 +45771,7 @@
         <v>100.186812</v>
       </c>
       <c r="R554" s="6" t="n">
-        <v>100.258657</v>
+        <v>100.281068</v>
       </c>
       <c r="S554" s="6" t="n">
         <v>99.37775999999999</v>
@@ -45855,7 +45855,7 @@
         <v>100.316216</v>
       </c>
       <c r="R555" s="9" t="n">
-        <v>100.094777</v>
+        <v>100.119486</v>
       </c>
       <c r="S555" s="9" t="n">
         <v>99.257627</v>
@@ -45939,7 +45939,7 @@
         <v>100.435533</v>
       </c>
       <c r="R556" s="6" t="n">
-        <v>99.932554</v>
+        <v>99.959986</v>
       </c>
       <c r="S556" s="6" t="n">
         <v>99.150362</v>
@@ -46023,7 +46023,7 @@
         <v>100.544096</v>
       </c>
       <c r="R557" s="9" t="n">
-        <v>99.776076</v>
+        <v>99.806404</v>
       </c>
       <c r="S557" s="9" t="n">
         <v>99.055179</v>
@@ -46107,7 +46107,7 @@
         <v>100.634441</v>
       </c>
       <c r="R558" s="6" t="n">
-        <v>99.643597</v>
+        <v>99.676424</v>
       </c>
       <c r="S558" s="6" t="n">
         <v>98.97037400000001</v>
@@ -46191,7 +46191,7 @@
         <v>100.687597</v>
       </c>
       <c r="R559" s="9" t="n">
-        <v>99.557343</v>
+        <v>99.591228</v>
       </c>
       <c r="S559" s="9" t="n">
         <v>98.89361700000001</v>
@@ -46275,7 +46275,7 @@
         <v>100.689859</v>
       </c>
       <c r="R560" s="6" t="n">
-        <v>99.530484</v>
+        <v>99.562355</v>
       </c>
       <c r="S560" s="6" t="n">
         <v>98.819743</v>
@@ -46359,7 +46359,7 @@
         <v>100.654205</v>
       </c>
       <c r="R561" s="9" t="n">
-        <v>99.544381</v>
+        <v>99.568915</v>
       </c>
       <c r="S561" s="9" t="n">
         <v>98.746636</v>
@@ -46443,7 +46443,7 @@
         <v>100.5928</v>
       </c>
       <c r="R562" s="6" t="n">
-        <v>99.586506</v>
+        <v>99.595789</v>
       </c>
       <c r="S562" s="6" t="n">
         <v>98.678714</v>
@@ -46527,7 +46527,7 @@
         <v>100.511198</v>
       </c>
       <c r="R563" s="9" t="n">
-        <v>99.64585</v>
+        <v>99.62963999999999</v>
       </c>
       <c r="S563" s="9" t="n">
         <v>98.620802</v>
@@ -46601,7 +46601,7 @@
         <v>100.418174</v>
       </c>
       <c r="R564" s="6" t="n">
-        <v>99.712586</v>
+        <v>99.659767</v>
       </c>
       <c r="S564" s="6" t="n">
         <v>98.573003</v>

--- a/downloads/indicadores/SIC/SIC_datos.xlsx
+++ b/downloads/indicadores/SIC/SIC_datos.xlsx
@@ -6222,7 +6222,7 @@
         <v>100.777636</v>
       </c>
       <c r="K78" s="6" t="n">
-        <v>104.277162</v>
+        <v>104.289335</v>
       </c>
       <c r="L78" s="6" t="n">
         <v>99.94885499999999</v>
@@ -6302,7 +6302,7 @@
         <v>100.570545</v>
       </c>
       <c r="K79" s="9" t="n">
-        <v>103.636482</v>
+        <v>103.646816</v>
       </c>
       <c r="L79" s="9" t="n">
         <v>99.825245</v>
@@ -6382,7 +6382,7 @@
         <v>100.321482</v>
       </c>
       <c r="K80" s="6" t="n">
-        <v>103.010763</v>
+        <v>103.019302</v>
       </c>
       <c r="L80" s="6" t="n">
         <v>99.712536</v>
@@ -6462,7 +6462,7 @@
         <v>100.034632</v>
       </c>
       <c r="K81" s="9" t="n">
-        <v>102.412687</v>
+        <v>102.41951</v>
       </c>
       <c r="L81" s="9" t="n">
         <v>99.603674</v>
@@ -6542,7 +6542,7 @@
         <v>99.70424199999999</v>
       </c>
       <c r="K82" s="6" t="n">
-        <v>101.868368</v>
+        <v>101.873629</v>
       </c>
       <c r="L82" s="6" t="n">
         <v>99.488235</v>
@@ -6622,7 +6622,7 @@
         <v>99.352293</v>
       </c>
       <c r="K83" s="9" t="n">
-        <v>101.38788</v>
+        <v>101.391763</v>
       </c>
       <c r="L83" s="9" t="n">
         <v>99.353919</v>
@@ -6702,7 +6702,7 @@
         <v>99.021517</v>
       </c>
       <c r="K84" s="6" t="n">
-        <v>100.980329</v>
+        <v>100.983042</v>
       </c>
       <c r="L84" s="6" t="n">
         <v>99.196039</v>
@@ -6782,7 +6782,7 @@
         <v>98.742053</v>
       </c>
       <c r="K85" s="9" t="n">
-        <v>100.599872</v>
+        <v>100.601494</v>
       </c>
       <c r="L85" s="9" t="n">
         <v>99.028826</v>
@@ -6862,7 +6862,7 @@
         <v>98.533401</v>
       </c>
       <c r="K86" s="6" t="n">
-        <v>100.235006</v>
+        <v>100.235581</v>
       </c>
       <c r="L86" s="6" t="n">
         <v>98.867582</v>
@@ -6942,7 +6942,7 @@
         <v>98.401898</v>
       </c>
       <c r="K87" s="9" t="n">
-        <v>99.87936000000001</v>
+        <v>99.87891500000001</v>
       </c>
       <c r="L87" s="9" t="n">
         <v>98.72774699999999</v>
@@ -7022,7 +7022,7 @@
         <v>98.349127</v>
       </c>
       <c r="K88" s="6" t="n">
-        <v>99.57098499999999</v>
+        <v>99.569655</v>
       </c>
       <c r="L88" s="6" t="n">
         <v>98.619692</v>
@@ -7102,7 +7102,7 @@
         <v>98.387426</v>
       </c>
       <c r="K89" s="9" t="n">
-        <v>99.319245</v>
+        <v>99.317193</v>
       </c>
       <c r="L89" s="9" t="n">
         <v>98.548402</v>
@@ -7182,7 +7182,7 @@
         <v>98.51583599999999</v>
       </c>
       <c r="K90" s="6" t="n">
-        <v>99.06425</v>
+        <v>99.061466</v>
       </c>
       <c r="L90" s="6" t="n">
         <v>98.513853</v>
@@ -7264,7 +7264,7 @@
         <v>98.72013099999999</v>
       </c>
       <c r="K91" s="9" t="n">
-        <v>98.80973</v>
+        <v>98.80621600000001</v>
       </c>
       <c r="L91" s="9" t="n">
         <v>98.51832899999999</v>
@@ -7346,7 +7346,7 @@
         <v>98.972852</v>
       </c>
       <c r="K92" s="6" t="n">
-        <v>98.547287</v>
+        <v>98.54302</v>
       </c>
       <c r="L92" s="6" t="n">
         <v>98.561089</v>
@@ -7428,7 +7428,7 @@
         <v>99.232601</v>
       </c>
       <c r="K93" s="9" t="n">
-        <v>98.28620600000001</v>
+        <v>98.28119100000001</v>
       </c>
       <c r="L93" s="9" t="n">
         <v>98.64266600000001</v>
@@ -7510,7 +7510,7 @@
         <v>99.465559</v>
       </c>
       <c r="K94" s="6" t="n">
-        <v>98.06012699999999</v>
+        <v>98.054463</v>
       </c>
       <c r="L94" s="6" t="n">
         <v>98.763024</v>
@@ -7592,7 +7592,7 @@
         <v>99.654509</v>
       </c>
       <c r="K95" s="9" t="n">
-        <v>97.97647600000001</v>
+        <v>97.970572</v>
       </c>
       <c r="L95" s="9" t="n">
         <v>98.914935</v>
@@ -7674,7 +7674,7 @@
         <v>99.797939</v>
       </c>
       <c r="K96" s="6" t="n">
-        <v>98.006775</v>
+        <v>98.000958</v>
       </c>
       <c r="L96" s="6" t="n">
         <v>99.085436</v>
@@ -7756,7 +7756,7 @@
         <v>99.898597</v>
       </c>
       <c r="K97" s="9" t="n">
-        <v>98.084563</v>
+        <v>98.078969</v>
       </c>
       <c r="L97" s="9" t="n">
         <v>99.256884</v>
@@ -7838,7 +7838,7 @@
         <v>99.95589699999999</v>
       </c>
       <c r="K98" s="6" t="n">
-        <v>98.135368</v>
+        <v>98.129921</v>
       </c>
       <c r="L98" s="6" t="n">
         <v>99.408141</v>
@@ -7920,7 +7920,7 @@
         <v>99.955144</v>
       </c>
       <c r="K99" s="9" t="n">
-        <v>98.124526</v>
+        <v>98.11904699999999</v>
       </c>
       <c r="L99" s="9" t="n">
         <v>99.51108600000001</v>
@@ -8002,7 +8002,7 @@
         <v>99.899158</v>
       </c>
       <c r="K100" s="6" t="n">
-        <v>98.046059</v>
+        <v>98.040356</v>
       </c>
       <c r="L100" s="6" t="n">
         <v>99.5478</v>
@@ -8084,7 +8084,7 @@
         <v>99.79517</v>
       </c>
       <c r="K101" s="9" t="n">
-        <v>97.91142600000001</v>
+        <v>97.90533600000001</v>
       </c>
       <c r="L101" s="9" t="n">
         <v>99.520081</v>
@@ -8166,7 +8166,7 @@
         <v>99.65251600000001</v>
       </c>
       <c r="K102" s="6" t="n">
-        <v>97.75468600000001</v>
+        <v>97.748147</v>
       </c>
       <c r="L102" s="6" t="n">
         <v>99.45335799999999</v>
@@ -8248,7 +8248,7 @@
         <v>99.498215</v>
       </c>
       <c r="K103" s="9" t="n">
-        <v>97.605265</v>
+        <v>97.598297</v>
       </c>
       <c r="L103" s="9" t="n">
         <v>99.373966</v>
@@ -8330,7 +8330,7 @@
         <v>99.344427</v>
       </c>
       <c r="K104" s="6" t="n">
-        <v>97.48639799999999</v>
+        <v>97.479089</v>
       </c>
       <c r="L104" s="6" t="n">
         <v>99.29294</v>
@@ -8412,7 +8412,7 @@
         <v>99.214026</v>
       </c>
       <c r="K105" s="9" t="n">
-        <v>97.414941</v>
+        <v>97.407427</v>
       </c>
       <c r="L105" s="9" t="n">
         <v>99.214922</v>
@@ -8494,7 +8494,7 @@
         <v>99.126301</v>
       </c>
       <c r="K106" s="6" t="n">
-        <v>97.41417199999999</v>
+        <v>97.406656</v>
       </c>
       <c r="L106" s="6" t="n">
         <v>99.140293</v>
@@ -8576,7 +8576,7 @@
         <v>99.09372500000001</v>
       </c>
       <c r="K107" s="9" t="n">
-        <v>97.45710200000001</v>
+        <v>97.449709</v>
       </c>
       <c r="L107" s="9" t="n">
         <v>99.06838399999999</v>
@@ -8658,7 +8658,7 @@
         <v>99.118274</v>
       </c>
       <c r="K108" s="6" t="n">
-        <v>97.554169</v>
+        <v>97.547055</v>
       </c>
       <c r="L108" s="6" t="n">
         <v>99.000872</v>
@@ -8740,7 +8740,7 @@
         <v>99.223685</v>
       </c>
       <c r="K109" s="9" t="n">
-        <v>97.712599</v>
+        <v>97.70594</v>
       </c>
       <c r="L109" s="9" t="n">
         <v>98.94105</v>
@@ -8822,7 +8822,7 @@
         <v>99.37857</v>
       </c>
       <c r="K110" s="6" t="n">
-        <v>97.913828</v>
+        <v>97.907746</v>
       </c>
       <c r="L110" s="6" t="n">
         <v>98.898489</v>
@@ -8904,7 +8904,7 @@
         <v>99.56629599999999</v>
       </c>
       <c r="K111" s="9" t="n">
-        <v>98.11767999999999</v>
+        <v>98.112183</v>
       </c>
       <c r="L111" s="9" t="n">
         <v>98.88025399999999</v>
@@ -8986,7 +8986,7 @@
         <v>99.756648</v>
       </c>
       <c r="K112" s="6" t="n">
-        <v>98.26485700000001</v>
+        <v>98.259783</v>
       </c>
       <c r="L112" s="6" t="n">
         <v>98.884218</v>
@@ -9068,7 +9068,7 @@
         <v>99.91161099999999</v>
       </c>
       <c r="K113" s="9" t="n">
-        <v>98.35598</v>
+        <v>98.351167</v>
       </c>
       <c r="L113" s="9" t="n">
         <v>98.903593</v>
@@ -9150,7 +9150,7 @@
         <v>100.021448</v>
       </c>
       <c r="K114" s="6" t="n">
-        <v>98.400333</v>
+        <v>98.39564900000001</v>
       </c>
       <c r="L114" s="6" t="n">
         <v>98.93374300000001</v>
@@ -9232,7 +9232,7 @@
         <v>100.091487</v>
       </c>
       <c r="K115" s="9" t="n">
-        <v>98.43590399999999</v>
+        <v>98.43132199999999</v>
       </c>
       <c r="L115" s="9" t="n">
         <v>98.972877</v>
@@ -9314,7 +9314,7 @@
         <v>100.135738</v>
       </c>
       <c r="K116" s="6" t="n">
-        <v>98.500176</v>
+        <v>98.495778</v>
       </c>
       <c r="L116" s="6" t="n">
         <v>99.015461</v>
@@ -9396,7 +9396,7 @@
         <v>100.164851</v>
       </c>
       <c r="K117" s="9" t="n">
-        <v>98.618269</v>
+        <v>98.614211</v>
       </c>
       <c r="L117" s="9" t="n">
         <v>99.065478</v>
@@ -9478,7 +9478,7 @@
         <v>100.171526</v>
       </c>
       <c r="K118" s="6" t="n">
-        <v>98.78058799999999</v>
+        <v>98.776996</v>
       </c>
       <c r="L118" s="6" t="n">
         <v>99.129929</v>
@@ -9560,7 +9560,7 @@
         <v>100.14894</v>
       </c>
       <c r="K119" s="9" t="n">
-        <v>98.98394399999999</v>
+        <v>98.980935</v>
       </c>
       <c r="L119" s="9" t="n">
         <v>99.213256</v>
@@ -9642,7 +9642,7 @@
         <v>100.084684</v>
       </c>
       <c r="K120" s="6" t="n">
-        <v>99.214545</v>
+        <v>99.212197</v>
       </c>
       <c r="L120" s="6" t="n">
         <v>99.314172</v>
@@ -9724,7 +9724,7 @@
         <v>99.99437</v>
       </c>
       <c r="K121" s="9" t="n">
-        <v>99.442705</v>
+        <v>99.441013</v>
       </c>
       <c r="L121" s="9" t="n">
         <v>99.42949299999999</v>
@@ -9806,7 +9806,7 @@
         <v>99.89514699999999</v>
       </c>
       <c r="K122" s="6" t="n">
-        <v>99.62115799999999</v>
+        <v>99.619978</v>
       </c>
       <c r="L122" s="6" t="n">
         <v>99.552221</v>
@@ -9888,7 +9888,7 @@
         <v>99.82761499999999</v>
       </c>
       <c r="K123" s="9" t="n">
-        <v>99.66643500000001</v>
+        <v>99.665385</v>
       </c>
       <c r="L123" s="9" t="n">
         <v>99.678282</v>
@@ -9970,7 +9970,7 @@
         <v>99.819779</v>
       </c>
       <c r="K124" s="6" t="n">
-        <v>99.616951</v>
+        <v>99.61575999999999</v>
       </c>
       <c r="L124" s="6" t="n">
         <v>99.801605</v>
@@ -10052,7 +10052,7 @@
         <v>99.88598500000001</v>
       </c>
       <c r="K125" s="9" t="n">
-        <v>99.507013</v>
+        <v>99.505506</v>
       </c>
       <c r="L125" s="9" t="n">
         <v>99.92883</v>
@@ -10134,7 +10134,7 @@
         <v>100.022931</v>
       </c>
       <c r="K126" s="6" t="n">
-        <v>99.340031</v>
+        <v>99.33804600000001</v>
       </c>
       <c r="L126" s="6" t="n">
         <v>100.067521</v>
@@ -10216,7 +10216,7 @@
         <v>100.198798</v>
       </c>
       <c r="K127" s="9" t="n">
-        <v>99.22066599999999</v>
+        <v>99.218339</v>
       </c>
       <c r="L127" s="9" t="n">
         <v>100.222544</v>
@@ -10298,7 +10298,7 @@
         <v>100.393776</v>
       </c>
       <c r="K128" s="6" t="n">
-        <v>99.24896200000001</v>
+        <v>99.24671600000001</v>
       </c>
       <c r="L128" s="6" t="n">
         <v>100.394328</v>
@@ -10380,7 +10380,7 @@
         <v>100.5642</v>
       </c>
       <c r="K129" s="9" t="n">
-        <v>99.384401</v>
+        <v>99.382544</v>
       </c>
       <c r="L129" s="9" t="n">
         <v>100.581786</v>
@@ -10462,7 +10462,7 @@
         <v>100.713116</v>
       </c>
       <c r="K130" s="6" t="n">
-        <v>99.60697500000001</v>
+        <v>99.605757</v>
       </c>
       <c r="L130" s="6" t="n">
         <v>100.778736</v>
@@ -10544,7 +10544,7 @@
         <v>100.821062</v>
       </c>
       <c r="K131" s="9" t="n">
-        <v>99.88468899999999</v>
+        <v>99.88426800000001</v>
       </c>
       <c r="L131" s="9" t="n">
         <v>100.98361</v>
@@ -10626,7 +10626,7 @@
         <v>100.881548</v>
       </c>
       <c r="K132" s="6" t="n">
-        <v>100.181375</v>
+        <v>100.181806</v>
       </c>
       <c r="L132" s="6" t="n">
         <v>101.192575</v>
@@ -10708,7 +10708,7 @@
         <v>100.889291</v>
       </c>
       <c r="K133" s="9" t="n">
-        <v>100.492003</v>
+        <v>100.493326</v>
       </c>
       <c r="L133" s="9" t="n">
         <v>101.401357</v>
@@ -10790,7 +10790,7 @@
         <v>100.850717</v>
       </c>
       <c r="K134" s="6" t="n">
-        <v>100.810063</v>
+        <v>100.812299</v>
       </c>
       <c r="L134" s="6" t="n">
         <v>101.604274</v>
@@ -10872,7 +10872,7 @@
         <v>100.777324</v>
       </c>
       <c r="K135" s="9" t="n">
-        <v>101.149559</v>
+        <v>101.15277</v>
       </c>
       <c r="L135" s="9" t="n">
         <v>101.795487</v>
@@ -10954,7 +10954,7 @@
         <v>100.678858</v>
       </c>
       <c r="K136" s="6" t="n">
-        <v>101.50124</v>
+        <v>101.505461</v>
       </c>
       <c r="L136" s="6" t="n">
         <v>101.975778</v>
@@ -11036,7 +11036,7 @@
         <v>100.583887</v>
       </c>
       <c r="K137" s="9" t="n">
-        <v>101.749734</v>
+        <v>101.754668</v>
       </c>
       <c r="L137" s="9" t="n">
         <v>102.145559</v>
@@ -11118,7 +11118,7 @@
         <v>100.516886</v>
       </c>
       <c r="K138" s="6" t="n">
-        <v>101.909866</v>
+        <v>101.91526</v>
       </c>
       <c r="L138" s="6" t="n">
         <v>102.300413</v>
@@ -11200,7 +11200,7 @@
         <v>100.473741</v>
       </c>
       <c r="K139" s="9" t="n">
-        <v>101.988702</v>
+        <v>101.994321</v>
       </c>
       <c r="L139" s="9" t="n">
         <v>102.438604</v>
@@ -11282,7 +11282,7 @@
         <v>100.448523</v>
       </c>
       <c r="K140" s="6" t="n">
-        <v>102.03686</v>
+        <v>102.042615</v>
       </c>
       <c r="L140" s="6" t="n">
         <v>102.558045</v>
@@ -11364,7 +11364,7 @@
         <v>100.439758</v>
       </c>
       <c r="K141" s="9" t="n">
-        <v>102.074398</v>
+        <v>102.080255</v>
       </c>
       <c r="L141" s="9" t="n">
         <v>102.658359</v>
@@ -11446,7 +11446,7 @@
         <v>100.424242</v>
       </c>
       <c r="K142" s="6" t="n">
-        <v>102.095122</v>
+        <v>102.101033</v>
       </c>
       <c r="L142" s="6" t="n">
         <v>102.742039</v>
@@ -11528,7 +11528,7 @@
         <v>100.399291</v>
       </c>
       <c r="K143" s="9" t="n">
-        <v>102.106415</v>
+        <v>102.112351</v>
       </c>
       <c r="L143" s="9" t="n">
         <v>102.803434</v>
@@ -11610,7 +11610,7 @@
         <v>100.383255</v>
       </c>
       <c r="K144" s="6" t="n">
-        <v>102.157903</v>
+        <v>102.16398</v>
       </c>
       <c r="L144" s="6" t="n">
         <v>102.840748</v>
@@ -11692,7 +11692,7 @@
         <v>100.377672</v>
       </c>
       <c r="K145" s="9" t="n">
-        <v>102.279108</v>
+        <v>102.285528</v>
       </c>
       <c r="L145" s="9" t="n">
         <v>102.858978</v>
@@ -11774,7 +11774,7 @@
         <v>100.394328</v>
       </c>
       <c r="K146" s="6" t="n">
-        <v>102.516068</v>
+        <v>102.523173</v>
       </c>
       <c r="L146" s="6" t="n">
         <v>102.861156</v>
@@ -11856,7 +11856,7 @@
         <v>100.426646</v>
       </c>
       <c r="K147" s="9" t="n">
-        <v>102.893429</v>
+        <v>102.901625</v>
       </c>
       <c r="L147" s="9" t="n">
         <v>102.846857</v>
@@ -11938,7 +11938,7 @@
         <v>100.433171</v>
       </c>
       <c r="K148" s="6" t="n">
-        <v>103.358702</v>
+        <v>103.368241</v>
       </c>
       <c r="L148" s="6" t="n">
         <v>102.809611</v>
@@ -12020,7 +12020,7 @@
         <v>100.436831</v>
       </c>
       <c r="K149" s="9" t="n">
-        <v>103.837194</v>
+        <v>103.848114</v>
       </c>
       <c r="L149" s="9" t="n">
         <v>102.745111</v>
@@ -12102,7 +12102,7 @@
         <v>100.475893</v>
       </c>
       <c r="K150" s="6" t="n">
-        <v>104.269634</v>
+        <v>104.2818</v>
       </c>
       <c r="L150" s="6" t="n">
         <v>102.648853</v>
@@ -12184,7 +12184,7 @@
         <v>100.580804</v>
       </c>
       <c r="K151" s="9" t="n">
-        <v>104.612728</v>
+        <v>104.625881</v>
       </c>
       <c r="L151" s="9" t="n">
         <v>102.518122</v>
@@ -12266,7 +12266,7 @@
         <v>100.719605</v>
       </c>
       <c r="K152" s="6" t="n">
-        <v>104.775175</v>
+        <v>104.788795</v>
       </c>
       <c r="L152" s="6" t="n">
         <v>102.356779</v>
@@ -12348,7 +12348,7 @@
         <v>100.835197</v>
       </c>
       <c r="K153" s="9" t="n">
-        <v>104.68406</v>
+        <v>104.697419</v>
       </c>
       <c r="L153" s="9" t="n">
         <v>102.1753</v>
@@ -12430,7 +12430,7 @@
         <v>100.933559</v>
       </c>
       <c r="K154" s="6" t="n">
-        <v>104.382801</v>
+        <v>104.395293</v>
       </c>
       <c r="L154" s="6" t="n">
         <v>101.990745</v>
@@ -12512,7 +12512,7 @@
         <v>100.984516</v>
       </c>
       <c r="K155" s="9" t="n">
-        <v>103.980196</v>
+        <v>103.991529</v>
       </c>
       <c r="L155" s="9" t="n">
         <v>101.815565</v>
@@ -12594,7 +12594,7 @@
         <v>100.970039</v>
       </c>
       <c r="K156" s="6" t="n">
-        <v>103.560859</v>
+        <v>103.570982</v>
       </c>
       <c r="L156" s="6" t="n">
         <v>101.658723</v>
@@ -12676,7 +12676,7 @@
         <v>100.897102</v>
       </c>
       <c r="K157" s="9" t="n">
-        <v>103.185515</v>
+        <v>103.194555</v>
       </c>
       <c r="L157" s="9" t="n">
         <v>101.516383</v>
@@ -12758,7 +12758,7 @@
         <v>100.806405</v>
       </c>
       <c r="K158" s="6" t="n">
-        <v>102.913052</v>
+        <v>102.921303</v>
       </c>
       <c r="L158" s="6" t="n">
         <v>101.384932</v>
@@ -12840,7 +12840,7 @@
         <v>100.70739</v>
       </c>
       <c r="K159" s="9" t="n">
-        <v>102.749224</v>
+        <v>102.757004</v>
       </c>
       <c r="L159" s="9" t="n">
         <v>101.263042</v>
@@ -12922,7 +12922,7 @@
         <v>100.622121</v>
       </c>
       <c r="K160" s="6" t="n">
-        <v>102.691821</v>
+        <v>102.699444</v>
       </c>
       <c r="L160" s="6" t="n">
         <v>101.157358</v>
@@ -13004,7 +13004,7 @@
         <v>100.585203</v>
       </c>
       <c r="K161" s="9" t="n">
-        <v>102.716523</v>
+        <v>102.724229</v>
       </c>
       <c r="L161" s="9" t="n">
         <v>101.073739</v>
@@ -13086,7 +13086,7 @@
         <v>100.605382</v>
       </c>
       <c r="K162" s="6" t="n">
-        <v>102.746672</v>
+        <v>102.75448</v>
       </c>
       <c r="L162" s="6" t="n">
         <v>101.014253</v>
@@ -13168,7 +13168,7 @@
         <v>100.668895</v>
       </c>
       <c r="K163" s="9" t="n">
-        <v>102.715374</v>
+        <v>102.723108</v>
       </c>
       <c r="L163" s="9" t="n">
         <v>100.971649</v>
@@ -13250,7 +13250,7 @@
         <v>100.713691</v>
       </c>
       <c r="K164" s="6" t="n">
-        <v>102.58826</v>
+        <v>102.595642</v>
       </c>
       <c r="L164" s="6" t="n">
         <v>100.930429</v>
@@ -13332,7 +13332,7 @@
         <v>100.711516</v>
       </c>
       <c r="K165" s="9" t="n">
-        <v>102.345592</v>
+        <v>102.352284</v>
       </c>
       <c r="L165" s="9" t="n">
         <v>100.86669</v>
@@ -13414,7 +13414,7 @@
         <v>100.676673</v>
       </c>
       <c r="K166" s="6" t="n">
-        <v>101.99878</v>
+        <v>102.004471</v>
       </c>
       <c r="L166" s="6" t="n">
         <v>100.758145</v>
@@ -13496,7 +13496,7 @@
         <v>100.629852</v>
       </c>
       <c r="K167" s="9" t="n">
-        <v>101.570928</v>
+        <v>101.575376</v>
       </c>
       <c r="L167" s="9" t="n">
         <v>100.596356</v>
@@ -13578,7 +13578,7 @@
         <v>100.594988</v>
       </c>
       <c r="K168" s="6" t="n">
-        <v>101.094371</v>
+        <v>101.097429</v>
       </c>
       <c r="L168" s="6" t="n">
         <v>100.386373</v>
@@ -13660,7 +13660,7 @@
         <v>100.579165</v>
       </c>
       <c r="K169" s="9" t="n">
-        <v>100.611334</v>
+        <v>100.612974</v>
       </c>
       <c r="L169" s="9" t="n">
         <v>100.147953</v>
@@ -13742,7 +13742,7 @@
         <v>100.591657</v>
       </c>
       <c r="K170" s="6" t="n">
-        <v>100.195008</v>
+        <v>100.195414</v>
       </c>
       <c r="L170" s="6" t="n">
         <v>99.91114899999999</v>
@@ -13824,7 +13824,7 @@
         <v>100.645569</v>
       </c>
       <c r="K171" s="9" t="n">
-        <v>99.97027799999999</v>
+        <v>99.969994</v>
       </c>
       <c r="L171" s="9" t="n">
         <v>99.706529</v>
@@ -13906,7 +13906,7 @@
         <v>100.746071</v>
       </c>
       <c r="K172" s="6" t="n">
-        <v>99.976355</v>
+        <v>99.976045</v>
       </c>
       <c r="L172" s="6" t="n">
         <v>99.55718299999999</v>
@@ -13988,7 +13988,7 @@
         <v>100.891962</v>
       </c>
       <c r="K173" s="9" t="n">
-        <v>100.23841</v>
+        <v>100.238827</v>
       </c>
       <c r="L173" s="9" t="n">
         <v>99.470354</v>
@@ -14070,7 +14070,7 @@
         <v>101.064597</v>
       </c>
       <c r="K174" s="6" t="n">
-        <v>100.673993</v>
+        <v>100.675683</v>
       </c>
       <c r="L174" s="6" t="n">
         <v>99.443833</v>
@@ -14152,7 +14152,7 @@
         <v>101.249497</v>
       </c>
       <c r="K175" s="9" t="n">
-        <v>101.179567</v>
+        <v>101.18275</v>
       </c>
       <c r="L175" s="9" t="n">
         <v>99.473946</v>
@@ -14234,7 +14234,7 @@
         <v>101.436302</v>
       </c>
       <c r="K176" s="6" t="n">
-        <v>101.648286</v>
+        <v>101.652857</v>
       </c>
       <c r="L176" s="6" t="n">
         <v>99.546986</v>
@@ -14316,7 +14316,7 @@
         <v>101.587182</v>
       </c>
       <c r="K177" s="9" t="n">
-        <v>102.058611</v>
+        <v>102.064394</v>
       </c>
       <c r="L177" s="9" t="n">
         <v>99.649176</v>
@@ -14398,7 +14398,7 @@
         <v>101.645416</v>
       </c>
       <c r="K178" s="6" t="n">
-        <v>102.385726</v>
+        <v>102.392473</v>
       </c>
       <c r="L178" s="6" t="n">
         <v>99.763194</v>
@@ -14480,7 +14480,7 @@
         <v>101.646356</v>
       </c>
       <c r="K179" s="9" t="n">
-        <v>102.606225</v>
+        <v>102.61362</v>
       </c>
       <c r="L179" s="9" t="n">
         <v>99.875409</v>
@@ -14562,7 +14562,7 @@
         <v>101.60753</v>
       </c>
       <c r="K180" s="6" t="n">
-        <v>102.719833</v>
+        <v>102.727561</v>
       </c>
       <c r="L180" s="6" t="n">
         <v>99.97479300000001</v>
@@ -14644,7 +14644,7 @@
         <v>101.520787</v>
       </c>
       <c r="K181" s="9" t="n">
-        <v>102.738243</v>
+        <v>102.746027</v>
       </c>
       <c r="L181" s="9" t="n">
         <v>100.042809</v>
@@ -14726,7 +14726,7 @@
         <v>101.345569</v>
       </c>
       <c r="K182" s="6" t="n">
-        <v>102.642848</v>
+        <v>102.650359</v>
       </c>
       <c r="L182" s="6" t="n">
         <v>100.05591</v>
@@ -14808,7 +14808,7 @@
         <v>101.039601</v>
       </c>
       <c r="K183" s="9" t="n">
-        <v>102.413085</v>
+        <v>102.419935</v>
       </c>
       <c r="L183" s="9" t="n">
         <v>99.990298</v>
@@ -14890,7 +14890,7 @@
         <v>100.574121</v>
       </c>
       <c r="K184" s="6" t="n">
-        <v>102.043048</v>
+        <v>102.048834</v>
       </c>
       <c r="L184" s="6" t="n">
         <v>99.81297000000001</v>
@@ -14972,7 +14972,7 @@
         <v>99.934015</v>
       </c>
       <c r="K185" s="9" t="n">
-        <v>101.536147</v>
+        <v>101.540476</v>
       </c>
       <c r="L185" s="9" t="n">
         <v>99.50678000000001</v>
@@ -15054,7 +15054,7 @@
         <v>99.137669</v>
       </c>
       <c r="K186" s="6" t="n">
-        <v>100.911013</v>
+        <v>100.913547</v>
       </c>
       <c r="L186" s="6" t="n">
         <v>99.077691</v>
@@ -15136,7 +15136,7 @@
         <v>98.270432</v>
       </c>
       <c r="K187" s="9" t="n">
-        <v>100.078365</v>
+        <v>100.078509</v>
       </c>
       <c r="L187" s="9" t="n">
         <v>98.550358</v>
@@ -15218,7 +15218,7 @@
         <v>97.439623</v>
       </c>
       <c r="K188" s="6" t="n">
-        <v>99.057491</v>
+        <v>99.054705</v>
       </c>
       <c r="L188" s="6" t="n">
         <v>97.976395</v>
@@ -15300,7 +15300,7 @@
         <v>96.732235</v>
       </c>
       <c r="K189" s="9" t="n">
-        <v>97.941221</v>
+        <v>97.935231</v>
       </c>
       <c r="L189" s="9" t="n">
         <v>97.410459</v>
@@ -15382,7 +15382,7 @@
         <v>96.230881</v>
       </c>
       <c r="K190" s="6" t="n">
-        <v>96.96925299999999</v>
+        <v>96.96047299999999</v>
       </c>
       <c r="L190" s="6" t="n">
         <v>96.888695</v>
@@ -15464,7 +15464,7 @@
         <v>95.961422</v>
       </c>
       <c r="K191" s="9" t="n">
-        <v>96.250635</v>
+        <v>96.23979300000001</v>
       </c>
       <c r="L191" s="9" t="n">
         <v>96.439447</v>
@@ -15546,7 +15546,7 @@
         <v>95.90942200000001</v>
       </c>
       <c r="K192" s="6" t="n">
-        <v>95.790237</v>
+        <v>95.778074</v>
       </c>
       <c r="L192" s="6" t="n">
         <v>96.07941700000001</v>
@@ -15628,7 +15628,7 @@
         <v>96.044656</v>
       </c>
       <c r="K193" s="9" t="n">
-        <v>95.54873499999999</v>
+        <v>95.535878</v>
       </c>
       <c r="L193" s="9" t="n">
         <v>95.820037</v>
@@ -15710,7 +15710,7 @@
         <v>96.334616</v>
       </c>
       <c r="K194" s="6" t="n">
-        <v>95.460396</v>
+        <v>95.44728499999999</v>
       </c>
       <c r="L194" s="6" t="n">
         <v>95.665671</v>
@@ -15792,7 +15792,7 @@
         <v>96.731908</v>
       </c>
       <c r="K195" s="9" t="n">
-        <v>95.478105</v>
+        <v>95.465045</v>
       </c>
       <c r="L195" s="9" t="n">
         <v>95.61212999999999</v>
@@ -15874,7 +15874,7 @@
         <v>97.182171</v>
       </c>
       <c r="K196" s="6" t="n">
-        <v>95.572959</v>
+        <v>95.56017</v>
       </c>
       <c r="L196" s="6" t="n">
         <v>95.651477</v>
@@ -15956,7 +15956,7 @@
         <v>97.62759200000001</v>
       </c>
       <c r="K197" s="9" t="n">
-        <v>95.72209599999999</v>
+        <v>95.70973499999999</v>
       </c>
       <c r="L197" s="9" t="n">
         <v>95.772733</v>
@@ -16038,7 +16038,7 @@
         <v>97.977828</v>
       </c>
       <c r="K198" s="6" t="n">
-        <v>95.94280000000001</v>
+        <v>95.931072</v>
       </c>
       <c r="L198" s="6" t="n">
         <v>95.960961</v>
@@ -16120,7 +16120,7 @@
         <v>98.22838</v>
       </c>
       <c r="K199" s="9" t="n">
-        <v>96.155137</v>
+        <v>96.144018</v>
       </c>
       <c r="L199" s="9" t="n">
         <v>96.19504499999999</v>
@@ -16202,7 +16202,7 @@
         <v>98.40828</v>
       </c>
       <c r="K200" s="6" t="n">
-        <v>96.319045</v>
+        <v>96.308395</v>
       </c>
       <c r="L200" s="6" t="n">
         <v>96.45236800000001</v>
@@ -16284,7 +16284,7 @@
         <v>98.537435</v>
       </c>
       <c r="K201" s="9" t="n">
-        <v>96.42022299999999</v>
+        <v>96.409863</v>
       </c>
       <c r="L201" s="9" t="n">
         <v>96.712782</v>
@@ -16366,7 +16366,7 @@
         <v>98.64779900000001</v>
       </c>
       <c r="K202" s="6" t="n">
-        <v>96.47741600000001</v>
+        <v>96.46722</v>
       </c>
       <c r="L202" s="6" t="n">
         <v>96.96629799999999</v>
@@ -16448,7 +16448,7 @@
         <v>98.744041</v>
       </c>
       <c r="K203" s="9" t="n">
-        <v>96.500541</v>
+        <v>96.49041</v>
       </c>
       <c r="L203" s="9" t="n">
         <v>97.207329</v>
@@ -16530,7 +16530,7 @@
         <v>98.825654</v>
       </c>
       <c r="K204" s="6" t="n">
-        <v>96.516373</v>
+        <v>96.506287</v>
       </c>
       <c r="L204" s="6" t="n">
         <v>97.435919</v>
@@ -16612,7 +16612,7 @@
         <v>98.91305199999999</v>
       </c>
       <c r="K205" s="9" t="n">
-        <v>96.552881</v>
+        <v>96.5429</v>
       </c>
       <c r="L205" s="9" t="n">
         <v>97.66217399999999</v>
@@ -16694,7 +16694,7 @@
         <v>99.024914</v>
       </c>
       <c r="K206" s="6" t="n">
-        <v>96.63799400000001</v>
+        <v>96.62825599999999</v>
       </c>
       <c r="L206" s="6" t="n">
         <v>97.896001</v>
@@ -16776,7 +16776,7 @@
         <v>99.163589</v>
       </c>
       <c r="K207" s="9" t="n">
-        <v>96.788833</v>
+        <v>96.779528</v>
       </c>
       <c r="L207" s="9" t="n">
         <v>98.148359</v>
@@ -16858,7 +16858,7 @@
         <v>99.30376</v>
       </c>
       <c r="K208" s="6" t="n">
-        <v>97.008837</v>
+        <v>97.000163</v>
       </c>
       <c r="L208" s="6" t="n">
         <v>98.421403</v>
@@ -16940,7 +16940,7 @@
         <v>99.421137</v>
       </c>
       <c r="K209" s="9" t="n">
-        <v>97.293414</v>
+        <v>97.285556</v>
       </c>
       <c r="L209" s="9" t="n">
         <v>98.71391300000001</v>
@@ -17022,7 +17022,7 @@
         <v>99.50055999999999</v>
       </c>
       <c r="K210" s="6" t="n">
-        <v>97.64757</v>
+        <v>97.640727</v>
       </c>
       <c r="L210" s="6" t="n">
         <v>99.018359</v>
@@ -17104,7 +17104,7 @@
         <v>99.588368</v>
       </c>
       <c r="K211" s="9" t="n">
-        <v>98.00141600000001</v>
+        <v>97.995588</v>
       </c>
       <c r="L211" s="9" t="n">
         <v>99.33840499999999</v>
@@ -17186,7 +17186,7 @@
         <v>99.708653</v>
       </c>
       <c r="K212" s="6" t="n">
-        <v>98.311964</v>
+        <v>98.30702599999999</v>
       </c>
       <c r="L212" s="6" t="n">
         <v>99.65942800000001</v>
@@ -17268,7 +17268,7 @@
         <v>99.86756200000001</v>
       </c>
       <c r="K213" s="9" t="n">
-        <v>98.571168</v>
+        <v>98.566974</v>
       </c>
       <c r="L213" s="9" t="n">
         <v>99.97058699999999</v>
@@ -17350,7 +17350,7 @@
         <v>100.051055</v>
       </c>
       <c r="K214" s="6" t="n">
-        <v>98.78951499999999</v>
+        <v>98.78594699999999</v>
       </c>
       <c r="L214" s="6" t="n">
         <v>100.255084</v>
@@ -17432,7 +17432,7 @@
         <v>100.242996</v>
       </c>
       <c r="K215" s="9" t="n">
-        <v>98.987549</v>
+        <v>98.984549</v>
       </c>
       <c r="L215" s="9" t="n">
         <v>100.493336</v>
@@ -17514,7 +17514,7 @@
         <v>100.429828</v>
       </c>
       <c r="K216" s="6" t="n">
-        <v>99.18158</v>
+        <v>99.179137</v>
       </c>
       <c r="L216" s="6" t="n">
         <v>100.672029</v>
@@ -17596,7 +17596,7 @@
         <v>100.606981</v>
       </c>
       <c r="K217" s="9" t="n">
-        <v>99.367919</v>
+        <v>99.36601</v>
       </c>
       <c r="L217" s="9" t="n">
         <v>100.779683</v>
@@ -17678,7 +17678,7 @@
         <v>100.777972</v>
       </c>
       <c r="K218" s="6" t="n">
-        <v>99.536793</v>
+        <v>99.53536800000001</v>
       </c>
       <c r="L218" s="6" t="n">
         <v>100.813832</v>
@@ -17760,7 +17760,7 @@
         <v>100.951876</v>
       </c>
       <c r="K219" s="9" t="n">
-        <v>99.690074</v>
+        <v>99.689088</v>
       </c>
       <c r="L219" s="9" t="n">
         <v>100.78481</v>
@@ -17842,7 +17842,7 @@
         <v>101.125506</v>
       </c>
       <c r="K220" s="6" t="n">
-        <v>99.817623</v>
+        <v>99.817003</v>
       </c>
       <c r="L220" s="6" t="n">
         <v>100.716317</v>
@@ -17924,7 +17924,7 @@
         <v>101.294793</v>
       </c>
       <c r="K221" s="9" t="n">
-        <v>99.93159900000001</v>
+        <v>99.93130499999999</v>
       </c>
       <c r="L221" s="9" t="n">
         <v>100.634413</v>
@@ -18006,7 +18006,7 @@
         <v>101.453255</v>
       </c>
       <c r="K222" s="6" t="n">
-        <v>100.04831</v>
+        <v>100.048351</v>
       </c>
       <c r="L222" s="6" t="n">
         <v>100.562551</v>
@@ -18088,7 +18088,7 @@
         <v>101.575128</v>
       </c>
       <c r="K223" s="9" t="n">
-        <v>100.172321</v>
+        <v>100.172717</v>
       </c>
       <c r="L223" s="9" t="n">
         <v>100.502471</v>
@@ -18170,7 +18170,7 @@
         <v>101.629326</v>
       </c>
       <c r="K224" s="6" t="n">
-        <v>100.277636</v>
+        <v>100.278334</v>
       </c>
       <c r="L224" s="6" t="n">
         <v>100.454243</v>
@@ -18252,7 +18252,7 @@
         <v>101.606158</v>
       </c>
       <c r="K225" s="9" t="n">
-        <v>100.349137</v>
+        <v>100.35004</v>
       </c>
       <c r="L225" s="9" t="n">
         <v>100.4139</v>
@@ -18334,7 +18334,7 @@
         <v>101.52207</v>
       </c>
       <c r="K226" s="6" t="n">
-        <v>100.376939</v>
+        <v>100.377922</v>
       </c>
       <c r="L226" s="6" t="n">
         <v>100.381088</v>
@@ -18416,7 +18416,7 @@
         <v>101.399451</v>
       </c>
       <c r="K227" s="9" t="n">
-        <v>100.350834</v>
+        <v>100.351741</v>
       </c>
       <c r="L227" s="9" t="n">
         <v>100.362406</v>
@@ -18498,7 +18498,7 @@
         <v>101.275459</v>
       </c>
       <c r="K228" s="6" t="n">
-        <v>100.269218</v>
+        <v>100.269891</v>
       </c>
       <c r="L228" s="6" t="n">
         <v>100.356367</v>
@@ -18580,7 +18580,7 @@
         <v>101.166954</v>
       </c>
       <c r="K229" s="9" t="n">
-        <v>100.131103</v>
+        <v>100.13138</v>
       </c>
       <c r="L229" s="9" t="n">
         <v>100.358212</v>
@@ -18662,7 +18662,7 @@
         <v>101.076699</v>
       </c>
       <c r="K230" s="6" t="n">
-        <v>99.91772400000001</v>
+        <v>99.917388</v>
       </c>
       <c r="L230" s="6" t="n">
         <v>100.366635</v>
@@ -18744,7 +18744,7 @@
         <v>101.009552</v>
       </c>
       <c r="K231" s="9" t="n">
-        <v>99.695739</v>
+        <v>99.694766</v>
       </c>
       <c r="L231" s="9" t="n">
         <v>100.379782</v>
@@ -18826,7 +18826,7 @@
         <v>100.963714</v>
       </c>
       <c r="K232" s="6" t="n">
-        <v>99.52135699999999</v>
+        <v>99.51988299999999</v>
       </c>
       <c r="L232" s="6" t="n">
         <v>100.39802</v>
@@ -18908,7 +18908,7 @@
         <v>100.9331</v>
       </c>
       <c r="K233" s="9" t="n">
-        <v>99.431949</v>
+        <v>99.430218</v>
       </c>
       <c r="L233" s="9" t="n">
         <v>100.423018</v>
@@ -18990,7 +18990,7 @@
         <v>100.900787</v>
       </c>
       <c r="K234" s="6" t="n">
-        <v>99.447104</v>
+        <v>99.44541599999999</v>
       </c>
       <c r="L234" s="6" t="n">
         <v>100.455249</v>
@@ -19072,7 +19072,7 @@
         <v>100.859061</v>
       </c>
       <c r="K235" s="9" t="n">
-        <v>99.563152</v>
+        <v>99.561797</v>
       </c>
       <c r="L235" s="9" t="n">
         <v>100.494933</v>
@@ -19154,7 +19154,7 @@
         <v>100.801514</v>
       </c>
       <c r="K236" s="6" t="n">
-        <v>99.738799</v>
+        <v>99.73794700000001</v>
       </c>
       <c r="L236" s="6" t="n">
         <v>100.54181</v>
@@ -19236,7 +19236,7 @@
         <v>100.724187</v>
       </c>
       <c r="K237" s="9" t="n">
-        <v>99.88226299999999</v>
+        <v>99.881823</v>
       </c>
       <c r="L237" s="9" t="n">
         <v>100.593761</v>
@@ -19318,7 +19318,7 @@
         <v>100.626892</v>
       </c>
       <c r="K238" s="6" t="n">
-        <v>100.010793</v>
+        <v>100.010722</v>
       </c>
       <c r="L238" s="6" t="n">
         <v>100.65059</v>
@@ -19400,7 +19400,7 @@
         <v>100.537404</v>
       </c>
       <c r="K239" s="9" t="n">
-        <v>100.113975</v>
+        <v>100.1142</v>
       </c>
       <c r="L239" s="9" t="n">
         <v>100.711124</v>
@@ -19482,7 +19482,7 @@
         <v>100.484594</v>
       </c>
       <c r="K240" s="6" t="n">
-        <v>100.151697</v>
+        <v>100.15203</v>
       </c>
       <c r="L240" s="6" t="n">
         <v>100.779653</v>
@@ -19564,7 +19564,7 @@
         <v>100.484384</v>
       </c>
       <c r="K241" s="9" t="n">
-        <v>100.165954</v>
+        <v>100.166327</v>
       </c>
       <c r="L241" s="9" t="n">
         <v>100.863838</v>
@@ -19646,7 +19646,7 @@
         <v>100.542596</v>
       </c>
       <c r="K242" s="6" t="n">
-        <v>100.195213</v>
+        <v>100.195671</v>
       </c>
       <c r="L242" s="6" t="n">
         <v>100.965499</v>
@@ -19728,7 +19728,7 @@
         <v>100.656932</v>
       </c>
       <c r="K243" s="9" t="n">
-        <v>100.251946</v>
+        <v>100.252566</v>
       </c>
       <c r="L243" s="9" t="n">
         <v>101.080452</v>
@@ -19810,7 +19810,7 @@
         <v>100.838893</v>
       </c>
       <c r="K244" s="6" t="n">
-        <v>100.331464</v>
+        <v>100.332312</v>
       </c>
       <c r="L244" s="6" t="n">
         <v>101.205421</v>
@@ -19892,7 +19892,7 @@
         <v>101.079707</v>
       </c>
       <c r="K245" s="9" t="n">
-        <v>100.428087</v>
+        <v>100.429212</v>
       </c>
       <c r="L245" s="9" t="n">
         <v>101.333791</v>
@@ -19974,7 +19974,7 @@
         <v>101.35663</v>
       </c>
       <c r="K246" s="6" t="n">
-        <v>100.551795</v>
+        <v>100.553274</v>
       </c>
       <c r="L246" s="6" t="n">
         <v>101.464669</v>
@@ -20056,7 +20056,7 @@
         <v>101.62921</v>
       </c>
       <c r="K247" s="9" t="n">
-        <v>100.700721</v>
+        <v>100.702628</v>
       </c>
       <c r="L247" s="9" t="n">
         <v>101.594272</v>
@@ -20138,7 +20138,7 @@
         <v>101.859607</v>
       </c>
       <c r="K248" s="6" t="n">
-        <v>100.883766</v>
+        <v>100.886198</v>
       </c>
       <c r="L248" s="6" t="n">
         <v>101.725532</v>
@@ -20220,7 +20220,7 @@
         <v>102.033326</v>
       </c>
       <c r="K249" s="9" t="n">
-        <v>101.105969</v>
+        <v>101.109039</v>
       </c>
       <c r="L249" s="9" t="n">
         <v>101.864546</v>
@@ -20302,7 +20302,7 @@
         <v>102.154063</v>
       </c>
       <c r="K250" s="6" t="n">
-        <v>101.333646</v>
+        <v>101.337369</v>
       </c>
       <c r="L250" s="6" t="n">
         <v>102.018747</v>
@@ -20384,7 +20384,7 @@
         <v>102.208027</v>
       </c>
       <c r="K251" s="9" t="n">
-        <v>101.534957</v>
+        <v>101.539257</v>
       </c>
       <c r="L251" s="9" t="n">
         <v>102.183681</v>
@@ -20466,7 +20466,7 @@
         <v>102.173246</v>
       </c>
       <c r="K252" s="6" t="n">
-        <v>101.681386</v>
+        <v>101.686106</v>
       </c>
       <c r="L252" s="6" t="n">
         <v>102.347064</v>
@@ -20548,7 +20548,7 @@
         <v>102.038919</v>
       </c>
       <c r="K253" s="9" t="n">
-        <v>101.767725</v>
+        <v>101.772693</v>
       </c>
       <c r="L253" s="9" t="n">
         <v>102.493415</v>
@@ -20630,7 +20630,7 @@
         <v>101.830198</v>
       </c>
       <c r="K254" s="6" t="n">
-        <v>101.795129</v>
+        <v>101.800175</v>
       </c>
       <c r="L254" s="6" t="n">
         <v>102.603847</v>
@@ -20712,7 +20712,7 @@
         <v>101.576997</v>
       </c>
       <c r="K255" s="9" t="n">
-        <v>101.766421</v>
+        <v>101.771385</v>
       </c>
       <c r="L255" s="9" t="n">
         <v>102.665559</v>
@@ -20794,7 +20794,7 @@
         <v>101.309641</v>
       </c>
       <c r="K256" s="6" t="n">
-        <v>101.702931</v>
+        <v>101.707713</v>
       </c>
       <c r="L256" s="6" t="n">
         <v>102.66886</v>
@@ -20876,7 +20876,7 @@
         <v>101.067279</v>
       </c>
       <c r="K257" s="9" t="n">
-        <v>101.632565</v>
+        <v>101.637145</v>
       </c>
       <c r="L257" s="9" t="n">
         <v>102.614546</v>
@@ -20958,7 +20958,7 @@
         <v>100.878504</v>
       </c>
       <c r="K258" s="6" t="n">
-        <v>101.567712</v>
+        <v>101.572106</v>
       </c>
       <c r="L258" s="6" t="n">
         <v>102.510288</v>
@@ -21040,7 +21040,7 @@
         <v>100.698913</v>
       </c>
       <c r="K259" s="9" t="n">
-        <v>101.477611</v>
+        <v>101.481747</v>
       </c>
       <c r="L259" s="9" t="n">
         <v>102.360796</v>
@@ -21122,7 +21122,7 @@
         <v>100.52203</v>
       </c>
       <c r="K260" s="6" t="n">
-        <v>101.344554</v>
+        <v>101.348308</v>
       </c>
       <c r="L260" s="6" t="n">
         <v>102.171199</v>
@@ -21204,7 +21204,7 @@
         <v>100.364493</v>
       </c>
       <c r="K261" s="9" t="n">
-        <v>101.174112</v>
+        <v>101.177377</v>
       </c>
       <c r="L261" s="9" t="n">
         <v>101.951559</v>
@@ -21286,7 +21286,7 @@
         <v>100.236657</v>
       </c>
       <c r="K262" s="6" t="n">
-        <v>100.990553</v>
+        <v>100.993291</v>
       </c>
       <c r="L262" s="6" t="n">
         <v>101.705424</v>
@@ -21368,7 +21368,7 @@
         <v>100.122309</v>
       </c>
       <c r="K263" s="9" t="n">
-        <v>100.817643</v>
+        <v>100.819885</v>
       </c>
       <c r="L263" s="9" t="n">
         <v>101.442132</v>
@@ -21450,7 +21450,7 @@
         <v>100.005972</v>
       </c>
       <c r="K264" s="6" t="n">
-        <v>100.66794</v>
+        <v>100.669753</v>
       </c>
       <c r="L264" s="6" t="n">
         <v>101.171947</v>
@@ -21532,7 +21532,7 @@
         <v>99.869801</v>
       </c>
       <c r="K265" s="9" t="n">
-        <v>100.55022</v>
+        <v>100.551696</v>
       </c>
       <c r="L265" s="9" t="n">
         <v>100.905403</v>
@@ -21614,7 +21614,7 @@
         <v>99.69949699999999</v>
       </c>
       <c r="K266" s="6" t="n">
-        <v>100.455605</v>
+        <v>100.45681</v>
       </c>
       <c r="L266" s="6" t="n">
         <v>100.655154</v>
@@ -21696,7 +21696,7 @@
         <v>99.48993400000001</v>
       </c>
       <c r="K267" s="9" t="n">
-        <v>100.371826</v>
+        <v>100.37279</v>
       </c>
       <c r="L267" s="9" t="n">
         <v>100.43561</v>
@@ -21778,7 +21778,7 @@
         <v>99.26567799999999</v>
       </c>
       <c r="K268" s="6" t="n">
-        <v>100.296692</v>
+        <v>100.297442</v>
       </c>
       <c r="L268" s="6" t="n">
         <v>100.252519</v>
@@ -21860,7 +21860,7 @@
         <v>99.032585</v>
       </c>
       <c r="K269" s="9" t="n">
-        <v>100.224022</v>
+        <v>100.224563</v>
       </c>
       <c r="L269" s="9" t="n">
         <v>100.105518</v>
@@ -21942,7 +21942,7 @@
         <v>98.817846</v>
       </c>
       <c r="K270" s="6" t="n">
-        <v>100.158442</v>
+        <v>100.158796</v>
       </c>
       <c r="L270" s="6" t="n">
         <v>99.988755</v>
@@ -22024,7 +22024,7 @@
         <v>98.66255</v>
       </c>
       <c r="K271" s="9" t="n">
-        <v>100.103399</v>
+        <v>100.103595</v>
       </c>
       <c r="L271" s="9" t="n">
         <v>99.903689</v>
@@ -22106,7 +22106,7 @@
         <v>98.605656</v>
       </c>
       <c r="K272" s="6" t="n">
-        <v>100.04936</v>
+        <v>100.049402</v>
       </c>
       <c r="L272" s="6" t="n">
         <v>99.84844</v>
@@ -22188,7 +22188,7 @@
         <v>98.630487</v>
       </c>
       <c r="K273" s="9" t="n">
-        <v>99.98881299999999</v>
+        <v>99.988682</v>
       </c>
       <c r="L273" s="9" t="n">
         <v>99.819211</v>
@@ -22270,7 +22270,7 @@
         <v>98.699488</v>
       </c>
       <c r="K274" s="6" t="n">
-        <v>99.92156</v>
+        <v>99.92123599999999</v>
       </c>
       <c r="L274" s="6" t="n">
         <v>99.80394200000001</v>
@@ -22352,7 +22352,7 @@
         <v>98.802305</v>
       </c>
       <c r="K275" s="9" t="n">
-        <v>99.84509799999999</v>
+        <v>99.844556</v>
       </c>
       <c r="L275" s="9" t="n">
         <v>99.789146</v>
@@ -22434,7 +22434,7 @@
         <v>98.92487</v>
       </c>
       <c r="K276" s="6" t="n">
-        <v>99.76624200000001</v>
+        <v>99.765474</v>
       </c>
       <c r="L276" s="6" t="n">
         <v>99.76751899999999</v>
@@ -22516,7 +22516,7 @@
         <v>99.04654499999999</v>
       </c>
       <c r="K277" s="9" t="n">
-        <v>99.682884</v>
+        <v>99.681878</v>
       </c>
       <c r="L277" s="9" t="n">
         <v>99.731506</v>
@@ -22598,7 +22598,7 @@
         <v>99.136026</v>
       </c>
       <c r="K278" s="6" t="n">
-        <v>99.591202</v>
+        <v>99.589933</v>
       </c>
       <c r="L278" s="6" t="n">
         <v>99.681707</v>
@@ -22680,7 +22680,7 @@
         <v>99.174533</v>
       </c>
       <c r="K279" s="9" t="n">
-        <v>99.499804</v>
+        <v>99.49827399999999</v>
       </c>
       <c r="L279" s="9" t="n">
         <v>99.614966</v>
@@ -22762,7 +22762,7 @@
         <v>99.144839</v>
       </c>
       <c r="K280" s="6" t="n">
-        <v>99.412802</v>
+        <v>99.411023</v>
       </c>
       <c r="L280" s="6" t="n">
         <v>99.53555799999999</v>
@@ -22844,7 +22844,7 @@
         <v>99.05958800000001</v>
       </c>
       <c r="K281" s="9" t="n">
-        <v>99.325695</v>
+        <v>99.323667</v>
       </c>
       <c r="L281" s="9" t="n">
         <v>99.445784</v>
@@ -22926,7 +22926,7 @@
         <v>98.96138500000001</v>
       </c>
       <c r="K282" s="6" t="n">
-        <v>99.23634800000001</v>
+        <v>99.234064</v>
       </c>
       <c r="L282" s="6" t="n">
         <v>99.344033</v>
@@ -23008,7 +23008,7 @@
         <v>98.894606</v>
       </c>
       <c r="K283" s="9" t="n">
-        <v>99.15377599999999</v>
+        <v>99.151257</v>
       </c>
       <c r="L283" s="9" t="n">
         <v>99.228668</v>
@@ -23090,7 +23090,7 @@
         <v>98.847508</v>
       </c>
       <c r="K284" s="6" t="n">
-        <v>99.084975</v>
+        <v>99.08225899999999</v>
       </c>
       <c r="L284" s="6" t="n">
         <v>99.09961</v>
@@ -23172,7 +23172,7 @@
         <v>98.820352</v>
       </c>
       <c r="K285" s="9" t="n">
-        <v>99.043097</v>
+        <v>99.040262</v>
       </c>
       <c r="L285" s="9" t="n">
         <v>98.95890199999999</v>
@@ -23254,7 +23254,7 @@
         <v>98.805173</v>
       </c>
       <c r="K286" s="6" t="n">
-        <v>99.027874</v>
+        <v>99.024997</v>
       </c>
       <c r="L286" s="6" t="n">
         <v>98.815286</v>
@@ -23336,7 +23336,7 @@
         <v>98.790729</v>
       </c>
       <c r="K287" s="9" t="n">
-        <v>99.03524299999999</v>
+        <v>99.03238899999999</v>
       </c>
       <c r="L287" s="9" t="n">
         <v>98.68198700000001</v>
@@ -23418,7 +23418,7 @@
         <v>98.769188</v>
       </c>
       <c r="K288" s="6" t="n">
-        <v>99.055537</v>
+        <v>99.05274199999999</v>
       </c>
       <c r="L288" s="6" t="n">
         <v>98.56939199999999</v>
@@ -23500,7 +23500,7 @@
         <v>98.752323</v>
       </c>
       <c r="K289" s="9" t="n">
-        <v>99.08980699999999</v>
+        <v>99.087112</v>
       </c>
       <c r="L289" s="9" t="n">
         <v>98.48859</v>
@@ -23582,7 +23582,7 @@
         <v>98.760479</v>
       </c>
       <c r="K290" s="6" t="n">
-        <v>99.145516</v>
+        <v>99.142983</v>
       </c>
       <c r="L290" s="6" t="n">
         <v>98.44544</v>
@@ -23664,7 +23664,7 @@
         <v>98.811851</v>
       </c>
       <c r="K291" s="9" t="n">
-        <v>99.228639</v>
+        <v>99.22634600000001</v>
       </c>
       <c r="L291" s="9" t="n">
         <v>98.433948</v>
@@ -23746,7 +23746,7 @@
         <v>98.910938</v>
       </c>
       <c r="K292" s="6" t="n">
-        <v>99.336675</v>
+        <v>99.334693</v>
       </c>
       <c r="L292" s="6" t="n">
         <v>98.44621100000001</v>
@@ -23828,7 +23828,7 @@
         <v>99.061953</v>
       </c>
       <c r="K293" s="9" t="n">
-        <v>99.466025</v>
+        <v>99.464417</v>
       </c>
       <c r="L293" s="9" t="n">
         <v>98.47429200000001</v>
@@ -23910,7 +23910,7 @@
         <v>99.237645</v>
       </c>
       <c r="K294" s="6" t="n">
-        <v>99.606852</v>
+        <v>99.60565</v>
       </c>
       <c r="L294" s="6" t="n">
         <v>98.512821</v>
@@ -23994,7 +23994,7 @@
         <v>99.416839</v>
       </c>
       <c r="K295" s="9" t="n">
-        <v>99.75336</v>
+        <v>99.75257999999999</v>
       </c>
       <c r="L295" s="9" t="n">
         <v>98.56082600000001</v>
@@ -24078,7 +24078,7 @@
         <v>99.576808</v>
       </c>
       <c r="K296" s="6" t="n">
-        <v>99.90554299999999</v>
+        <v>99.905202</v>
       </c>
       <c r="L296" s="6" t="n">
         <v>98.61641</v>
@@ -24162,7 +24162,7 @@
         <v>99.680408</v>
       </c>
       <c r="K297" s="9" t="n">
-        <v>100.044057</v>
+        <v>100.044115</v>
       </c>
       <c r="L297" s="9" t="n">
         <v>98.671498</v>
@@ -24246,7 +24246,7 @@
         <v>99.725283</v>
       </c>
       <c r="K298" s="6" t="n">
-        <v>100.155683</v>
+        <v>100.156064</v>
       </c>
       <c r="L298" s="6" t="n">
         <v>98.721891</v>
@@ -24330,7 +24330,7 @@
         <v>99.726805</v>
       </c>
       <c r="K299" s="9" t="n">
-        <v>100.248935</v>
+        <v>100.249586</v>
       </c>
       <c r="L299" s="9" t="n">
         <v>98.765805</v>
@@ -24414,7 +24414,7 @@
         <v>99.697169</v>
       </c>
       <c r="K300" s="6" t="n">
-        <v>100.33904</v>
+        <v>100.339951</v>
       </c>
       <c r="L300" s="6" t="n">
         <v>98.805159</v>
@@ -24498,7 +24498,7 @@
         <v>99.659879</v>
       </c>
       <c r="K301" s="9" t="n">
-        <v>100.422321</v>
+        <v>100.423474</v>
       </c>
       <c r="L301" s="9" t="n">
         <v>98.842484</v>
@@ -24582,7 +24582,7 @@
         <v>99.63108200000001</v>
       </c>
       <c r="K302" s="6" t="n">
-        <v>100.511676</v>
+        <v>100.513088</v>
       </c>
       <c r="L302" s="6" t="n">
         <v>98.879046</v>
@@ -24666,7 +24666,7 @@
         <v>99.61694900000001</v>
       </c>
       <c r="K303" s="9" t="n">
-        <v>100.59257</v>
+        <v>100.594217</v>
       </c>
       <c r="L303" s="9" t="n">
         <v>98.918227</v>
@@ -24750,7 +24750,7 @@
         <v>99.61451599999999</v>
       </c>
       <c r="K304" s="6" t="n">
-        <v>100.642998</v>
+        <v>100.644792</v>
       </c>
       <c r="L304" s="6" t="n">
         <v>98.963444</v>
@@ -24834,7 +24834,7 @@
         <v>99.619946</v>
       </c>
       <c r="K305" s="9" t="n">
-        <v>100.643966</v>
+        <v>100.645766</v>
       </c>
       <c r="L305" s="9" t="n">
         <v>99.008978</v>
@@ -24918,7 +24918,7 @@
         <v>99.625471</v>
       </c>
       <c r="K306" s="6" t="n">
-        <v>100.611988</v>
+        <v>100.613699</v>
       </c>
       <c r="L306" s="6" t="n">
         <v>99.051187</v>
@@ -25002,7 +25002,7 @@
         <v>99.623251</v>
       </c>
       <c r="K307" s="9" t="n">
-        <v>100.557763</v>
+        <v>100.559321</v>
       </c>
       <c r="L307" s="9" t="n">
         <v>99.087394</v>
@@ -25086,7 +25086,7 @@
         <v>99.608205</v>
       </c>
       <c r="K308" s="6" t="n">
-        <v>100.48503</v>
+        <v>100.486382</v>
       </c>
       <c r="L308" s="6" t="n">
         <v>99.119439</v>
@@ -25170,7 +25170,7 @@
         <v>99.587242</v>
       </c>
       <c r="K309" s="9" t="n">
-        <v>100.392663</v>
+        <v>100.393753</v>
       </c>
       <c r="L309" s="9" t="n">
         <v>99.15382200000001</v>
@@ -25254,7 +25254,7 @@
         <v>99.567359</v>
       </c>
       <c r="K310" s="6" t="n">
-        <v>100.312398</v>
+        <v>100.313261</v>
       </c>
       <c r="L310" s="6" t="n">
         <v>99.19474700000001</v>
@@ -25338,7 +25338,7 @@
         <v>99.56325200000001</v>
       </c>
       <c r="K311" s="9" t="n">
-        <v>100.260303</v>
+        <v>100.261019</v>
       </c>
       <c r="L311" s="9" t="n">
         <v>99.241946</v>
@@ -25422,7 +25422,7 @@
         <v>99.62327500000001</v>
       </c>
       <c r="K312" s="6" t="n">
-        <v>100.260721</v>
+        <v>100.261442</v>
       </c>
       <c r="L312" s="6" t="n">
         <v>99.296852</v>
@@ -25506,7 +25506,7 @@
         <v>99.78505800000001</v>
       </c>
       <c r="K313" s="9" t="n">
-        <v>100.299162</v>
+        <v>100.299997</v>
       </c>
       <c r="L313" s="9" t="n">
         <v>99.362253</v>
@@ -25590,7 +25590,7 @@
         <v>100.019083</v>
       </c>
       <c r="K314" s="6" t="n">
-        <v>100.347322</v>
+        <v>100.348298</v>
       </c>
       <c r="L314" s="6" t="n">
         <v>99.434291</v>
@@ -25674,7 +25674,7 @@
         <v>100.295076</v>
       </c>
       <c r="K315" s="9" t="n">
-        <v>100.369452</v>
+        <v>100.370495</v>
       </c>
       <c r="L315" s="9" t="n">
         <v>99.51062</v>
@@ -25758,7 +25758,7 @@
         <v>100.586443</v>
       </c>
       <c r="K316" s="6" t="n">
-        <v>100.375321</v>
+        <v>100.376384</v>
       </c>
       <c r="L316" s="6" t="n">
         <v>99.59127599999999</v>
@@ -25842,7 +25842,7 @@
         <v>100.855207</v>
       </c>
       <c r="K317" s="9" t="n">
-        <v>100.376468</v>
+        <v>100.377538</v>
       </c>
       <c r="L317" s="9" t="n">
         <v>99.67949400000001</v>
@@ -25926,7 +25926,7 @@
         <v>101.075279</v>
       </c>
       <c r="K318" s="6" t="n">
-        <v>100.373609</v>
+        <v>100.374674</v>
       </c>
       <c r="L318" s="6" t="n">
         <v>99.778583</v>
@@ -26010,7 +26010,7 @@
         <v>101.249857</v>
       </c>
       <c r="K319" s="9" t="n">
-        <v>100.360853</v>
+        <v>100.361885</v>
       </c>
       <c r="L319" s="9" t="n">
         <v>99.88722199999999</v>
@@ -26094,7 +26094,7 @@
         <v>101.400614</v>
       </c>
       <c r="K320" s="6" t="n">
-        <v>100.338976</v>
+        <v>100.339948</v>
       </c>
       <c r="L320" s="6" t="n">
         <v>100.002986</v>
@@ -26178,7 +26178,7 @@
         <v>101.529361</v>
       </c>
       <c r="K321" s="9" t="n">
-        <v>100.319182</v>
+        <v>100.3201</v>
       </c>
       <c r="L321" s="9" t="n">
         <v>100.121526</v>
@@ -26262,7 +26262,7 @@
         <v>101.634945</v>
       </c>
       <c r="K322" s="6" t="n">
-        <v>100.296158</v>
+        <v>100.297013</v>
       </c>
       <c r="L322" s="6" t="n">
         <v>100.239331</v>
@@ -26346,7 +26346,7 @@
         <v>101.70471</v>
       </c>
       <c r="K323" s="9" t="n">
-        <v>100.273877</v>
+        <v>100.27467</v>
       </c>
       <c r="L323" s="9" t="n">
         <v>100.353091</v>
@@ -26430,7 +26430,7 @@
         <v>101.737187</v>
       </c>
       <c r="K324" s="6" t="n">
-        <v>100.2593</v>
+        <v>100.260054</v>
       </c>
       <c r="L324" s="6" t="n">
         <v>100.459599</v>
@@ -26514,7 +26514,7 @@
         <v>101.736552</v>
       </c>
       <c r="K325" s="9" t="n">
-        <v>100.259375</v>
+        <v>100.260132</v>
       </c>
       <c r="L325" s="9" t="n">
         <v>100.557855</v>
@@ -26598,7 +26598,7 @@
         <v>101.706041</v>
       </c>
       <c r="K326" s="6" t="n">
-        <v>100.270614</v>
+        <v>100.271406</v>
       </c>
       <c r="L326" s="6" t="n">
         <v>100.650588</v>
@@ -26682,7 +26682,7 @@
         <v>101.661191</v>
       </c>
       <c r="K327" s="9" t="n">
-        <v>100.281872</v>
+        <v>100.2827</v>
       </c>
       <c r="L327" s="9" t="n">
         <v>100.741447</v>
@@ -26766,7 +26766,7 @@
         <v>101.617412</v>
       </c>
       <c r="K328" s="6" t="n">
-        <v>100.296229</v>
+        <v>100.297104</v>
       </c>
       <c r="L328" s="6" t="n">
         <v>100.834196</v>
@@ -26850,7 +26850,7 @@
         <v>101.590988</v>
       </c>
       <c r="K329" s="9" t="n">
-        <v>100.315116</v>
+        <v>100.316054</v>
       </c>
       <c r="L329" s="9" t="n">
         <v>100.931086</v>
@@ -26934,7 +26934,7 @@
         <v>101.60662</v>
       </c>
       <c r="K330" s="6" t="n">
-        <v>100.337885</v>
+        <v>100.3389</v>
       </c>
       <c r="L330" s="6" t="n">
         <v>101.034435</v>
@@ -27018,7 +27018,7 @@
         <v>101.663041</v>
       </c>
       <c r="K331" s="9" t="n">
-        <v>100.365142</v>
+        <v>100.366251</v>
       </c>
       <c r="L331" s="9" t="n">
         <v>101.138876</v>
@@ -27102,7 +27102,7 @@
         <v>101.73348</v>
       </c>
       <c r="K332" s="6" t="n">
-        <v>100.399774</v>
+        <v>100.401</v>
       </c>
       <c r="L332" s="6" t="n">
         <v>101.239138</v>
@@ -27186,7 +27186,7 @@
         <v>101.78549</v>
       </c>
       <c r="K333" s="9" t="n">
-        <v>100.452937</v>
+        <v>100.454335</v>
       </c>
       <c r="L333" s="9" t="n">
         <v>101.332629</v>
@@ -27270,7 +27270,7 @@
         <v>101.810185</v>
       </c>
       <c r="K334" s="6" t="n">
-        <v>100.527947</v>
+        <v>100.529574</v>
       </c>
       <c r="L334" s="6" t="n">
         <v>101.418797</v>
@@ -27354,7 +27354,7 @@
         <v>101.807483</v>
       </c>
       <c r="K335" s="9" t="n">
-        <v>100.617413</v>
+        <v>100.619294</v>
       </c>
       <c r="L335" s="9" t="n">
         <v>101.500618</v>
@@ -27438,7 +27438,7 @@
         <v>101.783563</v>
       </c>
       <c r="K336" s="6" t="n">
-        <v>100.70444</v>
+        <v>100.706536</v>
       </c>
       <c r="L336" s="6" t="n">
         <v>101.583306</v>
@@ -27522,7 +27522,7 @@
         <v>101.748897</v>
       </c>
       <c r="K337" s="9" t="n">
-        <v>100.777061</v>
+        <v>100.779278</v>
       </c>
       <c r="L337" s="9" t="n">
         <v>101.666105</v>
@@ -27606,7 +27606,7 @@
         <v>101.718082</v>
       </c>
       <c r="K338" s="6" t="n">
-        <v>100.830152</v>
+        <v>100.832357</v>
       </c>
       <c r="L338" s="6" t="n">
         <v>101.748682</v>
@@ -27690,7 +27690,7 @@
         <v>101.693324</v>
       </c>
       <c r="K339" s="9" t="n">
-        <v>100.864801</v>
+        <v>100.866847</v>
       </c>
       <c r="L339" s="9" t="n">
         <v>101.829521</v>
@@ -27774,7 +27774,7 @@
         <v>101.686671</v>
       </c>
       <c r="K340" s="6" t="n">
-        <v>100.890541</v>
+        <v>100.892303</v>
       </c>
       <c r="L340" s="6" t="n">
         <v>101.90382</v>
@@ -27858,7 +27858,7 @@
         <v>101.708757</v>
       </c>
       <c r="K341" s="9" t="n">
-        <v>100.917425</v>
+        <v>100.918839</v>
       </c>
       <c r="L341" s="9" t="n">
         <v>101.964273</v>
@@ -27942,7 +27942,7 @@
         <v>101.74514</v>
       </c>
       <c r="K342" s="6" t="n">
-        <v>100.956526</v>
+        <v>100.957647</v>
       </c>
       <c r="L342" s="6" t="n">
         <v>102.011084</v>
@@ -28026,7 +28026,7 @@
         <v>101.77598</v>
       </c>
       <c r="K343" s="9" t="n">
-        <v>100.981659</v>
+        <v>100.982653</v>
       </c>
       <c r="L343" s="9" t="n">
         <v>102.043142</v>
@@ -28110,7 +28110,7 @@
         <v>101.765745</v>
       </c>
       <c r="K344" s="6" t="n">
-        <v>100.98351</v>
+        <v>100.984733</v>
       </c>
       <c r="L344" s="6" t="n">
         <v>102.059054</v>
@@ -28194,7 +28194,7 @@
         <v>101.733837</v>
       </c>
       <c r="K345" s="9" t="n">
-        <v>100.966988</v>
+        <v>100.968518</v>
       </c>
       <c r="L345" s="9" t="n">
         <v>102.054679</v>
@@ -28278,7 +28278,7 @@
         <v>101.675774</v>
       </c>
       <c r="K346" s="6" t="n">
-        <v>100.920002</v>
+        <v>100.921826</v>
       </c>
       <c r="L346" s="6" t="n">
         <v>102.023885</v>
@@ -28362,7 +28362,7 @@
         <v>101.566637</v>
       </c>
       <c r="K347" s="9" t="n">
-        <v>100.843257</v>
+        <v>100.844978</v>
       </c>
       <c r="L347" s="9" t="n">
         <v>101.956562</v>
@@ -28446,7 +28446,7 @@
         <v>101.36948</v>
       </c>
       <c r="K348" s="6" t="n">
-        <v>100.737601</v>
+        <v>100.738959</v>
       </c>
       <c r="L348" s="6" t="n">
         <v>101.840977</v>
@@ -28530,7 +28530,7 @@
         <v>101.081784</v>
       </c>
       <c r="K349" s="9" t="n">
-        <v>100.60976</v>
+        <v>100.610764</v>
       </c>
       <c r="L349" s="9" t="n">
         <v>101.669757</v>
@@ -28614,7 +28614,7 @@
         <v>100.685638</v>
       </c>
       <c r="K350" s="6" t="n">
-        <v>100.475399</v>
+        <v>100.476352</v>
       </c>
       <c r="L350" s="6" t="n">
         <v>101.439009</v>
@@ -28698,7 +28698,7 @@
         <v>100.168217</v>
       </c>
       <c r="K351" s="9" t="n">
-        <v>100.347654</v>
+        <v>100.348684</v>
       </c>
       <c r="L351" s="9" t="n">
         <v>101.14673</v>
@@ -28782,7 +28782,7 @@
         <v>99.52229199999999</v>
       </c>
       <c r="K352" s="6" t="n">
-        <v>100.232412</v>
+        <v>100.233562</v>
       </c>
       <c r="L352" s="6" t="n">
         <v>100.797024</v>
@@ -28866,7 +28866,7 @@
         <v>98.787513</v>
       </c>
       <c r="K353" s="9" t="n">
-        <v>100.133465</v>
+        <v>100.134693</v>
       </c>
       <c r="L353" s="9" t="n">
         <v>100.403789</v>
@@ -28950,7 +28950,7 @@
         <v>98.03982000000001</v>
       </c>
       <c r="K354" s="6" t="n">
-        <v>100.04508</v>
+        <v>100.046103</v>
       </c>
       <c r="L354" s="6" t="n">
         <v>99.98400100000001</v>
@@ -29034,7 +29034,7 @@
         <v>97.406745</v>
       </c>
       <c r="K355" s="9" t="n">
-        <v>99.956264</v>
+        <v>99.956709</v>
       </c>
       <c r="L355" s="9" t="n">
         <v>99.56670800000001</v>
@@ -29118,7 +29118,7 @@
         <v>96.94794</v>
       </c>
       <c r="K356" s="6" t="n">
-        <v>99.86291300000001</v>
+        <v>99.86262000000001</v>
       </c>
       <c r="L356" s="6" t="n">
         <v>99.17800800000001</v>
@@ -29202,7 +29202,7 @@
         <v>96.68701799999999</v>
       </c>
       <c r="K357" s="9" t="n">
-        <v>99.756777</v>
+        <v>99.75608</v>
       </c>
       <c r="L357" s="9" t="n">
         <v>98.833833</v>
@@ -29286,7 +29286,7 @@
         <v>96.617347</v>
       </c>
       <c r="K358" s="6" t="n">
-        <v>99.65566</v>
+        <v>99.654662</v>
       </c>
       <c r="L358" s="6" t="n">
         <v>98.54447</v>
@@ -29370,7 +29370,7 @@
         <v>96.72145500000001</v>
       </c>
       <c r="K359" s="9" t="n">
-        <v>99.574326</v>
+        <v>99.57338300000001</v>
       </c>
       <c r="L359" s="9" t="n">
         <v>98.31887999999999</v>
@@ -29454,7 +29454,7 @@
         <v>96.96740699999999</v>
       </c>
       <c r="K360" s="6" t="n">
-        <v>99.513468</v>
+        <v>99.512595</v>
       </c>
       <c r="L360" s="6" t="n">
         <v>98.158868</v>
@@ -29538,7 +29538,7 @@
         <v>97.293564</v>
       </c>
       <c r="K361" s="9" t="n">
-        <v>99.465536</v>
+        <v>99.464564</v>
       </c>
       <c r="L361" s="9" t="n">
         <v>98.061081</v>
@@ -29622,7 +29622,7 @@
         <v>97.659549</v>
       </c>
       <c r="K362" s="6" t="n">
-        <v>99.43131</v>
+        <v>99.429982</v>
       </c>
       <c r="L362" s="6" t="n">
         <v>98.01920800000001</v>
@@ -29706,7 +29706,7 @@
         <v>98.020455</v>
       </c>
       <c r="K363" s="9" t="n">
-        <v>99.41036200000001</v>
+        <v>99.408844</v>
       </c>
       <c r="L363" s="9" t="n">
         <v>98.02971599999999</v>
@@ -29790,7 +29790,7 @@
         <v>98.34524</v>
       </c>
       <c r="K364" s="6" t="n">
-        <v>99.407606</v>
+        <v>99.40582499999999</v>
       </c>
       <c r="L364" s="6" t="n">
         <v>98.089327</v>
@@ -29874,7 +29874,7 @@
         <v>98.605819</v>
       </c>
       <c r="K365" s="9" t="n">
-        <v>99.422563</v>
+        <v>99.420489</v>
       </c>
       <c r="L365" s="9" t="n">
         <v>98.18641700000001</v>
@@ -29958,7 +29958,7 @@
         <v>98.801059</v>
       </c>
       <c r="K366" s="6" t="n">
-        <v>99.450855</v>
+        <v>99.448779</v>
       </c>
       <c r="L366" s="6" t="n">
         <v>98.306924</v>
@@ -30042,7 +30042,7 @@
         <v>98.95089299999999</v>
       </c>
       <c r="K367" s="9" t="n">
-        <v>99.49511099999999</v>
+        <v>99.493533</v>
       </c>
       <c r="L367" s="9" t="n">
         <v>98.43932100000001</v>
@@ -30126,7 +30126,7 @@
         <v>99.07379400000001</v>
       </c>
       <c r="K368" s="6" t="n">
-        <v>99.541842</v>
+        <v>99.54078</v>
       </c>
       <c r="L368" s="6" t="n">
         <v>98.572681</v>
@@ -30210,7 +30210,7 @@
         <v>99.159384</v>
       </c>
       <c r="K369" s="9" t="n">
-        <v>99.57778399999999</v>
+        <v>99.577088</v>
       </c>
       <c r="L369" s="9" t="n">
         <v>98.69810200000001</v>
@@ -30294,7 +30294,7 @@
         <v>99.19579299999999</v>
       </c>
       <c r="K370" s="6" t="n">
-        <v>99.603939</v>
+        <v>99.60337800000001</v>
       </c>
       <c r="L370" s="6" t="n">
         <v>98.81057300000001</v>
@@ -30378,7 +30378,7 @@
         <v>99.19694699999999</v>
       </c>
       <c r="K371" s="9" t="n">
-        <v>99.611013</v>
+        <v>99.610176</v>
       </c>
       <c r="L371" s="9" t="n">
         <v>98.90791400000001</v>
@@ -30462,7 +30462,7 @@
         <v>99.177706</v>
       </c>
       <c r="K372" s="6" t="n">
-        <v>99.60080499999999</v>
+        <v>99.599675</v>
       </c>
       <c r="L372" s="6" t="n">
         <v>98.99310699999999</v>
@@ -30546,7 +30546,7 @@
         <v>99.151837</v>
       </c>
       <c r="K373" s="9" t="n">
-        <v>99.576633</v>
+        <v>99.575132</v>
       </c>
       <c r="L373" s="9" t="n">
         <v>99.069782</v>
@@ -30630,7 +30630,7 @@
         <v>99.121506</v>
       </c>
       <c r="K374" s="6" t="n">
-        <v>99.533044</v>
+        <v>99.53141100000001</v>
       </c>
       <c r="L374" s="6" t="n">
         <v>99.14059399999999</v>
@@ -30714,7 +30714,7 @@
         <v>99.10315300000001</v>
       </c>
       <c r="K375" s="9" t="n">
-        <v>99.478324</v>
+        <v>99.47676800000001</v>
       </c>
       <c r="L375" s="9" t="n">
         <v>99.20860999999999</v>
@@ -30798,7 +30798,7 @@
         <v>99.107989</v>
       </c>
       <c r="K376" s="6" t="n">
-        <v>99.42358</v>
+        <v>99.422498</v>
       </c>
       <c r="L376" s="6" t="n">
         <v>99.27298500000001</v>
@@ -30882,7 +30882,7 @@
         <v>99.142107</v>
       </c>
       <c r="K377" s="9" t="n">
-        <v>99.395076</v>
+        <v>99.39439299999999</v>
       </c>
       <c r="L377" s="9" t="n">
         <v>99.332167</v>
@@ -30966,7 +30966,7 @@
         <v>99.19612100000001</v>
       </c>
       <c r="K378" s="6" t="n">
-        <v>99.375559</v>
+        <v>99.375062</v>
       </c>
       <c r="L378" s="6" t="n">
         <v>99.384793</v>
@@ -31050,7 +31050,7 @@
         <v>99.269543</v>
       </c>
       <c r="K379" s="9" t="n">
-        <v>99.360636</v>
+        <v>99.359846</v>
       </c>
       <c r="L379" s="9" t="n">
         <v>99.430361</v>
@@ -31134,7 +31134,7 @@
         <v>99.36842799999999</v>
       </c>
       <c r="K380" s="6" t="n">
-        <v>99.37269999999999</v>
+        <v>99.371391</v>
       </c>
       <c r="L380" s="6" t="n">
         <v>99.46854500000001</v>
@@ -31218,7 +31218,7 @@
         <v>99.48869999999999</v>
       </c>
       <c r="K381" s="9" t="n">
-        <v>99.407579</v>
+        <v>99.405869</v>
       </c>
       <c r="L381" s="9" t="n">
         <v>99.497806</v>
@@ -31302,7 +31302,7 @@
         <v>99.630185</v>
       </c>
       <c r="K382" s="6" t="n">
-        <v>99.447647</v>
+        <v>99.4457</v>
       </c>
       <c r="L382" s="6" t="n">
         <v>99.51745099999999</v>
@@ -31386,7 +31386,7 @@
         <v>99.780669</v>
       </c>
       <c r="K383" s="9" t="n">
-        <v>99.49385599999999</v>
+        <v>99.49186899999999</v>
       </c>
       <c r="L383" s="9" t="n">
         <v>99.532777</v>
@@ -31470,7 +31470,7 @@
         <v>99.93088400000001</v>
       </c>
       <c r="K384" s="6" t="n">
-        <v>99.554941</v>
+        <v>99.55290100000001</v>
       </c>
       <c r="L384" s="6" t="n">
         <v>99.54910700000001</v>
@@ -31554,7 +31554,7 @@
         <v>100.090452</v>
       </c>
       <c r="K385" s="9" t="n">
-        <v>99.64139400000001</v>
+        <v>99.639684</v>
       </c>
       <c r="L385" s="9" t="n">
         <v>99.570215</v>
@@ -31638,7 +31638,7 @@
         <v>100.265147</v>
       </c>
       <c r="K386" s="6" t="n">
-        <v>99.750096</v>
+        <v>99.74882599999999</v>
       </c>
       <c r="L386" s="6" t="n">
         <v>99.599389</v>
@@ -31722,7 +31722,7 @@
         <v>100.456892</v>
       </c>
       <c r="K387" s="9" t="n">
-        <v>99.87071400000001</v>
+        <v>99.870052</v>
       </c>
       <c r="L387" s="9" t="n">
         <v>99.63746500000001</v>
@@ -31806,7 +31806,7 @@
         <v>100.641121</v>
       </c>
       <c r="K388" s="6" t="n">
-        <v>100.000022</v>
+        <v>99.99978400000001</v>
       </c>
       <c r="L388" s="6" t="n">
         <v>99.684757</v>
@@ -31890,7 +31890,7 @@
         <v>100.793208</v>
       </c>
       <c r="K389" s="9" t="n">
-        <v>100.133444</v>
+        <v>100.13354</v>
       </c>
       <c r="L389" s="9" t="n">
         <v>99.74150899999999</v>
@@ -31974,7 +31974,7 @@
         <v>100.901147</v>
       </c>
       <c r="K390" s="6" t="n">
-        <v>100.251671</v>
+        <v>100.251953</v>
       </c>
       <c r="L390" s="6" t="n">
         <v>99.80497800000001</v>
@@ -32058,7 +32058,7 @@
         <v>100.968363</v>
       </c>
       <c r="K391" s="9" t="n">
-        <v>100.343198</v>
+        <v>100.343769</v>
       </c>
       <c r="L391" s="9" t="n">
         <v>99.86977</v>
@@ -32142,7 +32142,7 @@
         <v>101.004983</v>
       </c>
       <c r="K392" s="6" t="n">
-        <v>100.397579</v>
+        <v>100.398422</v>
       </c>
       <c r="L392" s="6" t="n">
         <v>99.93106400000001</v>
@@ -32226,7 +32226,7 @@
         <v>101.017521</v>
       </c>
       <c r="K393" s="9" t="n">
-        <v>100.417901</v>
+        <v>100.418693</v>
       </c>
       <c r="L393" s="9" t="n">
         <v>99.98683</v>
@@ -32310,7 +32310,7 @@
         <v>101.004797</v>
       </c>
       <c r="K394" s="6" t="n">
-        <v>100.413471</v>
+        <v>100.413961</v>
       </c>
       <c r="L394" s="6" t="n">
         <v>100.041283</v>
@@ -32394,7 +32394,7 @@
         <v>100.970435</v>
       </c>
       <c r="K395" s="9" t="n">
-        <v>100.394728</v>
+        <v>100.394821</v>
       </c>
       <c r="L395" s="9" t="n">
         <v>100.096492</v>
@@ -32478,7 +32478,7 @@
         <v>100.903814</v>
       </c>
       <c r="K396" s="6" t="n">
-        <v>100.370828</v>
+        <v>100.370633</v>
       </c>
       <c r="L396" s="6" t="n">
         <v>100.149178</v>
@@ -32562,7 +32562,7 @@
         <v>100.795328</v>
       </c>
       <c r="K397" s="9" t="n">
-        <v>100.355348</v>
+        <v>100.355277</v>
       </c>
       <c r="L397" s="9" t="n">
         <v>100.196955</v>
@@ -32646,7 +32646,7 @@
         <v>100.66385</v>
       </c>
       <c r="K398" s="6" t="n">
-        <v>100.325437</v>
+        <v>100.325709</v>
       </c>
       <c r="L398" s="6" t="n">
         <v>100.238385</v>
@@ -32730,7 +32730,7 @@
         <v>100.508824</v>
       </c>
       <c r="K399" s="9" t="n">
-        <v>100.261109</v>
+        <v>100.26201</v>
       </c>
       <c r="L399" s="9" t="n">
         <v>100.271204</v>
@@ -32814,7 +32814,7 @@
         <v>100.360917</v>
       </c>
       <c r="K400" s="6" t="n">
-        <v>100.17405</v>
+        <v>100.175342</v>
       </c>
       <c r="L400" s="6" t="n">
         <v>100.295719</v>
@@ -32898,7 +32898,7 @@
         <v>100.219762</v>
       </c>
       <c r="K401" s="9" t="n">
-        <v>100.086018</v>
+        <v>100.087265</v>
       </c>
       <c r="L401" s="9" t="n">
         <v>100.311138</v>
@@ -32982,7 +32982,7 @@
         <v>100.088888</v>
       </c>
       <c r="K402" s="6" t="n">
-        <v>100.024913</v>
+        <v>100.025711</v>
       </c>
       <c r="L402" s="6" t="n">
         <v>100.314671</v>
@@ -33066,7 +33066,7 @@
         <v>99.96141799999999</v>
       </c>
       <c r="K403" s="9" t="n">
-        <v>99.97686899999999</v>
+        <v>99.97709</v>
       </c>
       <c r="L403" s="9" t="n">
         <v>100.304761</v>
@@ -33150,7 +33150,7 @@
         <v>99.829155</v>
       </c>
       <c r="K404" s="6" t="n">
-        <v>99.935231</v>
+        <v>99.93495900000001</v>
       </c>
       <c r="L404" s="6" t="n">
         <v>100.281423</v>
@@ -33234,7 +33234,7 @@
         <v>99.71278</v>
       </c>
       <c r="K405" s="9" t="n">
-        <v>99.895686</v>
+        <v>99.895349</v>
       </c>
       <c r="L405" s="9" t="n">
         <v>100.246501</v>
@@ -33318,7 +33318,7 @@
         <v>99.629597</v>
       </c>
       <c r="K406" s="6" t="n">
-        <v>99.860005</v>
+        <v>99.85973199999999</v>
       </c>
       <c r="L406" s="6" t="n">
         <v>100.20246</v>
@@ -33402,7 +33402,7 @@
         <v>99.564835</v>
       </c>
       <c r="K407" s="9" t="n">
-        <v>99.81638</v>
+        <v>99.816146</v>
       </c>
       <c r="L407" s="9" t="n">
         <v>100.151369</v>
@@ -33486,7 +33486,7 @@
         <v>99.527833</v>
       </c>
       <c r="K408" s="6" t="n">
-        <v>99.760096</v>
+        <v>99.759885</v>
       </c>
       <c r="L408" s="6" t="n">
         <v>100.095988</v>
@@ -33570,7 +33570,7 @@
         <v>99.516475</v>
       </c>
       <c r="K409" s="9" t="n">
-        <v>99.688177</v>
+        <v>99.68767699999999</v>
       </c>
       <c r="L409" s="9" t="n">
         <v>100.039442</v>
@@ -33654,7 +33654,7 @@
         <v>99.521102</v>
       </c>
       <c r="K410" s="6" t="n">
-        <v>99.614542</v>
+        <v>99.613501</v>
       </c>
       <c r="L410" s="6" t="n">
         <v>99.98276</v>
@@ -33738,7 +33738,7 @@
         <v>99.554152</v>
       </c>
       <c r="K411" s="9" t="n">
-        <v>99.54498</v>
+        <v>99.54355</v>
       </c>
       <c r="L411" s="9" t="n">
         <v>99.927986</v>
@@ -33822,7 +33822,7 @@
         <v>99.61118999999999</v>
       </c>
       <c r="K412" s="6" t="n">
-        <v>99.48368499999999</v>
+        <v>99.482086</v>
       </c>
       <c r="L412" s="6" t="n">
         <v>99.87616</v>
@@ -33906,7 +33906,7 @@
         <v>99.700863</v>
       </c>
       <c r="K413" s="9" t="n">
-        <v>99.431759</v>
+        <v>99.43015699999999</v>
       </c>
       <c r="L413" s="9" t="n">
         <v>99.828113</v>
@@ -33990,7 +33990,7 @@
         <v>99.826043</v>
       </c>
       <c r="K414" s="6" t="n">
-        <v>99.401104</v>
+        <v>99.399823</v>
       </c>
       <c r="L414" s="6" t="n">
         <v>99.78765199999999</v>
@@ -34074,7 +34074,7 @@
         <v>99.983569</v>
       </c>
       <c r="K415" s="9" t="n">
-        <v>99.401213</v>
+        <v>99.40033200000001</v>
       </c>
       <c r="L415" s="9" t="n">
         <v>99.760356</v>
@@ -34158,7 +34158,7 @@
         <v>100.153452</v>
       </c>
       <c r="K416" s="6" t="n">
-        <v>99.422316</v>
+        <v>99.421667</v>
       </c>
       <c r="L416" s="6" t="n">
         <v>99.74726800000001</v>
@@ -34242,7 +34242,7 @@
         <v>100.295257</v>
       </c>
       <c r="K417" s="9" t="n">
-        <v>99.45326900000001</v>
+        <v>99.45246400000001</v>
       </c>
       <c r="L417" s="9" t="n">
         <v>99.74509500000001</v>
@@ -34326,7 +34326,7 @@
         <v>100.384612</v>
       </c>
       <c r="K418" s="6" t="n">
-        <v>99.47739</v>
+        <v>99.476305</v>
       </c>
       <c r="L418" s="6" t="n">
         <v>99.746015</v>
@@ -34410,7 +34410,7 @@
         <v>100.419364</v>
       </c>
       <c r="K419" s="9" t="n">
-        <v>99.493461</v>
+        <v>99.491794</v>
       </c>
       <c r="L419" s="9" t="n">
         <v>99.744907</v>
@@ -34494,7 +34494,7 @@
         <v>100.412135</v>
       </c>
       <c r="K420" s="6" t="n">
-        <v>99.50578899999999</v>
+        <v>99.503511</v>
       </c>
       <c r="L420" s="6" t="n">
         <v>99.74141400000001</v>
@@ -34578,7 +34578,7 @@
         <v>100.392867</v>
       </c>
       <c r="K421" s="9" t="n">
-        <v>99.520962</v>
+        <v>99.518345</v>
       </c>
       <c r="L421" s="9" t="n">
         <v>99.737787</v>
@@ -34662,7 +34662,7 @@
         <v>100.382709</v>
       </c>
       <c r="K422" s="6" t="n">
-        <v>99.54624800000001</v>
+        <v>99.54390600000001</v>
       </c>
       <c r="L422" s="6" t="n">
         <v>99.737934</v>
@@ -34746,7 +34746,7 @@
         <v>100.374417</v>
       </c>
       <c r="K423" s="9" t="n">
-        <v>99.59605500000001</v>
+        <v>99.594386</v>
       </c>
       <c r="L423" s="9" t="n">
         <v>99.745088</v>
@@ -34830,7 +34830,7 @@
         <v>100.352542</v>
       </c>
       <c r="K424" s="6" t="n">
-        <v>99.66585499999999</v>
+        <v>99.665059</v>
       </c>
       <c r="L424" s="6" t="n">
         <v>99.75875600000001</v>
@@ -34914,7 +34914,7 @@
         <v>100.321414</v>
       </c>
       <c r="K425" s="9" t="n">
-        <v>99.745029</v>
+        <v>99.745074</v>
       </c>
       <c r="L425" s="9" t="n">
         <v>99.777052</v>
@@ -34998,7 +34998,7 @@
         <v>100.296368</v>
       </c>
       <c r="K426" s="6" t="n">
-        <v>99.829702</v>
+        <v>99.83024399999999</v>
       </c>
       <c r="L426" s="6" t="n">
         <v>99.797504</v>
@@ -35082,7 +35082,7 @@
         <v>100.294732</v>
       </c>
       <c r="K427" s="9" t="n">
-        <v>99.908661</v>
+        <v>99.90929199999999</v>
       </c>
       <c r="L427" s="9" t="n">
         <v>99.817672</v>
@@ -35166,7 +35166,7 @@
         <v>100.319843</v>
       </c>
       <c r="K428" s="6" t="n">
-        <v>99.97863099999999</v>
+        <v>99.979212</v>
       </c>
       <c r="L428" s="6" t="n">
         <v>99.83668</v>
@@ -35250,7 +35250,7 @@
         <v>100.382161</v>
       </c>
       <c r="K429" s="9" t="n">
-        <v>100.043101</v>
+        <v>100.043758</v>
       </c>
       <c r="L429" s="9" t="n">
         <v>99.853525</v>
@@ -35334,7 +35334,7 @@
         <v>100.474625</v>
       </c>
       <c r="K430" s="6" t="n">
-        <v>100.106041</v>
+        <v>100.106733</v>
       </c>
       <c r="L430" s="6" t="n">
         <v>99.87008899999999</v>
@@ -35418,7 +35418,7 @@
         <v>100.604878</v>
       </c>
       <c r="K431" s="9" t="n">
-        <v>100.167669</v>
+        <v>100.168608</v>
       </c>
       <c r="L431" s="9" t="n">
         <v>99.88762699999999</v>
@@ -35502,7 +35502,7 @@
         <v>100.75284</v>
       </c>
       <c r="K432" s="6" t="n">
-        <v>100.223304</v>
+        <v>100.224451</v>
       </c>
       <c r="L432" s="6" t="n">
         <v>99.905023</v>
@@ -35586,7 +35586,7 @@
         <v>100.875865</v>
       </c>
       <c r="K433" s="9" t="n">
-        <v>100.26246</v>
+        <v>100.263607</v>
       </c>
       <c r="L433" s="9" t="n">
         <v>99.919095</v>
@@ -35670,7 +35670,7 @@
         <v>100.935262</v>
       </c>
       <c r="K434" s="6" t="n">
-        <v>100.283753</v>
+        <v>100.284649</v>
       </c>
       <c r="L434" s="6" t="n">
         <v>99.926748</v>
@@ -35754,7 +35754,7 @@
         <v>100.897003</v>
       </c>
       <c r="K435" s="9" t="n">
-        <v>100.298322</v>
+        <v>100.299052</v>
       </c>
       <c r="L435" s="9" t="n">
         <v>99.928811</v>
@@ -35838,7 +35838,7 @@
         <v>100.802066</v>
       </c>
       <c r="K436" s="6" t="n">
-        <v>100.324218</v>
+        <v>100.324722</v>
       </c>
       <c r="L436" s="6" t="n">
         <v>99.926316</v>
@@ -35922,7 +35922,7 @@
         <v>100.687725</v>
       </c>
       <c r="K437" s="9" t="n">
-        <v>100.3717</v>
+        <v>100.371951</v>
       </c>
       <c r="L437" s="9" t="n">
         <v>99.92084</v>
@@ -36006,7 +36006,7 @@
         <v>100.564657</v>
       </c>
       <c r="K438" s="6" t="n">
-        <v>100.437582</v>
+        <v>100.437756</v>
       </c>
       <c r="L438" s="6" t="n">
         <v>99.91552799999999</v>
@@ -36090,7 +36090,7 @@
         <v>100.439752</v>
       </c>
       <c r="K439" s="9" t="n">
-        <v>100.509397</v>
+        <v>100.509896</v>
       </c>
       <c r="L439" s="9" t="n">
         <v>99.912856</v>
@@ -36174,7 +36174,7 @@
         <v>100.32016</v>
       </c>
       <c r="K440" s="6" t="n">
-        <v>100.590122</v>
+        <v>100.590999</v>
       </c>
       <c r="L440" s="6" t="n">
         <v>99.91734099999999</v>
@@ -36258,7 +36258,7 @@
         <v>100.224722</v>
       </c>
       <c r="K441" s="9" t="n">
-        <v>100.680885</v>
+        <v>100.682113</v>
       </c>
       <c r="L441" s="9" t="n">
         <v>99.934405</v>
@@ -36342,7 +36342,7 @@
         <v>100.162078</v>
       </c>
       <c r="K442" s="6" t="n">
-        <v>100.780384</v>
+        <v>100.781951</v>
       </c>
       <c r="L442" s="6" t="n">
         <v>99.963785</v>
@@ -36426,7 +36426,7 @@
         <v>100.133649</v>
       </c>
       <c r="K443" s="9" t="n">
-        <v>100.882394</v>
+        <v>100.88436</v>
       </c>
       <c r="L443" s="9" t="n">
         <v>100.002612</v>
@@ -36510,7 +36510,7 @@
         <v>100.14632</v>
       </c>
       <c r="K444" s="6" t="n">
-        <v>100.972498</v>
+        <v>100.974757</v>
       </c>
       <c r="L444" s="6" t="n">
         <v>100.046572</v>
@@ -36594,7 +36594,7 @@
         <v>100.202135</v>
       </c>
       <c r="K445" s="9" t="n">
-        <v>101.047141</v>
+        <v>101.049884</v>
       </c>
       <c r="L445" s="9" t="n">
         <v>100.093063</v>
@@ -36678,7 +36678,7 @@
         <v>100.296429</v>
       </c>
       <c r="K446" s="6" t="n">
-        <v>101.093864</v>
+        <v>101.096947</v>
       </c>
       <c r="L446" s="6" t="n">
         <v>100.13986</v>
@@ -36762,7 +36762,7 @@
         <v>100.416139</v>
       </c>
       <c r="K447" s="9" t="n">
-        <v>101.098646</v>
+        <v>101.101778</v>
       </c>
       <c r="L447" s="9" t="n">
         <v>100.183591</v>
@@ -36846,7 +36846,7 @@
         <v>100.545152</v>
       </c>
       <c r="K448" s="6" t="n">
-        <v>101.050675</v>
+        <v>101.053499</v>
       </c>
       <c r="L448" s="6" t="n">
         <v>100.222783</v>
@@ -36930,7 +36930,7 @@
         <v>100.652855</v>
       </c>
       <c r="K449" s="9" t="n">
-        <v>100.957902</v>
+        <v>100.960346</v>
       </c>
       <c r="L449" s="9" t="n">
         <v>100.258677</v>
@@ -37014,7 +37014,7 @@
         <v>100.726413</v>
       </c>
       <c r="K450" s="6" t="n">
-        <v>100.833323</v>
+        <v>100.835273</v>
       </c>
       <c r="L450" s="6" t="n">
         <v>100.293792</v>
@@ -37098,7 +37098,7 @@
         <v>100.750799</v>
       </c>
       <c r="K451" s="9" t="n">
-        <v>100.700657</v>
+        <v>100.702366</v>
       </c>
       <c r="L451" s="9" t="n">
         <v>100.332558</v>
@@ -37182,7 +37182,7 @@
         <v>100.729223</v>
       </c>
       <c r="K452" s="6" t="n">
-        <v>100.573373</v>
+        <v>100.575012</v>
       </c>
       <c r="L452" s="6" t="n">
         <v>100.378673</v>
@@ -37266,7 +37266,7 @@
         <v>100.664028</v>
       </c>
       <c r="K453" s="9" t="n">
-        <v>100.464745</v>
+        <v>100.46638</v>
       </c>
       <c r="L453" s="9" t="n">
         <v>100.429921</v>
@@ -37350,7 +37350,7 @@
         <v>100.583629</v>
       </c>
       <c r="K454" s="6" t="n">
-        <v>100.371692</v>
+        <v>100.373394</v>
       </c>
       <c r="L454" s="6" t="n">
         <v>100.483996</v>
@@ -37434,7 +37434,7 @@
         <v>100.5061</v>
       </c>
       <c r="K455" s="9" t="n">
-        <v>100.293965</v>
+        <v>100.295519</v>
       </c>
       <c r="L455" s="9" t="n">
         <v>100.540134</v>
@@ -37518,7 +37518,7 @@
         <v>100.446362</v>
       </c>
       <c r="K456" s="6" t="n">
-        <v>100.232243</v>
+        <v>100.233488</v>
       </c>
       <c r="L456" s="6" t="n">
         <v>100.593187</v>
@@ -37602,7 +37602,7 @@
         <v>100.424528</v>
       </c>
       <c r="K457" s="9" t="n">
-        <v>100.181076</v>
+        <v>100.181716</v>
       </c>
       <c r="L457" s="9" t="n">
         <v>100.639926</v>
@@ -37686,7 +37686,7 @@
         <v>100.441202</v>
       </c>
       <c r="K458" s="6" t="n">
-        <v>100.141209</v>
+        <v>100.141308</v>
       </c>
       <c r="L458" s="6" t="n">
         <v>100.680515</v>
@@ -37770,7 +37770,7 @@
         <v>100.501744</v>
       </c>
       <c r="K459" s="9" t="n">
-        <v>100.114222</v>
+        <v>100.113959</v>
       </c>
       <c r="L459" s="9" t="n">
         <v>100.717894</v>
@@ -37854,7 +37854,7 @@
         <v>100.579009</v>
       </c>
       <c r="K460" s="6" t="n">
-        <v>100.0992</v>
+        <v>100.098971</v>
       </c>
       <c r="L460" s="6" t="n">
         <v>100.756268</v>
@@ -37938,7 +37938,7 @@
         <v>100.65092</v>
       </c>
       <c r="K461" s="9" t="n">
-        <v>100.096403</v>
+        <v>100.096317</v>
       </c>
       <c r="L461" s="9" t="n">
         <v>100.799292</v>
@@ -38022,7 +38022,7 @@
         <v>100.701616</v>
       </c>
       <c r="K462" s="6" t="n">
-        <v>100.093756</v>
+        <v>100.094047</v>
       </c>
       <c r="L462" s="6" t="n">
         <v>100.848305</v>
@@ -38106,7 +38106,7 @@
         <v>100.743151</v>
       </c>
       <c r="K463" s="9" t="n">
-        <v>100.089575</v>
+        <v>100.090066</v>
       </c>
       <c r="L463" s="9" t="n">
         <v>100.903266</v>
@@ -38190,7 +38190,7 @@
         <v>100.779422</v>
       </c>
       <c r="K464" s="6" t="n">
-        <v>100.08742</v>
+        <v>100.0879</v>
       </c>
       <c r="L464" s="6" t="n">
         <v>100.960851</v>
@@ -38274,7 +38274,7 @@
         <v>100.819922</v>
       </c>
       <c r="K465" s="9" t="n">
-        <v>100.082768</v>
+        <v>100.082807</v>
       </c>
       <c r="L465" s="9" t="n">
         <v>101.017018</v>
@@ -38358,7 +38358,7 @@
         <v>100.880134</v>
       </c>
       <c r="K466" s="6" t="n">
-        <v>100.085121</v>
+        <v>100.084532</v>
       </c>
       <c r="L466" s="6" t="n">
         <v>101.068626</v>
@@ -38442,7 +38442,7 @@
         <v>100.929644</v>
       </c>
       <c r="K467" s="9" t="n">
-        <v>100.095812</v>
+        <v>100.094683</v>
       </c>
       <c r="L467" s="9" t="n">
         <v>101.113769</v>
@@ -38526,7 +38526,7 @@
         <v>100.951699</v>
       </c>
       <c r="K468" s="6" t="n">
-        <v>100.113316</v>
+        <v>100.11191</v>
       </c>
       <c r="L468" s="6" t="n">
         <v>101.152758</v>
@@ -38610,7 +38610,7 @@
         <v>100.934167</v>
       </c>
       <c r="K469" s="9" t="n">
-        <v>100.139078</v>
+        <v>100.137896</v>
       </c>
       <c r="L469" s="9" t="n">
         <v>101.183695</v>
@@ -38694,7 +38694,7 @@
         <v>100.881029</v>
       </c>
       <c r="K470" s="6" t="n">
-        <v>100.175452</v>
+        <v>100.174839</v>
       </c>
       <c r="L470" s="6" t="n">
         <v>101.203493</v>
@@ -38778,7 +38778,7 @@
         <v>100.78398</v>
       </c>
       <c r="K471" s="9" t="n">
-        <v>100.215513</v>
+        <v>100.215595</v>
       </c>
       <c r="L471" s="9" t="n">
         <v>101.210982</v>
@@ -38862,7 +38862,7 @@
         <v>100.668397</v>
       </c>
       <c r="K472" s="6" t="n">
-        <v>100.245473</v>
+        <v>100.245998</v>
       </c>
       <c r="L472" s="6" t="n">
         <v>101.20839</v>
@@ -38946,7 +38946,7 @@
         <v>100.567977</v>
       </c>
       <c r="K473" s="9" t="n">
-        <v>100.262958</v>
+        <v>100.263556</v>
       </c>
       <c r="L473" s="9" t="n">
         <v>101.200657</v>
@@ -39030,7 +39030,7 @@
         <v>100.497751</v>
       </c>
       <c r="K474" s="6" t="n">
-        <v>100.276437</v>
+        <v>100.276566</v>
       </c>
       <c r="L474" s="6" t="n">
         <v>101.194131</v>
@@ -39114,7 +39114,7 @@
         <v>100.45314</v>
       </c>
       <c r="K475" s="9" t="n">
-        <v>100.283821</v>
+        <v>100.283273</v>
       </c>
       <c r="L475" s="9" t="n">
         <v>101.19272</v>
@@ -39198,7 +39198,7 @@
         <v>100.422245</v>
       </c>
       <c r="K476" s="6" t="n">
-        <v>100.282713</v>
+        <v>100.281673</v>
       </c>
       <c r="L476" s="6" t="n">
         <v>101.198031</v>
@@ -39282,7 +39282,7 @@
         <v>100.408371</v>
       </c>
       <c r="K477" s="9" t="n">
-        <v>100.282435</v>
+        <v>100.281377</v>
       </c>
       <c r="L477" s="9" t="n">
         <v>101.209262</v>
@@ -39366,7 +39366,7 @@
         <v>100.388246</v>
       </c>
       <c r="K478" s="6" t="n">
-        <v>100.285163</v>
+        <v>100.284323</v>
       </c>
       <c r="L478" s="6" t="n">
         <v>101.222569</v>
@@ -39450,7 +39450,7 @@
         <v>100.351666</v>
       </c>
       <c r="K479" s="9" t="n">
-        <v>100.287163</v>
+        <v>100.286714</v>
       </c>
       <c r="L479" s="9" t="n">
         <v>101.233733</v>
@@ -39534,7 +39534,7 @@
         <v>100.270376</v>
       </c>
       <c r="K480" s="6" t="n">
-        <v>100.279579</v>
+        <v>100.279551</v>
       </c>
       <c r="L480" s="6" t="n">
         <v>101.237004</v>
@@ -39618,7 +39618,7 @@
         <v>100.138318</v>
       </c>
       <c r="K481" s="9" t="n">
-        <v>100.257203</v>
+        <v>100.25724</v>
       </c>
       <c r="L481" s="9" t="n">
         <v>101.22696</v>
@@ -39702,7 +39702,7 @@
         <v>99.956729</v>
       </c>
       <c r="K482" s="6" t="n">
-        <v>100.212716</v>
+        <v>100.212354</v>
       </c>
       <c r="L482" s="6" t="n">
         <v>101.196122</v>
@@ -39786,7 +39786,7 @@
         <v>99.738558</v>
       </c>
       <c r="K483" s="9" t="n">
-        <v>100.14533</v>
+        <v>100.144186</v>
       </c>
       <c r="L483" s="9" t="n">
         <v>101.130806</v>
@@ -39870,7 +39870,7 @@
         <v>99.519688</v>
       </c>
       <c r="K484" s="6" t="n">
-        <v>100.047472</v>
+        <v>100.045353</v>
       </c>
       <c r="L484" s="6" t="n">
         <v>101.012468</v>
@@ -39954,7 +39954,7 @@
         <v>99.300033</v>
       </c>
       <c r="K485" s="9" t="n">
-        <v>99.898799</v>
+        <v>99.895624</v>
       </c>
       <c r="L485" s="9" t="n">
         <v>100.819419</v>
@@ -40038,7 +40038,7 @@
         <v>99.07543200000001</v>
       </c>
       <c r="K486" s="6" t="n">
-        <v>99.685355</v>
+        <v>99.68113099999999</v>
       </c>
       <c r="L486" s="6" t="n">
         <v>100.531006</v>
@@ -40122,7 +40122,7 @@
         <v>98.826033</v>
       </c>
       <c r="K487" s="9" t="n">
-        <v>99.419527</v>
+        <v>99.414175</v>
       </c>
       <c r="L487" s="9" t="n">
         <v>100.137542</v>
@@ -40206,7 +40206,7 @@
         <v>98.57625899999999</v>
       </c>
       <c r="K488" s="6" t="n">
-        <v>99.134522</v>
+        <v>99.12830700000001</v>
       </c>
       <c r="L488" s="6" t="n">
         <v>99.658266</v>
@@ -40290,7 +40290,7 @@
         <v>85.51202499999999</v>
       </c>
       <c r="K489" s="9" t="n">
-        <v>92.09486699999999</v>
+        <v>92.07571900000001</v>
       </c>
       <c r="L489" s="9" t="n">
         <v>99.136893</v>
@@ -40374,7 +40374,7 @@
         <v>85.468962</v>
       </c>
       <c r="K490" s="6" t="n">
-        <v>92.110906</v>
+        <v>92.07337</v>
       </c>
       <c r="L490" s="6" t="n">
         <v>98.631197</v>
@@ -40458,7 +40458,7 @@
         <v>93.293133</v>
       </c>
       <c r="K491" s="9" t="n">
-        <v>94.53784899999999</v>
+        <v>94.523594</v>
       </c>
       <c r="L491" s="9" t="n">
         <v>98.202202</v>
@@ -40542,7 +40542,7 @@
         <v>94.067013</v>
       </c>
       <c r="K492" s="6" t="n">
-        <v>95.715806</v>
+        <v>95.701256</v>
       </c>
       <c r="L492" s="6" t="n">
         <v>97.880655</v>
@@ -40626,7 +40626,7 @@
         <v>95.35747499999999</v>
       </c>
       <c r="K493" s="9" t="n">
-        <v>96.295664</v>
+        <v>96.283112</v>
       </c>
       <c r="L493" s="9" t="n">
         <v>97.664091</v>
@@ -40710,7 +40710,7 @@
         <v>96.56940299999999</v>
       </c>
       <c r="K494" s="6" t="n">
-        <v>96.90643</v>
+        <v>96.895595</v>
       </c>
       <c r="L494" s="6" t="n">
         <v>97.53728</v>
@@ -40794,7 +40794,7 @@
         <v>97.52677799999999</v>
       </c>
       <c r="K495" s="9" t="n">
-        <v>97.46845</v>
+        <v>97.45904400000001</v>
       </c>
       <c r="L495" s="9" t="n">
         <v>97.483351</v>
@@ -40878,7 +40878,7 @@
         <v>98.166375</v>
       </c>
       <c r="K496" s="6" t="n">
-        <v>97.97136</v>
+        <v>97.962907</v>
       </c>
       <c r="L496" s="6" t="n">
         <v>97.483677</v>
@@ -40962,7 +40962,7 @@
         <v>98.513998</v>
       </c>
       <c r="K497" s="9" t="n">
-        <v>98.416764</v>
+        <v>98.408996</v>
       </c>
       <c r="L497" s="9" t="n">
         <v>97.52389599999999</v>
@@ -41046,7 +41046,7 @@
         <v>98.651777</v>
       </c>
       <c r="K498" s="6" t="n">
-        <v>98.81958299999999</v>
+        <v>98.81255</v>
       </c>
       <c r="L498" s="6" t="n">
         <v>97.59943199999999</v>
@@ -41130,7 +41130,7 @@
         <v>98.675409</v>
       </c>
       <c r="K499" s="9" t="n">
-        <v>99.173204</v>
+        <v>99.167191</v>
       </c>
       <c r="L499" s="9" t="n">
         <v>97.720494</v>
@@ -41214,7 +41214,7 @@
         <v>98.65540799999999</v>
       </c>
       <c r="K500" s="6" t="n">
-        <v>99.453103</v>
+        <v>99.448131</v>
       </c>
       <c r="L500" s="6" t="n">
         <v>97.90008</v>
@@ -41298,7 +41298,7 @@
         <v>98.597115</v>
       </c>
       <c r="K501" s="9" t="n">
-        <v>99.63269099999999</v>
+        <v>99.628309</v>
       </c>
       <c r="L501" s="9" t="n">
         <v>98.143474</v>
@@ -41382,7 +41382,7 @@
         <v>98.519902</v>
       </c>
       <c r="K502" s="6" t="n">
-        <v>99.733542</v>
+        <v>99.729484</v>
       </c>
       <c r="L502" s="6" t="n">
         <v>98.44132999999999</v>
@@ -41466,7 +41466,7 @@
         <v>98.453154</v>
       </c>
       <c r="K503" s="9" t="n">
-        <v>99.78176000000001</v>
+        <v>99.777843</v>
       </c>
       <c r="L503" s="9" t="n">
         <v>98.755976</v>
@@ -41550,7 +41550,7 @@
         <v>98.42110700000001</v>
       </c>
       <c r="K504" s="6" t="n">
-        <v>99.807912</v>
+        <v>99.804259</v>
       </c>
       <c r="L504" s="6" t="n">
         <v>99.048254</v>
@@ -41634,7 +41634,7 @@
         <v>98.43960199999999</v>
       </c>
       <c r="K505" s="9" t="n">
-        <v>99.83334499999999</v>
+        <v>99.82990100000001</v>
       </c>
       <c r="L505" s="9" t="n">
         <v>99.291479</v>
@@ -41718,7 +41718,7 @@
         <v>98.52393600000001</v>
       </c>
       <c r="K506" s="6" t="n">
-        <v>99.866663</v>
+        <v>99.86350899999999</v>
       </c>
       <c r="L506" s="6" t="n">
         <v>99.479175</v>
@@ -41802,7 +41802,7 @@
         <v>98.698481</v>
       </c>
       <c r="K507" s="9" t="n">
-        <v>99.912217</v>
+        <v>99.90914100000001</v>
       </c>
       <c r="L507" s="9" t="n">
         <v>99.618077</v>
@@ -41886,7 +41886,7 @@
         <v>98.950447</v>
       </c>
       <c r="K508" s="6" t="n">
-        <v>99.975185</v>
+        <v>99.97229299999999</v>
       </c>
       <c r="L508" s="6" t="n">
         <v>99.721377</v>
@@ -41970,7 +41970,7 @@
         <v>99.252224</v>
       </c>
       <c r="K509" s="9" t="n">
-        <v>100.060613</v>
+        <v>100.057797</v>
       </c>
       <c r="L509" s="9" t="n">
         <v>99.800225</v>
@@ -42054,7 +42054,7 @@
         <v>99.559568</v>
       </c>
       <c r="K510" s="6" t="n">
-        <v>100.175994</v>
+        <v>100.173111</v>
       </c>
       <c r="L510" s="6" t="n">
         <v>99.862622</v>
@@ -42138,7 +42138,7 @@
         <v>99.832224</v>
       </c>
       <c r="K511" s="9" t="n">
-        <v>100.32811</v>
+        <v>100.325036</v>
       </c>
       <c r="L511" s="9" t="n">
         <v>99.912885</v>
@@ -42222,7 +42222,7 @@
         <v>100.054727</v>
       </c>
       <c r="K512" s="6" t="n">
-        <v>100.486554</v>
+        <v>100.483331</v>
       </c>
       <c r="L512" s="6" t="n">
         <v>99.95371900000001</v>
@@ -42306,7 +42306,7 @@
         <v>100.212389</v>
       </c>
       <c r="K513" s="9" t="n">
-        <v>100.616418</v>
+        <v>100.612968</v>
       </c>
       <c r="L513" s="9" t="n">
         <v>99.989208</v>
@@ -42390,7 +42390,7 @@
         <v>100.306984</v>
       </c>
       <c r="K514" s="6" t="n">
-        <v>100.721235</v>
+        <v>100.717916</v>
       </c>
       <c r="L514" s="6" t="n">
         <v>100.02222</v>
@@ -42474,7 +42474,7 @@
         <v>100.364155</v>
       </c>
       <c r="K515" s="9" t="n">
-        <v>100.799684</v>
+        <v>100.797138</v>
       </c>
       <c r="L515" s="9" t="n">
         <v>100.057293</v>
@@ -42558,7 +42558,7 @@
         <v>100.416245</v>
       </c>
       <c r="K516" s="6" t="n">
-        <v>100.857179</v>
+        <v>100.855715</v>
       </c>
       <c r="L516" s="6" t="n">
         <v>100.095591</v>
@@ -42642,7 +42642,7 @@
         <v>100.475021</v>
       </c>
       <c r="K517" s="9" t="n">
-        <v>100.899594</v>
+        <v>100.899606</v>
       </c>
       <c r="L517" s="9" t="n">
         <v>100.136804</v>
@@ -42726,7 +42726,7 @@
         <v>100.549796</v>
       </c>
       <c r="K518" s="6" t="n">
-        <v>100.921963</v>
+        <v>100.923189</v>
       </c>
       <c r="L518" s="6" t="n">
         <v>100.179837</v>
@@ -42810,7 +42810,7 @@
         <v>100.656071</v>
       </c>
       <c r="K519" s="9" t="n">
-        <v>100.931414</v>
+        <v>100.933184</v>
       </c>
       <c r="L519" s="9" t="n">
         <v>100.222659</v>
@@ -42894,7 +42894,7 @@
         <v>100.791385</v>
       </c>
       <c r="K520" s="6" t="n">
-        <v>100.930561</v>
+        <v>100.931932</v>
       </c>
       <c r="L520" s="6" t="n">
         <v>100.263781</v>
@@ -42978,7 +42978,7 @@
         <v>100.925472</v>
       </c>
       <c r="K521" s="9" t="n">
-        <v>100.928281</v>
+        <v>100.928644</v>
       </c>
       <c r="L521" s="9" t="n">
         <v>100.305966</v>
@@ -43062,7 +43062,7 @@
         <v>101.028024</v>
       </c>
       <c r="K522" s="6" t="n">
-        <v>100.922353</v>
+        <v>100.921182</v>
       </c>
       <c r="L522" s="6" t="n">
         <v>100.351294</v>
@@ -43146,7 +43146,7 @@
         <v>101.108626</v>
       </c>
       <c r="K523" s="9" t="n">
-        <v>100.916655</v>
+        <v>100.914412</v>
       </c>
       <c r="L523" s="9" t="n">
         <v>100.400924</v>
@@ -43230,7 +43230,7 @@
         <v>101.189325</v>
       </c>
       <c r="K524" s="6" t="n">
-        <v>100.922367</v>
+        <v>100.919381</v>
       </c>
       <c r="L524" s="6" t="n">
         <v>100.451343</v>
@@ -43314,7 +43314,7 @@
         <v>101.283764</v>
       </c>
       <c r="K525" s="9" t="n">
-        <v>100.947822</v>
+        <v>100.944665</v>
       </c>
       <c r="L525" s="9" t="n">
         <v>100.495799</v>
@@ -43398,7 +43398,7 @@
         <v>101.388892</v>
       </c>
       <c r="K526" s="6" t="n">
-        <v>100.981938</v>
+        <v>100.979837</v>
       </c>
       <c r="L526" s="6" t="n">
         <v>100.530697</v>
@@ -43482,7 +43482,7 @@
         <v>101.493341</v>
       </c>
       <c r="K527" s="9" t="n">
-        <v>101.015742</v>
+        <v>101.015555</v>
       </c>
       <c r="L527" s="9" t="n">
         <v>100.55323</v>
@@ -43566,7 +43566,7 @@
         <v>101.584921</v>
       </c>
       <c r="K528" s="6" t="n">
-        <v>101.024907</v>
+        <v>101.027032</v>
       </c>
       <c r="L528" s="6" t="n">
         <v>100.564068</v>
@@ -43650,7 +43650,7 @@
         <v>101.655708</v>
       </c>
       <c r="K529" s="9" t="n">
-        <v>101.002422</v>
+        <v>101.006236</v>
       </c>
       <c r="L529" s="9" t="n">
         <v>100.566624</v>
@@ -43734,7 +43734,7 @@
         <v>101.690968</v>
       </c>
       <c r="K530" s="6" t="n">
-        <v>100.951281</v>
+        <v>100.956051</v>
       </c>
       <c r="L530" s="6" t="n">
         <v>100.565101</v>
@@ -43818,7 +43818,7 @@
         <v>101.666622</v>
       </c>
       <c r="K531" s="9" t="n">
-        <v>100.868401</v>
+        <v>100.873205</v>
       </c>
       <c r="L531" s="9" t="n">
         <v>100.562499</v>
@@ -43902,7 +43902,7 @@
         <v>101.568531</v>
       </c>
       <c r="K532" s="6" t="n">
-        <v>100.748232</v>
+        <v>100.752497</v>
       </c>
       <c r="L532" s="6" t="n">
         <v>100.55948</v>
@@ -43986,7 +43986,7 @@
         <v>101.428694</v>
       </c>
       <c r="K533" s="9" t="n">
-        <v>100.595588</v>
+        <v>100.598401</v>
       </c>
       <c r="L533" s="9" t="n">
         <v>100.556327</v>
@@ -44070,7 +44070,7 @@
         <v>101.265916</v>
       </c>
       <c r="K534" s="6" t="n">
-        <v>100.430872</v>
+        <v>100.430969</v>
       </c>
       <c r="L534" s="6" t="n">
         <v>100.553928</v>
@@ -44154,7 +44154,7 @@
         <v>101.090678</v>
       </c>
       <c r="K535" s="9" t="n">
-        <v>100.277385</v>
+        <v>100.274535</v>
       </c>
       <c r="L535" s="9" t="n">
         <v>100.552199</v>
@@ -44238,7 +44238,7 @@
         <v>100.936379</v>
       </c>
       <c r="K536" s="6" t="n">
-        <v>100.139141</v>
+        <v>100.133131</v>
       </c>
       <c r="L536" s="6" t="n">
         <v>100.551102</v>
@@ -44322,7 +44322,7 @@
         <v>100.809771</v>
       </c>
       <c r="K537" s="9" t="n">
-        <v>100.022404</v>
+        <v>100.014388</v>
       </c>
       <c r="L537" s="9" t="n">
         <v>100.551086</v>
@@ -44406,7 +44406,7 @@
         <v>100.722871</v>
       </c>
       <c r="K538" s="6" t="n">
-        <v>99.926008</v>
+        <v>99.918116</v>
       </c>
       <c r="L538" s="6" t="n">
         <v>100.549269</v>
@@ -44490,7 +44490,7 @@
         <v>100.662984</v>
       </c>
       <c r="K539" s="9" t="n">
-        <v>99.850478</v>
+        <v>99.846045</v>
       </c>
       <c r="L539" s="9" t="n">
         <v>100.542064</v>
@@ -44574,7 +44574,7 @@
         <v>100.603624</v>
       </c>
       <c r="K540" s="6" t="n">
-        <v>99.797224</v>
+        <v>99.799049</v>
       </c>
       <c r="L540" s="6" t="n">
         <v>100.527691</v>
@@ -44658,7 +44658,7 @@
         <v>100.51623</v>
       </c>
       <c r="K541" s="9" t="n">
-        <v>99.754566</v>
+        <v>99.763848</v>
       </c>
       <c r="L541" s="9" t="n">
         <v>100.502775</v>
@@ -44742,7 +44742,7 @@
         <v>100.394529</v>
       </c>
       <c r="K542" s="6" t="n">
-        <v>99.718979</v>
+        <v>99.737196</v>
       </c>
       <c r="L542" s="6" t="n">
         <v>100.466622</v>
@@ -44826,7 +44826,7 @@
         <v>100.240854</v>
       </c>
       <c r="K543" s="9" t="n">
-        <v>99.68764299999999</v>
+        <v>99.71713699999999</v>
       </c>
       <c r="L543" s="9" t="n">
         <v>100.420502</v>
@@ -44910,7 +44910,7 @@
         <v>100.096105</v>
       </c>
       <c r="K544" s="6" t="n">
-        <v>99.669355</v>
+        <v>99.713838</v>
       </c>
       <c r="L544" s="6" t="n">
         <v>100.367899</v>
@@ -44994,7 +44994,7 @@
         <v>99.984133</v>
       </c>
       <c r="K545" s="9" t="n">
-        <v>99.669743</v>
+        <v>99.731785</v>
       </c>
       <c r="L545" s="9" t="n">
         <v>100.311633</v>
@@ -45078,7 +45078,7 @@
         <v>99.92702199999999</v>
       </c>
       <c r="K546" s="6" t="n">
-        <v>99.684161</v>
+        <v>99.760856</v>
       </c>
       <c r="L546" s="6" t="n">
         <v>100.252883</v>
@@ -45162,7 +45162,7 @@
         <v>99.9059</v>
       </c>
       <c r="K547" s="9" t="n">
-        <v>99.705506</v>
+        <v>99.788151</v>
       </c>
       <c r="L547" s="9" t="n">
         <v>100.192471</v>
@@ -45246,7 +45246,7 @@
         <v>99.871627</v>
       </c>
       <c r="K548" s="6" t="n">
-        <v>99.72686400000001</v>
+        <v>99.80586</v>
       </c>
       <c r="L548" s="6" t="n">
         <v>100.130644</v>
@@ -45330,7 +45330,7 @@
         <v>99.81034200000001</v>
       </c>
       <c r="K549" s="9" t="n">
-        <v>99.745225</v>
+        <v>99.814857</v>
       </c>
       <c r="L549" s="9" t="n">
         <v>100.066523</v>
@@ -45414,7 +45414,7 @@
         <v>99.729754</v>
       </c>
       <c r="K550" s="6" t="n">
-        <v>99.771908</v>
+        <v>99.82645100000001</v>
       </c>
       <c r="L550" s="6" t="n">
         <v>100.000477</v>
@@ -45498,7 +45498,7 @@
         <v>99.62351099999999</v>
       </c>
       <c r="K551" s="9" t="n">
-        <v>99.802165</v>
+        <v>99.841813</v>
       </c>
       <c r="L551" s="9" t="n">
         <v>99.93474399999999</v>
@@ -45582,7 +45582,7 @@
         <v>99.511067</v>
       </c>
       <c r="K552" s="6" t="n">
-        <v>99.836992</v>
+        <v>99.86333</v>
       </c>
       <c r="L552" s="6" t="n">
         <v>99.87217200000001</v>
@@ -45666,7 +45666,7 @@
         <v>99.429486</v>
       </c>
       <c r="K553" s="9" t="n">
-        <v>99.878079</v>
+        <v>99.89223</v>
       </c>
       <c r="L553" s="9" t="n">
         <v>99.816664</v>
@@ -45750,7 +45750,7 @@
         <v>99.396497</v>
       </c>
       <c r="K554" s="6" t="n">
-        <v>99.92247</v>
+        <v>99.925391</v>
       </c>
       <c r="L554" s="6" t="n">
         <v>99.771727</v>
@@ -45834,7 +45834,7 @@
         <v>99.410533</v>
       </c>
       <c r="K555" s="9" t="n">
-        <v>99.968703</v>
+        <v>99.960492</v>
       </c>
       <c r="L555" s="9" t="n">
         <v>99.73569000000001</v>
@@ -45918,7 +45918,7 @@
         <v>99.446281</v>
       </c>
       <c r="K556" s="6" t="n">
-        <v>100.008269</v>
+        <v>99.987179</v>
       </c>
       <c r="L556" s="6" t="n">
         <v>99.705551</v>
@@ -46002,7 +46002,7 @@
         <v>99.48218799999999</v>
       </c>
       <c r="K557" s="9" t="n">
-        <v>100.028605</v>
+        <v>99.99443599999999</v>
       </c>
       <c r="L557" s="9" t="n">
         <v>99.679518</v>
@@ -46086,7 +46086,7 @@
         <v>99.518897</v>
       </c>
       <c r="K558" s="6" t="n">
-        <v>100.025105</v>
+        <v>99.98420900000001</v>
       </c>
       <c r="L558" s="6" t="n">
         <v>99.65561</v>
@@ -46170,7 +46170,7 @@
         <v>99.57956</v>
       </c>
       <c r="K559" s="9" t="n">
-        <v>99.992802</v>
+        <v>99.95556000000001</v>
       </c>
       <c r="L559" s="9" t="n">
         <v>99.632307</v>
@@ -46254,7 +46254,7 @@
         <v>99.669968</v>
       </c>
       <c r="K560" s="6" t="n">
-        <v>99.94243299999999</v>
+        <v>99.92066199999999</v>
       </c>
       <c r="L560" s="6" t="n">
         <v>99.608284</v>
@@ -46338,7 +46338,7 @@
         <v>99.791371</v>
       </c>
       <c r="K561" s="9" t="n">
-        <v>99.878412</v>
+        <v>99.877825</v>
       </c>
       <c r="L561" s="9" t="n">
         <v>99.584</v>
@@ -46422,7 +46422,7 @@
         <v>99.91174100000001</v>
       </c>
       <c r="K562" s="6" t="n">
-        <v>99.80022700000001</v>
+        <v>99.824534</v>
       </c>
       <c r="L562" s="6" t="n">
         <v>99.562954</v>
@@ -46506,7 +46506,7 @@
         <v>100.033774</v>
       </c>
       <c r="K563" s="9" t="n">
-        <v>99.71626000000001</v>
+        <v>99.76123800000001</v>
       </c>
       <c r="L563" s="9" t="n">
         <v>99.54803</v>
@@ -46581,7 +46581,9 @@
       <c r="J564" s="6" t="n">
         <v>100.158475</v>
       </c>
-      <c r="K564" s="6" t="n"/>
+      <c r="K564" s="6" t="n">
+        <v>99.69396399999999</v>
+      </c>
       <c r="L564" s="6" t="n">
         <v>99.53705600000001</v>
       </c>

--- a/downloads/indicadores/SIC/SIC_datos.xlsx
+++ b/downloads/indicadores/SIC/SIC_datos.xlsx
@@ -668,7 +668,7 @@
       <c r="G6" s="7" t="n"/>
       <c r="H6" s="7" t="n"/>
       <c r="I6" s="6" t="n">
-        <v>97.07945100000001</v>
+        <v>97.077684</v>
       </c>
       <c r="J6" s="6" t="n">
         <v>98.58717300000001</v>
@@ -740,7 +740,7 @@
       </c>
       <c r="H7" s="10" t="n"/>
       <c r="I7" s="9" t="n">
-        <v>97.250129</v>
+        <v>97.248456</v>
       </c>
       <c r="J7" s="9" t="n">
         <v>98.620119</v>
@@ -812,7 +812,7 @@
       </c>
       <c r="H8" s="7" t="n"/>
       <c r="I8" s="6" t="n">
-        <v>97.429852</v>
+        <v>97.42827800000001</v>
       </c>
       <c r="J8" s="6" t="n">
         <v>98.65603900000001</v>
@@ -884,7 +884,7 @@
       </c>
       <c r="H9" s="10" t="n"/>
       <c r="I9" s="9" t="n">
-        <v>97.612549</v>
+        <v>97.611076</v>
       </c>
       <c r="J9" s="9" t="n">
         <v>98.701128</v>
@@ -956,7 +956,7 @@
       </c>
       <c r="H10" s="7" t="n"/>
       <c r="I10" s="6" t="n">
-        <v>97.827876</v>
+        <v>97.826522</v>
       </c>
       <c r="J10" s="6" t="n">
         <v>98.76903299999999</v>
@@ -1028,7 +1028,7 @@
       </c>
       <c r="H11" s="10" t="n"/>
       <c r="I11" s="9" t="n">
-        <v>98.094712</v>
+        <v>98.09350499999999</v>
       </c>
       <c r="J11" s="9" t="n">
         <v>98.871028</v>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="H12" s="7" t="n"/>
       <c r="I12" s="6" t="n">
-        <v>98.402804</v>
+        <v>98.40176700000001</v>
       </c>
       <c r="J12" s="6" t="n">
         <v>99.01839099999999</v>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="H13" s="10" t="n"/>
       <c r="I13" s="9" t="n">
-        <v>98.744767</v>
+        <v>98.74391900000001</v>
       </c>
       <c r="J13" s="9" t="n">
         <v>99.22478</v>
@@ -1244,7 +1244,7 @@
       </c>
       <c r="H14" s="7" t="n"/>
       <c r="I14" s="6" t="n">
-        <v>99.115554</v>
+        <v>99.11490999999999</v>
       </c>
       <c r="J14" s="6" t="n">
         <v>99.47457799999999</v>
@@ -1316,7 +1316,7 @@
       </c>
       <c r="H15" s="10" t="n"/>
       <c r="I15" s="9" t="n">
-        <v>99.51369</v>
+        <v>99.513266</v>
       </c>
       <c r="J15" s="9" t="n">
         <v>99.753721</v>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="H16" s="7" t="n"/>
       <c r="I16" s="6" t="n">
-        <v>99.91284400000001</v>
+        <v>99.91264099999999</v>
       </c>
       <c r="J16" s="6" t="n">
         <v>100.041046</v>
@@ -1460,7 +1460,7 @@
       </c>
       <c r="H17" s="10" t="n"/>
       <c r="I17" s="9" t="n">
-        <v>100.29497</v>
+        <v>100.294977</v>
       </c>
       <c r="J17" s="9" t="n">
         <v>100.321862</v>
@@ -1536,7 +1536,7 @@
         <v>2.228015</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>100.670384</v>
+        <v>100.670598</v>
       </c>
       <c r="J18" s="6" t="n">
         <v>100.588009</v>
@@ -1614,7 +1614,7 @@
         <v>2.069895</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>101.02324</v>
+        <v>101.023649</v>
       </c>
       <c r="J19" s="9" t="n">
         <v>100.838095</v>
@@ -1692,7 +1692,7 @@
         <v>1.933141</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>101.348522</v>
+        <v>101.34911</v>
       </c>
       <c r="J20" s="6" t="n">
         <v>101.073479</v>
@@ -1770,7 +1770,7 @@
         <v>1.751017</v>
       </c>
       <c r="I21" s="9" t="n">
-        <v>101.650489</v>
+        <v>101.651244</v>
       </c>
       <c r="J21" s="9" t="n">
         <v>101.289492</v>
@@ -1848,7 +1848,7 @@
         <v>1.420502</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>101.904045</v>
+        <v>101.90494</v>
       </c>
       <c r="J22" s="6" t="n">
         <v>101.48141</v>
@@ -1926,7 +1926,7 @@
         <v>0.941994</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>102.109505</v>
+        <v>102.110513</v>
       </c>
       <c r="J23" s="9" t="n">
         <v>101.651922</v>
@@ -2004,7 +2004,7 @@
         <v>0.35744</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>102.283409</v>
+        <v>102.284513</v>
       </c>
       <c r="J24" s="6" t="n">
         <v>101.801915</v>
@@ -2082,7 +2082,7 @@
         <v>-0.265773</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>102.434646</v>
+        <v>102.435834</v>
       </c>
       <c r="J25" s="9" t="n">
         <v>101.923297</v>
@@ -2160,7 +2160,7 @@
         <v>-0.8465780000000001</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>102.549871</v>
+        <v>102.551122</v>
       </c>
       <c r="J26" s="6" t="n">
         <v>102.008314</v>
@@ -2238,7 +2238,7 @@
         <v>-1.342403</v>
       </c>
       <c r="I27" s="9" t="n">
-        <v>102.622129</v>
+        <v>102.623419</v>
       </c>
       <c r="J27" s="9" t="n">
         <v>102.053854</v>
@@ -2316,7 +2316,7 @@
         <v>-1.797515</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>102.615231</v>
+        <v>102.616518</v>
       </c>
       <c r="J28" s="6" t="n">
         <v>102.067887</v>
@@ -2394,7 +2394,7 @@
         <v>-2.30673</v>
       </c>
       <c r="I29" s="9" t="n">
-        <v>102.509532</v>
+        <v>102.510761</v>
       </c>
       <c r="J29" s="9" t="n">
         <v>102.057652</v>
@@ -2472,7 +2472,7 @@
         <v>-2.976494</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>102.330116</v>
+        <v>102.331246</v>
       </c>
       <c r="J30" s="6" t="n">
         <v>102.028814</v>
@@ -2550,7 +2550,7 @@
         <v>-3.644784</v>
       </c>
       <c r="I31" s="9" t="n">
-        <v>102.130745</v>
+        <v>102.131764</v>
       </c>
       <c r="J31" s="9" t="n">
         <v>101.972544</v>
@@ -2628,7 +2628,7 @@
         <v>-4.410294</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>101.942022</v>
+        <v>101.942937</v>
       </c>
       <c r="J32" s="6" t="n">
         <v>101.879115</v>
@@ -2706,7 +2706,7 @@
         <v>-5.186972</v>
       </c>
       <c r="I33" s="9" t="n">
-        <v>101.785462</v>
+        <v>101.786291</v>
       </c>
       <c r="J33" s="9" t="n">
         <v>101.742962</v>
@@ -2784,7 +2784,7 @@
         <v>-5.838414</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>101.641114</v>
+        <v>101.641863</v>
       </c>
       <c r="J34" s="6" t="n">
         <v>101.562451</v>
@@ -2862,7 +2862,7 @@
         <v>-6.331195</v>
       </c>
       <c r="I35" s="9" t="n">
-        <v>101.47724</v>
+        <v>101.477899</v>
       </c>
       <c r="J35" s="9" t="n">
         <v>101.331819</v>
@@ -2940,7 +2940,7 @@
         <v>-6.618507</v>
       </c>
       <c r="I36" s="6" t="n">
-        <v>101.282818</v>
+        <v>101.283369</v>
       </c>
       <c r="J36" s="6" t="n">
         <v>101.054861</v>
@@ -3018,7 +3018,7 @@
         <v>-6.69206</v>
       </c>
       <c r="I37" s="9" t="n">
-        <v>101.04874</v>
+        <v>101.049162</v>
       </c>
       <c r="J37" s="9" t="n">
         <v>100.743844</v>
@@ -3096,7 +3096,7 @@
         <v>-6.566365</v>
       </c>
       <c r="I38" s="6" t="n">
-        <v>100.761233</v>
+        <v>100.761497</v>
       </c>
       <c r="J38" s="6" t="n">
         <v>100.410857</v>
@@ -3174,7 +3174,7 @@
         <v>-6.271965</v>
       </c>
       <c r="I39" s="9" t="n">
-        <v>100.426897</v>
+        <v>100.426977</v>
       </c>
       <c r="J39" s="9" t="n">
         <v>100.075436</v>
@@ -3252,7 +3252,7 @@
         <v>-5.827578</v>
       </c>
       <c r="I40" s="6" t="n">
-        <v>100.089284</v>
+        <v>100.089177</v>
       </c>
       <c r="J40" s="6" t="n">
         <v>99.760775</v>
@@ -3330,7 +3330,7 @@
         <v>-5.241624</v>
       </c>
       <c r="I41" s="9" t="n">
-        <v>99.77172299999999</v>
+        <v>99.77144</v>
       </c>
       <c r="J41" s="9" t="n">
         <v>99.456463</v>
@@ -3408,7 +3408,7 @@
         <v>-4.451157</v>
       </c>
       <c r="I42" s="6" t="n">
-        <v>99.472623</v>
+        <v>99.47217499999999</v>
       </c>
       <c r="J42" s="6" t="n">
         <v>99.165311</v>
@@ -3486,7 +3486,7 @@
         <v>-3.481839</v>
       </c>
       <c r="I43" s="9" t="n">
-        <v>99.193883</v>
+        <v>99.193282</v>
       </c>
       <c r="J43" s="9" t="n">
         <v>98.899021</v>
@@ -3564,7 +3564,7 @@
         <v>-2.395452</v>
       </c>
       <c r="I44" s="6" t="n">
-        <v>98.940072</v>
+        <v>98.93933</v>
       </c>
       <c r="J44" s="6" t="n">
         <v>98.675944</v>
@@ -3642,7 +3642,7 @@
         <v>-1.26622</v>
       </c>
       <c r="I45" s="9" t="n">
-        <v>98.72941</v>
+        <v>98.72855199999999</v>
       </c>
       <c r="J45" s="9" t="n">
         <v>98.505844</v>
@@ -3720,7 +3720,7 @@
         <v>-0.184339</v>
       </c>
       <c r="I46" s="6" t="n">
-        <v>98.609694</v>
+        <v>98.60877000000001</v>
       </c>
       <c r="J46" s="6" t="n">
         <v>98.386092</v>
@@ -3798,7 +3798,7 @@
         <v>0.819734</v>
       </c>
       <c r="I47" s="9" t="n">
-        <v>98.57434000000001</v>
+        <v>98.573397</v>
       </c>
       <c r="J47" s="9" t="n">
         <v>98.318573</v>
@@ -3876,7 +3876,7 @@
         <v>1.691211</v>
       </c>
       <c r="I48" s="6" t="n">
-        <v>98.60993000000001</v>
+        <v>98.60900599999999</v>
       </c>
       <c r="J48" s="6" t="n">
         <v>98.30156700000001</v>
@@ -3954,7 +3954,7 @@
         <v>2.384123</v>
       </c>
       <c r="I49" s="9" t="n">
-        <v>98.701831</v>
+        <v>98.700958</v>
       </c>
       <c r="J49" s="9" t="n">
         <v>98.332418</v>
@@ -4032,7 +4032,7 @@
         <v>2.904029</v>
       </c>
       <c r="I50" s="6" t="n">
-        <v>98.86187099999999</v>
+        <v>98.861086</v>
       </c>
       <c r="J50" s="6" t="n">
         <v>98.404588</v>
@@ -4110,7 +4110,7 @@
         <v>3.263978</v>
       </c>
       <c r="I51" s="9" t="n">
-        <v>99.075231</v>
+        <v>99.074564</v>
       </c>
       <c r="J51" s="9" t="n">
         <v>98.51092</v>
@@ -4188,7 +4188,7 @@
         <v>3.505921</v>
       </c>
       <c r="I52" s="6" t="n">
-        <v>99.304771</v>
+        <v>99.30423</v>
       </c>
       <c r="J52" s="6" t="n">
         <v>98.64318</v>
@@ -4266,7 +4266,7 @@
         <v>3.691583</v>
       </c>
       <c r="I53" s="9" t="n">
-        <v>99.55051899999999</v>
+        <v>99.55011399999999</v>
       </c>
       <c r="J53" s="9" t="n">
         <v>98.79303899999999</v>
@@ -4344,7 +4344,7 @@
         <v>3.798479</v>
       </c>
       <c r="I54" s="6" t="n">
-        <v>99.781324</v>
+        <v>99.781046</v>
       </c>
       <c r="J54" s="6" t="n">
         <v>98.945735</v>
@@ -4422,7 +4422,7 @@
         <v>3.791699</v>
       </c>
       <c r="I55" s="9" t="n">
-        <v>99.941276</v>
+        <v>99.941086</v>
       </c>
       <c r="J55" s="9" t="n">
         <v>99.101055</v>
@@ -4500,7 +4500,7 @@
         <v>3.684004</v>
       </c>
       <c r="I56" s="6" t="n">
-        <v>100.04085</v>
+        <v>100.040716</v>
       </c>
       <c r="J56" s="6" t="n">
         <v>99.25783300000001</v>
@@ -4578,7 +4578,7 @@
         <v>3.518113</v>
       </c>
       <c r="I57" s="9" t="n">
-        <v>100.101249</v>
+        <v>100.101148</v>
       </c>
       <c r="J57" s="9" t="n">
         <v>99.420851</v>
@@ -4656,7 +4656,7 @@
         <v>3.322246</v>
       </c>
       <c r="I58" s="6" t="n">
-        <v>100.161775</v>
+        <v>100.161708</v>
       </c>
       <c r="J58" s="6" t="n">
         <v>99.5958</v>
@@ -4734,7 +4734,7 @@
         <v>3.084358</v>
       </c>
       <c r="I59" s="9" t="n">
-        <v>100.272431</v>
+        <v>100.272424</v>
       </c>
       <c r="J59" s="9" t="n">
         <v>99.78183300000001</v>
@@ -4812,7 +4812,7 @@
         <v>2.832059</v>
       </c>
       <c r="I60" s="6" t="n">
-        <v>100.412885</v>
+        <v>100.412956</v>
       </c>
       <c r="J60" s="6" t="n">
         <v>99.965822</v>
@@ -4890,7 +4890,7 @@
         <v>2.594998</v>
       </c>
       <c r="I61" s="9" t="n">
-        <v>100.526602</v>
+        <v>100.526736</v>
       </c>
       <c r="J61" s="9" t="n">
         <v>100.135873</v>
@@ -4968,7 +4968,7 @@
         <v>2.318379</v>
       </c>
       <c r="I62" s="6" t="n">
-        <v>100.607962</v>
+        <v>100.60814</v>
       </c>
       <c r="J62" s="6" t="n">
         <v>100.291232</v>
@@ -5046,7 +5046,7 @@
         <v>2.00543</v>
       </c>
       <c r="I63" s="9" t="n">
-        <v>100.660417</v>
+        <v>100.660625</v>
       </c>
       <c r="J63" s="9" t="n">
         <v>100.437806</v>
@@ -5124,7 +5124,7 @@
         <v>1.689692</v>
       </c>
       <c r="I64" s="6" t="n">
-        <v>100.738791</v>
+        <v>100.739041</v>
       </c>
       <c r="J64" s="6" t="n">
         <v>100.603176</v>
@@ -5202,7 +5202,7 @@
         <v>1.408769</v>
       </c>
       <c r="I65" s="9" t="n">
-        <v>100.855855</v>
+        <v>100.85617</v>
       </c>
       <c r="J65" s="9" t="n">
         <v>100.773103</v>
@@ -5280,7 +5280,7 @@
         <v>1.180942</v>
       </c>
       <c r="I66" s="6" t="n">
-        <v>100.988432</v>
+        <v>100.98882</v>
       </c>
       <c r="J66" s="6" t="n">
         <v>100.930425</v>
@@ -5358,7 +5358,7 @@
         <v>1.0161</v>
       </c>
       <c r="I67" s="9" t="n">
-        <v>101.110681</v>
+        <v>101.111137</v>
       </c>
       <c r="J67" s="9" t="n">
         <v>101.064028</v>
@@ -5436,7 +5436,7 @@
         <v>0.848758</v>
       </c>
       <c r="I68" s="6" t="n">
-        <v>101.194781</v>
+        <v>101.195283</v>
       </c>
       <c r="J68" s="6" t="n">
         <v>101.165233</v>
@@ -5514,7 +5514,7 @@
         <v>0.6395110000000001</v>
       </c>
       <c r="I69" s="9" t="n">
-        <v>101.251699</v>
+        <v>101.252232</v>
       </c>
       <c r="J69" s="9" t="n">
         <v>101.237855</v>
@@ -5592,7 +5592,7 @@
         <v>0.365132</v>
       </c>
       <c r="I70" s="6" t="n">
-        <v>101.291784</v>
+        <v>101.29234</v>
       </c>
       <c r="J70" s="6" t="n">
         <v>101.301148</v>
@@ -5670,7 +5670,7 @@
         <v>0.060524</v>
       </c>
       <c r="I71" s="9" t="n">
-        <v>101.329983</v>
+        <v>101.33056</v>
       </c>
       <c r="J71" s="9" t="n">
         <v>101.354806</v>
@@ -5748,7 +5748,7 @@
         <v>-0.275461</v>
       </c>
       <c r="I72" s="6" t="n">
-        <v>101.337441</v>
+        <v>101.338021</v>
       </c>
       <c r="J72" s="6" t="n">
         <v>101.381146</v>
@@ -5826,7 +5826,7 @@
         <v>-0.623132</v>
       </c>
       <c r="I73" s="9" t="n">
-        <v>101.310338</v>
+        <v>101.310903</v>
       </c>
       <c r="J73" s="9" t="n">
         <v>101.365597</v>
@@ -5904,7 +5904,7 @@
         <v>-0.889608</v>
       </c>
       <c r="I74" s="6" t="n">
-        <v>101.231405</v>
+        <v>101.231927</v>
       </c>
       <c r="J74" s="6" t="n">
         <v>101.311635</v>
@@ -5982,7 +5982,7 @@
         <v>-1.071538</v>
       </c>
       <c r="I75" s="9" t="n">
-        <v>101.086615</v>
+        <v>101.087058</v>
       </c>
       <c r="J75" s="9" t="n">
         <v>101.222428</v>
@@ -6060,7 +6060,7 @@
         <v>-1.225863</v>
       </c>
       <c r="I76" s="6" t="n">
-        <v>100.8942</v>
+        <v>100.894536</v>
       </c>
       <c r="J76" s="6" t="n">
         <v>101.101558</v>
@@ -6138,7 +6138,7 @@
         <v>-1.425837</v>
       </c>
       <c r="I77" s="9" t="n">
-        <v>100.660268</v>
+        <v>100.660475</v>
       </c>
       <c r="J77" s="9" t="n">
         <v>100.951667</v>
@@ -6216,7 +6216,7 @@
         <v>-1.67802</v>
       </c>
       <c r="I78" s="6" t="n">
-        <v>100.405843</v>
+        <v>100.40591</v>
       </c>
       <c r="J78" s="6" t="n">
         <v>100.777636</v>
@@ -6296,7 +6296,7 @@
         <v>-1.95827</v>
       </c>
       <c r="I79" s="9" t="n">
-        <v>100.200927</v>
+        <v>100.200881</v>
       </c>
       <c r="J79" s="9" t="n">
         <v>100.570545</v>
@@ -6376,7 +6376,7 @@
         <v>-2.206269</v>
       </c>
       <c r="I80" s="6" t="n">
-        <v>100.02684</v>
+        <v>100.026697</v>
       </c>
       <c r="J80" s="6" t="n">
         <v>100.321482</v>
@@ -6456,7 +6456,7 @@
         <v>-2.407526</v>
       </c>
       <c r="I81" s="9" t="n">
-        <v>99.837746</v>
+        <v>99.83749899999999</v>
       </c>
       <c r="J81" s="9" t="n">
         <v>100.034632</v>
@@ -6536,7 +6536,7 @@
         <v>-2.532024</v>
       </c>
       <c r="I82" s="6" t="n">
-        <v>99.643517</v>
+        <v>99.643163</v>
       </c>
       <c r="J82" s="6" t="n">
         <v>99.70424199999999</v>
@@ -6616,7 +6616,7 @@
         <v>-2.553436</v>
       </c>
       <c r="I83" s="9" t="n">
-        <v>99.397637</v>
+        <v>99.397147</v>
       </c>
       <c r="J83" s="9" t="n">
         <v>99.352293</v>
@@ -6696,7 +6696,7 @@
         <v>-2.436963</v>
       </c>
       <c r="I84" s="6" t="n">
-        <v>99.089911</v>
+        <v>99.089251</v>
       </c>
       <c r="J84" s="6" t="n">
         <v>99.021517</v>
@@ -6776,7 +6776,7 @@
         <v>-2.183834</v>
       </c>
       <c r="I85" s="9" t="n">
-        <v>98.80702100000001</v>
+        <v>98.80620500000001</v>
       </c>
       <c r="J85" s="9" t="n">
         <v>98.742053</v>
@@ -6856,7 +6856,7 @@
         <v>-1.856011</v>
       </c>
       <c r="I86" s="6" t="n">
-        <v>98.577631</v>
+        <v>98.576689</v>
       </c>
       <c r="J86" s="6" t="n">
         <v>98.533401</v>
@@ -6936,7 +6936,7 @@
         <v>-1.467184</v>
       </c>
       <c r="I87" s="9" t="n">
-        <v>98.43034400000001</v>
+        <v>98.42932</v>
       </c>
       <c r="J87" s="9" t="n">
         <v>98.401898</v>
@@ -7016,7 +7016,7 @@
         <v>-0.997076</v>
       </c>
       <c r="I88" s="6" t="n">
-        <v>98.37706799999999</v>
+        <v>98.37601600000001</v>
       </c>
       <c r="J88" s="6" t="n">
         <v>98.349127</v>
@@ -7096,7 +7096,7 @@
         <v>-0.409008</v>
       </c>
       <c r="I89" s="9" t="n">
-        <v>98.40593</v>
+        <v>98.404894</v>
       </c>
       <c r="J89" s="9" t="n">
         <v>98.387426</v>
@@ -7176,7 +7176,7 @@
         <v>0.27803</v>
       </c>
       <c r="I90" s="6" t="n">
-        <v>98.52335600000001</v>
+        <v>98.522384</v>
       </c>
       <c r="J90" s="6" t="n">
         <v>98.51583599999999</v>
@@ -7258,7 +7258,7 @@
         <v>1.02531</v>
       </c>
       <c r="I91" s="9" t="n">
-        <v>98.706035</v>
+        <v>98.705164</v>
       </c>
       <c r="J91" s="9" t="n">
         <v>98.72013099999999</v>
@@ -7340,7 +7340,7 @@
         <v>1.791974</v>
       </c>
       <c r="I92" s="6" t="n">
-        <v>98.927432</v>
+        <v>98.92668399999999</v>
       </c>
       <c r="J92" s="6" t="n">
         <v>98.972852</v>
@@ -7422,7 +7422,7 @@
         <v>2.541677</v>
       </c>
       <c r="I93" s="9" t="n">
-        <v>99.173542</v>
+        <v>99.172929</v>
       </c>
       <c r="J93" s="9" t="n">
         <v>99.232601</v>
@@ -7504,7 +7504,7 @@
         <v>3.225731</v>
       </c>
       <c r="I94" s="6" t="n">
-        <v>99.368635</v>
+        <v>99.36812999999999</v>
       </c>
       <c r="J94" s="6" t="n">
         <v>99.465559</v>
@@ -7586,7 +7586,7 @@
         <v>3.729683</v>
       </c>
       <c r="I95" s="9" t="n">
-        <v>99.501644</v>
+        <v>99.501212</v>
       </c>
       <c r="J95" s="9" t="n">
         <v>99.654509</v>
@@ -7668,7 +7668,7 @@
         <v>3.918935</v>
       </c>
       <c r="I96" s="6" t="n">
-        <v>99.59035299999999</v>
+        <v>99.58997100000001</v>
       </c>
       <c r="J96" s="6" t="n">
         <v>99.797939</v>
@@ -7750,7 +7750,7 @@
         <v>3.689352</v>
       </c>
       <c r="I97" s="9" t="n">
-        <v>99.653149</v>
+        <v>99.65280199999999</v>
       </c>
       <c r="J97" s="9" t="n">
         <v>99.898597</v>
@@ -7832,7 +7832,7 @@
         <v>3.022983</v>
       </c>
       <c r="I98" s="6" t="n">
-        <v>99.68222</v>
+        <v>99.681888</v>
       </c>
       <c r="J98" s="6" t="n">
         <v>99.95589699999999</v>
@@ -7914,7 +7914,7 @@
         <v>2.011245</v>
       </c>
       <c r="I99" s="9" t="n">
-        <v>99.685993</v>
+        <v>99.68566300000001</v>
       </c>
       <c r="J99" s="9" t="n">
         <v>99.955144</v>
@@ -7996,7 +7996,7 @@
         <v>0.810294</v>
       </c>
       <c r="I100" s="6" t="n">
-        <v>99.632316</v>
+        <v>99.631958</v>
       </c>
       <c r="J100" s="6" t="n">
         <v>99.899158</v>
@@ -8078,7 +8078,7 @@
         <v>-0.364859</v>
       </c>
       <c r="I101" s="9" t="n">
-        <v>99.51055599999999</v>
+        <v>99.51013</v>
       </c>
       <c r="J101" s="9" t="n">
         <v>99.79517</v>
@@ -8160,7 +8160,7 @@
         <v>-1.347299</v>
       </c>
       <c r="I102" s="6" t="n">
-        <v>99.347176</v>
+        <v>99.346661</v>
       </c>
       <c r="J102" s="6" t="n">
         <v>99.65251600000001</v>
@@ -8242,7 +8242,7 @@
         <v>-2.07409</v>
       </c>
       <c r="I103" s="9" t="n">
-        <v>99.17376299999999</v>
+        <v>99.173152</v>
       </c>
       <c r="J103" s="9" t="n">
         <v>99.498215</v>
@@ -8324,7 +8324,7 @@
         <v>-2.54958</v>
       </c>
       <c r="I104" s="6" t="n">
-        <v>99.02681800000001</v>
+        <v>99.026126</v>
       </c>
       <c r="J104" s="6" t="n">
         <v>99.344427</v>
@@ -8406,7 +8406,7 @@
         <v>-2.806614</v>
       </c>
       <c r="I105" s="9" t="n">
-        <v>98.913107</v>
+        <v>98.912353</v>
       </c>
       <c r="J105" s="9" t="n">
         <v>99.214026</v>
@@ -8488,7 +8488,7 @@
         <v>-2.905402</v>
       </c>
       <c r="I106" s="6" t="n">
-        <v>98.822852</v>
+        <v>98.82204900000001</v>
       </c>
       <c r="J106" s="6" t="n">
         <v>99.126301</v>
@@ -8570,7 +8570,7 @@
         <v>-2.849049</v>
       </c>
       <c r="I107" s="9" t="n">
-        <v>98.74999200000001</v>
+        <v>98.74914800000001</v>
       </c>
       <c r="J107" s="9" t="n">
         <v>99.09372500000001</v>
@@ -8652,7 +8652,7 @@
         <v>-2.605571</v>
       </c>
       <c r="I108" s="6" t="n">
-        <v>98.703363</v>
+        <v>98.702493</v>
       </c>
       <c r="J108" s="6" t="n">
         <v>99.118274</v>
@@ -8734,7 +8734,7 @@
         <v>-2.125396</v>
       </c>
       <c r="I109" s="9" t="n">
-        <v>98.707352</v>
+        <v>98.706485</v>
       </c>
       <c r="J109" s="9" t="n">
         <v>99.223685</v>
@@ -8816,7 +8816,7 @@
         <v>-1.394472</v>
       </c>
       <c r="I110" s="6" t="n">
-        <v>98.788275</v>
+        <v>98.787453</v>
       </c>
       <c r="J110" s="6" t="n">
         <v>99.37857</v>
@@ -8898,7 +8898,7 @@
         <v>-0.479021</v>
       </c>
       <c r="I111" s="9" t="n">
-        <v>98.931273</v>
+        <v>98.93053</v>
       </c>
       <c r="J111" s="9" t="n">
         <v>99.56629599999999</v>
@@ -8980,7 +8980,7 @@
         <v>0.487032</v>
       </c>
       <c r="I112" s="6" t="n">
-        <v>99.083788</v>
+        <v>99.08313</v>
       </c>
       <c r="J112" s="6" t="n">
         <v>99.756648</v>
@@ -9062,7 +9062,7 @@
         <v>1.284467</v>
       </c>
       <c r="I113" s="9" t="n">
-        <v>99.250187</v>
+        <v>99.249621</v>
       </c>
       <c r="J113" s="9" t="n">
         <v>99.91161099999999</v>
@@ -9144,7 +9144,7 @@
         <v>1.80276</v>
       </c>
       <c r="I114" s="6" t="n">
-        <v>99.416923</v>
+        <v>99.41645</v>
       </c>
       <c r="J114" s="6" t="n">
         <v>100.021448</v>
@@ -9226,7 +9226,7 @@
         <v>2.050794</v>
       </c>
       <c r="I115" s="9" t="n">
-        <v>99.561936</v>
+        <v>99.561543</v>
       </c>
       <c r="J115" s="9" t="n">
         <v>100.091487</v>
@@ -9308,7 +9308,7 @@
         <v>2.0712</v>
       </c>
       <c r="I116" s="6" t="n">
-        <v>99.674353</v>
+        <v>99.67402199999999</v>
       </c>
       <c r="J116" s="6" t="n">
         <v>100.135738</v>
@@ -9390,7 +9390,7 @@
         <v>1.916345</v>
       </c>
       <c r="I117" s="9" t="n">
-        <v>99.749804</v>
+        <v>99.749515</v>
       </c>
       <c r="J117" s="9" t="n">
         <v>100.164851</v>
@@ -9472,7 +9472,7 @@
         <v>1.664456</v>
       </c>
       <c r="I118" s="6" t="n">
-        <v>99.792914</v>
+        <v>99.79264999999999</v>
       </c>
       <c r="J118" s="6" t="n">
         <v>100.171526</v>
@@ -9554,7 +9554,7 @@
         <v>1.377302</v>
       </c>
       <c r="I119" s="9" t="n">
-        <v>99.80533</v>
+        <v>99.805074</v>
       </c>
       <c r="J119" s="9" t="n">
         <v>100.14894</v>
@@ -9636,7 +9636,7 @@
         <v>1.097791</v>
       </c>
       <c r="I120" s="6" t="n">
-        <v>99.771565</v>
+        <v>99.77128999999999</v>
       </c>
       <c r="J120" s="6" t="n">
         <v>100.084684</v>
@@ -9718,7 +9718,7 @@
         <v>0.823702</v>
       </c>
       <c r="I121" s="9" t="n">
-        <v>99.688689</v>
+        <v>99.68836899999999</v>
       </c>
       <c r="J121" s="9" t="n">
         <v>99.99437</v>
@@ -9800,7 +9800,7 @@
         <v>0.559162</v>
       </c>
       <c r="I122" s="6" t="n">
-        <v>99.592313</v>
+        <v>99.59194100000001</v>
       </c>
       <c r="J122" s="6" t="n">
         <v>99.89514699999999</v>
@@ -9882,7 +9882,7 @@
         <v>0.314489</v>
       </c>
       <c r="I123" s="9" t="n">
-        <v>99.514679</v>
+        <v>99.514264</v>
       </c>
       <c r="J123" s="9" t="n">
         <v>99.82761499999999</v>
@@ -9964,7 +9964,7 @@
         <v>0.107691</v>
       </c>
       <c r="I124" s="6" t="n">
-        <v>99.49818</v>
+        <v>99.497756</v>
       </c>
       <c r="J124" s="6" t="n">
         <v>99.819779</v>
@@ -10046,7 +10046,7 @@
         <v>-0.025756</v>
       </c>
       <c r="I125" s="9" t="n">
-        <v>99.568594</v>
+        <v>99.56820999999999</v>
       </c>
       <c r="J125" s="9" t="n">
         <v>99.88598500000001</v>
@@ -10128,7 +10128,7 @@
         <v>-0.114588</v>
       </c>
       <c r="I126" s="6" t="n">
-        <v>99.710211</v>
+        <v>99.709906</v>
       </c>
       <c r="J126" s="6" t="n">
         <v>100.022931</v>
@@ -10210,7 +10210,7 @@
         <v>-0.185856</v>
       </c>
       <c r="I127" s="9" t="n">
-        <v>99.885671</v>
+        <v>99.885463</v>
       </c>
       <c r="J127" s="9" t="n">
         <v>100.198798</v>
@@ -10292,7 +10292,7 @@
         <v>-0.236064</v>
       </c>
       <c r="I128" s="6" t="n">
-        <v>100.068102</v>
+        <v>100.067996</v>
       </c>
       <c r="J128" s="6" t="n">
         <v>100.393776</v>
@@ -10374,7 +10374,7 @@
         <v>-0.275009</v>
       </c>
       <c r="I129" s="9" t="n">
-        <v>100.257203</v>
+        <v>100.257202</v>
       </c>
       <c r="J129" s="9" t="n">
         <v>100.5642</v>
@@ -10456,7 +10456,7 @@
         <v>-0.323058</v>
       </c>
       <c r="I130" s="6" t="n">
-        <v>100.394832</v>
+        <v>100.394907</v>
       </c>
       <c r="J130" s="6" t="n">
         <v>100.713116</v>
@@ -10538,7 +10538,7 @@
         <v>-0.4219</v>
       </c>
       <c r="I131" s="9" t="n">
-        <v>100.505706</v>
+        <v>100.505843</v>
       </c>
       <c r="J131" s="9" t="n">
         <v>100.821062</v>
@@ -10620,7 +10620,7 @@
         <v>-0.562029</v>
       </c>
       <c r="I132" s="6" t="n">
-        <v>100.587575</v>
+        <v>100.587758</v>
       </c>
       <c r="J132" s="6" t="n">
         <v>100.881548</v>
@@ -10702,7 +10702,7 @@
         <v>-0.688294</v>
       </c>
       <c r="I133" s="9" t="n">
-        <v>100.64489</v>
+        <v>100.645105</v>
       </c>
       <c r="J133" s="9" t="n">
         <v>100.889291</v>
@@ -10784,7 +10784,7 @@
         <v>-0.75161</v>
       </c>
       <c r="I134" s="6" t="n">
-        <v>100.694359</v>
+        <v>100.694602</v>
       </c>
       <c r="J134" s="6" t="n">
         <v>100.850717</v>
@@ -10866,7 +10866,7 @@
         <v>-0.736541</v>
       </c>
       <c r="I135" s="9" t="n">
-        <v>100.733577</v>
+        <v>100.733843</v>
       </c>
       <c r="J135" s="9" t="n">
         <v>100.777324</v>
@@ -10948,7 +10948,7 @@
         <v>-0.671682</v>
       </c>
       <c r="I136" s="6" t="n">
-        <v>100.761333</v>
+        <v>100.761615</v>
       </c>
       <c r="J136" s="6" t="n">
         <v>100.678858</v>
@@ -11030,7 +11030,7 @@
         <v>-0.5599229999999999</v>
       </c>
       <c r="I137" s="9" t="n">
-        <v>100.778761</v>
+        <v>100.779053</v>
       </c>
       <c r="J137" s="9" t="n">
         <v>100.583887</v>
@@ -11112,7 +11112,7 @@
         <v>-0.3893</v>
       </c>
       <c r="I138" s="6" t="n">
-        <v>100.793475</v>
+        <v>100.793776</v>
       </c>
       <c r="J138" s="6" t="n">
         <v>100.516886</v>
@@ -11194,7 +11194,7 @@
         <v>-0.158451</v>
       </c>
       <c r="I139" s="9" t="n">
-        <v>100.843834</v>
+        <v>100.844164</v>
       </c>
       <c r="J139" s="9" t="n">
         <v>100.473741</v>
@@ -11276,7 +11276,7 @@
         <v>0.085864</v>
       </c>
       <c r="I140" s="6" t="n">
-        <v>100.920915</v>
+        <v>100.921288</v>
       </c>
       <c r="J140" s="6" t="n">
         <v>100.448523</v>
@@ -11358,7 +11358,7 @@
         <v>0.317887</v>
       </c>
       <c r="I141" s="9" t="n">
-        <v>100.988605</v>
+        <v>100.989016</v>
       </c>
       <c r="J141" s="9" t="n">
         <v>100.439758</v>
@@ -11440,7 +11440,7 @@
         <v>0.52927</v>
       </c>
       <c r="I142" s="6" t="n">
-        <v>101.033444</v>
+        <v>101.03388</v>
       </c>
       <c r="J142" s="6" t="n">
         <v>100.424242</v>
@@ -11522,7 +11522,7 @@
         <v>0.746846</v>
       </c>
       <c r="I143" s="9" t="n">
-        <v>101.018411</v>
+        <v>101.01884</v>
       </c>
       <c r="J143" s="9" t="n">
         <v>100.399291</v>
@@ -11604,7 +11604,7 @@
         <v>0.977548</v>
       </c>
       <c r="I144" s="6" t="n">
-        <v>100.928267</v>
+        <v>100.928647</v>
       </c>
       <c r="J144" s="6" t="n">
         <v>100.383255</v>
@@ -11686,7 +11686,7 @@
         <v>1.204679</v>
       </c>
       <c r="I145" s="9" t="n">
-        <v>100.850567</v>
+        <v>100.850905</v>
       </c>
       <c r="J145" s="9" t="n">
         <v>100.377672</v>
@@ -11768,7 +11768,7 @@
         <v>1.396546</v>
       </c>
       <c r="I146" s="6" t="n">
-        <v>100.82501</v>
+        <v>100.825335</v>
       </c>
       <c r="J146" s="6" t="n">
         <v>100.394328</v>
@@ -11850,7 +11850,7 @@
         <v>1.538309</v>
       </c>
       <c r="I147" s="9" t="n">
-        <v>100.856509</v>
+        <v>100.856851</v>
       </c>
       <c r="J147" s="9" t="n">
         <v>100.426646</v>
@@ -11932,7 +11932,7 @@
         <v>1.670721</v>
       </c>
       <c r="I148" s="6" t="n">
-        <v>100.904768</v>
+        <v>100.90514</v>
       </c>
       <c r="J148" s="6" t="n">
         <v>100.433171</v>
@@ -12014,7 +12014,7 @@
         <v>1.78742</v>
       </c>
       <c r="I149" s="9" t="n">
-        <v>100.947485</v>
+        <v>100.947883</v>
       </c>
       <c r="J149" s="9" t="n">
         <v>100.436831</v>
@@ -12096,7 +12096,7 @@
         <v>1.851335</v>
       </c>
       <c r="I150" s="6" t="n">
-        <v>100.986634</v>
+        <v>100.987057</v>
       </c>
       <c r="J150" s="6" t="n">
         <v>100.475893</v>
@@ -12178,7 +12178,7 @@
         <v>1.797337</v>
       </c>
       <c r="I151" s="9" t="n">
-        <v>101.037413</v>
+        <v>101.037869</v>
       </c>
       <c r="J151" s="9" t="n">
         <v>100.580804</v>
@@ -12260,7 +12260,7 @@
         <v>1.613138</v>
       </c>
       <c r="I152" s="6" t="n">
-        <v>101.115317</v>
+        <v>101.11582</v>
       </c>
       <c r="J152" s="6" t="n">
         <v>100.719605</v>
@@ -12342,7 +12342,7 @@
         <v>1.316183</v>
       </c>
       <c r="I153" s="9" t="n">
-        <v>101.209877</v>
+        <v>101.210437</v>
       </c>
       <c r="J153" s="9" t="n">
         <v>100.835197</v>
@@ -12424,7 +12424,7 @@
         <v>0.923685</v>
       </c>
       <c r="I154" s="6" t="n">
-        <v>101.260421</v>
+        <v>101.26101</v>
       </c>
       <c r="J154" s="6" t="n">
         <v>100.933559</v>
@@ -12506,7 +12506,7 @@
         <v>0.470935</v>
       </c>
       <c r="I155" s="9" t="n">
-        <v>101.244913</v>
+        <v>101.245488</v>
       </c>
       <c r="J155" s="9" t="n">
         <v>100.984516</v>
@@ -12588,7 +12588,7 @@
         <v>0.01447</v>
       </c>
       <c r="I156" s="6" t="n">
-        <v>101.165925</v>
+        <v>101.16644</v>
       </c>
       <c r="J156" s="6" t="n">
         <v>100.970039</v>
@@ -12670,7 +12670,7 @@
         <v>-0.403561</v>
       </c>
       <c r="I157" s="9" t="n">
-        <v>101.063598</v>
+        <v>101.064022</v>
       </c>
       <c r="J157" s="9" t="n">
         <v>100.897102</v>
@@ -12752,7 +12752,7 @@
         <v>-0.740448</v>
       </c>
       <c r="I158" s="6" t="n">
-        <v>100.967689</v>
+        <v>100.968004</v>
       </c>
       <c r="J158" s="6" t="n">
         <v>100.806405</v>
@@ -12834,7 +12834,7 @@
         <v>-0.9863730000000001</v>
       </c>
       <c r="I159" s="9" t="n">
-        <v>100.916811</v>
+        <v>100.917017</v>
       </c>
       <c r="J159" s="9" t="n">
         <v>100.70739</v>
@@ -12916,7 +12916,7 @@
         <v>-1.185288</v>
       </c>
       <c r="I160" s="6" t="n">
-        <v>100.869191</v>
+        <v>100.869268</v>
       </c>
       <c r="J160" s="6" t="n">
         <v>100.622121</v>
@@ -12998,7 +12998,7 @@
         <v>-1.380066</v>
       </c>
       <c r="I161" s="9" t="n">
-        <v>100.815894</v>
+        <v>100.815835</v>
       </c>
       <c r="J161" s="9" t="n">
         <v>100.585203</v>
@@ -13080,7 +13080,7 @@
         <v>-1.565538</v>
       </c>
       <c r="I162" s="6" t="n">
-        <v>100.791526</v>
+        <v>100.791382</v>
       </c>
       <c r="J162" s="6" t="n">
         <v>100.605382</v>
@@ -13162,7 +13162,7 @@
         <v>-1.690168</v>
       </c>
       <c r="I163" s="9" t="n">
-        <v>100.808325</v>
+        <v>100.808215</v>
       </c>
       <c r="J163" s="9" t="n">
         <v>100.668895</v>
@@ -13244,7 +13244,7 @@
         <v>-1.700136</v>
       </c>
       <c r="I164" s="6" t="n">
-        <v>100.821538</v>
+        <v>100.821534</v>
       </c>
       <c r="J164" s="6" t="n">
         <v>100.713691</v>
@@ -13326,7 +13326,7 @@
         <v>-1.585816</v>
       </c>
       <c r="I165" s="9" t="n">
-        <v>100.816038</v>
+        <v>100.816181</v>
       </c>
       <c r="J165" s="9" t="n">
         <v>100.711516</v>
@@ -13408,7 +13408,7 @@
         <v>-1.319131</v>
       </c>
       <c r="I166" s="6" t="n">
-        <v>100.804199</v>
+        <v>100.804559</v>
       </c>
       <c r="J166" s="6" t="n">
         <v>100.676673</v>
@@ -13490,7 +13490,7 @@
         <v>-0.891714</v>
       </c>
       <c r="I167" s="9" t="n">
-        <v>100.775722</v>
+        <v>100.776298</v>
       </c>
       <c r="J167" s="9" t="n">
         <v>100.629852</v>
@@ -13572,7 +13572,7 @@
         <v>-0.379082</v>
       </c>
       <c r="I168" s="6" t="n">
-        <v>100.736747</v>
+        <v>100.737375</v>
       </c>
       <c r="J168" s="6" t="n">
         <v>100.594988</v>
@@ -13654,7 +13654,7 @@
         <v>0.158533</v>
       </c>
       <c r="I169" s="9" t="n">
-        <v>100.674338</v>
+        <v>100.67486</v>
       </c>
       <c r="J169" s="9" t="n">
         <v>100.579165</v>
@@ -13736,7 +13736,7 @@
         <v>0.662389</v>
       </c>
       <c r="I170" s="6" t="n">
-        <v>100.609042</v>
+        <v>100.609379</v>
       </c>
       <c r="J170" s="6" t="n">
         <v>100.591657</v>
@@ -13818,7 +13818,7 @@
         <v>1.097817</v>
       </c>
       <c r="I171" s="9" t="n">
-        <v>100.576462</v>
+        <v>100.576673</v>
       </c>
       <c r="J171" s="9" t="n">
         <v>100.645569</v>
@@ -13900,7 +13900,7 @@
         <v>1.443139</v>
       </c>
       <c r="I172" s="6" t="n">
-        <v>100.607447</v>
+        <v>100.6076</v>
       </c>
       <c r="J172" s="6" t="n">
         <v>100.746071</v>
@@ -13982,7 +13982,7 @@
         <v>1.696868</v>
       </c>
       <c r="I173" s="9" t="n">
-        <v>100.716753</v>
+        <v>100.716863</v>
       </c>
       <c r="J173" s="9" t="n">
         <v>100.891962</v>
@@ -14064,7 +14064,7 @@
         <v>1.849367</v>
       </c>
       <c r="I174" s="6" t="n">
-        <v>100.883377</v>
+        <v>100.883616</v>
       </c>
       <c r="J174" s="6" t="n">
         <v>101.064597</v>
@@ -14146,7 +14146,7 @@
         <v>1.879576</v>
       </c>
       <c r="I175" s="9" t="n">
-        <v>101.092654</v>
+        <v>101.093095</v>
       </c>
       <c r="J175" s="9" t="n">
         <v>101.249497</v>
@@ -14228,7 +14228,7 @@
         <v>1.775524</v>
       </c>
       <c r="I176" s="6" t="n">
-        <v>101.333522</v>
+        <v>101.334177</v>
       </c>
       <c r="J176" s="6" t="n">
         <v>101.436302</v>
@@ -14310,7 +14310,7 @@
         <v>1.571513</v>
       </c>
       <c r="I177" s="9" t="n">
-        <v>101.573585</v>
+        <v>101.574337</v>
       </c>
       <c r="J177" s="9" t="n">
         <v>101.587182</v>
@@ -14392,7 +14392,7 @@
         <v>1.301408</v>
       </c>
       <c r="I178" s="6" t="n">
-        <v>101.765591</v>
+        <v>101.76633</v>
       </c>
       <c r="J178" s="6" t="n">
         <v>101.645416</v>
@@ -14474,7 +14474,7 @@
         <v>0.973733</v>
       </c>
       <c r="I179" s="9" t="n">
-        <v>101.901437</v>
+        <v>101.902082</v>
       </c>
       <c r="J179" s="9" t="n">
         <v>101.646356</v>
@@ -14556,7 +14556,7 @@
         <v>0.623185</v>
       </c>
       <c r="I180" s="6" t="n">
-        <v>101.985937</v>
+        <v>101.986594</v>
       </c>
       <c r="J180" s="6" t="n">
         <v>101.60753</v>
@@ -14638,7 +14638,7 @@
         <v>0.224686</v>
       </c>
       <c r="I181" s="9" t="n">
-        <v>102.024532</v>
+        <v>102.025339</v>
       </c>
       <c r="J181" s="9" t="n">
         <v>101.520787</v>
@@ -14720,7 +14720,7 @@
         <v>-0.300493</v>
       </c>
       <c r="I182" s="6" t="n">
-        <v>101.978355</v>
+        <v>101.979362</v>
       </c>
       <c r="J182" s="6" t="n">
         <v>101.345569</v>
@@ -14802,7 +14802,7 @@
         <v>-1.032336</v>
       </c>
       <c r="I183" s="9" t="n">
-        <v>101.786267</v>
+        <v>101.787403</v>
       </c>
       <c r="J183" s="9" t="n">
         <v>101.039601</v>
@@ -14884,7 +14884,7 @@
         <v>-2.008815</v>
       </c>
       <c r="I184" s="6" t="n">
-        <v>101.3872</v>
+        <v>101.388268</v>
       </c>
       <c r="J184" s="6" t="n">
         <v>100.574121</v>
@@ -14966,7 +14966,7 @@
         <v>-3.182057</v>
       </c>
       <c r="I185" s="9" t="n">
-        <v>100.739302</v>
+        <v>100.740003</v>
       </c>
       <c r="J185" s="9" t="n">
         <v>99.934015</v>
@@ -15048,7 +15048,7 @@
         <v>-4.399908</v>
       </c>
       <c r="I186" s="6" t="n">
-        <v>99.854798</v>
+        <v>99.854777</v>
       </c>
       <c r="J186" s="6" t="n">
         <v>99.137669</v>
@@ -15130,7 +15130,7 @@
         <v>-5.425646</v>
       </c>
       <c r="I187" s="9" t="n">
-        <v>98.80493199999999</v>
+        <v>98.803917</v>
       </c>
       <c r="J187" s="9" t="n">
         <v>98.270432</v>
@@ -15212,7 +15212,7 @@
         <v>-6.036267</v>
       </c>
       <c r="I188" s="6" t="n">
-        <v>97.78291299999999</v>
+        <v>97.781021</v>
       </c>
       <c r="J188" s="6" t="n">
         <v>97.439623</v>
@@ -15294,7 +15294,7 @@
         <v>-6.150249</v>
       </c>
       <c r="I189" s="9" t="n">
-        <v>96.91513500000001</v>
+        <v>96.912764</v>
       </c>
       <c r="J189" s="9" t="n">
         <v>96.732235</v>
@@ -15376,7 +15376,7 @@
         <v>-5.854175</v>
       </c>
       <c r="I190" s="6" t="n">
-        <v>96.30721</v>
+        <v>96.304697</v>
       </c>
       <c r="J190" s="6" t="n">
         <v>96.230881</v>
@@ -15458,7 +15458,7 @@
         <v>-5.306489</v>
       </c>
       <c r="I191" s="9" t="n">
-        <v>95.986278</v>
+        <v>95.983831</v>
       </c>
       <c r="J191" s="9" t="n">
         <v>95.961422</v>
@@ -15540,7 +15540,7 @@
         <v>-4.676242</v>
       </c>
       <c r="I192" s="6" t="n">
-        <v>95.906893</v>
+        <v>95.90464900000001</v>
       </c>
       <c r="J192" s="6" t="n">
         <v>95.90942200000001</v>
@@ -15622,7 +15622,7 @@
         <v>-4.048365</v>
       </c>
       <c r="I193" s="9" t="n">
-        <v>96.007683</v>
+        <v>96.005684</v>
       </c>
       <c r="J193" s="9" t="n">
         <v>96.044656</v>
@@ -15704,7 +15704,7 @@
         <v>-3.400466</v>
       </c>
       <c r="I194" s="6" t="n">
-        <v>96.235477</v>
+        <v>96.23366</v>
       </c>
       <c r="J194" s="6" t="n">
         <v>96.334616</v>
@@ -15786,7 +15786,7 @@
         <v>-2.647555</v>
       </c>
       <c r="I195" s="9" t="n">
-        <v>96.55834</v>
+        <v>96.556589</v>
       </c>
       <c r="J195" s="9" t="n">
         <v>96.731908</v>
@@ -15868,7 +15868,7 @@
         <v>-1.671445</v>
       </c>
       <c r="I196" s="6" t="n">
-        <v>96.972919</v>
+        <v>96.971158</v>
       </c>
       <c r="J196" s="6" t="n">
         <v>97.182171</v>
@@ -15950,7 +15950,7 @@
         <v>-0.448657</v>
       </c>
       <c r="I197" s="9" t="n">
-        <v>97.387187</v>
+        <v>97.385548</v>
       </c>
       <c r="J197" s="9" t="n">
         <v>97.62759200000001</v>
@@ -16032,7 +16032,7 @@
         <v>0.895357</v>
       </c>
       <c r="I198" s="6" t="n">
-        <v>97.702088</v>
+        <v>97.700647</v>
       </c>
       <c r="J198" s="6" t="n">
         <v>97.977828</v>
@@ -16114,7 +16114,7 @@
         <v>2.125597</v>
       </c>
       <c r="I199" s="9" t="n">
-        <v>97.907241</v>
+        <v>97.905906</v>
       </c>
       <c r="J199" s="9" t="n">
         <v>98.22838</v>
@@ -16196,7 +16196,7 @@
         <v>3.023423</v>
       </c>
       <c r="I200" s="6" t="n">
-        <v>98.042912</v>
+        <v>98.041636</v>
       </c>
       <c r="J200" s="6" t="n">
         <v>98.40828</v>
@@ -16278,7 +16278,7 @@
         <v>3.472474</v>
       </c>
       <c r="I201" s="9" t="n">
-        <v>98.140366</v>
+        <v>98.13914200000001</v>
       </c>
       <c r="J201" s="9" t="n">
         <v>98.537435</v>
@@ -16360,7 +16360,7 @@
         <v>3.485766</v>
       </c>
       <c r="I202" s="6" t="n">
-        <v>98.234195</v>
+        <v>98.23297599999999</v>
       </c>
       <c r="J202" s="6" t="n">
         <v>98.64779900000001</v>
@@ -16442,7 +16442,7 @@
         <v>3.176567</v>
       </c>
       <c r="I203" s="9" t="n">
-        <v>98.32529599999999</v>
+        <v>98.324212</v>
       </c>
       <c r="J203" s="9" t="n">
         <v>98.744041</v>
@@ -16524,7 +16524,7 @@
         <v>2.728323</v>
       </c>
       <c r="I204" s="6" t="n">
-        <v>98.414328</v>
+        <v>98.41337300000001</v>
       </c>
       <c r="J204" s="6" t="n">
         <v>98.825654</v>
@@ -16606,7 +16606,7 @@
         <v>2.30256</v>
       </c>
       <c r="I205" s="9" t="n">
-        <v>98.51594299999999</v>
+        <v>98.515066</v>
       </c>
       <c r="J205" s="9" t="n">
         <v>98.91305199999999</v>
@@ -16688,7 +16688,7 @@
         <v>1.961701</v>
       </c>
       <c r="I206" s="6" t="n">
-        <v>98.642625</v>
+        <v>98.641824</v>
       </c>
       <c r="J206" s="6" t="n">
         <v>99.024914</v>
@@ -16770,7 +16770,7 @@
         <v>1.723988</v>
       </c>
       <c r="I207" s="9" t="n">
-        <v>98.786918</v>
+        <v>98.786248</v>
       </c>
       <c r="J207" s="9" t="n">
         <v>99.163589</v>
@@ -16852,7 +16852,7 @@
         <v>1.565028</v>
       </c>
       <c r="I208" s="6" t="n">
-        <v>98.93024699999999</v>
+        <v>98.92958</v>
       </c>
       <c r="J208" s="6" t="n">
         <v>99.30376</v>
@@ -16934,7 +16934,7 @@
         <v>1.469007</v>
       </c>
       <c r="I209" s="9" t="n">
-        <v>99.05145</v>
+        <v>99.05066600000001</v>
       </c>
       <c r="J209" s="9" t="n">
         <v>99.421137</v>
@@ -17016,7 +17016,7 @@
         <v>1.423851</v>
       </c>
       <c r="I210" s="6" t="n">
-        <v>99.153318</v>
+        <v>99.15240900000001</v>
       </c>
       <c r="J210" s="6" t="n">
         <v>99.50055999999999</v>
@@ -17098,7 +17098,7 @@
         <v>1.420496</v>
       </c>
       <c r="I211" s="9" t="n">
-        <v>99.267517</v>
+        <v>99.266676</v>
       </c>
       <c r="J211" s="9" t="n">
         <v>99.588368</v>
@@ -17180,7 +17180,7 @@
         <v>1.427499</v>
       </c>
       <c r="I212" s="6" t="n">
-        <v>99.414422</v>
+        <v>99.413782</v>
       </c>
       <c r="J212" s="6" t="n">
         <v>99.708653</v>
@@ -17262,7 +17262,7 @@
         <v>1.467977</v>
       </c>
       <c r="I213" s="9" t="n">
-        <v>99.597435</v>
+        <v>99.59703</v>
       </c>
       <c r="J213" s="9" t="n">
         <v>99.86756200000001</v>
@@ -17344,7 +17344,7 @@
         <v>1.580157</v>
       </c>
       <c r="I214" s="6" t="n">
-        <v>99.802319</v>
+        <v>99.802103</v>
       </c>
       <c r="J214" s="6" t="n">
         <v>100.051055</v>
@@ -17426,7 +17426,7 @@
         <v>1.766532</v>
       </c>
       <c r="I215" s="9" t="n">
-        <v>100.012214</v>
+        <v>100.012104</v>
       </c>
       <c r="J215" s="9" t="n">
         <v>100.242996</v>
@@ -17508,7 +17508,7 @@
         <v>1.968989</v>
       </c>
       <c r="I216" s="6" t="n">
-        <v>100.217371</v>
+        <v>100.217411</v>
       </c>
       <c r="J216" s="6" t="n">
         <v>100.429828</v>
@@ -17590,7 +17590,7 @@
         <v>2.125809</v>
       </c>
       <c r="I217" s="9" t="n">
-        <v>100.427421</v>
+        <v>100.427568</v>
       </c>
       <c r="J217" s="9" t="n">
         <v>100.606981</v>
@@ -17672,7 +17672,7 @@
         <v>2.231963</v>
       </c>
       <c r="I218" s="6" t="n">
-        <v>100.642805</v>
+        <v>100.643096</v>
       </c>
       <c r="J218" s="6" t="n">
         <v>100.777972</v>
@@ -17754,7 +17754,7 @@
         <v>2.258132</v>
       </c>
       <c r="I219" s="9" t="n">
-        <v>100.857957</v>
+        <v>100.858339</v>
       </c>
       <c r="J219" s="9" t="n">
         <v>100.951876</v>
@@ -17836,7 +17836,7 @@
         <v>2.186849</v>
       </c>
       <c r="I220" s="6" t="n">
-        <v>101.052415</v>
+        <v>101.053014</v>
       </c>
       <c r="J220" s="6" t="n">
         <v>101.125506</v>
@@ -17918,7 +17918,7 @@
         <v>2.012431</v>
       </c>
       <c r="I221" s="9" t="n">
-        <v>101.216743</v>
+        <v>101.217562</v>
       </c>
       <c r="J221" s="9" t="n">
         <v>101.294793</v>
@@ -18000,7 +18000,7 @@
         <v>1.744397</v>
       </c>
       <c r="I222" s="6" t="n">
-        <v>101.360058</v>
+        <v>101.361019</v>
       </c>
       <c r="J222" s="6" t="n">
         <v>101.453255</v>
@@ -18082,7 +18082,7 @@
         <v>1.420423</v>
       </c>
       <c r="I223" s="9" t="n">
-        <v>101.472909</v>
+        <v>101.473835</v>
       </c>
       <c r="J223" s="9" t="n">
         <v>101.575128</v>
@@ -18164,7 +18164,7 @@
         <v>1.041822</v>
       </c>
       <c r="I224" s="6" t="n">
-        <v>101.528942</v>
+        <v>101.529729</v>
       </c>
       <c r="J224" s="6" t="n">
         <v>101.629326</v>
@@ -18246,7 +18246,7 @@
         <v>0.561304</v>
       </c>
       <c r="I225" s="9" t="n">
-        <v>101.512951</v>
+        <v>101.513487</v>
       </c>
       <c r="J225" s="9" t="n">
         <v>101.606158</v>
@@ -18328,7 +18328,7 @@
         <v>-0.043194</v>
       </c>
       <c r="I226" s="6" t="n">
-        <v>101.435685</v>
+        <v>101.436028</v>
       </c>
       <c r="J226" s="6" t="n">
         <v>101.52207</v>
@@ -18410,7 +18410,7 @@
         <v>-0.742682</v>
       </c>
       <c r="I227" s="9" t="n">
-        <v>101.322059</v>
+        <v>101.322242</v>
       </c>
       <c r="J227" s="9" t="n">
         <v>101.399451</v>
@@ -18492,7 +18492,7 @@
         <v>-1.477418</v>
       </c>
       <c r="I228" s="6" t="n">
-        <v>101.198956</v>
+        <v>101.198958</v>
       </c>
       <c r="J228" s="6" t="n">
         <v>101.275459</v>
@@ -18574,7 +18574,7 @@
         <v>-2.177745</v>
       </c>
       <c r="I229" s="9" t="n">
-        <v>101.071242</v>
+        <v>101.071269</v>
       </c>
       <c r="J229" s="9" t="n">
         <v>101.166954</v>
@@ -18656,7 +18656,7 @@
         <v>-2.724461</v>
       </c>
       <c r="I230" s="6" t="n">
-        <v>100.945044</v>
+        <v>100.945175</v>
       </c>
       <c r="J230" s="6" t="n">
         <v>101.076699</v>
@@ -18738,7 +18738,7 @@
         <v>-3.030145</v>
       </c>
       <c r="I231" s="9" t="n">
-        <v>100.83971</v>
+        <v>100.839905</v>
       </c>
       <c r="J231" s="9" t="n">
         <v>101.009552</v>
@@ -18820,7 +18820,7 @@
         <v>-3.100455</v>
       </c>
       <c r="I232" s="6" t="n">
-        <v>100.768867</v>
+        <v>100.76906</v>
       </c>
       <c r="J232" s="6" t="n">
         <v>100.963714</v>
@@ -18902,7 +18902,7 @@
         <v>-2.976044</v>
       </c>
       <c r="I233" s="9" t="n">
-        <v>100.731165</v>
+        <v>100.7314</v>
       </c>
       <c r="J233" s="9" t="n">
         <v>100.9331</v>
@@ -18984,7 +18984,7 @@
         <v>-2.677645</v>
       </c>
       <c r="I234" s="6" t="n">
-        <v>100.710584</v>
+        <v>100.710807</v>
       </c>
       <c r="J234" s="6" t="n">
         <v>100.900787</v>
@@ -19066,7 +19066,7 @@
         <v>-2.239424</v>
       </c>
       <c r="I235" s="9" t="n">
-        <v>100.688487</v>
+        <v>100.688715</v>
       </c>
       <c r="J235" s="9" t="n">
         <v>100.859061</v>
@@ -19148,7 +19148,7 @@
         <v>-1.682009</v>
       </c>
       <c r="I236" s="6" t="n">
-        <v>100.662428</v>
+        <v>100.662718</v>
       </c>
       <c r="J236" s="6" t="n">
         <v>100.801514</v>
@@ -19230,7 +19230,7 @@
         <v>-1.040691</v>
       </c>
       <c r="I237" s="9" t="n">
-        <v>100.631096</v>
+        <v>100.631436</v>
       </c>
       <c r="J237" s="9" t="n">
         <v>100.724187</v>
@@ -19312,7 +19312,7 @@
         <v>-0.379119</v>
       </c>
       <c r="I238" s="6" t="n">
-        <v>100.598189</v>
+        <v>100.598586</v>
       </c>
       <c r="J238" s="6" t="n">
         <v>100.626892</v>
@@ -19394,7 +19394,7 @@
         <v>0.271591</v>
       </c>
       <c r="I239" s="9" t="n">
-        <v>100.572496</v>
+        <v>100.572942</v>
       </c>
       <c r="J239" s="9" t="n">
         <v>100.537404</v>
@@ -19476,7 +19476,7 @@
         <v>0.917283</v>
       </c>
       <c r="I240" s="6" t="n">
-        <v>100.574426</v>
+        <v>100.57487</v>
       </c>
       <c r="J240" s="6" t="n">
         <v>100.484594</v>
@@ -19558,7 +19558,7 @@
         <v>1.545798</v>
       </c>
       <c r="I241" s="9" t="n">
-        <v>100.610625</v>
+        <v>100.610989</v>
       </c>
       <c r="J241" s="9" t="n">
         <v>100.484384</v>
@@ -19640,7 +19640,7 @@
         <v>2.1006</v>
       </c>
       <c r="I242" s="6" t="n">
-        <v>100.69332</v>
+        <v>100.693563</v>
       </c>
       <c r="J242" s="6" t="n">
         <v>100.542596</v>
@@ -19722,7 +19722,7 @@
         <v>2.533705</v>
       </c>
       <c r="I243" s="9" t="n">
-        <v>100.822552</v>
+        <v>100.822833</v>
       </c>
       <c r="J243" s="9" t="n">
         <v>100.656932</v>
@@ -19804,7 +19804,7 @@
         <v>2.817838</v>
       </c>
       <c r="I244" s="6" t="n">
-        <v>101.006498</v>
+        <v>101.006919</v>
       </c>
       <c r="J244" s="6" t="n">
         <v>100.838893</v>
@@ -19886,7 +19886,7 @@
         <v>2.929408</v>
       </c>
       <c r="I245" s="9" t="n">
-        <v>101.236833</v>
+        <v>101.237319</v>
       </c>
       <c r="J245" s="9" t="n">
         <v>101.079707</v>
@@ -19968,7 +19968,7 @@
         <v>2.858063</v>
       </c>
       <c r="I246" s="6" t="n">
-        <v>101.476217</v>
+        <v>101.476854</v>
       </c>
       <c r="J246" s="6" t="n">
         <v>101.35663</v>
@@ -20050,7 +20050,7 @@
         <v>2.614067</v>
       </c>
       <c r="I247" s="9" t="n">
-        <v>101.668468</v>
+        <v>101.669203</v>
       </c>
       <c r="J247" s="9" t="n">
         <v>101.62921</v>
@@ -20132,7 +20132,7 @@
         <v>2.251081</v>
       </c>
       <c r="I248" s="6" t="n">
-        <v>101.816855</v>
+        <v>101.817562</v>
       </c>
       <c r="J248" s="6" t="n">
         <v>101.859607</v>
@@ -20214,7 +20214,7 @@
         <v>1.827043</v>
       </c>
       <c r="I249" s="9" t="n">
-        <v>101.937711</v>
+        <v>101.938496</v>
       </c>
       <c r="J249" s="9" t="n">
         <v>102.033326</v>
@@ -20296,7 +20296,7 @@
         <v>1.427139</v>
       </c>
       <c r="I250" s="6" t="n">
-        <v>102.036641</v>
+        <v>102.037514</v>
       </c>
       <c r="J250" s="6" t="n">
         <v>102.154063</v>
@@ -20378,7 +20378,7 @@
         <v>1.107264</v>
       </c>
       <c r="I251" s="9" t="n">
-        <v>102.099148</v>
+        <v>102.10011</v>
       </c>
       <c r="J251" s="9" t="n">
         <v>102.208027</v>
@@ -20460,7 +20460,7 @@
         <v>0.819308</v>
       </c>
       <c r="I252" s="6" t="n">
-        <v>102.104737</v>
+        <v>102.105857</v>
       </c>
       <c r="J252" s="6" t="n">
         <v>102.173246</v>
@@ -20542,7 +20542,7 @@
         <v>0.525068</v>
       </c>
       <c r="I253" s="9" t="n">
-        <v>102.042884</v>
+        <v>102.04413</v>
       </c>
       <c r="J253" s="9" t="n">
         <v>102.038919</v>
@@ -20624,7 +20624,7 @@
         <v>0.151321</v>
       </c>
       <c r="I254" s="6" t="n">
-        <v>101.92636</v>
+        <v>101.927567</v>
       </c>
       <c r="J254" s="6" t="n">
         <v>101.830198</v>
@@ -20706,7 +20706,7 @@
         <v>-0.332989</v>
       </c>
       <c r="I255" s="9" t="n">
-        <v>101.766719</v>
+        <v>101.76773</v>
       </c>
       <c r="J255" s="9" t="n">
         <v>101.576997</v>
@@ -20788,7 +20788,7 @@
         <v>-0.8726739999999999</v>
       </c>
       <c r="I256" s="6" t="n">
-        <v>101.574575</v>
+        <v>101.575308</v>
       </c>
       <c r="J256" s="6" t="n">
         <v>101.309641</v>
@@ -20870,7 +20870,7 @@
         <v>-1.393789</v>
       </c>
       <c r="I257" s="9" t="n">
-        <v>101.367834</v>
+        <v>101.368384</v>
       </c>
       <c r="J257" s="9" t="n">
         <v>101.067279</v>
@@ -20952,7 +20952,7 @@
         <v>-1.826023</v>
       </c>
       <c r="I258" s="6" t="n">
-        <v>101.166312</v>
+        <v>101.166747</v>
       </c>
       <c r="J258" s="6" t="n">
         <v>100.878504</v>
@@ -21034,7 +21034,7 @@
         <v>-2.123602</v>
       </c>
       <c r="I259" s="9" t="n">
-        <v>100.964472</v>
+        <v>100.964793</v>
       </c>
       <c r="J259" s="9" t="n">
         <v>100.698913</v>
@@ -21116,7 +21116,7 @@
         <v>-2.270595</v>
       </c>
       <c r="I260" s="6" t="n">
-        <v>100.77503</v>
+        <v>100.775288</v>
       </c>
       <c r="J260" s="6" t="n">
         <v>100.52203</v>
@@ -21198,7 +21198,7 @@
         <v>-2.249019</v>
       </c>
       <c r="I261" s="9" t="n">
-        <v>100.605579</v>
+        <v>100.605748</v>
       </c>
       <c r="J261" s="9" t="n">
         <v>100.364493</v>
@@ -21280,7 +21280,7 @@
         <v>-2.096965</v>
       </c>
       <c r="I262" s="6" t="n">
-        <v>100.458232</v>
+        <v>100.458358</v>
       </c>
       <c r="J262" s="6" t="n">
         <v>100.236657</v>
@@ -21362,7 +21362,7 @@
         <v>-1.921189</v>
       </c>
       <c r="I263" s="9" t="n">
-        <v>100.327363</v>
+        <v>100.327345</v>
       </c>
       <c r="J263" s="9" t="n">
         <v>100.122309</v>
@@ -21444,7 +21444,7 @@
         <v>-1.737511</v>
       </c>
       <c r="I264" s="6" t="n">
-        <v>100.19933</v>
+        <v>100.199074</v>
       </c>
       <c r="J264" s="6" t="n">
         <v>100.005972</v>
@@ -21526,7 +21526,7 @@
         <v>-1.539923</v>
       </c>
       <c r="I265" s="9" t="n">
-        <v>100.059678</v>
+        <v>100.059166</v>
       </c>
       <c r="J265" s="9" t="n">
         <v>99.869801</v>
@@ -21608,7 +21608,7 @@
         <v>-1.279661</v>
       </c>
       <c r="I266" s="6" t="n">
-        <v>99.89010500000001</v>
+        <v>99.88954099999999</v>
       </c>
       <c r="J266" s="6" t="n">
         <v>99.69949699999999</v>
@@ -21690,7 +21690,7 @@
         <v>-0.885038</v>
       </c>
       <c r="I267" s="9" t="n">
-        <v>99.69316000000001</v>
+        <v>99.692621</v>
       </c>
       <c r="J267" s="9" t="n">
         <v>99.48993400000001</v>
@@ -21772,7 +21772,7 @@
         <v>-0.396441</v>
       </c>
       <c r="I268" s="6" t="n">
-        <v>99.49404</v>
+        <v>99.493555</v>
       </c>
       <c r="J268" s="6" t="n">
         <v>99.26567799999999</v>
@@ -21854,7 +21854,7 @@
         <v>0.113278</v>
       </c>
       <c r="I269" s="9" t="n">
-        <v>99.30573200000001</v>
+        <v>99.305325</v>
       </c>
       <c r="J269" s="9" t="n">
         <v>99.032585</v>
@@ -21936,7 +21936,7 @@
         <v>0.548284</v>
       </c>
       <c r="I270" s="6" t="n">
-        <v>99.153239</v>
+        <v>99.15286500000001</v>
       </c>
       <c r="J270" s="6" t="n">
         <v>98.817846</v>
@@ -22018,7 +22018,7 @@
         <v>0.838089</v>
       </c>
       <c r="I271" s="9" t="n">
-        <v>99.073294</v>
+        <v>99.07285299999999</v>
       </c>
       <c r="J271" s="9" t="n">
         <v>98.66255</v>
@@ -22100,7 +22100,7 @@
         <v>0.933156</v>
       </c>
       <c r="I272" s="6" t="n">
-        <v>99.073195</v>
+        <v>99.072687</v>
       </c>
       <c r="J272" s="6" t="n">
         <v>98.605656</v>
@@ -22182,7 +22182,7 @@
         <v>0.784228</v>
       </c>
       <c r="I273" s="9" t="n">
-        <v>99.127313</v>
+        <v>99.126738</v>
       </c>
       <c r="J273" s="9" t="n">
         <v>98.630487</v>
@@ -22264,7 +22264,7 @@
         <v>0.419156</v>
       </c>
       <c r="I274" s="6" t="n">
-        <v>99.204289</v>
+        <v>99.203604</v>
       </c>
       <c r="J274" s="6" t="n">
         <v>98.699488</v>
@@ -22346,7 +22346,7 @@
         <v>-0.054744</v>
       </c>
       <c r="I275" s="9" t="n">
-        <v>99.287983</v>
+        <v>99.287351</v>
       </c>
       <c r="J275" s="9" t="n">
         <v>98.802305</v>
@@ -22428,7 +22428,7 @@
         <v>-0.528853</v>
       </c>
       <c r="I276" s="6" t="n">
-        <v>99.369147</v>
+        <v>99.36861500000001</v>
       </c>
       <c r="J276" s="6" t="n">
         <v>98.92487</v>
@@ -22510,7 +22510,7 @@
         <v>-0.939978</v>
       </c>
       <c r="I277" s="9" t="n">
-        <v>99.43124299999999</v>
+        <v>99.430807</v>
       </c>
       <c r="J277" s="9" t="n">
         <v>99.04654499999999</v>
@@ -22592,7 +22592,7 @@
         <v>-1.30014</v>
       </c>
       <c r="I278" s="6" t="n">
-        <v>99.454618</v>
+        <v>99.454221</v>
       </c>
       <c r="J278" s="6" t="n">
         <v>99.136026</v>
@@ -22674,7 +22674,7 @@
         <v>-1.663288</v>
       </c>
       <c r="I279" s="9" t="n">
-        <v>99.43814</v>
+        <v>99.43778399999999</v>
       </c>
       <c r="J279" s="9" t="n">
         <v>99.174533</v>
@@ -22756,7 +22756,7 @@
         <v>-2.035183</v>
       </c>
       <c r="I280" s="6" t="n">
-        <v>99.382769</v>
+        <v>99.38231500000001</v>
       </c>
       <c r="J280" s="6" t="n">
         <v>99.144839</v>
@@ -22838,7 +22838,7 @@
         <v>-2.402987</v>
       </c>
       <c r="I281" s="9" t="n">
-        <v>99.306066</v>
+        <v>99.305403</v>
       </c>
       <c r="J281" s="9" t="n">
         <v>99.05958800000001</v>
@@ -22920,7 +22920,7 @@
         <v>-2.699433</v>
       </c>
       <c r="I282" s="6" t="n">
-        <v>99.217624</v>
+        <v>99.216711</v>
       </c>
       <c r="J282" s="6" t="n">
         <v>98.96138500000001</v>
@@ -23002,7 +23002,7 @@
         <v>-2.830578</v>
       </c>
       <c r="I283" s="9" t="n">
-        <v>99.121774</v>
+        <v>99.120822</v>
       </c>
       <c r="J283" s="9" t="n">
         <v>98.894606</v>
@@ -23084,7 +23084,7 @@
         <v>-2.717498</v>
       </c>
       <c r="I284" s="6" t="n">
-        <v>99.015991</v>
+        <v>99.015102</v>
       </c>
       <c r="J284" s="6" t="n">
         <v>98.847508</v>
@@ -23166,7 +23166,7 @@
         <v>-2.300679</v>
       </c>
       <c r="I285" s="9" t="n">
-        <v>98.91551800000001</v>
+        <v>98.914725</v>
       </c>
       <c r="J285" s="9" t="n">
         <v>98.820352</v>
@@ -23248,7 +23248,7 @@
         <v>-1.645027</v>
       </c>
       <c r="I286" s="6" t="n">
-        <v>98.827195</v>
+        <v>98.826447</v>
       </c>
       <c r="J286" s="6" t="n">
         <v>98.805173</v>
@@ -23330,7 +23330,7 @@
         <v>-0.847953</v>
       </c>
       <c r="I287" s="9" t="n">
-        <v>98.756066</v>
+        <v>98.755296</v>
       </c>
       <c r="J287" s="9" t="n">
         <v>98.790729</v>
@@ -23412,7 +23412,7 @@
         <v>-0.055229</v>
       </c>
       <c r="I288" s="6" t="n">
-        <v>98.694964</v>
+        <v>98.69419499999999</v>
       </c>
       <c r="J288" s="6" t="n">
         <v>98.769188</v>
@@ -23494,7 +23494,7 @@
         <v>0.641448</v>
       </c>
       <c r="I289" s="9" t="n">
-        <v>98.655738</v>
+        <v>98.654949</v>
       </c>
       <c r="J289" s="9" t="n">
         <v>98.752323</v>
@@ -23576,7 +23576,7 @@
         <v>1.233135</v>
       </c>
       <c r="I290" s="6" t="n">
-        <v>98.669175</v>
+        <v>98.668381</v>
       </c>
       <c r="J290" s="6" t="n">
         <v>98.760479</v>
@@ -23658,7 +23658,7 @@
         <v>1.715971</v>
       </c>
       <c r="I291" s="9" t="n">
-        <v>98.746233</v>
+        <v>98.745349</v>
       </c>
       <c r="J291" s="9" t="n">
         <v>98.811851</v>
@@ -23740,7 +23740,7 @@
         <v>2.098804</v>
       </c>
       <c r="I292" s="6" t="n">
-        <v>98.88310799999999</v>
+        <v>98.882288</v>
       </c>
       <c r="J292" s="6" t="n">
         <v>98.910938</v>
@@ -23822,7 +23822,7 @@
         <v>2.406738</v>
       </c>
       <c r="I293" s="9" t="n">
-        <v>99.06513699999999</v>
+        <v>99.06447900000001</v>
       </c>
       <c r="J293" s="9" t="n">
         <v>99.061953</v>
@@ -23904,7 +23904,7 @@
         <v>2.618101</v>
       </c>
       <c r="I294" s="6" t="n">
-        <v>99.25819799999999</v>
+        <v>99.25767399999999</v>
       </c>
       <c r="J294" s="6" t="n">
         <v>99.237645</v>
@@ -23988,7 +23988,7 @@
         <v>2.708943</v>
       </c>
       <c r="I295" s="9" t="n">
-        <v>99.435998</v>
+        <v>99.435543</v>
       </c>
       <c r="J295" s="9" t="n">
         <v>99.416839</v>
@@ -24072,7 +24072,7 @@
         <v>2.608208</v>
       </c>
       <c r="I296" s="6" t="n">
-        <v>99.578211</v>
+        <v>99.57784100000001</v>
       </c>
       <c r="J296" s="6" t="n">
         <v>99.576808</v>
@@ -24156,7 +24156,7 @@
         <v>2.311396</v>
       </c>
       <c r="I297" s="9" t="n">
-        <v>99.663112</v>
+        <v>99.66283</v>
       </c>
       <c r="J297" s="9" t="n">
         <v>99.680408</v>
@@ -24240,7 +24240,7 @@
         <v>1.890369</v>
       </c>
       <c r="I298" s="6" t="n">
-        <v>99.69833</v>
+        <v>99.698207</v>
       </c>
       <c r="J298" s="6" t="n">
         <v>99.725283</v>
@@ -24324,7 +24324,7 @@
         <v>1.419524</v>
       </c>
       <c r="I299" s="9" t="n">
-        <v>99.695348</v>
+        <v>99.695364</v>
       </c>
       <c r="J299" s="9" t="n">
         <v>99.726805</v>
@@ -24408,7 +24408,7 @@
         <v>0.984066</v>
       </c>
       <c r="I300" s="6" t="n">
-        <v>99.667137</v>
+        <v>99.66714</v>
       </c>
       <c r="J300" s="6" t="n">
         <v>99.697169</v>
@@ -24492,7 +24492,7 @@
         <v>0.630225</v>
       </c>
       <c r="I301" s="9" t="n">
-        <v>99.640159</v>
+        <v>99.64004199999999</v>
       </c>
       <c r="J301" s="9" t="n">
         <v>99.659879</v>
@@ -24576,7 +24576,7 @@
         <v>0.358336</v>
       </c>
       <c r="I302" s="6" t="n">
-        <v>99.626715</v>
+        <v>99.626394</v>
       </c>
       <c r="J302" s="6" t="n">
         <v>99.63108200000001</v>
@@ -24660,7 +24660,7 @@
         <v>0.14796</v>
       </c>
       <c r="I303" s="9" t="n">
-        <v>99.630121</v>
+        <v>99.62969</v>
       </c>
       <c r="J303" s="9" t="n">
         <v>99.61694900000001</v>
@@ -24744,7 +24744,7 @@
         <v>-0.005938</v>
       </c>
       <c r="I304" s="6" t="n">
-        <v>99.638679</v>
+        <v>99.638194</v>
       </c>
       <c r="J304" s="6" t="n">
         <v>99.61451599999999</v>
@@ -24828,7 +24828,7 @@
         <v>-0.123476</v>
       </c>
       <c r="I305" s="9" t="n">
-        <v>99.630498</v>
+        <v>99.62995100000001</v>
       </c>
       <c r="J305" s="9" t="n">
         <v>99.619946</v>
@@ -24912,7 +24912,7 @@
         <v>-0.211719</v>
       </c>
       <c r="I306" s="6" t="n">
-        <v>99.60068</v>
+        <v>99.600236</v>
       </c>
       <c r="J306" s="6" t="n">
         <v>99.625471</v>
@@ -24996,7 +24996,7 @@
         <v>-0.315271</v>
       </c>
       <c r="I307" s="9" t="n">
-        <v>99.551992</v>
+        <v>99.551689</v>
       </c>
       <c r="J307" s="9" t="n">
         <v>99.623251</v>
@@ -25080,7 +25080,7 @@
         <v>-0.390542</v>
       </c>
       <c r="I308" s="6" t="n">
-        <v>99.493798</v>
+        <v>99.493551</v>
       </c>
       <c r="J308" s="6" t="n">
         <v>99.608205</v>
@@ -25164,7 +25164,7 @@
         <v>-0.417315</v>
       </c>
       <c r="I309" s="9" t="n">
-        <v>99.44589000000001</v>
+        <v>99.445517</v>
       </c>
       <c r="J309" s="9" t="n">
         <v>99.587242</v>
@@ -25248,7 +25248,7 @@
         <v>-0.370296</v>
       </c>
       <c r="I310" s="6" t="n">
-        <v>99.419293</v>
+        <v>99.41868599999999</v>
       </c>
       <c r="J310" s="6" t="n">
         <v>99.567359</v>
@@ -25332,7 +25332,7 @@
         <v>-0.251792</v>
       </c>
       <c r="I311" s="9" t="n">
-        <v>99.432997</v>
+        <v>99.43216099999999</v>
       </c>
       <c r="J311" s="9" t="n">
         <v>99.56325200000001</v>
@@ -25416,7 +25416,7 @@
         <v>-0.085091</v>
       </c>
       <c r="I312" s="6" t="n">
-        <v>99.518365</v>
+        <v>99.51751</v>
       </c>
       <c r="J312" s="6" t="n">
         <v>99.62327500000001</v>
@@ -25500,7 +25500,7 @@
         <v>0.102673</v>
       </c>
       <c r="I313" s="9" t="n">
-        <v>99.679074</v>
+        <v>99.678454</v>
       </c>
       <c r="J313" s="9" t="n">
         <v>99.78505800000001</v>
@@ -25584,7 +25584,7 @@
         <v>0.283421</v>
       </c>
       <c r="I314" s="6" t="n">
-        <v>99.891136</v>
+        <v>99.890883</v>
       </c>
       <c r="J314" s="6" t="n">
         <v>100.019083</v>
@@ -25668,7 +25668,7 @@
         <v>0.459963</v>
       </c>
       <c r="I315" s="9" t="n">
-        <v>100.13506</v>
+        <v>100.135256</v>
       </c>
       <c r="J315" s="9" t="n">
         <v>100.295076</v>
@@ -25752,7 +25752,7 @@
         <v>0.62096</v>
       </c>
       <c r="I316" s="6" t="n">
-        <v>100.39458</v>
+        <v>100.395182</v>
       </c>
       <c r="J316" s="6" t="n">
         <v>100.586443</v>
@@ -25836,7 +25836,7 @@
         <v>0.769973</v>
       </c>
       <c r="I317" s="9" t="n">
-        <v>100.643766</v>
+        <v>100.644594</v>
       </c>
       <c r="J317" s="9" t="n">
         <v>100.855207</v>
@@ -25920,7 +25920,7 @@
         <v>0.916258</v>
       </c>
       <c r="I318" s="6" t="n">
-        <v>100.857087</v>
+        <v>100.85787</v>
       </c>
       <c r="J318" s="6" t="n">
         <v>101.075279</v>
@@ -26004,7 +26004,7 @@
         <v>1.080875</v>
       </c>
       <c r="I319" s="9" t="n">
-        <v>101.008996</v>
+        <v>101.009495</v>
       </c>
       <c r="J319" s="9" t="n">
         <v>101.249857</v>
@@ -26088,7 +26088,7 @@
         <v>1.235879</v>
       </c>
       <c r="I320" s="6" t="n">
-        <v>101.12354</v>
+        <v>101.123711</v>
       </c>
       <c r="J320" s="6" t="n">
         <v>101.400614</v>
@@ -26172,7 +26172,7 @@
         <v>1.353593</v>
       </c>
       <c r="I321" s="9" t="n">
-        <v>101.216754</v>
+        <v>101.21678</v>
       </c>
       <c r="J321" s="9" t="n">
         <v>101.529361</v>
@@ -26256,7 +26256,7 @@
         <v>1.416123</v>
       </c>
       <c r="I322" s="6" t="n">
-        <v>101.286371</v>
+        <v>101.286351</v>
       </c>
       <c r="J322" s="6" t="n">
         <v>101.634945</v>
@@ -26340,7 +26340,7 @@
         <v>1.423092</v>
       </c>
       <c r="I323" s="9" t="n">
-        <v>101.320199</v>
+        <v>101.320251</v>
       </c>
       <c r="J323" s="9" t="n">
         <v>101.70471</v>
@@ -26424,7 +26424,7 @@
         <v>1.397348</v>
       </c>
       <c r="I324" s="6" t="n">
-        <v>101.324739</v>
+        <v>101.324999</v>
       </c>
       <c r="J324" s="6" t="n">
         <v>101.737187</v>
@@ -26508,7 +26508,7 @@
         <v>1.357902</v>
       </c>
       <c r="I325" s="9" t="n">
-        <v>101.311439</v>
+        <v>101.312037</v>
       </c>
       <c r="J325" s="9" t="n">
         <v>101.736552</v>
@@ -26592,7 +26592,7 @@
         <v>1.314818</v>
       </c>
       <c r="I326" s="6" t="n">
-        <v>101.289007</v>
+        <v>101.289823</v>
       </c>
       <c r="J326" s="6" t="n">
         <v>101.706041</v>
@@ -26676,7 +26676,7 @@
         <v>1.264096</v>
       </c>
       <c r="I327" s="9" t="n">
-        <v>101.26873</v>
+        <v>101.269616</v>
       </c>
       <c r="J327" s="9" t="n">
         <v>101.661191</v>
@@ -26760,7 +26760,7 @@
         <v>1.207813</v>
       </c>
       <c r="I328" s="6" t="n">
-        <v>101.25935</v>
+        <v>101.260163</v>
       </c>
       <c r="J328" s="6" t="n">
         <v>101.617412</v>
@@ -26844,7 +26844,7 @@
         <v>1.156829</v>
       </c>
       <c r="I329" s="9" t="n">
-        <v>101.274311</v>
+        <v>101.275097</v>
       </c>
       <c r="J329" s="9" t="n">
         <v>101.590988</v>
@@ -26928,7 +26928,7 @@
         <v>1.122761</v>
       </c>
       <c r="I330" s="6" t="n">
-        <v>101.314738</v>
+        <v>101.315538</v>
       </c>
       <c r="J330" s="6" t="n">
         <v>101.60662</v>
@@ -27012,7 +27012,7 @@
         <v>1.105192</v>
       </c>
       <c r="I331" s="9" t="n">
-        <v>101.381146</v>
+        <v>101.381979</v>
       </c>
       <c r="J331" s="9" t="n">
         <v>101.663041</v>
@@ -27096,7 +27096,7 @@
         <v>1.105898</v>
       </c>
       <c r="I332" s="6" t="n">
-        <v>101.46916</v>
+        <v>101.469961</v>
       </c>
       <c r="J332" s="6" t="n">
         <v>101.73348</v>
@@ -27180,7 +27180,7 @@
         <v>1.121261</v>
       </c>
       <c r="I333" s="9" t="n">
-        <v>101.562618</v>
+        <v>101.563269</v>
       </c>
       <c r="J333" s="9" t="n">
         <v>101.78549</v>
@@ -27264,7 +27264,7 @@
         <v>1.124992</v>
       </c>
       <c r="I334" s="6" t="n">
-        <v>101.644557</v>
+        <v>101.645022</v>
       </c>
       <c r="J334" s="6" t="n">
         <v>101.810185</v>
@@ -27348,7 +27348,7 @@
         <v>1.114996</v>
       </c>
       <c r="I335" s="9" t="n">
-        <v>101.703641</v>
+        <v>101.703883</v>
       </c>
       <c r="J335" s="9" t="n">
         <v>101.807483</v>
@@ -27432,7 +27432,7 @@
         <v>1.079981</v>
       </c>
       <c r="I336" s="6" t="n">
-        <v>101.732377</v>
+        <v>101.732412</v>
       </c>
       <c r="J336" s="6" t="n">
         <v>101.783563</v>
@@ -27516,7 +27516,7 @@
         <v>1.001222</v>
       </c>
       <c r="I337" s="9" t="n">
-        <v>101.734831</v>
+        <v>101.734915</v>
       </c>
       <c r="J337" s="9" t="n">
         <v>101.748897</v>
@@ -27600,7 +27600,7 @@
         <v>0.88393</v>
       </c>
       <c r="I338" s="6" t="n">
-        <v>101.713921</v>
+        <v>101.714332</v>
       </c>
       <c r="J338" s="6" t="n">
         <v>101.718082</v>
@@ -27684,7 +27684,7 @@
         <v>0.708843</v>
       </c>
       <c r="I339" s="9" t="n">
-        <v>101.676251</v>
+        <v>101.677054</v>
       </c>
       <c r="J339" s="9" t="n">
         <v>101.693324</v>
@@ -27768,7 +27768,7 @@
         <v>0.479401</v>
       </c>
       <c r="I340" s="6" t="n">
-        <v>101.637715</v>
+        <v>101.638798</v>
       </c>
       <c r="J340" s="6" t="n">
         <v>101.686671</v>
@@ -27852,7 +27852,7 @@
         <v>0.212761</v>
       </c>
       <c r="I341" s="9" t="n">
-        <v>101.616887</v>
+        <v>101.618118</v>
       </c>
       <c r="J341" s="9" t="n">
         <v>101.708757</v>
@@ -27936,7 +27936,7 @@
         <v>-0.081441</v>
       </c>
       <c r="I342" s="6" t="n">
-        <v>101.619496</v>
+        <v>101.620766</v>
       </c>
       <c r="J342" s="6" t="n">
         <v>101.74514</v>
@@ -28020,7 +28020,7 @@
         <v>-0.3883</v>
       </c>
       <c r="I343" s="9" t="n">
-        <v>101.638386</v>
+        <v>101.639652</v>
       </c>
       <c r="J343" s="9" t="n">
         <v>101.77598</v>
@@ -28104,7 +28104,7 @@
         <v>-0.690652</v>
       </c>
       <c r="I344" s="6" t="n">
-        <v>101.672584</v>
+        <v>101.673783</v>
       </c>
       <c r="J344" s="6" t="n">
         <v>101.765745</v>
@@ -28188,7 +28188,7 @@
         <v>-1.008416</v>
       </c>
       <c r="I345" s="9" t="n">
-        <v>101.728032</v>
+        <v>101.729031</v>
       </c>
       <c r="J345" s="9" t="n">
         <v>101.733837</v>
@@ -28272,7 +28272,7 @@
         <v>-1.3669</v>
       </c>
       <c r="I346" s="6" t="n">
-        <v>101.758282</v>
+        <v>101.758898</v>
       </c>
       <c r="J346" s="6" t="n">
         <v>101.675774</v>
@@ -28356,7 +28356,7 @@
         <v>-1.833245</v>
       </c>
       <c r="I347" s="9" t="n">
-        <v>101.73092</v>
+        <v>101.731161</v>
       </c>
       <c r="J347" s="9" t="n">
         <v>101.566637</v>
@@ -28440,7 +28440,7 @@
         <v>-2.444016</v>
       </c>
       <c r="I348" s="6" t="n">
-        <v>101.601926</v>
+        <v>101.602005</v>
       </c>
       <c r="J348" s="6" t="n">
         <v>101.36948</v>
@@ -28524,7 +28524,7 @@
         <v>-3.205012</v>
       </c>
       <c r="I349" s="9" t="n">
-        <v>101.345214</v>
+        <v>101.345483</v>
       </c>
       <c r="J349" s="9" t="n">
         <v>101.081784</v>
@@ -28608,7 +28608,7 @@
         <v>-4.096713</v>
       </c>
       <c r="I350" s="6" t="n">
-        <v>100.955778</v>
+        <v>100.95627</v>
       </c>
       <c r="J350" s="6" t="n">
         <v>100.685638</v>
@@ -28692,7 +28692,7 @@
         <v>-4.999865</v>
       </c>
       <c r="I351" s="9" t="n">
-        <v>100.423181</v>
+        <v>100.423675</v>
       </c>
       <c r="J351" s="9" t="n">
         <v>100.168217</v>
@@ -28776,7 +28776,7 @@
         <v>-5.754575</v>
       </c>
       <c r="I352" s="6" t="n">
-        <v>99.745102</v>
+        <v>99.74545999999999</v>
       </c>
       <c r="J352" s="6" t="n">
         <v>99.52229199999999</v>
@@ -28860,7 +28860,7 @@
         <v>-6.277289</v>
       </c>
       <c r="I353" s="9" t="n">
-        <v>98.966379</v>
+        <v>98.966345</v>
       </c>
       <c r="J353" s="9" t="n">
         <v>98.787513</v>
@@ -28944,7 +28944,7 @@
         <v>-6.536705</v>
       </c>
       <c r="I354" s="6" t="n">
-        <v>98.171916</v>
+        <v>98.17129300000001</v>
       </c>
       <c r="J354" s="6" t="n">
         <v>98.03982000000001</v>
@@ -29028,7 +29028,7 @@
         <v>-6.507158</v>
       </c>
       <c r="I355" s="9" t="n">
-        <v>97.49587099999999</v>
+        <v>97.494719</v>
       </c>
       <c r="J355" s="9" t="n">
         <v>97.406745</v>
@@ -29112,7 +29112,7 @@
         <v>-6.174519</v>
       </c>
       <c r="I356" s="6" t="n">
-        <v>97.003804</v>
+        <v>97.00215</v>
       </c>
       <c r="J356" s="6" t="n">
         <v>96.94794</v>
@@ -29196,7 +29196,7 @@
         <v>-5.550439</v>
       </c>
       <c r="I357" s="9" t="n">
-        <v>96.722875</v>
+        <v>96.720716</v>
       </c>
       <c r="J357" s="9" t="n">
         <v>96.68701799999999</v>
@@ -29280,7 +29280,7 @@
         <v>-4.701155</v>
       </c>
       <c r="I358" s="6" t="n">
-        <v>96.664252</v>
+        <v>96.661676</v>
       </c>
       <c r="J358" s="6" t="n">
         <v>96.617347</v>
@@ -29364,7 +29364,7 @@
         <v>-3.658755</v>
       </c>
       <c r="I359" s="9" t="n">
-        <v>96.805977</v>
+        <v>96.803201</v>
       </c>
       <c r="J359" s="9" t="n">
         <v>96.72145500000001</v>
@@ -29448,7 +29448,7 @@
         <v>-2.457381</v>
       </c>
       <c r="I360" s="6" t="n">
-        <v>97.075354</v>
+        <v>97.072547</v>
       </c>
       <c r="J360" s="6" t="n">
         <v>96.96740699999999</v>
@@ -29532,7 +29532,7 @@
         <v>-1.12425</v>
       </c>
       <c r="I361" s="9" t="n">
-        <v>97.395588</v>
+        <v>97.39340199999999</v>
       </c>
       <c r="J361" s="9" t="n">
         <v>97.293564</v>
@@ -29616,7 +29616,7 @@
         <v>0.292591</v>
       </c>
       <c r="I362" s="6" t="n">
-        <v>97.73065800000001</v>
+        <v>97.729226</v>
       </c>
       <c r="J362" s="6" t="n">
         <v>97.659549</v>
@@ -29700,7 +29700,7 @@
         <v>1.696642</v>
       </c>
       <c r="I363" s="9" t="n">
-        <v>98.050557</v>
+        <v>98.04966400000001</v>
       </c>
       <c r="J363" s="9" t="n">
         <v>98.020455</v>
@@ -29784,7 +29784,7 @@
         <v>2.920335</v>
       </c>
       <c r="I364" s="6" t="n">
-        <v>98.33188699999999</v>
+        <v>98.331205</v>
       </c>
       <c r="J364" s="6" t="n">
         <v>98.34524</v>
@@ -29868,7 +29868,7 @@
         <v>3.883912</v>
       </c>
       <c r="I365" s="9" t="n">
-        <v>98.56007700000001</v>
+        <v>98.55943600000001</v>
       </c>
       <c r="J365" s="9" t="n">
         <v>98.605819</v>
@@ -29952,7 +29952,7 @@
         <v>4.572413</v>
       </c>
       <c r="I366" s="6" t="n">
-        <v>98.74270199999999</v>
+        <v>98.74196600000001</v>
       </c>
       <c r="J366" s="6" t="n">
         <v>98.801059</v>
@@ -30036,7 +30036,7 @@
         <v>4.961283</v>
       </c>
       <c r="I367" s="9" t="n">
-        <v>98.910432</v>
+        <v>98.909769</v>
       </c>
       <c r="J367" s="9" t="n">
         <v>98.95089299999999</v>
@@ -30120,7 +30120,7 @@
         <v>5.028219</v>
       </c>
       <c r="I368" s="6" t="n">
-        <v>99.06559900000001</v>
+        <v>99.06503499999999</v>
       </c>
       <c r="J368" s="6" t="n">
         <v>99.07379400000001</v>
@@ -30204,7 +30204,7 @@
         <v>4.778026</v>
       </c>
       <c r="I369" s="9" t="n">
-        <v>99.196381</v>
+        <v>99.195863</v>
       </c>
       <c r="J369" s="9" t="n">
         <v>99.159384</v>
@@ -30288,7 +30288,7 @@
         <v>4.303932</v>
       </c>
       <c r="I370" s="6" t="n">
-        <v>99.28661099999999</v>
+        <v>99.286001</v>
       </c>
       <c r="J370" s="6" t="n">
         <v>99.19579299999999</v>
@@ -30372,7 +30372,7 @@
         <v>3.724425</v>
       </c>
       <c r="I371" s="9" t="n">
-        <v>99.345174</v>
+        <v>99.344471</v>
       </c>
       <c r="J371" s="9" t="n">
         <v>99.19694699999999</v>
@@ -30456,7 +30456,7 @@
         <v>3.141979</v>
       </c>
       <c r="I372" s="6" t="n">
-        <v>99.38622700000001</v>
+        <v>99.385468</v>
       </c>
       <c r="J372" s="6" t="n">
         <v>99.177706</v>
@@ -30540,7 +30540,7 @@
         <v>2.6239</v>
       </c>
       <c r="I373" s="9" t="n">
-        <v>99.41812400000001</v>
+        <v>99.41757699999999</v>
       </c>
       <c r="J373" s="9" t="n">
         <v>99.151837</v>
@@ -30624,7 +30624,7 @@
         <v>2.209125</v>
       </c>
       <c r="I374" s="6" t="n">
-        <v>99.44787599999999</v>
+        <v>99.447481</v>
       </c>
       <c r="J374" s="6" t="n">
         <v>99.121506</v>
@@ -30708,7 +30708,7 @@
         <v>1.883543</v>
       </c>
       <c r="I375" s="9" t="n">
-        <v>99.481613</v>
+        <v>99.481326</v>
       </c>
       <c r="J375" s="9" t="n">
         <v>99.10315300000001</v>
@@ -30792,7 +30792,7 @@
         <v>1.647884</v>
       </c>
       <c r="I376" s="6" t="n">
-        <v>99.52737500000001</v>
+        <v>99.527075</v>
       </c>
       <c r="J376" s="6" t="n">
         <v>99.107989</v>
@@ -30876,7 +30876,7 @@
         <v>1.474818</v>
       </c>
       <c r="I377" s="9" t="n">
-        <v>99.58476899999999</v>
+        <v>99.584295</v>
       </c>
       <c r="J377" s="9" t="n">
         <v>99.142107</v>
@@ -30960,7 +30960,7 @@
         <v>1.324966</v>
       </c>
       <c r="I378" s="6" t="n">
-        <v>99.64292</v>
+        <v>99.64242299999999</v>
       </c>
       <c r="J378" s="6" t="n">
         <v>99.19612100000001</v>
@@ -31044,7 +31044,7 @@
         <v>1.172158</v>
       </c>
       <c r="I379" s="9" t="n">
-        <v>99.70102799999999</v>
+        <v>99.700738</v>
       </c>
       <c r="J379" s="9" t="n">
         <v>99.269543</v>
@@ -31128,7 +31128,7 @@
         <v>1.001985</v>
       </c>
       <c r="I380" s="6" t="n">
-        <v>99.762861</v>
+        <v>99.762776</v>
       </c>
       <c r="J380" s="6" t="n">
         <v>99.36842799999999</v>
@@ -31212,7 +31212,7 @@
         <v>0.834806</v>
       </c>
       <c r="I381" s="9" t="n">
-        <v>99.834422</v>
+        <v>99.834366</v>
       </c>
       <c r="J381" s="9" t="n">
         <v>99.48869999999999</v>
@@ -31296,7 +31296,7 @@
         <v>0.670829</v>
       </c>
       <c r="I382" s="6" t="n">
-        <v>99.93682099999999</v>
+        <v>99.936494</v>
       </c>
       <c r="J382" s="6" t="n">
         <v>99.630185</v>
@@ -31380,7 +31380,7 @@
         <v>0.4819</v>
       </c>
       <c r="I383" s="9" t="n">
-        <v>100.056037</v>
+        <v>100.055366</v>
       </c>
       <c r="J383" s="9" t="n">
         <v>99.780669</v>
@@ -31464,7 +31464,7 @@
         <v>0.240818</v>
       </c>
       <c r="I384" s="6" t="n">
-        <v>100.180878</v>
+        <v>100.18013</v>
       </c>
       <c r="J384" s="6" t="n">
         <v>99.93088400000001</v>
@@ -31548,7 +31548,7 @@
         <v>-0.053126</v>
       </c>
       <c r="I385" s="9" t="n">
-        <v>100.30265</v>
+        <v>100.302255</v>
       </c>
       <c r="J385" s="9" t="n">
         <v>100.090452</v>
@@ -31632,7 +31632,7 @@
         <v>-0.356826</v>
       </c>
       <c r="I386" s="6" t="n">
-        <v>100.410564</v>
+        <v>100.410591</v>
       </c>
       <c r="J386" s="6" t="n">
         <v>100.265147</v>
@@ -31716,7 +31716,7 @@
         <v>-0.607657</v>
       </c>
       <c r="I387" s="9" t="n">
-        <v>100.507348</v>
+        <v>100.50774</v>
       </c>
       <c r="J387" s="9" t="n">
         <v>100.456892</v>
@@ -31800,7 +31800,7 @@
         <v>-0.781326</v>
       </c>
       <c r="I388" s="6" t="n">
-        <v>100.598694</v>
+        <v>100.599306</v>
       </c>
       <c r="J388" s="6" t="n">
         <v>100.641121</v>
@@ -31884,7 +31884,7 @@
         <v>-0.881684</v>
       </c>
       <c r="I389" s="9" t="n">
-        <v>100.68062</v>
+        <v>100.681257</v>
       </c>
       <c r="J389" s="9" t="n">
         <v>100.793208</v>
@@ -31968,7 +31968,7 @@
         <v>-0.9114</v>
       </c>
       <c r="I390" s="6" t="n">
-        <v>100.75247</v>
+        <v>100.752972</v>
       </c>
       <c r="J390" s="6" t="n">
         <v>100.901147</v>
@@ -32052,7 +32052,7 @@
         <v>-0.913286</v>
       </c>
       <c r="I391" s="9" t="n">
-        <v>100.801319</v>
+        <v>100.801695</v>
       </c>
       <c r="J391" s="9" t="n">
         <v>100.968363</v>
@@ -32136,7 +32136,7 @@
         <v>-0.924218</v>
       </c>
       <c r="I392" s="6" t="n">
-        <v>100.823524</v>
+        <v>100.823855</v>
       </c>
       <c r="J392" s="6" t="n">
         <v>101.004983</v>
@@ -32220,7 +32220,7 @@
         <v>-0.943196</v>
       </c>
       <c r="I393" s="9" t="n">
-        <v>100.821467</v>
+        <v>100.821764</v>
       </c>
       <c r="J393" s="9" t="n">
         <v>101.017521</v>
@@ -32304,7 +32304,7 @@
         <v>-0.920714</v>
       </c>
       <c r="I394" s="6" t="n">
-        <v>100.801819</v>
+        <v>100.802062</v>
       </c>
       <c r="J394" s="6" t="n">
         <v>101.004797</v>
@@ -32388,7 +32388,7 @@
         <v>-0.816269</v>
       </c>
       <c r="I395" s="9" t="n">
-        <v>100.777404</v>
+        <v>100.777497</v>
       </c>
       <c r="J395" s="9" t="n">
         <v>100.970435</v>
@@ -32472,7 +32472,7 @@
         <v>-0.6263300000000001</v>
       </c>
       <c r="I396" s="6" t="n">
-        <v>100.743712</v>
+        <v>100.743601</v>
       </c>
       <c r="J396" s="6" t="n">
         <v>100.903814</v>
@@ -32556,7 +32556,7 @@
         <v>-0.378254</v>
       </c>
       <c r="I397" s="9" t="n">
-        <v>100.698871</v>
+        <v>100.698623</v>
       </c>
       <c r="J397" s="9" t="n">
         <v>100.795328</v>
@@ -32640,7 +32640,7 @@
         <v>-0.127073</v>
       </c>
       <c r="I398" s="6" t="n">
-        <v>100.653855</v>
+        <v>100.653655</v>
       </c>
       <c r="J398" s="6" t="n">
         <v>100.66385</v>
@@ -32724,7 +32724,7 @@
         <v>0.07831</v>
       </c>
       <c r="I399" s="9" t="n">
-        <v>100.60579</v>
+        <v>100.60564</v>
       </c>
       <c r="J399" s="9" t="n">
         <v>100.508824</v>
@@ -32808,7 +32808,7 @@
         <v>0.215473</v>
       </c>
       <c r="I400" s="6" t="n">
-        <v>100.548795</v>
+        <v>100.548644</v>
       </c>
       <c r="J400" s="6" t="n">
         <v>100.360917</v>
@@ -32892,7 +32892,7 @@
         <v>0.300638</v>
       </c>
       <c r="I401" s="9" t="n">
-        <v>100.465353</v>
+        <v>100.465217</v>
       </c>
       <c r="J401" s="9" t="n">
         <v>100.219762</v>
@@ -32976,7 +32976,7 @@
         <v>0.320496</v>
       </c>
       <c r="I402" s="6" t="n">
-        <v>100.360024</v>
+        <v>100.359909</v>
       </c>
       <c r="J402" s="6" t="n">
         <v>100.088888</v>
@@ -33060,7 +33060,7 @@
         <v>0.31058</v>
       </c>
       <c r="I403" s="9" t="n">
-        <v>100.243889</v>
+        <v>100.243815</v>
       </c>
       <c r="J403" s="9" t="n">
         <v>99.96141799999999</v>
@@ -33144,7 +33144,7 @@
         <v>0.326595</v>
       </c>
       <c r="I404" s="6" t="n">
-        <v>100.130992</v>
+        <v>100.130933</v>
       </c>
       <c r="J404" s="6" t="n">
         <v>99.829155</v>
@@ -33228,7 +33228,7 @@
         <v>0.373978</v>
       </c>
       <c r="I405" s="9" t="n">
-        <v>100.033544</v>
+        <v>100.033482</v>
       </c>
       <c r="J405" s="9" t="n">
         <v>99.71278</v>
@@ -33312,7 +33312,7 @@
         <v>0.40545</v>
       </c>
       <c r="I406" s="6" t="n">
-        <v>99.959633</v>
+        <v>99.95945500000001</v>
       </c>
       <c r="J406" s="6" t="n">
         <v>99.629597</v>
@@ -33396,7 +33396,7 @@
         <v>0.383928</v>
       </c>
       <c r="I407" s="9" t="n">
-        <v>99.899542</v>
+        <v>99.899371</v>
       </c>
       <c r="J407" s="9" t="n">
         <v>99.564835</v>
@@ -33480,7 +33480,7 @@
         <v>0.329285</v>
       </c>
       <c r="I408" s="6" t="n">
-        <v>99.854792</v>
+        <v>99.854653</v>
       </c>
       <c r="J408" s="6" t="n">
         <v>99.527833</v>
@@ -33564,7 +33564,7 @@
         <v>0.256164</v>
       </c>
       <c r="I409" s="9" t="n">
-        <v>99.822543</v>
+        <v>99.822395</v>
       </c>
       <c r="J409" s="9" t="n">
         <v>99.516475</v>
@@ -33648,7 +33648,7 @@
         <v>0.180398</v>
       </c>
       <c r="I410" s="6" t="n">
-        <v>99.79326</v>
+        <v>99.793025</v>
       </c>
       <c r="J410" s="6" t="n">
         <v>99.521102</v>
@@ -33732,7 +33732,7 @@
         <v>0.106628</v>
       </c>
       <c r="I411" s="9" t="n">
-        <v>99.76964</v>
+        <v>99.769323</v>
       </c>
       <c r="J411" s="9" t="n">
         <v>99.554152</v>
@@ -33816,7 +33816,7 @@
         <v>0.036139</v>
       </c>
       <c r="I412" s="6" t="n">
-        <v>99.755798</v>
+        <v>99.75527099999999</v>
       </c>
       <c r="J412" s="6" t="n">
         <v>99.61118999999999</v>
@@ -33900,7 +33900,7 @@
         <v>-0.057207</v>
       </c>
       <c r="I413" s="9" t="n">
-        <v>99.763592</v>
+        <v>99.76277399999999</v>
       </c>
       <c r="J413" s="9" t="n">
         <v>99.700863</v>
@@ -33984,7 +33984,7 @@
         <v>-0.145472</v>
       </c>
       <c r="I414" s="6" t="n">
-        <v>99.79723</v>
+        <v>99.796195</v>
       </c>
       <c r="J414" s="6" t="n">
         <v>99.826043</v>
@@ -34068,7 +34068,7 @@
         <v>-0.176936</v>
       </c>
       <c r="I415" s="9" t="n">
-        <v>99.868223</v>
+        <v>99.86736000000001</v>
       </c>
       <c r="J415" s="9" t="n">
         <v>99.983569</v>
@@ -34152,7 +34152,7 @@
         <v>-0.131783</v>
       </c>
       <c r="I416" s="6" t="n">
-        <v>99.953914</v>
+        <v>99.95337499999999</v>
       </c>
       <c r="J416" s="6" t="n">
         <v>100.153452</v>
@@ -34236,7 +34236,7 @@
         <v>-0.024994</v>
       </c>
       <c r="I417" s="9" t="n">
-        <v>100.035193</v>
+        <v>100.034998</v>
       </c>
       <c r="J417" s="9" t="n">
         <v>100.295257</v>
@@ -34320,7 +34320,7 @@
         <v>0.13672</v>
       </c>
       <c r="I418" s="6" t="n">
-        <v>100.093726</v>
+        <v>100.093756</v>
       </c>
       <c r="J418" s="6" t="n">
         <v>100.384612</v>
@@ -34404,7 +34404,7 @@
         <v>0.334636</v>
       </c>
       <c r="I419" s="9" t="n">
-        <v>100.116339</v>
+        <v>100.116451</v>
       </c>
       <c r="J419" s="9" t="n">
         <v>100.419364</v>
@@ -34488,7 +34488,7 @@
         <v>0.513068</v>
       </c>
       <c r="I420" s="6" t="n">
-        <v>100.111751</v>
+        <v>100.111925</v>
       </c>
       <c r="J420" s="6" t="n">
         <v>100.412135</v>
@@ -34572,7 +34572,7 @@
         <v>0.640157</v>
       </c>
       <c r="I421" s="9" t="n">
-        <v>100.087375</v>
+        <v>100.087493</v>
       </c>
       <c r="J421" s="9" t="n">
         <v>100.392867</v>
@@ -34656,7 +34656,7 @@
         <v>0.685555</v>
       </c>
       <c r="I422" s="6" t="n">
-        <v>100.066037</v>
+        <v>100.066044</v>
       </c>
       <c r="J422" s="6" t="n">
         <v>100.382709</v>
@@ -34740,7 +34740,7 @@
         <v>0.644445</v>
       </c>
       <c r="I423" s="9" t="n">
-        <v>100.054426</v>
+        <v>100.054218</v>
       </c>
       <c r="J423" s="9" t="n">
         <v>100.374417</v>
@@ -34824,7 +34824,7 @@
         <v>0.542782</v>
       </c>
       <c r="I424" s="6" t="n">
-        <v>100.046266</v>
+        <v>100.04597</v>
       </c>
       <c r="J424" s="6" t="n">
         <v>100.352542</v>
@@ -34908,7 +34908,7 @@
         <v>0.434688</v>
       </c>
       <c r="I425" s="9" t="n">
-        <v>100.043123</v>
+        <v>100.042782</v>
       </c>
       <c r="J425" s="9" t="n">
         <v>100.321414</v>
@@ -34992,7 +34992,7 @@
         <v>0.352584</v>
       </c>
       <c r="I426" s="6" t="n">
-        <v>100.054017</v>
+        <v>100.053675</v>
       </c>
       <c r="J426" s="6" t="n">
         <v>100.296368</v>
@@ -35076,7 +35076,7 @@
         <v>0.266052</v>
       </c>
       <c r="I427" s="9" t="n">
-        <v>100.084315</v>
+        <v>100.084022</v>
       </c>
       <c r="J427" s="9" t="n">
         <v>100.294732</v>
@@ -35160,7 +35160,7 @@
         <v>0.130546</v>
       </c>
       <c r="I428" s="6" t="n">
-        <v>100.130793</v>
+        <v>100.130533</v>
       </c>
       <c r="J428" s="6" t="n">
         <v>100.319843</v>
@@ -35244,7 +35244,7 @@
         <v>-0.031245</v>
       </c>
       <c r="I429" s="9" t="n">
-        <v>100.187249</v>
+        <v>100.186973</v>
       </c>
       <c r="J429" s="9" t="n">
         <v>100.382161</v>
@@ -35328,7 +35328,7 @@
         <v>-0.211638</v>
       </c>
       <c r="I430" s="6" t="n">
-        <v>100.242505</v>
+        <v>100.242303</v>
       </c>
       <c r="J430" s="6" t="n">
         <v>100.474625</v>
@@ -35412,7 +35412,7 @@
         <v>-0.400296</v>
       </c>
       <c r="I431" s="9" t="n">
-        <v>100.304224</v>
+        <v>100.304127</v>
       </c>
       <c r="J431" s="9" t="n">
         <v>100.604878</v>
@@ -35496,7 +35496,7 @@
         <v>-0.577082</v>
       </c>
       <c r="I432" s="6" t="n">
-        <v>100.36124</v>
+        <v>100.36113</v>
       </c>
       <c r="J432" s="6" t="n">
         <v>100.75284</v>
@@ -35580,7 +35580,7 @@
         <v>-0.722069</v>
       </c>
       <c r="I433" s="9" t="n">
-        <v>100.390876</v>
+        <v>100.390851</v>
       </c>
       <c r="J433" s="9" t="n">
         <v>100.875865</v>
@@ -35664,7 +35664,7 @@
         <v>-0.809386</v>
       </c>
       <c r="I434" s="6" t="n">
-        <v>100.377994</v>
+        <v>100.378024</v>
       </c>
       <c r="J434" s="6" t="n">
         <v>100.935262</v>
@@ -35748,7 +35748,7 @@
         <v>-0.828732</v>
       </c>
       <c r="I435" s="9" t="n">
-        <v>100.304765</v>
+        <v>100.30473</v>
       </c>
       <c r="J435" s="9" t="n">
         <v>100.897003</v>
@@ -35832,7 +35832,7 @@
         <v>-0.818153</v>
       </c>
       <c r="I436" s="6" t="n">
-        <v>100.203889</v>
+        <v>100.203707</v>
       </c>
       <c r="J436" s="6" t="n">
         <v>100.802066</v>
@@ -35916,7 +35916,7 @@
         <v>-0.811288</v>
       </c>
       <c r="I437" s="9" t="n">
-        <v>100.1097</v>
+        <v>100.109448</v>
       </c>
       <c r="J437" s="9" t="n">
         <v>100.687725</v>
@@ -36000,7 +36000,7 @@
         <v>-0.823412</v>
       </c>
       <c r="I438" s="6" t="n">
-        <v>100.033967</v>
+        <v>100.033732</v>
       </c>
       <c r="J438" s="6" t="n">
         <v>100.564657</v>
@@ -36084,7 +36084,7 @@
         <v>-0.834323</v>
       </c>
       <c r="I439" s="9" t="n">
-        <v>99.97800700000001</v>
+        <v>99.97796099999999</v>
       </c>
       <c r="J439" s="9" t="n">
         <v>100.439752</v>
@@ -36168,7 +36168,7 @@
         <v>-0.811551</v>
       </c>
       <c r="I440" s="6" t="n">
-        <v>99.93898299999999</v>
+        <v>99.93913499999999</v>
       </c>
       <c r="J440" s="6" t="n">
         <v>100.32016</v>
@@ -36252,7 +36252,7 @@
         <v>-0.770517</v>
       </c>
       <c r="I441" s="9" t="n">
-        <v>99.92813099999999</v>
+        <v>99.928348</v>
       </c>
       <c r="J441" s="9" t="n">
         <v>100.224722</v>
@@ -36336,7 +36336,7 @@
         <v>-0.726924</v>
       </c>
       <c r="I442" s="6" t="n">
-        <v>99.949501</v>
+        <v>99.949658</v>
       </c>
       <c r="J442" s="6" t="n">
         <v>100.162078</v>
@@ -36420,7 +36420,7 @@
         <v>-0.6828070000000001</v>
       </c>
       <c r="I443" s="9" t="n">
-        <v>99.99887699999999</v>
+        <v>99.998912</v>
       </c>
       <c r="J443" s="9" t="n">
         <v>100.133649</v>
@@ -36504,7 +36504,7 @@
         <v>-0.65032</v>
       </c>
       <c r="I444" s="6" t="n">
-        <v>100.070359</v>
+        <v>100.070386</v>
       </c>
       <c r="J444" s="6" t="n">
         <v>100.14632</v>
@@ -36588,7 +36588,7 @@
         <v>-0.636587</v>
       </c>
       <c r="I445" s="9" t="n">
-        <v>100.163769</v>
+        <v>100.163886</v>
       </c>
       <c r="J445" s="9" t="n">
         <v>100.202135</v>
@@ -36672,7 +36672,7 @@
         <v>-0.653104</v>
       </c>
       <c r="I446" s="6" t="n">
-        <v>100.270539</v>
+        <v>100.270771</v>
       </c>
       <c r="J446" s="6" t="n">
         <v>100.296429</v>
@@ -36756,7 +36756,7 @@
         <v>-0.697808</v>
       </c>
       <c r="I447" s="9" t="n">
-        <v>100.374292</v>
+        <v>100.374695</v>
       </c>
       <c r="J447" s="9" t="n">
         <v>100.416139</v>
@@ -36840,7 +36840,7 @@
         <v>-0.720746</v>
       </c>
       <c r="I448" s="6" t="n">
-        <v>100.462827</v>
+        <v>100.46336</v>
       </c>
       <c r="J448" s="6" t="n">
         <v>100.545152</v>
@@ -36924,7 +36924,7 @@
         <v>-0.688735</v>
       </c>
       <c r="I449" s="9" t="n">
-        <v>100.525583</v>
+        <v>100.526073</v>
       </c>
       <c r="J449" s="9" t="n">
         <v>100.652855</v>
@@ -37008,7 +37008,7 @@
         <v>-0.578381</v>
       </c>
       <c r="I450" s="6" t="n">
-        <v>100.552171</v>
+        <v>100.552497</v>
       </c>
       <c r="J450" s="6" t="n">
         <v>100.726413</v>
@@ -37092,7 +37092,7 @@
         <v>-0.394926</v>
       </c>
       <c r="I451" s="9" t="n">
-        <v>100.542085</v>
+        <v>100.542199</v>
       </c>
       <c r="J451" s="9" t="n">
         <v>100.750799</v>
@@ -37176,7 +37176,7 @@
         <v>-0.174813</v>
       </c>
       <c r="I452" s="6" t="n">
-        <v>100.509733</v>
+        <v>100.509739</v>
       </c>
       <c r="J452" s="6" t="n">
         <v>100.729223</v>
@@ -37260,7 +37260,7 @@
         <v>0.041699</v>
       </c>
       <c r="I453" s="9" t="n">
-        <v>100.46267</v>
+        <v>100.462826</v>
       </c>
       <c r="J453" s="9" t="n">
         <v>100.664028</v>
@@ -37344,7 +37344,7 @@
         <v>0.247284</v>
       </c>
       <c r="I454" s="6" t="n">
-        <v>100.412658</v>
+        <v>100.413059</v>
       </c>
       <c r="J454" s="6" t="n">
         <v>100.583629</v>
@@ -37428,7 +37428,7 @@
         <v>0.413384</v>
       </c>
       <c r="I455" s="9" t="n">
-        <v>100.374008</v>
+        <v>100.374678</v>
       </c>
       <c r="J455" s="9" t="n">
         <v>100.5061</v>
@@ -37512,7 +37512,7 @@
         <v>0.53374</v>
       </c>
       <c r="I456" s="6" t="n">
-        <v>100.355325</v>
+        <v>100.356267</v>
       </c>
       <c r="J456" s="6" t="n">
         <v>100.446362</v>
@@ -37596,7 +37596,7 @@
         <v>0.614436</v>
       </c>
       <c r="I457" s="9" t="n">
-        <v>100.378503</v>
+        <v>100.379632</v>
       </c>
       <c r="J457" s="9" t="n">
         <v>100.424528</v>
@@ -37680,7 +37680,7 @@
         <v>0.677488</v>
       </c>
       <c r="I458" s="6" t="n">
-        <v>100.442411</v>
+        <v>100.443537</v>
       </c>
       <c r="J458" s="6" t="n">
         <v>100.441202</v>
@@ -37764,7 +37764,7 @@
         <v>0.738879</v>
       </c>
       <c r="I459" s="9" t="n">
-        <v>100.558685</v>
+        <v>100.559666</v>
       </c>
       <c r="J459" s="9" t="n">
         <v>100.501744</v>
@@ -37848,7 +37848,7 @@
         <v>0.800658</v>
       </c>
       <c r="I460" s="6" t="n">
-        <v>100.697232</v>
+        <v>100.698017</v>
       </c>
       <c r="J460" s="6" t="n">
         <v>100.579009</v>
@@ -37932,7 +37932,7 @@
         <v>0.8569290000000001</v>
       </c>
       <c r="I461" s="9" t="n">
-        <v>100.8265</v>
+        <v>100.827213</v>
       </c>
       <c r="J461" s="9" t="n">
         <v>100.65092</v>
@@ -38016,7 +38016,7 @@
         <v>0.85104</v>
       </c>
       <c r="I462" s="6" t="n">
-        <v>100.929015</v>
+        <v>100.929826</v>
       </c>
       <c r="J462" s="6" t="n">
         <v>100.701616</v>
@@ -38100,7 +38100,7 @@
         <v>0.750291</v>
       </c>
       <c r="I463" s="9" t="n">
-        <v>101.013689</v>
+        <v>101.01473</v>
       </c>
       <c r="J463" s="9" t="n">
         <v>100.743151</v>
@@ -38184,7 +38184,7 @@
         <v>0.5788450000000001</v>
       </c>
       <c r="I464" s="6" t="n">
-        <v>101.078443</v>
+        <v>101.079754</v>
       </c>
       <c r="J464" s="6" t="n">
         <v>100.779422</v>
@@ -38268,7 +38268,7 @@
         <v>0.380672</v>
       </c>
       <c r="I465" s="9" t="n">
-        <v>101.121419</v>
+        <v>101.122948</v>
       </c>
       <c r="J465" s="9" t="n">
         <v>100.819922</v>
@@ -38352,7 +38352,7 @@
         <v>0.190543</v>
       </c>
       <c r="I466" s="6" t="n">
-        <v>101.160257</v>
+        <v>101.16205</v>
       </c>
       <c r="J466" s="6" t="n">
         <v>100.880134</v>
@@ -38436,7 +38436,7 @@
         <v>0.057917</v>
       </c>
       <c r="I467" s="9" t="n">
-        <v>101.191843</v>
+        <v>101.193735</v>
       </c>
       <c r="J467" s="9" t="n">
         <v>100.929644</v>
@@ -38520,7 +38520,7 @@
         <v>-0.00081</v>
       </c>
       <c r="I468" s="6" t="n">
-        <v>101.216272</v>
+        <v>101.218068</v>
       </c>
       <c r="J468" s="6" t="n">
         <v>100.951699</v>
@@ -38604,7 +38604,7 @@
         <v>-0.015935</v>
       </c>
       <c r="I469" s="9" t="n">
-        <v>101.222956</v>
+        <v>101.224545</v>
       </c>
       <c r="J469" s="9" t="n">
         <v>100.934167</v>
@@ -38688,7 +38688,7 @@
         <v>-0.02958</v>
       </c>
       <c r="I470" s="6" t="n">
-        <v>101.200703</v>
+        <v>101.202244</v>
       </c>
       <c r="J470" s="6" t="n">
         <v>100.881029</v>
@@ -38772,7 +38772,7 @@
         <v>-0.073698</v>
       </c>
       <c r="I471" s="9" t="n">
-        <v>101.146362</v>
+        <v>101.14791</v>
       </c>
       <c r="J471" s="9" t="n">
         <v>100.78398</v>
@@ -38856,7 +38856,7 @@
         <v>-0.158793</v>
       </c>
       <c r="I472" s="6" t="n">
-        <v>101.068407</v>
+        <v>101.070004</v>
       </c>
       <c r="J472" s="6" t="n">
         <v>100.668397</v>
@@ -38940,7 +38940,7 @@
         <v>-0.257537</v>
       </c>
       <c r="I473" s="9" t="n">
-        <v>100.98473</v>
+        <v>100.986413</v>
       </c>
       <c r="J473" s="9" t="n">
         <v>100.567977</v>
@@ -39024,7 +39024,7 @@
         <v>-0.323054</v>
       </c>
       <c r="I474" s="6" t="n">
-        <v>100.90681</v>
+        <v>100.90861</v>
       </c>
       <c r="J474" s="6" t="n">
         <v>100.497751</v>
@@ -39108,7 +39108,7 @@
         <v>-0.360003</v>
       </c>
       <c r="I475" s="9" t="n">
-        <v>100.828835</v>
+        <v>100.830767</v>
       </c>
       <c r="J475" s="9" t="n">
         <v>100.45314</v>
@@ -39192,7 +39192,7 @@
         <v>-0.375498</v>
       </c>
       <c r="I476" s="6" t="n">
-        <v>100.7513</v>
+        <v>100.75335</v>
       </c>
       <c r="J476" s="6" t="n">
         <v>100.422245</v>
@@ -39276,7 +39276,7 @@
         <v>-0.380198</v>
       </c>
       <c r="I477" s="9" t="n">
-        <v>100.694886</v>
+        <v>100.697059</v>
       </c>
       <c r="J477" s="9" t="n">
         <v>100.408371</v>
@@ -39360,7 +39360,7 @@
         <v>-0.398275</v>
       </c>
       <c r="I478" s="6" t="n">
-        <v>100.659585</v>
+        <v>100.661816</v>
       </c>
       <c r="J478" s="6" t="n">
         <v>100.388246</v>
@@ -39444,7 +39444,7 @@
         <v>-0.423263</v>
       </c>
       <c r="I479" s="9" t="n">
-        <v>100.644538</v>
+        <v>100.646907</v>
       </c>
       <c r="J479" s="9" t="n">
         <v>100.351666</v>
@@ -39528,7 +39528,7 @@
         <v>-0.441759</v>
       </c>
       <c r="I480" s="6" t="n">
-        <v>100.63335</v>
+        <v>100.635819</v>
       </c>
       <c r="J480" s="6" t="n">
         <v>100.270376</v>
@@ -39612,7 +39612,7 @@
         <v>-0.429996</v>
       </c>
       <c r="I481" s="9" t="n">
-        <v>100.61356</v>
+        <v>100.616084</v>
       </c>
       <c r="J481" s="9" t="n">
         <v>100.138318</v>
@@ -39696,7 +39696,7 @@
         <v>-0.390501</v>
       </c>
       <c r="I482" s="6" t="n">
-        <v>100.568385</v>
+        <v>100.570925</v>
       </c>
       <c r="J482" s="6" t="n">
         <v>99.956729</v>
@@ -39780,7 +39780,7 @@
         <v>-0.322264</v>
       </c>
       <c r="I483" s="9" t="n">
-        <v>100.48129</v>
+        <v>100.483885</v>
       </c>
       <c r="J483" s="9" t="n">
         <v>99.738558</v>
@@ -39864,7 +39864,7 @@
         <v>-0.262508</v>
       </c>
       <c r="I484" s="6" t="n">
-        <v>100.355012</v>
+        <v>100.357631</v>
       </c>
       <c r="J484" s="6" t="n">
         <v>99.519688</v>
@@ -39948,7 +39948,7 @@
         <v>-0.303165</v>
       </c>
       <c r="I485" s="9" t="n">
-        <v>100.177571</v>
+        <v>100.18014</v>
       </c>
       <c r="J485" s="9" t="n">
         <v>99.300033</v>
@@ -40032,7 +40032,7 @@
         <v>-0.499981</v>
       </c>
       <c r="I486" s="6" t="n">
-        <v>99.938339</v>
+        <v>99.940834</v>
       </c>
       <c r="J486" s="6" t="n">
         <v>99.07543200000001</v>
@@ -40116,7 +40116,7 @@
         <v>-0.826005</v>
       </c>
       <c r="I487" s="9" t="n">
-        <v>99.633067</v>
+        <v>99.63569099999999</v>
       </c>
       <c r="J487" s="9" t="n">
         <v>98.826033</v>
@@ -40200,7 +40200,7 @@
         <v>-1.225837</v>
       </c>
       <c r="I488" s="6" t="n">
-        <v>99.312411</v>
+        <v>99.315038</v>
       </c>
       <c r="J488" s="6" t="n">
         <v>98.57625899999999</v>
@@ -40284,7 +40284,7 @@
         <v>-1.55667</v>
       </c>
       <c r="I489" s="9" t="n">
-        <v>87.086179</v>
+        <v>87.07612399999999</v>
       </c>
       <c r="J489" s="9" t="n">
         <v>85.51202499999999</v>
@@ -40368,7 +40368,7 @@
         <v>-1.696478</v>
       </c>
       <c r="I490" s="6" t="n">
-        <v>86.05866899999999</v>
+        <v>86.054305</v>
       </c>
       <c r="J490" s="6" t="n">
         <v>85.468962</v>
@@ -40452,7 +40452,7 @@
         <v>-1.653317</v>
       </c>
       <c r="I491" s="9" t="n">
-        <v>92.06177700000001</v>
+        <v>92.067036</v>
       </c>
       <c r="J491" s="9" t="n">
         <v>93.293133</v>
@@ -40536,7 +40536,7 @@
         <v>-1.473727</v>
       </c>
       <c r="I492" s="6" t="n">
-        <v>93.727487</v>
+        <v>93.726494</v>
       </c>
       <c r="J492" s="6" t="n">
         <v>94.067013</v>
@@ -40620,7 +40620,7 @@
         <v>-1.19252</v>
       </c>
       <c r="I493" s="9" t="n">
-        <v>94.88754400000001</v>
+        <v>94.88717800000001</v>
       </c>
       <c r="J493" s="9" t="n">
         <v>95.35747499999999</v>
@@ -40704,7 +40704,7 @@
         <v>-0.826483</v>
       </c>
       <c r="I494" s="6" t="n">
-        <v>96.065246</v>
+        <v>96.065577</v>
       </c>
       <c r="J494" s="6" t="n">
         <v>96.56940299999999</v>
@@ -40788,7 +40788,7 @@
         <v>-0.412452</v>
       </c>
       <c r="I495" s="9" t="n">
-        <v>97.066833</v>
+        <v>97.067708</v>
       </c>
       <c r="J495" s="9" t="n">
         <v>97.52677799999999</v>
@@ -40872,7 +40872,7 @@
         <v>0.037908</v>
       </c>
       <c r="I496" s="6" t="n">
-        <v>97.81243600000001</v>
+        <v>97.813734</v>
       </c>
       <c r="J496" s="6" t="n">
         <v>98.166375</v>
@@ -40956,7 +40956,7 @@
         <v>0.53933</v>
       </c>
       <c r="I497" s="9" t="n">
-        <v>98.303466</v>
+        <v>98.30518499999999</v>
       </c>
       <c r="J497" s="9" t="n">
         <v>98.513998</v>
@@ -41040,7 +41040,7 @@
         <v>1.102944</v>
       </c>
       <c r="I498" s="6" t="n">
-        <v>98.597145</v>
+        <v>98.599205</v>
       </c>
       <c r="J498" s="6" t="n">
         <v>98.651777</v>
@@ -41124,7 +41124,7 @@
         <v>1.73018</v>
       </c>
       <c r="I499" s="9" t="n">
-        <v>98.758105</v>
+        <v>98.760508</v>
       </c>
       <c r="J499" s="9" t="n">
         <v>98.675409</v>
@@ -41208,7 +41208,7 @@
         <v>2.39149</v>
       </c>
       <c r="I500" s="6" t="n">
-        <v>98.83748</v>
+        <v>98.84008799999999</v>
       </c>
       <c r="J500" s="6" t="n">
         <v>98.65540799999999</v>
@@ -41292,7 +41292,7 @@
         <v>2.955504</v>
       </c>
       <c r="I501" s="9" t="n">
-        <v>98.834453</v>
+        <v>98.83710000000001</v>
       </c>
       <c r="J501" s="9" t="n">
         <v>98.597115</v>
@@ -41376,7 +41376,7 @@
         <v>3.295354</v>
       </c>
       <c r="I502" s="6" t="n">
-        <v>98.764408</v>
+        <v>98.767016</v>
       </c>
       <c r="J502" s="6" t="n">
         <v>98.519902</v>
@@ -41460,7 +41460,7 @@
         <v>3.381642</v>
       </c>
       <c r="I503" s="9" t="n">
-        <v>98.649531</v>
+        <v>98.651916</v>
       </c>
       <c r="J503" s="9" t="n">
         <v>98.453154</v>
@@ -41544,7 +41544,7 @@
         <v>3.246794</v>
       </c>
       <c r="I504" s="6" t="n">
-        <v>98.521581</v>
+        <v>98.52353100000001</v>
       </c>
       <c r="J504" s="6" t="n">
         <v>98.42110700000001</v>
@@ -41628,7 +41628,7 @@
         <v>2.937396</v>
       </c>
       <c r="I505" s="9" t="n">
-        <v>98.42109600000001</v>
+        <v>98.42260400000001</v>
       </c>
       <c r="J505" s="9" t="n">
         <v>98.43960199999999</v>
@@ -41712,7 +41712,7 @@
         <v>2.508755</v>
       </c>
       <c r="I506" s="6" t="n">
-        <v>98.39023899999999</v>
+        <v>98.391453</v>
       </c>
       <c r="J506" s="6" t="n">
         <v>98.52393600000001</v>
@@ -41796,7 +41796,7 @@
         <v>2.020834</v>
       </c>
       <c r="I507" s="9" t="n">
-        <v>98.448289</v>
+        <v>98.44952600000001</v>
       </c>
       <c r="J507" s="9" t="n">
         <v>98.698481</v>
@@ -41880,7 +41880,7 @@
         <v>1.521819</v>
       </c>
       <c r="I508" s="6" t="n">
-        <v>98.581749</v>
+        <v>98.583315</v>
       </c>
       <c r="J508" s="6" t="n">
         <v>98.950447</v>
@@ -41964,7 +41964,7 @@
         <v>1.045453</v>
       </c>
       <c r="I509" s="9" t="n">
-        <v>98.764109</v>
+        <v>98.766127</v>
       </c>
       <c r="J509" s="9" t="n">
         <v>99.252224</v>
@@ -42048,7 +42048,7 @@
         <v>0.602397</v>
       </c>
       <c r="I510" s="6" t="n">
-        <v>98.967977</v>
+        <v>98.970637</v>
       </c>
       <c r="J510" s="6" t="n">
         <v>99.559568</v>
@@ -42132,7 +42132,7 @@
         <v>0.177682</v>
       </c>
       <c r="I511" s="9" t="n">
-        <v>99.169524</v>
+        <v>99.172735</v>
       </c>
       <c r="J511" s="9" t="n">
         <v>99.832224</v>
@@ -42216,7 +42216,7 @@
         <v>-0.26305</v>
       </c>
       <c r="I512" s="6" t="n">
-        <v>99.35535299999999</v>
+        <v>99.35871899999999</v>
       </c>
       <c r="J512" s="6" t="n">
         <v>100.054727</v>
@@ -42300,7 +42300,7 @@
         <v>-0.708538</v>
       </c>
       <c r="I513" s="9" t="n">
-        <v>99.512</v>
+        <v>99.514899</v>
       </c>
       <c r="J513" s="9" t="n">
         <v>100.212389</v>
@@ -42384,7 +42384,7 @@
         <v>-1.120559</v>
       </c>
       <c r="I514" s="6" t="n">
-        <v>99.634957</v>
+        <v>99.636751</v>
       </c>
       <c r="J514" s="6" t="n">
         <v>100.306984</v>
@@ -42468,7 +42468,7 @@
         <v>-1.464658</v>
       </c>
       <c r="I515" s="9" t="n">
-        <v>99.738906</v>
+        <v>99.739271</v>
       </c>
       <c r="J515" s="9" t="n">
         <v>100.364155</v>
@@ -42552,7 +42552,7 @@
         <v>-1.718087</v>
       </c>
       <c r="I516" s="6" t="n">
-        <v>99.845921</v>
+        <v>99.84506399999999</v>
       </c>
       <c r="J516" s="6" t="n">
         <v>100.416245</v>
@@ -42636,7 +42636,7 @@
         <v>-1.872845</v>
       </c>
       <c r="I517" s="9" t="n">
-        <v>99.961147</v>
+        <v>99.95968999999999</v>
       </c>
       <c r="J517" s="9" t="n">
         <v>100.475021</v>
@@ -42720,7 +42720,7 @@
         <v>-1.933884</v>
       </c>
       <c r="I518" s="6" t="n">
-        <v>100.08228</v>
+        <v>100.081</v>
       </c>
       <c r="J518" s="6" t="n">
         <v>100.549796</v>
@@ -42804,7 +42804,7 @@
         <v>-1.902854</v>
       </c>
       <c r="I519" s="9" t="n">
-        <v>100.20599</v>
+        <v>100.205604</v>
       </c>
       <c r="J519" s="9" t="n">
         <v>100.656071</v>
@@ -42888,7 +42888,7 @@
         <v>-1.803358</v>
       </c>
       <c r="I520" s="6" t="n">
-        <v>100.32151</v>
+        <v>100.322531</v>
       </c>
       <c r="J520" s="6" t="n">
         <v>100.791385</v>
@@ -42972,7 +42972,7 @@
         <v>-1.647062</v>
       </c>
       <c r="I521" s="9" t="n">
-        <v>100.41259</v>
+        <v>100.415127</v>
       </c>
       <c r="J521" s="9" t="n">
         <v>100.925472</v>
@@ -43056,7 +43056,7 @@
         <v>-1.429409</v>
       </c>
       <c r="I522" s="6" t="n">
-        <v>100.466217</v>
+        <v>100.469904</v>
       </c>
       <c r="J522" s="6" t="n">
         <v>101.028024</v>
@@ -43140,7 +43140,7 @@
         <v>-1.16813</v>
       </c>
       <c r="I523" s="9" t="n">
-        <v>100.494626</v>
+        <v>100.498619</v>
       </c>
       <c r="J523" s="9" t="n">
         <v>101.108626</v>
@@ -43224,7 +43224,7 @@
         <v>-0.86917</v>
       </c>
       <c r="I524" s="6" t="n">
-        <v>100.529188</v>
+        <v>100.532422</v>
       </c>
       <c r="J524" s="6" t="n">
         <v>101.189325</v>
@@ -43308,7 +43308,7 @@
         <v>-0.549793</v>
       </c>
       <c r="I525" s="9" t="n">
-        <v>100.588584</v>
+        <v>100.589925</v>
       </c>
       <c r="J525" s="9" t="n">
         <v>101.283764</v>
@@ -43392,7 +43392,7 @@
         <v>-0.235626</v>
       </c>
       <c r="I526" s="6" t="n">
-        <v>100.663596</v>
+        <v>100.661766</v>
       </c>
       <c r="J526" s="6" t="n">
         <v>101.388892</v>
@@ -43476,7 +43476,7 @@
         <v>0.054284</v>
       </c>
       <c r="I527" s="9" t="n">
-        <v>100.746361</v>
+        <v>100.740786</v>
       </c>
       <c r="J527" s="9" t="n">
         <v>101.493341</v>
@@ -43560,7 +43560,7 @@
         <v>0.289872</v>
       </c>
       <c r="I528" s="6" t="n">
-        <v>100.826882</v>
+        <v>100.818062</v>
       </c>
       <c r="J528" s="6" t="n">
         <v>101.584921</v>
@@ -43644,7 +43644,7 @@
         <v>0.458442</v>
       </c>
       <c r="I529" s="9" t="n">
-        <v>100.898812</v>
+        <v>100.888541</v>
       </c>
       <c r="J529" s="9" t="n">
         <v>101.655708</v>
@@ -43728,7 +43728,7 @@
         <v>0.573408</v>
       </c>
       <c r="I530" s="6" t="n">
-        <v>100.949689</v>
+        <v>100.939658</v>
       </c>
       <c r="J530" s="6" t="n">
         <v>101.690968</v>
@@ -43812,7 +43812,7 @@
         <v>0.655415</v>
       </c>
       <c r="I531" s="9" t="n">
-        <v>100.96379</v>
+        <v>100.955336</v>
       </c>
       <c r="J531" s="9" t="n">
         <v>101.666622</v>
@@ -43896,7 +43896,7 @@
         <v>0.739575</v>
       </c>
       <c r="I532" s="6" t="n">
-        <v>100.945883</v>
+        <v>100.939924</v>
       </c>
       <c r="J532" s="6" t="n">
         <v>101.568531</v>
@@ -43980,7 +43980,7 @@
         <v>0.814694</v>
       </c>
       <c r="I533" s="9" t="n">
-        <v>100.916478</v>
+        <v>100.913523</v>
       </c>
       <c r="J533" s="9" t="n">
         <v>101.428694</v>
@@ -44064,7 +44064,7 @@
         <v>0.84672</v>
       </c>
       <c r="I534" s="6" t="n">
-        <v>100.879828</v>
+        <v>100.87965</v>
       </c>
       <c r="J534" s="6" t="n">
         <v>101.265916</v>
@@ -44148,7 +44148,7 @@
         <v>0.829206</v>
       </c>
       <c r="I535" s="9" t="n">
-        <v>100.837469</v>
+        <v>100.838947</v>
       </c>
       <c r="J535" s="9" t="n">
         <v>101.090678</v>
@@ -44232,7 +44232,7 @@
         <v>0.765438</v>
       </c>
       <c r="I536" s="6" t="n">
-        <v>100.787246</v>
+        <v>100.788414</v>
       </c>
       <c r="J536" s="6" t="n">
         <v>100.936379</v>
@@ -44316,7 +44316,7 @@
         <v>0.646572</v>
       </c>
       <c r="I537" s="9" t="n">
-        <v>100.734447</v>
+        <v>100.732864</v>
       </c>
       <c r="J537" s="9" t="n">
         <v>100.809771</v>
@@ -44400,7 +44400,7 @@
         <v>0.481939</v>
       </c>
       <c r="I538" s="6" t="n">
-        <v>100.700539</v>
+        <v>100.693866</v>
       </c>
       <c r="J538" s="6" t="n">
         <v>100.722871</v>
@@ -44484,7 +44484,7 @@
         <v>0.282743</v>
       </c>
       <c r="I539" s="9" t="n">
-        <v>100.671965</v>
+        <v>100.658289</v>
       </c>
       <c r="J539" s="9" t="n">
         <v>100.662984</v>
@@ -44568,7 +44568,7 @@
         <v>0.085608</v>
       </c>
       <c r="I540" s="6" t="n">
-        <v>100.629136</v>
+        <v>100.607989</v>
       </c>
       <c r="J540" s="6" t="n">
         <v>100.603624</v>
@@ -44652,7 +44652,7 @@
         <v>-0.091961</v>
       </c>
       <c r="I541" s="9" t="n">
-        <v>100.549515</v>
+        <v>100.524119</v>
       </c>
       <c r="J541" s="9" t="n">
         <v>100.51623</v>
@@ -44736,7 +44736,7 @@
         <v>-0.255893</v>
       </c>
       <c r="I542" s="6" t="n">
-        <v>100.444459</v>
+        <v>100.418188</v>
       </c>
       <c r="J542" s="6" t="n">
         <v>100.394529</v>
@@ -44820,7 +44820,7 @@
         <v>-0.43423</v>
       </c>
       <c r="I543" s="9" t="n">
-        <v>100.327986</v>
+        <v>100.303743</v>
       </c>
       <c r="J543" s="9" t="n">
         <v>100.240854</v>
@@ -44904,7 +44904,7 @@
         <v>-0.657297</v>
       </c>
       <c r="I544" s="6" t="n">
-        <v>100.229065</v>
+        <v>100.208709</v>
       </c>
       <c r="J544" s="6" t="n">
         <v>100.096105</v>
@@ -44988,7 +44988,7 @@
         <v>-0.905767</v>
       </c>
       <c r="I545" s="9" t="n">
-        <v>100.158131</v>
+        <v>100.142715</v>
       </c>
       <c r="J545" s="9" t="n">
         <v>99.984133</v>
@@ -45072,7 +45072,7 @@
         <v>-1.13548</v>
       </c>
       <c r="I546" s="6" t="n">
-        <v>100.12761</v>
+        <v>100.117118</v>
       </c>
       <c r="J546" s="6" t="n">
         <v>99.92702199999999</v>
@@ -45156,7 +45156,7 @@
         <v>-1.308728</v>
       </c>
       <c r="I547" s="9" t="n">
-        <v>100.11628</v>
+        <v>100.109531</v>
       </c>
       <c r="J547" s="9" t="n">
         <v>99.9059</v>
@@ -45240,7 +45240,7 @@
         <v>-1.392918</v>
       </c>
       <c r="I548" s="6" t="n">
-        <v>100.095003</v>
+        <v>100.088978</v>
       </c>
       <c r="J548" s="6" t="n">
         <v>99.871627</v>
@@ -45324,7 +45324,7 @@
         <v>-1.34328</v>
       </c>
       <c r="I549" s="9" t="n">
-        <v>100.05924</v>
+        <v>100.050048</v>
       </c>
       <c r="J549" s="9" t="n">
         <v>99.81034200000001</v>
@@ -45408,7 +45408,7 @@
         <v>-1.151167</v>
       </c>
       <c r="I550" s="6" t="n">
-        <v>100.01461</v>
+        <v>99.99865699999999</v>
       </c>
       <c r="J550" s="6" t="n">
         <v>99.729754</v>
@@ -45492,7 +45492,7 @@
         <v>-0.857298</v>
       </c>
       <c r="I551" s="9" t="n">
-        <v>99.96387</v>
+        <v>99.936921</v>
       </c>
       <c r="J551" s="9" t="n">
         <v>99.62351099999999</v>
@@ -45576,7 +45576,7 @@
         <v>-0.517132</v>
       </c>
       <c r="I552" s="6" t="n">
-        <v>99.912727</v>
+        <v>99.87272299999999</v>
       </c>
       <c r="J552" s="6" t="n">
         <v>99.511067</v>
@@ -45660,7 +45660,7 @@
         <v>-0.174398</v>
       </c>
       <c r="I553" s="9" t="n">
-        <v>99.875226</v>
+        <v>99.826672</v>
       </c>
       <c r="J553" s="9" t="n">
         <v>99.429486</v>
@@ -45744,7 +45744,7 @@
         <v>0.1417</v>
       </c>
       <c r="I554" s="6" t="n">
-        <v>99.851462</v>
+        <v>99.798992</v>
       </c>
       <c r="J554" s="6" t="n">
         <v>99.396497</v>
@@ -45828,7 +45828,7 @@
         <v>0.420768</v>
       </c>
       <c r="I555" s="9" t="n">
-        <v>99.843879</v>
+        <v>99.791175</v>
       </c>
       <c r="J555" s="9" t="n">
         <v>99.410533</v>
@@ -45912,7 +45912,7 @@
         <v>0.6679929999999999</v>
       </c>
       <c r="I556" s="6" t="n">
-        <v>99.83741000000001</v>
+        <v>99.78725300000001</v>
       </c>
       <c r="J556" s="6" t="n">
         <v>99.446281</v>
@@ -45996,7 +45996,7 @@
         <v>0.893749</v>
       </c>
       <c r="I557" s="9" t="n">
-        <v>99.832916</v>
+        <v>99.787902</v>
       </c>
       <c r="J557" s="9" t="n">
         <v>99.48218799999999</v>
@@ -46080,7 +46080,7 @@
         <v>1.089155</v>
       </c>
       <c r="I558" s="6" t="n">
-        <v>99.83965499999999</v>
+        <v>99.80225</v>
       </c>
       <c r="J558" s="6" t="n">
         <v>99.518897</v>
@@ -46164,7 +46164,7 @@
         <v>1.239039</v>
       </c>
       <c r="I559" s="9" t="n">
-        <v>99.886094</v>
+        <v>99.85903999999999</v>
       </c>
       <c r="J559" s="9" t="n">
         <v>99.57956</v>
@@ -46248,7 +46248,7 @@
         <v>1.329632</v>
       </c>
       <c r="I560" s="6" t="n">
-        <v>99.975599</v>
+        <v>99.962011</v>
       </c>
       <c r="J560" s="6" t="n">
         <v>99.669968</v>
@@ -46332,7 +46332,7 @@
         <v>1.345132</v>
       </c>
       <c r="I561" s="9" t="n">
-        <v>100.089243</v>
+        <v>100.094416</v>
       </c>
       <c r="J561" s="9" t="n">
         <v>99.791371</v>
@@ -46416,7 +46416,7 @@
         <v>1.279731</v>
       </c>
       <c r="I562" s="6" t="n">
-        <v>100.193386</v>
+        <v>100.225959</v>
       </c>
       <c r="J562" s="6" t="n">
         <v>99.91174100000001</v>
@@ -46500,7 +46500,7 @@
         <v>1.158249</v>
       </c>
       <c r="I563" s="9" t="n">
-        <v>100.289746</v>
+        <v>100.356612</v>
       </c>
       <c r="J563" s="9" t="n">
         <v>100.033774</v>
@@ -46577,7 +46577,9 @@
       <c r="H564" s="7" t="n">
         <v>1.013072</v>
       </c>
-      <c r="I564" s="6" t="n"/>
+      <c r="I564" s="6" t="n">
+        <v>100.491865</v>
+      </c>
       <c r="J564" s="6" t="n">
         <v>100.158475</v>
       </c>

--- a/downloads/indicadores/SIC/SIC_datos.xlsx
+++ b/downloads/indicadores/SIC/SIC_datos.xlsx
@@ -7188,7 +7188,7 @@
         <v>98.513853</v>
       </c>
       <c r="M90" s="6" t="n">
-        <v>102.496955</v>
+        <v>102.50242</v>
       </c>
       <c r="N90" s="6" t="n">
         <v>97.889831</v>
@@ -7270,7 +7270,7 @@
         <v>98.51832899999999</v>
       </c>
       <c r="M91" s="9" t="n">
-        <v>102.13848</v>
+        <v>102.143164</v>
       </c>
       <c r="N91" s="9" t="n">
         <v>97.94937</v>
@@ -7352,7 +7352,7 @@
         <v>98.561089</v>
       </c>
       <c r="M92" s="6" t="n">
-        <v>101.742059</v>
+        <v>101.745879</v>
       </c>
       <c r="N92" s="6" t="n">
         <v>98.01599299999999</v>
@@ -7434,7 +7434,7 @@
         <v>98.64266600000001</v>
       </c>
       <c r="M93" s="9" t="n">
-        <v>101.333438</v>
+        <v>101.336368</v>
       </c>
       <c r="N93" s="9" t="n">
         <v>98.08319899999999</v>
@@ -7516,7 +7516,7 @@
         <v>98.763024</v>
       </c>
       <c r="M94" s="6" t="n">
-        <v>100.932229</v>
+        <v>100.934285</v>
       </c>
       <c r="N94" s="6" t="n">
         <v>98.162494</v>
@@ -7598,7 +7598,7 @@
         <v>98.914935</v>
       </c>
       <c r="M95" s="9" t="n">
-        <v>100.592383</v>
+        <v>100.593698</v>
       </c>
       <c r="N95" s="9" t="n">
         <v>98.269811</v>
@@ -7680,7 +7680,7 @@
         <v>99.085436</v>
       </c>
       <c r="M96" s="6" t="n">
-        <v>100.330256</v>
+        <v>100.331001</v>
       </c>
       <c r="N96" s="6" t="n">
         <v>98.409961</v>
@@ -7762,7 +7762,7 @@
         <v>99.256884</v>
       </c>
       <c r="M97" s="9" t="n">
-        <v>100.148861</v>
+        <v>100.14921</v>
       </c>
       <c r="N97" s="9" t="n">
         <v>98.54351800000001</v>
@@ -7844,7 +7844,7 @@
         <v>99.408141</v>
       </c>
       <c r="M98" s="6" t="n">
-        <v>100.048261</v>
+        <v>100.048391</v>
       </c>
       <c r="N98" s="6" t="n">
         <v>98.65055599999999</v>
@@ -7926,7 +7926,7 @@
         <v>99.51108600000001</v>
       </c>
       <c r="M99" s="9" t="n">
-        <v>100.011166</v>
+        <v>100.011216</v>
       </c>
       <c r="N99" s="9" t="n">
         <v>98.743258</v>
@@ -8008,7 +8008,7 @@
         <v>99.5478</v>
       </c>
       <c r="M100" s="6" t="n">
-        <v>100.001183</v>
+        <v>100.001211</v>
       </c>
       <c r="N100" s="6" t="n">
         <v>98.843352</v>
@@ -8090,7 +8090,7 @@
         <v>99.520081</v>
       </c>
       <c r="M101" s="9" t="n">
-        <v>100.034274</v>
+        <v>100.034374</v>
       </c>
       <c r="N101" s="9" t="n">
         <v>98.9953</v>
@@ -8172,7 +8172,7 @@
         <v>99.45335799999999</v>
       </c>
       <c r="M102" s="6" t="n">
-        <v>100.15432</v>
+        <v>100.154682</v>
       </c>
       <c r="N102" s="6" t="n">
         <v>99.239958</v>
@@ -8254,7 +8254,7 @@
         <v>99.373966</v>
       </c>
       <c r="M103" s="9" t="n">
-        <v>100.324502</v>
+        <v>100.325234</v>
       </c>
       <c r="N103" s="9" t="n">
         <v>99.544714</v>
@@ -8336,7 +8336,7 @@
         <v>99.29294</v>
       </c>
       <c r="M104" s="6" t="n">
-        <v>100.51421</v>
+        <v>100.515355</v>
       </c>
       <c r="N104" s="6" t="n">
         <v>99.882284</v>
@@ -8418,7 +8418,7 @@
         <v>99.214922</v>
       </c>
       <c r="M105" s="9" t="n">
-        <v>100.675399</v>
+        <v>100.676895</v>
       </c>
       <c r="N105" s="9" t="n">
         <v>100.223042</v>
@@ -8500,7 +8500,7 @@
         <v>99.140293</v>
       </c>
       <c r="M106" s="6" t="n">
-        <v>100.794127</v>
+        <v>100.795882</v>
       </c>
       <c r="N106" s="6" t="n">
         <v>100.543221</v>
@@ -8582,7 +8582,7 @@
         <v>99.06838399999999</v>
       </c>
       <c r="M107" s="9" t="n">
-        <v>100.866162</v>
+        <v>100.868074</v>
       </c>
       <c r="N107" s="9" t="n">
         <v>100.827865</v>
@@ -8664,7 +8664,7 @@
         <v>99.000872</v>
       </c>
       <c r="M108" s="6" t="n">
-        <v>100.89237</v>
+        <v>100.894339</v>
       </c>
       <c r="N108" s="6" t="n">
         <v>101.067592</v>
@@ -8746,7 +8746,7 @@
         <v>98.94105</v>
       </c>
       <c r="M109" s="9" t="n">
-        <v>100.898806</v>
+        <v>100.900789</v>
       </c>
       <c r="N109" s="9" t="n">
         <v>101.257588</v>
@@ -8828,7 +8828,7 @@
         <v>98.898489</v>
       </c>
       <c r="M110" s="6" t="n">
-        <v>100.908962</v>
+        <v>100.910968</v>
       </c>
       <c r="N110" s="6" t="n">
         <v>101.38472</v>
@@ -8910,7 +8910,7 @@
         <v>98.88025399999999</v>
       </c>
       <c r="M111" s="9" t="n">
-        <v>100.897366</v>
+        <v>100.899346</v>
       </c>
       <c r="N111" s="9" t="n">
         <v>101.455399</v>
@@ -8992,7 +8992,7 @@
         <v>98.884218</v>
       </c>
       <c r="M112" s="6" t="n">
-        <v>100.856823</v>
+        <v>100.858715</v>
       </c>
       <c r="N112" s="6" t="n">
         <v>101.487237</v>
@@ -9074,7 +9074,7 @@
         <v>98.903593</v>
       </c>
       <c r="M113" s="9" t="n">
-        <v>100.757101</v>
+        <v>100.758775</v>
       </c>
       <c r="N113" s="9" t="n">
         <v>101.487498</v>
@@ -9156,7 +9156,7 @@
         <v>98.93374300000001</v>
       </c>
       <c r="M114" s="6" t="n">
-        <v>100.577202</v>
+        <v>100.578485</v>
       </c>
       <c r="N114" s="6" t="n">
         <v>101.474435</v>
@@ -9238,7 +9238,7 @@
         <v>98.972877</v>
       </c>
       <c r="M115" s="9" t="n">
-        <v>100.332324</v>
+        <v>100.333073</v>
       </c>
       <c r="N115" s="9" t="n">
         <v>101.436576</v>
@@ -9320,7 +9320,7 @@
         <v>99.015461</v>
       </c>
       <c r="M116" s="6" t="n">
-        <v>100.077711</v>
+        <v>100.077905</v>
       </c>
       <c r="N116" s="6" t="n">
         <v>101.35198</v>
@@ -9402,7 +9402,7 @@
         <v>99.065478</v>
       </c>
       <c r="M117" s="9" t="n">
-        <v>99.848631</v>
+        <v>99.848326</v>
       </c>
       <c r="N117" s="9" t="n">
         <v>101.219874</v>
@@ -9484,7 +9484,7 @@
         <v>99.129929</v>
       </c>
       <c r="M118" s="6" t="n">
-        <v>99.66045800000001</v>
+        <v>99.65974300000001</v>
       </c>
       <c r="N118" s="6" t="n">
         <v>101.047109</v>
@@ -9566,7 +9566,7 @@
         <v>99.213256</v>
       </c>
       <c r="M119" s="9" t="n">
-        <v>99.493289</v>
+        <v>99.492211</v>
       </c>
       <c r="N119" s="9" t="n">
         <v>100.861248</v>
@@ -9648,7 +9648,7 @@
         <v>99.314172</v>
       </c>
       <c r="M120" s="6" t="n">
-        <v>99.351692</v>
+        <v>99.35030500000001</v>
       </c>
       <c r="N120" s="6" t="n">
         <v>100.674677</v>
@@ -9730,7 +9730,7 @@
         <v>99.42949299999999</v>
       </c>
       <c r="M121" s="9" t="n">
-        <v>99.21385600000001</v>
+        <v>99.21216800000001</v>
       </c>
       <c r="N121" s="9" t="n">
         <v>100.538541</v>
@@ -9812,7 +9812,7 @@
         <v>99.552221</v>
       </c>
       <c r="M122" s="6" t="n">
-        <v>99.05425200000001</v>
+        <v>99.052217</v>
       </c>
       <c r="N122" s="6" t="n">
         <v>100.451891</v>
@@ -9894,7 +9894,7 @@
         <v>99.678282</v>
       </c>
       <c r="M123" s="9" t="n">
-        <v>98.887705</v>
+        <v>98.885307</v>
       </c>
       <c r="N123" s="9" t="n">
         <v>100.375072</v>
@@ -9976,7 +9976,7 @@
         <v>99.801605</v>
       </c>
       <c r="M124" s="6" t="n">
-        <v>98.75347499999999</v>
+        <v>98.75078499999999</v>
       </c>
       <c r="N124" s="6" t="n">
         <v>100.293934</v>
@@ -10058,7 +10058,7 @@
         <v>99.92883</v>
       </c>
       <c r="M125" s="9" t="n">
-        <v>98.657574</v>
+        <v>98.654674</v>
       </c>
       <c r="N125" s="9" t="n">
         <v>100.202263</v>
@@ -10140,7 +10140,7 @@
         <v>100.067521</v>
       </c>
       <c r="M126" s="6" t="n">
-        <v>98.611852</v>
+        <v>98.60885399999999</v>
       </c>
       <c r="N126" s="6" t="n">
         <v>100.118217</v>
@@ -10222,7 +10222,7 @@
         <v>100.222544</v>
       </c>
       <c r="M127" s="9" t="n">
-        <v>98.667597</v>
+        <v>98.66471900000001</v>
       </c>
       <c r="N127" s="9" t="n">
         <v>100.061134</v>
@@ -10304,7 +10304,7 @@
         <v>100.394328</v>
       </c>
       <c r="M128" s="6" t="n">
-        <v>98.84280699999999</v>
+        <v>98.840311</v>
       </c>
       <c r="N128" s="6" t="n">
         <v>100.056587</v>
@@ -10386,7 +10386,7 @@
         <v>100.581786</v>
       </c>
       <c r="M129" s="9" t="n">
-        <v>99.110589</v>
+        <v>99.108677</v>
       </c>
       <c r="N129" s="9" t="n">
         <v>100.111083</v>
@@ -10468,7 +10468,7 @@
         <v>100.778736</v>
       </c>
       <c r="M130" s="6" t="n">
-        <v>99.397327</v>
+        <v>99.396039</v>
       </c>
       <c r="N130" s="6" t="n">
         <v>100.224766</v>
@@ -10550,7 +10550,7 @@
         <v>100.98361</v>
       </c>
       <c r="M131" s="9" t="n">
-        <v>99.63914</v>
+        <v>99.638379</v>
       </c>
       <c r="N131" s="9" t="n">
         <v>100.371558</v>
@@ -10632,7 +10632,7 @@
         <v>101.192575</v>
       </c>
       <c r="M132" s="6" t="n">
-        <v>99.768687</v>
+        <v>99.768208</v>
       </c>
       <c r="N132" s="6" t="n">
         <v>100.524099</v>
@@ -10714,7 +10714,7 @@
         <v>101.401357</v>
       </c>
       <c r="M133" s="9" t="n">
-        <v>99.74057500000001</v>
+        <v>99.74003500000001</v>
       </c>
       <c r="N133" s="9" t="n">
         <v>100.656981</v>
@@ -10796,7 +10796,7 @@
         <v>101.604274</v>
       </c>
       <c r="M134" s="6" t="n">
-        <v>99.62345000000001</v>
+        <v>99.62265499999999</v>
       </c>
       <c r="N134" s="6" t="n">
         <v>100.739497</v>
@@ -10878,7 +10878,7 @@
         <v>101.795487</v>
       </c>
       <c r="M135" s="9" t="n">
-        <v>99.486448</v>
+        <v>99.485354</v>
       </c>
       <c r="N135" s="9" t="n">
         <v>100.75915</v>
@@ -10960,7 +10960,7 @@
         <v>101.975778</v>
       </c>
       <c r="M136" s="6" t="n">
-        <v>99.296544</v>
+        <v>99.29503699999999</v>
       </c>
       <c r="N136" s="6" t="n">
         <v>100.717678</v>
@@ -11042,7 +11042,7 @@
         <v>102.145559</v>
       </c>
       <c r="M137" s="9" t="n">
-        <v>99.101662</v>
+        <v>99.09972999999999</v>
       </c>
       <c r="N137" s="9" t="n">
         <v>100.638116</v>
@@ -11124,7 +11124,7 @@
         <v>102.300413</v>
       </c>
       <c r="M138" s="6" t="n">
-        <v>98.91026599999999</v>
+        <v>98.907917</v>
       </c>
       <c r="N138" s="6" t="n">
         <v>100.529789</v>
@@ -11206,7 +11206,7 @@
         <v>102.438604</v>
       </c>
       <c r="M139" s="9" t="n">
-        <v>98.717378</v>
+        <v>98.714609</v>
       </c>
       <c r="N139" s="9" t="n">
         <v>100.417675</v>
@@ -11288,7 +11288,7 @@
         <v>102.558045</v>
       </c>
       <c r="M140" s="6" t="n">
-        <v>98.53489999999999</v>
+        <v>98.531734</v>
       </c>
       <c r="N140" s="6" t="n">
         <v>100.326796</v>
@@ -11370,7 +11370,7 @@
         <v>102.658359</v>
       </c>
       <c r="M141" s="9" t="n">
-        <v>98.346403</v>
+        <v>98.342826</v>
       </c>
       <c r="N141" s="9" t="n">
         <v>100.276567</v>
@@ -11452,7 +11452,7 @@
         <v>102.742039</v>
       </c>
       <c r="M142" s="6" t="n">
-        <v>98.226761</v>
+        <v>98.22292299999999</v>
       </c>
       <c r="N142" s="6" t="n">
         <v>100.259426</v>
@@ -11534,7 +11534,7 @@
         <v>102.803434</v>
       </c>
       <c r="M143" s="9" t="n">
-        <v>98.270596</v>
+        <v>98.266854</v>
       </c>
       <c r="N143" s="9" t="n">
         <v>100.262412</v>
@@ -11616,7 +11616,7 @@
         <v>102.840748</v>
       </c>
       <c r="M144" s="6" t="n">
-        <v>98.521176</v>
+        <v>98.517979</v>
       </c>
       <c r="N144" s="6" t="n">
         <v>100.28414</v>
@@ -11698,7 +11698,7 @@
         <v>102.858978</v>
       </c>
       <c r="M145" s="9" t="n">
-        <v>98.876863</v>
+        <v>98.874441</v>
       </c>
       <c r="N145" s="9" t="n">
         <v>100.316903</v>
@@ -11780,7 +11780,7 @@
         <v>102.861156</v>
       </c>
       <c r="M146" s="6" t="n">
-        <v>99.181747</v>
+        <v>99.17998900000001</v>
       </c>
       <c r="N146" s="6" t="n">
         <v>100.362035</v>
@@ -11862,7 +11862,7 @@
         <v>102.846857</v>
       </c>
       <c r="M147" s="9" t="n">
-        <v>99.38202099999999</v>
+        <v>99.3807</v>
       </c>
       <c r="N147" s="9" t="n">
         <v>100.426178</v>
@@ -11944,7 +11944,7 @@
         <v>102.809611</v>
       </c>
       <c r="M148" s="6" t="n">
-        <v>99.452015</v>
+        <v>99.450846</v>
       </c>
       <c r="N148" s="6" t="n">
         <v>100.514866</v>
@@ -12026,7 +12026,7 @@
         <v>102.745111</v>
       </c>
       <c r="M149" s="9" t="n">
-        <v>99.41650199999999</v>
+        <v>99.415256</v>
       </c>
       <c r="N149" s="9" t="n">
         <v>100.612528</v>
@@ -12108,7 +12108,7 @@
         <v>102.648853</v>
       </c>
       <c r="M150" s="6" t="n">
-        <v>99.314211</v>
+        <v>99.312742</v>
       </c>
       <c r="N150" s="6" t="n">
         <v>100.733488</v>
@@ -12190,7 +12190,7 @@
         <v>102.518122</v>
       </c>
       <c r="M151" s="9" t="n">
-        <v>99.16305699999999</v>
+        <v>99.161259</v>
       </c>
       <c r="N151" s="9" t="n">
         <v>100.875636</v>
@@ -12272,7 +12272,7 @@
         <v>102.356779</v>
       </c>
       <c r="M152" s="6" t="n">
-        <v>98.96531899999999</v>
+        <v>98.96308999999999</v>
       </c>
       <c r="N152" s="6" t="n">
         <v>101.01503</v>
@@ -12354,7 +12354,7 @@
         <v>102.1753</v>
       </c>
       <c r="M153" s="9" t="n">
-        <v>98.75939099999999</v>
+        <v>98.756714</v>
       </c>
       <c r="N153" s="9" t="n">
         <v>101.118198</v>
@@ -12436,7 +12436,7 @@
         <v>101.990745</v>
       </c>
       <c r="M154" s="6" t="n">
-        <v>98.55488699999999</v>
+        <v>98.55176400000001</v>
       </c>
       <c r="N154" s="6" t="n">
         <v>101.172073</v>
@@ -12518,7 +12518,7 @@
         <v>101.815565</v>
       </c>
       <c r="M155" s="9" t="n">
-        <v>98.341466</v>
+        <v>98.337878</v>
       </c>
       <c r="N155" s="9" t="n">
         <v>101.173279</v>
@@ -12600,7 +12600,7 @@
         <v>101.658723</v>
       </c>
       <c r="M156" s="6" t="n">
-        <v>98.149564</v>
+        <v>98.14555799999999</v>
       </c>
       <c r="N156" s="6" t="n">
         <v>101.129047</v>
@@ -12682,7 +12682,7 @@
         <v>101.516383</v>
       </c>
       <c r="M157" s="9" t="n">
-        <v>98.02409</v>
+        <v>98.01981000000001</v>
       </c>
       <c r="N157" s="9" t="n">
         <v>101.044343</v>
@@ -12764,7 +12764,7 @@
         <v>101.384932</v>
       </c>
       <c r="M158" s="6" t="n">
-        <v>98.052525</v>
+        <v>98.04830699999999</v>
       </c>
       <c r="N158" s="6" t="n">
         <v>100.940255</v>
@@ -12846,7 +12846,7 @@
         <v>101.263042</v>
       </c>
       <c r="M159" s="9" t="n">
-        <v>98.236671</v>
+        <v>98.232855</v>
       </c>
       <c r="N159" s="9" t="n">
         <v>100.826183</v>
@@ -12928,7 +12928,7 @@
         <v>101.157358</v>
       </c>
       <c r="M160" s="6" t="n">
-        <v>98.502843</v>
+        <v>98.499606</v>
       </c>
       <c r="N160" s="6" t="n">
         <v>100.694548</v>
@@ -13010,7 +13010,7 @@
         <v>101.073739</v>
       </c>
       <c r="M161" s="9" t="n">
-        <v>98.752332</v>
+        <v>98.749639</v>
       </c>
       <c r="N161" s="9" t="n">
         <v>100.551939</v>
@@ -13092,7 +13092,7 @@
         <v>101.014253</v>
       </c>
       <c r="M162" s="6" t="n">
-        <v>98.99847</v>
+        <v>98.996313</v>
       </c>
       <c r="N162" s="6" t="n">
         <v>100.41285</v>
@@ -13174,7 +13174,7 @@
         <v>100.971649</v>
       </c>
       <c r="M163" s="9" t="n">
-        <v>99.20557700000001</v>
+        <v>99.203872</v>
       </c>
       <c r="N163" s="9" t="n">
         <v>100.31019</v>
@@ -13256,7 +13256,7 @@
         <v>100.930429</v>
       </c>
       <c r="M164" s="6" t="n">
-        <v>99.334824</v>
+        <v>99.3334</v>
       </c>
       <c r="N164" s="6" t="n">
         <v>100.23428</v>
@@ -13338,7 +13338,7 @@
         <v>100.86669</v>
       </c>
       <c r="M165" s="9" t="n">
-        <v>99.396131</v>
+        <v>99.394841</v>
       </c>
       <c r="N165" s="9" t="n">
         <v>100.17566</v>
@@ -13420,7 +13420,7 @@
         <v>100.758145</v>
       </c>
       <c r="M166" s="6" t="n">
-        <v>99.4597</v>
+        <v>99.45854799999999</v>
       </c>
       <c r="N166" s="6" t="n">
         <v>100.113965</v>
@@ -13502,7 +13502,7 @@
         <v>100.596356</v>
       </c>
       <c r="M167" s="9" t="n">
-        <v>99.53191099999999</v>
+        <v>99.530917</v>
       </c>
       <c r="N167" s="9" t="n">
         <v>100.040907</v>
@@ -13584,7 +13584,7 @@
         <v>100.386373</v>
       </c>
       <c r="M168" s="6" t="n">
-        <v>99.63737500000001</v>
+        <v>99.63661</v>
       </c>
       <c r="N168" s="6" t="n">
         <v>99.94879</v>
@@ -13666,7 +13666,7 @@
         <v>100.147953</v>
       </c>
       <c r="M169" s="9" t="n">
-        <v>99.742812</v>
+        <v>99.742277</v>
       </c>
       <c r="N169" s="9" t="n">
         <v>99.84265600000001</v>
@@ -13748,7 +13748,7 @@
         <v>99.91114899999999</v>
       </c>
       <c r="M170" s="6" t="n">
-        <v>99.786491</v>
+        <v>99.786051</v>
       </c>
       <c r="N170" s="6" t="n">
         <v>99.780244</v>
@@ -13830,7 +13830,7 @@
         <v>99.706529</v>
       </c>
       <c r="M171" s="9" t="n">
-        <v>99.756557</v>
+        <v>99.756052</v>
       </c>
       <c r="N171" s="9" t="n">
         <v>99.774478</v>
@@ -13912,7 +13912,7 @@
         <v>99.55718299999999</v>
       </c>
       <c r="M172" s="6" t="n">
-        <v>99.681932</v>
+        <v>99.681265</v>
       </c>
       <c r="N172" s="6" t="n">
         <v>99.842524</v>
@@ -13994,7 +13994,7 @@
         <v>99.470354</v>
       </c>
       <c r="M173" s="9" t="n">
-        <v>99.56327400000001</v>
+        <v>99.562348</v>
       </c>
       <c r="N173" s="9" t="n">
         <v>100.003542</v>
@@ -14076,7 +14076,7 @@
         <v>99.443833</v>
       </c>
       <c r="M174" s="6" t="n">
-        <v>99.386021</v>
+        <v>99.384709</v>
       </c>
       <c r="N174" s="6" t="n">
         <v>100.217521</v>
@@ -14158,7 +14158,7 @@
         <v>99.473946</v>
       </c>
       <c r="M175" s="9" t="n">
-        <v>99.15218900000001</v>
+        <v>99.150368</v>
       </c>
       <c r="N175" s="9" t="n">
         <v>100.433683</v>
@@ -14240,7 +14240,7 @@
         <v>99.546986</v>
       </c>
       <c r="M176" s="6" t="n">
-        <v>98.899001</v>
+        <v>98.89662800000001</v>
       </c>
       <c r="N176" s="6" t="n">
         <v>100.617396</v>
@@ -14322,7 +14322,7 @@
         <v>99.649176</v>
       </c>
       <c r="M177" s="9" t="n">
-        <v>98.65521200000001</v>
+        <v>98.652308</v>
       </c>
       <c r="N177" s="9" t="n">
         <v>100.772735</v>
@@ -14404,7 +14404,7 @@
         <v>99.763194</v>
       </c>
       <c r="M178" s="6" t="n">
-        <v>98.44482000000001</v>
+        <v>98.441457</v>
       </c>
       <c r="N178" s="6" t="n">
         <v>100.893156</v>
@@ -14486,7 +14486,7 @@
         <v>99.875409</v>
       </c>
       <c r="M179" s="9" t="n">
-        <v>98.325277</v>
+        <v>98.321654</v>
       </c>
       <c r="N179" s="9" t="n">
         <v>100.973359</v>
@@ -14568,7 +14568,7 @@
         <v>99.97479300000001</v>
       </c>
       <c r="M180" s="6" t="n">
-        <v>98.31177599999999</v>
+        <v>98.30812400000001</v>
       </c>
       <c r="N180" s="6" t="n">
         <v>101.003453</v>
@@ -14650,7 +14650,7 @@
         <v>100.042809</v>
       </c>
       <c r="M181" s="9" t="n">
-        <v>98.415147</v>
+        <v>98.41171900000001</v>
       </c>
       <c r="N181" s="9" t="n">
         <v>100.979953</v>
@@ -14732,7 +14732,7 @@
         <v>100.05591</v>
       </c>
       <c r="M182" s="6" t="n">
-        <v>98.660819</v>
+        <v>98.657927</v>
       </c>
       <c r="N182" s="6" t="n">
         <v>100.904273</v>
@@ -14814,7 +14814,7 @@
         <v>99.990298</v>
       </c>
       <c r="M183" s="9" t="n">
-        <v>99.035676</v>
+        <v>99.03360000000001</v>
       </c>
       <c r="N183" s="9" t="n">
         <v>100.764799</v>
@@ -14896,7 +14896,7 @@
         <v>99.81297000000001</v>
       </c>
       <c r="M184" s="6" t="n">
-        <v>99.530185</v>
+        <v>99.52918699999999</v>
       </c>
       <c r="N184" s="6" t="n">
         <v>100.521356</v>
@@ -14978,7 +14978,7 @@
         <v>99.50678000000001</v>
       </c>
       <c r="M185" s="9" t="n">
-        <v>100.13902</v>
+        <v>100.139348</v>
       </c>
       <c r="N185" s="9" t="n">
         <v>100.154718</v>
@@ -15060,7 +15060,7 @@
         <v>99.077691</v>
       </c>
       <c r="M186" s="6" t="n">
-        <v>100.871625</v>
+        <v>100.873549</v>
       </c>
       <c r="N186" s="6" t="n">
         <v>99.687623</v>
@@ -15142,7 +15142,7 @@
         <v>98.550358</v>
       </c>
       <c r="M187" s="9" t="n">
-        <v>101.688614</v>
+        <v>101.692318</v>
       </c>
       <c r="N187" s="9" t="n">
         <v>99.18918600000001</v>
@@ -15224,7 +15224,7 @@
         <v>97.976395</v>
       </c>
       <c r="M188" s="6" t="n">
-        <v>102.513994</v>
+        <v>102.519496</v>
       </c>
       <c r="N188" s="6" t="n">
         <v>98.73203599999999</v>
@@ -15306,7 +15306,7 @@
         <v>97.410459</v>
       </c>
       <c r="M189" s="9" t="n">
-        <v>103.270632</v>
+        <v>103.277782</v>
       </c>
       <c r="N189" s="9" t="n">
         <v>98.353084</v>
@@ -15388,7 +15388,7 @@
         <v>96.888695</v>
       </c>
       <c r="M190" s="6" t="n">
-        <v>103.895876</v>
+        <v>103.904388</v>
       </c>
       <c r="N190" s="6" t="n">
         <v>98.10048399999999</v>
@@ -15470,7 +15470,7 @@
         <v>96.439447</v>
       </c>
       <c r="M191" s="9" t="n">
-        <v>104.345641</v>
+        <v>104.355133</v>
       </c>
       <c r="N191" s="9" t="n">
         <v>97.964465</v>
@@ -15552,7 +15552,7 @@
         <v>96.07941700000001</v>
       </c>
       <c r="M192" s="6" t="n">
-        <v>104.600881</v>
+        <v>104.610929</v>
       </c>
       <c r="N192" s="6" t="n">
         <v>97.923315</v>
@@ -15634,7 +15634,7 @@
         <v>95.820037</v>
       </c>
       <c r="M193" s="9" t="n">
-        <v>104.667286</v>
+        <v>104.677479</v>
       </c>
       <c r="N193" s="9" t="n">
         <v>97.957207</v>
@@ -15716,7 +15716,7 @@
         <v>95.665671</v>
       </c>
       <c r="M194" s="6" t="n">
-        <v>104.558614</v>
+        <v>104.56857</v>
       </c>
       <c r="N194" s="6" t="n">
         <v>98.024897</v>
@@ -15798,7 +15798,7 @@
         <v>95.61212999999999</v>
       </c>
       <c r="M195" s="9" t="n">
-        <v>104.324401</v>
+        <v>104.333847</v>
       </c>
       <c r="N195" s="9" t="n">
         <v>98.115427</v>
@@ -15880,7 +15880,7 @@
         <v>95.651477</v>
       </c>
       <c r="M196" s="6" t="n">
-        <v>104.0164</v>
+        <v>104.025174</v>
       </c>
       <c r="N196" s="6" t="n">
         <v>98.242285</v>
@@ -15962,7 +15962,7 @@
         <v>95.772733</v>
       </c>
       <c r="M197" s="9" t="n">
-        <v>103.66798</v>
+        <v>103.675995</v>
       </c>
       <c r="N197" s="9" t="n">
         <v>98.401079</v>
@@ -16044,7 +16044,7 @@
         <v>95.960961</v>
       </c>
       <c r="M198" s="6" t="n">
-        <v>103.289933</v>
+        <v>103.297125</v>
       </c>
       <c r="N198" s="6" t="n">
         <v>98.574071</v>
@@ -16126,7 +16126,7 @@
         <v>96.19504499999999</v>
       </c>
       <c r="M199" s="9" t="n">
-        <v>102.918896</v>
+        <v>102.925279</v>
       </c>
       <c r="N199" s="9" t="n">
         <v>98.748597</v>
@@ -16208,7 +16208,7 @@
         <v>96.45236800000001</v>
       </c>
       <c r="M200" s="6" t="n">
-        <v>102.582451</v>
+        <v>102.588102</v>
       </c>
       <c r="N200" s="6" t="n">
         <v>98.90607799999999</v>
@@ -16290,7 +16290,7 @@
         <v>96.712782</v>
       </c>
       <c r="M201" s="9" t="n">
-        <v>102.303379</v>
+        <v>102.308422</v>
       </c>
       <c r="N201" s="9" t="n">
         <v>99.043278</v>
@@ -16372,7 +16372,7 @@
         <v>96.96629799999999</v>
       </c>
       <c r="M202" s="6" t="n">
-        <v>102.098908</v>
+        <v>102.103506</v>
       </c>
       <c r="N202" s="6" t="n">
         <v>99.152389</v>
@@ -16454,7 +16454,7 @@
         <v>97.207329</v>
       </c>
       <c r="M203" s="9" t="n">
-        <v>101.986719</v>
+        <v>101.991072</v>
       </c>
       <c r="N203" s="9" t="n">
         <v>99.23554900000001</v>
@@ -16536,7 +16536,7 @@
         <v>97.435919</v>
       </c>
       <c r="M204" s="6" t="n">
-        <v>101.959261</v>
+        <v>101.963554</v>
       </c>
       <c r="N204" s="6" t="n">
         <v>99.32303899999999</v>
@@ -16618,7 +16618,7 @@
         <v>97.66217399999999</v>
       </c>
       <c r="M205" s="9" t="n">
-        <v>102.015947</v>
+        <v>102.020364</v>
       </c>
       <c r="N205" s="9" t="n">
         <v>99.406631</v>
@@ -16700,7 +16700,7 @@
         <v>97.896001</v>
       </c>
       <c r="M206" s="6" t="n">
-        <v>102.13838</v>
+        <v>102.143063</v>
       </c>
       <c r="N206" s="6" t="n">
         <v>99.47515300000001</v>
@@ -16782,7 +16782,7 @@
         <v>98.148359</v>
       </c>
       <c r="M207" s="9" t="n">
-        <v>102.24291</v>
+        <v>102.247821</v>
       </c>
       <c r="N207" s="9" t="n">
         <v>99.52127</v>
@@ -16864,7 +16864,7 @@
         <v>98.421403</v>
       </c>
       <c r="M208" s="6" t="n">
-        <v>102.246458</v>
+        <v>102.251376</v>
       </c>
       <c r="N208" s="6" t="n">
         <v>99.542169</v>
@@ -16946,7 +16946,7 @@
         <v>98.71391300000001</v>
       </c>
       <c r="M209" s="9" t="n">
-        <v>102.135273</v>
+        <v>102.13995</v>
       </c>
       <c r="N209" s="9" t="n">
         <v>99.561707</v>
@@ -17028,7 +17028,7 @@
         <v>99.018359</v>
       </c>
       <c r="M210" s="6" t="n">
-        <v>101.935632</v>
+        <v>101.939874</v>
       </c>
       <c r="N210" s="6" t="n">
         <v>99.61749500000001</v>
@@ -17110,7 +17110,7 @@
         <v>99.33840499999999</v>
       </c>
       <c r="M211" s="9" t="n">
-        <v>101.688919</v>
+        <v>101.692623</v>
       </c>
       <c r="N211" s="9" t="n">
         <v>99.702364</v>
@@ -17192,7 +17192,7 @@
         <v>99.65942800000001</v>
       </c>
       <c r="M212" s="6" t="n">
-        <v>101.444084</v>
+        <v>101.447255</v>
       </c>
       <c r="N212" s="6" t="n">
         <v>99.80806</v>
@@ -17274,7 +17274,7 @@
         <v>99.97058699999999</v>
       </c>
       <c r="M213" s="9" t="n">
-        <v>101.20397</v>
+        <v>101.206618</v>
       </c>
       <c r="N213" s="9" t="n">
         <v>99.920338</v>
@@ -17356,7 +17356,7 @@
         <v>100.255084</v>
       </c>
       <c r="M214" s="6" t="n">
-        <v>100.953772</v>
+        <v>100.955874</v>
       </c>
       <c r="N214" s="6" t="n">
         <v>100.031592</v>
@@ -17438,7 +17438,7 @@
         <v>100.493336</v>
       </c>
       <c r="M215" s="9" t="n">
-        <v>100.688729</v>
+        <v>100.690255</v>
       </c>
       <c r="N215" s="9" t="n">
         <v>100.143608</v>
@@ -17520,7 +17520,7 @@
         <v>100.672029</v>
       </c>
       <c r="M216" s="6" t="n">
-        <v>100.442566</v>
+        <v>100.443555</v>
       </c>
       <c r="N216" s="6" t="n">
         <v>100.24582</v>
@@ -17602,7 +17602,7 @@
         <v>100.779683</v>
       </c>
       <c r="M217" s="9" t="n">
-        <v>100.205179</v>
+        <v>100.205651</v>
       </c>
       <c r="N217" s="9" t="n">
         <v>100.332048</v>
@@ -17684,7 +17684,7 @@
         <v>100.813832</v>
       </c>
       <c r="M218" s="6" t="n">
-        <v>100.013169</v>
+        <v>100.013222</v>
       </c>
       <c r="N218" s="6" t="n">
         <v>100.406904</v>
@@ -17766,7 +17766,7 @@
         <v>100.78481</v>
       </c>
       <c r="M219" s="9" t="n">
-        <v>99.89203999999999</v>
+        <v>99.89183</v>
       </c>
       <c r="N219" s="9" t="n">
         <v>100.472965</v>
@@ -17848,7 +17848,7 @@
         <v>100.716317</v>
       </c>
       <c r="M220" s="6" t="n">
-        <v>99.844915</v>
+        <v>99.84460199999999</v>
       </c>
       <c r="N220" s="6" t="n">
         <v>100.530378</v>
@@ -17930,7 +17930,7 @@
         <v>100.634413</v>
       </c>
       <c r="M221" s="9" t="n">
-        <v>99.847084</v>
+        <v>99.84677600000001</v>
       </c>
       <c r="N221" s="9" t="n">
         <v>100.572069</v>
@@ -18012,7 +18012,7 @@
         <v>100.562551</v>
       </c>
       <c r="M222" s="6" t="n">
-        <v>99.89039099999999</v>
+        <v>99.89017699999999</v>
       </c>
       <c r="N222" s="6" t="n">
         <v>100.598634</v>
@@ -18094,7 +18094,7 @@
         <v>100.502471</v>
       </c>
       <c r="M223" s="9" t="n">
-        <v>99.93266</v>
+        <v>99.93253799999999</v>
       </c>
       <c r="N223" s="9" t="n">
         <v>100.595926</v>
@@ -18176,7 +18176,7 @@
         <v>100.454243</v>
       </c>
       <c r="M224" s="6" t="n">
-        <v>99.95354399999999</v>
+        <v>99.953468</v>
       </c>
       <c r="N224" s="6" t="n">
         <v>100.556732</v>
@@ -18258,7 +18258,7 @@
         <v>100.4139</v>
       </c>
       <c r="M225" s="9" t="n">
-        <v>99.96745300000001</v>
+        <v>99.96740699999999</v>
       </c>
       <c r="N225" s="9" t="n">
         <v>100.475153</v>
@@ -18340,7 +18340,7 @@
         <v>100.381088</v>
       </c>
       <c r="M226" s="6" t="n">
-        <v>100.000004</v>
+        <v>100.000029</v>
       </c>
       <c r="N226" s="6" t="n">
         <v>100.357043</v>
@@ -18422,7 +18422,7 @@
         <v>100.362406</v>
       </c>
       <c r="M227" s="9" t="n">
-        <v>100.026019</v>
+        <v>100.0261</v>
       </c>
       <c r="N227" s="9" t="n">
         <v>100.220583</v>
@@ -18504,7 +18504,7 @@
         <v>100.356367</v>
       </c>
       <c r="M228" s="6" t="n">
-        <v>100.013545</v>
+        <v>100.013599</v>
       </c>
       <c r="N228" s="6" t="n">
         <v>100.090112</v>
@@ -18586,7 +18586,7 @@
         <v>100.358212</v>
       </c>
       <c r="M229" s="9" t="n">
-        <v>99.974281</v>
+        <v>99.97425</v>
       </c>
       <c r="N229" s="9" t="n">
         <v>99.981256</v>
@@ -18668,7 +18668,7 @@
         <v>100.366635</v>
       </c>
       <c r="M230" s="6" t="n">
-        <v>99.924311</v>
+        <v>99.924171</v>
       </c>
       <c r="N230" s="6" t="n">
         <v>99.901003</v>
@@ -18750,7 +18750,7 @@
         <v>100.379782</v>
       </c>
       <c r="M231" s="9" t="n">
-        <v>99.858368</v>
+        <v>99.85808400000001</v>
       </c>
       <c r="N231" s="9" t="n">
         <v>99.84118100000001</v>
@@ -18832,7 +18832,7 @@
         <v>100.39802</v>
       </c>
       <c r="M232" s="6" t="n">
-        <v>99.76027000000001</v>
+        <v>99.759773</v>
       </c>
       <c r="N232" s="6" t="n">
         <v>99.799001</v>
@@ -18914,7 +18914,7 @@
         <v>100.423018</v>
       </c>
       <c r="M233" s="9" t="n">
-        <v>99.640958</v>
+        <v>99.640201</v>
       </c>
       <c r="N233" s="9" t="n">
         <v>99.77095300000001</v>
@@ -18996,7 +18996,7 @@
         <v>100.455249</v>
       </c>
       <c r="M234" s="6" t="n">
-        <v>99.47528699999999</v>
+        <v>99.47417</v>
       </c>
       <c r="N234" s="6" t="n">
         <v>99.77270900000001</v>
@@ -19078,7 +19078,7 @@
         <v>100.494933</v>
       </c>
       <c r="M235" s="9" t="n">
-        <v>99.288242</v>
+        <v>99.286716</v>
       </c>
       <c r="N235" s="9" t="n">
         <v>99.814262</v>
@@ -19160,7 +19160,7 @@
         <v>100.54181</v>
       </c>
       <c r="M236" s="6" t="n">
-        <v>99.06642600000001</v>
+        <v>99.06441700000001</v>
       </c>
       <c r="N236" s="6" t="n">
         <v>99.89098199999999</v>
@@ -19242,7 +19242,7 @@
         <v>100.593761</v>
       </c>
       <c r="M237" s="9" t="n">
-        <v>98.821381</v>
+        <v>98.818839</v>
       </c>
       <c r="N237" s="9" t="n">
         <v>99.988924</v>
@@ -19324,7 +19324,7 @@
         <v>100.65059</v>
       </c>
       <c r="M238" s="6" t="n">
-        <v>98.580859</v>
+        <v>98.577793</v>
       </c>
       <c r="N238" s="6" t="n">
         <v>100.093805</v>
@@ -19406,7 +19406,7 @@
         <v>100.711124</v>
       </c>
       <c r="M239" s="9" t="n">
-        <v>98.38892300000001</v>
+        <v>98.38543900000001</v>
       </c>
       <c r="N239" s="9" t="n">
         <v>100.193154</v>
@@ -19488,7 +19488,7 @@
         <v>100.779653</v>
       </c>
       <c r="M240" s="6" t="n">
-        <v>98.20914500000001</v>
+        <v>98.205269</v>
       </c>
       <c r="N240" s="6" t="n">
         <v>100.285531</v>
@@ -19570,7 +19570,7 @@
         <v>100.863838</v>
       </c>
       <c r="M241" s="9" t="n">
-        <v>98.08167400000001</v>
+        <v>98.07752000000001</v>
       </c>
       <c r="N241" s="9" t="n">
         <v>100.377911</v>
@@ -19652,7 +19652,7 @@
         <v>100.965499</v>
       </c>
       <c r="M242" s="6" t="n">
-        <v>98.00392600000001</v>
+        <v>97.999602</v>
       </c>
       <c r="N242" s="6" t="n">
         <v>100.474494</v>
@@ -19734,7 +19734,7 @@
         <v>101.080452</v>
       </c>
       <c r="M243" s="9" t="n">
-        <v>97.993225</v>
+        <v>97.988879</v>
       </c>
       <c r="N243" s="9" t="n">
         <v>100.582905</v>
@@ -19816,7 +19816,7 @@
         <v>101.205421</v>
       </c>
       <c r="M244" s="6" t="n">
-        <v>98.036835</v>
+        <v>98.032583</v>
       </c>
       <c r="N244" s="6" t="n">
         <v>100.703875</v>
@@ -19898,7 +19898,7 @@
         <v>101.333791</v>
       </c>
       <c r="M245" s="9" t="n">
-        <v>98.11254</v>
+        <v>98.108453</v>
       </c>
       <c r="N245" s="9" t="n">
         <v>100.83703</v>
@@ -19980,7 +19980,7 @@
         <v>101.464669</v>
       </c>
       <c r="M246" s="6" t="n">
-        <v>98.198795</v>
+        <v>98.194896</v>
       </c>
       <c r="N246" s="6" t="n">
         <v>100.975501</v>
@@ -20062,7 +20062,7 @@
         <v>101.594272</v>
       </c>
       <c r="M247" s="9" t="n">
-        <v>98.29145800000001</v>
+        <v>98.287761</v>
       </c>
       <c r="N247" s="9" t="n">
         <v>101.101968</v>
@@ -20144,7 +20144,7 @@
         <v>101.725532</v>
       </c>
       <c r="M248" s="6" t="n">
-        <v>98.374453</v>
+        <v>98.370937</v>
       </c>
       <c r="N248" s="6" t="n">
         <v>101.222493</v>
@@ -20226,7 +20226,7 @@
         <v>101.864546</v>
       </c>
       <c r="M249" s="9" t="n">
-        <v>98.43563</v>
+        <v>98.432248</v>
       </c>
       <c r="N249" s="9" t="n">
         <v>101.355417</v>
@@ -20308,7 +20308,7 @@
         <v>102.018747</v>
       </c>
       <c r="M250" s="6" t="n">
-        <v>98.433443</v>
+        <v>98.43005599999999</v>
       </c>
       <c r="N250" s="6" t="n">
         <v>101.494197</v>
@@ -20390,7 +20390,7 @@
         <v>102.183681</v>
       </c>
       <c r="M251" s="9" t="n">
-        <v>98.375146</v>
+        <v>98.37163200000001</v>
       </c>
       <c r="N251" s="9" t="n">
         <v>101.62275</v>
@@ -20472,7 +20472,7 @@
         <v>102.347064</v>
       </c>
       <c r="M252" s="6" t="n">
-        <v>98.30978399999999</v>
+        <v>98.306128</v>
       </c>
       <c r="N252" s="6" t="n">
         <v>101.729905</v>
@@ -20554,7 +20554,7 @@
         <v>102.493415</v>
       </c>
       <c r="M253" s="9" t="n">
-        <v>98.248532</v>
+        <v>98.244742</v>
       </c>
       <c r="N253" s="9" t="n">
         <v>101.797824</v>
@@ -20636,7 +20636,7 @@
         <v>102.603847</v>
       </c>
       <c r="M254" s="6" t="n">
-        <v>98.14920100000001</v>
+        <v>98.145195</v>
       </c>
       <c r="N254" s="6" t="n">
         <v>101.816273</v>
@@ -20718,7 +20718,7 @@
         <v>102.665559</v>
       </c>
       <c r="M255" s="9" t="n">
-        <v>98.041589</v>
+        <v>98.03734799999999</v>
       </c>
       <c r="N255" s="9" t="n">
         <v>101.782986</v>
@@ -20800,7 +20800,7 @@
         <v>102.66886</v>
       </c>
       <c r="M256" s="6" t="n">
-        <v>98.049093</v>
+        <v>98.04486900000001</v>
       </c>
       <c r="N256" s="6" t="n">
         <v>101.694376</v>
@@ -20882,7 +20882,7 @@
         <v>102.614546</v>
       </c>
       <c r="M257" s="9" t="n">
-        <v>98.190365</v>
+        <v>98.186449</v>
       </c>
       <c r="N257" s="9" t="n">
         <v>101.552745</v>
@@ -20964,7 +20964,7 @@
         <v>102.510288</v>
       </c>
       <c r="M258" s="6" t="n">
-        <v>98.41492700000001</v>
+        <v>98.41149900000001</v>
       </c>
       <c r="N258" s="6" t="n">
         <v>101.364321</v>
@@ -21046,7 +21046,7 @@
         <v>102.360796</v>
       </c>
       <c r="M259" s="9" t="n">
-        <v>98.63256199999999</v>
+        <v>98.629608</v>
       </c>
       <c r="N259" s="9" t="n">
         <v>101.156863</v>
@@ -21128,7 +21128,7 @@
         <v>102.171199</v>
       </c>
       <c r="M260" s="6" t="n">
-        <v>98.763634</v>
+        <v>98.760966</v>
       </c>
       <c r="N260" s="6" t="n">
         <v>100.943332</v>
@@ -21210,7 +21210,7 @@
         <v>101.951559</v>
       </c>
       <c r="M261" s="9" t="n">
-        <v>98.843035</v>
+        <v>98.84054</v>
       </c>
       <c r="N261" s="9" t="n">
         <v>100.714446</v>
@@ -21292,7 +21292,7 @@
         <v>101.705424</v>
       </c>
       <c r="M262" s="6" t="n">
-        <v>98.898658</v>
+        <v>98.89628399999999</v>
       </c>
       <c r="N262" s="6" t="n">
         <v>100.47235</v>
@@ -21374,7 +21374,7 @@
         <v>101.442132</v>
       </c>
       <c r="M263" s="9" t="n">
-        <v>98.911664</v>
+        <v>98.909319</v>
       </c>
       <c r="N263" s="9" t="n">
         <v>100.240886</v>
@@ -21456,7 +21456,7 @@
         <v>101.171947</v>
       </c>
       <c r="M264" s="6" t="n">
-        <v>98.927457</v>
+        <v>98.925146</v>
       </c>
       <c r="N264" s="6" t="n">
         <v>100.034684</v>
@@ -21538,7 +21538,7 @@
         <v>100.905403</v>
       </c>
       <c r="M265" s="9" t="n">
-        <v>98.982375</v>
+        <v>98.98018399999999</v>
       </c>
       <c r="N265" s="9" t="n">
         <v>99.867028</v>
@@ -21620,7 +21620,7 @@
         <v>100.655154</v>
       </c>
       <c r="M266" s="6" t="n">
-        <v>99.11982500000001</v>
+        <v>99.117932</v>
       </c>
       <c r="N266" s="6" t="n">
         <v>99.733161</v>
@@ -21702,7 +21702,7 @@
         <v>100.43561</v>
       </c>
       <c r="M267" s="9" t="n">
-        <v>99.319587</v>
+        <v>99.318129</v>
       </c>
       <c r="N267" s="9" t="n">
         <v>99.62600999999999</v>
@@ -21784,7 +21784,7 @@
         <v>100.252519</v>
       </c>
       <c r="M268" s="6" t="n">
-        <v>99.515934</v>
+        <v>99.514905</v>
       </c>
       <c r="N268" s="6" t="n">
         <v>99.54742299999999</v>
@@ -21866,7 +21866,7 @@
         <v>100.105518</v>
       </c>
       <c r="M269" s="9" t="n">
-        <v>99.687231</v>
+        <v>99.68657399999999</v>
       </c>
       <c r="N269" s="9" t="n">
         <v>99.50642000000001</v>
@@ -21948,7 +21948,7 @@
         <v>99.988755</v>
       </c>
       <c r="M270" s="6" t="n">
-        <v>99.782456</v>
+        <v>99.78200699999999</v>
       </c>
       <c r="N270" s="6" t="n">
         <v>99.50514200000001</v>
@@ -22030,7 +22030,7 @@
         <v>99.903689</v>
       </c>
       <c r="M271" s="9" t="n">
-        <v>99.79913500000001</v>
+        <v>99.798723</v>
       </c>
       <c r="N271" s="9" t="n">
         <v>99.54633</v>
@@ -22112,7 +22112,7 @@
         <v>99.84844</v>
       </c>
       <c r="M272" s="6" t="n">
-        <v>99.783709</v>
+        <v>99.78326300000001</v>
       </c>
       <c r="N272" s="6" t="n">
         <v>99.59899</v>
@@ -22194,7 +22194,7 @@
         <v>99.819211</v>
       </c>
       <c r="M273" s="9" t="n">
-        <v>99.738292</v>
+        <v>99.737747</v>
       </c>
       <c r="N273" s="9" t="n">
         <v>99.632284</v>
@@ -22276,7 +22276,7 @@
         <v>99.80394200000001</v>
       </c>
       <c r="M274" s="6" t="n">
-        <v>99.675224</v>
+        <v>99.674541</v>
       </c>
       <c r="N274" s="6" t="n">
         <v>99.64018299999999</v>
@@ -22358,7 +22358,7 @@
         <v>99.789146</v>
       </c>
       <c r="M275" s="9" t="n">
-        <v>99.60717200000001</v>
+        <v>99.606342</v>
       </c>
       <c r="N275" s="9" t="n">
         <v>99.616845</v>
@@ -22440,7 +22440,7 @@
         <v>99.76751899999999</v>
       </c>
       <c r="M276" s="6" t="n">
-        <v>99.560475</v>
+        <v>99.55954199999999</v>
       </c>
       <c r="N276" s="6" t="n">
         <v>99.56753999999999</v>
@@ -22522,7 +22522,7 @@
         <v>99.731506</v>
       </c>
       <c r="M277" s="9" t="n">
-        <v>99.490852</v>
+        <v>99.489768</v>
       </c>
       <c r="N277" s="9" t="n">
         <v>99.494981</v>
@@ -22604,7 +22604,7 @@
         <v>99.681707</v>
       </c>
       <c r="M278" s="6" t="n">
-        <v>99.399615</v>
+        <v>99.39833299999999</v>
       </c>
       <c r="N278" s="6" t="n">
         <v>99.40487899999999</v>
@@ -22686,7 +22686,7 @@
         <v>99.614966</v>
       </c>
       <c r="M279" s="9" t="n">
-        <v>99.28366200000001</v>
+        <v>99.28212600000001</v>
       </c>
       <c r="N279" s="9" t="n">
         <v>99.30386300000001</v>
@@ -22768,7 +22768,7 @@
         <v>99.53555799999999</v>
       </c>
       <c r="M280" s="6" t="n">
-        <v>99.194016</v>
+        <v>99.192285</v>
       </c>
       <c r="N280" s="6" t="n">
         <v>99.206407</v>
@@ -22850,7 +22850,7 @@
         <v>99.445784</v>
       </c>
       <c r="M281" s="9" t="n">
-        <v>99.154372</v>
+        <v>99.15255500000001</v>
       </c>
       <c r="N281" s="9" t="n">
         <v>99.118302</v>
@@ -22932,7 +22932,7 @@
         <v>99.344033</v>
       </c>
       <c r="M282" s="6" t="n">
-        <v>99.21282100000001</v>
+        <v>99.21113099999999</v>
       </c>
       <c r="N282" s="6" t="n">
         <v>99.04019</v>
@@ -23014,7 +23014,7 @@
         <v>99.228668</v>
       </c>
       <c r="M283" s="9" t="n">
-        <v>99.36743800000001</v>
+        <v>99.366085</v>
       </c>
       <c r="N283" s="9" t="n">
         <v>98.96835299999999</v>
@@ -23096,7 +23096,7 @@
         <v>99.09961</v>
       </c>
       <c r="M284" s="6" t="n">
-        <v>99.618748</v>
+        <v>99.617942</v>
       </c>
       <c r="N284" s="6" t="n">
         <v>98.902925</v>
@@ -23178,7 +23178,7 @@
         <v>98.95890199999999</v>
       </c>
       <c r="M285" s="9" t="n">
-        <v>99.941157</v>
+        <v>99.94105399999999</v>
       </c>
       <c r="N285" s="9" t="n">
         <v>98.83462900000001</v>
@@ -23260,7 +23260,7 @@
         <v>98.815286</v>
       </c>
       <c r="M286" s="6" t="n">
-        <v>100.316034</v>
+        <v>100.316748</v>
       </c>
       <c r="N286" s="6" t="n">
         <v>98.76460299999999</v>
@@ -23342,7 +23342,7 @@
         <v>98.68198700000001</v>
       </c>
       <c r="M287" s="9" t="n">
-        <v>100.732498</v>
+        <v>100.734119</v>
       </c>
       <c r="N287" s="9" t="n">
         <v>98.707785</v>
@@ -23424,7 +23424,7 @@
         <v>98.56939199999999</v>
       </c>
       <c r="M288" s="6" t="n">
-        <v>101.121582</v>
+        <v>101.12405</v>
       </c>
       <c r="N288" s="6" t="n">
         <v>98.672189</v>
@@ -23506,7 +23506,7 @@
         <v>98.48859</v>
       </c>
       <c r="M289" s="9" t="n">
-        <v>101.44805</v>
+        <v>101.451229</v>
       </c>
       <c r="N289" s="9" t="n">
         <v>98.660612</v>
@@ -23588,7 +23588,7 @@
         <v>98.44544</v>
       </c>
       <c r="M290" s="6" t="n">
-        <v>101.67769</v>
+        <v>101.681369</v>
       </c>
       <c r="N290" s="6" t="n">
         <v>98.68392299999999</v>
@@ -23670,7 +23670,7 @@
         <v>98.433948</v>
       </c>
       <c r="M291" s="9" t="n">
-        <v>101.817487</v>
+        <v>101.821471</v>
       </c>
       <c r="N291" s="9" t="n">
         <v>98.743408</v>
@@ -23752,7 +23752,7 @@
         <v>98.44621100000001</v>
       </c>
       <c r="M292" s="6" t="n">
-        <v>101.890207</v>
+        <v>101.89435</v>
       </c>
       <c r="N292" s="6" t="n">
         <v>98.829741</v>
@@ -23834,7 +23834,7 @@
         <v>98.47429200000001</v>
       </c>
       <c r="M293" s="9" t="n">
-        <v>101.918851</v>
+        <v>101.923056</v>
       </c>
       <c r="N293" s="9" t="n">
         <v>98.932936</v>
@@ -23916,7 +23916,7 @@
         <v>98.512821</v>
       </c>
       <c r="M294" s="6" t="n">
-        <v>101.952027</v>
+        <v>101.956305</v>
       </c>
       <c r="N294" s="6" t="n">
         <v>99.047489</v>
@@ -24000,7 +24000,7 @@
         <v>98.56082600000001</v>
       </c>
       <c r="M295" s="9" t="n">
-        <v>101.998139</v>
+        <v>102.002517</v>
       </c>
       <c r="N295" s="9" t="n">
         <v>99.17718000000001</v>
@@ -24084,7 +24084,7 @@
         <v>98.61641</v>
       </c>
       <c r="M296" s="6" t="n">
-        <v>102.030771</v>
+        <v>102.03522</v>
       </c>
       <c r="N296" s="6" t="n">
         <v>99.305249</v>
@@ -24168,7 +24168,7 @@
         <v>98.671498</v>
       </c>
       <c r="M297" s="9" t="n">
-        <v>102.027148</v>
+        <v>102.031589</v>
       </c>
       <c r="N297" s="9" t="n">
         <v>99.420963</v>
@@ -24252,7 +24252,7 @@
         <v>98.721891</v>
       </c>
       <c r="M298" s="6" t="n">
-        <v>101.996954</v>
+        <v>102.00133</v>
       </c>
       <c r="N298" s="6" t="n">
         <v>99.51691700000001</v>
@@ -24336,7 +24336,7 @@
         <v>98.765805</v>
       </c>
       <c r="M299" s="9" t="n">
-        <v>101.95441</v>
+        <v>101.958693</v>
       </c>
       <c r="N299" s="9" t="n">
         <v>99.580827</v>
@@ -24420,7 +24420,7 @@
         <v>98.805159</v>
       </c>
       <c r="M300" s="6" t="n">
-        <v>101.878568</v>
+        <v>101.882685</v>
       </c>
       <c r="N300" s="6" t="n">
         <v>99.624262</v>
@@ -24504,7 +24504,7 @@
         <v>98.842484</v>
       </c>
       <c r="M301" s="9" t="n">
-        <v>101.77148</v>
+        <v>101.775364</v>
       </c>
       <c r="N301" s="9" t="n">
         <v>99.657555</v>
@@ -24588,7 +24588,7 @@
         <v>98.879046</v>
       </c>
       <c r="M302" s="6" t="n">
-        <v>101.603877</v>
+        <v>101.607396</v>
       </c>
       <c r="N302" s="6" t="n">
         <v>99.693719</v>
@@ -24672,7 +24672,7 @@
         <v>98.918227</v>
       </c>
       <c r="M303" s="9" t="n">
-        <v>101.423221</v>
+        <v>101.426346</v>
       </c>
       <c r="N303" s="9" t="n">
         <v>99.744255</v>
@@ -24756,7 +24756,7 @@
         <v>98.963444</v>
       </c>
       <c r="M304" s="6" t="n">
-        <v>101.268851</v>
+        <v>101.27164</v>
       </c>
       <c r="N304" s="6" t="n">
         <v>99.794479</v>
@@ -24840,7 +24840,7 @@
         <v>99.008978</v>
       </c>
       <c r="M305" s="9" t="n">
-        <v>101.115457</v>
+        <v>101.117912</v>
       </c>
       <c r="N305" s="9" t="n">
         <v>99.821991</v>
@@ -24924,7 +24924,7 @@
         <v>99.051187</v>
       </c>
       <c r="M306" s="6" t="n">
-        <v>100.972602</v>
+        <v>100.974746</v>
       </c>
       <c r="N306" s="6" t="n">
         <v>99.829731</v>
@@ -25008,7 +25008,7 @@
         <v>99.087394</v>
       </c>
       <c r="M307" s="9" t="n">
-        <v>100.842558</v>
+        <v>100.844419</v>
       </c>
       <c r="N307" s="9" t="n">
         <v>99.81782800000001</v>
@@ -25092,7 +25092,7 @@
         <v>99.119439</v>
       </c>
       <c r="M308" s="6" t="n">
-        <v>100.720444</v>
+        <v>100.722039</v>
       </c>
       <c r="N308" s="6" t="n">
         <v>99.797179</v>
@@ -25176,7 +25176,7 @@
         <v>99.15382200000001</v>
       </c>
       <c r="M309" s="9" t="n">
-        <v>100.608651</v>
+        <v>100.610002</v>
       </c>
       <c r="N309" s="9" t="n">
         <v>99.78207500000001</v>
@@ -25260,7 +25260,7 @@
         <v>99.19474700000001</v>
       </c>
       <c r="M310" s="6" t="n">
-        <v>100.481347</v>
+        <v>100.48242</v>
       </c>
       <c r="N310" s="6" t="n">
         <v>99.778564</v>
@@ -25344,7 +25344,7 @@
         <v>99.241946</v>
       </c>
       <c r="M311" s="9" t="n">
-        <v>100.320577</v>
+        <v>100.3213</v>
       </c>
       <c r="N311" s="9" t="n">
         <v>99.799948</v>
@@ -25428,7 +25428,7 @@
         <v>99.296852</v>
       </c>
       <c r="M312" s="6" t="n">
-        <v>100.120086</v>
+        <v>100.120372</v>
       </c>
       <c r="N312" s="6" t="n">
         <v>99.848969</v>
@@ -25512,7 +25512,7 @@
         <v>99.362253</v>
       </c>
       <c r="M313" s="9" t="n">
-        <v>99.856976</v>
+        <v>99.856689</v>
       </c>
       <c r="N313" s="9" t="n">
         <v>99.93205399999999</v>
@@ -25596,7 +25596,7 @@
         <v>99.434291</v>
       </c>
       <c r="M314" s="6" t="n">
-        <v>99.584187</v>
+        <v>99.58330599999999</v>
       </c>
       <c r="N314" s="6" t="n">
         <v>100.052926</v>
@@ -25680,7 +25680,7 @@
         <v>99.51062</v>
       </c>
       <c r="M315" s="9" t="n">
-        <v>99.355237</v>
+        <v>99.353859</v>
       </c>
       <c r="N315" s="9" t="n">
         <v>100.206311</v>
@@ -25764,7 +25764,7 @@
         <v>99.59127599999999</v>
       </c>
       <c r="M316" s="6" t="n">
-        <v>99.182243</v>
+        <v>99.18049000000001</v>
       </c>
       <c r="N316" s="6" t="n">
         <v>100.364084</v>
@@ -25848,7 +25848,7 @@
         <v>99.67949400000001</v>
       </c>
       <c r="M317" s="9" t="n">
-        <v>99.09406300000001</v>
+        <v>99.09212100000001</v>
       </c>
       <c r="N317" s="9" t="n">
         <v>100.498919</v>
@@ -25932,7 +25932,7 @@
         <v>99.778583</v>
       </c>
       <c r="M318" s="6" t="n">
-        <v>99.07048</v>
+        <v>99.06849</v>
       </c>
       <c r="N318" s="6" t="n">
         <v>100.596669</v>
@@ -26016,7 +26016,7 @@
         <v>99.88722199999999</v>
       </c>
       <c r="M319" s="9" t="n">
-        <v>99.081197</v>
+        <v>99.07923599999999</v>
       </c>
       <c r="N319" s="9" t="n">
         <v>100.670667</v>
@@ -26100,7 +26100,7 @@
         <v>100.002986</v>
       </c>
       <c r="M320" s="6" t="n">
-        <v>99.09997</v>
+        <v>99.098054</v>
       </c>
       <c r="N320" s="6" t="n">
         <v>100.727728</v>
@@ -26184,7 +26184,7 @@
         <v>100.121526</v>
       </c>
       <c r="M321" s="9" t="n">
-        <v>99.13301300000001</v>
+        <v>99.13117</v>
       </c>
       <c r="N321" s="9" t="n">
         <v>100.769062</v>
@@ -26268,7 +26268,7 @@
         <v>100.239331</v>
       </c>
       <c r="M322" s="6" t="n">
-        <v>99.193163</v>
+        <v>99.191446</v>
       </c>
       <c r="N322" s="6" t="n">
         <v>100.791603</v>
@@ -26352,7 +26352,7 @@
         <v>100.353091</v>
       </c>
       <c r="M323" s="9" t="n">
-        <v>99.28701700000001</v>
+        <v>99.285488</v>
       </c>
       <c r="N323" s="9" t="n">
         <v>100.79205</v>
@@ -26436,7 +26436,7 @@
         <v>100.459599</v>
       </c>
       <c r="M324" s="6" t="n">
-        <v>99.36984699999999</v>
+        <v>99.368477</v>
       </c>
       <c r="N324" s="6" t="n">
         <v>100.778492</v>
@@ -26520,7 +26520,7 @@
         <v>100.557855</v>
       </c>
       <c r="M325" s="9" t="n">
-        <v>99.43084</v>
+        <v>99.429582</v>
       </c>
       <c r="N325" s="9" t="n">
         <v>100.757365</v>
@@ -26604,7 +26604,7 @@
         <v>100.650588</v>
       </c>
       <c r="M326" s="6" t="n">
-        <v>99.496438</v>
+        <v>99.495312</v>
       </c>
       <c r="N326" s="6" t="n">
         <v>100.728064</v>
@@ -26688,7 +26688,7 @@
         <v>100.741447</v>
       </c>
       <c r="M327" s="9" t="n">
-        <v>99.56363399999999</v>
+        <v>99.562656</v>
       </c>
       <c r="N327" s="9" t="n">
         <v>100.689275</v>
@@ -26772,7 +26772,7 @@
         <v>100.834196</v>
       </c>
       <c r="M328" s="6" t="n">
-        <v>99.626017</v>
+        <v>99.625191</v>
       </c>
       <c r="N328" s="6" t="n">
         <v>100.652292</v>
@@ -26856,7 +26856,7 @@
         <v>100.931086</v>
       </c>
       <c r="M329" s="9" t="n">
-        <v>99.66143</v>
+        <v>99.660704</v>
       </c>
       <c r="N329" s="9" t="n">
         <v>100.634878</v>
@@ -26940,7 +26940,7 @@
         <v>101.034435</v>
       </c>
       <c r="M330" s="6" t="n">
-        <v>99.669005</v>
+        <v>99.668324</v>
       </c>
       <c r="N330" s="6" t="n">
         <v>100.641401</v>
@@ -27024,7 +27024,7 @@
         <v>101.138876</v>
       </c>
       <c r="M331" s="9" t="n">
-        <v>99.63724499999999</v>
+        <v>99.63651900000001</v>
       </c>
       <c r="N331" s="9" t="n">
         <v>100.676763</v>
@@ -27108,7 +27108,7 @@
         <v>101.239138</v>
       </c>
       <c r="M332" s="6" t="n">
-        <v>99.55037400000001</v>
+        <v>99.549475</v>
       </c>
       <c r="N332" s="6" t="n">
         <v>100.736925</v>
@@ -27192,7 +27192,7 @@
         <v>101.332629</v>
       </c>
       <c r="M333" s="9" t="n">
-        <v>99.398448</v>
+        <v>99.397222</v>
       </c>
       <c r="N333" s="9" t="n">
         <v>100.815004</v>
@@ -27276,7 +27276,7 @@
         <v>101.418797</v>
       </c>
       <c r="M334" s="6" t="n">
-        <v>99.219463</v>
+        <v>99.217837</v>
       </c>
       <c r="N334" s="6" t="n">
         <v>100.89617</v>
@@ -27360,7 +27360,7 @@
         <v>101.500618</v>
       </c>
       <c r="M335" s="9" t="n">
-        <v>99.048348</v>
+        <v>99.046323</v>
       </c>
       <c r="N335" s="9" t="n">
         <v>100.964716</v>
@@ -27444,7 +27444,7 @@
         <v>101.583306</v>
       </c>
       <c r="M336" s="6" t="n">
-        <v>98.916072</v>
+        <v>98.91372800000001</v>
       </c>
       <c r="N336" s="6" t="n">
         <v>101.016888</v>
@@ -27528,7 +27528,7 @@
         <v>101.666105</v>
       </c>
       <c r="M337" s="9" t="n">
-        <v>98.857578</v>
+        <v>98.85507800000001</v>
       </c>
       <c r="N337" s="9" t="n">
         <v>101.070787</v>
@@ -27612,7 +27612,7 @@
         <v>101.748682</v>
       </c>
       <c r="M338" s="6" t="n">
-        <v>98.85244</v>
+        <v>98.849913</v>
       </c>
       <c r="N338" s="6" t="n">
         <v>101.128422</v>
@@ -27696,7 +27696,7 @@
         <v>101.829521</v>
       </c>
       <c r="M339" s="9" t="n">
-        <v>98.852841</v>
+        <v>98.850313</v>
       </c>
       <c r="N339" s="9" t="n">
         <v>101.192718</v>
@@ -27780,7 +27780,7 @@
         <v>101.90382</v>
       </c>
       <c r="M340" s="6" t="n">
-        <v>98.833071</v>
+        <v>98.83051399999999</v>
       </c>
       <c r="N340" s="6" t="n">
         <v>101.277266</v>
@@ -27864,7 +27864,7 @@
         <v>101.964273</v>
       </c>
       <c r="M341" s="9" t="n">
-        <v>98.791768</v>
+        <v>98.789145</v>
       </c>
       <c r="N341" s="9" t="n">
         <v>101.389755</v>
@@ -27948,7 +27948,7 @@
         <v>102.011084</v>
       </c>
       <c r="M342" s="6" t="n">
-        <v>98.706869</v>
+        <v>98.704089</v>
       </c>
       <c r="N342" s="6" t="n">
         <v>101.525656</v>
@@ -28032,7 +28032,7 @@
         <v>102.043142</v>
       </c>
       <c r="M343" s="9" t="n">
-        <v>98.568127</v>
+        <v>98.56507000000001</v>
       </c>
       <c r="N343" s="9" t="n">
         <v>101.665921</v>
@@ -28116,7 +28116,7 @@
         <v>102.059054</v>
       </c>
       <c r="M344" s="6" t="n">
-        <v>98.404978</v>
+        <v>98.401582</v>
       </c>
       <c r="N344" s="6" t="n">
         <v>101.797632</v>
@@ -28200,7 +28200,7 @@
         <v>102.054679</v>
       </c>
       <c r="M345" s="9" t="n">
-        <v>98.260772</v>
+        <v>98.25706599999999</v>
       </c>
       <c r="N345" s="9" t="n">
         <v>101.907274</v>
@@ -28284,7 +28284,7 @@
         <v>102.023885</v>
       </c>
       <c r="M346" s="6" t="n">
-        <v>98.18028099999999</v>
+        <v>98.17639</v>
       </c>
       <c r="N346" s="6" t="n">
         <v>101.969871</v>
@@ -28368,7 +28368,7 @@
         <v>101.956562</v>
       </c>
       <c r="M347" s="9" t="n">
-        <v>98.200013</v>
+        <v>98.19614</v>
       </c>
       <c r="N347" s="9" t="n">
         <v>101.960967</v>
@@ -28452,7 +28452,7 @@
         <v>101.840977</v>
       </c>
       <c r="M348" s="6" t="n">
-        <v>98.329184</v>
+        <v>98.325563</v>
       </c>
       <c r="N348" s="6" t="n">
         <v>101.839141</v>
@@ -28536,7 +28536,7 @@
         <v>101.669757</v>
       </c>
       <c r="M349" s="9" t="n">
-        <v>98.54293</v>
+        <v>98.53974700000001</v>
       </c>
       <c r="N349" s="9" t="n">
         <v>101.544885</v>
@@ -28620,7 +28620,7 @@
         <v>101.439009</v>
       </c>
       <c r="M350" s="6" t="n">
-        <v>98.840017</v>
+        <v>98.837464</v>
       </c>
       <c r="N350" s="6" t="n">
         <v>101.053193</v>
@@ -28704,7 +28704,7 @@
         <v>101.14673</v>
       </c>
       <c r="M351" s="9" t="n">
-        <v>99.232366</v>
+        <v>99.230667</v>
       </c>
       <c r="N351" s="9" t="n">
         <v>100.380012</v>
@@ -28788,7 +28788,7 @@
         <v>100.797024</v>
       </c>
       <c r="M352" s="6" t="n">
-        <v>99.691626</v>
+        <v>99.690941</v>
       </c>
       <c r="N352" s="6" t="n">
         <v>99.566422</v>
@@ -28872,7 +28872,7 @@
         <v>100.403789</v>
       </c>
       <c r="M353" s="9" t="n">
-        <v>100.153025</v>
+        <v>100.153367</v>
       </c>
       <c r="N353" s="9" t="n">
         <v>98.69760599999999</v>
@@ -28956,7 +28956,7 @@
         <v>99.98400100000001</v>
       </c>
       <c r="M354" s="6" t="n">
-        <v>100.5842</v>
+        <v>100.585507</v>
       </c>
       <c r="N354" s="6" t="n">
         <v>97.910884</v>
@@ -29040,7 +29040,7 @@
         <v>99.56670800000001</v>
       </c>
       <c r="M355" s="9" t="n">
-        <v>100.985488</v>
+        <v>100.987692</v>
       </c>
       <c r="N355" s="9" t="n">
         <v>97.28248499999999</v>
@@ -29124,7 +29124,7 @@
         <v>99.17800800000001</v>
       </c>
       <c r="M356" s="6" t="n">
-        <v>101.346704</v>
+        <v>101.349711</v>
       </c>
       <c r="N356" s="6" t="n">
         <v>96.84311</v>
@@ -29208,7 +29208,7 @@
         <v>98.833833</v>
       </c>
       <c r="M357" s="9" t="n">
-        <v>101.650508</v>
+        <v>101.654181</v>
       </c>
       <c r="N357" s="9" t="n">
         <v>96.60618599999999</v>
@@ -29292,7 +29292,7 @@
         <v>98.54447</v>
       </c>
       <c r="M358" s="6" t="n">
-        <v>101.85753</v>
+        <v>101.861645</v>
       </c>
       <c r="N358" s="6" t="n">
         <v>96.56907099999999</v>
@@ -29376,7 +29376,7 @@
         <v>98.31887999999999</v>
       </c>
       <c r="M359" s="9" t="n">
-        <v>101.959495</v>
+        <v>101.96381</v>
       </c>
       <c r="N359" s="9" t="n">
         <v>96.708754</v>
@@ -29460,7 +29460,7 @@
         <v>98.158868</v>
       </c>
       <c r="M360" s="6" t="n">
-        <v>101.9983</v>
+        <v>102.002672</v>
       </c>
       <c r="N360" s="6" t="n">
         <v>96.965065</v>
@@ -29544,7 +29544,7 @@
         <v>98.061081</v>
       </c>
       <c r="M361" s="9" t="n">
-        <v>101.968383</v>
+        <v>101.972665</v>
       </c>
       <c r="N361" s="9" t="n">
         <v>97.290541</v>
@@ -29628,7 +29628,7 @@
         <v>98.01920800000001</v>
       </c>
       <c r="M362" s="6" t="n">
-        <v>101.860956</v>
+        <v>101.864989</v>
       </c>
       <c r="N362" s="6" t="n">
         <v>97.646339</v>
@@ -29712,7 +29712,7 @@
         <v>98.02971599999999</v>
       </c>
       <c r="M363" s="9" t="n">
-        <v>101.673898</v>
+        <v>101.677523</v>
       </c>
       <c r="N363" s="9" t="n">
         <v>98.003462</v>
@@ -29796,7 +29796,7 @@
         <v>98.089327</v>
       </c>
       <c r="M364" s="6" t="n">
-        <v>101.456985</v>
+        <v>101.46015</v>
       </c>
       <c r="N364" s="6" t="n">
         <v>98.34691100000001</v>
@@ -29880,7 +29880,7 @@
         <v>98.18641700000001</v>
       </c>
       <c r="M365" s="9" t="n">
-        <v>101.270902</v>
+        <v>101.273682</v>
       </c>
       <c r="N365" s="9" t="n">
         <v>98.64769099999999</v>
@@ -29964,7 +29964,7 @@
         <v>98.306924</v>
       </c>
       <c r="M366" s="6" t="n">
-        <v>101.128262</v>
+        <v>101.130752</v>
       </c>
       <c r="N366" s="6" t="n">
         <v>98.907893</v>
@@ -30048,7 +30048,7 @@
         <v>98.43932100000001</v>
       </c>
       <c r="M367" s="9" t="n">
-        <v>100.995534</v>
+        <v>100.997754</v>
       </c>
       <c r="N367" s="9" t="n">
         <v>99.136805</v>
@@ -30132,7 +30132,7 @@
         <v>98.572681</v>
       </c>
       <c r="M368" s="6" t="n">
-        <v>100.889986</v>
+        <v>100.891988</v>
       </c>
       <c r="N368" s="6" t="n">
         <v>99.32791899999999</v>
@@ -30216,7 +30216,7 @@
         <v>98.69810200000001</v>
       </c>
       <c r="M369" s="9" t="n">
-        <v>100.804366</v>
+        <v>100.806185</v>
       </c>
       <c r="N369" s="9" t="n">
         <v>99.465743</v>
@@ -30300,7 +30300,7 @@
         <v>98.81057300000001</v>
       </c>
       <c r="M370" s="6" t="n">
-        <v>100.719171</v>
+        <v>100.720796</v>
       </c>
       <c r="N370" s="6" t="n">
         <v>99.548821</v>
@@ -30384,7 +30384,7 @@
         <v>98.90791400000001</v>
       </c>
       <c r="M371" s="9" t="n">
-        <v>100.635618</v>
+        <v>100.637042</v>
       </c>
       <c r="N371" s="9" t="n">
         <v>99.597269</v>
@@ -30468,7 +30468,7 @@
         <v>98.99310699999999</v>
       </c>
       <c r="M372" s="6" t="n">
-        <v>100.545647</v>
+        <v>100.546853</v>
       </c>
       <c r="N372" s="6" t="n">
         <v>99.649444</v>
@@ -30552,7 +30552,7 @@
         <v>99.069782</v>
       </c>
       <c r="M373" s="9" t="n">
-        <v>100.476005</v>
+        <v>100.477041</v>
       </c>
       <c r="N373" s="9" t="n">
         <v>99.724316</v>
@@ -30636,7 +30636,7 @@
         <v>99.14059399999999</v>
       </c>
       <c r="M374" s="6" t="n">
-        <v>100.46045</v>
+        <v>100.461442</v>
       </c>
       <c r="N374" s="6" t="n">
         <v>99.822829</v>
@@ -30720,7 +30720,7 @@
         <v>99.20860999999999</v>
       </c>
       <c r="M375" s="9" t="n">
-        <v>100.456118</v>
+        <v>100.457102</v>
       </c>
       <c r="N375" s="9" t="n">
         <v>99.94723500000001</v>
@@ -30804,7 +30804,7 @@
         <v>99.27298500000001</v>
       </c>
       <c r="M376" s="6" t="n">
-        <v>100.426559</v>
+        <v>100.427488</v>
       </c>
       <c r="N376" s="6" t="n">
         <v>100.082606</v>
@@ -30888,7 +30888,7 @@
         <v>99.332167</v>
       </c>
       <c r="M377" s="9" t="n">
-        <v>100.351096</v>
+        <v>100.351876</v>
       </c>
       <c r="N377" s="9" t="n">
         <v>100.219442</v>
@@ -30972,7 +30972,7 @@
         <v>99.384793</v>
       </c>
       <c r="M378" s="6" t="n">
-        <v>100.21429</v>
+        <v>100.214787</v>
       </c>
       <c r="N378" s="6" t="n">
         <v>100.347233</v>
@@ -31056,7 +31056,7 @@
         <v>99.430361</v>
       </c>
       <c r="M379" s="9" t="n">
-        <v>100.069054</v>
+        <v>100.069248</v>
       </c>
       <c r="N379" s="9" t="n">
         <v>100.459197</v>
@@ -31140,7 +31140,7 @@
         <v>99.46854500000001</v>
       </c>
       <c r="M380" s="6" t="n">
-        <v>99.95332000000001</v>
+        <v>99.95326799999999</v>
       </c>
       <c r="N380" s="6" t="n">
         <v>100.554858</v>
@@ -31224,7 +31224,7 @@
         <v>99.497806</v>
       </c>
       <c r="M381" s="9" t="n">
-        <v>99.893202</v>
+        <v>99.893018</v>
       </c>
       <c r="N381" s="9" t="n">
         <v>100.639007</v>
@@ -31308,7 +31308,7 @@
         <v>99.51745099999999</v>
       </c>
       <c r="M382" s="6" t="n">
-        <v>99.905421</v>
+        <v>99.90525599999999</v>
       </c>
       <c r="N382" s="6" t="n">
         <v>100.713288</v>
@@ -31392,7 +31392,7 @@
         <v>99.532777</v>
       </c>
       <c r="M383" s="9" t="n">
-        <v>99.92591899999999</v>
+        <v>99.92578399999999</v>
       </c>
       <c r="N383" s="9" t="n">
         <v>100.760865</v>
@@ -31476,7 +31476,7 @@
         <v>99.54910700000001</v>
       </c>
       <c r="M384" s="6" t="n">
-        <v>99.916524</v>
+        <v>99.916354</v>
       </c>
       <c r="N384" s="6" t="n">
         <v>100.770945</v>
@@ -31560,7 +31560,7 @@
         <v>99.570215</v>
       </c>
       <c r="M385" s="9" t="n">
-        <v>99.872393</v>
+        <v>99.87211600000001</v>
       </c>
       <c r="N385" s="9" t="n">
         <v>100.754741</v>
@@ -31644,7 +31644,7 @@
         <v>99.599389</v>
       </c>
       <c r="M386" s="6" t="n">
-        <v>99.810945</v>
+        <v>99.81053199999999</v>
       </c>
       <c r="N386" s="6" t="n">
         <v>100.73223</v>
@@ -31728,7 +31728,7 @@
         <v>99.63746500000001</v>
       </c>
       <c r="M387" s="9" t="n">
-        <v>99.75227099999999</v>
+        <v>99.751735</v>
       </c>
       <c r="N387" s="9" t="n">
         <v>100.708188</v>
@@ -31812,7 +31812,7 @@
         <v>99.684757</v>
       </c>
       <c r="M388" s="6" t="n">
-        <v>99.711022</v>
+        <v>99.71040600000001</v>
       </c>
       <c r="N388" s="6" t="n">
         <v>100.6967</v>
@@ -31896,7 +31896,7 @@
         <v>99.74150899999999</v>
       </c>
       <c r="M389" s="9" t="n">
-        <v>99.692168</v>
+        <v>99.69152200000001</v>
       </c>
       <c r="N389" s="9" t="n">
         <v>100.696862</v>
@@ -31980,7 +31980,7 @@
         <v>99.80497800000001</v>
       </c>
       <c r="M390" s="6" t="n">
-        <v>99.712537</v>
+        <v>99.71194199999999</v>
       </c>
       <c r="N390" s="6" t="n">
         <v>100.698227</v>
@@ -32064,7 +32064,7 @@
         <v>99.86977</v>
       </c>
       <c r="M391" s="9" t="n">
-        <v>99.75474699999999</v>
+        <v>99.754248</v>
       </c>
       <c r="N391" s="9" t="n">
         <v>100.68824</v>
@@ -32148,7 +32148,7 @@
         <v>99.93106400000001</v>
       </c>
       <c r="M392" s="6" t="n">
-        <v>99.76623600000001</v>
+        <v>99.765761</v>
       </c>
       <c r="N392" s="6" t="n">
         <v>100.655404</v>
@@ -32232,7 +32232,7 @@
         <v>99.98683</v>
       </c>
       <c r="M393" s="9" t="n">
-        <v>99.750426</v>
+        <v>99.749911</v>
       </c>
       <c r="N393" s="9" t="n">
         <v>100.606927</v>
@@ -32316,7 +32316,7 @@
         <v>100.041283</v>
       </c>
       <c r="M394" s="6" t="n">
-        <v>99.721917</v>
+        <v>99.72132999999999</v>
       </c>
       <c r="N394" s="6" t="n">
         <v>100.538502</v>
@@ -32400,7 +32400,7 @@
         <v>100.096492</v>
       </c>
       <c r="M395" s="9" t="n">
-        <v>99.684596</v>
+        <v>99.68391699999999</v>
       </c>
       <c r="N395" s="9" t="n">
         <v>100.465662</v>
@@ -32484,7 +32484,7 @@
         <v>100.149178</v>
       </c>
       <c r="M396" s="6" t="n">
-        <v>99.674216</v>
+        <v>99.673507</v>
       </c>
       <c r="N396" s="6" t="n">
         <v>100.416724</v>
@@ -32568,7 +32568,7 @@
         <v>100.196955</v>
       </c>
       <c r="M397" s="9" t="n">
-        <v>99.710047</v>
+        <v>99.70941500000001</v>
       </c>
       <c r="N397" s="9" t="n">
         <v>100.398944</v>
@@ -32652,7 +32652,7 @@
         <v>100.238385</v>
       </c>
       <c r="M398" s="6" t="n">
-        <v>99.785157</v>
+        <v>99.784696</v>
       </c>
       <c r="N398" s="6" t="n">
         <v>100.415212</v>
@@ -32736,7 +32736,7 @@
         <v>100.271204</v>
       </c>
       <c r="M399" s="9" t="n">
-        <v>99.908596</v>
+        <v>99.908417</v>
       </c>
       <c r="N399" s="9" t="n">
         <v>100.450686</v>
@@ -32820,7 +32820,7 @@
         <v>100.295719</v>
       </c>
       <c r="M400" s="6" t="n">
-        <v>100.052666</v>
+        <v>100.052815</v>
       </c>
       <c r="N400" s="6" t="n">
         <v>100.480564</v>
@@ -32904,7 +32904,7 @@
         <v>100.311138</v>
       </c>
       <c r="M401" s="9" t="n">
-        <v>100.174522</v>
+        <v>100.174945</v>
       </c>
       <c r="N401" s="9" t="n">
         <v>100.503075</v>
@@ -32988,7 +32988,7 @@
         <v>100.314671</v>
       </c>
       <c r="M402" s="6" t="n">
-        <v>100.247749</v>
+        <v>100.248327</v>
       </c>
       <c r="N402" s="6" t="n">
         <v>100.520293</v>
@@ -33072,7 +33072,7 @@
         <v>100.304761</v>
       </c>
       <c r="M403" s="9" t="n">
-        <v>100.261196</v>
+        <v>100.261794</v>
       </c>
       <c r="N403" s="9" t="n">
         <v>100.519411</v>
@@ -33156,7 +33156,7 @@
         <v>100.281423</v>
       </c>
       <c r="M404" s="6" t="n">
-        <v>100.239181</v>
+        <v>100.239719</v>
       </c>
       <c r="N404" s="6" t="n">
         <v>100.493714</v>
@@ -33240,7 +33240,7 @@
         <v>100.246501</v>
       </c>
       <c r="M405" s="9" t="n">
-        <v>100.182651</v>
+        <v>100.183052</v>
       </c>
       <c r="N405" s="9" t="n">
         <v>100.442384</v>
@@ -33324,7 +33324,7 @@
         <v>100.20246</v>
       </c>
       <c r="M406" s="6" t="n">
-        <v>100.081421</v>
+        <v>100.08159</v>
       </c>
       <c r="N406" s="6" t="n">
         <v>100.371756</v>
@@ -33408,7 +33408,7 @@
         <v>100.151369</v>
       </c>
       <c r="M407" s="9" t="n">
-        <v>99.988446</v>
+        <v>99.988404</v>
       </c>
       <c r="N407" s="9" t="n">
         <v>100.295858</v>
@@ -33492,7 +33492,7 @@
         <v>100.095988</v>
       </c>
       <c r="M408" s="6" t="n">
-        <v>99.914834</v>
+        <v>99.914632</v>
       </c>
       <c r="N408" s="6" t="n">
         <v>100.217923</v>
@@ -33576,7 +33576,7 @@
         <v>100.039442</v>
       </c>
       <c r="M409" s="9" t="n">
-        <v>99.882953</v>
+        <v>99.88269200000001</v>
       </c>
       <c r="N409" s="9" t="n">
         <v>100.139757</v>
@@ -33660,7 +33660,7 @@
         <v>99.98276</v>
       </c>
       <c r="M410" s="6" t="n">
-        <v>99.909919</v>
+        <v>99.909736</v>
       </c>
       <c r="N410" s="6" t="n">
         <v>100.073031</v>
@@ -33744,7 +33744,7 @@
         <v>99.927986</v>
       </c>
       <c r="M411" s="9" t="n">
-        <v>99.996758</v>
+        <v>99.996787</v>
       </c>
       <c r="N411" s="9" t="n">
         <v>100.030443</v>
@@ -33828,7 +33828,7 @@
         <v>99.87616</v>
       </c>
       <c r="M412" s="6" t="n">
-        <v>100.162724</v>
+        <v>100.163136</v>
       </c>
       <c r="N412" s="6" t="n">
         <v>100.020267</v>
@@ -33912,7 +33912,7 @@
         <v>99.828113</v>
       </c>
       <c r="M413" s="9" t="n">
-        <v>100.414378</v>
+        <v>100.415345</v>
       </c>
       <c r="N413" s="9" t="n">
         <v>100.05256</v>
@@ -33996,7 +33996,7 @@
         <v>99.78765199999999</v>
       </c>
       <c r="M414" s="6" t="n">
-        <v>100.674138</v>
+        <v>100.675654</v>
       </c>
       <c r="N414" s="6" t="n">
         <v>100.124124</v>
@@ -34080,7 +34080,7 @@
         <v>99.760356</v>
       </c>
       <c r="M415" s="9" t="n">
-        <v>100.881865</v>
+        <v>100.883808</v>
       </c>
       <c r="N415" s="9" t="n">
         <v>100.217252</v>
@@ -34164,7 +34164,7 @@
         <v>99.74726800000001</v>
       </c>
       <c r="M416" s="6" t="n">
-        <v>101.045797</v>
+        <v>101.04807</v>
       </c>
       <c r="N416" s="6" t="n">
         <v>100.31086</v>
@@ -34248,7 +34248,7 @@
         <v>99.74509500000001</v>
       </c>
       <c r="M417" s="9" t="n">
-        <v>101.14644</v>
+        <v>101.14891</v>
       </c>
       <c r="N417" s="9" t="n">
         <v>100.39033</v>
@@ -34332,7 +34332,7 @@
         <v>99.746015</v>
       </c>
       <c r="M418" s="6" t="n">
-        <v>101.176454</v>
+        <v>101.178974</v>
       </c>
       <c r="N418" s="6" t="n">
         <v>100.445697</v>
@@ -34416,7 +34416,7 @@
         <v>99.744907</v>
       </c>
       <c r="M419" s="9" t="n">
-        <v>101.161277</v>
+        <v>101.16376</v>
       </c>
       <c r="N419" s="9" t="n">
         <v>100.472978</v>
@@ -34500,7 +34500,7 @@
         <v>99.74141400000001</v>
       </c>
       <c r="M420" s="6" t="n">
-        <v>101.088385</v>
+        <v>101.090719</v>
       </c>
       <c r="N420" s="6" t="n">
         <v>100.475552</v>
@@ -34584,7 +34584,7 @@
         <v>99.737787</v>
       </c>
       <c r="M421" s="9" t="n">
-        <v>100.928963</v>
+        <v>100.930977</v>
       </c>
       <c r="N421" s="9" t="n">
         <v>100.460325</v>
@@ -34668,7 +34668,7 @@
         <v>99.737934</v>
       </c>
       <c r="M422" s="6" t="n">
-        <v>100.718963</v>
+        <v>100.720557</v>
       </c>
       <c r="N422" s="6" t="n">
         <v>100.419732</v>
@@ -34752,7 +34752,7 @@
         <v>99.745088</v>
       </c>
       <c r="M423" s="9" t="n">
-        <v>100.49357</v>
+        <v>100.494712</v>
       </c>
       <c r="N423" s="9" t="n">
         <v>100.369473</v>
@@ -34836,7 +34836,7 @@
         <v>99.75875600000001</v>
       </c>
       <c r="M424" s="6" t="n">
-        <v>100.273752</v>
+        <v>100.274444</v>
       </c>
       <c r="N424" s="6" t="n">
         <v>100.311294</v>
@@ -34920,7 +34920,7 @@
         <v>99.777052</v>
       </c>
       <c r="M425" s="9" t="n">
-        <v>100.106041</v>
+        <v>100.10637</v>
       </c>
       <c r="N425" s="9" t="n">
         <v>100.233727</v>
@@ -35004,7 +35004,7 @@
         <v>99.797504</v>
       </c>
       <c r="M426" s="6" t="n">
-        <v>100.020804</v>
+        <v>100.020909</v>
       </c>
       <c r="N426" s="6" t="n">
         <v>100.155964</v>
@@ -35088,7 +35088,7 @@
         <v>99.817672</v>
       </c>
       <c r="M427" s="9" t="n">
-        <v>99.99379399999999</v>
+        <v>99.993785</v>
       </c>
       <c r="N427" s="9" t="n">
         <v>100.100529</v>
@@ -35172,7 +35172,7 @@
         <v>99.83668</v>
       </c>
       <c r="M428" s="6" t="n">
-        <v>99.99829099999999</v>
+        <v>99.998238</v>
       </c>
       <c r="N428" s="6" t="n">
         <v>100.076986</v>
@@ -35256,7 +35256,7 @@
         <v>99.853525</v>
       </c>
       <c r="M429" s="9" t="n">
-        <v>100.03499</v>
+        <v>100.034975</v>
       </c>
       <c r="N429" s="9" t="n">
         <v>100.073032</v>
@@ -35340,7 +35340,7 @@
         <v>99.87008899999999</v>
       </c>
       <c r="M430" s="6" t="n">
-        <v>100.089292</v>
+        <v>100.089377</v>
       </c>
       <c r="N430" s="6" t="n">
         <v>100.078958</v>
@@ -35424,7 +35424,7 @@
         <v>99.88762699999999</v>
       </c>
       <c r="M431" s="9" t="n">
-        <v>100.131823</v>
+        <v>100.132016</v>
       </c>
       <c r="N431" s="9" t="n">
         <v>100.079687</v>
@@ -35508,7 +35508,7 @@
         <v>99.905023</v>
       </c>
       <c r="M432" s="6" t="n">
-        <v>100.163105</v>
+        <v>100.163409</v>
       </c>
       <c r="N432" s="6" t="n">
         <v>100.052593</v>
@@ -35592,7 +35592,7 @@
         <v>99.919095</v>
       </c>
       <c r="M433" s="9" t="n">
-        <v>100.177776</v>
+        <v>100.178177</v>
       </c>
       <c r="N433" s="9" t="n">
         <v>99.991704</v>
@@ -35676,7 +35676,7 @@
         <v>99.926748</v>
       </c>
       <c r="M434" s="6" t="n">
-        <v>100.180258</v>
+        <v>100.180738</v>
       </c>
       <c r="N434" s="6" t="n">
         <v>99.890794</v>
@@ -35760,7 +35760,7 @@
         <v>99.928811</v>
       </c>
       <c r="M435" s="9" t="n">
-        <v>100.163184</v>
+        <v>100.163692</v>
       </c>
       <c r="N435" s="9" t="n">
         <v>99.76481699999999</v>
@@ -35844,7 +35844,7 @@
         <v>99.926316</v>
       </c>
       <c r="M436" s="6" t="n">
-        <v>100.128891</v>
+        <v>100.129359</v>
       </c>
       <c r="N436" s="6" t="n">
         <v>99.624442</v>
@@ -35928,7 +35928,7 @@
         <v>99.92084</v>
       </c>
       <c r="M437" s="9" t="n">
-        <v>100.113289</v>
+        <v>100.113704</v>
       </c>
       <c r="N437" s="9" t="n">
         <v>99.486216</v>
@@ -36012,7 +36012,7 @@
         <v>99.91552799999999</v>
       </c>
       <c r="M438" s="6" t="n">
-        <v>100.060113</v>
+        <v>100.06032</v>
       </c>
       <c r="N438" s="6" t="n">
         <v>99.372911</v>
@@ -36096,7 +36096,7 @@
         <v>99.912856</v>
       </c>
       <c r="M439" s="9" t="n">
-        <v>99.99088399999999</v>
+        <v>99.990819</v>
       </c>
       <c r="N439" s="9" t="n">
         <v>99.28915499999999</v>
@@ -36180,7 +36180,7 @@
         <v>99.91734099999999</v>
       </c>
       <c r="M440" s="6" t="n">
-        <v>99.91515800000001</v>
+        <v>99.914817</v>
       </c>
       <c r="N440" s="6" t="n">
         <v>99.23840300000001</v>
@@ -36264,7 +36264,7 @@
         <v>99.934405</v>
       </c>
       <c r="M441" s="9" t="n">
-        <v>99.84824</v>
+        <v>99.84768099999999</v>
       </c>
       <c r="N441" s="9" t="n">
         <v>99.222514</v>
@@ -36348,7 +36348,7 @@
         <v>99.963785</v>
       </c>
       <c r="M442" s="6" t="n">
-        <v>99.80558499999999</v>
+        <v>99.804922</v>
       </c>
       <c r="N442" s="6" t="n">
         <v>99.230887</v>
@@ -36432,7 +36432,7 @@
         <v>100.002612</v>
       </c>
       <c r="M443" s="9" t="n">
-        <v>99.762361</v>
+        <v>99.761669</v>
       </c>
       <c r="N443" s="9" t="n">
         <v>99.26398399999999</v>
@@ -36516,7 +36516,7 @@
         <v>100.046572</v>
       </c>
       <c r="M444" s="6" t="n">
-        <v>99.724878</v>
+        <v>99.724226</v>
       </c>
       <c r="N444" s="6" t="n">
         <v>99.316062</v>
@@ -36600,7 +36600,7 @@
         <v>100.093063</v>
       </c>
       <c r="M445" s="9" t="n">
-        <v>99.692948</v>
+        <v>99.692379</v>
       </c>
       <c r="N445" s="9" t="n">
         <v>99.37822799999999</v>
@@ -36684,7 +36684,7 @@
         <v>100.13986</v>
       </c>
       <c r="M446" s="6" t="n">
-        <v>99.63210599999999</v>
+        <v>99.631556</v>
       </c>
       <c r="N446" s="6" t="n">
         <v>99.447562</v>
@@ -36768,7 +36768,7 @@
         <v>100.183591</v>
       </c>
       <c r="M447" s="9" t="n">
-        <v>99.49036599999999</v>
+        <v>99.48962</v>
       </c>
       <c r="N447" s="9" t="n">
         <v>99.514724</v>
@@ -36852,7 +36852,7 @@
         <v>100.222783</v>
       </c>
       <c r="M448" s="6" t="n">
-        <v>99.30413299999999</v>
+        <v>99.30301799999999</v>
       </c>
       <c r="N448" s="6" t="n">
         <v>99.58468499999999</v>
@@ -36936,7 +36936,7 @@
         <v>100.258677</v>
       </c>
       <c r="M449" s="9" t="n">
-        <v>99.085402</v>
+        <v>99.083732</v>
       </c>
       <c r="N449" s="9" t="n">
         <v>99.64937399999999</v>
@@ -37020,7 +37020,7 @@
         <v>100.293792</v>
       </c>
       <c r="M450" s="6" t="n">
-        <v>98.852627</v>
+        <v>98.850228</v>
       </c>
       <c r="N450" s="6" t="n">
         <v>99.702195</v>
@@ -37104,7 +37104,7 @@
         <v>100.332558</v>
       </c>
       <c r="M451" s="9" t="n">
-        <v>98.66904700000001</v>
+        <v>98.665977</v>
       </c>
       <c r="N451" s="9" t="n">
         <v>99.746343</v>
@@ -37188,7 +37188,7 @@
         <v>100.378673</v>
       </c>
       <c r="M452" s="6" t="n">
-        <v>98.580573</v>
+        <v>98.577077</v>
       </c>
       <c r="N452" s="6" t="n">
         <v>99.788827</v>
@@ -37272,7 +37272,7 @@
         <v>100.429921</v>
       </c>
       <c r="M453" s="9" t="n">
-        <v>98.55077</v>
+        <v>98.547087</v>
       </c>
       <c r="N453" s="9" t="n">
         <v>99.838741</v>
@@ -37356,7 +37356,7 @@
         <v>100.483996</v>
       </c>
       <c r="M454" s="6" t="n">
-        <v>98.556009</v>
+        <v>98.552368</v>
       </c>
       <c r="N454" s="6" t="n">
         <v>99.906627</v>
@@ -37440,7 +37440,7 @@
         <v>100.540134</v>
       </c>
       <c r="M455" s="9" t="n">
-        <v>98.599481</v>
+        <v>98.59612799999999</v>
       </c>
       <c r="N455" s="9" t="n">
         <v>99.984734</v>
@@ -37524,7 +37524,7 @@
         <v>100.593187</v>
       </c>
       <c r="M456" s="6" t="n">
-        <v>98.679941</v>
+        <v>98.677052</v>
       </c>
       <c r="N456" s="6" t="n">
         <v>100.070797</v>
@@ -37608,7 +37608,7 @@
         <v>100.639926</v>
       </c>
       <c r="M457" s="9" t="n">
-        <v>98.772239</v>
+        <v>98.769868</v>
       </c>
       <c r="N457" s="9" t="n">
         <v>100.1669</v>
@@ -37692,7 +37692,7 @@
         <v>100.680515</v>
       </c>
       <c r="M458" s="6" t="n">
-        <v>98.84582399999999</v>
+        <v>98.843898</v>
       </c>
       <c r="N458" s="6" t="n">
         <v>100.263306</v>
@@ -37776,7 +37776,7 @@
         <v>100.717894</v>
       </c>
       <c r="M459" s="9" t="n">
-        <v>98.872964</v>
+        <v>98.871287</v>
       </c>
       <c r="N459" s="9" t="n">
         <v>100.362087</v>
@@ -37860,7 +37860,7 @@
         <v>100.756268</v>
       </c>
       <c r="M460" s="6" t="n">
-        <v>98.86121300000001</v>
+        <v>98.85954099999999</v>
       </c>
       <c r="N460" s="6" t="n">
         <v>100.45936</v>
@@ -37944,7 +37944,7 @@
         <v>100.799292</v>
       </c>
       <c r="M461" s="9" t="n">
-        <v>98.833736</v>
+        <v>98.831816</v>
       </c>
       <c r="N461" s="9" t="n">
         <v>100.557882</v>
@@ -38028,7 +38028,7 @@
         <v>100.848305</v>
       </c>
       <c r="M462" s="6" t="n">
-        <v>98.811998</v>
+        <v>98.809579</v>
       </c>
       <c r="N462" s="6" t="n">
         <v>100.645344</v>
@@ -38112,7 +38112,7 @@
         <v>100.903266</v>
       </c>
       <c r="M463" s="9" t="n">
-        <v>98.79289799999999</v>
+        <v>98.78988</v>
       </c>
       <c r="N463" s="9" t="n">
         <v>100.731875</v>
@@ -38196,7 +38196,7 @@
         <v>100.960851</v>
       </c>
       <c r="M464" s="6" t="n">
-        <v>98.77428500000001</v>
+        <v>98.770734</v>
       </c>
       <c r="N464" s="6" t="n">
         <v>100.81209</v>
@@ -38280,7 +38280,7 @@
         <v>101.017018</v>
       </c>
       <c r="M465" s="9" t="n">
-        <v>98.74603999999999</v>
+        <v>98.742182</v>
       </c>
       <c r="N465" s="9" t="n">
         <v>100.879351</v>
@@ -38364,7 +38364,7 @@
         <v>101.068626</v>
       </c>
       <c r="M466" s="6" t="n">
-        <v>98.69668799999999</v>
+        <v>98.69288899999999</v>
       </c>
       <c r="N466" s="6" t="n">
         <v>100.94377</v>
@@ -38448,7 +38448,7 @@
         <v>101.113769</v>
       </c>
       <c r="M467" s="9" t="n">
-        <v>98.661429</v>
+        <v>98.65801999999999</v>
       </c>
       <c r="N467" s="9" t="n">
         <v>100.997708</v>
@@ -38532,7 +38532,7 @@
         <v>101.152758</v>
       </c>
       <c r="M468" s="6" t="n">
-        <v>98.62925300000001</v>
+        <v>98.626366</v>
       </c>
       <c r="N468" s="6" t="n">
         <v>101.031795</v>
@@ -38616,7 +38616,7 @@
         <v>101.183695</v>
       </c>
       <c r="M469" s="9" t="n">
-        <v>98.61937</v>
+        <v>98.617047</v>
       </c>
       <c r="N469" s="9" t="n">
         <v>101.041847</v>
@@ -38700,7 +38700,7 @@
         <v>101.203493</v>
       </c>
       <c r="M470" s="6" t="n">
-        <v>98.632058</v>
+        <v>98.63023800000001</v>
       </c>
       <c r="N470" s="6" t="n">
         <v>101.026968</v>
@@ -38784,7 +38784,7 @@
         <v>101.210982</v>
       </c>
       <c r="M471" s="9" t="n">
-        <v>98.70413000000001</v>
+        <v>98.702747</v>
       </c>
       <c r="N471" s="9" t="n">
         <v>100.981825</v>
@@ -38868,7 +38868,7 @@
         <v>101.20839</v>
       </c>
       <c r="M472" s="6" t="n">
-        <v>98.84439999999999</v>
+        <v>98.84331899999999</v>
       </c>
       <c r="N472" s="6" t="n">
         <v>100.904117</v>
@@ -38952,7 +38952,7 @@
         <v>101.200657</v>
       </c>
       <c r="M473" s="9" t="n">
-        <v>99.00823099999999</v>
+        <v>99.007141</v>
       </c>
       <c r="N473" s="9" t="n">
         <v>100.805549</v>
@@ -39036,7 +39036,7 @@
         <v>101.194131</v>
       </c>
       <c r="M474" s="6" t="n">
-        <v>99.119664</v>
+        <v>99.11803500000001</v>
       </c>
       <c r="N474" s="6" t="n">
         <v>100.712834</v>
@@ -39120,7 +39120,7 @@
         <v>101.19272</v>
       </c>
       <c r="M475" s="9" t="n">
-        <v>99.1977</v>
+        <v>99.19526399999999</v>
       </c>
       <c r="N475" s="9" t="n">
         <v>100.629907</v>
@@ -39204,7 +39204,7 @@
         <v>101.198031</v>
       </c>
       <c r="M476" s="6" t="n">
-        <v>99.243132</v>
+        <v>99.239897</v>
       </c>
       <c r="N476" s="6" t="n">
         <v>100.559192</v>
@@ -39288,7 +39288,7 @@
         <v>101.209262</v>
       </c>
       <c r="M477" s="9" t="n">
-        <v>99.259235</v>
+        <v>99.25556899999999</v>
       </c>
       <c r="N477" s="9" t="n">
         <v>100.49821</v>
@@ -39372,7 +39372,7 @@
         <v>101.222569</v>
       </c>
       <c r="M478" s="6" t="n">
-        <v>99.265045</v>
+        <v>99.261787</v>
       </c>
       <c r="N478" s="6" t="n">
         <v>100.438772</v>
@@ -39456,7 +39456,7 @@
         <v>101.233733</v>
       </c>
       <c r="M479" s="9" t="n">
-        <v>99.245042</v>
+        <v>99.242632</v>
       </c>
       <c r="N479" s="9" t="n">
         <v>100.379011</v>
@@ -39540,7 +39540,7 @@
         <v>101.237004</v>
       </c>
       <c r="M480" s="6" t="n">
-        <v>99.214519</v>
+        <v>99.21308999999999</v>
       </c>
       <c r="N480" s="6" t="n">
         <v>100.317631</v>
@@ -39624,7 +39624,7 @@
         <v>101.22696</v>
       </c>
       <c r="M481" s="9" t="n">
-        <v>99.189567</v>
+        <v>99.189075</v>
       </c>
       <c r="N481" s="9" t="n">
         <v>100.239692</v>
@@ -39708,7 +39708,7 @@
         <v>101.196122</v>
       </c>
       <c r="M482" s="6" t="n">
-        <v>99.19387500000001</v>
+        <v>99.194183</v>
       </c>
       <c r="N482" s="6" t="n">
         <v>100.136536</v>
@@ -39792,7 +39792,7 @@
         <v>101.130806</v>
       </c>
       <c r="M483" s="9" t="n">
-        <v>99.23739500000001</v>
+        <v>99.23823299999999</v>
       </c>
       <c r="N483" s="9" t="n">
         <v>100.000387</v>
@@ -39876,7 +39876,7 @@
         <v>101.012468</v>
       </c>
       <c r="M484" s="6" t="n">
-        <v>99.32328</v>
+        <v>99.324172</v>
       </c>
       <c r="N484" s="6" t="n">
         <v>99.816075</v>
@@ -39960,7 +39960,7 @@
         <v>100.819419</v>
       </c>
       <c r="M485" s="9" t="n">
-        <v>99.481589</v>
+        <v>99.48212100000001</v>
       </c>
       <c r="N485" s="9" t="n">
         <v>99.565625</v>
@@ -40044,7 +40044,7 @@
         <v>100.531006</v>
       </c>
       <c r="M486" s="6" t="n">
-        <v>99.77721</v>
+        <v>99.777096</v>
       </c>
       <c r="N486" s="6" t="n">
         <v>99.22620499999999</v>
@@ -40128,7 +40128,7 @@
         <v>100.137542</v>
       </c>
       <c r="M487" s="9" t="n">
-        <v>100.21106</v>
+        <v>100.2103</v>
       </c>
       <c r="N487" s="9" t="n">
         <v>98.779974</v>
@@ -40212,7 +40212,7 @@
         <v>99.658266</v>
       </c>
       <c r="M488" s="6" t="n">
-        <v>100.763144</v>
+        <v>100.762096</v>
       </c>
       <c r="N488" s="6" t="n">
         <v>98.24610699999999</v>
@@ -40296,7 +40296,7 @@
         <v>99.136893</v>
       </c>
       <c r="M489" s="9" t="n">
-        <v>101.437215</v>
+        <v>101.436864</v>
       </c>
       <c r="N489" s="9" t="n">
         <v>95.544766</v>
@@ -40380,7 +40380,7 @@
         <v>98.631197</v>
       </c>
       <c r="M490" s="6" t="n">
-        <v>102.116821</v>
+        <v>102.118757</v>
       </c>
       <c r="N490" s="6" t="n">
         <v>93.05402599999999</v>
@@ -40464,7 +40464,7 @@
         <v>98.202202</v>
       </c>
       <c r="M491" s="9" t="n">
-        <v>102.708314</v>
+        <v>102.713129</v>
       </c>
       <c r="N491" s="9" t="n">
         <v>95.727931</v>
@@ -40548,7 +40548,7 @@
         <v>97.880655</v>
       </c>
       <c r="M492" s="6" t="n">
-        <v>103.114588</v>
+        <v>103.122046</v>
       </c>
       <c r="N492" s="6" t="n">
         <v>96.061317</v>
@@ -40632,7 +40632,7 @@
         <v>97.664091</v>
       </c>
       <c r="M493" s="9" t="n">
-        <v>103.325394</v>
+        <v>103.334912</v>
       </c>
       <c r="N493" s="9" t="n">
         <v>97.099683</v>
@@ -40716,7 +40716,7 @@
         <v>97.53728</v>
       </c>
       <c r="M494" s="6" t="n">
-        <v>103.3754</v>
+        <v>103.386234</v>
       </c>
       <c r="N494" s="6" t="n">
         <v>97.44334499999999</v>
@@ -40800,7 +40800,7 @@
         <v>97.483351</v>
       </c>
       <c r="M495" s="9" t="n">
-        <v>103.316735</v>
+        <v>103.327991</v>
       </c>
       <c r="N495" s="9" t="n">
         <v>97.834868</v>
@@ -40884,7 +40884,7 @@
         <v>97.483677</v>
       </c>
       <c r="M496" s="6" t="n">
-        <v>103.208421</v>
+        <v>103.218996</v>
       </c>
       <c r="N496" s="6" t="n">
         <v>98.223889</v>
@@ -40968,7 +40968,7 @@
         <v>97.52389599999999</v>
       </c>
       <c r="M497" s="9" t="n">
-        <v>103.095652</v>
+        <v>103.104657</v>
       </c>
       <c r="N497" s="9" t="n">
         <v>98.561145</v>
@@ -41052,7 +41052,7 @@
         <v>97.59943199999999</v>
       </c>
       <c r="M498" s="6" t="n">
-        <v>103.012859</v>
+        <v>103.019589</v>
       </c>
       <c r="N498" s="6" t="n">
         <v>98.834394</v>
@@ -41136,7 +41136,7 @@
         <v>97.720494</v>
       </c>
       <c r="M499" s="9" t="n">
-        <v>102.901341</v>
+        <v>102.905384</v>
       </c>
       <c r="N499" s="9" t="n">
         <v>99.057787</v>
@@ -41220,7 +41220,7 @@
         <v>97.90008</v>
       </c>
       <c r="M500" s="6" t="n">
-        <v>102.769381</v>
+        <v>102.770952</v>
       </c>
       <c r="N500" s="6" t="n">
         <v>99.27468399999999</v>
@@ -41304,7 +41304,7 @@
         <v>98.143474</v>
       </c>
       <c r="M501" s="9" t="n">
-        <v>102.607878</v>
+        <v>102.608069</v>
       </c>
       <c r="N501" s="9" t="n">
         <v>99.496961</v>
@@ -41388,7 +41388,7 @@
         <v>98.44132999999999</v>
       </c>
       <c r="M502" s="6" t="n">
-        <v>102.415597</v>
+        <v>102.41672</v>
       </c>
       <c r="N502" s="6" t="n">
         <v>99.71266900000001</v>
@@ -41472,7 +41472,7 @@
         <v>98.755976</v>
       </c>
       <c r="M503" s="9" t="n">
-        <v>102.241828</v>
+        <v>102.245137</v>
       </c>
       <c r="N503" s="9" t="n">
         <v>99.901359</v>
@@ -41556,7 +41556,7 @@
         <v>99.048254</v>
       </c>
       <c r="M504" s="6" t="n">
-        <v>102.101795</v>
+        <v>102.107648</v>
       </c>
       <c r="N504" s="6" t="n">
         <v>100.059735</v>
@@ -41640,7 +41640,7 @@
         <v>99.291479</v>
       </c>
       <c r="M505" s="9" t="n">
-        <v>101.976133</v>
+        <v>101.984296</v>
       </c>
       <c r="N505" s="9" t="n">
         <v>100.180721</v>
@@ -41724,7 +41724,7 @@
         <v>99.479175</v>
       </c>
       <c r="M506" s="6" t="n">
-        <v>101.854597</v>
+        <v>101.864353</v>
       </c>
       <c r="N506" s="6" t="n">
         <v>100.293809</v>
@@ -41808,7 +41808,7 @@
         <v>99.618077</v>
       </c>
       <c r="M507" s="9" t="n">
-        <v>101.731337</v>
+        <v>101.741478</v>
       </c>
       <c r="N507" s="9" t="n">
         <v>100.425671</v>
@@ -41892,7 +41892,7 @@
         <v>99.721377</v>
       </c>
       <c r="M508" s="6" t="n">
-        <v>101.6102</v>
+        <v>101.619014</v>
       </c>
       <c r="N508" s="6" t="n">
         <v>100.582879</v>
@@ -41976,7 +41976,7 @@
         <v>99.800225</v>
       </c>
       <c r="M509" s="9" t="n">
-        <v>101.488279</v>
+        <v>101.494387</v>
       </c>
       <c r="N509" s="9" t="n">
         <v>100.75952</v>
@@ -42060,7 +42060,7 @@
         <v>99.862622</v>
       </c>
       <c r="M510" s="6" t="n">
-        <v>101.339484</v>
+        <v>101.341838</v>
       </c>
       <c r="N510" s="6" t="n">
         <v>100.949082</v>
@@ -42144,7 +42144,7 @@
         <v>99.912885</v>
       </c>
       <c r="M511" s="9" t="n">
-        <v>101.133415</v>
+        <v>101.131597</v>
       </c>
       <c r="N511" s="9" t="n">
         <v>101.158641</v>
@@ -42228,7 +42228,7 @@
         <v>99.95371900000001</v>
       </c>
       <c r="M512" s="6" t="n">
-        <v>100.84374</v>
+        <v>100.838256</v>
       </c>
       <c r="N512" s="6" t="n">
         <v>101.360203</v>
@@ -42312,7 +42312,7 @@
         <v>99.989208</v>
       </c>
       <c r="M513" s="9" t="n">
-        <v>100.554136</v>
+        <v>100.547023</v>
       </c>
       <c r="N513" s="9" t="n">
         <v>101.528176</v>
@@ -42396,7 +42396,7 @@
         <v>100.02222</v>
       </c>
       <c r="M514" s="6" t="n">
-        <v>100.322507</v>
+        <v>100.317165</v>
       </c>
       <c r="N514" s="6" t="n">
         <v>101.638937</v>
@@ -42480,7 +42480,7 @@
         <v>100.057293</v>
       </c>
       <c r="M515" s="9" t="n">
-        <v>100.146864</v>
+        <v>100.145127</v>
       </c>
       <c r="N515" s="9" t="n">
         <v>101.676133</v>
@@ -42564,7 +42564,7 @@
         <v>100.095591</v>
       </c>
       <c r="M516" s="6" t="n">
-        <v>100.011662</v>
+        <v>100.014042</v>
       </c>
       <c r="N516" s="6" t="n">
         <v>101.626996</v>
@@ -42648,7 +42648,7 @@
         <v>100.136804</v>
       </c>
       <c r="M517" s="9" t="n">
-        <v>99.91291099999999</v>
+        <v>99.919135</v>
       </c>
       <c r="N517" s="9" t="n">
         <v>101.505375</v>
@@ -42732,7 +42732,7 @@
         <v>100.179837</v>
       </c>
       <c r="M518" s="6" t="n">
-        <v>99.83016600000001</v>
+        <v>99.83895099999999</v>
       </c>
       <c r="N518" s="6" t="n">
         <v>101.3427</v>
@@ -42816,7 +42816,7 @@
         <v>100.222659</v>
       </c>
       <c r="M519" s="9" t="n">
-        <v>99.740756</v>
+        <v>99.75003700000001</v>
       </c>
       <c r="N519" s="9" t="n">
         <v>101.166546</v>
@@ -42900,7 +42900,7 @@
         <v>100.263781</v>
       </c>
       <c r="M520" s="6" t="n">
-        <v>99.60321500000001</v>
+        <v>99.61024500000001</v>
       </c>
       <c r="N520" s="6" t="n">
         <v>101.002344</v>
@@ -42984,7 +42984,7 @@
         <v>100.305966</v>
       </c>
       <c r="M521" s="9" t="n">
-        <v>99.436708</v>
+        <v>99.439331</v>
       </c>
       <c r="N521" s="9" t="n">
         <v>100.871385</v>
@@ -43068,7 +43068,7 @@
         <v>100.351294</v>
       </c>
       <c r="M522" s="6" t="n">
-        <v>99.248795</v>
+        <v>99.24552799999999</v>
       </c>
       <c r="N522" s="6" t="n">
         <v>100.764292</v>
@@ -43152,7 +43152,7 @@
         <v>100.400924</v>
       </c>
       <c r="M523" s="9" t="n">
-        <v>99.076531</v>
+        <v>99.067223</v>
       </c>
       <c r="N523" s="9" t="n">
         <v>100.663586</v>
@@ -43236,7 +43236,7 @@
         <v>100.451343</v>
       </c>
       <c r="M524" s="6" t="n">
-        <v>98.94109899999999</v>
+        <v>98.927182</v>
       </c>
       <c r="N524" s="6" t="n">
         <v>100.567512</v>
@@ -43320,7 +43320,7 @@
         <v>100.495799</v>
       </c>
       <c r="M525" s="9" t="n">
-        <v>98.844397</v>
+        <v>98.829159</v>
       </c>
       <c r="N525" s="9" t="n">
         <v>100.476974</v>
@@ -43404,7 +43404,7 @@
         <v>100.530697</v>
       </c>
       <c r="M526" s="6" t="n">
-        <v>98.755256</v>
+        <v>98.743075</v>
       </c>
       <c r="N526" s="6" t="n">
         <v>100.38367</v>
@@ -43488,7 +43488,7 @@
         <v>100.55323</v>
       </c>
       <c r="M527" s="9" t="n">
-        <v>98.704909</v>
+        <v>98.69872100000001</v>
       </c>
       <c r="N527" s="9" t="n">
         <v>100.292203</v>
@@ -43572,7 +43572,7 @@
         <v>100.564068</v>
       </c>
       <c r="M528" s="6" t="n">
-        <v>98.723112</v>
+        <v>98.7244</v>
       </c>
       <c r="N528" s="6" t="n">
         <v>100.21003</v>
@@ -43656,7 +43656,7 @@
         <v>100.566624</v>
       </c>
       <c r="M529" s="9" t="n">
-        <v>98.782865</v>
+        <v>98.791405</v>
       </c>
       <c r="N529" s="9" t="n">
         <v>100.14569</v>
@@ -43740,7 +43740,7 @@
         <v>100.565101</v>
       </c>
       <c r="M530" s="6" t="n">
-        <v>98.873553</v>
+        <v>98.885837</v>
       </c>
       <c r="N530" s="6" t="n">
         <v>100.094836</v>
@@ -43824,7 +43824,7 @@
         <v>100.562499</v>
       </c>
       <c r="M531" s="9" t="n">
-        <v>98.978506</v>
+        <v>98.990784</v>
       </c>
       <c r="N531" s="9" t="n">
         <v>100.044959</v>
@@ -43908,7 +43908,7 @@
         <v>100.55948</v>
       </c>
       <c r="M532" s="6" t="n">
-        <v>99.077924</v>
+        <v>99.086555</v>
       </c>
       <c r="N532" s="6" t="n">
         <v>100.007873</v>
@@ -43992,7 +43992,7 @@
         <v>100.556327</v>
       </c>
       <c r="M533" s="9" t="n">
-        <v>99.16212299999999</v>
+        <v>99.164484</v>
       </c>
       <c r="N533" s="9" t="n">
         <v>99.99654700000001</v>
@@ -44076,7 +44076,7 @@
         <v>100.553928</v>
       </c>
       <c r="M534" s="6" t="n">
-        <v>99.22792699999999</v>
+        <v>99.222487</v>
       </c>
       <c r="N534" s="6" t="n">
         <v>100.012407</v>
@@ -44160,7 +44160,7 @@
         <v>100.552199</v>
       </c>
       <c r="M535" s="9" t="n">
-        <v>99.27713199999999</v>
+        <v>99.26419300000001</v>
       </c>
       <c r="N535" s="9" t="n">
         <v>100.040139</v>
@@ -44244,7 +44244,7 @@
         <v>100.551102</v>
       </c>
       <c r="M536" s="6" t="n">
-        <v>99.31544700000001</v>
+        <v>99.29733</v>
       </c>
       <c r="N536" s="6" t="n">
         <v>100.042585</v>
@@ -44328,7 +44328,7 @@
         <v>100.551086</v>
       </c>
       <c r="M537" s="9" t="n">
-        <v>99.340414</v>
+        <v>99.32158099999999</v>
       </c>
       <c r="N537" s="9" t="n">
         <v>100.017249</v>
@@ -44412,7 +44412,7 @@
         <v>100.549269</v>
       </c>
       <c r="M538" s="6" t="n">
-        <v>99.360646</v>
+        <v>99.34638200000001</v>
       </c>
       <c r="N538" s="6" t="n">
         <v>99.96810600000001</v>
@@ -44496,7 +44496,7 @@
         <v>100.542064</v>
       </c>
       <c r="M539" s="9" t="n">
-        <v>99.358172</v>
+        <v>99.352293</v>
       </c>
       <c r="N539" s="9" t="n">
         <v>99.90411899999999</v>
@@ -44580,7 +44580,7 @@
         <v>100.527691</v>
       </c>
       <c r="M540" s="6" t="n">
-        <v>99.311294</v>
+        <v>99.31580599999999</v>
       </c>
       <c r="N540" s="6" t="n">
         <v>99.822546</v>
@@ -44664,7 +44664,7 @@
         <v>100.502775</v>
       </c>
       <c r="M541" s="9" t="n">
-        <v>99.231814</v>
+        <v>99.24623099999999</v>
       </c>
       <c r="N541" s="9" t="n">
         <v>99.727885</v>
@@ -44748,7 +44748,7 @@
         <v>100.466622</v>
       </c>
       <c r="M542" s="6" t="n">
-        <v>99.14628500000001</v>
+        <v>99.16469499999999</v>
       </c>
       <c r="N542" s="6" t="n">
         <v>99.62104100000001</v>
@@ -44832,7 +44832,7 @@
         <v>100.420502</v>
       </c>
       <c r="M543" s="9" t="n">
-        <v>99.082582</v>
+        <v>99.099536</v>
       </c>
       <c r="N543" s="9" t="n">
         <v>99.524879</v>
@@ -44916,7 +44916,7 @@
         <v>100.367899</v>
       </c>
       <c r="M544" s="6" t="n">
-        <v>99.07983299999999</v>
+        <v>99.09106</v>
       </c>
       <c r="N544" s="6" t="n">
         <v>99.43491299999999</v>
@@ -45000,7 +45000,7 @@
         <v>100.311633</v>
       </c>
       <c r="M545" s="9" t="n">
-        <v>99.122184</v>
+        <v>99.124756</v>
       </c>
       <c r="N545" s="9" t="n">
         <v>99.34053</v>
@@ -45084,7 +45084,7 @@
         <v>100.252883</v>
       </c>
       <c r="M546" s="6" t="n">
-        <v>99.187566</v>
+        <v>99.17992599999999</v>
       </c>
       <c r="N546" s="6" t="n">
         <v>99.249089</v>
@@ -45168,7 +45168,7 @@
         <v>100.192471</v>
       </c>
       <c r="M547" s="9" t="n">
-        <v>99.256524</v>
+        <v>99.239465</v>
       </c>
       <c r="N547" s="9" t="n">
         <v>99.171885</v>
@@ -45252,7 +45252,7 @@
         <v>100.130644</v>
       </c>
       <c r="M548" s="6" t="n">
-        <v>99.331357</v>
+        <v>99.30811199999999</v>
       </c>
       <c r="N548" s="6" t="n">
         <v>99.12424900000001</v>
@@ -45336,7 +45336,7 @@
         <v>100.066523</v>
       </c>
       <c r="M549" s="9" t="n">
-        <v>99.437933</v>
+        <v>99.41411100000001</v>
       </c>
       <c r="N549" s="9" t="n">
         <v>99.098016</v>
@@ -45420,7 +45420,7 @@
         <v>100.000477</v>
       </c>
       <c r="M550" s="6" t="n">
-        <v>99.540244</v>
+        <v>99.522002</v>
       </c>
       <c r="N550" s="6" t="n">
         <v>99.09165400000001</v>
@@ -45504,7 +45504,7 @@
         <v>99.93474399999999</v>
       </c>
       <c r="M551" s="9" t="n">
-        <v>99.64188</v>
+        <v>99.63457099999999</v>
       </c>
       <c r="N551" s="9" t="n">
         <v>99.113012</v>
@@ -45588,7 +45588,7 @@
         <v>99.87217200000001</v>
       </c>
       <c r="M552" s="6" t="n">
-        <v>99.75939200000001</v>
+        <v>99.766857</v>
       </c>
       <c r="N552" s="6" t="n">
         <v>99.168695</v>
@@ -45672,7 +45672,7 @@
         <v>99.816664</v>
       </c>
       <c r="M553" s="9" t="n">
-        <v>99.907774</v>
+        <v>99.930751</v>
       </c>
       <c r="N553" s="9" t="n">
         <v>99.263171</v>
@@ -45756,7 +45756,7 @@
         <v>99.771727</v>
       </c>
       <c r="M554" s="6" t="n">
-        <v>100.039078</v>
+        <v>100.070674</v>
       </c>
       <c r="N554" s="6" t="n">
         <v>99.378964</v>
@@ -45840,7 +45840,7 @@
         <v>99.73569000000001</v>
       </c>
       <c r="M555" s="9" t="n">
-        <v>100.117105</v>
+        <v>100.151774</v>
       </c>
       <c r="N555" s="9" t="n">
         <v>99.505286</v>
@@ -45924,7 +45924,7 @@
         <v>99.705551</v>
       </c>
       <c r="M556" s="6" t="n">
-        <v>100.182459</v>
+        <v>100.216711</v>
       </c>
       <c r="N556" s="6" t="n">
         <v>99.634331</v>
@@ -46008,7 +46008,7 @@
         <v>99.679518</v>
       </c>
       <c r="M557" s="9" t="n">
-        <v>100.25411</v>
+        <v>100.285121</v>
       </c>
       <c r="N557" s="9" t="n">
         <v>99.773279</v>
@@ -46092,7 +46092,7 @@
         <v>99.65561</v>
       </c>
       <c r="M558" s="6" t="n">
-        <v>100.365524</v>
+        <v>100.389843</v>
       </c>
       <c r="N558" s="6" t="n">
         <v>99.933976</v>
@@ -46176,7 +46176,7 @@
         <v>99.632307</v>
       </c>
       <c r="M559" s="9" t="n">
-        <v>100.503205</v>
+        <v>100.515751</v>
       </c>
       <c r="N559" s="9" t="n">
         <v>100.126678</v>
@@ -46260,7 +46260,7 @@
         <v>99.608284</v>
       </c>
       <c r="M560" s="6" t="n">
-        <v>100.64401</v>
+        <v>100.635757</v>
       </c>
       <c r="N560" s="6" t="n">
         <v>100.354928</v>
@@ -46344,7 +46344,7 @@
         <v>99.584</v>
       </c>
       <c r="M561" s="9" t="n">
-        <v>100.760031</v>
+        <v>100.715535</v>
       </c>
       <c r="N561" s="9" t="n">
         <v>100.615919</v>
@@ -46428,7 +46428,7 @@
         <v>99.562954</v>
       </c>
       <c r="M562" s="6" t="n">
-        <v>100.851858</v>
+        <v>100.746164</v>
       </c>
       <c r="N562" s="6" t="n">
         <v>100.906045</v>
@@ -46512,7 +46512,7 @@
         <v>99.54803</v>
       </c>
       <c r="M563" s="9" t="n">
-        <v>100.920144</v>
+        <v>100.719442</v>
       </c>
       <c r="N563" s="9" t="n">
         <v>101.22779</v>
@@ -46590,7 +46590,7 @@
         <v>99.53705600000001</v>
       </c>
       <c r="M564" s="6" t="n">
-        <v>100.970948</v>
+        <v>100.638019</v>
       </c>
       <c r="N564" s="6" t="n">
         <v>101.591978</v>

--- a/downloads/indicadores/SIC/SIC_datos.xlsx
+++ b/downloads/indicadores/SIC/SIC_datos.xlsx
@@ -679,7 +679,7 @@
       </c>
       <c r="M6" s="6" t="n"/>
       <c r="N6" s="6" t="n">
-        <v>96.01242499999999</v>
+        <v>96.01853800000001</v>
       </c>
       <c r="O6" s="6" t="n">
         <v>100.456177</v>
@@ -751,7 +751,7 @@
       </c>
       <c r="M7" s="9" t="n"/>
       <c r="N7" s="9" t="n">
-        <v>96.64352700000001</v>
+        <v>96.648679</v>
       </c>
       <c r="O7" s="9" t="n">
         <v>100.496514</v>
@@ -823,7 +823,7 @@
       </c>
       <c r="M8" s="6" t="n"/>
       <c r="N8" s="6" t="n">
-        <v>97.27531399999999</v>
+        <v>97.279504</v>
       </c>
       <c r="O8" s="6" t="n">
         <v>100.519198</v>
@@ -895,7 +895,7 @@
       </c>
       <c r="M9" s="9" t="n"/>
       <c r="N9" s="9" t="n">
-        <v>97.912537</v>
+        <v>97.915756</v>
       </c>
       <c r="O9" s="9" t="n">
         <v>100.5647</v>
@@ -967,7 +967,7 @@
       </c>
       <c r="M10" s="6" t="n"/>
       <c r="N10" s="6" t="n">
-        <v>98.55596799999999</v>
+        <v>98.558206</v>
       </c>
       <c r="O10" s="6" t="n">
         <v>100.709344</v>
@@ -1039,7 +1039,7 @@
       </c>
       <c r="M11" s="9" t="n"/>
       <c r="N11" s="9" t="n">
-        <v>99.21331600000001</v>
+        <v>99.214552</v>
       </c>
       <c r="O11" s="9" t="n">
         <v>100.953386</v>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="M12" s="6" t="n"/>
       <c r="N12" s="6" t="n">
-        <v>99.898045</v>
+        <v>99.89823800000001</v>
       </c>
       <c r="O12" s="6" t="n">
         <v>101.227689</v>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="M13" s="9" t="n"/>
       <c r="N13" s="9" t="n">
-        <v>100.597885</v>
+        <v>100.597011</v>
       </c>
       <c r="O13" s="9" t="n">
         <v>101.474909</v>
@@ -1255,7 +1255,7 @@
       </c>
       <c r="M14" s="6" t="n"/>
       <c r="N14" s="6" t="n">
-        <v>101.291187</v>
+        <v>101.289255</v>
       </c>
       <c r="O14" s="6" t="n">
         <v>101.610715</v>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="M15" s="9" t="n"/>
       <c r="N15" s="9" t="n">
-        <v>101.939694</v>
+        <v>101.936772</v>
       </c>
       <c r="O15" s="9" t="n">
         <v>101.581897</v>
@@ -1399,7 +1399,7 @@
       </c>
       <c r="M16" s="6" t="n"/>
       <c r="N16" s="6" t="n">
-        <v>102.50843</v>
+        <v>102.504641</v>
       </c>
       <c r="O16" s="6" t="n">
         <v>101.443181</v>
@@ -1471,7 +1471,7 @@
       </c>
       <c r="M17" s="9" t="n"/>
       <c r="N17" s="9" t="n">
-        <v>102.975587</v>
+        <v>102.971084</v>
       </c>
       <c r="O17" s="9" t="n">
         <v>101.286133</v>
@@ -1547,7 +1547,7 @@
       </c>
       <c r="M18" s="6" t="n"/>
       <c r="N18" s="6" t="n">
-        <v>103.335084</v>
+        <v>103.330031</v>
       </c>
       <c r="O18" s="6" t="n">
         <v>101.197989</v>
@@ -1625,7 +1625,7 @@
       </c>
       <c r="M19" s="9" t="n"/>
       <c r="N19" s="9" t="n">
-        <v>103.589263</v>
+        <v>103.583824</v>
       </c>
       <c r="O19" s="9" t="n">
         <v>101.198674</v>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="M20" s="6" t="n"/>
       <c r="N20" s="6" t="n">
-        <v>103.759695</v>
+        <v>103.754</v>
       </c>
       <c r="O20" s="6" t="n">
         <v>101.303176</v>
@@ -1781,7 +1781,7 @@
       </c>
       <c r="M21" s="9" t="n"/>
       <c r="N21" s="9" t="n">
-        <v>103.856387</v>
+        <v>103.850555</v>
       </c>
       <c r="O21" s="9" t="n">
         <v>101.485779</v>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="M22" s="6" t="n"/>
       <c r="N22" s="6" t="n">
-        <v>103.911966</v>
+        <v>103.906068</v>
       </c>
       <c r="O22" s="6" t="n">
         <v>101.604639</v>
@@ -1937,7 +1937,7 @@
       </c>
       <c r="M23" s="9" t="n"/>
       <c r="N23" s="9" t="n">
-        <v>103.957181</v>
+        <v>103.951245</v>
       </c>
       <c r="O23" s="9" t="n">
         <v>101.632068</v>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="M24" s="6" t="n"/>
       <c r="N24" s="6" t="n">
-        <v>104.023248</v>
+        <v>104.017258</v>
       </c>
       <c r="O24" s="6" t="n">
         <v>101.51966</v>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="M25" s="9" t="n"/>
       <c r="N25" s="9" t="n">
-        <v>104.122772</v>
+        <v>104.116691</v>
       </c>
       <c r="O25" s="9" t="n">
         <v>101.29563</v>
@@ -2171,7 +2171,7 @@
       </c>
       <c r="M26" s="6" t="n"/>
       <c r="N26" s="6" t="n">
-        <v>104.257082</v>
+        <v>104.250865</v>
       </c>
       <c r="O26" s="6" t="n">
         <v>101.045131</v>
@@ -2249,7 +2249,7 @@
       </c>
       <c r="M27" s="9" t="n"/>
       <c r="N27" s="9" t="n">
-        <v>104.391011</v>
+        <v>104.384649</v>
       </c>
       <c r="O27" s="9" t="n">
         <v>100.804025</v>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="M28" s="6" t="n"/>
       <c r="N28" s="6" t="n">
-        <v>104.442679</v>
+        <v>104.436256</v>
       </c>
       <c r="O28" s="6" t="n">
         <v>100.567089</v>
@@ -2405,7 +2405,7 @@
       </c>
       <c r="M29" s="9" t="n"/>
       <c r="N29" s="9" t="n">
-        <v>104.329097</v>
+        <v>104.322865</v>
       </c>
       <c r="O29" s="9" t="n">
         <v>100.300723</v>
@@ -2483,7 +2483,7 @@
       </c>
       <c r="M30" s="6" t="n"/>
       <c r="N30" s="6" t="n">
-        <v>104.026813</v>
+        <v>104.021082</v>
       </c>
       <c r="O30" s="6" t="n">
         <v>99.928262</v>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="M31" s="9" t="n"/>
       <c r="N31" s="9" t="n">
-        <v>103.541811</v>
+        <v>103.53688</v>
       </c>
       <c r="O31" s="9" t="n">
         <v>99.480819</v>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="M32" s="6" t="n"/>
       <c r="N32" s="6" t="n">
-        <v>102.872517</v>
+        <v>102.868663</v>
       </c>
       <c r="O32" s="6" t="n">
         <v>98.970206</v>
@@ -2717,7 +2717,7 @@
       </c>
       <c r="M33" s="9" t="n"/>
       <c r="N33" s="9" t="n">
-        <v>102.051892</v>
+        <v>102.049289</v>
       </c>
       <c r="O33" s="9" t="n">
         <v>98.374971</v>
@@ -2795,7 +2795,7 @@
       </c>
       <c r="M34" s="6" t="n"/>
       <c r="N34" s="6" t="n">
-        <v>101.096432</v>
+        <v>101.095145</v>
       </c>
       <c r="O34" s="6" t="n">
         <v>97.75676300000001</v>
@@ -2873,7 +2873,7 @@
       </c>
       <c r="M35" s="9" t="n"/>
       <c r="N35" s="9" t="n">
-        <v>100.035675</v>
+        <v>100.035605</v>
       </c>
       <c r="O35" s="9" t="n">
         <v>97.090909</v>
@@ -2951,7 +2951,7 @@
       </c>
       <c r="M36" s="6" t="n"/>
       <c r="N36" s="6" t="n">
-        <v>98.904843</v>
+        <v>98.9059</v>
       </c>
       <c r="O36" s="6" t="n">
         <v>96.468333</v>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="M37" s="9" t="n"/>
       <c r="N37" s="9" t="n">
-        <v>97.73985999999999</v>
+        <v>97.741972</v>
       </c>
       <c r="O37" s="9" t="n">
         <v>95.94629</v>
@@ -3107,7 +3107,7 @@
       </c>
       <c r="M38" s="6" t="n"/>
       <c r="N38" s="6" t="n">
-        <v>96.632527</v>
+        <v>96.635603</v>
       </c>
       <c r="O38" s="6" t="n">
         <v>95.561008</v>
@@ -3185,7 +3185,7 @@
       </c>
       <c r="M39" s="9" t="n"/>
       <c r="N39" s="9" t="n">
-        <v>95.672223</v>
+        <v>95.67626199999999</v>
       </c>
       <c r="O39" s="9" t="n">
         <v>95.389027</v>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="M40" s="6" t="n"/>
       <c r="N40" s="6" t="n">
-        <v>94.948302</v>
+        <v>94.953543</v>
       </c>
       <c r="O40" s="6" t="n">
         <v>95.47277</v>
@@ -3341,7 +3341,7 @@
       </c>
       <c r="M41" s="9" t="n"/>
       <c r="N41" s="9" t="n">
-        <v>94.52375499999999</v>
+        <v>94.529996</v>
       </c>
       <c r="O41" s="9" t="n">
         <v>95.734038</v>
@@ -3419,7 +3419,7 @@
       </c>
       <c r="M42" s="6" t="n"/>
       <c r="N42" s="6" t="n">
-        <v>94.399659</v>
+        <v>94.40653</v>
       </c>
       <c r="O42" s="6" t="n">
         <v>96.124185</v>
@@ -3497,7 +3497,7 @@
       </c>
       <c r="M43" s="9" t="n"/>
       <c r="N43" s="9" t="n">
-        <v>94.55231000000001</v>
+        <v>94.55947500000001</v>
       </c>
       <c r="O43" s="9" t="n">
         <v>96.546133</v>
@@ -3575,7 +3575,7 @@
       </c>
       <c r="M44" s="6" t="n"/>
       <c r="N44" s="6" t="n">
-        <v>94.93962399999999</v>
+        <v>94.946664</v>
       </c>
       <c r="O44" s="6" t="n">
         <v>96.932231</v>
@@ -3653,7 +3653,7 @@
       </c>
       <c r="M45" s="9" t="n"/>
       <c r="N45" s="9" t="n">
-        <v>95.460307</v>
+        <v>95.4669</v>
       </c>
       <c r="O45" s="9" t="n">
         <v>97.23724799999999</v>
@@ -3731,7 +3731,7 @@
       </c>
       <c r="M46" s="6" t="n"/>
       <c r="N46" s="6" t="n">
-        <v>96.009186</v>
+        <v>96.01516700000001</v>
       </c>
       <c r="O46" s="6" t="n">
         <v>97.484387</v>
@@ -3809,7 +3809,7 @@
       </c>
       <c r="M47" s="9" t="n"/>
       <c r="N47" s="9" t="n">
-        <v>96.50832200000001</v>
+        <v>96.513676</v>
       </c>
       <c r="O47" s="9" t="n">
         <v>97.758787</v>
@@ -3887,7 +3887,7 @@
       </c>
       <c r="M48" s="6" t="n"/>
       <c r="N48" s="6" t="n">
-        <v>96.914438</v>
+        <v>96.919253</v>
       </c>
       <c r="O48" s="6" t="n">
         <v>98.09311599999999</v>
@@ -3965,7 +3965,7 @@
       </c>
       <c r="M49" s="9" t="n"/>
       <c r="N49" s="9" t="n">
-        <v>97.228043</v>
+        <v>97.23245199999999</v>
       </c>
       <c r="O49" s="9" t="n">
         <v>98.43737</v>
@@ -4043,7 +4043,7 @@
       </c>
       <c r="M50" s="6" t="n"/>
       <c r="N50" s="6" t="n">
-        <v>97.452884</v>
+        <v>97.457053</v>
       </c>
       <c r="O50" s="6" t="n">
         <v>98.815051</v>
@@ -4121,7 +4121,7 @@
       </c>
       <c r="M51" s="9" t="n"/>
       <c r="N51" s="9" t="n">
-        <v>97.59644900000001</v>
+        <v>97.60056299999999</v>
       </c>
       <c r="O51" s="9" t="n">
         <v>99.222675</v>
@@ -4199,7 +4199,7 @@
       </c>
       <c r="M52" s="6" t="n"/>
       <c r="N52" s="6" t="n">
-        <v>97.683627</v>
+        <v>97.687847</v>
       </c>
       <c r="O52" s="6" t="n">
         <v>99.62356200000001</v>
@@ -4277,7 +4277,7 @@
       </c>
       <c r="M53" s="9" t="n"/>
       <c r="N53" s="9" t="n">
-        <v>97.789714</v>
+        <v>97.794072</v>
       </c>
       <c r="O53" s="9" t="n">
         <v>99.996397</v>
@@ -4355,7 +4355,7 @@
       </c>
       <c r="M54" s="6" t="n"/>
       <c r="N54" s="6" t="n">
-        <v>97.96185199999999</v>
+        <v>97.966244</v>
       </c>
       <c r="O54" s="6" t="n">
         <v>100.355146</v>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="M55" s="9" t="n"/>
       <c r="N55" s="9" t="n">
-        <v>98.226009</v>
+        <v>98.23016200000001</v>
       </c>
       <c r="O55" s="9" t="n">
         <v>100.705625</v>
@@ -4511,7 +4511,7 @@
       </c>
       <c r="M56" s="6" t="n"/>
       <c r="N56" s="6" t="n">
-        <v>98.559972</v>
+        <v>98.563427</v>
       </c>
       <c r="O56" s="6" t="n">
         <v>101.107123</v>
@@ -4589,7 +4589,7 @@
       </c>
       <c r="M57" s="9" t="n"/>
       <c r="N57" s="9" t="n">
-        <v>98.935433</v>
+        <v>98.93799</v>
       </c>
       <c r="O57" s="9" t="n">
         <v>101.579741</v>
@@ -4667,7 +4667,7 @@
       </c>
       <c r="M58" s="6" t="n"/>
       <c r="N58" s="6" t="n">
-        <v>99.34794100000001</v>
+        <v>99.34953899999999</v>
       </c>
       <c r="O58" s="6" t="n">
         <v>102.070067</v>
@@ -4745,7 +4745,7 @@
       </c>
       <c r="M59" s="9" t="n"/>
       <c r="N59" s="9" t="n">
-        <v>99.802111</v>
+        <v>99.802744</v>
       </c>
       <c r="O59" s="9" t="n">
         <v>102.463717</v>
@@ -4823,7 +4823,7 @@
       </c>
       <c r="M60" s="6" t="n"/>
       <c r="N60" s="6" t="n">
-        <v>100.258498</v>
+        <v>100.258239</v>
       </c>
       <c r="O60" s="6" t="n">
         <v>102.724338</v>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="M61" s="9" t="n"/>
       <c r="N61" s="9" t="n">
-        <v>100.666431</v>
+        <v>100.665427</v>
       </c>
       <c r="O61" s="9" t="n">
         <v>102.874708</v>
@@ -4979,7 +4979,7 @@
       </c>
       <c r="M62" s="6" t="n"/>
       <c r="N62" s="6" t="n">
-        <v>101.005984</v>
+        <v>101.004395</v>
       </c>
       <c r="O62" s="6" t="n">
         <v>102.891089</v>
@@ -5057,7 +5057,7 @@
       </c>
       <c r="M63" s="9" t="n"/>
       <c r="N63" s="9" t="n">
-        <v>101.274153</v>
+        <v>101.272127</v>
       </c>
       <c r="O63" s="9" t="n">
         <v>102.82425</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="M64" s="6" t="n"/>
       <c r="N64" s="6" t="n">
-        <v>101.486346</v>
+        <v>101.483991</v>
       </c>
       <c r="O64" s="6" t="n">
         <v>102.757241</v>
@@ -5213,7 +5213,7 @@
       </c>
       <c r="M65" s="9" t="n"/>
       <c r="N65" s="9" t="n">
-        <v>101.63459</v>
+        <v>101.632015</v>
       </c>
       <c r="O65" s="9" t="n">
         <v>102.782464</v>
@@ -5291,7 +5291,7 @@
       </c>
       <c r="M66" s="6" t="n"/>
       <c r="N66" s="6" t="n">
-        <v>101.692098</v>
+        <v>101.689445</v>
       </c>
       <c r="O66" s="6" t="n">
         <v>102.873683</v>
@@ -5369,7 +5369,7 @@
       </c>
       <c r="M67" s="9" t="n"/>
       <c r="N67" s="9" t="n">
-        <v>101.64247</v>
+        <v>101.639903</v>
       </c>
       <c r="O67" s="9" t="n">
         <v>102.9663</v>
@@ -5447,7 +5447,7 @@
       </c>
       <c r="M68" s="6" t="n"/>
       <c r="N68" s="6" t="n">
-        <v>101.536096</v>
+        <v>101.533699</v>
       </c>
       <c r="O68" s="6" t="n">
         <v>102.956107</v>
@@ -5525,7 +5525,7 @@
       </c>
       <c r="M69" s="9" t="n"/>
       <c r="N69" s="9" t="n">
-        <v>101.415654</v>
+        <v>101.413445</v>
       </c>
       <c r="O69" s="9" t="n">
         <v>102.85313</v>
@@ -5603,7 +5603,7 @@
       </c>
       <c r="M70" s="6" t="n"/>
       <c r="N70" s="6" t="n">
-        <v>101.296348</v>
+        <v>101.294322</v>
       </c>
       <c r="O70" s="6" t="n">
         <v>102.641042</v>
@@ -5681,7 +5681,7 @@
       </c>
       <c r="M71" s="9" t="n"/>
       <c r="N71" s="9" t="n">
-        <v>101.184754</v>
+        <v>101.182899</v>
       </c>
       <c r="O71" s="9" t="n">
         <v>102.338669</v>
@@ -5759,7 +5759,7 @@
       </c>
       <c r="M72" s="6" t="n"/>
       <c r="N72" s="6" t="n">
-        <v>101.099793</v>
+        <v>101.098066</v>
       </c>
       <c r="O72" s="6" t="n">
         <v>101.933907</v>
@@ -5837,7 +5837,7 @@
       </c>
       <c r="M73" s="9" t="n"/>
       <c r="N73" s="9" t="n">
-        <v>101.056817</v>
+        <v>101.055154</v>
       </c>
       <c r="O73" s="9" t="n">
         <v>101.452023</v>
@@ -5915,7 +5915,7 @@
       </c>
       <c r="M74" s="6" t="n"/>
       <c r="N74" s="6" t="n">
-        <v>101.023148</v>
+        <v>101.021534</v>
       </c>
       <c r="O74" s="6" t="n">
         <v>100.976584</v>
@@ -5993,7 +5993,7 @@
       </c>
       <c r="M75" s="9" t="n"/>
       <c r="N75" s="9" t="n">
-        <v>100.986004</v>
+        <v>100.984445</v>
       </c>
       <c r="O75" s="9" t="n">
         <v>100.493</v>
@@ -6071,7 +6071,7 @@
       </c>
       <c r="M76" s="6" t="n"/>
       <c r="N76" s="6" t="n">
-        <v>100.922261</v>
+        <v>100.920798</v>
       </c>
       <c r="O76" s="6" t="n">
         <v>100.004761</v>
@@ -6149,7 +6149,7 @@
       </c>
       <c r="M77" s="9" t="n"/>
       <c r="N77" s="9" t="n">
-        <v>100.793314</v>
+        <v>100.792046</v>
       </c>
       <c r="O77" s="9" t="n">
         <v>99.481098</v>
@@ -6229,7 +6229,7 @@
       </c>
       <c r="M78" s="6" t="n"/>
       <c r="N78" s="6" t="n">
-        <v>100.594857</v>
+        <v>100.593891</v>
       </c>
       <c r="O78" s="6" t="n">
         <v>98.95821100000001</v>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="M79" s="9" t="n"/>
       <c r="N79" s="9" t="n">
-        <v>100.322039</v>
+        <v>100.321488</v>
       </c>
       <c r="O79" s="9" t="n">
         <v>98.47627799999999</v>
@@ -6389,7 +6389,7 @@
       </c>
       <c r="M80" s="6" t="n"/>
       <c r="N80" s="6" t="n">
-        <v>99.992361</v>
+        <v>99.992313</v>
       </c>
       <c r="O80" s="6" t="n">
         <v>98.034485</v>
@@ -6469,7 +6469,7 @@
       </c>
       <c r="M81" s="9" t="n"/>
       <c r="N81" s="9" t="n">
-        <v>99.64582</v>
+        <v>99.64630099999999</v>
       </c>
       <c r="O81" s="9" t="n">
         <v>97.601446</v>
@@ -6549,7 +6549,7 @@
       </c>
       <c r="M82" s="6" t="n"/>
       <c r="N82" s="6" t="n">
-        <v>99.276055</v>
+        <v>99.277101</v>
       </c>
       <c r="O82" s="6" t="n">
         <v>97.18968</v>
@@ -6629,7 +6629,7 @@
       </c>
       <c r="M83" s="9" t="n"/>
       <c r="N83" s="9" t="n">
-        <v>98.88478499999999</v>
+        <v>98.886428</v>
       </c>
       <c r="O83" s="9" t="n">
         <v>96.90272400000001</v>
@@ -6709,7 +6709,7 @@
       </c>
       <c r="M84" s="6" t="n"/>
       <c r="N84" s="6" t="n">
-        <v>98.505931</v>
+        <v>98.50815299999999</v>
       </c>
       <c r="O84" s="6" t="n">
         <v>96.833494</v>
@@ -6789,7 +6789,7 @@
       </c>
       <c r="M85" s="9" t="n"/>
       <c r="N85" s="9" t="n">
-        <v>98.178217</v>
+        <v>98.180939</v>
       </c>
       <c r="O85" s="9" t="n">
         <v>97.009427</v>
@@ -6869,7 +6869,7 @@
       </c>
       <c r="M86" s="6" t="n"/>
       <c r="N86" s="6" t="n">
-        <v>97.947701</v>
+        <v>97.95077499999999</v>
       </c>
       <c r="O86" s="6" t="n">
         <v>97.359527</v>
@@ -6949,7 +6949,7 @@
       </c>
       <c r="M87" s="9" t="n"/>
       <c r="N87" s="9" t="n">
-        <v>97.836123</v>
+        <v>97.839367</v>
       </c>
       <c r="O87" s="9" t="n">
         <v>97.79688899999999</v>
@@ -7029,7 +7029,7 @@
       </c>
       <c r="M88" s="6" t="n"/>
       <c r="N88" s="6" t="n">
-        <v>97.80819200000001</v>
+        <v>97.81147900000001</v>
       </c>
       <c r="O88" s="6" t="n">
         <v>98.270624</v>
@@ -7109,7 +7109,7 @@
       </c>
       <c r="M89" s="9" t="n"/>
       <c r="N89" s="9" t="n">
-        <v>97.83842199999999</v>
+        <v>97.841663</v>
       </c>
       <c r="O89" s="9" t="n">
         <v>98.764004</v>
@@ -7191,7 +7191,7 @@
         <v>102.50242</v>
       </c>
       <c r="N90" s="6" t="n">
-        <v>97.889831</v>
+        <v>97.892993</v>
       </c>
       <c r="O90" s="6" t="n">
         <v>99.218654</v>
@@ -7273,7 +7273,7 @@
         <v>102.143164</v>
       </c>
       <c r="N91" s="9" t="n">
-        <v>97.94937</v>
+        <v>97.95244</v>
       </c>
       <c r="O91" s="9" t="n">
         <v>99.615182</v>
@@ -7355,7 +7355,7 @@
         <v>101.745879</v>
       </c>
       <c r="N92" s="6" t="n">
-        <v>98.01599299999999</v>
+        <v>98.018962</v>
       </c>
       <c r="O92" s="6" t="n">
         <v>99.989581</v>
@@ -7437,7 +7437,7 @@
         <v>101.336368</v>
       </c>
       <c r="N93" s="9" t="n">
-        <v>98.08319899999999</v>
+        <v>98.086065</v>
       </c>
       <c r="O93" s="9" t="n">
         <v>100.385563</v>
@@ -7519,7 +7519,7 @@
         <v>100.934285</v>
       </c>
       <c r="N94" s="6" t="n">
-        <v>98.162494</v>
+        <v>98.165239</v>
       </c>
       <c r="O94" s="6" t="n">
         <v>100.838551</v>
@@ -7601,7 +7601,7 @@
         <v>100.593698</v>
       </c>
       <c r="N95" s="9" t="n">
-        <v>98.269811</v>
+        <v>98.272392</v>
       </c>
       <c r="O95" s="9" t="n">
         <v>101.242305</v>
@@ -7683,7 +7683,7 @@
         <v>100.331001</v>
       </c>
       <c r="N96" s="6" t="n">
-        <v>98.409961</v>
+        <v>98.412328</v>
       </c>
       <c r="O96" s="6" t="n">
         <v>101.462828</v>
@@ -7765,7 +7765,7 @@
         <v>100.14921</v>
       </c>
       <c r="N97" s="9" t="n">
-        <v>98.54351800000001</v>
+        <v>98.545681</v>
       </c>
       <c r="O97" s="9" t="n">
         <v>101.455567</v>
@@ -7847,7 +7847,7 @@
         <v>100.048391</v>
       </c>
       <c r="N98" s="6" t="n">
-        <v>98.65055599999999</v>
+        <v>98.652556</v>
       </c>
       <c r="O98" s="6" t="n">
         <v>101.241452</v>
@@ -7929,7 +7929,7 @@
         <v>100.011216</v>
       </c>
       <c r="N99" s="9" t="n">
-        <v>98.743258</v>
+        <v>98.745116</v>
       </c>
       <c r="O99" s="9" t="n">
         <v>100.868724</v>
@@ -8011,7 +8011,7 @@
         <v>100.001211</v>
       </c>
       <c r="N100" s="6" t="n">
-        <v>98.843352</v>
+        <v>98.84505799999999</v>
       </c>
       <c r="O100" s="6" t="n">
         <v>100.352987</v>
@@ -8093,7 +8093,7 @@
         <v>100.034374</v>
       </c>
       <c r="N101" s="9" t="n">
-        <v>98.9953</v>
+        <v>98.996773</v>
       </c>
       <c r="O101" s="9" t="n">
         <v>99.789496</v>
@@ -8175,7 +8175,7 @@
         <v>100.154682</v>
       </c>
       <c r="N102" s="6" t="n">
-        <v>99.239958</v>
+        <v>99.241058</v>
       </c>
       <c r="O102" s="6" t="n">
         <v>99.272651</v>
@@ -8257,7 +8257,7 @@
         <v>100.325234</v>
       </c>
       <c r="N103" s="9" t="n">
-        <v>99.544714</v>
+        <v>99.545348</v>
       </c>
       <c r="O103" s="9" t="n">
         <v>98.862094</v>
@@ -8339,7 +8339,7 @@
         <v>100.515355</v>
       </c>
       <c r="N104" s="6" t="n">
-        <v>99.882284</v>
+        <v>99.882403</v>
       </c>
       <c r="O104" s="6" t="n">
         <v>98.62419300000001</v>
@@ -8421,7 +8421,7 @@
         <v>100.676895</v>
       </c>
       <c r="N105" s="9" t="n">
-        <v>100.223042</v>
+        <v>100.22264</v>
       </c>
       <c r="O105" s="9" t="n">
         <v>98.561871</v>
@@ -8503,7 +8503,7 @@
         <v>100.795882</v>
       </c>
       <c r="N106" s="6" t="n">
-        <v>100.543221</v>
+        <v>100.54233</v>
       </c>
       <c r="O106" s="6" t="n">
         <v>98.628688</v>
@@ -8585,7 +8585,7 @@
         <v>100.868074</v>
       </c>
       <c r="N107" s="9" t="n">
-        <v>100.827865</v>
+        <v>100.826539</v>
       </c>
       <c r="O107" s="9" t="n">
         <v>98.842822</v>
@@ -8667,7 +8667,7 @@
         <v>100.894339</v>
       </c>
       <c r="N108" s="6" t="n">
-        <v>101.067592</v>
+        <v>101.0659</v>
       </c>
       <c r="O108" s="6" t="n">
         <v>99.19426199999999</v>
@@ -8749,7 +8749,7 @@
         <v>100.900789</v>
       </c>
       <c r="N109" s="9" t="n">
-        <v>101.257588</v>
+        <v>101.255606</v>
       </c>
       <c r="O109" s="9" t="n">
         <v>99.651482</v>
@@ -8831,7 +8831,7 @@
         <v>100.910968</v>
       </c>
       <c r="N110" s="6" t="n">
-        <v>101.38472</v>
+        <v>101.382544</v>
       </c>
       <c r="O110" s="6" t="n">
         <v>100.156445</v>
@@ -8913,7 +8913,7 @@
         <v>100.899346</v>
       </c>
       <c r="N111" s="9" t="n">
-        <v>101.455399</v>
+        <v>101.453116</v>
       </c>
       <c r="O111" s="9" t="n">
         <v>100.686644</v>
@@ -8995,7 +8995,7 @@
         <v>100.858715</v>
       </c>
       <c r="N112" s="6" t="n">
-        <v>101.487237</v>
+        <v>101.484906</v>
       </c>
       <c r="O112" s="6" t="n">
         <v>101.222396</v>
@@ -9077,7 +9077,7 @@
         <v>100.758775</v>
       </c>
       <c r="N113" s="9" t="n">
-        <v>101.487498</v>
+        <v>101.485166</v>
       </c>
       <c r="O113" s="9" t="n">
         <v>101.653175</v>
@@ -9159,7 +9159,7 @@
         <v>100.578485</v>
       </c>
       <c r="N114" s="6" t="n">
-        <v>101.474435</v>
+        <v>101.472124</v>
       </c>
       <c r="O114" s="6" t="n">
         <v>101.952612</v>
@@ -9241,7 +9241,7 @@
         <v>100.333073</v>
       </c>
       <c r="N115" s="9" t="n">
-        <v>101.436576</v>
+        <v>101.434323</v>
       </c>
       <c r="O115" s="9" t="n">
         <v>102.128342</v>
@@ -9323,7 +9323,7 @@
         <v>100.077905</v>
       </c>
       <c r="N116" s="6" t="n">
-        <v>101.35198</v>
+        <v>101.349857</v>
       </c>
       <c r="O116" s="6" t="n">
         <v>102.152115</v>
@@ -9405,7 +9405,7 @@
         <v>99.848326</v>
       </c>
       <c r="N117" s="9" t="n">
-        <v>101.219874</v>
+        <v>101.217953</v>
       </c>
       <c r="O117" s="9" t="n">
         <v>102.022372</v>
@@ -9487,7 +9487,7 @@
         <v>99.65974300000001</v>
       </c>
       <c r="N118" s="6" t="n">
-        <v>101.047109</v>
+        <v>101.045453</v>
       </c>
       <c r="O118" s="6" t="n">
         <v>101.789472</v>
@@ -9569,7 +9569,7 @@
         <v>99.492211</v>
       </c>
       <c r="N119" s="9" t="n">
-        <v>100.861248</v>
+        <v>100.859876</v>
       </c>
       <c r="O119" s="9" t="n">
         <v>101.501531</v>
@@ -9651,7 +9651,7 @@
         <v>99.35030500000001</v>
       </c>
       <c r="N120" s="6" t="n">
-        <v>100.674677</v>
+        <v>100.673591</v>
       </c>
       <c r="O120" s="6" t="n">
         <v>101.18847</v>
@@ -9733,7 +9733,7 @@
         <v>99.21216800000001</v>
       </c>
       <c r="N121" s="9" t="n">
-        <v>100.538541</v>
+        <v>100.537663</v>
       </c>
       <c r="O121" s="9" t="n">
         <v>100.843202</v>
@@ -9815,7 +9815,7 @@
         <v>99.052217</v>
       </c>
       <c r="N122" s="6" t="n">
-        <v>100.451891</v>
+        <v>100.451146</v>
       </c>
       <c r="O122" s="6" t="n">
         <v>100.555799</v>
@@ -9897,7 +9897,7 @@
         <v>98.885307</v>
       </c>
       <c r="N123" s="9" t="n">
-        <v>100.375072</v>
+        <v>100.374445</v>
       </c>
       <c r="O123" s="9" t="n">
         <v>100.409143</v>
@@ -9979,7 +9979,7 @@
         <v>98.75078499999999</v>
       </c>
       <c r="N124" s="6" t="n">
-        <v>100.293934</v>
+        <v>100.293431</v>
       </c>
       <c r="O124" s="6" t="n">
         <v>100.407487</v>
@@ -10061,7 +10061,7 @@
         <v>98.654674</v>
       </c>
       <c r="N125" s="9" t="n">
-        <v>100.202263</v>
+        <v>100.201901</v>
       </c>
       <c r="O125" s="9" t="n">
         <v>100.508659</v>
@@ -10143,7 +10143,7 @@
         <v>98.60885399999999</v>
       </c>
       <c r="N126" s="6" t="n">
-        <v>100.118217</v>
+        <v>100.117984</v>
       </c>
       <c r="O126" s="6" t="n">
         <v>100.649017</v>
@@ -10225,7 +10225,7 @@
         <v>98.66471900000001</v>
       </c>
       <c r="N127" s="9" t="n">
-        <v>100.061134</v>
+        <v>100.060988</v>
       </c>
       <c r="O127" s="9" t="n">
         <v>100.780785</v>
@@ -10307,7 +10307,7 @@
         <v>98.840311</v>
       </c>
       <c r="N128" s="6" t="n">
-        <v>100.056587</v>
+        <v>100.056448</v>
       </c>
       <c r="O128" s="6" t="n">
         <v>100.890357</v>
@@ -10389,7 +10389,7 @@
         <v>99.108677</v>
       </c>
       <c r="N129" s="9" t="n">
-        <v>100.111083</v>
+        <v>100.110861</v>
       </c>
       <c r="O129" s="9" t="n">
         <v>100.951289</v>
@@ -10471,7 +10471,7 @@
         <v>99.396039</v>
       </c>
       <c r="N130" s="6" t="n">
-        <v>100.224766</v>
+        <v>100.22437</v>
       </c>
       <c r="O130" s="6" t="n">
         <v>100.975265</v>
@@ -10553,7 +10553,7 @@
         <v>99.638379</v>
       </c>
       <c r="N131" s="9" t="n">
-        <v>100.371558</v>
+        <v>100.370938</v>
       </c>
       <c r="O131" s="9" t="n">
         <v>100.954664</v>
@@ -10635,7 +10635,7 @@
         <v>99.768208</v>
       </c>
       <c r="N132" s="6" t="n">
-        <v>100.524099</v>
+        <v>100.523246</v>
       </c>
       <c r="O132" s="6" t="n">
         <v>100.947405</v>
@@ -10717,7 +10717,7 @@
         <v>99.74003500000001</v>
       </c>
       <c r="N133" s="9" t="n">
-        <v>100.656981</v>
+        <v>100.655925</v>
       </c>
       <c r="O133" s="9" t="n">
         <v>101.000878</v>
@@ -10799,7 +10799,7 @@
         <v>99.62265499999999</v>
       </c>
       <c r="N134" s="6" t="n">
-        <v>100.739497</v>
+        <v>100.738316</v>
       </c>
       <c r="O134" s="6" t="n">
         <v>101.065809</v>
@@ -10881,7 +10881,7 @@
         <v>99.485354</v>
       </c>
       <c r="N135" s="9" t="n">
-        <v>100.75915</v>
+        <v>100.757939</v>
       </c>
       <c r="O135" s="9" t="n">
         <v>101.068738</v>
@@ -10963,7 +10963,7 @@
         <v>99.29503699999999</v>
       </c>
       <c r="N136" s="6" t="n">
-        <v>100.717678</v>
+        <v>100.716531</v>
       </c>
       <c r="O136" s="6" t="n">
         <v>100.934708</v>
@@ -11045,7 +11045,7 @@
         <v>99.09972999999999</v>
       </c>
       <c r="N137" s="9" t="n">
-        <v>100.638116</v>
+        <v>100.63709</v>
       </c>
       <c r="O137" s="9" t="n">
         <v>100.719173</v>
@@ -11127,7 +11127,7 @@
         <v>98.907917</v>
       </c>
       <c r="N138" s="6" t="n">
-        <v>100.529789</v>
+        <v>100.528929</v>
       </c>
       <c r="O138" s="6" t="n">
         <v>100.479194</v>
@@ -11209,7 +11209,7 @@
         <v>98.714609</v>
       </c>
       <c r="N139" s="9" t="n">
-        <v>100.417675</v>
+        <v>100.416987</v>
       </c>
       <c r="O139" s="9" t="n">
         <v>100.282492</v>
@@ -11291,7 +11291,7 @@
         <v>98.531734</v>
       </c>
       <c r="N140" s="6" t="n">
-        <v>100.326796</v>
+        <v>100.326247</v>
       </c>
       <c r="O140" s="6" t="n">
         <v>100.143109</v>
@@ -11373,7 +11373,7 @@
         <v>98.342826</v>
       </c>
       <c r="N141" s="9" t="n">
-        <v>100.276567</v>
+        <v>100.276095</v>
       </c>
       <c r="O141" s="9" t="n">
         <v>100.081037</v>
@@ -11455,7 +11455,7 @@
         <v>98.22292299999999</v>
       </c>
       <c r="N142" s="6" t="n">
-        <v>100.259426</v>
+        <v>100.25898</v>
       </c>
       <c r="O142" s="6" t="n">
         <v>100.088563</v>
@@ -11537,7 +11537,7 @@
         <v>98.266854</v>
       </c>
       <c r="N143" s="9" t="n">
-        <v>100.262412</v>
+        <v>100.261962</v>
       </c>
       <c r="O143" s="9" t="n">
         <v>100.126727</v>
@@ -11619,7 +11619,7 @@
         <v>98.517979</v>
       </c>
       <c r="N144" s="6" t="n">
-        <v>100.28414</v>
+        <v>100.283657</v>
       </c>
       <c r="O144" s="6" t="n">
         <v>100.157413</v>
@@ -11701,7 +11701,7 @@
         <v>98.874441</v>
       </c>
       <c r="N145" s="9" t="n">
-        <v>100.316903</v>
+        <v>100.31637</v>
       </c>
       <c r="O145" s="9" t="n">
         <v>100.162456</v>
@@ -11783,7 +11783,7 @@
         <v>99.17998900000001</v>
       </c>
       <c r="N146" s="6" t="n">
-        <v>100.362035</v>
+        <v>100.361433</v>
       </c>
       <c r="O146" s="6" t="n">
         <v>100.11474</v>
@@ -11865,7 +11865,7 @@
         <v>99.3807</v>
       </c>
       <c r="N147" s="9" t="n">
-        <v>100.426178</v>
+        <v>100.425478</v>
       </c>
       <c r="O147" s="9" t="n">
         <v>99.996447</v>
@@ -11947,7 +11947,7 @@
         <v>99.450846</v>
       </c>
       <c r="N148" s="6" t="n">
-        <v>100.514866</v>
+        <v>100.51403</v>
       </c>
       <c r="O148" s="6" t="n">
         <v>99.90760299999999</v>
@@ -12029,7 +12029,7 @@
         <v>99.415256</v>
       </c>
       <c r="N149" s="9" t="n">
-        <v>100.612528</v>
+        <v>100.611543</v>
       </c>
       <c r="O149" s="9" t="n">
         <v>99.89572</v>
@@ -12111,7 +12111,7 @@
         <v>99.312742</v>
       </c>
       <c r="N150" s="6" t="n">
-        <v>100.733488</v>
+        <v>100.732318</v>
       </c>
       <c r="O150" s="6" t="n">
         <v>99.943676</v>
@@ -12193,7 +12193,7 @@
         <v>99.161259</v>
       </c>
       <c r="N151" s="9" t="n">
-        <v>100.875636</v>
+        <v>100.874249</v>
       </c>
       <c r="O151" s="9" t="n">
         <v>100.004613</v>
@@ -12275,7 +12275,7 @@
         <v>98.96308999999999</v>
       </c>
       <c r="N152" s="6" t="n">
-        <v>101.01503</v>
+        <v>101.01343</v>
       </c>
       <c r="O152" s="6" t="n">
         <v>100.036713</v>
@@ -12357,7 +12357,7 @@
         <v>98.756714</v>
       </c>
       <c r="N153" s="9" t="n">
-        <v>101.118198</v>
+        <v>101.11644</v>
       </c>
       <c r="O153" s="9" t="n">
         <v>100.027152</v>
@@ -12439,7 +12439,7 @@
         <v>98.55176400000001</v>
       </c>
       <c r="N154" s="6" t="n">
-        <v>101.172073</v>
+        <v>101.170233</v>
       </c>
       <c r="O154" s="6" t="n">
         <v>99.931394</v>
@@ -12521,7 +12521,7 @@
         <v>98.337878</v>
       </c>
       <c r="N155" s="9" t="n">
-        <v>101.173279</v>
+        <v>101.171436</v>
       </c>
       <c r="O155" s="9" t="n">
         <v>99.727223</v>
@@ -12603,7 +12603,7 @@
         <v>98.14555799999999</v>
       </c>
       <c r="N156" s="6" t="n">
-        <v>101.129047</v>
+        <v>101.127271</v>
       </c>
       <c r="O156" s="6" t="n">
         <v>99.44432</v>
@@ -12685,7 +12685,7 @@
         <v>98.01981000000001</v>
       </c>
       <c r="N157" s="9" t="n">
-        <v>101.044343</v>
+        <v>101.042696</v>
       </c>
       <c r="O157" s="9" t="n">
         <v>99.10198800000001</v>
@@ -12767,7 +12767,7 @@
         <v>98.04830699999999</v>
       </c>
       <c r="N158" s="6" t="n">
-        <v>100.940255</v>
+        <v>100.938767</v>
       </c>
       <c r="O158" s="6" t="n">
         <v>98.757592</v>
@@ -12849,7 +12849,7 @@
         <v>98.232855</v>
       </c>
       <c r="N159" s="9" t="n">
-        <v>100.826183</v>
+        <v>100.824871</v>
       </c>
       <c r="O159" s="9" t="n">
         <v>98.467595</v>
@@ -12931,7 +12931,7 @@
         <v>98.499606</v>
       </c>
       <c r="N160" s="6" t="n">
-        <v>100.694548</v>
+        <v>100.693439</v>
       </c>
       <c r="O160" s="6" t="n">
         <v>98.270861</v>
@@ -13013,7 +13013,7 @@
         <v>98.749639</v>
       </c>
       <c r="N161" s="9" t="n">
-        <v>100.551939</v>
+        <v>100.551053</v>
       </c>
       <c r="O161" s="9" t="n">
         <v>98.152787</v>
@@ -13095,7 +13095,7 @@
         <v>98.996313</v>
       </c>
       <c r="N162" s="6" t="n">
-        <v>100.41285</v>
+        <v>100.412185</v>
       </c>
       <c r="O162" s="6" t="n">
         <v>98.09493399999999</v>
@@ -13177,7 +13177,7 @@
         <v>99.203872</v>
       </c>
       <c r="N163" s="9" t="n">
-        <v>100.31019</v>
+        <v>100.309694</v>
       </c>
       <c r="O163" s="9" t="n">
         <v>98.071708</v>
@@ -13259,7 +13259,7 @@
         <v>99.3334</v>
       </c>
       <c r="N164" s="6" t="n">
-        <v>100.23428</v>
+        <v>100.233917</v>
       </c>
       <c r="O164" s="6" t="n">
         <v>98.09358899999999</v>
@@ -13341,7 +13341,7 @@
         <v>99.394841</v>
       </c>
       <c r="N165" s="9" t="n">
-        <v>100.17566</v>
+        <v>100.175406</v>
       </c>
       <c r="O165" s="9" t="n">
         <v>98.152066</v>
@@ -13423,7 +13423,7 @@
         <v>99.45854799999999</v>
       </c>
       <c r="N166" s="6" t="n">
-        <v>100.113965</v>
+        <v>100.113812</v>
       </c>
       <c r="O166" s="6" t="n">
         <v>98.262688</v>
@@ -13505,7 +13505,7 @@
         <v>99.530917</v>
       </c>
       <c r="N167" s="9" t="n">
-        <v>100.040907</v>
+        <v>100.040858</v>
       </c>
       <c r="O167" s="9" t="n">
         <v>98.444676</v>
@@ -13587,7 +13587,7 @@
         <v>99.63661</v>
       </c>
       <c r="N168" s="6" t="n">
-        <v>99.94879</v>
+        <v>99.94884500000001</v>
       </c>
       <c r="O168" s="6" t="n">
         <v>98.62534100000001</v>
@@ -13669,7 +13669,7 @@
         <v>99.742277</v>
       </c>
       <c r="N169" s="9" t="n">
-        <v>99.84265600000001</v>
+        <v>99.842817</v>
       </c>
       <c r="O169" s="9" t="n">
         <v>98.78278299999999</v>
@@ -13751,7 +13751,7 @@
         <v>99.786051</v>
       </c>
       <c r="N170" s="6" t="n">
-        <v>99.780244</v>
+        <v>99.78045299999999</v>
       </c>
       <c r="O170" s="6" t="n">
         <v>98.92977</v>
@@ -13833,7 +13833,7 @@
         <v>99.756052</v>
       </c>
       <c r="N171" s="9" t="n">
-        <v>99.774478</v>
+        <v>99.774691</v>
       </c>
       <c r="O171" s="9" t="n">
         <v>99.083189</v>
@@ -13915,7 +13915,7 @@
         <v>99.681265</v>
       </c>
       <c r="N172" s="6" t="n">
-        <v>99.842524</v>
+        <v>99.842652</v>
       </c>
       <c r="O172" s="6" t="n">
         <v>99.23689299999999</v>
@@ -13997,7 +13997,7 @@
         <v>99.562348</v>
       </c>
       <c r="N173" s="9" t="n">
-        <v>100.003542</v>
+        <v>100.003455</v>
       </c>
       <c r="O173" s="9" t="n">
         <v>99.378972</v>
@@ -14079,7 +14079,7 @@
         <v>99.384709</v>
       </c>
       <c r="N174" s="6" t="n">
-        <v>100.217521</v>
+        <v>100.21716</v>
       </c>
       <c r="O174" s="6" t="n">
         <v>99.55556900000001</v>
@@ -14161,7 +14161,7 @@
         <v>99.150368</v>
       </c>
       <c r="N175" s="9" t="n">
-        <v>100.433683</v>
+        <v>100.433036</v>
       </c>
       <c r="O175" s="9" t="n">
         <v>99.762925</v>
@@ -14243,7 +14243,7 @@
         <v>98.89662800000001</v>
       </c>
       <c r="N176" s="6" t="n">
-        <v>100.617396</v>
+        <v>100.616494</v>
       </c>
       <c r="O176" s="6" t="n">
         <v>99.946068</v>
@@ -14325,7 +14325,7 @@
         <v>98.652308</v>
       </c>
       <c r="N177" s="9" t="n">
-        <v>100.772735</v>
+        <v>100.771587</v>
       </c>
       <c r="O177" s="9" t="n">
         <v>100.037299</v>
@@ -14407,7 +14407,7 @@
         <v>98.441457</v>
       </c>
       <c r="N178" s="6" t="n">
-        <v>100.893156</v>
+        <v>100.891778</v>
       </c>
       <c r="O178" s="6" t="n">
         <v>100.024924</v>
@@ -14489,7 +14489,7 @@
         <v>98.321654</v>
       </c>
       <c r="N179" s="9" t="n">
-        <v>100.973359</v>
+        <v>100.971814</v>
       </c>
       <c r="O179" s="9" t="n">
         <v>99.93726100000001</v>
@@ -14571,7 +14571,7 @@
         <v>98.30812400000001</v>
       </c>
       <c r="N180" s="6" t="n">
-        <v>101.003453</v>
+        <v>101.001825</v>
       </c>
       <c r="O180" s="6" t="n">
         <v>99.842291</v>
@@ -14653,7 +14653,7 @@
         <v>98.41171900000001</v>
       </c>
       <c r="N181" s="9" t="n">
-        <v>100.979953</v>
+        <v>100.978331</v>
       </c>
       <c r="O181" s="9" t="n">
         <v>99.766375</v>
@@ -14735,7 +14735,7 @@
         <v>98.657927</v>
       </c>
       <c r="N182" s="6" t="n">
-        <v>100.904273</v>
+        <v>100.902762</v>
       </c>
       <c r="O182" s="6" t="n">
         <v>99.68075399999999</v>
@@ -14817,7 +14817,7 @@
         <v>99.03360000000001</v>
       </c>
       <c r="N183" s="9" t="n">
-        <v>100.764799</v>
+        <v>100.763539</v>
       </c>
       <c r="O183" s="9" t="n">
         <v>99.531198</v>
@@ -14899,7 +14899,7 @@
         <v>99.52918699999999</v>
       </c>
       <c r="N184" s="6" t="n">
-        <v>100.521356</v>
+        <v>100.520509</v>
       </c>
       <c r="O184" s="6" t="n">
         <v>99.232979</v>
@@ -14981,7 +14981,7 @@
         <v>100.139348</v>
       </c>
       <c r="N185" s="9" t="n">
-        <v>100.154718</v>
+        <v>100.154459</v>
       </c>
       <c r="O185" s="9" t="n">
         <v>98.78161900000001</v>
@@ -15063,7 +15063,7 @@
         <v>100.873549</v>
       </c>
       <c r="N186" s="6" t="n">
-        <v>99.687623</v>
+        <v>99.688078</v>
       </c>
       <c r="O186" s="6" t="n">
         <v>98.204131</v>
@@ -15145,7 +15145,7 @@
         <v>101.692318</v>
       </c>
       <c r="N187" s="9" t="n">
-        <v>99.18918600000001</v>
+        <v>99.19038999999999</v>
       </c>
       <c r="O187" s="9" t="n">
         <v>97.60439100000001</v>
@@ -15227,7 +15227,7 @@
         <v>102.519496</v>
       </c>
       <c r="N188" s="6" t="n">
-        <v>98.73203599999999</v>
+        <v>98.73393299999999</v>
       </c>
       <c r="O188" s="6" t="n">
         <v>97.129926</v>
@@ -15309,7 +15309,7 @@
         <v>103.277782</v>
       </c>
       <c r="N189" s="9" t="n">
-        <v>98.353084</v>
+        <v>98.35557900000001</v>
       </c>
       <c r="O189" s="9" t="n">
         <v>96.93074900000001</v>
@@ -15391,7 +15391,7 @@
         <v>103.904388</v>
       </c>
       <c r="N190" s="6" t="n">
-        <v>98.10048399999999</v>
+        <v>98.10335600000001</v>
       </c>
       <c r="O190" s="6" t="n">
         <v>97.054075</v>
@@ -15473,7 +15473,7 @@
         <v>104.355133</v>
       </c>
       <c r="N191" s="9" t="n">
-        <v>97.964465</v>
+        <v>97.967546</v>
       </c>
       <c r="O191" s="9" t="n">
         <v>97.463922</v>
@@ -15555,7 +15555,7 @@
         <v>104.610929</v>
       </c>
       <c r="N192" s="6" t="n">
-        <v>97.923315</v>
+        <v>97.926462</v>
       </c>
       <c r="O192" s="6" t="n">
         <v>98.040933</v>
@@ -15637,7 +15637,7 @@
         <v>104.677479</v>
       </c>
       <c r="N193" s="9" t="n">
-        <v>97.957207</v>
+        <v>97.960284</v>
       </c>
       <c r="O193" s="9" t="n">
         <v>98.690287</v>
@@ -15719,7 +15719,7 @@
         <v>104.56857</v>
       </c>
       <c r="N194" s="6" t="n">
-        <v>98.024897</v>
+        <v>98.027846</v>
       </c>
       <c r="O194" s="6" t="n">
         <v>99.351623</v>
@@ -15801,7 +15801,7 @@
         <v>104.333847</v>
       </c>
       <c r="N195" s="9" t="n">
-        <v>98.115427</v>
+        <v>98.11821500000001</v>
       </c>
       <c r="O195" s="9" t="n">
         <v>99.99029899999999</v>
@@ -15883,7 +15883,7 @@
         <v>104.025174</v>
       </c>
       <c r="N196" s="6" t="n">
-        <v>98.242285</v>
+        <v>98.24487000000001</v>
       </c>
       <c r="O196" s="6" t="n">
         <v>100.59591</v>
@@ -15965,7 +15965,7 @@
         <v>103.675995</v>
       </c>
       <c r="N197" s="9" t="n">
-        <v>98.401079</v>
+        <v>98.403447</v>
       </c>
       <c r="O197" s="9" t="n">
         <v>101.11932</v>
@@ -16047,7 +16047,7 @@
         <v>103.297125</v>
       </c>
       <c r="N198" s="6" t="n">
-        <v>98.574071</v>
+        <v>98.576204</v>
       </c>
       <c r="O198" s="6" t="n">
         <v>101.512671</v>
@@ -16129,7 +16129,7 @@
         <v>102.925279</v>
       </c>
       <c r="N199" s="9" t="n">
-        <v>98.748597</v>
+        <v>98.750491</v>
       </c>
       <c r="O199" s="9" t="n">
         <v>101.759907</v>
@@ -16211,7 +16211,7 @@
         <v>102.588102</v>
       </c>
       <c r="N200" s="6" t="n">
-        <v>98.90607799999999</v>
+        <v>98.90775499999999</v>
       </c>
       <c r="O200" s="6" t="n">
         <v>101.911364</v>
@@ -16293,7 +16293,7 @@
         <v>102.308422</v>
       </c>
       <c r="N201" s="9" t="n">
-        <v>99.043278</v>
+        <v>99.04475499999999</v>
       </c>
       <c r="O201" s="9" t="n">
         <v>101.976341</v>
@@ -16375,7 +16375,7 @@
         <v>102.103506</v>
       </c>
       <c r="N202" s="6" t="n">
-        <v>99.152389</v>
+        <v>99.153679</v>
       </c>
       <c r="O202" s="6" t="n">
         <v>101.951771</v>
@@ -16457,7 +16457,7 @@
         <v>101.991072</v>
       </c>
       <c r="N203" s="9" t="n">
-        <v>99.23554900000001</v>
+        <v>99.236716</v>
       </c>
       <c r="O203" s="9" t="n">
         <v>101.830243</v>
@@ -16539,7 +16539,7 @@
         <v>101.963554</v>
       </c>
       <c r="N204" s="6" t="n">
-        <v>99.32303899999999</v>
+        <v>99.32405</v>
       </c>
       <c r="O204" s="6" t="n">
         <v>101.658815</v>
@@ -16621,7 +16621,7 @@
         <v>102.020364</v>
       </c>
       <c r="N205" s="9" t="n">
-        <v>99.406631</v>
+        <v>99.407473</v>
       </c>
       <c r="O205" s="9" t="n">
         <v>101.461386</v>
@@ -16703,7 +16703,7 @@
         <v>102.143063</v>
       </c>
       <c r="N206" s="6" t="n">
-        <v>99.47515300000001</v>
+        <v>99.475847</v>
       </c>
       <c r="O206" s="6" t="n">
         <v>101.2378</v>
@@ -16785,7 +16785,7 @@
         <v>102.247821</v>
       </c>
       <c r="N207" s="9" t="n">
-        <v>99.52127</v>
+        <v>99.52188200000001</v>
       </c>
       <c r="O207" s="9" t="n">
         <v>101.030478</v>
@@ -16867,7 +16867,7 @@
         <v>102.251376</v>
       </c>
       <c r="N208" s="6" t="n">
-        <v>99.542169</v>
+        <v>99.542753</v>
       </c>
       <c r="O208" s="6" t="n">
         <v>100.894773</v>
@@ -16949,7 +16949,7 @@
         <v>102.13995</v>
       </c>
       <c r="N209" s="9" t="n">
-        <v>99.561707</v>
+        <v>99.56228400000001</v>
       </c>
       <c r="O209" s="9" t="n">
         <v>100.874089</v>
@@ -17031,7 +17031,7 @@
         <v>101.939874</v>
       </c>
       <c r="N210" s="6" t="n">
-        <v>99.61749500000001</v>
+        <v>99.618022</v>
       </c>
       <c r="O210" s="6" t="n">
         <v>100.947919</v>
@@ -17113,7 +17113,7 @@
         <v>101.692623</v>
       </c>
       <c r="N211" s="9" t="n">
-        <v>99.702364</v>
+        <v>99.70281900000001</v>
       </c>
       <c r="O211" s="9" t="n">
         <v>101.076858</v>
@@ -17195,7 +17195,7 @@
         <v>101.447255</v>
       </c>
       <c r="N212" s="6" t="n">
-        <v>99.80806</v>
+        <v>99.808397</v>
       </c>
       <c r="O212" s="6" t="n">
         <v>101.18498</v>
@@ -17277,7 +17277,7 @@
         <v>101.206618</v>
       </c>
       <c r="N213" s="9" t="n">
-        <v>99.920338</v>
+        <v>99.920496</v>
       </c>
       <c r="O213" s="9" t="n">
         <v>101.256925</v>
@@ -17359,7 +17359,7 @@
         <v>100.955874</v>
       </c>
       <c r="N214" s="6" t="n">
-        <v>100.031592</v>
+        <v>100.031551</v>
       </c>
       <c r="O214" s="6" t="n">
         <v>101.294384</v>
@@ -17441,7 +17441,7 @@
         <v>100.690255</v>
       </c>
       <c r="N215" s="9" t="n">
-        <v>100.143608</v>
+        <v>100.143371</v>
       </c>
       <c r="O215" s="9" t="n">
         <v>101.30859</v>
@@ -17523,7 +17523,7 @@
         <v>100.443555</v>
       </c>
       <c r="N216" s="6" t="n">
-        <v>100.24582</v>
+        <v>100.245406</v>
       </c>
       <c r="O216" s="6" t="n">
         <v>101.319354</v>
@@ -17605,7 +17605,7 @@
         <v>100.205651</v>
       </c>
       <c r="N217" s="9" t="n">
-        <v>100.332048</v>
+        <v>100.331473</v>
       </c>
       <c r="O217" s="9" t="n">
         <v>101.366923</v>
@@ -17687,7 +17687,7 @@
         <v>100.013222</v>
       </c>
       <c r="N218" s="6" t="n">
-        <v>100.406904</v>
+        <v>100.406185</v>
       </c>
       <c r="O218" s="6" t="n">
         <v>101.446717</v>
@@ -17769,7 +17769,7 @@
         <v>99.89183</v>
       </c>
       <c r="N219" s="9" t="n">
-        <v>100.472965</v>
+        <v>100.472125</v>
       </c>
       <c r="O219" s="9" t="n">
         <v>101.521993</v>
@@ -17851,7 +17851,7 @@
         <v>99.84460199999999</v>
       </c>
       <c r="N220" s="6" t="n">
-        <v>100.530378</v>
+        <v>100.529471</v>
       </c>
       <c r="O220" s="6" t="n">
         <v>101.56386</v>
@@ -17933,7 +17933,7 @@
         <v>99.84677600000001</v>
       </c>
       <c r="N221" s="9" t="n">
-        <v>100.572069</v>
+        <v>100.571143</v>
       </c>
       <c r="O221" s="9" t="n">
         <v>101.554706</v>
@@ -18015,7 +18015,7 @@
         <v>99.89017699999999</v>
       </c>
       <c r="N222" s="6" t="n">
-        <v>100.598634</v>
+        <v>100.597709</v>
       </c>
       <c r="O222" s="6" t="n">
         <v>101.490082</v>
@@ -18097,7 +18097,7 @@
         <v>99.93253799999999</v>
       </c>
       <c r="N223" s="9" t="n">
-        <v>100.595926</v>
+        <v>100.595021</v>
       </c>
       <c r="O223" s="9" t="n">
         <v>101.389847</v>
@@ -18179,7 +18179,7 @@
         <v>99.953468</v>
       </c>
       <c r="N224" s="6" t="n">
-        <v>100.556732</v>
+        <v>100.555884</v>
       </c>
       <c r="O224" s="6" t="n">
         <v>101.226108</v>
@@ -18261,7 +18261,7 @@
         <v>99.96740699999999</v>
       </c>
       <c r="N225" s="9" t="n">
-        <v>100.475153</v>
+        <v>100.474418</v>
       </c>
       <c r="O225" s="9" t="n">
         <v>100.996475</v>
@@ -18343,7 +18343,7 @@
         <v>100.000029</v>
       </c>
       <c r="N226" s="6" t="n">
-        <v>100.357043</v>
+        <v>100.356471</v>
       </c>
       <c r="O226" s="6" t="n">
         <v>100.767495</v>
@@ -18425,7 +18425,7 @@
         <v>100.0261</v>
       </c>
       <c r="N227" s="9" t="n">
-        <v>100.220583</v>
+        <v>100.220202</v>
       </c>
       <c r="O227" s="9" t="n">
         <v>100.566149</v>
@@ -18507,7 +18507,7 @@
         <v>100.013599</v>
       </c>
       <c r="N228" s="6" t="n">
-        <v>100.090112</v>
+        <v>100.089906</v>
       </c>
       <c r="O228" s="6" t="n">
         <v>100.375689</v>
@@ -18589,7 +18589,7 @@
         <v>99.97425</v>
       </c>
       <c r="N229" s="9" t="n">
-        <v>99.981256</v>
+        <v>99.981208</v>
       </c>
       <c r="O229" s="9" t="n">
         <v>100.1711</v>
@@ -18671,7 +18671,7 @@
         <v>99.924171</v>
       </c>
       <c r="N230" s="6" t="n">
-        <v>99.901003</v>
+        <v>99.90106299999999</v>
       </c>
       <c r="O230" s="6" t="n">
         <v>99.96679899999999</v>
@@ -18753,7 +18753,7 @@
         <v>99.85808400000001</v>
       </c>
       <c r="N231" s="9" t="n">
-        <v>99.84118100000001</v>
+        <v>99.841312</v>
       </c>
       <c r="O231" s="9" t="n">
         <v>99.766699</v>
@@ -18835,7 +18835,7 @@
         <v>99.759773</v>
       </c>
       <c r="N232" s="6" t="n">
-        <v>99.799001</v>
+        <v>99.799183</v>
       </c>
       <c r="O232" s="6" t="n">
         <v>99.570155</v>
@@ -18917,7 +18917,7 @@
         <v>99.640201</v>
       </c>
       <c r="N233" s="9" t="n">
-        <v>99.77095300000001</v>
+        <v>99.771214</v>
       </c>
       <c r="O233" s="9" t="n">
         <v>99.407647</v>
@@ -18999,7 +18999,7 @@
         <v>99.47417</v>
       </c>
       <c r="N234" s="6" t="n">
-        <v>99.77270900000001</v>
+        <v>99.77301300000001</v>
       </c>
       <c r="O234" s="6" t="n">
         <v>99.312195</v>
@@ -19081,7 +19081,7 @@
         <v>99.286716</v>
       </c>
       <c r="N235" s="9" t="n">
-        <v>99.814262</v>
+        <v>99.81453500000001</v>
       </c>
       <c r="O235" s="9" t="n">
         <v>99.309106</v>
@@ -19163,7 +19163,7 @@
         <v>99.06441700000001</v>
       </c>
       <c r="N236" s="6" t="n">
-        <v>99.89098199999999</v>
+        <v>99.891158</v>
       </c>
       <c r="O236" s="6" t="n">
         <v>99.40124900000001</v>
@@ -19245,7 +19245,7 @@
         <v>98.818839</v>
       </c>
       <c r="N237" s="9" t="n">
-        <v>99.988924</v>
+        <v>99.988962</v>
       </c>
       <c r="O237" s="9" t="n">
         <v>99.58260799999999</v>
@@ -19327,7 +19327,7 @@
         <v>98.577793</v>
       </c>
       <c r="N238" s="6" t="n">
-        <v>100.093805</v>
+        <v>100.093697</v>
       </c>
       <c r="O238" s="6" t="n">
         <v>99.785737</v>
@@ -19409,7 +19409,7 @@
         <v>98.38543900000001</v>
       </c>
       <c r="N239" s="9" t="n">
-        <v>100.193154</v>
+        <v>100.192889</v>
       </c>
       <c r="O239" s="9" t="n">
         <v>99.961455</v>
@@ -19491,7 +19491,7 @@
         <v>98.205269</v>
       </c>
       <c r="N240" s="6" t="n">
-        <v>100.285531</v>
+        <v>100.285093</v>
       </c>
       <c r="O240" s="6" t="n">
         <v>100.130032</v>
@@ -19573,7 +19573,7 @@
         <v>98.07752000000001</v>
       </c>
       <c r="N241" s="9" t="n">
-        <v>100.377911</v>
+        <v>100.377273</v>
       </c>
       <c r="O241" s="9" t="n">
         <v>100.27443</v>
@@ -19655,7 +19655,7 @@
         <v>97.999602</v>
       </c>
       <c r="N242" s="6" t="n">
-        <v>100.474494</v>
+        <v>100.473648</v>
       </c>
       <c r="O242" s="6" t="n">
         <v>100.421249</v>
@@ -19737,7 +19737,7 @@
         <v>97.988879</v>
       </c>
       <c r="N243" s="9" t="n">
-        <v>100.582905</v>
+        <v>100.581864</v>
       </c>
       <c r="O243" s="9" t="n">
         <v>100.588967</v>
@@ -19819,7 +19819,7 @@
         <v>98.032583</v>
       </c>
       <c r="N244" s="6" t="n">
-        <v>100.703875</v>
+        <v>100.702642</v>
       </c>
       <c r="O244" s="6" t="n">
         <v>100.745287</v>
@@ -19901,7 +19901,7 @@
         <v>98.108453</v>
       </c>
       <c r="N245" s="9" t="n">
-        <v>100.83703</v>
+        <v>100.835624</v>
       </c>
       <c r="O245" s="9" t="n">
         <v>100.881821</v>
@@ -19983,7 +19983,7 @@
         <v>98.194896</v>
       </c>
       <c r="N246" s="6" t="n">
-        <v>100.975501</v>
+        <v>100.973945</v>
       </c>
       <c r="O246" s="6" t="n">
         <v>100.992605</v>
@@ -20065,7 +20065,7 @@
         <v>98.287761</v>
       </c>
       <c r="N247" s="9" t="n">
-        <v>101.101968</v>
+        <v>101.100266</v>
       </c>
       <c r="O247" s="9" t="n">
         <v>101.037945</v>
@@ -20147,7 +20147,7 @@
         <v>98.370937</v>
       </c>
       <c r="N248" s="6" t="n">
-        <v>101.222493</v>
+        <v>101.220627</v>
       </c>
       <c r="O248" s="6" t="n">
         <v>101.058954</v>
@@ -20229,7 +20229,7 @@
         <v>98.432248</v>
       </c>
       <c r="N249" s="9" t="n">
-        <v>101.355417</v>
+        <v>101.353368</v>
       </c>
       <c r="O249" s="9" t="n">
         <v>101.056045</v>
@@ -20311,7 +20311,7 @@
         <v>98.43005599999999</v>
       </c>
       <c r="N250" s="6" t="n">
-        <v>101.494197</v>
+        <v>101.491925</v>
       </c>
       <c r="O250" s="6" t="n">
         <v>101.02356</v>
@@ -20393,7 +20393,7 @@
         <v>98.37163200000001</v>
       </c>
       <c r="N251" s="9" t="n">
-        <v>101.62275</v>
+        <v>101.620261</v>
       </c>
       <c r="O251" s="9" t="n">
         <v>100.989385</v>
@@ -20475,7 +20475,7 @@
         <v>98.306128</v>
       </c>
       <c r="N252" s="6" t="n">
-        <v>101.729905</v>
+        <v>101.727241</v>
       </c>
       <c r="O252" s="6" t="n">
         <v>100.901694</v>
@@ -20557,7 +20557,7 @@
         <v>98.244742</v>
       </c>
       <c r="N253" s="9" t="n">
-        <v>101.797824</v>
+        <v>101.795031</v>
       </c>
       <c r="O253" s="9" t="n">
         <v>100.774554</v>
@@ -20639,7 +20639,7 @@
         <v>98.145195</v>
       </c>
       <c r="N254" s="6" t="n">
-        <v>101.816273</v>
+        <v>101.813423</v>
       </c>
       <c r="O254" s="6" t="n">
         <v>100.595455</v>
@@ -20721,7 +20721,7 @@
         <v>98.03734799999999</v>
       </c>
       <c r="N255" s="9" t="n">
-        <v>101.782986</v>
+        <v>101.780165</v>
       </c>
       <c r="O255" s="9" t="n">
         <v>100.326067</v>
@@ -20803,7 +20803,7 @@
         <v>98.04486900000001</v>
       </c>
       <c r="N256" s="6" t="n">
-        <v>101.694376</v>
+        <v>101.691687</v>
       </c>
       <c r="O256" s="6" t="n">
         <v>100.000187</v>
@@ -20885,7 +20885,7 @@
         <v>98.186449</v>
       </c>
       <c r="N257" s="9" t="n">
-        <v>101.552745</v>
+        <v>101.550311</v>
       </c>
       <c r="O257" s="9" t="n">
         <v>99.614492</v>
@@ -20967,7 +20967,7 @@
         <v>98.41149900000001</v>
       </c>
       <c r="N258" s="6" t="n">
-        <v>101.364321</v>
+        <v>101.362216</v>
       </c>
       <c r="O258" s="6" t="n">
         <v>99.225587</v>
@@ -21049,7 +21049,7 @@
         <v>98.629608</v>
       </c>
       <c r="N259" s="9" t="n">
-        <v>101.156863</v>
+        <v>101.155111</v>
       </c>
       <c r="O259" s="9" t="n">
         <v>98.890961</v>
@@ -21131,7 +21131,7 @@
         <v>98.760966</v>
       </c>
       <c r="N260" s="6" t="n">
-        <v>100.943332</v>
+        <v>100.941924</v>
       </c>
       <c r="O260" s="6" t="n">
         <v>98.626341</v>
@@ -21213,7 +21213,7 @@
         <v>98.84054</v>
       </c>
       <c r="N261" s="9" t="n">
-        <v>100.714446</v>
+        <v>100.713381</v>
       </c>
       <c r="O261" s="9" t="n">
         <v>98.435362</v>
@@ -21295,7 +21295,7 @@
         <v>98.89628399999999</v>
       </c>
       <c r="N262" s="6" t="n">
-        <v>100.47235</v>
+        <v>100.471632</v>
       </c>
       <c r="O262" s="6" t="n">
         <v>98.348848</v>
@@ -21377,7 +21377,7 @@
         <v>98.909319</v>
       </c>
       <c r="N263" s="9" t="n">
-        <v>100.240886</v>
+        <v>100.240478</v>
       </c>
       <c r="O263" s="9" t="n">
         <v>98.328559</v>
@@ -21459,7 +21459,7 @@
         <v>98.925146</v>
       </c>
       <c r="N264" s="6" t="n">
-        <v>100.034684</v>
+        <v>100.034526</v>
       </c>
       <c r="O264" s="6" t="n">
         <v>98.366394</v>
@@ -21541,7 +21541,7 @@
         <v>98.98018399999999</v>
       </c>
       <c r="N265" s="9" t="n">
-        <v>99.867028</v>
+        <v>99.86706700000001</v>
       </c>
       <c r="O265" s="9" t="n">
         <v>98.42098</v>
@@ -21623,7 +21623,7 @@
         <v>99.117932</v>
       </c>
       <c r="N266" s="6" t="n">
-        <v>99.733161</v>
+        <v>99.733389</v>
       </c>
       <c r="O266" s="6" t="n">
         <v>98.467034</v>
@@ -21705,7 +21705,7 @@
         <v>99.318129</v>
       </c>
       <c r="N267" s="9" t="n">
-        <v>99.62600999999999</v>
+        <v>99.626424</v>
       </c>
       <c r="O267" s="9" t="n">
         <v>98.554562</v>
@@ -21787,7 +21787,7 @@
         <v>99.514905</v>
       </c>
       <c r="N268" s="6" t="n">
-        <v>99.54742299999999</v>
+        <v>99.548011</v>
       </c>
       <c r="O268" s="6" t="n">
         <v>98.693995</v>
@@ -21869,7 +21869,7 @@
         <v>99.68657399999999</v>
       </c>
       <c r="N269" s="9" t="n">
-        <v>99.50642000000001</v>
+        <v>99.507159</v>
       </c>
       <c r="O269" s="9" t="n">
         <v>98.90407399999999</v>
@@ -21951,7 +21951,7 @@
         <v>99.78200699999999</v>
       </c>
       <c r="N270" s="6" t="n">
-        <v>99.50514200000001</v>
+        <v>99.50595800000001</v>
       </c>
       <c r="O270" s="6" t="n">
         <v>99.156852</v>
@@ -22033,7 +22033,7 @@
         <v>99.798723</v>
       </c>
       <c r="N271" s="9" t="n">
-        <v>99.54633</v>
+        <v>99.547132</v>
       </c>
       <c r="O271" s="9" t="n">
         <v>99.415038</v>
@@ -22115,7 +22115,7 @@
         <v>99.78326300000001</v>
       </c>
       <c r="N272" s="6" t="n">
-        <v>99.59899</v>
+        <v>99.599718</v>
       </c>
       <c r="O272" s="6" t="n">
         <v>99.61366700000001</v>
@@ -22197,7 +22197,7 @@
         <v>99.737747</v>
       </c>
       <c r="N273" s="9" t="n">
-        <v>99.632284</v>
+        <v>99.632903</v>
       </c>
       <c r="O273" s="9" t="n">
         <v>99.693254</v>
@@ -22279,7 +22279,7 @@
         <v>99.674541</v>
       </c>
       <c r="N274" s="6" t="n">
-        <v>99.64018299999999</v>
+        <v>99.640725</v>
       </c>
       <c r="O274" s="6" t="n">
         <v>99.658778</v>
@@ -22361,7 +22361,7 @@
         <v>99.606342</v>
       </c>
       <c r="N275" s="9" t="n">
-        <v>99.616845</v>
+        <v>99.617377</v>
       </c>
       <c r="O275" s="9" t="n">
         <v>99.51366</v>
@@ -22443,7 +22443,7 @@
         <v>99.55954199999999</v>
       </c>
       <c r="N276" s="6" t="n">
-        <v>99.56753999999999</v>
+        <v>99.568095</v>
       </c>
       <c r="O276" s="6" t="n">
         <v>99.328683</v>
@@ -22525,7 +22525,7 @@
         <v>99.489768</v>
       </c>
       <c r="N277" s="9" t="n">
-        <v>99.494981</v>
+        <v>99.4956</v>
       </c>
       <c r="O277" s="9" t="n">
         <v>99.16018800000001</v>
@@ -22607,7 +22607,7 @@
         <v>99.39833299999999</v>
       </c>
       <c r="N278" s="6" t="n">
-        <v>99.40487899999999</v>
+        <v>99.405604</v>
       </c>
       <c r="O278" s="6" t="n">
         <v>99.03583500000001</v>
@@ -22689,7 +22689,7 @@
         <v>99.28212600000001</v>
       </c>
       <c r="N279" s="9" t="n">
-        <v>99.30386300000001</v>
+        <v>99.304765</v>
       </c>
       <c r="O279" s="9" t="n">
         <v>98.952285</v>
@@ -22771,7 +22771,7 @@
         <v>99.192285</v>
       </c>
       <c r="N280" s="6" t="n">
-        <v>99.206407</v>
+        <v>99.2075</v>
       </c>
       <c r="O280" s="6" t="n">
         <v>98.904871</v>
@@ -22853,7 +22853,7 @@
         <v>99.15255500000001</v>
       </c>
       <c r="N281" s="9" t="n">
-        <v>99.118302</v>
+        <v>99.119569</v>
       </c>
       <c r="O281" s="9" t="n">
         <v>98.857575</v>
@@ -22935,7 +22935,7 @@
         <v>99.21113099999999</v>
       </c>
       <c r="N282" s="6" t="n">
-        <v>99.04019</v>
+        <v>99.041619</v>
       </c>
       <c r="O282" s="6" t="n">
         <v>98.800386</v>
@@ -23017,7 +23017,7 @@
         <v>99.366085</v>
       </c>
       <c r="N283" s="9" t="n">
-        <v>98.96835299999999</v>
+        <v>98.96995800000001</v>
       </c>
       <c r="O283" s="9" t="n">
         <v>98.756376</v>
@@ -23099,7 +23099,7 @@
         <v>99.617942</v>
       </c>
       <c r="N284" s="6" t="n">
-        <v>98.902925</v>
+        <v>98.90468</v>
       </c>
       <c r="O284" s="6" t="n">
         <v>98.731526</v>
@@ -23181,7 +23181,7 @@
         <v>99.94105399999999</v>
       </c>
       <c r="N285" s="9" t="n">
-        <v>98.83462900000001</v>
+        <v>98.83648700000001</v>
       </c>
       <c r="O285" s="9" t="n">
         <v>98.77581600000001</v>
@@ -23263,7 +23263,7 @@
         <v>100.316748</v>
       </c>
       <c r="N286" s="6" t="n">
-        <v>98.76460299999999</v>
+        <v>98.76652199999999</v>
       </c>
       <c r="O286" s="6" t="n">
         <v>98.86663900000001</v>
@@ -23345,7 +23345,7 @@
         <v>100.734119</v>
       </c>
       <c r="N287" s="9" t="n">
-        <v>98.707785</v>
+        <v>98.709718</v>
       </c>
       <c r="O287" s="9" t="n">
         <v>99.039494</v>
@@ -23427,7 +23427,7 @@
         <v>101.12405</v>
       </c>
       <c r="N288" s="6" t="n">
-        <v>98.672189</v>
+        <v>98.67411800000001</v>
       </c>
       <c r="O288" s="6" t="n">
         <v>99.24391199999999</v>
@@ -23509,7 +23509,7 @@
         <v>101.451229</v>
       </c>
       <c r="N289" s="9" t="n">
-        <v>98.660612</v>
+        <v>98.66251800000001</v>
       </c>
       <c r="O289" s="9" t="n">
         <v>99.45800699999999</v>
@@ -23591,7 +23591,7 @@
         <v>101.681369</v>
       </c>
       <c r="N290" s="6" t="n">
-        <v>98.68392299999999</v>
+        <v>98.685772</v>
       </c>
       <c r="O290" s="6" t="n">
         <v>99.697919</v>
@@ -23673,7 +23673,7 @@
         <v>101.821471</v>
       </c>
       <c r="N291" s="9" t="n">
-        <v>98.743408</v>
+        <v>98.74519100000001</v>
       </c>
       <c r="O291" s="9" t="n">
         <v>99.95479</v>
@@ -23755,7 +23755,7 @@
         <v>101.89435</v>
       </c>
       <c r="N292" s="6" t="n">
-        <v>98.829741</v>
+        <v>98.83146000000001</v>
       </c>
       <c r="O292" s="6" t="n">
         <v>100.185889</v>
@@ -23837,7 +23837,7 @@
         <v>101.923056</v>
       </c>
       <c r="N293" s="9" t="n">
-        <v>98.932936</v>
+        <v>98.934561</v>
       </c>
       <c r="O293" s="9" t="n">
         <v>100.399319</v>
@@ -23919,7 +23919,7 @@
         <v>101.956305</v>
       </c>
       <c r="N294" s="6" t="n">
-        <v>99.047489</v>
+        <v>99.04898300000001</v>
       </c>
       <c r="O294" s="6" t="n">
         <v>100.593126</v>
@@ -24003,7 +24003,7 @@
         <v>102.002517</v>
       </c>
       <c r="N295" s="9" t="n">
-        <v>99.17718000000001</v>
+        <v>99.17849699999999</v>
       </c>
       <c r="O295" s="9" t="n">
         <v>100.782798</v>
@@ -24087,7 +24087,7 @@
         <v>102.03522</v>
       </c>
       <c r="N296" s="6" t="n">
-        <v>99.305249</v>
+        <v>99.30637400000001</v>
       </c>
       <c r="O296" s="6" t="n">
         <v>100.962147</v>
@@ -24171,7 +24171,7 @@
         <v>102.031589</v>
       </c>
       <c r="N297" s="9" t="n">
-        <v>99.420963</v>
+        <v>99.42188299999999</v>
       </c>
       <c r="O297" s="9" t="n">
         <v>101.09328</v>
@@ -24255,7 +24255,7 @@
         <v>102.00133</v>
       </c>
       <c r="N298" s="6" t="n">
-        <v>99.51691700000001</v>
+        <v>99.517658</v>
       </c>
       <c r="O298" s="6" t="n">
         <v>101.134342</v>
@@ -24339,7 +24339,7 @@
         <v>101.958693</v>
       </c>
       <c r="N299" s="9" t="n">
-        <v>99.580827</v>
+        <v>99.581422</v>
       </c>
       <c r="O299" s="9" t="n">
         <v>101.083115</v>
@@ -24423,7 +24423,7 @@
         <v>101.882685</v>
       </c>
       <c r="N300" s="6" t="n">
-        <v>99.624262</v>
+        <v>99.62473799999999</v>
       </c>
       <c r="O300" s="6" t="n">
         <v>100.977641</v>
@@ -24507,7 +24507,7 @@
         <v>101.775364</v>
       </c>
       <c r="N301" s="9" t="n">
-        <v>99.657555</v>
+        <v>99.657937</v>
       </c>
       <c r="O301" s="9" t="n">
         <v>100.846366</v>
@@ -24591,7 +24591,7 @@
         <v>101.607396</v>
       </c>
       <c r="N302" s="6" t="n">
-        <v>99.693719</v>
+        <v>99.69403200000001</v>
       </c>
       <c r="O302" s="6" t="n">
         <v>100.711857</v>
@@ -24675,7 +24675,7 @@
         <v>101.426346</v>
       </c>
       <c r="N303" s="9" t="n">
-        <v>99.744255</v>
+        <v>99.744525</v>
       </c>
       <c r="O303" s="9" t="n">
         <v>100.573441</v>
@@ -24759,7 +24759,7 @@
         <v>101.27164</v>
       </c>
       <c r="N304" s="6" t="n">
-        <v>99.794479</v>
+        <v>99.794731</v>
       </c>
       <c r="O304" s="6" t="n">
         <v>100.483985</v>
@@ -24843,7 +24843,7 @@
         <v>101.117912</v>
       </c>
       <c r="N305" s="9" t="n">
-        <v>99.821991</v>
+        <v>99.82226900000001</v>
       </c>
       <c r="O305" s="9" t="n">
         <v>100.431373</v>
@@ -24927,7 +24927,7 @@
         <v>100.974746</v>
       </c>
       <c r="N306" s="6" t="n">
-        <v>99.829731</v>
+        <v>99.830072</v>
       </c>
       <c r="O306" s="6" t="n">
         <v>100.383643</v>
@@ -25011,7 +25011,7 @@
         <v>100.844419</v>
       </c>
       <c r="N307" s="9" t="n">
-        <v>99.81782800000001</v>
+        <v>99.818237</v>
       </c>
       <c r="O307" s="9" t="n">
         <v>100.251411</v>
@@ -25095,7 +25095,7 @@
         <v>100.722039</v>
       </c>
       <c r="N308" s="6" t="n">
-        <v>99.797179</v>
+        <v>99.797618</v>
       </c>
       <c r="O308" s="6" t="n">
         <v>100.070944</v>
@@ -25179,7 +25179,7 @@
         <v>100.610002</v>
       </c>
       <c r="N309" s="9" t="n">
-        <v>99.78207500000001</v>
+        <v>99.78245099999999</v>
       </c>
       <c r="O309" s="9" t="n">
         <v>99.876531</v>
@@ -25263,7 +25263,7 @@
         <v>100.48242</v>
       </c>
       <c r="N310" s="6" t="n">
-        <v>99.778564</v>
+        <v>99.778835</v>
       </c>
       <c r="O310" s="6" t="n">
         <v>99.72992000000001</v>
@@ -25347,7 +25347,7 @@
         <v>100.3213</v>
       </c>
       <c r="N311" s="9" t="n">
-        <v>99.799948</v>
+        <v>99.800089</v>
       </c>
       <c r="O311" s="9" t="n">
         <v>99.671594</v>
@@ -25431,7 +25431,7 @@
         <v>100.120372</v>
       </c>
       <c r="N312" s="6" t="n">
-        <v>99.848969</v>
+        <v>99.84898699999999</v>
       </c>
       <c r="O312" s="6" t="n">
         <v>99.719598</v>
@@ -25515,7 +25515,7 @@
         <v>99.856689</v>
       </c>
       <c r="N313" s="9" t="n">
-        <v>99.93205399999999</v>
+        <v>99.931945</v>
       </c>
       <c r="O313" s="9" t="n">
         <v>99.86323</v>
@@ -25599,7 +25599,7 @@
         <v>99.58330599999999</v>
       </c>
       <c r="N314" s="6" t="n">
-        <v>100.052926</v>
+        <v>100.052675</v>
       </c>
       <c r="O314" s="6" t="n">
         <v>100.026447</v>
@@ -25683,7 +25683,7 @@
         <v>99.353859</v>
       </c>
       <c r="N315" s="9" t="n">
-        <v>100.206311</v>
+        <v>100.205912</v>
       </c>
       <c r="O315" s="9" t="n">
         <v>100.20532</v>
@@ -25767,7 +25767,7 @@
         <v>99.18049000000001</v>
       </c>
       <c r="N316" s="6" t="n">
-        <v>100.364084</v>
+        <v>100.363537</v>
       </c>
       <c r="O316" s="6" t="n">
         <v>100.353575</v>
@@ -25851,7 +25851,7 @@
         <v>99.09212100000001</v>
       </c>
       <c r="N317" s="9" t="n">
-        <v>100.498919</v>
+        <v>100.498237</v>
       </c>
       <c r="O317" s="9" t="n">
         <v>100.459646</v>
@@ -25935,7 +25935,7 @@
         <v>99.06849</v>
       </c>
       <c r="N318" s="6" t="n">
-        <v>100.596669</v>
+        <v>100.595855</v>
       </c>
       <c r="O318" s="6" t="n">
         <v>100.550188</v>
@@ -26019,7 +26019,7 @@
         <v>99.07923599999999</v>
       </c>
       <c r="N319" s="9" t="n">
-        <v>100.670667</v>
+        <v>100.66973</v>
       </c>
       <c r="O319" s="9" t="n">
         <v>100.673678</v>
@@ -26103,7 +26103,7 @@
         <v>99.098054</v>
       </c>
       <c r="N320" s="6" t="n">
-        <v>100.727728</v>
+        <v>100.726671</v>
       </c>
       <c r="O320" s="6" t="n">
         <v>100.831421</v>
@@ -26187,7 +26187,7 @@
         <v>99.13117</v>
       </c>
       <c r="N321" s="9" t="n">
-        <v>100.769062</v>
+        <v>100.767885</v>
       </c>
       <c r="O321" s="9" t="n">
         <v>101.004165</v>
@@ -26271,7 +26271,7 @@
         <v>99.191446</v>
       </c>
       <c r="N322" s="6" t="n">
-        <v>100.791603</v>
+        <v>100.790309</v>
       </c>
       <c r="O322" s="6" t="n">
         <v>101.169937</v>
@@ -26355,7 +26355,7 @@
         <v>99.285488</v>
       </c>
       <c r="N323" s="9" t="n">
-        <v>100.79205</v>
+        <v>100.79069</v>
       </c>
       <c r="O323" s="9" t="n">
         <v>101.250011</v>
@@ -26439,7 +26439,7 @@
         <v>99.368477</v>
       </c>
       <c r="N324" s="6" t="n">
-        <v>100.778492</v>
+        <v>100.777144</v>
       </c>
       <c r="O324" s="6" t="n">
         <v>101.203612</v>
@@ -26523,7 +26523,7 @@
         <v>99.429582</v>
       </c>
       <c r="N325" s="9" t="n">
-        <v>100.757365</v>
+        <v>100.756076</v>
       </c>
       <c r="O325" s="9" t="n">
         <v>101.069745</v>
@@ -26607,7 +26607,7 @@
         <v>99.495312</v>
       </c>
       <c r="N326" s="6" t="n">
-        <v>100.728064</v>
+        <v>100.726864</v>
       </c>
       <c r="O326" s="6" t="n">
         <v>100.897384</v>
@@ -26691,7 +26691,7 @@
         <v>99.562656</v>
       </c>
       <c r="N327" s="9" t="n">
-        <v>100.689275</v>
+        <v>100.688176</v>
       </c>
       <c r="O327" s="9" t="n">
         <v>100.727294</v>
@@ -26775,7 +26775,7 @@
         <v>99.625191</v>
       </c>
       <c r="N328" s="6" t="n">
-        <v>100.652292</v>
+        <v>100.651309</v>
       </c>
       <c r="O328" s="6" t="n">
         <v>100.575573</v>
@@ -26859,7 +26859,7 @@
         <v>99.660704</v>
       </c>
       <c r="N329" s="9" t="n">
-        <v>100.634878</v>
+        <v>100.63399</v>
       </c>
       <c r="O329" s="9" t="n">
         <v>100.469269</v>
@@ -26943,7 +26943,7 @@
         <v>99.668324</v>
       </c>
       <c r="N330" s="6" t="n">
-        <v>100.641401</v>
+        <v>100.640534</v>
       </c>
       <c r="O330" s="6" t="n">
         <v>100.437394</v>
@@ -27027,7 +27027,7 @@
         <v>99.63651900000001</v>
       </c>
       <c r="N331" s="9" t="n">
-        <v>100.676763</v>
+        <v>100.675856</v>
       </c>
       <c r="O331" s="9" t="n">
         <v>100.486409</v>
@@ -27111,7 +27111,7 @@
         <v>99.549475</v>
       </c>
       <c r="N332" s="6" t="n">
-        <v>100.736925</v>
+        <v>100.735903</v>
       </c>
       <c r="O332" s="6" t="n">
         <v>100.557355</v>
@@ -27195,7 +27195,7 @@
         <v>99.397222</v>
       </c>
       <c r="N333" s="9" t="n">
-        <v>100.815004</v>
+        <v>100.813787</v>
       </c>
       <c r="O333" s="9" t="n">
         <v>100.625063</v>
@@ -27279,7 +27279,7 @@
         <v>99.217837</v>
       </c>
       <c r="N334" s="6" t="n">
-        <v>100.89617</v>
+        <v>100.894728</v>
       </c>
       <c r="O334" s="6" t="n">
         <v>100.664964</v>
@@ -27363,7 +27363,7 @@
         <v>99.046323</v>
       </c>
       <c r="N335" s="9" t="n">
-        <v>100.964716</v>
+        <v>100.963076</v>
       </c>
       <c r="O335" s="9" t="n">
         <v>100.726715</v>
@@ -27447,7 +27447,7 @@
         <v>98.91372800000001</v>
       </c>
       <c r="N336" s="6" t="n">
-        <v>101.016888</v>
+        <v>101.01511</v>
       </c>
       <c r="O336" s="6" t="n">
         <v>100.830734</v>
@@ -27531,7 +27531,7 @@
         <v>98.85507800000001</v>
       </c>
       <c r="N337" s="9" t="n">
-        <v>101.070787</v>
+        <v>101.068919</v>
       </c>
       <c r="O337" s="9" t="n">
         <v>100.938252</v>
@@ -27615,7 +27615,7 @@
         <v>98.849913</v>
       </c>
       <c r="N338" s="6" t="n">
-        <v>101.128422</v>
+        <v>101.126517</v>
       </c>
       <c r="O338" s="6" t="n">
         <v>101.025242</v>
@@ -27699,7 +27699,7 @@
         <v>98.850313</v>
       </c>
       <c r="N339" s="9" t="n">
-        <v>101.192718</v>
+        <v>101.190783</v>
       </c>
       <c r="O339" s="9" t="n">
         <v>101.022981</v>
@@ -27783,7 +27783,7 @@
         <v>98.83051399999999</v>
       </c>
       <c r="N340" s="6" t="n">
-        <v>101.277266</v>
+        <v>101.275297</v>
       </c>
       <c r="O340" s="6" t="n">
         <v>100.962321</v>
@@ -27867,7 +27867,7 @@
         <v>98.789145</v>
       </c>
       <c r="N341" s="9" t="n">
-        <v>101.389755</v>
+        <v>101.387716</v>
       </c>
       <c r="O341" s="9" t="n">
         <v>100.864235</v>
@@ -27951,7 +27951,7 @@
         <v>98.704089</v>
       </c>
       <c r="N342" s="6" t="n">
-        <v>101.525656</v>
+        <v>101.523463</v>
       </c>
       <c r="O342" s="6" t="n">
         <v>100.707986</v>
@@ -28035,7 +28035,7 @@
         <v>98.56507000000001</v>
       </c>
       <c r="N343" s="9" t="n">
-        <v>101.665921</v>
+        <v>101.663543</v>
       </c>
       <c r="O343" s="9" t="n">
         <v>100.478227</v>
@@ -28119,7 +28119,7 @@
         <v>98.401582</v>
       </c>
       <c r="N344" s="6" t="n">
-        <v>101.797632</v>
+        <v>101.795039</v>
       </c>
       <c r="O344" s="6" t="n">
         <v>100.20346</v>
@@ -28203,7 +28203,7 @@
         <v>98.25706599999999</v>
       </c>
       <c r="N345" s="9" t="n">
-        <v>101.907274</v>
+        <v>101.904424</v>
       </c>
       <c r="O345" s="9" t="n">
         <v>99.88559100000001</v>
@@ -28287,7 +28287,7 @@
         <v>98.17639</v>
       </c>
       <c r="N346" s="6" t="n">
-        <v>101.969871</v>
+        <v>101.966805</v>
       </c>
       <c r="O346" s="6" t="n">
         <v>99.541909</v>
@@ -28371,7 +28371,7 @@
         <v>98.19614</v>
       </c>
       <c r="N347" s="9" t="n">
-        <v>101.960967</v>
+        <v>101.957807</v>
       </c>
       <c r="O347" s="9" t="n">
         <v>99.154095</v>
@@ -28455,7 +28455,7 @@
         <v>98.325563</v>
       </c>
       <c r="N348" s="6" t="n">
-        <v>101.839141</v>
+        <v>101.836125</v>
       </c>
       <c r="O348" s="6" t="n">
         <v>98.72523099999999</v>
@@ -28539,7 +28539,7 @@
         <v>98.53974700000001</v>
       </c>
       <c r="N349" s="9" t="n">
-        <v>101.544885</v>
+        <v>101.542324</v>
       </c>
       <c r="O349" s="9" t="n">
         <v>98.233794</v>
@@ -28623,7 +28623,7 @@
         <v>98.837464</v>
       </c>
       <c r="N350" s="6" t="n">
-        <v>101.053193</v>
+        <v>101.051415</v>
       </c>
       <c r="O350" s="6" t="n">
         <v>97.709093</v>
@@ -28707,7 +28707,7 @@
         <v>99.230667</v>
       </c>
       <c r="N351" s="9" t="n">
-        <v>100.380012</v>
+        <v>100.379316</v>
       </c>
       <c r="O351" s="9" t="n">
         <v>97.21190300000001</v>
@@ -28791,7 +28791,7 @@
         <v>99.690941</v>
       </c>
       <c r="N352" s="6" t="n">
-        <v>99.566422</v>
+        <v>99.567076</v>
       </c>
       <c r="O352" s="6" t="n">
         <v>96.808053</v>
@@ -28875,7 +28875,7 @@
         <v>100.153367</v>
       </c>
       <c r="N353" s="9" t="n">
-        <v>98.69760599999999</v>
+        <v>98.699679</v>
       </c>
       <c r="O353" s="9" t="n">
         <v>96.50884600000001</v>
@@ -28959,7 +28959,7 @@
         <v>100.585507</v>
       </c>
       <c r="N354" s="6" t="n">
-        <v>97.910884</v>
+        <v>97.914196</v>
       </c>
       <c r="O354" s="6" t="n">
         <v>96.27739</v>
@@ -29043,7 +29043,7 @@
         <v>100.987692</v>
       </c>
       <c r="N355" s="9" t="n">
-        <v>97.28248499999999</v>
+        <v>97.286761</v>
       </c>
       <c r="O355" s="9" t="n">
         <v>96.14963299999999</v>
@@ -29127,7 +29127,7 @@
         <v>101.349711</v>
       </c>
       <c r="N356" s="6" t="n">
-        <v>96.84311</v>
+        <v>96.848017</v>
       </c>
       <c r="O356" s="6" t="n">
         <v>96.15516</v>
@@ -29211,7 +29211,7 @@
         <v>101.654181</v>
       </c>
       <c r="N357" s="9" t="n">
-        <v>96.60618599999999</v>
+        <v>96.61138200000001</v>
       </c>
       <c r="O357" s="9" t="n">
         <v>96.35382199999999</v>
@@ -29295,7 +29295,7 @@
         <v>101.861645</v>
       </c>
       <c r="N358" s="6" t="n">
-        <v>96.56907099999999</v>
+        <v>96.574217</v>
       </c>
       <c r="O358" s="6" t="n">
         <v>96.743914</v>
@@ -29379,7 +29379,7 @@
         <v>101.96381</v>
       </c>
       <c r="N359" s="9" t="n">
-        <v>96.708754</v>
+        <v>96.71358600000001</v>
       </c>
       <c r="O359" s="9" t="n">
         <v>97.298091</v>
@@ -29463,7 +29463,7 @@
         <v>102.002672</v>
       </c>
       <c r="N360" s="6" t="n">
-        <v>96.965065</v>
+        <v>96.969452</v>
       </c>
       <c r="O360" s="6" t="n">
         <v>97.952263</v>
@@ -29547,7 +29547,7 @@
         <v>101.972665</v>
       </c>
       <c r="N361" s="9" t="n">
-        <v>97.290541</v>
+        <v>97.294439</v>
       </c>
       <c r="O361" s="9" t="n">
         <v>98.65101900000001</v>
@@ -29631,7 +29631,7 @@
         <v>101.864989</v>
       </c>
       <c r="N362" s="6" t="n">
-        <v>97.646339</v>
+        <v>97.64972899999999</v>
       </c>
       <c r="O362" s="6" t="n">
         <v>99.32866199999999</v>
@@ -29715,7 +29715,7 @@
         <v>101.677523</v>
       </c>
       <c r="N363" s="9" t="n">
-        <v>98.003462</v>
+        <v>98.006354</v>
       </c>
       <c r="O363" s="9" t="n">
         <v>99.96365299999999</v>
@@ -29799,7 +29799,7 @@
         <v>101.46015</v>
       </c>
       <c r="N364" s="6" t="n">
-        <v>98.34691100000001</v>
+        <v>98.349371</v>
       </c>
       <c r="O364" s="6" t="n">
         <v>100.460083</v>
@@ -29883,7 +29883,7 @@
         <v>101.273682</v>
       </c>
       <c r="N365" s="9" t="n">
-        <v>98.64769099999999</v>
+        <v>98.64978000000001</v>
       </c>
       <c r="O365" s="9" t="n">
         <v>100.819533</v>
@@ -29967,7 +29967,7 @@
         <v>101.130752</v>
       </c>
       <c r="N366" s="6" t="n">
-        <v>98.907893</v>
+        <v>98.909622</v>
       </c>
       <c r="O366" s="6" t="n">
         <v>101.100972</v>
@@ -30051,7 +30051,7 @@
         <v>100.997754</v>
       </c>
       <c r="N367" s="9" t="n">
-        <v>99.136805</v>
+        <v>99.13820200000001</v>
       </c>
       <c r="O367" s="9" t="n">
         <v>101.309975</v>
@@ -30135,7 +30135,7 @@
         <v>100.891988</v>
       </c>
       <c r="N368" s="6" t="n">
-        <v>99.32791899999999</v>
+        <v>99.329008</v>
       </c>
       <c r="O368" s="6" t="n">
         <v>101.469832</v>
@@ -30219,7 +30219,7 @@
         <v>100.806185</v>
       </c>
       <c r="N369" s="9" t="n">
-        <v>99.465743</v>
+        <v>99.46657399999999</v>
       </c>
       <c r="O369" s="9" t="n">
         <v>101.565326</v>
@@ -30303,7 +30303,7 @@
         <v>100.720796</v>
       </c>
       <c r="N370" s="6" t="n">
-        <v>99.548821</v>
+        <v>99.549446</v>
       </c>
       <c r="O370" s="6" t="n">
         <v>101.586304</v>
@@ -30387,7 +30387,7 @@
         <v>100.637042</v>
       </c>
       <c r="N371" s="9" t="n">
-        <v>99.597269</v>
+        <v>99.59773800000001</v>
       </c>
       <c r="O371" s="9" t="n">
         <v>101.538949</v>
@@ -30471,7 +30471,7 @@
         <v>100.546853</v>
       </c>
       <c r="N372" s="6" t="n">
-        <v>99.649444</v>
+        <v>99.649765</v>
       </c>
       <c r="O372" s="6" t="n">
         <v>101.447629</v>
@@ -30555,7 +30555,7 @@
         <v>100.477041</v>
       </c>
       <c r="N373" s="9" t="n">
-        <v>99.724316</v>
+        <v>99.724464</v>
       </c>
       <c r="O373" s="9" t="n">
         <v>101.332992</v>
@@ -30639,7 +30639,7 @@
         <v>100.461442</v>
       </c>
       <c r="N374" s="6" t="n">
-        <v>99.822829</v>
+        <v>99.822796</v>
       </c>
       <c r="O374" s="6" t="n">
         <v>101.210698</v>
@@ -30723,7 +30723,7 @@
         <v>100.457102</v>
       </c>
       <c r="N375" s="9" t="n">
-        <v>99.94723500000001</v>
+        <v>99.947025</v>
       </c>
       <c r="O375" s="9" t="n">
         <v>101.051229</v>
@@ -30807,7 +30807,7 @@
         <v>100.427488</v>
       </c>
       <c r="N376" s="6" t="n">
-        <v>100.082606</v>
+        <v>100.082285</v>
       </c>
       <c r="O376" s="6" t="n">
         <v>100.902368</v>
@@ -30891,7 +30891,7 @@
         <v>100.351876</v>
       </c>
       <c r="N377" s="9" t="n">
-        <v>100.219442</v>
+        <v>100.218999</v>
       </c>
       <c r="O377" s="9" t="n">
         <v>100.800654</v>
@@ -30975,7 +30975,7 @@
         <v>100.214787</v>
       </c>
       <c r="N378" s="6" t="n">
-        <v>100.347233</v>
+        <v>100.346661</v>
       </c>
       <c r="O378" s="6" t="n">
         <v>100.754268</v>
@@ -31059,7 +31059,7 @@
         <v>100.069248</v>
       </c>
       <c r="N379" s="9" t="n">
-        <v>100.459197</v>
+        <v>100.458514</v>
       </c>
       <c r="O379" s="9" t="n">
         <v>100.764424</v>
@@ -31143,7 +31143,7 @@
         <v>99.95326799999999</v>
       </c>
       <c r="N380" s="6" t="n">
-        <v>100.554858</v>
+        <v>100.55405</v>
       </c>
       <c r="O380" s="6" t="n">
         <v>100.808062</v>
@@ -31227,7 +31227,7 @@
         <v>99.893018</v>
       </c>
       <c r="N381" s="9" t="n">
-        <v>100.639007</v>
+        <v>100.63803</v>
       </c>
       <c r="O381" s="9" t="n">
         <v>100.864915</v>
@@ -31311,7 +31311,7 @@
         <v>99.90525599999999</v>
       </c>
       <c r="N382" s="6" t="n">
-        <v>100.713288</v>
+        <v>100.712082</v>
       </c>
       <c r="O382" s="6" t="n">
         <v>100.915419</v>
@@ -31395,7 +31395,7 @@
         <v>99.92578399999999</v>
       </c>
       <c r="N383" s="9" t="n">
-        <v>100.760865</v>
+        <v>100.75947</v>
       </c>
       <c r="O383" s="9" t="n">
         <v>100.956983</v>
@@ -31479,7 +31479,7 @@
         <v>99.916354</v>
       </c>
       <c r="N384" s="6" t="n">
-        <v>100.770945</v>
+        <v>100.769444</v>
       </c>
       <c r="O384" s="6" t="n">
         <v>100.984146</v>
@@ -31563,7 +31563,7 @@
         <v>99.87211600000001</v>
       </c>
       <c r="N385" s="9" t="n">
-        <v>100.754741</v>
+        <v>100.753206</v>
       </c>
       <c r="O385" s="9" t="n">
         <v>101.021215</v>
@@ -31647,7 +31647,7 @@
         <v>99.81053199999999</v>
       </c>
       <c r="N386" s="6" t="n">
-        <v>100.73223</v>
+        <v>100.730717</v>
       </c>
       <c r="O386" s="6" t="n">
         <v>101.075927</v>
@@ -31731,7 +31731,7 @@
         <v>99.751735</v>
       </c>
       <c r="N387" s="9" t="n">
-        <v>100.708188</v>
+        <v>100.706738</v>
       </c>
       <c r="O387" s="9" t="n">
         <v>101.167702</v>
@@ -31815,7 +31815,7 @@
         <v>99.71040600000001</v>
       </c>
       <c r="N388" s="6" t="n">
-        <v>100.6967</v>
+        <v>100.695379</v>
       </c>
       <c r="O388" s="6" t="n">
         <v>101.29389</v>
@@ -31899,7 +31899,7 @@
         <v>99.69152200000001</v>
       </c>
       <c r="N389" s="9" t="n">
-        <v>100.696862</v>
+        <v>100.695622</v>
       </c>
       <c r="O389" s="9" t="n">
         <v>101.412279</v>
@@ -31983,7 +31983,7 @@
         <v>99.71194199999999</v>
       </c>
       <c r="N390" s="6" t="n">
-        <v>100.698227</v>
+        <v>100.697007</v>
       </c>
       <c r="O390" s="6" t="n">
         <v>101.530935</v>
@@ -32067,7 +32067,7 @@
         <v>99.754248</v>
       </c>
       <c r="N391" s="9" t="n">
-        <v>100.68824</v>
+        <v>100.68705</v>
       </c>
       <c r="O391" s="9" t="n">
         <v>101.59783</v>
@@ -32151,7 +32151,7 @@
         <v>99.765761</v>
       </c>
       <c r="N392" s="6" t="n">
-        <v>100.655404</v>
+        <v>100.654299</v>
       </c>
       <c r="O392" s="6" t="n">
         <v>101.558208</v>
@@ -32235,7 +32235,7 @@
         <v>99.749911</v>
       </c>
       <c r="N393" s="9" t="n">
-        <v>100.606927</v>
+        <v>100.605926</v>
       </c>
       <c r="O393" s="9" t="n">
         <v>101.422647</v>
@@ -32319,7 +32319,7 @@
         <v>99.72132999999999</v>
       </c>
       <c r="N394" s="6" t="n">
-        <v>100.538502</v>
+        <v>100.537653</v>
       </c>
       <c r="O394" s="6" t="n">
         <v>101.26896</v>
@@ -32403,7 +32403,7 @@
         <v>99.68391699999999</v>
       </c>
       <c r="N395" s="9" t="n">
-        <v>100.465662</v>
+        <v>100.464907</v>
       </c>
       <c r="O395" s="9" t="n">
         <v>101.120029</v>
@@ -32487,7 +32487,7 @@
         <v>99.673507</v>
       </c>
       <c r="N396" s="6" t="n">
-        <v>100.416724</v>
+        <v>100.415927</v>
       </c>
       <c r="O396" s="6" t="n">
         <v>100.958158</v>
@@ -32571,7 +32571,7 @@
         <v>99.70941500000001</v>
       </c>
       <c r="N397" s="9" t="n">
-        <v>100.398944</v>
+        <v>100.397993</v>
       </c>
       <c r="O397" s="9" t="n">
         <v>100.795446</v>
@@ -32655,7 +32655,7 @@
         <v>99.784696</v>
       </c>
       <c r="N398" s="6" t="n">
-        <v>100.415212</v>
+        <v>100.414017</v>
       </c>
       <c r="O398" s="6" t="n">
         <v>100.665807</v>
@@ -32739,7 +32739,7 @@
         <v>99.908417</v>
       </c>
       <c r="N399" s="9" t="n">
-        <v>100.450686</v>
+        <v>100.449321</v>
       </c>
       <c r="O399" s="9" t="n">
         <v>100.591797</v>
@@ -32823,7 +32823,7 @@
         <v>100.052815</v>
       </c>
       <c r="N400" s="6" t="n">
-        <v>100.480564</v>
+        <v>100.479223</v>
       </c>
       <c r="O400" s="6" t="n">
         <v>100.536814</v>
@@ -32907,7 +32907,7 @@
         <v>100.174945</v>
       </c>
       <c r="N401" s="9" t="n">
-        <v>100.503075</v>
+        <v>100.501792</v>
       </c>
       <c r="O401" s="9" t="n">
         <v>100.474474</v>
@@ -32991,7 +32991,7 @@
         <v>100.248327</v>
       </c>
       <c r="N402" s="6" t="n">
-        <v>100.520293</v>
+        <v>100.519201</v>
       </c>
       <c r="O402" s="6" t="n">
         <v>100.314802</v>
@@ -33075,7 +33075,7 @@
         <v>100.261794</v>
       </c>
       <c r="N403" s="9" t="n">
-        <v>100.519411</v>
+        <v>100.518529</v>
       </c>
       <c r="O403" s="9" t="n">
         <v>100.059657</v>
@@ -33159,7 +33159,7 @@
         <v>100.239719</v>
       </c>
       <c r="N404" s="6" t="n">
-        <v>100.493714</v>
+        <v>100.49299</v>
       </c>
       <c r="O404" s="6" t="n">
         <v>99.78119700000001</v>
@@ -33243,7 +33243,7 @@
         <v>100.183052</v>
       </c>
       <c r="N405" s="9" t="n">
-        <v>100.442384</v>
+        <v>100.441688</v>
       </c>
       <c r="O405" s="9" t="n">
         <v>99.52534199999999</v>
@@ -33327,7 +33327,7 @@
         <v>100.08159</v>
       </c>
       <c r="N406" s="6" t="n">
-        <v>100.371756</v>
+        <v>100.370978</v>
       </c>
       <c r="O406" s="6" t="n">
         <v>99.291399</v>
@@ -33411,7 +33411,7 @@
         <v>99.988404</v>
       </c>
       <c r="N407" s="9" t="n">
-        <v>100.295858</v>
+        <v>100.294936</v>
       </c>
       <c r="O407" s="9" t="n">
         <v>99.077575</v>
@@ -33495,7 +33495,7 @@
         <v>99.914632</v>
       </c>
       <c r="N408" s="6" t="n">
-        <v>100.217923</v>
+        <v>100.216912</v>
       </c>
       <c r="O408" s="6" t="n">
         <v>98.924522</v>
@@ -33579,7 +33579,7 @@
         <v>99.88269200000001</v>
       </c>
       <c r="N409" s="9" t="n">
-        <v>100.139757</v>
+        <v>100.138756</v>
       </c>
       <c r="O409" s="9" t="n">
         <v>98.832689</v>
@@ -33663,7 +33663,7 @@
         <v>99.909736</v>
       </c>
       <c r="N410" s="6" t="n">
-        <v>100.073031</v>
+        <v>100.072091</v>
       </c>
       <c r="O410" s="6" t="n">
         <v>98.801393</v>
@@ -33747,7 +33747,7 @@
         <v>99.996787</v>
       </c>
       <c r="N411" s="9" t="n">
-        <v>100.030443</v>
+        <v>100.029666</v>
       </c>
       <c r="O411" s="9" t="n">
         <v>98.810033</v>
@@ -33831,7 +33831,7 @@
         <v>100.163136</v>
       </c>
       <c r="N412" s="6" t="n">
-        <v>100.020267</v>
+        <v>100.019786</v>
       </c>
       <c r="O412" s="6" t="n">
         <v>98.83141000000001</v>
@@ -33915,7 +33915,7 @@
         <v>100.415345</v>
       </c>
       <c r="N413" s="9" t="n">
-        <v>100.05256</v>
+        <v>100.052249</v>
       </c>
       <c r="O413" s="9" t="n">
         <v>98.801085</v>
@@ -33999,7 +33999,7 @@
         <v>100.675654</v>
       </c>
       <c r="N414" s="6" t="n">
-        <v>100.124124</v>
+        <v>100.123755</v>
       </c>
       <c r="O414" s="6" t="n">
         <v>98.72745</v>
@@ -34083,7 +34083,7 @@
         <v>100.883808</v>
       </c>
       <c r="N415" s="9" t="n">
-        <v>100.217252</v>
+        <v>100.216677</v>
       </c>
       <c r="O415" s="9" t="n">
         <v>98.686283</v>
@@ -34167,7 +34167,7 @@
         <v>101.04807</v>
       </c>
       <c r="N416" s="6" t="n">
-        <v>100.31086</v>
+        <v>100.310077</v>
       </c>
       <c r="O416" s="6" t="n">
         <v>98.732029</v>
@@ -34251,7 +34251,7 @@
         <v>101.14891</v>
       </c>
       <c r="N417" s="9" t="n">
-        <v>100.39033</v>
+        <v>100.389486</v>
       </c>
       <c r="O417" s="9" t="n">
         <v>98.80222000000001</v>
@@ -34335,7 +34335,7 @@
         <v>101.178974</v>
       </c>
       <c r="N418" s="6" t="n">
-        <v>100.445697</v>
+        <v>100.444756</v>
       </c>
       <c r="O418" s="6" t="n">
         <v>98.85823499999999</v>
@@ -34419,7 +34419,7 @@
         <v>101.16376</v>
       </c>
       <c r="N419" s="9" t="n">
-        <v>100.472978</v>
+        <v>100.471961</v>
       </c>
       <c r="O419" s="9" t="n">
         <v>98.888727</v>
@@ -34503,7 +34503,7 @@
         <v>101.090719</v>
       </c>
       <c r="N420" s="6" t="n">
-        <v>100.475552</v>
+        <v>100.474492</v>
       </c>
       <c r="O420" s="6" t="n">
         <v>98.907864</v>
@@ -34587,7 +34587,7 @@
         <v>100.930977</v>
       </c>
       <c r="N421" s="9" t="n">
-        <v>100.460325</v>
+        <v>100.459157</v>
       </c>
       <c r="O421" s="9" t="n">
         <v>98.933187</v>
@@ -34671,7 +34671,7 @@
         <v>100.720557</v>
       </c>
       <c r="N422" s="6" t="n">
-        <v>100.419732</v>
+        <v>100.418398</v>
       </c>
       <c r="O422" s="6" t="n">
         <v>98.946806</v>
@@ -34755,7 +34755,7 @@
         <v>100.494712</v>
       </c>
       <c r="N423" s="9" t="n">
-        <v>100.369473</v>
+        <v>100.368032</v>
       </c>
       <c r="O423" s="9" t="n">
         <v>98.93681100000001</v>
@@ -34839,7 +34839,7 @@
         <v>100.274444</v>
       </c>
       <c r="N424" s="6" t="n">
-        <v>100.311294</v>
+        <v>100.310085</v>
       </c>
       <c r="O424" s="6" t="n">
         <v>98.92834999999999</v>
@@ -34923,7 +34923,7 @@
         <v>100.10637</v>
       </c>
       <c r="N425" s="9" t="n">
-        <v>100.233727</v>
+        <v>100.232938</v>
       </c>
       <c r="O425" s="9" t="n">
         <v>98.980548</v>
@@ -35007,7 +35007,7 @@
         <v>100.020909</v>
       </c>
       <c r="N426" s="6" t="n">
-        <v>100.155964</v>
+        <v>100.155544</v>
       </c>
       <c r="O426" s="6" t="n">
         <v>99.114367</v>
@@ -35091,7 +35091,7 @@
         <v>99.993785</v>
       </c>
       <c r="N427" s="9" t="n">
-        <v>100.100529</v>
+        <v>100.100401</v>
       </c>
       <c r="O427" s="9" t="n">
         <v>99.278565</v>
@@ -35175,7 +35175,7 @@
         <v>99.998238</v>
       </c>
       <c r="N428" s="6" t="n">
-        <v>100.076986</v>
+        <v>100.077033</v>
       </c>
       <c r="O428" s="6" t="n">
         <v>99.39837300000001</v>
@@ -35259,7 +35259,7 @@
         <v>100.034975</v>
       </c>
       <c r="N429" s="9" t="n">
-        <v>100.073032</v>
+        <v>100.07313</v>
       </c>
       <c r="O429" s="9" t="n">
         <v>99.515666</v>
@@ -35343,7 +35343,7 @@
         <v>100.089377</v>
       </c>
       <c r="N430" s="6" t="n">
-        <v>100.078958</v>
+        <v>100.078951</v>
       </c>
       <c r="O430" s="6" t="n">
         <v>99.64281800000001</v>
@@ -35427,7 +35427,7 @@
         <v>100.132016</v>
       </c>
       <c r="N431" s="9" t="n">
-        <v>100.079687</v>
+        <v>100.079464</v>
       </c>
       <c r="O431" s="9" t="n">
         <v>99.794785</v>
@@ -35511,7 +35511,7 @@
         <v>100.163409</v>
       </c>
       <c r="N432" s="6" t="n">
-        <v>100.052593</v>
+        <v>100.052077</v>
       </c>
       <c r="O432" s="6" t="n">
         <v>99.968816</v>
@@ -35595,7 +35595,7 @@
         <v>100.178177</v>
       </c>
       <c r="N433" s="9" t="n">
-        <v>99.991704</v>
+        <v>99.990887</v>
       </c>
       <c r="O433" s="9" t="n">
         <v>100.131164</v>
@@ -35679,7 +35679,7 @@
         <v>100.180738</v>
       </c>
       <c r="N434" s="6" t="n">
-        <v>99.890794</v>
+        <v>99.88988000000001</v>
       </c>
       <c r="O434" s="6" t="n">
         <v>100.261671</v>
@@ -35763,7 +35763,7 @@
         <v>100.163692</v>
       </c>
       <c r="N435" s="9" t="n">
-        <v>99.76481699999999</v>
+        <v>99.76402899999999</v>
       </c>
       <c r="O435" s="9" t="n">
         <v>100.360237</v>
@@ -35847,7 +35847,7 @@
         <v>100.129359</v>
       </c>
       <c r="N436" s="6" t="n">
-        <v>99.624442</v>
+        <v>99.62432</v>
       </c>
       <c r="O436" s="6" t="n">
         <v>100.416296</v>
@@ -35931,7 +35931,7 @@
         <v>100.113704</v>
       </c>
       <c r="N437" s="9" t="n">
-        <v>99.486216</v>
+        <v>99.486923</v>
       </c>
       <c r="O437" s="9" t="n">
         <v>100.437097</v>
@@ -36015,7 +36015,7 @@
         <v>100.06032</v>
       </c>
       <c r="N438" s="6" t="n">
-        <v>99.372911</v>
+        <v>99.37418700000001</v>
       </c>
       <c r="O438" s="6" t="n">
         <v>100.430587</v>
@@ -36099,7 +36099,7 @@
         <v>99.990819</v>
       </c>
       <c r="N439" s="9" t="n">
-        <v>99.28915499999999</v>
+        <v>99.29082200000001</v>
       </c>
       <c r="O439" s="9" t="n">
         <v>100.389244</v>
@@ -36183,7 +36183,7 @@
         <v>99.914817</v>
       </c>
       <c r="N440" s="6" t="n">
-        <v>99.23840300000001</v>
+        <v>99.240371</v>
       </c>
       <c r="O440" s="6" t="n">
         <v>100.323214</v>
@@ -36267,7 +36267,7 @@
         <v>99.84768099999999</v>
       </c>
       <c r="N441" s="9" t="n">
-        <v>99.222514</v>
+        <v>99.22458</v>
       </c>
       <c r="O441" s="9" t="n">
         <v>100.275116</v>
@@ -36351,7 +36351,7 @@
         <v>99.804922</v>
       </c>
       <c r="N442" s="6" t="n">
-        <v>99.230887</v>
+        <v>99.23282</v>
       </c>
       <c r="O442" s="6" t="n">
         <v>100.245636</v>
@@ -36435,7 +36435,7 @@
         <v>99.761669</v>
       </c>
       <c r="N443" s="9" t="n">
-        <v>99.26398399999999</v>
+        <v>99.265654</v>
       </c>
       <c r="O443" s="9" t="n">
         <v>100.246782</v>
@@ -36519,7 +36519,7 @@
         <v>99.724226</v>
       </c>
       <c r="N444" s="6" t="n">
-        <v>99.316062</v>
+        <v>99.317403</v>
       </c>
       <c r="O444" s="6" t="n">
         <v>100.255031</v>
@@ -36603,7 +36603,7 @@
         <v>99.692379</v>
       </c>
       <c r="N445" s="9" t="n">
-        <v>99.37822799999999</v>
+        <v>99.379154</v>
       </c>
       <c r="O445" s="9" t="n">
         <v>100.268903</v>
@@ -36687,7 +36687,7 @@
         <v>99.631556</v>
       </c>
       <c r="N446" s="6" t="n">
-        <v>99.447562</v>
+        <v>99.448081</v>
       </c>
       <c r="O446" s="6" t="n">
         <v>100.297792</v>
@@ -36771,7 +36771,7 @@
         <v>99.48962</v>
       </c>
       <c r="N447" s="9" t="n">
-        <v>99.514724</v>
+        <v>99.515027</v>
       </c>
       <c r="O447" s="9" t="n">
         <v>100.335496</v>
@@ -36855,7 +36855,7 @@
         <v>99.30301799999999</v>
       </c>
       <c r="N448" s="6" t="n">
-        <v>99.58468499999999</v>
+        <v>99.58543299999999</v>
       </c>
       <c r="O448" s="6" t="n">
         <v>100.402995</v>
@@ -36939,7 +36939,7 @@
         <v>99.083732</v>
       </c>
       <c r="N449" s="9" t="n">
-        <v>99.64937399999999</v>
+        <v>99.650679</v>
       </c>
       <c r="O449" s="9" t="n">
         <v>100.485181</v>
@@ -37023,7 +37023,7 @@
         <v>98.850228</v>
       </c>
       <c r="N450" s="6" t="n">
-        <v>99.702195</v>
+        <v>99.70380900000001</v>
       </c>
       <c r="O450" s="6" t="n">
         <v>100.632379</v>
@@ -37107,7 +37107,7 @@
         <v>98.665977</v>
       </c>
       <c r="N451" s="9" t="n">
-        <v>99.746343</v>
+        <v>99.748104</v>
       </c>
       <c r="O451" s="9" t="n">
         <v>100.8527</v>
@@ -37191,7 +37191,7 @@
         <v>98.577077</v>
       </c>
       <c r="N452" s="6" t="n">
-        <v>99.788827</v>
+        <v>99.790616</v>
       </c>
       <c r="O452" s="6" t="n">
         <v>101.08244</v>
@@ -37275,7 +37275,7 @@
         <v>98.547087</v>
       </c>
       <c r="N453" s="9" t="n">
-        <v>99.838741</v>
+        <v>99.840459</v>
       </c>
       <c r="O453" s="9" t="n">
         <v>101.239188</v>
@@ -37359,7 +37359,7 @@
         <v>98.552368</v>
       </c>
       <c r="N454" s="6" t="n">
-        <v>99.906627</v>
+        <v>99.908192</v>
       </c>
       <c r="O454" s="6" t="n">
         <v>101.305714</v>
@@ -37443,7 +37443,7 @@
         <v>98.59612799999999</v>
       </c>
       <c r="N455" s="9" t="n">
-        <v>99.984734</v>
+        <v>99.986108</v>
       </c>
       <c r="O455" s="9" t="n">
         <v>101.225357</v>
@@ -37527,7 +37527,7 @@
         <v>98.677052</v>
       </c>
       <c r="N456" s="6" t="n">
-        <v>100.070797</v>
+        <v>100.071859</v>
       </c>
       <c r="O456" s="6" t="n">
         <v>101.005119</v>
@@ -37611,7 +37611,7 @@
         <v>98.769868</v>
       </c>
       <c r="N457" s="9" t="n">
-        <v>100.1669</v>
+        <v>100.167662</v>
       </c>
       <c r="O457" s="9" t="n">
         <v>100.701188</v>
@@ -37695,7 +37695,7 @@
         <v>98.843898</v>
       </c>
       <c r="N458" s="6" t="n">
-        <v>100.263306</v>
+        <v>100.263737</v>
       </c>
       <c r="O458" s="6" t="n">
         <v>100.391964</v>
@@ -37779,7 +37779,7 @@
         <v>98.871287</v>
       </c>
       <c r="N459" s="9" t="n">
-        <v>100.362087</v>
+        <v>100.362334</v>
       </c>
       <c r="O459" s="9" t="n">
         <v>100.136131</v>
@@ -37863,7 +37863,7 @@
         <v>98.85954099999999</v>
       </c>
       <c r="N460" s="6" t="n">
-        <v>100.45936</v>
+        <v>100.459892</v>
       </c>
       <c r="O460" s="6" t="n">
         <v>99.96272999999999</v>
@@ -37947,7 +37947,7 @@
         <v>98.831816</v>
       </c>
       <c r="N461" s="9" t="n">
-        <v>100.557882</v>
+        <v>100.558842</v>
       </c>
       <c r="O461" s="9" t="n">
         <v>99.898034</v>
@@ -38031,7 +38031,7 @@
         <v>98.809579</v>
       </c>
       <c r="N462" s="6" t="n">
-        <v>100.645344</v>
+        <v>100.646552</v>
       </c>
       <c r="O462" s="6" t="n">
         <v>99.889002</v>
@@ -38115,7 +38115,7 @@
         <v>98.78988</v>
       </c>
       <c r="N463" s="9" t="n">
-        <v>100.731875</v>
+        <v>100.733264</v>
       </c>
       <c r="O463" s="9" t="n">
         <v>99.91958099999999</v>
@@ -38199,7 +38199,7 @@
         <v>98.770734</v>
       </c>
       <c r="N464" s="6" t="n">
-        <v>100.81209</v>
+        <v>100.813605</v>
       </c>
       <c r="O464" s="6" t="n">
         <v>99.99393999999999</v>
@@ -38283,7 +38283,7 @@
         <v>98.742182</v>
       </c>
       <c r="N465" s="9" t="n">
-        <v>100.879351</v>
+        <v>100.881008</v>
       </c>
       <c r="O465" s="9" t="n">
         <v>100.086625</v>
@@ -38367,7 +38367,7 @@
         <v>98.69288899999999</v>
       </c>
       <c r="N466" s="6" t="n">
-        <v>100.94377</v>
+        <v>100.945593</v>
       </c>
       <c r="O466" s="6" t="n">
         <v>100.187025</v>
@@ -38451,7 +38451,7 @@
         <v>98.65801999999999</v>
       </c>
       <c r="N467" s="9" t="n">
-        <v>100.997708</v>
+        <v>100.999612</v>
       </c>
       <c r="O467" s="9" t="n">
         <v>100.281459</v>
@@ -38535,7 +38535,7 @@
         <v>98.626366</v>
       </c>
       <c r="N468" s="6" t="n">
-        <v>101.031795</v>
+        <v>101.033632</v>
       </c>
       <c r="O468" s="6" t="n">
         <v>100.36843</v>
@@ -38619,7 +38619,7 @@
         <v>98.617047</v>
       </c>
       <c r="N469" s="9" t="n">
-        <v>101.041847</v>
+        <v>101.043422</v>
       </c>
       <c r="O469" s="9" t="n">
         <v>100.449472</v>
@@ -38703,7 +38703,7 @@
         <v>98.63023800000001</v>
       </c>
       <c r="N470" s="6" t="n">
-        <v>101.026968</v>
+        <v>101.028239</v>
       </c>
       <c r="O470" s="6" t="n">
         <v>100.522437</v>
@@ -38787,7 +38787,7 @@
         <v>98.702747</v>
       </c>
       <c r="N471" s="9" t="n">
-        <v>100.981825</v>
+        <v>100.983073</v>
       </c>
       <c r="O471" s="9" t="n">
         <v>100.531292</v>
@@ -38871,7 +38871,7 @@
         <v>98.84331899999999</v>
       </c>
       <c r="N472" s="6" t="n">
-        <v>100.904117</v>
+        <v>100.905822</v>
       </c>
       <c r="O472" s="6" t="n">
         <v>100.419027</v>
@@ -38955,7 +38955,7 @@
         <v>99.007141</v>
       </c>
       <c r="N473" s="9" t="n">
-        <v>100.805549</v>
+        <v>100.807857</v>
       </c>
       <c r="O473" s="9" t="n">
         <v>100.218061</v>
@@ -39039,7 +39039,7 @@
         <v>99.11803500000001</v>
       </c>
       <c r="N474" s="6" t="n">
-        <v>100.712834</v>
+        <v>100.715774</v>
       </c>
       <c r="O474" s="6" t="n">
         <v>99.968356</v>
@@ -39123,7 +39123,7 @@
         <v>99.19526399999999</v>
       </c>
       <c r="N475" s="9" t="n">
-        <v>100.629907</v>
+        <v>100.633468</v>
       </c>
       <c r="O475" s="9" t="n">
         <v>99.68058499999999</v>
@@ -39207,7 +39207,7 @@
         <v>99.239897</v>
       </c>
       <c r="N476" s="6" t="n">
-        <v>100.559192</v>
+        <v>100.563245</v>
       </c>
       <c r="O476" s="6" t="n">
         <v>99.42294800000001</v>
@@ -39291,7 +39291,7 @@
         <v>99.25556899999999</v>
       </c>
       <c r="N477" s="9" t="n">
-        <v>100.49821</v>
+        <v>100.502645</v>
       </c>
       <c r="O477" s="9" t="n">
         <v>99.215371</v>
@@ -39375,7 +39375,7 @@
         <v>99.261787</v>
       </c>
       <c r="N478" s="6" t="n">
-        <v>100.438772</v>
+        <v>100.443481</v>
       </c>
       <c r="O478" s="6" t="n">
         <v>99.05097499999999</v>
@@ -39459,7 +39459,7 @@
         <v>99.242632</v>
       </c>
       <c r="N479" s="9" t="n">
-        <v>100.379011</v>
+        <v>100.383873</v>
       </c>
       <c r="O479" s="9" t="n">
         <v>98.995295</v>
@@ -39543,7 +39543,7 @@
         <v>99.21308999999999</v>
       </c>
       <c r="N480" s="6" t="n">
-        <v>100.317631</v>
+        <v>100.322616</v>
       </c>
       <c r="O480" s="6" t="n">
         <v>99.042288</v>
@@ -39627,7 +39627,7 @@
         <v>99.189075</v>
       </c>
       <c r="N481" s="9" t="n">
-        <v>100.239692</v>
+        <v>100.24474</v>
       </c>
       <c r="O481" s="9" t="n">
         <v>99.132893</v>
@@ -39711,7 +39711,7 @@
         <v>99.194183</v>
       </c>
       <c r="N482" s="6" t="n">
-        <v>100.136536</v>
+        <v>100.141689</v>
       </c>
       <c r="O482" s="6" t="n">
         <v>99.16364</v>
@@ -39795,7 +39795,7 @@
         <v>99.23823299999999</v>
       </c>
       <c r="N483" s="9" t="n">
-        <v>100.000387</v>
+        <v>100.005824</v>
       </c>
       <c r="O483" s="9" t="n">
         <v>99.16673400000001</v>
@@ -39879,7 +39879,7 @@
         <v>99.324172</v>
       </c>
       <c r="N484" s="6" t="n">
-        <v>99.816075</v>
+        <v>99.821956</v>
       </c>
       <c r="O484" s="6" t="n">
         <v>99.169365</v>
@@ -39963,7 +39963,7 @@
         <v>99.48212100000001</v>
       </c>
       <c r="N485" s="9" t="n">
-        <v>99.565625</v>
+        <v>99.57194800000001</v>
       </c>
       <c r="O485" s="9" t="n">
         <v>99.12859899999999</v>
@@ -40047,7 +40047,7 @@
         <v>99.777096</v>
       </c>
       <c r="N486" s="6" t="n">
-        <v>99.22620499999999</v>
+        <v>99.232862</v>
       </c>
       <c r="O486" s="6" t="n">
         <v>99.03926800000001</v>
@@ -40131,7 +40131,7 @@
         <v>100.2103</v>
       </c>
       <c r="N487" s="9" t="n">
-        <v>98.779974</v>
+        <v>98.78703299999999</v>
       </c>
       <c r="O487" s="9" t="n">
         <v>98.93617</v>
@@ -40215,7 +40215,7 @@
         <v>100.762096</v>
       </c>
       <c r="N488" s="6" t="n">
-        <v>98.24610699999999</v>
+        <v>98.253626</v>
       </c>
       <c r="O488" s="6" t="n">
         <v>98.79833499999999</v>
@@ -40299,7 +40299,7 @@
         <v>101.436864</v>
       </c>
       <c r="N489" s="9" t="n">
-        <v>95.544766</v>
+        <v>95.55669399999999</v>
       </c>
       <c r="O489" s="9" t="n">
         <v>98.667036</v>
@@ -40383,7 +40383,7 @@
         <v>102.118757</v>
       </c>
       <c r="N490" s="6" t="n">
-        <v>93.05402599999999</v>
+        <v>93.073734</v>
       </c>
       <c r="O490" s="6" t="n">
         <v>98.58877699999999</v>
@@ -40467,7 +40467,7 @@
         <v>102.713129</v>
       </c>
       <c r="N491" s="9" t="n">
-        <v>95.727931</v>
+        <v>95.743156</v>
       </c>
       <c r="O491" s="9" t="n">
         <v>98.58478100000001</v>
@@ -40551,7 +40551,7 @@
         <v>103.122046</v>
       </c>
       <c r="N492" s="6" t="n">
-        <v>96.061317</v>
+        <v>96.07962499999999</v>
       </c>
       <c r="O492" s="6" t="n">
         <v>98.681675</v>
@@ -40635,7 +40635,7 @@
         <v>103.334912</v>
       </c>
       <c r="N493" s="9" t="n">
-        <v>97.099683</v>
+        <v>97.10638899999999</v>
       </c>
       <c r="O493" s="9" t="n">
         <v>98.878523</v>
@@ -40719,7 +40719,7 @@
         <v>103.386234</v>
       </c>
       <c r="N494" s="6" t="n">
-        <v>97.44334499999999</v>
+        <v>97.453835</v>
       </c>
       <c r="O494" s="6" t="n">
         <v>99.15967499999999</v>
@@ -40803,7 +40803,7 @@
         <v>103.327991</v>
       </c>
       <c r="N495" s="9" t="n">
-        <v>97.834868</v>
+        <v>97.844987</v>
       </c>
       <c r="O495" s="9" t="n">
         <v>99.46768899999999</v>
@@ -40887,7 +40887,7 @@
         <v>103.218996</v>
       </c>
       <c r="N496" s="6" t="n">
-        <v>98.223889</v>
+        <v>98.23362299999999</v>
       </c>
       <c r="O496" s="6" t="n">
         <v>99.764928</v>
@@ -40971,7 +40971,7 @@
         <v>103.104657</v>
       </c>
       <c r="N497" s="9" t="n">
-        <v>98.561145</v>
+        <v>98.57064699999999</v>
       </c>
       <c r="O497" s="9" t="n">
         <v>100.034038</v>
@@ -41055,7 +41055,7 @@
         <v>103.019589</v>
       </c>
       <c r="N498" s="6" t="n">
-        <v>98.834394</v>
+        <v>98.843762</v>
       </c>
       <c r="O498" s="6" t="n">
         <v>100.254969</v>
@@ -41139,7 +41139,7 @@
         <v>102.905384</v>
       </c>
       <c r="N499" s="9" t="n">
-        <v>99.057787</v>
+        <v>99.067261</v>
       </c>
       <c r="O499" s="9" t="n">
         <v>100.433784</v>
@@ -41223,7 +41223,7 @@
         <v>102.770952</v>
       </c>
       <c r="N500" s="6" t="n">
-        <v>99.27468399999999</v>
+        <v>99.284261</v>
       </c>
       <c r="O500" s="6" t="n">
         <v>100.605971</v>
@@ -41307,7 +41307,7 @@
         <v>102.608069</v>
       </c>
       <c r="N501" s="9" t="n">
-        <v>99.496961</v>
+        <v>99.506621</v>
       </c>
       <c r="O501" s="9" t="n">
         <v>100.7565</v>
@@ -41391,7 +41391,7 @@
         <v>102.41672</v>
       </c>
       <c r="N502" s="6" t="n">
-        <v>99.71266900000001</v>
+        <v>99.72223</v>
       </c>
       <c r="O502" s="6" t="n">
         <v>100.853147</v>
@@ -41475,7 +41475,7 @@
         <v>102.245137</v>
       </c>
       <c r="N503" s="9" t="n">
-        <v>99.901359</v>
+        <v>99.910652</v>
       </c>
       <c r="O503" s="9" t="n">
         <v>100.870491</v>
@@ -41559,7 +41559,7 @@
         <v>102.107648</v>
       </c>
       <c r="N504" s="6" t="n">
-        <v>100.059735</v>
+        <v>100.06839</v>
       </c>
       <c r="O504" s="6" t="n">
         <v>100.809521</v>
@@ -41643,7 +41643,7 @@
         <v>101.984296</v>
       </c>
       <c r="N505" s="9" t="n">
-        <v>100.180721</v>
+        <v>100.188481</v>
       </c>
       <c r="O505" s="9" t="n">
         <v>100.69003</v>
@@ -41727,7 +41727,7 @@
         <v>101.864353</v>
       </c>
       <c r="N506" s="6" t="n">
-        <v>100.293809</v>
+        <v>100.300791</v>
       </c>
       <c r="O506" s="6" t="n">
         <v>100.540372</v>
@@ -41811,7 +41811,7 @@
         <v>101.741478</v>
       </c>
       <c r="N507" s="9" t="n">
-        <v>100.425671</v>
+        <v>100.432031</v>
       </c>
       <c r="O507" s="9" t="n">
         <v>100.380557</v>
@@ -41895,7 +41895,7 @@
         <v>101.619014</v>
       </c>
       <c r="N508" s="6" t="n">
-        <v>100.582879</v>
+        <v>100.588669</v>
       </c>
       <c r="O508" s="6" t="n">
         <v>100.250627</v>
@@ -41979,7 +41979,7 @@
         <v>101.494387</v>
       </c>
       <c r="N509" s="9" t="n">
-        <v>100.75952</v>
+        <v>100.764847</v>
       </c>
       <c r="O509" s="9" t="n">
         <v>100.165921</v>
@@ -42063,7 +42063,7 @@
         <v>101.341838</v>
       </c>
       <c r="N510" s="6" t="n">
-        <v>100.949082</v>
+        <v>100.954178</v>
       </c>
       <c r="O510" s="6" t="n">
         <v>100.124167</v>
@@ -42147,7 +42147,7 @@
         <v>101.131597</v>
       </c>
       <c r="N511" s="9" t="n">
-        <v>101.158641</v>
+        <v>101.163991</v>
       </c>
       <c r="O511" s="9" t="n">
         <v>100.114886</v>
@@ -42231,7 +42231,7 @@
         <v>100.838256</v>
       </c>
       <c r="N512" s="6" t="n">
-        <v>101.360203</v>
+        <v>101.365937</v>
       </c>
       <c r="O512" s="6" t="n">
         <v>100.113233</v>
@@ -42315,7 +42315,7 @@
         <v>100.547023</v>
       </c>
       <c r="N513" s="9" t="n">
-        <v>101.528176</v>
+        <v>101.534089</v>
       </c>
       <c r="O513" s="9" t="n">
         <v>100.130151</v>
@@ -42399,7 +42399,7 @@
         <v>100.317165</v>
       </c>
       <c r="N514" s="6" t="n">
-        <v>101.638937</v>
+        <v>101.644665</v>
       </c>
       <c r="O514" s="6" t="n">
         <v>100.184271</v>
@@ -42483,7 +42483,7 @@
         <v>100.145127</v>
       </c>
       <c r="N515" s="9" t="n">
-        <v>101.676133</v>
+        <v>101.681153</v>
       </c>
       <c r="O515" s="9" t="n">
         <v>100.25998</v>
@@ -42567,7 +42567,7 @@
         <v>100.014042</v>
       </c>
       <c r="N516" s="6" t="n">
-        <v>101.626996</v>
+        <v>101.630796</v>
       </c>
       <c r="O516" s="6" t="n">
         <v>100.331625</v>
@@ -42651,7 +42651,7 @@
         <v>99.919135</v>
       </c>
       <c r="N517" s="9" t="n">
-        <v>101.505375</v>
+        <v>101.507476</v>
       </c>
       <c r="O517" s="9" t="n">
         <v>100.380929</v>
@@ -42735,7 +42735,7 @@
         <v>99.83895099999999</v>
       </c>
       <c r="N518" s="6" t="n">
-        <v>101.3427</v>
+        <v>101.343523</v>
       </c>
       <c r="O518" s="6" t="n">
         <v>100.428309</v>
@@ -42819,7 +42819,7 @@
         <v>99.75003700000001</v>
       </c>
       <c r="N519" s="9" t="n">
-        <v>101.166546</v>
+        <v>101.166503</v>
       </c>
       <c r="O519" s="9" t="n">
         <v>100.480743</v>
@@ -42903,7 +42903,7 @@
         <v>99.61024500000001</v>
       </c>
       <c r="N520" s="6" t="n">
-        <v>101.002344</v>
+        <v>101.001868</v>
       </c>
       <c r="O520" s="6" t="n">
         <v>100.523257</v>
@@ -42987,7 +42987,7 @@
         <v>99.439331</v>
       </c>
       <c r="N521" s="9" t="n">
-        <v>100.871385</v>
+        <v>100.870706</v>
       </c>
       <c r="O521" s="9" t="n">
         <v>100.574339</v>
@@ -43071,7 +43071,7 @@
         <v>99.24552799999999</v>
       </c>
       <c r="N522" s="6" t="n">
-        <v>100.764292</v>
+        <v>100.763686</v>
       </c>
       <c r="O522" s="6" t="n">
         <v>100.642645</v>
@@ -43155,7 +43155,7 @@
         <v>99.067223</v>
       </c>
       <c r="N523" s="9" t="n">
-        <v>100.663586</v>
+        <v>100.663368</v>
       </c>
       <c r="O523" s="9" t="n">
         <v>100.713739</v>
@@ -43239,7 +43239,7 @@
         <v>98.927182</v>
       </c>
       <c r="N524" s="6" t="n">
-        <v>100.567512</v>
+        <v>100.567792</v>
       </c>
       <c r="O524" s="6" t="n">
         <v>100.766164</v>
@@ -43323,7 +43323,7 @@
         <v>98.829159</v>
       </c>
       <c r="N525" s="9" t="n">
-        <v>100.476974</v>
+        <v>100.477409</v>
       </c>
       <c r="O525" s="9" t="n">
         <v>100.780831</v>
@@ -43407,7 +43407,7 @@
         <v>98.743075</v>
       </c>
       <c r="N526" s="6" t="n">
-        <v>100.38367</v>
+        <v>100.383687</v>
       </c>
       <c r="O526" s="6" t="n">
         <v>100.74651</v>
@@ -43491,7 +43491,7 @@
         <v>98.69872100000001</v>
       </c>
       <c r="N527" s="9" t="n">
-        <v>100.292203</v>
+        <v>100.290873</v>
       </c>
       <c r="O527" s="9" t="n">
         <v>100.673886</v>
@@ -43575,7 +43575,7 @@
         <v>98.7244</v>
       </c>
       <c r="N528" s="6" t="n">
-        <v>100.21003</v>
+        <v>100.206185</v>
       </c>
       <c r="O528" s="6" t="n">
         <v>100.57701</v>
@@ -43659,7 +43659,7 @@
         <v>98.791405</v>
       </c>
       <c r="N529" s="9" t="n">
-        <v>100.14569</v>
+        <v>100.138378</v>
       </c>
       <c r="O529" s="9" t="n">
         <v>100.476548</v>
@@ -43743,7 +43743,7 @@
         <v>98.885837</v>
       </c>
       <c r="N530" s="6" t="n">
-        <v>100.094836</v>
+        <v>100.084765</v>
       </c>
       <c r="O530" s="6" t="n">
         <v>100.384973</v>
@@ -43827,7 +43827,7 @@
         <v>98.990784</v>
       </c>
       <c r="N531" s="9" t="n">
-        <v>100.044959</v>
+        <v>100.032874</v>
       </c>
       <c r="O531" s="9" t="n">
         <v>100.324882</v>
@@ -43911,7 +43911,7 @@
         <v>99.086555</v>
       </c>
       <c r="N532" s="6" t="n">
-        <v>100.007873</v>
+        <v>99.994353</v>
       </c>
       <c r="O532" s="6" t="n">
         <v>100.317893</v>
@@ -43995,7 +43995,7 @@
         <v>99.164484</v>
       </c>
       <c r="N533" s="9" t="n">
-        <v>99.99654700000001</v>
+        <v>99.982116</v>
       </c>
       <c r="O533" s="9" t="n">
         <v>100.352183</v>
@@ -44079,7 +44079,7 @@
         <v>99.222487</v>
       </c>
       <c r="N534" s="6" t="n">
-        <v>100.012407</v>
+        <v>99.997514</v>
       </c>
       <c r="O534" s="6" t="n">
         <v>100.40148</v>
@@ -44163,7 +44163,7 @@
         <v>99.26419300000001</v>
       </c>
       <c r="N535" s="9" t="n">
-        <v>100.040139</v>
+        <v>100.025173</v>
       </c>
       <c r="O535" s="9" t="n">
         <v>100.43898</v>
@@ -44247,7 +44247,7 @@
         <v>99.29733</v>
       </c>
       <c r="N536" s="6" t="n">
-        <v>100.042585</v>
+        <v>100.027704</v>
       </c>
       <c r="O536" s="6" t="n">
         <v>100.463058</v>
@@ -44331,7 +44331,7 @@
         <v>99.32158099999999</v>
       </c>
       <c r="N537" s="9" t="n">
-        <v>100.017249</v>
+        <v>100.001897</v>
       </c>
       <c r="O537" s="9" t="n">
         <v>100.464657</v>
@@ -44415,7 +44415,7 @@
         <v>99.34638200000001</v>
       </c>
       <c r="N538" s="6" t="n">
-        <v>99.96810600000001</v>
+        <v>99.951207</v>
       </c>
       <c r="O538" s="6" t="n">
         <v>100.44067</v>
@@ -44499,7 +44499,7 @@
         <v>99.352293</v>
       </c>
       <c r="N539" s="9" t="n">
-        <v>99.90411899999999</v>
+        <v>99.884123</v>
       </c>
       <c r="O539" s="9" t="n">
         <v>100.39169</v>
@@ -44583,7 +44583,7 @@
         <v>99.31580599999999</v>
       </c>
       <c r="N540" s="6" t="n">
-        <v>99.822546</v>
+        <v>99.79774500000001</v>
       </c>
       <c r="O540" s="6" t="n">
         <v>100.323872</v>
@@ -44667,7 +44667,7 @@
         <v>99.24623099999999</v>
       </c>
       <c r="N541" s="9" t="n">
-        <v>99.727885</v>
+        <v>99.696808</v>
       </c>
       <c r="O541" s="9" t="n">
         <v>100.254403</v>
@@ -44751,7 +44751,7 @@
         <v>99.16469499999999</v>
       </c>
       <c r="N542" s="6" t="n">
-        <v>99.62104100000001</v>
+        <v>99.585432</v>
       </c>
       <c r="O542" s="6" t="n">
         <v>100.187339</v>
@@ -44835,7 +44835,7 @@
         <v>99.099536</v>
       </c>
       <c r="N543" s="9" t="n">
-        <v>99.524879</v>
+        <v>99.486316</v>
       </c>
       <c r="O543" s="9" t="n">
         <v>100.10804</v>
@@ -44919,7 +44919,7 @@
         <v>99.09106</v>
       </c>
       <c r="N544" s="6" t="n">
-        <v>99.43491299999999</v>
+        <v>99.394492</v>
       </c>
       <c r="O544" s="6" t="n">
         <v>100.007474</v>
@@ -45003,7 +45003,7 @@
         <v>99.124756</v>
       </c>
       <c r="N545" s="9" t="n">
-        <v>99.34053</v>
+        <v>99.298998</v>
       </c>
       <c r="O545" s="9" t="n">
         <v>99.876864</v>
@@ -45087,7 +45087,7 @@
         <v>99.17992599999999</v>
       </c>
       <c r="N546" s="6" t="n">
-        <v>99.249089</v>
+        <v>99.206896</v>
       </c>
       <c r="O546" s="6" t="n">
         <v>99.73588599999999</v>
@@ -45171,7 +45171,7 @@
         <v>99.239465</v>
       </c>
       <c r="N547" s="9" t="n">
-        <v>99.171885</v>
+        <v>99.12917299999999</v>
       </c>
       <c r="O547" s="9" t="n">
         <v>99.589375</v>
@@ -45255,7 +45255,7 @@
         <v>99.30811199999999</v>
       </c>
       <c r="N548" s="6" t="n">
-        <v>99.12424900000001</v>
+        <v>99.080938</v>
       </c>
       <c r="O548" s="6" t="n">
         <v>99.443596</v>
@@ -45339,7 +45339,7 @@
         <v>99.41411100000001</v>
       </c>
       <c r="N549" s="9" t="n">
-        <v>99.098016</v>
+        <v>99.05335599999999</v>
       </c>
       <c r="O549" s="9" t="n">
         <v>99.329407</v>
@@ -45423,7 +45423,7 @@
         <v>99.522002</v>
       </c>
       <c r="N550" s="6" t="n">
-        <v>99.09165400000001</v>
+        <v>99.044051</v>
       </c>
       <c r="O550" s="6" t="n">
         <v>99.256207</v>
@@ -45507,7 +45507,7 @@
         <v>99.63457099999999</v>
       </c>
       <c r="N551" s="9" t="n">
-        <v>99.113012</v>
+        <v>99.06027</v>
       </c>
       <c r="O551" s="9" t="n">
         <v>99.219632</v>
@@ -45591,7 +45591,7 @@
         <v>99.766857</v>
       </c>
       <c r="N552" s="6" t="n">
-        <v>99.168695</v>
+        <v>99.10844299999999</v>
       </c>
       <c r="O552" s="6" t="n">
         <v>99.206112</v>
@@ -45675,7 +45675,7 @@
         <v>99.930751</v>
       </c>
       <c r="N553" s="9" t="n">
-        <v>99.263171</v>
+        <v>99.19386799999999</v>
       </c>
       <c r="O553" s="9" t="n">
         <v>99.20610600000001</v>
@@ -45759,7 +45759,7 @@
         <v>100.070674</v>
       </c>
       <c r="N554" s="6" t="n">
-        <v>99.378964</v>
+        <v>99.30423399999999</v>
       </c>
       <c r="O554" s="6" t="n">
         <v>99.208668</v>
@@ -45843,7 +45843,7 @@
         <v>100.151774</v>
       </c>
       <c r="N555" s="9" t="n">
-        <v>99.505286</v>
+        <v>99.42832</v>
       </c>
       <c r="O555" s="9" t="n">
         <v>99.22666700000001</v>
@@ -45927,7 +45927,7 @@
         <v>100.216711</v>
       </c>
       <c r="N556" s="6" t="n">
-        <v>99.634331</v>
+        <v>99.557726</v>
       </c>
       <c r="O556" s="6" t="n">
         <v>99.26781200000001</v>
@@ -46011,7 +46011,7 @@
         <v>100.285121</v>
       </c>
       <c r="N557" s="9" t="n">
-        <v>99.773279</v>
+        <v>99.698927</v>
       </c>
       <c r="O557" s="9" t="n">
         <v>99.350877</v>
@@ -46095,7 +46095,7 @@
         <v>100.389843</v>
       </c>
       <c r="N558" s="6" t="n">
-        <v>99.933976</v>
+        <v>99.862517</v>
       </c>
       <c r="O558" s="6" t="n">
         <v>99.47413400000001</v>
@@ -46179,7 +46179,7 @@
         <v>100.515751</v>
       </c>
       <c r="N559" s="9" t="n">
-        <v>100.126678</v>
+        <v>100.056753</v>
       </c>
       <c r="O559" s="9" t="n">
         <v>99.621951</v>
@@ -46263,7 +46263,7 @@
         <v>100.635757</v>
       </c>
       <c r="N560" s="6" t="n">
-        <v>100.354928</v>
+        <v>100.282217</v>
       </c>
       <c r="O560" s="6" t="n">
         <v>99.782504</v>
@@ -46347,7 +46347,7 @@
         <v>100.715535</v>
       </c>
       <c r="N561" s="9" t="n">
-        <v>100.615919</v>
+        <v>100.53139</v>
       </c>
       <c r="O561" s="9" t="n">
         <v>99.92449000000001</v>
@@ -46431,7 +46431,7 @@
         <v>100.746164</v>
       </c>
       <c r="N562" s="6" t="n">
-        <v>100.906045</v>
+        <v>100.79495</v>
       </c>
       <c r="O562" s="6" t="n">
         <v>100.050948</v>
@@ -46515,7 +46515,7 @@
         <v>100.719442</v>
       </c>
       <c r="N563" s="9" t="n">
-        <v>101.22779</v>
+        <v>101.069159</v>
       </c>
       <c r="O563" s="9" t="n">
         <v>100.157408</v>
@@ -46593,7 +46593,7 @@
         <v>100.638019</v>
       </c>
       <c r="N564" s="6" t="n">
-        <v>101.591978</v>
+        <v>101.360238</v>
       </c>
       <c r="O564" s="6" t="n">
         <v>100.255278</v>

--- a/downloads/indicadores/SIC/SIC_datos.xlsx
+++ b/downloads/indicadores/SIC/SIC_datos.xlsx
@@ -23925,7 +23925,7 @@
         <v>100.593126</v>
       </c>
       <c r="P294" s="6" t="n">
-        <v>98.540752</v>
+        <v>98.536314</v>
       </c>
       <c r="Q294" s="6" t="n">
         <v>99.62402400000001</v>
@@ -24009,7 +24009,7 @@
         <v>100.782798</v>
       </c>
       <c r="P295" s="9" t="n">
-        <v>98.703875</v>
+        <v>98.69995299999999</v>
       </c>
       <c r="Q295" s="9" t="n">
         <v>99.71603500000001</v>
@@ -24093,7 +24093,7 @@
         <v>100.962147</v>
       </c>
       <c r="P296" s="6" t="n">
-        <v>98.876873</v>
+        <v>98.873496</v>
       </c>
       <c r="Q296" s="6" t="n">
         <v>99.74854999999999</v>
@@ -24177,7 +24177,7 @@
         <v>101.09328</v>
       </c>
       <c r="P297" s="9" t="n">
-        <v>99.06832300000001</v>
+        <v>99.065544</v>
       </c>
       <c r="Q297" s="9" t="n">
         <v>99.722976</v>
@@ -24261,7 +24261,7 @@
         <v>101.134342</v>
       </c>
       <c r="P298" s="6" t="n">
-        <v>99.247865</v>
+        <v>99.245644</v>
       </c>
       <c r="Q298" s="6" t="n">
         <v>99.672467</v>
@@ -24345,7 +24345,7 @@
         <v>101.083115</v>
       </c>
       <c r="P299" s="9" t="n">
-        <v>99.386276</v>
+        <v>99.38448200000001</v>
       </c>
       <c r="Q299" s="9" t="n">
         <v>99.62397900000001</v>
@@ -24429,7 +24429,7 @@
         <v>100.977641</v>
       </c>
       <c r="P300" s="6" t="n">
-        <v>99.484945</v>
+        <v>99.48344899999999</v>
       </c>
       <c r="Q300" s="6" t="n">
         <v>99.59861100000001</v>
@@ -24513,7 +24513,7 @@
         <v>100.846366</v>
       </c>
       <c r="P301" s="9" t="n">
-        <v>99.551771</v>
+        <v>99.550466</v>
       </c>
       <c r="Q301" s="9" t="n">
         <v>99.617704</v>
@@ -24597,7 +24597,7 @@
         <v>100.711857</v>
       </c>
       <c r="P302" s="6" t="n">
-        <v>99.60554</v>
+        <v>99.604377</v>
       </c>
       <c r="Q302" s="6" t="n">
         <v>99.685011</v>
@@ -24681,7 +24681,7 @@
         <v>100.573441</v>
       </c>
       <c r="P303" s="9" t="n">
-        <v>99.662926</v>
+        <v>99.661912</v>
       </c>
       <c r="Q303" s="9" t="n">
         <v>99.780129</v>
@@ -24765,7 +24765,7 @@
         <v>100.483985</v>
       </c>
       <c r="P304" s="6" t="n">
-        <v>99.722613</v>
+        <v>99.721756</v>
       </c>
       <c r="Q304" s="6" t="n">
         <v>99.87445099999999</v>
@@ -24849,7 +24849,7 @@
         <v>100.431373</v>
       </c>
       <c r="P305" s="9" t="n">
-        <v>99.780147</v>
+        <v>99.779448</v>
       </c>
       <c r="Q305" s="9" t="n">
         <v>99.939657</v>
@@ -24933,7 +24933,7 @@
         <v>100.383643</v>
       </c>
       <c r="P306" s="6" t="n">
-        <v>99.83928299999999</v>
+        <v>99.838756</v>
       </c>
       <c r="Q306" s="6" t="n">
         <v>99.950822</v>
@@ -25017,7 +25017,7 @@
         <v>100.251411</v>
       </c>
       <c r="P307" s="9" t="n">
-        <v>99.90753599999999</v>
+        <v>99.90722100000001</v>
       </c>
       <c r="Q307" s="9" t="n">
         <v>99.90555500000001</v>
@@ -25101,7 +25101,7 @@
         <v>100.070944</v>
       </c>
       <c r="P308" s="6" t="n">
-        <v>99.982005</v>
+        <v>99.98192899999999</v>
       </c>
       <c r="Q308" s="6" t="n">
         <v>99.820559</v>
@@ -25185,7 +25185,7 @@
         <v>99.876531</v>
       </c>
       <c r="P309" s="9" t="n">
-        <v>100.054023</v>
+        <v>100.054185</v>
       </c>
       <c r="Q309" s="9" t="n">
         <v>99.75062800000001</v>
@@ -25269,7 +25269,7 @@
         <v>99.72992000000001</v>
       </c>
       <c r="P310" s="6" t="n">
-        <v>100.112333</v>
+        <v>100.112691</v>
       </c>
       <c r="Q310" s="6" t="n">
         <v>99.73730999999999</v>
@@ -25353,7 +25353,7 @@
         <v>99.671594</v>
       </c>
       <c r="P311" s="9" t="n">
-        <v>100.157176</v>
+        <v>100.157686</v>
       </c>
       <c r="Q311" s="9" t="n">
         <v>99.786838</v>
@@ -25437,7 +25437,7 @@
         <v>99.719598</v>
       </c>
       <c r="P312" s="6" t="n">
-        <v>100.183393</v>
+        <v>100.183987</v>
       </c>
       <c r="Q312" s="6" t="n">
         <v>99.889528</v>
@@ -25521,7 +25521,7 @@
         <v>99.86323</v>
       </c>
       <c r="P313" s="9" t="n">
-        <v>100.203185</v>
+        <v>100.203832</v>
       </c>
       <c r="Q313" s="9" t="n">
         <v>100.027822</v>
@@ -25605,7 +25605,7 @@
         <v>100.026447</v>
       </c>
       <c r="P314" s="6" t="n">
-        <v>100.233539</v>
+        <v>100.234257</v>
       </c>
       <c r="Q314" s="6" t="n">
         <v>100.192269</v>
@@ -25689,7 +25689,7 @@
         <v>100.20532</v>
       </c>
       <c r="P315" s="9" t="n">
-        <v>100.273473</v>
+        <v>100.274284</v>
       </c>
       <c r="Q315" s="9" t="n">
         <v>100.354791</v>
@@ -25773,7 +25773,7 @@
         <v>100.353575</v>
       </c>
       <c r="P316" s="6" t="n">
-        <v>100.319489</v>
+        <v>100.320411</v>
       </c>
       <c r="Q316" s="6" t="n">
         <v>100.511062</v>
@@ -25857,7 +25857,7 @@
         <v>100.459646</v>
       </c>
       <c r="P317" s="9" t="n">
-        <v>100.381873</v>
+        <v>100.382964</v>
       </c>
       <c r="Q317" s="9" t="n">
         <v>100.645611</v>
@@ -25941,7 +25941,7 @@
         <v>100.550188</v>
       </c>
       <c r="P318" s="6" t="n">
-        <v>100.46471</v>
+        <v>100.466043</v>
       </c>
       <c r="Q318" s="6" t="n">
         <v>100.742199</v>
@@ -26025,7 +26025,7 @@
         <v>100.673678</v>
       </c>
       <c r="P319" s="9" t="n">
-        <v>100.575136</v>
+        <v>100.576808</v>
       </c>
       <c r="Q319" s="9" t="n">
         <v>100.791261</v>
@@ -26109,7 +26109,7 @@
         <v>100.831421</v>
       </c>
       <c r="P320" s="6" t="n">
-        <v>100.680562</v>
+        <v>100.68257</v>
       </c>
       <c r="Q320" s="6" t="n">
         <v>100.802487</v>
@@ -26193,7 +26193,7 @@
         <v>101.004165</v>
       </c>
       <c r="P321" s="9" t="n">
-        <v>100.774705</v>
+        <v>100.777022</v>
       </c>
       <c r="Q321" s="9" t="n">
         <v>100.785345</v>
@@ -26277,7 +26277,7 @@
         <v>101.169937</v>
       </c>
       <c r="P322" s="6" t="n">
-        <v>100.863466</v>
+        <v>100.866076</v>
       </c>
       <c r="Q322" s="6" t="n">
         <v>100.754254</v>
@@ -26361,7 +26361,7 @@
         <v>101.250011</v>
       </c>
       <c r="P323" s="9" t="n">
-        <v>100.951543</v>
+        <v>100.954439</v>
       </c>
       <c r="Q323" s="9" t="n">
         <v>100.756692</v>
@@ -26445,7 +26445,7 @@
         <v>101.203612</v>
       </c>
       <c r="P324" s="6" t="n">
-        <v>101.056797</v>
+        <v>101.060017</v>
       </c>
       <c r="Q324" s="6" t="n">
         <v>100.815207</v>
@@ -26529,7 +26529,7 @@
         <v>101.069745</v>
       </c>
       <c r="P325" s="9" t="n">
-        <v>101.179752</v>
+        <v>101.183334</v>
       </c>
       <c r="Q325" s="9" t="n">
         <v>100.931193</v>
@@ -26613,7 +26613,7 @@
         <v>100.897384</v>
       </c>
       <c r="P326" s="6" t="n">
-        <v>101.292858</v>
+        <v>101.296754</v>
       </c>
       <c r="Q326" s="6" t="n">
         <v>101.096405</v>
@@ -26697,7 +26697,7 @@
         <v>100.727294</v>
       </c>
       <c r="P327" s="9" t="n">
-        <v>101.390583</v>
+        <v>101.394739</v>
       </c>
       <c r="Q327" s="9" t="n">
         <v>101.298183</v>
@@ -26781,7 +26781,7 @@
         <v>100.575573</v>
       </c>
       <c r="P328" s="6" t="n">
-        <v>101.492127</v>
+        <v>101.496553</v>
       </c>
       <c r="Q328" s="6" t="n">
         <v>101.515987</v>
@@ -26865,7 +26865,7 @@
         <v>100.469269</v>
       </c>
       <c r="P329" s="9" t="n">
-        <v>101.602763</v>
+        <v>101.607496</v>
       </c>
       <c r="Q329" s="9" t="n">
         <v>101.722834</v>
@@ -26949,7 +26949,7 @@
         <v>100.437394</v>
       </c>
       <c r="P330" s="6" t="n">
-        <v>101.716976</v>
+        <v>101.722044</v>
       </c>
       <c r="Q330" s="6" t="n">
         <v>101.901627</v>
@@ -27033,7 +27033,7 @@
         <v>100.486409</v>
       </c>
       <c r="P331" s="9" t="n">
-        <v>101.814597</v>
+        <v>101.819967</v>
       </c>
       <c r="Q331" s="9" t="n">
         <v>102.050419</v>
@@ -27117,7 +27117,7 @@
         <v>100.557355</v>
       </c>
       <c r="P332" s="6" t="n">
-        <v>101.884329</v>
+        <v>101.889934</v>
       </c>
       <c r="Q332" s="6" t="n">
         <v>102.181358</v>
@@ -27201,7 +27201,7 @@
         <v>100.625063</v>
       </c>
       <c r="P333" s="9" t="n">
-        <v>101.925133</v>
+        <v>101.930893</v>
       </c>
       <c r="Q333" s="9" t="n">
         <v>102.283007</v>
@@ -27285,7 +27285,7 @@
         <v>100.664964</v>
       </c>
       <c r="P334" s="6" t="n">
-        <v>101.945441</v>
+        <v>101.951296</v>
       </c>
       <c r="Q334" s="6" t="n">
         <v>102.343454</v>
@@ -27369,7 +27369,7 @@
         <v>100.726715</v>
       </c>
       <c r="P335" s="9" t="n">
-        <v>101.973837</v>
+        <v>101.979804</v>
       </c>
       <c r="Q335" s="9" t="n">
         <v>102.341101</v>
@@ -27453,7 +27453,7 @@
         <v>100.830734</v>
       </c>
       <c r="P336" s="6" t="n">
-        <v>102.019448</v>
+        <v>102.025564</v>
       </c>
       <c r="Q336" s="6" t="n">
         <v>102.278883</v>
@@ -27537,7 +27537,7 @@
         <v>100.938252</v>
       </c>
       <c r="P337" s="9" t="n">
-        <v>102.073088</v>
+        <v>102.079357</v>
       </c>
       <c r="Q337" s="9" t="n">
         <v>102.173165</v>
@@ -27621,7 +27621,7 @@
         <v>101.025242</v>
       </c>
       <c r="P338" s="6" t="n">
-        <v>102.117936</v>
+        <v>102.124311</v>
       </c>
       <c r="Q338" s="6" t="n">
         <v>102.041262</v>
@@ -27705,7 +27705,7 @@
         <v>101.022981</v>
       </c>
       <c r="P339" s="9" t="n">
-        <v>102.126047</v>
+        <v>102.132406</v>
       </c>
       <c r="Q339" s="9" t="n">
         <v>101.895441</v>
@@ -27789,7 +27789,7 @@
         <v>100.962321</v>
       </c>
       <c r="P340" s="6" t="n">
-        <v>102.054641</v>
+        <v>102.060746</v>
       </c>
       <c r="Q340" s="6" t="n">
         <v>101.741623</v>
@@ -27873,7 +27873,7 @@
         <v>100.864235</v>
       </c>
       <c r="P341" s="9" t="n">
-        <v>101.867877</v>
+        <v>101.873394</v>
       </c>
       <c r="Q341" s="9" t="n">
         <v>101.602397</v>
@@ -27957,7 +27957,7 @@
         <v>100.707986</v>
       </c>
       <c r="P342" s="6" t="n">
-        <v>101.585665</v>
+        <v>101.590329</v>
       </c>
       <c r="Q342" s="6" t="n">
         <v>101.489513</v>
@@ -28041,7 +28041,7 @@
         <v>100.478227</v>
       </c>
       <c r="P343" s="9" t="n">
-        <v>101.243023</v>
+        <v>101.246674</v>
       </c>
       <c r="Q343" s="9" t="n">
         <v>101.402357</v>
@@ -28125,7 +28125,7 @@
         <v>100.20346</v>
       </c>
       <c r="P344" s="6" t="n">
-        <v>100.88378</v>
+        <v>100.886384</v>
       </c>
       <c r="Q344" s="6" t="n">
         <v>101.315061</v>
@@ -28209,7 +28209,7 @@
         <v>99.88559100000001</v>
       </c>
       <c r="P345" s="9" t="n">
-        <v>100.531239</v>
+        <v>100.532826</v>
       </c>
       <c r="Q345" s="9" t="n">
         <v>101.178782</v>
@@ -28293,7 +28293,7 @@
         <v>99.541909</v>
       </c>
       <c r="P346" s="6" t="n">
-        <v>100.187058</v>
+        <v>100.187652</v>
       </c>
       <c r="Q346" s="6" t="n">
         <v>100.955255</v>
@@ -28377,7 +28377,7 @@
         <v>99.154095</v>
       </c>
       <c r="P347" s="9" t="n">
-        <v>99.7984</v>
+        <v>99.797861</v>
       </c>
       <c r="Q347" s="9" t="n">
         <v>100.609962</v>
@@ -28461,7 +28461,7 @@
         <v>98.72523099999999</v>
       </c>
       <c r="P348" s="6" t="n">
-        <v>99.30520300000001</v>
+        <v>99.303201</v>
       </c>
       <c r="Q348" s="6" t="n">
         <v>100.153682</v>
@@ -28545,7 +28545,7 @@
         <v>98.233794</v>
       </c>
       <c r="P349" s="9" t="n">
-        <v>98.675124</v>
+        <v>98.671228</v>
       </c>
       <c r="Q349" s="9" t="n">
         <v>99.616022</v>
@@ -28629,7 +28629,7 @@
         <v>97.709093</v>
       </c>
       <c r="P350" s="6" t="n">
-        <v>97.90809900000001</v>
+        <v>97.901875</v>
       </c>
       <c r="Q350" s="6" t="n">
         <v>99.035662</v>
@@ -28713,7 +28713,7 @@
         <v>97.21190300000001</v>
       </c>
       <c r="P351" s="9" t="n">
-        <v>97.08127500000001</v>
+        <v>97.072532</v>
       </c>
       <c r="Q351" s="9" t="n">
         <v>98.46801499999999</v>
@@ -28797,7 +28797,7 @@
         <v>96.808053</v>
       </c>
       <c r="P352" s="6" t="n">
-        <v>96.31001500000001</v>
+        <v>96.29892</v>
       </c>
       <c r="Q352" s="6" t="n">
         <v>97.99027700000001</v>
@@ -28881,7 +28881,7 @@
         <v>96.50884600000001</v>
       </c>
       <c r="P353" s="9" t="n">
-        <v>95.69615</v>
+        <v>95.68318600000001</v>
       </c>
       <c r="Q353" s="9" t="n">
         <v>97.629774</v>
@@ -28965,7 +28965,7 @@
         <v>96.27739</v>
       </c>
       <c r="P354" s="6" t="n">
-        <v>95.31896399999999</v>
+        <v>95.30486399999999</v>
       </c>
       <c r="Q354" s="6" t="n">
         <v>97.39106099999999</v>
@@ -29049,7 +29049,7 @@
         <v>96.14963299999999</v>
       </c>
       <c r="P355" s="9" t="n">
-        <v>95.183716</v>
+        <v>95.16922599999999</v>
       </c>
       <c r="Q355" s="9" t="n">
         <v>97.320742</v>
@@ -29133,7 +29133,7 @@
         <v>96.15516</v>
       </c>
       <c r="P356" s="6" t="n">
-        <v>95.27273</v>
+        <v>95.258537</v>
       </c>
       <c r="Q356" s="6" t="n">
         <v>97.448117</v>
@@ -29217,7 +29217,7 @@
         <v>96.35382199999999</v>
       </c>
       <c r="P357" s="9" t="n">
-        <v>95.499116</v>
+        <v>95.48564</v>
       </c>
       <c r="Q357" s="9" t="n">
         <v>97.733762</v>
@@ -29301,7 +29301,7 @@
         <v>96.743914</v>
       </c>
       <c r="P358" s="6" t="n">
-        <v>95.785263</v>
+        <v>95.772683</v>
       </c>
       <c r="Q358" s="6" t="n">
         <v>98.107777</v>
@@ -29385,7 +29385,7 @@
         <v>97.298091</v>
       </c>
       <c r="P359" s="9" t="n">
-        <v>96.093588</v>
+        <v>96.08196100000001</v>
       </c>
       <c r="Q359" s="9" t="n">
         <v>98.502821</v>
@@ -29469,7 +29469,7 @@
         <v>97.952263</v>
       </c>
       <c r="P360" s="6" t="n">
-        <v>96.397431</v>
+        <v>96.38672800000001</v>
       </c>
       <c r="Q360" s="6" t="n">
         <v>98.882034</v>
@@ -29553,7 +29553,7 @@
         <v>98.65101900000001</v>
       </c>
       <c r="P361" s="9" t="n">
-        <v>96.696</v>
+        <v>96.686184</v>
       </c>
       <c r="Q361" s="9" t="n">
         <v>99.207392</v>
@@ -29637,7 +29637,7 @@
         <v>99.32866199999999</v>
       </c>
       <c r="P362" s="6" t="n">
-        <v>97.00365499999999</v>
+        <v>96.994731</v>
       </c>
       <c r="Q362" s="6" t="n">
         <v>99.463691</v>
@@ -29721,7 +29721,7 @@
         <v>99.96365299999999</v>
       </c>
       <c r="P363" s="9" t="n">
-        <v>97.308723</v>
+        <v>97.300673</v>
       </c>
       <c r="Q363" s="9" t="n">
         <v>99.65195300000001</v>
@@ -29805,7 +29805,7 @@
         <v>100.460083</v>
       </c>
       <c r="P364" s="6" t="n">
-        <v>97.61432499999999</v>
+        <v>97.60715</v>
       </c>
       <c r="Q364" s="6" t="n">
         <v>99.785927</v>
@@ -29889,7 +29889,7 @@
         <v>100.819533</v>
       </c>
       <c r="P365" s="9" t="n">
-        <v>97.955451</v>
+        <v>97.94927</v>
       </c>
       <c r="Q365" s="9" t="n">
         <v>99.86318</v>
@@ -29973,7 +29973,7 @@
         <v>101.100972</v>
       </c>
       <c r="P366" s="6" t="n">
-        <v>98.356904</v>
+        <v>98.351921</v>
       </c>
       <c r="Q366" s="6" t="n">
         <v>99.891302</v>
@@ -30057,7 +30057,7 @@
         <v>101.309975</v>
       </c>
       <c r="P367" s="9" t="n">
-        <v>98.840416</v>
+        <v>98.836896</v>
       </c>
       <c r="Q367" s="9" t="n">
         <v>99.89702</v>
@@ -30141,7 +30141,7 @@
         <v>101.469832</v>
       </c>
       <c r="P368" s="6" t="n">
-        <v>99.365357</v>
+        <v>99.363438</v>
       </c>
       <c r="Q368" s="6" t="n">
         <v>99.885969</v>
@@ -30225,7 +30225,7 @@
         <v>101.565326</v>
       </c>
       <c r="P369" s="9" t="n">
-        <v>99.872889</v>
+        <v>99.87252599999999</v>
       </c>
       <c r="Q369" s="9" t="n">
         <v>99.85785</v>
@@ -30309,7 +30309,7 @@
         <v>101.586304</v>
       </c>
       <c r="P370" s="6" t="n">
-        <v>100.319776</v>
+        <v>100.320785</v>
       </c>
       <c r="Q370" s="6" t="n">
         <v>99.827597</v>
@@ -30393,7 +30393,7 @@
         <v>101.538949</v>
       </c>
       <c r="P371" s="9" t="n">
-        <v>100.683748</v>
+        <v>100.685873</v>
       </c>
       <c r="Q371" s="9" t="n">
         <v>99.817001</v>
@@ -30477,7 +30477,7 @@
         <v>101.447629</v>
       </c>
       <c r="P372" s="6" t="n">
-        <v>100.964737</v>
+        <v>100.967715</v>
       </c>
       <c r="Q372" s="6" t="n">
         <v>99.846878</v>
@@ -30561,7 +30561,7 @@
         <v>101.332992</v>
       </c>
       <c r="P373" s="9" t="n">
-        <v>101.177499</v>
+        <v>101.181109</v>
       </c>
       <c r="Q373" s="9" t="n">
         <v>99.920451</v>
@@ -30645,7 +30645,7 @@
         <v>101.210698</v>
       </c>
       <c r="P374" s="6" t="n">
-        <v>101.333756</v>
+        <v>101.33781</v>
       </c>
       <c r="Q374" s="6" t="n">
         <v>100.036883</v>
@@ -30729,7 +30729,7 @@
         <v>101.051229</v>
       </c>
       <c r="P375" s="9" t="n">
-        <v>101.44882</v>
+        <v>101.453186</v>
       </c>
       <c r="Q375" s="9" t="n">
         <v>100.171469</v>
@@ -30813,7 +30813,7 @@
         <v>100.902368</v>
       </c>
       <c r="P376" s="6" t="n">
-        <v>101.529301</v>
+        <v>101.533877</v>
       </c>
       <c r="Q376" s="6" t="n">
         <v>100.289159</v>
@@ -30897,7 +30897,7 @@
         <v>100.800654</v>
       </c>
       <c r="P377" s="9" t="n">
-        <v>101.575154</v>
+        <v>101.579847</v>
       </c>
       <c r="Q377" s="9" t="n">
         <v>100.363929</v>
@@ -30981,7 +30981,7 @@
         <v>100.754268</v>
       </c>
       <c r="P378" s="6" t="n">
-        <v>101.591076</v>
+        <v>101.595816</v>
       </c>
       <c r="Q378" s="6" t="n">
         <v>100.382134</v>
@@ -31065,7 +31065,7 @@
         <v>100.764424</v>
       </c>
       <c r="P379" s="9" t="n">
-        <v>101.584829</v>
+        <v>101.589565</v>
       </c>
       <c r="Q379" s="9" t="n">
         <v>100.356769</v>
@@ -31149,7 +31149,7 @@
         <v>100.808062</v>
       </c>
       <c r="P380" s="6" t="n">
-        <v>101.559793</v>
+        <v>101.564479</v>
       </c>
       <c r="Q380" s="6" t="n">
         <v>100.299063</v>
@@ -31233,7 +31233,7 @@
         <v>100.864915</v>
       </c>
       <c r="P381" s="9" t="n">
-        <v>101.517019</v>
+        <v>101.521606</v>
       </c>
       <c r="Q381" s="9" t="n">
         <v>100.216602</v>
@@ -31317,7 +31317,7 @@
         <v>100.915419</v>
       </c>
       <c r="P382" s="6" t="n">
-        <v>101.453464</v>
+        <v>101.457888</v>
       </c>
       <c r="Q382" s="6" t="n">
         <v>100.120313</v>
@@ -31401,7 +31401,7 @@
         <v>100.956983</v>
       </c>
       <c r="P383" s="9" t="n">
-        <v>101.356787</v>
+        <v>101.36094</v>
       </c>
       <c r="Q383" s="9" t="n">
         <v>100.021428</v>
@@ -31485,7 +31485,7 @@
         <v>100.984146</v>
       </c>
       <c r="P384" s="6" t="n">
-        <v>101.223873</v>
+        <v>101.227638</v>
       </c>
       <c r="Q384" s="6" t="n">
         <v>99.923676</v>
@@ -31569,7 +31569,7 @@
         <v>101.021215</v>
       </c>
       <c r="P385" s="9" t="n">
-        <v>101.05839</v>
+        <v>101.061655</v>
       </c>
       <c r="Q385" s="9" t="n">
         <v>99.83911000000001</v>
@@ -31653,7 +31653,7 @@
         <v>101.075927</v>
       </c>
       <c r="P386" s="6" t="n">
-        <v>100.892982</v>
+        <v>100.895736</v>
       </c>
       <c r="Q386" s="6" t="n">
         <v>99.78235599999999</v>
@@ -31737,7 +31737,7 @@
         <v>101.167702</v>
       </c>
       <c r="P387" s="9" t="n">
-        <v>100.743841</v>
+        <v>100.746127</v>
       </c>
       <c r="Q387" s="9" t="n">
         <v>99.769779</v>
@@ -31821,7 +31821,7 @@
         <v>101.29389</v>
       </c>
       <c r="P388" s="6" t="n">
-        <v>100.622468</v>
+        <v>100.624368</v>
       </c>
       <c r="Q388" s="6" t="n">
         <v>99.786102</v>
@@ -31905,7 +31905,7 @@
         <v>101.412279</v>
       </c>
       <c r="P389" s="9" t="n">
-        <v>100.532177</v>
+        <v>100.533795</v>
       </c>
       <c r="Q389" s="9" t="n">
         <v>99.820724</v>
@@ -31989,7 +31989,7 @@
         <v>101.530935</v>
       </c>
       <c r="P390" s="6" t="n">
-        <v>100.470968</v>
+        <v>100.472404</v>
       </c>
       <c r="Q390" s="6" t="n">
         <v>99.868849</v>
@@ -32073,7 +32073,7 @@
         <v>101.59783</v>
       </c>
       <c r="P391" s="9" t="n">
-        <v>100.407419</v>
+        <v>100.408679</v>
       </c>
       <c r="Q391" s="9" t="n">
         <v>99.92652699999999</v>
@@ -32157,7 +32157,7 @@
         <v>101.558208</v>
       </c>
       <c r="P392" s="6" t="n">
-        <v>100.32358</v>
+        <v>100.324608</v>
       </c>
       <c r="Q392" s="6" t="n">
         <v>99.986734</v>
@@ -32241,7 +32241,7 @@
         <v>101.422647</v>
       </c>
       <c r="P393" s="9" t="n">
-        <v>100.229832</v>
+        <v>100.2306</v>
       </c>
       <c r="Q393" s="9" t="n">
         <v>100.038167</v>
@@ -32325,7 +32325,7 @@
         <v>101.26896</v>
       </c>
       <c r="P394" s="6" t="n">
-        <v>100.149119</v>
+        <v>100.149665</v>
       </c>
       <c r="Q394" s="6" t="n">
         <v>100.082667</v>
@@ -32409,7 +32409,7 @@
         <v>101.120029</v>
       </c>
       <c r="P395" s="9" t="n">
-        <v>100.105785</v>
+        <v>100.106215</v>
       </c>
       <c r="Q395" s="9" t="n">
         <v>100.130917</v>
@@ -32493,7 +32493,7 @@
         <v>100.958158</v>
       </c>
       <c r="P396" s="6" t="n">
-        <v>100.115546</v>
+        <v>100.11601</v>
       </c>
       <c r="Q396" s="6" t="n">
         <v>100.177558</v>
@@ -32577,7 +32577,7 @@
         <v>100.795446</v>
       </c>
       <c r="P397" s="9" t="n">
-        <v>100.178485</v>
+        <v>100.179137</v>
       </c>
       <c r="Q397" s="9" t="n">
         <v>100.225799</v>
@@ -32661,7 +32661,7 @@
         <v>100.665807</v>
       </c>
       <c r="P398" s="6" t="n">
-        <v>100.27945</v>
+        <v>100.280395</v>
       </c>
       <c r="Q398" s="6" t="n">
         <v>100.286449</v>
@@ -32745,7 +32745,7 @@
         <v>100.591797</v>
       </c>
       <c r="P399" s="9" t="n">
-        <v>100.406936</v>
+        <v>100.40825</v>
       </c>
       <c r="Q399" s="9" t="n">
         <v>100.354497</v>
@@ -32829,7 +32829,7 @@
         <v>100.536814</v>
       </c>
       <c r="P400" s="6" t="n">
-        <v>100.546553</v>
+        <v>100.548273</v>
       </c>
       <c r="Q400" s="6" t="n">
         <v>100.420484</v>
@@ -32913,7 +32913,7 @@
         <v>100.474474</v>
       </c>
       <c r="P401" s="9" t="n">
-        <v>100.692626</v>
+        <v>100.694777</v>
       </c>
       <c r="Q401" s="9" t="n">
         <v>100.471575</v>
@@ -32997,7 +32997,7 @@
         <v>100.314802</v>
       </c>
       <c r="P402" s="6" t="n">
-        <v>100.843309</v>
+        <v>100.845915</v>
       </c>
       <c r="Q402" s="6" t="n">
         <v>100.484887</v>
@@ -33081,7 +33081,7 @@
         <v>100.059657</v>
       </c>
       <c r="P403" s="9" t="n">
-        <v>100.975911</v>
+        <v>100.978925</v>
       </c>
       <c r="Q403" s="9" t="n">
         <v>100.445016</v>
@@ -33165,7 +33165,7 @@
         <v>99.78119700000001</v>
       </c>
       <c r="P404" s="6" t="n">
-        <v>101.068183</v>
+        <v>101.071487</v>
       </c>
       <c r="Q404" s="6" t="n">
         <v>100.358911</v>
@@ -33249,7 +33249,7 @@
         <v>99.52534199999999</v>
       </c>
       <c r="P405" s="9" t="n">
-        <v>101.113819</v>
+        <v>101.117273</v>
       </c>
       <c r="Q405" s="9" t="n">
         <v>100.241392</v>
@@ -33333,7 +33333,7 @@
         <v>99.291399</v>
       </c>
       <c r="P406" s="6" t="n">
-        <v>101.105563</v>
+        <v>101.109004</v>
       </c>
       <c r="Q406" s="6" t="n">
         <v>100.116082</v>
@@ -33417,7 +33417,7 @@
         <v>99.077575</v>
       </c>
       <c r="P407" s="9" t="n">
-        <v>101.035813</v>
+        <v>101.039053</v>
       </c>
       <c r="Q407" s="9" t="n">
         <v>100.000267</v>
@@ -33501,7 +33501,7 @@
         <v>98.924522</v>
       </c>
       <c r="P408" s="6" t="n">
-        <v>100.91346</v>
+        <v>100.916336</v>
       </c>
       <c r="Q408" s="6" t="n">
         <v>99.90637099999999</v>
@@ -33585,7 +33585,7 @@
         <v>98.832689</v>
       </c>
       <c r="P409" s="9" t="n">
-        <v>100.747792</v>
+        <v>100.750172</v>
       </c>
       <c r="Q409" s="9" t="n">
         <v>99.83740400000001</v>
@@ -33669,7 +33669,7 @@
         <v>98.801393</v>
       </c>
       <c r="P410" s="6" t="n">
-        <v>100.560894</v>
+        <v>100.562709</v>
       </c>
       <c r="Q410" s="6" t="n">
         <v>99.796119</v>
@@ -33753,7 +33753,7 @@
         <v>98.810033</v>
       </c>
       <c r="P411" s="9" t="n">
-        <v>100.38404</v>
+        <v>100.385318</v>
       </c>
       <c r="Q411" s="9" t="n">
         <v>99.769999</v>
@@ -33837,7 +33837,7 @@
         <v>98.83141000000001</v>
       </c>
       <c r="P412" s="6" t="n">
-        <v>100.250069</v>
+        <v>100.250938</v>
       </c>
       <c r="Q412" s="6" t="n">
         <v>99.74104199999999</v>
@@ -33921,7 +33921,7 @@
         <v>98.801085</v>
       </c>
       <c r="P413" s="9" t="n">
-        <v>100.169082</v>
+        <v>100.169705</v>
       </c>
       <c r="Q413" s="9" t="n">
         <v>99.69591800000001</v>
@@ -34005,7 +34005,7 @@
         <v>98.72745</v>
       </c>
       <c r="P414" s="6" t="n">
-        <v>100.124881</v>
+        <v>100.125374</v>
       </c>
       <c r="Q414" s="6" t="n">
         <v>99.64142099999999</v>
@@ -34089,7 +34089,7 @@
         <v>98.686283</v>
       </c>
       <c r="P415" s="9" t="n">
-        <v>100.123011</v>
+        <v>100.123506</v>
       </c>
       <c r="Q415" s="9" t="n">
         <v>99.60718799999999</v>
@@ -34173,7 +34173,7 @@
         <v>98.732029</v>
       </c>
       <c r="P416" s="6" t="n">
-        <v>100.147522</v>
+        <v>100.148098</v>
       </c>
       <c r="Q416" s="6" t="n">
         <v>99.620942</v>
@@ -34257,7 +34257,7 @@
         <v>98.80222000000001</v>
       </c>
       <c r="P417" s="9" t="n">
-        <v>100.192245</v>
+        <v>100.192961</v>
       </c>
       <c r="Q417" s="9" t="n">
         <v>99.681202</v>
@@ -34341,7 +34341,7 @@
         <v>98.85823499999999</v>
       </c>
       <c r="P418" s="6" t="n">
-        <v>100.257431</v>
+        <v>100.258347</v>
       </c>
       <c r="Q418" s="6" t="n">
         <v>99.777332</v>
@@ -34425,7 +34425,7 @@
         <v>98.888727</v>
       </c>
       <c r="P419" s="9" t="n">
-        <v>100.344123</v>
+        <v>100.3453</v>
       </c>
       <c r="Q419" s="9" t="n">
         <v>99.88937199999999</v>
@@ -34509,7 +34509,7 @@
         <v>98.907864</v>
       </c>
       <c r="P420" s="6" t="n">
-        <v>100.435663</v>
+        <v>100.437113</v>
       </c>
       <c r="Q420" s="6" t="n">
         <v>99.99125600000001</v>
@@ -34593,7 +34593,7 @@
         <v>98.933187</v>
       </c>
       <c r="P421" s="9" t="n">
-        <v>100.500641</v>
+        <v>100.502282</v>
       </c>
       <c r="Q421" s="9" t="n">
         <v>100.0593</v>
@@ -34677,7 +34677,7 @@
         <v>98.946806</v>
       </c>
       <c r="P422" s="6" t="n">
-        <v>100.513591</v>
+        <v>100.515265</v>
       </c>
       <c r="Q422" s="6" t="n">
         <v>100.076785</v>
@@ -34761,7 +34761,7 @@
         <v>98.93681100000001</v>
       </c>
       <c r="P423" s="9" t="n">
-        <v>100.459976</v>
+        <v>100.461482</v>
       </c>
       <c r="Q423" s="9" t="n">
         <v>100.048877</v>
@@ -34845,7 +34845,7 @@
         <v>98.92834999999999</v>
       </c>
       <c r="P424" s="6" t="n">
-        <v>100.334583</v>
+        <v>100.335705</v>
       </c>
       <c r="Q424" s="6" t="n">
         <v>99.99153699999999</v>
@@ -34929,7 +34929,7 @@
         <v>98.980548</v>
       </c>
       <c r="P425" s="9" t="n">
-        <v>100.156102</v>
+        <v>100.156682</v>
       </c>
       <c r="Q425" s="9" t="n">
         <v>99.93123900000001</v>
@@ -35013,7 +35013,7 @@
         <v>99.114367</v>
       </c>
       <c r="P426" s="6" t="n">
-        <v>99.95702199999999</v>
+        <v>99.957003</v>
       </c>
       <c r="Q426" s="6" t="n">
         <v>99.894961</v>
@@ -35097,7 +35097,7 @@
         <v>99.278565</v>
       </c>
       <c r="P427" s="9" t="n">
-        <v>99.764042</v>
+        <v>99.76344400000001</v>
       </c>
       <c r="Q427" s="9" t="n">
         <v>99.89936</v>
@@ -35181,7 +35181,7 @@
         <v>99.39837300000001</v>
       </c>
       <c r="P428" s="6" t="n">
-        <v>99.597443</v>
+        <v>99.596346</v>
       </c>
       <c r="Q428" s="6" t="n">
         <v>99.926242</v>
@@ -35265,7 +35265,7 @@
         <v>99.515666</v>
       </c>
       <c r="P429" s="9" t="n">
-        <v>99.460455</v>
+        <v>99.458945</v>
       </c>
       <c r="Q429" s="9" t="n">
         <v>99.96231400000001</v>
@@ -35349,7 +35349,7 @@
         <v>99.64281800000001</v>
       </c>
       <c r="P430" s="6" t="n">
-        <v>99.355762</v>
+        <v>99.35393500000001</v>
       </c>
       <c r="Q430" s="6" t="n">
         <v>99.989831</v>
@@ -35433,7 +35433,7 @@
         <v>99.794785</v>
       </c>
       <c r="P431" s="9" t="n">
-        <v>99.277923</v>
+        <v>99.275858</v>
       </c>
       <c r="Q431" s="9" t="n">
         <v>99.996233</v>
@@ -35517,7 +35517,7 @@
         <v>99.968816</v>
       </c>
       <c r="P432" s="6" t="n">
-        <v>99.223203</v>
+        <v>99.220967</v>
       </c>
       <c r="Q432" s="6" t="n">
         <v>99.976822</v>
@@ -35601,7 +35601,7 @@
         <v>100.131164</v>
       </c>
       <c r="P433" s="9" t="n">
-        <v>99.196077</v>
+        <v>99.193749</v>
       </c>
       <c r="Q433" s="9" t="n">
         <v>99.93813299999999</v>
@@ -35685,7 +35685,7 @@
         <v>100.261671</v>
       </c>
       <c r="P434" s="6" t="n">
-        <v>99.198431</v>
+        <v>99.196096</v>
       </c>
       <c r="Q434" s="6" t="n">
         <v>99.895577</v>
@@ -35769,7 +35769,7 @@
         <v>100.360237</v>
       </c>
       <c r="P435" s="9" t="n">
-        <v>99.22541099999999</v>
+        <v>99.223141</v>
       </c>
       <c r="Q435" s="9" t="n">
         <v>99.86329499999999</v>
@@ -35853,7 +35853,7 @@
         <v>100.416296</v>
       </c>
       <c r="P436" s="6" t="n">
-        <v>99.253951</v>
+        <v>99.251749</v>
       </c>
       <c r="Q436" s="6" t="n">
         <v>99.84242999999999</v>
@@ -35937,7 +35937,7 @@
         <v>100.437097</v>
       </c>
       <c r="P437" s="9" t="n">
-        <v>99.272891</v>
+        <v>99.270729</v>
       </c>
       <c r="Q437" s="9" t="n">
         <v>99.844922</v>
@@ -36021,7 +36021,7 @@
         <v>100.430587</v>
       </c>
       <c r="P438" s="6" t="n">
-        <v>99.284637</v>
+        <v>99.282495</v>
       </c>
       <c r="Q438" s="6" t="n">
         <v>99.87924700000001</v>
@@ -36105,7 +36105,7 @@
         <v>100.389244</v>
       </c>
       <c r="P439" s="9" t="n">
-        <v>99.298716</v>
+        <v>99.29660199999999</v>
       </c>
       <c r="Q439" s="9" t="n">
         <v>99.943476</v>
@@ -36189,7 +36189,7 @@
         <v>100.323214</v>
       </c>
       <c r="P440" s="6" t="n">
-        <v>99.330686</v>
+        <v>99.328655</v>
       </c>
       <c r="Q440" s="6" t="n">
         <v>100.029788</v>
@@ -36273,7 +36273,7 @@
         <v>100.275116</v>
       </c>
       <c r="P441" s="9" t="n">
-        <v>99.382846</v>
+        <v>99.380957</v>
       </c>
       <c r="Q441" s="9" t="n">
         <v>100.119538</v>
@@ -36357,7 +36357,7 @@
         <v>100.245636</v>
       </c>
       <c r="P442" s="6" t="n">
-        <v>99.443241</v>
+        <v>99.441519</v>
       </c>
       <c r="Q442" s="6" t="n">
         <v>100.203196</v>
@@ -36441,7 +36441,7 @@
         <v>100.246782</v>
       </c>
       <c r="P443" s="9" t="n">
-        <v>99.49529</v>
+        <v>99.493708</v>
       </c>
       <c r="Q443" s="9" t="n">
         <v>100.275575</v>
@@ -36525,7 +36525,7 @@
         <v>100.255031</v>
       </c>
       <c r="P444" s="6" t="n">
-        <v>99.524237</v>
+        <v>99.522723</v>
       </c>
       <c r="Q444" s="6" t="n">
         <v>100.329573</v>
@@ -36609,7 +36609,7 @@
         <v>100.268903</v>
       </c>
       <c r="P445" s="9" t="n">
-        <v>99.530745</v>
+        <v>99.52922599999999</v>
       </c>
       <c r="Q445" s="9" t="n">
         <v>100.357538</v>
@@ -36693,7 +36693,7 @@
         <v>100.297792</v>
       </c>
       <c r="P446" s="6" t="n">
-        <v>99.51172800000001</v>
+        <v>99.510124</v>
       </c>
       <c r="Q446" s="6" t="n">
         <v>100.355306</v>
@@ -36777,7 +36777,7 @@
         <v>100.335496</v>
       </c>
       <c r="P447" s="9" t="n">
-        <v>99.46035500000001</v>
+        <v>99.45856499999999</v>
       </c>
       <c r="Q447" s="9" t="n">
         <v>100.330027</v>
@@ -36861,7 +36861,7 @@
         <v>100.402995</v>
       </c>
       <c r="P448" s="6" t="n">
-        <v>99.38675000000001</v>
+        <v>99.38470599999999</v>
       </c>
       <c r="Q448" s="6" t="n">
         <v>100.295144</v>
@@ -36945,7 +36945,7 @@
         <v>100.485181</v>
       </c>
       <c r="P449" s="9" t="n">
-        <v>99.301405</v>
+        <v>99.29907</v>
       </c>
       <c r="Q449" s="9" t="n">
         <v>100.279013</v>
@@ -37029,7 +37029,7 @@
         <v>100.632379</v>
       </c>
       <c r="P450" s="6" t="n">
-        <v>99.230868</v>
+        <v>99.22828800000001</v>
       </c>
       <c r="Q450" s="6" t="n">
         <v>100.293886</v>
@@ -37113,7 +37113,7 @@
         <v>100.8527</v>
       </c>
       <c r="P451" s="9" t="n">
-        <v>99.21886499999999</v>
+        <v>99.216216</v>
       </c>
       <c r="Q451" s="9" t="n">
         <v>100.340045</v>
@@ -37197,7 +37197,7 @@
         <v>101.08244</v>
       </c>
       <c r="P452" s="6" t="n">
-        <v>99.29834200000001</v>
+        <v>99.295901</v>
       </c>
       <c r="Q452" s="6" t="n">
         <v>100.413053</v>
@@ -37281,7 +37281,7 @@
         <v>101.239188</v>
       </c>
       <c r="P453" s="9" t="n">
-        <v>99.457239</v>
+        <v>99.455246</v>
       </c>
       <c r="Q453" s="9" t="n">
         <v>100.497417</v>
@@ -37365,7 +37365,7 @@
         <v>101.305714</v>
       </c>
       <c r="P454" s="6" t="n">
-        <v>99.670069</v>
+        <v>99.668685</v>
       </c>
       <c r="Q454" s="6" t="n">
         <v>100.578745</v>
@@ -37449,7 +37449,7 @@
         <v>101.225357</v>
       </c>
       <c r="P455" s="9" t="n">
-        <v>99.90283100000001</v>
+        <v>99.902114</v>
       </c>
       <c r="Q455" s="9" t="n">
         <v>100.646729</v>
@@ -37533,7 +37533,7 @@
         <v>101.005119</v>
       </c>
       <c r="P456" s="6" t="n">
-        <v>100.121048</v>
+        <v>100.120949</v>
       </c>
       <c r="Q456" s="6" t="n">
         <v>100.686671</v>
@@ -37617,7 +37617,7 @@
         <v>100.701188</v>
       </c>
       <c r="P457" s="9" t="n">
-        <v>100.296027</v>
+        <v>100.296408</v>
       </c>
       <c r="Q457" s="9" t="n">
         <v>100.686797</v>
@@ -37701,7 +37701,7 @@
         <v>100.391964</v>
       </c>
       <c r="P458" s="6" t="n">
-        <v>100.419933</v>
+        <v>100.420634</v>
       </c>
       <c r="Q458" s="6" t="n">
         <v>100.647609</v>
@@ -37785,7 +37785,7 @@
         <v>100.136131</v>
       </c>
       <c r="P459" s="9" t="n">
-        <v>100.493883</v>
+        <v>100.494749</v>
       </c>
       <c r="Q459" s="9" t="n">
         <v>100.583365</v>
@@ -37869,7 +37869,7 @@
         <v>99.96272999999999</v>
       </c>
       <c r="P460" s="6" t="n">
-        <v>100.548219</v>
+        <v>100.54919</v>
       </c>
       <c r="Q460" s="6" t="n">
         <v>100.516217</v>
@@ -37953,7 +37953,7 @@
         <v>99.898034</v>
       </c>
       <c r="P461" s="9" t="n">
-        <v>100.610985</v>
+        <v>100.612085</v>
       </c>
       <c r="Q461" s="9" t="n">
         <v>100.461014</v>
@@ -38037,7 +38037,7 @@
         <v>99.889002</v>
       </c>
       <c r="P462" s="6" t="n">
-        <v>100.686658</v>
+        <v>100.687926</v>
       </c>
       <c r="Q462" s="6" t="n">
         <v>100.409692</v>
@@ -38121,7 +38121,7 @@
         <v>99.91958099999999</v>
       </c>
       <c r="P463" s="9" t="n">
-        <v>100.766193</v>
+        <v>100.767643</v>
       </c>
       <c r="Q463" s="9" t="n">
         <v>100.359408</v>
@@ -38205,7 +38205,7 @@
         <v>99.99393999999999</v>
       </c>
       <c r="P464" s="6" t="n">
-        <v>100.826822</v>
+        <v>100.828406</v>
       </c>
       <c r="Q464" s="6" t="n">
         <v>100.327472</v>
@@ -38289,7 +38289,7 @@
         <v>100.086625</v>
       </c>
       <c r="P465" s="9" t="n">
-        <v>100.848875</v>
+        <v>100.850482</v>
       </c>
       <c r="Q465" s="9" t="n">
         <v>100.322226</v>
@@ -38373,7 +38373,7 @@
         <v>100.187025</v>
       </c>
       <c r="P466" s="6" t="n">
-        <v>100.848776</v>
+        <v>100.850342</v>
       </c>
       <c r="Q466" s="6" t="n">
         <v>100.330935</v>
@@ -38457,7 +38457,7 @@
         <v>100.281459</v>
       </c>
       <c r="P467" s="9" t="n">
-        <v>100.857108</v>
+        <v>100.858654</v>
       </c>
       <c r="Q467" s="9" t="n">
         <v>100.349622</v>
@@ -38541,7 +38541,7 @@
         <v>100.36843</v>
       </c>
       <c r="P468" s="6" t="n">
-        <v>100.896605</v>
+        <v>100.898216</v>
       </c>
       <c r="Q468" s="6" t="n">
         <v>100.343164</v>
@@ -38625,7 +38625,7 @@
         <v>100.449472</v>
       </c>
       <c r="P469" s="9" t="n">
-        <v>100.950376</v>
+        <v>100.952082</v>
       </c>
       <c r="Q469" s="9" t="n">
         <v>100.279067</v>
@@ -38709,7 +38709,7 @@
         <v>100.522437</v>
       </c>
       <c r="P470" s="6" t="n">
-        <v>101.002482</v>
+        <v>101.004263</v>
       </c>
       <c r="Q470" s="6" t="n">
         <v>100.149826</v>
@@ -38793,7 +38793,7 @@
         <v>100.531292</v>
       </c>
       <c r="P471" s="9" t="n">
-        <v>101.060466</v>
+        <v>101.062335</v>
       </c>
       <c r="Q471" s="9" t="n">
         <v>99.975212</v>
@@ -38877,7 +38877,7 @@
         <v>100.419027</v>
       </c>
       <c r="P472" s="6" t="n">
-        <v>101.133693</v>
+        <v>101.135696</v>
       </c>
       <c r="Q472" s="6" t="n">
         <v>99.811229</v>
@@ -38961,7 +38961,7 @@
         <v>100.218061</v>
       </c>
       <c r="P473" s="9" t="n">
-        <v>101.230651</v>
+        <v>101.232864</v>
       </c>
       <c r="Q473" s="9" t="n">
         <v>99.698545</v>
@@ -39045,7 +39045,7 @@
         <v>99.968356</v>
       </c>
       <c r="P474" s="6" t="n">
-        <v>101.352026</v>
+        <v>101.354525</v>
       </c>
       <c r="Q474" s="6" t="n">
         <v>99.644536</v>
@@ -39129,7 +39129,7 @@
         <v>99.68058499999999</v>
       </c>
       <c r="P475" s="9" t="n">
-        <v>101.465393</v>
+        <v>101.468152</v>
       </c>
       <c r="Q475" s="9" t="n">
         <v>99.62882399999999</v>
@@ -39213,7 +39213,7 @@
         <v>99.42294800000001</v>
       </c>
       <c r="P476" s="6" t="n">
-        <v>101.548096</v>
+        <v>101.551044</v>
       </c>
       <c r="Q476" s="6" t="n">
         <v>99.6384</v>
@@ -39297,7 +39297,7 @@
         <v>99.215371</v>
       </c>
       <c r="P477" s="9" t="n">
-        <v>101.580587</v>
+        <v>101.583581</v>
       </c>
       <c r="Q477" s="9" t="n">
         <v>99.656881</v>
@@ -39381,7 +39381,7 @@
         <v>99.05097499999999</v>
       </c>
       <c r="P478" s="6" t="n">
-        <v>101.544832</v>
+        <v>101.547676</v>
       </c>
       <c r="Q478" s="6" t="n">
         <v>99.669753</v>
@@ -39465,7 +39465,7 @@
         <v>98.995295</v>
       </c>
       <c r="P479" s="9" t="n">
-        <v>101.438764</v>
+        <v>101.441245</v>
       </c>
       <c r="Q479" s="9" t="n">
         <v>99.68104700000001</v>
@@ -39549,7 +39549,7 @@
         <v>99.042288</v>
       </c>
       <c r="P480" s="6" t="n">
-        <v>101.290546</v>
+        <v>101.292524</v>
       </c>
       <c r="Q480" s="6" t="n">
         <v>99.693533</v>
@@ -39633,7 +39633,7 @@
         <v>99.132893</v>
       </c>
       <c r="P481" s="9" t="n">
-        <v>101.125144</v>
+        <v>101.126542</v>
       </c>
       <c r="Q481" s="9" t="n">
         <v>99.714883</v>
@@ -39717,7 +39717,7 @@
         <v>99.16364</v>
       </c>
       <c r="P482" s="6" t="n">
-        <v>100.943846</v>
+        <v>100.944592</v>
       </c>
       <c r="Q482" s="6" t="n">
         <v>99.727627</v>
@@ -39801,7 +39801,7 @@
         <v>99.16673400000001</v>
       </c>
       <c r="P483" s="9" t="n">
-        <v>100.730865</v>
+        <v>100.73086</v>
       </c>
       <c r="Q483" s="9" t="n">
         <v>99.712333</v>
@@ -39885,7 +39885,7 @@
         <v>99.169365</v>
       </c>
       <c r="P484" s="6" t="n">
-        <v>100.460695</v>
+        <v>100.459774</v>
       </c>
       <c r="Q484" s="6" t="n">
         <v>99.65216100000001</v>
@@ -39969,7 +39969,7 @@
         <v>99.12859899999999</v>
       </c>
       <c r="P485" s="9" t="n">
-        <v>100.097811</v>
+        <v>100.09571</v>
       </c>
       <c r="Q485" s="9" t="n">
         <v>99.537077</v>
@@ -40053,7 +40053,7 @@
         <v>99.03926800000001</v>
       </c>
       <c r="P486" s="6" t="n">
-        <v>99.61394799999999</v>
+        <v>99.610316</v>
       </c>
       <c r="Q486" s="6" t="n">
         <v>99.35934899999999</v>
@@ -40137,7 +40137,7 @@
         <v>98.93617</v>
       </c>
       <c r="P487" s="9" t="n">
-        <v>99.00792</v>
+        <v>99.00239500000001</v>
       </c>
       <c r="Q487" s="9" t="n">
         <v>99.12958</v>
@@ -40221,7 +40221,7 @@
         <v>98.79833499999999</v>
       </c>
       <c r="P488" s="6" t="n">
-        <v>98.32839300000001</v>
+        <v>98.32079299999999</v>
       </c>
       <c r="Q488" s="6" t="n">
         <v>98.895561</v>
@@ -40305,7 +40305,7 @@
         <v>98.667036</v>
       </c>
       <c r="P489" s="9" t="n">
-        <v>97.684546</v>
+        <v>97.67500200000001</v>
       </c>
       <c r="Q489" s="9" t="n">
         <v>98.723353</v>
@@ -40389,7 +40389,7 @@
         <v>98.58877699999999</v>
       </c>
       <c r="P490" s="6" t="n">
-        <v>97.219554</v>
+        <v>97.20862</v>
       </c>
       <c r="Q490" s="6" t="n">
         <v>98.620248</v>
@@ -40473,7 +40473,7 @@
         <v>98.58478100000001</v>
       </c>
       <c r="P491" s="9" t="n">
-        <v>96.981893</v>
+        <v>96.970237</v>
       </c>
       <c r="Q491" s="9" t="n">
         <v>98.582958</v>
@@ -40557,7 +40557,7 @@
         <v>98.681675</v>
       </c>
       <c r="P492" s="6" t="n">
-        <v>96.936964</v>
+        <v>96.925134</v>
       </c>
       <c r="Q492" s="6" t="n">
         <v>98.59928600000001</v>
@@ -40641,7 +40641,7 @@
         <v>98.878523</v>
       </c>
       <c r="P493" s="9" t="n">
-        <v>97.027584</v>
+        <v>97.01593099999999</v>
       </c>
       <c r="Q493" s="9" t="n">
         <v>98.672332</v>
@@ -40725,7 +40725,7 @@
         <v>99.15967499999999</v>
       </c>
       <c r="P494" s="6" t="n">
-        <v>97.19841700000001</v>
+        <v>97.18713700000001</v>
       </c>
       <c r="Q494" s="6" t="n">
         <v>98.80711599999999</v>
@@ -40809,7 +40809,7 @@
         <v>99.46768899999999</v>
       </c>
       <c r="P495" s="9" t="n">
-        <v>97.396779</v>
+        <v>97.385947</v>
       </c>
       <c r="Q495" s="9" t="n">
         <v>99.001842</v>
@@ -40893,7 +40893,7 @@
         <v>99.764928</v>
       </c>
       <c r="P496" s="6" t="n">
-        <v>97.597275</v>
+        <v>97.58692499999999</v>
       </c>
       <c r="Q496" s="6" t="n">
         <v>99.247001</v>
@@ -40977,7 +40977,7 @@
         <v>100.034038</v>
       </c>
       <c r="P497" s="9" t="n">
-        <v>97.78906000000001</v>
+        <v>97.779211</v>
       </c>
       <c r="Q497" s="9" t="n">
         <v>99.50240700000001</v>
@@ -41061,7 +41061,7 @@
         <v>100.254969</v>
       </c>
       <c r="P498" s="6" t="n">
-        <v>97.97939</v>
+        <v>97.970084</v>
       </c>
       <c r="Q498" s="6" t="n">
         <v>99.745301</v>
@@ -41145,7 +41145,7 @@
         <v>100.433784</v>
       </c>
       <c r="P499" s="9" t="n">
-        <v>98.19193</v>
+        <v>98.18325900000001</v>
       </c>
       <c r="Q499" s="9" t="n">
         <v>99.97938499999999</v>
@@ -41229,7 +41229,7 @@
         <v>100.605971</v>
       </c>
       <c r="P500" s="6" t="n">
-        <v>98.442592</v>
+        <v>98.434737</v>
       </c>
       <c r="Q500" s="6" t="n">
         <v>100.200336</v>
@@ -41313,7 +41313,7 @@
         <v>100.7565</v>
       </c>
       <c r="P501" s="9" t="n">
-        <v>98.716746</v>
+        <v>98.709823</v>
       </c>
       <c r="Q501" s="9" t="n">
         <v>100.39602</v>
@@ -41397,7 +41397,7 @@
         <v>100.853147</v>
       </c>
       <c r="P502" s="6" t="n">
-        <v>98.98921199999999</v>
+        <v>98.98323600000001</v>
       </c>
       <c r="Q502" s="6" t="n">
         <v>100.557828</v>
@@ -41481,7 +41481,7 @@
         <v>100.870491</v>
       </c>
       <c r="P503" s="9" t="n">
-        <v>99.235879</v>
+        <v>99.230737</v>
       </c>
       <c r="Q503" s="9" t="n">
         <v>100.674094</v>
@@ -41565,7 +41565,7 @@
         <v>100.809521</v>
       </c>
       <c r="P504" s="6" t="n">
-        <v>99.43498599999999</v>
+        <v>99.43047</v>
       </c>
       <c r="Q504" s="6" t="n">
         <v>100.749093</v>
@@ -41649,7 +41649,7 @@
         <v>100.69003</v>
       </c>
       <c r="P505" s="9" t="n">
-        <v>99.586682</v>
+        <v>99.58254100000001</v>
       </c>
       <c r="Q505" s="9" t="n">
         <v>100.78608</v>
@@ -41733,7 +41733,7 @@
         <v>100.540372</v>
       </c>
       <c r="P506" s="6" t="n">
-        <v>99.716379</v>
+        <v>99.71243800000001</v>
       </c>
       <c r="Q506" s="6" t="n">
         <v>100.785381</v>
@@ -41817,7 +41817,7 @@
         <v>100.380557</v>
       </c>
       <c r="P507" s="9" t="n">
-        <v>99.840755</v>
+        <v>99.836997</v>
       </c>
       <c r="Q507" s="9" t="n">
         <v>100.766194</v>
@@ -41901,7 +41901,7 @@
         <v>100.250627</v>
       </c>
       <c r="P508" s="6" t="n">
-        <v>99.959497</v>
+        <v>99.955989</v>
       </c>
       <c r="Q508" s="6" t="n">
         <v>100.744143</v>
@@ -41985,7 +41985,7 @@
         <v>100.165921</v>
       </c>
       <c r="P509" s="9" t="n">
-        <v>100.074469</v>
+        <v>100.07133</v>
       </c>
       <c r="Q509" s="9" t="n">
         <v>100.727777</v>
@@ -42069,7 +42069,7 @@
         <v>100.124167</v>
       </c>
       <c r="P510" s="6" t="n">
-        <v>100.183225</v>
+        <v>100.180563</v>
       </c>
       <c r="Q510" s="6" t="n">
         <v>100.697338</v>
@@ -42153,7 +42153,7 @@
         <v>100.114886</v>
       </c>
       <c r="P511" s="9" t="n">
-        <v>100.285788</v>
+        <v>100.283659</v>
       </c>
       <c r="Q511" s="9" t="n">
         <v>100.641439</v>
@@ -42237,7 +42237,7 @@
         <v>100.113233</v>
       </c>
       <c r="P512" s="6" t="n">
-        <v>100.356675</v>
+        <v>100.355092</v>
       </c>
       <c r="Q512" s="6" t="n">
         <v>100.536507</v>
@@ -42321,7 +42321,7 @@
         <v>100.130151</v>
       </c>
       <c r="P513" s="9" t="n">
-        <v>100.41075</v>
+        <v>100.409727</v>
       </c>
       <c r="Q513" s="9" t="n">
         <v>100.367753</v>
@@ -42405,7 +42405,7 @@
         <v>100.184271</v>
       </c>
       <c r="P514" s="6" t="n">
-        <v>100.445469</v>
+        <v>100.444945</v>
       </c>
       <c r="Q514" s="6" t="n">
         <v>100.16217</v>
@@ -42489,7 +42489,7 @@
         <v>100.25998</v>
       </c>
       <c r="P515" s="9" t="n">
-        <v>100.451074</v>
+        <v>100.450859</v>
       </c>
       <c r="Q515" s="9" t="n">
         <v>99.947166</v>
@@ -42573,7 +42573,7 @@
         <v>100.331625</v>
       </c>
       <c r="P516" s="6" t="n">
-        <v>100.42789</v>
+        <v>100.427746</v>
       </c>
       <c r="Q516" s="6" t="n">
         <v>99.767995</v>
@@ -42657,7 +42657,7 @@
         <v>100.380929</v>
       </c>
       <c r="P517" s="9" t="n">
-        <v>100.391979</v>
+        <v>100.391661</v>
       </c>
       <c r="Q517" s="9" t="n">
         <v>99.65320699999999</v>
@@ -42741,7 +42741,7 @@
         <v>100.428309</v>
       </c>
       <c r="P518" s="6" t="n">
-        <v>100.348668</v>
+        <v>100.347957</v>
       </c>
       <c r="Q518" s="6" t="n">
         <v>99.630576</v>
@@ -42825,7 +42825,7 @@
         <v>100.480743</v>
       </c>
       <c r="P519" s="9" t="n">
-        <v>100.315581</v>
+        <v>100.314535</v>
       </c>
       <c r="Q519" s="9" t="n">
         <v>99.69457300000001</v>
@@ -42909,7 +42909,7 @@
         <v>100.523257</v>
       </c>
       <c r="P520" s="6" t="n">
-        <v>100.303053</v>
+        <v>100.301948</v>
       </c>
       <c r="Q520" s="6" t="n">
         <v>99.801202</v>
@@ -42993,7 +42993,7 @@
         <v>100.574339</v>
       </c>
       <c r="P521" s="9" t="n">
-        <v>100.320282</v>
+        <v>100.31952</v>
       </c>
       <c r="Q521" s="9" t="n">
         <v>99.920322</v>
@@ -43077,7 +43077,7 @@
         <v>100.642645</v>
       </c>
       <c r="P522" s="6" t="n">
-        <v>100.375709</v>
+        <v>100.375696</v>
       </c>
       <c r="Q522" s="6" t="n">
         <v>100.043416</v>
@@ -43161,7 +43161,7 @@
         <v>100.713739</v>
       </c>
       <c r="P523" s="9" t="n">
-        <v>100.459152</v>
+        <v>100.46012</v>
       </c>
       <c r="Q523" s="9" t="n">
         <v>100.138478</v>
@@ -43245,7 +43245,7 @@
         <v>100.766164</v>
       </c>
       <c r="P524" s="6" t="n">
-        <v>100.546283</v>
+        <v>100.548361</v>
       </c>
       <c r="Q524" s="6" t="n">
         <v>100.200833</v>
@@ -43329,7 +43329,7 @@
         <v>100.780831</v>
       </c>
       <c r="P525" s="9" t="n">
-        <v>100.629013</v>
+        <v>100.632198</v>
       </c>
       <c r="Q525" s="9" t="n">
         <v>100.225158</v>
@@ -43413,7 +43413,7 @@
         <v>100.74651</v>
       </c>
       <c r="P526" s="6" t="n">
-        <v>100.710041</v>
+        <v>100.714227</v>
       </c>
       <c r="Q526" s="6" t="n">
         <v>100.210858</v>
@@ -43497,7 +43497,7 @@
         <v>100.673886</v>
       </c>
       <c r="P527" s="9" t="n">
-        <v>100.79824</v>
+        <v>100.803232</v>
       </c>
       <c r="Q527" s="9" t="n">
         <v>100.172121</v>
@@ -43581,7 +43581,7 @@
         <v>100.57701</v>
       </c>
       <c r="P528" s="6" t="n">
-        <v>100.883805</v>
+        <v>100.889331</v>
       </c>
       <c r="Q528" s="6" t="n">
         <v>100.116177</v>
@@ -43665,7 +43665,7 @@
         <v>100.476548</v>
       </c>
       <c r="P529" s="9" t="n">
-        <v>100.962194</v>
+        <v>100.967887</v>
       </c>
       <c r="Q529" s="9" t="n">
         <v>100.053167</v>
@@ -43749,7 +43749,7 @@
         <v>100.384973</v>
       </c>
       <c r="P530" s="6" t="n">
-        <v>101.036162</v>
+        <v>101.04165</v>
       </c>
       <c r="Q530" s="6" t="n">
         <v>100.010003</v>
@@ -43833,7 +43833,7 @@
         <v>100.324882</v>
       </c>
       <c r="P531" s="9" t="n">
-        <v>101.107575</v>
+        <v>101.113018</v>
       </c>
       <c r="Q531" s="9" t="n">
         <v>100.013716</v>
@@ -43917,7 +43917,7 @@
         <v>100.317893</v>
       </c>
       <c r="P532" s="6" t="n">
-        <v>101.182753</v>
+        <v>101.18864</v>
       </c>
       <c r="Q532" s="6" t="n">
         <v>100.069662</v>
@@ -44001,7 +44001,7 @@
         <v>100.352183</v>
       </c>
       <c r="P533" s="9" t="n">
-        <v>101.261328</v>
+        <v>101.268301</v>
       </c>
       <c r="Q533" s="9" t="n">
         <v>100.139378</v>
@@ -44085,7 +44085,7 @@
         <v>100.40148</v>
       </c>
       <c r="P534" s="6" t="n">
-        <v>101.333157</v>
+        <v>101.341732</v>
       </c>
       <c r="Q534" s="6" t="n">
         <v>100.184547</v>
@@ -44169,7 +44169,7 @@
         <v>100.43898</v>
       </c>
       <c r="P535" s="9" t="n">
-        <v>101.388526</v>
+        <v>101.398878</v>
       </c>
       <c r="Q535" s="9" t="n">
         <v>100.189632</v>
@@ -44253,7 +44253,7 @@
         <v>100.463058</v>
       </c>
       <c r="P536" s="6" t="n">
-        <v>101.414975</v>
+        <v>101.427039</v>
       </c>
       <c r="Q536" s="6" t="n">
         <v>100.153181</v>
@@ -44337,7 +44337,7 @@
         <v>100.464657</v>
       </c>
       <c r="P537" s="9" t="n">
-        <v>101.395846</v>
+        <v>101.409301</v>
       </c>
       <c r="Q537" s="9" t="n">
         <v>100.067761</v>
@@ -44421,7 +44421,7 @@
         <v>100.44067</v>
       </c>
       <c r="P538" s="6" t="n">
-        <v>101.329275</v>
+        <v>101.343667</v>
       </c>
       <c r="Q538" s="6" t="n">
         <v>99.93894299999999</v>
@@ -44505,7 +44505,7 @@
         <v>100.39169</v>
       </c>
       <c r="P539" s="9" t="n">
-        <v>101.221741</v>
+        <v>101.236576</v>
       </c>
       <c r="Q539" s="9" t="n">
         <v>99.783644</v>
@@ -44589,7 +44589,7 @@
         <v>100.323872</v>
       </c>
       <c r="P540" s="6" t="n">
-        <v>101.094689</v>
+        <v>101.109561</v>
       </c>
       <c r="Q540" s="6" t="n">
         <v>99.62483899999999</v>
@@ -44673,7 +44673,7 @@
         <v>100.254403</v>
       </c>
       <c r="P541" s="9" t="n">
-        <v>100.957811</v>
+        <v>100.972291</v>
       </c>
       <c r="Q541" s="9" t="n">
         <v>99.472677</v>
@@ -44757,7 +44757,7 @@
         <v>100.187339</v>
       </c>
       <c r="P542" s="6" t="n">
-        <v>100.80569</v>
+        <v>100.819307</v>
       </c>
       <c r="Q542" s="6" t="n">
         <v>99.336128</v>
@@ -44841,7 +44841,7 @@
         <v>100.10804</v>
       </c>
       <c r="P543" s="9" t="n">
-        <v>100.650148</v>
+        <v>100.66315</v>
       </c>
       <c r="Q543" s="9" t="n">
         <v>99.221727</v>
@@ -44925,7 +44925,7 @@
         <v>100.007474</v>
       </c>
       <c r="P544" s="6" t="n">
-        <v>100.488316</v>
+        <v>100.501417</v>
       </c>
       <c r="Q544" s="6" t="n">
         <v>99.14724099999999</v>
@@ -45009,7 +45009,7 @@
         <v>99.876864</v>
       </c>
       <c r="P545" s="9" t="n">
-        <v>100.314638</v>
+        <v>100.328765</v>
       </c>
       <c r="Q545" s="9" t="n">
         <v>99.127163</v>
@@ -45093,7 +45093,7 @@
         <v>99.73588599999999</v>
       </c>
       <c r="P546" s="6" t="n">
-        <v>100.133531</v>
+        <v>100.149457</v>
       </c>
       <c r="Q546" s="6" t="n">
         <v>99.16571</v>
@@ -45177,7 +45177,7 @@
         <v>99.589375</v>
       </c>
       <c r="P547" s="9" t="n">
-        <v>99.948623</v>
+        <v>99.966641</v>
       </c>
       <c r="Q547" s="9" t="n">
         <v>99.251963</v>
@@ -45261,7 +45261,7 @@
         <v>99.443596</v>
       </c>
       <c r="P548" s="6" t="n">
-        <v>99.78811899999999</v>
+        <v>99.80820199999999</v>
       </c>
       <c r="Q548" s="6" t="n">
         <v>99.372514</v>
@@ -45345,7 +45345,7 @@
         <v>99.329407</v>
       </c>
       <c r="P549" s="9" t="n">
-        <v>99.674441</v>
+        <v>99.696308</v>
       </c>
       <c r="Q549" s="9" t="n">
         <v>99.51421000000001</v>
@@ -45429,7 +45429,7 @@
         <v>99.256207</v>
       </c>
       <c r="P550" s="6" t="n">
-        <v>99.62838499999999</v>
+        <v>99.651686</v>
       </c>
       <c r="Q550" s="6" t="n">
         <v>99.654281</v>
@@ -45513,7 +45513,7 @@
         <v>99.219632</v>
       </c>
       <c r="P551" s="9" t="n">
-        <v>99.620283</v>
+        <v>99.644609</v>
       </c>
       <c r="Q551" s="9" t="n">
         <v>99.784363</v>
@@ -45597,7 +45597,7 @@
         <v>99.206112</v>
       </c>
       <c r="P552" s="6" t="n">
-        <v>99.62472099999999</v>
+        <v>99.64967900000001</v>
       </c>
       <c r="Q552" s="6" t="n">
         <v>99.91254600000001</v>
@@ -45681,7 +45681,7 @@
         <v>99.20610600000001</v>
       </c>
       <c r="P553" s="9" t="n">
-        <v>99.61776999999999</v>
+        <v>99.642844</v>
       </c>
       <c r="Q553" s="9" t="n">
         <v>100.047651</v>
@@ -45765,7 +45765,7 @@
         <v>99.208668</v>
       </c>
       <c r="P554" s="6" t="n">
-        <v>99.59324599999999</v>
+        <v>99.617773</v>
       </c>
       <c r="Q554" s="6" t="n">
         <v>100.186812</v>
@@ -45849,7 +45849,7 @@
         <v>99.22666700000001</v>
       </c>
       <c r="P555" s="9" t="n">
-        <v>99.54774500000001</v>
+        <v>99.57182</v>
       </c>
       <c r="Q555" s="9" t="n">
         <v>100.316216</v>
@@ -45933,7 +45933,7 @@
         <v>99.26781200000001</v>
       </c>
       <c r="P556" s="6" t="n">
-        <v>99.488089</v>
+        <v>99.51242000000001</v>
       </c>
       <c r="Q556" s="6" t="n">
         <v>100.435533</v>
@@ -46017,7 +46017,7 @@
         <v>99.350877</v>
       </c>
       <c r="P557" s="9" t="n">
-        <v>99.424121</v>
+        <v>99.44973400000001</v>
       </c>
       <c r="Q557" s="9" t="n">
         <v>100.544096</v>
@@ -46101,7 +46101,7 @@
         <v>99.47413400000001</v>
       </c>
       <c r="P558" s="6" t="n">
-        <v>99.36145999999999</v>
+        <v>99.38923200000001</v>
       </c>
       <c r="Q558" s="6" t="n">
         <v>100.634441</v>
@@ -46185,7 +46185,7 @@
         <v>99.621951</v>
       </c>
       <c r="P559" s="9" t="n">
-        <v>99.303361</v>
+        <v>99.333716</v>
       </c>
       <c r="Q559" s="9" t="n">
         <v>100.687597</v>
@@ -46269,7 +46269,7 @@
         <v>99.782504</v>
       </c>
       <c r="P560" s="6" t="n">
-        <v>99.253698</v>
+        <v>99.286867</v>
       </c>
       <c r="Q560" s="6" t="n">
         <v>100.689859</v>
@@ -46353,7 +46353,7 @@
         <v>99.92449000000001</v>
       </c>
       <c r="P561" s="9" t="n">
-        <v>99.21717200000001</v>
+        <v>99.253601</v>
       </c>
       <c r="Q561" s="9" t="n">
         <v>100.654205</v>
@@ -46437,7 +46437,7 @@
         <v>100.050948</v>
       </c>
       <c r="P562" s="6" t="n">
-        <v>99.195198</v>
+        <v>99.236124</v>
       </c>
       <c r="Q562" s="6" t="n">
         <v>100.5928</v>
@@ -46521,7 +46521,7 @@
         <v>100.157408</v>
       </c>
       <c r="P563" s="9" t="n">
-        <v>99.194997</v>
+        <v>99.24297300000001</v>
       </c>
       <c r="Q563" s="9" t="n">
         <v>100.511198</v>
@@ -46599,7 +46599,7 @@
         <v>100.255278</v>
       </c>
       <c r="P564" s="6" t="n">
-        <v>99.205601</v>
+        <v>99.264543</v>
       </c>
       <c r="Q564" s="6" t="n">
         <v>100.418174</v>

--- a/downloads/indicadores/SIC/SIC_datos.xlsx
+++ b/downloads/indicadores/SIC/SIC_datos.xlsx
@@ -682,7 +682,7 @@
         <v>96.01853800000001</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>100.456177</v>
+        <v>100.455586</v>
       </c>
       <c r="P6" s="6" t="n"/>
       <c r="Q6" s="6" t="n"/>
@@ -754,7 +754,7 @@
         <v>96.648679</v>
       </c>
       <c r="O7" s="9" t="n">
-        <v>100.496514</v>
+        <v>100.495876</v>
       </c>
       <c r="P7" s="9" t="n"/>
       <c r="Q7" s="9" t="n"/>
@@ -826,7 +826,7 @@
         <v>97.279504</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>100.519198</v>
+        <v>100.518536</v>
       </c>
       <c r="P8" s="6" t="n"/>
       <c r="Q8" s="6" t="n"/>
@@ -898,7 +898,7 @@
         <v>97.915756</v>
       </c>
       <c r="O9" s="9" t="n">
-        <v>100.5647</v>
+        <v>100.563989</v>
       </c>
       <c r="P9" s="9" t="n"/>
       <c r="Q9" s="9" t="n"/>
@@ -970,7 +970,7 @@
         <v>98.558206</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>100.709344</v>
+        <v>100.708463</v>
       </c>
       <c r="P10" s="6" t="n"/>
       <c r="Q10" s="6" t="n"/>
@@ -1042,7 +1042,7 @@
         <v>99.214552</v>
       </c>
       <c r="O11" s="9" t="n">
-        <v>100.953386</v>
+        <v>100.952213</v>
       </c>
       <c r="P11" s="9" t="n"/>
       <c r="Q11" s="9" t="n"/>
@@ -1114,7 +1114,7 @@
         <v>99.89823800000001</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>101.227689</v>
+        <v>101.226189</v>
       </c>
       <c r="P12" s="6" t="n"/>
       <c r="Q12" s="6" t="n"/>
@@ -1186,7 +1186,7 @@
         <v>100.597011</v>
       </c>
       <c r="O13" s="9" t="n">
-        <v>101.474909</v>
+        <v>101.473115</v>
       </c>
       <c r="P13" s="9" t="n"/>
       <c r="Q13" s="9" t="n"/>
@@ -1258,7 +1258,7 @@
         <v>101.289255</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>101.610715</v>
+        <v>101.608758</v>
       </c>
       <c r="P14" s="6" t="n"/>
       <c r="Q14" s="6" t="n"/>
@@ -1330,7 +1330,7 @@
         <v>101.936772</v>
       </c>
       <c r="O15" s="9" t="n">
-        <v>101.581897</v>
+        <v>101.579974</v>
       </c>
       <c r="P15" s="9" t="n"/>
       <c r="Q15" s="9" t="n"/>
@@ -1402,7 +1402,7 @@
         <v>102.504641</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>101.443181</v>
+        <v>101.441421</v>
       </c>
       <c r="P16" s="6" t="n"/>
       <c r="Q16" s="6" t="n"/>
@@ -1474,7 +1474,7 @@
         <v>102.971084</v>
       </c>
       <c r="O17" s="9" t="n">
-        <v>101.286133</v>
+        <v>101.284557</v>
       </c>
       <c r="P17" s="9" t="n"/>
       <c r="Q17" s="9" t="n"/>
@@ -1550,7 +1550,7 @@
         <v>103.330031</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>101.197989</v>
+        <v>101.19651</v>
       </c>
       <c r="P18" s="6" t="n"/>
       <c r="Q18" s="6" t="n">
@@ -1628,7 +1628,7 @@
         <v>103.583824</v>
       </c>
       <c r="O19" s="9" t="n">
-        <v>101.198674</v>
+        <v>101.197183</v>
       </c>
       <c r="P19" s="9" t="n"/>
       <c r="Q19" s="9" t="n">
@@ -1706,7 +1706,7 @@
         <v>103.754</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>101.303176</v>
+        <v>101.30155</v>
       </c>
       <c r="P20" s="6" t="n"/>
       <c r="Q20" s="6" t="n">
@@ -1784,7 +1784,7 @@
         <v>103.850555</v>
       </c>
       <c r="O21" s="9" t="n">
-        <v>101.485779</v>
+        <v>101.483924</v>
       </c>
       <c r="P21" s="9" t="n"/>
       <c r="Q21" s="9" t="n">
@@ -1862,7 +1862,7 @@
         <v>103.906068</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>101.604639</v>
+        <v>101.602641</v>
       </c>
       <c r="P22" s="6" t="n"/>
       <c r="Q22" s="6" t="n">
@@ -1940,7 +1940,7 @@
         <v>103.951245</v>
       </c>
       <c r="O23" s="9" t="n">
-        <v>101.632068</v>
+        <v>101.630048</v>
       </c>
       <c r="P23" s="9" t="n"/>
       <c r="Q23" s="9" t="n">
@@ -2018,7 +2018,7 @@
         <v>104.017258</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>101.51966</v>
+        <v>101.517795</v>
       </c>
       <c r="P24" s="6" t="n"/>
       <c r="Q24" s="6" t="n">
@@ -2096,7 +2096,7 @@
         <v>104.116691</v>
       </c>
       <c r="O25" s="9" t="n">
-        <v>101.29563</v>
+        <v>101.294059</v>
       </c>
       <c r="P25" s="9" t="n"/>
       <c r="Q25" s="9" t="n">
@@ -2174,7 +2174,7 @@
         <v>104.250865</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>101.045131</v>
+        <v>101.043878</v>
       </c>
       <c r="P26" s="6" t="n"/>
       <c r="Q26" s="6" t="n">
@@ -2252,7 +2252,7 @@
         <v>104.384649</v>
       </c>
       <c r="O27" s="9" t="n">
-        <v>100.804025</v>
+        <v>100.80307</v>
       </c>
       <c r="P27" s="9" t="n"/>
       <c r="Q27" s="9" t="n">
@@ -2330,7 +2330,7 @@
         <v>104.436256</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>100.567089</v>
+        <v>100.566418</v>
       </c>
       <c r="P28" s="6" t="n"/>
       <c r="Q28" s="6" t="n">
@@ -2408,7 +2408,7 @@
         <v>104.322865</v>
       </c>
       <c r="O29" s="9" t="n">
-        <v>100.300723</v>
+        <v>100.300369</v>
       </c>
       <c r="P29" s="9" t="n"/>
       <c r="Q29" s="9" t="n">
@@ -2486,7 +2486,7 @@
         <v>104.021082</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>99.928262</v>
+        <v>99.928353</v>
       </c>
       <c r="P30" s="6" t="n"/>
       <c r="Q30" s="6" t="n">
@@ -2564,7 +2564,7 @@
         <v>103.53688</v>
       </c>
       <c r="O31" s="9" t="n">
-        <v>99.480819</v>
+        <v>99.481447</v>
       </c>
       <c r="P31" s="9" t="n"/>
       <c r="Q31" s="9" t="n">
@@ -2642,7 +2642,7 @@
         <v>102.868663</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>98.970206</v>
+        <v>98.97144900000001</v>
       </c>
       <c r="P32" s="6" t="n"/>
       <c r="Q32" s="6" t="n">
@@ -2720,7 +2720,7 @@
         <v>102.049289</v>
       </c>
       <c r="O33" s="9" t="n">
-        <v>98.374971</v>
+        <v>98.37693400000001</v>
       </c>
       <c r="P33" s="9" t="n"/>
       <c r="Q33" s="9" t="n">
@@ -2798,7 +2798,7 @@
         <v>101.095145</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>97.75676300000001</v>
+        <v>97.759479</v>
       </c>
       <c r="P34" s="6" t="n"/>
       <c r="Q34" s="6" t="n">
@@ -2876,7 +2876,7 @@
         <v>100.035605</v>
       </c>
       <c r="O35" s="9" t="n">
-        <v>97.090909</v>
+        <v>97.094443</v>
       </c>
       <c r="P35" s="9" t="n"/>
       <c r="Q35" s="9" t="n">
@@ -2954,7 +2954,7 @@
         <v>98.9059</v>
       </c>
       <c r="O36" s="6" t="n">
-        <v>96.468333</v>
+        <v>96.47264199999999</v>
       </c>
       <c r="P36" s="6" t="n"/>
       <c r="Q36" s="6" t="n">
@@ -3032,7 +3032,7 @@
         <v>97.741972</v>
       </c>
       <c r="O37" s="9" t="n">
-        <v>95.94629</v>
+        <v>95.951261</v>
       </c>
       <c r="P37" s="9" t="n"/>
       <c r="Q37" s="9" t="n">
@@ -3110,7 +3110,7 @@
         <v>96.635603</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>95.561008</v>
+        <v>95.566489</v>
       </c>
       <c r="P38" s="6" t="n"/>
       <c r="Q38" s="6" t="n">
@@ -3188,7 +3188,7 @@
         <v>95.67626199999999</v>
       </c>
       <c r="O39" s="9" t="n">
-        <v>95.389027</v>
+        <v>95.394738</v>
       </c>
       <c r="P39" s="9" t="n"/>
       <c r="Q39" s="9" t="n">
@@ -3266,7 +3266,7 @@
         <v>94.953543</v>
       </c>
       <c r="O40" s="6" t="n">
-        <v>95.47277</v>
+        <v>95.478382</v>
       </c>
       <c r="P40" s="6" t="n"/>
       <c r="Q40" s="6" t="n">
@@ -3344,7 +3344,7 @@
         <v>94.529996</v>
       </c>
       <c r="O41" s="9" t="n">
-        <v>95.734038</v>
+        <v>95.739322</v>
       </c>
       <c r="P41" s="9" t="n"/>
       <c r="Q41" s="9" t="n">
@@ -3422,7 +3422,7 @@
         <v>94.40653</v>
       </c>
       <c r="O42" s="6" t="n">
-        <v>96.124185</v>
+        <v>96.12897700000001</v>
       </c>
       <c r="P42" s="6" t="n"/>
       <c r="Q42" s="6" t="n">
@@ -3500,7 +3500,7 @@
         <v>94.55947500000001</v>
       </c>
       <c r="O43" s="9" t="n">
-        <v>96.546133</v>
+        <v>96.55039499999999</v>
       </c>
       <c r="P43" s="9" t="n"/>
       <c r="Q43" s="9" t="n">
@@ -3578,7 +3578,7 @@
         <v>94.946664</v>
       </c>
       <c r="O44" s="6" t="n">
-        <v>96.932231</v>
+        <v>96.93601099999999</v>
       </c>
       <c r="P44" s="6" t="n"/>
       <c r="Q44" s="6" t="n">
@@ -3656,7 +3656,7 @@
         <v>95.4669</v>
       </c>
       <c r="O45" s="9" t="n">
-        <v>97.23724799999999</v>
+        <v>97.24065400000001</v>
       </c>
       <c r="P45" s="9" t="n"/>
       <c r="Q45" s="9" t="n">
@@ -3734,7 +3734,7 @@
         <v>96.01516700000001</v>
       </c>
       <c r="O46" s="6" t="n">
-        <v>97.484387</v>
+        <v>97.487493</v>
       </c>
       <c r="P46" s="6" t="n"/>
       <c r="Q46" s="6" t="n">
@@ -3812,7 +3812,7 @@
         <v>96.513676</v>
       </c>
       <c r="O47" s="9" t="n">
-        <v>97.758787</v>
+        <v>97.761562</v>
       </c>
       <c r="P47" s="9" t="n"/>
       <c r="Q47" s="9" t="n">
@@ -3890,7 +3890,7 @@
         <v>96.919253</v>
       </c>
       <c r="O48" s="6" t="n">
-        <v>98.09311599999999</v>
+        <v>98.095491</v>
       </c>
       <c r="P48" s="6" t="n"/>
       <c r="Q48" s="6" t="n">
@@ -3968,7 +3968,7 @@
         <v>97.23245199999999</v>
       </c>
       <c r="O49" s="9" t="n">
-        <v>98.43737</v>
+        <v>98.439329</v>
       </c>
       <c r="P49" s="9" t="n"/>
       <c r="Q49" s="9" t="n">
@@ -4046,7 +4046,7 @@
         <v>97.457053</v>
       </c>
       <c r="O50" s="6" t="n">
-        <v>98.815051</v>
+        <v>98.816548</v>
       </c>
       <c r="P50" s="6" t="n"/>
       <c r="Q50" s="6" t="n">
@@ -4124,7 +4124,7 @@
         <v>97.60056299999999</v>
       </c>
       <c r="O51" s="9" t="n">
-        <v>99.222675</v>
+        <v>99.223665</v>
       </c>
       <c r="P51" s="9" t="n"/>
       <c r="Q51" s="9" t="n">
@@ -4202,7 +4202,7 @@
         <v>97.687847</v>
       </c>
       <c r="O52" s="6" t="n">
-        <v>99.62356200000001</v>
+        <v>99.624047</v>
       </c>
       <c r="P52" s="6" t="n"/>
       <c r="Q52" s="6" t="n">
@@ -4280,7 +4280,7 @@
         <v>97.794072</v>
       </c>
       <c r="O53" s="9" t="n">
-        <v>99.996397</v>
+        <v>99.99641200000001</v>
       </c>
       <c r="P53" s="9" t="n"/>
       <c r="Q53" s="9" t="n">
@@ -4358,7 +4358,7 @@
         <v>97.966244</v>
       </c>
       <c r="O54" s="6" t="n">
-        <v>100.355146</v>
+        <v>100.354708</v>
       </c>
       <c r="P54" s="6" t="n"/>
       <c r="Q54" s="6" t="n">
@@ -4436,7 +4436,7 @@
         <v>98.23016200000001</v>
       </c>
       <c r="O55" s="9" t="n">
-        <v>100.705625</v>
+        <v>100.704746</v>
       </c>
       <c r="P55" s="9" t="n"/>
       <c r="Q55" s="9" t="n">
@@ -4514,7 +4514,7 @@
         <v>98.563427</v>
       </c>
       <c r="O56" s="6" t="n">
-        <v>101.107123</v>
+        <v>101.105744</v>
       </c>
       <c r="P56" s="6" t="n"/>
       <c r="Q56" s="6" t="n">
@@ -4592,7 +4592,7 @@
         <v>98.93799</v>
       </c>
       <c r="O57" s="9" t="n">
-        <v>101.579741</v>
+        <v>101.577774</v>
       </c>
       <c r="P57" s="9" t="n"/>
       <c r="Q57" s="9" t="n">
@@ -4670,7 +4670,7 @@
         <v>99.34953899999999</v>
       </c>
       <c r="O58" s="6" t="n">
-        <v>102.070067</v>
+        <v>102.067495</v>
       </c>
       <c r="P58" s="6" t="n"/>
       <c r="Q58" s="6" t="n">
@@ -4748,7 +4748,7 @@
         <v>99.802744</v>
       </c>
       <c r="O59" s="9" t="n">
-        <v>102.463717</v>
+        <v>102.460664</v>
       </c>
       <c r="P59" s="9" t="n"/>
       <c r="Q59" s="9" t="n">
@@ -4826,7 +4826,7 @@
         <v>100.258239</v>
       </c>
       <c r="O60" s="6" t="n">
-        <v>102.724338</v>
+        <v>102.720971</v>
       </c>
       <c r="P60" s="6" t="n"/>
       <c r="Q60" s="6" t="n">
@@ -4904,7 +4904,7 @@
         <v>100.665427</v>
       </c>
       <c r="O61" s="9" t="n">
-        <v>102.874708</v>
+        <v>102.871162</v>
       </c>
       <c r="P61" s="9" t="n"/>
       <c r="Q61" s="9" t="n">
@@ -4982,7 +4982,7 @@
         <v>101.004395</v>
       </c>
       <c r="O62" s="6" t="n">
-        <v>102.891089</v>
+        <v>102.887526</v>
       </c>
       <c r="P62" s="6" t="n"/>
       <c r="Q62" s="6" t="n">
@@ -5060,7 +5060,7 @@
         <v>101.272127</v>
       </c>
       <c r="O63" s="9" t="n">
-        <v>102.82425</v>
+        <v>102.820769</v>
       </c>
       <c r="P63" s="9" t="n"/>
       <c r="Q63" s="9" t="n">
@@ -5138,7 +5138,7 @@
         <v>101.483991</v>
       </c>
       <c r="O64" s="6" t="n">
-        <v>102.757241</v>
+        <v>102.75384</v>
       </c>
       <c r="P64" s="6" t="n"/>
       <c r="Q64" s="6" t="n">
@@ -5216,7 +5216,7 @@
         <v>101.632015</v>
       </c>
       <c r="O65" s="9" t="n">
-        <v>102.782464</v>
+        <v>102.779026</v>
       </c>
       <c r="P65" s="9" t="n"/>
       <c r="Q65" s="9" t="n">
@@ -5294,7 +5294,7 @@
         <v>101.689445</v>
       </c>
       <c r="O66" s="6" t="n">
-        <v>102.873683</v>
+        <v>102.870128</v>
       </c>
       <c r="P66" s="6" t="n"/>
       <c r="Q66" s="6" t="n">
@@ -5372,7 +5372,7 @@
         <v>101.639903</v>
       </c>
       <c r="O67" s="9" t="n">
-        <v>102.9663</v>
+        <v>102.962627</v>
       </c>
       <c r="P67" s="9" t="n"/>
       <c r="Q67" s="9" t="n">
@@ -5450,7 +5450,7 @@
         <v>101.533699</v>
       </c>
       <c r="O68" s="6" t="n">
-        <v>102.956107</v>
+        <v>102.952446</v>
       </c>
       <c r="P68" s="6" t="n"/>
       <c r="Q68" s="6" t="n">
@@ -5528,7 +5528,7 @@
         <v>101.413445</v>
       </c>
       <c r="O69" s="9" t="n">
-        <v>102.85313</v>
+        <v>102.849597</v>
       </c>
       <c r="P69" s="9" t="n"/>
       <c r="Q69" s="9" t="n">
@@ -5606,7 +5606,7 @@
         <v>101.294322</v>
       </c>
       <c r="O70" s="6" t="n">
-        <v>102.641042</v>
+        <v>102.637772</v>
       </c>
       <c r="P70" s="6" t="n"/>
       <c r="Q70" s="6" t="n">
@@ -5684,7 +5684,7 @@
         <v>101.182899</v>
       </c>
       <c r="O71" s="9" t="n">
-        <v>102.338669</v>
+        <v>102.335775</v>
       </c>
       <c r="P71" s="9" t="n"/>
       <c r="Q71" s="9" t="n">
@@ -5762,7 +5762,7 @@
         <v>101.098066</v>
       </c>
       <c r="O72" s="6" t="n">
-        <v>101.933907</v>
+        <v>101.931515</v>
       </c>
       <c r="P72" s="6" t="n"/>
       <c r="Q72" s="6" t="n">
@@ -5840,7 +5840,7 @@
         <v>101.055154</v>
       </c>
       <c r="O73" s="9" t="n">
-        <v>101.452023</v>
+        <v>101.450228</v>
       </c>
       <c r="P73" s="9" t="n"/>
       <c r="Q73" s="9" t="n">
@@ -5918,7 +5918,7 @@
         <v>101.021534</v>
       </c>
       <c r="O74" s="6" t="n">
-        <v>100.976584</v>
+        <v>100.975378</v>
       </c>
       <c r="P74" s="6" t="n"/>
       <c r="Q74" s="6" t="n">
@@ -5996,7 +5996,7 @@
         <v>100.984445</v>
       </c>
       <c r="O75" s="9" t="n">
-        <v>100.493</v>
+        <v>100.492392</v>
       </c>
       <c r="P75" s="9" t="n"/>
       <c r="Q75" s="9" t="n">
@@ -6074,7 +6074,7 @@
         <v>100.920798</v>
       </c>
       <c r="O76" s="6" t="n">
-        <v>100.004761</v>
+        <v>100.004756</v>
       </c>
       <c r="P76" s="6" t="n"/>
       <c r="Q76" s="6" t="n">
@@ -6152,7 +6152,7 @@
         <v>100.792046</v>
       </c>
       <c r="O77" s="9" t="n">
-        <v>99.481098</v>
+        <v>99.481739</v>
       </c>
       <c r="P77" s="9" t="n"/>
       <c r="Q77" s="9" t="n">
@@ -6232,7 +6232,7 @@
         <v>100.593891</v>
       </c>
       <c r="O78" s="6" t="n">
-        <v>98.95821100000001</v>
+        <v>98.959497</v>
       </c>
       <c r="P78" s="6" t="n"/>
       <c r="Q78" s="6" t="n">
@@ -6312,7 +6312,7 @@
         <v>100.321488</v>
       </c>
       <c r="O79" s="9" t="n">
-        <v>98.47627799999999</v>
+        <v>98.47816</v>
       </c>
       <c r="P79" s="9" t="n"/>
       <c r="Q79" s="9" t="n">
@@ -6392,7 +6392,7 @@
         <v>99.992313</v>
       </c>
       <c r="O80" s="6" t="n">
-        <v>98.034485</v>
+        <v>98.03691499999999</v>
       </c>
       <c r="P80" s="6" t="n"/>
       <c r="Q80" s="6" t="n">
@@ -6472,7 +6472,7 @@
         <v>99.64630099999999</v>
       </c>
       <c r="O81" s="9" t="n">
-        <v>97.601446</v>
+        <v>97.60441400000001</v>
       </c>
       <c r="P81" s="9" t="n"/>
       <c r="Q81" s="9" t="n">
@@ -6552,7 +6552,7 @@
         <v>99.277101</v>
       </c>
       <c r="O82" s="6" t="n">
-        <v>97.18968</v>
+        <v>97.19315899999999</v>
       </c>
       <c r="P82" s="6" t="n"/>
       <c r="Q82" s="6" t="n">
@@ -6632,7 +6632,7 @@
         <v>98.886428</v>
       </c>
       <c r="O83" s="9" t="n">
-        <v>96.90272400000001</v>
+        <v>96.906559</v>
       </c>
       <c r="P83" s="9" t="n"/>
       <c r="Q83" s="9" t="n">
@@ -6712,7 +6712,7 @@
         <v>98.50815299999999</v>
       </c>
       <c r="O84" s="6" t="n">
-        <v>96.833494</v>
+        <v>96.837414</v>
       </c>
       <c r="P84" s="6" t="n"/>
       <c r="Q84" s="6" t="n">
@@ -6792,7 +6792,7 @@
         <v>98.180939</v>
       </c>
       <c r="O85" s="9" t="n">
-        <v>97.009427</v>
+        <v>97.01312900000001</v>
       </c>
       <c r="P85" s="9" t="n"/>
       <c r="Q85" s="9" t="n">
@@ -6872,7 +6872,7 @@
         <v>97.95077499999999</v>
       </c>
       <c r="O86" s="6" t="n">
-        <v>97.359527</v>
+        <v>97.362796</v>
       </c>
       <c r="P86" s="6" t="n"/>
       <c r="Q86" s="6" t="n">
@@ -6952,7 +6952,7 @@
         <v>97.839367</v>
       </c>
       <c r="O87" s="9" t="n">
-        <v>97.79688899999999</v>
+        <v>97.799617</v>
       </c>
       <c r="P87" s="9" t="n"/>
       <c r="Q87" s="9" t="n">
@@ -7032,7 +7032,7 @@
         <v>97.81147900000001</v>
       </c>
       <c r="O88" s="6" t="n">
-        <v>98.270624</v>
+        <v>98.272766</v>
       </c>
       <c r="P88" s="6" t="n"/>
       <c r="Q88" s="6" t="n">
@@ -7112,7 +7112,7 @@
         <v>97.841663</v>
       </c>
       <c r="O89" s="9" t="n">
-        <v>98.764004</v>
+        <v>98.765536</v>
       </c>
       <c r="P89" s="9" t="n"/>
       <c r="Q89" s="9" t="n">
@@ -7194,7 +7194,7 @@
         <v>97.892993</v>
       </c>
       <c r="O90" s="6" t="n">
-        <v>99.218654</v>
+        <v>99.219624</v>
       </c>
       <c r="P90" s="6" t="n"/>
       <c r="Q90" s="6" t="n">
@@ -7276,7 +7276,7 @@
         <v>97.95244</v>
       </c>
       <c r="O91" s="9" t="n">
-        <v>99.615182</v>
+        <v>99.615661</v>
       </c>
       <c r="P91" s="9" t="n"/>
       <c r="Q91" s="9" t="n">
@@ -7358,7 +7358,7 @@
         <v>98.018962</v>
       </c>
       <c r="O92" s="6" t="n">
-        <v>99.989581</v>
+        <v>99.98959499999999</v>
       </c>
       <c r="P92" s="6" t="n"/>
       <c r="Q92" s="6" t="n">
@@ -7440,7 +7440,7 @@
         <v>98.086065</v>
       </c>
       <c r="O93" s="9" t="n">
-        <v>100.385563</v>
+        <v>100.385082</v>
       </c>
       <c r="P93" s="9" t="n"/>
       <c r="Q93" s="9" t="n">
@@ -7522,7 +7522,7 @@
         <v>98.165239</v>
       </c>
       <c r="O94" s="6" t="n">
-        <v>100.838551</v>
+        <v>100.837509</v>
       </c>
       <c r="P94" s="6" t="n"/>
       <c r="Q94" s="6" t="n">
@@ -7604,7 +7604,7 @@
         <v>98.272392</v>
       </c>
       <c r="O95" s="9" t="n">
-        <v>101.242305</v>
+        <v>101.240763</v>
       </c>
       <c r="P95" s="9" t="n"/>
       <c r="Q95" s="9" t="n">
@@ -7686,7 +7686,7 @@
         <v>98.412328</v>
       </c>
       <c r="O96" s="6" t="n">
-        <v>101.462828</v>
+        <v>101.461014</v>
       </c>
       <c r="P96" s="6" t="n"/>
       <c r="Q96" s="6" t="n">
@@ -7768,7 +7768,7 @@
         <v>98.545681</v>
       </c>
       <c r="O97" s="9" t="n">
-        <v>101.455567</v>
+        <v>101.453763</v>
       </c>
       <c r="P97" s="9" t="n"/>
       <c r="Q97" s="9" t="n">
@@ -7850,7 +7850,7 @@
         <v>98.652556</v>
       </c>
       <c r="O98" s="6" t="n">
-        <v>101.241452</v>
+        <v>101.239914</v>
       </c>
       <c r="P98" s="6" t="n"/>
       <c r="Q98" s="6" t="n">
@@ -7932,7 +7932,7 @@
         <v>98.745116</v>
       </c>
       <c r="O99" s="9" t="n">
-        <v>100.868724</v>
+        <v>100.867646</v>
       </c>
       <c r="P99" s="9" t="n"/>
       <c r="Q99" s="9" t="n">
@@ -8014,7 +8014,7 @@
         <v>98.84505799999999</v>
       </c>
       <c r="O100" s="6" t="n">
-        <v>100.352987</v>
+        <v>100.352548</v>
       </c>
       <c r="P100" s="6" t="n"/>
       <c r="Q100" s="6" t="n">
@@ -8096,7 +8096,7 @@
         <v>98.996773</v>
       </c>
       <c r="O101" s="9" t="n">
-        <v>99.789496</v>
+        <v>99.789754</v>
       </c>
       <c r="P101" s="9" t="n"/>
       <c r="Q101" s="9" t="n">
@@ -8178,7 +8178,7 @@
         <v>99.241058</v>
       </c>
       <c r="O102" s="6" t="n">
-        <v>99.272651</v>
+        <v>99.273549</v>
       </c>
       <c r="P102" s="6" t="n"/>
       <c r="Q102" s="6" t="n">
@@ -8260,7 +8260,7 @@
         <v>99.545348</v>
       </c>
       <c r="O103" s="9" t="n">
-        <v>98.862094</v>
+        <v>98.863499</v>
       </c>
       <c r="P103" s="9" t="n"/>
       <c r="Q103" s="9" t="n">
@@ -8342,7 +8342,7 @@
         <v>99.882403</v>
       </c>
       <c r="O104" s="6" t="n">
-        <v>98.62419300000001</v>
+        <v>98.625893</v>
       </c>
       <c r="P104" s="6" t="n"/>
       <c r="Q104" s="6" t="n">
@@ -8424,7 +8424,7 @@
         <v>100.22264</v>
       </c>
       <c r="O105" s="9" t="n">
-        <v>98.561871</v>
+        <v>98.56365</v>
       </c>
       <c r="P105" s="9" t="n"/>
       <c r="Q105" s="9" t="n">
@@ -8506,7 +8506,7 @@
         <v>100.54233</v>
       </c>
       <c r="O106" s="6" t="n">
-        <v>98.628688</v>
+        <v>98.63038400000001</v>
       </c>
       <c r="P106" s="6" t="n"/>
       <c r="Q106" s="6" t="n">
@@ -8588,7 +8588,7 @@
         <v>100.826539</v>
       </c>
       <c r="O107" s="9" t="n">
-        <v>98.842822</v>
+        <v>98.84425400000001</v>
       </c>
       <c r="P107" s="9" t="n"/>
       <c r="Q107" s="9" t="n">
@@ -8670,7 +8670,7 @@
         <v>101.0659</v>
       </c>
       <c r="O108" s="6" t="n">
-        <v>99.19426199999999</v>
+        <v>99.19525899999999</v>
       </c>
       <c r="P108" s="6" t="n"/>
       <c r="Q108" s="6" t="n">
@@ -8752,7 +8752,7 @@
         <v>101.255606</v>
       </c>
       <c r="O109" s="9" t="n">
-        <v>99.651482</v>
+        <v>99.65191299999999</v>
       </c>
       <c r="P109" s="9" t="n"/>
       <c r="Q109" s="9" t="n">
@@ -8834,7 +8834,7 @@
         <v>101.382544</v>
       </c>
       <c r="O110" s="6" t="n">
-        <v>100.156445</v>
+        <v>100.15625</v>
       </c>
       <c r="P110" s="6" t="n"/>
       <c r="Q110" s="6" t="n">
@@ -8916,7 +8916,7 @@
         <v>101.453116</v>
       </c>
       <c r="O111" s="9" t="n">
-        <v>100.686644</v>
+        <v>100.685793</v>
       </c>
       <c r="P111" s="9" t="n"/>
       <c r="Q111" s="9" t="n">
@@ -8998,7 +8998,7 @@
         <v>101.484906</v>
       </c>
       <c r="O112" s="6" t="n">
-        <v>101.222396</v>
+        <v>101.220881</v>
       </c>
       <c r="P112" s="6" t="n"/>
       <c r="Q112" s="6" t="n">
@@ -9080,7 +9080,7 @@
         <v>101.485166</v>
       </c>
       <c r="O113" s="9" t="n">
-        <v>101.653175</v>
+        <v>101.651126</v>
       </c>
       <c r="P113" s="9" t="n"/>
       <c r="Q113" s="9" t="n">
@@ -9162,7 +9162,7 @@
         <v>101.472124</v>
       </c>
       <c r="O114" s="6" t="n">
-        <v>101.952612</v>
+        <v>101.950193</v>
       </c>
       <c r="P114" s="6" t="n"/>
       <c r="Q114" s="6" t="n">
@@ -9244,7 +9244,7 @@
         <v>101.434323</v>
       </c>
       <c r="O115" s="9" t="n">
-        <v>102.128342</v>
+        <v>102.125705</v>
       </c>
       <c r="P115" s="9" t="n"/>
       <c r="Q115" s="9" t="n">
@@ -9326,7 +9326,7 @@
         <v>101.349857</v>
       </c>
       <c r="O116" s="6" t="n">
-        <v>102.152115</v>
+        <v>102.14945</v>
       </c>
       <c r="P116" s="6" t="n"/>
       <c r="Q116" s="6" t="n">
@@ -9408,7 +9408,7 @@
         <v>101.217953</v>
       </c>
       <c r="O117" s="9" t="n">
-        <v>102.022372</v>
+        <v>102.01987</v>
       </c>
       <c r="P117" s="9" t="n"/>
       <c r="Q117" s="9" t="n">
@@ -9490,7 +9490,7 @@
         <v>101.045453</v>
       </c>
       <c r="O118" s="6" t="n">
-        <v>101.789472</v>
+        <v>101.78726</v>
       </c>
       <c r="P118" s="6" t="n"/>
       <c r="Q118" s="6" t="n">
@@ -9572,7 +9572,7 @@
         <v>100.859876</v>
       </c>
       <c r="O119" s="9" t="n">
-        <v>101.501531</v>
+        <v>101.499675</v>
       </c>
       <c r="P119" s="9" t="n"/>
       <c r="Q119" s="9" t="n">
@@ -9654,7 +9654,7 @@
         <v>100.673591</v>
       </c>
       <c r="O120" s="6" t="n">
-        <v>101.18847</v>
+        <v>101.187001</v>
       </c>
       <c r="P120" s="6" t="n"/>
       <c r="Q120" s="6" t="n">
@@ -9736,7 +9736,7 @@
         <v>100.537663</v>
       </c>
       <c r="O121" s="9" t="n">
-        <v>100.843202</v>
+        <v>100.842161</v>
       </c>
       <c r="P121" s="9" t="n"/>
       <c r="Q121" s="9" t="n">
@@ -9818,7 +9818,7 @@
         <v>100.451146</v>
       </c>
       <c r="O122" s="6" t="n">
-        <v>100.555799</v>
+        <v>100.555113</v>
       </c>
       <c r="P122" s="6" t="n"/>
       <c r="Q122" s="6" t="n">
@@ -9900,7 +9900,7 @@
         <v>100.374445</v>
       </c>
       <c r="O123" s="9" t="n">
-        <v>100.409143</v>
+        <v>100.408638</v>
       </c>
       <c r="P123" s="9" t="n"/>
       <c r="Q123" s="9" t="n">
@@ -9982,7 +9982,7 @@
         <v>100.293431</v>
       </c>
       <c r="O124" s="6" t="n">
-        <v>100.407487</v>
+        <v>100.406985</v>
       </c>
       <c r="P124" s="6" t="n"/>
       <c r="Q124" s="6" t="n">
@@ -10064,7 +10064,7 @@
         <v>100.201901</v>
       </c>
       <c r="O125" s="9" t="n">
-        <v>100.508659</v>
+        <v>100.508033</v>
       </c>
       <c r="P125" s="9" t="n"/>
       <c r="Q125" s="9" t="n">
@@ -10146,7 +10146,7 @@
         <v>100.117984</v>
       </c>
       <c r="O126" s="6" t="n">
-        <v>100.649017</v>
+        <v>100.648218</v>
       </c>
       <c r="P126" s="6" t="n"/>
       <c r="Q126" s="6" t="n">
@@ -10228,7 +10228,7 @@
         <v>100.060988</v>
       </c>
       <c r="O127" s="9" t="n">
-        <v>100.780785</v>
+        <v>100.779823</v>
       </c>
       <c r="P127" s="9" t="n"/>
       <c r="Q127" s="9" t="n">
@@ -10310,7 +10310,7 @@
         <v>100.056448</v>
       </c>
       <c r="O128" s="6" t="n">
-        <v>100.890357</v>
+        <v>100.889258</v>
       </c>
       <c r="P128" s="6" t="n"/>
       <c r="Q128" s="6" t="n">
@@ -10392,7 +10392,7 @@
         <v>100.110861</v>
       </c>
       <c r="O129" s="9" t="n">
-        <v>100.951289</v>
+        <v>100.950111</v>
       </c>
       <c r="P129" s="9" t="n"/>
       <c r="Q129" s="9" t="n">
@@ -10474,7 +10474,7 @@
         <v>100.22437</v>
       </c>
       <c r="O130" s="6" t="n">
-        <v>100.975265</v>
+        <v>100.974055</v>
       </c>
       <c r="P130" s="6" t="n"/>
       <c r="Q130" s="6" t="n">
@@ -10556,7 +10556,7 @@
         <v>100.370938</v>
       </c>
       <c r="O131" s="9" t="n">
-        <v>100.954664</v>
+        <v>100.95348</v>
       </c>
       <c r="P131" s="9" t="n"/>
       <c r="Q131" s="9" t="n">
@@ -10638,7 +10638,7 @@
         <v>100.523246</v>
       </c>
       <c r="O132" s="6" t="n">
-        <v>100.947405</v>
+        <v>100.946231</v>
       </c>
       <c r="P132" s="6" t="n"/>
       <c r="Q132" s="6" t="n">
@@ -10720,7 +10720,7 @@
         <v>100.655925</v>
       </c>
       <c r="O133" s="9" t="n">
-        <v>101.000878</v>
+        <v>100.999638</v>
       </c>
       <c r="P133" s="9" t="n"/>
       <c r="Q133" s="9" t="n">
@@ -10802,7 +10802,7 @@
         <v>100.738316</v>
       </c>
       <c r="O134" s="6" t="n">
-        <v>101.065809</v>
+        <v>101.064491</v>
       </c>
       <c r="P134" s="6" t="n"/>
       <c r="Q134" s="6" t="n">
@@ -10884,7 +10884,7 @@
         <v>100.757939</v>
       </c>
       <c r="O135" s="9" t="n">
-        <v>101.068738</v>
+        <v>101.067416</v>
       </c>
       <c r="P135" s="9" t="n"/>
       <c r="Q135" s="9" t="n">
@@ -10966,7 +10966,7 @@
         <v>100.716531</v>
       </c>
       <c r="O136" s="6" t="n">
-        <v>100.934708</v>
+        <v>100.933552</v>
       </c>
       <c r="P136" s="6" t="n"/>
       <c r="Q136" s="6" t="n">
@@ -11048,7 +11048,7 @@
         <v>100.63709</v>
       </c>
       <c r="O137" s="9" t="n">
-        <v>100.719173</v>
+        <v>100.718284</v>
       </c>
       <c r="P137" s="9" t="n"/>
       <c r="Q137" s="9" t="n">
@@ -11130,7 +11130,7 @@
         <v>100.528929</v>
       </c>
       <c r="O138" s="6" t="n">
-        <v>100.479194</v>
+        <v>100.478603</v>
       </c>
       <c r="P138" s="6" t="n"/>
       <c r="Q138" s="6" t="n">
@@ -11212,7 +11212,7 @@
         <v>100.416987</v>
       </c>
       <c r="O139" s="9" t="n">
-        <v>100.282492</v>
+        <v>100.282145</v>
       </c>
       <c r="P139" s="9" t="n"/>
       <c r="Q139" s="9" t="n">
@@ -11294,7 +11294,7 @@
         <v>100.326247</v>
       </c>
       <c r="O140" s="6" t="n">
-        <v>100.143109</v>
+        <v>100.142935</v>
       </c>
       <c r="P140" s="6" t="n"/>
       <c r="Q140" s="6" t="n">
@@ -11376,7 +11376,7 @@
         <v>100.276095</v>
       </c>
       <c r="O141" s="9" t="n">
-        <v>100.081037</v>
+        <v>100.080943</v>
       </c>
       <c r="P141" s="9" t="n"/>
       <c r="Q141" s="9" t="n">
@@ -11458,7 +11458,7 @@
         <v>100.25898</v>
       </c>
       <c r="O142" s="6" t="n">
-        <v>100.088563</v>
+        <v>100.088461</v>
       </c>
       <c r="P142" s="6" t="n"/>
       <c r="Q142" s="6" t="n">
@@ -11540,7 +11540,7 @@
         <v>100.261962</v>
       </c>
       <c r="O143" s="9" t="n">
-        <v>100.126727</v>
+        <v>100.126577</v>
       </c>
       <c r="P143" s="9" t="n"/>
       <c r="Q143" s="9" t="n">
@@ -11622,7 +11622,7 @@
         <v>100.283657</v>
       </c>
       <c r="O144" s="6" t="n">
-        <v>100.157413</v>
+        <v>100.157223</v>
       </c>
       <c r="P144" s="6" t="n"/>
       <c r="Q144" s="6" t="n">
@@ -11704,7 +11704,7 @@
         <v>100.31637</v>
       </c>
       <c r="O145" s="9" t="n">
-        <v>100.162456</v>
+        <v>100.16226</v>
       </c>
       <c r="P145" s="9" t="n"/>
       <c r="Q145" s="9" t="n">
@@ -11786,7 +11786,7 @@
         <v>100.361433</v>
       </c>
       <c r="O146" s="6" t="n">
-        <v>100.11474</v>
+        <v>100.114604</v>
       </c>
       <c r="P146" s="6" t="n"/>
       <c r="Q146" s="6" t="n">
@@ -11868,7 +11868,7 @@
         <v>100.425478</v>
       </c>
       <c r="O147" s="9" t="n">
-        <v>99.996447</v>
+        <v>99.996458</v>
       </c>
       <c r="P147" s="9" t="n"/>
       <c r="Q147" s="9" t="n">
@@ -11950,7 +11950,7 @@
         <v>100.51403</v>
       </c>
       <c r="O148" s="6" t="n">
-        <v>99.90760299999999</v>
+        <v>99.90772699999999</v>
       </c>
       <c r="P148" s="6" t="n"/>
       <c r="Q148" s="6" t="n">
@@ -12032,7 +12032,7 @@
         <v>100.611543</v>
       </c>
       <c r="O149" s="9" t="n">
-        <v>99.89572</v>
+        <v>99.89586199999999</v>
       </c>
       <c r="P149" s="9" t="n"/>
       <c r="Q149" s="9" t="n">
@@ -12114,7 +12114,7 @@
         <v>100.732318</v>
       </c>
       <c r="O150" s="6" t="n">
-        <v>99.943676</v>
+        <v>99.94376200000001</v>
       </c>
       <c r="P150" s="6" t="n"/>
       <c r="Q150" s="6" t="n">
@@ -12196,7 +12196,7 @@
         <v>100.874249</v>
       </c>
       <c r="O151" s="9" t="n">
-        <v>100.004613</v>
+        <v>100.004625</v>
       </c>
       <c r="P151" s="9" t="n"/>
       <c r="Q151" s="9" t="n">
@@ -12278,7 +12278,7 @@
         <v>101.01343</v>
       </c>
       <c r="O152" s="6" t="n">
-        <v>100.036713</v>
+        <v>100.036684</v>
       </c>
       <c r="P152" s="6" t="n"/>
       <c r="Q152" s="6" t="n">
@@ -12360,7 +12360,7 @@
         <v>101.11644</v>
       </c>
       <c r="O153" s="9" t="n">
-        <v>100.027152</v>
+        <v>100.027131</v>
       </c>
       <c r="P153" s="9" t="n"/>
       <c r="Q153" s="9" t="n">
@@ -12442,7 +12442,7 @@
         <v>101.170233</v>
       </c>
       <c r="O154" s="6" t="n">
-        <v>99.931394</v>
+        <v>99.931487</v>
       </c>
       <c r="P154" s="6" t="n"/>
       <c r="Q154" s="6" t="n">
@@ -12524,7 +12524,7 @@
         <v>101.171436</v>
       </c>
       <c r="O155" s="9" t="n">
-        <v>99.727223</v>
+        <v>99.727564</v>
       </c>
       <c r="P155" s="9" t="n"/>
       <c r="Q155" s="9" t="n">
@@ -12606,7 +12606,7 @@
         <v>101.127271</v>
       </c>
       <c r="O156" s="6" t="n">
-        <v>99.44432</v>
+        <v>99.44500600000001</v>
       </c>
       <c r="P156" s="6" t="n"/>
       <c r="Q156" s="6" t="n">
@@ -12688,7 +12688,7 @@
         <v>101.042696</v>
       </c>
       <c r="O157" s="9" t="n">
-        <v>99.10198800000001</v>
+        <v>99.103094</v>
       </c>
       <c r="P157" s="9" t="n"/>
       <c r="Q157" s="9" t="n">
@@ -12770,7 +12770,7 @@
         <v>100.938767</v>
       </c>
       <c r="O158" s="6" t="n">
-        <v>98.757592</v>
+        <v>98.759124</v>
       </c>
       <c r="P158" s="6" t="n"/>
       <c r="Q158" s="6" t="n">
@@ -12852,7 +12852,7 @@
         <v>100.824871</v>
       </c>
       <c r="O159" s="9" t="n">
-        <v>98.467595</v>
+        <v>98.46948999999999</v>
       </c>
       <c r="P159" s="9" t="n"/>
       <c r="Q159" s="9" t="n">
@@ -12934,7 +12934,7 @@
         <v>100.693439</v>
       </c>
       <c r="O160" s="6" t="n">
-        <v>98.270861</v>
+        <v>98.273011</v>
       </c>
       <c r="P160" s="6" t="n"/>
       <c r="Q160" s="6" t="n">
@@ -13016,7 +13016,7 @@
         <v>100.551053</v>
       </c>
       <c r="O161" s="9" t="n">
-        <v>98.152787</v>
+        <v>98.155097</v>
       </c>
       <c r="P161" s="9" t="n"/>
       <c r="Q161" s="9" t="n">
@@ -13098,7 +13098,7 @@
         <v>100.412185</v>
       </c>
       <c r="O162" s="6" t="n">
-        <v>98.09493399999999</v>
+        <v>98.09733</v>
       </c>
       <c r="P162" s="6" t="n"/>
       <c r="Q162" s="6" t="n">
@@ -13180,7 +13180,7 @@
         <v>100.309694</v>
       </c>
       <c r="O163" s="9" t="n">
-        <v>98.071708</v>
+        <v>98.07414</v>
       </c>
       <c r="P163" s="9" t="n"/>
       <c r="Q163" s="9" t="n">
@@ -13262,7 +13262,7 @@
         <v>100.233917</v>
       </c>
       <c r="O164" s="6" t="n">
-        <v>98.09358899999999</v>
+        <v>98.09599</v>
       </c>
       <c r="P164" s="6" t="n"/>
       <c r="Q164" s="6" t="n">
@@ -13344,7 +13344,7 @@
         <v>100.175406</v>
       </c>
       <c r="O165" s="9" t="n">
-        <v>98.152066</v>
+        <v>98.15438399999999</v>
       </c>
       <c r="P165" s="9" t="n"/>
       <c r="Q165" s="9" t="n">
@@ -13426,7 +13426,7 @@
         <v>100.113812</v>
       </c>
       <c r="O166" s="6" t="n">
-        <v>98.262688</v>
+        <v>98.264855</v>
       </c>
       <c r="P166" s="6" t="n"/>
       <c r="Q166" s="6" t="n">
@@ -13508,7 +13508,7 @@
         <v>100.040858</v>
       </c>
       <c r="O167" s="9" t="n">
-        <v>98.444676</v>
+        <v>98.446603</v>
       </c>
       <c r="P167" s="9" t="n"/>
       <c r="Q167" s="9" t="n">
@@ -13590,7 +13590,7 @@
         <v>99.94884500000001</v>
       </c>
       <c r="O168" s="6" t="n">
-        <v>98.62534100000001</v>
+        <v>98.627031</v>
       </c>
       <c r="P168" s="6" t="n"/>
       <c r="Q168" s="6" t="n">
@@ -13672,7 +13672,7 @@
         <v>99.842817</v>
       </c>
       <c r="O169" s="9" t="n">
-        <v>98.78278299999999</v>
+        <v>98.78427000000001</v>
       </c>
       <c r="P169" s="9" t="n"/>
       <c r="Q169" s="9" t="n">
@@ -13754,7 +13754,7 @@
         <v>99.78045299999999</v>
       </c>
       <c r="O170" s="6" t="n">
-        <v>98.92977</v>
+        <v>98.931074</v>
       </c>
       <c r="P170" s="6" t="n"/>
       <c r="Q170" s="6" t="n">
@@ -13836,7 +13836,7 @@
         <v>99.774691</v>
       </c>
       <c r="O171" s="9" t="n">
-        <v>99.083189</v>
+        <v>99.084312</v>
       </c>
       <c r="P171" s="9" t="n"/>
       <c r="Q171" s="9" t="n">
@@ -13918,7 +13918,7 @@
         <v>99.842652</v>
       </c>
       <c r="O172" s="6" t="n">
-        <v>99.23689299999999</v>
+        <v>99.23784499999999</v>
       </c>
       <c r="P172" s="6" t="n"/>
       <c r="Q172" s="6" t="n">
@@ -14000,7 +14000,7 @@
         <v>100.003455</v>
       </c>
       <c r="O173" s="9" t="n">
-        <v>99.378972</v>
+        <v>99.379774</v>
       </c>
       <c r="P173" s="9" t="n"/>
       <c r="Q173" s="9" t="n">
@@ -14082,7 +14082,7 @@
         <v>100.21716</v>
       </c>
       <c r="O174" s="6" t="n">
-        <v>99.55556900000001</v>
+        <v>99.556181</v>
       </c>
       <c r="P174" s="6" t="n"/>
       <c r="Q174" s="6" t="n">
@@ -14164,7 +14164,7 @@
         <v>100.433036</v>
       </c>
       <c r="O175" s="9" t="n">
-        <v>99.762925</v>
+        <v>99.763295</v>
       </c>
       <c r="P175" s="9" t="n"/>
       <c r="Q175" s="9" t="n">
@@ -14246,7 +14246,7 @@
         <v>100.616494</v>
       </c>
       <c r="O176" s="6" t="n">
-        <v>99.946068</v>
+        <v>99.94620999999999</v>
       </c>
       <c r="P176" s="6" t="n"/>
       <c r="Q176" s="6" t="n">
@@ -14328,7 +14328,7 @@
         <v>100.771587</v>
       </c>
       <c r="O177" s="9" t="n">
-        <v>100.037299</v>
+        <v>100.037318</v>
       </c>
       <c r="P177" s="9" t="n"/>
       <c r="Q177" s="9" t="n">
@@ -14410,7 +14410,7 @@
         <v>100.891778</v>
       </c>
       <c r="O178" s="6" t="n">
-        <v>100.024924</v>
+        <v>100.024936</v>
       </c>
       <c r="P178" s="6" t="n"/>
       <c r="Q178" s="6" t="n">
@@ -14492,7 +14492,7 @@
         <v>100.971814</v>
       </c>
       <c r="O179" s="9" t="n">
-        <v>99.93726100000001</v>
+        <v>99.937353</v>
       </c>
       <c r="P179" s="9" t="n"/>
       <c r="Q179" s="9" t="n">
@@ -14574,7 +14574,7 @@
         <v>101.001825</v>
       </c>
       <c r="O180" s="6" t="n">
-        <v>99.842291</v>
+        <v>99.84246899999999</v>
       </c>
       <c r="P180" s="6" t="n"/>
       <c r="Q180" s="6" t="n">
@@ -14656,7 +14656,7 @@
         <v>100.978331</v>
       </c>
       <c r="O181" s="9" t="n">
-        <v>99.766375</v>
+        <v>99.76661199999999</v>
       </c>
       <c r="P181" s="9" t="n"/>
       <c r="Q181" s="9" t="n">
@@ -14738,7 +14738,7 @@
         <v>100.902762</v>
       </c>
       <c r="O182" s="6" t="n">
-        <v>99.68075399999999</v>
+        <v>99.681062</v>
       </c>
       <c r="P182" s="6" t="n"/>
       <c r="Q182" s="6" t="n">
@@ -14820,7 +14820,7 @@
         <v>100.763539</v>
       </c>
       <c r="O183" s="9" t="n">
-        <v>99.531198</v>
+        <v>99.531655</v>
       </c>
       <c r="P183" s="9" t="n"/>
       <c r="Q183" s="9" t="n">
@@ -14902,7 +14902,7 @@
         <v>100.520509</v>
       </c>
       <c r="O184" s="6" t="n">
-        <v>99.232979</v>
+        <v>99.233773</v>
       </c>
       <c r="P184" s="6" t="n"/>
       <c r="Q184" s="6" t="n">
@@ -14984,7 +14984,7 @@
         <v>100.154459</v>
       </c>
       <c r="O185" s="9" t="n">
-        <v>98.78161900000001</v>
+        <v>98.78295</v>
       </c>
       <c r="P185" s="9" t="n"/>
       <c r="Q185" s="9" t="n">
@@ -15066,7 +15066,7 @@
         <v>99.688078</v>
       </c>
       <c r="O186" s="6" t="n">
-        <v>98.204131</v>
+        <v>98.206176</v>
       </c>
       <c r="P186" s="6" t="n"/>
       <c r="Q186" s="6" t="n">
@@ -15148,7 +15148,7 @@
         <v>99.19038999999999</v>
       </c>
       <c r="O187" s="9" t="n">
-        <v>97.60439100000001</v>
+        <v>97.607215</v>
       </c>
       <c r="P187" s="9" t="n"/>
       <c r="Q187" s="9" t="n">
@@ -15230,7 +15230,7 @@
         <v>98.73393299999999</v>
       </c>
       <c r="O188" s="6" t="n">
-        <v>97.129926</v>
+        <v>97.133386</v>
       </c>
       <c r="P188" s="6" t="n"/>
       <c r="Q188" s="6" t="n">
@@ -15312,7 +15312,7 @@
         <v>98.35557900000001</v>
       </c>
       <c r="O189" s="9" t="n">
-        <v>96.93074900000001</v>
+        <v>96.934489</v>
       </c>
       <c r="P189" s="9" t="n"/>
       <c r="Q189" s="9" t="n">
@@ -15394,7 +15394,7 @@
         <v>98.10335600000001</v>
       </c>
       <c r="O190" s="6" t="n">
-        <v>97.054075</v>
+        <v>97.057682</v>
       </c>
       <c r="P190" s="6" t="n"/>
       <c r="Q190" s="6" t="n">
@@ -15476,7 +15476,7 @@
         <v>97.967546</v>
       </c>
       <c r="O191" s="9" t="n">
-        <v>97.463922</v>
+        <v>97.46702999999999</v>
       </c>
       <c r="P191" s="9" t="n"/>
       <c r="Q191" s="9" t="n">
@@ -15558,7 +15558,7 @@
         <v>97.926462</v>
       </c>
       <c r="O192" s="6" t="n">
-        <v>98.040933</v>
+        <v>98.04333</v>
       </c>
       <c r="P192" s="6" t="n"/>
       <c r="Q192" s="6" t="n">
@@ -15640,7 +15640,7 @@
         <v>97.960284</v>
       </c>
       <c r="O193" s="9" t="n">
-        <v>98.690287</v>
+        <v>98.69188200000001</v>
       </c>
       <c r="P193" s="9" t="n"/>
       <c r="Q193" s="9" t="n">
@@ -15722,7 +15722,7 @@
         <v>98.027846</v>
       </c>
       <c r="O194" s="6" t="n">
-        <v>99.351623</v>
+        <v>99.352406</v>
       </c>
       <c r="P194" s="6" t="n"/>
       <c r="Q194" s="6" t="n">
@@ -15804,7 +15804,7 @@
         <v>98.11821500000001</v>
       </c>
       <c r="O195" s="9" t="n">
-        <v>99.99029899999999</v>
+        <v>99.99030399999999</v>
       </c>
       <c r="P195" s="9" t="n"/>
       <c r="Q195" s="9" t="n">
@@ -15886,7 +15886,7 @@
         <v>98.24487000000001</v>
       </c>
       <c r="O196" s="6" t="n">
-        <v>100.59591</v>
+        <v>100.595184</v>
       </c>
       <c r="P196" s="6" t="n"/>
       <c r="Q196" s="6" t="n">
@@ -15968,7 +15968,7 @@
         <v>98.403447</v>
       </c>
       <c r="O197" s="9" t="n">
-        <v>101.11932</v>
+        <v>101.117972</v>
       </c>
       <c r="P197" s="9" t="n"/>
       <c r="Q197" s="9" t="n">
@@ -16050,7 +16050,7 @@
         <v>98.576204</v>
       </c>
       <c r="O198" s="6" t="n">
-        <v>101.512671</v>
+        <v>101.510859</v>
       </c>
       <c r="P198" s="6" t="n"/>
       <c r="Q198" s="6" t="n">
@@ -16132,7 +16132,7 @@
         <v>98.750491</v>
       </c>
       <c r="O199" s="9" t="n">
-        <v>101.759907</v>
+        <v>101.757798</v>
       </c>
       <c r="P199" s="9" t="n"/>
       <c r="Q199" s="9" t="n">
@@ -16214,7 +16214,7 @@
         <v>98.90775499999999</v>
       </c>
       <c r="O200" s="6" t="n">
-        <v>101.911364</v>
+        <v>101.909062</v>
       </c>
       <c r="P200" s="6" t="n"/>
       <c r="Q200" s="6" t="n">
@@ -16296,7 +16296,7 @@
         <v>99.04475499999999</v>
       </c>
       <c r="O201" s="9" t="n">
-        <v>101.976341</v>
+        <v>101.973943</v>
       </c>
       <c r="P201" s="9" t="n"/>
       <c r="Q201" s="9" t="n">
@@ -16378,7 +16378,7 @@
         <v>99.153679</v>
       </c>
       <c r="O202" s="6" t="n">
-        <v>101.951771</v>
+        <v>101.949382</v>
       </c>
       <c r="P202" s="6" t="n"/>
       <c r="Q202" s="6" t="n">
@@ -16460,7 +16460,7 @@
         <v>99.236716</v>
       </c>
       <c r="O203" s="9" t="n">
-        <v>101.830243</v>
+        <v>101.827988</v>
       </c>
       <c r="P203" s="9" t="n"/>
       <c r="Q203" s="9" t="n">
@@ -16542,7 +16542,7 @@
         <v>99.32405</v>
       </c>
       <c r="O204" s="6" t="n">
-        <v>101.658815</v>
+        <v>101.656758</v>
       </c>
       <c r="P204" s="6" t="n"/>
       <c r="Q204" s="6" t="n">
@@ -16624,7 +16624,7 @@
         <v>99.407473</v>
       </c>
       <c r="O205" s="9" t="n">
-        <v>101.461386</v>
+        <v>101.459561</v>
       </c>
       <c r="P205" s="9" t="n"/>
       <c r="Q205" s="9" t="n">
@@ -16706,7 +16706,7 @@
         <v>99.475847</v>
       </c>
       <c r="O206" s="6" t="n">
-        <v>101.2378</v>
+        <v>101.236249</v>
       </c>
       <c r="P206" s="6" t="n"/>
       <c r="Q206" s="6" t="n">
@@ -16788,7 +16788,7 @@
         <v>99.52188200000001</v>
       </c>
       <c r="O207" s="9" t="n">
-        <v>101.030478</v>
+        <v>101.029187</v>
       </c>
       <c r="P207" s="9" t="n"/>
       <c r="Q207" s="9" t="n">
@@ -16870,7 +16870,7 @@
         <v>99.542753</v>
       </c>
       <c r="O208" s="6" t="n">
-        <v>100.894773</v>
+        <v>100.893659</v>
       </c>
       <c r="P208" s="6" t="n"/>
       <c r="Q208" s="6" t="n">
@@ -16952,7 +16952,7 @@
         <v>99.56228400000001</v>
       </c>
       <c r="O209" s="9" t="n">
-        <v>100.874089</v>
+        <v>100.873014</v>
       </c>
       <c r="P209" s="9" t="n"/>
       <c r="Q209" s="9" t="n">
@@ -17034,7 +17034,7 @@
         <v>99.618022</v>
       </c>
       <c r="O210" s="6" t="n">
-        <v>100.947919</v>
+        <v>100.946766</v>
       </c>
       <c r="P210" s="6" t="n"/>
       <c r="Q210" s="6" t="n">
@@ -17116,7 +17116,7 @@
         <v>99.70281900000001</v>
       </c>
       <c r="O211" s="9" t="n">
-        <v>101.076858</v>
+        <v>101.075557</v>
       </c>
       <c r="P211" s="9" t="n"/>
       <c r="Q211" s="9" t="n">
@@ -17198,7 +17198,7 @@
         <v>99.808397</v>
       </c>
       <c r="O212" s="6" t="n">
-        <v>101.18498</v>
+        <v>101.18355</v>
       </c>
       <c r="P212" s="6" t="n"/>
       <c r="Q212" s="6" t="n">
@@ -17280,7 +17280,7 @@
         <v>99.920496</v>
       </c>
       <c r="O213" s="9" t="n">
-        <v>101.256925</v>
+        <v>101.255403</v>
       </c>
       <c r="P213" s="9" t="n"/>
       <c r="Q213" s="9" t="n">
@@ -17362,7 +17362,7 @@
         <v>100.031551</v>
       </c>
       <c r="O214" s="6" t="n">
-        <v>101.294384</v>
+        <v>101.292803</v>
       </c>
       <c r="P214" s="6" t="n"/>
       <c r="Q214" s="6" t="n">
@@ -17444,7 +17444,7 @@
         <v>100.143371</v>
       </c>
       <c r="O215" s="9" t="n">
-        <v>101.30859</v>
+        <v>101.306987</v>
       </c>
       <c r="P215" s="9" t="n"/>
       <c r="Q215" s="9" t="n">
@@ -17526,7 +17526,7 @@
         <v>100.245406</v>
       </c>
       <c r="O216" s="6" t="n">
-        <v>101.319354</v>
+        <v>101.317731</v>
       </c>
       <c r="P216" s="6" t="n"/>
       <c r="Q216" s="6" t="n">
@@ -17608,7 +17608,7 @@
         <v>100.331473</v>
       </c>
       <c r="O217" s="9" t="n">
-        <v>101.366923</v>
+        <v>101.365232</v>
       </c>
       <c r="P217" s="9" t="n"/>
       <c r="Q217" s="9" t="n">
@@ -17690,7 +17690,7 @@
         <v>100.406185</v>
       </c>
       <c r="O218" s="6" t="n">
-        <v>101.446717</v>
+        <v>101.444929</v>
       </c>
       <c r="P218" s="6" t="n"/>
       <c r="Q218" s="6" t="n">
@@ -17772,7 +17772,7 @@
         <v>100.472125</v>
       </c>
       <c r="O219" s="9" t="n">
-        <v>101.521993</v>
+        <v>101.520116</v>
       </c>
       <c r="P219" s="9" t="n"/>
       <c r="Q219" s="9" t="n">
@@ -17854,7 +17854,7 @@
         <v>100.529471</v>
       </c>
       <c r="O220" s="6" t="n">
-        <v>101.56386</v>
+        <v>101.561943</v>
       </c>
       <c r="P220" s="6" t="n"/>
       <c r="Q220" s="6" t="n">
@@ -17936,7 +17936,7 @@
         <v>100.571143</v>
       </c>
       <c r="O221" s="9" t="n">
-        <v>101.554706</v>
+        <v>101.552815</v>
       </c>
       <c r="P221" s="9" t="n"/>
       <c r="Q221" s="9" t="n">
@@ -18018,7 +18018,7 @@
         <v>100.597709</v>
       </c>
       <c r="O222" s="6" t="n">
-        <v>101.490082</v>
+        <v>101.488278</v>
       </c>
       <c r="P222" s="6" t="n"/>
       <c r="Q222" s="6" t="n">
@@ -18100,7 +18100,7 @@
         <v>100.595021</v>
       </c>
       <c r="O223" s="9" t="n">
-        <v>101.389847</v>
+        <v>101.388178</v>
       </c>
       <c r="P223" s="9" t="n"/>
       <c r="Q223" s="9" t="n">
@@ -18182,7 +18182,7 @@
         <v>100.555884</v>
       </c>
       <c r="O224" s="6" t="n">
-        <v>101.226108</v>
+        <v>101.224646</v>
       </c>
       <c r="P224" s="6" t="n"/>
       <c r="Q224" s="6" t="n">
@@ -18264,7 +18264,7 @@
         <v>100.474418</v>
       </c>
       <c r="O225" s="9" t="n">
-        <v>100.996475</v>
+        <v>100.99528</v>
       </c>
       <c r="P225" s="9" t="n"/>
       <c r="Q225" s="9" t="n">
@@ -18346,7 +18346,7 @@
         <v>100.356471</v>
       </c>
       <c r="O226" s="6" t="n">
-        <v>100.767495</v>
+        <v>100.766572</v>
       </c>
       <c r="P226" s="6" t="n"/>
       <c r="Q226" s="6" t="n">
@@ -18428,7 +18428,7 @@
         <v>100.220202</v>
       </c>
       <c r="O227" s="9" t="n">
-        <v>100.566149</v>
+        <v>100.56545</v>
       </c>
       <c r="P227" s="9" t="n"/>
       <c r="Q227" s="9" t="n">
@@ -18510,7 +18510,7 @@
         <v>100.089906</v>
       </c>
       <c r="O228" s="6" t="n">
-        <v>100.375689</v>
+        <v>100.375216</v>
       </c>
       <c r="P228" s="6" t="n"/>
       <c r="Q228" s="6" t="n">
@@ -18592,7 +18592,7 @@
         <v>99.981208</v>
       </c>
       <c r="O229" s="9" t="n">
-        <v>100.1711</v>
+        <v>100.170897</v>
       </c>
       <c r="P229" s="9" t="n"/>
       <c r="Q229" s="9" t="n">
@@ -18674,7 +18674,7 @@
         <v>99.90106299999999</v>
       </c>
       <c r="O230" s="6" t="n">
-        <v>99.96679899999999</v>
+        <v>99.96684999999999</v>
       </c>
       <c r="P230" s="6" t="n"/>
       <c r="Q230" s="6" t="n">
@@ -18756,7 +18756,7 @@
         <v>99.841312</v>
       </c>
       <c r="O231" s="9" t="n">
-        <v>99.766699</v>
+        <v>99.76700200000001</v>
       </c>
       <c r="P231" s="9" t="n"/>
       <c r="Q231" s="9" t="n">
@@ -18838,7 +18838,7 @@
         <v>99.799183</v>
       </c>
       <c r="O232" s="6" t="n">
-        <v>99.570155</v>
+        <v>99.570707</v>
       </c>
       <c r="P232" s="6" t="n"/>
       <c r="Q232" s="6" t="n">
@@ -18920,7 +18920,7 @@
         <v>99.771214</v>
       </c>
       <c r="O233" s="9" t="n">
-        <v>99.407647</v>
+        <v>99.408389</v>
       </c>
       <c r="P233" s="9" t="n"/>
       <c r="Q233" s="9" t="n">
@@ -19002,7 +19002,7 @@
         <v>99.77301300000001</v>
       </c>
       <c r="O234" s="6" t="n">
-        <v>99.312195</v>
+        <v>99.313047</v>
       </c>
       <c r="P234" s="6" t="n"/>
       <c r="Q234" s="6" t="n">
@@ -19084,7 +19084,7 @@
         <v>99.81453500000001</v>
       </c>
       <c r="O235" s="9" t="n">
-        <v>99.309106</v>
+        <v>99.309934</v>
       </c>
       <c r="P235" s="9" t="n"/>
       <c r="Q235" s="9" t="n">
@@ -19166,7 +19166,7 @@
         <v>99.891158</v>
       </c>
       <c r="O236" s="6" t="n">
-        <v>99.40124900000001</v>
+        <v>99.40194</v>
       </c>
       <c r="P236" s="6" t="n"/>
       <c r="Q236" s="6" t="n">
@@ -19248,7 +19248,7 @@
         <v>99.988962</v>
       </c>
       <c r="O237" s="9" t="n">
-        <v>99.58260799999999</v>
+        <v>99.583088</v>
       </c>
       <c r="P237" s="9" t="n"/>
       <c r="Q237" s="9" t="n">
@@ -19330,7 +19330,7 @@
         <v>100.093697</v>
       </c>
       <c r="O238" s="6" t="n">
-        <v>99.785737</v>
+        <v>99.786002</v>
       </c>
       <c r="P238" s="6" t="n"/>
       <c r="Q238" s="6" t="n">
@@ -19412,7 +19412,7 @@
         <v>100.192889</v>
       </c>
       <c r="O239" s="9" t="n">
-        <v>99.961455</v>
+        <v>99.961513</v>
       </c>
       <c r="P239" s="9" t="n"/>
       <c r="Q239" s="9" t="n">
@@ -19494,7 +19494,7 @@
         <v>100.285093</v>
       </c>
       <c r="O240" s="6" t="n">
-        <v>100.130032</v>
+        <v>100.129883</v>
       </c>
       <c r="P240" s="6" t="n"/>
       <c r="Q240" s="6" t="n">
@@ -19576,7 +19576,7 @@
         <v>100.377273</v>
       </c>
       <c r="O241" s="9" t="n">
-        <v>100.27443</v>
+        <v>100.274099</v>
       </c>
       <c r="P241" s="9" t="n"/>
       <c r="Q241" s="9" t="n">
@@ -19658,7 +19658,7 @@
         <v>100.473648</v>
       </c>
       <c r="O242" s="6" t="n">
-        <v>100.421249</v>
+        <v>100.420729</v>
       </c>
       <c r="P242" s="6" t="n"/>
       <c r="Q242" s="6" t="n">
@@ -19740,7 +19740,7 @@
         <v>100.581864</v>
       </c>
       <c r="O243" s="9" t="n">
-        <v>100.588967</v>
+        <v>100.58824</v>
       </c>
       <c r="P243" s="9" t="n"/>
       <c r="Q243" s="9" t="n">
@@ -19822,7 +19822,7 @@
         <v>100.702642</v>
       </c>
       <c r="O244" s="6" t="n">
-        <v>100.745287</v>
+        <v>100.744343</v>
       </c>
       <c r="P244" s="6" t="n"/>
       <c r="Q244" s="6" t="n">
@@ -19904,7 +19904,7 @@
         <v>100.835624</v>
       </c>
       <c r="O245" s="9" t="n">
-        <v>100.881821</v>
+        <v>100.880699</v>
       </c>
       <c r="P245" s="9" t="n"/>
       <c r="Q245" s="9" t="n">
@@ -19986,7 +19986,7 @@
         <v>100.973945</v>
       </c>
       <c r="O246" s="6" t="n">
-        <v>100.992605</v>
+        <v>100.991365</v>
       </c>
       <c r="P246" s="6" t="n"/>
       <c r="Q246" s="6" t="n">
@@ -20068,7 +20068,7 @@
         <v>101.100266</v>
       </c>
       <c r="O247" s="9" t="n">
-        <v>101.037945</v>
+        <v>101.03665</v>
       </c>
       <c r="P247" s="9" t="n"/>
       <c r="Q247" s="9" t="n">
@@ -20150,7 +20150,7 @@
         <v>101.220627</v>
       </c>
       <c r="O248" s="6" t="n">
-        <v>101.058954</v>
+        <v>101.057634</v>
       </c>
       <c r="P248" s="6" t="n"/>
       <c r="Q248" s="6" t="n">
@@ -20232,7 +20232,7 @@
         <v>101.353368</v>
       </c>
       <c r="O249" s="9" t="n">
-        <v>101.056045</v>
+        <v>101.054736</v>
       </c>
       <c r="P249" s="9" t="n"/>
       <c r="Q249" s="9" t="n">
@@ -20314,7 +20314,7 @@
         <v>101.491925</v>
       </c>
       <c r="O250" s="6" t="n">
-        <v>101.02356</v>
+        <v>101.02227</v>
       </c>
       <c r="P250" s="6" t="n"/>
       <c r="Q250" s="6" t="n">
@@ -20396,7 +20396,7 @@
         <v>101.620261</v>
       </c>
       <c r="O251" s="9" t="n">
-        <v>100.989385</v>
+        <v>100.98814</v>
       </c>
       <c r="P251" s="9" t="n"/>
       <c r="Q251" s="9" t="n">
@@ -20478,7 +20478,7 @@
         <v>101.727241</v>
       </c>
       <c r="O252" s="6" t="n">
-        <v>100.901694</v>
+        <v>100.900579</v>
       </c>
       <c r="P252" s="6" t="n"/>
       <c r="Q252" s="6" t="n">
@@ -20560,7 +20560,7 @@
         <v>101.795031</v>
       </c>
       <c r="O253" s="9" t="n">
-        <v>100.774554</v>
+        <v>100.773598</v>
       </c>
       <c r="P253" s="9" t="n"/>
       <c r="Q253" s="9" t="n">
@@ -20642,7 +20642,7 @@
         <v>101.813423</v>
       </c>
       <c r="O254" s="6" t="n">
-        <v>100.595455</v>
+        <v>100.594735</v>
       </c>
       <c r="P254" s="6" t="n"/>
       <c r="Q254" s="6" t="n">
@@ -20724,7 +20724,7 @@
         <v>101.780165</v>
       </c>
       <c r="O255" s="9" t="n">
-        <v>100.326067</v>
+        <v>100.325693</v>
       </c>
       <c r="P255" s="9" t="n"/>
       <c r="Q255" s="9" t="n">
@@ -20806,7 +20806,7 @@
         <v>101.691687</v>
       </c>
       <c r="O256" s="6" t="n">
-        <v>100.000187</v>
+        <v>100.000222</v>
       </c>
       <c r="P256" s="6" t="n"/>
       <c r="Q256" s="6" t="n">
@@ -20888,7 +20888,7 @@
         <v>101.550311</v>
       </c>
       <c r="O257" s="9" t="n">
-        <v>99.614492</v>
+        <v>99.615005</v>
       </c>
       <c r="P257" s="9" t="n"/>
       <c r="Q257" s="9" t="n">
@@ -20970,7 +20970,7 @@
         <v>101.362216</v>
       </c>
       <c r="O258" s="6" t="n">
-        <v>99.225587</v>
+        <v>99.226553</v>
       </c>
       <c r="P258" s="6" t="n"/>
       <c r="Q258" s="6" t="n">
@@ -21052,7 +21052,7 @@
         <v>101.155111</v>
       </c>
       <c r="O259" s="9" t="n">
-        <v>98.890961</v>
+        <v>98.89233</v>
       </c>
       <c r="P259" s="9" t="n"/>
       <c r="Q259" s="9" t="n">
@@ -21134,7 +21134,7 @@
         <v>100.941924</v>
       </c>
       <c r="O260" s="6" t="n">
-        <v>98.626341</v>
+        <v>98.62803</v>
       </c>
       <c r="P260" s="6" t="n"/>
       <c r="Q260" s="6" t="n">
@@ -21216,7 +21216,7 @@
         <v>100.713381</v>
       </c>
       <c r="O261" s="9" t="n">
-        <v>98.435362</v>
+        <v>98.437274</v>
       </c>
       <c r="P261" s="9" t="n"/>
       <c r="Q261" s="9" t="n">
@@ -21298,7 +21298,7 @@
         <v>100.471632</v>
       </c>
       <c r="O262" s="6" t="n">
-        <v>98.348848</v>
+        <v>98.350855</v>
       </c>
       <c r="P262" s="6" t="n"/>
       <c r="Q262" s="6" t="n">
@@ -21380,7 +21380,7 @@
         <v>100.240478</v>
       </c>
       <c r="O263" s="9" t="n">
-        <v>98.328559</v>
+        <v>98.330592</v>
       </c>
       <c r="P263" s="9" t="n"/>
       <c r="Q263" s="9" t="n">
@@ -21462,7 +21462,7 @@
         <v>100.034526</v>
       </c>
       <c r="O264" s="6" t="n">
-        <v>98.366394</v>
+        <v>98.36838400000001</v>
       </c>
       <c r="P264" s="6" t="n"/>
       <c r="Q264" s="6" t="n">
@@ -21544,7 +21544,7 @@
         <v>99.86706700000001</v>
       </c>
       <c r="O265" s="9" t="n">
-        <v>98.42098</v>
+        <v>98.422907</v>
       </c>
       <c r="P265" s="9" t="n"/>
       <c r="Q265" s="9" t="n">
@@ -21626,7 +21626,7 @@
         <v>99.733389</v>
       </c>
       <c r="O266" s="6" t="n">
-        <v>98.467034</v>
+        <v>98.46892</v>
       </c>
       <c r="P266" s="6" t="n"/>
       <c r="Q266" s="6" t="n">
@@ -21708,7 +21708,7 @@
         <v>99.626424</v>
       </c>
       <c r="O267" s="9" t="n">
-        <v>98.554562</v>
+        <v>98.556331</v>
       </c>
       <c r="P267" s="9" t="n"/>
       <c r="Q267" s="9" t="n">
@@ -21790,7 +21790,7 @@
         <v>99.548011</v>
       </c>
       <c r="O268" s="6" t="n">
-        <v>98.693995</v>
+        <v>98.695598</v>
       </c>
       <c r="P268" s="6" t="n"/>
       <c r="Q268" s="6" t="n">
@@ -21872,7 +21872,7 @@
         <v>99.507159</v>
       </c>
       <c r="O269" s="9" t="n">
-        <v>98.90407399999999</v>
+        <v>98.90544</v>
       </c>
       <c r="P269" s="9" t="n"/>
       <c r="Q269" s="9" t="n">
@@ -21954,7 +21954,7 @@
         <v>99.50595800000001</v>
       </c>
       <c r="O270" s="6" t="n">
-        <v>99.156852</v>
+        <v>99.157911</v>
       </c>
       <c r="P270" s="6" t="n"/>
       <c r="Q270" s="6" t="n">
@@ -22036,7 +22036,7 @@
         <v>99.547132</v>
       </c>
       <c r="O271" s="9" t="n">
-        <v>99.415038</v>
+        <v>99.41578699999999</v>
       </c>
       <c r="P271" s="9" t="n"/>
       <c r="Q271" s="9" t="n">
@@ -22118,7 +22118,7 @@
         <v>99.599718</v>
       </c>
       <c r="O272" s="6" t="n">
-        <v>99.61366700000001</v>
+        <v>99.614178</v>
       </c>
       <c r="P272" s="6" t="n"/>
       <c r="Q272" s="6" t="n">
@@ -22200,7 +22200,7 @@
         <v>99.632903</v>
       </c>
       <c r="O273" s="9" t="n">
-        <v>99.693254</v>
+        <v>99.693658</v>
       </c>
       <c r="P273" s="9" t="n"/>
       <c r="Q273" s="9" t="n">
@@ -22282,7 +22282,7 @@
         <v>99.640725</v>
       </c>
       <c r="O274" s="6" t="n">
-        <v>99.658778</v>
+        <v>99.659221</v>
       </c>
       <c r="P274" s="6" t="n"/>
       <c r="Q274" s="6" t="n">
@@ -22364,7 +22364,7 @@
         <v>99.617377</v>
       </c>
       <c r="O275" s="9" t="n">
-        <v>99.51366</v>
+        <v>99.514285</v>
       </c>
       <c r="P275" s="9" t="n"/>
       <c r="Q275" s="9" t="n">
@@ -22446,7 +22446,7 @@
         <v>99.568095</v>
       </c>
       <c r="O276" s="6" t="n">
-        <v>99.328683</v>
+        <v>99.329511</v>
       </c>
       <c r="P276" s="6" t="n"/>
       <c r="Q276" s="6" t="n">
@@ -22528,7 +22528,7 @@
         <v>99.4956</v>
       </c>
       <c r="O277" s="9" t="n">
-        <v>99.16018800000001</v>
+        <v>99.161208</v>
       </c>
       <c r="P277" s="9" t="n"/>
       <c r="Q277" s="9" t="n">
@@ -22610,7 +22610,7 @@
         <v>99.405604</v>
       </c>
       <c r="O278" s="6" t="n">
-        <v>99.03583500000001</v>
+        <v>99.03699400000001</v>
       </c>
       <c r="P278" s="6" t="n"/>
       <c r="Q278" s="6" t="n">
@@ -22692,7 +22692,7 @@
         <v>99.304765</v>
       </c>
       <c r="O279" s="9" t="n">
-        <v>98.952285</v>
+        <v>98.953535</v>
       </c>
       <c r="P279" s="9" t="n"/>
       <c r="Q279" s="9" t="n">
@@ -22774,7 +22774,7 @@
         <v>99.2075</v>
       </c>
       <c r="O280" s="6" t="n">
-        <v>98.904871</v>
+        <v>98.906184</v>
       </c>
       <c r="P280" s="6" t="n"/>
       <c r="Q280" s="6" t="n">
@@ -22856,7 +22856,7 @@
         <v>99.119569</v>
       </c>
       <c r="O281" s="9" t="n">
-        <v>98.857575</v>
+        <v>98.858953</v>
       </c>
       <c r="P281" s="9" t="n"/>
       <c r="Q281" s="9" t="n">
@@ -22938,7 +22938,7 @@
         <v>99.041619</v>
       </c>
       <c r="O282" s="6" t="n">
-        <v>98.800386</v>
+        <v>98.801851</v>
       </c>
       <c r="P282" s="6" t="n"/>
       <c r="Q282" s="6" t="n">
@@ -23020,7 +23020,7 @@
         <v>98.96995800000001</v>
       </c>
       <c r="O283" s="9" t="n">
-        <v>98.756376</v>
+        <v>98.757936</v>
       </c>
       <c r="P283" s="9" t="n"/>
       <c r="Q283" s="9" t="n">
@@ -23102,7 +23102,7 @@
         <v>98.90468</v>
       </c>
       <c r="O284" s="6" t="n">
-        <v>98.731526</v>
+        <v>98.733155</v>
       </c>
       <c r="P284" s="6" t="n"/>
       <c r="Q284" s="6" t="n">
@@ -23184,7 +23184,7 @@
         <v>98.83648700000001</v>
       </c>
       <c r="O285" s="9" t="n">
-        <v>98.77581600000001</v>
+        <v>98.77739</v>
       </c>
       <c r="P285" s="9" t="n"/>
       <c r="Q285" s="9" t="n">
@@ -23266,7 +23266,7 @@
         <v>98.76652199999999</v>
       </c>
       <c r="O286" s="6" t="n">
-        <v>98.86663900000001</v>
+        <v>98.868092</v>
       </c>
       <c r="P286" s="6" t="n"/>
       <c r="Q286" s="6" t="n">
@@ -23348,7 +23348,7 @@
         <v>98.709718</v>
       </c>
       <c r="O287" s="9" t="n">
-        <v>99.039494</v>
+        <v>99.040721</v>
       </c>
       <c r="P287" s="9" t="n"/>
       <c r="Q287" s="9" t="n">
@@ -23430,7 +23430,7 @@
         <v>98.67411800000001</v>
       </c>
       <c r="O288" s="6" t="n">
-        <v>99.24391199999999</v>
+        <v>99.244872</v>
       </c>
       <c r="P288" s="6" t="n"/>
       <c r="Q288" s="6" t="n">
@@ -23512,7 +23512,7 @@
         <v>98.66251800000001</v>
       </c>
       <c r="O289" s="9" t="n">
-        <v>99.45800699999999</v>
+        <v>99.458702</v>
       </c>
       <c r="P289" s="9" t="n"/>
       <c r="Q289" s="9" t="n">
@@ -23594,7 +23594,7 @@
         <v>98.685772</v>
       </c>
       <c r="O290" s="6" t="n">
-        <v>99.697919</v>
+        <v>99.69829799999999</v>
       </c>
       <c r="P290" s="6" t="n"/>
       <c r="Q290" s="6" t="n">
@@ -23676,7 +23676,7 @@
         <v>98.74519100000001</v>
       </c>
       <c r="O291" s="9" t="n">
-        <v>99.95479</v>
+        <v>99.954849</v>
       </c>
       <c r="P291" s="9" t="n"/>
       <c r="Q291" s="9" t="n">
@@ -23758,7 +23758,7 @@
         <v>98.83146000000001</v>
       </c>
       <c r="O292" s="6" t="n">
-        <v>100.185889</v>
+        <v>100.185682</v>
       </c>
       <c r="P292" s="6" t="n"/>
       <c r="Q292" s="6" t="n">
@@ -23840,7 +23840,7 @@
         <v>98.934561</v>
       </c>
       <c r="O293" s="9" t="n">
-        <v>100.399319</v>
+        <v>100.398835</v>
       </c>
       <c r="P293" s="9" t="n"/>
       <c r="Q293" s="9" t="n">
@@ -23922,7 +23922,7 @@
         <v>99.04898300000001</v>
       </c>
       <c r="O294" s="6" t="n">
-        <v>100.593126</v>
+        <v>100.592393</v>
       </c>
       <c r="P294" s="6" t="n">
         <v>98.536314</v>
@@ -24006,7 +24006,7 @@
         <v>99.17849699999999</v>
       </c>
       <c r="O295" s="9" t="n">
-        <v>100.782798</v>
+        <v>100.781812</v>
       </c>
       <c r="P295" s="9" t="n">
         <v>98.69995299999999</v>
@@ -24090,7 +24090,7 @@
         <v>99.30637400000001</v>
       </c>
       <c r="O296" s="6" t="n">
-        <v>100.962147</v>
+        <v>100.960914</v>
       </c>
       <c r="P296" s="6" t="n">
         <v>98.873496</v>
@@ -24174,7 +24174,7 @@
         <v>99.42188299999999</v>
       </c>
       <c r="O297" s="9" t="n">
-        <v>101.09328</v>
+        <v>101.091886</v>
       </c>
       <c r="P297" s="9" t="n">
         <v>99.065544</v>
@@ -24258,7 +24258,7 @@
         <v>99.517658</v>
       </c>
       <c r="O298" s="6" t="n">
-        <v>101.134342</v>
+        <v>101.132925</v>
       </c>
       <c r="P298" s="6" t="n">
         <v>99.245644</v>
@@ -24342,7 +24342,7 @@
         <v>99.581422</v>
       </c>
       <c r="O299" s="9" t="n">
-        <v>101.083115</v>
+        <v>101.081769</v>
       </c>
       <c r="P299" s="9" t="n">
         <v>99.38448200000001</v>
@@ -24426,7 +24426,7 @@
         <v>99.62473799999999</v>
       </c>
       <c r="O300" s="6" t="n">
-        <v>100.977641</v>
+        <v>100.976439</v>
       </c>
       <c r="P300" s="6" t="n">
         <v>99.48344899999999</v>
@@ -24510,7 +24510,7 @@
         <v>99.657937</v>
       </c>
       <c r="O301" s="9" t="n">
-        <v>100.846366</v>
+        <v>100.845339</v>
       </c>
       <c r="P301" s="9" t="n">
         <v>99.550466</v>
@@ -24594,7 +24594,7 @@
         <v>99.69403200000001</v>
       </c>
       <c r="O302" s="6" t="n">
-        <v>100.711857</v>
+        <v>100.711</v>
       </c>
       <c r="P302" s="6" t="n">
         <v>99.604377</v>
@@ -24678,7 +24678,7 @@
         <v>99.744525</v>
       </c>
       <c r="O303" s="9" t="n">
-        <v>100.573441</v>
+        <v>100.572751</v>
       </c>
       <c r="P303" s="9" t="n">
         <v>99.661912</v>
@@ -24762,7 +24762,7 @@
         <v>99.794731</v>
       </c>
       <c r="O304" s="6" t="n">
-        <v>100.483985</v>
+        <v>100.483379</v>
       </c>
       <c r="P304" s="6" t="n">
         <v>99.721756</v>
@@ -24846,7 +24846,7 @@
         <v>99.82226900000001</v>
       </c>
       <c r="O305" s="9" t="n">
-        <v>100.431373</v>
+        <v>100.430824</v>
       </c>
       <c r="P305" s="9" t="n">
         <v>99.779448</v>
@@ -24930,7 +24930,7 @@
         <v>99.830072</v>
       </c>
       <c r="O306" s="6" t="n">
-        <v>100.383643</v>
+        <v>100.383167</v>
       </c>
       <c r="P306" s="6" t="n">
         <v>99.838756</v>
@@ -25014,7 +25014,7 @@
         <v>99.818237</v>
       </c>
       <c r="O307" s="9" t="n">
-        <v>100.251411</v>
+        <v>100.251087</v>
       </c>
       <c r="P307" s="9" t="n">
         <v>99.90722100000001</v>
@@ -25098,7 +25098,7 @@
         <v>99.797618</v>
       </c>
       <c r="O308" s="6" t="n">
-        <v>100.070944</v>
+        <v>100.07084</v>
       </c>
       <c r="P308" s="6" t="n">
         <v>99.98192899999999</v>
@@ -25182,7 +25182,7 @@
         <v>99.78245099999999</v>
       </c>
       <c r="O309" s="9" t="n">
-        <v>99.876531</v>
+        <v>99.876687</v>
       </c>
       <c r="P309" s="9" t="n">
         <v>100.054185</v>
@@ -25266,7 +25266,7 @@
         <v>99.778835</v>
       </c>
       <c r="O310" s="6" t="n">
-        <v>99.72992000000001</v>
+        <v>99.730268</v>
       </c>
       <c r="P310" s="6" t="n">
         <v>100.112691</v>
@@ -25350,7 +25350,7 @@
         <v>99.800089</v>
       </c>
       <c r="O311" s="9" t="n">
-        <v>99.671594</v>
+        <v>99.672015</v>
       </c>
       <c r="P311" s="9" t="n">
         <v>100.157686</v>
@@ -25434,7 +25434,7 @@
         <v>99.84898699999999</v>
       </c>
       <c r="O312" s="6" t="n">
-        <v>99.719598</v>
+        <v>99.71995699999999</v>
       </c>
       <c r="P312" s="6" t="n">
         <v>100.183987</v>
@@ -25518,7 +25518,7 @@
         <v>99.931945</v>
       </c>
       <c r="O313" s="9" t="n">
-        <v>99.86323</v>
+        <v>99.863394</v>
       </c>
       <c r="P313" s="9" t="n">
         <v>100.203832</v>
@@ -25602,7 +25602,7 @@
         <v>100.052675</v>
       </c>
       <c r="O314" s="6" t="n">
-        <v>100.026447</v>
+        <v>100.026412</v>
       </c>
       <c r="P314" s="6" t="n">
         <v>100.234257</v>
@@ -25686,7 +25686,7 @@
         <v>100.205912</v>
       </c>
       <c r="O315" s="9" t="n">
-        <v>100.20532</v>
+        <v>100.205086</v>
       </c>
       <c r="P315" s="9" t="n">
         <v>100.274284</v>
@@ -25770,7 +25770,7 @@
         <v>100.363537</v>
       </c>
       <c r="O316" s="6" t="n">
-        <v>100.353575</v>
+        <v>100.353158</v>
       </c>
       <c r="P316" s="6" t="n">
         <v>100.320411</v>
@@ -25854,7 +25854,7 @@
         <v>100.498237</v>
       </c>
       <c r="O317" s="9" t="n">
-        <v>100.459646</v>
+        <v>100.459098</v>
       </c>
       <c r="P317" s="9" t="n">
         <v>100.382964</v>
@@ -25938,7 +25938,7 @@
         <v>100.595855</v>
       </c>
       <c r="O318" s="6" t="n">
-        <v>100.550188</v>
+        <v>100.549525</v>
       </c>
       <c r="P318" s="6" t="n">
         <v>100.466043</v>
@@ -26022,7 +26022,7 @@
         <v>100.66973</v>
       </c>
       <c r="O319" s="9" t="n">
-        <v>100.673678</v>
+        <v>100.672854</v>
       </c>
       <c r="P319" s="9" t="n">
         <v>100.576808</v>
@@ -26106,7 +26106,7 @@
         <v>100.726671</v>
       </c>
       <c r="O320" s="6" t="n">
-        <v>100.831421</v>
+        <v>100.830395</v>
       </c>
       <c r="P320" s="6" t="n">
         <v>100.68257</v>
@@ -26190,7 +26190,7 @@
         <v>100.767885</v>
       </c>
       <c r="O321" s="9" t="n">
-        <v>101.004165</v>
+        <v>101.002921</v>
       </c>
       <c r="P321" s="9" t="n">
         <v>100.777022</v>
@@ -26274,7 +26274,7 @@
         <v>100.790309</v>
       </c>
       <c r="O322" s="6" t="n">
-        <v>101.169937</v>
+        <v>101.16847</v>
       </c>
       <c r="P322" s="6" t="n">
         <v>100.866076</v>
@@ -26358,7 +26358,7 @@
         <v>100.79069</v>
       </c>
       <c r="O323" s="9" t="n">
-        <v>101.250011</v>
+        <v>101.248448</v>
       </c>
       <c r="P323" s="9" t="n">
         <v>100.954439</v>
@@ -26442,7 +26442,7 @@
         <v>100.777144</v>
       </c>
       <c r="O324" s="6" t="n">
-        <v>101.203612</v>
+        <v>101.202129</v>
       </c>
       <c r="P324" s="6" t="n">
         <v>101.060017</v>
@@ -26526,7 +26526,7 @@
         <v>100.756076</v>
       </c>
       <c r="O325" s="9" t="n">
-        <v>101.069745</v>
+        <v>101.068439</v>
       </c>
       <c r="P325" s="9" t="n">
         <v>101.183334</v>
@@ -26610,7 +26610,7 @@
         <v>100.726864</v>
       </c>
       <c r="O326" s="6" t="n">
-        <v>100.897384</v>
+        <v>100.896307</v>
       </c>
       <c r="P326" s="6" t="n">
         <v>101.296754</v>
@@ -26694,7 +26694,7 @@
         <v>100.688176</v>
       </c>
       <c r="O327" s="9" t="n">
-        <v>100.727294</v>
+        <v>100.726436</v>
       </c>
       <c r="P327" s="9" t="n">
         <v>101.394739</v>
@@ -26778,7 +26778,7 @@
         <v>100.651309</v>
       </c>
       <c r="O328" s="6" t="n">
-        <v>100.575573</v>
+        <v>100.574905</v>
       </c>
       <c r="P328" s="6" t="n">
         <v>101.496553</v>
@@ -26862,7 +26862,7 @@
         <v>100.63399</v>
       </c>
       <c r="O329" s="9" t="n">
-        <v>100.469269</v>
+        <v>100.468732</v>
       </c>
       <c r="P329" s="9" t="n">
         <v>101.607496</v>
@@ -26946,7 +26946,7 @@
         <v>100.640534</v>
       </c>
       <c r="O330" s="6" t="n">
-        <v>100.437394</v>
+        <v>100.436874</v>
       </c>
       <c r="P330" s="6" t="n">
         <v>101.722044</v>
@@ -27030,7 +27030,7 @@
         <v>100.675856</v>
       </c>
       <c r="O331" s="9" t="n">
-        <v>100.486409</v>
+        <v>100.485819</v>
       </c>
       <c r="P331" s="9" t="n">
         <v>101.819967</v>
@@ -27114,7 +27114,7 @@
         <v>100.735903</v>
       </c>
       <c r="O332" s="6" t="n">
-        <v>100.557355</v>
+        <v>100.556668</v>
       </c>
       <c r="P332" s="6" t="n">
         <v>101.889934</v>
@@ -27198,7 +27198,7 @@
         <v>100.813787</v>
       </c>
       <c r="O333" s="9" t="n">
-        <v>100.625063</v>
+        <v>100.624279</v>
       </c>
       <c r="P333" s="9" t="n">
         <v>101.930893</v>
@@ -27282,7 +27282,7 @@
         <v>100.894728</v>
       </c>
       <c r="O334" s="6" t="n">
-        <v>100.664964</v>
+        <v>100.664121</v>
       </c>
       <c r="P334" s="6" t="n">
         <v>101.951296</v>
@@ -27366,7 +27366,7 @@
         <v>100.963076</v>
       </c>
       <c r="O335" s="9" t="n">
-        <v>100.726715</v>
+        <v>100.725804</v>
       </c>
       <c r="P335" s="9" t="n">
         <v>101.979804</v>
@@ -27450,7 +27450,7 @@
         <v>101.01511</v>
       </c>
       <c r="O336" s="6" t="n">
-        <v>100.830734</v>
+        <v>100.829693</v>
       </c>
       <c r="P336" s="6" t="n">
         <v>102.025564</v>
@@ -27534,7 +27534,7 @@
         <v>101.068919</v>
       </c>
       <c r="O337" s="9" t="n">
-        <v>100.938252</v>
+        <v>100.937077</v>
       </c>
       <c r="P337" s="9" t="n">
         <v>102.079357</v>
@@ -27618,7 +27618,7 @@
         <v>101.126517</v>
       </c>
       <c r="O338" s="6" t="n">
-        <v>101.025242</v>
+        <v>101.023968</v>
       </c>
       <c r="P338" s="6" t="n">
         <v>102.124311</v>
@@ -27702,7 +27702,7 @@
         <v>101.190783</v>
       </c>
       <c r="O339" s="9" t="n">
-        <v>101.022981</v>
+        <v>101.021686</v>
       </c>
       <c r="P339" s="9" t="n">
         <v>102.132406</v>
@@ -27786,7 +27786,7 @@
         <v>101.275297</v>
       </c>
       <c r="O340" s="6" t="n">
-        <v>100.962321</v>
+        <v>100.961097</v>
       </c>
       <c r="P340" s="6" t="n">
         <v>102.060746</v>
@@ -27870,7 +27870,7 @@
         <v>101.387716</v>
       </c>
       <c r="O341" s="9" t="n">
-        <v>100.864235</v>
+        <v>100.863154</v>
       </c>
       <c r="P341" s="9" t="n">
         <v>101.873394</v>
@@ -27954,7 +27954,7 @@
         <v>101.523463</v>
       </c>
       <c r="O342" s="6" t="n">
-        <v>100.707986</v>
+        <v>100.707109</v>
       </c>
       <c r="P342" s="6" t="n">
         <v>101.590329</v>
@@ -28038,7 +28038,7 @@
         <v>101.663543</v>
       </c>
       <c r="O343" s="9" t="n">
-        <v>100.478227</v>
+        <v>100.477666</v>
       </c>
       <c r="P343" s="9" t="n">
         <v>101.246674</v>
@@ -28122,7 +28122,7 @@
         <v>101.795039</v>
       </c>
       <c r="O344" s="6" t="n">
-        <v>100.20346</v>
+        <v>100.203274</v>
       </c>
       <c r="P344" s="6" t="n">
         <v>100.886384</v>
@@ -28206,7 +28206,7 @@
         <v>101.904424</v>
       </c>
       <c r="O345" s="9" t="n">
-        <v>99.88559100000001</v>
+        <v>99.885807</v>
       </c>
       <c r="P345" s="9" t="n">
         <v>100.532826</v>
@@ -28290,7 +28290,7 @@
         <v>101.966805</v>
       </c>
       <c r="O346" s="6" t="n">
-        <v>99.541909</v>
+        <v>99.542552</v>
       </c>
       <c r="P346" s="6" t="n">
         <v>100.187652</v>
@@ -28374,7 +28374,7 @@
         <v>101.957807</v>
       </c>
       <c r="O347" s="9" t="n">
-        <v>99.154095</v>
+        <v>99.155209</v>
       </c>
       <c r="P347" s="9" t="n">
         <v>99.797861</v>
@@ -28458,7 +28458,7 @@
         <v>101.836125</v>
       </c>
       <c r="O348" s="6" t="n">
-        <v>98.72523099999999</v>
+        <v>98.72685</v>
       </c>
       <c r="P348" s="6" t="n">
         <v>99.303201</v>
@@ -28542,7 +28542,7 @@
         <v>101.542324</v>
       </c>
       <c r="O349" s="9" t="n">
-        <v>98.233794</v>
+        <v>98.23600399999999</v>
       </c>
       <c r="P349" s="9" t="n">
         <v>98.671228</v>
@@ -28626,7 +28626,7 @@
         <v>101.051415</v>
       </c>
       <c r="O350" s="6" t="n">
-        <v>97.709093</v>
+        <v>97.71191899999999</v>
       </c>
       <c r="P350" s="6" t="n">
         <v>97.901875</v>
@@ -28710,7 +28710,7 @@
         <v>100.379316</v>
       </c>
       <c r="O351" s="9" t="n">
-        <v>97.21190300000001</v>
+        <v>97.21533700000001</v>
       </c>
       <c r="P351" s="9" t="n">
         <v>97.072532</v>
@@ -28794,7 +28794,7 @@
         <v>99.567076</v>
       </c>
       <c r="O352" s="6" t="n">
-        <v>96.808053</v>
+        <v>96.81200200000001</v>
       </c>
       <c r="P352" s="6" t="n">
         <v>96.29892</v>
@@ -28878,7 +28878,7 @@
         <v>98.699679</v>
       </c>
       <c r="O353" s="9" t="n">
-        <v>96.50884600000001</v>
+        <v>96.513154</v>
       </c>
       <c r="P353" s="9" t="n">
         <v>95.68318600000001</v>
@@ -28962,7 +28962,7 @@
         <v>97.914196</v>
       </c>
       <c r="O354" s="6" t="n">
-        <v>96.27739</v>
+        <v>96.281989</v>
       </c>
       <c r="P354" s="6" t="n">
         <v>95.30486399999999</v>
@@ -29046,7 +29046,7 @@
         <v>97.286761</v>
       </c>
       <c r="O355" s="9" t="n">
-        <v>96.14963299999999</v>
+        <v>96.154399</v>
       </c>
       <c r="P355" s="9" t="n">
         <v>95.16922599999999</v>
@@ -29130,7 +29130,7 @@
         <v>96.848017</v>
       </c>
       <c r="O356" s="6" t="n">
-        <v>96.15516</v>
+        <v>96.159921</v>
       </c>
       <c r="P356" s="6" t="n">
         <v>95.258537</v>
@@ -29214,7 +29214,7 @@
         <v>96.61138200000001</v>
       </c>
       <c r="O357" s="9" t="n">
-        <v>96.35382199999999</v>
+        <v>96.358328</v>
       </c>
       <c r="P357" s="9" t="n">
         <v>95.48564</v>
@@ -29298,7 +29298,7 @@
         <v>96.574217</v>
       </c>
       <c r="O358" s="6" t="n">
-        <v>96.743914</v>
+        <v>96.74793200000001</v>
       </c>
       <c r="P358" s="6" t="n">
         <v>95.772683</v>
@@ -29382,7 +29382,7 @@
         <v>96.71358600000001</v>
       </c>
       <c r="O359" s="9" t="n">
-        <v>97.298091</v>
+        <v>97.301406</v>
       </c>
       <c r="P359" s="9" t="n">
         <v>96.08196100000001</v>
@@ -29466,7 +29466,7 @@
         <v>96.969452</v>
       </c>
       <c r="O360" s="6" t="n">
-        <v>97.952263</v>
+        <v>97.95477099999999</v>
       </c>
       <c r="P360" s="6" t="n">
         <v>96.38672800000001</v>
@@ -29550,7 +29550,7 @@
         <v>97.294439</v>
       </c>
       <c r="O361" s="9" t="n">
-        <v>98.65101900000001</v>
+        <v>98.652686</v>
       </c>
       <c r="P361" s="9" t="n">
         <v>96.686184</v>
@@ -29634,7 +29634,7 @@
         <v>97.64972899999999</v>
       </c>
       <c r="O362" s="6" t="n">
-        <v>99.32866199999999</v>
+        <v>99.329498</v>
       </c>
       <c r="P362" s="6" t="n">
         <v>96.994731</v>
@@ -29718,7 +29718,7 @@
         <v>98.006354</v>
       </c>
       <c r="O363" s="9" t="n">
-        <v>99.96365299999999</v>
+        <v>99.963708</v>
       </c>
       <c r="P363" s="9" t="n">
         <v>97.300673</v>
@@ -29802,7 +29802,7 @@
         <v>98.349371</v>
       </c>
       <c r="O364" s="6" t="n">
-        <v>100.460083</v>
+        <v>100.459522</v>
       </c>
       <c r="P364" s="6" t="n">
         <v>97.60715</v>
@@ -29886,7 +29886,7 @@
         <v>98.64978000000001</v>
       </c>
       <c r="O365" s="9" t="n">
-        <v>100.819533</v>
+        <v>100.818514</v>
       </c>
       <c r="P365" s="9" t="n">
         <v>97.94927</v>
@@ -29970,7 +29970,7 @@
         <v>98.909622</v>
       </c>
       <c r="O366" s="6" t="n">
-        <v>101.100972</v>
+        <v>101.099589</v>
       </c>
       <c r="P366" s="6" t="n">
         <v>98.351921</v>
@@ -30054,7 +30054,7 @@
         <v>99.13820200000001</v>
       </c>
       <c r="O367" s="9" t="n">
-        <v>101.309975</v>
+        <v>101.308297</v>
       </c>
       <c r="P367" s="9" t="n">
         <v>98.836896</v>
@@ -30138,7 +30138,7 @@
         <v>99.329008</v>
       </c>
       <c r="O368" s="6" t="n">
-        <v>101.469832</v>
+        <v>101.467926</v>
       </c>
       <c r="P368" s="6" t="n">
         <v>99.363438</v>
@@ -30222,7 +30222,7 @@
         <v>99.46657399999999</v>
       </c>
       <c r="O369" s="9" t="n">
-        <v>101.565326</v>
+        <v>101.563309</v>
       </c>
       <c r="P369" s="9" t="n">
         <v>99.87252599999999</v>
@@ -30306,7 +30306,7 @@
         <v>99.549446</v>
       </c>
       <c r="O370" s="6" t="n">
-        <v>101.586304</v>
+        <v>101.584287</v>
       </c>
       <c r="P370" s="6" t="n">
         <v>100.320785</v>
@@ -30390,7 +30390,7 @@
         <v>99.59773800000001</v>
       </c>
       <c r="O371" s="9" t="n">
-        <v>101.538949</v>
+        <v>101.537002</v>
       </c>
       <c r="P371" s="9" t="n">
         <v>100.685873</v>
@@ -30474,7 +30474,7 @@
         <v>99.649765</v>
       </c>
       <c r="O372" s="6" t="n">
-        <v>101.447629</v>
+        <v>101.445804</v>
       </c>
       <c r="P372" s="6" t="n">
         <v>100.967715</v>
@@ -30558,7 +30558,7 @@
         <v>99.724464</v>
       </c>
       <c r="O373" s="9" t="n">
-        <v>101.332992</v>
+        <v>101.33131</v>
       </c>
       <c r="P373" s="9" t="n">
         <v>101.181109</v>
@@ -30642,7 +30642,7 @@
         <v>99.822796</v>
       </c>
       <c r="O374" s="6" t="n">
-        <v>101.210698</v>
+        <v>101.209165</v>
       </c>
       <c r="P374" s="6" t="n">
         <v>101.33781</v>
@@ -30726,7 +30726,7 @@
         <v>99.947025</v>
       </c>
       <c r="O375" s="9" t="n">
-        <v>101.051229</v>
+        <v>101.049888</v>
       </c>
       <c r="P375" s="9" t="n">
         <v>101.453186</v>
@@ -30810,7 +30810,7 @@
         <v>100.082285</v>
       </c>
       <c r="O376" s="6" t="n">
-        <v>100.902368</v>
+        <v>100.901185</v>
       </c>
       <c r="P376" s="6" t="n">
         <v>101.533877</v>
@@ -30894,7 +30894,7 @@
         <v>100.218999</v>
       </c>
       <c r="O377" s="9" t="n">
-        <v>100.800654</v>
+        <v>100.799588</v>
       </c>
       <c r="P377" s="9" t="n">
         <v>101.579847</v>
@@ -30978,7 +30978,7 @@
         <v>100.346661</v>
       </c>
       <c r="O378" s="6" t="n">
-        <v>100.754268</v>
+        <v>100.753267</v>
       </c>
       <c r="P378" s="6" t="n">
         <v>101.595816</v>
@@ -31062,7 +31062,7 @@
         <v>100.458514</v>
       </c>
       <c r="O379" s="9" t="n">
-        <v>100.764424</v>
+        <v>100.763402</v>
       </c>
       <c r="P379" s="9" t="n">
         <v>101.589565</v>
@@ -31146,7 +31146,7 @@
         <v>100.55405</v>
       </c>
       <c r="O380" s="6" t="n">
-        <v>100.808062</v>
+        <v>100.806973</v>
       </c>
       <c r="P380" s="6" t="n">
         <v>101.564479</v>
@@ -31230,7 +31230,7 @@
         <v>100.63803</v>
       </c>
       <c r="O381" s="9" t="n">
-        <v>100.864915</v>
+        <v>100.863752</v>
       </c>
       <c r="P381" s="9" t="n">
         <v>101.521606</v>
@@ -31314,7 +31314,7 @@
         <v>100.712082</v>
       </c>
       <c r="O382" s="6" t="n">
-        <v>100.915419</v>
+        <v>100.914184</v>
       </c>
       <c r="P382" s="6" t="n">
         <v>101.457888</v>
@@ -31398,7 +31398,7 @@
         <v>100.75947</v>
       </c>
       <c r="O383" s="9" t="n">
-        <v>100.956983</v>
+        <v>100.955688</v>
       </c>
       <c r="P383" s="9" t="n">
         <v>101.36094</v>
@@ -31482,7 +31482,7 @@
         <v>100.769444</v>
       </c>
       <c r="O384" s="6" t="n">
-        <v>100.984146</v>
+        <v>100.982817</v>
       </c>
       <c r="P384" s="6" t="n">
         <v>101.227638</v>
@@ -31566,7 +31566,7 @@
         <v>100.753206</v>
       </c>
       <c r="O385" s="9" t="n">
-        <v>101.021215</v>
+        <v>101.019819</v>
       </c>
       <c r="P385" s="9" t="n">
         <v>101.061655</v>
@@ -31650,7 +31650,7 @@
         <v>100.730717</v>
       </c>
       <c r="O386" s="6" t="n">
-        <v>101.075927</v>
+        <v>101.074465</v>
       </c>
       <c r="P386" s="6" t="n">
         <v>100.895736</v>
@@ -31734,7 +31734,7 @@
         <v>100.706738</v>
       </c>
       <c r="O387" s="9" t="n">
-        <v>101.167702</v>
+        <v>101.16615</v>
       </c>
       <c r="P387" s="9" t="n">
         <v>100.746127</v>
@@ -31818,7 +31818,7 @@
         <v>100.695379</v>
       </c>
       <c r="O388" s="6" t="n">
-        <v>101.29389</v>
+        <v>101.292182</v>
       </c>
       <c r="P388" s="6" t="n">
         <v>100.624368</v>
@@ -31902,7 +31902,7 @@
         <v>100.695622</v>
       </c>
       <c r="O389" s="9" t="n">
-        <v>101.412279</v>
+        <v>101.410419</v>
       </c>
       <c r="P389" s="9" t="n">
         <v>100.533795</v>
@@ -31986,7 +31986,7 @@
         <v>100.697007</v>
       </c>
       <c r="O390" s="6" t="n">
-        <v>101.530935</v>
+        <v>101.528913</v>
       </c>
       <c r="P390" s="6" t="n">
         <v>100.472404</v>
@@ -32070,7 +32070,7 @@
         <v>100.68705</v>
       </c>
       <c r="O391" s="9" t="n">
-        <v>101.59783</v>
+        <v>101.59571</v>
       </c>
       <c r="P391" s="9" t="n">
         <v>100.408679</v>
@@ -32154,7 +32154,7 @@
         <v>100.654299</v>
       </c>
       <c r="O392" s="6" t="n">
-        <v>101.558208</v>
+        <v>101.556125</v>
       </c>
       <c r="P392" s="6" t="n">
         <v>100.324608</v>
@@ -32238,7 +32238,7 @@
         <v>100.605926</v>
       </c>
       <c r="O393" s="9" t="n">
-        <v>101.422647</v>
+        <v>101.420716</v>
       </c>
       <c r="P393" s="9" t="n">
         <v>100.2306</v>
@@ -32322,7 +32322,7 @@
         <v>100.537653</v>
       </c>
       <c r="O394" s="6" t="n">
-        <v>101.26896</v>
+        <v>101.267194</v>
       </c>
       <c r="P394" s="6" t="n">
         <v>100.149665</v>
@@ -32406,7 +32406,7 @@
         <v>100.464907</v>
       </c>
       <c r="O395" s="9" t="n">
-        <v>101.120029</v>
+        <v>101.118442</v>
       </c>
       <c r="P395" s="9" t="n">
         <v>100.106215</v>
@@ -32490,7 +32490,7 @@
         <v>100.415927</v>
       </c>
       <c r="O396" s="6" t="n">
-        <v>100.958158</v>
+        <v>100.956772</v>
       </c>
       <c r="P396" s="6" t="n">
         <v>100.11601</v>
@@ -32574,7 +32574,7 @@
         <v>100.397993</v>
       </c>
       <c r="O397" s="9" t="n">
-        <v>100.795446</v>
+        <v>100.794263</v>
       </c>
       <c r="P397" s="9" t="n">
         <v>100.179137</v>
@@ -32658,7 +32658,7 @@
         <v>100.414017</v>
       </c>
       <c r="O398" s="6" t="n">
-        <v>100.665807</v>
+        <v>100.664795</v>
       </c>
       <c r="P398" s="6" t="n">
         <v>100.280395</v>
@@ -32742,7 +32742,7 @@
         <v>100.449321</v>
       </c>
       <c r="O399" s="9" t="n">
-        <v>100.591797</v>
+        <v>100.590856</v>
       </c>
       <c r="P399" s="9" t="n">
         <v>100.40825</v>
@@ -32826,7 +32826,7 @@
         <v>100.479223</v>
       </c>
       <c r="O400" s="6" t="n">
-        <v>100.536814</v>
+        <v>100.53594</v>
       </c>
       <c r="P400" s="6" t="n">
         <v>100.548273</v>
@@ -32910,7 +32910,7 @@
         <v>100.501792</v>
       </c>
       <c r="O401" s="9" t="n">
-        <v>100.474474</v>
+        <v>100.473692</v>
       </c>
       <c r="P401" s="9" t="n">
         <v>100.694777</v>
@@ -32994,7 +32994,7 @@
         <v>100.519201</v>
       </c>
       <c r="O402" s="6" t="n">
-        <v>100.314802</v>
+        <v>100.31421</v>
       </c>
       <c r="P402" s="6" t="n">
         <v>100.845915</v>
@@ -33078,7 +33078,7 @@
         <v>100.518529</v>
       </c>
       <c r="O403" s="9" t="n">
-        <v>100.059657</v>
+        <v>100.059382</v>
       </c>
       <c r="P403" s="9" t="n">
         <v>100.978925</v>
@@ -33162,7 +33162,7 @@
         <v>100.49299</v>
       </c>
       <c r="O404" s="6" t="n">
-        <v>99.78119700000001</v>
+        <v>99.781265</v>
       </c>
       <c r="P404" s="6" t="n">
         <v>101.071487</v>
@@ -33246,7 +33246,7 @@
         <v>100.441688</v>
       </c>
       <c r="O405" s="9" t="n">
-        <v>99.52534199999999</v>
+        <v>99.525713</v>
       </c>
       <c r="P405" s="9" t="n">
         <v>101.117273</v>
@@ -33330,7 +33330,7 @@
         <v>100.370978</v>
       </c>
       <c r="O406" s="6" t="n">
-        <v>99.291399</v>
+        <v>99.29205</v>
       </c>
       <c r="P406" s="6" t="n">
         <v>101.109004</v>
@@ -33414,7 +33414,7 @@
         <v>100.294936</v>
       </c>
       <c r="O407" s="9" t="n">
-        <v>99.077575</v>
+        <v>99.078492</v>
       </c>
       <c r="P407" s="9" t="n">
         <v>101.039053</v>
@@ -33498,7 +33498,7 @@
         <v>100.216912</v>
       </c>
       <c r="O408" s="6" t="n">
-        <v>98.924522</v>
+        <v>98.925603</v>
       </c>
       <c r="P408" s="6" t="n">
         <v>100.916336</v>
@@ -33582,7 +33582,7 @@
         <v>100.138756</v>
       </c>
       <c r="O409" s="9" t="n">
-        <v>98.832689</v>
+        <v>98.83386400000001</v>
       </c>
       <c r="P409" s="9" t="n">
         <v>100.750172</v>
@@ -33666,7 +33666,7 @@
         <v>100.072091</v>
       </c>
       <c r="O410" s="6" t="n">
-        <v>98.801393</v>
+        <v>98.802589</v>
       </c>
       <c r="P410" s="6" t="n">
         <v>100.562709</v>
@@ -33750,7 +33750,7 @@
         <v>100.029666</v>
       </c>
       <c r="O411" s="9" t="n">
-        <v>98.810033</v>
+        <v>98.811201</v>
       </c>
       <c r="P411" s="9" t="n">
         <v>100.385318</v>
@@ -33834,7 +33834,7 @@
         <v>100.019786</v>
       </c>
       <c r="O412" s="6" t="n">
-        <v>98.83141000000001</v>
+        <v>98.832548</v>
       </c>
       <c r="P412" s="6" t="n">
         <v>100.250938</v>
@@ -33918,7 +33918,7 @@
         <v>100.052249</v>
       </c>
       <c r="O413" s="9" t="n">
-        <v>98.801085</v>
+        <v>98.80226500000001</v>
       </c>
       <c r="P413" s="9" t="n">
         <v>100.169705</v>
@@ -34002,7 +34002,7 @@
         <v>100.123755</v>
       </c>
       <c r="O414" s="6" t="n">
-        <v>98.72745</v>
+        <v>98.72873300000001</v>
       </c>
       <c r="P414" s="6" t="n">
         <v>100.125374</v>
@@ -34086,7 +34086,7 @@
         <v>100.216677</v>
       </c>
       <c r="O415" s="9" t="n">
-        <v>98.686283</v>
+        <v>98.68765399999999</v>
       </c>
       <c r="P415" s="9" t="n">
         <v>100.123506</v>
@@ -34170,7 +34170,7 @@
         <v>100.310077</v>
       </c>
       <c r="O416" s="6" t="n">
-        <v>98.732029</v>
+        <v>98.733374</v>
       </c>
       <c r="P416" s="6" t="n">
         <v>100.148098</v>
@@ -34254,7 +34254,7 @@
         <v>100.389486</v>
       </c>
       <c r="O417" s="9" t="n">
-        <v>98.80222000000001</v>
+        <v>98.80347399999999</v>
       </c>
       <c r="P417" s="9" t="n">
         <v>100.192961</v>
@@ -34338,7 +34338,7 @@
         <v>100.444756</v>
       </c>
       <c r="O418" s="6" t="n">
-        <v>98.85823499999999</v>
+        <v>98.85941800000001</v>
       </c>
       <c r="P418" s="6" t="n">
         <v>100.258347</v>
@@ -34422,7 +34422,7 @@
         <v>100.471961</v>
       </c>
       <c r="O419" s="9" t="n">
-        <v>98.888727</v>
+        <v>98.889866</v>
       </c>
       <c r="P419" s="9" t="n">
         <v>100.3453</v>
@@ -34506,7 +34506,7 @@
         <v>100.474492</v>
       </c>
       <c r="O420" s="6" t="n">
-        <v>98.907864</v>
+        <v>98.908968</v>
       </c>
       <c r="P420" s="6" t="n">
         <v>100.437113</v>
@@ -34590,7 +34590,7 @@
         <v>100.459157</v>
       </c>
       <c r="O421" s="9" t="n">
-        <v>98.933187</v>
+        <v>98.93425499999999</v>
       </c>
       <c r="P421" s="9" t="n">
         <v>100.502282</v>
@@ -34674,7 +34674,7 @@
         <v>100.418398</v>
       </c>
       <c r="O422" s="6" t="n">
-        <v>98.946806</v>
+        <v>98.947836</v>
       </c>
       <c r="P422" s="6" t="n">
         <v>100.515265</v>
@@ -34758,7 +34758,7 @@
         <v>100.368032</v>
       </c>
       <c r="O423" s="9" t="n">
-        <v>98.93681100000001</v>
+        <v>98.93785200000001</v>
       </c>
       <c r="P423" s="9" t="n">
         <v>100.461482</v>
@@ -34842,7 +34842,7 @@
         <v>100.310085</v>
       </c>
       <c r="O424" s="6" t="n">
-        <v>98.92834999999999</v>
+        <v>98.929418</v>
       </c>
       <c r="P424" s="6" t="n">
         <v>100.335705</v>
@@ -34926,7 +34926,7 @@
         <v>100.232938</v>
       </c>
       <c r="O425" s="9" t="n">
-        <v>98.980548</v>
+        <v>98.98154599999999</v>
       </c>
       <c r="P425" s="9" t="n">
         <v>100.156682</v>
@@ -35010,7 +35010,7 @@
         <v>100.155544</v>
       </c>
       <c r="O426" s="6" t="n">
-        <v>99.114367</v>
+        <v>99.115207</v>
       </c>
       <c r="P426" s="6" t="n">
         <v>99.957003</v>
@@ -35094,7 +35094,7 @@
         <v>100.100401</v>
       </c>
       <c r="O427" s="9" t="n">
-        <v>99.278565</v>
+        <v>99.279213</v>
       </c>
       <c r="P427" s="9" t="n">
         <v>99.76344400000001</v>
@@ -35178,7 +35178,7 @@
         <v>100.077033</v>
       </c>
       <c r="O428" s="6" t="n">
-        <v>99.39837300000001</v>
+        <v>99.398883</v>
       </c>
       <c r="P428" s="6" t="n">
         <v>99.596346</v>
@@ -35262,7 +35262,7 @@
         <v>100.07313</v>
       </c>
       <c r="O429" s="9" t="n">
-        <v>99.515666</v>
+        <v>99.516049</v>
       </c>
       <c r="P429" s="9" t="n">
         <v>99.458945</v>
@@ -35346,7 +35346,7 @@
         <v>100.078951</v>
       </c>
       <c r="O430" s="6" t="n">
-        <v>99.64281800000001</v>
+        <v>99.643069</v>
       </c>
       <c r="P430" s="6" t="n">
         <v>99.35393500000001</v>
@@ -35430,7 +35430,7 @@
         <v>100.079464</v>
       </c>
       <c r="O431" s="9" t="n">
-        <v>99.794785</v>
+        <v>99.79485</v>
       </c>
       <c r="P431" s="9" t="n">
         <v>99.275858</v>
@@ -35514,7 +35514,7 @@
         <v>100.052077</v>
       </c>
       <c r="O432" s="6" t="n">
-        <v>99.968816</v>
+        <v>99.96868600000001</v>
       </c>
       <c r="P432" s="6" t="n">
         <v>99.220967</v>
@@ -35598,7 +35598,7 @@
         <v>99.990887</v>
       </c>
       <c r="O433" s="9" t="n">
-        <v>100.131164</v>
+        <v>100.13088</v>
       </c>
       <c r="P433" s="9" t="n">
         <v>99.193749</v>
@@ -35682,7 +35682,7 @@
         <v>99.88988000000001</v>
       </c>
       <c r="O434" s="6" t="n">
-        <v>100.261671</v>
+        <v>100.261252</v>
       </c>
       <c r="P434" s="6" t="n">
         <v>99.196096</v>
@@ -35766,7 +35766,7 @@
         <v>99.76402899999999</v>
       </c>
       <c r="O435" s="9" t="n">
-        <v>100.360237</v>
+        <v>100.359718</v>
       </c>
       <c r="P435" s="9" t="n">
         <v>99.223141</v>
@@ -35850,7 +35850,7 @@
         <v>99.62432</v>
       </c>
       <c r="O436" s="6" t="n">
-        <v>100.416296</v>
+        <v>100.415724</v>
       </c>
       <c r="P436" s="6" t="n">
         <v>99.251749</v>
@@ -35934,7 +35934,7 @@
         <v>99.486923</v>
       </c>
       <c r="O437" s="9" t="n">
-        <v>100.437097</v>
+        <v>100.436515</v>
       </c>
       <c r="P437" s="9" t="n">
         <v>99.270729</v>
@@ -36018,7 +36018,7 @@
         <v>99.37418700000001</v>
       </c>
       <c r="O438" s="6" t="n">
-        <v>100.430587</v>
+        <v>100.430038</v>
       </c>
       <c r="P438" s="6" t="n">
         <v>99.282495</v>
@@ -36102,7 +36102,7 @@
         <v>99.29082200000001</v>
       </c>
       <c r="O439" s="9" t="n">
-        <v>100.389244</v>
+        <v>100.388748</v>
       </c>
       <c r="P439" s="9" t="n">
         <v>99.29660199999999</v>
@@ -36186,7 +36186,7 @@
         <v>99.240371</v>
       </c>
       <c r="O440" s="6" t="n">
-        <v>100.323214</v>
+        <v>100.322816</v>
       </c>
       <c r="P440" s="6" t="n">
         <v>99.328655</v>
@@ -36270,7 +36270,7 @@
         <v>99.22458</v>
       </c>
       <c r="O441" s="9" t="n">
-        <v>100.275116</v>
+        <v>100.274831</v>
       </c>
       <c r="P441" s="9" t="n">
         <v>99.380957</v>
@@ -36354,7 +36354,7 @@
         <v>99.23282</v>
       </c>
       <c r="O442" s="6" t="n">
-        <v>100.245636</v>
+        <v>100.245444</v>
       </c>
       <c r="P442" s="6" t="n">
         <v>99.441519</v>
@@ -36438,7 +36438,7 @@
         <v>99.265654</v>
       </c>
       <c r="O443" s="9" t="n">
-        <v>100.246782</v>
+        <v>100.246641</v>
       </c>
       <c r="P443" s="9" t="n">
         <v>99.493708</v>
@@ -36522,7 +36522,7 @@
         <v>99.317403</v>
       </c>
       <c r="O444" s="6" t="n">
-        <v>100.255031</v>
+        <v>100.254928</v>
       </c>
       <c r="P444" s="6" t="n">
         <v>99.522723</v>
@@ -36606,7 +36606,7 @@
         <v>99.379154</v>
       </c>
       <c r="O445" s="9" t="n">
-        <v>100.268903</v>
+        <v>100.268812</v>
       </c>
       <c r="P445" s="9" t="n">
         <v>99.52922599999999</v>
@@ -36690,7 +36690,7 @@
         <v>99.448081</v>
       </c>
       <c r="O446" s="6" t="n">
-        <v>100.297792</v>
+        <v>100.297718</v>
       </c>
       <c r="P446" s="6" t="n">
         <v>99.510124</v>
@@ -36774,7 +36774,7 @@
         <v>99.515027</v>
       </c>
       <c r="O447" s="9" t="n">
-        <v>100.335496</v>
+        <v>100.335448</v>
       </c>
       <c r="P447" s="9" t="n">
         <v>99.45856499999999</v>
@@ -36858,7 +36858,7 @@
         <v>99.58543299999999</v>
       </c>
       <c r="O448" s="6" t="n">
-        <v>100.402995</v>
+        <v>100.402915</v>
       </c>
       <c r="P448" s="6" t="n">
         <v>99.38470599999999</v>
@@ -36942,7 +36942,7 @@
         <v>99.650679</v>
       </c>
       <c r="O449" s="9" t="n">
-        <v>100.485181</v>
+        <v>100.48506</v>
       </c>
       <c r="P449" s="9" t="n">
         <v>99.29907</v>
@@ -37026,7 +37026,7 @@
         <v>99.70380900000001</v>
       </c>
       <c r="O450" s="6" t="n">
-        <v>100.632379</v>
+        <v>100.63214</v>
       </c>
       <c r="P450" s="6" t="n">
         <v>99.22828800000001</v>
@@ -37110,7 +37110,7 @@
         <v>99.748104</v>
       </c>
       <c r="O451" s="9" t="n">
-        <v>100.8527</v>
+        <v>100.852252</v>
       </c>
       <c r="P451" s="9" t="n">
         <v>99.216216</v>
@@ -37194,7 +37194,7 @@
         <v>99.790616</v>
       </c>
       <c r="O452" s="6" t="n">
-        <v>101.08244</v>
+        <v>101.081772</v>
       </c>
       <c r="P452" s="6" t="n">
         <v>99.295901</v>
@@ -37278,7 +37278,7 @@
         <v>99.840459</v>
       </c>
       <c r="O453" s="9" t="n">
-        <v>101.239188</v>
+        <v>101.238397</v>
       </c>
       <c r="P453" s="9" t="n">
         <v>99.455246</v>
@@ -37362,7 +37362,7 @@
         <v>99.908192</v>
       </c>
       <c r="O454" s="6" t="n">
-        <v>101.305714</v>
+        <v>101.304899</v>
       </c>
       <c r="P454" s="6" t="n">
         <v>99.668685</v>
@@ -37446,7 +37446,7 @@
         <v>99.986108</v>
       </c>
       <c r="O455" s="9" t="n">
-        <v>101.225357</v>
+        <v>101.224725</v>
       </c>
       <c r="P455" s="9" t="n">
         <v>99.902114</v>
@@ -37530,7 +37530,7 @@
         <v>100.071859</v>
       </c>
       <c r="O456" s="6" t="n">
-        <v>101.005119</v>
+        <v>101.004863</v>
       </c>
       <c r="P456" s="6" t="n">
         <v>100.120949</v>
@@ -37614,7 +37614,7 @@
         <v>100.167662</v>
       </c>
       <c r="O457" s="9" t="n">
-        <v>100.701188</v>
+        <v>100.701399</v>
       </c>
       <c r="P457" s="9" t="n">
         <v>100.296408</v>
@@ -37698,7 +37698,7 @@
         <v>100.263737</v>
       </c>
       <c r="O458" s="6" t="n">
-        <v>100.391964</v>
+        <v>100.392656</v>
       </c>
       <c r="P458" s="6" t="n">
         <v>100.420634</v>
@@ -37782,7 +37782,7 @@
         <v>100.362334</v>
       </c>
       <c r="O459" s="9" t="n">
-        <v>100.136131</v>
+        <v>100.137233</v>
       </c>
       <c r="P459" s="9" t="n">
         <v>100.494749</v>
@@ -37866,7 +37866,7 @@
         <v>100.459892</v>
       </c>
       <c r="O460" s="6" t="n">
-        <v>99.96272999999999</v>
+        <v>99.96413800000001</v>
       </c>
       <c r="P460" s="6" t="n">
         <v>100.54919</v>
@@ -37950,7 +37950,7 @@
         <v>100.558842</v>
       </c>
       <c r="O461" s="9" t="n">
-        <v>99.898034</v>
+        <v>99.899615</v>
       </c>
       <c r="P461" s="9" t="n">
         <v>100.612085</v>
@@ -38034,7 +38034,7 @@
         <v>100.646552</v>
       </c>
       <c r="O462" s="6" t="n">
-        <v>99.889002</v>
+        <v>99.89067900000001</v>
       </c>
       <c r="P462" s="6" t="n">
         <v>100.687926</v>
@@ -38118,7 +38118,7 @@
         <v>100.733264</v>
       </c>
       <c r="O463" s="9" t="n">
-        <v>99.91958099999999</v>
+        <v>99.92132599999999</v>
       </c>
       <c r="P463" s="9" t="n">
         <v>100.767643</v>
@@ -38202,7 +38202,7 @@
         <v>100.813605</v>
       </c>
       <c r="O464" s="6" t="n">
-        <v>99.99393999999999</v>
+        <v>99.995718</v>
       </c>
       <c r="P464" s="6" t="n">
         <v>100.828406</v>
@@ -38286,7 +38286,7 @@
         <v>100.881008</v>
       </c>
       <c r="O465" s="9" t="n">
-        <v>100.086625</v>
+        <v>100.088421</v>
       </c>
       <c r="P465" s="9" t="n">
         <v>100.850482</v>
@@ -38370,7 +38370,7 @@
         <v>100.945593</v>
       </c>
       <c r="O466" s="6" t="n">
-        <v>100.187025</v>
+        <v>100.188819</v>
       </c>
       <c r="P466" s="6" t="n">
         <v>100.850342</v>
@@ -38454,7 +38454,7 @@
         <v>100.999612</v>
       </c>
       <c r="O467" s="9" t="n">
-        <v>100.281459</v>
+        <v>100.283258</v>
       </c>
       <c r="P467" s="9" t="n">
         <v>100.858654</v>
@@ -38538,7 +38538,7 @@
         <v>101.033632</v>
       </c>
       <c r="O468" s="6" t="n">
-        <v>100.36843</v>
+        <v>100.370237</v>
       </c>
       <c r="P468" s="6" t="n">
         <v>100.898216</v>
@@ -38622,7 +38622,7 @@
         <v>101.043422</v>
       </c>
       <c r="O469" s="9" t="n">
-        <v>100.449472</v>
+        <v>100.451297</v>
       </c>
       <c r="P469" s="9" t="n">
         <v>100.952082</v>
@@ -38706,7 +38706,7 @@
         <v>101.028239</v>
       </c>
       <c r="O470" s="6" t="n">
-        <v>100.522437</v>
+        <v>100.524302</v>
       </c>
       <c r="P470" s="6" t="n">
         <v>101.004263</v>
@@ -38790,7 +38790,7 @@
         <v>100.983073</v>
       </c>
       <c r="O471" s="9" t="n">
-        <v>100.531292</v>
+        <v>100.533258</v>
       </c>
       <c r="P471" s="9" t="n">
         <v>101.062335</v>
@@ -38874,7 +38874,7 @@
         <v>100.905822</v>
       </c>
       <c r="O472" s="6" t="n">
-        <v>100.419027</v>
+        <v>100.421271</v>
       </c>
       <c r="P472" s="6" t="n">
         <v>101.135696</v>
@@ -38958,7 +38958,7 @@
         <v>100.807857</v>
       </c>
       <c r="O473" s="9" t="n">
-        <v>100.218061</v>
+        <v>100.220718</v>
       </c>
       <c r="P473" s="9" t="n">
         <v>101.232864</v>
@@ -39042,7 +39042,7 @@
         <v>100.715774</v>
       </c>
       <c r="O474" s="6" t="n">
-        <v>99.968356</v>
+        <v>99.971486</v>
       </c>
       <c r="P474" s="6" t="n">
         <v>101.354525</v>
@@ -39126,7 +39126,7 @@
         <v>100.633468</v>
       </c>
       <c r="O475" s="9" t="n">
-        <v>99.68058499999999</v>
+        <v>99.68424899999999</v>
       </c>
       <c r="P475" s="9" t="n">
         <v>101.468152</v>
@@ -39210,7 +39210,7 @@
         <v>100.563245</v>
       </c>
       <c r="O476" s="6" t="n">
-        <v>99.42294800000001</v>
+        <v>99.42711</v>
       </c>
       <c r="P476" s="6" t="n">
         <v>101.551044</v>
@@ -39294,7 +39294,7 @@
         <v>100.502645</v>
       </c>
       <c r="O477" s="9" t="n">
-        <v>99.215371</v>
+        <v>99.219936</v>
       </c>
       <c r="P477" s="9" t="n">
         <v>101.583581</v>
@@ -39378,7 +39378,7 @@
         <v>100.443481</v>
       </c>
       <c r="O478" s="6" t="n">
-        <v>99.05097499999999</v>
+        <v>99.055898</v>
       </c>
       <c r="P478" s="6" t="n">
         <v>101.547676</v>
@@ -39462,7 +39462,7 @@
         <v>100.383873</v>
       </c>
       <c r="O479" s="9" t="n">
-        <v>98.995295</v>
+        <v>99.000445</v>
       </c>
       <c r="P479" s="9" t="n">
         <v>101.441245</v>
@@ -39546,7 +39546,7 @@
         <v>100.322616</v>
       </c>
       <c r="O480" s="6" t="n">
-        <v>99.042288</v>
+        <v>99.047498</v>
       </c>
       <c r="P480" s="6" t="n">
         <v>101.292524</v>
@@ -39630,7 +39630,7 @@
         <v>100.24474</v>
       </c>
       <c r="O481" s="9" t="n">
-        <v>99.132893</v>
+        <v>99.13811099999999</v>
       </c>
       <c r="P481" s="9" t="n">
         <v>101.126542</v>
@@ -39714,7 +39714,7 @@
         <v>100.141689</v>
       </c>
       <c r="O482" s="6" t="n">
-        <v>99.16364</v>
+        <v>99.168932</v>
       </c>
       <c r="P482" s="6" t="n">
         <v>100.944592</v>
@@ -39798,7 +39798,7 @@
         <v>100.005824</v>
       </c>
       <c r="O483" s="9" t="n">
-        <v>99.16673400000001</v>
+        <v>99.172121</v>
       </c>
       <c r="P483" s="9" t="n">
         <v>100.73086</v>
@@ -39882,7 +39882,7 @@
         <v>99.821956</v>
       </c>
       <c r="O484" s="6" t="n">
-        <v>99.169365</v>
+        <v>99.17484</v>
       </c>
       <c r="P484" s="6" t="n">
         <v>100.459774</v>
@@ -39966,7 +39966,7 @@
         <v>99.57194800000001</v>
       </c>
       <c r="O485" s="9" t="n">
-        <v>99.12859899999999</v>
+        <v>99.13416599999999</v>
       </c>
       <c r="P485" s="9" t="n">
         <v>100.09571</v>
@@ -40050,7 +40050,7 @@
         <v>99.232862</v>
       </c>
       <c r="O486" s="6" t="n">
-        <v>99.03926800000001</v>
+        <v>99.044944</v>
       </c>
       <c r="P486" s="6" t="n">
         <v>99.610316</v>
@@ -40134,7 +40134,7 @@
         <v>98.78703299999999</v>
       </c>
       <c r="O487" s="9" t="n">
-        <v>98.93617</v>
+        <v>98.941948</v>
       </c>
       <c r="P487" s="9" t="n">
         <v>99.00239500000001</v>
@@ -40218,7 +40218,7 @@
         <v>98.253626</v>
       </c>
       <c r="O488" s="6" t="n">
-        <v>98.79833499999999</v>
+        <v>98.804221</v>
       </c>
       <c r="P488" s="6" t="n">
         <v>98.32079299999999</v>
@@ -40302,7 +40302,7 @@
         <v>95.55669399999999</v>
       </c>
       <c r="O489" s="9" t="n">
-        <v>98.667036</v>
+        <v>98.67305</v>
       </c>
       <c r="P489" s="9" t="n">
         <v>97.67500200000001</v>
@@ -40386,7 +40386,7 @@
         <v>93.073734</v>
       </c>
       <c r="O490" s="6" t="n">
-        <v>98.58877699999999</v>
+        <v>98.59501299999999</v>
       </c>
       <c r="P490" s="6" t="n">
         <v>97.20862</v>
@@ -40470,7 +40470,7 @@
         <v>95.743156</v>
       </c>
       <c r="O491" s="9" t="n">
-        <v>98.58478100000001</v>
+        <v>98.59129299999999</v>
       </c>
       <c r="P491" s="9" t="n">
         <v>96.970237</v>
@@ -40554,7 +40554,7 @@
         <v>96.07962499999999</v>
       </c>
       <c r="O492" s="6" t="n">
-        <v>98.681675</v>
+        <v>98.68841</v>
       </c>
       <c r="P492" s="6" t="n">
         <v>96.925134</v>
@@ -40638,7 +40638,7 @@
         <v>97.10638899999999</v>
       </c>
       <c r="O493" s="9" t="n">
-        <v>98.878523</v>
+        <v>98.88535899999999</v>
       </c>
       <c r="P493" s="9" t="n">
         <v>97.01593099999999</v>
@@ -40722,7 +40722,7 @@
         <v>97.453835</v>
       </c>
       <c r="O494" s="6" t="n">
-        <v>99.15967499999999</v>
+        <v>99.166437</v>
       </c>
       <c r="P494" s="6" t="n">
         <v>97.18713700000001</v>
@@ -40806,7 +40806,7 @@
         <v>97.844987</v>
       </c>
       <c r="O495" s="9" t="n">
-        <v>99.46768899999999</v>
+        <v>99.474293</v>
       </c>
       <c r="P495" s="9" t="n">
         <v>97.385947</v>
@@ -40890,7 +40890,7 @@
         <v>98.23362299999999</v>
       </c>
       <c r="O496" s="6" t="n">
-        <v>99.764928</v>
+        <v>99.771334</v>
       </c>
       <c r="P496" s="6" t="n">
         <v>97.58692499999999</v>
@@ -40974,7 +40974,7 @@
         <v>98.57064699999999</v>
       </c>
       <c r="O497" s="9" t="n">
-        <v>100.034038</v>
+        <v>100.040225</v>
       </c>
       <c r="P497" s="9" t="n">
         <v>97.779211</v>
@@ -41058,7 +41058,7 @@
         <v>98.843762</v>
       </c>
       <c r="O498" s="6" t="n">
-        <v>100.254969</v>
+        <v>100.260968</v>
       </c>
       <c r="P498" s="6" t="n">
         <v>97.970084</v>
@@ -41142,7 +41142,7 @@
         <v>99.067261</v>
       </c>
       <c r="O499" s="9" t="n">
-        <v>100.433784</v>
+        <v>100.439602</v>
       </c>
       <c r="P499" s="9" t="n">
         <v>98.18325900000001</v>
@@ -41226,7 +41226,7 @@
         <v>99.284261</v>
       </c>
       <c r="O500" s="6" t="n">
-        <v>100.605971</v>
+        <v>100.611608</v>
       </c>
       <c r="P500" s="6" t="n">
         <v>98.434737</v>
@@ -41310,7 +41310,7 @@
         <v>99.506621</v>
       </c>
       <c r="O501" s="9" t="n">
-        <v>100.7565</v>
+        <v>100.761999</v>
       </c>
       <c r="P501" s="9" t="n">
         <v>98.709823</v>
@@ -41394,7 +41394,7 @@
         <v>99.72223</v>
       </c>
       <c r="O502" s="6" t="n">
-        <v>100.853147</v>
+        <v>100.858559</v>
       </c>
       <c r="P502" s="6" t="n">
         <v>98.98323600000001</v>
@@ -41478,7 +41478,7 @@
         <v>99.910652</v>
       </c>
       <c r="O503" s="9" t="n">
-        <v>100.870491</v>
+        <v>100.87585</v>
       </c>
       <c r="P503" s="9" t="n">
         <v>99.230737</v>
@@ -41562,7 +41562,7 @@
         <v>100.06839</v>
       </c>
       <c r="O504" s="6" t="n">
-        <v>100.809521</v>
+        <v>100.814893</v>
       </c>
       <c r="P504" s="6" t="n">
         <v>99.43047</v>
@@ -41646,7 +41646,7 @@
         <v>100.188481</v>
       </c>
       <c r="O505" s="9" t="n">
-        <v>100.69003</v>
+        <v>100.695469</v>
       </c>
       <c r="P505" s="9" t="n">
         <v>99.58254100000001</v>
@@ -41730,7 +41730,7 @@
         <v>100.300791</v>
       </c>
       <c r="O506" s="6" t="n">
-        <v>100.540372</v>
+        <v>100.545911</v>
       </c>
       <c r="P506" s="6" t="n">
         <v>99.71243800000001</v>
@@ -41814,7 +41814,7 @@
         <v>100.432031</v>
       </c>
       <c r="O507" s="9" t="n">
-        <v>100.380557</v>
+        <v>100.386218</v>
       </c>
       <c r="P507" s="9" t="n">
         <v>99.836997</v>
@@ -41898,7 +41898,7 @@
         <v>100.588669</v>
       </c>
       <c r="O508" s="6" t="n">
-        <v>100.250627</v>
+        <v>100.256376</v>
       </c>
       <c r="P508" s="6" t="n">
         <v>99.955989</v>
@@ -41982,7 +41982,7 @@
         <v>100.764847</v>
       </c>
       <c r="O509" s="9" t="n">
-        <v>100.165921</v>
+        <v>100.171727</v>
       </c>
       <c r="P509" s="9" t="n">
         <v>100.07133</v>
@@ -42066,7 +42066,7 @@
         <v>100.954178</v>
       </c>
       <c r="O510" s="6" t="n">
-        <v>100.124167</v>
+        <v>100.12999</v>
       </c>
       <c r="P510" s="6" t="n">
         <v>100.180563</v>
@@ -42150,7 +42150,7 @@
         <v>101.163991</v>
       </c>
       <c r="O511" s="9" t="n">
-        <v>100.114886</v>
+        <v>100.120627</v>
       </c>
       <c r="P511" s="9" t="n">
         <v>100.283659</v>
@@ -42234,7 +42234,7 @@
         <v>101.365937</v>
       </c>
       <c r="O512" s="6" t="n">
-        <v>100.113233</v>
+        <v>100.118806</v>
       </c>
       <c r="P512" s="6" t="n">
         <v>100.355092</v>
@@ -42318,7 +42318,7 @@
         <v>101.534089</v>
       </c>
       <c r="O513" s="9" t="n">
-        <v>100.130151</v>
+        <v>100.135434</v>
       </c>
       <c r="P513" s="9" t="n">
         <v>100.409727</v>
@@ -42402,7 +42402,7 @@
         <v>101.644665</v>
       </c>
       <c r="O514" s="6" t="n">
-        <v>100.184271</v>
+        <v>100.189094</v>
       </c>
       <c r="P514" s="6" t="n">
         <v>100.444945</v>
@@ -42486,7 +42486,7 @@
         <v>101.681153</v>
       </c>
       <c r="O515" s="9" t="n">
-        <v>100.25998</v>
+        <v>100.264195</v>
       </c>
       <c r="P515" s="9" t="n">
         <v>100.450859</v>
@@ -42570,7 +42570,7 @@
         <v>101.630796</v>
       </c>
       <c r="O516" s="6" t="n">
-        <v>100.331625</v>
+        <v>100.335159</v>
       </c>
       <c r="P516" s="6" t="n">
         <v>100.427746</v>
@@ -42654,7 +42654,7 @@
         <v>101.507476</v>
       </c>
       <c r="O517" s="9" t="n">
-        <v>100.380929</v>
+        <v>100.383775</v>
       </c>
       <c r="P517" s="9" t="n">
         <v>100.391661</v>
@@ -42738,7 +42738,7 @@
         <v>101.343523</v>
       </c>
       <c r="O518" s="6" t="n">
-        <v>100.428309</v>
+        <v>100.430545</v>
       </c>
       <c r="P518" s="6" t="n">
         <v>100.347957</v>
@@ -42822,7 +42822,7 @@
         <v>101.166503</v>
       </c>
       <c r="O519" s="9" t="n">
-        <v>100.480743</v>
+        <v>100.482495</v>
       </c>
       <c r="P519" s="9" t="n">
         <v>100.314535</v>
@@ -42906,7 +42906,7 @@
         <v>101.001868</v>
       </c>
       <c r="O520" s="6" t="n">
-        <v>100.523257</v>
+        <v>100.524667</v>
       </c>
       <c r="P520" s="6" t="n">
         <v>100.301948</v>
@@ -42990,7 +42990,7 @@
         <v>100.870706</v>
       </c>
       <c r="O521" s="9" t="n">
-        <v>100.574339</v>
+        <v>100.575517</v>
       </c>
       <c r="P521" s="9" t="n">
         <v>100.31952</v>
@@ -43074,7 +43074,7 @@
         <v>100.763686</v>
       </c>
       <c r="O522" s="6" t="n">
-        <v>100.642645</v>
+        <v>100.64361</v>
       </c>
       <c r="P522" s="6" t="n">
         <v>100.375696</v>
@@ -43158,7 +43158,7 @@
         <v>100.663368</v>
       </c>
       <c r="O523" s="9" t="n">
-        <v>100.713739</v>
+        <v>100.714411</v>
       </c>
       <c r="P523" s="9" t="n">
         <v>100.46012</v>
@@ -43242,7 +43242,7 @@
         <v>100.567792</v>
       </c>
       <c r="O524" s="6" t="n">
-        <v>100.766164</v>
+        <v>100.766356</v>
       </c>
       <c r="P524" s="6" t="n">
         <v>100.548361</v>
@@ -43326,7 +43326,7 @@
         <v>100.477409</v>
       </c>
       <c r="O525" s="9" t="n">
-        <v>100.780831</v>
+        <v>100.78027</v>
       </c>
       <c r="P525" s="9" t="n">
         <v>100.632198</v>
@@ -43410,7 +43410,7 @@
         <v>100.383687</v>
       </c>
       <c r="O526" s="6" t="n">
-        <v>100.74651</v>
+        <v>100.744827</v>
       </c>
       <c r="P526" s="6" t="n">
         <v>100.714227</v>
@@ -43494,7 +43494,7 @@
         <v>100.290873</v>
       </c>
       <c r="O527" s="9" t="n">
-        <v>100.673886</v>
+        <v>100.670756</v>
       </c>
       <c r="P527" s="9" t="n">
         <v>100.803232</v>
@@ -43578,7 +43578,7 @@
         <v>100.206185</v>
       </c>
       <c r="O528" s="6" t="n">
-        <v>100.57701</v>
+        <v>100.572192</v>
       </c>
       <c r="P528" s="6" t="n">
         <v>100.889331</v>
@@ -43662,7 +43662,7 @@
         <v>100.138378</v>
       </c>
       <c r="O529" s="9" t="n">
-        <v>100.476548</v>
+        <v>100.469904</v>
       </c>
       <c r="P529" s="9" t="n">
         <v>100.967887</v>
@@ -43746,7 +43746,7 @@
         <v>100.084765</v>
       </c>
       <c r="O530" s="6" t="n">
-        <v>100.384973</v>
+        <v>100.376591</v>
       </c>
       <c r="P530" s="6" t="n">
         <v>101.04165</v>
@@ -43830,7 +43830,7 @@
         <v>100.032874</v>
       </c>
       <c r="O531" s="9" t="n">
-        <v>100.324882</v>
+        <v>100.315029</v>
       </c>
       <c r="P531" s="9" t="n">
         <v>101.113018</v>
@@ -43914,7 +43914,7 @@
         <v>99.994353</v>
       </c>
       <c r="O532" s="6" t="n">
-        <v>100.317893</v>
+        <v>100.30701</v>
       </c>
       <c r="P532" s="6" t="n">
         <v>101.18864</v>
@@ -43998,7 +43998,7 @@
         <v>99.982116</v>
       </c>
       <c r="O533" s="9" t="n">
-        <v>100.352183</v>
+        <v>100.340843</v>
       </c>
       <c r="P533" s="9" t="n">
         <v>101.268301</v>
@@ -44082,7 +44082,7 @@
         <v>99.997514</v>
       </c>
       <c r="O534" s="6" t="n">
-        <v>100.40148</v>
+        <v>100.390247</v>
       </c>
       <c r="P534" s="6" t="n">
         <v>101.341732</v>
@@ -44166,7 +44166,7 @@
         <v>100.025173</v>
       </c>
       <c r="O535" s="9" t="n">
-        <v>100.43898</v>
+        <v>100.428315</v>
       </c>
       <c r="P535" s="9" t="n">
         <v>101.398878</v>
@@ -44250,7 +44250,7 @@
         <v>100.027704</v>
       </c>
       <c r="O536" s="6" t="n">
-        <v>100.463058</v>
+        <v>100.453038</v>
       </c>
       <c r="P536" s="6" t="n">
         <v>101.427039</v>
@@ -44334,7 +44334,7 @@
         <v>100.001897</v>
       </c>
       <c r="O537" s="9" t="n">
-        <v>100.464657</v>
+        <v>100.454715</v>
       </c>
       <c r="P537" s="9" t="n">
         <v>101.409301</v>
@@ -44418,7 +44418,7 @@
         <v>99.951207</v>
       </c>
       <c r="O538" s="6" t="n">
-        <v>100.44067</v>
+        <v>100.429545</v>
       </c>
       <c r="P538" s="6" t="n">
         <v>101.343667</v>
@@ -44502,7 +44502,7 @@
         <v>99.884123</v>
       </c>
       <c r="O539" s="9" t="n">
-        <v>100.39169</v>
+        <v>100.377561</v>
       </c>
       <c r="P539" s="9" t="n">
         <v>101.236576</v>
@@ -44586,7 +44586,7 @@
         <v>99.79774500000001</v>
       </c>
       <c r="O540" s="6" t="n">
-        <v>100.323872</v>
+        <v>100.304682</v>
       </c>
       <c r="P540" s="6" t="n">
         <v>101.109561</v>
@@ -44670,7 +44670,7 @@
         <v>99.696808</v>
       </c>
       <c r="O541" s="9" t="n">
-        <v>100.254403</v>
+        <v>100.228566</v>
       </c>
       <c r="P541" s="9" t="n">
         <v>100.972291</v>
@@ -44754,7 +44754,7 @@
         <v>99.585432</v>
       </c>
       <c r="O542" s="6" t="n">
-        <v>100.187339</v>
+        <v>100.154715</v>
       </c>
       <c r="P542" s="6" t="n">
         <v>100.819307</v>
@@ -44838,7 +44838,7 @@
         <v>99.486316</v>
       </c>
       <c r="O543" s="9" t="n">
-        <v>100.10804</v>
+        <v>100.071439</v>
       </c>
       <c r="P543" s="9" t="n">
         <v>100.66315</v>
@@ -44922,7 +44922,7 @@
         <v>99.394492</v>
       </c>
       <c r="O544" s="6" t="n">
-        <v>100.007474</v>
+        <v>99.96960199999999</v>
       </c>
       <c r="P544" s="6" t="n">
         <v>100.501417</v>
@@ -45006,7 +45006,7 @@
         <v>99.298998</v>
       </c>
       <c r="O545" s="9" t="n">
-        <v>99.876864</v>
+        <v>99.839995</v>
       </c>
       <c r="P545" s="9" t="n">
         <v>100.328765</v>
@@ -45090,7 +45090,7 @@
         <v>99.206896</v>
       </c>
       <c r="O546" s="6" t="n">
-        <v>99.73588599999999</v>
+        <v>99.701699</v>
       </c>
       <c r="P546" s="6" t="n">
         <v>100.149457</v>
@@ -45174,7 +45174,7 @@
         <v>99.12917299999999</v>
       </c>
       <c r="O547" s="9" t="n">
-        <v>99.589375</v>
+        <v>99.558834</v>
       </c>
       <c r="P547" s="9" t="n">
         <v>99.966641</v>
@@ -45258,7 +45258,7 @@
         <v>99.080938</v>
       </c>
       <c r="O548" s="6" t="n">
-        <v>99.443596</v>
+        <v>99.416664</v>
       </c>
       <c r="P548" s="6" t="n">
         <v>99.80820199999999</v>
@@ -45342,7 +45342,7 @@
         <v>99.05335599999999</v>
       </c>
       <c r="O549" s="9" t="n">
-        <v>99.329407</v>
+        <v>99.30459399999999</v>
       </c>
       <c r="P549" s="9" t="n">
         <v>99.696308</v>
@@ -45426,7 +45426,7 @@
         <v>99.044051</v>
       </c>
       <c r="O550" s="6" t="n">
-        <v>99.256207</v>
+        <v>99.23044</v>
       </c>
       <c r="P550" s="6" t="n">
         <v>99.651686</v>
@@ -45510,7 +45510,7 @@
         <v>99.06027</v>
       </c>
       <c r="O551" s="9" t="n">
-        <v>99.219632</v>
+        <v>99.18846499999999</v>
       </c>
       <c r="P551" s="9" t="n">
         <v>99.644609</v>
@@ -45594,7 +45594,7 @@
         <v>99.10844299999999</v>
       </c>
       <c r="O552" s="6" t="n">
-        <v>99.206112</v>
+        <v>99.16442600000001</v>
       </c>
       <c r="P552" s="6" t="n">
         <v>99.64967900000001</v>
@@ -45678,7 +45678,7 @@
         <v>99.19386799999999</v>
       </c>
       <c r="O553" s="9" t="n">
-        <v>99.20610600000001</v>
+        <v>99.149593</v>
       </c>
       <c r="P553" s="9" t="n">
         <v>99.642844</v>
@@ -45762,7 +45762,7 @@
         <v>99.30423399999999</v>
       </c>
       <c r="O554" s="6" t="n">
-        <v>99.208668</v>
+        <v>99.136381</v>
       </c>
       <c r="P554" s="6" t="n">
         <v>99.617773</v>
@@ -45846,7 +45846,7 @@
         <v>99.42832</v>
       </c>
       <c r="O555" s="9" t="n">
-        <v>99.22666700000001</v>
+        <v>99.14503000000001</v>
       </c>
       <c r="P555" s="9" t="n">
         <v>99.57182</v>
@@ -45930,7 +45930,7 @@
         <v>99.557726</v>
       </c>
       <c r="O556" s="6" t="n">
-        <v>99.26781200000001</v>
+        <v>99.182095</v>
       </c>
       <c r="P556" s="6" t="n">
         <v>99.51242000000001</v>
@@ -46014,7 +46014,7 @@
         <v>99.698927</v>
       </c>
       <c r="O557" s="9" t="n">
-        <v>99.350877</v>
+        <v>99.265089</v>
       </c>
       <c r="P557" s="9" t="n">
         <v>99.44973400000001</v>
@@ -46098,7 +46098,7 @@
         <v>99.862517</v>
       </c>
       <c r="O558" s="6" t="n">
-        <v>99.47413400000001</v>
+        <v>99.391604</v>
       </c>
       <c r="P558" s="6" t="n">
         <v>99.38923200000001</v>
@@ -46182,7 +46182,7 @@
         <v>100.056753</v>
       </c>
       <c r="O559" s="9" t="n">
-        <v>99.621951</v>
+        <v>99.546012</v>
       </c>
       <c r="P559" s="9" t="n">
         <v>99.333716</v>
@@ -46266,7 +46266,7 @@
         <v>100.282217</v>
       </c>
       <c r="O560" s="6" t="n">
-        <v>99.782504</v>
+        <v>99.717207</v>
       </c>
       <c r="P560" s="6" t="n">
         <v>99.286867</v>
@@ -46350,7 +46350,7 @@
         <v>100.53139</v>
       </c>
       <c r="O561" s="9" t="n">
-        <v>99.92449000000001</v>
+        <v>99.874979</v>
       </c>
       <c r="P561" s="9" t="n">
         <v>99.253601</v>
@@ -46434,7 +46434,7 @@
         <v>100.79495</v>
       </c>
       <c r="O562" s="6" t="n">
-        <v>100.050948</v>
+        <v>100.023675</v>
       </c>
       <c r="P562" s="6" t="n">
         <v>99.236124</v>
@@ -46518,7 +46518,7 @@
         <v>101.069159</v>
       </c>
       <c r="O563" s="9" t="n">
-        <v>100.157408</v>
+        <v>100.160256</v>
       </c>
       <c r="P563" s="9" t="n">
         <v>99.24297300000001</v>
@@ -46602,7 +46602,7 @@
         <v>101.360238</v>
       </c>
       <c r="O564" s="6" t="n">
-        <v>100.255278</v>
+        <v>100.296868</v>
       </c>
       <c r="P564" s="6" t="n">
         <v>99.264543</v>
@@ -46674,7 +46674,7 @@
         <v>101.628724</v>
       </c>
       <c r="O565" s="9" t="n">
-        <v>100.339636</v>
+        <v>100.427363</v>
       </c>
       <c r="P565" s="9" t="n">
         <v>99.300256</v>

--- a/downloads/indicadores/SIC/SIC_datos.xlsx
+++ b/downloads/indicadores/SIC/SIC_datos.xlsx
@@ -1554,7 +1554,7 @@
       </c>
       <c r="P18" s="6" t="n"/>
       <c r="Q18" s="6" t="n">
-        <v>106.952153</v>
+        <v>106.977071</v>
       </c>
       <c r="R18" s="6" t="n">
         <v>98.480585</v>
@@ -1632,7 +1632,7 @@
       </c>
       <c r="P19" s="9" t="n"/>
       <c r="Q19" s="9" t="n">
-        <v>106.502529</v>
+        <v>106.525836</v>
       </c>
       <c r="R19" s="9" t="n">
         <v>98.193574</v>
@@ -1710,7 +1710,7 @@
       </c>
       <c r="P20" s="6" t="n"/>
       <c r="Q20" s="6" t="n">
-        <v>106.051782</v>
+        <v>106.073473</v>
       </c>
       <c r="R20" s="6" t="n">
         <v>97.92594099999999</v>
@@ -1788,7 +1788,7 @@
       </c>
       <c r="P21" s="9" t="n"/>
       <c r="Q21" s="9" t="n">
-        <v>105.594574</v>
+        <v>105.614626</v>
       </c>
       <c r="R21" s="9" t="n">
         <v>97.67979800000001</v>
@@ -1866,7 +1866,7 @@
       </c>
       <c r="P22" s="6" t="n"/>
       <c r="Q22" s="6" t="n">
-        <v>105.122658</v>
+        <v>105.141018</v>
       </c>
       <c r="R22" s="6" t="n">
         <v>97.45354</v>
@@ -1944,7 +1944,7 @@
       </c>
       <c r="P23" s="9" t="n"/>
       <c r="Q23" s="9" t="n">
-        <v>104.64142</v>
+        <v>104.658056</v>
       </c>
       <c r="R23" s="9" t="n">
         <v>97.24066500000001</v>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="P24" s="6" t="n"/>
       <c r="Q24" s="6" t="n">
-        <v>104.157259</v>
+        <v>104.172159</v>
       </c>
       <c r="R24" s="6" t="n">
         <v>97.03708</v>
@@ -2100,7 +2100,7 @@
       </c>
       <c r="P25" s="9" t="n"/>
       <c r="Q25" s="9" t="n">
-        <v>103.672064</v>
+        <v>103.685225</v>
       </c>
       <c r="R25" s="9" t="n">
         <v>96.849934</v>
@@ -2178,7 +2178,7 @@
       </c>
       <c r="P26" s="6" t="n"/>
       <c r="Q26" s="6" t="n">
-        <v>103.183298</v>
+        <v>103.194708</v>
       </c>
       <c r="R26" s="6" t="n">
         <v>96.705758</v>
@@ -2256,7 +2256,7 @@
       </c>
       <c r="P27" s="9" t="n"/>
       <c r="Q27" s="9" t="n">
-        <v>102.686076</v>
+        <v>102.695704</v>
       </c>
       <c r="R27" s="9" t="n">
         <v>96.647215</v>
@@ -2334,7 +2334,7 @@
       </c>
       <c r="P28" s="6" t="n"/>
       <c r="Q28" s="6" t="n">
-        <v>102.16971</v>
+        <v>102.177487</v>
       </c>
       <c r="R28" s="6" t="n">
         <v>96.73735000000001</v>
@@ -2412,7 +2412,7 @@
       </c>
       <c r="P29" s="9" t="n"/>
       <c r="Q29" s="9" t="n">
-        <v>101.580592</v>
+        <v>101.586258</v>
       </c>
       <c r="R29" s="9" t="n">
         <v>97.043802</v>
@@ -2490,7 +2490,7 @@
       </c>
       <c r="P30" s="6" t="n"/>
       <c r="Q30" s="6" t="n">
-        <v>100.876556</v>
+        <v>100.879698</v>
       </c>
       <c r="R30" s="6" t="n">
         <v>97.616789</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="P31" s="9" t="n"/>
       <c r="Q31" s="9" t="n">
-        <v>100.081219</v>
+        <v>100.08151</v>
       </c>
       <c r="R31" s="9" t="n">
         <v>98.444929</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="P32" s="6" t="n"/>
       <c r="Q32" s="6" t="n">
-        <v>99.2047</v>
+        <v>99.20184999999999</v>
       </c>
       <c r="R32" s="6" t="n">
         <v>99.367648</v>
@@ -2724,7 +2724,7 @@
       </c>
       <c r="P33" s="9" t="n"/>
       <c r="Q33" s="9" t="n">
-        <v>98.289587</v>
+        <v>98.283457</v>
       </c>
       <c r="R33" s="9" t="n">
         <v>100.193865</v>
@@ -2802,7 +2802,7 @@
       </c>
       <c r="P34" s="6" t="n"/>
       <c r="Q34" s="6" t="n">
-        <v>97.450121</v>
+        <v>97.44098200000001</v>
       </c>
       <c r="R34" s="6" t="n">
         <v>100.829396</v>
@@ -2880,7 +2880,7 @@
       </c>
       <c r="P35" s="9" t="n"/>
       <c r="Q35" s="9" t="n">
-        <v>96.787127</v>
+        <v>96.775612</v>
       </c>
       <c r="R35" s="9" t="n">
         <v>101.308747</v>
@@ -2958,7 +2958,7 @@
       </c>
       <c r="P36" s="6" t="n"/>
       <c r="Q36" s="6" t="n">
-        <v>96.303622</v>
+        <v>96.290374</v>
       </c>
       <c r="R36" s="6" t="n">
         <v>101.707294</v>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="P37" s="9" t="n"/>
       <c r="Q37" s="9" t="n">
-        <v>96.00009</v>
+        <v>95.985755</v>
       </c>
       <c r="R37" s="9" t="n">
         <v>102.077392</v>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="P38" s="6" t="n"/>
       <c r="Q38" s="6" t="n">
-        <v>95.833355</v>
+        <v>95.818421</v>
       </c>
       <c r="R38" s="6" t="n">
         <v>102.378652</v>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="P39" s="9" t="n"/>
       <c r="Q39" s="9" t="n">
-        <v>95.712726</v>
+        <v>95.69736</v>
       </c>
       <c r="R39" s="9" t="n">
         <v>102.566638</v>
@@ -3270,7 +3270,7 @@
       </c>
       <c r="P40" s="6" t="n"/>
       <c r="Q40" s="6" t="n">
-        <v>95.60773</v>
+        <v>95.591988</v>
       </c>
       <c r="R40" s="6" t="n">
         <v>102.687969</v>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="P41" s="9" t="n"/>
       <c r="Q41" s="9" t="n">
-        <v>95.505442</v>
+        <v>95.489333</v>
       </c>
       <c r="R41" s="9" t="n">
         <v>102.801567</v>
@@ -3426,7 +3426,7 @@
       </c>
       <c r="P42" s="6" t="n"/>
       <c r="Q42" s="6" t="n">
-        <v>95.467579</v>
+        <v>95.451335</v>
       </c>
       <c r="R42" s="6" t="n">
         <v>102.901158</v>
@@ -3504,7 +3504,7 @@
       </c>
       <c r="P43" s="9" t="n"/>
       <c r="Q43" s="9" t="n">
-        <v>95.52218499999999</v>
+        <v>95.506136</v>
       </c>
       <c r="R43" s="9" t="n">
         <v>102.937119</v>
@@ -3582,7 +3582,7 @@
       </c>
       <c r="P44" s="6" t="n"/>
       <c r="Q44" s="6" t="n">
-        <v>95.697683</v>
+        <v>95.68226300000001</v>
       </c>
       <c r="R44" s="6" t="n">
         <v>102.89332</v>
@@ -3660,7 +3660,7 @@
       </c>
       <c r="P45" s="9" t="n"/>
       <c r="Q45" s="9" t="n">
-        <v>96.034391</v>
+        <v>96.020178</v>
       </c>
       <c r="R45" s="9" t="n">
         <v>102.783008</v>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="P46" s="6" t="n"/>
       <c r="Q46" s="6" t="n">
-        <v>96.52513399999999</v>
+        <v>96.51267900000001</v>
       </c>
       <c r="R46" s="6" t="n">
         <v>102.631606</v>
@@ -3816,7 +3816,7 @@
       </c>
       <c r="P47" s="9" t="n"/>
       <c r="Q47" s="9" t="n">
-        <v>97.10444099999999</v>
+        <v>97.09406199999999</v>
       </c>
       <c r="R47" s="9" t="n">
         <v>102.455392</v>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="P48" s="6" t="n"/>
       <c r="Q48" s="6" t="n">
-        <v>97.68363100000001</v>
+        <v>97.675329</v>
       </c>
       <c r="R48" s="6" t="n">
         <v>102.261819</v>
@@ -3972,7 +3972,7 @@
       </c>
       <c r="P49" s="9" t="n"/>
       <c r="Q49" s="9" t="n">
-        <v>98.226795</v>
+        <v>98.220439</v>
       </c>
       <c r="R49" s="9" t="n">
         <v>102.054093</v>
@@ -4050,7 +4050,7 @@
       </c>
       <c r="P50" s="6" t="n"/>
       <c r="Q50" s="6" t="n">
-        <v>98.73935899999999</v>
+        <v>98.73484000000001</v>
       </c>
       <c r="R50" s="6" t="n">
         <v>101.823955</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="P51" s="9" t="n"/>
       <c r="Q51" s="9" t="n">
-        <v>99.196934</v>
+        <v>99.19405399999999</v>
       </c>
       <c r="R51" s="9" t="n">
         <v>101.556001</v>
@@ -4206,7 +4206,7 @@
       </c>
       <c r="P52" s="6" t="n"/>
       <c r="Q52" s="6" t="n">
-        <v>99.61892899999999</v>
+        <v>99.617563</v>
       </c>
       <c r="R52" s="6" t="n">
         <v>101.242898</v>
@@ -4284,7 +4284,7 @@
       </c>
       <c r="P53" s="9" t="n"/>
       <c r="Q53" s="9" t="n">
-        <v>100.00957</v>
+        <v>100.009604</v>
       </c>
       <c r="R53" s="9" t="n">
         <v>100.897152</v>
@@ -4362,7 +4362,7 @@
       </c>
       <c r="P54" s="6" t="n"/>
       <c r="Q54" s="6" t="n">
-        <v>100.298536</v>
+        <v>100.299604</v>
       </c>
       <c r="R54" s="6" t="n">
         <v>100.535859</v>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="P55" s="9" t="n"/>
       <c r="Q55" s="9" t="n">
-        <v>100.384109</v>
+        <v>100.385484</v>
       </c>
       <c r="R55" s="9" t="n">
         <v>100.184283</v>
@@ -4518,7 +4518,7 @@
       </c>
       <c r="P56" s="6" t="n"/>
       <c r="Q56" s="6" t="n">
-        <v>100.242564</v>
+        <v>100.243432</v>
       </c>
       <c r="R56" s="6" t="n">
         <v>99.86248500000001</v>
@@ -4596,7 +4596,7 @@
       </c>
       <c r="P57" s="9" t="n"/>
       <c r="Q57" s="9" t="n">
-        <v>99.98224500000001</v>
+        <v>99.98218</v>
       </c>
       <c r="R57" s="9" t="n">
         <v>99.580146</v>
@@ -4674,7 +4674,7 @@
       </c>
       <c r="P58" s="6" t="n"/>
       <c r="Q58" s="6" t="n">
-        <v>99.72409399999999</v>
+        <v>99.72310299999999</v>
       </c>
       <c r="R58" s="6" t="n">
         <v>99.337064</v>
@@ -4752,7 +4752,7 @@
       </c>
       <c r="P59" s="9" t="n"/>
       <c r="Q59" s="9" t="n">
-        <v>99.507971</v>
+        <v>99.50620600000001</v>
       </c>
       <c r="R59" s="9" t="n">
         <v>99.12311099999999</v>
@@ -4830,7 +4830,7 @@
       </c>
       <c r="P60" s="6" t="n"/>
       <c r="Q60" s="6" t="n">
-        <v>99.353987</v>
+        <v>99.35167</v>
       </c>
       <c r="R60" s="6" t="n">
         <v>98.923866</v>
@@ -4908,7 +4908,7 @@
       </c>
       <c r="P61" s="9" t="n"/>
       <c r="Q61" s="9" t="n">
-        <v>99.230988</v>
+        <v>99.22823</v>
       </c>
       <c r="R61" s="9" t="n">
         <v>98.720533</v>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="P62" s="6" t="n"/>
       <c r="Q62" s="6" t="n">
-        <v>99.061644</v>
+        <v>99.058279</v>
       </c>
       <c r="R62" s="6" t="n">
         <v>98.492166</v>
@@ -5064,7 +5064,7 @@
       </c>
       <c r="P63" s="9" t="n"/>
       <c r="Q63" s="9" t="n">
-        <v>98.792233</v>
+        <v>98.787902</v>
       </c>
       <c r="R63" s="9" t="n">
         <v>98.224097</v>
@@ -5142,7 +5142,7 @@
       </c>
       <c r="P64" s="6" t="n"/>
       <c r="Q64" s="6" t="n">
-        <v>98.440395</v>
+        <v>98.434803</v>
       </c>
       <c r="R64" s="6" t="n">
         <v>97.916408</v>
@@ -5220,7 +5220,7 @@
       </c>
       <c r="P65" s="9" t="n"/>
       <c r="Q65" s="9" t="n">
-        <v>98.03715200000001</v>
+        <v>98.030115</v>
       </c>
       <c r="R65" s="9" t="n">
         <v>97.58654799999999</v>
@@ -5298,7 +5298,7 @@
       </c>
       <c r="P66" s="6" t="n"/>
       <c r="Q66" s="6" t="n">
-        <v>97.649612</v>
+        <v>97.64118499999999</v>
       </c>
       <c r="R66" s="6" t="n">
         <v>97.272071</v>
@@ -5376,7 +5376,7 @@
       </c>
       <c r="P67" s="9" t="n"/>
       <c r="Q67" s="9" t="n">
-        <v>97.353213</v>
+        <v>97.34372500000001</v>
       </c>
       <c r="R67" s="9" t="n">
         <v>97.02912000000001</v>
@@ -5454,7 +5454,7 @@
       </c>
       <c r="P68" s="6" t="n"/>
       <c r="Q68" s="6" t="n">
-        <v>97.164259</v>
+        <v>97.154093</v>
       </c>
       <c r="R68" s="6" t="n">
         <v>96.90107</v>
@@ -5532,7 +5532,7 @@
       </c>
       <c r="P69" s="9" t="n"/>
       <c r="Q69" s="9" t="n">
-        <v>97.092613</v>
+        <v>97.08219</v>
       </c>
       <c r="R69" s="9" t="n">
         <v>96.918099</v>
@@ -5610,7 +5610,7 @@
       </c>
       <c r="P70" s="6" t="n"/>
       <c r="Q70" s="6" t="n">
-        <v>97.145049</v>
+        <v>97.13481400000001</v>
       </c>
       <c r="R70" s="6" t="n">
         <v>97.09395600000001</v>
@@ -5688,7 +5688,7 @@
       </c>
       <c r="P71" s="9" t="n"/>
       <c r="Q71" s="9" t="n">
-        <v>97.349131</v>
+        <v>97.339628</v>
       </c>
       <c r="R71" s="9" t="n">
         <v>97.425248</v>
@@ -5766,7 +5766,7 @@
       </c>
       <c r="P72" s="6" t="n"/>
       <c r="Q72" s="6" t="n">
-        <v>97.69759999999999</v>
+        <v>97.689345</v>
       </c>
       <c r="R72" s="6" t="n">
         <v>97.886003</v>
@@ -5844,7 +5844,7 @@
       </c>
       <c r="P73" s="9" t="n"/>
       <c r="Q73" s="9" t="n">
-        <v>98.14623899999999</v>
+        <v>98.13959199999999</v>
       </c>
       <c r="R73" s="9" t="n">
         <v>98.40803200000001</v>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="P74" s="6" t="n"/>
       <c r="Q74" s="6" t="n">
-        <v>98.630112</v>
+        <v>98.625198</v>
       </c>
       <c r="R74" s="6" t="n">
         <v>98.889538</v>
@@ -6000,7 +6000,7 @@
       </c>
       <c r="P75" s="9" t="n"/>
       <c r="Q75" s="9" t="n">
-        <v>99.083766</v>
+        <v>99.080479</v>
       </c>
       <c r="R75" s="9" t="n">
         <v>99.297634</v>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="P76" s="6" t="n"/>
       <c r="Q76" s="6" t="n">
-        <v>99.411209</v>
+        <v>99.40909499999999</v>
       </c>
       <c r="R76" s="6" t="n">
         <v>99.63561900000001</v>
@@ -6156,7 +6156,7 @@
       </c>
       <c r="P77" s="9" t="n"/>
       <c r="Q77" s="9" t="n">
-        <v>99.565517</v>
+        <v>99.563956</v>
       </c>
       <c r="R77" s="9" t="n">
         <v>99.926952</v>
@@ -6236,7 +6236,7 @@
       </c>
       <c r="P78" s="6" t="n"/>
       <c r="Q78" s="6" t="n">
-        <v>99.54959599999999</v>
+        <v>99.547978</v>
       </c>
       <c r="R78" s="6" t="n">
         <v>100.200313</v>
@@ -6316,7 +6316,7 @@
       </c>
       <c r="P79" s="9" t="n"/>
       <c r="Q79" s="9" t="n">
-        <v>99.37104600000001</v>
+        <v>99.368788</v>
       </c>
       <c r="R79" s="9" t="n">
         <v>100.480278</v>
@@ -6396,7 +6396,7 @@
       </c>
       <c r="P80" s="6" t="n"/>
       <c r="Q80" s="6" t="n">
-        <v>99.10888</v>
+        <v>99.105682</v>
       </c>
       <c r="R80" s="6" t="n">
         <v>100.766848</v>
@@ -6476,7 +6476,7 @@
       </c>
       <c r="P81" s="9" t="n"/>
       <c r="Q81" s="9" t="n">
-        <v>98.88258</v>
+        <v>98.87857099999999</v>
       </c>
       <c r="R81" s="9" t="n">
         <v>101.051878</v>
@@ -6556,7 +6556,7 @@
       </c>
       <c r="P82" s="6" t="n"/>
       <c r="Q82" s="6" t="n">
-        <v>98.798497</v>
+        <v>98.79418699999999</v>
       </c>
       <c r="R82" s="6" t="n">
         <v>101.340214</v>
@@ -6636,7 +6636,7 @@
       </c>
       <c r="P83" s="9" t="n"/>
       <c r="Q83" s="9" t="n">
-        <v>98.901359</v>
+        <v>98.897417</v>
       </c>
       <c r="R83" s="9" t="n">
         <v>101.641237</v>
@@ -6716,7 +6716,7 @@
       </c>
       <c r="P84" s="6" t="n"/>
       <c r="Q84" s="6" t="n">
-        <v>99.208271</v>
+        <v>99.205429</v>
       </c>
       <c r="R84" s="6" t="n">
         <v>101.956728</v>
@@ -6796,7 +6796,7 @@
       </c>
       <c r="P85" s="9" t="n"/>
       <c r="Q85" s="9" t="n">
-        <v>99.69279299999999</v>
+        <v>99.691687</v>
       </c>
       <c r="R85" s="9" t="n">
         <v>102.269787</v>
@@ -6876,7 +6876,7 @@
       </c>
       <c r="P86" s="6" t="n"/>
       <c r="Q86" s="6" t="n">
-        <v>100.323211</v>
+        <v>100.324364</v>
       </c>
       <c r="R86" s="6" t="n">
         <v>102.555633</v>
@@ -6956,7 +6956,7 @@
       </c>
       <c r="P87" s="9" t="n"/>
       <c r="Q87" s="9" t="n">
-        <v>101.046648</v>
+        <v>101.050393</v>
       </c>
       <c r="R87" s="9" t="n">
         <v>102.78546</v>
@@ -7036,7 +7036,7 @@
       </c>
       <c r="P88" s="6" t="n"/>
       <c r="Q88" s="6" t="n">
-        <v>101.828367</v>
+        <v>101.834913</v>
       </c>
       <c r="R88" s="6" t="n">
         <v>102.943042</v>
@@ -7116,7 +7116,7 @@
       </c>
       <c r="P89" s="9" t="n"/>
       <c r="Q89" s="9" t="n">
-        <v>102.663793</v>
+        <v>102.673333</v>
       </c>
       <c r="R89" s="9" t="n">
         <v>103.031257</v>
@@ -7198,7 +7198,7 @@
       </c>
       <c r="P90" s="6" t="n"/>
       <c r="Q90" s="6" t="n">
-        <v>103.560733</v>
+        <v>103.573488</v>
       </c>
       <c r="R90" s="6" t="n">
         <v>103.06476</v>
@@ -7280,7 +7280,7 @@
       </c>
       <c r="P91" s="9" t="n"/>
       <c r="Q91" s="9" t="n">
-        <v>104.486584</v>
+        <v>104.502658</v>
       </c>
       <c r="R91" s="9" t="n">
         <v>103.056789</v>
@@ -7362,7 +7362,7 @@
       </c>
       <c r="P92" s="6" t="n"/>
       <c r="Q92" s="6" t="n">
-        <v>105.377068</v>
+        <v>105.396336</v>
       </c>
       <c r="R92" s="6" t="n">
         <v>103.01117</v>
@@ -7444,7 +7444,7 @@
       </c>
       <c r="P93" s="9" t="n"/>
       <c r="Q93" s="9" t="n">
-        <v>106.165579</v>
+        <v>106.187678</v>
       </c>
       <c r="R93" s="9" t="n">
         <v>102.925817</v>
@@ -7526,7 +7526,7 @@
       </c>
       <c r="P94" s="6" t="n"/>
       <c r="Q94" s="6" t="n">
-        <v>106.780635</v>
+        <v>106.804946</v>
       </c>
       <c r="R94" s="6" t="n">
         <v>102.806465</v>
@@ -7608,7 +7608,7 @@
       </c>
       <c r="P95" s="9" t="n"/>
       <c r="Q95" s="9" t="n">
-        <v>107.143222</v>
+        <v>107.168842</v>
       </c>
       <c r="R95" s="9" t="n">
         <v>102.655164</v>
@@ -7690,7 +7690,7 @@
       </c>
       <c r="P96" s="6" t="n"/>
       <c r="Q96" s="6" t="n">
-        <v>107.151878</v>
+        <v>107.177542</v>
       </c>
       <c r="R96" s="6" t="n">
         <v>102.471786</v>
@@ -7772,7 +7772,7 @@
       </c>
       <c r="P97" s="9" t="n"/>
       <c r="Q97" s="9" t="n">
-        <v>106.667278</v>
+        <v>106.691217</v>
       </c>
       <c r="R97" s="9" t="n">
         <v>102.264885</v>
@@ -7854,7 +7854,7 @@
       </c>
       <c r="P98" s="6" t="n"/>
       <c r="Q98" s="6" t="n">
-        <v>105.635126</v>
+        <v>105.655374</v>
       </c>
       <c r="R98" s="6" t="n">
         <v>102.04272</v>
@@ -7936,7 +7936,7 @@
       </c>
       <c r="P99" s="9" t="n"/>
       <c r="Q99" s="9" t="n">
-        <v>104.188999</v>
+        <v>104.204056</v>
       </c>
       <c r="R99" s="9" t="n">
         <v>101.803778</v>
@@ -8018,7 +8018,7 @@
       </c>
       <c r="P100" s="6" t="n"/>
       <c r="Q100" s="6" t="n">
-        <v>102.610306</v>
+        <v>102.619693</v>
       </c>
       <c r="R100" s="6" t="n">
         <v>101.546291</v>
@@ -8100,7 +8100,7 @@
       </c>
       <c r="P101" s="9" t="n"/>
       <c r="Q101" s="9" t="n">
-        <v>101.243674</v>
+        <v>101.24815</v>
       </c>
       <c r="R101" s="9" t="n">
         <v>101.255835</v>
@@ -8182,7 +8182,7 @@
       </c>
       <c r="P102" s="6" t="n"/>
       <c r="Q102" s="6" t="n">
-        <v>100.251374</v>
+        <v>100.252283</v>
       </c>
       <c r="R102" s="6" t="n">
         <v>100.906186</v>
@@ -8264,7 +8264,7 @@
       </c>
       <c r="P103" s="9" t="n"/>
       <c r="Q103" s="9" t="n">
-        <v>99.58345</v>
+        <v>99.581957</v>
       </c>
       <c r="R103" s="9" t="n">
         <v>100.518501</v>
@@ -8346,7 +8346,7 @@
       </c>
       <c r="P104" s="6" t="n"/>
       <c r="Q104" s="6" t="n">
-        <v>99.105767</v>
+        <v>99.102558</v>
       </c>
       <c r="R104" s="6" t="n">
         <v>100.140638</v>
@@ -8428,7 +8428,7 @@
       </c>
       <c r="P105" s="9" t="n"/>
       <c r="Q105" s="9" t="n">
-        <v>98.783759</v>
+        <v>98.779393</v>
       </c>
       <c r="R105" s="9" t="n">
         <v>99.80798900000001</v>
@@ -8510,7 +8510,7 @@
       </c>
       <c r="P106" s="6" t="n"/>
       <c r="Q106" s="6" t="n">
-        <v>98.600138</v>
+        <v>98.595113</v>
       </c>
       <c r="R106" s="6" t="n">
         <v>99.54019</v>
@@ -8592,7 +8592,7 @@
       </c>
       <c r="P107" s="9" t="n"/>
       <c r="Q107" s="9" t="n">
-        <v>98.480902</v>
+        <v>98.47545</v>
       </c>
       <c r="R107" s="9" t="n">
         <v>99.34128800000001</v>
@@ -8674,7 +8674,7 @@
       </c>
       <c r="P108" s="6" t="n"/>
       <c r="Q108" s="6" t="n">
-        <v>98.389815</v>
+        <v>98.38403700000001</v>
       </c>
       <c r="R108" s="6" t="n">
         <v>99.206305</v>
@@ -8756,7 +8756,7 @@
       </c>
       <c r="P109" s="9" t="n"/>
       <c r="Q109" s="9" t="n">
-        <v>98.307175</v>
+        <v>98.301102</v>
       </c>
       <c r="R109" s="9" t="n">
         <v>99.12282399999999</v>
@@ -8838,7 +8838,7 @@
       </c>
       <c r="P110" s="6" t="n"/>
       <c r="Q110" s="6" t="n">
-        <v>98.21720999999999</v>
+        <v>98.210815</v>
       </c>
       <c r="R110" s="6" t="n">
         <v>99.072012</v>
@@ -8920,7 +8920,7 @@
       </c>
       <c r="P111" s="9" t="n"/>
       <c r="Q111" s="9" t="n">
-        <v>98.118065</v>
+        <v>98.111315</v>
       </c>
       <c r="R111" s="9" t="n">
         <v>99.035623</v>
@@ -9002,7 +9002,7 @@
       </c>
       <c r="P112" s="6" t="n"/>
       <c r="Q112" s="6" t="n">
-        <v>98.01443500000001</v>
+        <v>98.00731399999999</v>
       </c>
       <c r="R112" s="6" t="n">
         <v>99.00669600000001</v>
@@ -9084,7 +9084,7 @@
       </c>
       <c r="P113" s="9" t="n"/>
       <c r="Q113" s="9" t="n">
-        <v>97.906109</v>
+        <v>97.8986</v>
       </c>
       <c r="R113" s="9" t="n">
         <v>98.993583</v>
@@ -9166,7 +9166,7 @@
       </c>
       <c r="P114" s="6" t="n"/>
       <c r="Q114" s="6" t="n">
-        <v>97.853639</v>
+        <v>97.84594199999999</v>
       </c>
       <c r="R114" s="6" t="n">
         <v>99.01441800000001</v>
@@ -9248,7 +9248,7 @@
       </c>
       <c r="P115" s="9" t="n"/>
       <c r="Q115" s="9" t="n">
-        <v>97.917035</v>
+        <v>97.909565</v>
       </c>
       <c r="R115" s="9" t="n">
         <v>99.082059</v>
@@ -9330,7 +9330,7 @@
       </c>
       <c r="P116" s="6" t="n"/>
       <c r="Q116" s="6" t="n">
-        <v>98.129069</v>
+        <v>98.12236</v>
       </c>
       <c r="R116" s="6" t="n">
         <v>99.194333</v>
@@ -9412,7 +9412,7 @@
       </c>
       <c r="P117" s="9" t="n"/>
       <c r="Q117" s="9" t="n">
-        <v>98.464539</v>
+        <v>98.45903199999999</v>
       </c>
       <c r="R117" s="9" t="n">
         <v>99.33959400000001</v>
@@ -9494,7 +9494,7 @@
       </c>
       <c r="P118" s="6" t="n"/>
       <c r="Q118" s="6" t="n">
-        <v>98.86287400000001</v>
+        <v>98.858795</v>
       </c>
       <c r="R118" s="6" t="n">
         <v>99.504352</v>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="P119" s="9" t="n"/>
       <c r="Q119" s="9" t="n">
-        <v>99.246559</v>
+        <v>99.243855</v>
       </c>
       <c r="R119" s="9" t="n">
         <v>99.67560400000001</v>
@@ -9658,7 +9658,7 @@
       </c>
       <c r="P120" s="6" t="n"/>
       <c r="Q120" s="6" t="n">
-        <v>99.549491</v>
+        <v>99.547873</v>
       </c>
       <c r="R120" s="6" t="n">
         <v>99.841067</v>
@@ -9740,7 +9740,7 @@
       </c>
       <c r="P121" s="9" t="n"/>
       <c r="Q121" s="9" t="n">
-        <v>99.74402600000001</v>
+        <v>99.743105</v>
       </c>
       <c r="R121" s="9" t="n">
         <v>99.987183</v>
@@ -9822,7 +9822,7 @@
       </c>
       <c r="P122" s="6" t="n"/>
       <c r="Q122" s="6" t="n">
-        <v>99.808858</v>
+        <v>99.80816900000001</v>
       </c>
       <c r="R122" s="6" t="n">
         <v>100.100228</v>
@@ -9904,7 +9904,7 @@
       </c>
       <c r="P123" s="9" t="n"/>
       <c r="Q123" s="9" t="n">
-        <v>99.760751</v>
+        <v>99.759891</v>
       </c>
       <c r="R123" s="9" t="n">
         <v>100.167511</v>
@@ -9986,7 +9986,7 @@
       </c>
       <c r="P124" s="6" t="n"/>
       <c r="Q124" s="6" t="n">
-        <v>99.66736</v>
+        <v>99.66616500000001</v>
       </c>
       <c r="R124" s="6" t="n">
         <v>100.183978</v>
@@ -10068,7 +10068,7 @@
       </c>
       <c r="P125" s="9" t="n"/>
       <c r="Q125" s="9" t="n">
-        <v>99.593937</v>
+        <v>99.592478</v>
       </c>
       <c r="R125" s="9" t="n">
         <v>100.156235</v>
@@ -10150,7 +10150,7 @@
       </c>
       <c r="P126" s="6" t="n"/>
       <c r="Q126" s="6" t="n">
-        <v>99.567795</v>
+        <v>99.566244</v>
       </c>
       <c r="R126" s="6" t="n">
         <v>100.10851</v>
@@ -10232,7 +10232,7 @@
       </c>
       <c r="P127" s="9" t="n"/>
       <c r="Q127" s="9" t="n">
-        <v>99.597928</v>
+        <v>99.596484</v>
       </c>
       <c r="R127" s="9" t="n">
         <v>100.06881</v>
@@ -10314,7 +10314,7 @@
       </c>
       <c r="P128" s="6" t="n"/>
       <c r="Q128" s="6" t="n">
-        <v>99.67031799999999</v>
+        <v>99.669134</v>
       </c>
       <c r="R128" s="6" t="n">
         <v>100.050184</v>
@@ -10396,7 +10396,7 @@
       </c>
       <c r="P129" s="9" t="n"/>
       <c r="Q129" s="9" t="n">
-        <v>99.753517</v>
+        <v>99.75263099999999</v>
       </c>
       <c r="R129" s="9" t="n">
         <v>100.052977</v>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="P130" s="6" t="n"/>
       <c r="Q130" s="6" t="n">
-        <v>99.7894</v>
+        <v>99.78864299999999</v>
       </c>
       <c r="R130" s="6" t="n">
         <v>100.072171</v>
@@ -10560,7 +10560,7 @@
       </c>
       <c r="P131" s="9" t="n"/>
       <c r="Q131" s="9" t="n">
-        <v>99.704002</v>
+        <v>99.702939</v>
       </c>
       <c r="R131" s="9" t="n">
         <v>100.101749</v>
@@ -10642,7 +10642,7 @@
       </c>
       <c r="P132" s="6" t="n"/>
       <c r="Q132" s="6" t="n">
-        <v>99.496607</v>
+        <v>99.4948</v>
       </c>
       <c r="R132" s="6" t="n">
         <v>100.134947</v>
@@ -10724,7 +10724,7 @@
       </c>
       <c r="P133" s="9" t="n"/>
       <c r="Q133" s="9" t="n">
-        <v>99.191838</v>
+        <v>99.188939</v>
       </c>
       <c r="R133" s="9" t="n">
         <v>100.161514</v>
@@ -10806,7 +10806,7 @@
       </c>
       <c r="P134" s="6" t="n"/>
       <c r="Q134" s="6" t="n">
-        <v>98.88020299999999</v>
+        <v>98.876188</v>
       </c>
       <c r="R134" s="6" t="n">
         <v>100.165945</v>
@@ -10888,7 +10888,7 @@
       </c>
       <c r="P135" s="9" t="n"/>
       <c r="Q135" s="9" t="n">
-        <v>98.639599</v>
+        <v>98.634722</v>
       </c>
       <c r="R135" s="9" t="n">
         <v>100.132803</v>
@@ -10970,7 +10970,7 @@
       </c>
       <c r="P136" s="6" t="n"/>
       <c r="Q136" s="6" t="n">
-        <v>98.48047800000001</v>
+        <v>98.47503</v>
       </c>
       <c r="R136" s="6" t="n">
         <v>100.056433</v>
@@ -11052,7 +11052,7 @@
       </c>
       <c r="P137" s="9" t="n"/>
       <c r="Q137" s="9" t="n">
-        <v>98.427623</v>
+        <v>98.421986</v>
       </c>
       <c r="R137" s="9" t="n">
         <v>99.95031299999999</v>
@@ -11134,7 +11134,7 @@
       </c>
       <c r="P138" s="6" t="n"/>
       <c r="Q138" s="6" t="n">
-        <v>98.51862300000001</v>
+        <v>98.513313</v>
       </c>
       <c r="R138" s="6" t="n">
         <v>99.839538</v>
@@ -11216,7 +11216,7 @@
       </c>
       <c r="P139" s="9" t="n"/>
       <c r="Q139" s="9" t="n">
-        <v>98.78081</v>
+        <v>98.776439</v>
       </c>
       <c r="R139" s="9" t="n">
         <v>99.744573</v>
@@ -11298,7 +11298,7 @@
       </c>
       <c r="P140" s="6" t="n"/>
       <c r="Q140" s="6" t="n">
-        <v>99.19443099999999</v>
+        <v>99.191543</v>
       </c>
       <c r="R140" s="6" t="n">
         <v>99.67737700000001</v>
@@ -11380,7 +11380,7 @@
       </c>
       <c r="P141" s="9" t="n"/>
       <c r="Q141" s="9" t="n">
-        <v>99.68305700000001</v>
+        <v>99.68192000000001</v>
       </c>
       <c r="R141" s="9" t="n">
         <v>99.640828</v>
@@ -11462,7 +11462,7 @@
       </c>
       <c r="P142" s="6" t="n"/>
       <c r="Q142" s="6" t="n">
-        <v>100.170586</v>
+        <v>100.171197</v>
       </c>
       <c r="R142" s="6" t="n">
         <v>99.62907</v>
@@ -11544,7 +11544,7 @@
       </c>
       <c r="P143" s="9" t="n"/>
       <c r="Q143" s="9" t="n">
-        <v>100.590688</v>
+        <v>100.592804</v>
       </c>
       <c r="R143" s="9" t="n">
         <v>99.630719</v>
@@ -11626,7 +11626,7 @@
       </c>
       <c r="P144" s="6" t="n"/>
       <c r="Q144" s="6" t="n">
-        <v>100.940242</v>
+        <v>100.943611</v>
       </c>
       <c r="R144" s="6" t="n">
         <v>99.632086</v>
@@ -11708,7 +11708,7 @@
       </c>
       <c r="P145" s="9" t="n"/>
       <c r="Q145" s="9" t="n">
-        <v>101.213714</v>
+        <v>101.218064</v>
       </c>
       <c r="R145" s="9" t="n">
         <v>99.617853</v>
@@ -11790,7 +11790,7 @@
       </c>
       <c r="P146" s="6" t="n"/>
       <c r="Q146" s="6" t="n">
-        <v>101.427154</v>
+        <v>101.432268</v>
       </c>
       <c r="R146" s="6" t="n">
         <v>99.57256700000001</v>
@@ -11872,7 +11872,7 @@
       </c>
       <c r="P147" s="9" t="n"/>
       <c r="Q147" s="9" t="n">
-        <v>101.611</v>
+        <v>101.616774</v>
       </c>
       <c r="R147" s="9" t="n">
         <v>99.486701</v>
@@ -11954,7 +11954,7 @@
       </c>
       <c r="P148" s="6" t="n"/>
       <c r="Q148" s="6" t="n">
-        <v>101.780354</v>
+        <v>101.786734</v>
       </c>
       <c r="R148" s="6" t="n">
         <v>99.36316600000001</v>
@@ -12036,7 +12036,7 @@
       </c>
       <c r="P149" s="9" t="n"/>
       <c r="Q149" s="9" t="n">
-        <v>101.951922</v>
+        <v>101.958917</v>
       </c>
       <c r="R149" s="9" t="n">
         <v>99.220337</v>
@@ -12118,7 +12118,7 @@
       </c>
       <c r="P150" s="6" t="n"/>
       <c r="Q150" s="6" t="n">
-        <v>102.114124</v>
+        <v>102.1217</v>
       </c>
       <c r="R150" s="6" t="n">
         <v>99.083035</v>
@@ -12200,7 +12200,7 @@
       </c>
       <c r="P151" s="9" t="n"/>
       <c r="Q151" s="9" t="n">
-        <v>102.210828</v>
+        <v>102.218751</v>
       </c>
       <c r="R151" s="9" t="n">
         <v>98.970873</v>
@@ -12282,7 +12282,7 @@
       </c>
       <c r="P152" s="6" t="n"/>
       <c r="Q152" s="6" t="n">
-        <v>102.178211</v>
+        <v>102.186018</v>
       </c>
       <c r="R152" s="6" t="n">
         <v>98.892762</v>
@@ -12364,7 +12364,7 @@
       </c>
       <c r="P153" s="9" t="n"/>
       <c r="Q153" s="9" t="n">
-        <v>101.995538</v>
+        <v>102.00269</v>
       </c>
       <c r="R153" s="9" t="n">
         <v>98.847004</v>
@@ -12446,7 +12446,7 @@
       </c>
       <c r="P154" s="6" t="n"/>
       <c r="Q154" s="6" t="n">
-        <v>101.677787</v>
+        <v>101.6838</v>
       </c>
       <c r="R154" s="6" t="n">
         <v>98.825093</v>
@@ -12528,7 +12528,7 @@
       </c>
       <c r="P155" s="9" t="n"/>
       <c r="Q155" s="9" t="n">
-        <v>101.264903</v>
+        <v>101.269436</v>
       </c>
       <c r="R155" s="9" t="n">
         <v>98.81035300000001</v>
@@ -12610,7 +12610,7 @@
       </c>
       <c r="P156" s="6" t="n"/>
       <c r="Q156" s="6" t="n">
-        <v>100.84855</v>
+        <v>100.851591</v>
       </c>
       <c r="R156" s="6" t="n">
         <v>98.787862</v>
@@ -12692,7 +12692,7 @@
       </c>
       <c r="P157" s="9" t="n"/>
       <c r="Q157" s="9" t="n">
-        <v>100.500391</v>
+        <v>100.502185</v>
       </c>
       <c r="R157" s="9" t="n">
         <v>98.75145999999999</v>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="P158" s="6" t="n"/>
       <c r="Q158" s="6" t="n">
-        <v>100.281196</v>
+        <v>100.282203</v>
       </c>
       <c r="R158" s="6" t="n">
         <v>98.702074</v>
@@ -12856,7 +12856,7 @@
       </c>
       <c r="P159" s="9" t="n"/>
       <c r="Q159" s="9" t="n">
-        <v>100.194326</v>
+        <v>100.195022</v>
       </c>
       <c r="R159" s="9" t="n">
         <v>98.639105</v>
@@ -12938,7 +12938,7 @@
       </c>
       <c r="P160" s="6" t="n"/>
       <c r="Q160" s="6" t="n">
-        <v>100.161221</v>
+        <v>100.161799</v>
       </c>
       <c r="R160" s="6" t="n">
         <v>98.55705</v>
@@ -13020,7 +13020,7 @@
       </c>
       <c r="P161" s="9" t="n"/>
       <c r="Q161" s="9" t="n">
-        <v>100.116365</v>
+        <v>100.116782</v>
       </c>
       <c r="R161" s="9" t="n">
         <v>98.459255</v>
@@ -13102,7 +13102,7 @@
       </c>
       <c r="P162" s="6" t="n"/>
       <c r="Q162" s="6" t="n">
-        <v>100.037181</v>
+        <v>100.037315</v>
       </c>
       <c r="R162" s="6" t="n">
         <v>98.357454</v>
@@ -13184,7 +13184,7 @@
       </c>
       <c r="P163" s="9" t="n"/>
       <c r="Q163" s="9" t="n">
-        <v>99.947171</v>
+        <v>99.94698200000001</v>
       </c>
       <c r="R163" s="9" t="n">
         <v>98.262426</v>
@@ -13266,7 +13266,7 @@
       </c>
       <c r="P164" s="6" t="n"/>
       <c r="Q164" s="6" t="n">
-        <v>99.87590899999999</v>
+        <v>99.87546399999999</v>
       </c>
       <c r="R164" s="6" t="n">
         <v>98.17930699999999</v>
@@ -13348,7 +13348,7 @@
       </c>
       <c r="P165" s="9" t="n"/>
       <c r="Q165" s="9" t="n">
-        <v>99.820103</v>
+        <v>99.819458</v>
       </c>
       <c r="R165" s="9" t="n">
         <v>98.105729</v>
@@ -13430,7 +13430,7 @@
       </c>
       <c r="P166" s="6" t="n"/>
       <c r="Q166" s="6" t="n">
-        <v>99.813124</v>
+        <v>99.812455</v>
       </c>
       <c r="R166" s="6" t="n">
         <v>98.038326</v>
@@ -13512,7 +13512,7 @@
       </c>
       <c r="P167" s="9" t="n"/>
       <c r="Q167" s="9" t="n">
-        <v>99.887991</v>
+        <v>99.88758900000001</v>
       </c>
       <c r="R167" s="9" t="n">
         <v>97.969256</v>
@@ -13594,7 +13594,7 @@
       </c>
       <c r="P168" s="6" t="n"/>
       <c r="Q168" s="6" t="n">
-        <v>100.053144</v>
+        <v>100.053334</v>
       </c>
       <c r="R168" s="6" t="n">
         <v>97.896126</v>
@@ -13676,7 +13676,7 @@
       </c>
       <c r="P169" s="9" t="n"/>
       <c r="Q169" s="9" t="n">
-        <v>100.298468</v>
+        <v>100.299538</v>
       </c>
       <c r="R169" s="9" t="n">
         <v>97.82019699999999</v>
@@ -13758,7 +13758,7 @@
       </c>
       <c r="P170" s="6" t="n"/>
       <c r="Q170" s="6" t="n">
-        <v>100.607789</v>
+        <v>100.609967</v>
       </c>
       <c r="R170" s="6" t="n">
         <v>97.746363</v>
@@ -13840,7 +13840,7 @@
       </c>
       <c r="P171" s="9" t="n"/>
       <c r="Q171" s="9" t="n">
-        <v>100.97425</v>
+        <v>100.977742</v>
       </c>
       <c r="R171" s="9" t="n">
         <v>97.680449</v>
@@ -13922,7 +13922,7 @@
       </c>
       <c r="P172" s="6" t="n"/>
       <c r="Q172" s="6" t="n">
-        <v>101.352183</v>
+        <v>101.35703</v>
       </c>
       <c r="R172" s="6" t="n">
         <v>97.626532</v>
@@ -14004,7 +14004,7 @@
       </c>
       <c r="P173" s="9" t="n"/>
       <c r="Q173" s="9" t="n">
-        <v>101.675228</v>
+        <v>101.681232</v>
       </c>
       <c r="R173" s="9" t="n">
         <v>97.590146</v>
@@ -14086,7 +14086,7 @@
       </c>
       <c r="P174" s="6" t="n"/>
       <c r="Q174" s="6" t="n">
-        <v>101.873339</v>
+        <v>101.880053</v>
       </c>
       <c r="R174" s="6" t="n">
         <v>97.591443</v>
@@ -14168,7 +14168,7 @@
       </c>
       <c r="P175" s="9" t="n"/>
       <c r="Q175" s="9" t="n">
-        <v>101.929007</v>
+        <v>101.935921</v>
       </c>
       <c r="R175" s="9" t="n">
         <v>97.638873</v>
@@ -14250,7 +14250,7 @@
       </c>
       <c r="P176" s="6" t="n"/>
       <c r="Q176" s="6" t="n">
-        <v>101.892081</v>
+        <v>101.898863</v>
       </c>
       <c r="R176" s="6" t="n">
         <v>97.720208</v>
@@ -14332,7 +14332,7 @@
       </c>
       <c r="P177" s="9" t="n"/>
       <c r="Q177" s="9" t="n">
-        <v>101.831877</v>
+        <v>101.838443</v>
       </c>
       <c r="R177" s="9" t="n">
         <v>97.795918</v>
@@ -14414,7 +14414,7 @@
       </c>
       <c r="P178" s="6" t="n"/>
       <c r="Q178" s="6" t="n">
-        <v>101.797768</v>
+        <v>101.804212</v>
       </c>
       <c r="R178" s="6" t="n">
         <v>97.851598</v>
@@ -14496,7 +14496,7 @@
       </c>
       <c r="P179" s="9" t="n"/>
       <c r="Q179" s="9" t="n">
-        <v>101.792885</v>
+        <v>101.799311</v>
       </c>
       <c r="R179" s="9" t="n">
         <v>97.908799</v>
@@ -14578,7 +14578,7 @@
       </c>
       <c r="P180" s="6" t="n"/>
       <c r="Q180" s="6" t="n">
-        <v>101.815146</v>
+        <v>101.821652</v>
       </c>
       <c r="R180" s="6" t="n">
         <v>97.999133</v>
@@ -14660,7 +14660,7 @@
       </c>
       <c r="P181" s="9" t="n"/>
       <c r="Q181" s="9" t="n">
-        <v>101.804005</v>
+        <v>101.810471</v>
       </c>
       <c r="R181" s="9" t="n">
         <v>98.171583</v>
@@ -14742,7 +14742,7 @@
       </c>
       <c r="P182" s="6" t="n"/>
       <c r="Q182" s="6" t="n">
-        <v>101.680889</v>
+        <v>101.686913</v>
       </c>
       <c r="R182" s="6" t="n">
         <v>98.494057</v>
@@ -14824,7 +14824,7 @@
       </c>
       <c r="P183" s="9" t="n"/>
       <c r="Q183" s="9" t="n">
-        <v>101.396729</v>
+        <v>101.401735</v>
       </c>
       <c r="R183" s="9" t="n">
         <v>99.030894</v>
@@ -14906,7 +14906,7 @@
       </c>
       <c r="P184" s="6" t="n"/>
       <c r="Q184" s="6" t="n">
-        <v>100.945133</v>
+        <v>100.948521</v>
       </c>
       <c r="R184" s="6" t="n">
         <v>99.816804</v>
@@ -14988,7 +14988,7 @@
       </c>
       <c r="P185" s="9" t="n"/>
       <c r="Q185" s="9" t="n">
-        <v>100.340606</v>
+        <v>100.341827</v>
       </c>
       <c r="R185" s="9" t="n">
         <v>100.815363</v>
@@ -15070,7 +15070,7 @@
       </c>
       <c r="P186" s="6" t="n"/>
       <c r="Q186" s="6" t="n">
-        <v>99.656263</v>
+        <v>99.65503099999999</v>
       </c>
       <c r="R186" s="6" t="n">
         <v>101.863362</v>
@@ -15152,7 +15152,7 @@
       </c>
       <c r="P187" s="9" t="n"/>
       <c r="Q187" s="9" t="n">
-        <v>99.016271</v>
+        <v>99.012745</v>
       </c>
       <c r="R187" s="9" t="n">
         <v>102.738096</v>
@@ -15234,7 +15234,7 @@
       </c>
       <c r="P188" s="6" t="n"/>
       <c r="Q188" s="6" t="n">
-        <v>98.558041</v>
+        <v>98.55287300000001</v>
       </c>
       <c r="R188" s="6" t="n">
         <v>103.273818</v>
@@ -15316,7 +15316,7 @@
       </c>
       <c r="P189" s="9" t="n"/>
       <c r="Q189" s="9" t="n">
-        <v>98.295478</v>
+        <v>98.28936899999999</v>
       </c>
       <c r="R189" s="9" t="n">
         <v>103.445088</v>
@@ -15398,7 +15398,7 @@
       </c>
       <c r="P190" s="6" t="n"/>
       <c r="Q190" s="6" t="n">
-        <v>98.211574</v>
+        <v>98.20516499999999</v>
       </c>
       <c r="R190" s="6" t="n">
         <v>103.356836</v>
@@ -15480,7 +15480,7 @@
       </c>
       <c r="P191" s="9" t="n"/>
       <c r="Q191" s="9" t="n">
-        <v>98.273008</v>
+        <v>98.266819</v>
       </c>
       <c r="R191" s="9" t="n">
         <v>103.168145</v>
@@ -15562,7 +15562,7 @@
       </c>
       <c r="P192" s="6" t="n"/>
       <c r="Q192" s="6" t="n">
-        <v>98.4109</v>
+        <v>98.405205</v>
       </c>
       <c r="R192" s="6" t="n">
         <v>102.986595</v>
@@ -15644,7 +15644,7 @@
       </c>
       <c r="P193" s="9" t="n"/>
       <c r="Q193" s="9" t="n">
-        <v>98.56554800000001</v>
+        <v>98.560407</v>
       </c>
       <c r="R193" s="9" t="n">
         <v>102.894306</v>
@@ -15726,7 +15726,7 @@
       </c>
       <c r="P194" s="6" t="n"/>
       <c r="Q194" s="6" t="n">
-        <v>98.708696</v>
+        <v>98.704069</v>
       </c>
       <c r="R194" s="6" t="n">
         <v>102.919843</v>
@@ -15808,7 +15808,7 @@
       </c>
       <c r="P195" s="9" t="n"/>
       <c r="Q195" s="9" t="n">
-        <v>98.85575900000001</v>
+        <v>98.851658</v>
       </c>
       <c r="R195" s="9" t="n">
         <v>103.035263</v>
@@ -15890,7 +15890,7 @@
       </c>
       <c r="P196" s="6" t="n"/>
       <c r="Q196" s="6" t="n">
-        <v>99.01858199999999</v>
+        <v>99.01506500000001</v>
       </c>
       <c r="R196" s="6" t="n">
         <v>103.151231</v>
@@ -15972,7 +15972,7 @@
       </c>
       <c r="P197" s="9" t="n"/>
       <c r="Q197" s="9" t="n">
-        <v>99.164647</v>
+        <v>99.161653</v>
       </c>
       <c r="R197" s="9" t="n">
         <v>103.155249</v>
@@ -16054,7 +16054,7 @@
       </c>
       <c r="P198" s="6" t="n"/>
       <c r="Q198" s="6" t="n">
-        <v>99.27675600000001</v>
+        <v>99.274164</v>
       </c>
       <c r="R198" s="6" t="n">
         <v>103.028527</v>
@@ -16136,7 +16136,7 @@
       </c>
       <c r="P199" s="9" t="n"/>
       <c r="Q199" s="9" t="n">
-        <v>99.34424</v>
+        <v>99.34189000000001</v>
       </c>
       <c r="R199" s="9" t="n">
         <v>102.806429</v>
@@ -16218,7 +16218,7 @@
       </c>
       <c r="P200" s="6" t="n"/>
       <c r="Q200" s="6" t="n">
-        <v>99.38457099999999</v>
+        <v>99.38236499999999</v>
       </c>
       <c r="R200" s="6" t="n">
         <v>102.52797</v>
@@ -16300,7 +16300,7 @@
       </c>
       <c r="P201" s="9" t="n"/>
       <c r="Q201" s="9" t="n">
-        <v>99.390698</v>
+        <v>99.388514</v>
       </c>
       <c r="R201" s="9" t="n">
         <v>102.227779</v>
@@ -16382,7 +16382,7 @@
       </c>
       <c r="P202" s="6" t="n"/>
       <c r="Q202" s="6" t="n">
-        <v>99.36143</v>
+        <v>99.35914200000001</v>
       </c>
       <c r="R202" s="6" t="n">
         <v>101.946043</v>
@@ -16464,7 +16464,7 @@
       </c>
       <c r="P203" s="9" t="n"/>
       <c r="Q203" s="9" t="n">
-        <v>99.307081</v>
+        <v>99.304597</v>
       </c>
       <c r="R203" s="9" t="n">
         <v>101.705157</v>
@@ -16546,7 +16546,7 @@
       </c>
       <c r="P204" s="6" t="n"/>
       <c r="Q204" s="6" t="n">
-        <v>99.246447</v>
+        <v>99.243746</v>
       </c>
       <c r="R204" s="6" t="n">
         <v>101.504583</v>
@@ -16628,7 +16628,7 @@
       </c>
       <c r="P205" s="9" t="n"/>
       <c r="Q205" s="9" t="n">
-        <v>99.20444999999999</v>
+        <v>99.201599</v>
       </c>
       <c r="R205" s="9" t="n">
         <v>101.336843</v>
@@ -16710,7 +16710,7 @@
       </c>
       <c r="P206" s="6" t="n"/>
       <c r="Q206" s="6" t="n">
-        <v>99.17540099999999</v>
+        <v>99.172445</v>
       </c>
       <c r="R206" s="6" t="n">
         <v>101.19977</v>
@@ -16792,7 +16792,7 @@
       </c>
       <c r="P207" s="9" t="n"/>
       <c r="Q207" s="9" t="n">
-        <v>99.171048</v>
+        <v>99.168077</v>
       </c>
       <c r="R207" s="9" t="n">
         <v>101.078342</v>
@@ -16874,7 +16874,7 @@
       </c>
       <c r="P208" s="6" t="n"/>
       <c r="Q208" s="6" t="n">
-        <v>99.204382</v>
+        <v>99.20153000000001</v>
       </c>
       <c r="R208" s="6" t="n">
         <v>100.944957</v>
@@ -16956,7 +16956,7 @@
       </c>
       <c r="P209" s="9" t="n"/>
       <c r="Q209" s="9" t="n">
-        <v>99.28100499999999</v>
+        <v>99.27842800000001</v>
       </c>
       <c r="R209" s="9" t="n">
         <v>100.778926</v>
@@ -17038,7 +17038,7 @@
       </c>
       <c r="P210" s="6" t="n"/>
       <c r="Q210" s="6" t="n">
-        <v>99.403109</v>
+        <v>99.40097</v>
       </c>
       <c r="R210" s="6" t="n">
         <v>100.596083</v>
@@ -17120,7 +17120,7 @@
       </c>
       <c r="P211" s="9" t="n"/>
       <c r="Q211" s="9" t="n">
-        <v>99.55976699999999</v>
+        <v>99.558189</v>
       </c>
       <c r="R211" s="9" t="n">
         <v>100.418932</v>
@@ -17202,7 +17202,7 @@
       </c>
       <c r="P212" s="6" t="n"/>
       <c r="Q212" s="6" t="n">
-        <v>99.749802</v>
+        <v>99.74890499999999</v>
       </c>
       <c r="R212" s="6" t="n">
         <v>100.258698</v>
@@ -17284,7 +17284,7 @@
       </c>
       <c r="P213" s="9" t="n"/>
       <c r="Q213" s="9" t="n">
-        <v>99.990821</v>
+        <v>99.99078799999999</v>
       </c>
       <c r="R213" s="9" t="n">
         <v>100.108117</v>
@@ -17366,7 +17366,7 @@
       </c>
       <c r="P214" s="6" t="n"/>
       <c r="Q214" s="6" t="n">
-        <v>100.287335</v>
+        <v>100.288365</v>
       </c>
       <c r="R214" s="6" t="n">
         <v>99.96768299999999</v>
@@ -17448,7 +17448,7 @@
       </c>
       <c r="P215" s="9" t="n"/>
       <c r="Q215" s="9" t="n">
-        <v>100.610424</v>
+        <v>100.612611</v>
       </c>
       <c r="R215" s="9" t="n">
         <v>99.837991</v>
@@ -17530,7 +17530,7 @@
       </c>
       <c r="P216" s="6" t="n"/>
       <c r="Q216" s="6" t="n">
-        <v>100.902453</v>
+        <v>100.905688</v>
       </c>
       <c r="R216" s="6" t="n">
         <v>99.721152</v>
@@ -17612,7 +17612,7 @@
       </c>
       <c r="P217" s="9" t="n"/>
       <c r="Q217" s="9" t="n">
-        <v>101.112802</v>
+        <v>101.116791</v>
       </c>
       <c r="R217" s="9" t="n">
         <v>99.62923600000001</v>
@@ -17694,7 +17694,7 @@
       </c>
       <c r="P218" s="6" t="n"/>
       <c r="Q218" s="6" t="n">
-        <v>101.24229</v>
+        <v>101.246742</v>
       </c>
       <c r="R218" s="6" t="n">
         <v>99.577082</v>
@@ -17776,7 +17776,7 @@
       </c>
       <c r="P219" s="9" t="n"/>
       <c r="Q219" s="9" t="n">
-        <v>101.278586</v>
+        <v>101.283169</v>
       </c>
       <c r="R219" s="9" t="n">
         <v>99.568145</v>
@@ -17858,7 +17858,7 @@
       </c>
       <c r="P220" s="6" t="n"/>
       <c r="Q220" s="6" t="n">
-        <v>101.254075</v>
+        <v>101.258569</v>
       </c>
       <c r="R220" s="6" t="n">
         <v>99.588961</v>
@@ -17940,7 +17940,7 @@
       </c>
       <c r="P221" s="9" t="n"/>
       <c r="Q221" s="9" t="n">
-        <v>101.168014</v>
+        <v>101.1722</v>
       </c>
       <c r="R221" s="9" t="n">
         <v>99.61055899999999</v>
@@ -18022,7 +18022,7 @@
       </c>
       <c r="P222" s="6" t="n"/>
       <c r="Q222" s="6" t="n">
-        <v>101.020104</v>
+        <v>101.02376</v>
       </c>
       <c r="R222" s="6" t="n">
         <v>99.644159</v>
@@ -18104,7 +18104,7 @@
       </c>
       <c r="P223" s="9" t="n"/>
       <c r="Q223" s="9" t="n">
-        <v>100.837332</v>
+        <v>100.840333</v>
       </c>
       <c r="R223" s="9" t="n">
         <v>99.703934</v>
@@ -18186,7 +18186,7 @@
       </c>
       <c r="P224" s="6" t="n"/>
       <c r="Q224" s="6" t="n">
-        <v>100.602289</v>
+        <v>100.604448</v>
       </c>
       <c r="R224" s="6" t="n">
         <v>99.791303</v>
@@ -18268,7 +18268,7 @@
       </c>
       <c r="P225" s="9" t="n"/>
       <c r="Q225" s="9" t="n">
-        <v>100.282961</v>
+        <v>100.283975</v>
       </c>
       <c r="R225" s="9" t="n">
         <v>99.918728</v>
@@ -18350,7 +18350,7 @@
       </c>
       <c r="P226" s="6" t="n"/>
       <c r="Q226" s="6" t="n">
-        <v>99.869989</v>
+        <v>99.869523</v>
       </c>
       <c r="R226" s="6" t="n">
         <v>100.105617</v>
@@ -18432,7 +18432,7 @@
       </c>
       <c r="P227" s="9" t="n"/>
       <c r="Q227" s="9" t="n">
-        <v>99.40459199999999</v>
+        <v>99.402458</v>
       </c>
       <c r="R227" s="9" t="n">
         <v>100.354757</v>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="P228" s="6" t="n"/>
       <c r="Q228" s="6" t="n">
-        <v>98.941974</v>
+        <v>98.938182</v>
       </c>
       <c r="R228" s="6" t="n">
         <v>100.643533</v>
@@ -18596,7 +18596,7 @@
       </c>
       <c r="P229" s="9" t="n"/>
       <c r="Q229" s="9" t="n">
-        <v>98.54958499999999</v>
+        <v>98.544387</v>
       </c>
       <c r="R229" s="9" t="n">
         <v>100.941378</v>
@@ -18678,7 +18678,7 @@
       </c>
       <c r="P230" s="6" t="n"/>
       <c r="Q230" s="6" t="n">
-        <v>98.331613</v>
+        <v>98.32563399999999</v>
       </c>
       <c r="R230" s="6" t="n">
         <v>101.18414</v>
@@ -18760,7 +18760,7 @@
       </c>
       <c r="P231" s="9" t="n"/>
       <c r="Q231" s="9" t="n">
-        <v>98.265986</v>
+        <v>98.259771</v>
       </c>
       <c r="R231" s="9" t="n">
         <v>101.292468</v>
@@ -18842,7 +18842,7 @@
       </c>
       <c r="P232" s="6" t="n"/>
       <c r="Q232" s="6" t="n">
-        <v>98.30688000000001</v>
+        <v>98.300811</v>
       </c>
       <c r="R232" s="6" t="n">
         <v>101.254237</v>
@@ -18924,7 +18924,7 @@
       </c>
       <c r="P233" s="9" t="n"/>
       <c r="Q233" s="9" t="n">
-        <v>98.45351700000001</v>
+        <v>98.447975</v>
       </c>
       <c r="R233" s="9" t="n">
         <v>101.099846</v>
@@ -19006,7 +19006,7 @@
       </c>
       <c r="P234" s="6" t="n"/>
       <c r="Q234" s="6" t="n">
-        <v>98.69708</v>
+        <v>98.69241</v>
       </c>
       <c r="R234" s="6" t="n">
         <v>100.869682</v>
@@ -19088,7 +19088,7 @@
       </c>
       <c r="P235" s="9" t="n"/>
       <c r="Q235" s="9" t="n">
-        <v>99.02433000000001</v>
+        <v>99.020833</v>
       </c>
       <c r="R235" s="9" t="n">
         <v>100.591827</v>
@@ -19170,7 +19170,7 @@
       </c>
       <c r="P236" s="6" t="n"/>
       <c r="Q236" s="6" t="n">
-        <v>99.387246</v>
+        <v>99.38505000000001</v>
       </c>
       <c r="R236" s="6" t="n">
         <v>100.29979</v>
@@ -19252,7 +19252,7 @@
       </c>
       <c r="P237" s="9" t="n"/>
       <c r="Q237" s="9" t="n">
-        <v>99.712446</v>
+        <v>99.711415</v>
       </c>
       <c r="R237" s="9" t="n">
         <v>100.031559</v>
@@ -19334,7 +19334,7 @@
       </c>
       <c r="P238" s="6" t="n"/>
       <c r="Q238" s="6" t="n">
-        <v>99.948785</v>
+        <v>99.948601</v>
       </c>
       <c r="R238" s="6" t="n">
         <v>99.818804</v>
@@ -19416,7 +19416,7 @@
       </c>
       <c r="P239" s="9" t="n"/>
       <c r="Q239" s="9" t="n">
-        <v>100.089676</v>
+        <v>100.089997</v>
       </c>
       <c r="R239" s="9" t="n">
         <v>99.668752</v>
@@ -19498,7 +19498,7 @@
       </c>
       <c r="P240" s="6" t="n"/>
       <c r="Q240" s="6" t="n">
-        <v>100.159501</v>
+        <v>100.160072</v>
       </c>
       <c r="R240" s="6" t="n">
         <v>99.56615499999999</v>
@@ -19580,7 +19580,7 @@
       </c>
       <c r="P241" s="9" t="n"/>
       <c r="Q241" s="9" t="n">
-        <v>100.233589</v>
+        <v>100.234426</v>
       </c>
       <c r="R241" s="9" t="n">
         <v>99.503038</v>
@@ -19662,7 +19662,7 @@
       </c>
       <c r="P242" s="6" t="n"/>
       <c r="Q242" s="6" t="n">
-        <v>100.374955</v>
+        <v>100.376299</v>
       </c>
       <c r="R242" s="6" t="n">
         <v>99.46426599999999</v>
@@ -19744,7 +19744,7 @@
       </c>
       <c r="P243" s="9" t="n"/>
       <c r="Q243" s="9" t="n">
-        <v>100.60819</v>
+        <v>100.61037</v>
       </c>
       <c r="R243" s="9" t="n">
         <v>99.436999</v>
@@ -19826,7 +19826,7 @@
       </c>
       <c r="P244" s="6" t="n"/>
       <c r="Q244" s="6" t="n">
-        <v>100.900397</v>
+        <v>100.903624</v>
       </c>
       <c r="R244" s="6" t="n">
         <v>99.404409</v>
@@ -19908,7 +19908,7 @@
       </c>
       <c r="P245" s="9" t="n"/>
       <c r="Q245" s="9" t="n">
-        <v>101.18183</v>
+        <v>101.186066</v>
       </c>
       <c r="R245" s="9" t="n">
         <v>99.371184</v>
@@ -19990,7 +19990,7 @@
       </c>
       <c r="P246" s="6" t="n"/>
       <c r="Q246" s="6" t="n">
-        <v>101.383522</v>
+        <v>101.388481</v>
       </c>
       <c r="R246" s="6" t="n">
         <v>99.345528</v>
@@ -20072,7 +20072,7 @@
       </c>
       <c r="P247" s="9" t="n"/>
       <c r="Q247" s="9" t="n">
-        <v>101.491861</v>
+        <v>101.497208</v>
       </c>
       <c r="R247" s="9" t="n">
         <v>99.333338</v>
@@ -20154,7 +20154,7 @@
       </c>
       <c r="P248" s="6" t="n"/>
       <c r="Q248" s="6" t="n">
-        <v>101.484281</v>
+        <v>101.4896</v>
       </c>
       <c r="R248" s="6" t="n">
         <v>99.340299</v>
@@ -20236,7 +20236,7 @@
       </c>
       <c r="P249" s="9" t="n"/>
       <c r="Q249" s="9" t="n">
-        <v>101.376545</v>
+        <v>101.381479</v>
       </c>
       <c r="R249" s="9" t="n">
         <v>99.368892</v>
@@ -20318,7 +20318,7 @@
       </c>
       <c r="P250" s="6" t="n"/>
       <c r="Q250" s="6" t="n">
-        <v>101.227509</v>
+        <v>101.231909</v>
       </c>
       <c r="R250" s="6" t="n">
         <v>99.40609499999999</v>
@@ -20400,7 +20400,7 @@
       </c>
       <c r="P251" s="9" t="n"/>
       <c r="Q251" s="9" t="n">
-        <v>101.080193</v>
+        <v>101.084064</v>
       </c>
       <c r="R251" s="9" t="n">
         <v>99.429134</v>
@@ -20482,7 +20482,7 @@
       </c>
       <c r="P252" s="6" t="n"/>
       <c r="Q252" s="6" t="n">
-        <v>100.912205</v>
+        <v>100.915474</v>
       </c>
       <c r="R252" s="6" t="n">
         <v>99.419318</v>
@@ -20564,7 +20564,7 @@
       </c>
       <c r="P253" s="9" t="n"/>
       <c r="Q253" s="9" t="n">
-        <v>100.724512</v>
+        <v>100.727109</v>
       </c>
       <c r="R253" s="9" t="n">
         <v>99.398242</v>
@@ -20646,7 +20646,7 @@
       </c>
       <c r="P254" s="6" t="n"/>
       <c r="Q254" s="6" t="n">
-        <v>100.516194</v>
+        <v>100.518045</v>
       </c>
       <c r="R254" s="6" t="n">
         <v>99.39018</v>
@@ -20728,7 +20728,7 @@
       </c>
       <c r="P255" s="9" t="n"/>
       <c r="Q255" s="9" t="n">
-        <v>100.306412</v>
+        <v>100.30751</v>
       </c>
       <c r="R255" s="9" t="n">
         <v>99.39808600000001</v>
@@ -20810,7 +20810,7 @@
       </c>
       <c r="P256" s="6" t="n"/>
       <c r="Q256" s="6" t="n">
-        <v>100.117372</v>
+        <v>100.117793</v>
       </c>
       <c r="R256" s="6" t="n">
         <v>99.410833</v>
@@ -20892,7 +20892,7 @@
       </c>
       <c r="P257" s="9" t="n"/>
       <c r="Q257" s="9" t="n">
-        <v>99.989724</v>
+        <v>99.989687</v>
       </c>
       <c r="R257" s="9" t="n">
         <v>99.422613</v>
@@ -20974,7 +20974,7 @@
       </c>
       <c r="P258" s="6" t="n"/>
       <c r="Q258" s="6" t="n">
-        <v>99.924504</v>
+        <v>99.924233</v>
       </c>
       <c r="R258" s="6" t="n">
         <v>99.42576</v>
@@ -21056,7 +21056,7 @@
       </c>
       <c r="P259" s="9" t="n"/>
       <c r="Q259" s="9" t="n">
-        <v>99.885246</v>
+        <v>99.884834</v>
       </c>
       <c r="R259" s="9" t="n">
         <v>99.39037500000001</v>
@@ -21138,7 +21138,7 @@
       </c>
       <c r="P260" s="6" t="n"/>
       <c r="Q260" s="6" t="n">
-        <v>99.872829</v>
+        <v>99.872373</v>
       </c>
       <c r="R260" s="6" t="n">
         <v>99.307137</v>
@@ -21220,7 +21220,7 @@
       </c>
       <c r="P261" s="9" t="n"/>
       <c r="Q261" s="9" t="n">
-        <v>99.887429</v>
+        <v>99.88702499999999</v>
       </c>
       <c r="R261" s="9" t="n">
         <v>99.189998</v>
@@ -21302,7 +21302,7 @@
       </c>
       <c r="P262" s="6" t="n"/>
       <c r="Q262" s="6" t="n">
-        <v>99.896699</v>
+        <v>99.89632899999999</v>
       </c>
       <c r="R262" s="6" t="n">
         <v>99.07001099999999</v>
@@ -21384,7 +21384,7 @@
       </c>
       <c r="P263" s="9" t="n"/>
       <c r="Q263" s="9" t="n">
-        <v>99.85391300000001</v>
+        <v>99.85338900000001</v>
       </c>
       <c r="R263" s="9" t="n">
         <v>98.97175900000001</v>
@@ -21466,7 +21466,7 @@
       </c>
       <c r="P264" s="6" t="n"/>
       <c r="Q264" s="6" t="n">
-        <v>99.745859</v>
+        <v>99.74494900000001</v>
       </c>
       <c r="R264" s="6" t="n">
         <v>98.900954</v>
@@ -21548,7 +21548,7 @@
       </c>
       <c r="P265" s="9" t="n"/>
       <c r="Q265" s="9" t="n">
-        <v>99.59824399999999</v>
+        <v>99.59680400000001</v>
       </c>
       <c r="R265" s="9" t="n">
         <v>98.84665200000001</v>
@@ -21630,7 +21630,7 @@
       </c>
       <c r="P266" s="6" t="n"/>
       <c r="Q266" s="6" t="n">
-        <v>99.466937</v>
+        <v>99.46502599999999</v>
       </c>
       <c r="R266" s="6" t="n">
         <v>98.795109</v>
@@ -21712,7 +21712,7 @@
       </c>
       <c r="P267" s="9" t="n"/>
       <c r="Q267" s="9" t="n">
-        <v>99.429259</v>
+        <v>99.42721299999999</v>
       </c>
       <c r="R267" s="9" t="n">
         <v>98.725313</v>
@@ -21794,7 +21794,7 @@
       </c>
       <c r="P268" s="6" t="n"/>
       <c r="Q268" s="6" t="n">
-        <v>99.50279999999999</v>
+        <v>99.501018</v>
       </c>
       <c r="R268" s="6" t="n">
         <v>98.640336</v>
@@ -21876,7 +21876,7 @@
       </c>
       <c r="P269" s="9" t="n"/>
       <c r="Q269" s="9" t="n">
-        <v>99.655947</v>
+        <v>99.654714</v>
       </c>
       <c r="R269" s="9" t="n">
         <v>98.562673</v>
@@ -21958,7 +21958,7 @@
       </c>
       <c r="P270" s="6" t="n"/>
       <c r="Q270" s="6" t="n">
-        <v>99.825416</v>
+        <v>99.82478999999999</v>
       </c>
       <c r="R270" s="6" t="n">
         <v>98.517076</v>
@@ -22040,7 +22040,7 @@
       </c>
       <c r="P271" s="9" t="n"/>
       <c r="Q271" s="9" t="n">
-        <v>99.94861299999999</v>
+        <v>99.94842800000001</v>
       </c>
       <c r="R271" s="9" t="n">
         <v>98.524092</v>
@@ -22122,7 +22122,7 @@
       </c>
       <c r="P272" s="6" t="n"/>
       <c r="Q272" s="6" t="n">
-        <v>99.987859</v>
+        <v>99.987815</v>
       </c>
       <c r="R272" s="6" t="n">
         <v>98.595952</v>
@@ -22204,7 +22204,7 @@
       </c>
       <c r="P273" s="9" t="n"/>
       <c r="Q273" s="9" t="n">
-        <v>99.90312299999999</v>
+        <v>99.902776</v>
       </c>
       <c r="R273" s="9" t="n">
         <v>98.73514299999999</v>
@@ -22286,7 +22286,7 @@
       </c>
       <c r="P274" s="6" t="n"/>
       <c r="Q274" s="6" t="n">
-        <v>99.69028900000001</v>
+        <v>99.689179</v>
       </c>
       <c r="R274" s="6" t="n">
         <v>98.926821</v>
@@ -22368,7 +22368,7 @@
       </c>
       <c r="P275" s="9" t="n"/>
       <c r="Q275" s="9" t="n">
-        <v>99.38884899999999</v>
+        <v>99.386658</v>
       </c>
       <c r="R275" s="9" t="n">
         <v>99.136111</v>
@@ -22450,7 +22450,7 @@
       </c>
       <c r="P276" s="6" t="n"/>
       <c r="Q276" s="6" t="n">
-        <v>99.058719</v>
+        <v>99.055346</v>
       </c>
       <c r="R276" s="6" t="n">
         <v>99.336586</v>
@@ -22532,7 +22532,7 @@
       </c>
       <c r="P277" s="9" t="n"/>
       <c r="Q277" s="9" t="n">
-        <v>98.749514</v>
+        <v>98.74503199999999</v>
       </c>
       <c r="R277" s="9" t="n">
         <v>99.520489</v>
@@ -22614,7 +22614,7 @@
       </c>
       <c r="P278" s="6" t="n"/>
       <c r="Q278" s="6" t="n">
-        <v>98.480343</v>
+        <v>98.474896</v>
       </c>
       <c r="R278" s="6" t="n">
         <v>99.689502</v>
@@ -22696,7 +22696,7 @@
       </c>
       <c r="P279" s="9" t="n"/>
       <c r="Q279" s="9" t="n">
-        <v>98.272036</v>
+        <v>98.265843</v>
       </c>
       <c r="R279" s="9" t="n">
         <v>99.844058</v>
@@ -22778,7 +22778,7 @@
       </c>
       <c r="P280" s="6" t="n"/>
       <c r="Q280" s="6" t="n">
-        <v>98.114341</v>
+        <v>98.10758300000001</v>
       </c>
       <c r="R280" s="6" t="n">
         <v>99.99127799999999</v>
@@ -22860,7 +22860,7 @@
       </c>
       <c r="P281" s="9" t="n"/>
       <c r="Q281" s="9" t="n">
-        <v>97.99497700000001</v>
+        <v>97.987791</v>
       </c>
       <c r="R281" s="9" t="n">
         <v>100.137039</v>
@@ -22942,7 +22942,7 @@
       </c>
       <c r="P282" s="6" t="n"/>
       <c r="Q282" s="6" t="n">
-        <v>97.91765700000001</v>
+        <v>97.910194</v>
       </c>
       <c r="R282" s="6" t="n">
         <v>100.277755</v>
@@ -23024,7 +23024,7 @@
       </c>
       <c r="P283" s="9" t="n"/>
       <c r="Q283" s="9" t="n">
-        <v>97.899818</v>
+        <v>97.892291</v>
       </c>
       <c r="R283" s="9" t="n">
         <v>100.381355</v>
@@ -23106,7 +23106,7 @@
       </c>
       <c r="P284" s="6" t="n"/>
       <c r="Q284" s="6" t="n">
-        <v>97.95455200000001</v>
+        <v>97.947221</v>
       </c>
       <c r="R284" s="6" t="n">
         <v>100.418961</v>
@@ -23188,7 +23188,7 @@
       </c>
       <c r="P285" s="9" t="n"/>
       <c r="Q285" s="9" t="n">
-        <v>98.08153299999999</v>
+        <v>98.074657</v>
       </c>
       <c r="R285" s="9" t="n">
         <v>100.399905</v>
@@ -23270,7 +23270,7 @@
       </c>
       <c r="P286" s="6" t="n"/>
       <c r="Q286" s="6" t="n">
-        <v>98.251891</v>
+        <v>98.245626</v>
       </c>
       <c r="R286" s="6" t="n">
         <v>100.370286</v>
@@ -23352,7 +23352,7 @@
       </c>
       <c r="P287" s="9" t="n"/>
       <c r="Q287" s="9" t="n">
-        <v>98.442635</v>
+        <v>98.437054</v>
       </c>
       <c r="R287" s="9" t="n">
         <v>100.375719</v>
@@ -23434,7 +23434,7 @@
       </c>
       <c r="P288" s="6" t="n"/>
       <c r="Q288" s="6" t="n">
-        <v>98.634355</v>
+        <v>98.62946100000001</v>
       </c>
       <c r="R288" s="6" t="n">
         <v>100.422529</v>
@@ -23516,7 +23516,7 @@
       </c>
       <c r="P289" s="9" t="n"/>
       <c r="Q289" s="9" t="n">
-        <v>98.817407</v>
+        <v>98.813169</v>
       </c>
       <c r="R289" s="9" t="n">
         <v>100.50435</v>
@@ -23598,7 +23598,7 @@
       </c>
       <c r="P290" s="6" t="n"/>
       <c r="Q290" s="6" t="n">
-        <v>98.992075</v>
+        <v>98.988463</v>
       </c>
       <c r="R290" s="6" t="n">
         <v>100.591596</v>
@@ -23680,7 +23680,7 @@
       </c>
       <c r="P291" s="9" t="n"/>
       <c r="Q291" s="9" t="n">
-        <v>99.162947</v>
+        <v>99.159947</v>
       </c>
       <c r="R291" s="9" t="n">
         <v>100.657242</v>
@@ -23762,7 +23762,7 @@
       </c>
       <c r="P292" s="6" t="n"/>
       <c r="Q292" s="6" t="n">
-        <v>99.331231</v>
+        <v>99.328834</v>
       </c>
       <c r="R292" s="6" t="n">
         <v>100.686946</v>
@@ -23844,7 +23844,7 @@
       </c>
       <c r="P293" s="9" t="n"/>
       <c r="Q293" s="9" t="n">
-        <v>99.48864</v>
+        <v>99.486807</v>
       </c>
       <c r="R293" s="9" t="n">
         <v>100.693993</v>
@@ -23928,7 +23928,7 @@
         <v>98.536314</v>
       </c>
       <c r="Q294" s="6" t="n">
-        <v>99.62402400000001</v>
+        <v>99.622676</v>
       </c>
       <c r="R294" s="6" t="n">
         <v>100.697571</v>
@@ -24012,7 +24012,7 @@
         <v>98.69995299999999</v>
       </c>
       <c r="Q295" s="9" t="n">
-        <v>99.71603500000001</v>
+        <v>99.715018</v>
       </c>
       <c r="R295" s="9" t="n">
         <v>100.730465</v>
@@ -24096,7 +24096,7 @@
         <v>98.873496</v>
       </c>
       <c r="Q296" s="6" t="n">
-        <v>99.74854999999999</v>
+        <v>99.747649</v>
       </c>
       <c r="R296" s="6" t="n">
         <v>100.801992</v>
@@ -24180,7 +24180,7 @@
         <v>99.065544</v>
       </c>
       <c r="Q297" s="9" t="n">
-        <v>99.722976</v>
+        <v>99.72198299999999</v>
       </c>
       <c r="R297" s="9" t="n">
         <v>100.902695</v>
@@ -24264,7 +24264,7 @@
         <v>99.245644</v>
       </c>
       <c r="Q298" s="6" t="n">
-        <v>99.672467</v>
+        <v>99.67129300000001</v>
       </c>
       <c r="R298" s="6" t="n">
         <v>101.000309</v>
@@ -24348,7 +24348,7 @@
         <v>99.38448200000001</v>
       </c>
       <c r="Q299" s="9" t="n">
-        <v>99.62397900000001</v>
+        <v>99.622631</v>
       </c>
       <c r="R299" s="9" t="n">
         <v>101.059867</v>
@@ -24432,7 +24432,7 @@
         <v>99.48344899999999</v>
       </c>
       <c r="Q300" s="6" t="n">
-        <v>99.59861100000001</v>
+        <v>99.597172</v>
       </c>
       <c r="R300" s="6" t="n">
         <v>101.07148</v>
@@ -24516,7 +24516,7 @@
         <v>99.550466</v>
       </c>
       <c r="Q301" s="9" t="n">
-        <v>99.617704</v>
+        <v>99.61633399999999</v>
       </c>
       <c r="R301" s="9" t="n">
         <v>101.033582</v>
@@ -24600,7 +24600,7 @@
         <v>99.604377</v>
       </c>
       <c r="Q302" s="6" t="n">
-        <v>99.685011</v>
+        <v>99.68388299999999</v>
       </c>
       <c r="R302" s="6" t="n">
         <v>100.956345</v>
@@ -24684,7 +24684,7 @@
         <v>99.661912</v>
       </c>
       <c r="Q303" s="9" t="n">
-        <v>99.780129</v>
+        <v>99.779341</v>
       </c>
       <c r="R303" s="9" t="n">
         <v>100.84879</v>
@@ -24768,7 +24768,7 @@
         <v>99.721756</v>
       </c>
       <c r="Q304" s="6" t="n">
-        <v>99.87445099999999</v>
+        <v>99.874002</v>
       </c>
       <c r="R304" s="6" t="n">
         <v>100.72533</v>
@@ -24852,7 +24852,7 @@
         <v>99.779448</v>
       </c>
       <c r="Q305" s="9" t="n">
-        <v>99.939657</v>
+        <v>99.939441</v>
       </c>
       <c r="R305" s="9" t="n">
         <v>100.601157</v>
@@ -24936,7 +24936,7 @@
         <v>99.838756</v>
       </c>
       <c r="Q306" s="6" t="n">
-        <v>99.950822</v>
+        <v>99.95064499999999</v>
       </c>
       <c r="R306" s="6" t="n">
         <v>100.491863</v>
@@ -25020,7 +25020,7 @@
         <v>99.90722100000001</v>
       </c>
       <c r="Q307" s="9" t="n">
-        <v>99.90555500000001</v>
+        <v>99.90521699999999</v>
       </c>
       <c r="R307" s="9" t="n">
         <v>100.396171</v>
@@ -25104,7 +25104,7 @@
         <v>99.98192899999999</v>
       </c>
       <c r="Q308" s="6" t="n">
-        <v>99.820559</v>
+        <v>99.81991600000001</v>
       </c>
       <c r="R308" s="6" t="n">
         <v>100.309908</v>
@@ -25188,7 +25188,7 @@
         <v>100.054185</v>
       </c>
       <c r="Q309" s="9" t="n">
-        <v>99.75062800000001</v>
+        <v>99.749734</v>
       </c>
       <c r="R309" s="9" t="n">
         <v>100.224091</v>
@@ -25272,7 +25272,7 @@
         <v>100.112691</v>
       </c>
       <c r="Q310" s="6" t="n">
-        <v>99.73730999999999</v>
+        <v>99.736369</v>
       </c>
       <c r="R310" s="6" t="n">
         <v>100.132397</v>
@@ -25356,7 +25356,7 @@
         <v>100.157686</v>
       </c>
       <c r="Q311" s="9" t="n">
-        <v>99.786838</v>
+        <v>99.786074</v>
       </c>
       <c r="R311" s="9" t="n">
         <v>100.039605</v>
@@ -25440,7 +25440,7 @@
         <v>100.183987</v>
       </c>
       <c r="Q312" s="6" t="n">
-        <v>99.889528</v>
+        <v>99.889132</v>
       </c>
       <c r="R312" s="6" t="n">
         <v>99.955387</v>
@@ -25524,7 +25524,7 @@
         <v>100.203832</v>
       </c>
       <c r="Q313" s="9" t="n">
-        <v>100.027822</v>
+        <v>100.027922</v>
       </c>
       <c r="R313" s="9" t="n">
         <v>99.885068</v>
@@ -25608,7 +25608,7 @@
         <v>100.234257</v>
       </c>
       <c r="Q314" s="6" t="n">
-        <v>100.192269</v>
+        <v>100.192958</v>
       </c>
       <c r="R314" s="6" t="n">
         <v>99.820503</v>
@@ -25692,7 +25692,7 @@
         <v>100.274284</v>
       </c>
       <c r="Q315" s="9" t="n">
-        <v>100.354791</v>
+        <v>100.356063</v>
       </c>
       <c r="R315" s="9" t="n">
         <v>99.746527</v>
@@ -25776,7 +25776,7 @@
         <v>100.320411</v>
       </c>
       <c r="Q316" s="6" t="n">
-        <v>100.511062</v>
+        <v>100.512894</v>
       </c>
       <c r="R316" s="6" t="n">
         <v>99.666077</v>
@@ -25860,7 +25860,7 @@
         <v>100.382964</v>
       </c>
       <c r="Q317" s="9" t="n">
-        <v>100.645611</v>
+        <v>100.647925</v>
       </c>
       <c r="R317" s="9" t="n">
         <v>99.61009900000001</v>
@@ -25944,7 +25944,7 @@
         <v>100.466043</v>
       </c>
       <c r="Q318" s="6" t="n">
-        <v>100.742199</v>
+        <v>100.74486</v>
       </c>
       <c r="R318" s="6" t="n">
         <v>99.610108</v>
@@ -26028,7 +26028,7 @@
         <v>100.576808</v>
       </c>
       <c r="Q319" s="9" t="n">
-        <v>100.791261</v>
+        <v>100.794097</v>
       </c>
       <c r="R319" s="9" t="n">
         <v>99.681774</v>
@@ -26112,7 +26112,7 @@
         <v>100.68257</v>
       </c>
       <c r="Q320" s="6" t="n">
-        <v>100.802487</v>
+        <v>100.805363</v>
       </c>
       <c r="R320" s="6" t="n">
         <v>99.82058499999999</v>
@@ -26196,7 +26196,7 @@
         <v>100.777022</v>
       </c>
       <c r="Q321" s="9" t="n">
-        <v>100.785345</v>
+        <v>100.78816</v>
       </c>
       <c r="R321" s="9" t="n">
         <v>99.98728</v>
@@ -26280,7 +26280,7 @@
         <v>100.866076</v>
       </c>
       <c r="Q322" s="6" t="n">
-        <v>100.754254</v>
+        <v>100.756958</v>
       </c>
       <c r="R322" s="6" t="n">
         <v>100.12685</v>
@@ -26364,7 +26364,7 @@
         <v>100.954439</v>
       </c>
       <c r="Q323" s="9" t="n">
-        <v>100.756692</v>
+        <v>100.759405</v>
       </c>
       <c r="R323" s="9" t="n">
         <v>100.197057</v>
@@ -26448,7 +26448,7 @@
         <v>101.060017</v>
       </c>
       <c r="Q324" s="6" t="n">
-        <v>100.815207</v>
+        <v>100.818129</v>
       </c>
       <c r="R324" s="6" t="n">
         <v>100.174371</v>
@@ -26532,7 +26532,7 @@
         <v>101.183334</v>
       </c>
       <c r="Q325" s="9" t="n">
-        <v>100.931193</v>
+        <v>100.934531</v>
       </c>
       <c r="R325" s="9" t="n">
         <v>100.081647</v>
@@ -26616,7 +26616,7 @@
         <v>101.296754</v>
       </c>
       <c r="Q326" s="6" t="n">
-        <v>101.096405</v>
+        <v>101.100335</v>
       </c>
       <c r="R326" s="6" t="n">
         <v>99.952215</v>
@@ -26700,7 +26700,7 @@
         <v>101.394739</v>
       </c>
       <c r="Q327" s="9" t="n">
-        <v>101.298183</v>
+        <v>101.302836</v>
       </c>
       <c r="R327" s="9" t="n">
         <v>99.81625</v>
@@ -26784,7 +26784,7 @@
         <v>101.496553</v>
       </c>
       <c r="Q328" s="6" t="n">
-        <v>101.515987</v>
+        <v>101.52142</v>
       </c>
       <c r="R328" s="6" t="n">
         <v>99.70243000000001</v>
@@ -26868,7 +26868,7 @@
         <v>101.607496</v>
       </c>
       <c r="Q329" s="9" t="n">
-        <v>101.722834</v>
+        <v>101.729009</v>
       </c>
       <c r="R329" s="9" t="n">
         <v>99.63011</v>
@@ -26952,7 +26952,7 @@
         <v>101.722044</v>
       </c>
       <c r="Q330" s="6" t="n">
-        <v>101.901627</v>
+        <v>101.908443</v>
       </c>
       <c r="R330" s="6" t="n">
         <v>99.60608000000001</v>
@@ -27036,7 +27036,7 @@
         <v>101.819967</v>
       </c>
       <c r="Q331" s="9" t="n">
-        <v>102.050419</v>
+        <v>102.057768</v>
       </c>
       <c r="R331" s="9" t="n">
         <v>99.62086499999999</v>
@@ -27120,7 +27120,7 @@
         <v>101.889934</v>
       </c>
       <c r="Q332" s="6" t="n">
-        <v>102.181358</v>
+        <v>102.189177</v>
       </c>
       <c r="R332" s="6" t="n">
         <v>99.654573</v>
@@ -27204,7 +27204,7 @@
         <v>101.930893</v>
       </c>
       <c r="Q333" s="9" t="n">
-        <v>102.283007</v>
+        <v>102.29119</v>
       </c>
       <c r="R333" s="9" t="n">
         <v>99.683598</v>
@@ -27288,7 +27288,7 @@
         <v>101.951296</v>
       </c>
       <c r="Q334" s="6" t="n">
-        <v>102.343454</v>
+        <v>102.351854</v>
       </c>
       <c r="R334" s="6" t="n">
         <v>99.699654</v>
@@ -27372,7 +27372,7 @@
         <v>101.979804</v>
       </c>
       <c r="Q335" s="9" t="n">
-        <v>102.341101</v>
+        <v>102.349492</v>
       </c>
       <c r="R335" s="9" t="n">
         <v>99.70114</v>
@@ -27456,7 +27456,7 @@
         <v>102.025564</v>
       </c>
       <c r="Q336" s="6" t="n">
-        <v>102.278883</v>
+        <v>102.287051</v>
       </c>
       <c r="R336" s="6" t="n">
         <v>99.686604</v>
@@ -27540,7 +27540,7 @@
         <v>102.079357</v>
       </c>
       <c r="Q337" s="9" t="n">
-        <v>102.173165</v>
+        <v>102.180954</v>
       </c>
       <c r="R337" s="9" t="n">
         <v>99.65498700000001</v>
@@ -27624,7 +27624,7 @@
         <v>102.124311</v>
       </c>
       <c r="Q338" s="6" t="n">
-        <v>102.041262</v>
+        <v>102.048578</v>
       </c>
       <c r="R338" s="6" t="n">
         <v>99.59654500000001</v>
@@ -27708,7 +27708,7 @@
         <v>102.132406</v>
       </c>
       <c r="Q339" s="9" t="n">
-        <v>101.895441</v>
+        <v>101.902235</v>
       </c>
       <c r="R339" s="9" t="n">
         <v>99.51276799999999</v>
@@ -27792,7 +27792,7 @@
         <v>102.060746</v>
       </c>
       <c r="Q340" s="6" t="n">
-        <v>101.741623</v>
+        <v>101.747865</v>
       </c>
       <c r="R340" s="6" t="n">
         <v>99.414777</v>
@@ -27876,7 +27876,7 @@
         <v>101.873394</v>
       </c>
       <c r="Q341" s="9" t="n">
-        <v>101.602397</v>
+        <v>101.608141</v>
       </c>
       <c r="R341" s="9" t="n">
         <v>99.304884</v>
@@ -27960,7 +27960,7 @@
         <v>101.590329</v>
       </c>
       <c r="Q342" s="6" t="n">
-        <v>101.489513</v>
+        <v>101.494852</v>
       </c>
       <c r="R342" s="6" t="n">
         <v>99.183913</v>
@@ -28044,7 +28044,7 @@
         <v>101.246674</v>
       </c>
       <c r="Q343" s="9" t="n">
-        <v>101.402357</v>
+        <v>101.407383</v>
       </c>
       <c r="R343" s="9" t="n">
         <v>99.050804</v>
@@ -28128,7 +28128,7 @@
         <v>100.886384</v>
       </c>
       <c r="Q344" s="6" t="n">
-        <v>101.315061</v>
+        <v>101.319775</v>
       </c>
       <c r="R344" s="6" t="n">
         <v>98.917841</v>
@@ -28212,7 +28212,7 @@
         <v>100.532826</v>
       </c>
       <c r="Q345" s="9" t="n">
-        <v>101.178782</v>
+        <v>101.183008</v>
       </c>
       <c r="R345" s="9" t="n">
         <v>98.804445</v>
@@ -28296,7 +28296,7 @@
         <v>100.187652</v>
       </c>
       <c r="Q346" s="6" t="n">
-        <v>100.955255</v>
+        <v>100.958679</v>
       </c>
       <c r="R346" s="6" t="n">
         <v>98.742493</v>
@@ -28380,7 +28380,7 @@
         <v>99.797861</v>
       </c>
       <c r="Q347" s="9" t="n">
-        <v>100.609962</v>
+        <v>100.612148</v>
       </c>
       <c r="R347" s="9" t="n">
         <v>98.765486</v>
@@ -28464,7 +28464,7 @@
         <v>99.303201</v>
       </c>
       <c r="Q348" s="6" t="n">
-        <v>100.153682</v>
+        <v>100.154233</v>
       </c>
       <c r="R348" s="6" t="n">
         <v>98.914593</v>
@@ -28548,7 +28548,7 @@
         <v>98.671228</v>
       </c>
       <c r="Q349" s="9" t="n">
-        <v>99.616022</v>
+        <v>99.61464599999999</v>
       </c>
       <c r="R349" s="9" t="n">
         <v>99.22901400000001</v>
@@ -28632,7 +28632,7 @@
         <v>97.901875</v>
       </c>
       <c r="Q350" s="6" t="n">
-        <v>99.035662</v>
+        <v>99.032206</v>
       </c>
       <c r="R350" s="6" t="n">
         <v>99.72358</v>
@@ -28716,7 +28716,7 @@
         <v>97.072532</v>
       </c>
       <c r="Q351" s="9" t="n">
-        <v>98.46801499999999</v>
+        <v>98.462525</v>
       </c>
       <c r="R351" s="9" t="n">
         <v>100.337008</v>
@@ -28800,7 +28800,7 @@
         <v>96.29892</v>
       </c>
       <c r="Q352" s="6" t="n">
-        <v>97.99027700000001</v>
+        <v>97.983074</v>
       </c>
       <c r="R352" s="6" t="n">
         <v>100.940035</v>
@@ -28884,7 +28884,7 @@
         <v>95.68318600000001</v>
       </c>
       <c r="Q353" s="9" t="n">
-        <v>97.629774</v>
+        <v>97.621279</v>
       </c>
       <c r="R353" s="9" t="n">
         <v>101.461672</v>
@@ -28968,7 +28968,7 @@
         <v>95.30486399999999</v>
       </c>
       <c r="Q354" s="6" t="n">
-        <v>97.39106099999999</v>
+        <v>97.381711</v>
       </c>
       <c r="R354" s="6" t="n">
         <v>101.862679</v>
@@ -29052,7 +29052,7 @@
         <v>95.16922599999999</v>
       </c>
       <c r="Q355" s="9" t="n">
-        <v>97.320742</v>
+        <v>97.311139</v>
       </c>
       <c r="R355" s="9" t="n">
         <v>102.104454</v>
@@ -29136,7 +29136,7 @@
         <v>95.258537</v>
       </c>
       <c r="Q356" s="6" t="n">
-        <v>97.448117</v>
+        <v>97.438971</v>
       </c>
       <c r="R356" s="6" t="n">
         <v>102.162162</v>
@@ -29220,7 +29220,7 @@
         <v>95.48564</v>
       </c>
       <c r="Q357" s="9" t="n">
-        <v>97.733762</v>
+        <v>97.725639</v>
       </c>
       <c r="R357" s="9" t="n">
         <v>102.064212</v>
@@ -29304,7 +29304,7 @@
         <v>95.772683</v>
       </c>
       <c r="Q358" s="6" t="n">
-        <v>98.107777</v>
+        <v>98.100995</v>
       </c>
       <c r="R358" s="6" t="n">
         <v>101.900981</v>
@@ -29388,7 +29388,7 @@
         <v>96.08196100000001</v>
       </c>
       <c r="Q359" s="9" t="n">
-        <v>98.502821</v>
+        <v>98.497455</v>
       </c>
       <c r="R359" s="9" t="n">
         <v>101.72755</v>
@@ -29472,7 +29472,7 @@
         <v>96.38672800000001</v>
       </c>
       <c r="Q360" s="6" t="n">
-        <v>98.882034</v>
+        <v>98.87802600000001</v>
       </c>
       <c r="R360" s="6" t="n">
         <v>101.557888</v>
@@ -29556,7 +29556,7 @@
         <v>96.686184</v>
       </c>
       <c r="Q361" s="9" t="n">
-        <v>99.207392</v>
+        <v>99.204551</v>
       </c>
       <c r="R361" s="9" t="n">
         <v>101.395511</v>
@@ -29640,7 +29640,7 @@
         <v>96.994731</v>
       </c>
       <c r="Q362" s="6" t="n">
-        <v>99.463691</v>
+        <v>99.46176800000001</v>
       </c>
       <c r="R362" s="6" t="n">
         <v>101.241683</v>
@@ -29724,7 +29724,7 @@
         <v>97.300673</v>
       </c>
       <c r="Q363" s="9" t="n">
-        <v>99.65195300000001</v>
+        <v>99.650705</v>
       </c>
       <c r="R363" s="9" t="n">
         <v>101.074806</v>
@@ -29808,7 +29808,7 @@
         <v>97.60715</v>
       </c>
       <c r="Q364" s="6" t="n">
-        <v>99.785927</v>
+        <v>99.78515899999999</v>
       </c>
       <c r="R364" s="6" t="n">
         <v>100.890722</v>
@@ -29892,7 +29892,7 @@
         <v>97.94927</v>
       </c>
       <c r="Q365" s="9" t="n">
-        <v>99.86318</v>
+        <v>99.862689</v>
       </c>
       <c r="R365" s="9" t="n">
         <v>100.700112</v>
@@ -29976,7 +29976,7 @@
         <v>98.351921</v>
       </c>
       <c r="Q366" s="6" t="n">
-        <v>99.891302</v>
+        <v>99.890912</v>
       </c>
       <c r="R366" s="6" t="n">
         <v>100.524626</v>
@@ -30060,7 +30060,7 @@
         <v>98.836896</v>
       </c>
       <c r="Q367" s="9" t="n">
-        <v>99.89702</v>
+        <v>99.89665100000001</v>
       </c>
       <c r="R367" s="9" t="n">
         <v>100.378542</v>
@@ -30144,7 +30144,7 @@
         <v>99.363438</v>
       </c>
       <c r="Q368" s="6" t="n">
-        <v>99.885969</v>
+        <v>99.88556</v>
       </c>
       <c r="R368" s="6" t="n">
         <v>100.268622</v>
@@ -30228,7 +30228,7 @@
         <v>99.87252599999999</v>
       </c>
       <c r="Q369" s="9" t="n">
-        <v>99.85785</v>
+        <v>99.85733999999999</v>
       </c>
       <c r="R369" s="9" t="n">
         <v>100.211919</v>
@@ -30312,7 +30312,7 @@
         <v>100.320785</v>
       </c>
       <c r="Q370" s="6" t="n">
-        <v>99.827597</v>
+        <v>99.826978</v>
       </c>
       <c r="R370" s="6" t="n">
         <v>100.208511</v>
@@ -30396,7 +30396,7 @@
         <v>100.685873</v>
       </c>
       <c r="Q371" s="9" t="n">
-        <v>99.817001</v>
+        <v>99.816344</v>
       </c>
       <c r="R371" s="9" t="n">
         <v>100.216513</v>
@@ -30480,7 +30480,7 @@
         <v>100.967715</v>
       </c>
       <c r="Q372" s="6" t="n">
-        <v>99.846878</v>
+        <v>99.846328</v>
       </c>
       <c r="R372" s="6" t="n">
         <v>100.201181</v>
@@ -30564,7 +30564,7 @@
         <v>101.181109</v>
       </c>
       <c r="Q373" s="9" t="n">
-        <v>99.920451</v>
+        <v>99.920164</v>
       </c>
       <c r="R373" s="9" t="n">
         <v>100.137122</v>
@@ -30648,7 +30648,7 @@
         <v>101.33781</v>
       </c>
       <c r="Q374" s="6" t="n">
-        <v>100.036883</v>
+        <v>100.037014</v>
       </c>
       <c r="R374" s="6" t="n">
         <v>100.016973</v>
@@ -30732,7 +30732,7 @@
         <v>101.453186</v>
       </c>
       <c r="Q375" s="9" t="n">
-        <v>100.171469</v>
+        <v>100.172082</v>
       </c>
       <c r="R375" s="9" t="n">
         <v>99.84446199999999</v>
@@ -30816,7 +30816,7 @@
         <v>101.533877</v>
       </c>
       <c r="Q376" s="6" t="n">
-        <v>100.289159</v>
+        <v>100.290194</v>
       </c>
       <c r="R376" s="6" t="n">
         <v>99.649674</v>
@@ -30900,7 +30900,7 @@
         <v>101.579847</v>
       </c>
       <c r="Q377" s="9" t="n">
-        <v>100.363929</v>
+        <v>100.365232</v>
       </c>
       <c r="R377" s="9" t="n">
         <v>99.45838000000001</v>
@@ -30984,7 +30984,7 @@
         <v>101.595816</v>
       </c>
       <c r="Q378" s="6" t="n">
-        <v>100.382134</v>
+        <v>100.383501</v>
       </c>
       <c r="R378" s="6" t="n">
         <v>99.28510799999999</v>
@@ -31068,7 +31068,7 @@
         <v>101.589565</v>
       </c>
       <c r="Q379" s="9" t="n">
-        <v>100.356769</v>
+        <v>100.358046</v>
       </c>
       <c r="R379" s="9" t="n">
         <v>99.150021</v>
@@ -31152,7 +31152,7 @@
         <v>101.564479</v>
       </c>
       <c r="Q380" s="6" t="n">
-        <v>100.299063</v>
+        <v>100.300133</v>
       </c>
       <c r="R380" s="6" t="n">
         <v>99.067115</v>
@@ -31236,7 +31236,7 @@
         <v>101.521606</v>
       </c>
       <c r="Q381" s="9" t="n">
-        <v>100.216602</v>
+        <v>100.217377</v>
       </c>
       <c r="R381" s="9" t="n">
         <v>99.047814</v>
@@ -31320,7 +31320,7 @@
         <v>101.457888</v>
       </c>
       <c r="Q382" s="6" t="n">
-        <v>100.120313</v>
+        <v>100.120742</v>
       </c>
       <c r="R382" s="6" t="n">
         <v>99.110263</v>
@@ -31404,7 +31404,7 @@
         <v>101.36094</v>
       </c>
       <c r="Q383" s="9" t="n">
-        <v>100.021428</v>
+        <v>100.021502</v>
       </c>
       <c r="R383" s="9" t="n">
         <v>99.26267199999999</v>
@@ -31488,7 +31488,7 @@
         <v>101.227638</v>
       </c>
       <c r="Q384" s="6" t="n">
-        <v>99.923676</v>
+        <v>99.9234</v>
       </c>
       <c r="R384" s="6" t="n">
         <v>99.501452</v>
@@ -31572,7 +31572,7 @@
         <v>101.061655</v>
       </c>
       <c r="Q385" s="9" t="n">
-        <v>99.83911000000001</v>
+        <v>99.838531</v>
       </c>
       <c r="R385" s="9" t="n">
         <v>99.812797</v>
@@ -31656,7 +31656,7 @@
         <v>100.895736</v>
       </c>
       <c r="Q386" s="6" t="n">
-        <v>99.78235599999999</v>
+        <v>99.78157299999999</v>
       </c>
       <c r="R386" s="6" t="n">
         <v>100.139056</v>
@@ -31740,7 +31740,7 @@
         <v>100.746127</v>
       </c>
       <c r="Q387" s="9" t="n">
-        <v>99.769779</v>
+        <v>99.768951</v>
       </c>
       <c r="R387" s="9" t="n">
         <v>100.405066</v>
@@ -31824,7 +31824,7 @@
         <v>100.624368</v>
       </c>
       <c r="Q388" s="6" t="n">
-        <v>99.786102</v>
+        <v>99.785332</v>
       </c>
       <c r="R388" s="6" t="n">
         <v>100.562798</v>
@@ -31908,7 +31908,7 @@
         <v>100.533795</v>
       </c>
       <c r="Q389" s="9" t="n">
-        <v>99.820724</v>
+        <v>99.820078</v>
       </c>
       <c r="R389" s="9" t="n">
         <v>100.609642</v>
@@ -31992,7 +31992,7 @@
         <v>100.472404</v>
       </c>
       <c r="Q390" s="6" t="n">
-        <v>99.868849</v>
+        <v>99.868376</v>
       </c>
       <c r="R390" s="6" t="n">
         <v>100.576061</v>
@@ -32076,7 +32076,7 @@
         <v>100.408679</v>
       </c>
       <c r="Q391" s="9" t="n">
-        <v>99.92652699999999</v>
+        <v>99.92626</v>
       </c>
       <c r="R391" s="9" t="n">
         <v>100.518806</v>
@@ -32160,7 +32160,7 @@
         <v>100.324608</v>
       </c>
       <c r="Q392" s="6" t="n">
-        <v>99.986734</v>
+        <v>99.986683</v>
       </c>
       <c r="R392" s="6" t="n">
         <v>100.498351</v>
@@ -32244,7 +32244,7 @@
         <v>100.2306</v>
       </c>
       <c r="Q393" s="9" t="n">
-        <v>100.038167</v>
+        <v>100.0383</v>
       </c>
       <c r="R393" s="9" t="n">
         <v>100.5229</v>
@@ -32328,7 +32328,7 @@
         <v>100.149665</v>
       </c>
       <c r="Q394" s="6" t="n">
-        <v>100.082667</v>
+        <v>100.082959</v>
       </c>
       <c r="R394" s="6" t="n">
         <v>100.552714</v>
@@ -32412,7 +32412,7 @@
         <v>100.106215</v>
       </c>
       <c r="Q395" s="9" t="n">
-        <v>100.130917</v>
+        <v>100.131382</v>
       </c>
       <c r="R395" s="9" t="n">
         <v>100.530672</v>
@@ -32496,7 +32496,7 @@
         <v>100.11601</v>
       </c>
       <c r="Q396" s="6" t="n">
-        <v>100.177558</v>
+        <v>100.17819</v>
       </c>
       <c r="R396" s="6" t="n">
         <v>100.424936</v>
@@ -32580,7 +32580,7 @@
         <v>100.179137</v>
       </c>
       <c r="Q397" s="9" t="n">
-        <v>100.225799</v>
+        <v>100.226603</v>
       </c>
       <c r="R397" s="9" t="n">
         <v>100.257915</v>
@@ -32664,7 +32664,7 @@
         <v>100.280395</v>
       </c>
       <c r="Q398" s="6" t="n">
-        <v>100.286449</v>
+        <v>100.287471</v>
       </c>
       <c r="R398" s="6" t="n">
         <v>100.053964</v>
@@ -32748,7 +32748,7 @@
         <v>100.40825</v>
       </c>
       <c r="Q399" s="9" t="n">
-        <v>100.354497</v>
+        <v>100.355763</v>
       </c>
       <c r="R399" s="9" t="n">
         <v>99.834435</v>
@@ -32832,7 +32832,7 @@
         <v>100.548273</v>
       </c>
       <c r="Q400" s="6" t="n">
-        <v>100.420484</v>
+        <v>100.421986</v>
       </c>
       <c r="R400" s="6" t="n">
         <v>99.61371200000001</v>
@@ -32916,7 +32916,7 @@
         <v>100.694777</v>
       </c>
       <c r="Q401" s="9" t="n">
-        <v>100.471575</v>
+        <v>100.47326</v>
       </c>
       <c r="R401" s="9" t="n">
         <v>99.396663</v>
@@ -33000,7 +33000,7 @@
         <v>100.845915</v>
       </c>
       <c r="Q402" s="6" t="n">
-        <v>100.484887</v>
+        <v>100.486619</v>
       </c>
       <c r="R402" s="6" t="n">
         <v>99.198302</v>
@@ -33084,7 +33084,7 @@
         <v>100.978925</v>
       </c>
       <c r="Q403" s="9" t="n">
-        <v>100.445016</v>
+        <v>100.446606</v>
       </c>
       <c r="R403" s="9" t="n">
         <v>99.03193</v>
@@ -33168,7 +33168,7 @@
         <v>101.071487</v>
       </c>
       <c r="Q404" s="6" t="n">
-        <v>100.358911</v>
+        <v>100.360192</v>
       </c>
       <c r="R404" s="6" t="n">
         <v>98.90683300000001</v>
@@ -33252,7 +33252,7 @@
         <v>101.117273</v>
       </c>
       <c r="Q405" s="9" t="n">
-        <v>100.241392</v>
+        <v>100.242251</v>
       </c>
       <c r="R405" s="9" t="n">
         <v>98.840951</v>
@@ -33336,7 +33336,7 @@
         <v>101.109004</v>
       </c>
       <c r="Q406" s="6" t="n">
-        <v>100.116082</v>
+        <v>100.116492</v>
       </c>
       <c r="R406" s="6" t="n">
         <v>98.849161</v>
@@ -33420,7 +33420,7 @@
         <v>101.039053</v>
       </c>
       <c r="Q407" s="9" t="n">
-        <v>100.000267</v>
+        <v>100.000262</v>
       </c>
       <c r="R407" s="9" t="n">
         <v>98.910831</v>
@@ -33504,7 +33504,7 @@
         <v>100.916336</v>
       </c>
       <c r="Q408" s="6" t="n">
-        <v>99.90637099999999</v>
+        <v>99.906029</v>
       </c>
       <c r="R408" s="6" t="n">
         <v>98.974934</v>
@@ -33588,7 +33588,7 @@
         <v>100.750172</v>
       </c>
       <c r="Q409" s="9" t="n">
-        <v>99.83740400000001</v>
+        <v>99.836815</v>
       </c>
       <c r="R409" s="9" t="n">
         <v>99.018914</v>
@@ -33672,7 +33672,7 @@
         <v>100.562709</v>
       </c>
       <c r="Q410" s="6" t="n">
-        <v>99.796119</v>
+        <v>99.795382</v>
       </c>
       <c r="R410" s="6" t="n">
         <v>99.028266</v>
@@ -33756,7 +33756,7 @@
         <v>100.385318</v>
       </c>
       <c r="Q411" s="9" t="n">
-        <v>99.769999</v>
+        <v>99.76916799999999</v>
       </c>
       <c r="R411" s="9" t="n">
         <v>98.995935</v>
@@ -33840,7 +33840,7 @@
         <v>100.250938</v>
       </c>
       <c r="Q412" s="6" t="n">
-        <v>99.74104199999999</v>
+        <v>99.74010699999999</v>
       </c>
       <c r="R412" s="6" t="n">
         <v>98.935008</v>
@@ -33924,7 +33924,7 @@
         <v>100.169705</v>
       </c>
       <c r="Q413" s="9" t="n">
-        <v>99.69591800000001</v>
+        <v>99.694822</v>
       </c>
       <c r="R413" s="9" t="n">
         <v>98.86249100000001</v>
@@ -34008,7 +34008,7 @@
         <v>100.125374</v>
       </c>
       <c r="Q414" s="6" t="n">
-        <v>99.64142099999999</v>
+        <v>99.640129</v>
       </c>
       <c r="R414" s="6" t="n">
         <v>98.790852</v>
@@ -34092,7 +34092,7 @@
         <v>100.123506</v>
       </c>
       <c r="Q415" s="9" t="n">
-        <v>99.60718799999999</v>
+        <v>99.605774</v>
       </c>
       <c r="R415" s="9" t="n">
         <v>98.717893</v>
@@ -34176,7 +34176,7 @@
         <v>100.148098</v>
       </c>
       <c r="Q416" s="6" t="n">
-        <v>99.620942</v>
+        <v>99.61957700000001</v>
       </c>
       <c r="R416" s="6" t="n">
         <v>98.638488</v>
@@ -34260,7 +34260,7 @@
         <v>100.192961</v>
       </c>
       <c r="Q417" s="9" t="n">
-        <v>99.681202</v>
+        <v>99.680053</v>
       </c>
       <c r="R417" s="9" t="n">
         <v>98.554901</v>
@@ -34344,7 +34344,7 @@
         <v>100.258347</v>
       </c>
       <c r="Q418" s="6" t="n">
-        <v>99.777332</v>
+        <v>99.776528</v>
       </c>
       <c r="R418" s="6" t="n">
         <v>98.47601299999999</v>
@@ -34428,7 +34428,7 @@
         <v>100.3453</v>
       </c>
       <c r="Q419" s="9" t="n">
-        <v>99.88937199999999</v>
+        <v>99.888969</v>
       </c>
       <c r="R419" s="9" t="n">
         <v>98.411861</v>
@@ -34512,7 +34512,7 @@
         <v>100.437113</v>
       </c>
       <c r="Q420" s="6" t="n">
-        <v>99.99125600000001</v>
+        <v>99.991218</v>
       </c>
       <c r="R420" s="6" t="n">
         <v>98.371735</v>
@@ -34596,7 +34596,7 @@
         <v>100.502282</v>
       </c>
       <c r="Q421" s="9" t="n">
-        <v>100.0593</v>
+        <v>100.059506</v>
       </c>
       <c r="R421" s="9" t="n">
         <v>98.36732499999999</v>
@@ -34680,7 +34680,7 @@
         <v>100.515265</v>
       </c>
       <c r="Q422" s="6" t="n">
-        <v>100.076785</v>
+        <v>100.077054</v>
       </c>
       <c r="R422" s="6" t="n">
         <v>98.406216</v>
@@ -34764,7 +34764,7 @@
         <v>100.461482</v>
       </c>
       <c r="Q423" s="9" t="n">
-        <v>100.048877</v>
+        <v>100.049046</v>
       </c>
       <c r="R423" s="9" t="n">
         <v>98.496641</v>
@@ -34848,7 +34848,7 @@
         <v>100.335705</v>
       </c>
       <c r="Q424" s="6" t="n">
-        <v>99.99153699999999</v>
+        <v>99.991501</v>
       </c>
       <c r="R424" s="6" t="n">
         <v>98.639825</v>
@@ -34932,7 +34932,7 @@
         <v>100.156682</v>
       </c>
       <c r="Q425" s="9" t="n">
-        <v>99.93123900000001</v>
+        <v>99.930987</v>
       </c>
       <c r="R425" s="9" t="n">
         <v>98.832921</v>
@@ -35016,7 +35016,7 @@
         <v>99.957003</v>
       </c>
       <c r="Q426" s="6" t="n">
-        <v>99.894961</v>
+        <v>99.89457899999999</v>
       </c>
       <c r="R426" s="6" t="n">
         <v>99.046823</v>
@@ -35100,7 +35100,7 @@
         <v>99.76344400000001</v>
       </c>
       <c r="Q427" s="9" t="n">
-        <v>99.89936</v>
+        <v>99.898994</v>
       </c>
       <c r="R427" s="9" t="n">
         <v>99.26434399999999</v>
@@ -35184,7 +35184,7 @@
         <v>99.596346</v>
       </c>
       <c r="Q428" s="6" t="n">
-        <v>99.926242</v>
+        <v>99.925972</v>
       </c>
       <c r="R428" s="6" t="n">
         <v>99.474709</v>
@@ -35268,7 +35268,7 @@
         <v>99.458945</v>
       </c>
       <c r="Q429" s="9" t="n">
-        <v>99.96231400000001</v>
+        <v>99.962175</v>
       </c>
       <c r="R429" s="9" t="n">
         <v>99.67397200000001</v>
@@ -35352,7 +35352,7 @@
         <v>99.35393500000001</v>
       </c>
       <c r="Q430" s="6" t="n">
-        <v>99.989831</v>
+        <v>99.98979</v>
       </c>
       <c r="R430" s="6" t="n">
         <v>99.86816899999999</v>
@@ -35436,7 +35436,7 @@
         <v>99.275858</v>
       </c>
       <c r="Q431" s="9" t="n">
-        <v>99.996233</v>
+        <v>99.996216</v>
       </c>
       <c r="R431" s="9" t="n">
         <v>100.060364</v>
@@ -35520,7 +35520,7 @@
         <v>99.220967</v>
       </c>
       <c r="Q432" s="6" t="n">
-        <v>99.976822</v>
+        <v>99.976736</v>
       </c>
       <c r="R432" s="6" t="n">
         <v>100.245093</v>
@@ -35604,7 +35604,7 @@
         <v>99.193749</v>
       </c>
       <c r="Q433" s="9" t="n">
-        <v>99.93813299999999</v>
+        <v>99.93790799999999</v>
       </c>
       <c r="R433" s="9" t="n">
         <v>100.406011</v>
@@ -35688,7 +35688,7 @@
         <v>99.196096</v>
       </c>
       <c r="Q434" s="6" t="n">
-        <v>99.895577</v>
+        <v>99.8952</v>
       </c>
       <c r="R434" s="6" t="n">
         <v>100.527076</v>
@@ -35772,7 +35772,7 @@
         <v>99.223141</v>
       </c>
       <c r="Q435" s="9" t="n">
-        <v>99.86329499999999</v>
+        <v>99.862802</v>
       </c>
       <c r="R435" s="9" t="n">
         <v>100.613973</v>
@@ -35856,7 +35856,7 @@
         <v>99.251749</v>
       </c>
       <c r="Q436" s="6" t="n">
-        <v>99.84242999999999</v>
+        <v>99.841863</v>
       </c>
       <c r="R436" s="6" t="n">
         <v>100.697748</v>
@@ -35940,7 +35940,7 @@
         <v>99.270729</v>
       </c>
       <c r="Q437" s="9" t="n">
-        <v>99.844922</v>
+        <v>99.84436599999999</v>
       </c>
       <c r="R437" s="9" t="n">
         <v>100.800136</v>
@@ -36024,7 +36024,7 @@
         <v>99.282495</v>
       </c>
       <c r="Q438" s="6" t="n">
-        <v>99.87924700000001</v>
+        <v>99.87881400000001</v>
       </c>
       <c r="R438" s="6" t="n">
         <v>100.915398</v>
@@ -36108,7 +36108,7 @@
         <v>99.29660199999999</v>
       </c>
       <c r="Q439" s="9" t="n">
-        <v>99.943476</v>
+        <v>99.943274</v>
       </c>
       <c r="R439" s="9" t="n">
         <v>101.013894</v>
@@ -36192,7 +36192,7 @@
         <v>99.328655</v>
       </c>
       <c r="Q440" s="6" t="n">
-        <v>100.029788</v>
+        <v>100.029896</v>
       </c>
       <c r="R440" s="6" t="n">
         <v>101.090225</v>
@@ -36276,7 +36276,7 @@
         <v>99.380957</v>
       </c>
       <c r="Q441" s="9" t="n">
-        <v>100.119538</v>
+        <v>100.119969</v>
       </c>
       <c r="R441" s="9" t="n">
         <v>101.178604</v>
@@ -36360,7 +36360,7 @@
         <v>99.441519</v>
       </c>
       <c r="Q442" s="6" t="n">
-        <v>100.203196</v>
+        <v>100.203927</v>
       </c>
       <c r="R442" s="6" t="n">
         <v>101.297652</v>
@@ -36444,7 +36444,7 @@
         <v>99.493708</v>
       </c>
       <c r="Q443" s="9" t="n">
-        <v>100.275575</v>
+        <v>100.276567</v>
       </c>
       <c r="R443" s="9" t="n">
         <v>101.431714</v>
@@ -36528,7 +36528,7 @@
         <v>99.522723</v>
       </c>
       <c r="Q444" s="6" t="n">
-        <v>100.329573</v>
+        <v>100.330759</v>
       </c>
       <c r="R444" s="6" t="n">
         <v>101.56255</v>
@@ -36612,7 +36612,7 @@
         <v>99.52922599999999</v>
       </c>
       <c r="Q445" s="9" t="n">
-        <v>100.357538</v>
+        <v>100.358826</v>
       </c>
       <c r="R445" s="9" t="n">
         <v>101.695303</v>
@@ -36696,7 +36696,7 @@
         <v>99.510124</v>
       </c>
       <c r="Q446" s="6" t="n">
-        <v>100.355306</v>
+        <v>100.356587</v>
       </c>
       <c r="R446" s="6" t="n">
         <v>101.834426</v>
@@ -36780,7 +36780,7 @@
         <v>99.45856499999999</v>
       </c>
       <c r="Q447" s="9" t="n">
-        <v>100.330027</v>
+        <v>100.331218</v>
       </c>
       <c r="R447" s="9" t="n">
         <v>101.961214</v>
@@ -36864,7 +36864,7 @@
         <v>99.38470599999999</v>
       </c>
       <c r="Q448" s="6" t="n">
-        <v>100.295144</v>
+        <v>100.296212</v>
       </c>
       <c r="R448" s="6" t="n">
         <v>102.055508</v>
@@ -36948,7 +36948,7 @@
         <v>99.29907</v>
       </c>
       <c r="Q449" s="9" t="n">
-        <v>100.279013</v>
+        <v>100.280024</v>
       </c>
       <c r="R449" s="9" t="n">
         <v>102.064859</v>
@@ -37032,7 +37032,7 @@
         <v>99.22828800000001</v>
       </c>
       <c r="Q450" s="6" t="n">
-        <v>100.293886</v>
+        <v>100.294952</v>
       </c>
       <c r="R450" s="6" t="n">
         <v>101.94158</v>
@@ -37116,7 +37116,7 @@
         <v>99.216216</v>
       </c>
       <c r="Q451" s="9" t="n">
-        <v>100.340045</v>
+        <v>100.341278</v>
       </c>
       <c r="R451" s="9" t="n">
         <v>101.665439</v>
@@ -37200,7 +37200,7 @@
         <v>99.295901</v>
       </c>
       <c r="Q452" s="6" t="n">
-        <v>100.413053</v>
+        <v>100.414549</v>
       </c>
       <c r="R452" s="6" t="n">
         <v>101.282968</v>
@@ -37284,7 +37284,7 @@
         <v>99.455246</v>
       </c>
       <c r="Q453" s="9" t="n">
-        <v>100.497417</v>
+        <v>100.499217</v>
       </c>
       <c r="R453" s="9" t="n">
         <v>100.865309</v>
@@ -37368,7 +37368,7 @@
         <v>99.668685</v>
       </c>
       <c r="Q454" s="6" t="n">
-        <v>100.578745</v>
+        <v>100.580839</v>
       </c>
       <c r="R454" s="6" t="n">
         <v>100.469044</v>
@@ -37452,7 +37452,7 @@
         <v>99.902114</v>
       </c>
       <c r="Q455" s="9" t="n">
-        <v>100.646729</v>
+        <v>100.649068</v>
       </c>
       <c r="R455" s="9" t="n">
         <v>100.125169</v>
@@ -37536,7 +37536,7 @@
         <v>100.120949</v>
       </c>
       <c r="Q456" s="6" t="n">
-        <v>100.686671</v>
+        <v>100.689155</v>
       </c>
       <c r="R456" s="6" t="n">
         <v>99.86801800000001</v>
@@ -37620,7 +37620,7 @@
         <v>100.296408</v>
       </c>
       <c r="Q457" s="9" t="n">
-        <v>100.686797</v>
+        <v>100.689284</v>
       </c>
       <c r="R457" s="9" t="n">
         <v>99.71737299999999</v>
@@ -37704,7 +37704,7 @@
         <v>100.420634</v>
       </c>
       <c r="Q458" s="6" t="n">
-        <v>100.647609</v>
+        <v>100.649957</v>
       </c>
       <c r="R458" s="6" t="n">
         <v>99.666714</v>
@@ -37788,7 +37788,7 @@
         <v>100.494749</v>
       </c>
       <c r="Q459" s="9" t="n">
-        <v>100.583365</v>
+        <v>100.585485</v>
       </c>
       <c r="R459" s="9" t="n">
         <v>99.685793</v>
@@ -37872,7 +37872,7 @@
         <v>100.54919</v>
       </c>
       <c r="Q460" s="6" t="n">
-        <v>100.516217</v>
+        <v>100.518099</v>
       </c>
       <c r="R460" s="6" t="n">
         <v>99.723131</v>
@@ -37956,7 +37956,7 @@
         <v>100.612085</v>
       </c>
       <c r="Q461" s="9" t="n">
-        <v>100.461014</v>
+        <v>100.462701</v>
       </c>
       <c r="R461" s="9" t="n">
         <v>99.75232200000001</v>
@@ -38040,7 +38040,7 @@
         <v>100.687926</v>
       </c>
       <c r="Q462" s="6" t="n">
-        <v>100.409692</v>
+        <v>100.411197</v>
       </c>
       <c r="R462" s="6" t="n">
         <v>99.770194</v>
@@ -38124,7 +38124,7 @@
         <v>100.767643</v>
       </c>
       <c r="Q463" s="9" t="n">
-        <v>100.359408</v>
+        <v>100.360736</v>
       </c>
       <c r="R463" s="9" t="n">
         <v>99.789751</v>
@@ -38208,7 +38208,7 @@
         <v>100.828406</v>
       </c>
       <c r="Q464" s="6" t="n">
-        <v>100.327472</v>
+        <v>100.328687</v>
       </c>
       <c r="R464" s="6" t="n">
         <v>99.83286099999999</v>
@@ -38292,7 +38292,7 @@
         <v>100.850482</v>
       </c>
       <c r="Q465" s="9" t="n">
-        <v>100.322226</v>
+        <v>100.323425</v>
       </c>
       <c r="R465" s="9" t="n">
         <v>99.904284</v>
@@ -38376,7 +38376,7 @@
         <v>100.850342</v>
       </c>
       <c r="Q466" s="6" t="n">
-        <v>100.330935</v>
+        <v>100.332168</v>
       </c>
       <c r="R466" s="6" t="n">
         <v>99.98861599999999</v>
@@ -38460,7 +38460,7 @@
         <v>100.858654</v>
       </c>
       <c r="Q467" s="9" t="n">
-        <v>100.349622</v>
+        <v>100.350925</v>
       </c>
       <c r="R467" s="9" t="n">
         <v>100.030436</v>
@@ -38544,7 +38544,7 @@
         <v>100.898216</v>
       </c>
       <c r="Q468" s="6" t="n">
-        <v>100.343164</v>
+        <v>100.344447</v>
       </c>
       <c r="R468" s="6" t="n">
         <v>100.002699</v>
@@ -38628,7 +38628,7 @@
         <v>100.952082</v>
       </c>
       <c r="Q469" s="9" t="n">
-        <v>100.279067</v>
+        <v>100.280123</v>
       </c>
       <c r="R469" s="9" t="n">
         <v>99.946867</v>
@@ -38712,7 +38712,7 @@
         <v>101.004263</v>
       </c>
       <c r="Q470" s="6" t="n">
-        <v>100.149826</v>
+        <v>100.150422</v>
       </c>
       <c r="R470" s="6" t="n">
         <v>99.897031</v>
@@ -38796,7 +38796,7 @@
         <v>101.062335</v>
       </c>
       <c r="Q471" s="9" t="n">
-        <v>99.975212</v>
+        <v>99.975185</v>
       </c>
       <c r="R471" s="9" t="n">
         <v>99.85736900000001</v>
@@ -38880,7 +38880,7 @@
         <v>101.135696</v>
       </c>
       <c r="Q472" s="6" t="n">
-        <v>99.811229</v>
+        <v>99.81061800000001</v>
       </c>
       <c r="R472" s="6" t="n">
         <v>99.815563</v>
@@ -38964,7 +38964,7 @@
         <v>101.232864</v>
       </c>
       <c r="Q473" s="9" t="n">
-        <v>99.698545</v>
+        <v>99.697534</v>
       </c>
       <c r="R473" s="9" t="n">
         <v>99.740854</v>
@@ -39048,7 +39048,7 @@
         <v>101.354525</v>
       </c>
       <c r="Q474" s="6" t="n">
-        <v>99.644536</v>
+        <v>99.643334</v>
       </c>
       <c r="R474" s="6" t="n">
         <v>99.641769</v>
@@ -39132,7 +39132,7 @@
         <v>101.468152</v>
       </c>
       <c r="Q475" s="9" t="n">
-        <v>99.62882399999999</v>
+        <v>99.62756899999999</v>
       </c>
       <c r="R475" s="9" t="n">
         <v>99.554343</v>
@@ -39216,7 +39216,7 @@
         <v>101.551044</v>
       </c>
       <c r="Q476" s="6" t="n">
-        <v>99.6384</v>
+        <v>99.637182</v>
       </c>
       <c r="R476" s="6" t="n">
         <v>99.49288199999999</v>
@@ -39300,7 +39300,7 @@
         <v>101.583581</v>
       </c>
       <c r="Q477" s="9" t="n">
-        <v>99.656881</v>
+        <v>99.655733</v>
       </c>
       <c r="R477" s="9" t="n">
         <v>99.458901</v>
@@ -39384,7 +39384,7 @@
         <v>101.547676</v>
       </c>
       <c r="Q478" s="6" t="n">
-        <v>99.669753</v>
+        <v>99.668656</v>
       </c>
       <c r="R478" s="6" t="n">
         <v>99.449331</v>
@@ -39468,7 +39468,7 @@
         <v>101.441245</v>
       </c>
       <c r="Q479" s="9" t="n">
-        <v>99.68104700000001</v>
+        <v>99.679993</v>
       </c>
       <c r="R479" s="9" t="n">
         <v>99.450913</v>
@@ -39552,7 +39552,7 @@
         <v>101.292524</v>
       </c>
       <c r="Q480" s="6" t="n">
-        <v>99.693533</v>
+        <v>99.692527</v>
       </c>
       <c r="R480" s="6" t="n">
         <v>99.449946</v>
@@ -39636,7 +39636,7 @@
         <v>101.126542</v>
       </c>
       <c r="Q481" s="9" t="n">
-        <v>99.714883</v>
+        <v>99.71395699999999</v>
       </c>
       <c r="R481" s="9" t="n">
         <v>99.443313</v>
@@ -39720,7 +39720,7 @@
         <v>100.944592</v>
       </c>
       <c r="Q482" s="6" t="n">
-        <v>99.727627</v>
+        <v>99.72675099999999</v>
       </c>
       <c r="R482" s="6" t="n">
         <v>99.422166</v>
@@ -39804,7 +39804,7 @@
         <v>100.73086</v>
       </c>
       <c r="Q483" s="9" t="n">
-        <v>99.712333</v>
+        <v>99.711406</v>
       </c>
       <c r="R483" s="9" t="n">
         <v>99.403437</v>
@@ -39888,7 +39888,7 @@
         <v>100.459774</v>
       </c>
       <c r="Q484" s="6" t="n">
-        <v>99.65216100000001</v>
+        <v>99.651021</v>
       </c>
       <c r="R484" s="6" t="n">
         <v>99.431031</v>
@@ -39972,7 +39972,7 @@
         <v>100.09571</v>
       </c>
       <c r="Q485" s="9" t="n">
-        <v>99.537077</v>
+        <v>99.535528</v>
       </c>
       <c r="R485" s="9" t="n">
         <v>99.558414</v>
@@ -40056,7 +40056,7 @@
         <v>99.610316</v>
       </c>
       <c r="Q486" s="6" t="n">
-        <v>99.35934899999999</v>
+        <v>99.357167</v>
       </c>
       <c r="R486" s="6" t="n">
         <v>99.83211900000001</v>
@@ -40140,7 +40140,7 @@
         <v>99.00239500000001</v>
       </c>
       <c r="Q487" s="9" t="n">
-        <v>99.12958</v>
+        <v>99.126577</v>
       </c>
       <c r="R487" s="9" t="n">
         <v>100.268294</v>
@@ -40224,7 +40224,7 @@
         <v>98.32079299999999</v>
       </c>
       <c r="Q488" s="6" t="n">
-        <v>98.895561</v>
+        <v>98.891723</v>
       </c>
       <c r="R488" s="6" t="n">
         <v>100.809561</v>
@@ -40308,7 +40308,7 @@
         <v>97.67500200000001</v>
       </c>
       <c r="Q489" s="9" t="n">
-        <v>98.723353</v>
+        <v>98.718901</v>
       </c>
       <c r="R489" s="9" t="n">
         <v>101.290001</v>
@@ -40392,7 +40392,7 @@
         <v>97.20862</v>
       </c>
       <c r="Q490" s="6" t="n">
-        <v>98.620248</v>
+        <v>98.61542900000001</v>
       </c>
       <c r="R490" s="6" t="n">
         <v>101.576836</v>
@@ -40476,7 +40476,7 @@
         <v>96.970237</v>
       </c>
       <c r="Q491" s="9" t="n">
-        <v>98.582958</v>
+        <v>98.57800899999999</v>
       </c>
       <c r="R491" s="9" t="n">
         <v>101.655069</v>
@@ -40560,7 +40560,7 @@
         <v>96.925134</v>
       </c>
       <c r="Q492" s="6" t="n">
-        <v>98.59928600000001</v>
+        <v>98.594399</v>
       </c>
       <c r="R492" s="6" t="n">
         <v>101.571462</v>
@@ -40644,7 +40644,7 @@
         <v>97.01593099999999</v>
       </c>
       <c r="Q493" s="9" t="n">
-        <v>98.672332</v>
+        <v>98.667708</v>
       </c>
       <c r="R493" s="9" t="n">
         <v>101.359907</v>
@@ -40728,7 +40728,7 @@
         <v>97.18713700000001</v>
       </c>
       <c r="Q494" s="6" t="n">
-        <v>98.80711599999999</v>
+        <v>98.802978</v>
       </c>
       <c r="R494" s="6" t="n">
         <v>101.060557</v>
@@ -40812,7 +40812,7 @@
         <v>97.385947</v>
       </c>
       <c r="Q495" s="9" t="n">
-        <v>99.001842</v>
+        <v>98.99840500000001</v>
       </c>
       <c r="R495" s="9" t="n">
         <v>100.722506</v>
@@ -40896,7 +40896,7 @@
         <v>97.58692499999999</v>
       </c>
       <c r="Q496" s="6" t="n">
-        <v>99.247001</v>
+        <v>99.244445</v>
       </c>
       <c r="R496" s="6" t="n">
         <v>100.394326</v>
@@ -40980,7 +40980,7 @@
         <v>97.779211</v>
       </c>
       <c r="Q497" s="9" t="n">
-        <v>99.50240700000001</v>
+        <v>99.50076799999999</v>
       </c>
       <c r="R497" s="9" t="n">
         <v>100.127633</v>
@@ -41064,7 +41064,7 @@
         <v>97.970084</v>
       </c>
       <c r="Q498" s="6" t="n">
-        <v>99.745301</v>
+        <v>99.744534</v>
       </c>
       <c r="R498" s="6" t="n">
         <v>99.953828</v>
@@ -41148,7 +41148,7 @@
         <v>98.18325900000001</v>
       </c>
       <c r="Q499" s="9" t="n">
-        <v>99.97938499999999</v>
+        <v>99.97945799999999</v>
       </c>
       <c r="R499" s="9" t="n">
         <v>99.871509</v>
@@ -41232,7 +41232,7 @@
         <v>98.434737</v>
       </c>
       <c r="Q500" s="6" t="n">
-        <v>100.200336</v>
+        <v>100.201202</v>
       </c>
       <c r="R500" s="6" t="n">
         <v>99.850319</v>
@@ -41316,7 +41316,7 @@
         <v>98.709823</v>
       </c>
       <c r="Q501" s="9" t="n">
-        <v>100.39602</v>
+        <v>100.397587</v>
       </c>
       <c r="R501" s="9" t="n">
         <v>99.858057</v>
@@ -41400,7 +41400,7 @@
         <v>98.98323600000001</v>
       </c>
       <c r="Q502" s="6" t="n">
-        <v>100.557828</v>
+        <v>100.559976</v>
       </c>
       <c r="R502" s="6" t="n">
         <v>99.893686</v>
@@ -41484,7 +41484,7 @@
         <v>99.230737</v>
       </c>
       <c r="Q503" s="9" t="n">
-        <v>100.674094</v>
+        <v>100.676659</v>
       </c>
       <c r="R503" s="9" t="n">
         <v>99.952899</v>
@@ -41568,7 +41568,7 @@
         <v>99.43047</v>
       </c>
       <c r="Q504" s="6" t="n">
-        <v>100.749093</v>
+        <v>100.751926</v>
       </c>
       <c r="R504" s="6" t="n">
         <v>100.030564</v>
@@ -41652,7 +41652,7 @@
         <v>99.58254100000001</v>
       </c>
       <c r="Q505" s="9" t="n">
-        <v>100.78608</v>
+        <v>100.789044</v>
       </c>
       <c r="R505" s="9" t="n">
         <v>100.126421</v>
@@ -41736,7 +41736,7 @@
         <v>99.71243800000001</v>
       </c>
       <c r="Q506" s="6" t="n">
-        <v>100.785381</v>
+        <v>100.788341</v>
       </c>
       <c r="R506" s="6" t="n">
         <v>100.236931</v>
@@ -41820,7 +41820,7 @@
         <v>99.836997</v>
       </c>
       <c r="Q507" s="9" t="n">
-        <v>100.766194</v>
+        <v>100.769083</v>
       </c>
       <c r="R507" s="9" t="n">
         <v>100.355775</v>
@@ -41904,7 +41904,7 @@
         <v>99.955989</v>
       </c>
       <c r="Q508" s="6" t="n">
-        <v>100.744143</v>
+        <v>100.74695</v>
       </c>
       <c r="R508" s="6" t="n">
         <v>100.461955</v>
@@ -41988,7 +41988,7 @@
         <v>100.07133</v>
       </c>
       <c r="Q509" s="9" t="n">
-        <v>100.727777</v>
+        <v>100.730522</v>
       </c>
       <c r="R509" s="9" t="n">
         <v>100.540389</v>
@@ -42072,7 +42072,7 @@
         <v>100.180563</v>
       </c>
       <c r="Q510" s="6" t="n">
-        <v>100.697338</v>
+        <v>100.69997</v>
       </c>
       <c r="R510" s="6" t="n">
         <v>100.587053</v>
@@ -42156,7 +42156,7 @@
         <v>100.283659</v>
       </c>
       <c r="Q511" s="9" t="n">
-        <v>100.641439</v>
+        <v>100.643866</v>
       </c>
       <c r="R511" s="9" t="n">
         <v>100.616813</v>
@@ -42240,7 +42240,7 @@
         <v>100.355092</v>
       </c>
       <c r="Q512" s="6" t="n">
-        <v>100.536507</v>
+        <v>100.538553</v>
       </c>
       <c r="R512" s="6" t="n">
         <v>100.637243</v>
@@ -42324,7 +42324,7 @@
         <v>100.409727</v>
       </c>
       <c r="Q513" s="9" t="n">
-        <v>100.367753</v>
+        <v>100.369189</v>
       </c>
       <c r="R513" s="9" t="n">
         <v>100.650982</v>
@@ -42408,7 +42408,7 @@
         <v>100.444945</v>
       </c>
       <c r="Q514" s="6" t="n">
-        <v>100.16217</v>
+        <v>100.162862</v>
       </c>
       <c r="R514" s="6" t="n">
         <v>100.66827</v>
@@ -42492,7 +42492,7 @@
         <v>100.450859</v>
       </c>
       <c r="Q515" s="9" t="n">
-        <v>99.947166</v>
+        <v>99.94708</v>
       </c>
       <c r="R515" s="9" t="n">
         <v>100.677583</v>
@@ -42576,7 +42576,7 @@
         <v>100.427746</v>
       </c>
       <c r="Q516" s="6" t="n">
-        <v>99.767995</v>
+        <v>99.767257</v>
       </c>
       <c r="R516" s="6" t="n">
         <v>100.661862</v>
@@ -42660,7 +42660,7 @@
         <v>100.391661</v>
       </c>
       <c r="Q517" s="9" t="n">
-        <v>99.65320699999999</v>
+        <v>99.65204900000001</v>
       </c>
       <c r="R517" s="9" t="n">
         <v>100.599361</v>
@@ -42744,7 +42744,7 @@
         <v>100.347957</v>
       </c>
       <c r="Q518" s="6" t="n">
-        <v>99.630576</v>
+        <v>99.62932499999999</v>
       </c>
       <c r="R518" s="6" t="n">
         <v>100.490913</v>
@@ -42828,7 +42828,7 @@
         <v>100.314535</v>
       </c>
       <c r="Q519" s="9" t="n">
-        <v>99.69457300000001</v>
+        <v>99.693541</v>
       </c>
       <c r="R519" s="9" t="n">
         <v>100.337616</v>
@@ -42912,7 +42912,7 @@
         <v>100.301948</v>
       </c>
       <c r="Q520" s="6" t="n">
-        <v>99.801202</v>
+        <v>99.800539</v>
       </c>
       <c r="R520" s="6" t="n">
         <v>100.143441</v>
@@ -42996,7 +42996,7 @@
         <v>100.31952</v>
       </c>
       <c r="Q521" s="9" t="n">
-        <v>99.920322</v>
+        <v>99.920072</v>
       </c>
       <c r="R521" s="9" t="n">
         <v>99.924505</v>
@@ -43080,7 +43080,7 @@
         <v>100.375696</v>
       </c>
       <c r="Q522" s="6" t="n">
-        <v>100.043416</v>
+        <v>100.043593</v>
       </c>
       <c r="R522" s="6" t="n">
         <v>99.688456</v>
@@ -43164,7 +43164,7 @@
         <v>100.46012</v>
       </c>
       <c r="Q523" s="9" t="n">
-        <v>100.138478</v>
+        <v>100.138979</v>
       </c>
       <c r="R523" s="9" t="n">
         <v>99.45082499999999</v>
@@ -43248,7 +43248,7 @@
         <v>100.548361</v>
       </c>
       <c r="Q524" s="6" t="n">
-        <v>100.200833</v>
+        <v>100.201541</v>
       </c>
       <c r="R524" s="6" t="n">
         <v>99.224676</v>
@@ -43332,7 +43332,7 @@
         <v>100.632198</v>
       </c>
       <c r="Q525" s="9" t="n">
-        <v>100.225158</v>
+        <v>100.225934</v>
       </c>
       <c r="R525" s="9" t="n">
         <v>99.01658399999999</v>
@@ -43416,7 +43416,7 @@
         <v>100.714227</v>
       </c>
       <c r="Q526" s="6" t="n">
-        <v>100.210858</v>
+        <v>100.211562</v>
       </c>
       <c r="R526" s="6" t="n">
         <v>98.832268</v>
@@ -43500,7 +43500,7 @@
         <v>100.803232</v>
       </c>
       <c r="Q527" s="9" t="n">
-        <v>100.172121</v>
+        <v>100.172665</v>
       </c>
       <c r="R527" s="9" t="n">
         <v>98.681269</v>
@@ -43584,7 +43584,7 @@
         <v>100.889331</v>
       </c>
       <c r="Q528" s="6" t="n">
-        <v>100.116177</v>
+        <v>100.116498</v>
       </c>
       <c r="R528" s="6" t="n">
         <v>98.578451</v>
@@ -43668,7 +43668,7 @@
         <v>100.967887</v>
       </c>
       <c r="Q529" s="9" t="n">
-        <v>100.053167</v>
+        <v>100.053238</v>
       </c>
       <c r="R529" s="9" t="n">
         <v>98.52960899999999</v>
@@ -43752,7 +43752,7 @@
         <v>101.04165</v>
       </c>
       <c r="Q530" s="6" t="n">
-        <v>100.010003</v>
+        <v>100.009894</v>
       </c>
       <c r="R530" s="6" t="n">
         <v>98.515494</v>
@@ -43836,7 +43836,7 @@
         <v>101.113018</v>
       </c>
       <c r="Q531" s="9" t="n">
-        <v>100.013716</v>
+        <v>100.013592</v>
       </c>
       <c r="R531" s="9" t="n">
         <v>98.498902</v>
@@ -43920,7 +43920,7 @@
         <v>101.18864</v>
       </c>
       <c r="Q532" s="6" t="n">
-        <v>100.069662</v>
+        <v>100.069709</v>
       </c>
       <c r="R532" s="6" t="n">
         <v>98.445566</v>
@@ -44004,7 +44004,7 @@
         <v>101.268301</v>
       </c>
       <c r="Q533" s="9" t="n">
-        <v>100.139378</v>
+        <v>100.139644</v>
       </c>
       <c r="R533" s="9" t="n">
         <v>98.375821</v>
@@ -44088,7 +44088,7 @@
         <v>101.341732</v>
       </c>
       <c r="Q534" s="6" t="n">
-        <v>100.184547</v>
+        <v>100.184943</v>
       </c>
       <c r="R534" s="6" t="n">
         <v>98.324331</v>
@@ -44172,7 +44172,7 @@
         <v>101.398878</v>
       </c>
       <c r="Q535" s="9" t="n">
-        <v>100.189632</v>
+        <v>100.190012</v>
       </c>
       <c r="R535" s="9" t="n">
         <v>98.323947</v>
@@ -44256,7 +44256,7 @@
         <v>101.427039</v>
       </c>
       <c r="Q536" s="6" t="n">
-        <v>100.153181</v>
+        <v>100.153395</v>
       </c>
       <c r="R536" s="6" t="n">
         <v>98.397749</v>
@@ -44340,7 +44340,7 @@
         <v>101.409301</v>
       </c>
       <c r="Q537" s="9" t="n">
-        <v>100.067761</v>
+        <v>100.067633</v>
       </c>
       <c r="R537" s="9" t="n">
         <v>98.57089000000001</v>
@@ -44424,7 +44424,7 @@
         <v>101.343667</v>
       </c>
       <c r="Q538" s="6" t="n">
-        <v>99.93894299999999</v>
+        <v>99.93831400000001</v>
       </c>
       <c r="R538" s="6" t="n">
         <v>98.855294</v>
@@ -44508,7 +44508,7 @@
         <v>101.236576</v>
       </c>
       <c r="Q539" s="9" t="n">
-        <v>99.783644</v>
+        <v>99.782419</v>
       </c>
       <c r="R539" s="9" t="n">
         <v>99.23741200000001</v>
@@ -44592,7 +44592,7 @@
         <v>101.109561</v>
       </c>
       <c r="Q540" s="6" t="n">
-        <v>99.62483899999999</v>
+        <v>99.62300399999999</v>
       </c>
       <c r="R540" s="6" t="n">
         <v>99.667238</v>
@@ -44676,7 +44676,7 @@
         <v>100.972291</v>
       </c>
       <c r="Q541" s="9" t="n">
-        <v>99.472677</v>
+        <v>99.470253</v>
       </c>
       <c r="R541" s="9" t="n">
         <v>100.115067</v>
@@ -44760,7 +44760,7 @@
         <v>100.819307</v>
       </c>
       <c r="Q542" s="6" t="n">
-        <v>99.336128</v>
+        <v>99.333169</v>
       </c>
       <c r="R542" s="6" t="n">
         <v>100.53274</v>
@@ -44844,7 +44844,7 @@
         <v>100.66315</v>
       </c>
       <c r="Q543" s="9" t="n">
-        <v>99.221727</v>
+        <v>99.21830799999999</v>
       </c>
       <c r="R543" s="9" t="n">
         <v>100.886346</v>
@@ -44928,7 +44928,7 @@
         <v>100.501417</v>
       </c>
       <c r="Q544" s="6" t="n">
-        <v>99.14724099999999</v>
+        <v>99.14349799999999</v>
       </c>
       <c r="R544" s="6" t="n">
         <v>101.165426</v>
@@ -45012,7 +45012,7 @@
         <v>100.328765</v>
       </c>
       <c r="Q545" s="9" t="n">
-        <v>99.127163</v>
+        <v>99.123283</v>
       </c>
       <c r="R545" s="9" t="n">
         <v>101.357244</v>
@@ -45096,7 +45096,7 @@
         <v>100.149457</v>
       </c>
       <c r="Q546" s="6" t="n">
-        <v>99.16571</v>
+        <v>99.161889</v>
       </c>
       <c r="R546" s="6" t="n">
         <v>101.461922</v>
@@ -45180,7 +45180,7 @@
         <v>99.966641</v>
       </c>
       <c r="Q547" s="9" t="n">
-        <v>99.251963</v>
+        <v>99.24835899999999</v>
       </c>
       <c r="R547" s="9" t="n">
         <v>101.473213</v>
@@ -45264,7 +45264,7 @@
         <v>99.80820199999999</v>
       </c>
       <c r="Q548" s="6" t="n">
-        <v>99.372514</v>
+        <v>99.369235</v>
       </c>
       <c r="R548" s="6" t="n">
         <v>101.396573</v>
@@ -45348,7 +45348,7 @@
         <v>99.696308</v>
       </c>
       <c r="Q549" s="9" t="n">
-        <v>99.51421000000001</v>
+        <v>99.511323</v>
       </c>
       <c r="R549" s="9" t="n">
         <v>101.247851</v>
@@ -45432,7 +45432,7 @@
         <v>99.651686</v>
       </c>
       <c r="Q550" s="6" t="n">
-        <v>99.654281</v>
+        <v>99.65178400000001</v>
       </c>
       <c r="R550" s="6" t="n">
         <v>101.048854</v>
@@ -45516,7 +45516,7 @@
         <v>99.644609</v>
       </c>
       <c r="Q551" s="9" t="n">
-        <v>99.784363</v>
+        <v>99.78225</v>
       </c>
       <c r="R551" s="9" t="n">
         <v>100.834673</v>
@@ -45600,7 +45600,7 @@
         <v>99.64967900000001</v>
       </c>
       <c r="Q552" s="6" t="n">
-        <v>99.91254600000001</v>
+        <v>99.910884</v>
       </c>
       <c r="R552" s="6" t="n">
         <v>100.630632</v>
@@ -45684,7 +45684,7 @@
         <v>99.642844</v>
       </c>
       <c r="Q553" s="9" t="n">
-        <v>100.047651</v>
+        <v>100.046594</v>
       </c>
       <c r="R553" s="9" t="n">
         <v>100.448813</v>
@@ -45768,7 +45768,7 @@
         <v>99.617773</v>
       </c>
       <c r="Q554" s="6" t="n">
-        <v>100.186812</v>
+        <v>100.186579</v>
       </c>
       <c r="R554" s="6" t="n">
         <v>100.281068</v>
@@ -45852,7 +45852,7 @@
         <v>99.57182</v>
       </c>
       <c r="Q555" s="9" t="n">
-        <v>100.316216</v>
+        <v>100.317047</v>
       </c>
       <c r="R555" s="9" t="n">
         <v>100.119486</v>
@@ -45936,7 +45936,7 @@
         <v>99.51242000000001</v>
       </c>
       <c r="Q556" s="6" t="n">
-        <v>100.435533</v>
+        <v>100.437709</v>
       </c>
       <c r="R556" s="6" t="n">
         <v>99.959986</v>
@@ -46020,7 +46020,7 @@
         <v>99.44973400000001</v>
       </c>
       <c r="Q557" s="9" t="n">
-        <v>100.544096</v>
+        <v>100.547861</v>
       </c>
       <c r="R557" s="9" t="n">
         <v>99.806404</v>
@@ -46104,7 +46104,7 @@
         <v>99.38923200000001</v>
       </c>
       <c r="Q558" s="6" t="n">
-        <v>100.634441</v>
+        <v>100.639832</v>
       </c>
       <c r="R558" s="6" t="n">
         <v>99.676424</v>
@@ -46188,7 +46188,7 @@
         <v>99.333716</v>
       </c>
       <c r="Q559" s="9" t="n">
-        <v>100.687597</v>
+        <v>100.694158</v>
       </c>
       <c r="R559" s="9" t="n">
         <v>99.591228</v>
@@ -46272,7 +46272,7 @@
         <v>99.286867</v>
       </c>
       <c r="Q560" s="6" t="n">
-        <v>100.689859</v>
+        <v>100.696326</v>
       </c>
       <c r="R560" s="6" t="n">
         <v>99.562355</v>
@@ -46356,7 +46356,7 @@
         <v>99.253601</v>
       </c>
       <c r="Q561" s="9" t="n">
-        <v>100.654205</v>
+        <v>100.658182</v>
       </c>
       <c r="R561" s="9" t="n">
         <v>99.568915</v>
@@ -46440,7 +46440,7 @@
         <v>99.236124</v>
       </c>
       <c r="Q562" s="6" t="n">
-        <v>100.5928</v>
+        <v>100.59035</v>
       </c>
       <c r="R562" s="6" t="n">
         <v>99.595789</v>
@@ -46524,7 +46524,7 @@
         <v>99.24297300000001</v>
       </c>
       <c r="Q563" s="9" t="n">
-        <v>100.511198</v>
+        <v>100.496565</v>
       </c>
       <c r="R563" s="9" t="n">
         <v>99.62963999999999</v>
@@ -46608,7 +46608,7 @@
         <v>99.264543</v>
       </c>
       <c r="Q564" s="6" t="n">
-        <v>100.418174</v>
+        <v>100.383987</v>
       </c>
       <c r="R564" s="6" t="n">
         <v>99.659767</v>
@@ -46680,7 +46680,7 @@
         <v>99.300256</v>
       </c>
       <c r="Q565" s="9" t="n">
-        <v>100.318829</v>
+        <v>100.257128</v>
       </c>
       <c r="R565" s="9" t="n">
         <v>99.68128400000001</v>

--- a/downloads/indicadores/SIC/SIC_datos.xlsx
+++ b/downloads/indicadores/SIC/SIC_datos.xlsx
@@ -671,11 +671,11 @@
         <v>97.077684</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>98.58717300000001</v>
+        <v>98.586946</v>
       </c>
       <c r="K6" s="6" t="n"/>
       <c r="L6" s="6" t="n">
-        <v>97.319694</v>
+        <v>97.316185</v>
       </c>
       <c r="M6" s="6" t="n"/>
       <c r="N6" s="6" t="n">
@@ -743,11 +743,11 @@
         <v>97.248456</v>
       </c>
       <c r="J7" s="9" t="n">
-        <v>98.620119</v>
+        <v>98.619894</v>
       </c>
       <c r="K7" s="9" t="n"/>
       <c r="L7" s="9" t="n">
-        <v>97.457849</v>
+        <v>97.454514</v>
       </c>
       <c r="M7" s="9" t="n"/>
       <c r="N7" s="9" t="n">
@@ -815,11 +815,11 @@
         <v>97.42827800000001</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>98.65603900000001</v>
+        <v>98.655816</v>
       </c>
       <c r="K8" s="6" t="n"/>
       <c r="L8" s="6" t="n">
-        <v>97.58938000000001</v>
+        <v>97.586213</v>
       </c>
       <c r="M8" s="6" t="n"/>
       <c r="N8" s="6" t="n">
@@ -887,11 +887,11 @@
         <v>97.611076</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>98.701128</v>
+        <v>98.700909</v>
       </c>
       <c r="K9" s="9" t="n"/>
       <c r="L9" s="9" t="n">
-        <v>97.720654</v>
+        <v>97.717659</v>
       </c>
       <c r="M9" s="9" t="n"/>
       <c r="N9" s="9" t="n">
@@ -959,11 +959,11 @@
         <v>97.826522</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>98.76903299999999</v>
+        <v>98.768818</v>
       </c>
       <c r="K10" s="6" t="n"/>
       <c r="L10" s="6" t="n">
-        <v>97.861007</v>
+        <v>97.85819600000001</v>
       </c>
       <c r="M10" s="6" t="n"/>
       <c r="N10" s="6" t="n">
@@ -1031,11 +1031,11 @@
         <v>98.09350499999999</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>98.871028</v>
+        <v>98.87081999999999</v>
       </c>
       <c r="K11" s="9" t="n"/>
       <c r="L11" s="9" t="n">
-        <v>98.023399</v>
+        <v>98.02079999999999</v>
       </c>
       <c r="M11" s="9" t="n"/>
       <c r="N11" s="9" t="n">
@@ -1103,11 +1103,11 @@
         <v>98.40176700000001</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>99.01839099999999</v>
+        <v>99.018193</v>
       </c>
       <c r="K12" s="6" t="n"/>
       <c r="L12" s="6" t="n">
-        <v>98.217446</v>
+        <v>98.21510000000001</v>
       </c>
       <c r="M12" s="6" t="n"/>
       <c r="N12" s="6" t="n">
@@ -1175,11 +1175,11 @@
         <v>98.74391900000001</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>99.22478</v>
+        <v>99.22459600000001</v>
       </c>
       <c r="K13" s="9" t="n"/>
       <c r="L13" s="9" t="n">
-        <v>98.445128</v>
+        <v>98.443079</v>
       </c>
       <c r="M13" s="9" t="n"/>
       <c r="N13" s="9" t="n">
@@ -1247,11 +1247,11 @@
         <v>99.11490999999999</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>99.47457799999999</v>
+        <v>99.474411</v>
       </c>
       <c r="K14" s="6" t="n"/>
       <c r="L14" s="6" t="n">
-        <v>98.696641</v>
+        <v>98.69492</v>
       </c>
       <c r="M14" s="6" t="n"/>
       <c r="N14" s="6" t="n">
@@ -1319,11 +1319,11 @@
         <v>99.513266</v>
       </c>
       <c r="J15" s="9" t="n">
-        <v>99.753721</v>
+        <v>99.753573</v>
       </c>
       <c r="K15" s="9" t="n"/>
       <c r="L15" s="9" t="n">
-        <v>98.961184</v>
+        <v>98.959808</v>
       </c>
       <c r="M15" s="9" t="n"/>
       <c r="N15" s="9" t="n">
@@ -1391,11 +1391,11 @@
         <v>99.91264099999999</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>100.041046</v>
+        <v>100.040917</v>
       </c>
       <c r="K16" s="6" t="n"/>
       <c r="L16" s="6" t="n">
-        <v>99.231365</v>
+        <v>99.23034199999999</v>
       </c>
       <c r="M16" s="6" t="n"/>
       <c r="N16" s="6" t="n">
@@ -1463,11 +1463,11 @@
         <v>100.294977</v>
       </c>
       <c r="J17" s="9" t="n">
-        <v>100.321862</v>
+        <v>100.321753</v>
       </c>
       <c r="K17" s="9" t="n"/>
       <c r="L17" s="9" t="n">
-        <v>99.519037</v>
+        <v>99.518393</v>
       </c>
       <c r="M17" s="9" t="n"/>
       <c r="N17" s="9" t="n">
@@ -1539,11 +1539,11 @@
         <v>100.670598</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>100.588009</v>
+        <v>100.587918</v>
       </c>
       <c r="K18" s="6" t="n"/>
       <c r="L18" s="6" t="n">
-        <v>99.83847</v>
+        <v>99.838246</v>
       </c>
       <c r="M18" s="6" t="n"/>
       <c r="N18" s="6" t="n">
@@ -1617,11 +1617,11 @@
         <v>101.023649</v>
       </c>
       <c r="J19" s="9" t="n">
-        <v>100.838095</v>
+        <v>100.83802</v>
       </c>
       <c r="K19" s="9" t="n"/>
       <c r="L19" s="9" t="n">
-        <v>100.187992</v>
+        <v>100.18823</v>
       </c>
       <c r="M19" s="9" t="n"/>
       <c r="N19" s="9" t="n">
@@ -1695,11 +1695,11 @@
         <v>101.34911</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>101.073479</v>
+        <v>101.07342</v>
       </c>
       <c r="K20" s="6" t="n"/>
       <c r="L20" s="6" t="n">
-        <v>100.55915</v>
+        <v>100.559881</v>
       </c>
       <c r="M20" s="6" t="n"/>
       <c r="N20" s="6" t="n">
@@ -1773,11 +1773,11 @@
         <v>101.651244</v>
       </c>
       <c r="J21" s="9" t="n">
-        <v>101.289492</v>
+        <v>101.289448</v>
       </c>
       <c r="K21" s="9" t="n"/>
       <c r="L21" s="9" t="n">
-        <v>100.943042</v>
+        <v>100.944282</v>
       </c>
       <c r="M21" s="9" t="n"/>
       <c r="N21" s="9" t="n">
@@ -1851,11 +1851,11 @@
         <v>101.90494</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>101.48141</v>
+        <v>101.481379</v>
       </c>
       <c r="K22" s="6" t="n"/>
       <c r="L22" s="6" t="n">
-        <v>101.330218</v>
+        <v>101.331971</v>
       </c>
       <c r="M22" s="6" t="n"/>
       <c r="N22" s="6" t="n">
@@ -1929,11 +1929,11 @@
         <v>102.110513</v>
       </c>
       <c r="J23" s="9" t="n">
-        <v>101.651922</v>
+        <v>101.651903</v>
       </c>
       <c r="K23" s="9" t="n"/>
       <c r="L23" s="9" t="n">
-        <v>101.710752</v>
+        <v>101.713007</v>
       </c>
       <c r="M23" s="9" t="n"/>
       <c r="N23" s="9" t="n">
@@ -2007,11 +2007,11 @@
         <v>102.284513</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>101.801915</v>
+        <v>101.801905</v>
       </c>
       <c r="K24" s="6" t="n"/>
       <c r="L24" s="6" t="n">
-        <v>102.072578</v>
+        <v>102.075306</v>
       </c>
       <c r="M24" s="6" t="n"/>
       <c r="N24" s="6" t="n">
@@ -2085,11 +2085,11 @@
         <v>102.435834</v>
       </c>
       <c r="J25" s="9" t="n">
-        <v>101.923297</v>
+        <v>101.923296</v>
       </c>
       <c r="K25" s="9" t="n"/>
       <c r="L25" s="9" t="n">
-        <v>102.403093</v>
+        <v>102.406253</v>
       </c>
       <c r="M25" s="9" t="n"/>
       <c r="N25" s="9" t="n">
@@ -2163,11 +2163,11 @@
         <v>102.551122</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>102.008314</v>
+        <v>102.008319</v>
       </c>
       <c r="K26" s="6" t="n"/>
       <c r="L26" s="6" t="n">
-        <v>102.68716</v>
+        <v>102.690691</v>
       </c>
       <c r="M26" s="6" t="n"/>
       <c r="N26" s="6" t="n">
@@ -2241,11 +2241,11 @@
         <v>102.623419</v>
       </c>
       <c r="J27" s="9" t="n">
-        <v>102.053854</v>
+        <v>102.053862</v>
       </c>
       <c r="K27" s="9" t="n"/>
       <c r="L27" s="9" t="n">
-        <v>102.904778</v>
+        <v>102.908593</v>
       </c>
       <c r="M27" s="9" t="n"/>
       <c r="N27" s="9" t="n">
@@ -2319,11 +2319,11 @@
         <v>102.616518</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>102.067887</v>
+        <v>102.067896</v>
       </c>
       <c r="K28" s="6" t="n"/>
       <c r="L28" s="6" t="n">
-        <v>103.041282</v>
+        <v>103.045276</v>
       </c>
       <c r="M28" s="6" t="n"/>
       <c r="N28" s="6" t="n">
@@ -2397,11 +2397,11 @@
         <v>102.510761</v>
       </c>
       <c r="J29" s="9" t="n">
-        <v>102.057652</v>
+        <v>102.05766</v>
       </c>
       <c r="K29" s="9" t="n"/>
       <c r="L29" s="9" t="n">
-        <v>103.088254</v>
+        <v>103.092311</v>
       </c>
       <c r="M29" s="9" t="n"/>
       <c r="N29" s="9" t="n">
@@ -2475,11 +2475,11 @@
         <v>102.331246</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>102.028814</v>
+        <v>102.028821</v>
       </c>
       <c r="K30" s="6" t="n"/>
       <c r="L30" s="6" t="n">
-        <v>103.048994</v>
+        <v>103.053003</v>
       </c>
       <c r="M30" s="6" t="n"/>
       <c r="N30" s="6" t="n">
@@ -2553,11 +2553,11 @@
         <v>102.131764</v>
       </c>
       <c r="J31" s="9" t="n">
-        <v>101.972544</v>
+        <v>101.972547</v>
       </c>
       <c r="K31" s="9" t="n"/>
       <c r="L31" s="9" t="n">
-        <v>102.94501</v>
+        <v>102.948886</v>
       </c>
       <c r="M31" s="9" t="n"/>
       <c r="N31" s="9" t="n">
@@ -2631,11 +2631,11 @@
         <v>101.942937</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>101.879115</v>
+        <v>101.879111</v>
       </c>
       <c r="K32" s="6" t="n"/>
       <c r="L32" s="6" t="n">
-        <v>102.801102</v>
+        <v>102.804793</v>
       </c>
       <c r="M32" s="6" t="n"/>
       <c r="N32" s="6" t="n">
@@ -2709,11 +2709,11 @@
         <v>101.786291</v>
       </c>
       <c r="J33" s="9" t="n">
-        <v>101.742962</v>
+        <v>101.74295</v>
       </c>
       <c r="K33" s="9" t="n"/>
       <c r="L33" s="9" t="n">
-        <v>102.631013</v>
+        <v>102.634483</v>
       </c>
       <c r="M33" s="9" t="n"/>
       <c r="N33" s="9" t="n">
@@ -2787,11 +2787,11 @@
         <v>101.641863</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>101.562451</v>
+        <v>101.562426</v>
       </c>
       <c r="K34" s="6" t="n"/>
       <c r="L34" s="6" t="n">
-        <v>102.430556</v>
+        <v>102.433761</v>
       </c>
       <c r="M34" s="6" t="n"/>
       <c r="N34" s="6" t="n">
@@ -2865,11 +2865,11 @@
         <v>101.477899</v>
       </c>
       <c r="J35" s="9" t="n">
-        <v>101.331819</v>
+        <v>101.331778</v>
       </c>
       <c r="K35" s="9" t="n"/>
       <c r="L35" s="9" t="n">
-        <v>102.184822</v>
+        <v>102.187703</v>
       </c>
       <c r="M35" s="9" t="n"/>
       <c r="N35" s="9" t="n">
@@ -2943,11 +2943,11 @@
         <v>101.283369</v>
       </c>
       <c r="J36" s="6" t="n">
-        <v>101.054861</v>
+        <v>101.054802</v>
       </c>
       <c r="K36" s="6" t="n"/>
       <c r="L36" s="6" t="n">
-        <v>101.876632</v>
+        <v>101.879104</v>
       </c>
       <c r="M36" s="6" t="n"/>
       <c r="N36" s="6" t="n">
@@ -3021,11 +3021,11 @@
         <v>101.049162</v>
       </c>
       <c r="J37" s="9" t="n">
-        <v>100.743844</v>
+        <v>100.743763</v>
       </c>
       <c r="K37" s="9" t="n"/>
       <c r="L37" s="9" t="n">
-        <v>101.50901</v>
+        <v>101.510996</v>
       </c>
       <c r="M37" s="9" t="n"/>
       <c r="N37" s="9" t="n">
@@ -3099,11 +3099,11 @@
         <v>100.761497</v>
       </c>
       <c r="J38" s="6" t="n">
-        <v>100.410857</v>
+        <v>100.410754</v>
       </c>
       <c r="K38" s="6" t="n"/>
       <c r="L38" s="6" t="n">
-        <v>101.105963</v>
+        <v>101.107416</v>
       </c>
       <c r="M38" s="6" t="n"/>
       <c r="N38" s="6" t="n">
@@ -3177,11 +3177,11 @@
         <v>100.426977</v>
       </c>
       <c r="J39" s="9" t="n">
-        <v>100.075436</v>
+        <v>100.07531</v>
       </c>
       <c r="K39" s="9" t="n"/>
       <c r="L39" s="9" t="n">
-        <v>100.70147</v>
+        <v>100.702392</v>
       </c>
       <c r="M39" s="9" t="n"/>
       <c r="N39" s="9" t="n">
@@ -3255,11 +3255,11 @@
         <v>100.089177</v>
       </c>
       <c r="J40" s="6" t="n">
-        <v>99.760775</v>
+        <v>99.760628</v>
       </c>
       <c r="K40" s="6" t="n"/>
       <c r="L40" s="6" t="n">
-        <v>100.323783</v>
+        <v>100.324211</v>
       </c>
       <c r="M40" s="6" t="n"/>
       <c r="N40" s="6" t="n">
@@ -3333,11 +3333,11 @@
         <v>99.77144</v>
       </c>
       <c r="J41" s="9" t="n">
-        <v>99.456463</v>
+        <v>99.456295</v>
       </c>
       <c r="K41" s="9" t="n"/>
       <c r="L41" s="9" t="n">
-        <v>99.981026</v>
+        <v>99.98100700000001</v>
       </c>
       <c r="M41" s="9" t="n"/>
       <c r="N41" s="9" t="n">
@@ -3411,11 +3411,11 @@
         <v>99.47217499999999</v>
       </c>
       <c r="J42" s="6" t="n">
-        <v>99.165311</v>
+        <v>99.16512299999999</v>
       </c>
       <c r="K42" s="6" t="n"/>
       <c r="L42" s="6" t="n">
-        <v>99.677126</v>
+        <v>99.67671</v>
       </c>
       <c r="M42" s="6" t="n"/>
       <c r="N42" s="6" t="n">
@@ -3489,11 +3489,11 @@
         <v>99.193282</v>
       </c>
       <c r="J43" s="9" t="n">
-        <v>98.899021</v>
+        <v>98.898816</v>
       </c>
       <c r="K43" s="9" t="n"/>
       <c r="L43" s="9" t="n">
-        <v>99.413718</v>
+        <v>99.41295599999999</v>
       </c>
       <c r="M43" s="9" t="n"/>
       <c r="N43" s="9" t="n">
@@ -3567,11 +3567,11 @@
         <v>98.93933</v>
       </c>
       <c r="J44" s="6" t="n">
-        <v>98.675944</v>
+        <v>98.675723</v>
       </c>
       <c r="K44" s="6" t="n"/>
       <c r="L44" s="6" t="n">
-        <v>99.190757</v>
+        <v>99.1897</v>
       </c>
       <c r="M44" s="6" t="n"/>
       <c r="N44" s="6" t="n">
@@ -3645,11 +3645,11 @@
         <v>98.72855199999999</v>
       </c>
       <c r="J45" s="9" t="n">
-        <v>98.505844</v>
+        <v>98.505612</v>
       </c>
       <c r="K45" s="9" t="n"/>
       <c r="L45" s="9" t="n">
-        <v>99.00913</v>
+        <v>99.00783300000001</v>
       </c>
       <c r="M45" s="9" t="n"/>
       <c r="N45" s="9" t="n">
@@ -3723,11 +3723,11 @@
         <v>98.60877000000001</v>
       </c>
       <c r="J46" s="6" t="n">
-        <v>98.386092</v>
+        <v>98.385851</v>
       </c>
       <c r="K46" s="6" t="n"/>
       <c r="L46" s="6" t="n">
-        <v>98.86191599999999</v>
+        <v>98.86042399999999</v>
       </c>
       <c r="M46" s="6" t="n"/>
       <c r="N46" s="6" t="n">
@@ -3801,11 +3801,11 @@
         <v>98.573397</v>
       </c>
       <c r="J47" s="9" t="n">
-        <v>98.318573</v>
+        <v>98.31832799999999</v>
       </c>
       <c r="K47" s="9" t="n"/>
       <c r="L47" s="9" t="n">
-        <v>98.742594</v>
+        <v>98.740943</v>
       </c>
       <c r="M47" s="9" t="n"/>
       <c r="N47" s="9" t="n">
@@ -3879,11 +3879,11 @@
         <v>98.60900599999999</v>
       </c>
       <c r="J48" s="6" t="n">
-        <v>98.30156700000001</v>
+        <v>98.301321</v>
       </c>
       <c r="K48" s="6" t="n"/>
       <c r="L48" s="6" t="n">
-        <v>98.656136</v>
+        <v>98.65436800000001</v>
       </c>
       <c r="M48" s="6" t="n"/>
       <c r="N48" s="6" t="n">
@@ -3957,11 +3957,11 @@
         <v>98.700958</v>
       </c>
       <c r="J49" s="9" t="n">
-        <v>98.332418</v>
+        <v>98.33217399999999</v>
       </c>
       <c r="K49" s="9" t="n"/>
       <c r="L49" s="9" t="n">
-        <v>98.59921199999999</v>
+        <v>98.59736700000001</v>
       </c>
       <c r="M49" s="9" t="n"/>
       <c r="N49" s="9" t="n">
@@ -4035,11 +4035,11 @@
         <v>98.861086</v>
       </c>
       <c r="J50" s="6" t="n">
-        <v>98.404588</v>
+        <v>98.404349</v>
       </c>
       <c r="K50" s="6" t="n"/>
       <c r="L50" s="6" t="n">
-        <v>98.56798000000001</v>
+        <v>98.566091</v>
       </c>
       <c r="M50" s="6" t="n"/>
       <c r="N50" s="6" t="n">
@@ -4113,11 +4113,11 @@
         <v>99.074564</v>
       </c>
       <c r="J51" s="9" t="n">
-        <v>98.51092</v>
+        <v>98.510688</v>
       </c>
       <c r="K51" s="9" t="n"/>
       <c r="L51" s="9" t="n">
-        <v>98.55940200000001</v>
+        <v>98.557501</v>
       </c>
       <c r="M51" s="9" t="n"/>
       <c r="N51" s="9" t="n">
@@ -4191,11 +4191,11 @@
         <v>99.30423</v>
       </c>
       <c r="J52" s="6" t="n">
-        <v>98.64318</v>
+        <v>98.64295799999999</v>
       </c>
       <c r="K52" s="6" t="n"/>
       <c r="L52" s="6" t="n">
-        <v>98.574197</v>
+        <v>98.572316</v>
       </c>
       <c r="M52" s="6" t="n"/>
       <c r="N52" s="6" t="n">
@@ -4269,11 +4269,11 @@
         <v>99.55011399999999</v>
       </c>
       <c r="J53" s="9" t="n">
-        <v>98.79303899999999</v>
+        <v>98.792827</v>
       </c>
       <c r="K53" s="9" t="n"/>
       <c r="L53" s="9" t="n">
-        <v>98.61604800000001</v>
+        <v>98.614223</v>
       </c>
       <c r="M53" s="9" t="n"/>
       <c r="N53" s="9" t="n">
@@ -4347,11 +4347,11 @@
         <v>99.781046</v>
       </c>
       <c r="J54" s="6" t="n">
-        <v>98.945735</v>
+        <v>98.945533</v>
       </c>
       <c r="K54" s="6" t="n"/>
       <c r="L54" s="6" t="n">
-        <v>98.68562799999999</v>
+        <v>98.683897</v>
       </c>
       <c r="M54" s="6" t="n"/>
       <c r="N54" s="6" t="n">
@@ -4425,11 +4425,11 @@
         <v>99.941086</v>
       </c>
       <c r="J55" s="9" t="n">
-        <v>99.101055</v>
+        <v>99.100864</v>
       </c>
       <c r="K55" s="9" t="n"/>
       <c r="L55" s="9" t="n">
-        <v>98.77939000000001</v>
+        <v>98.777784</v>
       </c>
       <c r="M55" s="9" t="n"/>
       <c r="N55" s="9" t="n">
@@ -4503,11 +4503,11 @@
         <v>100.040716</v>
       </c>
       <c r="J56" s="6" t="n">
-        <v>99.25783300000001</v>
+        <v>99.25765199999999</v>
       </c>
       <c r="K56" s="6" t="n"/>
       <c r="L56" s="6" t="n">
-        <v>98.892691</v>
+        <v>98.89123499999999</v>
       </c>
       <c r="M56" s="6" t="n"/>
       <c r="N56" s="6" t="n">
@@ -4581,11 +4581,11 @@
         <v>100.101148</v>
       </c>
       <c r="J57" s="9" t="n">
-        <v>99.420851</v>
+        <v>99.420682</v>
       </c>
       <c r="K57" s="9" t="n"/>
       <c r="L57" s="9" t="n">
-        <v>99.018602</v>
+        <v>99.017312</v>
       </c>
       <c r="M57" s="9" t="n"/>
       <c r="N57" s="9" t="n">
@@ -4659,11 +4659,11 @@
         <v>100.161708</v>
       </c>
       <c r="J58" s="6" t="n">
-        <v>99.5958</v>
+        <v>99.595643</v>
       </c>
       <c r="K58" s="6" t="n"/>
       <c r="L58" s="6" t="n">
-        <v>99.161614</v>
+        <v>99.16051299999999</v>
       </c>
       <c r="M58" s="6" t="n"/>
       <c r="N58" s="6" t="n">
@@ -4737,11 +4737,11 @@
         <v>100.272424</v>
       </c>
       <c r="J59" s="9" t="n">
-        <v>99.78183300000001</v>
+        <v>99.78168700000001</v>
       </c>
       <c r="K59" s="9" t="n"/>
       <c r="L59" s="9" t="n">
-        <v>99.326081</v>
+        <v>99.325194</v>
       </c>
       <c r="M59" s="9" t="n"/>
       <c r="N59" s="9" t="n">
@@ -4815,11 +4815,11 @@
         <v>100.412956</v>
       </c>
       <c r="J60" s="6" t="n">
-        <v>99.965822</v>
+        <v>99.965689</v>
       </c>
       <c r="K60" s="6" t="n"/>
       <c r="L60" s="6" t="n">
-        <v>99.513823</v>
+        <v>99.513182</v>
       </c>
       <c r="M60" s="6" t="n"/>
       <c r="N60" s="6" t="n">
@@ -4893,11 +4893,11 @@
         <v>100.526736</v>
       </c>
       <c r="J61" s="9" t="n">
-        <v>100.135873</v>
+        <v>100.135751</v>
       </c>
       <c r="K61" s="9" t="n"/>
       <c r="L61" s="9" t="n">
-        <v>99.721763</v>
+        <v>99.721394</v>
       </c>
       <c r="M61" s="9" t="n"/>
       <c r="N61" s="9" t="n">
@@ -4971,11 +4971,11 @@
         <v>100.60814</v>
       </c>
       <c r="J62" s="6" t="n">
-        <v>100.291232</v>
+        <v>100.291121</v>
       </c>
       <c r="K62" s="6" t="n"/>
       <c r="L62" s="6" t="n">
-        <v>99.93935</v>
+        <v>99.93926500000001</v>
       </c>
       <c r="M62" s="6" t="n"/>
       <c r="N62" s="6" t="n">
@@ -5049,11 +5049,11 @@
         <v>100.660625</v>
       </c>
       <c r="J63" s="9" t="n">
-        <v>100.437806</v>
+        <v>100.437705</v>
       </c>
       <c r="K63" s="9" t="n"/>
       <c r="L63" s="9" t="n">
-        <v>100.147988</v>
+        <v>100.148179</v>
       </c>
       <c r="M63" s="9" t="n"/>
       <c r="N63" s="9" t="n">
@@ -5127,11 +5127,11 @@
         <v>100.739041</v>
       </c>
       <c r="J64" s="6" t="n">
-        <v>100.603176</v>
+        <v>100.603087</v>
       </c>
       <c r="K64" s="6" t="n"/>
       <c r="L64" s="6" t="n">
-        <v>100.328747</v>
+        <v>100.329176</v>
       </c>
       <c r="M64" s="6" t="n"/>
       <c r="N64" s="6" t="n">
@@ -5205,11 +5205,11 @@
         <v>100.85617</v>
       </c>
       <c r="J65" s="9" t="n">
-        <v>100.773103</v>
+        <v>100.773025</v>
       </c>
       <c r="K65" s="9" t="n"/>
       <c r="L65" s="9" t="n">
-        <v>100.471841</v>
+        <v>100.47246</v>
       </c>
       <c r="M65" s="9" t="n"/>
       <c r="N65" s="9" t="n">
@@ -5283,11 +5283,11 @@
         <v>100.98882</v>
       </c>
       <c r="J66" s="6" t="n">
-        <v>100.930425</v>
+        <v>100.930358</v>
       </c>
       <c r="K66" s="6" t="n"/>
       <c r="L66" s="6" t="n">
-        <v>100.577966</v>
+        <v>100.578726</v>
       </c>
       <c r="M66" s="6" t="n"/>
       <c r="N66" s="6" t="n">
@@ -5361,11 +5361,11 @@
         <v>101.111137</v>
       </c>
       <c r="J67" s="9" t="n">
-        <v>101.064028</v>
+        <v>101.06397</v>
       </c>
       <c r="K67" s="9" t="n"/>
       <c r="L67" s="9" t="n">
-        <v>100.653472</v>
+        <v>100.654331</v>
       </c>
       <c r="M67" s="9" t="n"/>
       <c r="N67" s="9" t="n">
@@ -5439,11 +5439,11 @@
         <v>101.195283</v>
       </c>
       <c r="J68" s="6" t="n">
-        <v>101.165233</v>
+        <v>101.165182</v>
       </c>
       <c r="K68" s="6" t="n"/>
       <c r="L68" s="6" t="n">
-        <v>100.711073</v>
+        <v>100.712009</v>
       </c>
       <c r="M68" s="6" t="n"/>
       <c r="N68" s="6" t="n">
@@ -5517,11 +5517,11 @@
         <v>101.252232</v>
       </c>
       <c r="J69" s="9" t="n">
-        <v>101.237855</v>
+        <v>101.237809</v>
       </c>
       <c r="K69" s="9" t="n"/>
       <c r="L69" s="9" t="n">
-        <v>100.750763</v>
+        <v>100.751751</v>
       </c>
       <c r="M69" s="9" t="n"/>
       <c r="N69" s="9" t="n">
@@ -5595,11 +5595,11 @@
         <v>101.29234</v>
       </c>
       <c r="J70" s="6" t="n">
-        <v>101.301148</v>
+        <v>101.301106</v>
       </c>
       <c r="K70" s="6" t="n"/>
       <c r="L70" s="6" t="n">
-        <v>100.76974</v>
+        <v>100.770752</v>
       </c>
       <c r="M70" s="6" t="n"/>
       <c r="N70" s="6" t="n">
@@ -5673,11 +5673,11 @@
         <v>101.33056</v>
       </c>
       <c r="J71" s="9" t="n">
-        <v>101.354806</v>
+        <v>101.354768</v>
       </c>
       <c r="K71" s="9" t="n"/>
       <c r="L71" s="9" t="n">
-        <v>100.764562</v>
+        <v>100.765566</v>
       </c>
       <c r="M71" s="9" t="n"/>
       <c r="N71" s="9" t="n">
@@ -5751,11 +5751,11 @@
         <v>101.338021</v>
       </c>
       <c r="J72" s="6" t="n">
-        <v>101.381146</v>
+        <v>101.38111</v>
       </c>
       <c r="K72" s="6" t="n"/>
       <c r="L72" s="6" t="n">
-        <v>100.725208</v>
+        <v>100.726159</v>
       </c>
       <c r="M72" s="6" t="n"/>
       <c r="N72" s="6" t="n">
@@ -5829,11 +5829,11 @@
         <v>101.310903</v>
       </c>
       <c r="J73" s="9" t="n">
-        <v>101.365597</v>
+        <v>101.365559</v>
       </c>
       <c r="K73" s="9" t="n"/>
       <c r="L73" s="9" t="n">
-        <v>100.642431</v>
+        <v>100.643273</v>
       </c>
       <c r="M73" s="9" t="n"/>
       <c r="N73" s="9" t="n">
@@ -5907,11 +5907,11 @@
         <v>101.231927</v>
       </c>
       <c r="J74" s="6" t="n">
-        <v>101.311635</v>
+        <v>101.311594</v>
       </c>
       <c r="K74" s="6" t="n"/>
       <c r="L74" s="6" t="n">
-        <v>100.523078</v>
+        <v>100.523763</v>
       </c>
       <c r="M74" s="6" t="n"/>
       <c r="N74" s="6" t="n">
@@ -5985,11 +5985,11 @@
         <v>101.087058</v>
       </c>
       <c r="J75" s="9" t="n">
-        <v>101.222428</v>
+        <v>101.222381</v>
       </c>
       <c r="K75" s="9" t="n"/>
       <c r="L75" s="9" t="n">
-        <v>100.37838</v>
+        <v>100.378875</v>
       </c>
       <c r="M75" s="9" t="n"/>
       <c r="N75" s="9" t="n">
@@ -6063,11 +6063,11 @@
         <v>100.894536</v>
       </c>
       <c r="J76" s="6" t="n">
-        <v>101.101558</v>
+        <v>101.101502</v>
       </c>
       <c r="K76" s="6" t="n"/>
       <c r="L76" s="6" t="n">
-        <v>100.228013</v>
+        <v>100.228313</v>
       </c>
       <c r="M76" s="6" t="n"/>
       <c r="N76" s="6" t="n">
@@ -6141,11 +6141,11 @@
         <v>100.660475</v>
       </c>
       <c r="J77" s="9" t="n">
-        <v>100.951667</v>
+        <v>100.951601</v>
       </c>
       <c r="K77" s="9" t="n"/>
       <c r="L77" s="9" t="n">
-        <v>100.083696</v>
+        <v>100.083807</v>
       </c>
       <c r="M77" s="9" t="n"/>
       <c r="N77" s="9" t="n">
@@ -6219,13 +6219,13 @@
         <v>100.40591</v>
       </c>
       <c r="J78" s="6" t="n">
-        <v>100.777636</v>
+        <v>100.777559</v>
       </c>
       <c r="K78" s="6" t="n">
         <v>104.289335</v>
       </c>
       <c r="L78" s="6" t="n">
-        <v>99.94885499999999</v>
+        <v>99.94879</v>
       </c>
       <c r="M78" s="6" t="n"/>
       <c r="N78" s="6" t="n">
@@ -6299,13 +6299,13 @@
         <v>100.200881</v>
       </c>
       <c r="J79" s="9" t="n">
-        <v>100.570545</v>
+        <v>100.570453</v>
       </c>
       <c r="K79" s="9" t="n">
         <v>103.646816</v>
       </c>
       <c r="L79" s="9" t="n">
-        <v>99.825245</v>
+        <v>99.825017</v>
       </c>
       <c r="M79" s="9" t="n"/>
       <c r="N79" s="9" t="n">
@@ -6379,13 +6379,13 @@
         <v>100.026697</v>
       </c>
       <c r="J80" s="6" t="n">
-        <v>100.321482</v>
+        <v>100.321374</v>
       </c>
       <c r="K80" s="6" t="n">
         <v>103.019302</v>
       </c>
       <c r="L80" s="6" t="n">
-        <v>99.712536</v>
+        <v>99.712158</v>
       </c>
       <c r="M80" s="6" t="n"/>
       <c r="N80" s="6" t="n">
@@ -6459,13 +6459,13 @@
         <v>99.83749899999999</v>
       </c>
       <c r="J81" s="9" t="n">
-        <v>100.034632</v>
+        <v>100.034504</v>
       </c>
       <c r="K81" s="9" t="n">
         <v>102.41951</v>
       </c>
       <c r="L81" s="9" t="n">
-        <v>99.603674</v>
+        <v>99.60315199999999</v>
       </c>
       <c r="M81" s="9" t="n"/>
       <c r="N81" s="9" t="n">
@@ -6539,13 +6539,13 @@
         <v>99.643163</v>
       </c>
       <c r="J82" s="6" t="n">
-        <v>99.70424199999999</v>
+        <v>99.70409100000001</v>
       </c>
       <c r="K82" s="6" t="n">
         <v>101.873629</v>
       </c>
       <c r="L82" s="6" t="n">
-        <v>99.488235</v>
+        <v>99.48755800000001</v>
       </c>
       <c r="M82" s="6" t="n"/>
       <c r="N82" s="6" t="n">
@@ -6619,13 +6619,13 @@
         <v>99.397147</v>
       </c>
       <c r="J83" s="9" t="n">
-        <v>99.352293</v>
+        <v>99.352118</v>
       </c>
       <c r="K83" s="9" t="n">
         <v>101.391763</v>
       </c>
       <c r="L83" s="9" t="n">
-        <v>99.353919</v>
+        <v>99.353064</v>
       </c>
       <c r="M83" s="9" t="n"/>
       <c r="N83" s="9" t="n">
@@ -6699,13 +6699,13 @@
         <v>99.089251</v>
       </c>
       <c r="J84" s="6" t="n">
-        <v>99.021517</v>
+        <v>99.02132</v>
       </c>
       <c r="K84" s="6" t="n">
         <v>100.983042</v>
       </c>
       <c r="L84" s="6" t="n">
-        <v>99.196039</v>
+        <v>99.194975</v>
       </c>
       <c r="M84" s="6" t="n"/>
       <c r="N84" s="6" t="n">
@@ -6779,13 +6779,13 @@
         <v>98.80620500000001</v>
       </c>
       <c r="J85" s="9" t="n">
-        <v>98.742053</v>
+        <v>98.741837</v>
       </c>
       <c r="K85" s="9" t="n">
         <v>100.601494</v>
       </c>
       <c r="L85" s="9" t="n">
-        <v>99.028826</v>
+        <v>99.027541</v>
       </c>
       <c r="M85" s="9" t="n"/>
       <c r="N85" s="9" t="n">
@@ -6859,13 +6859,13 @@
         <v>98.576689</v>
       </c>
       <c r="J86" s="6" t="n">
-        <v>98.533401</v>
+        <v>98.53317</v>
       </c>
       <c r="K86" s="6" t="n">
         <v>100.235581</v>
       </c>
       <c r="L86" s="6" t="n">
-        <v>98.867582</v>
+        <v>98.86608699999999</v>
       </c>
       <c r="M86" s="6" t="n"/>
       <c r="N86" s="6" t="n">
@@ -6939,13 +6939,13 @@
         <v>98.42932</v>
       </c>
       <c r="J87" s="9" t="n">
-        <v>98.401898</v>
+        <v>98.401658</v>
       </c>
       <c r="K87" s="9" t="n">
         <v>99.87891500000001</v>
       </c>
       <c r="L87" s="9" t="n">
-        <v>98.72774699999999</v>
+        <v>98.72607000000001</v>
       </c>
       <c r="M87" s="9" t="n"/>
       <c r="N87" s="9" t="n">
@@ -7019,13 +7019,13 @@
         <v>98.37601600000001</v>
       </c>
       <c r="J88" s="6" t="n">
-        <v>98.349127</v>
+        <v>98.348884</v>
       </c>
       <c r="K88" s="6" t="n">
         <v>99.569655</v>
       </c>
       <c r="L88" s="6" t="n">
-        <v>98.619692</v>
+        <v>98.617874</v>
       </c>
       <c r="M88" s="6" t="n"/>
       <c r="N88" s="6" t="n">
@@ -7099,13 +7099,13 @@
         <v>98.404894</v>
       </c>
       <c r="J89" s="9" t="n">
-        <v>98.387426</v>
+        <v>98.387186</v>
       </c>
       <c r="K89" s="9" t="n">
         <v>99.317193</v>
       </c>
       <c r="L89" s="9" t="n">
-        <v>98.548402</v>
+        <v>98.546494</v>
       </c>
       <c r="M89" s="9" t="n"/>
       <c r="N89" s="9" t="n">
@@ -7179,13 +7179,13 @@
         <v>98.522384</v>
       </c>
       <c r="J90" s="6" t="n">
-        <v>98.51583599999999</v>
+        <v>98.515604</v>
       </c>
       <c r="K90" s="6" t="n">
         <v>99.061466</v>
       </c>
       <c r="L90" s="6" t="n">
-        <v>98.513853</v>
+        <v>98.51190200000001</v>
       </c>
       <c r="M90" s="6" t="n">
         <v>102.50242</v>
@@ -7261,13 +7261,13 @@
         <v>98.705164</v>
       </c>
       <c r="J91" s="9" t="n">
-        <v>98.72013099999999</v>
+        <v>98.71991300000001</v>
       </c>
       <c r="K91" s="9" t="n">
         <v>98.80621600000001</v>
       </c>
       <c r="L91" s="9" t="n">
-        <v>98.51832899999999</v>
+        <v>98.516383</v>
       </c>
       <c r="M91" s="9" t="n">
         <v>102.143164</v>
@@ -7343,13 +7343,13 @@
         <v>98.92668399999999</v>
       </c>
       <c r="J92" s="6" t="n">
-        <v>98.972852</v>
+        <v>98.972651</v>
       </c>
       <c r="K92" s="6" t="n">
         <v>98.54302</v>
       </c>
       <c r="L92" s="6" t="n">
-        <v>98.561089</v>
+        <v>98.5592</v>
       </c>
       <c r="M92" s="6" t="n">
         <v>101.745879</v>
@@ -7425,13 +7425,13 @@
         <v>99.172929</v>
       </c>
       <c r="J93" s="9" t="n">
-        <v>99.232601</v>
+        <v>99.232417</v>
       </c>
       <c r="K93" s="9" t="n">
         <v>98.28119100000001</v>
       </c>
       <c r="L93" s="9" t="n">
-        <v>98.64266600000001</v>
+        <v>98.640883</v>
       </c>
       <c r="M93" s="9" t="n">
         <v>101.336368</v>
@@ -7507,13 +7507,13 @@
         <v>99.36812999999999</v>
       </c>
       <c r="J94" s="6" t="n">
-        <v>99.465559</v>
+        <v>99.465391</v>
       </c>
       <c r="K94" s="6" t="n">
         <v>98.054463</v>
       </c>
       <c r="L94" s="6" t="n">
-        <v>98.763024</v>
+        <v>98.76139999999999</v>
       </c>
       <c r="M94" s="6" t="n">
         <v>100.934285</v>
@@ -7589,13 +7589,13 @@
         <v>99.501212</v>
       </c>
       <c r="J95" s="9" t="n">
-        <v>99.654509</v>
+        <v>99.654354</v>
       </c>
       <c r="K95" s="9" t="n">
         <v>97.970572</v>
       </c>
       <c r="L95" s="9" t="n">
-        <v>98.914935</v>
+        <v>98.913512</v>
       </c>
       <c r="M95" s="9" t="n">
         <v>100.593698</v>
@@ -7671,13 +7671,13 @@
         <v>99.58997100000001</v>
       </c>
       <c r="J96" s="6" t="n">
-        <v>99.797939</v>
+        <v>99.797794</v>
       </c>
       <c r="K96" s="6" t="n">
         <v>98.000958</v>
       </c>
       <c r="L96" s="6" t="n">
-        <v>99.085436</v>
+        <v>99.08424100000001</v>
       </c>
       <c r="M96" s="6" t="n">
         <v>100.331001</v>
@@ -7753,13 +7753,13 @@
         <v>99.65280199999999</v>
       </c>
       <c r="J97" s="9" t="n">
-        <v>99.898597</v>
+        <v>99.89845800000001</v>
       </c>
       <c r="K97" s="9" t="n">
         <v>98.078969</v>
       </c>
       <c r="L97" s="9" t="n">
-        <v>99.256884</v>
+        <v>99.25591900000001</v>
       </c>
       <c r="M97" s="9" t="n">
         <v>100.14921</v>
@@ -7835,13 +7835,13 @@
         <v>99.681888</v>
       </c>
       <c r="J98" s="6" t="n">
-        <v>99.95589699999999</v>
+        <v>99.95576199999999</v>
       </c>
       <c r="K98" s="6" t="n">
         <v>98.129921</v>
       </c>
       <c r="L98" s="6" t="n">
-        <v>99.408141</v>
+        <v>99.40737900000001</v>
       </c>
       <c r="M98" s="6" t="n">
         <v>100.048391</v>
@@ -7917,13 +7917,13 @@
         <v>99.68566300000001</v>
       </c>
       <c r="J99" s="9" t="n">
-        <v>99.955144</v>
+        <v>99.95500800000001</v>
       </c>
       <c r="K99" s="9" t="n">
         <v>98.11904699999999</v>
       </c>
       <c r="L99" s="9" t="n">
-        <v>99.51108600000001</v>
+        <v>99.51046100000001</v>
       </c>
       <c r="M99" s="9" t="n">
         <v>100.011216</v>
@@ -7999,13 +7999,13 @@
         <v>99.631958</v>
       </c>
       <c r="J100" s="6" t="n">
-        <v>99.899158</v>
+        <v>99.899019</v>
       </c>
       <c r="K100" s="6" t="n">
         <v>98.040356</v>
       </c>
       <c r="L100" s="6" t="n">
-        <v>99.5478</v>
+        <v>99.547225</v>
       </c>
       <c r="M100" s="6" t="n">
         <v>100.001211</v>
@@ -8081,13 +8081,13 @@
         <v>99.51013</v>
       </c>
       <c r="J101" s="9" t="n">
-        <v>99.79517</v>
+        <v>99.795023</v>
       </c>
       <c r="K101" s="9" t="n">
         <v>97.90533600000001</v>
       </c>
       <c r="L101" s="9" t="n">
-        <v>99.520081</v>
+        <v>99.51947</v>
       </c>
       <c r="M101" s="9" t="n">
         <v>100.034374</v>
@@ -8163,13 +8163,13 @@
         <v>99.346661</v>
       </c>
       <c r="J102" s="6" t="n">
-        <v>99.65251600000001</v>
+        <v>99.652359</v>
       </c>
       <c r="K102" s="6" t="n">
         <v>97.748147</v>
       </c>
       <c r="L102" s="6" t="n">
-        <v>99.45335799999999</v>
+        <v>99.452657</v>
       </c>
       <c r="M102" s="6" t="n">
         <v>100.154682</v>
@@ -8245,13 +8245,13 @@
         <v>99.173152</v>
       </c>
       <c r="J103" s="9" t="n">
-        <v>99.498215</v>
+        <v>99.498048</v>
       </c>
       <c r="K103" s="9" t="n">
         <v>97.598297</v>
       </c>
       <c r="L103" s="9" t="n">
-        <v>99.373966</v>
+        <v>99.37315700000001</v>
       </c>
       <c r="M103" s="9" t="n">
         <v>100.325234</v>
@@ -8327,13 +8327,13 @@
         <v>99.026126</v>
       </c>
       <c r="J104" s="6" t="n">
-        <v>99.344427</v>
+        <v>99.34424799999999</v>
       </c>
       <c r="K104" s="6" t="n">
         <v>97.479089</v>
       </c>
       <c r="L104" s="6" t="n">
-        <v>99.29294</v>
+        <v>99.29202100000001</v>
       </c>
       <c r="M104" s="6" t="n">
         <v>100.515355</v>
@@ -8409,13 +8409,13 @@
         <v>98.912353</v>
       </c>
       <c r="J105" s="9" t="n">
-        <v>99.214026</v>
+        <v>99.21383899999999</v>
       </c>
       <c r="K105" s="9" t="n">
         <v>97.407427</v>
       </c>
       <c r="L105" s="9" t="n">
-        <v>99.214922</v>
+        <v>99.21389600000001</v>
       </c>
       <c r="M105" s="9" t="n">
         <v>100.676895</v>
@@ -8491,13 +8491,13 @@
         <v>98.82204900000001</v>
       </c>
       <c r="J106" s="6" t="n">
-        <v>99.126301</v>
+        <v>99.126107</v>
       </c>
       <c r="K106" s="6" t="n">
         <v>97.406656</v>
       </c>
       <c r="L106" s="6" t="n">
-        <v>99.140293</v>
+        <v>99.13916500000001</v>
       </c>
       <c r="M106" s="6" t="n">
         <v>100.795882</v>
@@ -8573,13 +8573,13 @@
         <v>98.74914800000001</v>
       </c>
       <c r="J107" s="9" t="n">
-        <v>99.09372500000001</v>
+        <v>99.093529</v>
       </c>
       <c r="K107" s="9" t="n">
         <v>97.449709</v>
       </c>
       <c r="L107" s="9" t="n">
-        <v>99.06838399999999</v>
+        <v>99.06715699999999</v>
       </c>
       <c r="M107" s="9" t="n">
         <v>100.868074</v>
@@ -8655,13 +8655,13 @@
         <v>98.702493</v>
       </c>
       <c r="J108" s="6" t="n">
-        <v>99.118274</v>
+        <v>99.11807899999999</v>
       </c>
       <c r="K108" s="6" t="n">
         <v>97.547055</v>
       </c>
       <c r="L108" s="6" t="n">
-        <v>99.000872</v>
+        <v>98.999554</v>
       </c>
       <c r="M108" s="6" t="n">
         <v>100.894339</v>
@@ -8737,13 +8737,13 @@
         <v>98.706485</v>
       </c>
       <c r="J109" s="9" t="n">
-        <v>99.223685</v>
+        <v>99.22349699999999</v>
       </c>
       <c r="K109" s="9" t="n">
         <v>97.70594</v>
       </c>
       <c r="L109" s="9" t="n">
-        <v>98.94105</v>
+        <v>98.939651</v>
       </c>
       <c r="M109" s="9" t="n">
         <v>100.900789</v>
@@ -8819,13 +8819,13 @@
         <v>98.787453</v>
       </c>
       <c r="J110" s="6" t="n">
-        <v>99.37857</v>
+        <v>99.37839200000001</v>
       </c>
       <c r="K110" s="6" t="n">
         <v>97.907746</v>
       </c>
       <c r="L110" s="6" t="n">
-        <v>98.898489</v>
+        <v>98.89703299999999</v>
       </c>
       <c r="M110" s="6" t="n">
         <v>100.910968</v>
@@ -8901,13 +8901,13 @@
         <v>98.93053</v>
       </c>
       <c r="J111" s="9" t="n">
-        <v>99.56629599999999</v>
+        <v>99.566131</v>
       </c>
       <c r="K111" s="9" t="n">
         <v>98.112183</v>
       </c>
       <c r="L111" s="9" t="n">
-        <v>98.88025399999999</v>
+        <v>98.878773</v>
       </c>
       <c r="M111" s="9" t="n">
         <v>100.899346</v>
@@ -8983,13 +8983,13 @@
         <v>99.08313</v>
       </c>
       <c r="J112" s="6" t="n">
-        <v>99.756648</v>
+        <v>99.756495</v>
       </c>
       <c r="K112" s="6" t="n">
         <v>98.259783</v>
       </c>
       <c r="L112" s="6" t="n">
-        <v>98.884218</v>
+        <v>98.88274199999999</v>
       </c>
       <c r="M112" s="6" t="n">
         <v>100.858715</v>
@@ -9065,13 +9065,13 @@
         <v>99.249621</v>
       </c>
       <c r="J113" s="9" t="n">
-        <v>99.91161099999999</v>
+        <v>99.911468</v>
       </c>
       <c r="K113" s="9" t="n">
         <v>98.351167</v>
       </c>
       <c r="L113" s="9" t="n">
-        <v>98.903593</v>
+        <v>98.90213900000001</v>
       </c>
       <c r="M113" s="9" t="n">
         <v>100.758775</v>
@@ -9147,13 +9147,13 @@
         <v>99.41645</v>
       </c>
       <c r="J114" s="6" t="n">
-        <v>100.021448</v>
+        <v>100.021312</v>
       </c>
       <c r="K114" s="6" t="n">
         <v>98.39564900000001</v>
       </c>
       <c r="L114" s="6" t="n">
-        <v>98.93374300000001</v>
+        <v>98.932323</v>
       </c>
       <c r="M114" s="6" t="n">
         <v>100.578485</v>
@@ -9229,13 +9229,13 @@
         <v>99.561543</v>
       </c>
       <c r="J115" s="9" t="n">
-        <v>100.091487</v>
+        <v>100.091356</v>
       </c>
       <c r="K115" s="9" t="n">
         <v>98.43132199999999</v>
       </c>
       <c r="L115" s="9" t="n">
-        <v>98.972877</v>
+        <v>98.971503</v>
       </c>
       <c r="M115" s="9" t="n">
         <v>100.333073</v>
@@ -9311,13 +9311,13 @@
         <v>99.67402199999999</v>
       </c>
       <c r="J116" s="6" t="n">
-        <v>100.135738</v>
+        <v>100.135609</v>
       </c>
       <c r="K116" s="6" t="n">
         <v>98.495778</v>
       </c>
       <c r="L116" s="6" t="n">
-        <v>99.015461</v>
+        <v>99.01414</v>
       </c>
       <c r="M116" s="6" t="n">
         <v>100.077905</v>
@@ -9393,13 +9393,13 @@
         <v>99.749515</v>
       </c>
       <c r="J117" s="9" t="n">
-        <v>100.164851</v>
+        <v>100.164723</v>
       </c>
       <c r="K117" s="9" t="n">
         <v>98.614211</v>
       </c>
       <c r="L117" s="9" t="n">
-        <v>99.065478</v>
+        <v>99.06422499999999</v>
       </c>
       <c r="M117" s="9" t="n">
         <v>99.848326</v>
@@ -9475,13 +9475,13 @@
         <v>99.79264999999999</v>
       </c>
       <c r="J118" s="6" t="n">
-        <v>100.171526</v>
+        <v>100.171398</v>
       </c>
       <c r="K118" s="6" t="n">
         <v>98.776996</v>
       </c>
       <c r="L118" s="6" t="n">
-        <v>99.129929</v>
+        <v>99.128767</v>
       </c>
       <c r="M118" s="6" t="n">
         <v>99.65974300000001</v>
@@ -9557,13 +9557,13 @@
         <v>99.805074</v>
       </c>
       <c r="J119" s="9" t="n">
-        <v>100.14894</v>
+        <v>100.14881</v>
       </c>
       <c r="K119" s="9" t="n">
         <v>98.980935</v>
       </c>
       <c r="L119" s="9" t="n">
-        <v>99.213256</v>
+        <v>99.21220700000001</v>
       </c>
       <c r="M119" s="9" t="n">
         <v>99.492211</v>
@@ -9639,13 +9639,13 @@
         <v>99.77128999999999</v>
       </c>
       <c r="J120" s="6" t="n">
-        <v>100.084684</v>
+        <v>100.084549</v>
       </c>
       <c r="K120" s="6" t="n">
         <v>99.212197</v>
       </c>
       <c r="L120" s="6" t="n">
-        <v>99.314172</v>
+        <v>99.313259</v>
       </c>
       <c r="M120" s="6" t="n">
         <v>99.35030500000001</v>
@@ -9721,13 +9721,13 @@
         <v>99.68836899999999</v>
       </c>
       <c r="J121" s="9" t="n">
-        <v>99.99437</v>
+        <v>99.99422800000001</v>
       </c>
       <c r="K121" s="9" t="n">
         <v>99.441013</v>
       </c>
       <c r="L121" s="9" t="n">
-        <v>99.42949299999999</v>
+        <v>99.42873299999999</v>
       </c>
       <c r="M121" s="9" t="n">
         <v>99.21216800000001</v>
@@ -9803,13 +9803,13 @@
         <v>99.59194100000001</v>
       </c>
       <c r="J122" s="6" t="n">
-        <v>99.89514699999999</v>
+        <v>99.894998</v>
       </c>
       <c r="K122" s="6" t="n">
         <v>99.619978</v>
       </c>
       <c r="L122" s="6" t="n">
-        <v>99.552221</v>
+        <v>99.551625</v>
       </c>
       <c r="M122" s="6" t="n">
         <v>99.052217</v>
@@ -9885,13 +9885,13 @@
         <v>99.514264</v>
       </c>
       <c r="J123" s="9" t="n">
-        <v>99.82761499999999</v>
+        <v>99.827461</v>
       </c>
       <c r="K123" s="9" t="n">
         <v>99.665385</v>
       </c>
       <c r="L123" s="9" t="n">
-        <v>99.678282</v>
+        <v>99.67785499999999</v>
       </c>
       <c r="M123" s="9" t="n">
         <v>98.885307</v>
@@ -9967,13 +9967,13 @@
         <v>99.497756</v>
       </c>
       <c r="J124" s="6" t="n">
-        <v>99.819779</v>
+        <v>99.819624</v>
       </c>
       <c r="K124" s="6" t="n">
         <v>99.61575999999999</v>
       </c>
       <c r="L124" s="6" t="n">
-        <v>99.801605</v>
+        <v>99.801344</v>
       </c>
       <c r="M124" s="6" t="n">
         <v>98.75078499999999</v>
@@ -10049,13 +10049,13 @@
         <v>99.56820999999999</v>
       </c>
       <c r="J125" s="9" t="n">
-        <v>99.88598500000001</v>
+        <v>99.885834</v>
       </c>
       <c r="K125" s="9" t="n">
         <v>99.505506</v>
       </c>
       <c r="L125" s="9" t="n">
-        <v>99.92883</v>
+        <v>99.928741</v>
       </c>
       <c r="M125" s="9" t="n">
         <v>98.654674</v>
@@ -10131,13 +10131,13 @@
         <v>99.709906</v>
       </c>
       <c r="J126" s="6" t="n">
-        <v>100.022931</v>
+        <v>100.022789</v>
       </c>
       <c r="K126" s="6" t="n">
         <v>99.33804600000001</v>
       </c>
       <c r="L126" s="6" t="n">
-        <v>100.067521</v>
+        <v>100.067618</v>
       </c>
       <c r="M126" s="6" t="n">
         <v>98.60885399999999</v>
@@ -10213,13 +10213,13 @@
         <v>99.885463</v>
       </c>
       <c r="J127" s="9" t="n">
-        <v>100.198798</v>
+        <v>100.198667</v>
       </c>
       <c r="K127" s="9" t="n">
         <v>99.218339</v>
       </c>
       <c r="L127" s="9" t="n">
-        <v>100.222544</v>
+        <v>100.222847</v>
       </c>
       <c r="M127" s="9" t="n">
         <v>98.66471900000001</v>
@@ -10295,13 +10295,13 @@
         <v>100.067996</v>
       </c>
       <c r="J128" s="6" t="n">
-        <v>100.393776</v>
+        <v>100.393657</v>
       </c>
       <c r="K128" s="6" t="n">
         <v>99.24671600000001</v>
       </c>
       <c r="L128" s="6" t="n">
-        <v>100.394328</v>
+        <v>100.394859</v>
       </c>
       <c r="M128" s="6" t="n">
         <v>98.840311</v>
@@ -10377,13 +10377,13 @@
         <v>100.257202</v>
       </c>
       <c r="J129" s="9" t="n">
-        <v>100.5642</v>
+        <v>100.564093</v>
       </c>
       <c r="K129" s="9" t="n">
         <v>99.382544</v>
       </c>
       <c r="L129" s="9" t="n">
-        <v>100.581786</v>
+        <v>100.582563</v>
       </c>
       <c r="M129" s="9" t="n">
         <v>99.108677</v>
@@ -10459,13 +10459,13 @@
         <v>100.394907</v>
       </c>
       <c r="J130" s="6" t="n">
-        <v>100.713116</v>
+        <v>100.713018</v>
       </c>
       <c r="K130" s="6" t="n">
         <v>99.605757</v>
       </c>
       <c r="L130" s="6" t="n">
-        <v>100.778736</v>
+        <v>100.779769</v>
       </c>
       <c r="M130" s="6" t="n">
         <v>99.396039</v>
@@ -10541,13 +10541,13 @@
         <v>100.505843</v>
       </c>
       <c r="J131" s="9" t="n">
-        <v>100.821062</v>
+        <v>100.82097</v>
       </c>
       <c r="K131" s="9" t="n">
         <v>99.88426800000001</v>
       </c>
       <c r="L131" s="9" t="n">
-        <v>100.98361</v>
+        <v>100.984909</v>
       </c>
       <c r="M131" s="9" t="n">
         <v>99.638379</v>
@@ -10623,13 +10623,13 @@
         <v>100.587758</v>
       </c>
       <c r="J132" s="6" t="n">
-        <v>100.881548</v>
+        <v>100.88146</v>
       </c>
       <c r="K132" s="6" t="n">
         <v>100.181806</v>
       </c>
       <c r="L132" s="6" t="n">
-        <v>101.192575</v>
+        <v>101.194144</v>
       </c>
       <c r="M132" s="6" t="n">
         <v>99.768208</v>
@@ -10705,13 +10705,13 @@
         <v>100.645105</v>
       </c>
       <c r="J133" s="9" t="n">
-        <v>100.889291</v>
+        <v>100.889203</v>
       </c>
       <c r="K133" s="9" t="n">
         <v>100.493326</v>
       </c>
       <c r="L133" s="9" t="n">
-        <v>101.401357</v>
+        <v>101.403197</v>
       </c>
       <c r="M133" s="9" t="n">
         <v>99.74003500000001</v>
@@ -10787,13 +10787,13 @@
         <v>100.694602</v>
       </c>
       <c r="J134" s="6" t="n">
-        <v>100.850717</v>
+        <v>100.850625</v>
       </c>
       <c r="K134" s="6" t="n">
         <v>100.812299</v>
       </c>
       <c r="L134" s="6" t="n">
-        <v>101.604274</v>
+        <v>101.606379</v>
       </c>
       <c r="M134" s="6" t="n">
         <v>99.62265499999999</v>
@@ -10869,13 +10869,13 @@
         <v>100.733843</v>
       </c>
       <c r="J135" s="9" t="n">
-        <v>100.777324</v>
+        <v>100.777227</v>
       </c>
       <c r="K135" s="9" t="n">
         <v>101.15277</v>
       </c>
       <c r="L135" s="9" t="n">
-        <v>101.795487</v>
+        <v>101.797846</v>
       </c>
       <c r="M135" s="9" t="n">
         <v>99.485354</v>
@@ -10951,13 +10951,13 @@
         <v>100.761615</v>
       </c>
       <c r="J136" s="6" t="n">
-        <v>100.678858</v>
+        <v>100.678754</v>
       </c>
       <c r="K136" s="6" t="n">
         <v>101.505461</v>
       </c>
       <c r="L136" s="6" t="n">
-        <v>101.975778</v>
+        <v>101.978377</v>
       </c>
       <c r="M136" s="6" t="n">
         <v>99.29503699999999</v>
@@ -11033,13 +11033,13 @@
         <v>100.779053</v>
       </c>
       <c r="J137" s="9" t="n">
-        <v>100.583887</v>
+        <v>100.583776</v>
       </c>
       <c r="K137" s="9" t="n">
         <v>101.754668</v>
       </c>
       <c r="L137" s="9" t="n">
-        <v>102.145559</v>
+        <v>102.148385</v>
       </c>
       <c r="M137" s="9" t="n">
         <v>99.09972999999999</v>
@@ -11115,13 +11115,13 @@
         <v>100.793776</v>
       </c>
       <c r="J138" s="6" t="n">
-        <v>100.516886</v>
+        <v>100.516769</v>
       </c>
       <c r="K138" s="6" t="n">
         <v>101.91526</v>
       </c>
       <c r="L138" s="6" t="n">
-        <v>102.300413</v>
+        <v>102.303445</v>
       </c>
       <c r="M138" s="6" t="n">
         <v>98.907917</v>
@@ -11197,13 +11197,13 @@
         <v>100.844164</v>
       </c>
       <c r="J139" s="9" t="n">
-        <v>100.473741</v>
+        <v>100.473621</v>
       </c>
       <c r="K139" s="9" t="n">
         <v>101.994321</v>
       </c>
       <c r="L139" s="9" t="n">
-        <v>102.438604</v>
+        <v>102.44182</v>
       </c>
       <c r="M139" s="9" t="n">
         <v>98.714609</v>
@@ -11279,13 +11279,13 @@
         <v>100.921288</v>
       </c>
       <c r="J140" s="6" t="n">
-        <v>100.448523</v>
+        <v>100.448401</v>
       </c>
       <c r="K140" s="6" t="n">
         <v>102.042615</v>
       </c>
       <c r="L140" s="6" t="n">
-        <v>102.558045</v>
+        <v>102.561421</v>
       </c>
       <c r="M140" s="6" t="n">
         <v>98.531734</v>
@@ -11361,13 +11361,13 @@
         <v>100.989016</v>
       </c>
       <c r="J141" s="9" t="n">
-        <v>100.439758</v>
+        <v>100.439634</v>
       </c>
       <c r="K141" s="9" t="n">
         <v>102.080255</v>
       </c>
       <c r="L141" s="9" t="n">
-        <v>102.658359</v>
+        <v>102.661869</v>
       </c>
       <c r="M141" s="9" t="n">
         <v>98.342826</v>
@@ -11443,13 +11443,13 @@
         <v>101.03388</v>
       </c>
       <c r="J142" s="6" t="n">
-        <v>100.424242</v>
+        <v>100.424116</v>
       </c>
       <c r="K142" s="6" t="n">
         <v>102.101033</v>
       </c>
       <c r="L142" s="6" t="n">
-        <v>102.742039</v>
+        <v>102.745657</v>
       </c>
       <c r="M142" s="6" t="n">
         <v>98.22292299999999</v>
@@ -11525,13 +11525,13 @@
         <v>101.01884</v>
       </c>
       <c r="J143" s="9" t="n">
-        <v>100.399291</v>
+        <v>100.399163</v>
       </c>
       <c r="K143" s="9" t="n">
         <v>102.112351</v>
       </c>
       <c r="L143" s="9" t="n">
-        <v>102.803434</v>
+        <v>102.807129</v>
       </c>
       <c r="M143" s="9" t="n">
         <v>98.266854</v>
@@ -11607,13 +11607,13 @@
         <v>100.928647</v>
       </c>
       <c r="J144" s="6" t="n">
-        <v>100.383255</v>
+        <v>100.383126</v>
       </c>
       <c r="K144" s="6" t="n">
         <v>102.16398</v>
       </c>
       <c r="L144" s="6" t="n">
-        <v>102.840748</v>
+        <v>102.844488</v>
       </c>
       <c r="M144" s="6" t="n">
         <v>98.517979</v>
@@ -11689,13 +11689,13 @@
         <v>100.850905</v>
       </c>
       <c r="J145" s="9" t="n">
-        <v>100.377672</v>
+        <v>100.377542</v>
       </c>
       <c r="K145" s="9" t="n">
         <v>102.285528</v>
       </c>
       <c r="L145" s="9" t="n">
-        <v>102.858978</v>
+        <v>102.862739</v>
       </c>
       <c r="M145" s="9" t="n">
         <v>98.874441</v>
@@ -11771,13 +11771,13 @@
         <v>100.825335</v>
       </c>
       <c r="J146" s="6" t="n">
-        <v>100.394328</v>
+        <v>100.394198</v>
       </c>
       <c r="K146" s="6" t="n">
         <v>102.523173</v>
       </c>
       <c r="L146" s="6" t="n">
-        <v>102.861156</v>
+        <v>102.864919</v>
       </c>
       <c r="M146" s="6" t="n">
         <v>99.17998900000001</v>
@@ -11853,13 +11853,13 @@
         <v>100.856851</v>
       </c>
       <c r="J147" s="9" t="n">
-        <v>100.426646</v>
+        <v>100.426517</v>
       </c>
       <c r="K147" s="9" t="n">
         <v>102.901625</v>
       </c>
       <c r="L147" s="9" t="n">
-        <v>102.846857</v>
+        <v>102.850605</v>
       </c>
       <c r="M147" s="9" t="n">
         <v>99.3807</v>
@@ -11935,13 +11935,13 @@
         <v>100.90514</v>
       </c>
       <c r="J148" s="6" t="n">
-        <v>100.433171</v>
+        <v>100.43304</v>
       </c>
       <c r="K148" s="6" t="n">
         <v>103.368241</v>
       </c>
       <c r="L148" s="6" t="n">
-        <v>102.809611</v>
+        <v>102.813314</v>
       </c>
       <c r="M148" s="6" t="n">
         <v>99.450846</v>
@@ -12017,13 +12017,13 @@
         <v>100.947883</v>
       </c>
       <c r="J149" s="9" t="n">
-        <v>100.436831</v>
+        <v>100.436697</v>
       </c>
       <c r="K149" s="9" t="n">
         <v>103.848114</v>
       </c>
       <c r="L149" s="9" t="n">
-        <v>102.745111</v>
+        <v>102.748735</v>
       </c>
       <c r="M149" s="9" t="n">
         <v>99.415256</v>
@@ -12099,13 +12099,13 @@
         <v>100.987057</v>
       </c>
       <c r="J150" s="6" t="n">
-        <v>100.475893</v>
+        <v>100.475758</v>
       </c>
       <c r="K150" s="6" t="n">
         <v>104.2818</v>
       </c>
       <c r="L150" s="6" t="n">
-        <v>102.648853</v>
+        <v>102.652354</v>
       </c>
       <c r="M150" s="6" t="n">
         <v>99.312742</v>
@@ -12181,13 +12181,13 @@
         <v>101.037869</v>
       </c>
       <c r="J151" s="9" t="n">
-        <v>100.580804</v>
+        <v>100.580672</v>
       </c>
       <c r="K151" s="9" t="n">
         <v>104.625881</v>
       </c>
       <c r="L151" s="9" t="n">
-        <v>102.518122</v>
+        <v>102.521451</v>
       </c>
       <c r="M151" s="9" t="n">
         <v>99.161259</v>
@@ -12263,13 +12263,13 @@
         <v>101.11582</v>
       </c>
       <c r="J152" s="6" t="n">
-        <v>100.719605</v>
+        <v>100.719477</v>
       </c>
       <c r="K152" s="6" t="n">
         <v>104.788795</v>
       </c>
       <c r="L152" s="6" t="n">
-        <v>102.356779</v>
+        <v>102.359896</v>
       </c>
       <c r="M152" s="6" t="n">
         <v>98.96308999999999</v>
@@ -12345,13 +12345,13 @@
         <v>101.210437</v>
       </c>
       <c r="J153" s="9" t="n">
-        <v>100.835197</v>
+        <v>100.835074</v>
       </c>
       <c r="K153" s="9" t="n">
         <v>104.697419</v>
       </c>
       <c r="L153" s="9" t="n">
-        <v>102.1753</v>
+        <v>102.178178</v>
       </c>
       <c r="M153" s="9" t="n">
         <v>98.756714</v>
@@ -12427,13 +12427,13 @@
         <v>101.26101</v>
       </c>
       <c r="J154" s="6" t="n">
-        <v>100.933559</v>
+        <v>100.933444</v>
       </c>
       <c r="K154" s="6" t="n">
         <v>104.395293</v>
       </c>
       <c r="L154" s="6" t="n">
-        <v>101.990745</v>
+        <v>101.993376</v>
       </c>
       <c r="M154" s="6" t="n">
         <v>98.55176400000001</v>
@@ -12509,13 +12509,13 @@
         <v>101.245488</v>
       </c>
       <c r="J155" s="9" t="n">
-        <v>100.984516</v>
+        <v>100.984415</v>
       </c>
       <c r="K155" s="9" t="n">
         <v>103.991529</v>
       </c>
       <c r="L155" s="9" t="n">
-        <v>101.815565</v>
+        <v>101.81796</v>
       </c>
       <c r="M155" s="9" t="n">
         <v>98.337878</v>
@@ -12591,13 +12591,13 @@
         <v>101.16644</v>
       </c>
       <c r="J156" s="6" t="n">
-        <v>100.970039</v>
+        <v>100.969963</v>
       </c>
       <c r="K156" s="6" t="n">
         <v>103.570982</v>
       </c>
       <c r="L156" s="6" t="n">
-        <v>101.658723</v>
+        <v>101.660902</v>
       </c>
       <c r="M156" s="6" t="n">
         <v>98.14555799999999</v>
@@ -12673,13 +12673,13 @@
         <v>101.064022</v>
       </c>
       <c r="J157" s="9" t="n">
-        <v>100.897102</v>
+        <v>100.897067</v>
       </c>
       <c r="K157" s="9" t="n">
         <v>103.194555</v>
       </c>
       <c r="L157" s="9" t="n">
-        <v>101.516383</v>
+        <v>101.518364</v>
       </c>
       <c r="M157" s="9" t="n">
         <v>98.01981000000001</v>
@@ -12755,13 +12755,13 @@
         <v>100.968004</v>
       </c>
       <c r="J158" s="6" t="n">
-        <v>100.806405</v>
+        <v>100.806436</v>
       </c>
       <c r="K158" s="6" t="n">
         <v>102.921303</v>
       </c>
       <c r="L158" s="6" t="n">
-        <v>101.384932</v>
+        <v>101.386728</v>
       </c>
       <c r="M158" s="6" t="n">
         <v>98.04830699999999</v>
@@ -12837,13 +12837,13 @@
         <v>100.917017</v>
       </c>
       <c r="J159" s="9" t="n">
-        <v>100.70739</v>
+        <v>100.707513</v>
       </c>
       <c r="K159" s="9" t="n">
         <v>102.757004</v>
       </c>
       <c r="L159" s="9" t="n">
-        <v>101.263042</v>
+        <v>101.264668</v>
       </c>
       <c r="M159" s="9" t="n">
         <v>98.232855</v>
@@ -12919,13 +12919,13 @@
         <v>100.869268</v>
       </c>
       <c r="J160" s="6" t="n">
-        <v>100.622121</v>
+        <v>100.622354</v>
       </c>
       <c r="K160" s="6" t="n">
         <v>102.699444</v>
       </c>
       <c r="L160" s="6" t="n">
-        <v>101.157358</v>
+        <v>101.158839</v>
       </c>
       <c r="M160" s="6" t="n">
         <v>98.499606</v>
@@ -13001,13 +13001,13 @@
         <v>100.815835</v>
       </c>
       <c r="J161" s="9" t="n">
-        <v>100.585203</v>
+        <v>100.58554</v>
       </c>
       <c r="K161" s="9" t="n">
         <v>102.724229</v>
       </c>
       <c r="L161" s="9" t="n">
-        <v>101.073739</v>
+        <v>101.07511</v>
       </c>
       <c r="M161" s="9" t="n">
         <v>98.749639</v>
@@ -13083,13 +13083,13 @@
         <v>100.791382</v>
       </c>
       <c r="J162" s="6" t="n">
-        <v>100.605382</v>
+        <v>100.605765</v>
       </c>
       <c r="K162" s="6" t="n">
         <v>102.75448</v>
       </c>
       <c r="L162" s="6" t="n">
-        <v>101.014253</v>
+        <v>101.015554</v>
       </c>
       <c r="M162" s="6" t="n">
         <v>98.996313</v>
@@ -13165,13 +13165,13 @@
         <v>100.808215</v>
       </c>
       <c r="J163" s="9" t="n">
-        <v>100.668895</v>
+        <v>100.669182</v>
       </c>
       <c r="K163" s="9" t="n">
         <v>102.723108</v>
       </c>
       <c r="L163" s="9" t="n">
-        <v>100.971649</v>
+        <v>100.972908</v>
       </c>
       <c r="M163" s="9" t="n">
         <v>99.203872</v>
@@ -13247,13 +13247,13 @@
         <v>100.821534</v>
       </c>
       <c r="J164" s="6" t="n">
-        <v>100.713691</v>
+        <v>100.713813</v>
       </c>
       <c r="K164" s="6" t="n">
         <v>102.595642</v>
       </c>
       <c r="L164" s="6" t="n">
-        <v>100.930429</v>
+        <v>100.931648</v>
       </c>
       <c r="M164" s="6" t="n">
         <v>99.3334</v>
@@ -13329,13 +13329,13 @@
         <v>100.816181</v>
       </c>
       <c r="J165" s="9" t="n">
-        <v>100.711516</v>
+        <v>100.711479</v>
       </c>
       <c r="K165" s="9" t="n">
         <v>102.352284</v>
       </c>
       <c r="L165" s="9" t="n">
-        <v>100.86669</v>
+        <v>100.867833</v>
       </c>
       <c r="M165" s="9" t="n">
         <v>99.394841</v>
@@ -13411,13 +13411,13 @@
         <v>100.804559</v>
       </c>
       <c r="J166" s="6" t="n">
-        <v>100.676673</v>
+        <v>100.67648</v>
       </c>
       <c r="K166" s="6" t="n">
         <v>102.004471</v>
       </c>
       <c r="L166" s="6" t="n">
-        <v>100.758145</v>
+        <v>100.759148</v>
       </c>
       <c r="M166" s="6" t="n">
         <v>99.45854799999999</v>
@@ -13493,13 +13493,13 @@
         <v>100.776298</v>
       </c>
       <c r="J167" s="9" t="n">
-        <v>100.629852</v>
+        <v>100.629585</v>
       </c>
       <c r="K167" s="9" t="n">
         <v>101.575376</v>
       </c>
       <c r="L167" s="9" t="n">
-        <v>100.596356</v>
+        <v>100.597146</v>
       </c>
       <c r="M167" s="9" t="n">
         <v>99.530917</v>
@@ -13575,13 +13575,13 @@
         <v>100.737375</v>
       </c>
       <c r="J168" s="6" t="n">
-        <v>100.594988</v>
+        <v>100.594698</v>
       </c>
       <c r="K168" s="6" t="n">
         <v>101.097429</v>
       </c>
       <c r="L168" s="6" t="n">
-        <v>100.386373</v>
+        <v>100.386884</v>
       </c>
       <c r="M168" s="6" t="n">
         <v>99.63661</v>
@@ -13657,13 +13657,13 @@
         <v>100.67486</v>
       </c>
       <c r="J169" s="9" t="n">
-        <v>100.579165</v>
+        <v>100.57889</v>
       </c>
       <c r="K169" s="9" t="n">
         <v>100.612974</v>
       </c>
       <c r="L169" s="9" t="n">
-        <v>100.147953</v>
+        <v>100.148146</v>
       </c>
       <c r="M169" s="9" t="n">
         <v>99.742277</v>
@@ -13739,13 +13739,13 @@
         <v>100.609379</v>
       </c>
       <c r="J170" s="6" t="n">
-        <v>100.591657</v>
+        <v>100.59143</v>
       </c>
       <c r="K170" s="6" t="n">
         <v>100.195414</v>
       </c>
       <c r="L170" s="6" t="n">
-        <v>99.91114899999999</v>
+        <v>99.911027</v>
       </c>
       <c r="M170" s="6" t="n">
         <v>99.786051</v>
@@ -13821,13 +13821,13 @@
         <v>100.576673</v>
       </c>
       <c r="J171" s="9" t="n">
-        <v>100.645569</v>
+        <v>100.645437</v>
       </c>
       <c r="K171" s="9" t="n">
         <v>99.969994</v>
       </c>
       <c r="L171" s="9" t="n">
-        <v>99.706529</v>
+        <v>99.706137</v>
       </c>
       <c r="M171" s="9" t="n">
         <v>99.756052</v>
@@ -13903,13 +13903,13 @@
         <v>100.6076</v>
       </c>
       <c r="J172" s="6" t="n">
-        <v>100.746071</v>
+        <v>100.745986</v>
       </c>
       <c r="K172" s="6" t="n">
         <v>99.976045</v>
       </c>
       <c r="L172" s="6" t="n">
-        <v>99.55718299999999</v>
+        <v>99.556597</v>
       </c>
       <c r="M172" s="6" t="n">
         <v>99.681265</v>
@@ -13985,13 +13985,13 @@
         <v>100.716863</v>
       </c>
       <c r="J173" s="9" t="n">
-        <v>100.891962</v>
+        <v>100.891905</v>
       </c>
       <c r="K173" s="9" t="n">
         <v>100.238827</v>
       </c>
       <c r="L173" s="9" t="n">
-        <v>99.470354</v>
+        <v>99.469658</v>
       </c>
       <c r="M173" s="9" t="n">
         <v>99.562348</v>
@@ -14067,13 +14067,13 @@
         <v>100.883616</v>
       </c>
       <c r="J174" s="6" t="n">
-        <v>101.064597</v>
+        <v>101.06454</v>
       </c>
       <c r="K174" s="6" t="n">
         <v>100.675683</v>
       </c>
       <c r="L174" s="6" t="n">
-        <v>99.443833</v>
+        <v>99.443105</v>
       </c>
       <c r="M174" s="6" t="n">
         <v>99.384709</v>
@@ -14149,13 +14149,13 @@
         <v>101.093095</v>
       </c>
       <c r="J175" s="9" t="n">
-        <v>101.249497</v>
+        <v>101.24947</v>
       </c>
       <c r="K175" s="9" t="n">
         <v>101.18275</v>
       </c>
       <c r="L175" s="9" t="n">
-        <v>99.473946</v>
+        <v>99.47326</v>
       </c>
       <c r="M175" s="9" t="n">
         <v>99.150368</v>
@@ -14231,13 +14231,13 @@
         <v>101.334177</v>
       </c>
       <c r="J176" s="6" t="n">
-        <v>101.436302</v>
+        <v>101.436306</v>
       </c>
       <c r="K176" s="6" t="n">
         <v>101.652857</v>
       </c>
       <c r="L176" s="6" t="n">
-        <v>99.546986</v>
+        <v>99.546398</v>
       </c>
       <c r="M176" s="6" t="n">
         <v>98.89662800000001</v>
@@ -14313,13 +14313,13 @@
         <v>101.574337</v>
       </c>
       <c r="J177" s="9" t="n">
-        <v>101.587182</v>
+        <v>101.58721</v>
       </c>
       <c r="K177" s="9" t="n">
         <v>102.064394</v>
       </c>
       <c r="L177" s="9" t="n">
-        <v>99.649176</v>
+        <v>99.64872200000001</v>
       </c>
       <c r="M177" s="9" t="n">
         <v>98.652308</v>
@@ -14395,13 +14395,13 @@
         <v>101.76633</v>
       </c>
       <c r="J178" s="6" t="n">
-        <v>101.645416</v>
+        <v>101.645436</v>
       </c>
       <c r="K178" s="6" t="n">
         <v>102.392473</v>
       </c>
       <c r="L178" s="6" t="n">
-        <v>99.763194</v>
+        <v>99.762888</v>
       </c>
       <c r="M178" s="6" t="n">
         <v>98.441457</v>
@@ -14477,13 +14477,13 @@
         <v>101.902082</v>
       </c>
       <c r="J179" s="9" t="n">
-        <v>101.646356</v>
+        <v>101.646348</v>
       </c>
       <c r="K179" s="9" t="n">
         <v>102.61362</v>
       </c>
       <c r="L179" s="9" t="n">
-        <v>99.875409</v>
+        <v>99.875248</v>
       </c>
       <c r="M179" s="9" t="n">
         <v>98.321654</v>
@@ -14559,13 +14559,13 @@
         <v>101.986594</v>
       </c>
       <c r="J180" s="6" t="n">
-        <v>101.60753</v>
+        <v>101.607516</v>
       </c>
       <c r="K180" s="6" t="n">
         <v>102.727561</v>
       </c>
       <c r="L180" s="6" t="n">
-        <v>99.97479300000001</v>
+        <v>99.974761</v>
       </c>
       <c r="M180" s="6" t="n">
         <v>98.30812400000001</v>
@@ -14641,13 +14641,13 @@
         <v>102.025339</v>
       </c>
       <c r="J181" s="9" t="n">
-        <v>101.520787</v>
+        <v>101.520731</v>
       </c>
       <c r="K181" s="9" t="n">
         <v>102.746027</v>
       </c>
       <c r="L181" s="9" t="n">
-        <v>100.042809</v>
+        <v>100.042863</v>
       </c>
       <c r="M181" s="9" t="n">
         <v>98.41171900000001</v>
@@ -14723,13 +14723,13 @@
         <v>101.979362</v>
       </c>
       <c r="J182" s="6" t="n">
-        <v>101.345569</v>
+        <v>101.345464</v>
       </c>
       <c r="K182" s="6" t="n">
         <v>102.650359</v>
       </c>
       <c r="L182" s="6" t="n">
-        <v>100.05591</v>
+        <v>100.055979</v>
       </c>
       <c r="M182" s="6" t="n">
         <v>98.657927</v>
@@ -14805,13 +14805,13 @@
         <v>101.787403</v>
       </c>
       <c r="J183" s="9" t="n">
-        <v>101.039601</v>
+        <v>101.039437</v>
       </c>
       <c r="K183" s="9" t="n">
         <v>102.419935</v>
       </c>
       <c r="L183" s="9" t="n">
-        <v>99.990298</v>
+        <v>99.990279</v>
       </c>
       <c r="M183" s="9" t="n">
         <v>99.03360000000001</v>
@@ -14887,13 +14887,13 @@
         <v>101.388268</v>
       </c>
       <c r="J184" s="6" t="n">
-        <v>100.574121</v>
+        <v>100.573974</v>
       </c>
       <c r="K184" s="6" t="n">
         <v>102.048834</v>
       </c>
       <c r="L184" s="6" t="n">
-        <v>99.81297000000001</v>
+        <v>99.812718</v>
       </c>
       <c r="M184" s="6" t="n">
         <v>99.52918699999999</v>
@@ -14969,13 +14969,13 @@
         <v>100.740003</v>
       </c>
       <c r="J185" s="9" t="n">
-        <v>99.934015</v>
+        <v>99.933902</v>
       </c>
       <c r="K185" s="9" t="n">
         <v>101.540476</v>
       </c>
       <c r="L185" s="9" t="n">
-        <v>99.50678000000001</v>
+        <v>99.506129</v>
       </c>
       <c r="M185" s="9" t="n">
         <v>100.139348</v>
@@ -15051,13 +15051,13 @@
         <v>99.854777</v>
       </c>
       <c r="J186" s="6" t="n">
-        <v>99.137669</v>
+        <v>99.137591</v>
       </c>
       <c r="K186" s="6" t="n">
         <v>100.913547</v>
       </c>
       <c r="L186" s="6" t="n">
-        <v>99.077691</v>
+        <v>99.076477</v>
       </c>
       <c r="M186" s="6" t="n">
         <v>100.873549</v>
@@ -15133,13 +15133,13 @@
         <v>98.803917</v>
       </c>
       <c r="J187" s="9" t="n">
-        <v>98.270432</v>
+        <v>98.270338</v>
       </c>
       <c r="K187" s="9" t="n">
         <v>100.078509</v>
       </c>
       <c r="L187" s="9" t="n">
-        <v>98.550358</v>
+        <v>98.54845400000001</v>
       </c>
       <c r="M187" s="9" t="n">
         <v>101.692318</v>
@@ -15215,13 +15215,13 @@
         <v>97.781021</v>
       </c>
       <c r="J188" s="6" t="n">
-        <v>97.439623</v>
+        <v>97.439446</v>
       </c>
       <c r="K188" s="6" t="n">
         <v>99.054705</v>
       </c>
       <c r="L188" s="6" t="n">
-        <v>97.976395</v>
+        <v>97.973736</v>
       </c>
       <c r="M188" s="6" t="n">
         <v>102.519496</v>
@@ -15297,13 +15297,13 @@
         <v>96.912764</v>
       </c>
       <c r="J189" s="9" t="n">
-        <v>96.732235</v>
+        <v>96.731899</v>
       </c>
       <c r="K189" s="9" t="n">
         <v>97.935231</v>
       </c>
       <c r="L189" s="9" t="n">
-        <v>97.410459</v>
+        <v>97.407055</v>
       </c>
       <c r="M189" s="9" t="n">
         <v>103.277782</v>
@@ -15379,13 +15379,13 @@
         <v>96.304697</v>
       </c>
       <c r="J190" s="6" t="n">
-        <v>96.230881</v>
+        <v>96.230408</v>
       </c>
       <c r="K190" s="6" t="n">
         <v>96.96047299999999</v>
       </c>
       <c r="L190" s="6" t="n">
-        <v>96.888695</v>
+        <v>96.884603</v>
       </c>
       <c r="M190" s="6" t="n">
         <v>103.904388</v>
@@ -15461,13 +15461,13 @@
         <v>95.983831</v>
       </c>
       <c r="J191" s="9" t="n">
-        <v>95.961422</v>
+        <v>95.960842</v>
       </c>
       <c r="K191" s="9" t="n">
         <v>96.23979300000001</v>
       </c>
       <c r="L191" s="9" t="n">
-        <v>96.439447</v>
+        <v>96.434763</v>
       </c>
       <c r="M191" s="9" t="n">
         <v>104.355133</v>
@@ -15543,13 +15543,13 @@
         <v>95.90464900000001</v>
       </c>
       <c r="J192" s="6" t="n">
-        <v>95.90942200000001</v>
+        <v>95.908733</v>
       </c>
       <c r="K192" s="6" t="n">
         <v>95.778074</v>
       </c>
       <c r="L192" s="6" t="n">
-        <v>96.07941700000001</v>
+        <v>96.074258</v>
       </c>
       <c r="M192" s="6" t="n">
         <v>104.610929</v>
@@ -15625,13 +15625,13 @@
         <v>96.005684</v>
       </c>
       <c r="J193" s="9" t="n">
-        <v>96.044656</v>
+        <v>96.043942</v>
       </c>
       <c r="K193" s="9" t="n">
         <v>95.535878</v>
       </c>
       <c r="L193" s="9" t="n">
-        <v>95.820037</v>
+        <v>95.814539</v>
       </c>
       <c r="M193" s="9" t="n">
         <v>104.677479</v>
@@ -15707,13 +15707,13 @@
         <v>96.23366</v>
       </c>
       <c r="J194" s="6" t="n">
-        <v>96.334616</v>
+        <v>96.33393100000001</v>
       </c>
       <c r="K194" s="6" t="n">
         <v>95.44728499999999</v>
       </c>
       <c r="L194" s="6" t="n">
-        <v>95.665671</v>
+        <v>95.659972</v>
       </c>
       <c r="M194" s="6" t="n">
         <v>104.56857</v>
@@ -15789,13 +15789,13 @@
         <v>96.556589</v>
       </c>
       <c r="J195" s="9" t="n">
-        <v>96.731908</v>
+        <v>96.73128800000001</v>
       </c>
       <c r="K195" s="9" t="n">
         <v>95.465045</v>
       </c>
       <c r="L195" s="9" t="n">
-        <v>95.61212999999999</v>
+        <v>95.60636599999999</v>
       </c>
       <c r="M195" s="9" t="n">
         <v>104.333847</v>
@@ -15871,13 +15871,13 @@
         <v>96.971158</v>
       </c>
       <c r="J196" s="6" t="n">
-        <v>97.182171</v>
+        <v>97.181674</v>
       </c>
       <c r="K196" s="6" t="n">
         <v>95.56017</v>
       </c>
       <c r="L196" s="6" t="n">
-        <v>95.651477</v>
+        <v>95.645771</v>
       </c>
       <c r="M196" s="6" t="n">
         <v>104.025174</v>
@@ -15953,13 +15953,13 @@
         <v>97.385548</v>
       </c>
       <c r="J197" s="9" t="n">
-        <v>97.62759200000001</v>
+        <v>97.627257</v>
       </c>
       <c r="K197" s="9" t="n">
         <v>95.70973499999999</v>
       </c>
       <c r="L197" s="9" t="n">
-        <v>95.772733</v>
+        <v>95.767191</v>
       </c>
       <c r="M197" s="9" t="n">
         <v>103.675995</v>
@@ -16035,13 +16035,13 @@
         <v>97.700647</v>
       </c>
       <c r="J198" s="6" t="n">
-        <v>97.977828</v>
+        <v>97.97762899999999</v>
       </c>
       <c r="K198" s="6" t="n">
         <v>95.931072</v>
       </c>
       <c r="L198" s="6" t="n">
-        <v>95.960961</v>
+        <v>95.95566599999999</v>
       </c>
       <c r="M198" s="6" t="n">
         <v>103.297125</v>
@@ -16117,13 +16117,13 @@
         <v>97.905906</v>
       </c>
       <c r="J199" s="9" t="n">
-        <v>98.22838</v>
+        <v>98.228292</v>
       </c>
       <c r="K199" s="9" t="n">
         <v>96.144018</v>
       </c>
       <c r="L199" s="9" t="n">
-        <v>96.19504499999999</v>
+        <v>96.190055</v>
       </c>
       <c r="M199" s="9" t="n">
         <v>102.925279</v>
@@ -16199,13 +16199,13 @@
         <v>98.041636</v>
       </c>
       <c r="J200" s="6" t="n">
-        <v>98.40828</v>
+        <v>98.40825700000001</v>
       </c>
       <c r="K200" s="6" t="n">
         <v>96.308395</v>
       </c>
       <c r="L200" s="6" t="n">
-        <v>96.45236800000001</v>
+        <v>96.447711</v>
       </c>
       <c r="M200" s="6" t="n">
         <v>102.588102</v>
@@ -16281,13 +16281,13 @@
         <v>98.13914200000001</v>
       </c>
       <c r="J201" s="9" t="n">
-        <v>98.537435</v>
+        <v>98.53738800000001</v>
       </c>
       <c r="K201" s="9" t="n">
         <v>96.409863</v>
       </c>
       <c r="L201" s="9" t="n">
-        <v>96.712782</v>
+        <v>96.708462</v>
       </c>
       <c r="M201" s="9" t="n">
         <v>102.308422</v>
@@ -16363,13 +16363,13 @@
         <v>98.23297599999999</v>
       </c>
       <c r="J202" s="6" t="n">
-        <v>98.64779900000001</v>
+        <v>98.64767399999999</v>
       </c>
       <c r="K202" s="6" t="n">
         <v>96.46722</v>
       </c>
       <c r="L202" s="6" t="n">
-        <v>96.96629799999999</v>
+        <v>96.962307</v>
       </c>
       <c r="M202" s="6" t="n">
         <v>102.103506</v>
@@ -16445,13 +16445,13 @@
         <v>98.324212</v>
       </c>
       <c r="J203" s="9" t="n">
-        <v>98.744041</v>
+        <v>98.743802</v>
       </c>
       <c r="K203" s="9" t="n">
         <v>96.49041</v>
       </c>
       <c r="L203" s="9" t="n">
-        <v>97.207329</v>
+        <v>97.20365200000001</v>
       </c>
       <c r="M203" s="9" t="n">
         <v>101.991072</v>
@@ -16527,13 +16527,13 @@
         <v>98.41337300000001</v>
       </c>
       <c r="J204" s="6" t="n">
-        <v>98.825654</v>
+        <v>98.82535300000001</v>
       </c>
       <c r="K204" s="6" t="n">
         <v>96.506287</v>
       </c>
       <c r="L204" s="6" t="n">
-        <v>97.435919</v>
+        <v>97.432541</v>
       </c>
       <c r="M204" s="6" t="n">
         <v>101.963554</v>
@@ -16609,13 +16609,13 @@
         <v>98.515066</v>
       </c>
       <c r="J205" s="9" t="n">
-        <v>98.91305199999999</v>
+        <v>98.912744</v>
       </c>
       <c r="K205" s="9" t="n">
         <v>96.5429</v>
       </c>
       <c r="L205" s="9" t="n">
-        <v>97.66217399999999</v>
+        <v>97.659094</v>
       </c>
       <c r="M205" s="9" t="n">
         <v>102.020364</v>
@@ -16691,13 +16691,13 @@
         <v>98.641824</v>
       </c>
       <c r="J206" s="6" t="n">
-        <v>99.024914</v>
+        <v>99.024647</v>
       </c>
       <c r="K206" s="6" t="n">
         <v>96.62825599999999</v>
       </c>
       <c r="L206" s="6" t="n">
-        <v>97.896001</v>
+        <v>97.89322799999999</v>
       </c>
       <c r="M206" s="6" t="n">
         <v>102.143063</v>
@@ -16773,13 +16773,13 @@
         <v>98.786248</v>
       </c>
       <c r="J207" s="9" t="n">
-        <v>99.163589</v>
+        <v>99.16342400000001</v>
       </c>
       <c r="K207" s="9" t="n">
         <v>96.779528</v>
       </c>
       <c r="L207" s="9" t="n">
-        <v>98.148359</v>
+        <v>98.14591900000001</v>
       </c>
       <c r="M207" s="9" t="n">
         <v>102.247821</v>
@@ -16855,13 +16855,13 @@
         <v>98.92958</v>
       </c>
       <c r="J208" s="6" t="n">
-        <v>99.30376</v>
+        <v>99.303696</v>
       </c>
       <c r="K208" s="6" t="n">
         <v>97.000163</v>
       </c>
       <c r="L208" s="6" t="n">
-        <v>98.421403</v>
+        <v>98.419324</v>
       </c>
       <c r="M208" s="6" t="n">
         <v>102.251376</v>
@@ -16937,13 +16937,13 @@
         <v>99.05066600000001</v>
       </c>
       <c r="J209" s="9" t="n">
-        <v>99.421137</v>
+        <v>99.4211</v>
       </c>
       <c r="K209" s="9" t="n">
         <v>97.285556</v>
       </c>
       <c r="L209" s="9" t="n">
-        <v>98.71391300000001</v>
+        <v>98.712219</v>
       </c>
       <c r="M209" s="9" t="n">
         <v>102.13995</v>
@@ -17019,13 +17019,13 @@
         <v>99.15240900000001</v>
       </c>
       <c r="J210" s="6" t="n">
-        <v>99.50055999999999</v>
+        <v>99.50048</v>
       </c>
       <c r="K210" s="6" t="n">
         <v>97.640727</v>
       </c>
       <c r="L210" s="6" t="n">
-        <v>99.018359</v>
+        <v>99.017067</v>
       </c>
       <c r="M210" s="6" t="n">
         <v>101.939874</v>
@@ -17101,13 +17101,13 @@
         <v>99.266676</v>
       </c>
       <c r="J211" s="9" t="n">
-        <v>99.588368</v>
+        <v>99.588167</v>
       </c>
       <c r="K211" s="9" t="n">
         <v>97.995588</v>
       </c>
       <c r="L211" s="9" t="n">
-        <v>99.33840499999999</v>
+        <v>99.33753299999999</v>
       </c>
       <c r="M211" s="9" t="n">
         <v>101.692623</v>
@@ -17183,13 +17183,13 @@
         <v>99.413782</v>
       </c>
       <c r="J212" s="6" t="n">
-        <v>99.708653</v>
+        <v>99.708342</v>
       </c>
       <c r="K212" s="6" t="n">
         <v>98.30702599999999</v>
       </c>
       <c r="L212" s="6" t="n">
-        <v>99.65942800000001</v>
+        <v>99.658978</v>
       </c>
       <c r="M212" s="6" t="n">
         <v>101.447255</v>
@@ -17265,13 +17265,13 @@
         <v>99.59703</v>
       </c>
       <c r="J213" s="9" t="n">
-        <v>99.86756200000001</v>
+        <v>99.867265</v>
       </c>
       <c r="K213" s="9" t="n">
         <v>98.566974</v>
       </c>
       <c r="L213" s="9" t="n">
-        <v>99.97058699999999</v>
+        <v>99.970547</v>
       </c>
       <c r="M213" s="9" t="n">
         <v>101.206618</v>
@@ -17347,13 +17347,13 @@
         <v>99.802103</v>
       </c>
       <c r="J214" s="6" t="n">
-        <v>100.051055</v>
+        <v>100.050824</v>
       </c>
       <c r="K214" s="6" t="n">
         <v>98.78594699999999</v>
       </c>
       <c r="L214" s="6" t="n">
-        <v>100.255084</v>
+        <v>100.255419</v>
       </c>
       <c r="M214" s="6" t="n">
         <v>100.955874</v>
@@ -17429,13 +17429,13 @@
         <v>100.012104</v>
       </c>
       <c r="J215" s="9" t="n">
-        <v>100.242996</v>
+        <v>100.242871</v>
       </c>
       <c r="K215" s="9" t="n">
         <v>98.984549</v>
       </c>
       <c r="L215" s="9" t="n">
-        <v>100.493336</v>
+        <v>100.493988</v>
       </c>
       <c r="M215" s="9" t="n">
         <v>100.690255</v>
@@ -17511,13 +17511,13 @@
         <v>100.217411</v>
       </c>
       <c r="J216" s="6" t="n">
-        <v>100.429828</v>
+        <v>100.429831</v>
       </c>
       <c r="K216" s="6" t="n">
         <v>99.179137</v>
       </c>
       <c r="L216" s="6" t="n">
-        <v>100.672029</v>
+        <v>100.672919</v>
       </c>
       <c r="M216" s="6" t="n">
         <v>100.443555</v>
@@ -17593,13 +17593,13 @@
         <v>100.427568</v>
       </c>
       <c r="J217" s="9" t="n">
-        <v>100.606981</v>
+        <v>100.607078</v>
       </c>
       <c r="K217" s="9" t="n">
         <v>99.36601</v>
       </c>
       <c r="L217" s="9" t="n">
-        <v>100.779683</v>
+        <v>100.780714</v>
       </c>
       <c r="M217" s="9" t="n">
         <v>100.205651</v>
@@ -17675,13 +17675,13 @@
         <v>100.643096</v>
       </c>
       <c r="J218" s="6" t="n">
-        <v>100.777972</v>
+        <v>100.778066</v>
       </c>
       <c r="K218" s="6" t="n">
         <v>99.53536800000001</v>
       </c>
       <c r="L218" s="6" t="n">
-        <v>100.813832</v>
+        <v>100.814908</v>
       </c>
       <c r="M218" s="6" t="n">
         <v>100.013222</v>
@@ -17757,13 +17757,13 @@
         <v>100.858339</v>
       </c>
       <c r="J219" s="9" t="n">
-        <v>100.951876</v>
+        <v>100.951909</v>
       </c>
       <c r="K219" s="9" t="n">
         <v>99.689088</v>
       </c>
       <c r="L219" s="9" t="n">
-        <v>100.78481</v>
+        <v>100.785847</v>
       </c>
       <c r="M219" s="9" t="n">
         <v>99.89183</v>
@@ -17839,13 +17839,13 @@
         <v>101.053014</v>
       </c>
       <c r="J220" s="6" t="n">
-        <v>101.125506</v>
+        <v>101.125429</v>
       </c>
       <c r="K220" s="6" t="n">
         <v>99.817003</v>
       </c>
       <c r="L220" s="6" t="n">
-        <v>100.716317</v>
+        <v>100.717263</v>
       </c>
       <c r="M220" s="6" t="n">
         <v>99.84460199999999</v>
@@ -17921,13 +17921,13 @@
         <v>101.217562</v>
       </c>
       <c r="J221" s="9" t="n">
-        <v>101.294793</v>
+        <v>101.294647</v>
       </c>
       <c r="K221" s="9" t="n">
         <v>99.93130499999999</v>
       </c>
       <c r="L221" s="9" t="n">
-        <v>100.634413</v>
+        <v>100.63525</v>
       </c>
       <c r="M221" s="9" t="n">
         <v>99.84677600000001</v>
@@ -18003,13 +18003,13 @@
         <v>101.361019</v>
       </c>
       <c r="J222" s="6" t="n">
-        <v>101.453255</v>
+        <v>101.453106</v>
       </c>
       <c r="K222" s="6" t="n">
         <v>100.048351</v>
       </c>
       <c r="L222" s="6" t="n">
-        <v>100.562551</v>
+        <v>100.563292</v>
       </c>
       <c r="M222" s="6" t="n">
         <v>99.89017699999999</v>
@@ -18085,13 +18085,13 @@
         <v>101.473835</v>
       </c>
       <c r="J223" s="9" t="n">
-        <v>101.575128</v>
+        <v>101.575015</v>
       </c>
       <c r="K223" s="9" t="n">
         <v>100.172717</v>
       </c>
       <c r="L223" s="9" t="n">
-        <v>100.502471</v>
+        <v>100.50313</v>
       </c>
       <c r="M223" s="9" t="n">
         <v>99.93253799999999</v>
@@ -18167,13 +18167,13 @@
         <v>101.529729</v>
       </c>
       <c r="J224" s="6" t="n">
-        <v>101.629326</v>
+        <v>101.629263</v>
       </c>
       <c r="K224" s="6" t="n">
         <v>100.278334</v>
       </c>
       <c r="L224" s="6" t="n">
-        <v>100.454243</v>
+        <v>100.454836</v>
       </c>
       <c r="M224" s="6" t="n">
         <v>99.953468</v>
@@ -18249,13 +18249,13 @@
         <v>101.513487</v>
       </c>
       <c r="J225" s="9" t="n">
-        <v>101.606158</v>
+        <v>101.606145</v>
       </c>
       <c r="K225" s="9" t="n">
         <v>100.35004</v>
       </c>
       <c r="L225" s="9" t="n">
-        <v>100.4139</v>
+        <v>100.414439</v>
       </c>
       <c r="M225" s="9" t="n">
         <v>99.96740699999999</v>
@@ -18331,13 +18331,13 @@
         <v>101.436028</v>
       </c>
       <c r="J226" s="6" t="n">
-        <v>101.52207</v>
+        <v>101.522112</v>
       </c>
       <c r="K226" s="6" t="n">
         <v>100.377922</v>
       </c>
       <c r="L226" s="6" t="n">
-        <v>100.381088</v>
+        <v>100.381583</v>
       </c>
       <c r="M226" s="6" t="n">
         <v>100.000029</v>
@@ -18413,13 +18413,13 @@
         <v>101.322242</v>
       </c>
       <c r="J227" s="9" t="n">
-        <v>101.399451</v>
+        <v>101.399479</v>
       </c>
       <c r="K227" s="9" t="n">
         <v>100.351741</v>
       </c>
       <c r="L227" s="9" t="n">
-        <v>100.362406</v>
+        <v>100.362878</v>
       </c>
       <c r="M227" s="9" t="n">
         <v>100.0261</v>
@@ -18495,13 +18495,13 @@
         <v>101.198958</v>
       </c>
       <c r="J228" s="6" t="n">
-        <v>101.275459</v>
+        <v>101.27543</v>
       </c>
       <c r="K228" s="6" t="n">
         <v>100.269891</v>
       </c>
       <c r="L228" s="6" t="n">
-        <v>100.356367</v>
+        <v>100.356834</v>
       </c>
       <c r="M228" s="6" t="n">
         <v>100.013599</v>
@@ -18577,13 +18577,13 @@
         <v>101.071269</v>
       </c>
       <c r="J229" s="9" t="n">
-        <v>101.166954</v>
+        <v>101.166822</v>
       </c>
       <c r="K229" s="9" t="n">
         <v>100.13138</v>
       </c>
       <c r="L229" s="9" t="n">
-        <v>100.358212</v>
+        <v>100.358683</v>
       </c>
       <c r="M229" s="9" t="n">
         <v>99.97425</v>
@@ -18659,13 +18659,13 @@
         <v>100.945175</v>
       </c>
       <c r="J230" s="6" t="n">
-        <v>101.076699</v>
+        <v>101.076543</v>
       </c>
       <c r="K230" s="6" t="n">
         <v>99.917388</v>
       </c>
       <c r="L230" s="6" t="n">
-        <v>100.366635</v>
+        <v>100.367118</v>
       </c>
       <c r="M230" s="6" t="n">
         <v>99.924171</v>
@@ -18741,13 +18741,13 @@
         <v>100.839905</v>
       </c>
       <c r="J231" s="9" t="n">
-        <v>101.009552</v>
+        <v>101.009401</v>
       </c>
       <c r="K231" s="9" t="n">
         <v>99.694766</v>
       </c>
       <c r="L231" s="9" t="n">
-        <v>100.379782</v>
+        <v>100.380282</v>
       </c>
       <c r="M231" s="9" t="n">
         <v>99.85808400000001</v>
@@ -18823,13 +18823,13 @@
         <v>100.76906</v>
       </c>
       <c r="J232" s="6" t="n">
-        <v>100.963714</v>
+        <v>100.963615</v>
       </c>
       <c r="K232" s="6" t="n">
         <v>99.51988299999999</v>
       </c>
       <c r="L232" s="6" t="n">
-        <v>100.39802</v>
+        <v>100.398545</v>
       </c>
       <c r="M232" s="6" t="n">
         <v>99.759773</v>
@@ -18905,13 +18905,13 @@
         <v>100.7314</v>
       </c>
       <c r="J233" s="9" t="n">
-        <v>100.9331</v>
+        <v>100.933077</v>
       </c>
       <c r="K233" s="9" t="n">
         <v>99.430218</v>
       </c>
       <c r="L233" s="9" t="n">
-        <v>100.423018</v>
+        <v>100.423575</v>
       </c>
       <c r="M233" s="9" t="n">
         <v>99.640201</v>
@@ -18987,13 +18987,13 @@
         <v>100.710807</v>
       </c>
       <c r="J234" s="6" t="n">
-        <v>100.900787</v>
+        <v>100.900827</v>
       </c>
       <c r="K234" s="6" t="n">
         <v>99.44541599999999</v>
       </c>
       <c r="L234" s="6" t="n">
-        <v>100.455249</v>
+        <v>100.455848</v>
       </c>
       <c r="M234" s="6" t="n">
         <v>99.47417</v>
@@ -19069,13 +19069,13 @@
         <v>100.688715</v>
       </c>
       <c r="J235" s="9" t="n">
-        <v>100.859061</v>
+        <v>100.859093</v>
       </c>
       <c r="K235" s="9" t="n">
         <v>99.561797</v>
       </c>
       <c r="L235" s="9" t="n">
-        <v>100.494933</v>
+        <v>100.495583</v>
       </c>
       <c r="M235" s="9" t="n">
         <v>99.286716</v>
@@ -19151,13 +19151,13 @@
         <v>100.662718</v>
       </c>
       <c r="J236" s="6" t="n">
-        <v>100.801514</v>
+        <v>100.801506</v>
       </c>
       <c r="K236" s="6" t="n">
         <v>99.73794700000001</v>
       </c>
       <c r="L236" s="6" t="n">
-        <v>100.54181</v>
+        <v>100.54252</v>
       </c>
       <c r="M236" s="6" t="n">
         <v>99.06441700000001</v>
@@ -19233,13 +19233,13 @@
         <v>100.631436</v>
       </c>
       <c r="J237" s="9" t="n">
-        <v>100.724187</v>
+        <v>100.724126</v>
       </c>
       <c r="K237" s="9" t="n">
         <v>99.881823</v>
       </c>
       <c r="L237" s="9" t="n">
-        <v>100.593761</v>
+        <v>100.594537</v>
       </c>
       <c r="M237" s="9" t="n">
         <v>98.818839</v>
@@ -19315,13 +19315,13 @@
         <v>100.598586</v>
       </c>
       <c r="J238" s="6" t="n">
-        <v>100.626892</v>
+        <v>100.626731</v>
       </c>
       <c r="K238" s="6" t="n">
         <v>100.010722</v>
       </c>
       <c r="L238" s="6" t="n">
-        <v>100.65059</v>
+        <v>100.651441</v>
       </c>
       <c r="M238" s="6" t="n">
         <v>98.577793</v>
@@ -19397,13 +19397,13 @@
         <v>100.572942</v>
       </c>
       <c r="J239" s="9" t="n">
-        <v>100.537404</v>
+        <v>100.537224</v>
       </c>
       <c r="K239" s="9" t="n">
         <v>100.1142</v>
       </c>
       <c r="L239" s="9" t="n">
-        <v>100.711124</v>
+        <v>100.712058</v>
       </c>
       <c r="M239" s="9" t="n">
         <v>98.38543900000001</v>
@@ -19479,13 +19479,13 @@
         <v>100.57487</v>
       </c>
       <c r="J240" s="6" t="n">
-        <v>100.484594</v>
+        <v>100.484435</v>
       </c>
       <c r="K240" s="6" t="n">
         <v>100.15203</v>
       </c>
       <c r="L240" s="6" t="n">
-        <v>100.779653</v>
+        <v>100.780679</v>
       </c>
       <c r="M240" s="6" t="n">
         <v>98.205269</v>
@@ -19561,13 +19561,13 @@
         <v>100.610989</v>
       </c>
       <c r="J241" s="9" t="n">
-        <v>100.484384</v>
+        <v>100.484262</v>
       </c>
       <c r="K241" s="9" t="n">
         <v>100.166327</v>
       </c>
       <c r="L241" s="9" t="n">
-        <v>100.863838</v>
+        <v>100.864976</v>
       </c>
       <c r="M241" s="9" t="n">
         <v>98.07752000000001</v>
@@ -19643,13 +19643,13 @@
         <v>100.693563</v>
       </c>
       <c r="J242" s="6" t="n">
-        <v>100.542596</v>
+        <v>100.542528</v>
       </c>
       <c r="K242" s="6" t="n">
         <v>100.195671</v>
       </c>
       <c r="L242" s="6" t="n">
-        <v>100.965499</v>
+        <v>100.966771</v>
       </c>
       <c r="M242" s="6" t="n">
         <v>97.999602</v>
@@ -19725,13 +19725,13 @@
         <v>100.822833</v>
       </c>
       <c r="J243" s="9" t="n">
-        <v>100.656932</v>
+        <v>100.656953</v>
       </c>
       <c r="K243" s="9" t="n">
         <v>100.252566</v>
       </c>
       <c r="L243" s="9" t="n">
-        <v>101.080452</v>
+        <v>101.081875</v>
       </c>
       <c r="M243" s="9" t="n">
         <v>97.988879</v>
@@ -19807,13 +19807,13 @@
         <v>101.006919</v>
       </c>
       <c r="J244" s="6" t="n">
-        <v>100.838893</v>
+        <v>100.838987</v>
       </c>
       <c r="K244" s="6" t="n">
         <v>100.332312</v>
       </c>
       <c r="L244" s="6" t="n">
-        <v>101.205421</v>
+        <v>101.207008</v>
       </c>
       <c r="M244" s="6" t="n">
         <v>98.032583</v>
@@ -19889,13 +19889,13 @@
         <v>101.237319</v>
       </c>
       <c r="J245" s="9" t="n">
-        <v>101.079707</v>
+        <v>101.079846</v>
       </c>
       <c r="K245" s="9" t="n">
         <v>100.429212</v>
       </c>
       <c r="L245" s="9" t="n">
-        <v>101.333791</v>
+        <v>101.335547</v>
       </c>
       <c r="M245" s="9" t="n">
         <v>98.108453</v>
@@ -19971,13 +19971,13 @@
         <v>101.476854</v>
       </c>
       <c r="J246" s="6" t="n">
-        <v>101.35663</v>
+        <v>101.356756</v>
       </c>
       <c r="K246" s="6" t="n">
         <v>100.553274</v>
       </c>
       <c r="L246" s="6" t="n">
-        <v>101.464669</v>
+        <v>101.466596</v>
       </c>
       <c r="M246" s="6" t="n">
         <v>98.194896</v>
@@ -20053,13 +20053,13 @@
         <v>101.669203</v>
       </c>
       <c r="J247" s="9" t="n">
-        <v>101.62921</v>
+        <v>101.629364</v>
       </c>
       <c r="K247" s="9" t="n">
         <v>100.702628</v>
       </c>
       <c r="L247" s="9" t="n">
-        <v>101.594272</v>
+        <v>101.59637</v>
       </c>
       <c r="M247" s="9" t="n">
         <v>98.287761</v>
@@ -20135,13 +20135,13 @@
         <v>101.817562</v>
       </c>
       <c r="J248" s="6" t="n">
-        <v>101.859607</v>
+        <v>101.859741</v>
       </c>
       <c r="K248" s="6" t="n">
         <v>100.886198</v>
       </c>
       <c r="L248" s="6" t="n">
-        <v>101.725532</v>
+        <v>101.727801</v>
       </c>
       <c r="M248" s="6" t="n">
         <v>98.370937</v>
@@ -20217,13 +20217,13 @@
         <v>101.938496</v>
       </c>
       <c r="J249" s="9" t="n">
-        <v>102.033326</v>
+        <v>102.033347</v>
       </c>
       <c r="K249" s="9" t="n">
         <v>101.109039</v>
       </c>
       <c r="L249" s="9" t="n">
-        <v>101.864546</v>
+        <v>101.866996</v>
       </c>
       <c r="M249" s="9" t="n">
         <v>98.432248</v>
@@ -20299,13 +20299,13 @@
         <v>102.037514</v>
       </c>
       <c r="J250" s="6" t="n">
-        <v>102.154063</v>
+        <v>102.153983</v>
       </c>
       <c r="K250" s="6" t="n">
         <v>101.337369</v>
       </c>
       <c r="L250" s="6" t="n">
-        <v>102.018747</v>
+        <v>102.021401</v>
       </c>
       <c r="M250" s="6" t="n">
         <v>98.43005599999999</v>
@@ -20381,13 +20381,13 @@
         <v>102.10011</v>
       </c>
       <c r="J251" s="9" t="n">
-        <v>102.208027</v>
+        <v>102.207856</v>
       </c>
       <c r="K251" s="9" t="n">
         <v>101.539257</v>
       </c>
       <c r="L251" s="9" t="n">
-        <v>102.183681</v>
+        <v>102.186555</v>
       </c>
       <c r="M251" s="9" t="n">
         <v>98.37163200000001</v>
@@ -20463,13 +20463,13 @@
         <v>102.105857</v>
       </c>
       <c r="J252" s="6" t="n">
-        <v>102.173246</v>
+        <v>102.172985</v>
       </c>
       <c r="K252" s="6" t="n">
         <v>101.686106</v>
       </c>
       <c r="L252" s="6" t="n">
-        <v>102.347064</v>
+        <v>102.350154</v>
       </c>
       <c r="M252" s="6" t="n">
         <v>98.306128</v>
@@ -20545,13 +20545,13 @@
         <v>102.04413</v>
       </c>
       <c r="J253" s="9" t="n">
-        <v>102.038919</v>
+        <v>102.038678</v>
       </c>
       <c r="K253" s="9" t="n">
         <v>101.772693</v>
       </c>
       <c r="L253" s="9" t="n">
-        <v>102.493415</v>
+        <v>102.496698</v>
       </c>
       <c r="M253" s="9" t="n">
         <v>98.244742</v>
@@ -20627,13 +20627,13 @@
         <v>101.927567</v>
       </c>
       <c r="J254" s="6" t="n">
-        <v>101.830198</v>
+        <v>101.830025</v>
       </c>
       <c r="K254" s="6" t="n">
         <v>101.800175</v>
       </c>
       <c r="L254" s="6" t="n">
-        <v>102.603847</v>
+        <v>102.607274</v>
       </c>
       <c r="M254" s="6" t="n">
         <v>98.145195</v>
@@ -20709,13 +20709,13 @@
         <v>101.76773</v>
       </c>
       <c r="J255" s="9" t="n">
-        <v>101.576997</v>
+        <v>101.576864</v>
       </c>
       <c r="K255" s="9" t="n">
         <v>101.771385</v>
       </c>
       <c r="L255" s="9" t="n">
-        <v>102.665559</v>
+        <v>102.669066</v>
       </c>
       <c r="M255" s="9" t="n">
         <v>98.03734799999999</v>
@@ -20791,13 +20791,13 @@
         <v>101.575308</v>
       </c>
       <c r="J256" s="6" t="n">
-        <v>101.309641</v>
+        <v>101.309553</v>
       </c>
       <c r="K256" s="6" t="n">
         <v>101.707713</v>
       </c>
       <c r="L256" s="6" t="n">
-        <v>102.66886</v>
+        <v>102.672369</v>
       </c>
       <c r="M256" s="6" t="n">
         <v>98.04486900000001</v>
@@ -20873,13 +20873,13 @@
         <v>101.368384</v>
       </c>
       <c r="J257" s="9" t="n">
-        <v>101.067279</v>
+        <v>101.067248</v>
       </c>
       <c r="K257" s="9" t="n">
         <v>101.637145</v>
       </c>
       <c r="L257" s="9" t="n">
-        <v>102.614546</v>
+        <v>102.617983</v>
       </c>
       <c r="M257" s="9" t="n">
         <v>98.186449</v>
@@ -20955,13 +20955,13 @@
         <v>101.166747</v>
       </c>
       <c r="J258" s="6" t="n">
-        <v>100.878504</v>
+        <v>100.878459</v>
       </c>
       <c r="K258" s="6" t="n">
         <v>101.572106</v>
       </c>
       <c r="L258" s="6" t="n">
-        <v>102.510288</v>
+        <v>102.513589</v>
       </c>
       <c r="M258" s="6" t="n">
         <v>98.41149900000001</v>
@@ -21037,13 +21037,13 @@
         <v>100.964793</v>
       </c>
       <c r="J259" s="9" t="n">
-        <v>100.698913</v>
+        <v>100.698828</v>
       </c>
       <c r="K259" s="9" t="n">
         <v>101.481747</v>
       </c>
       <c r="L259" s="9" t="n">
-        <v>102.360796</v>
+        <v>102.363902</v>
       </c>
       <c r="M259" s="9" t="n">
         <v>98.629608</v>
@@ -21119,13 +21119,13 @@
         <v>100.775288</v>
       </c>
       <c r="J260" s="6" t="n">
-        <v>100.52203</v>
+        <v>100.521928</v>
       </c>
       <c r="K260" s="6" t="n">
         <v>101.348308</v>
       </c>
       <c r="L260" s="6" t="n">
-        <v>102.171199</v>
+        <v>102.174057</v>
       </c>
       <c r="M260" s="6" t="n">
         <v>98.760966</v>
@@ -21201,13 +21201,13 @@
         <v>100.605748</v>
       </c>
       <c r="J261" s="9" t="n">
-        <v>100.364493</v>
+        <v>100.364414</v>
       </c>
       <c r="K261" s="9" t="n">
         <v>101.177377</v>
       </c>
       <c r="L261" s="9" t="n">
-        <v>101.951559</v>
+        <v>101.954128</v>
       </c>
       <c r="M261" s="9" t="n">
         <v>98.84054</v>
@@ -21283,13 +21283,13 @@
         <v>100.458358</v>
       </c>
       <c r="J262" s="6" t="n">
-        <v>100.236657</v>
+        <v>100.236646</v>
       </c>
       <c r="K262" s="6" t="n">
         <v>100.993291</v>
       </c>
       <c r="L262" s="6" t="n">
-        <v>101.705424</v>
+        <v>101.70767</v>
       </c>
       <c r="M262" s="6" t="n">
         <v>98.89628399999999</v>
@@ -21365,13 +21365,13 @@
         <v>100.327345</v>
       </c>
       <c r="J263" s="9" t="n">
-        <v>100.122309</v>
+        <v>100.122365</v>
       </c>
       <c r="K263" s="9" t="n">
         <v>100.819885</v>
       </c>
       <c r="L263" s="9" t="n">
-        <v>101.442132</v>
+        <v>101.444033</v>
       </c>
       <c r="M263" s="9" t="n">
         <v>98.909319</v>
@@ -21447,13 +21447,13 @@
         <v>100.199074</v>
       </c>
       <c r="J264" s="6" t="n">
-        <v>100.005972</v>
+        <v>100.00604</v>
       </c>
       <c r="K264" s="6" t="n">
         <v>100.669753</v>
       </c>
       <c r="L264" s="6" t="n">
-        <v>101.171947</v>
+        <v>101.173492</v>
       </c>
       <c r="M264" s="6" t="n">
         <v>98.925146</v>
@@ -21529,13 +21529,13 @@
         <v>100.059166</v>
       </c>
       <c r="J265" s="9" t="n">
-        <v>99.869801</v>
+        <v>99.86980200000001</v>
       </c>
       <c r="K265" s="9" t="n">
         <v>100.551696</v>
       </c>
       <c r="L265" s="9" t="n">
-        <v>100.905403</v>
+        <v>100.906596</v>
       </c>
       <c r="M265" s="9" t="n">
         <v>98.98018399999999</v>
@@ -21611,13 +21611,13 @@
         <v>99.88954099999999</v>
       </c>
       <c r="J266" s="6" t="n">
-        <v>99.69949699999999</v>
+        <v>99.699366</v>
       </c>
       <c r="K266" s="6" t="n">
         <v>100.45681</v>
       </c>
       <c r="L266" s="6" t="n">
-        <v>100.655154</v>
+        <v>100.656017</v>
       </c>
       <c r="M266" s="6" t="n">
         <v>99.117932</v>
@@ -21693,13 +21693,13 @@
         <v>99.692621</v>
       </c>
       <c r="J267" s="9" t="n">
-        <v>99.48993400000001</v>
+        <v>99.489704</v>
       </c>
       <c r="K267" s="9" t="n">
         <v>100.37279</v>
       </c>
       <c r="L267" s="9" t="n">
-        <v>100.43561</v>
+        <v>100.436181</v>
       </c>
       <c r="M267" s="9" t="n">
         <v>99.318129</v>
@@ -21775,13 +21775,13 @@
         <v>99.493555</v>
       </c>
       <c r="J268" s="6" t="n">
-        <v>99.26567799999999</v>
+        <v>99.265398</v>
       </c>
       <c r="K268" s="6" t="n">
         <v>100.297442</v>
       </c>
       <c r="L268" s="6" t="n">
-        <v>100.252519</v>
+        <v>100.252847</v>
       </c>
       <c r="M268" s="6" t="n">
         <v>99.514905</v>
@@ -21857,13 +21857,13 @@
         <v>99.305325</v>
       </c>
       <c r="J269" s="9" t="n">
-        <v>99.032585</v>
+        <v>99.032257</v>
       </c>
       <c r="K269" s="9" t="n">
         <v>100.224563</v>
       </c>
       <c r="L269" s="9" t="n">
-        <v>100.105518</v>
+        <v>100.10565</v>
       </c>
       <c r="M269" s="9" t="n">
         <v>99.68657399999999</v>
@@ -21939,13 +21939,13 @@
         <v>99.15286500000001</v>
       </c>
       <c r="J270" s="6" t="n">
-        <v>98.817846</v>
+        <v>98.817561</v>
       </c>
       <c r="K270" s="6" t="n">
         <v>100.158796</v>
       </c>
       <c r="L270" s="6" t="n">
-        <v>99.988755</v>
+        <v>99.988736</v>
       </c>
       <c r="M270" s="6" t="n">
         <v>99.78200699999999</v>
@@ -22021,13 +22021,13 @@
         <v>99.07285299999999</v>
       </c>
       <c r="J271" s="9" t="n">
-        <v>98.66255</v>
+        <v>98.66233200000001</v>
       </c>
       <c r="K271" s="9" t="n">
         <v>100.103595</v>
       </c>
       <c r="L271" s="9" t="n">
-        <v>99.903689</v>
+        <v>99.903561</v>
       </c>
       <c r="M271" s="9" t="n">
         <v>99.798723</v>
@@ -22103,13 +22103,13 @@
         <v>99.072687</v>
       </c>
       <c r="J272" s="6" t="n">
-        <v>98.605656</v>
+        <v>98.60550499999999</v>
       </c>
       <c r="K272" s="6" t="n">
         <v>100.049402</v>
       </c>
       <c r="L272" s="6" t="n">
-        <v>99.84844</v>
+        <v>99.848242</v>
       </c>
       <c r="M272" s="6" t="n">
         <v>99.78326300000001</v>
@@ -22185,13 +22185,13 @@
         <v>99.126738</v>
       </c>
       <c r="J273" s="9" t="n">
-        <v>98.630487</v>
+        <v>98.63034500000001</v>
       </c>
       <c r="K273" s="9" t="n">
         <v>99.988682</v>
       </c>
       <c r="L273" s="9" t="n">
-        <v>99.819211</v>
+        <v>99.818977</v>
       </c>
       <c r="M273" s="9" t="n">
         <v>99.737747</v>
@@ -22267,13 +22267,13 @@
         <v>99.203604</v>
       </c>
       <c r="J274" s="6" t="n">
-        <v>98.699488</v>
+        <v>98.69931</v>
       </c>
       <c r="K274" s="6" t="n">
         <v>99.92123599999999</v>
       </c>
       <c r="L274" s="6" t="n">
-        <v>99.80394200000001</v>
+        <v>99.80368799999999</v>
       </c>
       <c r="M274" s="6" t="n">
         <v>99.674541</v>
@@ -22349,13 +22349,13 @@
         <v>99.287351</v>
       </c>
       <c r="J275" s="9" t="n">
-        <v>98.802305</v>
+        <v>98.802026</v>
       </c>
       <c r="K275" s="9" t="n">
         <v>99.844556</v>
       </c>
       <c r="L275" s="9" t="n">
-        <v>99.789146</v>
+        <v>99.788872</v>
       </c>
       <c r="M275" s="9" t="n">
         <v>99.606342</v>
@@ -22431,13 +22431,13 @@
         <v>99.36861500000001</v>
       </c>
       <c r="J276" s="6" t="n">
-        <v>98.92487</v>
+        <v>98.924543</v>
       </c>
       <c r="K276" s="6" t="n">
         <v>99.765474</v>
       </c>
       <c r="L276" s="6" t="n">
-        <v>99.76751899999999</v>
+        <v>99.76721499999999</v>
       </c>
       <c r="M276" s="6" t="n">
         <v>99.55954199999999</v>
@@ -22513,13 +22513,13 @@
         <v>99.430807</v>
       </c>
       <c r="J277" s="9" t="n">
-        <v>99.04654499999999</v>
+        <v>99.046228</v>
       </c>
       <c r="K277" s="9" t="n">
         <v>99.681878</v>
       </c>
       <c r="L277" s="9" t="n">
-        <v>99.731506</v>
+        <v>99.73115300000001</v>
       </c>
       <c r="M277" s="9" t="n">
         <v>99.489768</v>
@@ -22595,13 +22595,13 @@
         <v>99.454221</v>
       </c>
       <c r="J278" s="6" t="n">
-        <v>99.136026</v>
+        <v>99.135785</v>
       </c>
       <c r="K278" s="6" t="n">
         <v>99.589933</v>
       </c>
       <c r="L278" s="6" t="n">
-        <v>99.681707</v>
+        <v>99.681287</v>
       </c>
       <c r="M278" s="6" t="n">
         <v>99.39833299999999</v>
@@ -22677,13 +22677,13 @@
         <v>99.43778399999999</v>
       </c>
       <c r="J279" s="9" t="n">
-        <v>99.174533</v>
+        <v>99.174409</v>
       </c>
       <c r="K279" s="9" t="n">
         <v>99.49827399999999</v>
       </c>
       <c r="L279" s="9" t="n">
-        <v>99.614966</v>
+        <v>99.614457</v>
       </c>
       <c r="M279" s="9" t="n">
         <v>99.28212600000001</v>
@@ -22759,13 +22759,13 @@
         <v>99.38231500000001</v>
       </c>
       <c r="J280" s="6" t="n">
-        <v>99.144839</v>
+        <v>99.144828</v>
       </c>
       <c r="K280" s="6" t="n">
         <v>99.411023</v>
       </c>
       <c r="L280" s="6" t="n">
-        <v>99.53555799999999</v>
+        <v>99.534943</v>
       </c>
       <c r="M280" s="6" t="n">
         <v>99.192285</v>
@@ -22841,13 +22841,13 @@
         <v>99.305403</v>
       </c>
       <c r="J281" s="9" t="n">
-        <v>99.05958800000001</v>
+        <v>99.059608</v>
       </c>
       <c r="K281" s="9" t="n">
         <v>99.323667</v>
       </c>
       <c r="L281" s="9" t="n">
-        <v>99.445784</v>
+        <v>99.44505100000001</v>
       </c>
       <c r="M281" s="9" t="n">
         <v>99.15255500000001</v>
@@ -22923,13 +22923,13 @@
         <v>99.216711</v>
       </c>
       <c r="J282" s="6" t="n">
-        <v>98.96138500000001</v>
+        <v>98.961314</v>
       </c>
       <c r="K282" s="6" t="n">
         <v>99.234064</v>
       </c>
       <c r="L282" s="6" t="n">
-        <v>99.344033</v>
+        <v>99.343169</v>
       </c>
       <c r="M282" s="6" t="n">
         <v>99.21113099999999</v>
@@ -23005,13 +23005,13 @@
         <v>99.120822</v>
       </c>
       <c r="J283" s="9" t="n">
-        <v>98.894606</v>
+        <v>98.89430900000001</v>
       </c>
       <c r="K283" s="9" t="n">
         <v>99.151257</v>
       </c>
       <c r="L283" s="9" t="n">
-        <v>99.228668</v>
+        <v>99.227654</v>
       </c>
       <c r="M283" s="9" t="n">
         <v>99.366085</v>
@@ -23087,13 +23087,13 @@
         <v>99.015102</v>
       </c>
       <c r="J284" s="6" t="n">
-        <v>98.847508</v>
+        <v>98.847026</v>
       </c>
       <c r="K284" s="6" t="n">
         <v>99.08225899999999</v>
       </c>
       <c r="L284" s="6" t="n">
-        <v>99.09961</v>
+        <v>99.098427</v>
       </c>
       <c r="M284" s="6" t="n">
         <v>99.617942</v>
@@ -23169,13 +23169,13 @@
         <v>98.914725</v>
       </c>
       <c r="J285" s="9" t="n">
-        <v>98.820352</v>
+        <v>98.819878</v>
       </c>
       <c r="K285" s="9" t="n">
         <v>99.040262</v>
       </c>
       <c r="L285" s="9" t="n">
-        <v>98.95890199999999</v>
+        <v>98.957534</v>
       </c>
       <c r="M285" s="9" t="n">
         <v>99.94105399999999</v>
@@ -23251,13 +23251,13 @@
         <v>98.826447</v>
       </c>
       <c r="J286" s="6" t="n">
-        <v>98.805173</v>
+        <v>98.80480300000001</v>
       </c>
       <c r="K286" s="6" t="n">
         <v>99.024997</v>
       </c>
       <c r="L286" s="6" t="n">
-        <v>98.815286</v>
+        <v>98.813729</v>
       </c>
       <c r="M286" s="6" t="n">
         <v>100.316748</v>
@@ -23333,13 +23333,13 @@
         <v>98.755296</v>
       </c>
       <c r="J287" s="9" t="n">
-        <v>98.790729</v>
+        <v>98.79048</v>
       </c>
       <c r="K287" s="9" t="n">
         <v>99.03238899999999</v>
       </c>
       <c r="L287" s="9" t="n">
-        <v>98.68198700000001</v>
+        <v>98.68025299999999</v>
       </c>
       <c r="M287" s="9" t="n">
         <v>100.734119</v>
@@ -23415,13 +23415,13 @@
         <v>98.69419499999999</v>
       </c>
       <c r="J288" s="6" t="n">
-        <v>98.769188</v>
+        <v>98.769066</v>
       </c>
       <c r="K288" s="6" t="n">
         <v>99.05274199999999</v>
       </c>
       <c r="L288" s="6" t="n">
-        <v>98.56939199999999</v>
+        <v>98.567509</v>
       </c>
       <c r="M288" s="6" t="n">
         <v>101.12405</v>
@@ -23497,13 +23497,13 @@
         <v>98.654949</v>
       </c>
       <c r="J289" s="9" t="n">
-        <v>98.752323</v>
+        <v>98.752287</v>
       </c>
       <c r="K289" s="9" t="n">
         <v>99.087112</v>
       </c>
       <c r="L289" s="9" t="n">
-        <v>98.48859</v>
+        <v>98.486598</v>
       </c>
       <c r="M289" s="9" t="n">
         <v>101.451229</v>
@@ -23579,13 +23579,13 @@
         <v>98.668381</v>
       </c>
       <c r="J290" s="6" t="n">
-        <v>98.760479</v>
+        <v>98.760458</v>
       </c>
       <c r="K290" s="6" t="n">
         <v>99.142983</v>
       </c>
       <c r="L290" s="6" t="n">
-        <v>98.44544</v>
+        <v>98.44338999999999</v>
       </c>
       <c r="M290" s="6" t="n">
         <v>101.681369</v>
@@ -23661,13 +23661,13 @@
         <v>98.745349</v>
       </c>
       <c r="J291" s="9" t="n">
-        <v>98.811851</v>
+        <v>98.811789</v>
       </c>
       <c r="K291" s="9" t="n">
         <v>99.22634600000001</v>
       </c>
       <c r="L291" s="9" t="n">
-        <v>98.433948</v>
+        <v>98.431883</v>
       </c>
       <c r="M291" s="9" t="n">
         <v>101.821471</v>
@@ -23743,13 +23743,13 @@
         <v>98.882288</v>
       </c>
       <c r="J292" s="6" t="n">
-        <v>98.910938</v>
+        <v>98.910783</v>
       </c>
       <c r="K292" s="6" t="n">
         <v>99.334693</v>
       </c>
       <c r="L292" s="6" t="n">
-        <v>98.44621100000001</v>
+        <v>98.44416200000001</v>
       </c>
       <c r="M292" s="6" t="n">
         <v>101.89435</v>
@@ -23825,13 +23825,13 @@
         <v>99.06447900000001</v>
       </c>
       <c r="J293" s="9" t="n">
-        <v>99.061953</v>
+        <v>99.06177</v>
       </c>
       <c r="K293" s="9" t="n">
         <v>99.464417</v>
       </c>
       <c r="L293" s="9" t="n">
-        <v>98.47429200000001</v>
+        <v>98.472281</v>
       </c>
       <c r="M293" s="9" t="n">
         <v>101.923056</v>
@@ -23907,13 +23907,13 @@
         <v>99.25767399999999</v>
       </c>
       <c r="J294" s="6" t="n">
-        <v>99.237645</v>
+        <v>99.23747899999999</v>
       </c>
       <c r="K294" s="6" t="n">
         <v>99.60565</v>
       </c>
       <c r="L294" s="6" t="n">
-        <v>98.512821</v>
+        <v>98.510863</v>
       </c>
       <c r="M294" s="6" t="n">
         <v>101.956305</v>
@@ -23991,13 +23991,13 @@
         <v>99.435543</v>
       </c>
       <c r="J295" s="9" t="n">
-        <v>99.416839</v>
+        <v>99.416667</v>
       </c>
       <c r="K295" s="9" t="n">
         <v>99.75257999999999</v>
       </c>
       <c r="L295" s="9" t="n">
-        <v>98.56082600000001</v>
+        <v>98.558933</v>
       </c>
       <c r="M295" s="9" t="n">
         <v>102.002517</v>
@@ -24075,13 +24075,13 @@
         <v>99.57784100000001</v>
       </c>
       <c r="J296" s="6" t="n">
-        <v>99.576808</v>
+        <v>99.57662000000001</v>
       </c>
       <c r="K296" s="6" t="n">
         <v>99.905202</v>
       </c>
       <c r="L296" s="6" t="n">
-        <v>98.61641</v>
+        <v>98.614593</v>
       </c>
       <c r="M296" s="6" t="n">
         <v>102.03522</v>
@@ -24159,13 +24159,13 @@
         <v>99.66283</v>
       </c>
       <c r="J297" s="9" t="n">
-        <v>99.680408</v>
+        <v>99.68022499999999</v>
       </c>
       <c r="K297" s="9" t="n">
         <v>100.044115</v>
       </c>
       <c r="L297" s="9" t="n">
-        <v>98.671498</v>
+        <v>98.669754</v>
       </c>
       <c r="M297" s="9" t="n">
         <v>102.031589</v>
@@ -24243,13 +24243,13 @@
         <v>99.698207</v>
       </c>
       <c r="J298" s="6" t="n">
-        <v>99.725283</v>
+        <v>99.725082</v>
       </c>
       <c r="K298" s="6" t="n">
         <v>100.156064</v>
       </c>
       <c r="L298" s="6" t="n">
-        <v>98.721891</v>
+        <v>98.72021100000001</v>
       </c>
       <c r="M298" s="6" t="n">
         <v>102.00133</v>
@@ -24327,13 +24327,13 @@
         <v>99.695364</v>
       </c>
       <c r="J299" s="9" t="n">
-        <v>99.726805</v>
+        <v>99.726629</v>
       </c>
       <c r="K299" s="9" t="n">
         <v>100.249586</v>
       </c>
       <c r="L299" s="9" t="n">
-        <v>98.765805</v>
+        <v>98.76418099999999</v>
       </c>
       <c r="M299" s="9" t="n">
         <v>101.958693</v>
@@ -24411,13 +24411,13 @@
         <v>99.66714</v>
       </c>
       <c r="J300" s="6" t="n">
-        <v>99.697169</v>
+        <v>99.696996</v>
       </c>
       <c r="K300" s="6" t="n">
         <v>100.339951</v>
       </c>
       <c r="L300" s="6" t="n">
-        <v>98.805159</v>
+        <v>98.803584</v>
       </c>
       <c r="M300" s="6" t="n">
         <v>101.882685</v>
@@ -24495,13 +24495,13 @@
         <v>99.64004199999999</v>
       </c>
       <c r="J301" s="9" t="n">
-        <v>99.659879</v>
+        <v>99.659678</v>
       </c>
       <c r="K301" s="9" t="n">
         <v>100.423474</v>
       </c>
       <c r="L301" s="9" t="n">
-        <v>98.842484</v>
+        <v>98.840957</v>
       </c>
       <c r="M301" s="9" t="n">
         <v>101.775364</v>
@@ -24579,13 +24579,13 @@
         <v>99.626394</v>
       </c>
       <c r="J302" s="6" t="n">
-        <v>99.63108200000001</v>
+        <v>99.630871</v>
       </c>
       <c r="K302" s="6" t="n">
         <v>100.513088</v>
       </c>
       <c r="L302" s="6" t="n">
-        <v>98.879046</v>
+        <v>98.877566</v>
       </c>
       <c r="M302" s="6" t="n">
         <v>101.607396</v>
@@ -24663,13 +24663,13 @@
         <v>99.62969</v>
       </c>
       <c r="J303" s="9" t="n">
-        <v>99.61694900000001</v>
+        <v>99.616765</v>
       </c>
       <c r="K303" s="9" t="n">
         <v>100.594217</v>
       </c>
       <c r="L303" s="9" t="n">
-        <v>98.918227</v>
+        <v>98.916799</v>
       </c>
       <c r="M303" s="9" t="n">
         <v>101.426346</v>
@@ -24747,13 +24747,13 @@
         <v>99.638194</v>
       </c>
       <c r="J304" s="6" t="n">
-        <v>99.61451599999999</v>
+        <v>99.61432499999999</v>
       </c>
       <c r="K304" s="6" t="n">
         <v>100.644792</v>
       </c>
       <c r="L304" s="6" t="n">
-        <v>98.963444</v>
+        <v>98.962076</v>
       </c>
       <c r="M304" s="6" t="n">
         <v>101.27164</v>
@@ -24831,13 +24831,13 @@
         <v>99.62995100000001</v>
       </c>
       <c r="J305" s="9" t="n">
-        <v>99.619946</v>
+        <v>99.619725</v>
       </c>
       <c r="K305" s="9" t="n">
         <v>100.645766</v>
       </c>
       <c r="L305" s="9" t="n">
-        <v>99.008978</v>
+        <v>99.007672</v>
       </c>
       <c r="M305" s="9" t="n">
         <v>101.117912</v>
@@ -24915,13 +24915,13 @@
         <v>99.600236</v>
       </c>
       <c r="J306" s="6" t="n">
-        <v>99.625471</v>
+        <v>99.625196</v>
       </c>
       <c r="K306" s="6" t="n">
         <v>100.613699</v>
       </c>
       <c r="L306" s="6" t="n">
-        <v>99.051187</v>
+        <v>99.049937</v>
       </c>
       <c r="M306" s="6" t="n">
         <v>100.974746</v>
@@ -24999,13 +24999,13 @@
         <v>99.551689</v>
       </c>
       <c r="J307" s="9" t="n">
-        <v>99.623251</v>
+        <v>99.623008</v>
       </c>
       <c r="K307" s="9" t="n">
         <v>100.559321</v>
       </c>
       <c r="L307" s="9" t="n">
-        <v>99.087394</v>
+        <v>99.08619299999999</v>
       </c>
       <c r="M307" s="9" t="n">
         <v>100.844419</v>
@@ -25083,13 +25083,13 @@
         <v>99.493551</v>
       </c>
       <c r="J308" s="6" t="n">
-        <v>99.608205</v>
+        <v>99.608045</v>
       </c>
       <c r="K308" s="6" t="n">
         <v>100.486382</v>
       </c>
       <c r="L308" s="6" t="n">
-        <v>99.119439</v>
+        <v>99.11828</v>
       </c>
       <c r="M308" s="6" t="n">
         <v>100.722039</v>
@@ -25167,13 +25167,13 @@
         <v>99.445517</v>
       </c>
       <c r="J309" s="9" t="n">
-        <v>99.587242</v>
+        <v>99.587181</v>
       </c>
       <c r="K309" s="9" t="n">
         <v>100.393753</v>
       </c>
       <c r="L309" s="9" t="n">
-        <v>99.15382200000001</v>
+        <v>99.152708</v>
       </c>
       <c r="M309" s="9" t="n">
         <v>100.610002</v>
@@ -25251,13 +25251,13 @@
         <v>99.41868599999999</v>
       </c>
       <c r="J310" s="6" t="n">
-        <v>99.567359</v>
+        <v>99.567351</v>
       </c>
       <c r="K310" s="6" t="n">
         <v>100.313261</v>
       </c>
       <c r="L310" s="6" t="n">
-        <v>99.19474700000001</v>
+        <v>99.193686</v>
       </c>
       <c r="M310" s="6" t="n">
         <v>100.48242</v>
@@ -25335,13 +25335,13 @@
         <v>99.43216099999999</v>
       </c>
       <c r="J311" s="9" t="n">
-        <v>99.56325200000001</v>
+        <v>99.56322</v>
       </c>
       <c r="K311" s="9" t="n">
         <v>100.261019</v>
       </c>
       <c r="L311" s="9" t="n">
-        <v>99.241946</v>
+        <v>99.240945</v>
       </c>
       <c r="M311" s="9" t="n">
         <v>100.3213</v>
@@ -25419,13 +25419,13 @@
         <v>99.51751</v>
       </c>
       <c r="J312" s="6" t="n">
-        <v>99.62327500000001</v>
+        <v>99.623222</v>
       </c>
       <c r="K312" s="6" t="n">
         <v>100.261442</v>
       </c>
       <c r="L312" s="6" t="n">
-        <v>99.296852</v>
+        <v>99.295922</v>
       </c>
       <c r="M312" s="6" t="n">
         <v>100.120372</v>
@@ -25503,13 +25503,13 @@
         <v>99.678454</v>
       </c>
       <c r="J313" s="9" t="n">
-        <v>99.78505800000001</v>
+        <v>99.784924</v>
       </c>
       <c r="K313" s="9" t="n">
         <v>100.299997</v>
       </c>
       <c r="L313" s="9" t="n">
-        <v>99.362253</v>
+        <v>99.36141000000001</v>
       </c>
       <c r="M313" s="9" t="n">
         <v>99.856689</v>
@@ -25587,13 +25587,13 @@
         <v>99.890883</v>
       </c>
       <c r="J314" s="6" t="n">
-        <v>100.019083</v>
+        <v>100.018898</v>
       </c>
       <c r="K314" s="6" t="n">
         <v>100.348298</v>
       </c>
       <c r="L314" s="6" t="n">
-        <v>99.434291</v>
+        <v>99.433543</v>
       </c>
       <c r="M314" s="6" t="n">
         <v>99.58330599999999</v>
@@ -25671,13 +25671,13 @@
         <v>100.135256</v>
       </c>
       <c r="J315" s="9" t="n">
-        <v>100.295076</v>
+        <v>100.29486</v>
       </c>
       <c r="K315" s="9" t="n">
         <v>100.370495</v>
       </c>
       <c r="L315" s="9" t="n">
-        <v>99.51062</v>
+        <v>99.509973</v>
       </c>
       <c r="M315" s="9" t="n">
         <v>99.353859</v>
@@ -25755,13 +25755,13 @@
         <v>100.395182</v>
       </c>
       <c r="J316" s="6" t="n">
-        <v>100.586443</v>
+        <v>100.586342</v>
       </c>
       <c r="K316" s="6" t="n">
         <v>100.376384</v>
       </c>
       <c r="L316" s="6" t="n">
-        <v>99.59127599999999</v>
+        <v>99.590737</v>
       </c>
       <c r="M316" s="6" t="n">
         <v>99.18049000000001</v>
@@ -25839,13 +25839,13 @@
         <v>100.644594</v>
       </c>
       <c r="J317" s="9" t="n">
-        <v>100.855207</v>
+        <v>100.855263</v>
       </c>
       <c r="K317" s="9" t="n">
         <v>100.377538</v>
       </c>
       <c r="L317" s="9" t="n">
-        <v>99.67949400000001</v>
+        <v>99.67907099999999</v>
       </c>
       <c r="M317" s="9" t="n">
         <v>99.09212100000001</v>
@@ -25923,13 +25923,13 @@
         <v>100.85787</v>
       </c>
       <c r="J318" s="6" t="n">
-        <v>101.075279</v>
+        <v>101.075482</v>
       </c>
       <c r="K318" s="6" t="n">
         <v>100.374674</v>
       </c>
       <c r="L318" s="6" t="n">
-        <v>99.778583</v>
+        <v>99.778291</v>
       </c>
       <c r="M318" s="6" t="n">
         <v>99.06849</v>
@@ -26007,13 +26007,13 @@
         <v>101.009495</v>
       </c>
       <c r="J319" s="9" t="n">
-        <v>101.249857</v>
+        <v>101.250123</v>
       </c>
       <c r="K319" s="9" t="n">
         <v>100.361885</v>
       </c>
       <c r="L319" s="9" t="n">
-        <v>99.88722199999999</v>
+        <v>99.887074</v>
       </c>
       <c r="M319" s="9" t="n">
         <v>99.07923599999999</v>
@@ -26091,13 +26091,13 @@
         <v>101.123711</v>
       </c>
       <c r="J320" s="6" t="n">
-        <v>101.400614</v>
+        <v>101.400839</v>
       </c>
       <c r="K320" s="6" t="n">
         <v>100.339948</v>
       </c>
       <c r="L320" s="6" t="n">
-        <v>100.002986</v>
+        <v>100.002989</v>
       </c>
       <c r="M320" s="6" t="n">
         <v>99.098054</v>
@@ -26175,13 +26175,13 @@
         <v>101.21678</v>
       </c>
       <c r="J321" s="9" t="n">
-        <v>101.529361</v>
+        <v>101.52941</v>
       </c>
       <c r="K321" s="9" t="n">
         <v>100.3201</v>
       </c>
       <c r="L321" s="9" t="n">
-        <v>100.121526</v>
+        <v>100.121683</v>
       </c>
       <c r="M321" s="9" t="n">
         <v>99.13117</v>
@@ -26259,13 +26259,13 @@
         <v>101.286351</v>
       </c>
       <c r="J322" s="6" t="n">
-        <v>101.634945</v>
+        <v>101.634813</v>
       </c>
       <c r="K322" s="6" t="n">
         <v>100.297013</v>
       </c>
       <c r="L322" s="6" t="n">
-        <v>100.239331</v>
+        <v>100.239641</v>
       </c>
       <c r="M322" s="6" t="n">
         <v>99.191446</v>
@@ -26343,13 +26343,13 @@
         <v>101.320251</v>
       </c>
       <c r="J323" s="9" t="n">
-        <v>101.70471</v>
+        <v>101.704394</v>
       </c>
       <c r="K323" s="9" t="n">
         <v>100.27467</v>
       </c>
       <c r="L323" s="9" t="n">
-        <v>100.353091</v>
+        <v>100.353548</v>
       </c>
       <c r="M323" s="9" t="n">
         <v>99.285488</v>
@@ -26427,13 +26427,13 @@
         <v>101.324999</v>
       </c>
       <c r="J324" s="6" t="n">
-        <v>101.737187</v>
+        <v>101.736751</v>
       </c>
       <c r="K324" s="6" t="n">
         <v>100.260054</v>
       </c>
       <c r="L324" s="6" t="n">
-        <v>100.459599</v>
+        <v>100.460196</v>
       </c>
       <c r="M324" s="6" t="n">
         <v>99.368477</v>
@@ -26511,13 +26511,13 @@
         <v>101.312037</v>
       </c>
       <c r="J325" s="9" t="n">
-        <v>101.736552</v>
+        <v>101.736143</v>
       </c>
       <c r="K325" s="9" t="n">
         <v>100.260132</v>
       </c>
       <c r="L325" s="9" t="n">
-        <v>100.557855</v>
+        <v>100.558583</v>
       </c>
       <c r="M325" s="9" t="n">
         <v>99.429582</v>
@@ -26595,13 +26595,13 @@
         <v>101.289823</v>
       </c>
       <c r="J326" s="6" t="n">
-        <v>101.706041</v>
+        <v>101.705753</v>
       </c>
       <c r="K326" s="6" t="n">
         <v>100.271406</v>
       </c>
       <c r="L326" s="6" t="n">
-        <v>100.650588</v>
+        <v>100.65144</v>
       </c>
       <c r="M326" s="6" t="n">
         <v>99.495312</v>
@@ -26679,13 +26679,13 @@
         <v>101.269616</v>
       </c>
       <c r="J327" s="9" t="n">
-        <v>101.661191</v>
+        <v>101.661041</v>
       </c>
       <c r="K327" s="9" t="n">
         <v>100.2827</v>
       </c>
       <c r="L327" s="9" t="n">
-        <v>100.741447</v>
+        <v>100.742419</v>
       </c>
       <c r="M327" s="9" t="n">
         <v>99.562656</v>
@@ -26763,13 +26763,13 @@
         <v>101.260163</v>
       </c>
       <c r="J328" s="6" t="n">
-        <v>101.617412</v>
+        <v>101.617399</v>
       </c>
       <c r="K328" s="6" t="n">
         <v>100.297104</v>
       </c>
       <c r="L328" s="6" t="n">
-        <v>100.834196</v>
+        <v>100.835291</v>
       </c>
       <c r="M328" s="6" t="n">
         <v>99.625191</v>
@@ -26847,13 +26847,13 @@
         <v>101.275097</v>
       </c>
       <c r="J329" s="9" t="n">
-        <v>101.590988</v>
+        <v>101.591129</v>
       </c>
       <c r="K329" s="9" t="n">
         <v>100.316054</v>
       </c>
       <c r="L329" s="9" t="n">
-        <v>100.931086</v>
+        <v>100.93231</v>
       </c>
       <c r="M329" s="9" t="n">
         <v>99.660704</v>
@@ -26931,13 +26931,13 @@
         <v>101.315538</v>
       </c>
       <c r="J330" s="6" t="n">
-        <v>101.60662</v>
+        <v>101.606839</v>
       </c>
       <c r="K330" s="6" t="n">
         <v>100.3389</v>
       </c>
       <c r="L330" s="6" t="n">
-        <v>101.034435</v>
+        <v>101.035795</v>
       </c>
       <c r="M330" s="6" t="n">
         <v>99.668324</v>
@@ -27015,13 +27015,13 @@
         <v>101.381979</v>
       </c>
       <c r="J331" s="9" t="n">
-        <v>101.663041</v>
+        <v>101.663269</v>
       </c>
       <c r="K331" s="9" t="n">
         <v>100.366251</v>
       </c>
       <c r="L331" s="9" t="n">
-        <v>101.138876</v>
+        <v>101.140373</v>
       </c>
       <c r="M331" s="9" t="n">
         <v>99.63651900000001</v>
@@ -27099,13 +27099,13 @@
         <v>101.469961</v>
       </c>
       <c r="J332" s="6" t="n">
-        <v>101.73348</v>
+        <v>101.733652</v>
       </c>
       <c r="K332" s="6" t="n">
         <v>100.401</v>
       </c>
       <c r="L332" s="6" t="n">
-        <v>101.239138</v>
+        <v>101.240767</v>
       </c>
       <c r="M332" s="6" t="n">
         <v>99.549475</v>
@@ -27183,13 +27183,13 @@
         <v>101.563269</v>
       </c>
       <c r="J333" s="9" t="n">
-        <v>101.78549</v>
+        <v>101.785554</v>
       </c>
       <c r="K333" s="9" t="n">
         <v>100.454335</v>
       </c>
       <c r="L333" s="9" t="n">
-        <v>101.332629</v>
+        <v>101.334378</v>
       </c>
       <c r="M333" s="9" t="n">
         <v>99.397222</v>
@@ -27267,13 +27267,13 @@
         <v>101.645022</v>
       </c>
       <c r="J334" s="6" t="n">
-        <v>101.810185</v>
+        <v>101.81014</v>
       </c>
       <c r="K334" s="6" t="n">
         <v>100.529574</v>
       </c>
       <c r="L334" s="6" t="n">
-        <v>101.418797</v>
+        <v>101.420657</v>
       </c>
       <c r="M334" s="6" t="n">
         <v>99.217837</v>
@@ -27351,13 +27351,13 @@
         <v>101.703883</v>
       </c>
       <c r="J335" s="9" t="n">
-        <v>101.807483</v>
+        <v>101.807362</v>
       </c>
       <c r="K335" s="9" t="n">
         <v>100.619294</v>
       </c>
       <c r="L335" s="9" t="n">
-        <v>101.500618</v>
+        <v>101.502584</v>
       </c>
       <c r="M335" s="9" t="n">
         <v>99.046323</v>
@@ -27435,13 +27435,13 @@
         <v>101.732412</v>
       </c>
       <c r="J336" s="6" t="n">
-        <v>101.783563</v>
+        <v>101.783489</v>
       </c>
       <c r="K336" s="6" t="n">
         <v>100.706536</v>
       </c>
       <c r="L336" s="6" t="n">
-        <v>101.583306</v>
+        <v>101.585381</v>
       </c>
       <c r="M336" s="6" t="n">
         <v>98.91372800000001</v>
@@ -27519,13 +27519,13 @@
         <v>101.734915</v>
       </c>
       <c r="J337" s="9" t="n">
-        <v>101.748897</v>
+        <v>101.748871</v>
       </c>
       <c r="K337" s="9" t="n">
         <v>100.779278</v>
       </c>
       <c r="L337" s="9" t="n">
-        <v>101.666105</v>
+        <v>101.668291</v>
       </c>
       <c r="M337" s="9" t="n">
         <v>98.85507800000001</v>
@@ -27603,13 +27603,13 @@
         <v>101.714332</v>
       </c>
       <c r="J338" s="6" t="n">
-        <v>101.718082</v>
+        <v>101.718057</v>
       </c>
       <c r="K338" s="6" t="n">
         <v>100.832357</v>
       </c>
       <c r="L338" s="6" t="n">
-        <v>101.748682</v>
+        <v>101.750979</v>
       </c>
       <c r="M338" s="6" t="n">
         <v>98.849913</v>
@@ -27687,13 +27687,13 @@
         <v>101.677054</v>
       </c>
       <c r="J339" s="9" t="n">
-        <v>101.693324</v>
+        <v>101.693356</v>
       </c>
       <c r="K339" s="9" t="n">
         <v>100.866847</v>
       </c>
       <c r="L339" s="9" t="n">
-        <v>101.829521</v>
+        <v>101.831928</v>
       </c>
       <c r="M339" s="9" t="n">
         <v>98.850313</v>
@@ -27771,13 +27771,13 @@
         <v>101.638798</v>
       </c>
       <c r="J340" s="6" t="n">
-        <v>101.686671</v>
+        <v>101.686789</v>
       </c>
       <c r="K340" s="6" t="n">
         <v>100.892303</v>
       </c>
       <c r="L340" s="6" t="n">
-        <v>101.90382</v>
+        <v>101.906327</v>
       </c>
       <c r="M340" s="6" t="n">
         <v>98.83051399999999</v>
@@ -27855,13 +27855,13 @@
         <v>101.618118</v>
       </c>
       <c r="J341" s="9" t="n">
-        <v>101.708757</v>
+        <v>101.708914</v>
       </c>
       <c r="K341" s="9" t="n">
         <v>100.918839</v>
       </c>
       <c r="L341" s="9" t="n">
-        <v>101.964273</v>
+        <v>101.966859</v>
       </c>
       <c r="M341" s="9" t="n">
         <v>98.789145</v>
@@ -27939,13 +27939,13 @@
         <v>101.620766</v>
       </c>
       <c r="J342" s="6" t="n">
-        <v>101.74514</v>
+        <v>101.745379</v>
       </c>
       <c r="K342" s="6" t="n">
         <v>100.957647</v>
       </c>
       <c r="L342" s="6" t="n">
-        <v>102.011084</v>
+        <v>102.013731</v>
       </c>
       <c r="M342" s="6" t="n">
         <v>98.704089</v>
@@ -28023,13 +28023,13 @@
         <v>101.639652</v>
       </c>
       <c r="J343" s="9" t="n">
-        <v>101.77598</v>
+        <v>101.776216</v>
       </c>
       <c r="K343" s="9" t="n">
         <v>100.982653</v>
       </c>
       <c r="L343" s="9" t="n">
-        <v>102.043142</v>
+        <v>102.04583</v>
       </c>
       <c r="M343" s="9" t="n">
         <v>98.56507000000001</v>
@@ -28107,13 +28107,13 @@
         <v>101.673783</v>
       </c>
       <c r="J344" s="6" t="n">
-        <v>101.765745</v>
+        <v>101.765782</v>
       </c>
       <c r="K344" s="6" t="n">
         <v>100.984733</v>
       </c>
       <c r="L344" s="6" t="n">
-        <v>102.059054</v>
+        <v>102.061759</v>
       </c>
       <c r="M344" s="6" t="n">
         <v>98.401582</v>
@@ -28191,13 +28191,13 @@
         <v>101.729031</v>
       </c>
       <c r="J345" s="9" t="n">
-        <v>101.733837</v>
+        <v>101.733667</v>
       </c>
       <c r="K345" s="9" t="n">
         <v>100.968518</v>
       </c>
       <c r="L345" s="9" t="n">
-        <v>102.054679</v>
+        <v>102.057377</v>
       </c>
       <c r="M345" s="9" t="n">
         <v>98.25706599999999</v>
@@ -28275,13 +28275,13 @@
         <v>101.758898</v>
       </c>
       <c r="J346" s="6" t="n">
-        <v>101.675774</v>
+        <v>101.675375</v>
       </c>
       <c r="K346" s="6" t="n">
         <v>100.921826</v>
       </c>
       <c r="L346" s="6" t="n">
-        <v>102.023885</v>
+        <v>102.026541</v>
       </c>
       <c r="M346" s="6" t="n">
         <v>98.17639</v>
@@ -28359,13 +28359,13 @@
         <v>101.731161</v>
       </c>
       <c r="J347" s="9" t="n">
-        <v>101.566637</v>
+        <v>101.5661</v>
       </c>
       <c r="K347" s="9" t="n">
         <v>100.844978</v>
       </c>
       <c r="L347" s="9" t="n">
-        <v>101.956562</v>
+        <v>101.959127</v>
       </c>
       <c r="M347" s="9" t="n">
         <v>98.19614</v>
@@ -28443,13 +28443,13 @@
         <v>101.602005</v>
       </c>
       <c r="J348" s="6" t="n">
-        <v>101.36948</v>
+        <v>101.369122</v>
       </c>
       <c r="K348" s="6" t="n">
         <v>100.738959</v>
       </c>
       <c r="L348" s="6" t="n">
-        <v>101.840977</v>
+        <v>101.843392</v>
       </c>
       <c r="M348" s="6" t="n">
         <v>98.325563</v>
@@ -28527,13 +28527,13 @@
         <v>101.345483</v>
       </c>
       <c r="J349" s="9" t="n">
-        <v>101.081784</v>
+        <v>101.081684</v>
       </c>
       <c r="K349" s="9" t="n">
         <v>100.610764</v>
       </c>
       <c r="L349" s="9" t="n">
-        <v>101.669757</v>
+        <v>101.671949</v>
       </c>
       <c r="M349" s="9" t="n">
         <v>98.53974700000001</v>
@@ -28611,13 +28611,13 @@
         <v>100.95627</v>
       </c>
       <c r="J350" s="6" t="n">
-        <v>100.685638</v>
+        <v>100.685709</v>
       </c>
       <c r="K350" s="6" t="n">
         <v>100.476352</v>
       </c>
       <c r="L350" s="6" t="n">
-        <v>101.439009</v>
+        <v>101.440902</v>
       </c>
       <c r="M350" s="6" t="n">
         <v>98.837464</v>
@@ -28695,13 +28695,13 @@
         <v>100.423675</v>
       </c>
       <c r="J351" s="9" t="n">
-        <v>100.168217</v>
+        <v>100.16835</v>
       </c>
       <c r="K351" s="9" t="n">
         <v>100.348684</v>
       </c>
       <c r="L351" s="9" t="n">
-        <v>101.14673</v>
+        <v>101.148242</v>
       </c>
       <c r="M351" s="9" t="n">
         <v>99.230667</v>
@@ -28779,13 +28779,13 @@
         <v>99.74545999999999</v>
       </c>
       <c r="J352" s="6" t="n">
-        <v>99.52229199999999</v>
+        <v>99.522375</v>
       </c>
       <c r="K352" s="6" t="n">
         <v>100.233562</v>
       </c>
       <c r="L352" s="6" t="n">
-        <v>100.797024</v>
+        <v>100.798077</v>
       </c>
       <c r="M352" s="6" t="n">
         <v>99.690941</v>
@@ -28863,13 +28863,13 @@
         <v>98.966345</v>
       </c>
       <c r="J353" s="9" t="n">
-        <v>98.787513</v>
+        <v>98.787548</v>
       </c>
       <c r="K353" s="9" t="n">
         <v>100.134693</v>
       </c>
       <c r="L353" s="9" t="n">
-        <v>100.403789</v>
+        <v>100.404325</v>
       </c>
       <c r="M353" s="9" t="n">
         <v>100.153367</v>
@@ -28947,13 +28947,13 @@
         <v>98.17129300000001</v>
       </c>
       <c r="J354" s="6" t="n">
-        <v>98.03982000000001</v>
+        <v>98.03980199999999</v>
       </c>
       <c r="K354" s="6" t="n">
         <v>100.046103</v>
       </c>
       <c r="L354" s="6" t="n">
-        <v>99.98400100000001</v>
+        <v>99.98398400000001</v>
       </c>
       <c r="M354" s="6" t="n">
         <v>100.585507</v>
@@ -29031,13 +29031,13 @@
         <v>97.494719</v>
       </c>
       <c r="J355" s="9" t="n">
-        <v>97.406745</v>
+        <v>97.406628</v>
       </c>
       <c r="K355" s="9" t="n">
         <v>99.956709</v>
       </c>
       <c r="L355" s="9" t="n">
-        <v>99.56670800000001</v>
+        <v>99.566142</v>
       </c>
       <c r="M355" s="9" t="n">
         <v>100.987692</v>
@@ -29115,13 +29115,13 @@
         <v>97.00215</v>
       </c>
       <c r="J356" s="6" t="n">
-        <v>96.94794</v>
+        <v>96.94768500000001</v>
       </c>
       <c r="K356" s="6" t="n">
         <v>99.86262000000001</v>
       </c>
       <c r="L356" s="6" t="n">
-        <v>99.17800800000001</v>
+        <v>99.176928</v>
       </c>
       <c r="M356" s="6" t="n">
         <v>101.349711</v>
@@ -29199,13 +29199,13 @@
         <v>96.720716</v>
       </c>
       <c r="J357" s="9" t="n">
-        <v>96.68701799999999</v>
+        <v>96.686582</v>
       </c>
       <c r="K357" s="9" t="n">
         <v>99.75608</v>
       </c>
       <c r="L357" s="9" t="n">
-        <v>98.833833</v>
+        <v>98.83229799999999</v>
       </c>
       <c r="M357" s="9" t="n">
         <v>101.654181</v>
@@ -29283,13 +29283,13 @@
         <v>96.661676</v>
       </c>
       <c r="J358" s="6" t="n">
-        <v>96.617347</v>
+        <v>96.61674499999999</v>
       </c>
       <c r="K358" s="6" t="n">
         <v>99.654662</v>
       </c>
       <c r="L358" s="6" t="n">
-        <v>98.54447</v>
+        <v>98.542553</v>
       </c>
       <c r="M358" s="6" t="n">
         <v>101.861645</v>
@@ -29367,13 +29367,13 @@
         <v>96.803201</v>
       </c>
       <c r="J359" s="9" t="n">
-        <v>96.72145500000001</v>
+        <v>96.720698</v>
       </c>
       <c r="K359" s="9" t="n">
         <v>99.57338300000001</v>
       </c>
       <c r="L359" s="9" t="n">
-        <v>98.31887999999999</v>
+        <v>98.316666</v>
       </c>
       <c r="M359" s="9" t="n">
         <v>101.96381</v>
@@ -29451,13 +29451,13 @@
         <v>97.072547</v>
       </c>
       <c r="J360" s="6" t="n">
-        <v>96.96740699999999</v>
+        <v>96.966677</v>
       </c>
       <c r="K360" s="6" t="n">
         <v>99.512595</v>
       </c>
       <c r="L360" s="6" t="n">
-        <v>98.158868</v>
+        <v>98.15644399999999</v>
       </c>
       <c r="M360" s="6" t="n">
         <v>102.002672</v>
@@ -29535,13 +29535,13 @@
         <v>97.39340199999999</v>
       </c>
       <c r="J361" s="9" t="n">
-        <v>97.293564</v>
+        <v>97.29292599999999</v>
       </c>
       <c r="K361" s="9" t="n">
         <v>99.464564</v>
       </c>
       <c r="L361" s="9" t="n">
-        <v>98.061081</v>
+        <v>98.05853</v>
       </c>
       <c r="M361" s="9" t="n">
         <v>101.972665</v>
@@ -29619,13 +29619,13 @@
         <v>97.729226</v>
       </c>
       <c r="J362" s="6" t="n">
-        <v>97.659549</v>
+        <v>97.659109</v>
       </c>
       <c r="K362" s="6" t="n">
         <v>99.429982</v>
       </c>
       <c r="L362" s="6" t="n">
-        <v>98.01920800000001</v>
+        <v>98.016605</v>
       </c>
       <c r="M362" s="6" t="n">
         <v>101.864989</v>
@@ -29703,13 +29703,13 @@
         <v>98.04966400000001</v>
       </c>
       <c r="J363" s="9" t="n">
-        <v>98.020455</v>
+        <v>98.020214</v>
       </c>
       <c r="K363" s="9" t="n">
         <v>99.408844</v>
       </c>
       <c r="L363" s="9" t="n">
-        <v>98.02971599999999</v>
+        <v>98.02713</v>
       </c>
       <c r="M363" s="9" t="n">
         <v>101.677523</v>
@@ -29787,13 +29787,13 @@
         <v>98.331205</v>
       </c>
       <c r="J364" s="6" t="n">
-        <v>98.34524</v>
+        <v>98.34518799999999</v>
       </c>
       <c r="K364" s="6" t="n">
         <v>99.40582499999999</v>
       </c>
       <c r="L364" s="6" t="n">
-        <v>98.089327</v>
+        <v>98.086822</v>
       </c>
       <c r="M364" s="6" t="n">
         <v>101.46015</v>
@@ -29871,13 +29871,13 @@
         <v>98.55943600000001</v>
       </c>
       <c r="J365" s="9" t="n">
-        <v>98.605819</v>
+        <v>98.605935</v>
       </c>
       <c r="K365" s="9" t="n">
         <v>99.420489</v>
       </c>
       <c r="L365" s="9" t="n">
-        <v>98.18641700000001</v>
+        <v>98.18404099999999</v>
       </c>
       <c r="M365" s="9" t="n">
         <v>101.273682</v>
@@ -29955,13 +29955,13 @@
         <v>98.74196600000001</v>
       </c>
       <c r="J366" s="6" t="n">
-        <v>98.801059</v>
+        <v>98.801265</v>
       </c>
       <c r="K366" s="6" t="n">
         <v>99.448779</v>
       </c>
       <c r="L366" s="6" t="n">
-        <v>98.306924</v>
+        <v>98.30470699999999</v>
       </c>
       <c r="M366" s="6" t="n">
         <v>101.130752</v>
@@ -30039,13 +30039,13 @@
         <v>98.909769</v>
       </c>
       <c r="J367" s="9" t="n">
-        <v>98.95089299999999</v>
+        <v>98.95103400000001</v>
       </c>
       <c r="K367" s="9" t="n">
         <v>99.493533</v>
       </c>
       <c r="L367" s="9" t="n">
-        <v>98.43932100000001</v>
+        <v>98.437279</v>
       </c>
       <c r="M367" s="9" t="n">
         <v>100.997754</v>
@@ -30123,13 +30123,13 @@
         <v>99.06503499999999</v>
       </c>
       <c r="J368" s="6" t="n">
-        <v>99.07379400000001</v>
+        <v>99.073775</v>
       </c>
       <c r="K368" s="6" t="n">
         <v>99.54078</v>
       </c>
       <c r="L368" s="6" t="n">
-        <v>98.572681</v>
+        <v>98.570815</v>
       </c>
       <c r="M368" s="6" t="n">
         <v>100.891988</v>
@@ -30207,13 +30207,13 @@
         <v>99.195863</v>
       </c>
       <c r="J369" s="9" t="n">
-        <v>99.159384</v>
+        <v>99.159145</v>
       </c>
       <c r="K369" s="9" t="n">
         <v>99.577088</v>
       </c>
       <c r="L369" s="9" t="n">
-        <v>98.69810200000001</v>
+        <v>98.69640099999999</v>
       </c>
       <c r="M369" s="9" t="n">
         <v>100.806185</v>
@@ -30291,13 +30291,13 @@
         <v>99.286001</v>
       </c>
       <c r="J370" s="6" t="n">
-        <v>99.19579299999999</v>
+        <v>99.195295</v>
       </c>
       <c r="K370" s="6" t="n">
         <v>99.60337800000001</v>
       </c>
       <c r="L370" s="6" t="n">
-        <v>98.81057300000001</v>
+        <v>98.80901900000001</v>
       </c>
       <c r="M370" s="6" t="n">
         <v>100.720796</v>
@@ -30375,13 +30375,13 @@
         <v>99.344471</v>
       </c>
       <c r="J371" s="9" t="n">
-        <v>99.19694699999999</v>
+        <v>99.196333</v>
       </c>
       <c r="K371" s="9" t="n">
         <v>99.610176</v>
       </c>
       <c r="L371" s="9" t="n">
-        <v>98.90791400000001</v>
+        <v>98.90648899999999</v>
       </c>
       <c r="M371" s="9" t="n">
         <v>100.637042</v>
@@ -30459,13 +30459,13 @@
         <v>99.385468</v>
       </c>
       <c r="J372" s="6" t="n">
-        <v>99.177706</v>
+        <v>99.177138</v>
       </c>
       <c r="K372" s="6" t="n">
         <v>99.599675</v>
       </c>
       <c r="L372" s="6" t="n">
-        <v>98.99310699999999</v>
+        <v>98.991794</v>
       </c>
       <c r="M372" s="6" t="n">
         <v>100.546853</v>
@@ -30543,13 +30543,13 @@
         <v>99.41757699999999</v>
       </c>
       <c r="J373" s="9" t="n">
-        <v>99.151837</v>
+        <v>99.151408</v>
       </c>
       <c r="K373" s="9" t="n">
         <v>99.575132</v>
       </c>
       <c r="L373" s="9" t="n">
-        <v>99.069782</v>
+        <v>99.06857100000001</v>
       </c>
       <c r="M373" s="9" t="n">
         <v>100.477041</v>
@@ -30627,13 +30627,13 @@
         <v>99.447481</v>
       </c>
       <c r="J374" s="6" t="n">
-        <v>99.121506</v>
+        <v>99.12123099999999</v>
       </c>
       <c r="K374" s="6" t="n">
         <v>99.53141100000001</v>
       </c>
       <c r="L374" s="6" t="n">
-        <v>99.14059399999999</v>
+        <v>99.13948000000001</v>
       </c>
       <c r="M374" s="6" t="n">
         <v>100.461442</v>
@@ -30711,13 +30711,13 @@
         <v>99.481326</v>
       </c>
       <c r="J375" s="9" t="n">
-        <v>99.10315300000001</v>
+        <v>99.103025</v>
       </c>
       <c r="K375" s="9" t="n">
         <v>99.47676800000001</v>
       </c>
       <c r="L375" s="9" t="n">
-        <v>99.20860999999999</v>
+        <v>99.207588</v>
       </c>
       <c r="M375" s="9" t="n">
         <v>100.457102</v>
@@ -30795,13 +30795,13 @@
         <v>99.527075</v>
       </c>
       <c r="J376" s="6" t="n">
-        <v>99.107989</v>
+        <v>99.107911</v>
       </c>
       <c r="K376" s="6" t="n">
         <v>99.422498</v>
       </c>
       <c r="L376" s="6" t="n">
-        <v>99.27298500000001</v>
+        <v>99.272052</v>
       </c>
       <c r="M376" s="6" t="n">
         <v>100.427488</v>
@@ -30879,13 +30879,13 @@
         <v>99.584295</v>
       </c>
       <c r="J377" s="9" t="n">
-        <v>99.142107</v>
+        <v>99.142009</v>
       </c>
       <c r="K377" s="9" t="n">
         <v>99.39439299999999</v>
       </c>
       <c r="L377" s="9" t="n">
-        <v>99.332167</v>
+        <v>99.33131299999999</v>
       </c>
       <c r="M377" s="9" t="n">
         <v>100.351876</v>
@@ -30963,13 +30963,13 @@
         <v>99.64242299999999</v>
       </c>
       <c r="J378" s="6" t="n">
-        <v>99.19612100000001</v>
+        <v>99.195933</v>
       </c>
       <c r="K378" s="6" t="n">
         <v>99.375062</v>
       </c>
       <c r="L378" s="6" t="n">
-        <v>99.384793</v>
+        <v>99.38401</v>
       </c>
       <c r="M378" s="6" t="n">
         <v>100.214787</v>
@@ -31047,13 +31047,13 @@
         <v>99.700738</v>
       </c>
       <c r="J379" s="9" t="n">
-        <v>99.269543</v>
+        <v>99.26933699999999</v>
       </c>
       <c r="K379" s="9" t="n">
         <v>99.359846</v>
       </c>
       <c r="L379" s="9" t="n">
-        <v>99.430361</v>
+        <v>99.429638</v>
       </c>
       <c r="M379" s="9" t="n">
         <v>100.069248</v>
@@ -31131,13 +31131,13 @@
         <v>99.762776</v>
       </c>
       <c r="J380" s="6" t="n">
-        <v>99.36842799999999</v>
+        <v>99.368239</v>
       </c>
       <c r="K380" s="6" t="n">
         <v>99.371391</v>
       </c>
       <c r="L380" s="6" t="n">
-        <v>99.46854500000001</v>
+        <v>99.467873</v>
       </c>
       <c r="M380" s="6" t="n">
         <v>99.95326799999999</v>
@@ -31215,13 +31215,13 @@
         <v>99.834366</v>
       </c>
       <c r="J381" s="9" t="n">
-        <v>99.48869999999999</v>
+        <v>99.48851000000001</v>
       </c>
       <c r="K381" s="9" t="n">
         <v>99.405869</v>
       </c>
       <c r="L381" s="9" t="n">
-        <v>99.497806</v>
+        <v>99.497173</v>
       </c>
       <c r="M381" s="9" t="n">
         <v>99.893018</v>
@@ -31299,13 +31299,13 @@
         <v>99.936494</v>
       </c>
       <c r="J382" s="6" t="n">
-        <v>99.630185</v>
+        <v>99.62996200000001</v>
       </c>
       <c r="K382" s="6" t="n">
         <v>99.4457</v>
       </c>
       <c r="L382" s="6" t="n">
-        <v>99.51745099999999</v>
+        <v>99.516845</v>
       </c>
       <c r="M382" s="6" t="n">
         <v>99.90525599999999</v>
@@ -31383,13 +31383,13 @@
         <v>100.055366</v>
       </c>
       <c r="J383" s="9" t="n">
-        <v>99.780669</v>
+        <v>99.78041399999999</v>
       </c>
       <c r="K383" s="9" t="n">
         <v>99.49186899999999</v>
       </c>
       <c r="L383" s="9" t="n">
-        <v>99.532777</v>
+        <v>99.53219300000001</v>
       </c>
       <c r="M383" s="9" t="n">
         <v>99.92578399999999</v>
@@ -31467,13 +31467,13 @@
         <v>100.18013</v>
       </c>
       <c r="J384" s="6" t="n">
-        <v>99.93088400000001</v>
+        <v>99.930651</v>
       </c>
       <c r="K384" s="6" t="n">
         <v>99.55290100000001</v>
       </c>
       <c r="L384" s="6" t="n">
-        <v>99.54910700000001</v>
+        <v>99.548546</v>
       </c>
       <c r="M384" s="6" t="n">
         <v>99.916354</v>
@@ -31551,13 +31551,13 @@
         <v>100.302255</v>
       </c>
       <c r="J385" s="9" t="n">
-        <v>100.090452</v>
+        <v>100.090241</v>
       </c>
       <c r="K385" s="9" t="n">
         <v>99.639684</v>
       </c>
       <c r="L385" s="9" t="n">
-        <v>99.570215</v>
+        <v>99.569684</v>
       </c>
       <c r="M385" s="9" t="n">
         <v>99.87211600000001</v>
@@ -31635,13 +31635,13 @@
         <v>100.410591</v>
       </c>
       <c r="J386" s="6" t="n">
-        <v>100.265147</v>
+        <v>100.264956</v>
       </c>
       <c r="K386" s="6" t="n">
         <v>99.74882599999999</v>
       </c>
       <c r="L386" s="6" t="n">
-        <v>99.599389</v>
+        <v>99.598899</v>
       </c>
       <c r="M386" s="6" t="n">
         <v>99.81053199999999</v>
@@ -31719,13 +31719,13 @@
         <v>100.50774</v>
       </c>
       <c r="J387" s="9" t="n">
-        <v>100.456892</v>
+        <v>100.456663</v>
       </c>
       <c r="K387" s="9" t="n">
         <v>99.870052</v>
       </c>
       <c r="L387" s="9" t="n">
-        <v>99.63746500000001</v>
+        <v>99.637028</v>
       </c>
       <c r="M387" s="9" t="n">
         <v>99.751735</v>
@@ -31803,13 +31803,13 @@
         <v>100.599306</v>
       </c>
       <c r="J388" s="6" t="n">
-        <v>100.641121</v>
+        <v>100.640929</v>
       </c>
       <c r="K388" s="6" t="n">
         <v>99.99978400000001</v>
       </c>
       <c r="L388" s="6" t="n">
-        <v>99.684757</v>
+        <v>99.68438399999999</v>
       </c>
       <c r="M388" s="6" t="n">
         <v>99.71040600000001</v>
@@ -31887,13 +31887,13 @@
         <v>100.681257</v>
       </c>
       <c r="J389" s="9" t="n">
-        <v>100.793208</v>
+        <v>100.793069</v>
       </c>
       <c r="K389" s="9" t="n">
         <v>100.13354</v>
       </c>
       <c r="L389" s="9" t="n">
-        <v>99.74150899999999</v>
+        <v>99.741213</v>
       </c>
       <c r="M389" s="9" t="n">
         <v>99.69152200000001</v>
@@ -31971,13 +31971,13 @@
         <v>100.752972</v>
       </c>
       <c r="J390" s="6" t="n">
-        <v>100.901147</v>
+        <v>100.901033</v>
       </c>
       <c r="K390" s="6" t="n">
         <v>100.251953</v>
       </c>
       <c r="L390" s="6" t="n">
-        <v>99.80497800000001</v>
+        <v>99.804768</v>
       </c>
       <c r="M390" s="6" t="n">
         <v>99.71194199999999</v>
@@ -32055,13 +32055,13 @@
         <v>100.801695</v>
       </c>
       <c r="J391" s="9" t="n">
-        <v>100.968363</v>
+        <v>100.968247</v>
       </c>
       <c r="K391" s="9" t="n">
         <v>100.343769</v>
       </c>
       <c r="L391" s="9" t="n">
-        <v>99.86977</v>
+        <v>99.869647</v>
       </c>
       <c r="M391" s="9" t="n">
         <v>99.754248</v>
@@ -32139,13 +32139,13 @@
         <v>100.823855</v>
       </c>
       <c r="J392" s="6" t="n">
-        <v>101.004983</v>
+        <v>101.004862</v>
       </c>
       <c r="K392" s="6" t="n">
         <v>100.398422</v>
       </c>
       <c r="L392" s="6" t="n">
-        <v>99.93106400000001</v>
+        <v>99.93102399999999</v>
       </c>
       <c r="M392" s="6" t="n">
         <v>99.765761</v>
@@ -32223,13 +32223,13 @@
         <v>100.821764</v>
       </c>
       <c r="J393" s="9" t="n">
-        <v>101.017521</v>
+        <v>101.017402</v>
       </c>
       <c r="K393" s="9" t="n">
         <v>100.418693</v>
       </c>
       <c r="L393" s="9" t="n">
-        <v>99.98683</v>
+        <v>99.98686499999999</v>
       </c>
       <c r="M393" s="9" t="n">
         <v>99.749911</v>
@@ -32307,13 +32307,13 @@
         <v>100.802062</v>
       </c>
       <c r="J394" s="6" t="n">
-        <v>101.004797</v>
+        <v>101.004737</v>
       </c>
       <c r="K394" s="6" t="n">
         <v>100.413961</v>
       </c>
       <c r="L394" s="6" t="n">
-        <v>100.041283</v>
+        <v>100.041392</v>
       </c>
       <c r="M394" s="6" t="n">
         <v>99.72132999999999</v>
@@ -32391,13 +32391,13 @@
         <v>100.777497</v>
       </c>
       <c r="J395" s="9" t="n">
-        <v>100.970435</v>
+        <v>100.970436</v>
       </c>
       <c r="K395" s="9" t="n">
         <v>100.394821</v>
       </c>
       <c r="L395" s="9" t="n">
-        <v>100.096492</v>
+        <v>100.096676</v>
       </c>
       <c r="M395" s="9" t="n">
         <v>99.68391699999999</v>
@@ -32475,13 +32475,13 @@
         <v>100.743601</v>
       </c>
       <c r="J396" s="6" t="n">
-        <v>100.903814</v>
+        <v>100.903804</v>
       </c>
       <c r="K396" s="6" t="n">
         <v>100.370633</v>
       </c>
       <c r="L396" s="6" t="n">
-        <v>100.149178</v>
+        <v>100.149433</v>
       </c>
       <c r="M396" s="6" t="n">
         <v>99.673507</v>
@@ -32559,13 +32559,13 @@
         <v>100.698623</v>
       </c>
       <c r="J397" s="9" t="n">
-        <v>100.795328</v>
+        <v>100.795256</v>
       </c>
       <c r="K397" s="9" t="n">
         <v>100.355277</v>
       </c>
       <c r="L397" s="9" t="n">
-        <v>100.196955</v>
+        <v>100.197275</v>
       </c>
       <c r="M397" s="9" t="n">
         <v>99.70941500000001</v>
@@ -32643,13 +32643,13 @@
         <v>100.653655</v>
       </c>
       <c r="J398" s="6" t="n">
-        <v>100.66385</v>
+        <v>100.663653</v>
       </c>
       <c r="K398" s="6" t="n">
         <v>100.325709</v>
       </c>
       <c r="L398" s="6" t="n">
-        <v>100.238385</v>
+        <v>100.238762</v>
       </c>
       <c r="M398" s="6" t="n">
         <v>99.784696</v>
@@ -32727,13 +32727,13 @@
         <v>100.60564</v>
       </c>
       <c r="J399" s="9" t="n">
-        <v>100.508824</v>
+        <v>100.508538</v>
       </c>
       <c r="K399" s="9" t="n">
         <v>100.26201</v>
       </c>
       <c r="L399" s="9" t="n">
-        <v>100.271204</v>
+        <v>100.271627</v>
       </c>
       <c r="M399" s="9" t="n">
         <v>99.908417</v>
@@ -32811,13 +32811,13 @@
         <v>100.548644</v>
       </c>
       <c r="J400" s="6" t="n">
-        <v>100.360917</v>
+        <v>100.360567</v>
       </c>
       <c r="K400" s="6" t="n">
         <v>100.175342</v>
       </c>
       <c r="L400" s="6" t="n">
-        <v>100.295719</v>
+        <v>100.296176</v>
       </c>
       <c r="M400" s="6" t="n">
         <v>100.052815</v>
@@ -32895,13 +32895,13 @@
         <v>100.465217</v>
       </c>
       <c r="J401" s="9" t="n">
-        <v>100.219762</v>
+        <v>100.219358</v>
       </c>
       <c r="K401" s="9" t="n">
         <v>100.087265</v>
       </c>
       <c r="L401" s="9" t="n">
-        <v>100.311138</v>
+        <v>100.311617</v>
       </c>
       <c r="M401" s="9" t="n">
         <v>100.174945</v>
@@ -32979,13 +32979,13 @@
         <v>100.359909</v>
       </c>
       <c r="J402" s="6" t="n">
-        <v>100.088888</v>
+        <v>100.088554</v>
       </c>
       <c r="K402" s="6" t="n">
         <v>100.025711</v>
       </c>
       <c r="L402" s="6" t="n">
-        <v>100.314671</v>
+        <v>100.315157</v>
       </c>
       <c r="M402" s="6" t="n">
         <v>100.248327</v>
@@ -33063,13 +33063,13 @@
         <v>100.243815</v>
       </c>
       <c r="J403" s="9" t="n">
-        <v>99.96141799999999</v>
+        <v>99.961204</v>
       </c>
       <c r="K403" s="9" t="n">
         <v>99.97709</v>
       </c>
       <c r="L403" s="9" t="n">
-        <v>100.304761</v>
+        <v>100.305235</v>
       </c>
       <c r="M403" s="9" t="n">
         <v>100.261794</v>
@@ -33147,13 +33147,13 @@
         <v>100.130933</v>
       </c>
       <c r="J404" s="6" t="n">
-        <v>99.829155</v>
+        <v>99.829032</v>
       </c>
       <c r="K404" s="6" t="n">
         <v>99.93495900000001</v>
       </c>
       <c r="L404" s="6" t="n">
-        <v>100.281423</v>
+        <v>100.281868</v>
       </c>
       <c r="M404" s="6" t="n">
         <v>100.239719</v>
@@ -33231,13 +33231,13 @@
         <v>100.033482</v>
       </c>
       <c r="J405" s="9" t="n">
-        <v>99.71278</v>
+        <v>99.712627</v>
       </c>
       <c r="K405" s="9" t="n">
         <v>99.895349</v>
       </c>
       <c r="L405" s="9" t="n">
-        <v>100.246501</v>
+        <v>100.246902</v>
       </c>
       <c r="M405" s="9" t="n">
         <v>100.183052</v>
@@ -33315,13 +33315,13 @@
         <v>99.95945500000001</v>
       </c>
       <c r="J406" s="6" t="n">
-        <v>99.629597</v>
+        <v>99.629347</v>
       </c>
       <c r="K406" s="6" t="n">
         <v>99.85973199999999</v>
       </c>
       <c r="L406" s="6" t="n">
-        <v>100.20246</v>
+        <v>100.202807</v>
       </c>
       <c r="M406" s="6" t="n">
         <v>100.08159</v>
@@ -33399,13 +33399,13 @@
         <v>99.899371</v>
       </c>
       <c r="J407" s="9" t="n">
-        <v>99.564835</v>
+        <v>99.564437</v>
       </c>
       <c r="K407" s="9" t="n">
         <v>99.816146</v>
       </c>
       <c r="L407" s="9" t="n">
-        <v>100.151369</v>
+        <v>100.15165</v>
       </c>
       <c r="M407" s="9" t="n">
         <v>99.988404</v>
@@ -33483,13 +33483,13 @@
         <v>99.854653</v>
       </c>
       <c r="J408" s="6" t="n">
-        <v>99.527833</v>
+        <v>99.527354</v>
       </c>
       <c r="K408" s="6" t="n">
         <v>99.759885</v>
       </c>
       <c r="L408" s="6" t="n">
-        <v>100.095988</v>
+        <v>100.096199</v>
       </c>
       <c r="M408" s="6" t="n">
         <v>99.914632</v>
@@ -33567,13 +33567,13 @@
         <v>99.822395</v>
       </c>
       <c r="J409" s="9" t="n">
-        <v>99.516475</v>
+        <v>99.516019</v>
       </c>
       <c r="K409" s="9" t="n">
         <v>99.68767699999999</v>
       </c>
       <c r="L409" s="9" t="n">
-        <v>100.039442</v>
+        <v>100.03958</v>
       </c>
       <c r="M409" s="9" t="n">
         <v>99.88269200000001</v>
@@ -33651,13 +33651,13 @@
         <v>99.793025</v>
       </c>
       <c r="J410" s="6" t="n">
-        <v>99.521102</v>
+        <v>99.520746</v>
       </c>
       <c r="K410" s="6" t="n">
         <v>99.613501</v>
       </c>
       <c r="L410" s="6" t="n">
-        <v>99.98276</v>
+        <v>99.98282500000001</v>
       </c>
       <c r="M410" s="6" t="n">
         <v>99.909736</v>
@@ -33735,13 +33735,13 @@
         <v>99.769323</v>
       </c>
       <c r="J411" s="9" t="n">
-        <v>99.554152</v>
+        <v>99.553943</v>
       </c>
       <c r="K411" s="9" t="n">
         <v>99.54355</v>
       </c>
       <c r="L411" s="9" t="n">
-        <v>99.927986</v>
+        <v>99.927981</v>
       </c>
       <c r="M411" s="9" t="n">
         <v>99.996787</v>
@@ -33819,13 +33819,13 @@
         <v>99.75527099999999</v>
       </c>
       <c r="J412" s="6" t="n">
-        <v>99.61118999999999</v>
+        <v>99.611103</v>
       </c>
       <c r="K412" s="6" t="n">
         <v>99.482086</v>
       </c>
       <c r="L412" s="6" t="n">
-        <v>99.87616</v>
+        <v>99.87608899999999</v>
       </c>
       <c r="M412" s="6" t="n">
         <v>100.163136</v>
@@ -33903,13 +33903,13 @@
         <v>99.76277399999999</v>
       </c>
       <c r="J413" s="9" t="n">
-        <v>99.700863</v>
+        <v>99.7008</v>
       </c>
       <c r="K413" s="9" t="n">
         <v>99.43015699999999</v>
       </c>
       <c r="L413" s="9" t="n">
-        <v>99.828113</v>
+        <v>99.827979</v>
       </c>
       <c r="M413" s="9" t="n">
         <v>100.415345</v>
@@ -33987,13 +33987,13 @@
         <v>99.796195</v>
       </c>
       <c r="J414" s="6" t="n">
-        <v>99.826043</v>
+        <v>99.82587700000001</v>
       </c>
       <c r="K414" s="6" t="n">
         <v>99.399823</v>
       </c>
       <c r="L414" s="6" t="n">
-        <v>99.78765199999999</v>
+        <v>99.787465</v>
       </c>
       <c r="M414" s="6" t="n">
         <v>100.675654</v>
@@ -34071,13 +34071,13 @@
         <v>99.86736000000001</v>
       </c>
       <c r="J415" s="9" t="n">
-        <v>99.983569</v>
+        <v>99.983197</v>
       </c>
       <c r="K415" s="9" t="n">
         <v>99.40033200000001</v>
       </c>
       <c r="L415" s="9" t="n">
-        <v>99.760356</v>
+        <v>99.760132</v>
       </c>
       <c r="M415" s="9" t="n">
         <v>100.883808</v>
@@ -34155,13 +34155,13 @@
         <v>99.95337499999999</v>
       </c>
       <c r="J416" s="6" t="n">
-        <v>100.153452</v>
+        <v>100.152898</v>
       </c>
       <c r="K416" s="6" t="n">
         <v>99.421667</v>
       </c>
       <c r="L416" s="6" t="n">
-        <v>99.74726800000001</v>
+        <v>99.74702600000001</v>
       </c>
       <c r="M416" s="6" t="n">
         <v>101.04807</v>
@@ -34239,13 +34239,13 @@
         <v>100.034998</v>
       </c>
       <c r="J417" s="9" t="n">
-        <v>100.295257</v>
+        <v>100.294693</v>
       </c>
       <c r="K417" s="9" t="n">
         <v>99.45246400000001</v>
       </c>
       <c r="L417" s="9" t="n">
-        <v>99.74509500000001</v>
+        <v>99.74485</v>
       </c>
       <c r="M417" s="9" t="n">
         <v>101.14891</v>
@@ -34323,13 +34323,13 @@
         <v>100.093756</v>
       </c>
       <c r="J418" s="6" t="n">
-        <v>100.384612</v>
+        <v>100.384111</v>
       </c>
       <c r="K418" s="6" t="n">
         <v>99.476305</v>
       </c>
       <c r="L418" s="6" t="n">
-        <v>99.746015</v>
+        <v>99.745771</v>
       </c>
       <c r="M418" s="6" t="n">
         <v>101.178974</v>
@@ -34407,13 +34407,13 @@
         <v>100.116451</v>
       </c>
       <c r="J419" s="9" t="n">
-        <v>100.419364</v>
+        <v>100.419001</v>
       </c>
       <c r="K419" s="9" t="n">
         <v>99.491794</v>
       </c>
       <c r="L419" s="9" t="n">
-        <v>99.744907</v>
+        <v>99.74466200000001</v>
       </c>
       <c r="M419" s="9" t="n">
         <v>101.16376</v>
@@ -34491,13 +34491,13 @@
         <v>100.111925</v>
       </c>
       <c r="J420" s="6" t="n">
-        <v>100.412135</v>
+        <v>100.411943</v>
       </c>
       <c r="K420" s="6" t="n">
         <v>99.503511</v>
       </c>
       <c r="L420" s="6" t="n">
-        <v>99.74141400000001</v>
+        <v>99.741164</v>
       </c>
       <c r="M420" s="6" t="n">
         <v>101.090719</v>
@@ -34575,13 +34575,13 @@
         <v>100.087493</v>
       </c>
       <c r="J421" s="9" t="n">
-        <v>100.392867</v>
+        <v>100.392828</v>
       </c>
       <c r="K421" s="9" t="n">
         <v>99.518345</v>
       </c>
       <c r="L421" s="9" t="n">
-        <v>99.737787</v>
+        <v>99.737532</v>
       </c>
       <c r="M421" s="9" t="n">
         <v>100.930977</v>
@@ -34659,13 +34659,13 @@
         <v>100.066044</v>
       </c>
       <c r="J422" s="6" t="n">
-        <v>100.382709</v>
+        <v>100.382712</v>
       </c>
       <c r="K422" s="6" t="n">
         <v>99.54390600000001</v>
       </c>
       <c r="L422" s="6" t="n">
-        <v>99.737934</v>
+        <v>99.737679</v>
       </c>
       <c r="M422" s="6" t="n">
         <v>100.720557</v>
@@ -34743,13 +34743,13 @@
         <v>100.054218</v>
       </c>
       <c r="J423" s="9" t="n">
-        <v>100.374417</v>
+        <v>100.374373</v>
       </c>
       <c r="K423" s="9" t="n">
         <v>99.594386</v>
       </c>
       <c r="L423" s="9" t="n">
-        <v>99.745088</v>
+        <v>99.74484099999999</v>
       </c>
       <c r="M423" s="9" t="n">
         <v>100.494712</v>
@@ -34827,13 +34827,13 @@
         <v>100.04597</v>
       </c>
       <c r="J424" s="6" t="n">
-        <v>100.352542</v>
+        <v>100.352348</v>
       </c>
       <c r="K424" s="6" t="n">
         <v>99.665059</v>
       </c>
       <c r="L424" s="6" t="n">
-        <v>99.75875600000001</v>
+        <v>99.758526</v>
       </c>
       <c r="M424" s="6" t="n">
         <v>100.274444</v>
@@ -34911,13 +34911,13 @@
         <v>100.042782</v>
       </c>
       <c r="J425" s="9" t="n">
-        <v>100.321414</v>
+        <v>100.321112</v>
       </c>
       <c r="K425" s="9" t="n">
         <v>99.745074</v>
       </c>
       <c r="L425" s="9" t="n">
-        <v>99.777052</v>
+        <v>99.776844</v>
       </c>
       <c r="M425" s="9" t="n">
         <v>100.10637</v>
@@ -34995,13 +34995,13 @@
         <v>100.053675</v>
       </c>
       <c r="J426" s="6" t="n">
-        <v>100.296368</v>
+        <v>100.296011</v>
       </c>
       <c r="K426" s="6" t="n">
         <v>99.83024399999999</v>
       </c>
       <c r="L426" s="6" t="n">
-        <v>99.797504</v>
+        <v>99.79732</v>
       </c>
       <c r="M426" s="6" t="n">
         <v>100.020909</v>
@@ -35079,13 +35079,13 @@
         <v>100.084022</v>
       </c>
       <c r="J427" s="9" t="n">
-        <v>100.294732</v>
+        <v>100.294382</v>
       </c>
       <c r="K427" s="9" t="n">
         <v>99.90929199999999</v>
       </c>
       <c r="L427" s="9" t="n">
-        <v>99.817672</v>
+        <v>99.81751</v>
       </c>
       <c r="M427" s="9" t="n">
         <v>99.993785</v>
@@ -35163,13 +35163,13 @@
         <v>100.130533</v>
       </c>
       <c r="J428" s="6" t="n">
-        <v>100.319843</v>
+        <v>100.319524</v>
       </c>
       <c r="K428" s="6" t="n">
         <v>99.979212</v>
       </c>
       <c r="L428" s="6" t="n">
-        <v>99.83668</v>
+        <v>99.836539</v>
       </c>
       <c r="M428" s="6" t="n">
         <v>99.998238</v>
@@ -35247,13 +35247,13 @@
         <v>100.186973</v>
       </c>
       <c r="J429" s="9" t="n">
-        <v>100.382161</v>
+        <v>100.38189</v>
       </c>
       <c r="K429" s="9" t="n">
         <v>100.043758</v>
       </c>
       <c r="L429" s="9" t="n">
-        <v>99.853525</v>
+        <v>99.853403</v>
       </c>
       <c r="M429" s="9" t="n">
         <v>100.034975</v>
@@ -35331,13 +35331,13 @@
         <v>100.242303</v>
       </c>
       <c r="J430" s="6" t="n">
-        <v>100.474625</v>
+        <v>100.474424</v>
       </c>
       <c r="K430" s="6" t="n">
         <v>100.106733</v>
       </c>
       <c r="L430" s="6" t="n">
-        <v>99.87008899999999</v>
+        <v>99.869984</v>
       </c>
       <c r="M430" s="6" t="n">
         <v>100.089377</v>
@@ -35415,13 +35415,13 @@
         <v>100.304127</v>
       </c>
       <c r="J431" s="9" t="n">
-        <v>100.604878</v>
+        <v>100.604704</v>
       </c>
       <c r="K431" s="9" t="n">
         <v>100.168608</v>
       </c>
       <c r="L431" s="9" t="n">
-        <v>99.88762699999999</v>
+        <v>99.88754</v>
       </c>
       <c r="M431" s="9" t="n">
         <v>100.132016</v>
@@ -35499,13 +35499,13 @@
         <v>100.36113</v>
       </c>
       <c r="J432" s="6" t="n">
-        <v>100.75284</v>
+        <v>100.752647</v>
       </c>
       <c r="K432" s="6" t="n">
         <v>100.224451</v>
       </c>
       <c r="L432" s="6" t="n">
-        <v>99.905023</v>
+        <v>99.90495199999999</v>
       </c>
       <c r="M432" s="6" t="n">
         <v>100.163409</v>
@@ -35583,13 +35583,13 @@
         <v>100.390851</v>
       </c>
       <c r="J433" s="9" t="n">
-        <v>100.875865</v>
+        <v>100.875599</v>
       </c>
       <c r="K433" s="9" t="n">
         <v>100.263607</v>
       </c>
       <c r="L433" s="9" t="n">
-        <v>99.919095</v>
+        <v>99.91903600000001</v>
       </c>
       <c r="M433" s="9" t="n">
         <v>100.178177</v>
@@ -35667,13 +35667,13 @@
         <v>100.378024</v>
       </c>
       <c r="J434" s="6" t="n">
-        <v>100.935262</v>
+        <v>100.935011</v>
       </c>
       <c r="K434" s="6" t="n">
         <v>100.284649</v>
       </c>
       <c r="L434" s="6" t="n">
-        <v>99.926748</v>
+        <v>99.92669100000001</v>
       </c>
       <c r="M434" s="6" t="n">
         <v>100.180738</v>
@@ -35751,13 +35751,13 @@
         <v>100.30473</v>
       </c>
       <c r="J435" s="9" t="n">
-        <v>100.897003</v>
+        <v>100.896788</v>
       </c>
       <c r="K435" s="9" t="n">
         <v>100.299052</v>
       </c>
       <c r="L435" s="9" t="n">
-        <v>99.928811</v>
+        <v>99.92874999999999</v>
       </c>
       <c r="M435" s="9" t="n">
         <v>100.163692</v>
@@ -35835,13 +35835,13 @@
         <v>100.203707</v>
       </c>
       <c r="J436" s="6" t="n">
-        <v>100.802066</v>
+        <v>100.801882</v>
       </c>
       <c r="K436" s="6" t="n">
         <v>100.324722</v>
       </c>
       <c r="L436" s="6" t="n">
-        <v>99.926316</v>
+        <v>99.92624499999999</v>
       </c>
       <c r="M436" s="6" t="n">
         <v>100.129359</v>
@@ -35919,13 +35919,13 @@
         <v>100.109448</v>
       </c>
       <c r="J437" s="9" t="n">
-        <v>100.687725</v>
+        <v>100.687586</v>
       </c>
       <c r="K437" s="9" t="n">
         <v>100.371951</v>
       </c>
       <c r="L437" s="9" t="n">
-        <v>99.92084</v>
+        <v>99.920755</v>
       </c>
       <c r="M437" s="9" t="n">
         <v>100.113704</v>
@@ -36003,13 +36003,13 @@
         <v>100.033732</v>
       </c>
       <c r="J438" s="6" t="n">
-        <v>100.564657</v>
+        <v>100.564559</v>
       </c>
       <c r="K438" s="6" t="n">
         <v>100.437756</v>
       </c>
       <c r="L438" s="6" t="n">
-        <v>99.91552799999999</v>
+        <v>99.915426</v>
       </c>
       <c r="M438" s="6" t="n">
         <v>100.06032</v>
@@ -36087,13 +36087,13 @@
         <v>99.97796099999999</v>
       </c>
       <c r="J439" s="9" t="n">
-        <v>100.439752</v>
+        <v>100.439677</v>
       </c>
       <c r="K439" s="9" t="n">
         <v>100.509896</v>
       </c>
       <c r="L439" s="9" t="n">
-        <v>99.912856</v>
+        <v>99.912741</v>
       </c>
       <c r="M439" s="9" t="n">
         <v>99.990819</v>
@@ -36171,13 +36171,13 @@
         <v>99.93913499999999</v>
       </c>
       <c r="J440" s="6" t="n">
-        <v>100.32016</v>
+        <v>100.320142</v>
       </c>
       <c r="K440" s="6" t="n">
         <v>100.590999</v>
       </c>
       <c r="L440" s="6" t="n">
-        <v>99.91734099999999</v>
+        <v>99.917221</v>
       </c>
       <c r="M440" s="6" t="n">
         <v>99.914817</v>
@@ -36255,13 +36255,13 @@
         <v>99.928348</v>
       </c>
       <c r="J441" s="9" t="n">
-        <v>100.224722</v>
+        <v>100.224769</v>
       </c>
       <c r="K441" s="9" t="n">
         <v>100.682113</v>
       </c>
       <c r="L441" s="9" t="n">
-        <v>99.934405</v>
+        <v>99.93429500000001</v>
       </c>
       <c r="M441" s="9" t="n">
         <v>99.84768099999999</v>
@@ -36339,13 +36339,13 @@
         <v>99.949658</v>
       </c>
       <c r="J442" s="6" t="n">
-        <v>100.162078</v>
+        <v>100.162153</v>
       </c>
       <c r="K442" s="6" t="n">
         <v>100.781951</v>
       </c>
       <c r="L442" s="6" t="n">
-        <v>99.963785</v>
+        <v>99.96369900000001</v>
       </c>
       <c r="M442" s="6" t="n">
         <v>99.804922</v>
@@ -36423,13 +36423,13 @@
         <v>99.998912</v>
       </c>
       <c r="J443" s="9" t="n">
-        <v>100.133649</v>
+        <v>100.133762</v>
       </c>
       <c r="K443" s="9" t="n">
         <v>100.88436</v>
       </c>
       <c r="L443" s="9" t="n">
-        <v>100.002612</v>
+        <v>100.002561</v>
       </c>
       <c r="M443" s="9" t="n">
         <v>99.761669</v>
@@ -36507,13 +36507,13 @@
         <v>100.070386</v>
       </c>
       <c r="J444" s="6" t="n">
-        <v>100.14632</v>
+        <v>100.1465</v>
       </c>
       <c r="K444" s="6" t="n">
         <v>100.974757</v>
       </c>
       <c r="L444" s="6" t="n">
-        <v>100.046572</v>
+        <v>100.046562</v>
       </c>
       <c r="M444" s="6" t="n">
         <v>99.724226</v>
@@ -36591,13 +36591,13 @@
         <v>100.163886</v>
       </c>
       <c r="J445" s="9" t="n">
-        <v>100.202135</v>
+        <v>100.202335</v>
       </c>
       <c r="K445" s="9" t="n">
         <v>101.049884</v>
       </c>
       <c r="L445" s="9" t="n">
-        <v>100.093063</v>
+        <v>100.093098</v>
       </c>
       <c r="M445" s="9" t="n">
         <v>99.692379</v>
@@ -36675,13 +36675,13 @@
         <v>100.270771</v>
       </c>
       <c r="J446" s="6" t="n">
-        <v>100.296429</v>
+        <v>100.296623</v>
       </c>
       <c r="K446" s="6" t="n">
         <v>101.096947</v>
       </c>
       <c r="L446" s="6" t="n">
-        <v>100.13986</v>
+        <v>100.139941</v>
       </c>
       <c r="M446" s="6" t="n">
         <v>99.631556</v>
@@ -36759,13 +36759,13 @@
         <v>100.374695</v>
       </c>
       <c r="J447" s="9" t="n">
-        <v>100.416139</v>
+        <v>100.416303</v>
       </c>
       <c r="K447" s="9" t="n">
         <v>101.101778</v>
       </c>
       <c r="L447" s="9" t="n">
-        <v>100.183591</v>
+        <v>100.183714</v>
       </c>
       <c r="M447" s="9" t="n">
         <v>99.48962</v>
@@ -36843,13 +36843,13 @@
         <v>100.46336</v>
       </c>
       <c r="J448" s="6" t="n">
-        <v>100.545152</v>
+        <v>100.545392</v>
       </c>
       <c r="K448" s="6" t="n">
         <v>101.053499</v>
       </c>
       <c r="L448" s="6" t="n">
-        <v>100.222783</v>
+        <v>100.222943</v>
       </c>
       <c r="M448" s="6" t="n">
         <v>99.30301799999999</v>
@@ -36927,13 +36927,13 @@
         <v>100.526073</v>
       </c>
       <c r="J449" s="9" t="n">
-        <v>100.652855</v>
+        <v>100.653184</v>
       </c>
       <c r="K449" s="9" t="n">
         <v>100.960346</v>
       </c>
       <c r="L449" s="9" t="n">
-        <v>100.258677</v>
+        <v>100.258868</v>
       </c>
       <c r="M449" s="9" t="n">
         <v>99.083732</v>
@@ -37011,13 +37011,13 @@
         <v>100.552497</v>
       </c>
       <c r="J450" s="6" t="n">
-        <v>100.726413</v>
+        <v>100.726824</v>
       </c>
       <c r="K450" s="6" t="n">
         <v>100.835273</v>
       </c>
       <c r="L450" s="6" t="n">
-        <v>100.293792</v>
+        <v>100.294011</v>
       </c>
       <c r="M450" s="6" t="n">
         <v>98.850228</v>
@@ -37095,13 +37095,13 @@
         <v>100.542199</v>
       </c>
       <c r="J451" s="9" t="n">
-        <v>100.750799</v>
+        <v>100.751273</v>
       </c>
       <c r="K451" s="9" t="n">
         <v>100.702366</v>
       </c>
       <c r="L451" s="9" t="n">
-        <v>100.332558</v>
+        <v>100.332805</v>
       </c>
       <c r="M451" s="9" t="n">
         <v>98.665977</v>
@@ -37179,13 +37179,13 @@
         <v>100.509739</v>
       </c>
       <c r="J452" s="6" t="n">
-        <v>100.729223</v>
+        <v>100.729694</v>
       </c>
       <c r="K452" s="6" t="n">
         <v>100.575012</v>
       </c>
       <c r="L452" s="6" t="n">
-        <v>100.378673</v>
+        <v>100.378956</v>
       </c>
       <c r="M452" s="6" t="n">
         <v>98.577077</v>
@@ -37263,13 +37263,13 @@
         <v>100.462826</v>
       </c>
       <c r="J453" s="9" t="n">
-        <v>100.664028</v>
+        <v>100.664404</v>
       </c>
       <c r="K453" s="9" t="n">
         <v>100.46638</v>
       </c>
       <c r="L453" s="9" t="n">
-        <v>100.429921</v>
+        <v>100.430245</v>
       </c>
       <c r="M453" s="9" t="n">
         <v>98.547087</v>
@@ -37347,13 +37347,13 @@
         <v>100.413059</v>
       </c>
       <c r="J454" s="6" t="n">
-        <v>100.583629</v>
+        <v>100.583946</v>
       </c>
       <c r="K454" s="6" t="n">
         <v>100.373394</v>
       </c>
       <c r="L454" s="6" t="n">
-        <v>100.483996</v>
+        <v>100.484362</v>
       </c>
       <c r="M454" s="6" t="n">
         <v>98.552368</v>
@@ -37431,13 +37431,13 @@
         <v>100.374678</v>
       </c>
       <c r="J455" s="9" t="n">
-        <v>100.5061</v>
+        <v>100.506393</v>
       </c>
       <c r="K455" s="9" t="n">
         <v>100.295519</v>
       </c>
       <c r="L455" s="9" t="n">
-        <v>100.540134</v>
+        <v>100.540542</v>
       </c>
       <c r="M455" s="9" t="n">
         <v>98.59612799999999</v>
@@ -37515,13 +37515,13 @@
         <v>100.356267</v>
       </c>
       <c r="J456" s="6" t="n">
-        <v>100.446362</v>
+        <v>100.446615</v>
       </c>
       <c r="K456" s="6" t="n">
         <v>100.233488</v>
       </c>
       <c r="L456" s="6" t="n">
-        <v>100.593187</v>
+        <v>100.593631</v>
       </c>
       <c r="M456" s="6" t="n">
         <v>98.677052</v>
@@ -37599,13 +37599,13 @@
         <v>100.379632</v>
       </c>
       <c r="J457" s="9" t="n">
-        <v>100.424528</v>
+        <v>100.42486</v>
       </c>
       <c r="K457" s="9" t="n">
         <v>100.181716</v>
       </c>
       <c r="L457" s="9" t="n">
-        <v>100.639926</v>
+        <v>100.640401</v>
       </c>
       <c r="M457" s="9" t="n">
         <v>98.769868</v>
@@ -37683,13 +37683,13 @@
         <v>100.443537</v>
       </c>
       <c r="J458" s="6" t="n">
-        <v>100.441202</v>
+        <v>100.441656</v>
       </c>
       <c r="K458" s="6" t="n">
         <v>100.141308</v>
       </c>
       <c r="L458" s="6" t="n">
-        <v>100.680515</v>
+        <v>100.681016</v>
       </c>
       <c r="M458" s="6" t="n">
         <v>98.843898</v>
@@ -37767,13 +37767,13 @@
         <v>100.559666</v>
       </c>
       <c r="J459" s="9" t="n">
-        <v>100.501744</v>
+        <v>100.502298</v>
       </c>
       <c r="K459" s="9" t="n">
         <v>100.113959</v>
       </c>
       <c r="L459" s="9" t="n">
-        <v>100.717894</v>
+        <v>100.718419</v>
       </c>
       <c r="M459" s="9" t="n">
         <v>98.871287</v>
@@ -37851,13 +37851,13 @@
         <v>100.698017</v>
       </c>
       <c r="J460" s="6" t="n">
-        <v>100.579009</v>
+        <v>100.579637</v>
       </c>
       <c r="K460" s="6" t="n">
         <v>100.098971</v>
       </c>
       <c r="L460" s="6" t="n">
-        <v>100.756268</v>
+        <v>100.756817</v>
       </c>
       <c r="M460" s="6" t="n">
         <v>98.85954099999999</v>
@@ -37935,13 +37935,13 @@
         <v>100.827213</v>
       </c>
       <c r="J461" s="9" t="n">
-        <v>100.65092</v>
+        <v>100.651651</v>
       </c>
       <c r="K461" s="9" t="n">
         <v>100.096317</v>
       </c>
       <c r="L461" s="9" t="n">
-        <v>100.799292</v>
+        <v>100.799872</v>
       </c>
       <c r="M461" s="9" t="n">
         <v>98.831816</v>
@@ -38019,13 +38019,13 @@
         <v>100.929826</v>
       </c>
       <c r="J462" s="6" t="n">
-        <v>100.701616</v>
+        <v>100.702414</v>
       </c>
       <c r="K462" s="6" t="n">
         <v>100.094047</v>
       </c>
       <c r="L462" s="6" t="n">
-        <v>100.848305</v>
+        <v>100.848921</v>
       </c>
       <c r="M462" s="6" t="n">
         <v>98.809579</v>
@@ -38103,13 +38103,13 @@
         <v>101.01473</v>
       </c>
       <c r="J463" s="9" t="n">
-        <v>100.743151</v>
+        <v>100.74405</v>
       </c>
       <c r="K463" s="9" t="n">
         <v>100.090066</v>
       </c>
       <c r="L463" s="9" t="n">
-        <v>100.903266</v>
+        <v>100.903918</v>
       </c>
       <c r="M463" s="9" t="n">
         <v>98.78988</v>
@@ -38187,13 +38187,13 @@
         <v>101.079754</v>
       </c>
       <c r="J464" s="6" t="n">
-        <v>100.779422</v>
+        <v>100.780445</v>
       </c>
       <c r="K464" s="6" t="n">
         <v>100.0879</v>
       </c>
       <c r="L464" s="6" t="n">
-        <v>100.960851</v>
+        <v>100.961544</v>
       </c>
       <c r="M464" s="6" t="n">
         <v>98.770734</v>
@@ -38271,13 +38271,13 @@
         <v>101.122948</v>
       </c>
       <c r="J465" s="9" t="n">
-        <v>100.819922</v>
+        <v>100.821121</v>
       </c>
       <c r="K465" s="9" t="n">
         <v>100.082807</v>
       </c>
       <c r="L465" s="9" t="n">
-        <v>101.017018</v>
+        <v>101.017753</v>
       </c>
       <c r="M465" s="9" t="n">
         <v>98.742182</v>
@@ -38355,13 +38355,13 @@
         <v>101.16205</v>
       </c>
       <c r="J466" s="6" t="n">
-        <v>100.880134</v>
+        <v>100.881561</v>
       </c>
       <c r="K466" s="6" t="n">
         <v>100.084532</v>
       </c>
       <c r="L466" s="6" t="n">
-        <v>101.068626</v>
+        <v>101.06939</v>
       </c>
       <c r="M466" s="6" t="n">
         <v>98.69288899999999</v>
@@ -38439,13 +38439,13 @@
         <v>101.193735</v>
       </c>
       <c r="J467" s="9" t="n">
-        <v>100.929644</v>
+        <v>100.931266</v>
       </c>
       <c r="K467" s="9" t="n">
         <v>100.094683</v>
       </c>
       <c r="L467" s="9" t="n">
-        <v>101.113769</v>
+        <v>101.114533</v>
       </c>
       <c r="M467" s="9" t="n">
         <v>98.65801999999999</v>
@@ -38523,13 +38523,13 @@
         <v>101.218068</v>
       </c>
       <c r="J468" s="6" t="n">
-        <v>100.951699</v>
+        <v>100.953381</v>
       </c>
       <c r="K468" s="6" t="n">
         <v>100.11191</v>
       </c>
       <c r="L468" s="6" t="n">
-        <v>101.152758</v>
+        <v>101.153505</v>
       </c>
       <c r="M468" s="6" t="n">
         <v>98.626366</v>
@@ -38607,13 +38607,13 @@
         <v>101.224545</v>
       </c>
       <c r="J469" s="9" t="n">
-        <v>100.934167</v>
+        <v>100.935749</v>
       </c>
       <c r="K469" s="9" t="n">
         <v>100.137896</v>
       </c>
       <c r="L469" s="9" t="n">
-        <v>101.183695</v>
+        <v>101.184419</v>
       </c>
       <c r="M469" s="9" t="n">
         <v>98.617047</v>
@@ -38691,13 +38691,13 @@
         <v>101.202244</v>
       </c>
       <c r="J470" s="6" t="n">
-        <v>100.881029</v>
+        <v>100.882407</v>
       </c>
       <c r="K470" s="6" t="n">
         <v>100.174839</v>
       </c>
       <c r="L470" s="6" t="n">
-        <v>101.203493</v>
+        <v>101.204191</v>
       </c>
       <c r="M470" s="6" t="n">
         <v>98.63023800000001</v>
@@ -38775,13 +38775,13 @@
         <v>101.14791</v>
       </c>
       <c r="J471" s="9" t="n">
-        <v>100.78398</v>
+        <v>100.785227</v>
       </c>
       <c r="K471" s="9" t="n">
         <v>100.215595</v>
       </c>
       <c r="L471" s="9" t="n">
-        <v>101.210982</v>
+        <v>101.21165</v>
       </c>
       <c r="M471" s="9" t="n">
         <v>98.702747</v>
@@ -38859,13 +38859,13 @@
         <v>101.070004</v>
       </c>
       <c r="J472" s="6" t="n">
-        <v>100.668397</v>
+        <v>100.669595</v>
       </c>
       <c r="K472" s="6" t="n">
         <v>100.245998</v>
       </c>
       <c r="L472" s="6" t="n">
-        <v>101.20839</v>
+        <v>101.209028</v>
       </c>
       <c r="M472" s="6" t="n">
         <v>98.84331899999999</v>
@@ -38943,13 +38943,13 @@
         <v>100.986413</v>
       </c>
       <c r="J473" s="9" t="n">
-        <v>100.567977</v>
+        <v>100.569196</v>
       </c>
       <c r="K473" s="9" t="n">
         <v>100.263556</v>
       </c>
       <c r="L473" s="9" t="n">
-        <v>101.200657</v>
+        <v>101.201261</v>
       </c>
       <c r="M473" s="9" t="n">
         <v>99.007141</v>
@@ -39027,13 +39027,13 @@
         <v>100.90861</v>
       </c>
       <c r="J474" s="6" t="n">
-        <v>100.497751</v>
+        <v>100.499193</v>
       </c>
       <c r="K474" s="6" t="n">
         <v>100.276566</v>
       </c>
       <c r="L474" s="6" t="n">
-        <v>101.194131</v>
+        <v>101.194706</v>
       </c>
       <c r="M474" s="6" t="n">
         <v>99.11803500000001</v>
@@ -39111,13 +39111,13 @@
         <v>100.830767</v>
       </c>
       <c r="J475" s="9" t="n">
-        <v>100.45314</v>
+        <v>100.45492</v>
       </c>
       <c r="K475" s="9" t="n">
         <v>100.283273</v>
       </c>
       <c r="L475" s="9" t="n">
-        <v>101.19272</v>
+        <v>101.193266</v>
       </c>
       <c r="M475" s="9" t="n">
         <v>99.19526399999999</v>
@@ -39195,13 +39195,13 @@
         <v>100.75335</v>
       </c>
       <c r="J476" s="6" t="n">
-        <v>100.422245</v>
+        <v>100.424351</v>
       </c>
       <c r="K476" s="6" t="n">
         <v>100.281673</v>
       </c>
       <c r="L476" s="6" t="n">
-        <v>101.198031</v>
+        <v>101.198558</v>
       </c>
       <c r="M476" s="6" t="n">
         <v>99.239897</v>
@@ -39279,13 +39279,13 @@
         <v>100.697059</v>
       </c>
       <c r="J477" s="9" t="n">
-        <v>100.408371</v>
+        <v>100.410702</v>
       </c>
       <c r="K477" s="9" t="n">
         <v>100.281377</v>
       </c>
       <c r="L477" s="9" t="n">
-        <v>101.209262</v>
+        <v>101.209779</v>
       </c>
       <c r="M477" s="9" t="n">
         <v>99.25556899999999</v>
@@ -39363,13 +39363,13 @@
         <v>100.661816</v>
       </c>
       <c r="J478" s="6" t="n">
-        <v>100.388246</v>
+        <v>100.390693</v>
       </c>
       <c r="K478" s="6" t="n">
         <v>100.284323</v>
       </c>
       <c r="L478" s="6" t="n">
-        <v>101.222569</v>
+        <v>101.223059</v>
       </c>
       <c r="M478" s="6" t="n">
         <v>99.261787</v>
@@ -39447,13 +39447,13 @@
         <v>100.646907</v>
       </c>
       <c r="J479" s="9" t="n">
-        <v>100.351666</v>
+        <v>100.354062</v>
       </c>
       <c r="K479" s="9" t="n">
         <v>100.286714</v>
       </c>
       <c r="L479" s="9" t="n">
-        <v>101.233733</v>
+        <v>101.234141</v>
       </c>
       <c r="M479" s="9" t="n">
         <v>99.242632</v>
@@ -39531,13 +39531,13 @@
         <v>100.635819</v>
       </c>
       <c r="J480" s="6" t="n">
-        <v>100.270376</v>
+        <v>100.272682</v>
       </c>
       <c r="K480" s="6" t="n">
         <v>100.279551</v>
       </c>
       <c r="L480" s="6" t="n">
-        <v>101.237004</v>
+        <v>101.237288</v>
       </c>
       <c r="M480" s="6" t="n">
         <v>99.21308999999999</v>
@@ -39615,13 +39615,13 @@
         <v>100.616084</v>
       </c>
       <c r="J481" s="9" t="n">
-        <v>100.138318</v>
+        <v>100.140509</v>
       </c>
       <c r="K481" s="9" t="n">
         <v>100.25724</v>
       </c>
       <c r="L481" s="9" t="n">
-        <v>101.22696</v>
+        <v>101.2271</v>
       </c>
       <c r="M481" s="9" t="n">
         <v>99.189075</v>
@@ -39699,13 +39699,13 @@
         <v>100.570925</v>
       </c>
       <c r="J482" s="6" t="n">
-        <v>99.956729</v>
+        <v>99.95886</v>
       </c>
       <c r="K482" s="6" t="n">
         <v>100.212354</v>
       </c>
       <c r="L482" s="6" t="n">
-        <v>101.196122</v>
+        <v>101.196117</v>
       </c>
       <c r="M482" s="6" t="n">
         <v>99.194183</v>
@@ -39783,13 +39783,13 @@
         <v>100.483885</v>
       </c>
       <c r="J483" s="9" t="n">
-        <v>99.738558</v>
+        <v>99.740737</v>
       </c>
       <c r="K483" s="9" t="n">
         <v>100.144186</v>
       </c>
       <c r="L483" s="9" t="n">
-        <v>101.130806</v>
+        <v>101.130652</v>
       </c>
       <c r="M483" s="9" t="n">
         <v>99.23823299999999</v>
@@ -39867,13 +39867,13 @@
         <v>100.357631</v>
       </c>
       <c r="J484" s="6" t="n">
-        <v>99.519688</v>
+        <v>99.521987</v>
       </c>
       <c r="K484" s="6" t="n">
         <v>100.045353</v>
       </c>
       <c r="L484" s="6" t="n">
-        <v>101.012468</v>
+        <v>101.01215</v>
       </c>
       <c r="M484" s="6" t="n">
         <v>99.324172</v>
@@ -39951,13 +39951,13 @@
         <v>100.18014</v>
       </c>
       <c r="J485" s="9" t="n">
-        <v>99.300033</v>
+        <v>99.30245600000001</v>
       </c>
       <c r="K485" s="9" t="n">
         <v>99.895624</v>
       </c>
       <c r="L485" s="9" t="n">
-        <v>100.819419</v>
+        <v>100.818869</v>
       </c>
       <c r="M485" s="9" t="n">
         <v>99.48212100000001</v>
@@ -40035,13 +40035,13 @@
         <v>99.940834</v>
       </c>
       <c r="J486" s="6" t="n">
-        <v>99.07543200000001</v>
+        <v>99.077945</v>
       </c>
       <c r="K486" s="6" t="n">
         <v>99.68113099999999</v>
       </c>
       <c r="L486" s="6" t="n">
-        <v>100.531006</v>
+        <v>100.530118</v>
       </c>
       <c r="M486" s="6" t="n">
         <v>99.777096</v>
@@ -40119,13 +40119,13 @@
         <v>99.63569099999999</v>
       </c>
       <c r="J487" s="9" t="n">
-        <v>98.826033</v>
+        <v>98.828571</v>
       </c>
       <c r="K487" s="9" t="n">
         <v>99.414175</v>
       </c>
       <c r="L487" s="9" t="n">
-        <v>100.137542</v>
+        <v>100.13616</v>
       </c>
       <c r="M487" s="9" t="n">
         <v>100.2103</v>
@@ -40203,13 +40203,13 @@
         <v>99.315038</v>
       </c>
       <c r="J488" s="6" t="n">
-        <v>98.57625899999999</v>
+        <v>98.578856</v>
       </c>
       <c r="K488" s="6" t="n">
         <v>99.12830700000001</v>
       </c>
       <c r="L488" s="6" t="n">
-        <v>99.658266</v>
+        <v>99.656261</v>
       </c>
       <c r="M488" s="6" t="n">
         <v>100.762096</v>
@@ -40287,13 +40287,13 @@
         <v>87.07612399999999</v>
       </c>
       <c r="J489" s="9" t="n">
-        <v>85.51202499999999</v>
+        <v>85.513008</v>
       </c>
       <c r="K489" s="9" t="n">
         <v>92.07571900000001</v>
       </c>
       <c r="L489" s="9" t="n">
-        <v>99.136893</v>
+        <v>99.134218</v>
       </c>
       <c r="M489" s="9" t="n">
         <v>101.436864</v>
@@ -40371,13 +40371,13 @@
         <v>86.054305</v>
       </c>
       <c r="J490" s="6" t="n">
-        <v>85.468962</v>
+        <v>85.472877</v>
       </c>
       <c r="K490" s="6" t="n">
         <v>92.07337</v>
       </c>
       <c r="L490" s="6" t="n">
-        <v>98.631197</v>
+        <v>98.627835</v>
       </c>
       <c r="M490" s="6" t="n">
         <v>102.118757</v>
@@ -40455,13 +40455,13 @@
         <v>92.067036</v>
       </c>
       <c r="J491" s="9" t="n">
-        <v>93.293133</v>
+        <v>93.296547</v>
       </c>
       <c r="K491" s="9" t="n">
         <v>94.523594</v>
       </c>
       <c r="L491" s="9" t="n">
-        <v>98.202202</v>
+        <v>98.198143</v>
       </c>
       <c r="M491" s="9" t="n">
         <v>102.713129</v>
@@ -40539,13 +40539,13 @@
         <v>93.726494</v>
       </c>
       <c r="J492" s="6" t="n">
-        <v>94.067013</v>
+        <v>94.06985899999999</v>
       </c>
       <c r="K492" s="6" t="n">
         <v>95.701256</v>
       </c>
       <c r="L492" s="6" t="n">
-        <v>97.880655</v>
+        <v>97.875964</v>
       </c>
       <c r="M492" s="6" t="n">
         <v>103.122046</v>
@@ -40623,13 +40623,13 @@
         <v>94.88717800000001</v>
       </c>
       <c r="J493" s="9" t="n">
-        <v>95.35747499999999</v>
+        <v>95.36012599999999</v>
       </c>
       <c r="K493" s="9" t="n">
         <v>96.283112</v>
       </c>
       <c r="L493" s="9" t="n">
-        <v>97.664091</v>
+        <v>97.658879</v>
       </c>
       <c r="M493" s="9" t="n">
         <v>103.334912</v>
@@ -40707,13 +40707,13 @@
         <v>96.065577</v>
       </c>
       <c r="J494" s="6" t="n">
-        <v>96.56940299999999</v>
+        <v>96.57197499999999</v>
       </c>
       <c r="K494" s="6" t="n">
         <v>96.895595</v>
       </c>
       <c r="L494" s="6" t="n">
-        <v>97.53728</v>
+        <v>97.531682</v>
       </c>
       <c r="M494" s="6" t="n">
         <v>103.386234</v>
@@ -40791,13 +40791,13 @@
         <v>97.067708</v>
       </c>
       <c r="J495" s="9" t="n">
-        <v>97.52677799999999</v>
+        <v>97.529372</v>
       </c>
       <c r="K495" s="9" t="n">
         <v>97.45904400000001</v>
       </c>
       <c r="L495" s="9" t="n">
-        <v>97.483351</v>
+        <v>97.47754500000001</v>
       </c>
       <c r="M495" s="9" t="n">
         <v>103.327991</v>
@@ -40875,13 +40875,13 @@
         <v>97.813734</v>
       </c>
       <c r="J496" s="6" t="n">
-        <v>98.166375</v>
+        <v>98.169107</v>
       </c>
       <c r="K496" s="6" t="n">
         <v>97.962907</v>
       </c>
       <c r="L496" s="6" t="n">
-        <v>97.483677</v>
+        <v>97.47793</v>
       </c>
       <c r="M496" s="6" t="n">
         <v>103.218996</v>
@@ -40959,13 +40959,13 @@
         <v>98.30518499999999</v>
       </c>
       <c r="J497" s="9" t="n">
-        <v>98.513998</v>
+        <v>98.517003</v>
       </c>
       <c r="K497" s="9" t="n">
         <v>98.408996</v>
       </c>
       <c r="L497" s="9" t="n">
-        <v>97.52389599999999</v>
+        <v>97.518314</v>
       </c>
       <c r="M497" s="9" t="n">
         <v>103.104657</v>
@@ -41043,13 +41043,13 @@
         <v>98.599205</v>
       </c>
       <c r="J498" s="6" t="n">
-        <v>98.651777</v>
+        <v>98.655096</v>
       </c>
       <c r="K498" s="6" t="n">
         <v>98.81255</v>
       </c>
       <c r="L498" s="6" t="n">
-        <v>97.59943199999999</v>
+        <v>97.594053</v>
       </c>
       <c r="M498" s="6" t="n">
         <v>103.019589</v>
@@ -41127,13 +41127,13 @@
         <v>98.760508</v>
       </c>
       <c r="J499" s="9" t="n">
-        <v>98.675409</v>
+        <v>98.678971</v>
       </c>
       <c r="K499" s="9" t="n">
         <v>99.167191</v>
       </c>
       <c r="L499" s="9" t="n">
-        <v>97.720494</v>
+        <v>97.71531299999999</v>
       </c>
       <c r="M499" s="9" t="n">
         <v>102.905384</v>
@@ -41211,13 +41211,13 @@
         <v>98.84008799999999</v>
       </c>
       <c r="J500" s="6" t="n">
-        <v>98.65540799999999</v>
+        <v>98.65911800000001</v>
       </c>
       <c r="K500" s="6" t="n">
         <v>99.448131</v>
       </c>
       <c r="L500" s="6" t="n">
-        <v>97.90008</v>
+        <v>97.89507999999999</v>
       </c>
       <c r="M500" s="6" t="n">
         <v>102.770952</v>
@@ -41295,13 +41295,13 @@
         <v>98.83710000000001</v>
       </c>
       <c r="J501" s="9" t="n">
-        <v>98.597115</v>
+        <v>98.60088500000001</v>
       </c>
       <c r="K501" s="9" t="n">
         <v>99.628309</v>
       </c>
       <c r="L501" s="9" t="n">
-        <v>98.143474</v>
+        <v>98.13861900000001</v>
       </c>
       <c r="M501" s="9" t="n">
         <v>102.608069</v>
@@ -41379,13 +41379,13 @@
         <v>98.767016</v>
       </c>
       <c r="J502" s="6" t="n">
-        <v>98.519902</v>
+        <v>98.523594</v>
       </c>
       <c r="K502" s="6" t="n">
         <v>99.729484</v>
       </c>
       <c r="L502" s="6" t="n">
-        <v>98.44132999999999</v>
+        <v>98.436666</v>
       </c>
       <c r="M502" s="6" t="n">
         <v>102.41672</v>
@@ -41463,13 +41463,13 @@
         <v>98.651916</v>
       </c>
       <c r="J503" s="9" t="n">
-        <v>98.453154</v>
+        <v>98.456734</v>
       </c>
       <c r="K503" s="9" t="n">
         <v>99.777843</v>
       </c>
       <c r="L503" s="9" t="n">
-        <v>98.755976</v>
+        <v>98.751597</v>
       </c>
       <c r="M503" s="9" t="n">
         <v>102.245137</v>
@@ -41547,13 +41547,13 @@
         <v>98.52353100000001</v>
       </c>
       <c r="J504" s="6" t="n">
-        <v>98.42110700000001</v>
+        <v>98.424458</v>
       </c>
       <c r="K504" s="6" t="n">
         <v>99.804259</v>
       </c>
       <c r="L504" s="6" t="n">
-        <v>99.048254</v>
+        <v>99.04414800000001</v>
       </c>
       <c r="M504" s="6" t="n">
         <v>102.107648</v>
@@ -41631,13 +41631,13 @@
         <v>98.42260400000001</v>
       </c>
       <c r="J505" s="9" t="n">
-        <v>98.43960199999999</v>
+        <v>98.44262999999999</v>
       </c>
       <c r="K505" s="9" t="n">
         <v>99.82990100000001</v>
       </c>
       <c r="L505" s="9" t="n">
-        <v>99.291479</v>
+        <v>99.28756799999999</v>
       </c>
       <c r="M505" s="9" t="n">
         <v>101.984296</v>
@@ -41715,13 +41715,13 @@
         <v>98.391453</v>
       </c>
       <c r="J506" s="6" t="n">
-        <v>98.52393600000001</v>
+        <v>98.526662</v>
       </c>
       <c r="K506" s="6" t="n">
         <v>99.86350899999999</v>
       </c>
       <c r="L506" s="6" t="n">
-        <v>99.479175</v>
+        <v>99.475399</v>
       </c>
       <c r="M506" s="6" t="n">
         <v>101.864353</v>
@@ -41799,13 +41799,13 @@
         <v>98.44952600000001</v>
       </c>
       <c r="J507" s="9" t="n">
-        <v>98.698481</v>
+        <v>98.70104600000001</v>
       </c>
       <c r="K507" s="9" t="n">
         <v>99.90914100000001</v>
       </c>
       <c r="L507" s="9" t="n">
-        <v>99.618077</v>
+        <v>99.61449399999999</v>
       </c>
       <c r="M507" s="9" t="n">
         <v>101.741478</v>
@@ -41883,13 +41883,13 @@
         <v>98.583315</v>
       </c>
       <c r="J508" s="6" t="n">
-        <v>98.950447</v>
+        <v>98.952949</v>
       </c>
       <c r="K508" s="6" t="n">
         <v>99.97229299999999</v>
       </c>
       <c r="L508" s="6" t="n">
-        <v>99.721377</v>
+        <v>99.718289</v>
       </c>
       <c r="M508" s="6" t="n">
         <v>101.619014</v>
@@ -41967,13 +41967,13 @@
         <v>98.766127</v>
       </c>
       <c r="J509" s="9" t="n">
-        <v>99.252224</v>
+        <v>99.254807</v>
       </c>
       <c r="K509" s="9" t="n">
         <v>100.057797</v>
       </c>
       <c r="L509" s="9" t="n">
-        <v>99.800225</v>
+        <v>99.797732</v>
       </c>
       <c r="M509" s="9" t="n">
         <v>101.494387</v>
@@ -42051,13 +42051,13 @@
         <v>98.970637</v>
       </c>
       <c r="J510" s="6" t="n">
-        <v>99.559568</v>
+        <v>99.56235700000001</v>
       </c>
       <c r="K510" s="6" t="n">
         <v>100.173111</v>
       </c>
       <c r="L510" s="6" t="n">
-        <v>99.862622</v>
+        <v>99.860732</v>
       </c>
       <c r="M510" s="6" t="n">
         <v>101.341838</v>
@@ -42135,13 +42135,13 @@
         <v>99.172735</v>
       </c>
       <c r="J511" s="9" t="n">
-        <v>99.832224</v>
+        <v>99.83539399999999</v>
       </c>
       <c r="K511" s="9" t="n">
         <v>100.325036</v>
       </c>
       <c r="L511" s="9" t="n">
-        <v>99.912885</v>
+        <v>99.91152700000001</v>
       </c>
       <c r="M511" s="9" t="n">
         <v>101.131597</v>
@@ -42219,13 +42219,13 @@
         <v>99.35871899999999</v>
       </c>
       <c r="J512" s="6" t="n">
-        <v>100.054727</v>
+        <v>100.058233</v>
       </c>
       <c r="K512" s="6" t="n">
         <v>100.483331</v>
       </c>
       <c r="L512" s="6" t="n">
-        <v>99.95371900000001</v>
+        <v>99.952749</v>
       </c>
       <c r="M512" s="6" t="n">
         <v>100.838256</v>
@@ -42303,13 +42303,13 @@
         <v>99.514899</v>
       </c>
       <c r="J513" s="9" t="n">
-        <v>100.212389</v>
+        <v>100.216011</v>
       </c>
       <c r="K513" s="9" t="n">
         <v>100.612968</v>
       </c>
       <c r="L513" s="9" t="n">
-        <v>99.989208</v>
+        <v>99.988383</v>
       </c>
       <c r="M513" s="9" t="n">
         <v>100.547023</v>
@@ -42387,13 +42387,13 @@
         <v>99.636751</v>
       </c>
       <c r="J514" s="6" t="n">
-        <v>100.306984</v>
+        <v>100.310393</v>
       </c>
       <c r="K514" s="6" t="n">
         <v>100.717916</v>
       </c>
       <c r="L514" s="6" t="n">
-        <v>100.02222</v>
+        <v>100.021356</v>
       </c>
       <c r="M514" s="6" t="n">
         <v>100.317165</v>
@@ -42471,13 +42471,13 @@
         <v>99.739271</v>
       </c>
       <c r="J515" s="9" t="n">
-        <v>100.364155</v>
+        <v>100.367013</v>
       </c>
       <c r="K515" s="9" t="n">
         <v>100.797138</v>
       </c>
       <c r="L515" s="9" t="n">
-        <v>100.057293</v>
+        <v>100.056195</v>
       </c>
       <c r="M515" s="9" t="n">
         <v>100.145127</v>
@@ -42555,13 +42555,13 @@
         <v>99.84506399999999</v>
       </c>
       <c r="J516" s="6" t="n">
-        <v>100.416245</v>
+        <v>100.418301</v>
       </c>
       <c r="K516" s="6" t="n">
         <v>100.855715</v>
       </c>
       <c r="L516" s="6" t="n">
-        <v>100.095591</v>
+        <v>100.094198</v>
       </c>
       <c r="M516" s="6" t="n">
         <v>100.014042</v>
@@ -42639,13 +42639,13 @@
         <v>99.95968999999999</v>
       </c>
       <c r="J517" s="9" t="n">
-        <v>100.475021</v>
+        <v>100.476073</v>
       </c>
       <c r="K517" s="9" t="n">
         <v>100.899606</v>
       </c>
       <c r="L517" s="9" t="n">
-        <v>100.136804</v>
+        <v>100.135134</v>
       </c>
       <c r="M517" s="9" t="n">
         <v>99.919135</v>
@@ -42723,13 +42723,13 @@
         <v>100.081</v>
       </c>
       <c r="J518" s="6" t="n">
-        <v>100.549796</v>
+        <v>100.549889</v>
       </c>
       <c r="K518" s="6" t="n">
         <v>100.923189</v>
       </c>
       <c r="L518" s="6" t="n">
-        <v>100.179837</v>
+        <v>100.17799</v>
       </c>
       <c r="M518" s="6" t="n">
         <v>99.83895099999999</v>
@@ -42807,13 +42807,13 @@
         <v>100.205604</v>
       </c>
       <c r="J519" s="9" t="n">
-        <v>100.656071</v>
+        <v>100.655448</v>
       </c>
       <c r="K519" s="9" t="n">
         <v>100.933184</v>
       </c>
       <c r="L519" s="9" t="n">
-        <v>100.222659</v>
+        <v>100.220885</v>
       </c>
       <c r="M519" s="9" t="n">
         <v>99.75003700000001</v>
@@ -42891,13 +42891,13 @@
         <v>100.322531</v>
       </c>
       <c r="J520" s="6" t="n">
-        <v>100.791385</v>
+        <v>100.790567</v>
       </c>
       <c r="K520" s="6" t="n">
         <v>100.931932</v>
       </c>
       <c r="L520" s="6" t="n">
-        <v>100.263781</v>
+        <v>100.262626</v>
       </c>
       <c r="M520" s="6" t="n">
         <v>99.61024500000001</v>
@@ -42975,13 +42975,13 @@
         <v>100.415127</v>
       </c>
       <c r="J521" s="9" t="n">
-        <v>100.925472</v>
+        <v>100.924947</v>
       </c>
       <c r="K521" s="9" t="n">
         <v>100.928644</v>
       </c>
       <c r="L521" s="9" t="n">
-        <v>100.305966</v>
+        <v>100.305645</v>
       </c>
       <c r="M521" s="9" t="n">
         <v>99.439331</v>
@@ -43059,13 +43059,13 @@
         <v>100.469904</v>
       </c>
       <c r="J522" s="6" t="n">
-        <v>101.028024</v>
+        <v>101.028206</v>
       </c>
       <c r="K522" s="6" t="n">
         <v>100.921182</v>
       </c>
       <c r="L522" s="6" t="n">
-        <v>100.351294</v>
+        <v>100.351844</v>
       </c>
       <c r="M522" s="6" t="n">
         <v>99.24552799999999</v>
@@ -43143,13 +43143,13 @@
         <v>100.498619</v>
       </c>
       <c r="J523" s="9" t="n">
-        <v>101.108626</v>
+        <v>101.109661</v>
       </c>
       <c r="K523" s="9" t="n">
         <v>100.914412</v>
       </c>
       <c r="L523" s="9" t="n">
-        <v>100.400924</v>
+        <v>100.402255</v>
       </c>
       <c r="M523" s="9" t="n">
         <v>99.067223</v>
@@ -43227,13 +43227,13 @@
         <v>100.532422</v>
       </c>
       <c r="J524" s="6" t="n">
-        <v>101.189325</v>
+        <v>101.191005</v>
       </c>
       <c r="K524" s="6" t="n">
         <v>100.919381</v>
       </c>
       <c r="L524" s="6" t="n">
-        <v>100.451343</v>
+        <v>100.453242</v>
       </c>
       <c r="M524" s="6" t="n">
         <v>98.927182</v>
@@ -43311,13 +43311,13 @@
         <v>100.589925</v>
       </c>
       <c r="J525" s="9" t="n">
-        <v>101.283764</v>
+        <v>101.28547</v>
       </c>
       <c r="K525" s="9" t="n">
         <v>100.944665</v>
       </c>
       <c r="L525" s="9" t="n">
-        <v>100.495799</v>
+        <v>100.497898</v>
       </c>
       <c r="M525" s="9" t="n">
         <v>98.829159</v>
@@ -43395,13 +43395,13 @@
         <v>100.661766</v>
       </c>
       <c r="J526" s="6" t="n">
-        <v>101.388892</v>
+        <v>101.389861</v>
       </c>
       <c r="K526" s="6" t="n">
         <v>100.979837</v>
       </c>
       <c r="L526" s="6" t="n">
-        <v>100.530697</v>
+        <v>100.532758</v>
       </c>
       <c r="M526" s="6" t="n">
         <v>98.743075</v>
@@ -43479,13 +43479,13 @@
         <v>100.740786</v>
       </c>
       <c r="J527" s="9" t="n">
-        <v>101.493341</v>
+        <v>101.49271</v>
       </c>
       <c r="K527" s="9" t="n">
         <v>101.015555</v>
       </c>
       <c r="L527" s="9" t="n">
-        <v>100.55323</v>
+        <v>100.555063</v>
       </c>
       <c r="M527" s="9" t="n">
         <v>98.69872100000001</v>
@@ -43563,13 +43563,13 @@
         <v>100.818062</v>
       </c>
       <c r="J528" s="6" t="n">
-        <v>101.584921</v>
+        <v>101.58194</v>
       </c>
       <c r="K528" s="6" t="n">
         <v>101.027032</v>
       </c>
       <c r="L528" s="6" t="n">
-        <v>100.564068</v>
+        <v>100.565701</v>
       </c>
       <c r="M528" s="6" t="n">
         <v>98.7244</v>
@@ -43647,13 +43647,13 @@
         <v>100.888541</v>
       </c>
       <c r="J529" s="9" t="n">
-        <v>101.655708</v>
+        <v>101.650164</v>
       </c>
       <c r="K529" s="9" t="n">
         <v>101.006236</v>
       </c>
       <c r="L529" s="9" t="n">
-        <v>100.566624</v>
+        <v>100.568192</v>
       </c>
       <c r="M529" s="9" t="n">
         <v>98.791405</v>
@@ -43731,13 +43731,13 @@
         <v>100.939658</v>
       </c>
       <c r="J530" s="6" t="n">
-        <v>101.690968</v>
+        <v>101.683087</v>
       </c>
       <c r="K530" s="6" t="n">
         <v>100.956051</v>
       </c>
       <c r="L530" s="6" t="n">
-        <v>100.565101</v>
+        <v>100.566838</v>
       </c>
       <c r="M530" s="6" t="n">
         <v>98.885837</v>
@@ -43815,13 +43815,13 @@
         <v>100.955336</v>
       </c>
       <c r="J531" s="9" t="n">
-        <v>101.666622</v>
+        <v>101.657057</v>
       </c>
       <c r="K531" s="9" t="n">
         <v>100.873205</v>
       </c>
       <c r="L531" s="9" t="n">
-        <v>100.562499</v>
+        <v>100.564714</v>
       </c>
       <c r="M531" s="9" t="n">
         <v>98.990784</v>
@@ -43899,13 +43899,13 @@
         <v>100.939924</v>
       </c>
       <c r="J532" s="6" t="n">
-        <v>101.568531</v>
+        <v>101.558299</v>
       </c>
       <c r="K532" s="6" t="n">
         <v>100.752497</v>
       </c>
       <c r="L532" s="6" t="n">
-        <v>100.55948</v>
+        <v>100.562632</v>
       </c>
       <c r="M532" s="6" t="n">
         <v>99.086555</v>
@@ -43983,13 +43983,13 @@
         <v>100.913523</v>
       </c>
       <c r="J533" s="9" t="n">
-        <v>101.428694</v>
+        <v>101.419006</v>
       </c>
       <c r="K533" s="9" t="n">
         <v>100.598401</v>
       </c>
       <c r="L533" s="9" t="n">
-        <v>100.556327</v>
+        <v>100.560597</v>
       </c>
       <c r="M533" s="9" t="n">
         <v>99.164484</v>
@@ -44067,13 +44067,13 @@
         <v>100.87965</v>
       </c>
       <c r="J534" s="6" t="n">
-        <v>101.265916</v>
+        <v>101.257861</v>
       </c>
       <c r="K534" s="6" t="n">
         <v>100.430969</v>
       </c>
       <c r="L534" s="6" t="n">
-        <v>100.553928</v>
+        <v>100.559299</v>
       </c>
       <c r="M534" s="6" t="n">
         <v>99.222487</v>
@@ -44151,13 +44151,13 @@
         <v>100.838947</v>
       </c>
       <c r="J535" s="9" t="n">
-        <v>101.090678</v>
+        <v>101.085013</v>
       </c>
       <c r="K535" s="9" t="n">
         <v>100.274535</v>
       </c>
       <c r="L535" s="9" t="n">
-        <v>100.552199</v>
+        <v>100.558504</v>
       </c>
       <c r="M535" s="9" t="n">
         <v>99.26419300000001</v>
@@ -44235,13 +44235,13 @@
         <v>100.788414</v>
       </c>
       <c r="J536" s="6" t="n">
-        <v>100.936379</v>
+        <v>100.933128</v>
       </c>
       <c r="K536" s="6" t="n">
         <v>100.133131</v>
       </c>
       <c r="L536" s="6" t="n">
-        <v>100.551102</v>
+        <v>100.558039</v>
       </c>
       <c r="M536" s="6" t="n">
         <v>99.29733</v>
@@ -44319,13 +44319,13 @@
         <v>100.732864</v>
       </c>
       <c r="J537" s="9" t="n">
-        <v>100.809771</v>
+        <v>100.807882</v>
       </c>
       <c r="K537" s="9" t="n">
         <v>100.014388</v>
       </c>
       <c r="L537" s="9" t="n">
-        <v>100.551086</v>
+        <v>100.558219</v>
       </c>
       <c r="M537" s="9" t="n">
         <v>99.32158099999999</v>
@@ -44403,13 +44403,13 @@
         <v>100.693866</v>
       </c>
       <c r="J538" s="6" t="n">
-        <v>100.722871</v>
+        <v>100.720319</v>
       </c>
       <c r="K538" s="6" t="n">
         <v>99.918116</v>
       </c>
       <c r="L538" s="6" t="n">
-        <v>100.549269</v>
+        <v>100.556353</v>
       </c>
       <c r="M538" s="6" t="n">
         <v>99.34638200000001</v>
@@ -44487,13 +44487,13 @@
         <v>100.658289</v>
       </c>
       <c r="J539" s="9" t="n">
-        <v>100.662984</v>
+        <v>100.657102</v>
       </c>
       <c r="K539" s="9" t="n">
         <v>99.846045</v>
       </c>
       <c r="L539" s="9" t="n">
-        <v>100.542064</v>
+        <v>100.54897</v>
       </c>
       <c r="M539" s="9" t="n">
         <v>99.352293</v>
@@ -44571,13 +44571,13 @@
         <v>100.607989</v>
       </c>
       <c r="J540" s="6" t="n">
-        <v>100.603624</v>
+        <v>100.591947</v>
       </c>
       <c r="K540" s="6" t="n">
         <v>99.799049</v>
       </c>
       <c r="L540" s="6" t="n">
-        <v>100.527691</v>
+        <v>100.534621</v>
       </c>
       <c r="M540" s="6" t="n">
         <v>99.31580599999999</v>
@@ -44655,13 +44655,13 @@
         <v>100.524119</v>
       </c>
       <c r="J541" s="9" t="n">
-        <v>100.51623</v>
+        <v>100.497531</v>
       </c>
       <c r="K541" s="9" t="n">
         <v>99.763848</v>
       </c>
       <c r="L541" s="9" t="n">
-        <v>100.502775</v>
+        <v>100.51008</v>
       </c>
       <c r="M541" s="9" t="n">
         <v>99.24623099999999</v>
@@ -44739,13 +44739,13 @@
         <v>100.418188</v>
       </c>
       <c r="J542" s="6" t="n">
-        <v>100.394529</v>
+        <v>100.370502</v>
       </c>
       <c r="K542" s="6" t="n">
         <v>99.737196</v>
       </c>
       <c r="L542" s="6" t="n">
-        <v>100.466622</v>
+        <v>100.474732</v>
       </c>
       <c r="M542" s="6" t="n">
         <v>99.16469499999999</v>
@@ -44823,13 +44823,13 @@
         <v>100.303743</v>
       </c>
       <c r="J543" s="9" t="n">
-        <v>100.240854</v>
+        <v>100.213821</v>
       </c>
       <c r="K543" s="9" t="n">
         <v>99.71713699999999</v>
       </c>
       <c r="L543" s="9" t="n">
-        <v>100.420502</v>
+        <v>100.42974</v>
       </c>
       <c r="M543" s="9" t="n">
         <v>99.099536</v>
@@ -44907,13 +44907,13 @@
         <v>100.208709</v>
       </c>
       <c r="J544" s="6" t="n">
-        <v>100.096105</v>
+        <v>100.068431</v>
       </c>
       <c r="K544" s="6" t="n">
         <v>99.713838</v>
       </c>
       <c r="L544" s="6" t="n">
-        <v>100.367899</v>
+        <v>100.378549</v>
       </c>
       <c r="M544" s="6" t="n">
         <v>99.09106</v>
@@ -44991,13 +44991,13 @@
         <v>100.142715</v>
       </c>
       <c r="J545" s="9" t="n">
-        <v>99.984133</v>
+        <v>99.957966</v>
       </c>
       <c r="K545" s="9" t="n">
         <v>99.731785</v>
       </c>
       <c r="L545" s="9" t="n">
-        <v>100.311633</v>
+        <v>100.323723</v>
       </c>
       <c r="M545" s="9" t="n">
         <v>99.124756</v>
@@ -45075,13 +45075,13 @@
         <v>100.117118</v>
       </c>
       <c r="J546" s="6" t="n">
-        <v>99.92702199999999</v>
+        <v>99.904202</v>
       </c>
       <c r="K546" s="6" t="n">
         <v>99.760856</v>
       </c>
       <c r="L546" s="6" t="n">
-        <v>100.252883</v>
+        <v>100.26626</v>
       </c>
       <c r="M546" s="6" t="n">
         <v>99.17992599999999</v>
@@ -45159,13 +45159,13 @@
         <v>100.109531</v>
       </c>
       <c r="J547" s="9" t="n">
-        <v>99.9059</v>
+        <v>99.887636</v>
       </c>
       <c r="K547" s="9" t="n">
         <v>99.788151</v>
       </c>
       <c r="L547" s="9" t="n">
-        <v>100.192471</v>
+        <v>100.206858</v>
       </c>
       <c r="M547" s="9" t="n">
         <v>99.239465</v>
@@ -45243,13 +45243,13 @@
         <v>100.088978</v>
       </c>
       <c r="J548" s="6" t="n">
-        <v>99.871627</v>
+        <v>99.85809999999999</v>
       </c>
       <c r="K548" s="6" t="n">
         <v>99.80586</v>
       </c>
       <c r="L548" s="6" t="n">
-        <v>100.130644</v>
+        <v>100.145668</v>
       </c>
       <c r="M548" s="6" t="n">
         <v>99.30811199999999</v>
@@ -45327,13 +45327,13 @@
         <v>100.050048</v>
       </c>
       <c r="J549" s="9" t="n">
-        <v>99.81034200000001</v>
+        <v>99.80019299999999</v>
       </c>
       <c r="K549" s="9" t="n">
         <v>99.814857</v>
       </c>
       <c r="L549" s="9" t="n">
-        <v>100.066523</v>
+        <v>100.081705</v>
       </c>
       <c r="M549" s="9" t="n">
         <v>99.41411100000001</v>
@@ -45411,13 +45411,13 @@
         <v>99.99865699999999</v>
       </c>
       <c r="J550" s="6" t="n">
-        <v>99.729754</v>
+        <v>99.719556</v>
       </c>
       <c r="K550" s="6" t="n">
         <v>99.82645100000001</v>
       </c>
       <c r="L550" s="6" t="n">
-        <v>100.000477</v>
+        <v>100.015623</v>
       </c>
       <c r="M550" s="6" t="n">
         <v>99.522002</v>
@@ -45495,13 +45495,13 @@
         <v>99.936921</v>
       </c>
       <c r="J551" s="9" t="n">
-        <v>99.62351099999999</v>
+        <v>99.608245</v>
       </c>
       <c r="K551" s="9" t="n">
         <v>99.841813</v>
       </c>
       <c r="L551" s="9" t="n">
-        <v>99.93474399999999</v>
+        <v>99.949878</v>
       </c>
       <c r="M551" s="9" t="n">
         <v>99.63457099999999</v>
@@ -45579,13 +45579,13 @@
         <v>99.87272299999999</v>
       </c>
       <c r="J552" s="6" t="n">
-        <v>99.511067</v>
+        <v>99.485319</v>
       </c>
       <c r="K552" s="6" t="n">
         <v>99.86333</v>
       </c>
       <c r="L552" s="6" t="n">
-        <v>99.87217200000001</v>
+        <v>99.887653</v>
       </c>
       <c r="M552" s="6" t="n">
         <v>99.766857</v>
@@ -45663,13 +45663,13 @@
         <v>99.826672</v>
       </c>
       <c r="J553" s="9" t="n">
-        <v>99.429486</v>
+        <v>99.389957</v>
       </c>
       <c r="K553" s="9" t="n">
         <v>99.89223</v>
       </c>
       <c r="L553" s="9" t="n">
-        <v>99.816664</v>
+        <v>99.833029</v>
       </c>
       <c r="M553" s="9" t="n">
         <v>99.930751</v>
@@ -45747,13 +45747,13 @@
         <v>99.798992</v>
       </c>
       <c r="J554" s="6" t="n">
-        <v>99.396497</v>
+        <v>99.346199</v>
       </c>
       <c r="K554" s="6" t="n">
         <v>99.925391</v>
       </c>
       <c r="L554" s="6" t="n">
-        <v>99.771727</v>
+        <v>99.789569</v>
       </c>
       <c r="M554" s="6" t="n">
         <v>100.070674</v>
@@ -45831,13 +45831,13 @@
         <v>99.791175</v>
       </c>
       <c r="J555" s="9" t="n">
-        <v>99.410533</v>
+        <v>99.353003</v>
       </c>
       <c r="K555" s="9" t="n">
         <v>99.960492</v>
       </c>
       <c r="L555" s="9" t="n">
-        <v>99.73569000000001</v>
+        <v>99.75531599999999</v>
       </c>
       <c r="M555" s="9" t="n">
         <v>100.151774</v>
@@ -45915,13 +45915,13 @@
         <v>99.78725300000001</v>
       </c>
       <c r="J556" s="6" t="n">
-        <v>99.446281</v>
+        <v>99.38487499999999</v>
       </c>
       <c r="K556" s="6" t="n">
         <v>99.987179</v>
       </c>
       <c r="L556" s="6" t="n">
-        <v>99.705551</v>
+        <v>99.727041</v>
       </c>
       <c r="M556" s="6" t="n">
         <v>100.216711</v>
@@ -45999,13 +45999,13 @@
         <v>99.787902</v>
       </c>
       <c r="J557" s="9" t="n">
-        <v>99.48218799999999</v>
+        <v>99.420351</v>
       </c>
       <c r="K557" s="9" t="n">
         <v>99.99443599999999</v>
       </c>
       <c r="L557" s="9" t="n">
-        <v>99.679518</v>
+        <v>99.702732</v>
       </c>
       <c r="M557" s="9" t="n">
         <v>100.285121</v>
@@ -46083,13 +46083,13 @@
         <v>99.80225</v>
       </c>
       <c r="J558" s="6" t="n">
-        <v>99.518897</v>
+        <v>99.460641</v>
       </c>
       <c r="K558" s="6" t="n">
         <v>99.98420900000001</v>
       </c>
       <c r="L558" s="6" t="n">
-        <v>99.65561</v>
+        <v>99.680273</v>
       </c>
       <c r="M558" s="6" t="n">
         <v>100.389843</v>
@@ -46167,13 +46167,13 @@
         <v>99.85903999999999</v>
       </c>
       <c r="J559" s="9" t="n">
-        <v>99.57956</v>
+        <v>99.53000299999999</v>
       </c>
       <c r="K559" s="9" t="n">
         <v>99.95556000000001</v>
       </c>
       <c r="L559" s="9" t="n">
-        <v>99.632307</v>
+        <v>99.658101</v>
       </c>
       <c r="M559" s="9" t="n">
         <v>100.515751</v>
@@ -46251,13 +46251,13 @@
         <v>99.962011</v>
       </c>
       <c r="J560" s="6" t="n">
-        <v>99.669968</v>
+        <v>99.635588</v>
       </c>
       <c r="K560" s="6" t="n">
         <v>99.92066199999999</v>
       </c>
       <c r="L560" s="6" t="n">
-        <v>99.608284</v>
+        <v>99.63489800000001</v>
       </c>
       <c r="M560" s="6" t="n">
         <v>100.635757</v>
@@ -46335,13 +46335,13 @@
         <v>100.094416</v>
       </c>
       <c r="J561" s="9" t="n">
-        <v>99.791371</v>
+        <v>99.780231</v>
       </c>
       <c r="K561" s="9" t="n">
         <v>99.877825</v>
       </c>
       <c r="L561" s="9" t="n">
-        <v>99.584</v>
+        <v>99.611126</v>
       </c>
       <c r="M561" s="9" t="n">
         <v>100.715535</v>
@@ -46419,13 +46419,13 @@
         <v>100.225959</v>
       </c>
       <c r="J562" s="6" t="n">
-        <v>99.91174100000001</v>
+        <v>99.933437</v>
       </c>
       <c r="K562" s="6" t="n">
         <v>99.824534</v>
       </c>
       <c r="L562" s="6" t="n">
-        <v>99.562954</v>
+        <v>99.590773</v>
       </c>
       <c r="M562" s="6" t="n">
         <v>100.746164</v>
@@ -46503,13 +46503,13 @@
         <v>100.356612</v>
       </c>
       <c r="J563" s="9" t="n">
-        <v>100.033774</v>
+        <v>100.098738</v>
       </c>
       <c r="K563" s="9" t="n">
         <v>99.76123800000001</v>
       </c>
       <c r="L563" s="9" t="n">
-        <v>99.54803</v>
+        <v>99.57714300000001</v>
       </c>
       <c r="M563" s="9" t="n">
         <v>100.719442</v>
@@ -46587,13 +46587,13 @@
         <v>100.491865</v>
       </c>
       <c r="J564" s="6" t="n">
-        <v>100.158475</v>
+        <v>100.276559</v>
       </c>
       <c r="K564" s="6" t="n">
         <v>99.69396399999999</v>
       </c>
       <c r="L564" s="6" t="n">
-        <v>99.53705600000001</v>
+        <v>99.568476</v>
       </c>
       <c r="M564" s="6" t="n">
         <v>100.638019</v>
@@ -46662,10 +46662,12 @@
         <v>0.856274</v>
       </c>
       <c r="I565" s="9" t="n"/>
-      <c r="J565" s="9" t="n"/>
+      <c r="J565" s="9" t="n">
+        <v>100.461215</v>
+      </c>
       <c r="K565" s="9" t="n"/>
       <c r="L565" s="9" t="n">
-        <v>99.528155</v>
+        <v>99.56307200000001</v>
       </c>
       <c r="M565" s="9" t="n">
         <v>100.528134</v>

--- a/downloads/indicadores/SIC/SIC_datos.xlsx
+++ b/downloads/indicadores/SIC/SIC_datos.xlsx
@@ -687,7 +687,7 @@
       <c r="P6" s="6" t="n"/>
       <c r="Q6" s="6" t="n"/>
       <c r="R6" s="6" t="n">
-        <v>101.941389</v>
+        <v>101.944201</v>
       </c>
       <c r="S6" s="6" t="n">
         <v>99.495051</v>
@@ -759,7 +759,7 @@
       <c r="P7" s="9" t="n"/>
       <c r="Q7" s="9" t="n"/>
       <c r="R7" s="9" t="n">
-        <v>101.679166</v>
+        <v>101.681602</v>
       </c>
       <c r="S7" s="9" t="n">
         <v>99.51201500000001</v>
@@ -831,7 +831,7 @@
       <c r="P8" s="6" t="n"/>
       <c r="Q8" s="6" t="n"/>
       <c r="R8" s="6" t="n">
-        <v>101.415867</v>
+        <v>101.417925</v>
       </c>
       <c r="S8" s="6" t="n">
         <v>99.525755</v>
@@ -903,7 +903,7 @@
       <c r="P9" s="9" t="n"/>
       <c r="Q9" s="9" t="n"/>
       <c r="R9" s="9" t="n">
-        <v>101.147129</v>
+        <v>101.148802</v>
       </c>
       <c r="S9" s="9" t="n">
         <v>99.52974399999999</v>
@@ -975,7 +975,7 @@
       <c r="P10" s="6" t="n"/>
       <c r="Q10" s="6" t="n"/>
       <c r="R10" s="6" t="n">
-        <v>100.867318</v>
+        <v>100.868589</v>
       </c>
       <c r="S10" s="6" t="n">
         <v>99.52053600000001</v>
@@ -1047,7 +1047,7 @@
       <c r="P11" s="9" t="n"/>
       <c r="Q11" s="9" t="n"/>
       <c r="R11" s="9" t="n">
-        <v>100.572872</v>
+        <v>100.573721</v>
       </c>
       <c r="S11" s="9" t="n">
         <v>99.500668</v>
@@ -1119,7 +1119,7 @@
       <c r="P12" s="6" t="n"/>
       <c r="Q12" s="6" t="n"/>
       <c r="R12" s="6" t="n">
-        <v>100.267224</v>
+        <v>100.267634</v>
       </c>
       <c r="S12" s="6" t="n">
         <v>99.48083200000001</v>
@@ -1191,7 +1191,7 @@
       <c r="P13" s="9" t="n"/>
       <c r="Q13" s="9" t="n"/>
       <c r="R13" s="9" t="n">
-        <v>99.963548</v>
+        <v>99.963522</v>
       </c>
       <c r="S13" s="9" t="n">
         <v>99.473626</v>
@@ -1263,7 +1263,7 @@
       <c r="P14" s="6" t="n"/>
       <c r="Q14" s="6" t="n"/>
       <c r="R14" s="6" t="n">
-        <v>99.667934</v>
+        <v>99.667484</v>
       </c>
       <c r="S14" s="6" t="n">
         <v>99.48698400000001</v>
@@ -1335,7 +1335,7 @@
       <c r="P15" s="9" t="n"/>
       <c r="Q15" s="9" t="n"/>
       <c r="R15" s="9" t="n">
-        <v>99.37602</v>
+        <v>99.375151</v>
       </c>
       <c r="S15" s="9" t="n">
         <v>99.52090699999999</v>
@@ -1407,7 +1407,7 @@
       <c r="P16" s="6" t="n"/>
       <c r="Q16" s="6" t="n"/>
       <c r="R16" s="6" t="n">
-        <v>99.081114</v>
+        <v>99.079823</v>
       </c>
       <c r="S16" s="6" t="n">
         <v>99.56989799999999</v>
@@ -1479,7 +1479,7 @@
       <c r="P17" s="9" t="n"/>
       <c r="Q17" s="9" t="n"/>
       <c r="R17" s="9" t="n">
-        <v>98.780384</v>
+        <v>98.778662</v>
       </c>
       <c r="S17" s="9" t="n">
         <v>99.62732099999999</v>
@@ -1557,7 +1557,7 @@
         <v>106.977071</v>
       </c>
       <c r="R18" s="6" t="n">
-        <v>98.480585</v>
+        <v>98.478433</v>
       </c>
       <c r="S18" s="6" t="n">
         <v>99.67873</v>
@@ -1635,7 +1635,7 @@
         <v>106.525836</v>
       </c>
       <c r="R19" s="9" t="n">
-        <v>98.193574</v>
+        <v>98.191012</v>
       </c>
       <c r="S19" s="9" t="n">
         <v>99.71287700000001</v>
@@ -1713,7 +1713,7 @@
         <v>106.073473</v>
       </c>
       <c r="R20" s="6" t="n">
-        <v>97.92594099999999</v>
+        <v>97.922997</v>
       </c>
       <c r="S20" s="6" t="n">
         <v>99.727823</v>
@@ -1791,7 +1791,7 @@
         <v>105.614626</v>
       </c>
       <c r="R21" s="9" t="n">
-        <v>97.67979800000001</v>
+        <v>97.67650399999999</v>
       </c>
       <c r="S21" s="9" t="n">
         <v>99.72718399999999</v>
@@ -1869,7 +1869,7 @@
         <v>105.141018</v>
       </c>
       <c r="R22" s="6" t="n">
-        <v>97.45354</v>
+        <v>97.44992499999999</v>
       </c>
       <c r="S22" s="6" t="n">
         <v>99.719031</v>
@@ -1947,7 +1947,7 @@
         <v>104.658056</v>
       </c>
       <c r="R23" s="9" t="n">
-        <v>97.24066500000001</v>
+        <v>97.236746</v>
       </c>
       <c r="S23" s="9" t="n">
         <v>99.711484</v>
@@ -2025,7 +2025,7 @@
         <v>104.172159</v>
       </c>
       <c r="R24" s="6" t="n">
-        <v>97.03708</v>
+        <v>97.03286799999999</v>
       </c>
       <c r="S24" s="6" t="n">
         <v>99.70883000000001</v>
@@ -2103,7 +2103,7 @@
         <v>103.685225</v>
       </c>
       <c r="R25" s="9" t="n">
-        <v>96.849934</v>
+        <v>96.845449</v>
       </c>
       <c r="S25" s="9" t="n">
         <v>99.709293</v>
@@ -2181,7 +2181,7 @@
         <v>103.194708</v>
       </c>
       <c r="R26" s="6" t="n">
-        <v>96.705758</v>
+        <v>96.70105100000001</v>
       </c>
       <c r="S26" s="6" t="n">
         <v>99.70683699999999</v>
@@ -2259,7 +2259,7 @@
         <v>102.695704</v>
       </c>
       <c r="R27" s="9" t="n">
-        <v>96.647215</v>
+        <v>96.642398</v>
       </c>
       <c r="S27" s="9" t="n">
         <v>99.696804</v>
@@ -2337,7 +2337,7 @@
         <v>102.177487</v>
       </c>
       <c r="R28" s="6" t="n">
-        <v>96.73735000000001</v>
+        <v>96.732619</v>
       </c>
       <c r="S28" s="6" t="n">
         <v>99.679502</v>
@@ -2415,7 +2415,7 @@
         <v>101.586258</v>
       </c>
       <c r="R29" s="9" t="n">
-        <v>97.043802</v>
+        <v>97.039451</v>
       </c>
       <c r="S29" s="9" t="n">
         <v>99.661873</v>
@@ -2493,7 +2493,7 @@
         <v>100.879698</v>
       </c>
       <c r="R30" s="6" t="n">
-        <v>97.616789</v>
+        <v>97.61318799999999</v>
       </c>
       <c r="S30" s="6" t="n">
         <v>99.65682</v>
@@ -2571,7 +2571,7 @@
         <v>100.08151</v>
       </c>
       <c r="R31" s="9" t="n">
-        <v>98.444929</v>
+        <v>98.442449</v>
       </c>
       <c r="S31" s="9" t="n">
         <v>99.676376</v>
@@ -2649,7 +2649,7 @@
         <v>99.20184999999999</v>
       </c>
       <c r="R32" s="6" t="n">
-        <v>99.367648</v>
+        <v>99.366455</v>
       </c>
       <c r="S32" s="6" t="n">
         <v>99.729839</v>
@@ -2727,7 +2727,7 @@
         <v>98.283457</v>
       </c>
       <c r="R33" s="9" t="n">
-        <v>100.193865</v>
+        <v>100.193903</v>
       </c>
       <c r="S33" s="9" t="n">
         <v>99.826806</v>
@@ -2805,7 +2805,7 @@
         <v>97.44098200000001</v>
       </c>
       <c r="R34" s="6" t="n">
-        <v>100.829396</v>
+        <v>100.830425</v>
       </c>
       <c r="S34" s="6" t="n">
         <v>99.967636</v>
@@ -2883,7 +2883,7 @@
         <v>96.775612</v>
       </c>
       <c r="R35" s="9" t="n">
-        <v>101.308747</v>
+        <v>101.310544</v>
       </c>
       <c r="S35" s="9" t="n">
         <v>100.136444</v>
@@ -2961,7 +2961,7 @@
         <v>96.290374</v>
       </c>
       <c r="R36" s="6" t="n">
-        <v>101.707294</v>
+        <v>101.709731</v>
       </c>
       <c r="S36" s="6" t="n">
         <v>100.303386</v>
@@ -3039,7 +3039,7 @@
         <v>95.985755</v>
       </c>
       <c r="R37" s="9" t="n">
-        <v>102.077392</v>
+        <v>102.080407</v>
       </c>
       <c r="S37" s="9" t="n">
         <v>100.438595</v>
@@ -3117,7 +3117,7 @@
         <v>95.818421</v>
       </c>
       <c r="R38" s="6" t="n">
-        <v>102.378652</v>
+        <v>102.38212</v>
       </c>
       <c r="S38" s="6" t="n">
         <v>100.526597</v>
@@ -3195,7 +3195,7 @@
         <v>95.69736</v>
       </c>
       <c r="R39" s="9" t="n">
-        <v>102.566638</v>
+        <v>102.570381</v>
       </c>
       <c r="S39" s="9" t="n">
         <v>100.576466</v>
@@ -3273,7 +3273,7 @@
         <v>95.591988</v>
       </c>
       <c r="R40" s="6" t="n">
-        <v>102.687969</v>
+        <v>102.691884</v>
       </c>
       <c r="S40" s="6" t="n">
         <v>100.619789</v>
@@ -3351,7 +3351,7 @@
         <v>95.489333</v>
       </c>
       <c r="R41" s="9" t="n">
-        <v>102.801567</v>
+        <v>102.805638</v>
       </c>
       <c r="S41" s="9" t="n">
         <v>100.683553</v>
@@ -3429,7 +3429,7 @@
         <v>95.451335</v>
       </c>
       <c r="R42" s="6" t="n">
-        <v>102.901158</v>
+        <v>102.905363</v>
       </c>
       <c r="S42" s="6" t="n">
         <v>100.775272</v>
@@ -3507,7 +3507,7 @@
         <v>95.506136</v>
       </c>
       <c r="R43" s="9" t="n">
-        <v>102.937119</v>
+        <v>102.941369</v>
       </c>
       <c r="S43" s="9" t="n">
         <v>100.876143</v>
@@ -3585,7 +3585,7 @@
         <v>95.68226300000001</v>
       </c>
       <c r="R44" s="6" t="n">
-        <v>102.89332</v>
+        <v>102.897502</v>
       </c>
       <c r="S44" s="6" t="n">
         <v>100.961051</v>
@@ -3663,7 +3663,7 @@
         <v>96.020178</v>
       </c>
       <c r="R45" s="9" t="n">
-        <v>102.783008</v>
+        <v>102.787028</v>
       </c>
       <c r="S45" s="9" t="n">
         <v>101.013736</v>
@@ -3741,7 +3741,7 @@
         <v>96.51267900000001</v>
       </c>
       <c r="R46" s="6" t="n">
-        <v>102.631606</v>
+        <v>102.635407</v>
       </c>
       <c r="S46" s="6" t="n">
         <v>101.027292</v>
@@ -3819,7 +3819,7 @@
         <v>97.09406199999999</v>
       </c>
       <c r="R47" s="9" t="n">
-        <v>102.455392</v>
+        <v>102.458939</v>
       </c>
       <c r="S47" s="9" t="n">
         <v>101.000688</v>
@@ -3897,7 +3897,7 @@
         <v>97.675329</v>
       </c>
       <c r="R48" s="6" t="n">
-        <v>102.261819</v>
+        <v>102.265087</v>
       </c>
       <c r="S48" s="6" t="n">
         <v>100.93728</v>
@@ -3975,7 +3975,7 @@
         <v>98.220439</v>
       </c>
       <c r="R49" s="9" t="n">
-        <v>102.054093</v>
+        <v>102.057061</v>
       </c>
       <c r="S49" s="9" t="n">
         <v>100.843322</v>
@@ -4053,7 +4053,7 @@
         <v>98.73484000000001</v>
       </c>
       <c r="R50" s="6" t="n">
-        <v>101.823955</v>
+        <v>101.826592</v>
       </c>
       <c r="S50" s="6" t="n">
         <v>100.726676</v>
@@ -4131,7 +4131,7 @@
         <v>99.19405399999999</v>
       </c>
       <c r="R51" s="9" t="n">
-        <v>101.556001</v>
+        <v>101.558253</v>
       </c>
       <c r="S51" s="9" t="n">
         <v>100.593785</v>
@@ -4209,7 +4209,7 @@
         <v>99.617563</v>
       </c>
       <c r="R52" s="6" t="n">
-        <v>101.242898</v>
+        <v>101.2447</v>
       </c>
       <c r="S52" s="6" t="n">
         <v>100.448705</v>
@@ -4287,7 +4287,7 @@
         <v>100.009604</v>
       </c>
       <c r="R53" s="9" t="n">
-        <v>100.897152</v>
+        <v>100.898457</v>
       </c>
       <c r="S53" s="9" t="n">
         <v>100.292144</v>
@@ -4365,7 +4365,7 @@
         <v>100.299604</v>
       </c>
       <c r="R54" s="6" t="n">
-        <v>100.535859</v>
+        <v>100.536646</v>
       </c>
       <c r="S54" s="6" t="n">
         <v>100.123674</v>
@@ -4443,7 +4443,7 @@
         <v>100.385484</v>
       </c>
       <c r="R55" s="9" t="n">
-        <v>100.184283</v>
+        <v>100.184564</v>
       </c>
       <c r="S55" s="9" t="n">
         <v>99.944523</v>
@@ -4521,7 +4521,7 @@
         <v>100.243432</v>
       </c>
       <c r="R56" s="6" t="n">
-        <v>99.86248500000001</v>
+        <v>99.862303</v>
       </c>
       <c r="S56" s="6" t="n">
         <v>99.760547</v>
@@ -4599,7 +4599,7 @@
         <v>99.98218</v>
       </c>
       <c r="R57" s="9" t="n">
-        <v>99.580146</v>
+        <v>99.57955699999999</v>
       </c>
       <c r="S57" s="9" t="n">
         <v>99.58397100000001</v>
@@ -4677,7 +4677,7 @@
         <v>99.72310299999999</v>
       </c>
       <c r="R58" s="6" t="n">
-        <v>99.337064</v>
+        <v>99.33612599999999</v>
       </c>
       <c r="S58" s="6" t="n">
         <v>99.42626</v>
@@ -4755,7 +4755,7 @@
         <v>99.50620600000001</v>
       </c>
       <c r="R59" s="9" t="n">
-        <v>99.12311099999999</v>
+        <v>99.121865</v>
       </c>
       <c r="S59" s="9" t="n">
         <v>99.290352</v>
@@ -4833,7 +4833,7 @@
         <v>99.35167</v>
       </c>
       <c r="R60" s="6" t="n">
-        <v>98.923866</v>
+        <v>98.92233400000001</v>
       </c>
       <c r="S60" s="6" t="n">
         <v>99.169241</v>
@@ -4911,7 +4911,7 @@
         <v>99.22823</v>
       </c>
       <c r="R61" s="9" t="n">
-        <v>98.720533</v>
+        <v>98.71870800000001</v>
       </c>
       <c r="S61" s="9" t="n">
         <v>99.052787</v>
@@ -4989,7 +4989,7 @@
         <v>99.058279</v>
       </c>
       <c r="R62" s="6" t="n">
-        <v>98.492166</v>
+        <v>98.49001199999999</v>
       </c>
       <c r="S62" s="6" t="n">
         <v>98.933986</v>
@@ -5067,7 +5067,7 @@
         <v>98.787902</v>
       </c>
       <c r="R63" s="9" t="n">
-        <v>98.224097</v>
+        <v>98.221558</v>
       </c>
       <c r="S63" s="9" t="n">
         <v>98.81443</v>
@@ -5145,7 +5145,7 @@
         <v>98.434803</v>
       </c>
       <c r="R64" s="6" t="n">
-        <v>97.916408</v>
+        <v>97.913426</v>
       </c>
       <c r="S64" s="6" t="n">
         <v>98.70566599999999</v>
@@ -5223,7 +5223,7 @@
         <v>98.030115</v>
       </c>
       <c r="R65" s="9" t="n">
-        <v>97.58654799999999</v>
+        <v>97.58309199999999</v>
       </c>
       <c r="S65" s="9" t="n">
         <v>98.62342599999999</v>
@@ -5301,7 +5301,7 @@
         <v>97.64118499999999</v>
       </c>
       <c r="R66" s="6" t="n">
-        <v>97.272071</v>
+        <v>97.268163</v>
       </c>
       <c r="S66" s="6" t="n">
         <v>98.582815</v>
@@ -5379,7 +5379,7 @@
         <v>97.34372500000001</v>
       </c>
       <c r="R67" s="9" t="n">
-        <v>97.02912000000001</v>
+        <v>97.024863</v>
       </c>
       <c r="S67" s="9" t="n">
         <v>98.59373600000001</v>
@@ -5457,7 +5457,7 @@
         <v>97.154093</v>
       </c>
       <c r="R68" s="6" t="n">
-        <v>96.90107</v>
+        <v>96.89662800000001</v>
       </c>
       <c r="S68" s="6" t="n">
         <v>98.656718</v>
@@ -5535,7 +5535,7 @@
         <v>97.08219</v>
       </c>
       <c r="R69" s="9" t="n">
-        <v>96.918099</v>
+        <v>96.913681</v>
       </c>
       <c r="S69" s="9" t="n">
         <v>98.759541</v>
@@ -5613,7 +5613,7 @@
         <v>97.13481400000001</v>
       </c>
       <c r="R70" s="6" t="n">
-        <v>97.09395600000001</v>
+        <v>97.08978999999999</v>
       </c>
       <c r="S70" s="6" t="n">
         <v>98.885443</v>
@@ -5691,7 +5691,7 @@
         <v>97.339628</v>
       </c>
       <c r="R71" s="9" t="n">
-        <v>97.425248</v>
+        <v>97.42155700000001</v>
       </c>
       <c r="S71" s="9" t="n">
         <v>99.022081</v>
@@ -5769,7 +5769,7 @@
         <v>97.689345</v>
       </c>
       <c r="R72" s="6" t="n">
-        <v>97.886003</v>
+        <v>97.88297300000001</v>
       </c>
       <c r="S72" s="6" t="n">
         <v>99.162721</v>
@@ -5847,7 +5847,7 @@
         <v>98.13959199999999</v>
       </c>
       <c r="R73" s="9" t="n">
-        <v>98.40803200000001</v>
+        <v>98.40575200000001</v>
       </c>
       <c r="S73" s="9" t="n">
         <v>99.301509</v>
@@ -5925,7 +5925,7 @@
         <v>98.625198</v>
       </c>
       <c r="R74" s="6" t="n">
-        <v>98.889538</v>
+        <v>98.88794799999999</v>
       </c>
       <c r="S74" s="6" t="n">
         <v>99.434918</v>
@@ -6003,7 +6003,7 @@
         <v>99.080479</v>
       </c>
       <c r="R75" s="9" t="n">
-        <v>99.297634</v>
+        <v>99.29662999999999</v>
       </c>
       <c r="S75" s="9" t="n">
         <v>99.562859</v>
@@ -6081,7 +6081,7 @@
         <v>99.40909499999999</v>
       </c>
       <c r="R76" s="6" t="n">
-        <v>99.63561900000001</v>
+        <v>99.635099</v>
       </c>
       <c r="S76" s="6" t="n">
         <v>99.68895000000001</v>
@@ -6159,7 +6159,7 @@
         <v>99.563956</v>
       </c>
       <c r="R77" s="9" t="n">
-        <v>99.926952</v>
+        <v>99.92685</v>
       </c>
       <c r="S77" s="9" t="n">
         <v>99.81718100000001</v>
@@ -6239,7 +6239,7 @@
         <v>99.547978</v>
       </c>
       <c r="R78" s="6" t="n">
-        <v>100.200313</v>
+        <v>100.200603</v>
       </c>
       <c r="S78" s="6" t="n">
         <v>99.94744799999999</v>
@@ -6319,7 +6319,7 @@
         <v>99.368788</v>
       </c>
       <c r="R79" s="9" t="n">
-        <v>100.480278</v>
+        <v>100.48097</v>
       </c>
       <c r="S79" s="9" t="n">
         <v>100.078071</v>
@@ -6399,7 +6399,7 @@
         <v>99.105682</v>
       </c>
       <c r="R80" s="6" t="n">
-        <v>100.766848</v>
+        <v>100.767951</v>
       </c>
       <c r="S80" s="6" t="n">
         <v>100.211572</v>
@@ -6479,7 +6479,7 @@
         <v>98.87857099999999</v>
       </c>
       <c r="R81" s="9" t="n">
-        <v>101.051878</v>
+        <v>101.05339</v>
       </c>
       <c r="S81" s="9" t="n">
         <v>100.353576</v>
@@ -6559,7 +6559,7 @@
         <v>98.79418699999999</v>
       </c>
       <c r="R82" s="6" t="n">
-        <v>101.340214</v>
+        <v>101.34214</v>
       </c>
       <c r="S82" s="6" t="n">
         <v>100.510072</v>
@@ -6639,7 +6639,7 @@
         <v>98.897417</v>
       </c>
       <c r="R83" s="9" t="n">
-        <v>101.641237</v>
+        <v>101.643595</v>
       </c>
       <c r="S83" s="9" t="n">
         <v>100.685227</v>
@@ -6719,7 +6719,7 @@
         <v>99.205429</v>
       </c>
       <c r="R84" s="6" t="n">
-        <v>101.956728</v>
+        <v>101.959539</v>
       </c>
       <c r="S84" s="6" t="n">
         <v>100.877476</v>
@@ -6799,7 +6799,7 @@
         <v>99.691687</v>
       </c>
       <c r="R85" s="9" t="n">
-        <v>102.269787</v>
+        <v>102.273046</v>
       </c>
       <c r="S85" s="9" t="n">
         <v>101.076442</v>
@@ -6879,7 +6879,7 @@
         <v>100.324364</v>
       </c>
       <c r="R86" s="6" t="n">
-        <v>102.555633</v>
+        <v>102.559303</v>
       </c>
       <c r="S86" s="6" t="n">
         <v>101.270689</v>
@@ -6959,7 +6959,7 @@
         <v>101.050393</v>
       </c>
       <c r="R87" s="9" t="n">
-        <v>102.78546</v>
+        <v>102.789459</v>
       </c>
       <c r="S87" s="9" t="n">
         <v>101.447834</v>
@@ -7039,7 +7039,7 @@
         <v>101.834913</v>
       </c>
       <c r="R88" s="6" t="n">
-        <v>102.943042</v>
+        <v>102.947267</v>
       </c>
       <c r="S88" s="6" t="n">
         <v>101.596085</v>
@@ -7119,7 +7119,7 @@
         <v>102.673333</v>
       </c>
       <c r="R89" s="9" t="n">
-        <v>103.031257</v>
+        <v>103.035608</v>
       </c>
       <c r="S89" s="9" t="n">
         <v>101.708644</v>
@@ -7201,7 +7201,7 @@
         <v>103.573488</v>
       </c>
       <c r="R90" s="6" t="n">
-        <v>103.06476</v>
+        <v>103.06916</v>
       </c>
       <c r="S90" s="6" t="n">
         <v>101.785439</v>
@@ -7283,7 +7283,7 @@
         <v>104.502658</v>
       </c>
       <c r="R91" s="9" t="n">
-        <v>103.056789</v>
+        <v>103.061177</v>
       </c>
       <c r="S91" s="9" t="n">
         <v>101.830917</v>
@@ -7365,7 +7365,7 @@
         <v>105.396336</v>
       </c>
       <c r="R92" s="6" t="n">
-        <v>103.01117</v>
+        <v>103.015492</v>
       </c>
       <c r="S92" s="6" t="n">
         <v>101.852296</v>
@@ -7447,7 +7447,7 @@
         <v>106.187678</v>
       </c>
       <c r="R93" s="9" t="n">
-        <v>102.925817</v>
+        <v>102.930017</v>
       </c>
       <c r="S93" s="9" t="n">
         <v>101.859323</v>
@@ -7529,7 +7529,7 @@
         <v>106.804946</v>
       </c>
       <c r="R94" s="6" t="n">
-        <v>102.806465</v>
+        <v>102.810493</v>
       </c>
       <c r="S94" s="6" t="n">
         <v>101.865042</v>
@@ -7611,7 +7611,7 @@
         <v>107.168842</v>
       </c>
       <c r="R95" s="9" t="n">
-        <v>102.655164</v>
+        <v>102.658975</v>
       </c>
       <c r="S95" s="9" t="n">
         <v>101.885786</v>
@@ -7693,7 +7693,7 @@
         <v>107.177542</v>
       </c>
       <c r="R96" s="6" t="n">
-        <v>102.471786</v>
+        <v>102.475334</v>
       </c>
       <c r="S96" s="6" t="n">
         <v>101.939364</v>
@@ -7775,7 +7775,7 @@
         <v>106.691217</v>
       </c>
       <c r="R97" s="9" t="n">
-        <v>102.264885</v>
+        <v>102.268135</v>
       </c>
       <c r="S97" s="9" t="n">
         <v>102.042293</v>
@@ -7857,7 +7857,7 @@
         <v>105.655374</v>
       </c>
       <c r="R98" s="6" t="n">
-        <v>102.04272</v>
+        <v>102.045651</v>
       </c>
       <c r="S98" s="6" t="n">
         <v>102.205742</v>
@@ -7939,7 +7939,7 @@
         <v>104.204056</v>
       </c>
       <c r="R99" s="9" t="n">
-        <v>101.803778</v>
+        <v>101.806365</v>
       </c>
       <c r="S99" s="9" t="n">
         <v>102.428587</v>
@@ -8021,7 +8021,7 @@
         <v>102.619693</v>
       </c>
       <c r="R100" s="6" t="n">
-        <v>101.546291</v>
+        <v>101.548509</v>
       </c>
       <c r="S100" s="6" t="n">
         <v>102.684824</v>
@@ -8103,7 +8103,7 @@
         <v>101.24815</v>
       </c>
       <c r="R101" s="9" t="n">
-        <v>101.255835</v>
+        <v>101.257636</v>
       </c>
       <c r="S101" s="9" t="n">
         <v>102.908781</v>
@@ -8185,7 +8185,7 @@
         <v>100.252283</v>
       </c>
       <c r="R102" s="6" t="n">
-        <v>100.906186</v>
+        <v>100.907484</v>
       </c>
       <c r="S102" s="6" t="n">
         <v>102.990298</v>
@@ -8267,7 +8267,7 @@
         <v>99.581957</v>
       </c>
       <c r="R103" s="9" t="n">
-        <v>100.518501</v>
+        <v>100.519243</v>
       </c>
       <c r="S103" s="9" t="n">
         <v>102.811656</v>
@@ -8349,7 +8349,7 @@
         <v>99.102558</v>
       </c>
       <c r="R104" s="6" t="n">
-        <v>100.140638</v>
+        <v>100.140838</v>
       </c>
       <c r="S104" s="6" t="n">
         <v>102.310887</v>
@@ -8431,7 +8431,7 @@
         <v>98.779393</v>
       </c>
       <c r="R105" s="9" t="n">
-        <v>99.80798900000001</v>
+        <v>99.807711</v>
       </c>
       <c r="S105" s="9" t="n">
         <v>101.541136</v>
@@ -8513,7 +8513,7 @@
         <v>98.595113</v>
       </c>
       <c r="R106" s="6" t="n">
-        <v>99.54019</v>
+        <v>99.53952700000001</v>
       </c>
       <c r="S106" s="6" t="n">
         <v>100.653592</v>
@@ -8595,7 +8595,7 @@
         <v>98.47545</v>
       </c>
       <c r="R107" s="9" t="n">
-        <v>99.34128800000001</v>
+        <v>99.340339</v>
       </c>
       <c r="S107" s="9" t="n">
         <v>99.81284599999999</v>
@@ -8677,7 +8677,7 @@
         <v>98.38403700000001</v>
       </c>
       <c r="R108" s="6" t="n">
-        <v>99.206305</v>
+        <v>99.205163</v>
       </c>
       <c r="S108" s="6" t="n">
         <v>99.152238</v>
@@ -8759,7 +8759,7 @@
         <v>98.301102</v>
       </c>
       <c r="R109" s="9" t="n">
-        <v>99.12282399999999</v>
+        <v>99.121562</v>
       </c>
       <c r="S109" s="9" t="n">
         <v>98.738884</v>
@@ -8841,7 +8841,7 @@
         <v>98.210815</v>
       </c>
       <c r="R110" s="6" t="n">
-        <v>99.072012</v>
+        <v>99.070677</v>
       </c>
       <c r="S110" s="6" t="n">
         <v>98.57372599999999</v>
@@ -8923,7 +8923,7 @@
         <v>98.111315</v>
       </c>
       <c r="R111" s="9" t="n">
-        <v>99.035623</v>
+        <v>99.03423600000001</v>
       </c>
       <c r="S111" s="9" t="n">
         <v>98.620175</v>
@@ -9005,7 +9005,7 @@
         <v>98.00731399999999</v>
       </c>
       <c r="R112" s="6" t="n">
-        <v>99.00669600000001</v>
+        <v>99.005268</v>
       </c>
       <c r="S112" s="6" t="n">
         <v>98.82308999999999</v>
@@ -9087,7 +9087,7 @@
         <v>97.8986</v>
       </c>
       <c r="R113" s="9" t="n">
-        <v>98.993583</v>
+        <v>98.992135</v>
       </c>
       <c r="S113" s="9" t="n">
         <v>99.114014</v>
@@ -9169,7 +9169,7 @@
         <v>97.84594199999999</v>
       </c>
       <c r="R114" s="6" t="n">
-        <v>99.01441800000001</v>
+        <v>99.01300000000001</v>
       </c>
       <c r="S114" s="6" t="n">
         <v>99.41955299999999</v>
@@ -9251,7 +9251,7 @@
         <v>97.909565</v>
       </c>
       <c r="R115" s="9" t="n">
-        <v>99.082059</v>
+        <v>99.08073899999999</v>
       </c>
       <c r="S115" s="9" t="n">
         <v>99.682526</v>
@@ -9333,7 +9333,7 @@
         <v>98.12236</v>
       </c>
       <c r="R116" s="6" t="n">
-        <v>99.194333</v>
+        <v>99.193175</v>
       </c>
       <c r="S116" s="6" t="n">
         <v>99.87996200000001</v>
@@ -9415,7 +9415,7 @@
         <v>98.45903199999999</v>
       </c>
       <c r="R117" s="9" t="n">
-        <v>99.33959400000001</v>
+        <v>99.338644</v>
       </c>
       <c r="S117" s="9" t="n">
         <v>100.006665</v>
@@ -9497,7 +9497,7 @@
         <v>98.858795</v>
       </c>
       <c r="R118" s="6" t="n">
-        <v>99.504352</v>
+        <v>99.503638</v>
       </c>
       <c r="S118" s="6" t="n">
         <v>100.057558</v>
@@ -9579,7 +9579,7 @@
         <v>99.243855</v>
       </c>
       <c r="R119" s="9" t="n">
-        <v>99.67560400000001</v>
+        <v>99.67513599999999</v>
       </c>
       <c r="S119" s="9" t="n">
         <v>100.023353</v>
@@ -9661,7 +9661,7 @@
         <v>99.547873</v>
       </c>
       <c r="R120" s="6" t="n">
-        <v>99.841067</v>
+        <v>99.84083699999999</v>
       </c>
       <c r="S120" s="6" t="n">
         <v>99.91333</v>
@@ -9743,7 +9743,7 @@
         <v>99.743105</v>
       </c>
       <c r="R121" s="9" t="n">
-        <v>99.987183</v>
+        <v>99.987162</v>
       </c>
       <c r="S121" s="9" t="n">
         <v>99.787943</v>
@@ -9825,7 +9825,7 @@
         <v>99.80816900000001</v>
       </c>
       <c r="R122" s="6" t="n">
-        <v>100.100228</v>
+        <v>100.10037</v>
       </c>
       <c r="S122" s="6" t="n">
         <v>99.729377</v>
@@ -9907,7 +9907,7 @@
         <v>99.759891</v>
       </c>
       <c r="R123" s="9" t="n">
-        <v>100.167511</v>
+        <v>100.16775</v>
       </c>
       <c r="S123" s="9" t="n">
         <v>99.783062</v>
@@ -9989,7 +9989,7 @@
         <v>99.66616500000001</v>
       </c>
       <c r="R124" s="6" t="n">
-        <v>100.183978</v>
+        <v>100.184241</v>
       </c>
       <c r="S124" s="6" t="n">
         <v>99.93962000000001</v>
@@ -10071,7 +10071,7 @@
         <v>99.592478</v>
       </c>
       <c r="R125" s="9" t="n">
-        <v>100.156235</v>
+        <v>100.156458</v>
       </c>
       <c r="S125" s="9" t="n">
         <v>100.162625</v>
@@ -10153,7 +10153,7 @@
         <v>99.566244</v>
       </c>
       <c r="R126" s="6" t="n">
-        <v>100.10851</v>
+        <v>100.108665</v>
       </c>
       <c r="S126" s="6" t="n">
         <v>100.407201</v>
@@ -10235,7 +10235,7 @@
         <v>99.596484</v>
       </c>
       <c r="R127" s="9" t="n">
-        <v>100.06881</v>
+        <v>100.068908</v>
       </c>
       <c r="S127" s="9" t="n">
         <v>100.618369</v>
@@ -10317,7 +10317,7 @@
         <v>99.669134</v>
       </c>
       <c r="R128" s="6" t="n">
-        <v>100.050184</v>
+        <v>100.050255</v>
       </c>
       <c r="S128" s="6" t="n">
         <v>100.740657</v>
@@ -10399,7 +10399,7 @@
         <v>99.75263099999999</v>
       </c>
       <c r="R129" s="9" t="n">
-        <v>100.052977</v>
+        <v>100.053053</v>
       </c>
       <c r="S129" s="9" t="n">
         <v>100.736496</v>
@@ -10481,7 +10481,7 @@
         <v>99.78864299999999</v>
       </c>
       <c r="R130" s="6" t="n">
-        <v>100.072171</v>
+        <v>100.072275</v>
       </c>
       <c r="S130" s="6" t="n">
         <v>100.6053</v>
@@ -10563,7 +10563,7 @@
         <v>99.702939</v>
       </c>
       <c r="R131" s="9" t="n">
-        <v>100.101749</v>
+        <v>100.101896</v>
       </c>
       <c r="S131" s="9" t="n">
         <v>100.392492</v>
@@ -10645,7 +10645,7 @@
         <v>99.4948</v>
       </c>
       <c r="R132" s="6" t="n">
-        <v>100.134947</v>
+        <v>100.135142</v>
       </c>
       <c r="S132" s="6" t="n">
         <v>100.167307</v>
@@ -10727,7 +10727,7 @@
         <v>99.188939</v>
       </c>
       <c r="R133" s="9" t="n">
-        <v>100.161514</v>
+        <v>100.161747</v>
       </c>
       <c r="S133" s="9" t="n">
         <v>99.971177</v>
@@ -10809,7 +10809,7 @@
         <v>98.876188</v>
       </c>
       <c r="R134" s="6" t="n">
-        <v>100.165945</v>
+        <v>100.166184</v>
       </c>
       <c r="S134" s="6" t="n">
         <v>99.81801900000001</v>
@@ -10891,7 +10891,7 @@
         <v>98.634722</v>
       </c>
       <c r="R135" s="9" t="n">
-        <v>100.132803</v>
+        <v>100.132995</v>
       </c>
       <c r="S135" s="9" t="n">
         <v>99.694855</v>
@@ -10973,7 +10973,7 @@
         <v>98.47503</v>
       </c>
       <c r="R136" s="6" t="n">
-        <v>100.056433</v>
+        <v>100.056516</v>
       </c>
       <c r="S136" s="6" t="n">
         <v>99.578869</v>
@@ -11055,7 +11055,7 @@
         <v>98.421986</v>
       </c>
       <c r="R137" s="9" t="n">
-        <v>99.95031299999999</v>
+        <v>99.950244</v>
       </c>
       <c r="S137" s="9" t="n">
         <v>99.459264</v>
@@ -11137,7 +11137,7 @@
         <v>98.513313</v>
       </c>
       <c r="R138" s="6" t="n">
-        <v>99.839538</v>
+        <v>99.83931</v>
       </c>
       <c r="S138" s="6" t="n">
         <v>99.328357</v>
@@ -11219,7 +11219,7 @@
         <v>98.776439</v>
       </c>
       <c r="R139" s="9" t="n">
-        <v>99.744573</v>
+        <v>99.744209</v>
       </c>
       <c r="S139" s="9" t="n">
         <v>99.19355299999999</v>
@@ -11301,7 +11301,7 @@
         <v>99.191543</v>
       </c>
       <c r="R140" s="6" t="n">
-        <v>99.67737700000001</v>
+        <v>99.676918</v>
       </c>
       <c r="S140" s="6" t="n">
         <v>99.06552600000001</v>
@@ -11383,7 +11383,7 @@
         <v>99.68192000000001</v>
       </c>
       <c r="R141" s="9" t="n">
-        <v>99.640828</v>
+        <v>99.640317</v>
       </c>
       <c r="S141" s="9" t="n">
         <v>98.954261</v>
@@ -11465,7 +11465,7 @@
         <v>100.171197</v>
       </c>
       <c r="R142" s="6" t="n">
-        <v>99.62907</v>
+        <v>99.628542</v>
       </c>
       <c r="S142" s="6" t="n">
         <v>98.863564</v>
@@ -11547,7 +11547,7 @@
         <v>100.592804</v>
       </c>
       <c r="R143" s="9" t="n">
-        <v>99.630719</v>
+        <v>99.63019300000001</v>
       </c>
       <c r="S143" s="9" t="n">
         <v>98.795236</v>
@@ -11629,7 +11629,7 @@
         <v>100.943611</v>
       </c>
       <c r="R144" s="6" t="n">
-        <v>99.632086</v>
+        <v>99.631563</v>
       </c>
       <c r="S144" s="6" t="n">
         <v>98.753902</v>
@@ -11711,7 +11711,7 @@
         <v>101.218064</v>
       </c>
       <c r="R145" s="9" t="n">
-        <v>99.617853</v>
+        <v>99.61731</v>
       </c>
       <c r="S145" s="9" t="n">
         <v>98.736068</v>
@@ -11793,7 +11793,7 @@
         <v>101.432268</v>
       </c>
       <c r="R146" s="6" t="n">
-        <v>99.57256700000001</v>
+        <v>99.57196</v>
       </c>
       <c r="S146" s="6" t="n">
         <v>98.725235</v>
@@ -11875,7 +11875,7 @@
         <v>101.616774</v>
       </c>
       <c r="R147" s="9" t="n">
-        <v>99.486701</v>
+        <v>99.48596999999999</v>
       </c>
       <c r="S147" s="9" t="n">
         <v>98.69114500000001</v>
@@ -11957,7 +11957,7 @@
         <v>101.786734</v>
       </c>
       <c r="R148" s="6" t="n">
-        <v>99.36316600000001</v>
+        <v>99.36225899999999</v>
       </c>
       <c r="S148" s="6" t="n">
         <v>98.617823</v>
@@ -12039,7 +12039,7 @@
         <v>101.958917</v>
       </c>
       <c r="R149" s="9" t="n">
-        <v>99.220337</v>
+        <v>99.21922499999999</v>
       </c>
       <c r="S149" s="9" t="n">
         <v>98.50411699999999</v>
@@ -12121,7 +12121,7 @@
         <v>102.1217</v>
       </c>
       <c r="R150" s="6" t="n">
-        <v>99.083035</v>
+        <v>99.081727</v>
       </c>
       <c r="S150" s="6" t="n">
         <v>98.360353</v>
@@ -12203,7 +12203,7 @@
         <v>102.218751</v>
       </c>
       <c r="R151" s="9" t="n">
-        <v>98.970873</v>
+        <v>98.969404</v>
       </c>
       <c r="S151" s="9" t="n">
         <v>98.211007</v>
@@ -12285,7 +12285,7 @@
         <v>102.186018</v>
       </c>
       <c r="R152" s="6" t="n">
-        <v>98.892762</v>
+        <v>98.891181</v>
       </c>
       <c r="S152" s="6" t="n">
         <v>98.09096599999999</v>
@@ -12367,7 +12367,7 @@
         <v>102.00269</v>
       </c>
       <c r="R153" s="9" t="n">
-        <v>98.847004</v>
+        <v>98.845358</v>
       </c>
       <c r="S153" s="9" t="n">
         <v>98.045401</v>
@@ -12449,7 +12449,7 @@
         <v>101.6838</v>
       </c>
       <c r="R154" s="6" t="n">
-        <v>98.825093</v>
+        <v>98.82341700000001</v>
       </c>
       <c r="S154" s="6" t="n">
         <v>98.107512</v>
@@ -12531,7 +12531,7 @@
         <v>101.269436</v>
       </c>
       <c r="R155" s="9" t="n">
-        <v>98.81035300000001</v>
+        <v>98.808656</v>
       </c>
       <c r="S155" s="9" t="n">
         <v>98.28594699999999</v>
@@ -12613,7 +12613,7 @@
         <v>100.851591</v>
       </c>
       <c r="R156" s="6" t="n">
-        <v>98.787862</v>
+        <v>98.786134</v>
       </c>
       <c r="S156" s="6" t="n">
         <v>98.55988499999999</v>
@@ -12695,7 +12695,7 @@
         <v>100.502185</v>
       </c>
       <c r="R157" s="9" t="n">
-        <v>98.75145999999999</v>
+        <v>98.74968</v>
       </c>
       <c r="S157" s="9" t="n">
         <v>98.880629</v>
@@ -12777,7 +12777,7 @@
         <v>100.282203</v>
       </c>
       <c r="R158" s="6" t="n">
-        <v>98.702074</v>
+        <v>98.70022400000001</v>
       </c>
       <c r="S158" s="6" t="n">
         <v>99.201472</v>
@@ -12859,7 +12859,7 @@
         <v>100.195022</v>
       </c>
       <c r="R159" s="9" t="n">
-        <v>98.639105</v>
+        <v>98.637165</v>
       </c>
       <c r="S159" s="9" t="n">
         <v>99.487694</v>
@@ -12941,7 +12941,7 @@
         <v>100.161799</v>
       </c>
       <c r="R160" s="6" t="n">
-        <v>98.55705</v>
+        <v>98.554992</v>
       </c>
       <c r="S160" s="6" t="n">
         <v>99.70842500000001</v>
@@ -13023,7 +13023,7 @@
         <v>100.116782</v>
       </c>
       <c r="R161" s="9" t="n">
-        <v>98.459255</v>
+        <v>98.457059</v>
       </c>
       <c r="S161" s="9" t="n">
         <v>99.849761</v>
@@ -13105,7 +13105,7 @@
         <v>100.037315</v>
       </c>
       <c r="R162" s="6" t="n">
-        <v>98.357454</v>
+        <v>98.35511200000001</v>
       </c>
       <c r="S162" s="6" t="n">
         <v>99.900103</v>
@@ -13187,7 +13187,7 @@
         <v>99.94698200000001</v>
       </c>
       <c r="R163" s="9" t="n">
-        <v>98.262426</v>
+        <v>98.25994799999999</v>
       </c>
       <c r="S163" s="9" t="n">
         <v>99.85893900000001</v>
@@ -13269,7 +13269,7 @@
         <v>99.87546399999999</v>
       </c>
       <c r="R164" s="6" t="n">
-        <v>98.17930699999999</v>
+        <v>98.17671</v>
       </c>
       <c r="S164" s="6" t="n">
         <v>99.73560000000001</v>
@@ -13351,7 +13351,7 @@
         <v>99.819458</v>
       </c>
       <c r="R165" s="9" t="n">
-        <v>98.105729</v>
+        <v>98.103027</v>
       </c>
       <c r="S165" s="9" t="n">
         <v>99.552713</v>
@@ -13433,7 +13433,7 @@
         <v>99.812455</v>
       </c>
       <c r="R166" s="6" t="n">
-        <v>98.038326</v>
+        <v>98.035528</v>
       </c>
       <c r="S166" s="6" t="n">
         <v>99.331923</v>
@@ -13515,7 +13515,7 @@
         <v>99.88758900000001</v>
       </c>
       <c r="R167" s="9" t="n">
-        <v>97.969256</v>
+        <v>97.966359</v>
       </c>
       <c r="S167" s="9" t="n">
         <v>99.087048</v>
@@ -13597,7 +13597,7 @@
         <v>100.053334</v>
       </c>
       <c r="R168" s="6" t="n">
-        <v>97.896126</v>
+        <v>97.893126</v>
       </c>
       <c r="S168" s="6" t="n">
         <v>98.833032</v>
@@ -13679,7 +13679,7 @@
         <v>100.299538</v>
       </c>
       <c r="R169" s="9" t="n">
-        <v>97.82019699999999</v>
+        <v>97.817088</v>
       </c>
       <c r="S169" s="9" t="n">
         <v>98.58288</v>
@@ -13761,7 +13761,7 @@
         <v>100.609967</v>
       </c>
       <c r="R170" s="6" t="n">
-        <v>97.746363</v>
+        <v>97.74314800000001</v>
       </c>
       <c r="S170" s="6" t="n">
         <v>98.33849600000001</v>
@@ -13843,7 +13843,7 @@
         <v>100.977742</v>
       </c>
       <c r="R171" s="9" t="n">
-        <v>97.680449</v>
+        <v>97.67714100000001</v>
       </c>
       <c r="S171" s="9" t="n">
         <v>98.099064</v>
@@ -13925,7 +13925,7 @@
         <v>101.35703</v>
       </c>
       <c r="R172" s="6" t="n">
-        <v>97.626532</v>
+        <v>97.623147</v>
       </c>
       <c r="S172" s="6" t="n">
         <v>97.86205099999999</v>
@@ -14007,7 +14007,7 @@
         <v>101.681232</v>
       </c>
       <c r="R173" s="9" t="n">
-        <v>97.590146</v>
+        <v>97.58671099999999</v>
       </c>
       <c r="S173" s="9" t="n">
         <v>97.625705</v>
@@ -14089,7 +14089,7 @@
         <v>101.880053</v>
       </c>
       <c r="R174" s="6" t="n">
-        <v>97.591443</v>
+        <v>97.58801099999999</v>
       </c>
       <c r="S174" s="6" t="n">
         <v>97.43049600000001</v>
@@ -14171,7 +14171,7 @@
         <v>101.935921</v>
       </c>
       <c r="R175" s="9" t="n">
-        <v>97.638873</v>
+        <v>97.63551099999999</v>
       </c>
       <c r="S175" s="9" t="n">
         <v>97.32860700000001</v>
@@ -14253,7 +14253,7 @@
         <v>101.898863</v>
       </c>
       <c r="R176" s="6" t="n">
-        <v>97.720208</v>
+        <v>97.716966</v>
       </c>
       <c r="S176" s="6" t="n">
         <v>97.357901</v>
@@ -14335,7 +14335,7 @@
         <v>101.838443</v>
       </c>
       <c r="R177" s="9" t="n">
-        <v>97.795918</v>
+        <v>97.792788</v>
       </c>
       <c r="S177" s="9" t="n">
         <v>97.511008</v>
@@ -14417,7 +14417,7 @@
         <v>101.804212</v>
       </c>
       <c r="R178" s="6" t="n">
-        <v>97.851598</v>
+        <v>97.848551</v>
       </c>
       <c r="S178" s="6" t="n">
         <v>97.718675</v>
@@ -14499,7 +14499,7 @@
         <v>101.799311</v>
       </c>
       <c r="R179" s="9" t="n">
-        <v>97.908799</v>
+        <v>97.905834</v>
       </c>
       <c r="S179" s="9" t="n">
         <v>97.914546</v>
@@ -14581,7 +14581,7 @@
         <v>101.821652</v>
       </c>
       <c r="R180" s="6" t="n">
-        <v>97.999133</v>
+        <v>97.996295</v>
       </c>
       <c r="S180" s="6" t="n">
         <v>98.088756</v>
@@ -14663,7 +14663,7 @@
         <v>101.810471</v>
       </c>
       <c r="R181" s="9" t="n">
-        <v>98.171583</v>
+        <v>98.168981</v>
       </c>
       <c r="S181" s="9" t="n">
         <v>98.275819</v>
@@ -14745,7 +14745,7 @@
         <v>101.686913</v>
       </c>
       <c r="R182" s="6" t="n">
-        <v>98.494057</v>
+        <v>98.49189800000001</v>
       </c>
       <c r="S182" s="6" t="n">
         <v>98.554558</v>
@@ -14827,7 +14827,7 @@
         <v>101.401735</v>
       </c>
       <c r="R183" s="9" t="n">
-        <v>99.030894</v>
+        <v>99.029472</v>
       </c>
       <c r="S183" s="9" t="n">
         <v>99.01888099999999</v>
@@ -14909,7 +14909,7 @@
         <v>100.948521</v>
       </c>
       <c r="R184" s="6" t="n">
-        <v>99.816804</v>
+        <v>99.816462</v>
       </c>
       <c r="S184" s="6" t="n">
         <v>99.746393</v>
@@ -14991,7 +14991,7 @@
         <v>100.341827</v>
       </c>
       <c r="R185" s="9" t="n">
-        <v>100.815363</v>
+        <v>100.816395</v>
       </c>
       <c r="S185" s="9" t="n">
         <v>100.745591</v>
@@ -15073,7 +15073,7 @@
         <v>99.65503099999999</v>
       </c>
       <c r="R186" s="6" t="n">
-        <v>101.863362</v>
+        <v>101.865839</v>
       </c>
       <c r="S186" s="6" t="n">
         <v>101.911044</v>
@@ -15155,7 +15155,7 @@
         <v>99.012745</v>
       </c>
       <c r="R187" s="9" t="n">
-        <v>102.738096</v>
+        <v>102.741792</v>
       </c>
       <c r="S187" s="9" t="n">
         <v>103.026484</v>
@@ -15237,7 +15237,7 @@
         <v>98.55287300000001</v>
       </c>
       <c r="R188" s="6" t="n">
-        <v>103.273818</v>
+        <v>103.278275</v>
       </c>
       <c r="S188" s="6" t="n">
         <v>103.834805</v>
@@ -15319,7 +15319,7 @@
         <v>98.28936899999999</v>
       </c>
       <c r="R189" s="9" t="n">
-        <v>103.445088</v>
+        <v>103.449838</v>
       </c>
       <c r="S189" s="9" t="n">
         <v>104.171434</v>
@@ -15401,7 +15401,7 @@
         <v>98.20516499999999</v>
       </c>
       <c r="R190" s="6" t="n">
-        <v>103.356836</v>
+        <v>103.361523</v>
       </c>
       <c r="S190" s="6" t="n">
         <v>104.06311</v>
@@ -15483,7 +15483,7 @@
         <v>98.266819</v>
       </c>
       <c r="R191" s="9" t="n">
-        <v>103.168145</v>
+        <v>103.172622</v>
       </c>
       <c r="S191" s="9" t="n">
         <v>103.682887</v>
@@ -15565,7 +15565,7 @@
         <v>98.405205</v>
       </c>
       <c r="R192" s="6" t="n">
-        <v>102.986595</v>
+        <v>102.990858</v>
       </c>
       <c r="S192" s="6" t="n">
         <v>103.219509</v>
@@ -15647,7 +15647,7 @@
         <v>98.560407</v>
       </c>
       <c r="R193" s="9" t="n">
-        <v>102.894306</v>
+        <v>102.89847</v>
       </c>
       <c r="S193" s="9" t="n">
         <v>102.823776</v>
@@ -15729,7 +15729,7 @@
         <v>98.704069</v>
       </c>
       <c r="R194" s="6" t="n">
-        <v>102.919843</v>
+        <v>102.924063</v>
       </c>
       <c r="S194" s="6" t="n">
         <v>102.584616</v>
@@ -15811,7 +15811,7 @@
         <v>98.851658</v>
       </c>
       <c r="R195" s="9" t="n">
-        <v>103.035263</v>
+        <v>103.039657</v>
       </c>
       <c r="S195" s="9" t="n">
         <v>102.503083</v>
@@ -15893,7 +15893,7 @@
         <v>99.01506500000001</v>
       </c>
       <c r="R196" s="6" t="n">
-        <v>103.151231</v>
+        <v>103.155794</v>
       </c>
       <c r="S196" s="6" t="n">
         <v>102.485692</v>
@@ -15975,7 +15975,7 @@
         <v>99.161653</v>
       </c>
       <c r="R197" s="9" t="n">
-        <v>103.155249</v>
+        <v>103.159816</v>
       </c>
       <c r="S197" s="9" t="n">
         <v>102.422921</v>
@@ -16057,7 +16057,7 @@
         <v>99.274164</v>
       </c>
       <c r="R198" s="6" t="n">
-        <v>103.028527</v>
+        <v>103.03291</v>
       </c>
       <c r="S198" s="6" t="n">
         <v>102.267574</v>
@@ -16139,7 +16139,7 @@
         <v>99.34189000000001</v>
       </c>
       <c r="R199" s="9" t="n">
-        <v>102.806429</v>
+        <v>102.81049</v>
       </c>
       <c r="S199" s="9" t="n">
         <v>102.036322</v>
@@ -16221,7 +16221,7 @@
         <v>99.38236499999999</v>
       </c>
       <c r="R200" s="6" t="n">
-        <v>102.52797</v>
+        <v>102.531628</v>
       </c>
       <c r="S200" s="6" t="n">
         <v>101.746773</v>
@@ -16303,7 +16303,7 @@
         <v>99.388514</v>
       </c>
       <c r="R201" s="9" t="n">
-        <v>102.227779</v>
+        <v>102.231004</v>
       </c>
       <c r="S201" s="9" t="n">
         <v>101.409677</v>
@@ -16385,7 +16385,7 @@
         <v>99.35914200000001</v>
       </c>
       <c r="R202" s="6" t="n">
-        <v>101.946043</v>
+        <v>101.948862</v>
       </c>
       <c r="S202" s="6" t="n">
         <v>101.077262</v>
@@ -16467,7 +16467,7 @@
         <v>99.304597</v>
       </c>
       <c r="R203" s="9" t="n">
-        <v>101.705157</v>
+        <v>101.707628</v>
       </c>
       <c r="S203" s="9" t="n">
         <v>100.804428</v>
@@ -16549,7 +16549,7 @@
         <v>99.243746</v>
       </c>
       <c r="R204" s="6" t="n">
-        <v>101.504583</v>
+        <v>101.506765</v>
       </c>
       <c r="S204" s="6" t="n">
         <v>100.597947</v>
@@ -16631,7 +16631,7 @@
         <v>99.201599</v>
       </c>
       <c r="R205" s="9" t="n">
-        <v>101.336843</v>
+        <v>101.338783</v>
       </c>
       <c r="S205" s="9" t="n">
         <v>100.434376</v>
@@ -16713,7 +16713,7 @@
         <v>99.172445</v>
       </c>
       <c r="R206" s="6" t="n">
-        <v>101.19977</v>
+        <v>101.201514</v>
       </c>
       <c r="S206" s="6" t="n">
         <v>100.3185</v>
@@ -16795,7 +16795,7 @@
         <v>99.168077</v>
       </c>
       <c r="R207" s="9" t="n">
-        <v>101.078342</v>
+        <v>101.07991</v>
       </c>
       <c r="S207" s="9" t="n">
         <v>100.243819</v>
@@ -16877,7 +16877,7 @@
         <v>99.20153000000001</v>
       </c>
       <c r="R208" s="6" t="n">
-        <v>100.944957</v>
+        <v>100.946333</v>
       </c>
       <c r="S208" s="6" t="n">
         <v>100.166202</v>
@@ -16959,7 +16959,7 @@
         <v>99.27842800000001</v>
       </c>
       <c r="R209" s="9" t="n">
-        <v>100.778926</v>
+        <v>100.780063</v>
       </c>
       <c r="S209" s="9" t="n">
         <v>100.037684</v>
@@ -17041,7 +17041,7 @@
         <v>99.40097</v>
       </c>
       <c r="R210" s="6" t="n">
-        <v>100.596083</v>
+        <v>100.596957</v>
       </c>
       <c r="S210" s="6" t="n">
         <v>99.86107800000001</v>
@@ -17123,7 +17123,7 @@
         <v>99.558189</v>
       </c>
       <c r="R211" s="9" t="n">
-        <v>100.418932</v>
+        <v>100.419551</v>
       </c>
       <c r="S211" s="9" t="n">
         <v>99.670851</v>
@@ -17205,7 +17205,7 @@
         <v>99.74890499999999</v>
       </c>
       <c r="R212" s="6" t="n">
-        <v>100.258698</v>
+        <v>100.259086</v>
       </c>
       <c r="S212" s="6" t="n">
         <v>99.491225</v>
@@ -17287,7 +17287,7 @@
         <v>99.99078799999999</v>
       </c>
       <c r="R213" s="9" t="n">
-        <v>100.108117</v>
+        <v>100.108289</v>
       </c>
       <c r="S213" s="9" t="n">
         <v>99.326352</v>
@@ -17369,7 +17369,7 @@
         <v>100.288365</v>
       </c>
       <c r="R214" s="6" t="n">
-        <v>99.96768299999999</v>
+        <v>99.967652</v>
       </c>
       <c r="S214" s="6" t="n">
         <v>99.16921600000001</v>
@@ -17451,7 +17451,7 @@
         <v>100.612611</v>
       </c>
       <c r="R215" s="9" t="n">
-        <v>99.837991</v>
+        <v>99.837773</v>
       </c>
       <c r="S215" s="9" t="n">
         <v>99.016541</v>
@@ -17533,7 +17533,7 @@
         <v>100.905688</v>
       </c>
       <c r="R216" s="6" t="n">
-        <v>99.721152</v>
+        <v>99.720766</v>
       </c>
       <c r="S216" s="6" t="n">
         <v>98.883028</v>
@@ -17615,7 +17615,7 @@
         <v>101.116791</v>
       </c>
       <c r="R217" s="9" t="n">
-        <v>99.62923600000001</v>
+        <v>99.62871699999999</v>
       </c>
       <c r="S217" s="9" t="n">
         <v>98.79002199999999</v>
@@ -17697,7 +17697,7 @@
         <v>101.246742</v>
       </c>
       <c r="R218" s="6" t="n">
-        <v>99.577082</v>
+        <v>99.576487</v>
       </c>
       <c r="S218" s="6" t="n">
         <v>98.740363</v>
@@ -17779,7 +17779,7 @@
         <v>101.283169</v>
       </c>
       <c r="R219" s="9" t="n">
-        <v>99.568145</v>
+        <v>99.567537</v>
       </c>
       <c r="S219" s="9" t="n">
         <v>98.730909</v>
@@ -17861,7 +17861,7 @@
         <v>101.258569</v>
       </c>
       <c r="R220" s="6" t="n">
-        <v>99.588961</v>
+        <v>99.58838299999999</v>
       </c>
       <c r="S220" s="6" t="n">
         <v>98.751338</v>
@@ -17943,7 +17943,7 @@
         <v>101.1722</v>
       </c>
       <c r="R221" s="9" t="n">
-        <v>99.61055899999999</v>
+        <v>99.61001</v>
       </c>
       <c r="S221" s="9" t="n">
         <v>98.777614</v>
@@ -18025,7 +18025,7 @@
         <v>101.02376</v>
       </c>
       <c r="R222" s="6" t="n">
-        <v>99.644159</v>
+        <v>99.643659</v>
       </c>
       <c r="S222" s="6" t="n">
         <v>98.82121100000001</v>
@@ -18107,7 +18107,7 @@
         <v>100.840333</v>
       </c>
       <c r="R223" s="9" t="n">
-        <v>99.703934</v>
+        <v>99.703518</v>
       </c>
       <c r="S223" s="9" t="n">
         <v>98.89920600000001</v>
@@ -18189,7 +18189,7 @@
         <v>100.604448</v>
       </c>
       <c r="R224" s="6" t="n">
-        <v>99.791303</v>
+        <v>99.79101199999999</v>
       </c>
       <c r="S224" s="6" t="n">
         <v>99.02023199999999</v>
@@ -18271,7 +18271,7 @@
         <v>100.283975</v>
       </c>
       <c r="R225" s="9" t="n">
-        <v>99.918728</v>
+        <v>99.91862</v>
       </c>
       <c r="S225" s="9" t="n">
         <v>99.198268</v>
@@ -18353,7 +18353,7 @@
         <v>99.869523</v>
       </c>
       <c r="R226" s="6" t="n">
-        <v>100.105617</v>
+        <v>100.105777</v>
       </c>
       <c r="S226" s="6" t="n">
         <v>99.470151</v>
@@ -18435,7 +18435,7 @@
         <v>99.402458</v>
       </c>
       <c r="R227" s="9" t="n">
-        <v>100.354757</v>
+        <v>100.355274</v>
       </c>
       <c r="S227" s="9" t="n">
         <v>99.865422</v>
@@ -18517,7 +18517,7 @@
         <v>98.938182</v>
       </c>
       <c r="R228" s="6" t="n">
-        <v>100.643533</v>
+        <v>100.644464</v>
       </c>
       <c r="S228" s="6" t="n">
         <v>100.378304</v>
@@ -18599,7 +18599,7 @@
         <v>98.544387</v>
       </c>
       <c r="R229" s="9" t="n">
-        <v>100.941378</v>
+        <v>100.942736</v>
       </c>
       <c r="S229" s="9" t="n">
         <v>100.974132</v>
@@ -18681,7 +18681,7 @@
         <v>98.32563399999999</v>
       </c>
       <c r="R230" s="6" t="n">
-        <v>101.18414</v>
+        <v>101.185847</v>
       </c>
       <c r="S230" s="6" t="n">
         <v>101.564728</v>
@@ -18763,7 +18763,7 @@
         <v>98.259771</v>
       </c>
       <c r="R231" s="9" t="n">
-        <v>101.292468</v>
+        <v>101.29433</v>
       </c>
       <c r="S231" s="9" t="n">
         <v>102.035926</v>
@@ -18845,7 +18845,7 @@
         <v>98.300811</v>
       </c>
       <c r="R232" s="6" t="n">
-        <v>101.254237</v>
+        <v>101.256043</v>
       </c>
       <c r="S232" s="6" t="n">
         <v>102.319349</v>
@@ -18927,7 +18927,7 @@
         <v>98.447975</v>
       </c>
       <c r="R233" s="9" t="n">
-        <v>101.099846</v>
+        <v>101.10143</v>
       </c>
       <c r="S233" s="9" t="n">
         <v>102.405744</v>
@@ -19009,7 +19009,7 @@
         <v>98.69241</v>
       </c>
       <c r="R234" s="6" t="n">
-        <v>100.869682</v>
+        <v>100.870935</v>
       </c>
       <c r="S234" s="6" t="n">
         <v>102.298251</v>
@@ -19091,7 +19091,7 @@
         <v>99.020833</v>
       </c>
       <c r="R235" s="9" t="n">
-        <v>100.591827</v>
+        <v>100.592681</v>
       </c>
       <c r="S235" s="9" t="n">
         <v>102.033003</v>
@@ -19173,7 +19173,7 @@
         <v>99.38505000000001</v>
       </c>
       <c r="R236" s="6" t="n">
-        <v>100.29979</v>
+        <v>100.300224</v>
       </c>
       <c r="S236" s="6" t="n">
         <v>101.682654</v>
@@ -19255,7 +19255,7 @@
         <v>99.711415</v>
       </c>
       <c r="R237" s="9" t="n">
-        <v>100.031559</v>
+        <v>100.031607</v>
       </c>
       <c r="S237" s="9" t="n">
         <v>101.339005</v>
@@ -19337,7 +19337,7 @@
         <v>99.948601</v>
       </c>
       <c r="R238" s="6" t="n">
-        <v>99.818804</v>
+        <v>99.818547</v>
       </c>
       <c r="S238" s="6" t="n">
         <v>101.071708</v>
@@ -19419,7 +19419,7 @@
         <v>100.089997</v>
       </c>
       <c r="R239" s="9" t="n">
-        <v>99.668752</v>
+        <v>99.66828</v>
       </c>
       <c r="S239" s="9" t="n">
         <v>100.88887</v>
@@ -19501,7 +19501,7 @@
         <v>100.160072</v>
       </c>
       <c r="R240" s="6" t="n">
-        <v>99.56615499999999</v>
+        <v>99.565535</v>
       </c>
       <c r="S240" s="6" t="n">
         <v>100.762162</v>
@@ -19583,7 +19583,7 @@
         <v>100.234426</v>
       </c>
       <c r="R241" s="9" t="n">
-        <v>99.503038</v>
+        <v>99.50232699999999</v>
       </c>
       <c r="S241" s="9" t="n">
         <v>100.665094</v>
@@ -19665,7 +19665,7 @@
         <v>100.376299</v>
       </c>
       <c r="R242" s="6" t="n">
-        <v>99.46426599999999</v>
+        <v>99.463498</v>
       </c>
       <c r="S242" s="6" t="n">
         <v>100.562638</v>
@@ -19747,7 +19747,7 @@
         <v>100.61037</v>
       </c>
       <c r="R243" s="9" t="n">
-        <v>99.436999</v>
+        <v>99.43619200000001</v>
       </c>
       <c r="S243" s="9" t="n">
         <v>100.442934</v>
@@ -19829,7 +19829,7 @@
         <v>100.903624</v>
       </c>
       <c r="R244" s="6" t="n">
-        <v>99.404409</v>
+        <v>99.403555</v>
       </c>
       <c r="S244" s="6" t="n">
         <v>100.312228</v>
@@ -19911,7 +19911,7 @@
         <v>101.186066</v>
       </c>
       <c r="R245" s="9" t="n">
-        <v>99.371184</v>
+        <v>99.370283</v>
       </c>
       <c r="S245" s="9" t="n">
         <v>100.184046</v>
@@ -19993,7 +19993,7 @@
         <v>101.388481</v>
       </c>
       <c r="R246" s="6" t="n">
-        <v>99.345528</v>
+        <v>99.344589</v>
       </c>
       <c r="S246" s="6" t="n">
         <v>100.063027</v>
@@ -20075,7 +20075,7 @@
         <v>101.497208</v>
       </c>
       <c r="R247" s="9" t="n">
-        <v>99.333338</v>
+        <v>99.332381</v>
       </c>
       <c r="S247" s="9" t="n">
         <v>99.955853</v>
@@ -20157,7 +20157,7 @@
         <v>101.4896</v>
       </c>
       <c r="R248" s="6" t="n">
-        <v>99.340299</v>
+        <v>99.339353</v>
       </c>
       <c r="S248" s="6" t="n">
         <v>99.882992</v>
@@ -20239,7 +20239,7 @@
         <v>101.381479</v>
       </c>
       <c r="R249" s="9" t="n">
-        <v>99.368892</v>
+        <v>99.367986</v>
       </c>
       <c r="S249" s="9" t="n">
         <v>99.885125</v>
@@ -20321,7 +20321,7 @@
         <v>101.231909</v>
       </c>
       <c r="R250" s="6" t="n">
-        <v>99.40609499999999</v>
+        <v>99.405242</v>
       </c>
       <c r="S250" s="6" t="n">
         <v>99.979767</v>
@@ -20403,7 +20403,7 @@
         <v>101.084064</v>
       </c>
       <c r="R251" s="9" t="n">
-        <v>99.429134</v>
+        <v>99.428315</v>
       </c>
       <c r="S251" s="9" t="n">
         <v>100.141749</v>
@@ -20485,7 +20485,7 @@
         <v>100.915474</v>
       </c>
       <c r="R252" s="6" t="n">
-        <v>99.419318</v>
+        <v>99.41848400000001</v>
       </c>
       <c r="S252" s="6" t="n">
         <v>100.334889</v>
@@ -20567,7 +20567,7 @@
         <v>100.727109</v>
       </c>
       <c r="R253" s="9" t="n">
-        <v>99.398242</v>
+        <v>99.397378</v>
       </c>
       <c r="S253" s="9" t="n">
         <v>100.54455</v>
@@ -20649,7 +20649,7 @@
         <v>100.518045</v>
       </c>
       <c r="R254" s="6" t="n">
-        <v>99.39018</v>
+        <v>99.389304</v>
       </c>
       <c r="S254" s="6" t="n">
         <v>100.768819</v>
@@ -20731,7 +20731,7 @@
         <v>100.30751</v>
       </c>
       <c r="R255" s="9" t="n">
-        <v>99.39808600000001</v>
+        <v>99.397222</v>
       </c>
       <c r="S255" s="9" t="n">
         <v>100.994904</v>
@@ -20813,7 +20813,7 @@
         <v>100.117793</v>
       </c>
       <c r="R256" s="6" t="n">
-        <v>99.410833</v>
+        <v>99.409987</v>
       </c>
       <c r="S256" s="6" t="n">
         <v>101.194555</v>
@@ -20895,7 +20895,7 @@
         <v>99.989687</v>
       </c>
       <c r="R257" s="9" t="n">
-        <v>99.422613</v>
+        <v>99.421783</v>
       </c>
       <c r="S257" s="9" t="n">
         <v>101.330092</v>
@@ -20977,7 +20977,7 @@
         <v>99.924233</v>
       </c>
       <c r="R258" s="6" t="n">
-        <v>99.42576</v>
+        <v>99.424935</v>
       </c>
       <c r="S258" s="6" t="n">
         <v>101.376039</v>
@@ -21059,7 +21059,7 @@
         <v>99.884834</v>
       </c>
       <c r="R259" s="9" t="n">
-        <v>99.39037500000001</v>
+        <v>99.389499</v>
       </c>
       <c r="S259" s="9" t="n">
         <v>101.312041</v>
@@ -21141,7 +21141,7 @@
         <v>99.872373</v>
       </c>
       <c r="R260" s="6" t="n">
-        <v>99.307137</v>
+        <v>99.306141</v>
       </c>
       <c r="S260" s="6" t="n">
         <v>101.132584</v>
@@ -21223,7 +21223,7 @@
         <v>99.88702499999999</v>
       </c>
       <c r="R261" s="9" t="n">
-        <v>99.189998</v>
+        <v>99.188835</v>
       </c>
       <c r="S261" s="9" t="n">
         <v>100.848777</v>
@@ -21305,7 +21305,7 @@
         <v>99.89632899999999</v>
       </c>
       <c r="R262" s="6" t="n">
-        <v>99.07001099999999</v>
+        <v>99.068674</v>
       </c>
       <c r="S262" s="6" t="n">
         <v>100.490334</v>
@@ -21387,7 +21387,7 @@
         <v>99.85338900000001</v>
       </c>
       <c r="R263" s="9" t="n">
-        <v>98.97175900000001</v>
+        <v>98.970281</v>
       </c>
       <c r="S263" s="9" t="n">
         <v>100.112128</v>
@@ -21469,7 +21469,7 @@
         <v>99.74494900000001</v>
       </c>
       <c r="R264" s="6" t="n">
-        <v>98.900954</v>
+        <v>98.89937500000001</v>
       </c>
       <c r="S264" s="6" t="n">
         <v>99.76826699999999</v>
@@ -21551,7 +21551,7 @@
         <v>99.59680400000001</v>
       </c>
       <c r="R265" s="9" t="n">
-        <v>98.84665200000001</v>
+        <v>98.844995</v>
       </c>
       <c r="S265" s="9" t="n">
         <v>99.47092000000001</v>
@@ -21633,7 +21633,7 @@
         <v>99.46502599999999</v>
       </c>
       <c r="R266" s="6" t="n">
-        <v>98.795109</v>
+        <v>98.793378</v>
       </c>
       <c r="S266" s="6" t="n">
         <v>99.203928</v>
@@ -21715,7 +21715,7 @@
         <v>99.42721299999999</v>
       </c>
       <c r="R267" s="9" t="n">
-        <v>98.725313</v>
+        <v>98.72348100000001</v>
       </c>
       <c r="S267" s="9" t="n">
         <v>98.95337000000001</v>
@@ -21797,7 +21797,7 @@
         <v>99.501018</v>
       </c>
       <c r="R268" s="6" t="n">
-        <v>98.640336</v>
+        <v>98.638383</v>
       </c>
       <c r="S268" s="6" t="n">
         <v>98.72768000000001</v>
@@ -21879,7 +21879,7 @@
         <v>99.654714</v>
       </c>
       <c r="R269" s="9" t="n">
-        <v>98.562673</v>
+        <v>98.560608</v>
       </c>
       <c r="S269" s="9" t="n">
         <v>98.560407</v>
@@ -21961,7 +21961,7 @@
         <v>99.82478999999999</v>
       </c>
       <c r="R270" s="6" t="n">
-        <v>98.517076</v>
+        <v>98.514945</v>
       </c>
       <c r="S270" s="6" t="n">
         <v>98.474076</v>
@@ -22043,7 +22043,7 @@
         <v>99.94842800000001</v>
       </c>
       <c r="R271" s="9" t="n">
-        <v>98.524092</v>
+        <v>98.52197200000001</v>
       </c>
       <c r="S271" s="9" t="n">
         <v>98.454042</v>
@@ -22125,7 +22125,7 @@
         <v>99.987815</v>
       </c>
       <c r="R272" s="6" t="n">
-        <v>98.595952</v>
+        <v>98.593935</v>
       </c>
       <c r="S272" s="6" t="n">
         <v>98.46351300000001</v>
@@ -22207,7 +22207,7 @@
         <v>99.902776</v>
       </c>
       <c r="R273" s="9" t="n">
-        <v>98.73514299999999</v>
+        <v>98.73332600000001</v>
       </c>
       <c r="S273" s="9" t="n">
         <v>98.500258</v>
@@ -22289,7 +22289,7 @@
         <v>99.689179</v>
       </c>
       <c r="R274" s="6" t="n">
-        <v>98.926821</v>
+        <v>98.925279</v>
       </c>
       <c r="S274" s="6" t="n">
         <v>98.57915300000001</v>
@@ -22371,7 +22371,7 @@
         <v>99.386658</v>
       </c>
       <c r="R275" s="9" t="n">
-        <v>99.136111</v>
+        <v>99.13486899999999</v>
       </c>
       <c r="S275" s="9" t="n">
         <v>98.696242</v>
@@ -22453,7 +22453,7 @@
         <v>99.055346</v>
       </c>
       <c r="R276" s="6" t="n">
-        <v>99.336586</v>
+        <v>99.335632</v>
       </c>
       <c r="S276" s="6" t="n">
         <v>98.833429</v>
@@ -22535,7 +22535,7 @@
         <v>98.74503199999999</v>
       </c>
       <c r="R277" s="9" t="n">
-        <v>99.520489</v>
+        <v>99.5198</v>
       </c>
       <c r="S277" s="9" t="n">
         <v>98.990754</v>
@@ -22617,7 +22617,7 @@
         <v>98.474896</v>
       </c>
       <c r="R278" s="6" t="n">
-        <v>99.689502</v>
+        <v>99.689054</v>
       </c>
       <c r="S278" s="6" t="n">
         <v>99.179085</v>
@@ -22699,7 +22699,7 @@
         <v>98.265843</v>
       </c>
       <c r="R279" s="9" t="n">
-        <v>99.844058</v>
+        <v>99.843833</v>
       </c>
       <c r="S279" s="9" t="n">
         <v>99.378407</v>
@@ -22781,7 +22781,7 @@
         <v>98.10758300000001</v>
       </c>
       <c r="R280" s="6" t="n">
-        <v>99.99127799999999</v>
+        <v>99.991264</v>
       </c>
       <c r="S280" s="6" t="n">
         <v>99.568309</v>
@@ -22863,7 +22863,7 @@
         <v>97.987791</v>
       </c>
       <c r="R281" s="9" t="n">
-        <v>100.137039</v>
+        <v>100.137234</v>
       </c>
       <c r="S281" s="9" t="n">
         <v>99.73353</v>
@@ -22945,7 +22945,7 @@
         <v>97.910194</v>
       </c>
       <c r="R282" s="6" t="n">
-        <v>100.277755</v>
+        <v>100.278153</v>
       </c>
       <c r="S282" s="6" t="n">
         <v>99.83994300000001</v>
@@ -23027,7 +23027,7 @@
         <v>97.892291</v>
       </c>
       <c r="R283" s="9" t="n">
-        <v>100.381355</v>
+        <v>100.381901</v>
       </c>
       <c r="S283" s="9" t="n">
         <v>99.824724</v>
@@ -23109,7 +23109,7 @@
         <v>97.947221</v>
       </c>
       <c r="R284" s="6" t="n">
-        <v>100.418961</v>
+        <v>100.419561</v>
       </c>
       <c r="S284" s="6" t="n">
         <v>99.63433999999999</v>
@@ -23191,7 +23191,7 @@
         <v>98.074657</v>
       </c>
       <c r="R285" s="9" t="n">
-        <v>100.399905</v>
+        <v>100.400477</v>
       </c>
       <c r="S285" s="9" t="n">
         <v>99.262945</v>
@@ -23273,7 +23273,7 @@
         <v>98.245626</v>
       </c>
       <c r="R286" s="6" t="n">
-        <v>100.370286</v>
+        <v>100.370816</v>
       </c>
       <c r="S286" s="6" t="n">
         <v>98.772841</v>
@@ -23355,7 +23355,7 @@
         <v>98.437054</v>
       </c>
       <c r="R287" s="9" t="n">
-        <v>100.375719</v>
+        <v>100.376257</v>
       </c>
       <c r="S287" s="9" t="n">
         <v>98.26613999999999</v>
@@ -23437,7 +23437,7 @@
         <v>98.62946100000001</v>
       </c>
       <c r="R288" s="6" t="n">
-        <v>100.422529</v>
+        <v>100.423134</v>
       </c>
       <c r="S288" s="6" t="n">
         <v>97.836163</v>
@@ -23519,7 +23519,7 @@
         <v>98.813169</v>
       </c>
       <c r="R289" s="9" t="n">
-        <v>100.50435</v>
+        <v>100.505072</v>
       </c>
       <c r="S289" s="9" t="n">
         <v>97.53900899999999</v>
@@ -23601,7 +23601,7 @@
         <v>98.988463</v>
       </c>
       <c r="R290" s="6" t="n">
-        <v>100.591596</v>
+        <v>100.592444</v>
       </c>
       <c r="S290" s="6" t="n">
         <v>97.393039</v>
@@ -23683,7 +23683,7 @@
         <v>99.159947</v>
       </c>
       <c r="R291" s="9" t="n">
-        <v>100.657242</v>
+        <v>100.658184</v>
       </c>
       <c r="S291" s="9" t="n">
         <v>97.37823400000001</v>
@@ -23765,7 +23765,7 @@
         <v>99.328834</v>
       </c>
       <c r="R292" s="6" t="n">
-        <v>100.686946</v>
+        <v>100.687931</v>
       </c>
       <c r="S292" s="6" t="n">
         <v>97.45654500000001</v>
@@ -23847,7 +23847,7 @@
         <v>99.486807</v>
       </c>
       <c r="R293" s="9" t="n">
-        <v>100.693993</v>
+        <v>100.694988</v>
       </c>
       <c r="S293" s="9" t="n">
         <v>97.617519</v>
@@ -23931,7 +23931,7 @@
         <v>99.622676</v>
       </c>
       <c r="R294" s="6" t="n">
-        <v>100.697571</v>
+        <v>100.698571</v>
       </c>
       <c r="S294" s="6" t="n">
         <v>97.857501</v>
@@ -24015,7 +24015,7 @@
         <v>99.715018</v>
       </c>
       <c r="R295" s="9" t="n">
-        <v>100.730465</v>
+        <v>100.731512</v>
       </c>
       <c r="S295" s="9" t="n">
         <v>98.15657299999999</v>
@@ -24099,7 +24099,7 @@
         <v>99.747649</v>
       </c>
       <c r="R296" s="6" t="n">
-        <v>100.801992</v>
+        <v>100.803142</v>
       </c>
       <c r="S296" s="6" t="n">
         <v>98.47907499999999</v>
@@ -24183,7 +24183,7 @@
         <v>99.72198299999999</v>
       </c>
       <c r="R297" s="9" t="n">
-        <v>100.902695</v>
+        <v>100.90399</v>
       </c>
       <c r="S297" s="9" t="n">
         <v>98.78541300000001</v>
@@ -24267,7 +24267,7 @@
         <v>99.67129300000001</v>
       </c>
       <c r="R298" s="6" t="n">
-        <v>101.000309</v>
+        <v>101.001744</v>
       </c>
       <c r="S298" s="6" t="n">
         <v>99.05676</v>
@@ -24351,7 +24351,7 @@
         <v>99.622631</v>
       </c>
       <c r="R299" s="9" t="n">
-        <v>101.059867</v>
+        <v>101.061387</v>
       </c>
       <c r="S299" s="9" t="n">
         <v>99.297982</v>
@@ -24435,7 +24435,7 @@
         <v>99.597172</v>
       </c>
       <c r="R300" s="6" t="n">
-        <v>101.07148</v>
+        <v>101.073016</v>
       </c>
       <c r="S300" s="6" t="n">
         <v>99.524608</v>
@@ -24519,7 +24519,7 @@
         <v>99.61633399999999</v>
       </c>
       <c r="R301" s="9" t="n">
-        <v>101.033582</v>
+        <v>101.035064</v>
       </c>
       <c r="S301" s="9" t="n">
         <v>99.75129099999999</v>
@@ -24603,7 +24603,7 @@
         <v>99.68388299999999</v>
       </c>
       <c r="R302" s="6" t="n">
-        <v>100.956345</v>
+        <v>100.957717</v>
       </c>
       <c r="S302" s="6" t="n">
         <v>99.98224399999999</v>
@@ -24687,7 +24687,7 @@
         <v>99.779341</v>
       </c>
       <c r="R303" s="9" t="n">
-        <v>100.84879</v>
+        <v>100.850007</v>
       </c>
       <c r="S303" s="9" t="n">
         <v>100.217796</v>
@@ -24771,7 +24771,7 @@
         <v>99.874002</v>
       </c>
       <c r="R304" s="6" t="n">
-        <v>100.72533</v>
+        <v>100.72637</v>
       </c>
       <c r="S304" s="6" t="n">
         <v>100.453819</v>
@@ -24855,7 +24855,7 @@
         <v>99.939441</v>
       </c>
       <c r="R305" s="9" t="n">
-        <v>100.601157</v>
+        <v>100.602018</v>
       </c>
       <c r="S305" s="9" t="n">
         <v>100.679715</v>
@@ -24939,7 +24939,7 @@
         <v>99.95064499999999</v>
       </c>
       <c r="R306" s="6" t="n">
-        <v>100.491863</v>
+        <v>100.492567</v>
       </c>
       <c r="S306" s="6" t="n">
         <v>100.889033</v>
@@ -25023,7 +25023,7 @@
         <v>99.90521699999999</v>
       </c>
       <c r="R307" s="9" t="n">
-        <v>100.396171</v>
+        <v>100.396738</v>
       </c>
       <c r="S307" s="9" t="n">
         <v>101.079378</v>
@@ -25107,7 +25107,7 @@
         <v>99.81991600000001</v>
       </c>
       <c r="R308" s="6" t="n">
-        <v>100.309908</v>
+        <v>100.310351</v>
       </c>
       <c r="S308" s="6" t="n">
         <v>101.240183</v>
@@ -25191,7 +25191,7 @@
         <v>99.749734</v>
       </c>
       <c r="R309" s="9" t="n">
-        <v>100.224091</v>
+        <v>100.224411</v>
       </c>
       <c r="S309" s="9" t="n">
         <v>101.361658</v>
@@ -25275,7 +25275,7 @@
         <v>99.736369</v>
       </c>
       <c r="R310" s="6" t="n">
-        <v>100.132397</v>
+        <v>100.132585</v>
       </c>
       <c r="S310" s="6" t="n">
         <v>101.43702</v>
@@ -25359,7 +25359,7 @@
         <v>99.786074</v>
       </c>
       <c r="R311" s="9" t="n">
-        <v>100.039605</v>
+        <v>100.03966</v>
       </c>
       <c r="S311" s="9" t="n">
         <v>101.463916</v>
@@ -25443,7 +25443,7 @@
         <v>99.889132</v>
       </c>
       <c r="R312" s="6" t="n">
-        <v>99.955387</v>
+        <v>99.955321</v>
       </c>
       <c r="S312" s="6" t="n">
         <v>101.444212</v>
@@ -25527,7 +25527,7 @@
         <v>100.027922</v>
       </c>
       <c r="R313" s="9" t="n">
-        <v>99.885068</v>
+        <v>99.8849</v>
       </c>
       <c r="S313" s="9" t="n">
         <v>101.378512</v>
@@ -25611,7 +25611,7 @@
         <v>100.192958</v>
       </c>
       <c r="R314" s="6" t="n">
-        <v>99.820503</v>
+        <v>99.820243</v>
       </c>
       <c r="S314" s="6" t="n">
         <v>101.268374</v>
@@ -25695,7 +25695,7 @@
         <v>100.356063</v>
       </c>
       <c r="R315" s="9" t="n">
-        <v>99.746527</v>
+        <v>99.746161</v>
       </c>
       <c r="S315" s="9" t="n">
         <v>101.120625</v>
@@ -25779,7 +25779,7 @@
         <v>100.512894</v>
       </c>
       <c r="R316" s="6" t="n">
-        <v>99.666077</v>
+        <v>99.66559599999999</v>
       </c>
       <c r="S316" s="6" t="n">
         <v>100.942636</v>
@@ -25863,7 +25863,7 @@
         <v>100.647925</v>
       </c>
       <c r="R317" s="9" t="n">
-        <v>99.61009900000001</v>
+        <v>99.609537</v>
       </c>
       <c r="S317" s="9" t="n">
         <v>100.743675</v>
@@ -25947,7 +25947,7 @@
         <v>100.74486</v>
       </c>
       <c r="R318" s="6" t="n">
-        <v>99.610108</v>
+        <v>99.60954599999999</v>
       </c>
       <c r="S318" s="6" t="n">
         <v>100.538188</v>
@@ -26031,7 +26031,7 @@
         <v>100.794097</v>
       </c>
       <c r="R319" s="9" t="n">
-        <v>99.681774</v>
+        <v>99.681315</v>
       </c>
       <c r="S319" s="9" t="n">
         <v>100.340822</v>
@@ -26115,7 +26115,7 @@
         <v>100.805363</v>
       </c>
       <c r="R320" s="6" t="n">
-        <v>99.82058499999999</v>
+        <v>99.820325</v>
       </c>
       <c r="S320" s="6" t="n">
         <v>100.167576</v>
@@ -26199,7 +26199,7 @@
         <v>100.78816</v>
       </c>
       <c r="R321" s="9" t="n">
-        <v>99.98728</v>
+        <v>99.98725899999999</v>
       </c>
       <c r="S321" s="9" t="n">
         <v>100.029393</v>
@@ -26283,7 +26283,7 @@
         <v>100.756958</v>
       </c>
       <c r="R322" s="6" t="n">
-        <v>100.12685</v>
+        <v>100.127029</v>
       </c>
       <c r="S322" s="6" t="n">
         <v>99.930706</v>
@@ -26367,7 +26367,7 @@
         <v>100.759405</v>
       </c>
       <c r="R323" s="9" t="n">
-        <v>100.197057</v>
+        <v>100.197338</v>
       </c>
       <c r="S323" s="9" t="n">
         <v>99.871368</v>
@@ -26451,7 +26451,7 @@
         <v>100.818129</v>
       </c>
       <c r="R324" s="6" t="n">
-        <v>100.174371</v>
+        <v>100.174619</v>
       </c>
       <c r="S324" s="6" t="n">
         <v>99.84447299999999</v>
@@ -26535,7 +26535,7 @@
         <v>100.934531</v>
       </c>
       <c r="R325" s="9" t="n">
-        <v>100.081647</v>
+        <v>100.081762</v>
       </c>
       <c r="S325" s="9" t="n">
         <v>99.842192</v>
@@ -26619,7 +26619,7 @@
         <v>101.100335</v>
       </c>
       <c r="R326" s="6" t="n">
-        <v>99.952215</v>
+        <v>99.952144</v>
       </c>
       <c r="S326" s="6" t="n">
         <v>99.85766700000001</v>
@@ -26703,7 +26703,7 @@
         <v>101.302836</v>
       </c>
       <c r="R327" s="9" t="n">
-        <v>99.81625</v>
+        <v>99.815983</v>
       </c>
       <c r="S327" s="9" t="n">
         <v>99.885735</v>
@@ -26787,7 +26787,7 @@
         <v>101.52142</v>
       </c>
       <c r="R328" s="6" t="n">
-        <v>99.70243000000001</v>
+        <v>99.702</v>
       </c>
       <c r="S328" s="6" t="n">
         <v>99.92352099999999</v>
@@ -26871,7 +26871,7 @@
         <v>101.729009</v>
       </c>
       <c r="R329" s="9" t="n">
-        <v>99.63011</v>
+        <v>99.629576</v>
       </c>
       <c r="S329" s="9" t="n">
         <v>99.969624</v>
@@ -26955,7 +26955,7 @@
         <v>101.908443</v>
       </c>
       <c r="R330" s="6" t="n">
-        <v>99.60608000000001</v>
+        <v>99.605512</v>
       </c>
       <c r="S330" s="6" t="n">
         <v>100.022125</v>
@@ -27039,7 +27039,7 @@
         <v>102.057768</v>
       </c>
       <c r="R331" s="9" t="n">
-        <v>99.62086499999999</v>
+        <v>99.620318</v>
       </c>
       <c r="S331" s="9" t="n">
         <v>100.078775</v>
@@ -27123,7 +27123,7 @@
         <v>102.189177</v>
       </c>
       <c r="R332" s="6" t="n">
-        <v>99.654573</v>
+        <v>99.65407399999999</v>
       </c>
       <c r="S332" s="6" t="n">
         <v>100.1384</v>
@@ -27207,7 +27207,7 @@
         <v>102.29119</v>
       </c>
       <c r="R333" s="9" t="n">
-        <v>99.683598</v>
+        <v>99.68314100000001</v>
       </c>
       <c r="S333" s="9" t="n">
         <v>100.20097</v>
@@ -27291,7 +27291,7 @@
         <v>102.351854</v>
       </c>
       <c r="R334" s="6" t="n">
-        <v>99.699654</v>
+        <v>99.69922</v>
       </c>
       <c r="S334" s="6" t="n">
         <v>100.264833</v>
@@ -27375,7 +27375,7 @@
         <v>102.349492</v>
       </c>
       <c r="R335" s="9" t="n">
-        <v>99.70114</v>
+        <v>99.70070800000001</v>
       </c>
       <c r="S335" s="9" t="n">
         <v>100.324352</v>
@@ -27459,7 +27459,7 @@
         <v>102.287051</v>
       </c>
       <c r="R336" s="6" t="n">
-        <v>99.686604</v>
+        <v>99.68615200000001</v>
       </c>
       <c r="S336" s="6" t="n">
         <v>100.379101</v>
@@ -27543,7 +27543,7 @@
         <v>102.180954</v>
       </c>
       <c r="R337" s="9" t="n">
-        <v>99.65498700000001</v>
+        <v>99.654489</v>
       </c>
       <c r="S337" s="9" t="n">
         <v>100.431334</v>
@@ -27627,7 +27627,7 @@
         <v>102.048578</v>
       </c>
       <c r="R338" s="6" t="n">
-        <v>99.59654500000001</v>
+        <v>99.595963</v>
       </c>
       <c r="S338" s="6" t="n">
         <v>100.48389</v>
@@ -27711,7 +27711,7 @@
         <v>101.902235</v>
       </c>
       <c r="R339" s="9" t="n">
-        <v>99.51276799999999</v>
+        <v>99.512066</v>
       </c>
       <c r="S339" s="9" t="n">
         <v>100.538877</v>
@@ -27795,7 +27795,7 @@
         <v>101.747865</v>
       </c>
       <c r="R340" s="6" t="n">
-        <v>99.414777</v>
+        <v>99.413935</v>
       </c>
       <c r="S340" s="6" t="n">
         <v>100.595386</v>
@@ -27879,7 +27879,7 @@
         <v>101.608141</v>
       </c>
       <c r="R341" s="9" t="n">
-        <v>99.304884</v>
+        <v>99.303883</v>
       </c>
       <c r="S341" s="9" t="n">
         <v>100.649194</v>
@@ -27963,7 +27963,7 @@
         <v>101.494852</v>
       </c>
       <c r="R342" s="6" t="n">
-        <v>99.183913</v>
+        <v>99.182739</v>
       </c>
       <c r="S342" s="6" t="n">
         <v>100.701102</v>
@@ -28047,7 +28047,7 @@
         <v>101.407383</v>
       </c>
       <c r="R343" s="9" t="n">
-        <v>99.050804</v>
+        <v>99.04943900000001</v>
       </c>
       <c r="S343" s="9" t="n">
         <v>100.755363</v>
@@ -28131,7 +28131,7 @@
         <v>101.319775</v>
       </c>
       <c r="R344" s="6" t="n">
-        <v>98.917841</v>
+        <v>98.916285</v>
       </c>
       <c r="S344" s="6" t="n">
         <v>100.818336</v>
@@ -28215,7 +28215,7 @@
         <v>101.183008</v>
       </c>
       <c r="R345" s="9" t="n">
-        <v>98.804445</v>
+        <v>98.80272600000001</v>
       </c>
       <c r="S345" s="9" t="n">
         <v>100.89708</v>
@@ -28299,7 +28299,7 @@
         <v>100.958679</v>
       </c>
       <c r="R346" s="6" t="n">
-        <v>98.742493</v>
+        <v>98.740685</v>
       </c>
       <c r="S346" s="6" t="n">
         <v>100.997417</v>
@@ -28383,7 +28383,7 @@
         <v>100.612148</v>
       </c>
       <c r="R347" s="9" t="n">
-        <v>98.765486</v>
+        <v>98.763712</v>
       </c>
       <c r="S347" s="9" t="n">
         <v>101.121468</v>
@@ -28467,7 +28467,7 @@
         <v>100.154233</v>
       </c>
       <c r="R348" s="6" t="n">
-        <v>98.914593</v>
+        <v>98.913034</v>
       </c>
       <c r="S348" s="6" t="n">
         <v>101.262736</v>
@@ -28551,7 +28551,7 @@
         <v>99.61464599999999</v>
       </c>
       <c r="R349" s="9" t="n">
-        <v>99.22901400000001</v>
+        <v>99.227906</v>
       </c>
       <c r="S349" s="9" t="n">
         <v>101.403596</v>
@@ -28635,7 +28635,7 @@
         <v>99.032206</v>
       </c>
       <c r="R350" s="6" t="n">
-        <v>99.72358</v>
+        <v>99.72318199999999</v>
       </c>
       <c r="S350" s="6" t="n">
         <v>101.521885</v>
@@ -28719,7 +28719,7 @@
         <v>98.462525</v>
       </c>
       <c r="R351" s="9" t="n">
-        <v>100.337008</v>
+        <v>100.337491</v>
       </c>
       <c r="S351" s="9" t="n">
         <v>101.597157</v>
@@ -28803,7 +28803,7 @@
         <v>97.983074</v>
       </c>
       <c r="R352" s="6" t="n">
-        <v>100.940035</v>
+        <v>100.941385</v>
       </c>
       <c r="S352" s="6" t="n">
         <v>101.610018</v>
@@ -28887,7 +28887,7 @@
         <v>97.621279</v>
       </c>
       <c r="R353" s="9" t="n">
-        <v>101.461672</v>
+        <v>101.463771</v>
       </c>
       <c r="S353" s="9" t="n">
         <v>101.540913</v>
@@ -28971,7 +28971,7 @@
         <v>97.381711</v>
       </c>
       <c r="R354" s="6" t="n">
-        <v>101.862679</v>
+        <v>101.865353</v>
       </c>
       <c r="S354" s="6" t="n">
         <v>101.374872</v>
@@ -29055,7 +29055,7 @@
         <v>97.311139</v>
       </c>
       <c r="R355" s="9" t="n">
-        <v>102.104454</v>
+        <v>102.107476</v>
       </c>
       <c r="S355" s="9" t="n">
         <v>101.110374</v>
@@ -29139,7 +29139,7 @@
         <v>97.438971</v>
       </c>
       <c r="R356" s="6" t="n">
-        <v>102.162162</v>
+        <v>102.165267</v>
       </c>
       <c r="S356" s="6" t="n">
         <v>100.759431</v>
@@ -29223,7 +29223,7 @@
         <v>97.725639</v>
       </c>
       <c r="R357" s="9" t="n">
-        <v>102.064212</v>
+        <v>102.067177</v>
       </c>
       <c r="S357" s="9" t="n">
         <v>100.347208</v>
@@ -29307,7 +29307,7 @@
         <v>98.100995</v>
       </c>
       <c r="R358" s="6" t="n">
-        <v>101.900981</v>
+        <v>101.903712</v>
       </c>
       <c r="S358" s="6" t="n">
         <v>99.925511</v>
@@ -29391,7 +29391,7 @@
         <v>98.497455</v>
       </c>
       <c r="R359" s="9" t="n">
-        <v>101.72755</v>
+        <v>101.730033</v>
       </c>
       <c r="S359" s="9" t="n">
         <v>99.55247300000001</v>
@@ -29475,7 +29475,7 @@
         <v>98.87802600000001</v>
       </c>
       <c r="R360" s="6" t="n">
-        <v>101.557888</v>
+        <v>101.560128</v>
       </c>
       <c r="S360" s="6" t="n">
         <v>99.26881299999999</v>
@@ -29559,7 +29559,7 @@
         <v>99.204551</v>
       </c>
       <c r="R361" s="9" t="n">
-        <v>101.395511</v>
+        <v>101.397518</v>
       </c>
       <c r="S361" s="9" t="n">
         <v>99.090783</v>
@@ -29643,7 +29643,7 @@
         <v>99.46176800000001</v>
       </c>
       <c r="R362" s="6" t="n">
-        <v>101.241683</v>
+        <v>101.243469</v>
       </c>
       <c r="S362" s="6" t="n">
         <v>99.00770199999999</v>
@@ -29727,7 +29727,7 @@
         <v>99.650705</v>
       </c>
       <c r="R363" s="9" t="n">
-        <v>101.074806</v>
+        <v>101.076354</v>
       </c>
       <c r="S363" s="9" t="n">
         <v>98.996182</v>
@@ -29811,7 +29811,7 @@
         <v>99.78515899999999</v>
       </c>
       <c r="R364" s="6" t="n">
-        <v>100.890722</v>
+        <v>100.892006</v>
       </c>
       <c r="S364" s="6" t="n">
         <v>99.03162399999999</v>
@@ -29895,7 +29895,7 @@
         <v>99.862689</v>
       </c>
       <c r="R365" s="9" t="n">
-        <v>100.700112</v>
+        <v>100.701122</v>
       </c>
       <c r="S365" s="9" t="n">
         <v>99.092963</v>
@@ -29979,7 +29979,7 @@
         <v>99.890912</v>
       </c>
       <c r="R366" s="6" t="n">
-        <v>100.524626</v>
+        <v>100.525385</v>
       </c>
       <c r="S366" s="6" t="n">
         <v>99.16566899999999</v>
@@ -30063,7 +30063,7 @@
         <v>99.89665100000001</v>
       </c>
       <c r="R367" s="9" t="n">
-        <v>100.378542</v>
+        <v>100.379092</v>
       </c>
       <c r="S367" s="9" t="n">
         <v>99.24126200000001</v>
@@ -30147,7 +30147,7 @@
         <v>99.88556</v>
       </c>
       <c r="R368" s="6" t="n">
-        <v>100.268622</v>
+        <v>100.269015</v>
       </c>
       <c r="S368" s="6" t="n">
         <v>99.314387</v>
@@ -30231,7 +30231,7 @@
         <v>99.85733999999999</v>
       </c>
       <c r="R369" s="9" t="n">
-        <v>100.211919</v>
+        <v>100.212231</v>
       </c>
       <c r="S369" s="9" t="n">
         <v>99.382098</v>
@@ -30315,7 +30315,7 @@
         <v>99.826978</v>
       </c>
       <c r="R370" s="6" t="n">
-        <v>100.208511</v>
+        <v>100.208819</v>
       </c>
       <c r="S370" s="6" t="n">
         <v>99.442502</v>
@@ -30399,7 +30399,7 @@
         <v>99.816344</v>
       </c>
       <c r="R371" s="9" t="n">
-        <v>100.216513</v>
+        <v>100.216833</v>
       </c>
       <c r="S371" s="9" t="n">
         <v>99.49538699999999</v>
@@ -30483,7 +30483,7 @@
         <v>99.846328</v>
       </c>
       <c r="R372" s="6" t="n">
-        <v>100.201181</v>
+        <v>100.20148</v>
       </c>
       <c r="S372" s="6" t="n">
         <v>99.541725</v>
@@ -30567,7 +30567,7 @@
         <v>99.920164</v>
       </c>
       <c r="R373" s="9" t="n">
-        <v>100.137122</v>
+        <v>100.13733</v>
       </c>
       <c r="S373" s="9" t="n">
         <v>99.583702</v>
@@ -30651,7 +30651,7 @@
         <v>100.037014</v>
       </c>
       <c r="R374" s="6" t="n">
-        <v>100.016973</v>
+        <v>100.017009</v>
       </c>
       <c r="S374" s="6" t="n">
         <v>99.623555</v>
@@ -30735,7 +30735,7 @@
         <v>100.172082</v>
       </c>
       <c r="R375" s="9" t="n">
-        <v>99.84446199999999</v>
+        <v>99.844252</v>
       </c>
       <c r="S375" s="9" t="n">
         <v>99.66269200000001</v>
@@ -30819,7 +30819,7 @@
         <v>100.290194</v>
       </c>
       <c r="R376" s="6" t="n">
-        <v>99.649674</v>
+        <v>99.649185</v>
       </c>
       <c r="S376" s="6" t="n">
         <v>99.702549</v>
@@ -30903,7 +30903,7 @@
         <v>100.365232</v>
       </c>
       <c r="R377" s="9" t="n">
-        <v>99.45838000000001</v>
+        <v>99.457618</v>
       </c>
       <c r="S377" s="9" t="n">
         <v>99.74301199999999</v>
@@ -30987,7 +30987,7 @@
         <v>100.383501</v>
       </c>
       <c r="R378" s="6" t="n">
-        <v>99.28510799999999</v>
+        <v>99.284098</v>
       </c>
       <c r="S378" s="6" t="n">
         <v>99.783203</v>
@@ -31071,7 +31071,7 @@
         <v>100.358046</v>
       </c>
       <c r="R379" s="9" t="n">
-        <v>99.150021</v>
+        <v>99.14881699999999</v>
       </c>
       <c r="S379" s="9" t="n">
         <v>99.823812</v>
@@ -31155,7 +31155,7 @@
         <v>100.300133</v>
       </c>
       <c r="R380" s="6" t="n">
-        <v>99.067115</v>
+        <v>99.065794</v>
       </c>
       <c r="S380" s="6" t="n">
         <v>99.865314</v>
@@ -31239,7 +31239,7 @@
         <v>100.217377</v>
       </c>
       <c r="R381" s="9" t="n">
-        <v>99.047814</v>
+        <v>99.046466</v>
       </c>
       <c r="S381" s="9" t="n">
         <v>99.90692199999999</v>
@@ -31323,7 +31323,7 @@
         <v>100.120742</v>
       </c>
       <c r="R382" s="6" t="n">
-        <v>99.110263</v>
+        <v>99.10900599999999</v>
       </c>
       <c r="S382" s="6" t="n">
         <v>99.947074</v>
@@ -31407,7 +31407,7 @@
         <v>100.021502</v>
       </c>
       <c r="R383" s="9" t="n">
-        <v>99.26267199999999</v>
+        <v>99.261635</v>
       </c>
       <c r="S383" s="9" t="n">
         <v>99.984689</v>
@@ -31491,7 +31491,7 @@
         <v>99.9234</v>
       </c>
       <c r="R384" s="6" t="n">
-        <v>99.501452</v>
+        <v>99.50076</v>
       </c>
       <c r="S384" s="6" t="n">
         <v>100.019657</v>
@@ -31575,7 +31575,7 @@
         <v>99.838531</v>
       </c>
       <c r="R385" s="9" t="n">
-        <v>99.812797</v>
+        <v>99.812552</v>
       </c>
       <c r="S385" s="9" t="n">
         <v>100.053457</v>
@@ -31659,7 +31659,7 @@
         <v>99.78157299999999</v>
       </c>
       <c r="R386" s="6" t="n">
-        <v>100.139056</v>
+        <v>100.139281</v>
       </c>
       <c r="S386" s="6" t="n">
         <v>100.087436</v>
@@ -31743,7 +31743,7 @@
         <v>99.768951</v>
       </c>
       <c r="R387" s="9" t="n">
-        <v>100.405066</v>
+        <v>100.405674</v>
       </c>
       <c r="S387" s="9" t="n">
         <v>100.122765</v>
@@ -31827,7 +31827,7 @@
         <v>99.785332</v>
       </c>
       <c r="R388" s="6" t="n">
-        <v>100.562798</v>
+        <v>100.563635</v>
       </c>
       <c r="S388" s="6" t="n">
         <v>100.158665</v>
@@ -31911,7 +31911,7 @@
         <v>99.820078</v>
       </c>
       <c r="R389" s="9" t="n">
-        <v>100.609642</v>
+        <v>100.610547</v>
       </c>
       <c r="S389" s="9" t="n">
         <v>100.193802</v>
@@ -31995,7 +31995,7 @@
         <v>99.868376</v>
       </c>
       <c r="R390" s="6" t="n">
-        <v>100.576061</v>
+        <v>100.576919</v>
       </c>
       <c r="S390" s="6" t="n">
         <v>100.227592</v>
@@ -32079,7 +32079,7 @@
         <v>99.92626</v>
       </c>
       <c r="R391" s="9" t="n">
-        <v>100.518806</v>
+        <v>100.519583</v>
       </c>
       <c r="S391" s="9" t="n">
         <v>100.260668</v>
@@ -32163,7 +32163,7 @@
         <v>99.986683</v>
       </c>
       <c r="R392" s="6" t="n">
-        <v>100.498351</v>
+        <v>100.499101</v>
       </c>
       <c r="S392" s="6" t="n">
         <v>100.294543</v>
@@ -32247,7 +32247,7 @@
         <v>100.0383</v>
       </c>
       <c r="R393" s="9" t="n">
-        <v>100.5229</v>
+        <v>100.523686</v>
       </c>
       <c r="S393" s="9" t="n">
         <v>100.331268</v>
@@ -32331,7 +32331,7 @@
         <v>100.082959</v>
       </c>
       <c r="R394" s="6" t="n">
-        <v>100.552714</v>
+        <v>100.553544</v>
       </c>
       <c r="S394" s="6" t="n">
         <v>100.372964</v>
@@ -32415,7 +32415,7 @@
         <v>100.131382</v>
       </c>
       <c r="R395" s="9" t="n">
-        <v>100.530672</v>
+        <v>100.531472</v>
       </c>
       <c r="S395" s="9" t="n">
         <v>100.419403</v>
@@ -32499,7 +32499,7 @@
         <v>100.17819</v>
       </c>
       <c r="R396" s="6" t="n">
-        <v>100.424936</v>
+        <v>100.425586</v>
       </c>
       <c r="S396" s="6" t="n">
         <v>100.469358</v>
@@ -32583,7 +32583,7 @@
         <v>100.226603</v>
       </c>
       <c r="R397" s="9" t="n">
-        <v>100.257915</v>
+        <v>100.258326</v>
       </c>
       <c r="S397" s="9" t="n">
         <v>100.519873</v>
@@ -32667,7 +32667,7 @@
         <v>100.287471</v>
       </c>
       <c r="R398" s="6" t="n">
-        <v>100.053964</v>
+        <v>100.054085</v>
       </c>
       <c r="S398" s="6" t="n">
         <v>100.566872</v>
@@ -32751,7 +32751,7 @@
         <v>100.355763</v>
       </c>
       <c r="R399" s="9" t="n">
-        <v>99.834435</v>
+        <v>99.834242</v>
       </c>
       <c r="S399" s="9" t="n">
         <v>100.604819</v>
@@ -32835,7 +32835,7 @@
         <v>100.421986</v>
       </c>
       <c r="R400" s="6" t="n">
-        <v>99.61371200000001</v>
+        <v>99.613204</v>
       </c>
       <c r="S400" s="6" t="n">
         <v>100.626549</v>
@@ -32919,7 +32919,7 @@
         <v>100.47326</v>
       </c>
       <c r="R401" s="9" t="n">
-        <v>99.396663</v>
+        <v>99.395844</v>
       </c>
       <c r="S401" s="9" t="n">
         <v>100.624496</v>
@@ -33003,7 +33003,7 @@
         <v>100.486619</v>
       </c>
       <c r="R402" s="6" t="n">
-        <v>99.198302</v>
+        <v>99.197199</v>
       </c>
       <c r="S402" s="6" t="n">
         <v>100.59299</v>
@@ -33087,7 +33087,7 @@
         <v>100.446606</v>
       </c>
       <c r="R403" s="9" t="n">
-        <v>99.03193</v>
+        <v>99.03059</v>
       </c>
       <c r="S403" s="9" t="n">
         <v>100.530526</v>
@@ -33171,7 +33171,7 @@
         <v>100.360192</v>
       </c>
       <c r="R404" s="6" t="n">
-        <v>98.90683300000001</v>
+        <v>98.905314</v>
       </c>
       <c r="S404" s="6" t="n">
         <v>100.444049</v>
@@ -33255,7 +33255,7 @@
         <v>100.242251</v>
       </c>
       <c r="R405" s="9" t="n">
-        <v>98.840951</v>
+        <v>98.83934000000001</v>
       </c>
       <c r="S405" s="9" t="n">
         <v>100.353713</v>
@@ -33339,7 +33339,7 @@
         <v>100.116492</v>
       </c>
       <c r="R406" s="6" t="n">
-        <v>98.849161</v>
+        <v>98.847562</v>
       </c>
       <c r="S406" s="6" t="n">
         <v>100.271697</v>
@@ -33423,7 +33423,7 @@
         <v>100.000262</v>
       </c>
       <c r="R407" s="9" t="n">
-        <v>98.910831</v>
+        <v>98.909322</v>
       </c>
       <c r="S407" s="9" t="n">
         <v>100.196804</v>
@@ -33507,7 +33507,7 @@
         <v>99.906029</v>
       </c>
       <c r="R408" s="6" t="n">
-        <v>98.974934</v>
+        <v>98.973519</v>
       </c>
       <c r="S408" s="6" t="n">
         <v>100.121036</v>
@@ -33591,7 +33591,7 @@
         <v>99.836815</v>
       </c>
       <c r="R409" s="9" t="n">
-        <v>99.018914</v>
+        <v>99.017563</v>
       </c>
       <c r="S409" s="9" t="n">
         <v>100.034604</v>
@@ -33675,7 +33675,7 @@
         <v>99.795382</v>
       </c>
       <c r="R410" s="6" t="n">
-        <v>99.028266</v>
+        <v>99.026929</v>
       </c>
       <c r="S410" s="6" t="n">
         <v>99.934584</v>
@@ -33759,7 +33759,7 @@
         <v>99.76916799999999</v>
       </c>
       <c r="R411" s="9" t="n">
-        <v>98.995935</v>
+        <v>98.994552</v>
       </c>
       <c r="S411" s="9" t="n">
         <v>99.831434</v>
@@ -33843,7 +33843,7 @@
         <v>99.74010699999999</v>
       </c>
       <c r="R412" s="6" t="n">
-        <v>98.935008</v>
+        <v>98.933539</v>
       </c>
       <c r="S412" s="6" t="n">
         <v>99.73732</v>
@@ -33927,7 +33927,7 @@
         <v>99.694822</v>
       </c>
       <c r="R413" s="9" t="n">
-        <v>98.86249100000001</v>
+        <v>98.860919</v>
       </c>
       <c r="S413" s="9" t="n">
         <v>99.66261799999999</v>
@@ -34011,7 +34011,7 @@
         <v>99.640129</v>
       </c>
       <c r="R414" s="6" t="n">
-        <v>98.790852</v>
+        <v>98.789177</v>
       </c>
       <c r="S414" s="6" t="n">
         <v>99.603942</v>
@@ -34095,7 +34095,7 @@
         <v>99.605774</v>
       </c>
       <c r="R415" s="9" t="n">
-        <v>98.717893</v>
+        <v>98.716114</v>
       </c>
       <c r="S415" s="9" t="n">
         <v>99.55016500000001</v>
@@ -34179,7 +34179,7 @@
         <v>99.61957700000001</v>
       </c>
       <c r="R416" s="6" t="n">
-        <v>98.638488</v>
+        <v>98.636596</v>
       </c>
       <c r="S416" s="6" t="n">
         <v>99.486075</v>
@@ -34263,7 +34263,7 @@
         <v>99.680053</v>
       </c>
       <c r="R417" s="9" t="n">
-        <v>98.554901</v>
+        <v>98.55288899999999</v>
       </c>
       <c r="S417" s="9" t="n">
         <v>99.397633</v>
@@ -34347,7 +34347,7 @@
         <v>99.776528</v>
       </c>
       <c r="R418" s="6" t="n">
-        <v>98.47601299999999</v>
+        <v>98.473887</v>
       </c>
       <c r="S418" s="6" t="n">
         <v>99.277788</v>
@@ -34431,7 +34431,7 @@
         <v>99.888969</v>
       </c>
       <c r="R419" s="9" t="n">
-        <v>98.411861</v>
+        <v>98.409643</v>
       </c>
       <c r="S419" s="9" t="n">
         <v>99.133869</v>
@@ -34515,7 +34515,7 @@
         <v>99.991218</v>
       </c>
       <c r="R420" s="6" t="n">
-        <v>98.371735</v>
+        <v>98.36945900000001</v>
       </c>
       <c r="S420" s="6" t="n">
         <v>98.99495899999999</v>
@@ -34599,7 +34599,7 @@
         <v>100.059506</v>
       </c>
       <c r="R421" s="9" t="n">
-        <v>98.36732499999999</v>
+        <v>98.365042</v>
       </c>
       <c r="S421" s="9" t="n">
         <v>98.88093600000001</v>
@@ -34683,7 +34683,7 @@
         <v>100.077054</v>
       </c>
       <c r="R422" s="6" t="n">
-        <v>98.406216</v>
+        <v>98.403988</v>
       </c>
       <c r="S422" s="6" t="n">
         <v>98.796458</v>
@@ -34767,7 +34767,7 @@
         <v>100.049046</v>
       </c>
       <c r="R423" s="9" t="n">
-        <v>98.496641</v>
+        <v>98.494542</v>
       </c>
       <c r="S423" s="9" t="n">
         <v>98.73840199999999</v>
@@ -34851,7 +34851,7 @@
         <v>99.991501</v>
       </c>
       <c r="R424" s="6" t="n">
-        <v>98.639825</v>
+        <v>98.63793</v>
       </c>
       <c r="S424" s="6" t="n">
         <v>98.69978</v>
@@ -34935,7 +34935,7 @@
         <v>99.930987</v>
       </c>
       <c r="R425" s="9" t="n">
-        <v>98.832921</v>
+        <v>98.83130199999999</v>
       </c>
       <c r="S425" s="9" t="n">
         <v>98.672764</v>
@@ -35019,7 +35019,7 @@
         <v>99.89457899999999</v>
       </c>
       <c r="R426" s="6" t="n">
-        <v>99.046823</v>
+        <v>99.045509</v>
       </c>
       <c r="S426" s="6" t="n">
         <v>98.650132</v>
@@ -35103,7 +35103,7 @@
         <v>99.898994</v>
       </c>
       <c r="R427" s="9" t="n">
-        <v>99.26434399999999</v>
+        <v>99.26334</v>
       </c>
       <c r="S427" s="9" t="n">
         <v>98.626881</v>
@@ -35187,7 +35187,7 @@
         <v>99.925972</v>
       </c>
       <c r="R428" s="6" t="n">
-        <v>99.474709</v>
+        <v>99.47400500000001</v>
       </c>
       <c r="S428" s="6" t="n">
         <v>98.60012399999999</v>
@@ -35271,7 +35271,7 @@
         <v>99.962175</v>
       </c>
       <c r="R429" s="9" t="n">
-        <v>99.67397200000001</v>
+        <v>99.673551</v>
       </c>
       <c r="S429" s="9" t="n">
         <v>98.568827</v>
@@ -35355,7 +35355,7 @@
         <v>99.98979</v>
       </c>
       <c r="R430" s="6" t="n">
-        <v>99.86816899999999</v>
+        <v>99.86802400000001</v>
       </c>
       <c r="S430" s="6" t="n">
         <v>98.53360499999999</v>
@@ -35439,7 +35439,7 @@
         <v>99.996216</v>
       </c>
       <c r="R431" s="9" t="n">
-        <v>100.060364</v>
+        <v>100.060492</v>
       </c>
       <c r="S431" s="9" t="n">
         <v>98.49663700000001</v>
@@ -35523,7 +35523,7 @@
         <v>99.976736</v>
       </c>
       <c r="R432" s="6" t="n">
-        <v>100.245093</v>
+        <v>100.245482</v>
       </c>
       <c r="S432" s="6" t="n">
         <v>98.46169</v>
@@ -35607,7 +35607,7 @@
         <v>99.93790799999999</v>
       </c>
       <c r="R433" s="9" t="n">
-        <v>100.406011</v>
+        <v>100.406627</v>
       </c>
       <c r="S433" s="9" t="n">
         <v>98.434055</v>
@@ -35691,7 +35691,7 @@
         <v>99.8952</v>
       </c>
       <c r="R434" s="6" t="n">
-        <v>100.527076</v>
+        <v>100.527861</v>
       </c>
       <c r="S434" s="6" t="n">
         <v>98.420169</v>
@@ -35775,7 +35775,7 @@
         <v>99.862802</v>
       </c>
       <c r="R435" s="9" t="n">
-        <v>100.613973</v>
+        <v>100.614878</v>
       </c>
       <c r="S435" s="9" t="n">
         <v>98.42894099999999</v>
@@ -35859,7 +35859,7 @@
         <v>99.841863</v>
       </c>
       <c r="R436" s="6" t="n">
-        <v>100.697748</v>
+        <v>100.698767</v>
       </c>
       <c r="S436" s="6" t="n">
         <v>98.47069999999999</v>
@@ -35943,7 +35943,7 @@
         <v>99.84436599999999</v>
       </c>
       <c r="R437" s="9" t="n">
-        <v>100.800136</v>
+        <v>100.801296</v>
       </c>
       <c r="S437" s="9" t="n">
         <v>98.550743</v>
@@ -36027,7 +36027,7 @@
         <v>99.87881400000001</v>
       </c>
       <c r="R438" s="6" t="n">
-        <v>100.915398</v>
+        <v>100.916717</v>
       </c>
       <c r="S438" s="6" t="n">
         <v>98.663965</v>
@@ -36111,7 +36111,7 @@
         <v>99.943274</v>
       </c>
       <c r="R439" s="9" t="n">
-        <v>101.013894</v>
+        <v>101.015347</v>
       </c>
       <c r="S439" s="9" t="n">
         <v>98.79724</v>
@@ -36195,7 +36195,7 @@
         <v>100.029896</v>
       </c>
       <c r="R440" s="6" t="n">
-        <v>101.090225</v>
+        <v>101.091781</v>
       </c>
       <c r="S440" s="6" t="n">
         <v>98.933442</v>
@@ -36279,7 +36279,7 @@
         <v>100.119969</v>
       </c>
       <c r="R441" s="9" t="n">
-        <v>101.178604</v>
+        <v>101.180278</v>
       </c>
       <c r="S441" s="9" t="n">
         <v>99.05864200000001</v>
@@ -36363,7 +36363,7 @@
         <v>100.203927</v>
       </c>
       <c r="R442" s="6" t="n">
-        <v>101.297652</v>
+        <v>101.299488</v>
       </c>
       <c r="S442" s="6" t="n">
         <v>99.17992599999999</v>
@@ -36447,7 +36447,7 @@
         <v>100.276567</v>
       </c>
       <c r="R443" s="9" t="n">
-        <v>101.431714</v>
+        <v>101.433734</v>
       </c>
       <c r="S443" s="9" t="n">
         <v>99.312166</v>
@@ -36531,7 +36531,7 @@
         <v>100.330759</v>
       </c>
       <c r="R444" s="6" t="n">
-        <v>101.56255</v>
+        <v>101.564748</v>
       </c>
       <c r="S444" s="6" t="n">
         <v>99.46694100000001</v>
@@ -36615,7 +36615,7 @@
         <v>100.358826</v>
       </c>
       <c r="R445" s="9" t="n">
-        <v>101.695303</v>
+        <v>101.69768</v>
       </c>
       <c r="S445" s="9" t="n">
         <v>99.64057</v>
@@ -36699,7 +36699,7 @@
         <v>100.356587</v>
       </c>
       <c r="R446" s="6" t="n">
-        <v>101.834426</v>
+        <v>101.836992</v>
       </c>
       <c r="S446" s="6" t="n">
         <v>99.840971</v>
@@ -36783,7 +36783,7 @@
         <v>100.331218</v>
       </c>
       <c r="R447" s="9" t="n">
-        <v>101.961214</v>
+        <v>101.96395</v>
       </c>
       <c r="S447" s="9" t="n">
         <v>100.073258</v>
@@ -36867,7 +36867,7 @@
         <v>100.296212</v>
       </c>
       <c r="R448" s="6" t="n">
-        <v>102.055508</v>
+        <v>102.058367</v>
       </c>
       <c r="S448" s="6" t="n">
         <v>100.322485</v>
@@ -36951,7 +36951,7 @@
         <v>100.280024</v>
       </c>
       <c r="R449" s="9" t="n">
-        <v>102.064859</v>
+        <v>102.067718</v>
       </c>
       <c r="S449" s="9" t="n">
         <v>100.573451</v>
@@ -37035,7 +37035,7 @@
         <v>100.294952</v>
       </c>
       <c r="R450" s="6" t="n">
-        <v>101.94158</v>
+        <v>101.944248</v>
       </c>
       <c r="S450" s="6" t="n">
         <v>100.80574</v>
@@ -37119,7 +37119,7 @@
         <v>100.341278</v>
       </c>
       <c r="R451" s="9" t="n">
-        <v>101.665439</v>
+        <v>101.667696</v>
       </c>
       <c r="S451" s="9" t="n">
         <v>101.00678</v>
@@ -37203,7 +37203,7 @@
         <v>100.414549</v>
       </c>
       <c r="R452" s="6" t="n">
-        <v>101.282968</v>
+        <v>101.28466</v>
       </c>
       <c r="S452" s="6" t="n">
         <v>101.169872</v>
@@ -37287,7 +37287,7 @@
         <v>100.499217</v>
       </c>
       <c r="R453" s="9" t="n">
-        <v>100.865309</v>
+        <v>100.866385</v>
       </c>
       <c r="S453" s="9" t="n">
         <v>101.294817</v>
@@ -37371,7 +37371,7 @@
         <v>100.580839</v>
       </c>
       <c r="R454" s="6" t="n">
-        <v>100.469044</v>
+        <v>100.469534</v>
       </c>
       <c r="S454" s="6" t="n">
         <v>101.383222</v>
@@ -37455,7 +37455,7 @@
         <v>100.649068</v>
       </c>
       <c r="R455" s="9" t="n">
-        <v>100.125169</v>
+        <v>100.125148</v>
       </c>
       <c r="S455" s="9" t="n">
         <v>101.439167</v>
@@ -37539,7 +37539,7 @@
         <v>100.689155</v>
       </c>
       <c r="R456" s="6" t="n">
-        <v>99.86801800000001</v>
+        <v>99.867609</v>
       </c>
       <c r="S456" s="6" t="n">
         <v>101.464711</v>
@@ -37623,7 +37623,7 @@
         <v>100.689284</v>
       </c>
       <c r="R457" s="9" t="n">
-        <v>99.71737299999999</v>
+        <v>99.71672700000001</v>
       </c>
       <c r="S457" s="9" t="n">
         <v>101.464385</v>
@@ -37707,7 +37707,7 @@
         <v>100.649957</v>
       </c>
       <c r="R458" s="6" t="n">
-        <v>99.666714</v>
+        <v>99.665976</v>
       </c>
       <c r="S458" s="6" t="n">
         <v>101.447774</v>
@@ -37791,7 +37791,7 @@
         <v>100.585485</v>
       </c>
       <c r="R459" s="9" t="n">
-        <v>99.685793</v>
+        <v>99.685061</v>
       </c>
       <c r="S459" s="9" t="n">
         <v>101.425817</v>
@@ -37875,7 +37875,7 @@
         <v>100.518099</v>
       </c>
       <c r="R460" s="6" t="n">
-        <v>99.723131</v>
+        <v>99.722431</v>
       </c>
       <c r="S460" s="6" t="n">
         <v>101.407829</v>
@@ -37959,7 +37959,7 @@
         <v>100.462701</v>
       </c>
       <c r="R461" s="9" t="n">
-        <v>99.75232200000001</v>
+        <v>99.75164100000001</v>
       </c>
       <c r="S461" s="9" t="n">
         <v>101.399015</v>
@@ -38043,7 +38043,7 @@
         <v>100.411197</v>
       </c>
       <c r="R462" s="6" t="n">
-        <v>99.770194</v>
+        <v>99.769515</v>
       </c>
       <c r="S462" s="6" t="n">
         <v>101.397808</v>
@@ -38127,7 +38127,7 @@
         <v>100.360736</v>
       </c>
       <c r="R463" s="9" t="n">
-        <v>99.789751</v>
+        <v>99.78907599999999</v>
       </c>
       <c r="S463" s="9" t="n">
         <v>101.399643</v>
@@ -38211,7 +38211,7 @@
         <v>100.328687</v>
       </c>
       <c r="R464" s="6" t="n">
-        <v>99.83286099999999</v>
+        <v>99.832223</v>
       </c>
       <c r="S464" s="6" t="n">
         <v>101.400185</v>
@@ -38295,7 +38295,7 @@
         <v>100.323425</v>
       </c>
       <c r="R465" s="9" t="n">
-        <v>99.904284</v>
+        <v>99.903722</v>
       </c>
       <c r="S465" s="9" t="n">
         <v>101.398875</v>
@@ -38379,7 +38379,7 @@
         <v>100.332168</v>
       </c>
       <c r="R466" s="6" t="n">
-        <v>99.98861599999999</v>
+        <v>99.98814900000001</v>
       </c>
       <c r="S466" s="6" t="n">
         <v>101.39799</v>
@@ -38463,7 +38463,7 @@
         <v>100.350925</v>
       </c>
       <c r="R467" s="9" t="n">
-        <v>100.030436</v>
+        <v>100.030001</v>
       </c>
       <c r="S467" s="9" t="n">
         <v>101.399944</v>
@@ -38547,7 +38547,7 @@
         <v>100.344447</v>
       </c>
       <c r="R468" s="6" t="n">
-        <v>100.002699</v>
+        <v>100.002195</v>
       </c>
       <c r="S468" s="6" t="n">
         <v>101.404675</v>
@@ -38631,7 +38631,7 @@
         <v>100.280123</v>
       </c>
       <c r="R469" s="9" t="n">
-        <v>99.946867</v>
+        <v>99.946254</v>
       </c>
       <c r="S469" s="9" t="n">
         <v>101.410523</v>
@@ -38715,7 +38715,7 @@
         <v>100.150422</v>
       </c>
       <c r="R470" s="6" t="n">
-        <v>99.897031</v>
+        <v>99.896317</v>
       </c>
       <c r="S470" s="6" t="n">
         <v>101.419471</v>
@@ -38799,7 +38799,7 @@
         <v>99.975185</v>
       </c>
       <c r="R471" s="9" t="n">
-        <v>99.85736900000001</v>
+        <v>99.856568</v>
       </c>
       <c r="S471" s="9" t="n">
         <v>101.434457</v>
@@ -38883,7 +38883,7 @@
         <v>99.81061800000001</v>
       </c>
       <c r="R472" s="6" t="n">
-        <v>99.815563</v>
+        <v>99.814671</v>
       </c>
       <c r="S472" s="6" t="n">
         <v>101.456125</v>
@@ -38967,7 +38967,7 @@
         <v>99.697534</v>
       </c>
       <c r="R473" s="9" t="n">
-        <v>99.740854</v>
+        <v>99.739823</v>
       </c>
       <c r="S473" s="9" t="n">
         <v>101.479767</v>
@@ -39051,7 +39051,7 @@
         <v>99.643334</v>
       </c>
       <c r="R474" s="6" t="n">
-        <v>99.641769</v>
+        <v>99.640563</v>
       </c>
       <c r="S474" s="6" t="n">
         <v>101.497774</v>
@@ -39135,7 +39135,7 @@
         <v>99.62756899999999</v>
       </c>
       <c r="R475" s="9" t="n">
-        <v>99.554343</v>
+        <v>99.55297899999999</v>
       </c>
       <c r="S475" s="9" t="n">
         <v>101.503411</v>
@@ -39219,7 +39219,7 @@
         <v>99.637182</v>
       </c>
       <c r="R476" s="6" t="n">
-        <v>99.49288199999999</v>
+        <v>99.49139599999999</v>
       </c>
       <c r="S476" s="6" t="n">
         <v>101.495915</v>
@@ -39303,7 +39303,7 @@
         <v>99.655733</v>
       </c>
       <c r="R477" s="9" t="n">
-        <v>99.458901</v>
+        <v>99.45733300000001</v>
       </c>
       <c r="S477" s="9" t="n">
         <v>101.476748</v>
@@ -39387,7 +39387,7 @@
         <v>99.668656</v>
       </c>
       <c r="R478" s="6" t="n">
-        <v>99.449331</v>
+        <v>99.447716</v>
       </c>
       <c r="S478" s="6" t="n">
         <v>101.446445</v>
@@ -39471,7 +39471,7 @@
         <v>99.679993</v>
       </c>
       <c r="R479" s="9" t="n">
-        <v>99.450913</v>
+        <v>99.449265</v>
       </c>
       <c r="S479" s="9" t="n">
         <v>101.403343</v>
@@ -39555,7 +39555,7 @@
         <v>99.692527</v>
       </c>
       <c r="R480" s="6" t="n">
-        <v>99.449946</v>
+        <v>99.448263</v>
       </c>
       <c r="S480" s="6" t="n">
         <v>101.344632</v>
@@ -39639,7 +39639,7 @@
         <v>99.71395699999999</v>
       </c>
       <c r="R481" s="9" t="n">
-        <v>99.443313</v>
+        <v>99.441585</v>
       </c>
       <c r="S481" s="9" t="n">
         <v>101.267954</v>
@@ -39723,7 +39723,7 @@
         <v>99.72675099999999</v>
       </c>
       <c r="R482" s="6" t="n">
-        <v>99.422166</v>
+        <v>99.420374</v>
       </c>
       <c r="S482" s="6" t="n">
         <v>101.172804</v>
@@ -39807,7 +39807,7 @@
         <v>99.711406</v>
       </c>
       <c r="R483" s="9" t="n">
-        <v>99.403437</v>
+        <v>99.401583</v>
       </c>
       <c r="S483" s="9" t="n">
         <v>101.059502</v>
@@ -39891,7 +39891,7 @@
         <v>99.651021</v>
       </c>
       <c r="R484" s="6" t="n">
-        <v>99.431031</v>
+        <v>99.429182</v>
       </c>
       <c r="S484" s="6" t="n">
         <v>100.926581</v>
@@ -39975,7 +39975,7 @@
         <v>99.535528</v>
       </c>
       <c r="R485" s="9" t="n">
-        <v>99.558414</v>
+        <v>99.556714</v>
       </c>
       <c r="S485" s="9" t="n">
         <v>100.767879</v>
@@ -40059,7 +40059,7 @@
         <v>99.357167</v>
       </c>
       <c r="R486" s="6" t="n">
-        <v>99.83211900000001</v>
+        <v>99.83077900000001</v>
       </c>
       <c r="S486" s="6" t="n">
         <v>100.574409</v>
@@ -40143,7 +40143,7 @@
         <v>99.126577</v>
       </c>
       <c r="R487" s="9" t="n">
-        <v>100.268294</v>
+        <v>100.267547</v>
       </c>
       <c r="S487" s="9" t="n">
         <v>100.335938</v>
@@ -40227,7 +40227,7 @@
         <v>98.891723</v>
       </c>
       <c r="R488" s="6" t="n">
-        <v>100.809561</v>
+        <v>100.80956</v>
       </c>
       <c r="S488" s="6" t="n">
         <v>100.044901</v>
@@ -40311,7 +40311,7 @@
         <v>98.718901</v>
       </c>
       <c r="R489" s="9" t="n">
-        <v>101.290001</v>
+        <v>101.290658</v>
       </c>
       <c r="S489" s="9" t="n">
         <v>99.704982</v>
@@ -40395,7 +40395,7 @@
         <v>98.61542900000001</v>
       </c>
       <c r="R490" s="6" t="n">
-        <v>101.576836</v>
+        <v>101.577874</v>
       </c>
       <c r="S490" s="6" t="n">
         <v>99.33497199999999</v>
@@ -40479,7 +40479,7 @@
         <v>98.57800899999999</v>
       </c>
       <c r="R491" s="9" t="n">
-        <v>101.655069</v>
+        <v>101.65619</v>
       </c>
       <c r="S491" s="9" t="n">
         <v>98.959307</v>
@@ -40563,7 +40563,7 @@
         <v>98.594399</v>
       </c>
       <c r="R492" s="6" t="n">
-        <v>101.571462</v>
+        <v>101.572435</v>
       </c>
       <c r="S492" s="6" t="n">
         <v>98.599131</v>
@@ -40647,7 +40647,7 @@
         <v>98.667708</v>
       </c>
       <c r="R493" s="9" t="n">
-        <v>101.359907</v>
+        <v>101.360549</v>
       </c>
       <c r="S493" s="9" t="n">
         <v>98.274146</v>
@@ -40731,7 +40731,7 @@
         <v>98.802978</v>
       </c>
       <c r="R494" s="6" t="n">
-        <v>101.060557</v>
+        <v>101.060745</v>
       </c>
       <c r="S494" s="6" t="n">
         <v>97.996454</v>
@@ -40815,7 +40815,7 @@
         <v>98.99840500000001</v>
       </c>
       <c r="R495" s="9" t="n">
-        <v>100.722506</v>
+        <v>100.722186</v>
       </c>
       <c r="S495" s="9" t="n">
         <v>97.77229800000001</v>
@@ -40899,7 +40899,7 @@
         <v>99.244445</v>
       </c>
       <c r="R496" s="6" t="n">
-        <v>100.394326</v>
+        <v>100.393514</v>
       </c>
       <c r="S496" s="6" t="n">
         <v>97.600083</v>
@@ -40983,7 +40983,7 @@
         <v>99.50076799999999</v>
       </c>
       <c r="R497" s="9" t="n">
-        <v>100.127633</v>
+        <v>100.12642</v>
       </c>
       <c r="S497" s="9" t="n">
         <v>97.468677</v>
@@ -41067,7 +41067,7 @@
         <v>99.744534</v>
       </c>
       <c r="R498" s="6" t="n">
-        <v>99.953828</v>
+        <v>99.952349</v>
       </c>
       <c r="S498" s="6" t="n">
         <v>97.36564799999999</v>
@@ -41151,7 +41151,7 @@
         <v>99.97945799999999</v>
       </c>
       <c r="R499" s="9" t="n">
-        <v>99.871509</v>
+        <v>99.86989800000001</v>
       </c>
       <c r="S499" s="9" t="n">
         <v>97.28423600000001</v>
@@ -41235,7 +41235,7 @@
         <v>100.201202</v>
       </c>
       <c r="R500" s="6" t="n">
-        <v>99.850319</v>
+        <v>99.848668</v>
       </c>
       <c r="S500" s="6" t="n">
         <v>97.22727999999999</v>
@@ -41319,7 +41319,7 @@
         <v>100.397587</v>
       </c>
       <c r="R501" s="9" t="n">
-        <v>99.858057</v>
+        <v>99.85641099999999</v>
       </c>
       <c r="S501" s="9" t="n">
         <v>97.20132099999999</v>
@@ -41403,7 +41403,7 @@
         <v>100.559976</v>
       </c>
       <c r="R502" s="6" t="n">
-        <v>99.893686</v>
+        <v>99.892087</v>
       </c>
       <c r="S502" s="6" t="n">
         <v>97.211375</v>
@@ -41487,7 +41487,7 @@
         <v>100.676659</v>
       </c>
       <c r="R503" s="9" t="n">
-        <v>99.952899</v>
+        <v>99.951385</v>
       </c>
       <c r="S503" s="9" t="n">
         <v>97.260769</v>
@@ -41571,7 +41571,7 @@
         <v>100.751926</v>
       </c>
       <c r="R504" s="6" t="n">
-        <v>100.030564</v>
+        <v>100.029167</v>
       </c>
       <c r="S504" s="6" t="n">
         <v>97.34919600000001</v>
@@ -41655,7 +41655,7 @@
         <v>100.789044</v>
       </c>
       <c r="R505" s="9" t="n">
-        <v>100.126421</v>
+        <v>100.125171</v>
       </c>
       <c r="S505" s="9" t="n">
         <v>97.46968099999999</v>
@@ -41739,7 +41739,7 @@
         <v>100.788341</v>
       </c>
       <c r="R506" s="6" t="n">
-        <v>100.236931</v>
+        <v>100.235853</v>
       </c>
       <c r="S506" s="6" t="n">
         <v>97.617914</v>
@@ -41823,7 +41823,7 @@
         <v>100.769083</v>
       </c>
       <c r="R507" s="9" t="n">
-        <v>100.355775</v>
+        <v>100.354887</v>
       </c>
       <c r="S507" s="9" t="n">
         <v>97.792419</v>
@@ -41907,7 +41907,7 @@
         <v>100.74695</v>
       </c>
       <c r="R508" s="6" t="n">
-        <v>100.461955</v>
+        <v>100.461244</v>
       </c>
       <c r="S508" s="6" t="n">
         <v>97.989796</v>
@@ -41991,7 +41991,7 @@
         <v>100.730522</v>
       </c>
       <c r="R509" s="9" t="n">
-        <v>100.540389</v>
+        <v>100.539821</v>
       </c>
       <c r="S509" s="9" t="n">
         <v>98.208354</v>
@@ -42075,7 +42075,7 @@
         <v>100.69997</v>
       </c>
       <c r="R510" s="6" t="n">
-        <v>100.587053</v>
+        <v>100.586589</v>
       </c>
       <c r="S510" s="6" t="n">
         <v>98.442981</v>
@@ -42159,7 +42159,7 @@
         <v>100.643866</v>
       </c>
       <c r="R511" s="9" t="n">
-        <v>100.616813</v>
+        <v>100.616434</v>
       </c>
       <c r="S511" s="9" t="n">
         <v>98.689977</v>
@@ -42243,7 +42243,7 @@
         <v>100.538553</v>
       </c>
       <c r="R512" s="6" t="n">
-        <v>100.637243</v>
+        <v>100.636944</v>
       </c>
       <c r="S512" s="6" t="n">
         <v>98.947277</v>
@@ -42327,7 +42327,7 @@
         <v>100.369189</v>
       </c>
       <c r="R513" s="9" t="n">
-        <v>100.650982</v>
+        <v>100.65076</v>
       </c>
       <c r="S513" s="9" t="n">
         <v>99.214083</v>
@@ -42411,7 +42411,7 @@
         <v>100.162862</v>
       </c>
       <c r="R514" s="6" t="n">
-        <v>100.66827</v>
+        <v>100.668138</v>
       </c>
       <c r="S514" s="6" t="n">
         <v>99.48934</v>
@@ -42495,7 +42495,7 @@
         <v>99.94708</v>
       </c>
       <c r="R515" s="9" t="n">
-        <v>100.677583</v>
+        <v>100.677537</v>
       </c>
       <c r="S515" s="9" t="n">
         <v>99.773906</v>
@@ -42579,7 +42579,7 @@
         <v>99.767257</v>
       </c>
       <c r="R516" s="6" t="n">
-        <v>100.661862</v>
+        <v>100.661875</v>
       </c>
       <c r="S516" s="6" t="n">
         <v>100.063891</v>
@@ -42663,7 +42663,7 @@
         <v>99.65204900000001</v>
       </c>
       <c r="R517" s="9" t="n">
-        <v>100.599361</v>
+        <v>100.599375</v>
       </c>
       <c r="S517" s="9" t="n">
         <v>100.349731</v>
@@ -42747,7 +42747,7 @@
         <v>99.62932499999999</v>
       </c>
       <c r="R518" s="6" t="n">
-        <v>100.490913</v>
+        <v>100.490871</v>
       </c>
       <c r="S518" s="6" t="n">
         <v>100.624218</v>
@@ -42831,7 +42831,7 @@
         <v>99.693541</v>
       </c>
       <c r="R519" s="9" t="n">
-        <v>100.337616</v>
+        <v>100.337464</v>
       </c>
       <c r="S519" s="9" t="n">
         <v>100.881013</v>
@@ -42915,7 +42915,7 @@
         <v>99.800539</v>
       </c>
       <c r="R520" s="6" t="n">
-        <v>100.143441</v>
+        <v>100.14313</v>
       </c>
       <c r="S520" s="6" t="n">
         <v>101.109683</v>
@@ -42999,7 +42999,7 @@
         <v>99.920072</v>
       </c>
       <c r="R521" s="9" t="n">
-        <v>99.924505</v>
+        <v>99.92401</v>
       </c>
       <c r="S521" s="9" t="n">
         <v>101.303159</v>
@@ -43083,7 +43083,7 @@
         <v>100.043593</v>
       </c>
       <c r="R522" s="6" t="n">
-        <v>99.688456</v>
+        <v>99.687763</v>
       </c>
       <c r="S522" s="6" t="n">
         <v>101.456207</v>
@@ -43167,7 +43167,7 @@
         <v>100.138979</v>
       </c>
       <c r="R523" s="9" t="n">
-        <v>99.45082499999999</v>
+        <v>99.449945</v>
       </c>
       <c r="S523" s="9" t="n">
         <v>101.569141</v>
@@ -43251,7 +43251,7 @@
         <v>100.201541</v>
       </c>
       <c r="R524" s="6" t="n">
-        <v>99.224676</v>
+        <v>99.223636</v>
       </c>
       <c r="S524" s="6" t="n">
         <v>101.64327</v>
@@ -43335,7 +43335,7 @@
         <v>100.225934</v>
       </c>
       <c r="R525" s="9" t="n">
-        <v>99.01658399999999</v>
+        <v>99.015424</v>
       </c>
       <c r="S525" s="9" t="n">
         <v>101.681604</v>
@@ -43419,7 +43419,7 @@
         <v>100.211562</v>
       </c>
       <c r="R526" s="6" t="n">
-        <v>98.832268</v>
+        <v>98.831034</v>
       </c>
       <c r="S526" s="6" t="n">
         <v>101.689322</v>
@@ -43503,7 +43503,7 @@
         <v>100.172665</v>
       </c>
       <c r="R527" s="9" t="n">
-        <v>98.681269</v>
+        <v>98.68002199999999</v>
       </c>
       <c r="S527" s="9" t="n">
         <v>101.674991</v>
@@ -43587,7 +43587,7 @@
         <v>100.116498</v>
       </c>
       <c r="R528" s="6" t="n">
-        <v>98.578451</v>
+        <v>98.577274</v>
       </c>
       <c r="S528" s="6" t="n">
         <v>101.64782</v>
@@ -43671,7 +43671,7 @@
         <v>100.053238</v>
       </c>
       <c r="R529" s="9" t="n">
-        <v>98.52960899999999</v>
+        <v>98.528595</v>
       </c>
       <c r="S529" s="9" t="n">
         <v>101.614883</v>
@@ -43755,7 +43755,7 @@
         <v>100.009894</v>
       </c>
       <c r="R530" s="6" t="n">
-        <v>98.515494</v>
+        <v>98.514707</v>
       </c>
       <c r="S530" s="6" t="n">
         <v>101.580775</v>
@@ -43839,7 +43839,7 @@
         <v>100.013592</v>
       </c>
       <c r="R531" s="9" t="n">
-        <v>98.498902</v>
+        <v>98.49835299999999</v>
       </c>
       <c r="S531" s="9" t="n">
         <v>101.547826</v>
@@ -43923,7 +43923,7 @@
         <v>100.069709</v>
       </c>
       <c r="R532" s="6" t="n">
-        <v>98.445566</v>
+        <v>98.44521899999999</v>
       </c>
       <c r="S532" s="6" t="n">
         <v>101.516534</v>
@@ -44007,7 +44007,7 @@
         <v>100.139644</v>
       </c>
       <c r="R533" s="9" t="n">
-        <v>98.375821</v>
+        <v>98.37566700000001</v>
       </c>
       <c r="S533" s="9" t="n">
         <v>101.486065</v>
@@ -44091,7 +44091,7 @@
         <v>100.184943</v>
       </c>
       <c r="R534" s="6" t="n">
-        <v>98.324331</v>
+        <v>98.32441300000001</v>
       </c>
       <c r="S534" s="6" t="n">
         <v>101.455128</v>
@@ -44175,7 +44175,7 @@
         <v>100.190012</v>
       </c>
       <c r="R535" s="9" t="n">
-        <v>98.323947</v>
+        <v>98.32435599999999</v>
       </c>
       <c r="S535" s="9" t="n">
         <v>101.422243</v>
@@ -44259,7 +44259,7 @@
         <v>100.153395</v>
       </c>
       <c r="R536" s="6" t="n">
-        <v>98.397749</v>
+        <v>98.398608</v>
       </c>
       <c r="S536" s="6" t="n">
         <v>101.386554</v>
@@ -44343,7 +44343,7 @@
         <v>100.067633</v>
       </c>
       <c r="R537" s="9" t="n">
-        <v>98.57089000000001</v>
+        <v>98.57235900000001</v>
       </c>
       <c r="S537" s="9" t="n">
         <v>101.348927</v>
@@ -44427,7 +44427,7 @@
         <v>99.93831400000001</v>
       </c>
       <c r="R538" s="6" t="n">
-        <v>98.855294</v>
+        <v>98.857551</v>
       </c>
       <c r="S538" s="6" t="n">
         <v>101.311315</v>
@@ -44511,7 +44511,7 @@
         <v>99.782419</v>
       </c>
       <c r="R539" s="9" t="n">
-        <v>99.23741200000001</v>
+        <v>99.24061500000001</v>
       </c>
       <c r="S539" s="9" t="n">
         <v>101.271822</v>
@@ -44595,7 +44595,7 @@
         <v>99.62300399999999</v>
       </c>
       <c r="R540" s="6" t="n">
-        <v>99.667238</v>
+        <v>99.671474</v>
       </c>
       <c r="S540" s="6" t="n">
         <v>101.22625</v>
@@ -44679,7 +44679,7 @@
         <v>99.470253</v>
       </c>
       <c r="R541" s="9" t="n">
-        <v>100.115067</v>
+        <v>100.120381</v>
       </c>
       <c r="S541" s="9" t="n">
         <v>101.170281</v>
@@ -44763,7 +44763,7 @@
         <v>99.333169</v>
       </c>
       <c r="R542" s="6" t="n">
-        <v>100.53274</v>
+        <v>100.539107</v>
       </c>
       <c r="S542" s="6" t="n">
         <v>101.10261</v>
@@ -44847,7 +44847,7 @@
         <v>99.21830799999999</v>
       </c>
       <c r="R543" s="9" t="n">
-        <v>100.886346</v>
+        <v>100.893692</v>
       </c>
       <c r="S543" s="9" t="n">
         <v>101.022522</v>
@@ -44931,7 +44931,7 @@
         <v>99.14349799999999</v>
       </c>
       <c r="R544" s="6" t="n">
-        <v>101.165426</v>
+        <v>101.173664</v>
       </c>
       <c r="S544" s="6" t="n">
         <v>100.929824</v>
@@ -45015,7 +45015,7 @@
         <v>99.123283</v>
       </c>
       <c r="R545" s="9" t="n">
-        <v>101.357244</v>
+        <v>101.366267</v>
       </c>
       <c r="S545" s="9" t="n">
         <v>100.822778</v>
@@ -45099,7 +45099,7 @@
         <v>99.161889</v>
       </c>
       <c r="R546" s="6" t="n">
-        <v>101.461922</v>
+        <v>101.471623</v>
       </c>
       <c r="S546" s="6" t="n">
         <v>100.699946</v>
@@ -45183,7 +45183,7 @@
         <v>99.24835899999999</v>
       </c>
       <c r="R547" s="9" t="n">
-        <v>101.473213</v>
+        <v>101.483478</v>
       </c>
       <c r="S547" s="9" t="n">
         <v>100.559297</v>
@@ -45267,7 +45267,7 @@
         <v>99.369235</v>
       </c>
       <c r="R548" s="6" t="n">
-        <v>101.396573</v>
+        <v>101.407294</v>
       </c>
       <c r="S548" s="6" t="n">
         <v>100.403452</v>
@@ -45351,7 +45351,7 @@
         <v>99.511323</v>
       </c>
       <c r="R549" s="9" t="n">
-        <v>101.247851</v>
+        <v>101.258942</v>
       </c>
       <c r="S549" s="9" t="n">
         <v>100.234336</v>
@@ -45435,7 +45435,7 @@
         <v>99.65178400000001</v>
       </c>
       <c r="R550" s="6" t="n">
-        <v>101.048854</v>
+        <v>101.060263</v>
       </c>
       <c r="S550" s="6" t="n">
         <v>100.059178</v>
@@ -45519,7 +45519,7 @@
         <v>99.78225</v>
       </c>
       <c r="R551" s="9" t="n">
-        <v>100.834673</v>
+        <v>100.846396</v>
       </c>
       <c r="S551" s="9" t="n">
         <v>99.883934</v>
@@ -45603,7 +45603,7 @@
         <v>99.910884</v>
       </c>
       <c r="R552" s="6" t="n">
-        <v>100.630632</v>
+        <v>100.642705</v>
       </c>
       <c r="S552" s="6" t="n">
         <v>99.716537</v>
@@ -45687,7 +45687,7 @@
         <v>100.046594</v>
       </c>
       <c r="R553" s="9" t="n">
-        <v>100.448813</v>
+        <v>100.461288</v>
       </c>
       <c r="S553" s="9" t="n">
         <v>99.56632999999999</v>
@@ -45771,7 +45771,7 @@
         <v>100.186579</v>
       </c>
       <c r="R554" s="6" t="n">
-        <v>100.281068</v>
+        <v>100.293988</v>
       </c>
       <c r="S554" s="6" t="n">
         <v>99.434381</v>
@@ -45855,7 +45855,7 @@
         <v>100.317047</v>
       </c>
       <c r="R555" s="9" t="n">
-        <v>100.119486</v>
+        <v>100.132884</v>
       </c>
       <c r="S555" s="9" t="n">
         <v>99.31686999999999</v>
@@ -45939,7 +45939,7 @@
         <v>100.437709</v>
       </c>
       <c r="R556" s="6" t="n">
-        <v>99.959986</v>
+        <v>99.97389</v>
       </c>
       <c r="S556" s="6" t="n">
         <v>99.212073</v>
@@ -46023,7 +46023,7 @@
         <v>100.547861</v>
       </c>
       <c r="R557" s="9" t="n">
-        <v>99.806404</v>
+        <v>99.82084399999999</v>
       </c>
       <c r="S557" s="9" t="n">
         <v>99.11922300000001</v>
@@ -46107,7 +46107,7 @@
         <v>100.639832</v>
       </c>
       <c r="R558" s="6" t="n">
-        <v>99.676424</v>
+        <v>99.691451</v>
       </c>
       <c r="S558" s="6" t="n">
         <v>99.036744</v>
@@ -46191,7 +46191,7 @@
         <v>100.694158</v>
       </c>
       <c r="R559" s="9" t="n">
-        <v>99.591228</v>
+        <v>99.60691</v>
       </c>
       <c r="S559" s="9" t="n">
         <v>98.96260599999999</v>
@@ -46275,7 +46275,7 @@
         <v>100.696326</v>
       </c>
       <c r="R560" s="6" t="n">
-        <v>99.562355</v>
+        <v>99.578755</v>
       </c>
       <c r="S560" s="6" t="n">
         <v>98.89219</v>
@@ -46359,7 +46359,7 @@
         <v>100.658182</v>
       </c>
       <c r="R561" s="9" t="n">
-        <v>99.568915</v>
+        <v>99.586032</v>
       </c>
       <c r="S561" s="9" t="n">
         <v>98.82422699999999</v>
@@ -46443,7 +46443,7 @@
         <v>100.59035</v>
       </c>
       <c r="R562" s="6" t="n">
-        <v>99.595789</v>
+        <v>99.613556</v>
       </c>
       <c r="S562" s="6" t="n">
         <v>98.76428199999999</v>
@@ -46527,7 +46527,7 @@
         <v>100.496565</v>
       </c>
       <c r="R563" s="9" t="n">
-        <v>99.62963999999999</v>
+        <v>99.647916</v>
       </c>
       <c r="S563" s="9" t="n">
         <v>98.71851100000001</v>
@@ -46611,7 +46611,7 @@
         <v>100.383987</v>
       </c>
       <c r="R564" s="6" t="n">
-        <v>99.659767</v>
+        <v>99.678352</v>
       </c>
       <c r="S564" s="6" t="n">
         <v>98.688209</v>
@@ -46685,7 +46685,7 @@
         <v>100.257128</v>
       </c>
       <c r="R565" s="9" t="n">
-        <v>99.68128400000001</v>
+        <v>99.69994800000001</v>
       </c>
       <c r="S565" s="9" t="n">
         <v>98.66841700000001</v>

--- a/downloads/indicadores/SIC/SIC_datos.xlsx
+++ b/downloads/indicadores/SIC/SIC_datos.xlsx
@@ -6222,7 +6222,7 @@
         <v>100.777559</v>
       </c>
       <c r="K78" s="6" t="n">
-        <v>104.289335</v>
+        <v>104.298415</v>
       </c>
       <c r="L78" s="6" t="n">
         <v>99.94879</v>
@@ -6302,7 +6302,7 @@
         <v>100.570453</v>
       </c>
       <c r="K79" s="9" t="n">
-        <v>103.646816</v>
+        <v>103.654521</v>
       </c>
       <c r="L79" s="9" t="n">
         <v>99.825017</v>
@@ -6382,7 +6382,7 @@
         <v>100.321374</v>
       </c>
       <c r="K80" s="6" t="n">
-        <v>103.019302</v>
+        <v>103.025664</v>
       </c>
       <c r="L80" s="6" t="n">
         <v>99.712158</v>
@@ -6462,7 +6462,7 @@
         <v>100.034504</v>
       </c>
       <c r="K81" s="9" t="n">
-        <v>102.41951</v>
+        <v>102.424589</v>
       </c>
       <c r="L81" s="9" t="n">
         <v>99.60315199999999</v>
@@ -6542,7 +6542,7 @@
         <v>99.70409100000001</v>
       </c>
       <c r="K82" s="6" t="n">
-        <v>101.873629</v>
+        <v>101.877539</v>
       </c>
       <c r="L82" s="6" t="n">
         <v>99.48755800000001</v>
@@ -6622,7 +6622,7 @@
         <v>99.352118</v>
       </c>
       <c r="K83" s="9" t="n">
-        <v>101.391763</v>
+        <v>101.394641</v>
       </c>
       <c r="L83" s="9" t="n">
         <v>99.353064</v>
@@ -6702,7 +6702,7 @@
         <v>99.02132</v>
       </c>
       <c r="K84" s="6" t="n">
-        <v>100.983042</v>
+        <v>100.985046</v>
       </c>
       <c r="L84" s="6" t="n">
         <v>99.194975</v>
@@ -6782,7 +6782,7 @@
         <v>98.741837</v>
       </c>
       <c r="K85" s="9" t="n">
-        <v>100.601494</v>
+        <v>100.602681</v>
       </c>
       <c r="L85" s="9" t="n">
         <v>99.027541</v>
@@ -6862,7 +6862,7 @@
         <v>98.53317</v>
       </c>
       <c r="K86" s="6" t="n">
-        <v>100.235581</v>
+        <v>100.235985</v>
       </c>
       <c r="L86" s="6" t="n">
         <v>98.86608699999999</v>
@@ -6942,7 +6942,7 @@
         <v>98.401658</v>
       </c>
       <c r="K87" s="9" t="n">
-        <v>99.87891500000001</v>
+        <v>99.87855500000001</v>
       </c>
       <c r="L87" s="9" t="n">
         <v>98.72607000000001</v>
@@ -7022,7 +7022,7 @@
         <v>98.348884</v>
       </c>
       <c r="K88" s="6" t="n">
-        <v>99.569655</v>
+        <v>99.568634</v>
       </c>
       <c r="L88" s="6" t="n">
         <v>98.617874</v>
@@ -7102,7 +7102,7 @@
         <v>98.387186</v>
       </c>
       <c r="K89" s="9" t="n">
-        <v>99.317193</v>
+        <v>99.315631</v>
       </c>
       <c r="L89" s="9" t="n">
         <v>98.546494</v>
@@ -7182,7 +7182,7 @@
         <v>98.515604</v>
       </c>
       <c r="K90" s="6" t="n">
-        <v>99.061466</v>
+        <v>99.05935700000001</v>
       </c>
       <c r="L90" s="6" t="n">
         <v>98.51190200000001</v>
@@ -7264,7 +7264,7 @@
         <v>98.71991300000001</v>
       </c>
       <c r="K91" s="9" t="n">
-        <v>98.80621600000001</v>
+        <v>98.80356</v>
       </c>
       <c r="L91" s="9" t="n">
         <v>98.516383</v>
@@ -7346,7 +7346,7 @@
         <v>98.972651</v>
       </c>
       <c r="K92" s="6" t="n">
-        <v>98.54302</v>
+        <v>98.539801</v>
       </c>
       <c r="L92" s="6" t="n">
         <v>98.5592</v>
@@ -7428,7 +7428,7 @@
         <v>99.232417</v>
       </c>
       <c r="K93" s="9" t="n">
-        <v>98.28119100000001</v>
+        <v>98.277411</v>
       </c>
       <c r="L93" s="9" t="n">
         <v>98.640883</v>
@@ -7510,7 +7510,7 @@
         <v>99.465391</v>
       </c>
       <c r="K94" s="6" t="n">
-        <v>98.054463</v>
+        <v>98.05019799999999</v>
       </c>
       <c r="L94" s="6" t="n">
         <v>98.76139999999999</v>
@@ -7592,7 +7592,7 @@
         <v>99.654354</v>
       </c>
       <c r="K95" s="9" t="n">
-        <v>97.970572</v>
+        <v>97.966127</v>
       </c>
       <c r="L95" s="9" t="n">
         <v>98.913512</v>
@@ -7674,7 +7674,7 @@
         <v>99.797794</v>
       </c>
       <c r="K96" s="6" t="n">
-        <v>98.000958</v>
+        <v>97.996578</v>
       </c>
       <c r="L96" s="6" t="n">
         <v>99.08424100000001</v>
@@ -7756,7 +7756,7 @@
         <v>99.89845800000001</v>
       </c>
       <c r="K97" s="9" t="n">
-        <v>98.078969</v>
+        <v>98.07475599999999</v>
       </c>
       <c r="L97" s="9" t="n">
         <v>99.25591900000001</v>
@@ -7838,7 +7838,7 @@
         <v>99.95576199999999</v>
       </c>
       <c r="K98" s="6" t="n">
-        <v>98.129921</v>
+        <v>98.125816</v>
       </c>
       <c r="L98" s="6" t="n">
         <v>99.40737900000001</v>
@@ -7920,7 +7920,7 @@
         <v>99.95500800000001</v>
       </c>
       <c r="K99" s="9" t="n">
-        <v>98.11904699999999</v>
+        <v>98.114919</v>
       </c>
       <c r="L99" s="9" t="n">
         <v>99.51046100000001</v>
@@ -8002,7 +8002,7 @@
         <v>99.899019</v>
       </c>
       <c r="K100" s="6" t="n">
-        <v>98.040356</v>
+        <v>98.03605899999999</v>
       </c>
       <c r="L100" s="6" t="n">
         <v>99.547225</v>
@@ -8084,7 +8084,7 @@
         <v>99.795023</v>
       </c>
       <c r="K101" s="9" t="n">
-        <v>97.90533600000001</v>
+        <v>97.90075</v>
       </c>
       <c r="L101" s="9" t="n">
         <v>99.51947</v>
@@ -8166,7 +8166,7 @@
         <v>99.652359</v>
       </c>
       <c r="K102" s="6" t="n">
-        <v>97.748147</v>
+        <v>97.743225</v>
       </c>
       <c r="L102" s="6" t="n">
         <v>99.452657</v>
@@ -8248,7 +8248,7 @@
         <v>99.498048</v>
       </c>
       <c r="K103" s="9" t="n">
-        <v>97.598297</v>
+        <v>97.593054</v>
       </c>
       <c r="L103" s="9" t="n">
         <v>99.37315700000001</v>
@@ -8330,7 +8330,7 @@
         <v>99.34424799999999</v>
       </c>
       <c r="K104" s="6" t="n">
-        <v>97.479089</v>
+        <v>97.47359</v>
       </c>
       <c r="L104" s="6" t="n">
         <v>99.29202100000001</v>
@@ -8412,7 +8412,7 @@
         <v>99.21383899999999</v>
       </c>
       <c r="K105" s="9" t="n">
-        <v>97.407427</v>
+        <v>97.401775</v>
       </c>
       <c r="L105" s="9" t="n">
         <v>99.21389600000001</v>
@@ -8494,7 +8494,7 @@
         <v>99.126107</v>
       </c>
       <c r="K106" s="6" t="n">
-        <v>97.406656</v>
+        <v>97.40100200000001</v>
       </c>
       <c r="L106" s="6" t="n">
         <v>99.13916500000001</v>
@@ -8576,7 +8576,7 @@
         <v>99.093529</v>
       </c>
       <c r="K107" s="9" t="n">
-        <v>97.449709</v>
+        <v>97.444147</v>
       </c>
       <c r="L107" s="9" t="n">
         <v>99.06715699999999</v>
@@ -8658,7 +8658,7 @@
         <v>99.11807899999999</v>
       </c>
       <c r="K108" s="6" t="n">
-        <v>97.547055</v>
+        <v>97.541701</v>
       </c>
       <c r="L108" s="6" t="n">
         <v>98.999554</v>
@@ -8740,7 +8740,7 @@
         <v>99.22349699999999</v>
       </c>
       <c r="K109" s="9" t="n">
-        <v>97.70594</v>
+        <v>97.700925</v>
       </c>
       <c r="L109" s="9" t="n">
         <v>98.939651</v>
@@ -8822,7 +8822,7 @@
         <v>99.37839200000001</v>
       </c>
       <c r="K110" s="6" t="n">
-        <v>97.907746</v>
+        <v>97.90316300000001</v>
       </c>
       <c r="L110" s="6" t="n">
         <v>98.89703299999999</v>
@@ -8904,7 +8904,7 @@
         <v>99.566131</v>
       </c>
       <c r="K111" s="9" t="n">
-        <v>98.112183</v>
+        <v>98.10803799999999</v>
       </c>
       <c r="L111" s="9" t="n">
         <v>98.878773</v>
@@ -8986,7 +8986,7 @@
         <v>99.756495</v>
       </c>
       <c r="K112" s="6" t="n">
-        <v>98.259783</v>
+        <v>98.25595300000001</v>
       </c>
       <c r="L112" s="6" t="n">
         <v>98.88274199999999</v>
@@ -9068,7 +9068,7 @@
         <v>99.911468</v>
       </c>
       <c r="K113" s="9" t="n">
-        <v>98.351167</v>
+        <v>98.347533</v>
       </c>
       <c r="L113" s="9" t="n">
         <v>98.90213900000001</v>
@@ -9150,7 +9150,7 @@
         <v>100.021312</v>
       </c>
       <c r="K114" s="6" t="n">
-        <v>98.39564900000001</v>
+        <v>98.392109</v>
       </c>
       <c r="L114" s="6" t="n">
         <v>98.932323</v>
@@ -9232,7 +9232,7 @@
         <v>100.091356</v>
       </c>
       <c r="K115" s="9" t="n">
-        <v>98.43132199999999</v>
+        <v>98.427858</v>
       </c>
       <c r="L115" s="9" t="n">
         <v>98.971503</v>
@@ -9314,7 +9314,7 @@
         <v>100.135609</v>
       </c>
       <c r="K116" s="6" t="n">
-        <v>98.495778</v>
+        <v>98.492452</v>
       </c>
       <c r="L116" s="6" t="n">
         <v>99.01414</v>
@@ -9396,7 +9396,7 @@
         <v>100.164723</v>
       </c>
       <c r="K117" s="9" t="n">
-        <v>98.614211</v>
+        <v>98.611138</v>
       </c>
       <c r="L117" s="9" t="n">
         <v>99.06422499999999</v>
@@ -9478,7 +9478,7 @@
         <v>100.171398</v>
       </c>
       <c r="K118" s="6" t="n">
-        <v>98.776996</v>
+        <v>98.774271</v>
       </c>
       <c r="L118" s="6" t="n">
         <v>99.128767</v>
@@ -9560,7 +9560,7 @@
         <v>100.14881</v>
       </c>
       <c r="K119" s="9" t="n">
-        <v>98.980935</v>
+        <v>98.978646</v>
       </c>
       <c r="L119" s="9" t="n">
         <v>99.21220700000001</v>
@@ -9642,7 +9642,7 @@
         <v>100.084549</v>
       </c>
       <c r="K120" s="6" t="n">
-        <v>99.212197</v>
+        <v>99.210403</v>
       </c>
       <c r="L120" s="6" t="n">
         <v>99.313259</v>
@@ -9724,7 +9724,7 @@
         <v>99.99422800000001</v>
       </c>
       <c r="K121" s="9" t="n">
-        <v>99.441013</v>
+        <v>99.439707</v>
       </c>
       <c r="L121" s="9" t="n">
         <v>99.42873299999999</v>
@@ -9806,7 +9806,7 @@
         <v>99.894998</v>
       </c>
       <c r="K122" s="6" t="n">
-        <v>99.619978</v>
+        <v>99.619056</v>
       </c>
       <c r="L122" s="6" t="n">
         <v>99.551625</v>
@@ -9888,7 +9888,7 @@
         <v>99.827461</v>
       </c>
       <c r="K123" s="9" t="n">
-        <v>99.665385</v>
+        <v>99.664559</v>
       </c>
       <c r="L123" s="9" t="n">
         <v>99.67785499999999</v>
@@ -9970,7 +9970,7 @@
         <v>99.819624</v>
       </c>
       <c r="K124" s="6" t="n">
-        <v>99.61575999999999</v>
+        <v>99.614828</v>
       </c>
       <c r="L124" s="6" t="n">
         <v>99.801344</v>
@@ -10052,7 +10052,7 @@
         <v>99.885834</v>
       </c>
       <c r="K125" s="9" t="n">
-        <v>99.505506</v>
+        <v>99.504338</v>
       </c>
       <c r="L125" s="9" t="n">
         <v>99.928741</v>
@@ -10134,7 +10134,7 @@
         <v>100.022789</v>
       </c>
       <c r="K126" s="6" t="n">
-        <v>99.33804600000001</v>
+        <v>99.336519</v>
       </c>
       <c r="L126" s="6" t="n">
         <v>100.067618</v>
@@ -10216,7 +10216,7 @@
         <v>100.198667</v>
       </c>
       <c r="K127" s="9" t="n">
-        <v>99.218339</v>
+        <v>99.216555</v>
       </c>
       <c r="L127" s="9" t="n">
         <v>100.222847</v>
@@ -10298,7 +10298,7 @@
         <v>100.393657</v>
       </c>
       <c r="K128" s="6" t="n">
-        <v>99.24671600000001</v>
+        <v>99.244992</v>
       </c>
       <c r="L128" s="6" t="n">
         <v>100.394859</v>
@@ -10380,7 +10380,7 @@
         <v>100.564093</v>
       </c>
       <c r="K129" s="9" t="n">
-        <v>99.382544</v>
+        <v>99.381111</v>
       </c>
       <c r="L129" s="9" t="n">
         <v>100.582563</v>
@@ -10462,7 +10462,7 @@
         <v>100.713018</v>
       </c>
       <c r="K130" s="6" t="n">
-        <v>99.605757</v>
+        <v>99.60480099999999</v>
       </c>
       <c r="L130" s="6" t="n">
         <v>100.779769</v>
@@ -10544,7 +10544,7 @@
         <v>100.82097</v>
       </c>
       <c r="K131" s="9" t="n">
-        <v>99.88426800000001</v>
+        <v>99.88390699999999</v>
       </c>
       <c r="L131" s="9" t="n">
         <v>100.984909</v>
@@ -10626,7 +10626,7 @@
         <v>100.88146</v>
       </c>
       <c r="K132" s="6" t="n">
-        <v>100.181806</v>
+        <v>100.182081</v>
       </c>
       <c r="L132" s="6" t="n">
         <v>101.194144</v>
@@ -10708,7 +10708,7 @@
         <v>100.889203</v>
       </c>
       <c r="K133" s="9" t="n">
-        <v>100.493326</v>
+        <v>100.494266</v>
       </c>
       <c r="L133" s="9" t="n">
         <v>101.403197</v>
@@ -10790,7 +10790,7 @@
         <v>100.850625</v>
       </c>
       <c r="K134" s="6" t="n">
-        <v>100.812299</v>
+        <v>100.813921</v>
       </c>
       <c r="L134" s="6" t="n">
         <v>101.606379</v>
@@ -10872,7 +10872,7 @@
         <v>100.777227</v>
       </c>
       <c r="K135" s="9" t="n">
-        <v>101.15277</v>
+        <v>101.15512</v>
       </c>
       <c r="L135" s="9" t="n">
         <v>101.797846</v>
@@ -10954,7 +10954,7 @@
         <v>100.678754</v>
       </c>
       <c r="K136" s="6" t="n">
-        <v>101.505461</v>
+        <v>101.508565</v>
       </c>
       <c r="L136" s="6" t="n">
         <v>101.978377</v>
@@ -11036,7 +11036,7 @@
         <v>100.583776</v>
       </c>
       <c r="K137" s="9" t="n">
-        <v>101.754668</v>
+        <v>101.758304</v>
       </c>
       <c r="L137" s="9" t="n">
         <v>102.148385</v>
@@ -11118,7 +11118,7 @@
         <v>100.516769</v>
       </c>
       <c r="K138" s="6" t="n">
-        <v>101.91526</v>
+        <v>101.91924</v>
       </c>
       <c r="L138" s="6" t="n">
         <v>102.303445</v>
@@ -11200,7 +11200,7 @@
         <v>100.473621</v>
       </c>
       <c r="K139" s="9" t="n">
-        <v>101.994321</v>
+        <v>101.998472</v>
       </c>
       <c r="L139" s="9" t="n">
         <v>102.44182</v>
@@ -11282,7 +11282,7 @@
         <v>100.448401</v>
       </c>
       <c r="K140" s="6" t="n">
-        <v>102.042615</v>
+        <v>102.046873</v>
       </c>
       <c r="L140" s="6" t="n">
         <v>102.561421</v>
@@ -11364,7 +11364,7 @@
         <v>100.439634</v>
       </c>
       <c r="K141" s="9" t="n">
-        <v>102.080255</v>
+        <v>102.0846</v>
       </c>
       <c r="L141" s="9" t="n">
         <v>102.661869</v>
@@ -11446,7 +11446,7 @@
         <v>100.424116</v>
       </c>
       <c r="K142" s="6" t="n">
-        <v>102.101033</v>
+        <v>102.105431</v>
       </c>
       <c r="L142" s="6" t="n">
         <v>102.745657</v>
@@ -11528,7 +11528,7 @@
         <v>100.399163</v>
       </c>
       <c r="K143" s="9" t="n">
-        <v>102.112351</v>
+        <v>102.116785</v>
       </c>
       <c r="L143" s="9" t="n">
         <v>102.807129</v>
@@ -11610,7 +11610,7 @@
         <v>100.383126</v>
       </c>
       <c r="K144" s="6" t="n">
-        <v>102.16398</v>
+        <v>102.168534</v>
       </c>
       <c r="L144" s="6" t="n">
         <v>102.844488</v>
@@ -11692,7 +11692,7 @@
         <v>100.377542</v>
       </c>
       <c r="K145" s="9" t="n">
-        <v>102.285528</v>
+        <v>102.290348</v>
       </c>
       <c r="L145" s="9" t="n">
         <v>102.862739</v>
@@ -11774,7 +11774,7 @@
         <v>100.394198</v>
       </c>
       <c r="K146" s="6" t="n">
-        <v>102.523173</v>
+        <v>102.528495</v>
       </c>
       <c r="L146" s="6" t="n">
         <v>102.864919</v>
@@ -11856,7 +11856,7 @@
         <v>100.426517</v>
       </c>
       <c r="K147" s="9" t="n">
-        <v>102.901625</v>
+        <v>102.907744</v>
       </c>
       <c r="L147" s="9" t="n">
         <v>102.850605</v>
@@ -11938,7 +11938,7 @@
         <v>100.43304</v>
       </c>
       <c r="K148" s="6" t="n">
-        <v>103.368241</v>
+        <v>103.375347</v>
       </c>
       <c r="L148" s="6" t="n">
         <v>102.813314</v>
@@ -12020,7 +12020,7 @@
         <v>100.436697</v>
       </c>
       <c r="K149" s="9" t="n">
-        <v>103.848114</v>
+        <v>103.856236</v>
       </c>
       <c r="L149" s="9" t="n">
         <v>102.748735</v>
@@ -12102,7 +12102,7 @@
         <v>100.475758</v>
       </c>
       <c r="K150" s="6" t="n">
-        <v>104.2818</v>
+        <v>104.290843</v>
       </c>
       <c r="L150" s="6" t="n">
         <v>102.652354</v>
@@ -12184,7 +12184,7 @@
         <v>100.580672</v>
       </c>
       <c r="K151" s="9" t="n">
-        <v>104.625881</v>
+        <v>104.635656</v>
       </c>
       <c r="L151" s="9" t="n">
         <v>102.521451</v>
@@ -12266,7 +12266,7 @@
         <v>100.719477</v>
       </c>
       <c r="K152" s="6" t="n">
-        <v>104.788795</v>
+        <v>104.798917</v>
       </c>
       <c r="L152" s="6" t="n">
         <v>102.359896</v>
@@ -12348,7 +12348,7 @@
         <v>100.835074</v>
       </c>
       <c r="K153" s="9" t="n">
-        <v>104.697419</v>
+        <v>104.707346</v>
       </c>
       <c r="L153" s="9" t="n">
         <v>102.178178</v>
@@ -12430,7 +12430,7 @@
         <v>100.933444</v>
       </c>
       <c r="K154" s="6" t="n">
-        <v>104.395293</v>
+        <v>104.404577</v>
       </c>
       <c r="L154" s="6" t="n">
         <v>101.993376</v>
@@ -12512,7 +12512,7 @@
         <v>100.984415</v>
       </c>
       <c r="K155" s="9" t="n">
-        <v>103.991529</v>
+        <v>103.999955</v>
       </c>
       <c r="L155" s="9" t="n">
         <v>101.81796</v>
@@ -12594,7 +12594,7 @@
         <v>100.969963</v>
       </c>
       <c r="K156" s="6" t="n">
-        <v>103.570982</v>
+        <v>103.578517</v>
       </c>
       <c r="L156" s="6" t="n">
         <v>101.660902</v>
@@ -12676,7 +12676,7 @@
         <v>100.897067</v>
       </c>
       <c r="K157" s="9" t="n">
-        <v>103.194555</v>
+        <v>103.201294</v>
       </c>
       <c r="L157" s="9" t="n">
         <v>101.518364</v>
@@ -12758,7 +12758,7 @@
         <v>100.806436</v>
       </c>
       <c r="K158" s="6" t="n">
-        <v>102.921303</v>
+        <v>102.927466</v>
       </c>
       <c r="L158" s="6" t="n">
         <v>101.386728</v>
@@ -12840,7 +12840,7 @@
         <v>100.707513</v>
       </c>
       <c r="K159" s="9" t="n">
-        <v>102.757004</v>
+        <v>102.762817</v>
       </c>
       <c r="L159" s="9" t="n">
         <v>101.264668</v>
@@ -12922,7 +12922,7 @@
         <v>100.622354</v>
       </c>
       <c r="K160" s="6" t="n">
-        <v>102.699444</v>
+        <v>102.705123</v>
       </c>
       <c r="L160" s="6" t="n">
         <v>101.158839</v>
@@ -13004,7 +13004,7 @@
         <v>100.58554</v>
       </c>
       <c r="K161" s="9" t="n">
-        <v>102.724229</v>
+        <v>102.729944</v>
       </c>
       <c r="L161" s="9" t="n">
         <v>101.07511</v>
@@ -13086,7 +13086,7 @@
         <v>100.605765</v>
       </c>
       <c r="K162" s="6" t="n">
-        <v>102.75448</v>
+        <v>102.760237</v>
       </c>
       <c r="L162" s="6" t="n">
         <v>101.015554</v>
@@ -13168,7 +13168,7 @@
         <v>100.669182</v>
       </c>
       <c r="K163" s="9" t="n">
-        <v>102.723108</v>
+        <v>102.728776</v>
       </c>
       <c r="L163" s="9" t="n">
         <v>100.972908</v>
@@ -13250,7 +13250,7 @@
         <v>100.713813</v>
       </c>
       <c r="K164" s="6" t="n">
-        <v>102.595642</v>
+        <v>102.601019</v>
       </c>
       <c r="L164" s="6" t="n">
         <v>100.931648</v>
@@ -13332,7 +13332,7 @@
         <v>100.711479</v>
       </c>
       <c r="K165" s="9" t="n">
-        <v>102.352284</v>
+        <v>102.357131</v>
       </c>
       <c r="L165" s="9" t="n">
         <v>100.867833</v>
@@ -13414,7 +13414,7 @@
         <v>100.67648</v>
       </c>
       <c r="K166" s="6" t="n">
-        <v>102.004471</v>
+        <v>102.008582</v>
       </c>
       <c r="L166" s="6" t="n">
         <v>100.759148</v>
@@ -13496,7 +13496,7 @@
         <v>100.629585</v>
       </c>
       <c r="K167" s="9" t="n">
-        <v>101.575376</v>
+        <v>101.57859</v>
       </c>
       <c r="L167" s="9" t="n">
         <v>100.597146</v>
@@ -13578,7 +13578,7 @@
         <v>100.594698</v>
       </c>
       <c r="K168" s="6" t="n">
-        <v>101.097429</v>
+        <v>101.099653</v>
       </c>
       <c r="L168" s="6" t="n">
         <v>100.386884</v>
@@ -13660,7 +13660,7 @@
         <v>100.57889</v>
       </c>
       <c r="K169" s="9" t="n">
-        <v>100.612974</v>
+        <v>100.614207</v>
       </c>
       <c r="L169" s="9" t="n">
         <v>100.148146</v>
@@ -13742,7 +13742,7 @@
         <v>100.59143</v>
       </c>
       <c r="K170" s="6" t="n">
-        <v>100.195414</v>
+        <v>100.19581</v>
       </c>
       <c r="L170" s="6" t="n">
         <v>99.911027</v>
@@ -13824,7 +13824,7 @@
         <v>100.645437</v>
       </c>
       <c r="K171" s="9" t="n">
-        <v>99.969994</v>
+        <v>99.969973</v>
       </c>
       <c r="L171" s="9" t="n">
         <v>99.706137</v>
@@ -13906,7 +13906,7 @@
         <v>100.745986</v>
       </c>
       <c r="K172" s="6" t="n">
-        <v>99.976045</v>
+        <v>99.976099</v>
       </c>
       <c r="L172" s="6" t="n">
         <v>99.556597</v>
@@ -13988,7 +13988,7 @@
         <v>100.891905</v>
       </c>
       <c r="K173" s="9" t="n">
-        <v>100.238827</v>
+        <v>100.239479</v>
       </c>
       <c r="L173" s="9" t="n">
         <v>99.469658</v>
@@ -14070,7 +14070,7 @@
         <v>101.06454</v>
       </c>
       <c r="K174" s="6" t="n">
-        <v>100.675683</v>
+        <v>100.677236</v>
       </c>
       <c r="L174" s="6" t="n">
         <v>99.443105</v>
@@ -14152,7 +14152,7 @@
         <v>101.24947</v>
       </c>
       <c r="K175" s="9" t="n">
-        <v>101.18275</v>
+        <v>101.185328</v>
       </c>
       <c r="L175" s="9" t="n">
         <v>99.47326</v>
@@ -14234,7 +14234,7 @@
         <v>101.436306</v>
       </c>
       <c r="K176" s="6" t="n">
-        <v>101.652857</v>
+        <v>101.65638</v>
       </c>
       <c r="L176" s="6" t="n">
         <v>99.546398</v>
@@ -14316,7 +14316,7 @@
         <v>101.58721</v>
       </c>
       <c r="K177" s="9" t="n">
-        <v>102.064394</v>
+        <v>102.068748</v>
       </c>
       <c r="L177" s="9" t="n">
         <v>99.64872200000001</v>
@@ -14398,7 +14398,7 @@
         <v>101.645436</v>
       </c>
       <c r="K178" s="6" t="n">
-        <v>102.392473</v>
+        <v>102.397492</v>
       </c>
       <c r="L178" s="6" t="n">
         <v>99.762888</v>
@@ -14480,7 +14480,7 @@
         <v>101.646348</v>
       </c>
       <c r="K179" s="9" t="n">
-        <v>102.61362</v>
+        <v>102.61909</v>
       </c>
       <c r="L179" s="9" t="n">
         <v>99.875248</v>
@@ -14562,7 +14562,7 @@
         <v>101.607516</v>
       </c>
       <c r="K180" s="6" t="n">
-        <v>102.727561</v>
+        <v>102.733264</v>
       </c>
       <c r="L180" s="6" t="n">
         <v>99.974761</v>
@@ -14644,7 +14644,7 @@
         <v>101.520731</v>
       </c>
       <c r="K181" s="9" t="n">
-        <v>102.746027</v>
+        <v>102.751765</v>
       </c>
       <c r="L181" s="9" t="n">
         <v>100.042863</v>
@@ -14726,7 +14726,7 @@
         <v>101.345464</v>
       </c>
       <c r="K182" s="6" t="n">
-        <v>102.650359</v>
+        <v>102.655893</v>
       </c>
       <c r="L182" s="6" t="n">
         <v>100.055979</v>
@@ -14808,7 +14808,7 @@
         <v>101.039437</v>
       </c>
       <c r="K183" s="9" t="n">
-        <v>102.419935</v>
+        <v>102.424978</v>
       </c>
       <c r="L183" s="9" t="n">
         <v>99.990279</v>
@@ -14890,7 +14890,7 @@
         <v>100.573974</v>
       </c>
       <c r="K184" s="6" t="n">
-        <v>102.048834</v>
+        <v>102.053085</v>
       </c>
       <c r="L184" s="6" t="n">
         <v>99.812718</v>
@@ -14972,7 +14972,7 @@
         <v>99.933902</v>
       </c>
       <c r="K185" s="9" t="n">
-        <v>101.540476</v>
+        <v>101.543643</v>
       </c>
       <c r="L185" s="9" t="n">
         <v>99.506129</v>
@@ -15054,7 +15054,7 @@
         <v>99.137591</v>
       </c>
       <c r="K186" s="6" t="n">
-        <v>100.913547</v>
+        <v>100.915375</v>
       </c>
       <c r="L186" s="6" t="n">
         <v>99.076477</v>
@@ -15136,7 +15136,7 @@
         <v>98.270338</v>
       </c>
       <c r="K187" s="9" t="n">
-        <v>100.078509</v>
+        <v>100.078551</v>
       </c>
       <c r="L187" s="9" t="n">
         <v>98.54845400000001</v>
@@ -15218,7 +15218,7 @@
         <v>97.439446</v>
       </c>
       <c r="K188" s="6" t="n">
-        <v>99.054705</v>
+        <v>99.05255699999999</v>
       </c>
       <c r="L188" s="6" t="n">
         <v>97.973736</v>
@@ -15300,7 +15300,7 @@
         <v>96.731899</v>
       </c>
       <c r="K189" s="9" t="n">
-        <v>97.935231</v>
+        <v>97.930689</v>
       </c>
       <c r="L189" s="9" t="n">
         <v>97.407055</v>
@@ -15382,7 +15382,7 @@
         <v>96.230408</v>
       </c>
       <c r="K190" s="6" t="n">
-        <v>96.96047299999999</v>
+        <v>96.953846</v>
       </c>
       <c r="L190" s="6" t="n">
         <v>96.884603</v>
@@ -15464,7 +15464,7 @@
         <v>95.960842</v>
       </c>
       <c r="K191" s="9" t="n">
-        <v>96.23979300000001</v>
+        <v>96.231624</v>
       </c>
       <c r="L191" s="9" t="n">
         <v>96.434763</v>
@@ -15546,7 +15546,7 @@
         <v>95.908733</v>
       </c>
       <c r="K192" s="6" t="n">
-        <v>95.778074</v>
+        <v>95.768917</v>
       </c>
       <c r="L192" s="6" t="n">
         <v>96.074258</v>
@@ -15628,7 +15628,7 @@
         <v>96.043942</v>
       </c>
       <c r="K193" s="9" t="n">
-        <v>95.535878</v>
+        <v>95.52620400000001</v>
       </c>
       <c r="L193" s="9" t="n">
         <v>95.814539</v>
@@ -15710,7 +15710,7 @@
         <v>96.33393100000001</v>
       </c>
       <c r="K194" s="6" t="n">
-        <v>95.44728499999999</v>
+        <v>95.437422</v>
       </c>
       <c r="L194" s="6" t="n">
         <v>95.659972</v>
@@ -15792,7 +15792,7 @@
         <v>96.73128800000001</v>
       </c>
       <c r="K195" s="9" t="n">
-        <v>95.465045</v>
+        <v>95.45522</v>
       </c>
       <c r="L195" s="9" t="n">
         <v>95.60636599999999</v>
@@ -15874,7 +15874,7 @@
         <v>97.181674</v>
       </c>
       <c r="K196" s="6" t="n">
-        <v>95.56017</v>
+        <v>95.550549</v>
       </c>
       <c r="L196" s="6" t="n">
         <v>95.645771</v>
@@ -15956,7 +15956,7 @@
         <v>97.627257</v>
       </c>
       <c r="K197" s="9" t="n">
-        <v>95.70973499999999</v>
+        <v>95.700435</v>
       </c>
       <c r="L197" s="9" t="n">
         <v>95.767191</v>
@@ -16038,7 +16038,7 @@
         <v>97.97762899999999</v>
       </c>
       <c r="K198" s="6" t="n">
-        <v>95.931072</v>
+        <v>95.922246</v>
       </c>
       <c r="L198" s="6" t="n">
         <v>95.95566599999999</v>
@@ -16120,7 +16120,7 @@
         <v>98.228292</v>
       </c>
       <c r="K199" s="9" t="n">
-        <v>96.144018</v>
+        <v>96.135649</v>
       </c>
       <c r="L199" s="9" t="n">
         <v>96.190055</v>
@@ -16202,7 +16202,7 @@
         <v>98.40825700000001</v>
       </c>
       <c r="K200" s="6" t="n">
-        <v>96.308395</v>
+        <v>96.30037799999999</v>
       </c>
       <c r="L200" s="6" t="n">
         <v>96.447711</v>
@@ -16284,7 +16284,7 @@
         <v>98.53738800000001</v>
       </c>
       <c r="K201" s="9" t="n">
-        <v>96.409863</v>
+        <v>96.402064</v>
       </c>
       <c r="L201" s="9" t="n">
         <v>96.708462</v>
@@ -16366,7 +16366,7 @@
         <v>98.64767399999999</v>
       </c>
       <c r="K202" s="6" t="n">
-        <v>96.46722</v>
+        <v>96.45954399999999</v>
       </c>
       <c r="L202" s="6" t="n">
         <v>96.962307</v>
@@ -16448,7 +16448,7 @@
         <v>98.743802</v>
       </c>
       <c r="K203" s="9" t="n">
-        <v>96.49041</v>
+        <v>96.48278500000001</v>
       </c>
       <c r="L203" s="9" t="n">
         <v>97.20365200000001</v>
@@ -16530,7 +16530,7 @@
         <v>98.82535300000001</v>
       </c>
       <c r="K204" s="6" t="n">
-        <v>96.506287</v>
+        <v>96.498696</v>
       </c>
       <c r="L204" s="6" t="n">
         <v>97.432541</v>
@@ -16612,7 +16612,7 @@
         <v>98.912744</v>
       </c>
       <c r="K205" s="9" t="n">
-        <v>96.5429</v>
+        <v>96.535388</v>
       </c>
       <c r="L205" s="9" t="n">
         <v>97.659094</v>
@@ -16694,7 +16694,7 @@
         <v>99.024647</v>
       </c>
       <c r="K206" s="6" t="n">
-        <v>96.62825599999999</v>
+        <v>96.62092800000001</v>
       </c>
       <c r="L206" s="6" t="n">
         <v>97.89322799999999</v>
@@ -16776,7 +16776,7 @@
         <v>99.16342400000001</v>
       </c>
       <c r="K207" s="9" t="n">
-        <v>96.779528</v>
+        <v>96.772524</v>
       </c>
       <c r="L207" s="9" t="n">
         <v>98.14591900000001</v>
@@ -16858,7 +16858,7 @@
         <v>99.303696</v>
       </c>
       <c r="K208" s="6" t="n">
-        <v>97.000163</v>
+        <v>96.99363099999999</v>
       </c>
       <c r="L208" s="6" t="n">
         <v>98.419324</v>
@@ -16940,7 +16940,7 @@
         <v>99.4211</v>
       </c>
       <c r="K209" s="9" t="n">
-        <v>97.285556</v>
+        <v>97.279636</v>
       </c>
       <c r="L209" s="9" t="n">
         <v>98.712219</v>
@@ -17022,7 +17022,7 @@
         <v>99.50048</v>
       </c>
       <c r="K210" s="6" t="n">
-        <v>97.640727</v>
+        <v>97.63556800000001</v>
       </c>
       <c r="L210" s="6" t="n">
         <v>99.017067</v>
@@ -17104,7 +17104,7 @@
         <v>99.588167</v>
       </c>
       <c r="K211" s="9" t="n">
-        <v>97.995588</v>
+        <v>97.99118900000001</v>
       </c>
       <c r="L211" s="9" t="n">
         <v>99.33753299999999</v>
@@ -17186,7 +17186,7 @@
         <v>99.708342</v>
       </c>
       <c r="K212" s="6" t="n">
-        <v>98.30702599999999</v>
+        <v>98.30329399999999</v>
       </c>
       <c r="L212" s="6" t="n">
         <v>99.658978</v>
@@ -17268,7 +17268,7 @@
         <v>99.867265</v>
       </c>
       <c r="K213" s="9" t="n">
-        <v>98.566974</v>
+        <v>98.563799</v>
       </c>
       <c r="L213" s="9" t="n">
         <v>99.970547</v>
@@ -17350,7 +17350,7 @@
         <v>100.050824</v>
       </c>
       <c r="K214" s="6" t="n">
-        <v>98.78594699999999</v>
+        <v>98.78324000000001</v>
       </c>
       <c r="L214" s="6" t="n">
         <v>100.255419</v>
@@ -17432,7 +17432,7 @@
         <v>100.242871</v>
       </c>
       <c r="K215" s="9" t="n">
-        <v>98.984549</v>
+        <v>98.982269</v>
       </c>
       <c r="L215" s="9" t="n">
         <v>100.493988</v>
@@ -17514,7 +17514,7 @@
         <v>100.429831</v>
       </c>
       <c r="K216" s="6" t="n">
-        <v>99.179137</v>
+        <v>99.177273</v>
       </c>
       <c r="L216" s="6" t="n">
         <v>100.672919</v>
@@ -17596,7 +17596,7 @@
         <v>100.607078</v>
       </c>
       <c r="K217" s="9" t="n">
-        <v>99.36601</v>
+        <v>99.364546</v>
       </c>
       <c r="L217" s="9" t="n">
         <v>100.780714</v>
@@ -17678,7 +17678,7 @@
         <v>100.778066</v>
       </c>
       <c r="K218" s="6" t="n">
-        <v>99.53536800000001</v>
+        <v>99.534267</v>
       </c>
       <c r="L218" s="6" t="n">
         <v>100.814908</v>
@@ -17760,7 +17760,7 @@
         <v>100.951909</v>
       </c>
       <c r="K219" s="9" t="n">
-        <v>99.689088</v>
+        <v>99.688317</v>
       </c>
       <c r="L219" s="9" t="n">
         <v>100.785847</v>
@@ -17842,7 +17842,7 @@
         <v>101.125429</v>
       </c>
       <c r="K220" s="6" t="n">
-        <v>99.817003</v>
+        <v>99.81650500000001</v>
       </c>
       <c r="L220" s="6" t="n">
         <v>100.717263</v>
@@ -17924,7 +17924,7 @@
         <v>101.294647</v>
       </c>
       <c r="K221" s="9" t="n">
-        <v>99.93130499999999</v>
+        <v>99.93105300000001</v>
       </c>
       <c r="L221" s="9" t="n">
         <v>100.63525</v>
@@ -18006,7 +18006,7 @@
         <v>101.453106</v>
       </c>
       <c r="K222" s="6" t="n">
-        <v>100.048351</v>
+        <v>100.048349</v>
       </c>
       <c r="L222" s="6" t="n">
         <v>100.563292</v>
@@ -18088,7 +18088,7 @@
         <v>101.575015</v>
       </c>
       <c r="K223" s="9" t="n">
-        <v>100.172717</v>
+        <v>100.172982</v>
       </c>
       <c r="L223" s="9" t="n">
         <v>100.50313</v>
@@ -18170,7 +18170,7 @@
         <v>101.629263</v>
       </c>
       <c r="K224" s="6" t="n">
-        <v>100.278334</v>
+        <v>100.278825</v>
       </c>
       <c r="L224" s="6" t="n">
         <v>100.454836</v>
@@ -18252,7 +18252,7 @@
         <v>101.606145</v>
       </c>
       <c r="K225" s="9" t="n">
-        <v>100.35004</v>
+        <v>100.350685</v>
       </c>
       <c r="L225" s="9" t="n">
         <v>100.414439</v>
@@ -18334,7 +18334,7 @@
         <v>101.522112</v>
       </c>
       <c r="K226" s="6" t="n">
-        <v>100.377922</v>
+        <v>100.378627</v>
       </c>
       <c r="L226" s="6" t="n">
         <v>100.381583</v>
@@ -18416,7 +18416,7 @@
         <v>101.399479</v>
       </c>
       <c r="K227" s="9" t="n">
-        <v>100.351741</v>
+        <v>100.352391</v>
       </c>
       <c r="L227" s="9" t="n">
         <v>100.362878</v>
@@ -18498,7 +18498,7 @@
         <v>101.27543</v>
       </c>
       <c r="K228" s="6" t="n">
-        <v>100.269891</v>
+        <v>100.270366</v>
       </c>
       <c r="L228" s="6" t="n">
         <v>100.356834</v>
@@ -18580,7 +18580,7 @@
         <v>101.166822</v>
       </c>
       <c r="K229" s="9" t="n">
-        <v>100.13138</v>
+        <v>100.131558</v>
       </c>
       <c r="L229" s="9" t="n">
         <v>100.358683</v>
@@ -18662,7 +18662,7 @@
         <v>101.076543</v>
       </c>
       <c r="K230" s="6" t="n">
-        <v>99.917388</v>
+        <v>99.917109</v>
       </c>
       <c r="L230" s="6" t="n">
         <v>100.367118</v>
@@ -18744,7 +18744,7 @@
         <v>101.009401</v>
       </c>
       <c r="K231" s="9" t="n">
-        <v>99.694766</v>
+        <v>99.69401000000001</v>
       </c>
       <c r="L231" s="9" t="n">
         <v>100.380282</v>
@@ -18826,7 +18826,7 @@
         <v>100.963615</v>
       </c>
       <c r="K232" s="6" t="n">
-        <v>99.51988299999999</v>
+        <v>99.518754</v>
       </c>
       <c r="L232" s="6" t="n">
         <v>100.398545</v>
@@ -18908,7 +18908,7 @@
         <v>100.933077</v>
       </c>
       <c r="K233" s="9" t="n">
-        <v>99.430218</v>
+        <v>99.42889700000001</v>
       </c>
       <c r="L233" s="9" t="n">
         <v>100.423575</v>
@@ -18990,7 +18990,7 @@
         <v>100.900827</v>
       </c>
       <c r="K234" s="6" t="n">
-        <v>99.44541599999999</v>
+        <v>99.44412800000001</v>
       </c>
       <c r="L234" s="6" t="n">
         <v>100.455848</v>
@@ -19072,7 +19072,7 @@
         <v>100.859093</v>
       </c>
       <c r="K235" s="9" t="n">
-        <v>99.561797</v>
+        <v>99.56075800000001</v>
       </c>
       <c r="L235" s="9" t="n">
         <v>100.495583</v>
@@ -19154,7 +19154,7 @@
         <v>100.801506</v>
       </c>
       <c r="K236" s="6" t="n">
-        <v>99.73794700000001</v>
+        <v>99.737286</v>
       </c>
       <c r="L236" s="6" t="n">
         <v>100.54252</v>
@@ -19236,7 +19236,7 @@
         <v>100.724126</v>
       </c>
       <c r="K237" s="9" t="n">
-        <v>99.881823</v>
+        <v>99.881469</v>
       </c>
       <c r="L237" s="9" t="n">
         <v>100.594537</v>
@@ -19318,7 +19318,7 @@
         <v>100.626731</v>
       </c>
       <c r="K238" s="6" t="n">
-        <v>100.010722</v>
+        <v>100.010644</v>
       </c>
       <c r="L238" s="6" t="n">
         <v>100.651441</v>
@@ -19400,7 +19400,7 @@
         <v>100.537224</v>
       </c>
       <c r="K239" s="9" t="n">
-        <v>100.1142</v>
+        <v>100.114344</v>
       </c>
       <c r="L239" s="9" t="n">
         <v>100.712058</v>
@@ -19482,7 +19482,7 @@
         <v>100.484435</v>
       </c>
       <c r="K240" s="6" t="n">
-        <v>100.15203</v>
+        <v>100.152255</v>
       </c>
       <c r="L240" s="6" t="n">
         <v>100.780679</v>
@@ -19564,7 +19564,7 @@
         <v>100.484262</v>
       </c>
       <c r="K241" s="9" t="n">
-        <v>100.166327</v>
+        <v>100.166583</v>
       </c>
       <c r="L241" s="9" t="n">
         <v>100.864976</v>
@@ -19646,7 +19646,7 @@
         <v>100.542528</v>
       </c>
       <c r="K242" s="6" t="n">
-        <v>100.195671</v>
+        <v>100.195989</v>
       </c>
       <c r="L242" s="6" t="n">
         <v>100.966771</v>
@@ -19728,7 +19728,7 @@
         <v>100.656953</v>
       </c>
       <c r="K243" s="9" t="n">
-        <v>100.252566</v>
+        <v>100.253007</v>
       </c>
       <c r="L243" s="9" t="n">
         <v>101.081875</v>
@@ -19810,7 +19810,7 @@
         <v>100.838987</v>
       </c>
       <c r="K244" s="6" t="n">
-        <v>100.332312</v>
+        <v>100.332923</v>
       </c>
       <c r="L244" s="6" t="n">
         <v>101.207008</v>
@@ -19892,7 +19892,7 @@
         <v>101.079846</v>
       </c>
       <c r="K245" s="9" t="n">
-        <v>100.429212</v>
+        <v>100.43003</v>
       </c>
       <c r="L245" s="9" t="n">
         <v>101.335547</v>
@@ -19974,7 +19974,7 @@
         <v>101.356756</v>
       </c>
       <c r="K246" s="6" t="n">
-        <v>100.553274</v>
+        <v>100.554359</v>
       </c>
       <c r="L246" s="6" t="n">
         <v>101.466596</v>
@@ -20056,7 +20056,7 @@
         <v>101.629364</v>
       </c>
       <c r="K247" s="9" t="n">
-        <v>100.702628</v>
+        <v>100.704032</v>
       </c>
       <c r="L247" s="9" t="n">
         <v>101.59637</v>
@@ -20138,7 +20138,7 @@
         <v>101.859741</v>
       </c>
       <c r="K248" s="6" t="n">
-        <v>100.886198</v>
+        <v>100.887995</v>
       </c>
       <c r="L248" s="6" t="n">
         <v>101.727801</v>
@@ -20220,7 +20220,7 @@
         <v>102.033347</v>
       </c>
       <c r="K249" s="9" t="n">
-        <v>101.109039</v>
+        <v>101.111313</v>
       </c>
       <c r="L249" s="9" t="n">
         <v>101.866996</v>
@@ -20302,7 +20302,7 @@
         <v>102.153983</v>
       </c>
       <c r="K250" s="6" t="n">
-        <v>101.337369</v>
+        <v>101.340132</v>
       </c>
       <c r="L250" s="6" t="n">
         <v>102.021401</v>
@@ -20384,7 +20384,7 @@
         <v>102.207856</v>
       </c>
       <c r="K251" s="9" t="n">
-        <v>101.539257</v>
+        <v>101.542452</v>
       </c>
       <c r="L251" s="9" t="n">
         <v>102.186555</v>
@@ -20466,7 +20466,7 @@
         <v>102.172985</v>
       </c>
       <c r="K252" s="6" t="n">
-        <v>101.686106</v>
+        <v>101.689615</v>
       </c>
       <c r="L252" s="6" t="n">
         <v>102.350154</v>
@@ -20548,7 +20548,7 @@
         <v>102.038678</v>
       </c>
       <c r="K253" s="9" t="n">
-        <v>101.772693</v>
+        <v>101.776388</v>
       </c>
       <c r="L253" s="9" t="n">
         <v>102.496698</v>
@@ -20630,7 +20630,7 @@
         <v>101.830025</v>
       </c>
       <c r="K254" s="6" t="n">
-        <v>101.800175</v>
+        <v>101.803929</v>
       </c>
       <c r="L254" s="6" t="n">
         <v>102.607274</v>
@@ -20712,7 +20712,7 @@
         <v>101.576864</v>
       </c>
       <c r="K255" s="9" t="n">
-        <v>101.771385</v>
+        <v>101.775077</v>
       </c>
       <c r="L255" s="9" t="n">
         <v>102.669066</v>
@@ -20794,7 +20794,7 @@
         <v>101.309553</v>
       </c>
       <c r="K256" s="6" t="n">
-        <v>101.707713</v>
+        <v>101.711268</v>
       </c>
       <c r="L256" s="6" t="n">
         <v>102.672369</v>
@@ -20876,7 +20876,7 @@
         <v>101.067248</v>
       </c>
       <c r="K257" s="9" t="n">
-        <v>101.637145</v>
+        <v>101.640549</v>
       </c>
       <c r="L257" s="9" t="n">
         <v>102.617983</v>
@@ -20958,7 +20958,7 @@
         <v>100.878459</v>
       </c>
       <c r="K258" s="6" t="n">
-        <v>101.572106</v>
+        <v>101.575371</v>
       </c>
       <c r="L258" s="6" t="n">
         <v>102.513589</v>
@@ -21040,7 +21040,7 @@
         <v>100.698828</v>
       </c>
       <c r="K259" s="9" t="n">
-        <v>101.481747</v>
+        <v>101.484819</v>
       </c>
       <c r="L259" s="9" t="n">
         <v>102.363902</v>
@@ -21122,7 +21122,7 @@
         <v>100.521928</v>
       </c>
       <c r="K260" s="6" t="n">
-        <v>101.348308</v>
+        <v>101.351094</v>
       </c>
       <c r="L260" s="6" t="n">
         <v>102.174057</v>
@@ -21204,7 +21204,7 @@
         <v>100.364414</v>
       </c>
       <c r="K261" s="9" t="n">
-        <v>101.177377</v>
+        <v>101.179797</v>
       </c>
       <c r="L261" s="9" t="n">
         <v>101.954128</v>
@@ -21286,7 +21286,7 @@
         <v>100.236646</v>
       </c>
       <c r="K262" s="6" t="n">
-        <v>100.993291</v>
+        <v>100.995317</v>
       </c>
       <c r="L262" s="6" t="n">
         <v>101.70767</v>
@@ -21368,7 +21368,7 @@
         <v>100.122365</v>
       </c>
       <c r="K263" s="9" t="n">
-        <v>100.819885</v>
+        <v>100.821541</v>
       </c>
       <c r="L263" s="9" t="n">
         <v>101.444033</v>
@@ -21450,7 +21450,7 @@
         <v>100.00604</v>
       </c>
       <c r="K264" s="6" t="n">
-        <v>100.669753</v>
+        <v>100.671087</v>
       </c>
       <c r="L264" s="6" t="n">
         <v>101.173492</v>
@@ -21532,7 +21532,7 @@
         <v>99.86980200000001</v>
       </c>
       <c r="K265" s="9" t="n">
-        <v>100.551696</v>
+        <v>100.552776</v>
       </c>
       <c r="L265" s="9" t="n">
         <v>100.906596</v>
@@ -21614,7 +21614,7 @@
         <v>99.699366</v>
       </c>
       <c r="K266" s="6" t="n">
-        <v>100.45681</v>
+        <v>100.457688</v>
       </c>
       <c r="L266" s="6" t="n">
         <v>100.656017</v>
@@ -21696,7 +21696,7 @@
         <v>99.489704</v>
       </c>
       <c r="K267" s="9" t="n">
-        <v>100.37279</v>
+        <v>100.373488</v>
       </c>
       <c r="L267" s="9" t="n">
         <v>100.436181</v>
@@ -21778,7 +21778,7 @@
         <v>99.265398</v>
       </c>
       <c r="K268" s="6" t="n">
-        <v>100.297442</v>
+        <v>100.297978</v>
       </c>
       <c r="L268" s="6" t="n">
         <v>100.252847</v>
@@ -21860,7 +21860,7 @@
         <v>99.032257</v>
       </c>
       <c r="K269" s="9" t="n">
-        <v>100.224563</v>
+        <v>100.224944</v>
       </c>
       <c r="L269" s="9" t="n">
         <v>100.10565</v>
@@ -21942,7 +21942,7 @@
         <v>98.817561</v>
       </c>
       <c r="K270" s="6" t="n">
-        <v>100.158796</v>
+        <v>100.159035</v>
       </c>
       <c r="L270" s="6" t="n">
         <v>99.988736</v>
@@ -22024,7 +22024,7 @@
         <v>98.66233200000001</v>
       </c>
       <c r="K271" s="9" t="n">
-        <v>100.103595</v>
+        <v>100.103716</v>
       </c>
       <c r="L271" s="9" t="n">
         <v>99.903561</v>
@@ -22106,7 +22106,7 @@
         <v>98.60550499999999</v>
       </c>
       <c r="K272" s="6" t="n">
-        <v>100.049402</v>
+        <v>100.049406</v>
       </c>
       <c r="L272" s="6" t="n">
         <v>99.848242</v>
@@ -22188,7 +22188,7 @@
         <v>98.63034500000001</v>
       </c>
       <c r="K273" s="9" t="n">
-        <v>99.988682</v>
+        <v>99.988556</v>
       </c>
       <c r="L273" s="9" t="n">
         <v>99.818977</v>
@@ -22270,7 +22270,7 @@
         <v>98.69931</v>
       </c>
       <c r="K274" s="6" t="n">
-        <v>99.92123599999999</v>
+        <v>99.92096600000001</v>
       </c>
       <c r="L274" s="6" t="n">
         <v>99.80368799999999</v>
@@ -22352,7 +22352,7 @@
         <v>98.802026</v>
       </c>
       <c r="K275" s="9" t="n">
-        <v>99.844556</v>
+        <v>99.844121</v>
       </c>
       <c r="L275" s="9" t="n">
         <v>99.788872</v>
@@ -22434,7 +22434,7 @@
         <v>98.924543</v>
       </c>
       <c r="K276" s="6" t="n">
-        <v>99.765474</v>
+        <v>99.76487</v>
       </c>
       <c r="L276" s="6" t="n">
         <v>99.76721499999999</v>
@@ -22516,7 +22516,7 @@
         <v>99.046228</v>
       </c>
       <c r="K277" s="9" t="n">
-        <v>99.681878</v>
+        <v>99.681094</v>
       </c>
       <c r="L277" s="9" t="n">
         <v>99.73115300000001</v>
@@ -22598,7 +22598,7 @@
         <v>99.135785</v>
       </c>
       <c r="K278" s="6" t="n">
-        <v>99.589933</v>
+        <v>99.588953</v>
       </c>
       <c r="L278" s="6" t="n">
         <v>99.681287</v>
@@ -22680,7 +22680,7 @@
         <v>99.174409</v>
       </c>
       <c r="K279" s="9" t="n">
-        <v>99.49827399999999</v>
+        <v>99.497097</v>
       </c>
       <c r="L279" s="9" t="n">
         <v>99.614457</v>
@@ -22762,7 +22762,7 @@
         <v>99.144828</v>
       </c>
       <c r="K280" s="6" t="n">
-        <v>99.411023</v>
+        <v>99.409659</v>
       </c>
       <c r="L280" s="6" t="n">
         <v>99.534943</v>
@@ -22844,7 +22844,7 @@
         <v>99.059608</v>
       </c>
       <c r="K281" s="9" t="n">
-        <v>99.323667</v>
+        <v>99.322115</v>
       </c>
       <c r="L281" s="9" t="n">
         <v>99.44505100000001</v>
@@ -22926,7 +22926,7 @@
         <v>98.961314</v>
       </c>
       <c r="K282" s="6" t="n">
-        <v>99.234064</v>
+        <v>99.232321</v>
       </c>
       <c r="L282" s="6" t="n">
         <v>99.343169</v>
@@ -23008,7 +23008,7 @@
         <v>98.89430900000001</v>
       </c>
       <c r="K283" s="9" t="n">
-        <v>99.151257</v>
+        <v>99.14933600000001</v>
       </c>
       <c r="L283" s="9" t="n">
         <v>99.227654</v>
@@ -23090,7 +23090,7 @@
         <v>98.847026</v>
       </c>
       <c r="K284" s="6" t="n">
-        <v>99.08225899999999</v>
+        <v>99.08019</v>
       </c>
       <c r="L284" s="6" t="n">
         <v>99.098427</v>
@@ -23172,7 +23172,7 @@
         <v>98.819878</v>
       </c>
       <c r="K285" s="9" t="n">
-        <v>99.040262</v>
+        <v>99.03810199999999</v>
       </c>
       <c r="L285" s="9" t="n">
         <v>98.957534</v>
@@ -23254,7 +23254,7 @@
         <v>98.80480300000001</v>
       </c>
       <c r="K286" s="6" t="n">
-        <v>99.024997</v>
+        <v>99.02280399999999</v>
       </c>
       <c r="L286" s="6" t="n">
         <v>98.813729</v>
@@ -23336,7 +23336,7 @@
         <v>98.79048</v>
       </c>
       <c r="K287" s="9" t="n">
-        <v>99.03238899999999</v>
+        <v>99.03021099999999</v>
       </c>
       <c r="L287" s="9" t="n">
         <v>98.68025299999999</v>
@@ -23418,7 +23418,7 @@
         <v>98.769066</v>
       </c>
       <c r="K288" s="6" t="n">
-        <v>99.05274199999999</v>
+        <v>99.050608</v>
       </c>
       <c r="L288" s="6" t="n">
         <v>98.567509</v>
@@ -23500,7 +23500,7 @@
         <v>98.752287</v>
       </c>
       <c r="K289" s="9" t="n">
-        <v>99.087112</v>
+        <v>99.08505</v>
       </c>
       <c r="L289" s="9" t="n">
         <v>98.486598</v>
@@ -23582,7 +23582,7 @@
         <v>98.760458</v>
       </c>
       <c r="K290" s="6" t="n">
-        <v>99.142983</v>
+        <v>99.14104</v>
       </c>
       <c r="L290" s="6" t="n">
         <v>98.44338999999999</v>
@@ -23664,7 +23664,7 @@
         <v>98.811789</v>
       </c>
       <c r="K291" s="9" t="n">
-        <v>99.22634600000001</v>
+        <v>99.22458</v>
       </c>
       <c r="L291" s="9" t="n">
         <v>98.431883</v>
@@ -23746,7 +23746,7 @@
         <v>98.910783</v>
       </c>
       <c r="K292" s="6" t="n">
-        <v>99.334693</v>
+        <v>99.33315899999999</v>
       </c>
       <c r="L292" s="6" t="n">
         <v>98.44416200000001</v>
@@ -23828,7 +23828,7 @@
         <v>99.06177</v>
       </c>
       <c r="K293" s="9" t="n">
-        <v>99.464417</v>
+        <v>99.46316</v>
       </c>
       <c r="L293" s="9" t="n">
         <v>98.472281</v>
@@ -23910,7 +23910,7 @@
         <v>99.23747899999999</v>
       </c>
       <c r="K294" s="6" t="n">
-        <v>99.60565</v>
+        <v>99.60469399999999</v>
       </c>
       <c r="L294" s="6" t="n">
         <v>98.510863</v>
@@ -23994,7 +23994,7 @@
         <v>99.416667</v>
       </c>
       <c r="K295" s="9" t="n">
-        <v>99.75257999999999</v>
+        <v>99.751938</v>
       </c>
       <c r="L295" s="9" t="n">
         <v>98.558933</v>
@@ -24078,7 +24078,7 @@
         <v>99.57662000000001</v>
       </c>
       <c r="K296" s="6" t="n">
-        <v>99.905202</v>
+        <v>99.90488499999999</v>
       </c>
       <c r="L296" s="6" t="n">
         <v>98.614593</v>
@@ -24162,7 +24162,7 @@
         <v>99.68022499999999</v>
       </c>
       <c r="K297" s="9" t="n">
-        <v>100.044115</v>
+        <v>100.044095</v>
       </c>
       <c r="L297" s="9" t="n">
         <v>98.669754</v>
@@ -24246,7 +24246,7 @@
         <v>99.725082</v>
       </c>
       <c r="K298" s="6" t="n">
-        <v>100.156064</v>
+        <v>100.156282</v>
       </c>
       <c r="L298" s="6" t="n">
         <v>98.72021100000001</v>
@@ -24330,7 +24330,7 @@
         <v>99.726629</v>
       </c>
       <c r="K299" s="9" t="n">
-        <v>100.249586</v>
+        <v>100.250004</v>
       </c>
       <c r="L299" s="9" t="n">
         <v>98.76418099999999</v>
@@ -24414,7 +24414,7 @@
         <v>99.696996</v>
       </c>
       <c r="K300" s="6" t="n">
-        <v>100.339951</v>
+        <v>100.340562</v>
       </c>
       <c r="L300" s="6" t="n">
         <v>98.803584</v>
@@ -24498,7 +24498,7 @@
         <v>99.659678</v>
       </c>
       <c r="K301" s="9" t="n">
-        <v>100.423474</v>
+        <v>100.424262</v>
       </c>
       <c r="L301" s="9" t="n">
         <v>98.840957</v>
@@ -24582,7 +24582,7 @@
         <v>99.630871</v>
       </c>
       <c r="K302" s="6" t="n">
-        <v>100.513088</v>
+        <v>100.514066</v>
       </c>
       <c r="L302" s="6" t="n">
         <v>98.877566</v>
@@ -24666,7 +24666,7 @@
         <v>99.616765</v>
       </c>
       <c r="K303" s="9" t="n">
-        <v>100.594217</v>
+        <v>100.595368</v>
       </c>
       <c r="L303" s="9" t="n">
         <v>98.916799</v>
@@ -24750,7 +24750,7 @@
         <v>99.61432499999999</v>
       </c>
       <c r="K304" s="6" t="n">
-        <v>100.644792</v>
+        <v>100.646051</v>
       </c>
       <c r="L304" s="6" t="n">
         <v>98.962076</v>
@@ -24834,7 +24834,7 @@
         <v>99.619725</v>
       </c>
       <c r="K305" s="9" t="n">
-        <v>100.645766</v>
+        <v>100.647025</v>
       </c>
       <c r="L305" s="9" t="n">
         <v>99.007672</v>
@@ -24918,7 +24918,7 @@
         <v>99.625196</v>
       </c>
       <c r="K306" s="6" t="n">
-        <v>100.613699</v>
+        <v>100.614888</v>
       </c>
       <c r="L306" s="6" t="n">
         <v>99.049937</v>
@@ -25002,7 +25002,7 @@
         <v>99.623008</v>
       </c>
       <c r="K307" s="9" t="n">
-        <v>100.559321</v>
+        <v>100.560393</v>
       </c>
       <c r="L307" s="9" t="n">
         <v>99.08619299999999</v>
@@ -25086,7 +25086,7 @@
         <v>99.608045</v>
       </c>
       <c r="K308" s="6" t="n">
-        <v>100.486382</v>
+        <v>100.487296</v>
       </c>
       <c r="L308" s="6" t="n">
         <v>99.11828</v>
@@ -25170,7 +25170,7 @@
         <v>99.587181</v>
       </c>
       <c r="K309" s="9" t="n">
-        <v>100.393753</v>
+        <v>100.394468</v>
       </c>
       <c r="L309" s="9" t="n">
         <v>99.152708</v>
@@ -25254,7 +25254,7 @@
         <v>99.567351</v>
       </c>
       <c r="K310" s="6" t="n">
-        <v>100.313261</v>
+        <v>100.313802</v>
       </c>
       <c r="L310" s="6" t="n">
         <v>99.193686</v>
@@ -25338,7 +25338,7 @@
         <v>99.56322</v>
       </c>
       <c r="K311" s="9" t="n">
-        <v>100.261019</v>
+        <v>100.261448</v>
       </c>
       <c r="L311" s="9" t="n">
         <v>99.240945</v>
@@ -25422,7 +25422,7 @@
         <v>99.623222</v>
       </c>
       <c r="K312" s="6" t="n">
-        <v>100.261442</v>
+        <v>100.26187</v>
       </c>
       <c r="L312" s="6" t="n">
         <v>99.295922</v>
@@ -25506,7 +25506,7 @@
         <v>99.784924</v>
       </c>
       <c r="K313" s="9" t="n">
-        <v>100.299997</v>
+        <v>100.300506</v>
       </c>
       <c r="L313" s="9" t="n">
         <v>99.36141000000001</v>
@@ -25590,7 +25590,7 @@
         <v>100.018898</v>
       </c>
       <c r="K314" s="6" t="n">
-        <v>100.348298</v>
+        <v>100.348909</v>
       </c>
       <c r="L314" s="6" t="n">
         <v>99.433543</v>
@@ -25674,7 +25674,7 @@
         <v>100.29486</v>
       </c>
       <c r="K315" s="9" t="n">
-        <v>100.370495</v>
+        <v>100.371152</v>
       </c>
       <c r="L315" s="9" t="n">
         <v>99.509973</v>
@@ -25758,7 +25758,7 @@
         <v>100.586342</v>
       </c>
       <c r="K316" s="6" t="n">
-        <v>100.376384</v>
+        <v>100.377053</v>
       </c>
       <c r="L316" s="6" t="n">
         <v>99.590737</v>
@@ -25842,7 +25842,7 @@
         <v>100.855263</v>
       </c>
       <c r="K317" s="9" t="n">
-        <v>100.377538</v>
+        <v>100.378207</v>
       </c>
       <c r="L317" s="9" t="n">
         <v>99.67907099999999</v>
@@ -25926,7 +25926,7 @@
         <v>101.075482</v>
       </c>
       <c r="K318" s="6" t="n">
-        <v>100.374674</v>
+        <v>100.375336</v>
       </c>
       <c r="L318" s="6" t="n">
         <v>99.778291</v>
@@ -26010,7 +26010,7 @@
         <v>101.250123</v>
       </c>
       <c r="K319" s="9" t="n">
-        <v>100.361885</v>
+        <v>100.362518</v>
       </c>
       <c r="L319" s="9" t="n">
         <v>99.887074</v>
@@ -26094,7 +26094,7 @@
         <v>101.400839</v>
       </c>
       <c r="K320" s="6" t="n">
-        <v>100.339948</v>
+        <v>100.340532</v>
       </c>
       <c r="L320" s="6" t="n">
         <v>100.002989</v>
@@ -26178,7 +26178,7 @@
         <v>101.52941</v>
       </c>
       <c r="K321" s="9" t="n">
-        <v>100.3201</v>
+        <v>100.320641</v>
       </c>
       <c r="L321" s="9" t="n">
         <v>100.121683</v>
@@ -26262,7 +26262,7 @@
         <v>101.634813</v>
       </c>
       <c r="K322" s="6" t="n">
-        <v>100.297013</v>
+        <v>100.297503</v>
       </c>
       <c r="L322" s="6" t="n">
         <v>100.239641</v>
@@ -26346,7 +26346,7 @@
         <v>101.704394</v>
       </c>
       <c r="K323" s="9" t="n">
-        <v>100.27467</v>
+        <v>100.275112</v>
       </c>
       <c r="L323" s="9" t="n">
         <v>100.353548</v>
@@ -26430,7 +26430,7 @@
         <v>101.736751</v>
       </c>
       <c r="K324" s="6" t="n">
-        <v>100.260054</v>
+        <v>100.260464</v>
       </c>
       <c r="L324" s="6" t="n">
         <v>100.460196</v>
@@ -26514,7 +26514,7 @@
         <v>101.736143</v>
       </c>
       <c r="K325" s="9" t="n">
-        <v>100.260132</v>
+        <v>100.26054</v>
       </c>
       <c r="L325" s="9" t="n">
         <v>100.558583</v>
@@ -26598,7 +26598,7 @@
         <v>101.705753</v>
       </c>
       <c r="K326" s="6" t="n">
-        <v>100.271406</v>
+        <v>100.271837</v>
       </c>
       <c r="L326" s="6" t="n">
         <v>100.65144</v>
@@ -26682,7 +26682,7 @@
         <v>101.661041</v>
       </c>
       <c r="K327" s="9" t="n">
-        <v>100.2827</v>
+        <v>100.283153</v>
       </c>
       <c r="L327" s="9" t="n">
         <v>100.742419</v>
@@ -26766,7 +26766,7 @@
         <v>101.617399</v>
       </c>
       <c r="K328" s="6" t="n">
-        <v>100.297104</v>
+        <v>100.297585</v>
       </c>
       <c r="L328" s="6" t="n">
         <v>100.835291</v>
@@ -26850,7 +26850,7 @@
         <v>101.591129</v>
       </c>
       <c r="K329" s="9" t="n">
-        <v>100.316054</v>
+        <v>100.316571</v>
       </c>
       <c r="L329" s="9" t="n">
         <v>100.93231</v>
@@ -26934,7 +26934,7 @@
         <v>101.606839</v>
       </c>
       <c r="K330" s="6" t="n">
-        <v>100.3389</v>
+        <v>100.33946</v>
       </c>
       <c r="L330" s="6" t="n">
         <v>101.035795</v>
@@ -27018,7 +27018,7 @@
         <v>101.663269</v>
       </c>
       <c r="K331" s="9" t="n">
-        <v>100.366251</v>
+        <v>100.366862</v>
       </c>
       <c r="L331" s="9" t="n">
         <v>101.140373</v>
@@ -27102,7 +27102,7 @@
         <v>101.733652</v>
       </c>
       <c r="K332" s="6" t="n">
-        <v>100.401</v>
+        <v>100.401677</v>
       </c>
       <c r="L332" s="6" t="n">
         <v>101.240767</v>
@@ -27186,7 +27186,7 @@
         <v>101.785554</v>
       </c>
       <c r="K333" s="9" t="n">
-        <v>100.454335</v>
+        <v>100.455119</v>
       </c>
       <c r="L333" s="9" t="n">
         <v>101.334378</v>
@@ -27270,7 +27270,7 @@
         <v>101.81014</v>
       </c>
       <c r="K334" s="6" t="n">
-        <v>100.529574</v>
+        <v>100.530516</v>
       </c>
       <c r="L334" s="6" t="n">
         <v>101.420657</v>
@@ -27354,7 +27354,7 @@
         <v>101.807362</v>
       </c>
       <c r="K335" s="9" t="n">
-        <v>100.619294</v>
+        <v>100.620435</v>
       </c>
       <c r="L335" s="9" t="n">
         <v>101.502584</v>
@@ -27438,7 +27438,7 @@
         <v>101.783489</v>
       </c>
       <c r="K336" s="6" t="n">
-        <v>100.706536</v>
+        <v>100.707889</v>
       </c>
       <c r="L336" s="6" t="n">
         <v>101.585381</v>
@@ -27522,7 +27522,7 @@
         <v>101.748871</v>
       </c>
       <c r="K337" s="9" t="n">
-        <v>100.779278</v>
+        <v>100.780839</v>
       </c>
       <c r="L337" s="9" t="n">
         <v>101.668291</v>
@@ -27606,7 +27606,7 @@
         <v>101.718057</v>
       </c>
       <c r="K338" s="6" t="n">
-        <v>100.832357</v>
+        <v>100.834122</v>
       </c>
       <c r="L338" s="6" t="n">
         <v>101.750979</v>
@@ -27690,7 +27690,7 @@
         <v>101.693356</v>
       </c>
       <c r="K339" s="9" t="n">
-        <v>100.866847</v>
+        <v>100.868816</v>
       </c>
       <c r="L339" s="9" t="n">
         <v>101.831928</v>
@@ -27774,7 +27774,7 @@
         <v>101.686789</v>
       </c>
       <c r="K340" s="6" t="n">
-        <v>100.892303</v>
+        <v>100.894495</v>
       </c>
       <c r="L340" s="6" t="n">
         <v>101.906327</v>
@@ -27858,7 +27858,7 @@
         <v>101.708914</v>
       </c>
       <c r="K341" s="9" t="n">
-        <v>100.918839</v>
+        <v>100.921267</v>
       </c>
       <c r="L341" s="9" t="n">
         <v>101.966859</v>
@@ -27942,7 +27942,7 @@
         <v>101.745379</v>
       </c>
       <c r="K342" s="6" t="n">
-        <v>100.957647</v>
+        <v>100.960295</v>
       </c>
       <c r="L342" s="6" t="n">
         <v>102.013731</v>
@@ -28026,7 +28026,7 @@
         <v>101.776216</v>
       </c>
       <c r="K343" s="9" t="n">
-        <v>100.982653</v>
+        <v>100.985343</v>
       </c>
       <c r="L343" s="9" t="n">
         <v>102.04583</v>
@@ -28110,7 +28110,7 @@
         <v>101.765782</v>
       </c>
       <c r="K344" s="6" t="n">
-        <v>100.984733</v>
+        <v>100.987183</v>
       </c>
       <c r="L344" s="6" t="n">
         <v>102.061759</v>
@@ -28194,7 +28194,7 @@
         <v>101.733667</v>
       </c>
       <c r="K345" s="9" t="n">
-        <v>100.968518</v>
+        <v>100.970761</v>
       </c>
       <c r="L345" s="9" t="n">
         <v>102.057377</v>
@@ -28278,7 +28278,7 @@
         <v>101.675375</v>
       </c>
       <c r="K346" s="6" t="n">
-        <v>100.921826</v>
+        <v>100.923814</v>
       </c>
       <c r="L346" s="6" t="n">
         <v>102.026541</v>
@@ -28362,7 +28362,7 @@
         <v>101.5661</v>
       </c>
       <c r="K347" s="9" t="n">
-        <v>100.844978</v>
+        <v>100.846693</v>
       </c>
       <c r="L347" s="9" t="n">
         <v>101.959127</v>
@@ -28446,7 +28446,7 @@
         <v>101.369122</v>
       </c>
       <c r="K348" s="6" t="n">
-        <v>100.738959</v>
+        <v>100.740452</v>
       </c>
       <c r="L348" s="6" t="n">
         <v>101.843392</v>
@@ -28530,7 +28530,7 @@
         <v>101.081684</v>
       </c>
       <c r="K349" s="9" t="n">
-        <v>100.610764</v>
+        <v>100.612061</v>
       </c>
       <c r="L349" s="9" t="n">
         <v>101.671949</v>
@@ -28614,7 +28614,7 @@
         <v>100.685709</v>
       </c>
       <c r="K350" s="6" t="n">
-        <v>100.476352</v>
+        <v>100.477315</v>
       </c>
       <c r="L350" s="6" t="n">
         <v>101.440902</v>
@@ -28698,7 +28698,7 @@
         <v>100.16835</v>
       </c>
       <c r="K351" s="9" t="n">
-        <v>100.348684</v>
+        <v>100.349298</v>
       </c>
       <c r="L351" s="9" t="n">
         <v>101.148242</v>
@@ -28782,7 +28782,7 @@
         <v>99.522375</v>
       </c>
       <c r="K352" s="6" t="n">
-        <v>100.233562</v>
+        <v>100.233811</v>
       </c>
       <c r="L352" s="6" t="n">
         <v>100.798077</v>
@@ -28866,7 +28866,7 @@
         <v>98.787548</v>
       </c>
       <c r="K353" s="9" t="n">
-        <v>100.134693</v>
+        <v>100.134667</v>
       </c>
       <c r="L353" s="9" t="n">
         <v>100.404325</v>
@@ -28950,7 +28950,7 @@
         <v>98.03980199999999</v>
       </c>
       <c r="K354" s="6" t="n">
-        <v>100.046103</v>
+        <v>100.045903</v>
       </c>
       <c r="L354" s="6" t="n">
         <v>99.98398400000001</v>
@@ -29034,7 +29034,7 @@
         <v>97.406628</v>
       </c>
       <c r="K355" s="9" t="n">
-        <v>99.956709</v>
+        <v>99.956335</v>
       </c>
       <c r="L355" s="9" t="n">
         <v>99.566142</v>
@@ -29118,7 +29118,7 @@
         <v>96.94768500000001</v>
       </c>
       <c r="K356" s="6" t="n">
-        <v>99.86262000000001</v>
+        <v>99.862144</v>
       </c>
       <c r="L356" s="6" t="n">
         <v>99.176928</v>
@@ -29202,7 +29202,7 @@
         <v>96.686582</v>
       </c>
       <c r="K357" s="9" t="n">
-        <v>99.75608</v>
+        <v>99.755471</v>
       </c>
       <c r="L357" s="9" t="n">
         <v>98.83229799999999</v>
@@ -29286,7 +29286,7 @@
         <v>96.61674499999999</v>
       </c>
       <c r="K358" s="6" t="n">
-        <v>99.654662</v>
+        <v>99.653941</v>
       </c>
       <c r="L358" s="6" t="n">
         <v>98.542553</v>
@@ -29370,7 +29370,7 @@
         <v>96.720698</v>
       </c>
       <c r="K359" s="9" t="n">
-        <v>99.57338300000001</v>
+        <v>99.57240400000001</v>
       </c>
       <c r="L359" s="9" t="n">
         <v>98.316666</v>
@@ -29454,7 +29454,7 @@
         <v>96.966677</v>
       </c>
       <c r="K360" s="6" t="n">
-        <v>99.512595</v>
+        <v>99.51127200000001</v>
       </c>
       <c r="L360" s="6" t="n">
         <v>98.15644399999999</v>
@@ -29538,7 +29538,7 @@
         <v>97.29292599999999</v>
       </c>
       <c r="K361" s="9" t="n">
-        <v>99.464564</v>
+        <v>99.462857</v>
       </c>
       <c r="L361" s="9" t="n">
         <v>98.05853</v>
@@ -29622,7 +29622,7 @@
         <v>97.659109</v>
       </c>
       <c r="K362" s="6" t="n">
-        <v>99.429982</v>
+        <v>99.428117</v>
       </c>
       <c r="L362" s="6" t="n">
         <v>98.016605</v>
@@ -29706,7 +29706,7 @@
         <v>98.020214</v>
       </c>
       <c r="K363" s="9" t="n">
-        <v>99.408844</v>
+        <v>99.406998</v>
       </c>
       <c r="L363" s="9" t="n">
         <v>98.02713</v>
@@ -29790,7 +29790,7 @@
         <v>98.34518799999999</v>
       </c>
       <c r="K364" s="6" t="n">
-        <v>99.40582499999999</v>
+        <v>99.404167</v>
       </c>
       <c r="L364" s="6" t="n">
         <v>98.086822</v>
@@ -29874,7 +29874,7 @@
         <v>98.605935</v>
       </c>
       <c r="K365" s="9" t="n">
-        <v>99.420489</v>
+        <v>99.41912499999999</v>
       </c>
       <c r="L365" s="9" t="n">
         <v>98.18404099999999</v>
@@ -29958,7 +29958,7 @@
         <v>98.801265</v>
       </c>
       <c r="K366" s="6" t="n">
-        <v>99.448779</v>
+        <v>99.447721</v>
       </c>
       <c r="L366" s="6" t="n">
         <v>98.30470699999999</v>
@@ -30042,7 +30042,7 @@
         <v>98.95103400000001</v>
       </c>
       <c r="K367" s="9" t="n">
-        <v>99.493533</v>
+        <v>99.49263500000001</v>
       </c>
       <c r="L367" s="9" t="n">
         <v>98.437279</v>
@@ -30126,7 +30126,7 @@
         <v>99.073775</v>
       </c>
       <c r="K368" s="6" t="n">
-        <v>99.54078</v>
+        <v>99.540002</v>
       </c>
       <c r="L368" s="6" t="n">
         <v>98.570815</v>
@@ -30210,7 +30210,7 @@
         <v>99.159145</v>
       </c>
       <c r="K369" s="9" t="n">
-        <v>99.577088</v>
+        <v>99.576323</v>
       </c>
       <c r="L369" s="9" t="n">
         <v>98.69640099999999</v>
@@ -30294,7 +30294,7 @@
         <v>99.195295</v>
       </c>
       <c r="K370" s="6" t="n">
-        <v>99.60337800000001</v>
+        <v>99.60248199999999</v>
       </c>
       <c r="L370" s="6" t="n">
         <v>98.80901900000001</v>
@@ -30378,7 +30378,7 @@
         <v>99.196333</v>
       </c>
       <c r="K371" s="9" t="n">
-        <v>99.610176</v>
+        <v>99.609188</v>
       </c>
       <c r="L371" s="9" t="n">
         <v>98.90648899999999</v>
@@ -30462,7 +30462,7 @@
         <v>99.177138</v>
       </c>
       <c r="K372" s="6" t="n">
-        <v>99.599675</v>
+        <v>99.598517</v>
       </c>
       <c r="L372" s="6" t="n">
         <v>98.991794</v>
@@ -30546,7 +30546,7 @@
         <v>99.151408</v>
       </c>
       <c r="K373" s="9" t="n">
-        <v>99.575132</v>
+        <v>99.573807</v>
       </c>
       <c r="L373" s="9" t="n">
         <v>99.06857100000001</v>
@@ -30630,7 +30630,7 @@
         <v>99.12123099999999</v>
       </c>
       <c r="K374" s="6" t="n">
-        <v>99.53141100000001</v>
+        <v>99.529931</v>
       </c>
       <c r="L374" s="6" t="n">
         <v>99.13948000000001</v>
@@ -30714,7 +30714,7 @@
         <v>99.103025</v>
       </c>
       <c r="K375" s="9" t="n">
-        <v>99.47676800000001</v>
+        <v>99.475272</v>
       </c>
       <c r="L375" s="9" t="n">
         <v>99.207588</v>
@@ -30798,7 +30798,7 @@
         <v>99.107911</v>
       </c>
       <c r="K376" s="6" t="n">
-        <v>99.422498</v>
+        <v>99.420919</v>
       </c>
       <c r="L376" s="6" t="n">
         <v>99.272052</v>
@@ -30882,7 +30882,7 @@
         <v>99.142009</v>
       </c>
       <c r="K377" s="9" t="n">
-        <v>99.39439299999999</v>
+        <v>99.392731</v>
       </c>
       <c r="L377" s="9" t="n">
         <v>99.33131299999999</v>
@@ -30966,7 +30966,7 @@
         <v>99.195933</v>
       </c>
       <c r="K378" s="6" t="n">
-        <v>99.375062</v>
+        <v>99.373288</v>
       </c>
       <c r="L378" s="6" t="n">
         <v>99.38401</v>
@@ -31050,7 +31050,7 @@
         <v>99.26933699999999</v>
       </c>
       <c r="K379" s="9" t="n">
-        <v>99.359846</v>
+        <v>99.358176</v>
       </c>
       <c r="L379" s="9" t="n">
         <v>99.429638</v>
@@ -31134,7 +31134,7 @@
         <v>99.368239</v>
       </c>
       <c r="K380" s="6" t="n">
-        <v>99.371391</v>
+        <v>99.370008</v>
       </c>
       <c r="L380" s="6" t="n">
         <v>99.467873</v>
@@ -31218,7 +31218,7 @@
         <v>99.48851000000001</v>
       </c>
       <c r="K381" s="9" t="n">
-        <v>99.405869</v>
+        <v>99.404771</v>
       </c>
       <c r="L381" s="9" t="n">
         <v>99.497173</v>
@@ -31302,7 +31302,7 @@
         <v>99.62996200000001</v>
       </c>
       <c r="K382" s="6" t="n">
-        <v>99.4457</v>
+        <v>99.44474700000001</v>
       </c>
       <c r="L382" s="6" t="n">
         <v>99.516845</v>
@@ -31386,7 +31386,7 @@
         <v>99.78041399999999</v>
       </c>
       <c r="K383" s="9" t="n">
-        <v>99.49186899999999</v>
+        <v>99.49094700000001</v>
       </c>
       <c r="L383" s="9" t="n">
         <v>99.53219300000001</v>
@@ -31470,7 +31470,7 @@
         <v>99.930651</v>
       </c>
       <c r="K384" s="6" t="n">
-        <v>99.55290100000001</v>
+        <v>99.55199500000001</v>
       </c>
       <c r="L384" s="6" t="n">
         <v>99.548546</v>
@@ -31554,7 +31554,7 @@
         <v>100.090241</v>
       </c>
       <c r="K385" s="9" t="n">
-        <v>99.639684</v>
+        <v>99.63877599999999</v>
       </c>
       <c r="L385" s="9" t="n">
         <v>99.569684</v>
@@ -31638,7 +31638,7 @@
         <v>100.264956</v>
       </c>
       <c r="K386" s="6" t="n">
-        <v>99.74882599999999</v>
+        <v>99.74797700000001</v>
       </c>
       <c r="L386" s="6" t="n">
         <v>99.598899</v>
@@ -31722,7 +31722,7 @@
         <v>100.456663</v>
       </c>
       <c r="K387" s="9" t="n">
-        <v>99.870052</v>
+        <v>99.86936300000001</v>
       </c>
       <c r="L387" s="9" t="n">
         <v>99.637028</v>
@@ -31806,7 +31806,7 @@
         <v>100.640929</v>
       </c>
       <c r="K388" s="6" t="n">
-        <v>99.99978400000001</v>
+        <v>99.999488</v>
       </c>
       <c r="L388" s="6" t="n">
         <v>99.68438399999999</v>
@@ -31890,7 +31890,7 @@
         <v>100.793069</v>
       </c>
       <c r="K389" s="9" t="n">
-        <v>100.13354</v>
+        <v>100.133732</v>
       </c>
       <c r="L389" s="9" t="n">
         <v>99.741213</v>
@@ -31974,7 +31974,7 @@
         <v>100.901033</v>
       </c>
       <c r="K390" s="6" t="n">
-        <v>100.251953</v>
+        <v>100.252623</v>
       </c>
       <c r="L390" s="6" t="n">
         <v>99.804768</v>
@@ -32058,7 +32058,7 @@
         <v>100.968247</v>
       </c>
       <c r="K391" s="9" t="n">
-        <v>100.343769</v>
+        <v>100.344806</v>
       </c>
       <c r="L391" s="9" t="n">
         <v>99.869647</v>
@@ -32142,7 +32142,7 @@
         <v>101.004862</v>
       </c>
       <c r="K392" s="6" t="n">
-        <v>100.398422</v>
+        <v>100.39967</v>
       </c>
       <c r="L392" s="6" t="n">
         <v>99.93102399999999</v>
@@ -32226,7 +32226,7 @@
         <v>101.017402</v>
       </c>
       <c r="K393" s="9" t="n">
-        <v>100.418693</v>
+        <v>100.419994</v>
       </c>
       <c r="L393" s="9" t="n">
         <v>99.98686499999999</v>
@@ -32310,7 +32310,7 @@
         <v>101.004737</v>
       </c>
       <c r="K394" s="6" t="n">
-        <v>100.413961</v>
+        <v>100.415264</v>
       </c>
       <c r="L394" s="6" t="n">
         <v>100.041392</v>
@@ -32394,7 +32394,7 @@
         <v>100.970436</v>
       </c>
       <c r="K395" s="9" t="n">
-        <v>100.394821</v>
+        <v>100.396011</v>
       </c>
       <c r="L395" s="9" t="n">
         <v>100.096676</v>
@@ -32478,7 +32478,7 @@
         <v>100.903804</v>
       </c>
       <c r="K396" s="6" t="n">
-        <v>100.370633</v>
+        <v>100.371519</v>
       </c>
       <c r="L396" s="6" t="n">
         <v>100.149433</v>
@@ -32562,7 +32562,7 @@
         <v>100.795256</v>
       </c>
       <c r="K397" s="9" t="n">
-        <v>100.355277</v>
+        <v>100.355837</v>
       </c>
       <c r="L397" s="9" t="n">
         <v>100.197275</v>
@@ -32646,7 +32646,7 @@
         <v>100.663653</v>
       </c>
       <c r="K398" s="6" t="n">
-        <v>100.325709</v>
+        <v>100.325888</v>
       </c>
       <c r="L398" s="6" t="n">
         <v>100.238762</v>
@@ -32730,7 +32730,7 @@
         <v>100.508538</v>
       </c>
       <c r="K399" s="9" t="n">
-        <v>100.26201</v>
+        <v>100.262017</v>
       </c>
       <c r="L399" s="9" t="n">
         <v>100.271627</v>
@@ -32814,7 +32814,7 @@
         <v>100.360567</v>
       </c>
       <c r="K400" s="6" t="n">
-        <v>100.175342</v>
+        <v>100.175216</v>
       </c>
       <c r="L400" s="6" t="n">
         <v>100.296176</v>
@@ -32898,7 +32898,7 @@
         <v>100.219358</v>
       </c>
       <c r="K401" s="9" t="n">
-        <v>100.087265</v>
+        <v>100.087012</v>
       </c>
       <c r="L401" s="9" t="n">
         <v>100.311617</v>
@@ -32982,7 +32982,7 @@
         <v>100.088554</v>
       </c>
       <c r="K402" s="6" t="n">
-        <v>100.025711</v>
+        <v>100.025618</v>
       </c>
       <c r="L402" s="6" t="n">
         <v>100.315157</v>
@@ -33066,7 +33066,7 @@
         <v>99.961204</v>
       </c>
       <c r="K403" s="9" t="n">
-        <v>99.97709</v>
+        <v>99.97721900000001</v>
       </c>
       <c r="L403" s="9" t="n">
         <v>100.305235</v>
@@ -33150,7 +33150,7 @@
         <v>99.829032</v>
       </c>
       <c r="K404" s="6" t="n">
-        <v>99.93495900000001</v>
+        <v>99.935233</v>
       </c>
       <c r="L404" s="6" t="n">
         <v>100.281868</v>
@@ -33234,7 +33234,7 @@
         <v>99.712627</v>
       </c>
       <c r="K405" s="9" t="n">
-        <v>99.895349</v>
+        <v>99.895492</v>
       </c>
       <c r="L405" s="9" t="n">
         <v>100.246902</v>
@@ -33318,7 +33318,7 @@
         <v>99.629347</v>
       </c>
       <c r="K406" s="6" t="n">
-        <v>99.85973199999999</v>
+        <v>99.859537</v>
       </c>
       <c r="L406" s="6" t="n">
         <v>100.202807</v>
@@ -33402,7 +33402,7 @@
         <v>99.564437</v>
       </c>
       <c r="K407" s="9" t="n">
-        <v>99.816146</v>
+        <v>99.81542399999999</v>
       </c>
       <c r="L407" s="9" t="n">
         <v>100.15165</v>
@@ -33486,7 +33486,7 @@
         <v>99.527354</v>
       </c>
       <c r="K408" s="6" t="n">
-        <v>99.759885</v>
+        <v>99.758684</v>
       </c>
       <c r="L408" s="6" t="n">
         <v>100.096199</v>
@@ -33570,7 +33570,7 @@
         <v>99.516019</v>
       </c>
       <c r="K409" s="9" t="n">
-        <v>99.68767699999999</v>
+        <v>99.68617399999999</v>
       </c>
       <c r="L409" s="9" t="n">
         <v>100.03958</v>
@@ -33654,7 +33654,7 @@
         <v>99.520746</v>
       </c>
       <c r="K410" s="6" t="n">
-        <v>99.613501</v>
+        <v>99.61192200000001</v>
       </c>
       <c r="L410" s="6" t="n">
         <v>99.98282500000001</v>
@@ -33738,7 +33738,7 @@
         <v>99.553943</v>
       </c>
       <c r="K411" s="9" t="n">
-        <v>99.54355</v>
+        <v>99.542233</v>
       </c>
       <c r="L411" s="9" t="n">
         <v>99.927981</v>
@@ -33822,7 +33822,7 @@
         <v>99.611103</v>
       </c>
       <c r="K412" s="6" t="n">
-        <v>99.482086</v>
+        <v>99.481093</v>
       </c>
       <c r="L412" s="6" t="n">
         <v>99.87608899999999</v>
@@ -33906,7 +33906,7 @@
         <v>99.7008</v>
       </c>
       <c r="K413" s="9" t="n">
-        <v>99.43015699999999</v>
+        <v>99.429329</v>
       </c>
       <c r="L413" s="9" t="n">
         <v>99.827979</v>
@@ -33990,7 +33990,7 @@
         <v>99.82587700000001</v>
       </c>
       <c r="K414" s="6" t="n">
-        <v>99.399823</v>
+        <v>99.398957</v>
       </c>
       <c r="L414" s="6" t="n">
         <v>99.787465</v>
@@ -34074,7 +34074,7 @@
         <v>99.983197</v>
       </c>
       <c r="K415" s="9" t="n">
-        <v>99.40033200000001</v>
+        <v>99.399174</v>
       </c>
       <c r="L415" s="9" t="n">
         <v>99.760132</v>
@@ -34158,7 +34158,7 @@
         <v>100.152898</v>
       </c>
       <c r="K416" s="6" t="n">
-        <v>99.421667</v>
+        <v>99.42021200000001</v>
       </c>
       <c r="L416" s="6" t="n">
         <v>99.74702600000001</v>
@@ -34242,7 +34242,7 @@
         <v>100.294693</v>
       </c>
       <c r="K417" s="9" t="n">
-        <v>99.45246400000001</v>
+        <v>99.45093799999999</v>
       </c>
       <c r="L417" s="9" t="n">
         <v>99.74485</v>
@@ -34326,7 +34326,7 @@
         <v>100.384111</v>
       </c>
       <c r="K418" s="6" t="n">
-        <v>99.476305</v>
+        <v>99.47476</v>
       </c>
       <c r="L418" s="6" t="n">
         <v>99.745771</v>
@@ -34410,7 +34410,7 @@
         <v>100.419001</v>
       </c>
       <c r="K419" s="9" t="n">
-        <v>99.491794</v>
+        <v>99.4903</v>
       </c>
       <c r="L419" s="9" t="n">
         <v>99.74466200000001</v>
@@ -34494,7 +34494,7 @@
         <v>100.411943</v>
       </c>
       <c r="K420" s="6" t="n">
-        <v>99.503511</v>
+        <v>99.50212999999999</v>
       </c>
       <c r="L420" s="6" t="n">
         <v>99.741164</v>
@@ -34578,7 +34578,7 @@
         <v>100.392828</v>
       </c>
       <c r="K421" s="9" t="n">
-        <v>99.518345</v>
+        <v>99.517101</v>
       </c>
       <c r="L421" s="9" t="n">
         <v>99.737532</v>
@@ -34662,7 +34662,7 @@
         <v>100.382712</v>
       </c>
       <c r="K422" s="6" t="n">
-        <v>99.54390600000001</v>
+        <v>99.542731</v>
       </c>
       <c r="L422" s="6" t="n">
         <v>99.737679</v>
@@ -34746,7 +34746,7 @@
         <v>100.374373</v>
       </c>
       <c r="K423" s="9" t="n">
-        <v>99.594386</v>
+        <v>99.593377</v>
       </c>
       <c r="L423" s="9" t="n">
         <v>99.74484099999999</v>
@@ -34830,7 +34830,7 @@
         <v>100.352348</v>
       </c>
       <c r="K424" s="6" t="n">
-        <v>99.665059</v>
+        <v>99.66416599999999</v>
       </c>
       <c r="L424" s="6" t="n">
         <v>99.758526</v>
@@ -34914,7 +34914,7 @@
         <v>100.321112</v>
       </c>
       <c r="K425" s="9" t="n">
-        <v>99.745074</v>
+        <v>99.744379</v>
       </c>
       <c r="L425" s="9" t="n">
         <v>99.776844</v>
@@ -34998,7 +34998,7 @@
         <v>100.296011</v>
       </c>
       <c r="K426" s="6" t="n">
-        <v>99.83024399999999</v>
+        <v>99.829785</v>
       </c>
       <c r="L426" s="6" t="n">
         <v>99.79732</v>
@@ -35082,7 +35082,7 @@
         <v>100.294382</v>
       </c>
       <c r="K427" s="9" t="n">
-        <v>99.90929199999999</v>
+        <v>99.90901700000001</v>
       </c>
       <c r="L427" s="9" t="n">
         <v>99.81751</v>
@@ -35166,7 +35166,7 @@
         <v>100.319524</v>
       </c>
       <c r="K428" s="6" t="n">
-        <v>99.979212</v>
+        <v>99.97907499999999</v>
       </c>
       <c r="L428" s="6" t="n">
         <v>99.836539</v>
@@ -35250,7 +35250,7 @@
         <v>100.38189</v>
       </c>
       <c r="K429" s="9" t="n">
-        <v>100.043758</v>
+        <v>100.043749</v>
       </c>
       <c r="L429" s="9" t="n">
         <v>99.853403</v>
@@ -35334,7 +35334,7 @@
         <v>100.474424</v>
       </c>
       <c r="K430" s="6" t="n">
-        <v>100.106733</v>
+        <v>100.106881</v>
       </c>
       <c r="L430" s="6" t="n">
         <v>99.869984</v>
@@ -35418,7 +35418,7 @@
         <v>100.604704</v>
       </c>
       <c r="K431" s="9" t="n">
-        <v>100.168608</v>
+        <v>100.168839</v>
       </c>
       <c r="L431" s="9" t="n">
         <v>99.88754</v>
@@ -35502,7 +35502,7 @@
         <v>100.752647</v>
       </c>
       <c r="K432" s="6" t="n">
-        <v>100.224451</v>
+        <v>100.224679</v>
       </c>
       <c r="L432" s="6" t="n">
         <v>99.90495199999999</v>
@@ -35586,7 +35586,7 @@
         <v>100.875599</v>
       </c>
       <c r="K433" s="9" t="n">
-        <v>100.263607</v>
+        <v>100.263706</v>
       </c>
       <c r="L433" s="9" t="n">
         <v>99.91903600000001</v>
@@ -35670,7 +35670,7 @@
         <v>100.935011</v>
       </c>
       <c r="K434" s="6" t="n">
-        <v>100.284649</v>
+        <v>100.284765</v>
       </c>
       <c r="L434" s="6" t="n">
         <v>99.92669100000001</v>
@@ -35754,7 +35754,7 @@
         <v>100.896788</v>
       </c>
       <c r="K435" s="9" t="n">
-        <v>100.299052</v>
+        <v>100.299294</v>
       </c>
       <c r="L435" s="9" t="n">
         <v>99.92874999999999</v>
@@ -35838,7 +35838,7 @@
         <v>100.801882</v>
       </c>
       <c r="K436" s="6" t="n">
-        <v>100.324722</v>
+        <v>100.325174</v>
       </c>
       <c r="L436" s="6" t="n">
         <v>99.92624499999999</v>
@@ -35922,7 +35922,7 @@
         <v>100.687586</v>
       </c>
       <c r="K437" s="9" t="n">
-        <v>100.371951</v>
+        <v>100.372726</v>
       </c>
       <c r="L437" s="9" t="n">
         <v>99.920755</v>
@@ -36006,7 +36006,7 @@
         <v>100.564559</v>
       </c>
       <c r="K438" s="6" t="n">
-        <v>100.437756</v>
+        <v>100.438881</v>
       </c>
       <c r="L438" s="6" t="n">
         <v>99.915426</v>
@@ -36090,7 +36090,7 @@
         <v>100.439677</v>
       </c>
       <c r="K439" s="9" t="n">
-        <v>100.509896</v>
+        <v>100.511254</v>
       </c>
       <c r="L439" s="9" t="n">
         <v>99.912741</v>
@@ -36174,7 +36174,7 @@
         <v>100.320142</v>
       </c>
       <c r="K440" s="6" t="n">
-        <v>100.590999</v>
+        <v>100.592566</v>
       </c>
       <c r="L440" s="6" t="n">
         <v>99.917221</v>
@@ -36258,7 +36258,7 @@
         <v>100.224769</v>
       </c>
       <c r="K441" s="9" t="n">
-        <v>100.682113</v>
+        <v>100.683884</v>
       </c>
       <c r="L441" s="9" t="n">
         <v>99.93429500000001</v>
@@ -36342,7 +36342,7 @@
         <v>100.162153</v>
       </c>
       <c r="K442" s="6" t="n">
-        <v>100.781951</v>
+        <v>100.78387</v>
       </c>
       <c r="L442" s="6" t="n">
         <v>99.96369900000001</v>
@@ -36426,7 +36426,7 @@
         <v>100.133762</v>
       </c>
       <c r="K443" s="9" t="n">
-        <v>100.88436</v>
+        <v>100.886471</v>
       </c>
       <c r="L443" s="9" t="n">
         <v>100.002561</v>
@@ -36510,7 +36510,7 @@
         <v>100.1465</v>
       </c>
       <c r="K444" s="6" t="n">
-        <v>100.974757</v>
+        <v>100.977107</v>
       </c>
       <c r="L444" s="6" t="n">
         <v>100.046562</v>
@@ -36594,7 +36594,7 @@
         <v>100.202335</v>
       </c>
       <c r="K445" s="9" t="n">
-        <v>101.049884</v>
+        <v>101.05236</v>
       </c>
       <c r="L445" s="9" t="n">
         <v>100.093098</v>
@@ -36678,7 +36678,7 @@
         <v>100.296623</v>
       </c>
       <c r="K446" s="6" t="n">
-        <v>101.096947</v>
+        <v>101.099436</v>
       </c>
       <c r="L446" s="6" t="n">
         <v>100.139941</v>
@@ -36762,7 +36762,7 @@
         <v>100.416303</v>
       </c>
       <c r="K447" s="9" t="n">
-        <v>101.101778</v>
+        <v>101.104121</v>
       </c>
       <c r="L447" s="9" t="n">
         <v>100.183714</v>
@@ -36846,7 +36846,7 @@
         <v>100.545392</v>
       </c>
       <c r="K448" s="6" t="n">
-        <v>101.053499</v>
+        <v>101.055737</v>
       </c>
       <c r="L448" s="6" t="n">
         <v>100.222943</v>
@@ -36930,7 +36930,7 @@
         <v>100.653184</v>
       </c>
       <c r="K449" s="9" t="n">
-        <v>100.960346</v>
+        <v>100.962409</v>
       </c>
       <c r="L449" s="9" t="n">
         <v>100.258868</v>
@@ -37014,7 +37014,7 @@
         <v>100.726824</v>
       </c>
       <c r="K450" s="6" t="n">
-        <v>100.835273</v>
+        <v>100.837096</v>
       </c>
       <c r="L450" s="6" t="n">
         <v>100.294011</v>
@@ -37098,7 +37098,7 @@
         <v>100.751273</v>
       </c>
       <c r="K451" s="9" t="n">
-        <v>100.702366</v>
+        <v>100.703933</v>
       </c>
       <c r="L451" s="9" t="n">
         <v>100.332805</v>
@@ -37182,7 +37182,7 @@
         <v>100.729694</v>
       </c>
       <c r="K452" s="6" t="n">
-        <v>100.575012</v>
+        <v>100.576284</v>
       </c>
       <c r="L452" s="6" t="n">
         <v>100.378956</v>
@@ -37266,7 +37266,7 @@
         <v>100.664404</v>
       </c>
       <c r="K453" s="9" t="n">
-        <v>100.46638</v>
+        <v>100.467278</v>
       </c>
       <c r="L453" s="9" t="n">
         <v>100.430245</v>
@@ -37350,7 +37350,7 @@
         <v>100.583946</v>
       </c>
       <c r="K454" s="6" t="n">
-        <v>100.373394</v>
+        <v>100.373984</v>
       </c>
       <c r="L454" s="6" t="n">
         <v>100.484362</v>
@@ -37434,7 +37434,7 @@
         <v>100.506393</v>
       </c>
       <c r="K455" s="9" t="n">
-        <v>100.295519</v>
+        <v>100.295867</v>
       </c>
       <c r="L455" s="9" t="n">
         <v>100.540542</v>
@@ -37518,7 +37518,7 @@
         <v>100.446615</v>
       </c>
       <c r="K456" s="6" t="n">
-        <v>100.233488</v>
+        <v>100.233574</v>
       </c>
       <c r="L456" s="6" t="n">
         <v>100.593631</v>
@@ -37602,7 +37602,7 @@
         <v>100.42486</v>
       </c>
       <c r="K457" s="9" t="n">
-        <v>100.181716</v>
+        <v>100.181764</v>
       </c>
       <c r="L457" s="9" t="n">
         <v>100.640401</v>
@@ -37686,7 +37686,7 @@
         <v>100.441656</v>
       </c>
       <c r="K458" s="6" t="n">
-        <v>100.141308</v>
+        <v>100.14141</v>
       </c>
       <c r="L458" s="6" t="n">
         <v>100.681016</v>
@@ -37770,7 +37770,7 @@
         <v>100.502298</v>
       </c>
       <c r="K459" s="9" t="n">
-        <v>100.113959</v>
+        <v>100.114077</v>
       </c>
       <c r="L459" s="9" t="n">
         <v>100.718419</v>
@@ -37854,7 +37854,7 @@
         <v>100.579637</v>
       </c>
       <c r="K460" s="6" t="n">
-        <v>100.098971</v>
+        <v>100.099062</v>
       </c>
       <c r="L460" s="6" t="n">
         <v>100.756817</v>
@@ -37938,7 +37938,7 @@
         <v>100.651651</v>
       </c>
       <c r="K461" s="9" t="n">
-        <v>100.096317</v>
+        <v>100.096435</v>
       </c>
       <c r="L461" s="9" t="n">
         <v>100.799872</v>
@@ -38022,7 +38022,7 @@
         <v>100.702414</v>
       </c>
       <c r="K462" s="6" t="n">
-        <v>100.094047</v>
+        <v>100.094114</v>
       </c>
       <c r="L462" s="6" t="n">
         <v>100.848921</v>
@@ -38106,7 +38106,7 @@
         <v>100.74405</v>
       </c>
       <c r="K463" s="9" t="n">
-        <v>100.090066</v>
+        <v>100.090129</v>
       </c>
       <c r="L463" s="9" t="n">
         <v>100.903918</v>
@@ -38190,7 +38190,7 @@
         <v>100.780445</v>
       </c>
       <c r="K464" s="6" t="n">
-        <v>100.0879</v>
+        <v>100.088032</v>
       </c>
       <c r="L464" s="6" t="n">
         <v>100.961544</v>
@@ -38274,7 +38274,7 @@
         <v>100.821121</v>
       </c>
       <c r="K465" s="9" t="n">
-        <v>100.082807</v>
+        <v>100.083099</v>
       </c>
       <c r="L465" s="9" t="n">
         <v>101.017753</v>
@@ -38358,7 +38358,7 @@
         <v>100.881561</v>
       </c>
       <c r="K466" s="6" t="n">
-        <v>100.084532</v>
+        <v>100.085059</v>
       </c>
       <c r="L466" s="6" t="n">
         <v>101.06939</v>
@@ -38442,7 +38442,7 @@
         <v>100.931266</v>
       </c>
       <c r="K467" s="9" t="n">
-        <v>100.094683</v>
+        <v>100.095431</v>
       </c>
       <c r="L467" s="9" t="n">
         <v>101.114533</v>
@@ -38526,7 +38526,7 @@
         <v>100.953381</v>
       </c>
       <c r="K468" s="6" t="n">
-        <v>100.11191</v>
+        <v>100.112718</v>
       </c>
       <c r="L468" s="6" t="n">
         <v>101.153505</v>
@@ -38610,7 +38610,7 @@
         <v>100.935749</v>
       </c>
       <c r="K469" s="9" t="n">
-        <v>100.137896</v>
+        <v>100.138602</v>
       </c>
       <c r="L469" s="9" t="n">
         <v>101.184419</v>
@@ -38694,7 +38694,7 @@
         <v>100.882407</v>
       </c>
       <c r="K470" s="6" t="n">
-        <v>100.174839</v>
+        <v>100.175308</v>
       </c>
       <c r="L470" s="6" t="n">
         <v>101.204191</v>
@@ -38778,7 +38778,7 @@
         <v>100.785227</v>
       </c>
       <c r="K471" s="9" t="n">
-        <v>100.215595</v>
+        <v>100.215921</v>
       </c>
       <c r="L471" s="9" t="n">
         <v>101.21165</v>
@@ -38862,7 +38862,7 @@
         <v>100.669595</v>
       </c>
       <c r="K472" s="6" t="n">
-        <v>100.245998</v>
+        <v>100.246212</v>
       </c>
       <c r="L472" s="6" t="n">
         <v>101.209028</v>
@@ -38946,7 +38946,7 @@
         <v>100.569196</v>
       </c>
       <c r="K473" s="9" t="n">
-        <v>100.263556</v>
+        <v>100.26366</v>
       </c>
       <c r="L473" s="9" t="n">
         <v>101.201261</v>
@@ -39030,7 +39030,7 @@
         <v>100.499193</v>
       </c>
       <c r="K474" s="6" t="n">
-        <v>100.276566</v>
+        <v>100.276805</v>
       </c>
       <c r="L474" s="6" t="n">
         <v>101.194706</v>
@@ -39114,7 +39114,7 @@
         <v>100.45492</v>
       </c>
       <c r="K475" s="9" t="n">
-        <v>100.283273</v>
+        <v>100.283806</v>
       </c>
       <c r="L475" s="9" t="n">
         <v>101.193266</v>
@@ -39198,7 +39198,7 @@
         <v>100.424351</v>
       </c>
       <c r="K476" s="6" t="n">
-        <v>100.281673</v>
+        <v>100.282501</v>
       </c>
       <c r="L476" s="6" t="n">
         <v>101.198558</v>
@@ -39282,7 +39282,7 @@
         <v>100.410702</v>
       </c>
       <c r="K477" s="9" t="n">
-        <v>100.281377</v>
+        <v>100.282381</v>
       </c>
       <c r="L477" s="9" t="n">
         <v>101.209779</v>
@@ -39366,7 +39366,7 @@
         <v>100.390693</v>
       </c>
       <c r="K478" s="6" t="n">
-        <v>100.284323</v>
+        <v>100.285355</v>
       </c>
       <c r="L478" s="6" t="n">
         <v>101.223059</v>
@@ -39450,7 +39450,7 @@
         <v>100.354062</v>
       </c>
       <c r="K479" s="9" t="n">
-        <v>100.286714</v>
+        <v>100.28758</v>
       </c>
       <c r="L479" s="9" t="n">
         <v>101.234141</v>
@@ -39534,7 +39534,7 @@
         <v>100.272682</v>
       </c>
       <c r="K480" s="6" t="n">
-        <v>100.279551</v>
+        <v>100.280283</v>
       </c>
       <c r="L480" s="6" t="n">
         <v>101.237288</v>
@@ -39618,7 +39618,7 @@
         <v>100.140509</v>
       </c>
       <c r="K481" s="9" t="n">
-        <v>100.25724</v>
+        <v>100.257864</v>
       </c>
       <c r="L481" s="9" t="n">
         <v>101.2271</v>
@@ -39702,7 +39702,7 @@
         <v>99.95886</v>
       </c>
       <c r="K482" s="6" t="n">
-        <v>100.212354</v>
+        <v>100.212897</v>
       </c>
       <c r="L482" s="6" t="n">
         <v>101.196117</v>
@@ -39786,7 +39786,7 @@
         <v>99.740737</v>
       </c>
       <c r="K483" s="9" t="n">
-        <v>100.144186</v>
+        <v>100.144724</v>
       </c>
       <c r="L483" s="9" t="n">
         <v>101.130652</v>
@@ -39870,7 +39870,7 @@
         <v>99.521987</v>
       </c>
       <c r="K484" s="6" t="n">
-        <v>100.045353</v>
+        <v>100.04584</v>
       </c>
       <c r="L484" s="6" t="n">
         <v>101.01215</v>
@@ -39954,7 +39954,7 @@
         <v>99.30245600000001</v>
       </c>
       <c r="K485" s="9" t="n">
-        <v>99.895624</v>
+        <v>99.895844</v>
       </c>
       <c r="L485" s="9" t="n">
         <v>100.818869</v>
@@ -40038,7 +40038,7 @@
         <v>99.077945</v>
       </c>
       <c r="K486" s="6" t="n">
-        <v>99.68113099999999</v>
+        <v>99.680814</v>
       </c>
       <c r="L486" s="6" t="n">
         <v>100.530118</v>
@@ -40122,7 +40122,7 @@
         <v>98.828571</v>
       </c>
       <c r="K487" s="9" t="n">
-        <v>99.414175</v>
+        <v>99.41310199999999</v>
       </c>
       <c r="L487" s="9" t="n">
         <v>100.13616</v>
@@ -40206,7 +40206,7 @@
         <v>98.578856</v>
       </c>
       <c r="K488" s="6" t="n">
-        <v>99.12830700000001</v>
+        <v>99.126504</v>
       </c>
       <c r="L488" s="6" t="n">
         <v>99.656261</v>
@@ -40290,7 +40290,7 @@
         <v>85.513008</v>
       </c>
       <c r="K489" s="9" t="n">
-        <v>92.07571900000001</v>
+        <v>92.056197</v>
       </c>
       <c r="L489" s="9" t="n">
         <v>99.134218</v>
@@ -40374,7 +40374,7 @@
         <v>85.472877</v>
       </c>
       <c r="K490" s="6" t="n">
-        <v>92.07337</v>
+        <v>92.060582</v>
       </c>
       <c r="L490" s="6" t="n">
         <v>98.627835</v>
@@ -40458,7 +40458,7 @@
         <v>93.296547</v>
       </c>
       <c r="K491" s="9" t="n">
-        <v>94.523594</v>
+        <v>94.511869</v>
       </c>
       <c r="L491" s="9" t="n">
         <v>98.198143</v>
@@ -40542,7 +40542,7 @@
         <v>94.06985899999999</v>
       </c>
       <c r="K492" s="6" t="n">
-        <v>95.701256</v>
+        <v>95.69269300000001</v>
       </c>
       <c r="L492" s="6" t="n">
         <v>97.875964</v>
@@ -40626,7 +40626,7 @@
         <v>95.36012599999999</v>
       </c>
       <c r="K493" s="9" t="n">
-        <v>96.283112</v>
+        <v>96.27548899999999</v>
       </c>
       <c r="L493" s="9" t="n">
         <v>97.658879</v>
@@ -40710,7 +40710,7 @@
         <v>96.57197499999999</v>
       </c>
       <c r="K494" s="6" t="n">
-        <v>96.895595</v>
+        <v>96.88907</v>
       </c>
       <c r="L494" s="6" t="n">
         <v>97.531682</v>
@@ -40794,7 +40794,7 @@
         <v>97.529372</v>
       </c>
       <c r="K495" s="9" t="n">
-        <v>97.45904400000001</v>
+        <v>97.45352800000001</v>
       </c>
       <c r="L495" s="9" t="n">
         <v>97.47754500000001</v>
@@ -40878,7 +40878,7 @@
         <v>98.169107</v>
       </c>
       <c r="K496" s="6" t="n">
-        <v>97.962907</v>
+        <v>97.958324</v>
       </c>
       <c r="L496" s="6" t="n">
         <v>97.47793</v>
@@ -40962,7 +40962,7 @@
         <v>98.517003</v>
       </c>
       <c r="K497" s="9" t="n">
-        <v>98.408996</v>
+        <v>98.40536899999999</v>
       </c>
       <c r="L497" s="9" t="n">
         <v>97.518314</v>
@@ -41046,7 +41046,7 @@
         <v>98.655096</v>
       </c>
       <c r="K498" s="6" t="n">
-        <v>98.81255</v>
+        <v>98.809882</v>
       </c>
       <c r="L498" s="6" t="n">
         <v>97.594053</v>
@@ -41130,7 +41130,7 @@
         <v>98.678971</v>
       </c>
       <c r="K499" s="9" t="n">
-        <v>99.167191</v>
+        <v>99.16543900000001</v>
       </c>
       <c r="L499" s="9" t="n">
         <v>97.71531299999999</v>
@@ -41214,7 +41214,7 @@
         <v>98.65911800000001</v>
       </c>
       <c r="K500" s="6" t="n">
-        <v>99.448131</v>
+        <v>99.447187</v>
       </c>
       <c r="L500" s="6" t="n">
         <v>97.89507999999999</v>
@@ -41298,7 +41298,7 @@
         <v>98.60088500000001</v>
       </c>
       <c r="K501" s="9" t="n">
-        <v>99.628309</v>
+        <v>99.62799200000001</v>
       </c>
       <c r="L501" s="9" t="n">
         <v>98.13861900000001</v>
@@ -41382,7 +41382,7 @@
         <v>98.523594</v>
       </c>
       <c r="K502" s="6" t="n">
-        <v>99.729484</v>
+        <v>99.729529</v>
       </c>
       <c r="L502" s="6" t="n">
         <v>98.436666</v>
@@ -41466,7 +41466,7 @@
         <v>98.456734</v>
       </c>
       <c r="K503" s="9" t="n">
-        <v>99.777843</v>
+        <v>99.778142</v>
       </c>
       <c r="L503" s="9" t="n">
         <v>98.751597</v>
@@ -41550,7 +41550,7 @@
         <v>98.424458</v>
       </c>
       <c r="K504" s="6" t="n">
-        <v>99.804259</v>
+        <v>99.80456</v>
       </c>
       <c r="L504" s="6" t="n">
         <v>99.04414800000001</v>
@@ -41634,7 +41634,7 @@
         <v>98.44262999999999</v>
       </c>
       <c r="K505" s="9" t="n">
-        <v>99.82990100000001</v>
+        <v>99.82998600000001</v>
       </c>
       <c r="L505" s="9" t="n">
         <v>99.28756799999999</v>
@@ -41718,7 +41718,7 @@
         <v>98.526662</v>
       </c>
       <c r="K506" s="6" t="n">
-        <v>99.86350899999999</v>
+        <v>99.863283</v>
       </c>
       <c r="L506" s="6" t="n">
         <v>99.475399</v>
@@ -41802,7 +41802,7 @@
         <v>98.70104600000001</v>
       </c>
       <c r="K507" s="9" t="n">
-        <v>99.90914100000001</v>
+        <v>99.908693</v>
       </c>
       <c r="L507" s="9" t="n">
         <v>99.61449399999999</v>
@@ -41886,7 +41886,7 @@
         <v>98.952949</v>
       </c>
       <c r="K508" s="6" t="n">
-        <v>99.97229299999999</v>
+        <v>99.97163</v>
       </c>
       <c r="L508" s="6" t="n">
         <v>99.718289</v>
@@ -41970,7 +41970,7 @@
         <v>99.254807</v>
       </c>
       <c r="K509" s="9" t="n">
-        <v>100.057797</v>
+        <v>100.057074</v>
       </c>
       <c r="L509" s="9" t="n">
         <v>99.797732</v>
@@ -42054,7 +42054,7 @@
         <v>99.56235700000001</v>
       </c>
       <c r="K510" s="6" t="n">
-        <v>100.173111</v>
+        <v>100.172617</v>
       </c>
       <c r="L510" s="6" t="n">
         <v>99.860732</v>
@@ -42138,7 +42138,7 @@
         <v>99.83539399999999</v>
       </c>
       <c r="K511" s="9" t="n">
-        <v>100.325036</v>
+        <v>100.325404</v>
       </c>
       <c r="L511" s="9" t="n">
         <v>99.91152700000001</v>
@@ -42222,7 +42222,7 @@
         <v>100.058233</v>
       </c>
       <c r="K512" s="6" t="n">
-        <v>100.483331</v>
+        <v>100.484805</v>
       </c>
       <c r="L512" s="6" t="n">
         <v>99.952749</v>
@@ -42306,7 +42306,7 @@
         <v>100.216011</v>
       </c>
       <c r="K513" s="9" t="n">
-        <v>100.612968</v>
+        <v>100.615419</v>
       </c>
       <c r="L513" s="9" t="n">
         <v>99.988383</v>
@@ -42390,7 +42390,7 @@
         <v>100.310393</v>
       </c>
       <c r="K514" s="6" t="n">
-        <v>100.717916</v>
+        <v>100.72097</v>
       </c>
       <c r="L514" s="6" t="n">
         <v>100.021356</v>
@@ -42474,7 +42474,7 @@
         <v>100.367013</v>
       </c>
       <c r="K515" s="9" t="n">
-        <v>100.797138</v>
+        <v>100.8003</v>
       </c>
       <c r="L515" s="9" t="n">
         <v>100.056195</v>
@@ -42558,7 +42558,7 @@
         <v>100.418301</v>
       </c>
       <c r="K516" s="6" t="n">
-        <v>100.855715</v>
+        <v>100.85851</v>
       </c>
       <c r="L516" s="6" t="n">
         <v>100.094198</v>
@@ -42642,7 +42642,7 @@
         <v>100.476073</v>
       </c>
       <c r="K517" s="9" t="n">
-        <v>100.899606</v>
+        <v>100.901558</v>
       </c>
       <c r="L517" s="9" t="n">
         <v>100.135134</v>
@@ -42726,7 +42726,7 @@
         <v>100.549889</v>
       </c>
       <c r="K518" s="6" t="n">
-        <v>100.923189</v>
+        <v>100.924121</v>
       </c>
       <c r="L518" s="6" t="n">
         <v>100.17799</v>
@@ -42810,7 +42810,7 @@
         <v>100.655448</v>
       </c>
       <c r="K519" s="9" t="n">
-        <v>100.933184</v>
+        <v>100.933222</v>
       </c>
       <c r="L519" s="9" t="n">
         <v>100.220885</v>
@@ -42894,7 +42894,7 @@
         <v>100.790567</v>
       </c>
       <c r="K520" s="6" t="n">
-        <v>100.931932</v>
+        <v>100.931615</v>
       </c>
       <c r="L520" s="6" t="n">
         <v>100.262626</v>
@@ -42978,7 +42978,7 @@
         <v>100.924947</v>
       </c>
       <c r="K521" s="9" t="n">
-        <v>100.928644</v>
+        <v>100.928537</v>
       </c>
       <c r="L521" s="9" t="n">
         <v>100.305645</v>
@@ -43062,7 +43062,7 @@
         <v>101.028206</v>
       </c>
       <c r="K522" s="6" t="n">
-        <v>100.921182</v>
+        <v>100.921905</v>
       </c>
       <c r="L522" s="6" t="n">
         <v>100.351844</v>
@@ -43146,7 +43146,7 @@
         <v>101.109661</v>
       </c>
       <c r="K523" s="9" t="n">
-        <v>100.914412</v>
+        <v>100.916494</v>
       </c>
       <c r="L523" s="9" t="n">
         <v>100.402255</v>
@@ -43230,7 +43230,7 @@
         <v>101.191005</v>
       </c>
       <c r="K524" s="6" t="n">
-        <v>100.919381</v>
+        <v>100.922947</v>
       </c>
       <c r="L524" s="6" t="n">
         <v>100.453242</v>
@@ -43314,7 +43314,7 @@
         <v>101.28547</v>
       </c>
       <c r="K525" s="9" t="n">
-        <v>100.944665</v>
+        <v>100.949353</v>
       </c>
       <c r="L525" s="9" t="n">
         <v>100.497898</v>
@@ -43398,7 +43398,7 @@
         <v>101.389861</v>
       </c>
       <c r="K526" s="6" t="n">
-        <v>100.979837</v>
+        <v>100.985084</v>
       </c>
       <c r="L526" s="6" t="n">
         <v>100.532758</v>
@@ -43482,7 +43482,7 @@
         <v>101.49271</v>
       </c>
       <c r="K527" s="9" t="n">
-        <v>101.015555</v>
+        <v>101.020423</v>
       </c>
       <c r="L527" s="9" t="n">
         <v>100.555063</v>
@@ -43566,7 +43566,7 @@
         <v>101.58194</v>
       </c>
       <c r="K528" s="6" t="n">
-        <v>101.027032</v>
+        <v>101.030214</v>
       </c>
       <c r="L528" s="6" t="n">
         <v>100.565701</v>
@@ -43650,7 +43650,7 @@
         <v>101.650164</v>
       </c>
       <c r="K529" s="9" t="n">
-        <v>101.006236</v>
+        <v>101.006945</v>
       </c>
       <c r="L529" s="9" t="n">
         <v>100.568192</v>
@@ -43734,7 +43734,7 @@
         <v>101.683087</v>
       </c>
       <c r="K530" s="6" t="n">
-        <v>100.956051</v>
+        <v>100.954322</v>
       </c>
       <c r="L530" s="6" t="n">
         <v>100.566838</v>
@@ -43818,7 +43818,7 @@
         <v>101.657057</v>
       </c>
       <c r="K531" s="9" t="n">
-        <v>100.873205</v>
+        <v>100.869742</v>
       </c>
       <c r="L531" s="9" t="n">
         <v>100.564714</v>
@@ -43902,7 +43902,7 @@
         <v>101.558299</v>
       </c>
       <c r="K532" s="6" t="n">
-        <v>100.752497</v>
+        <v>100.748432</v>
       </c>
       <c r="L532" s="6" t="n">
         <v>100.562632</v>
@@ -43986,7 +43986,7 @@
         <v>101.419006</v>
       </c>
       <c r="K533" s="9" t="n">
-        <v>100.598401</v>
+        <v>100.595078</v>
       </c>
       <c r="L533" s="9" t="n">
         <v>100.560597</v>
@@ -44070,7 +44070,7 @@
         <v>101.257861</v>
       </c>
       <c r="K534" s="6" t="n">
-        <v>100.430969</v>
+        <v>100.429558</v>
       </c>
       <c r="L534" s="6" t="n">
         <v>100.559299</v>
@@ -44154,7 +44154,7 @@
         <v>101.085013</v>
       </c>
       <c r="K535" s="9" t="n">
-        <v>100.274535</v>
+        <v>100.275891</v>
       </c>
       <c r="L535" s="9" t="n">
         <v>100.558504</v>
@@ -44238,7 +44238,7 @@
         <v>100.933128</v>
       </c>
       <c r="K536" s="6" t="n">
-        <v>100.133131</v>
+        <v>100.137291</v>
       </c>
       <c r="L536" s="6" t="n">
         <v>100.558039</v>
@@ -44322,7 +44322,7 @@
         <v>100.807882</v>
       </c>
       <c r="K537" s="9" t="n">
-        <v>100.014388</v>
+        <v>100.020441</v>
       </c>
       <c r="L537" s="9" t="n">
         <v>100.558219</v>
@@ -44406,7 +44406,7 @@
         <v>100.720319</v>
       </c>
       <c r="K538" s="6" t="n">
-        <v>99.918116</v>
+        <v>99.92440499999999</v>
       </c>
       <c r="L538" s="6" t="n">
         <v>100.556353</v>
@@ -44490,7 +44490,7 @@
         <v>100.657102</v>
       </c>
       <c r="K539" s="9" t="n">
-        <v>99.846045</v>
+        <v>99.850324</v>
       </c>
       <c r="L539" s="9" t="n">
         <v>100.54897</v>
@@ -44574,7 +44574,7 @@
         <v>100.591947</v>
       </c>
       <c r="K540" s="6" t="n">
-        <v>99.799049</v>
+        <v>99.799098</v>
       </c>
       <c r="L540" s="6" t="n">
         <v>100.534621</v>
@@ -44658,7 +44658,7 @@
         <v>100.497531</v>
       </c>
       <c r="K541" s="9" t="n">
-        <v>99.763848</v>
+        <v>99.758358</v>
       </c>
       <c r="L541" s="9" t="n">
         <v>100.51008</v>
@@ -44742,7 +44742,7 @@
         <v>100.370502</v>
       </c>
       <c r="K542" s="6" t="n">
-        <v>99.737196</v>
+        <v>99.727598</v>
       </c>
       <c r="L542" s="6" t="n">
         <v>100.474732</v>
@@ -44826,7 +44826,7 @@
         <v>100.213821</v>
       </c>
       <c r="K543" s="9" t="n">
-        <v>99.71713699999999</v>
+        <v>99.70564299999999</v>
       </c>
       <c r="L543" s="9" t="n">
         <v>100.42974</v>
@@ -44910,7 +44910,7 @@
         <v>100.068431</v>
       </c>
       <c r="K544" s="6" t="n">
-        <v>99.713838</v>
+        <v>99.702899</v>
       </c>
       <c r="L544" s="6" t="n">
         <v>100.378549</v>
@@ -44994,7 +44994,7 @@
         <v>99.957966</v>
       </c>
       <c r="K545" s="9" t="n">
-        <v>99.731785</v>
+        <v>99.723466</v>
       </c>
       <c r="L545" s="9" t="n">
         <v>100.323723</v>
@@ -45078,7 +45078,7 @@
         <v>99.904202</v>
       </c>
       <c r="K546" s="6" t="n">
-        <v>99.760856</v>
+        <v>99.7567</v>
       </c>
       <c r="L546" s="6" t="n">
         <v>100.26626</v>
@@ -45162,7 +45162,7 @@
         <v>99.887636</v>
       </c>
       <c r="K547" s="9" t="n">
-        <v>99.788151</v>
+        <v>99.78882900000001</v>
       </c>
       <c r="L547" s="9" t="n">
         <v>100.206858</v>
@@ -45246,7 +45246,7 @@
         <v>99.85809999999999</v>
       </c>
       <c r="K548" s="6" t="n">
-        <v>99.80586</v>
+        <v>99.811143</v>
       </c>
       <c r="L548" s="6" t="n">
         <v>100.145668</v>
@@ -45330,7 +45330,7 @@
         <v>99.80019299999999</v>
       </c>
       <c r="K549" s="9" t="n">
-        <v>99.814857</v>
+        <v>99.82344000000001</v>
       </c>
       <c r="L549" s="9" t="n">
         <v>100.081705</v>
@@ -45414,7 +45414,7 @@
         <v>99.719556</v>
       </c>
       <c r="K550" s="6" t="n">
-        <v>99.82645100000001</v>
+        <v>99.835537</v>
       </c>
       <c r="L550" s="6" t="n">
         <v>100.015623</v>
@@ -45498,7 +45498,7 @@
         <v>99.608245</v>
       </c>
       <c r="K551" s="9" t="n">
-        <v>99.841813</v>
+        <v>99.847582</v>
       </c>
       <c r="L551" s="9" t="n">
         <v>99.949878</v>
@@ -45582,7 +45582,7 @@
         <v>99.485319</v>
       </c>
       <c r="K552" s="6" t="n">
-        <v>99.86333</v>
+        <v>99.861757</v>
       </c>
       <c r="L552" s="6" t="n">
         <v>99.887653</v>
@@ -45666,7 +45666,7 @@
         <v>99.389957</v>
       </c>
       <c r="K553" s="9" t="n">
-        <v>99.89223</v>
+        <v>99.88090699999999</v>
       </c>
       <c r="L553" s="9" t="n">
         <v>99.833029</v>
@@ -45750,7 +45750,7 @@
         <v>99.346199</v>
       </c>
       <c r="K554" s="6" t="n">
-        <v>99.925391</v>
+        <v>99.906873</v>
       </c>
       <c r="L554" s="6" t="n">
         <v>99.789569</v>
@@ -45834,7 +45834,7 @@
         <v>99.353003</v>
       </c>
       <c r="K555" s="9" t="n">
-        <v>99.960492</v>
+        <v>99.93761499999999</v>
       </c>
       <c r="L555" s="9" t="n">
         <v>99.75531599999999</v>
@@ -45918,7 +45918,7 @@
         <v>99.38487499999999</v>
       </c>
       <c r="K556" s="6" t="n">
-        <v>99.987179</v>
+        <v>99.96288300000001</v>
       </c>
       <c r="L556" s="6" t="n">
         <v>99.727041</v>
@@ -46002,7 +46002,7 @@
         <v>99.420351</v>
       </c>
       <c r="K557" s="9" t="n">
-        <v>99.99443599999999</v>
+        <v>99.971501</v>
       </c>
       <c r="L557" s="9" t="n">
         <v>99.702732</v>
@@ -46086,7 +46086,7 @@
         <v>99.460641</v>
       </c>
       <c r="K558" s="6" t="n">
-        <v>99.98420900000001</v>
+        <v>99.96554999999999</v>
       </c>
       <c r="L558" s="6" t="n">
         <v>99.680273</v>
@@ -46170,7 +46170,7 @@
         <v>99.53000299999999</v>
       </c>
       <c r="K559" s="9" t="n">
-        <v>99.95556000000001</v>
+        <v>99.944818</v>
       </c>
       <c r="L559" s="9" t="n">
         <v>99.658101</v>
@@ -46254,7 +46254,7 @@
         <v>99.635588</v>
       </c>
       <c r="K560" s="6" t="n">
-        <v>99.92066199999999</v>
+        <v>99.922996</v>
       </c>
       <c r="L560" s="6" t="n">
         <v>99.63489800000001</v>
@@ -46338,7 +46338,7 @@
         <v>99.780231</v>
       </c>
       <c r="K561" s="9" t="n">
-        <v>99.877825</v>
+        <v>99.900615</v>
       </c>
       <c r="L561" s="9" t="n">
         <v>99.611126</v>
@@ -46422,7 +46422,7 @@
         <v>99.933437</v>
       </c>
       <c r="K562" s="6" t="n">
-        <v>99.824534</v>
+        <v>99.87781699999999</v>
       </c>
       <c r="L562" s="6" t="n">
         <v>99.590773</v>
@@ -46506,7 +46506,7 @@
         <v>100.098738</v>
       </c>
       <c r="K563" s="9" t="n">
-        <v>99.76123800000001</v>
+        <v>99.857197</v>
       </c>
       <c r="L563" s="9" t="n">
         <v>99.57714300000001</v>
@@ -46590,7 +46590,7 @@
         <v>100.276559</v>
       </c>
       <c r="K564" s="6" t="n">
-        <v>99.69396399999999</v>
+        <v>99.845423</v>
       </c>
       <c r="L564" s="6" t="n">
         <v>99.568476</v>
@@ -46665,7 +46665,9 @@
       <c r="J565" s="9" t="n">
         <v>100.461215</v>
       </c>
-      <c r="K565" s="9" t="n"/>
+      <c r="K565" s="9" t="n">
+        <v>99.84323500000001</v>
+      </c>
       <c r="L565" s="9" t="n">
         <v>99.56307200000001</v>
       </c>

--- a/downloads/indicadores/SIC/SIC_datos.xlsx
+++ b/downloads/indicadores/SIC/SIC_datos.xlsx
@@ -7188,7 +7188,7 @@
         <v>98.51190200000001</v>
       </c>
       <c r="M90" s="6" t="n">
-        <v>102.50242</v>
+        <v>102.505645</v>
       </c>
       <c r="N90" s="6" t="n">
         <v>97.892993</v>
@@ -7270,7 +7270,7 @@
         <v>98.516383</v>
       </c>
       <c r="M91" s="9" t="n">
-        <v>102.143164</v>
+        <v>102.145931</v>
       </c>
       <c r="N91" s="9" t="n">
         <v>97.95244</v>
@@ -7352,7 +7352,7 @@
         <v>98.5592</v>
       </c>
       <c r="M92" s="6" t="n">
-        <v>101.745879</v>
+        <v>101.748141</v>
       </c>
       <c r="N92" s="6" t="n">
         <v>98.018962</v>
@@ -7434,7 +7434,7 @@
         <v>98.640883</v>
       </c>
       <c r="M93" s="9" t="n">
-        <v>101.336368</v>
+        <v>101.338109</v>
       </c>
       <c r="N93" s="9" t="n">
         <v>98.086065</v>
@@ -7516,7 +7516,7 @@
         <v>98.76139999999999</v>
       </c>
       <c r="M94" s="6" t="n">
-        <v>100.934285</v>
+        <v>100.935514</v>
       </c>
       <c r="N94" s="6" t="n">
         <v>98.165239</v>
@@ -7598,7 +7598,7 @@
         <v>98.913512</v>
       </c>
       <c r="M95" s="9" t="n">
-        <v>100.593698</v>
+        <v>100.594494</v>
       </c>
       <c r="N95" s="9" t="n">
         <v>98.272392</v>
@@ -7680,7 +7680,7 @@
         <v>99.08424100000001</v>
       </c>
       <c r="M96" s="6" t="n">
-        <v>100.331001</v>
+        <v>100.331462</v>
       </c>
       <c r="N96" s="6" t="n">
         <v>98.412328</v>
@@ -7762,7 +7762,7 @@
         <v>99.25591900000001</v>
       </c>
       <c r="M97" s="9" t="n">
-        <v>100.14921</v>
+        <v>100.14944</v>
       </c>
       <c r="N97" s="9" t="n">
         <v>98.545681</v>
@@ -7844,7 +7844,7 @@
         <v>99.40737900000001</v>
       </c>
       <c r="M98" s="6" t="n">
-        <v>100.048391</v>
+        <v>100.048493</v>
       </c>
       <c r="N98" s="6" t="n">
         <v>98.652556</v>
@@ -7926,7 +7926,7 @@
         <v>99.51046100000001</v>
       </c>
       <c r="M99" s="9" t="n">
-        <v>100.011216</v>
+        <v>100.01127</v>
       </c>
       <c r="N99" s="9" t="n">
         <v>98.745116</v>
@@ -8008,7 +8008,7 @@
         <v>99.547225</v>
       </c>
       <c r="M100" s="6" t="n">
-        <v>100.001211</v>
+        <v>100.001253</v>
       </c>
       <c r="N100" s="6" t="n">
         <v>98.84505799999999</v>
@@ -8090,7 +8090,7 @@
         <v>99.51947</v>
       </c>
       <c r="M101" s="9" t="n">
-        <v>100.034374</v>
+        <v>100.034458</v>
       </c>
       <c r="N101" s="9" t="n">
         <v>98.996773</v>
@@ -8172,7 +8172,7 @@
         <v>99.452657</v>
       </c>
       <c r="M102" s="6" t="n">
-        <v>100.154682</v>
+        <v>100.154919</v>
       </c>
       <c r="N102" s="6" t="n">
         <v>99.241058</v>
@@ -8254,7 +8254,7 @@
         <v>99.37315700000001</v>
       </c>
       <c r="M103" s="9" t="n">
-        <v>100.325234</v>
+        <v>100.325688</v>
       </c>
       <c r="N103" s="9" t="n">
         <v>99.545348</v>
@@ -8336,7 +8336,7 @@
         <v>99.29202100000001</v>
       </c>
       <c r="M104" s="6" t="n">
-        <v>100.515355</v>
+        <v>100.516051</v>
       </c>
       <c r="N104" s="6" t="n">
         <v>99.882403</v>
@@ -8418,7 +8418,7 @@
         <v>99.21389600000001</v>
       </c>
       <c r="M105" s="9" t="n">
-        <v>100.676895</v>
+        <v>100.677797</v>
       </c>
       <c r="N105" s="9" t="n">
         <v>100.22264</v>
@@ -8500,7 +8500,7 @@
         <v>99.13916500000001</v>
       </c>
       <c r="M106" s="6" t="n">
-        <v>100.795882</v>
+        <v>100.796935</v>
       </c>
       <c r="N106" s="6" t="n">
         <v>100.54233</v>
@@ -8582,7 +8582,7 @@
         <v>99.06715699999999</v>
       </c>
       <c r="M107" s="9" t="n">
-        <v>100.868074</v>
+        <v>100.869219</v>
       </c>
       <c r="N107" s="9" t="n">
         <v>100.826539</v>
@@ -8664,7 +8664,7 @@
         <v>98.999554</v>
       </c>
       <c r="M108" s="6" t="n">
-        <v>100.894339</v>
+        <v>100.895517</v>
       </c>
       <c r="N108" s="6" t="n">
         <v>101.0659</v>
@@ -8746,7 +8746,7 @@
         <v>98.939651</v>
       </c>
       <c r="M109" s="9" t="n">
-        <v>100.900789</v>
+        <v>100.901976</v>
       </c>
       <c r="N109" s="9" t="n">
         <v>101.255606</v>
@@ -8828,7 +8828,7 @@
         <v>98.89703299999999</v>
       </c>
       <c r="M110" s="6" t="n">
-        <v>100.910968</v>
+        <v>100.912167</v>
       </c>
       <c r="N110" s="6" t="n">
         <v>101.382544</v>
@@ -8910,7 +8910,7 @@
         <v>98.878773</v>
       </c>
       <c r="M111" s="9" t="n">
-        <v>100.899346</v>
+        <v>100.90053</v>
       </c>
       <c r="N111" s="9" t="n">
         <v>101.453116</v>
@@ -8992,7 +8992,7 @@
         <v>98.88274199999999</v>
       </c>
       <c r="M112" s="6" t="n">
-        <v>100.858715</v>
+        <v>100.859848</v>
       </c>
       <c r="N112" s="6" t="n">
         <v>101.484906</v>
@@ -9074,7 +9074,7 @@
         <v>98.90213900000001</v>
       </c>
       <c r="M113" s="9" t="n">
-        <v>100.758775</v>
+        <v>100.759781</v>
       </c>
       <c r="N113" s="9" t="n">
         <v>101.485166</v>
@@ -9156,7 +9156,7 @@
         <v>98.932323</v>
       </c>
       <c r="M114" s="6" t="n">
-        <v>100.578485</v>
+        <v>100.579261</v>
       </c>
       <c r="N114" s="6" t="n">
         <v>101.472124</v>
@@ -9238,7 +9238,7 @@
         <v>98.971503</v>
       </c>
       <c r="M115" s="9" t="n">
-        <v>100.333073</v>
+        <v>100.333537</v>
       </c>
       <c r="N115" s="9" t="n">
         <v>101.434323</v>
@@ -9320,7 +9320,7 @@
         <v>99.01414</v>
       </c>
       <c r="M116" s="6" t="n">
-        <v>100.077905</v>
+        <v>100.078044</v>
       </c>
       <c r="N116" s="6" t="n">
         <v>101.349857</v>
@@ -9402,7 +9402,7 @@
         <v>99.06422499999999</v>
       </c>
       <c r="M117" s="9" t="n">
-        <v>99.848326</v>
+        <v>99.848173</v>
       </c>
       <c r="N117" s="9" t="n">
         <v>101.217953</v>
@@ -9484,7 +9484,7 @@
         <v>99.128767</v>
       </c>
       <c r="M118" s="6" t="n">
-        <v>99.65974300000001</v>
+        <v>99.65935</v>
       </c>
       <c r="N118" s="6" t="n">
         <v>101.045453</v>
@@ -9566,7 +9566,7 @@
         <v>99.21220700000001</v>
       </c>
       <c r="M119" s="9" t="n">
-        <v>99.492211</v>
+        <v>99.49160500000001</v>
       </c>
       <c r="N119" s="9" t="n">
         <v>100.859876</v>
@@ -9648,7 +9648,7 @@
         <v>99.313259</v>
       </c>
       <c r="M120" s="6" t="n">
-        <v>99.35030500000001</v>
+        <v>99.349518</v>
       </c>
       <c r="N120" s="6" t="n">
         <v>100.673591</v>
@@ -9730,7 +9730,7 @@
         <v>99.42873299999999</v>
       </c>
       <c r="M121" s="9" t="n">
-        <v>99.21216800000001</v>
+        <v>99.211206</v>
       </c>
       <c r="N121" s="9" t="n">
         <v>100.537663</v>
@@ -9812,7 +9812,7 @@
         <v>99.551625</v>
       </c>
       <c r="M122" s="6" t="n">
-        <v>99.052217</v>
+        <v>99.051051</v>
       </c>
       <c r="N122" s="6" t="n">
         <v>100.451146</v>
@@ -9894,7 +9894,7 @@
         <v>99.67785499999999</v>
       </c>
       <c r="M123" s="9" t="n">
-        <v>98.885307</v>
+        <v>98.88392899999999</v>
       </c>
       <c r="N123" s="9" t="n">
         <v>100.374445</v>
@@ -9976,7 +9976,7 @@
         <v>99.801344</v>
       </c>
       <c r="M124" s="6" t="n">
-        <v>98.75078499999999</v>
+        <v>98.749235</v>
       </c>
       <c r="N124" s="6" t="n">
         <v>100.293431</v>
@@ -10058,7 +10058,7 @@
         <v>99.928741</v>
       </c>
       <c r="M125" s="9" t="n">
-        <v>98.654674</v>
+        <v>98.653002</v>
       </c>
       <c r="N125" s="9" t="n">
         <v>100.201901</v>
@@ -10140,7 +10140,7 @@
         <v>100.067618</v>
       </c>
       <c r="M126" s="6" t="n">
-        <v>98.60885399999999</v>
+        <v>98.607123</v>
       </c>
       <c r="N126" s="6" t="n">
         <v>100.117984</v>
@@ -10222,7 +10222,7 @@
         <v>100.222847</v>
       </c>
       <c r="M127" s="9" t="n">
-        <v>98.66471900000001</v>
+        <v>98.66306</v>
       </c>
       <c r="N127" s="9" t="n">
         <v>100.060988</v>
@@ -10304,7 +10304,7 @@
         <v>100.394859</v>
       </c>
       <c r="M128" s="6" t="n">
-        <v>98.840311</v>
+        <v>98.838875</v>
       </c>
       <c r="N128" s="6" t="n">
         <v>100.056448</v>
@@ -10386,7 +10386,7 @@
         <v>100.582563</v>
       </c>
       <c r="M129" s="9" t="n">
-        <v>99.108677</v>
+        <v>99.10758199999999</v>
       </c>
       <c r="N129" s="9" t="n">
         <v>100.110861</v>
@@ -10468,7 +10468,7 @@
         <v>100.779769</v>
       </c>
       <c r="M130" s="6" t="n">
-        <v>99.396039</v>
+        <v>99.39531100000001</v>
       </c>
       <c r="N130" s="6" t="n">
         <v>100.22437</v>
@@ -10550,7 +10550,7 @@
         <v>100.984909</v>
       </c>
       <c r="M131" s="9" t="n">
-        <v>99.638379</v>
+        <v>99.637959</v>
       </c>
       <c r="N131" s="9" t="n">
         <v>100.370938</v>
@@ -10632,7 +10632,7 @@
         <v>101.194144</v>
       </c>
       <c r="M132" s="6" t="n">
-        <v>99.768208</v>
+        <v>99.767954</v>
       </c>
       <c r="N132" s="6" t="n">
         <v>100.523246</v>
@@ -10714,7 +10714,7 @@
         <v>101.403197</v>
       </c>
       <c r="M133" s="9" t="n">
-        <v>99.74003500000001</v>
+        <v>99.739744</v>
       </c>
       <c r="N133" s="9" t="n">
         <v>100.655925</v>
@@ -10796,7 +10796,7 @@
         <v>101.606379</v>
       </c>
       <c r="M134" s="6" t="n">
-        <v>99.62265499999999</v>
+        <v>99.622214</v>
       </c>
       <c r="N134" s="6" t="n">
         <v>100.738316</v>
@@ -10878,7 +10878,7 @@
         <v>101.797846</v>
       </c>
       <c r="M135" s="9" t="n">
-        <v>99.485354</v>
+        <v>99.484739</v>
       </c>
       <c r="N135" s="9" t="n">
         <v>100.757939</v>
@@ -10960,7 +10960,7 @@
         <v>101.978377</v>
       </c>
       <c r="M136" s="6" t="n">
-        <v>99.29503699999999</v>
+        <v>99.29418</v>
       </c>
       <c r="N136" s="6" t="n">
         <v>100.716531</v>
@@ -11042,7 +11042,7 @@
         <v>102.148385</v>
       </c>
       <c r="M137" s="9" t="n">
-        <v>99.09972999999999</v>
+        <v>99.098625</v>
       </c>
       <c r="N137" s="9" t="n">
         <v>100.63709</v>
@@ -11124,7 +11124,7 @@
         <v>102.303445</v>
       </c>
       <c r="M138" s="6" t="n">
-        <v>98.907917</v>
+        <v>98.90656799999999</v>
       </c>
       <c r="N138" s="6" t="n">
         <v>100.528929</v>
@@ -11206,7 +11206,7 @@
         <v>102.44182</v>
       </c>
       <c r="M139" s="9" t="n">
-        <v>98.714609</v>
+        <v>98.713013</v>
       </c>
       <c r="N139" s="9" t="n">
         <v>100.416987</v>
@@ -11288,7 +11288,7 @@
         <v>102.561421</v>
       </c>
       <c r="M140" s="6" t="n">
-        <v>98.531734</v>
+        <v>98.529905</v>
       </c>
       <c r="N140" s="6" t="n">
         <v>100.326247</v>
@@ -11370,7 +11370,7 @@
         <v>102.661869</v>
       </c>
       <c r="M141" s="9" t="n">
-        <v>98.342826</v>
+        <v>98.340757</v>
       </c>
       <c r="N141" s="9" t="n">
         <v>100.276095</v>
@@ -11452,7 +11452,7 @@
         <v>102.745657</v>
       </c>
       <c r="M142" s="6" t="n">
-        <v>98.22292299999999</v>
+        <v>98.22070100000001</v>
       </c>
       <c r="N142" s="6" t="n">
         <v>100.25898</v>
@@ -11534,7 +11534,7 @@
         <v>102.807129</v>
       </c>
       <c r="M143" s="9" t="n">
-        <v>98.266854</v>
+        <v>98.264689</v>
       </c>
       <c r="N143" s="9" t="n">
         <v>100.261962</v>
@@ -11616,7 +11616,7 @@
         <v>102.844488</v>
       </c>
       <c r="M144" s="6" t="n">
-        <v>98.517979</v>
+        <v>98.516133</v>
       </c>
       <c r="N144" s="6" t="n">
         <v>100.283657</v>
@@ -11698,7 +11698,7 @@
         <v>102.862739</v>
       </c>
       <c r="M145" s="9" t="n">
-        <v>98.874441</v>
+        <v>98.87304899999999</v>
       </c>
       <c r="N145" s="9" t="n">
         <v>100.31637</v>
@@ -11780,7 +11780,7 @@
         <v>102.864919</v>
       </c>
       <c r="M146" s="6" t="n">
-        <v>99.17998900000001</v>
+        <v>99.17898599999999</v>
       </c>
       <c r="N146" s="6" t="n">
         <v>100.361433</v>
@@ -11862,7 +11862,7 @@
         <v>102.850605</v>
       </c>
       <c r="M147" s="9" t="n">
-        <v>99.3807</v>
+        <v>99.379952</v>
       </c>
       <c r="N147" s="9" t="n">
         <v>100.425478</v>
@@ -11944,7 +11944,7 @@
         <v>102.813314</v>
       </c>
       <c r="M148" s="6" t="n">
-        <v>99.450846</v>
+        <v>99.450188</v>
       </c>
       <c r="N148" s="6" t="n">
         <v>100.51403</v>
@@ -12026,7 +12026,7 @@
         <v>102.748735</v>
       </c>
       <c r="M149" s="9" t="n">
-        <v>99.415256</v>
+        <v>99.414552</v>
       </c>
       <c r="N149" s="9" t="n">
         <v>100.611543</v>
@@ -12108,7 +12108,7 @@
         <v>102.652354</v>
       </c>
       <c r="M150" s="6" t="n">
-        <v>99.312742</v>
+        <v>99.311908</v>
       </c>
       <c r="N150" s="6" t="n">
         <v>100.732318</v>
@@ -12190,7 +12190,7 @@
         <v>102.521451</v>
       </c>
       <c r="M151" s="9" t="n">
-        <v>99.161259</v>
+        <v>99.160231</v>
       </c>
       <c r="N151" s="9" t="n">
         <v>100.874249</v>
@@ -12272,7 +12272,7 @@
         <v>102.359896</v>
       </c>
       <c r="M152" s="6" t="n">
-        <v>98.96308999999999</v>
+        <v>98.96181</v>
       </c>
       <c r="N152" s="6" t="n">
         <v>101.01343</v>
@@ -12354,7 +12354,7 @@
         <v>102.178178</v>
       </c>
       <c r="M153" s="9" t="n">
-        <v>98.756714</v>
+        <v>98.755171</v>
       </c>
       <c r="N153" s="9" t="n">
         <v>101.11644</v>
@@ -12436,7 +12436,7 @@
         <v>101.993376</v>
       </c>
       <c r="M154" s="6" t="n">
-        <v>98.55176400000001</v>
+        <v>98.549961</v>
       </c>
       <c r="N154" s="6" t="n">
         <v>101.170233</v>
@@ -12518,7 +12518,7 @@
         <v>101.81796</v>
       </c>
       <c r="M155" s="9" t="n">
-        <v>98.337878</v>
+        <v>98.335803</v>
       </c>
       <c r="N155" s="9" t="n">
         <v>101.171436</v>
@@ -12600,7 +12600,7 @@
         <v>101.660902</v>
       </c>
       <c r="M156" s="6" t="n">
-        <v>98.14555799999999</v>
+        <v>98.143238</v>
       </c>
       <c r="N156" s="6" t="n">
         <v>101.127271</v>
@@ -12682,7 +12682,7 @@
         <v>101.518364</v>
       </c>
       <c r="M157" s="9" t="n">
-        <v>98.01981000000001</v>
+        <v>98.01733</v>
       </c>
       <c r="N157" s="9" t="n">
         <v>101.042696</v>
@@ -12764,7 +12764,7 @@
         <v>101.386728</v>
       </c>
       <c r="M158" s="6" t="n">
-        <v>98.04830699999999</v>
+        <v>98.045863</v>
       </c>
       <c r="N158" s="6" t="n">
         <v>100.938767</v>
@@ -12846,7 +12846,7 @@
         <v>101.264668</v>
       </c>
       <c r="M159" s="9" t="n">
-        <v>98.232855</v>
+        <v>98.23064599999999</v>
       </c>
       <c r="N159" s="9" t="n">
         <v>100.824871</v>
@@ -12928,7 +12928,7 @@
         <v>101.158839</v>
       </c>
       <c r="M160" s="6" t="n">
-        <v>98.499606</v>
+        <v>98.497737</v>
       </c>
       <c r="N160" s="6" t="n">
         <v>100.693439</v>
@@ -13010,7 +13010,7 @@
         <v>101.07511</v>
       </c>
       <c r="M161" s="9" t="n">
-        <v>98.749639</v>
+        <v>98.748088</v>
       </c>
       <c r="N161" s="9" t="n">
         <v>100.551053</v>
@@ -13092,7 +13092,7 @@
         <v>101.015554</v>
       </c>
       <c r="M162" s="6" t="n">
-        <v>98.996313</v>
+        <v>98.995076</v>
       </c>
       <c r="N162" s="6" t="n">
         <v>100.412185</v>
@@ -13174,7 +13174,7 @@
         <v>100.972908</v>
       </c>
       <c r="M163" s="9" t="n">
-        <v>99.203872</v>
+        <v>99.202899</v>
       </c>
       <c r="N163" s="9" t="n">
         <v>100.309694</v>
@@ -13256,7 +13256,7 @@
         <v>100.931648</v>
       </c>
       <c r="M164" s="6" t="n">
-        <v>99.3334</v>
+        <v>99.33259200000001</v>
       </c>
       <c r="N164" s="6" t="n">
         <v>100.233917</v>
@@ -13338,7 +13338,7 @@
         <v>100.867833</v>
       </c>
       <c r="M165" s="9" t="n">
-        <v>99.394841</v>
+        <v>99.394111</v>
       </c>
       <c r="N165" s="9" t="n">
         <v>100.175406</v>
@@ -13420,7 +13420,7 @@
         <v>100.759148</v>
       </c>
       <c r="M166" s="6" t="n">
-        <v>99.45854799999999</v>
+        <v>99.457899</v>
       </c>
       <c r="N166" s="6" t="n">
         <v>100.113812</v>
@@ -13502,7 +13502,7 @@
         <v>100.597146</v>
       </c>
       <c r="M167" s="9" t="n">
-        <v>99.530917</v>
+        <v>99.53036</v>
       </c>
       <c r="N167" s="9" t="n">
         <v>100.040858</v>
@@ -13584,7 +13584,7 @@
         <v>100.386884</v>
       </c>
       <c r="M168" s="6" t="n">
-        <v>99.63661</v>
+        <v>99.636188</v>
       </c>
       <c r="N168" s="6" t="n">
         <v>99.94884500000001</v>
@@ -13666,7 +13666,7 @@
         <v>100.148146</v>
       </c>
       <c r="M169" s="9" t="n">
-        <v>99.742277</v>
+        <v>99.741989</v>
       </c>
       <c r="N169" s="9" t="n">
         <v>99.842817</v>
@@ -13748,7 +13748,7 @@
         <v>99.911027</v>
       </c>
       <c r="M170" s="6" t="n">
-        <v>99.786051</v>
+        <v>99.785819</v>
       </c>
       <c r="N170" s="6" t="n">
         <v>99.78045299999999</v>
@@ -13830,7 +13830,7 @@
         <v>99.706137</v>
       </c>
       <c r="M171" s="9" t="n">
-        <v>99.756052</v>
+        <v>99.755782</v>
       </c>
       <c r="N171" s="9" t="n">
         <v>99.774691</v>
@@ -13912,7 +13912,7 @@
         <v>99.556597</v>
       </c>
       <c r="M172" s="6" t="n">
-        <v>99.681265</v>
+        <v>99.680899</v>
       </c>
       <c r="N172" s="6" t="n">
         <v>99.842652</v>
@@ -13994,7 +13994,7 @@
         <v>99.469658</v>
       </c>
       <c r="M173" s="9" t="n">
-        <v>99.562348</v>
+        <v>99.561831</v>
       </c>
       <c r="N173" s="9" t="n">
         <v>100.003455</v>
@@ -14076,7 +14076,7 @@
         <v>99.443105</v>
       </c>
       <c r="M174" s="6" t="n">
-        <v>99.384709</v>
+        <v>99.383966</v>
       </c>
       <c r="N174" s="6" t="n">
         <v>100.21716</v>
@@ -14158,7 +14158,7 @@
         <v>99.47326</v>
       </c>
       <c r="M175" s="9" t="n">
-        <v>99.150368</v>
+        <v>99.149326</v>
       </c>
       <c r="N175" s="9" t="n">
         <v>100.433036</v>
@@ -14240,7 +14240,7 @@
         <v>99.546398</v>
       </c>
       <c r="M176" s="6" t="n">
-        <v>98.89662800000001</v>
+        <v>98.895264</v>
       </c>
       <c r="N176" s="6" t="n">
         <v>100.616494</v>
@@ -14322,7 +14322,7 @@
         <v>99.64872200000001</v>
       </c>
       <c r="M177" s="9" t="n">
-        <v>98.652308</v>
+        <v>98.650632</v>
       </c>
       <c r="N177" s="9" t="n">
         <v>100.771587</v>
@@ -14404,7 +14404,7 @@
         <v>99.762888</v>
       </c>
       <c r="M178" s="6" t="n">
-        <v>98.441457</v>
+        <v>98.43951300000001</v>
       </c>
       <c r="N178" s="6" t="n">
         <v>100.891778</v>
@@ -14486,7 +14486,7 @@
         <v>99.875248</v>
       </c>
       <c r="M179" s="9" t="n">
-        <v>98.321654</v>
+        <v>98.319558</v>
       </c>
       <c r="N179" s="9" t="n">
         <v>100.971814</v>
@@ -14568,7 +14568,7 @@
         <v>99.974761</v>
       </c>
       <c r="M180" s="6" t="n">
-        <v>98.30812400000001</v>
+        <v>98.30601</v>
       </c>
       <c r="N180" s="6" t="n">
         <v>101.001825</v>
@@ -14650,7 +14650,7 @@
         <v>100.042863</v>
       </c>
       <c r="M181" s="9" t="n">
-        <v>98.41171900000001</v>
+        <v>98.409738</v>
       </c>
       <c r="N181" s="9" t="n">
         <v>100.978331</v>
@@ -14732,7 +14732,7 @@
         <v>100.055979</v>
       </c>
       <c r="M182" s="6" t="n">
-        <v>98.657927</v>
+        <v>98.65625900000001</v>
       </c>
       <c r="N182" s="6" t="n">
         <v>100.902762</v>
@@ -14814,7 +14814,7 @@
         <v>99.990279</v>
       </c>
       <c r="M183" s="9" t="n">
-        <v>99.03360000000001</v>
+        <v>99.032411</v>
       </c>
       <c r="N183" s="9" t="n">
         <v>100.763539</v>
@@ -14896,7 +14896,7 @@
         <v>99.812718</v>
       </c>
       <c r="M184" s="6" t="n">
-        <v>99.52918699999999</v>
+        <v>99.528628</v>
       </c>
       <c r="N184" s="6" t="n">
         <v>100.520509</v>
@@ -14978,7 +14978,7 @@
         <v>99.506129</v>
       </c>
       <c r="M185" s="9" t="n">
-        <v>100.139348</v>
+        <v>100.139565</v>
       </c>
       <c r="N185" s="9" t="n">
         <v>100.154459</v>
@@ -15060,7 +15060,7 @@
         <v>99.076477</v>
       </c>
       <c r="M186" s="6" t="n">
-        <v>100.873549</v>
+        <v>100.874701</v>
       </c>
       <c r="N186" s="6" t="n">
         <v>99.688078</v>
@@ -15142,7 +15142,7 @@
         <v>98.54845400000001</v>
       </c>
       <c r="M187" s="9" t="n">
-        <v>101.692318</v>
+        <v>101.694512</v>
       </c>
       <c r="N187" s="9" t="n">
         <v>99.19038999999999</v>
@@ -15224,7 +15224,7 @@
         <v>97.973736</v>
       </c>
       <c r="M188" s="6" t="n">
-        <v>102.519496</v>
+        <v>102.522743</v>
       </c>
       <c r="N188" s="6" t="n">
         <v>98.73393299999999</v>
@@ -15306,7 +15306,7 @@
         <v>97.407055</v>
       </c>
       <c r="M189" s="9" t="n">
-        <v>103.277782</v>
+        <v>103.281993</v>
       </c>
       <c r="N189" s="9" t="n">
         <v>98.35557900000001</v>
@@ -15388,7 +15388,7 @@
         <v>96.884603</v>
       </c>
       <c r="M190" s="6" t="n">
-        <v>103.904388</v>
+        <v>103.909397</v>
       </c>
       <c r="N190" s="6" t="n">
         <v>98.10335600000001</v>
@@ -15470,7 +15470,7 @@
         <v>96.434763</v>
       </c>
       <c r="M191" s="9" t="n">
-        <v>104.355133</v>
+        <v>104.360716</v>
       </c>
       <c r="N191" s="9" t="n">
         <v>97.967546</v>
@@ -15552,7 +15552,7 @@
         <v>96.074258</v>
       </c>
       <c r="M192" s="6" t="n">
-        <v>104.610929</v>
+        <v>104.616837</v>
       </c>
       <c r="N192" s="6" t="n">
         <v>97.926462</v>
@@ -15634,7 +15634,7 @@
         <v>95.814539</v>
       </c>
       <c r="M193" s="9" t="n">
-        <v>104.677479</v>
+        <v>104.683472</v>
       </c>
       <c r="N193" s="9" t="n">
         <v>97.960284</v>
@@ -15716,7 +15716,7 @@
         <v>95.659972</v>
       </c>
       <c r="M194" s="6" t="n">
-        <v>104.56857</v>
+        <v>104.574424</v>
       </c>
       <c r="N194" s="6" t="n">
         <v>98.027846</v>
@@ -15798,7 +15798,7 @@
         <v>95.60636599999999</v>
       </c>
       <c r="M195" s="9" t="n">
-        <v>104.333847</v>
+        <v>104.339403</v>
       </c>
       <c r="N195" s="9" t="n">
         <v>98.11821500000001</v>
@@ -15880,7 +15880,7 @@
         <v>95.645771</v>
       </c>
       <c r="M196" s="6" t="n">
-        <v>104.025174</v>
+        <v>104.030338</v>
       </c>
       <c r="N196" s="6" t="n">
         <v>98.24487000000001</v>
@@ -15962,7 +15962,7 @@
         <v>95.767191</v>
       </c>
       <c r="M197" s="9" t="n">
-        <v>103.675995</v>
+        <v>103.680714</v>
       </c>
       <c r="N197" s="9" t="n">
         <v>98.403447</v>
@@ -16044,7 +16044,7 @@
         <v>95.95566599999999</v>
       </c>
       <c r="M198" s="6" t="n">
-        <v>103.297125</v>
+        <v>103.301362</v>
       </c>
       <c r="N198" s="6" t="n">
         <v>98.576204</v>
@@ -16126,7 +16126,7 @@
         <v>96.190055</v>
       </c>
       <c r="M199" s="9" t="n">
-        <v>102.925279</v>
+        <v>102.929043</v>
       </c>
       <c r="N199" s="9" t="n">
         <v>98.750491</v>
@@ -16208,7 +16208,7 @@
         <v>96.447711</v>
       </c>
       <c r="M200" s="6" t="n">
-        <v>102.588102</v>
+        <v>102.591436</v>
       </c>
       <c r="N200" s="6" t="n">
         <v>98.90775499999999</v>
@@ -16290,7 +16290,7 @@
         <v>96.708462</v>
       </c>
       <c r="M201" s="9" t="n">
-        <v>102.308422</v>
+        <v>102.3114</v>
       </c>
       <c r="N201" s="9" t="n">
         <v>99.04475499999999</v>
@@ -16372,7 +16372,7 @@
         <v>96.962307</v>
       </c>
       <c r="M202" s="6" t="n">
-        <v>102.103506</v>
+        <v>102.106223</v>
       </c>
       <c r="N202" s="6" t="n">
         <v>99.153679</v>
@@ -16454,7 +16454,7 @@
         <v>97.20365200000001</v>
       </c>
       <c r="M203" s="9" t="n">
-        <v>101.991072</v>
+        <v>101.993646</v>
       </c>
       <c r="N203" s="9" t="n">
         <v>99.236716</v>
@@ -16536,7 +16536,7 @@
         <v>97.432541</v>
       </c>
       <c r="M204" s="6" t="n">
-        <v>101.963554</v>
+        <v>101.966094</v>
       </c>
       <c r="N204" s="6" t="n">
         <v>99.32405</v>
@@ -16618,7 +16618,7 @@
         <v>97.659094</v>
       </c>
       <c r="M205" s="9" t="n">
-        <v>102.020364</v>
+        <v>102.022975</v>
       </c>
       <c r="N205" s="9" t="n">
         <v>99.407473</v>
@@ -16700,7 +16700,7 @@
         <v>97.89322799999999</v>
       </c>
       <c r="M206" s="6" t="n">
-        <v>102.143063</v>
+        <v>102.145831</v>
       </c>
       <c r="N206" s="6" t="n">
         <v>99.475847</v>
@@ -16782,7 +16782,7 @@
         <v>98.14591900000001</v>
       </c>
       <c r="M207" s="9" t="n">
-        <v>102.247821</v>
+        <v>102.250722</v>
       </c>
       <c r="N207" s="9" t="n">
         <v>99.52188200000001</v>
@@ -16864,7 +16864,7 @@
         <v>98.419324</v>
       </c>
       <c r="M208" s="6" t="n">
-        <v>102.251376</v>
+        <v>102.254282</v>
       </c>
       <c r="N208" s="6" t="n">
         <v>99.542753</v>
@@ -16946,7 +16946,7 @@
         <v>98.712219</v>
       </c>
       <c r="M209" s="9" t="n">
-        <v>102.13995</v>
+        <v>102.142713</v>
       </c>
       <c r="N209" s="9" t="n">
         <v>99.56228400000001</v>
@@ -17028,7 +17028,7 @@
         <v>99.017067</v>
       </c>
       <c r="M210" s="6" t="n">
-        <v>101.939874</v>
+        <v>101.942383</v>
       </c>
       <c r="N210" s="6" t="n">
         <v>99.618022</v>
@@ -17110,7 +17110,7 @@
         <v>99.33753299999999</v>
       </c>
       <c r="M211" s="9" t="n">
-        <v>101.692623</v>
+        <v>101.694818</v>
       </c>
       <c r="N211" s="9" t="n">
         <v>99.70281900000001</v>
@@ -17192,7 +17192,7 @@
         <v>99.658978</v>
       </c>
       <c r="M212" s="6" t="n">
-        <v>101.447255</v>
+        <v>101.449137</v>
       </c>
       <c r="N212" s="6" t="n">
         <v>99.808397</v>
@@ -17274,7 +17274,7 @@
         <v>99.970547</v>
       </c>
       <c r="M213" s="9" t="n">
-        <v>101.206618</v>
+        <v>101.208194</v>
       </c>
       <c r="N213" s="9" t="n">
         <v>99.920496</v>
@@ -17356,7 +17356,7 @@
         <v>100.255419</v>
       </c>
       <c r="M214" s="6" t="n">
-        <v>100.955874</v>
+        <v>100.957131</v>
       </c>
       <c r="N214" s="6" t="n">
         <v>100.031551</v>
@@ -17438,7 +17438,7 @@
         <v>100.493988</v>
       </c>
       <c r="M215" s="9" t="n">
-        <v>100.690255</v>
+        <v>100.691173</v>
       </c>
       <c r="N215" s="9" t="n">
         <v>100.143371</v>
@@ -17520,7 +17520,7 @@
         <v>100.672919</v>
       </c>
       <c r="M216" s="6" t="n">
-        <v>100.443555</v>
+        <v>100.444159</v>
       </c>
       <c r="N216" s="6" t="n">
         <v>100.245406</v>
@@ -17602,7 +17602,7 @@
         <v>100.780714</v>
       </c>
       <c r="M217" s="9" t="n">
-        <v>100.205651</v>
+        <v>100.205953</v>
       </c>
       <c r="N217" s="9" t="n">
         <v>100.331473</v>
@@ -17684,7 +17684,7 @@
         <v>100.814908</v>
       </c>
       <c r="M218" s="6" t="n">
-        <v>100.013222</v>
+        <v>100.013279</v>
       </c>
       <c r="N218" s="6" t="n">
         <v>100.406185</v>
@@ -17766,7 +17766,7 @@
         <v>100.785847</v>
       </c>
       <c r="M219" s="9" t="n">
-        <v>99.89183</v>
+        <v>99.891732</v>
       </c>
       <c r="N219" s="9" t="n">
         <v>100.472125</v>
@@ -17848,7 +17848,7 @@
         <v>100.717263</v>
       </c>
       <c r="M220" s="6" t="n">
-        <v>99.84460199999999</v>
+        <v>99.844444</v>
       </c>
       <c r="N220" s="6" t="n">
         <v>100.529471</v>
@@ -17930,7 +17930,7 @@
         <v>100.63525</v>
       </c>
       <c r="M221" s="9" t="n">
-        <v>99.84677600000001</v>
+        <v>99.846621</v>
       </c>
       <c r="N221" s="9" t="n">
         <v>100.571143</v>
@@ -18012,7 +18012,7 @@
         <v>100.563292</v>
       </c>
       <c r="M222" s="6" t="n">
-        <v>99.89017699999999</v>
+        <v>99.89007700000001</v>
       </c>
       <c r="N222" s="6" t="n">
         <v>100.597709</v>
@@ -18094,7 +18094,7 @@
         <v>100.50313</v>
       </c>
       <c r="M223" s="9" t="n">
-        <v>99.93253799999999</v>
+        <v>99.932492</v>
       </c>
       <c r="N223" s="9" t="n">
         <v>100.595021</v>
@@ -18176,7 +18176,7 @@
         <v>100.454836</v>
       </c>
       <c r="M224" s="6" t="n">
-        <v>99.953468</v>
+        <v>99.95344900000001</v>
       </c>
       <c r="N224" s="6" t="n">
         <v>100.555884</v>
@@ -18258,7 +18258,7 @@
         <v>100.414439</v>
       </c>
       <c r="M225" s="9" t="n">
-        <v>99.96740699999999</v>
+        <v>99.967405</v>
       </c>
       <c r="N225" s="9" t="n">
         <v>100.474418</v>
@@ -18340,7 +18340,7 @@
         <v>100.381583</v>
       </c>
       <c r="M226" s="6" t="n">
-        <v>100.000029</v>
+        <v>100.000069</v>
       </c>
       <c r="N226" s="6" t="n">
         <v>100.356471</v>
@@ -18422,7 +18422,7 @@
         <v>100.362878</v>
       </c>
       <c r="M227" s="9" t="n">
-        <v>100.0261</v>
+        <v>100.026174</v>
       </c>
       <c r="N227" s="9" t="n">
         <v>100.220202</v>
@@ -18504,7 +18504,7 @@
         <v>100.356834</v>
       </c>
       <c r="M228" s="6" t="n">
-        <v>100.013599</v>
+        <v>100.013657</v>
       </c>
       <c r="N228" s="6" t="n">
         <v>100.089906</v>
@@ -18586,7 +18586,7 @@
         <v>100.358683</v>
       </c>
       <c r="M229" s="9" t="n">
-        <v>99.97425</v>
+        <v>99.97425699999999</v>
       </c>
       <c r="N229" s="9" t="n">
         <v>99.981208</v>
@@ -18668,7 +18668,7 @@
         <v>100.367118</v>
       </c>
       <c r="M230" s="6" t="n">
-        <v>99.924171</v>
+        <v>99.924115</v>
       </c>
       <c r="N230" s="6" t="n">
         <v>99.90106299999999</v>
@@ -18750,7 +18750,7 @@
         <v>100.380282</v>
       </c>
       <c r="M231" s="9" t="n">
-        <v>99.85808400000001</v>
+        <v>99.85794300000001</v>
       </c>
       <c r="N231" s="9" t="n">
         <v>99.841312</v>
@@ -18832,7 +18832,7 @@
         <v>100.398545</v>
       </c>
       <c r="M232" s="6" t="n">
-        <v>99.759773</v>
+        <v>99.759507</v>
       </c>
       <c r="N232" s="6" t="n">
         <v>99.799183</v>
@@ -18914,7 +18914,7 @@
         <v>100.423575</v>
       </c>
       <c r="M233" s="9" t="n">
-        <v>99.640201</v>
+        <v>99.63978299999999</v>
       </c>
       <c r="N233" s="9" t="n">
         <v>99.771214</v>
@@ -18996,7 +18996,7 @@
         <v>100.455848</v>
       </c>
       <c r="M234" s="6" t="n">
-        <v>99.47417</v>
+        <v>99.47354</v>
       </c>
       <c r="N234" s="6" t="n">
         <v>99.77301300000001</v>
@@ -19078,7 +19078,7 @@
         <v>100.495583</v>
       </c>
       <c r="M235" s="9" t="n">
-        <v>99.286716</v>
+        <v>99.285849</v>
       </c>
       <c r="N235" s="9" t="n">
         <v>99.81453500000001</v>
@@ -19160,7 +19160,7 @@
         <v>100.54252</v>
       </c>
       <c r="M236" s="6" t="n">
-        <v>99.06441700000001</v>
+        <v>99.063266</v>
       </c>
       <c r="N236" s="6" t="n">
         <v>99.891158</v>
@@ -19242,7 +19242,7 @@
         <v>100.594537</v>
       </c>
       <c r="M237" s="9" t="n">
-        <v>98.818839</v>
+        <v>98.817375</v>
       </c>
       <c r="N237" s="9" t="n">
         <v>99.988962</v>
@@ -19324,7 +19324,7 @@
         <v>100.651441</v>
       </c>
       <c r="M238" s="6" t="n">
-        <v>98.577793</v>
+        <v>98.57602300000001</v>
       </c>
       <c r="N238" s="6" t="n">
         <v>100.093697</v>
@@ -19406,7 +19406,7 @@
         <v>100.712058</v>
       </c>
       <c r="M239" s="9" t="n">
-        <v>98.38543900000001</v>
+        <v>98.38342400000001</v>
       </c>
       <c r="N239" s="9" t="n">
         <v>100.192889</v>
@@ -19488,7 +19488,7 @@
         <v>100.780679</v>
       </c>
       <c r="M240" s="6" t="n">
-        <v>98.205269</v>
+        <v>98.203025</v>
       </c>
       <c r="N240" s="6" t="n">
         <v>100.285093</v>
@@ -19570,7 +19570,7 @@
         <v>100.864976</v>
       </c>
       <c r="M241" s="9" t="n">
-        <v>98.07752000000001</v>
+        <v>98.075113</v>
       </c>
       <c r="N241" s="9" t="n">
         <v>100.377273</v>
@@ -19652,7 +19652,7 @@
         <v>100.966771</v>
       </c>
       <c r="M242" s="6" t="n">
-        <v>97.999602</v>
+        <v>97.997096</v>
       </c>
       <c r="N242" s="6" t="n">
         <v>100.473648</v>
@@ -19734,7 +19734,7 @@
         <v>101.081875</v>
       </c>
       <c r="M243" s="9" t="n">
-        <v>97.988879</v>
+        <v>97.98635899999999</v>
       </c>
       <c r="N243" s="9" t="n">
         <v>100.581864</v>
@@ -19816,7 +19816,7 @@
         <v>101.207008</v>
       </c>
       <c r="M244" s="6" t="n">
-        <v>98.032583</v>
+        <v>98.030119</v>
       </c>
       <c r="N244" s="6" t="n">
         <v>100.702642</v>
@@ -19898,7 +19898,7 @@
         <v>101.335547</v>
       </c>
       <c r="M245" s="9" t="n">
-        <v>98.108453</v>
+        <v>98.106086</v>
       </c>
       <c r="N245" s="9" t="n">
         <v>100.835624</v>
@@ -19980,7 +19980,7 @@
         <v>101.466596</v>
       </c>
       <c r="M246" s="6" t="n">
-        <v>98.194896</v>
+        <v>98.192639</v>
       </c>
       <c r="N246" s="6" t="n">
         <v>100.973945</v>
@@ -20062,7 +20062,7 @@
         <v>101.59637</v>
       </c>
       <c r="M247" s="9" t="n">
-        <v>98.287761</v>
+        <v>98.285622</v>
       </c>
       <c r="N247" s="9" t="n">
         <v>101.100266</v>
@@ -20144,7 +20144,7 @@
         <v>101.727801</v>
       </c>
       <c r="M248" s="6" t="n">
-        <v>98.370937</v>
+        <v>98.368903</v>
       </c>
       <c r="N248" s="6" t="n">
         <v>101.220627</v>
@@ -20226,7 +20226,7 @@
         <v>101.866996</v>
       </c>
       <c r="M249" s="9" t="n">
-        <v>98.432248</v>
+        <v>98.43029199999999</v>
       </c>
       <c r="N249" s="9" t="n">
         <v>101.353368</v>
@@ -20308,7 +20308,7 @@
         <v>102.021401</v>
       </c>
       <c r="M250" s="6" t="n">
-        <v>98.43005599999999</v>
+        <v>98.42809699999999</v>
       </c>
       <c r="N250" s="6" t="n">
         <v>101.491925</v>
@@ -20390,7 +20390,7 @@
         <v>102.186555</v>
       </c>
       <c r="M251" s="9" t="n">
-        <v>98.37163200000001</v>
+        <v>98.36959899999999</v>
       </c>
       <c r="N251" s="9" t="n">
         <v>101.620261</v>
@@ -20472,7 +20472,7 @@
         <v>102.350154</v>
       </c>
       <c r="M252" s="6" t="n">
-        <v>98.306128</v>
+        <v>98.304012</v>
       </c>
       <c r="N252" s="6" t="n">
         <v>101.727241</v>
@@ -20554,7 +20554,7 @@
         <v>102.496698</v>
       </c>
       <c r="M253" s="9" t="n">
-        <v>98.244742</v>
+        <v>98.242548</v>
       </c>
       <c r="N253" s="9" t="n">
         <v>101.795031</v>
@@ -20636,7 +20636,7 @@
         <v>102.607274</v>
       </c>
       <c r="M254" s="6" t="n">
-        <v>98.145195</v>
+        <v>98.14287400000001</v>
       </c>
       <c r="N254" s="6" t="n">
         <v>101.813423</v>
@@ -20718,7 +20718,7 @@
         <v>102.669066</v>
       </c>
       <c r="M255" s="9" t="n">
-        <v>98.03734799999999</v>
+        <v>98.03489</v>
       </c>
       <c r="N255" s="9" t="n">
         <v>101.780165</v>
@@ -20800,7 +20800,7 @@
         <v>102.672369</v>
       </c>
       <c r="M256" s="6" t="n">
-        <v>98.04486900000001</v>
+        <v>98.04242000000001</v>
       </c>
       <c r="N256" s="6" t="n">
         <v>101.691687</v>
@@ -20882,7 +20882,7 @@
         <v>102.617983</v>
       </c>
       <c r="M257" s="9" t="n">
-        <v>98.186449</v>
+        <v>98.18418</v>
       </c>
       <c r="N257" s="9" t="n">
         <v>101.550311</v>
@@ -20964,7 +20964,7 @@
         <v>102.513589</v>
       </c>
       <c r="M258" s="6" t="n">
-        <v>98.41149900000001</v>
+        <v>98.40951699999999</v>
       </c>
       <c r="N258" s="6" t="n">
         <v>101.362216</v>
@@ -21046,7 +21046,7 @@
         <v>102.363902</v>
       </c>
       <c r="M259" s="9" t="n">
-        <v>98.629608</v>
+        <v>98.627904</v>
       </c>
       <c r="N259" s="9" t="n">
         <v>101.155111</v>
@@ -21128,7 +21128,7 @@
         <v>102.174057</v>
       </c>
       <c r="M260" s="6" t="n">
-        <v>98.760966</v>
+        <v>98.759429</v>
       </c>
       <c r="N260" s="6" t="n">
         <v>100.941924</v>
@@ -21210,7 +21210,7 @@
         <v>101.954128</v>
       </c>
       <c r="M261" s="9" t="n">
-        <v>98.84054</v>
+        <v>98.83910400000001</v>
       </c>
       <c r="N261" s="9" t="n">
         <v>100.713381</v>
@@ -21292,7 +21292,7 @@
         <v>101.70767</v>
       </c>
       <c r="M262" s="6" t="n">
-        <v>98.89628399999999</v>
+        <v>98.894919</v>
       </c>
       <c r="N262" s="6" t="n">
         <v>100.471632</v>
@@ -21374,7 +21374,7 @@
         <v>101.444033</v>
       </c>
       <c r="M263" s="9" t="n">
-        <v>98.909319</v>
+        <v>98.907971</v>
       </c>
       <c r="N263" s="9" t="n">
         <v>100.240478</v>
@@ -21456,7 +21456,7 @@
         <v>101.173492</v>
       </c>
       <c r="M264" s="6" t="n">
-        <v>98.925146</v>
+        <v>98.923818</v>
       </c>
       <c r="N264" s="6" t="n">
         <v>100.034526</v>
@@ -21538,7 +21538,7 @@
         <v>100.906596</v>
       </c>
       <c r="M265" s="9" t="n">
-        <v>98.98018399999999</v>
+        <v>98.978926</v>
       </c>
       <c r="N265" s="9" t="n">
         <v>99.86706700000001</v>
@@ -21620,7 +21620,7 @@
         <v>100.656017</v>
       </c>
       <c r="M266" s="6" t="n">
-        <v>99.117932</v>
+        <v>99.11685</v>
       </c>
       <c r="N266" s="6" t="n">
         <v>99.733389</v>
@@ -21702,7 +21702,7 @@
         <v>100.436181</v>
       </c>
       <c r="M267" s="9" t="n">
-        <v>99.318129</v>
+        <v>99.317302</v>
       </c>
       <c r="N267" s="9" t="n">
         <v>99.626424</v>
@@ -21784,7 +21784,7 @@
         <v>100.252847</v>
       </c>
       <c r="M268" s="6" t="n">
-        <v>99.514905</v>
+        <v>99.51432699999999</v>
       </c>
       <c r="N268" s="6" t="n">
         <v>99.548011</v>
@@ -21866,7 +21866,7 @@
         <v>100.10565</v>
       </c>
       <c r="M269" s="9" t="n">
-        <v>99.68657399999999</v>
+        <v>99.686216</v>
       </c>
       <c r="N269" s="9" t="n">
         <v>99.507159</v>
@@ -21948,7 +21948,7 @@
         <v>99.988736</v>
       </c>
       <c r="M270" s="6" t="n">
-        <v>99.78200699999999</v>
+        <v>99.78176999999999</v>
       </c>
       <c r="N270" s="6" t="n">
         <v>99.50595800000001</v>
@@ -22030,7 +22030,7 @@
         <v>99.903561</v>
       </c>
       <c r="M271" s="9" t="n">
-        <v>99.798723</v>
+        <v>99.798507</v>
       </c>
       <c r="N271" s="9" t="n">
         <v>99.547132</v>
@@ -22112,7 +22112,7 @@
         <v>99.848242</v>
       </c>
       <c r="M272" s="6" t="n">
-        <v>99.78326300000001</v>
+        <v>99.783028</v>
       </c>
       <c r="N272" s="6" t="n">
         <v>99.599718</v>
@@ -22194,7 +22194,7 @@
         <v>99.818977</v>
       </c>
       <c r="M273" s="9" t="n">
-        <v>99.737747</v>
+        <v>99.737453</v>
       </c>
       <c r="N273" s="9" t="n">
         <v>99.632903</v>
@@ -22276,7 +22276,7 @@
         <v>99.80368799999999</v>
       </c>
       <c r="M274" s="6" t="n">
-        <v>99.674541</v>
+        <v>99.674167</v>
       </c>
       <c r="N274" s="6" t="n">
         <v>99.640725</v>
@@ -22358,7 +22358,7 @@
         <v>99.788872</v>
       </c>
       <c r="M275" s="9" t="n">
-        <v>99.606342</v>
+        <v>99.605881</v>
       </c>
       <c r="N275" s="9" t="n">
         <v>99.617377</v>
@@ -22440,7 +22440,7 @@
         <v>99.76721499999999</v>
       </c>
       <c r="M276" s="6" t="n">
-        <v>99.55954199999999</v>
+        <v>99.559022</v>
       </c>
       <c r="N276" s="6" t="n">
         <v>99.568095</v>
@@ -22522,7 +22522,7 @@
         <v>99.73115300000001</v>
       </c>
       <c r="M277" s="9" t="n">
-        <v>99.489768</v>
+        <v>99.489159</v>
       </c>
       <c r="N277" s="9" t="n">
         <v>99.4956</v>
@@ -22604,7 +22604,7 @@
         <v>99.681287</v>
       </c>
       <c r="M278" s="6" t="n">
-        <v>99.39833299999999</v>
+        <v>99.39760699999999</v>
       </c>
       <c r="N278" s="6" t="n">
         <v>99.405604</v>
@@ -22686,7 +22686,7 @@
         <v>99.614457</v>
       </c>
       <c r="M279" s="9" t="n">
-        <v>99.28212600000001</v>
+        <v>99.28125300000001</v>
       </c>
       <c r="N279" s="9" t="n">
         <v>99.304765</v>
@@ -22768,7 +22768,7 @@
         <v>99.534943</v>
       </c>
       <c r="M280" s="6" t="n">
-        <v>99.192285</v>
+        <v>99.191298</v>
       </c>
       <c r="N280" s="6" t="n">
         <v>99.2075</v>
@@ -22850,7 +22850,7 @@
         <v>99.44505100000001</v>
       </c>
       <c r="M281" s="9" t="n">
-        <v>99.15255500000001</v>
+        <v>99.151517</v>
       </c>
       <c r="N281" s="9" t="n">
         <v>99.119569</v>
@@ -22932,7 +22932,7 @@
         <v>99.343169</v>
       </c>
       <c r="M282" s="6" t="n">
-        <v>99.21113099999999</v>
+        <v>99.210168</v>
       </c>
       <c r="N282" s="6" t="n">
         <v>99.041619</v>
@@ -23014,7 +23014,7 @@
         <v>99.227654</v>
       </c>
       <c r="M283" s="9" t="n">
-        <v>99.366085</v>
+        <v>99.365319</v>
       </c>
       <c r="N283" s="9" t="n">
         <v>98.96995800000001</v>
@@ -23096,7 +23096,7 @@
         <v>99.098427</v>
       </c>
       <c r="M284" s="6" t="n">
-        <v>99.617942</v>
+        <v>99.617497</v>
       </c>
       <c r="N284" s="6" t="n">
         <v>98.90468</v>
@@ -23178,7 +23178,7 @@
         <v>98.957534</v>
       </c>
       <c r="M285" s="9" t="n">
-        <v>99.94105399999999</v>
+        <v>99.94101999999999</v>
       </c>
       <c r="N285" s="9" t="n">
         <v>98.83648700000001</v>
@@ -23260,7 +23260,7 @@
         <v>98.813729</v>
       </c>
       <c r="M286" s="6" t="n">
-        <v>100.316748</v>
+        <v>100.317192</v>
       </c>
       <c r="N286" s="6" t="n">
         <v>98.76652199999999</v>
@@ -23342,7 +23342,7 @@
         <v>98.68025299999999</v>
       </c>
       <c r="M287" s="9" t="n">
-        <v>100.734119</v>
+        <v>100.735094</v>
       </c>
       <c r="N287" s="9" t="n">
         <v>98.709718</v>
@@ -23424,7 +23424,7 @@
         <v>98.567509</v>
       </c>
       <c r="M288" s="6" t="n">
-        <v>101.12405</v>
+        <v>101.125522</v>
       </c>
       <c r="N288" s="6" t="n">
         <v>98.67411800000001</v>
@@ -23506,7 +23506,7 @@
         <v>98.486598</v>
       </c>
       <c r="M289" s="9" t="n">
-        <v>101.451229</v>
+        <v>101.453117</v>
       </c>
       <c r="N289" s="9" t="n">
         <v>98.66251800000001</v>
@@ -23588,7 +23588,7 @@
         <v>98.44338999999999</v>
       </c>
       <c r="M290" s="6" t="n">
-        <v>101.681369</v>
+        <v>101.683551</v>
       </c>
       <c r="N290" s="6" t="n">
         <v>98.685772</v>
@@ -23670,7 +23670,7 @@
         <v>98.431883</v>
       </c>
       <c r="M291" s="9" t="n">
-        <v>101.821471</v>
+        <v>101.82383</v>
       </c>
       <c r="N291" s="9" t="n">
         <v>98.74519100000001</v>
@@ -23752,7 +23752,7 @@
         <v>98.44416200000001</v>
       </c>
       <c r="M292" s="6" t="n">
-        <v>101.89435</v>
+        <v>101.896802</v>
       </c>
       <c r="N292" s="6" t="n">
         <v>98.83146000000001</v>
@@ -23834,7 +23834,7 @@
         <v>98.472281</v>
       </c>
       <c r="M293" s="9" t="n">
-        <v>101.923056</v>
+        <v>101.925545</v>
       </c>
       <c r="N293" s="9" t="n">
         <v>98.934561</v>
@@ -23916,7 +23916,7 @@
         <v>98.510863</v>
       </c>
       <c r="M294" s="6" t="n">
-        <v>101.956305</v>
+        <v>101.958836</v>
       </c>
       <c r="N294" s="6" t="n">
         <v>99.04898300000001</v>
@@ -24000,7 +24000,7 @@
         <v>98.558933</v>
       </c>
       <c r="M295" s="9" t="n">
-        <v>102.002517</v>
+        <v>102.005107</v>
       </c>
       <c r="N295" s="9" t="n">
         <v>99.17849699999999</v>
@@ -24084,7 +24084,7 @@
         <v>98.614593</v>
       </c>
       <c r="M296" s="6" t="n">
-        <v>102.03522</v>
+        <v>102.037852</v>
       </c>
       <c r="N296" s="6" t="n">
         <v>99.30637400000001</v>
@@ -24168,7 +24168,7 @@
         <v>98.669754</v>
       </c>
       <c r="M297" s="9" t="n">
-        <v>102.031589</v>
+        <v>102.034217</v>
       </c>
       <c r="N297" s="9" t="n">
         <v>99.42188299999999</v>
@@ -24252,7 +24252,7 @@
         <v>98.72021100000001</v>
       </c>
       <c r="M298" s="6" t="n">
-        <v>102.00133</v>
+        <v>102.003919</v>
       </c>
       <c r="N298" s="6" t="n">
         <v>99.517658</v>
@@ -24336,7 +24336,7 @@
         <v>98.76418099999999</v>
       </c>
       <c r="M299" s="9" t="n">
-        <v>101.958693</v>
+        <v>101.961228</v>
       </c>
       <c r="N299" s="9" t="n">
         <v>99.581422</v>
@@ -24420,7 +24420,7 @@
         <v>98.803584</v>
       </c>
       <c r="M300" s="6" t="n">
-        <v>101.882685</v>
+        <v>101.885123</v>
       </c>
       <c r="N300" s="6" t="n">
         <v>99.62473799999999</v>
@@ -24504,7 +24504,7 @@
         <v>98.840957</v>
       </c>
       <c r="M301" s="9" t="n">
-        <v>101.775364</v>
+        <v>101.777666</v>
       </c>
       <c r="N301" s="9" t="n">
         <v>99.657937</v>
@@ -24588,7 +24588,7 @@
         <v>98.877566</v>
       </c>
       <c r="M302" s="6" t="n">
-        <v>101.607396</v>
+        <v>101.609484</v>
       </c>
       <c r="N302" s="6" t="n">
         <v>99.69403200000001</v>
@@ -24672,7 +24672,7 @@
         <v>98.916799</v>
       </c>
       <c r="M303" s="9" t="n">
-        <v>101.426346</v>
+        <v>101.428204</v>
       </c>
       <c r="N303" s="9" t="n">
         <v>99.744525</v>
@@ -24756,7 +24756,7 @@
         <v>98.962076</v>
       </c>
       <c r="M304" s="6" t="n">
-        <v>101.27164</v>
+        <v>101.273301</v>
       </c>
       <c r="N304" s="6" t="n">
         <v>99.794731</v>
@@ -24840,7 +24840,7 @@
         <v>99.007672</v>
       </c>
       <c r="M305" s="9" t="n">
-        <v>101.117912</v>
+        <v>101.119377</v>
       </c>
       <c r="N305" s="9" t="n">
         <v>99.82226900000001</v>
@@ -24924,7 +24924,7 @@
         <v>99.049937</v>
       </c>
       <c r="M306" s="6" t="n">
-        <v>100.974746</v>
+        <v>100.976029</v>
       </c>
       <c r="N306" s="6" t="n">
         <v>99.830072</v>
@@ -25008,7 +25008,7 @@
         <v>99.08619299999999</v>
       </c>
       <c r="M307" s="9" t="n">
-        <v>100.844419</v>
+        <v>100.845536</v>
       </c>
       <c r="N307" s="9" t="n">
         <v>99.818237</v>
@@ -25092,7 +25092,7 @@
         <v>99.11828</v>
       </c>
       <c r="M308" s="6" t="n">
-        <v>100.722039</v>
+        <v>100.723</v>
       </c>
       <c r="N308" s="6" t="n">
         <v>99.797618</v>
@@ -25176,7 +25176,7 @@
         <v>99.152708</v>
       </c>
       <c r="M309" s="9" t="n">
-        <v>100.610002</v>
+        <v>100.610822</v>
       </c>
       <c r="N309" s="9" t="n">
         <v>99.78245099999999</v>
@@ -25260,7 +25260,7 @@
         <v>99.193686</v>
       </c>
       <c r="M310" s="6" t="n">
-        <v>100.48242</v>
+        <v>100.483077</v>
       </c>
       <c r="N310" s="6" t="n">
         <v>99.778835</v>
@@ -25344,7 +25344,7 @@
         <v>99.240945</v>
       </c>
       <c r="M311" s="9" t="n">
-        <v>100.3213</v>
+        <v>100.321752</v>
       </c>
       <c r="N311" s="9" t="n">
         <v>99.800089</v>
@@ -25428,7 +25428,7 @@
         <v>99.295922</v>
       </c>
       <c r="M312" s="6" t="n">
-        <v>100.120372</v>
+        <v>100.120569</v>
       </c>
       <c r="N312" s="6" t="n">
         <v>99.84898699999999</v>
@@ -25512,7 +25512,7 @@
         <v>99.36141000000001</v>
       </c>
       <c r="M313" s="9" t="n">
-        <v>99.856689</v>
+        <v>99.856549</v>
       </c>
       <c r="N313" s="9" t="n">
         <v>99.931945</v>
@@ -25596,7 +25596,7 @@
         <v>99.433543</v>
       </c>
       <c r="M314" s="6" t="n">
-        <v>99.58330599999999</v>
+        <v>99.582819</v>
       </c>
       <c r="N314" s="6" t="n">
         <v>100.052675</v>
@@ -25680,7 +25680,7 @@
         <v>99.509973</v>
       </c>
       <c r="M315" s="9" t="n">
-        <v>99.353859</v>
+        <v>99.35308000000001</v>
       </c>
       <c r="N315" s="9" t="n">
         <v>100.205912</v>
@@ -25764,7 +25764,7 @@
         <v>99.590737</v>
       </c>
       <c r="M316" s="6" t="n">
-        <v>99.18049000000001</v>
+        <v>99.179491</v>
       </c>
       <c r="N316" s="6" t="n">
         <v>100.363537</v>
@@ -25848,7 +25848,7 @@
         <v>99.67907099999999</v>
       </c>
       <c r="M317" s="9" t="n">
-        <v>99.09212100000001</v>
+        <v>99.09101</v>
       </c>
       <c r="N317" s="9" t="n">
         <v>100.498237</v>
@@ -25932,7 +25932,7 @@
         <v>99.778291</v>
       </c>
       <c r="M318" s="6" t="n">
-        <v>99.06849</v>
+        <v>99.06735</v>
       </c>
       <c r="N318" s="6" t="n">
         <v>100.595855</v>
@@ -26016,7 +26016,7 @@
         <v>99.887074</v>
       </c>
       <c r="M319" s="9" t="n">
-        <v>99.07923599999999</v>
+        <v>99.07811100000001</v>
       </c>
       <c r="N319" s="9" t="n">
         <v>100.66973</v>
@@ -26100,7 +26100,7 @@
         <v>100.002989</v>
       </c>
       <c r="M320" s="6" t="n">
-        <v>99.098054</v>
+        <v>99.096953</v>
       </c>
       <c r="N320" s="6" t="n">
         <v>100.726671</v>
@@ -26184,7 +26184,7 @@
         <v>100.121683</v>
       </c>
       <c r="M321" s="9" t="n">
-        <v>99.13117</v>
+        <v>99.130112</v>
       </c>
       <c r="N321" s="9" t="n">
         <v>100.767885</v>
@@ -26268,7 +26268,7 @@
         <v>100.239641</v>
       </c>
       <c r="M322" s="6" t="n">
-        <v>99.191446</v>
+        <v>99.19046400000001</v>
       </c>
       <c r="N322" s="6" t="n">
         <v>100.790309</v>
@@ -26352,7 +26352,7 @@
         <v>100.353548</v>
       </c>
       <c r="M323" s="9" t="n">
-        <v>99.285488</v>
+        <v>99.284623</v>
       </c>
       <c r="N323" s="9" t="n">
         <v>100.79069</v>
@@ -26436,7 +26436,7 @@
         <v>100.460196</v>
       </c>
       <c r="M324" s="6" t="n">
-        <v>99.368477</v>
+        <v>99.36771400000001</v>
       </c>
       <c r="N324" s="6" t="n">
         <v>100.777144</v>
@@ -26520,7 +26520,7 @@
         <v>100.558583</v>
       </c>
       <c r="M325" s="9" t="n">
-        <v>99.429582</v>
+        <v>99.428893</v>
       </c>
       <c r="N325" s="9" t="n">
         <v>100.756076</v>
@@ -26604,7 +26604,7 @@
         <v>100.65144</v>
       </c>
       <c r="M326" s="6" t="n">
-        <v>99.495312</v>
+        <v>99.494704</v>
       </c>
       <c r="N326" s="6" t="n">
         <v>100.726864</v>
@@ -26688,7 +26688,7 @@
         <v>100.742419</v>
       </c>
       <c r="M327" s="9" t="n">
-        <v>99.562656</v>
+        <v>99.562135</v>
       </c>
       <c r="N327" s="9" t="n">
         <v>100.688176</v>
@@ -26772,7 +26772,7 @@
         <v>100.835291</v>
       </c>
       <c r="M328" s="6" t="n">
-        <v>99.625191</v>
+        <v>99.624752</v>
       </c>
       <c r="N328" s="6" t="n">
         <v>100.651309</v>
@@ -26856,7 +26856,7 @@
         <v>100.93231</v>
       </c>
       <c r="M329" s="9" t="n">
-        <v>99.660704</v>
+        <v>99.660315</v>
       </c>
       <c r="N329" s="9" t="n">
         <v>100.63399</v>
@@ -26940,7 +26940,7 @@
         <v>101.035795</v>
       </c>
       <c r="M330" s="6" t="n">
-        <v>99.668324</v>
+        <v>99.66794899999999</v>
       </c>
       <c r="N330" s="6" t="n">
         <v>100.640534</v>
@@ -27024,7 +27024,7 @@
         <v>101.140373</v>
       </c>
       <c r="M331" s="9" t="n">
-        <v>99.63651900000001</v>
+        <v>99.636107</v>
       </c>
       <c r="N331" s="9" t="n">
         <v>100.675856</v>
@@ -27108,7 +27108,7 @@
         <v>101.240767</v>
       </c>
       <c r="M332" s="6" t="n">
-        <v>99.549475</v>
+        <v>99.548956</v>
       </c>
       <c r="N332" s="6" t="n">
         <v>100.735903</v>
@@ -27192,7 +27192,7 @@
         <v>101.334378</v>
       </c>
       <c r="M333" s="9" t="n">
-        <v>99.397222</v>
+        <v>99.39650899999999</v>
       </c>
       <c r="N333" s="9" t="n">
         <v>100.813787</v>
@@ -27276,7 +27276,7 @@
         <v>101.420657</v>
       </c>
       <c r="M334" s="6" t="n">
-        <v>99.217837</v>
+        <v>99.216894</v>
       </c>
       <c r="N334" s="6" t="n">
         <v>100.894728</v>
@@ -27360,7 +27360,7 @@
         <v>101.502584</v>
       </c>
       <c r="M335" s="9" t="n">
-        <v>99.046323</v>
+        <v>99.045158</v>
       </c>
       <c r="N335" s="9" t="n">
         <v>100.963076</v>
@@ -27444,7 +27444,7 @@
         <v>101.585381</v>
       </c>
       <c r="M336" s="6" t="n">
-        <v>98.91372800000001</v>
+        <v>98.912389</v>
       </c>
       <c r="N336" s="6" t="n">
         <v>101.01511</v>
@@ -27528,7 +27528,7 @@
         <v>101.668291</v>
       </c>
       <c r="M337" s="9" t="n">
-        <v>98.85507800000001</v>
+        <v>98.85366</v>
       </c>
       <c r="N337" s="9" t="n">
         <v>101.068919</v>
@@ -27612,7 +27612,7 @@
         <v>101.750979</v>
       </c>
       <c r="M338" s="6" t="n">
-        <v>98.849913</v>
+        <v>98.848484</v>
       </c>
       <c r="N338" s="6" t="n">
         <v>101.126517</v>
@@ -27696,7 +27696,7 @@
         <v>101.831928</v>
       </c>
       <c r="M339" s="9" t="n">
-        <v>98.850313</v>
+        <v>98.848885</v>
       </c>
       <c r="N339" s="9" t="n">
         <v>101.190783</v>
@@ -27780,7 +27780,7 @@
         <v>101.906327</v>
       </c>
       <c r="M340" s="6" t="n">
-        <v>98.83051399999999</v>
+        <v>98.829064</v>
       </c>
       <c r="N340" s="6" t="n">
         <v>101.275297</v>
@@ -27864,7 +27864,7 @@
         <v>101.966859</v>
       </c>
       <c r="M341" s="9" t="n">
-        <v>98.789145</v>
+        <v>98.787646</v>
       </c>
       <c r="N341" s="9" t="n">
         <v>101.387716</v>
@@ -27948,7 +27948,7 @@
         <v>102.013731</v>
       </c>
       <c r="M342" s="6" t="n">
-        <v>98.704089</v>
+        <v>98.702485</v>
       </c>
       <c r="N342" s="6" t="n">
         <v>101.523463</v>
@@ -28032,7 +28032,7 @@
         <v>102.04583</v>
       </c>
       <c r="M343" s="9" t="n">
-        <v>98.56507000000001</v>
+        <v>98.563294</v>
       </c>
       <c r="N343" s="9" t="n">
         <v>101.663543</v>
@@ -28116,7 +28116,7 @@
         <v>102.061759</v>
       </c>
       <c r="M344" s="6" t="n">
-        <v>98.401582</v>
+        <v>98.399601</v>
       </c>
       <c r="N344" s="6" t="n">
         <v>101.795039</v>
@@ -28200,7 +28200,7 @@
         <v>102.057377</v>
       </c>
       <c r="M345" s="9" t="n">
-        <v>98.25706599999999</v>
+        <v>98.254901</v>
       </c>
       <c r="N345" s="9" t="n">
         <v>101.904424</v>
@@ -28284,7 +28284,7 @@
         <v>102.026541</v>
       </c>
       <c r="M346" s="6" t="n">
-        <v>98.17639</v>
+        <v>98.174121</v>
       </c>
       <c r="N346" s="6" t="n">
         <v>101.966805</v>
@@ -28368,7 +28368,7 @@
         <v>101.959127</v>
       </c>
       <c r="M347" s="9" t="n">
-        <v>98.19614</v>
+        <v>98.19389200000001</v>
       </c>
       <c r="N347" s="9" t="n">
         <v>101.957807</v>
@@ -28452,7 +28452,7 @@
         <v>101.843392</v>
       </c>
       <c r="M348" s="6" t="n">
-        <v>98.325563</v>
+        <v>98.32347300000001</v>
       </c>
       <c r="N348" s="6" t="n">
         <v>101.836125</v>
@@ -28536,7 +28536,7 @@
         <v>101.671949</v>
       </c>
       <c r="M349" s="9" t="n">
-        <v>98.53974700000001</v>
+        <v>98.537925</v>
       </c>
       <c r="N349" s="9" t="n">
         <v>101.542324</v>
@@ -28620,7 +28620,7 @@
         <v>101.440902</v>
       </c>
       <c r="M350" s="6" t="n">
-        <v>98.837464</v>
+        <v>98.836018</v>
       </c>
       <c r="N350" s="6" t="n">
         <v>101.051415</v>
@@ -28704,7 +28704,7 @@
         <v>101.148242</v>
       </c>
       <c r="M351" s="9" t="n">
-        <v>99.230667</v>
+        <v>99.229721</v>
       </c>
       <c r="N351" s="9" t="n">
         <v>100.379316</v>
@@ -28788,7 +28788,7 @@
         <v>100.798077</v>
       </c>
       <c r="M352" s="6" t="n">
-        <v>99.690941</v>
+        <v>99.69058200000001</v>
       </c>
       <c r="N352" s="6" t="n">
         <v>99.567076</v>
@@ -28872,7 +28872,7 @@
         <v>100.404325</v>
       </c>
       <c r="M353" s="9" t="n">
-        <v>100.153367</v>
+        <v>100.1536</v>
       </c>
       <c r="N353" s="9" t="n">
         <v>98.699679</v>
@@ -28956,7 +28956,7 @@
         <v>99.98398400000001</v>
       </c>
       <c r="M354" s="6" t="n">
-        <v>100.585507</v>
+        <v>100.586294</v>
       </c>
       <c r="N354" s="6" t="n">
         <v>97.914196</v>
@@ -29040,7 +29040,7 @@
         <v>99.566142</v>
       </c>
       <c r="M355" s="9" t="n">
-        <v>100.987692</v>
+        <v>100.988994</v>
       </c>
       <c r="N355" s="9" t="n">
         <v>97.286761</v>
@@ -29124,7 +29124,7 @@
         <v>99.176928</v>
       </c>
       <c r="M356" s="6" t="n">
-        <v>101.349711</v>
+        <v>101.351476</v>
       </c>
       <c r="N356" s="6" t="n">
         <v>96.848017</v>
@@ -29208,7 +29208,7 @@
         <v>98.83229799999999</v>
       </c>
       <c r="M357" s="9" t="n">
-        <v>101.654181</v>
+        <v>101.656333</v>
       </c>
       <c r="N357" s="9" t="n">
         <v>96.61138200000001</v>
@@ -29292,7 +29292,7 @@
         <v>98.542553</v>
       </c>
       <c r="M358" s="6" t="n">
-        <v>101.861645</v>
+        <v>101.864059</v>
       </c>
       <c r="N358" s="6" t="n">
         <v>96.574217</v>
@@ -29376,7 +29376,7 @@
         <v>98.316666</v>
       </c>
       <c r="M359" s="9" t="n">
-        <v>101.96381</v>
+        <v>101.96635</v>
       </c>
       <c r="N359" s="9" t="n">
         <v>96.71358600000001</v>
@@ -29460,7 +29460,7 @@
         <v>98.15644399999999</v>
       </c>
       <c r="M360" s="6" t="n">
-        <v>102.002672</v>
+        <v>102.005256</v>
       </c>
       <c r="N360" s="6" t="n">
         <v>96.969452</v>
@@ -29544,7 +29544,7 @@
         <v>98.05853</v>
       </c>
       <c r="M361" s="9" t="n">
-        <v>101.972665</v>
+        <v>101.975205</v>
       </c>
       <c r="N361" s="9" t="n">
         <v>97.294439</v>
@@ -29628,7 +29628,7 @@
         <v>98.016605</v>
       </c>
       <c r="M362" s="6" t="n">
-        <v>101.864989</v>
+        <v>101.867389</v>
       </c>
       <c r="N362" s="6" t="n">
         <v>97.64972899999999</v>
@@ -29712,7 +29712,7 @@
         <v>98.02713</v>
       </c>
       <c r="M363" s="9" t="n">
-        <v>101.677523</v>
+        <v>101.679683</v>
       </c>
       <c r="N363" s="9" t="n">
         <v>98.006354</v>
@@ -29796,7 +29796,7 @@
         <v>98.086822</v>
       </c>
       <c r="M364" s="6" t="n">
-        <v>101.46015</v>
+        <v>101.462034</v>
       </c>
       <c r="N364" s="6" t="n">
         <v>98.349371</v>
@@ -29880,7 +29880,7 @@
         <v>98.18404099999999</v>
       </c>
       <c r="M365" s="9" t="n">
-        <v>101.273682</v>
+        <v>101.275331</v>
       </c>
       <c r="N365" s="9" t="n">
         <v>98.64978000000001</v>
@@ -29964,7 +29964,7 @@
         <v>98.30470699999999</v>
       </c>
       <c r="M366" s="6" t="n">
-        <v>101.130752</v>
+        <v>101.132222</v>
       </c>
       <c r="N366" s="6" t="n">
         <v>98.909622</v>
@@ -30048,7 +30048,7 @@
         <v>98.437279</v>
       </c>
       <c r="M367" s="9" t="n">
-        <v>100.997754</v>
+        <v>100.999057</v>
       </c>
       <c r="N367" s="9" t="n">
         <v>99.13820200000001</v>
@@ -30132,7 +30132,7 @@
         <v>98.570815</v>
       </c>
       <c r="M368" s="6" t="n">
-        <v>100.891988</v>
+        <v>100.893157</v>
       </c>
       <c r="N368" s="6" t="n">
         <v>99.329008</v>
@@ -30216,7 +30216,7 @@
         <v>98.69640099999999</v>
       </c>
       <c r="M369" s="9" t="n">
-        <v>100.806185</v>
+        <v>100.807244</v>
       </c>
       <c r="N369" s="9" t="n">
         <v>99.46657399999999</v>
@@ -30300,7 +30300,7 @@
         <v>98.80901900000001</v>
       </c>
       <c r="M370" s="6" t="n">
-        <v>100.720796</v>
+        <v>100.721744</v>
       </c>
       <c r="N370" s="6" t="n">
         <v>99.549446</v>
@@ -30384,7 +30384,7 @@
         <v>98.90648899999999</v>
       </c>
       <c r="M371" s="9" t="n">
-        <v>100.637042</v>
+        <v>100.63788</v>
       </c>
       <c r="N371" s="9" t="n">
         <v>99.59773800000001</v>
@@ -30468,7 +30468,7 @@
         <v>98.991794</v>
       </c>
       <c r="M372" s="6" t="n">
-        <v>100.546853</v>
+        <v>100.547571</v>
       </c>
       <c r="N372" s="6" t="n">
         <v>99.649765</v>
@@ -30552,7 +30552,7 @@
         <v>99.06857100000001</v>
       </c>
       <c r="M373" s="9" t="n">
-        <v>100.477041</v>
+        <v>100.477664</v>
       </c>
       <c r="N373" s="9" t="n">
         <v>99.724464</v>
@@ -30636,7 +30636,7 @@
         <v>99.13948000000001</v>
       </c>
       <c r="M374" s="6" t="n">
-        <v>100.461442</v>
+        <v>100.462042</v>
       </c>
       <c r="N374" s="6" t="n">
         <v>99.822796</v>
@@ -30720,7 +30720,7 @@
         <v>99.207588</v>
       </c>
       <c r="M375" s="9" t="n">
-        <v>100.457102</v>
+        <v>100.457695</v>
       </c>
       <c r="N375" s="9" t="n">
         <v>99.947025</v>
@@ -30804,7 +30804,7 @@
         <v>99.272052</v>
       </c>
       <c r="M376" s="6" t="n">
-        <v>100.427488</v>
+        <v>100.428043</v>
       </c>
       <c r="N376" s="6" t="n">
         <v>100.082285</v>
@@ -30888,7 +30888,7 @@
         <v>99.33131299999999</v>
       </c>
       <c r="M377" s="9" t="n">
-        <v>100.351876</v>
+        <v>100.352335</v>
       </c>
       <c r="N377" s="9" t="n">
         <v>100.218999</v>
@@ -30972,7 +30972,7 @@
         <v>99.38401</v>
       </c>
       <c r="M378" s="6" t="n">
-        <v>100.214787</v>
+        <v>100.215073</v>
       </c>
       <c r="N378" s="6" t="n">
         <v>100.346661</v>
@@ -31056,7 +31056,7 @@
         <v>99.429638</v>
       </c>
       <c r="M379" s="9" t="n">
-        <v>100.069248</v>
+        <v>100.069349</v>
       </c>
       <c r="N379" s="9" t="n">
         <v>100.458514</v>
@@ -31140,7 +31140,7 @@
         <v>99.467873</v>
       </c>
       <c r="M380" s="6" t="n">
-        <v>99.95326799999999</v>
+        <v>99.953221</v>
       </c>
       <c r="N380" s="6" t="n">
         <v>100.55405</v>
@@ -31224,7 +31224,7 @@
         <v>99.497173</v>
       </c>
       <c r="M381" s="9" t="n">
-        <v>99.893018</v>
+        <v>99.892893</v>
       </c>
       <c r="N381" s="9" t="n">
         <v>100.63803</v>
@@ -31308,7 +31308,7 @@
         <v>99.516845</v>
       </c>
       <c r="M382" s="6" t="n">
-        <v>99.90525599999999</v>
+        <v>99.905143</v>
       </c>
       <c r="N382" s="6" t="n">
         <v>100.712082</v>
@@ -31392,7 +31392,7 @@
         <v>99.53219300000001</v>
       </c>
       <c r="M383" s="9" t="n">
-        <v>99.92578399999999</v>
+        <v>99.925693</v>
       </c>
       <c r="N383" s="9" t="n">
         <v>100.75947</v>
@@ -31476,7 +31476,7 @@
         <v>99.548546</v>
       </c>
       <c r="M384" s="6" t="n">
-        <v>99.916354</v>
+        <v>99.916246</v>
       </c>
       <c r="N384" s="6" t="n">
         <v>100.769444</v>
@@ -31560,7 +31560,7 @@
         <v>99.569684</v>
       </c>
       <c r="M385" s="9" t="n">
-        <v>99.87211600000001</v>
+        <v>99.871948</v>
       </c>
       <c r="N385" s="9" t="n">
         <v>100.753206</v>
@@ -31644,7 +31644,7 @@
         <v>99.598899</v>
       </c>
       <c r="M386" s="6" t="n">
-        <v>99.81053199999999</v>
+        <v>99.810282</v>
       </c>
       <c r="N386" s="6" t="n">
         <v>100.730717</v>
@@ -31728,7 +31728,7 @@
         <v>99.637028</v>
       </c>
       <c r="M387" s="9" t="n">
-        <v>99.751735</v>
+        <v>99.751407</v>
       </c>
       <c r="N387" s="9" t="n">
         <v>100.706738</v>
@@ -31812,7 +31812,7 @@
         <v>99.68438399999999</v>
       </c>
       <c r="M388" s="6" t="n">
-        <v>99.71040600000001</v>
+        <v>99.710025</v>
       </c>
       <c r="N388" s="6" t="n">
         <v>100.695379</v>
@@ -31896,7 +31896,7 @@
         <v>99.741213</v>
       </c>
       <c r="M389" s="9" t="n">
-        <v>99.69152200000001</v>
+        <v>99.69111599999999</v>
       </c>
       <c r="N389" s="9" t="n">
         <v>100.695622</v>
@@ -31980,7 +31980,7 @@
         <v>99.804768</v>
       </c>
       <c r="M390" s="6" t="n">
-        <v>99.71194199999999</v>
+        <v>99.711561</v>
       </c>
       <c r="N390" s="6" t="n">
         <v>100.697007</v>
@@ -32064,7 +32064,7 @@
         <v>99.869647</v>
       </c>
       <c r="M391" s="9" t="n">
-        <v>99.754248</v>
+        <v>99.75391999999999</v>
       </c>
       <c r="N391" s="9" t="n">
         <v>100.68705</v>
@@ -32148,7 +32148,7 @@
         <v>99.93102399999999</v>
       </c>
       <c r="M392" s="6" t="n">
-        <v>99.765761</v>
+        <v>99.765445</v>
       </c>
       <c r="N392" s="6" t="n">
         <v>100.654299</v>
@@ -32232,7 +32232,7 @@
         <v>99.98686499999999</v>
       </c>
       <c r="M393" s="9" t="n">
-        <v>99.749911</v>
+        <v>99.749572</v>
       </c>
       <c r="N393" s="9" t="n">
         <v>100.605926</v>
@@ -32316,7 +32316,7 @@
         <v>100.041392</v>
       </c>
       <c r="M394" s="6" t="n">
-        <v>99.72132999999999</v>
+        <v>99.720951</v>
       </c>
       <c r="N394" s="6" t="n">
         <v>100.537653</v>
@@ -32400,7 +32400,7 @@
         <v>100.096676</v>
       </c>
       <c r="M395" s="9" t="n">
-        <v>99.68391699999999</v>
+        <v>99.683486</v>
       </c>
       <c r="N395" s="9" t="n">
         <v>100.464907</v>
@@ -32484,7 +32484,7 @@
         <v>100.149433</v>
       </c>
       <c r="M396" s="6" t="n">
-        <v>99.673507</v>
+        <v>99.67305899999999</v>
       </c>
       <c r="N396" s="6" t="n">
         <v>100.415927</v>
@@ -32568,7 +32568,7 @@
         <v>100.197275</v>
       </c>
       <c r="M397" s="9" t="n">
-        <v>99.70941500000001</v>
+        <v>99.70900899999999</v>
       </c>
       <c r="N397" s="9" t="n">
         <v>100.397993</v>
@@ -32652,7 +32652,7 @@
         <v>100.238762</v>
       </c>
       <c r="M398" s="6" t="n">
-        <v>99.784696</v>
+        <v>99.784384</v>
       </c>
       <c r="N398" s="6" t="n">
         <v>100.414017</v>
@@ -32736,7 +32736,7 @@
         <v>100.271627</v>
       </c>
       <c r="M399" s="9" t="n">
-        <v>99.908417</v>
+        <v>99.908261</v>
       </c>
       <c r="N399" s="9" t="n">
         <v>100.449321</v>
@@ -32820,7 +32820,7 @@
         <v>100.296176</v>
       </c>
       <c r="M400" s="6" t="n">
-        <v>100.052815</v>
+        <v>100.052841</v>
       </c>
       <c r="N400" s="6" t="n">
         <v>100.479223</v>
@@ -32904,7 +32904,7 @@
         <v>100.311617</v>
       </c>
       <c r="M401" s="9" t="n">
-        <v>100.174945</v>
+        <v>100.175126</v>
       </c>
       <c r="N401" s="9" t="n">
         <v>100.501792</v>
@@ -32988,7 +32988,7 @@
         <v>100.315157</v>
       </c>
       <c r="M402" s="6" t="n">
-        <v>100.248327</v>
+        <v>100.248598</v>
       </c>
       <c r="N402" s="6" t="n">
         <v>100.519201</v>
@@ -33072,7 +33072,7 @@
         <v>100.305235</v>
       </c>
       <c r="M403" s="9" t="n">
-        <v>100.261794</v>
+        <v>100.26208</v>
       </c>
       <c r="N403" s="9" t="n">
         <v>100.518529</v>
@@ -33156,7 +33156,7 @@
         <v>100.281868</v>
       </c>
       <c r="M404" s="6" t="n">
-        <v>100.239719</v>
+        <v>100.239974</v>
       </c>
       <c r="N404" s="6" t="n">
         <v>100.49299</v>
@@ -33240,7 +33240,7 @@
         <v>100.246902</v>
       </c>
       <c r="M405" s="9" t="n">
-        <v>100.183052</v>
+        <v>100.183232</v>
       </c>
       <c r="N405" s="9" t="n">
         <v>100.441688</v>
@@ -33324,7 +33324,7 @@
         <v>100.202807</v>
       </c>
       <c r="M406" s="6" t="n">
-        <v>100.08159</v>
+        <v>100.081637</v>
       </c>
       <c r="N406" s="6" t="n">
         <v>100.370978</v>
@@ -33408,7 +33408,7 @@
         <v>100.15165</v>
       </c>
       <c r="M407" s="9" t="n">
-        <v>99.988404</v>
+        <v>99.98832899999999</v>
       </c>
       <c r="N407" s="9" t="n">
         <v>100.294936</v>
@@ -33492,7 +33492,7 @@
         <v>100.096199</v>
       </c>
       <c r="M408" s="6" t="n">
-        <v>99.914632</v>
+        <v>99.91446000000001</v>
       </c>
       <c r="N408" s="6" t="n">
         <v>100.216912</v>
@@ -33576,7 +33576,7 @@
         <v>100.03958</v>
       </c>
       <c r="M409" s="9" t="n">
-        <v>99.88269200000001</v>
+        <v>99.88247800000001</v>
       </c>
       <c r="N409" s="9" t="n">
         <v>100.138756</v>
@@ -33660,7 +33660,7 @@
         <v>99.98282500000001</v>
       </c>
       <c r="M410" s="6" t="n">
-        <v>99.909736</v>
+        <v>99.90955700000001</v>
       </c>
       <c r="N410" s="6" t="n">
         <v>100.072091</v>
@@ -33744,7 +33744,7 @@
         <v>99.927981</v>
       </c>
       <c r="M411" s="9" t="n">
-        <v>99.996787</v>
+        <v>99.996719</v>
       </c>
       <c r="N411" s="9" t="n">
         <v>100.029666</v>
@@ -33828,7 +33828,7 @@
         <v>99.87608899999999</v>
       </c>
       <c r="M412" s="6" t="n">
-        <v>100.163136</v>
+        <v>100.163279</v>
       </c>
       <c r="N412" s="6" t="n">
         <v>100.019786</v>
@@ -33912,7 +33912,7 @@
         <v>99.827979</v>
       </c>
       <c r="M413" s="9" t="n">
-        <v>100.415345</v>
+        <v>100.41581</v>
       </c>
       <c r="N413" s="9" t="n">
         <v>100.052249</v>
@@ -33996,7 +33996,7 @@
         <v>99.787465</v>
       </c>
       <c r="M414" s="6" t="n">
-        <v>100.675654</v>
+        <v>100.676447</v>
       </c>
       <c r="N414" s="6" t="n">
         <v>100.123755</v>
@@ -34080,7 +34080,7 @@
         <v>99.760132</v>
       </c>
       <c r="M415" s="9" t="n">
-        <v>100.883808</v>
+        <v>100.884864</v>
       </c>
       <c r="N415" s="9" t="n">
         <v>100.216677</v>
@@ -34164,7 +34164,7 @@
         <v>99.74702600000001</v>
       </c>
       <c r="M416" s="6" t="n">
-        <v>101.04807</v>
+        <v>101.049333</v>
       </c>
       <c r="N416" s="6" t="n">
         <v>100.310077</v>
@@ -34248,7 +34248,7 @@
         <v>99.74485</v>
       </c>
       <c r="M417" s="9" t="n">
-        <v>101.14891</v>
+        <v>101.150299</v>
       </c>
       <c r="N417" s="9" t="n">
         <v>100.389486</v>
@@ -34332,7 +34332,7 @@
         <v>99.745771</v>
       </c>
       <c r="M418" s="6" t="n">
-        <v>101.178974</v>
+        <v>101.1804</v>
       </c>
       <c r="N418" s="6" t="n">
         <v>100.444756</v>
@@ -34416,7 +34416,7 @@
         <v>99.74466200000001</v>
       </c>
       <c r="M419" s="9" t="n">
-        <v>101.16376</v>
+        <v>101.165166</v>
       </c>
       <c r="N419" s="9" t="n">
         <v>100.471961</v>
@@ -34500,7 +34500,7 @@
         <v>99.741164</v>
       </c>
       <c r="M420" s="6" t="n">
-        <v>101.090719</v>
+        <v>101.092033</v>
       </c>
       <c r="N420" s="6" t="n">
         <v>100.474492</v>
@@ -34584,7 +34584,7 @@
         <v>99.737532</v>
       </c>
       <c r="M421" s="9" t="n">
-        <v>100.930977</v>
+        <v>100.932091</v>
       </c>
       <c r="N421" s="9" t="n">
         <v>100.459157</v>
@@ -34668,7 +34668,7 @@
         <v>99.737679</v>
       </c>
       <c r="M422" s="6" t="n">
-        <v>100.720557</v>
+        <v>100.721407</v>
       </c>
       <c r="N422" s="6" t="n">
         <v>100.418398</v>
@@ -34752,7 +34752,7 @@
         <v>99.74484099999999</v>
       </c>
       <c r="M423" s="9" t="n">
-        <v>100.494712</v>
+        <v>100.49528</v>
       </c>
       <c r="N423" s="9" t="n">
         <v>100.368032</v>
@@ -34836,7 +34836,7 @@
         <v>99.758526</v>
       </c>
       <c r="M424" s="6" t="n">
-        <v>100.274444</v>
+        <v>100.274736</v>
       </c>
       <c r="N424" s="6" t="n">
         <v>100.310085</v>
@@ -34920,7 +34920,7 @@
         <v>99.776844</v>
       </c>
       <c r="M425" s="9" t="n">
-        <v>100.10637</v>
+        <v>100.106451</v>
       </c>
       <c r="N425" s="9" t="n">
         <v>100.232938</v>
@@ -35004,7 +35004,7 @@
         <v>99.79732</v>
       </c>
       <c r="M426" s="6" t="n">
-        <v>100.020909</v>
+        <v>100.020882</v>
       </c>
       <c r="N426" s="6" t="n">
         <v>100.155544</v>
@@ -35088,7 +35088,7 @@
         <v>99.81751</v>
       </c>
       <c r="M427" s="9" t="n">
-        <v>99.993785</v>
+        <v>99.993723</v>
       </c>
       <c r="N427" s="9" t="n">
         <v>100.100401</v>
@@ -35172,7 +35172,7 @@
         <v>99.836539</v>
       </c>
       <c r="M428" s="6" t="n">
-        <v>99.998238</v>
+        <v>99.998182</v>
       </c>
       <c r="N428" s="6" t="n">
         <v>100.077033</v>
@@ -35256,7 +35256,7 @@
         <v>99.853403</v>
       </c>
       <c r="M429" s="9" t="n">
-        <v>100.034975</v>
+        <v>100.034968</v>
       </c>
       <c r="N429" s="9" t="n">
         <v>100.07313</v>
@@ -35340,7 +35340,7 @@
         <v>99.869984</v>
       </c>
       <c r="M430" s="6" t="n">
-        <v>100.089377</v>
+        <v>100.089443</v>
       </c>
       <c r="N430" s="6" t="n">
         <v>100.078951</v>
@@ -35424,7 +35424,7 @@
         <v>99.88754</v>
       </c>
       <c r="M431" s="9" t="n">
-        <v>100.132016</v>
+        <v>100.132142</v>
       </c>
       <c r="N431" s="9" t="n">
         <v>100.079464</v>
@@ -35508,7 +35508,7 @@
         <v>99.90495199999999</v>
       </c>
       <c r="M432" s="6" t="n">
-        <v>100.163409</v>
+        <v>100.163585</v>
       </c>
       <c r="N432" s="6" t="n">
         <v>100.052077</v>
@@ -35592,7 +35592,7 @@
         <v>99.91903600000001</v>
       </c>
       <c r="M433" s="9" t="n">
-        <v>100.178177</v>
+        <v>100.178385</v>
       </c>
       <c r="N433" s="9" t="n">
         <v>99.990887</v>
@@ -35676,7 +35676,7 @@
         <v>99.92669100000001</v>
       </c>
       <c r="M434" s="6" t="n">
-        <v>100.180738</v>
+        <v>100.180964</v>
       </c>
       <c r="N434" s="6" t="n">
         <v>99.88988000000001</v>
@@ -35760,7 +35760,7 @@
         <v>99.92874999999999</v>
       </c>
       <c r="M435" s="9" t="n">
-        <v>100.163692</v>
+        <v>100.163911</v>
       </c>
       <c r="N435" s="9" t="n">
         <v>99.76402899999999</v>
@@ -35844,7 +35844,7 @@
         <v>99.92624499999999</v>
       </c>
       <c r="M436" s="6" t="n">
-        <v>100.129359</v>
+        <v>100.129547</v>
       </c>
       <c r="N436" s="6" t="n">
         <v>99.62432</v>
@@ -35928,7 +35928,7 @@
         <v>99.920755</v>
       </c>
       <c r="M437" s="9" t="n">
-        <v>100.113704</v>
+        <v>100.113881</v>
       </c>
       <c r="N437" s="9" t="n">
         <v>99.486923</v>
@@ -36012,7 +36012,7 @@
         <v>99.915426</v>
       </c>
       <c r="M438" s="6" t="n">
-        <v>100.06032</v>
+        <v>100.060432</v>
       </c>
       <c r="N438" s="6" t="n">
         <v>99.37418700000001</v>
@@ -36096,7 +36096,7 @@
         <v>99.912741</v>
       </c>
       <c r="M439" s="9" t="n">
-        <v>99.990819</v>
+        <v>99.990843</v>
       </c>
       <c r="N439" s="9" t="n">
         <v>99.29082200000001</v>
@@ -36180,7 +36180,7 @@
         <v>99.917221</v>
       </c>
       <c r="M440" s="6" t="n">
-        <v>99.914817</v>
+        <v>99.91474700000001</v>
       </c>
       <c r="N440" s="6" t="n">
         <v>99.240371</v>
@@ -36264,7 +36264,7 @@
         <v>99.93429500000001</v>
       </c>
       <c r="M441" s="9" t="n">
-        <v>99.84768099999999</v>
+        <v>99.847533</v>
       </c>
       <c r="N441" s="9" t="n">
         <v>99.22458</v>
@@ -36348,7 +36348,7 @@
         <v>99.96369900000001</v>
       </c>
       <c r="M442" s="6" t="n">
-        <v>99.804922</v>
+        <v>99.80473499999999</v>
       </c>
       <c r="N442" s="6" t="n">
         <v>99.23282</v>
@@ -36432,7 +36432,7 @@
         <v>100.002561</v>
       </c>
       <c r="M443" s="9" t="n">
-        <v>99.761669</v>
+        <v>99.76145</v>
       </c>
       <c r="N443" s="9" t="n">
         <v>99.265654</v>
@@ -36516,7 +36516,7 @@
         <v>100.046562</v>
       </c>
       <c r="M444" s="6" t="n">
-        <v>99.724226</v>
+        <v>99.723989</v>
       </c>
       <c r="N444" s="6" t="n">
         <v>99.317403</v>
@@ -36600,7 +36600,7 @@
         <v>100.093098</v>
       </c>
       <c r="M445" s="9" t="n">
-        <v>99.692379</v>
+        <v>99.692137</v>
       </c>
       <c r="N445" s="9" t="n">
         <v>99.379154</v>
@@ -36684,7 +36684,7 @@
         <v>100.139941</v>
       </c>
       <c r="M446" s="6" t="n">
-        <v>99.631556</v>
+        <v>99.631274</v>
       </c>
       <c r="N446" s="6" t="n">
         <v>99.448081</v>
@@ -36768,7 +36768,7 @@
         <v>100.183714</v>
       </c>
       <c r="M447" s="9" t="n">
-        <v>99.48962</v>
+        <v>99.48919100000001</v>
       </c>
       <c r="N447" s="9" t="n">
         <v>99.515027</v>
@@ -36852,7 +36852,7 @@
         <v>100.222943</v>
       </c>
       <c r="M448" s="6" t="n">
-        <v>99.30301799999999</v>
+        <v>99.30237700000001</v>
       </c>
       <c r="N448" s="6" t="n">
         <v>99.58543299999999</v>
@@ -36936,7 +36936,7 @@
         <v>100.258868</v>
       </c>
       <c r="M449" s="9" t="n">
-        <v>99.083732</v>
+        <v>99.082825</v>
       </c>
       <c r="N449" s="9" t="n">
         <v>99.650679</v>
@@ -37020,7 +37020,7 @@
         <v>100.294011</v>
       </c>
       <c r="M450" s="6" t="n">
-        <v>98.850228</v>
+        <v>98.84902099999999</v>
       </c>
       <c r="N450" s="6" t="n">
         <v>99.70380900000001</v>
@@ -37104,7 +37104,7 @@
         <v>100.332805</v>
       </c>
       <c r="M451" s="9" t="n">
-        <v>98.665977</v>
+        <v>98.664529</v>
       </c>
       <c r="N451" s="9" t="n">
         <v>99.748104</v>
@@ -37188,7 +37188,7 @@
         <v>100.378956</v>
       </c>
       <c r="M452" s="6" t="n">
-        <v>98.577077</v>
+        <v>98.575514</v>
       </c>
       <c r="N452" s="6" t="n">
         <v>99.790616</v>
@@ -37272,7 +37272,7 @@
         <v>100.430245</v>
       </c>
       <c r="M453" s="9" t="n">
-        <v>98.547087</v>
+        <v>98.545501</v>
       </c>
       <c r="N453" s="9" t="n">
         <v>99.840459</v>
@@ -37356,7 +37356,7 @@
         <v>100.484362</v>
       </c>
       <c r="M454" s="6" t="n">
-        <v>98.552368</v>
+        <v>98.550822</v>
       </c>
       <c r="N454" s="6" t="n">
         <v>99.908192</v>
@@ -37440,7 +37440,7 @@
         <v>100.540542</v>
       </c>
       <c r="M455" s="9" t="n">
-        <v>98.59612799999999</v>
+        <v>98.59469199999999</v>
       </c>
       <c r="N455" s="9" t="n">
         <v>99.986108</v>
@@ -37524,7 +37524,7 @@
         <v>100.593631</v>
       </c>
       <c r="M456" s="6" t="n">
-        <v>98.677052</v>
+        <v>98.67578899999999</v>
       </c>
       <c r="N456" s="6" t="n">
         <v>100.071859</v>
@@ -37608,7 +37608,7 @@
         <v>100.640401</v>
       </c>
       <c r="M457" s="9" t="n">
-        <v>98.769868</v>
+        <v>98.768801</v>
       </c>
       <c r="N457" s="9" t="n">
         <v>100.167662</v>
@@ -37692,7 +37692,7 @@
         <v>100.681016</v>
       </c>
       <c r="M458" s="6" t="n">
-        <v>98.843898</v>
+        <v>98.843002</v>
       </c>
       <c r="N458" s="6" t="n">
         <v>100.263737</v>
@@ -37776,7 +37776,7 @@
         <v>100.718419</v>
       </c>
       <c r="M459" s="9" t="n">
-        <v>98.871287</v>
+        <v>98.87049</v>
       </c>
       <c r="N459" s="9" t="n">
         <v>100.362334</v>
@@ -37860,7 +37860,7 @@
         <v>100.756817</v>
       </c>
       <c r="M460" s="6" t="n">
-        <v>98.85954099999999</v>
+        <v>98.858771</v>
       </c>
       <c r="N460" s="6" t="n">
         <v>100.459892</v>
@@ -37944,7 +37944,7 @@
         <v>100.799872</v>
       </c>
       <c r="M461" s="9" t="n">
-        <v>98.831816</v>
+        <v>98.83102100000001</v>
       </c>
       <c r="N461" s="9" t="n">
         <v>100.558842</v>
@@ -38028,7 +38028,7 @@
         <v>100.848921</v>
       </c>
       <c r="M462" s="6" t="n">
-        <v>98.809579</v>
+        <v>98.808734</v>
       </c>
       <c r="N462" s="6" t="n">
         <v>100.646552</v>
@@ -38112,7 +38112,7 @@
         <v>100.903918</v>
       </c>
       <c r="M463" s="9" t="n">
-        <v>98.78988</v>
+        <v>98.78897499999999</v>
       </c>
       <c r="N463" s="9" t="n">
         <v>100.733264</v>
@@ -38196,7 +38196,7 @@
         <v>100.961544</v>
       </c>
       <c r="M464" s="6" t="n">
-        <v>98.770734</v>
+        <v>98.769777</v>
       </c>
       <c r="N464" s="6" t="n">
         <v>100.813605</v>
@@ -38280,7 +38280,7 @@
         <v>101.017753</v>
       </c>
       <c r="M465" s="9" t="n">
-        <v>98.742182</v>
+        <v>98.741198</v>
       </c>
       <c r="N465" s="9" t="n">
         <v>100.881008</v>
@@ -38364,7 +38364,7 @@
         <v>101.06939</v>
       </c>
       <c r="M466" s="6" t="n">
-        <v>98.69288899999999</v>
+        <v>98.691909</v>
       </c>
       <c r="N466" s="6" t="n">
         <v>100.945593</v>
@@ -38448,7 +38448,7 @@
         <v>101.114533</v>
       </c>
       <c r="M467" s="9" t="n">
-        <v>98.65801999999999</v>
+        <v>98.65710799999999</v>
       </c>
       <c r="N467" s="9" t="n">
         <v>100.999612</v>
@@ -38532,7 +38532,7 @@
         <v>101.153505</v>
       </c>
       <c r="M468" s="6" t="n">
-        <v>98.626366</v>
+        <v>98.625551</v>
       </c>
       <c r="N468" s="6" t="n">
         <v>101.033632</v>
@@ -38616,7 +38616,7 @@
         <v>101.184419</v>
       </c>
       <c r="M469" s="9" t="n">
-        <v>98.617047</v>
+        <v>98.616364</v>
       </c>
       <c r="N469" s="9" t="n">
         <v>101.043422</v>
@@ -38700,7 +38700,7 @@
         <v>101.204191</v>
       </c>
       <c r="M470" s="6" t="n">
-        <v>98.63023800000001</v>
+        <v>98.629704</v>
       </c>
       <c r="N470" s="6" t="n">
         <v>101.028239</v>
@@ -38784,7 +38784,7 @@
         <v>101.21165</v>
       </c>
       <c r="M471" s="9" t="n">
-        <v>98.702747</v>
+        <v>98.702406</v>
       </c>
       <c r="N471" s="9" t="n">
         <v>100.983073</v>
@@ -38868,7 +38868,7 @@
         <v>101.209028</v>
       </c>
       <c r="M472" s="6" t="n">
-        <v>98.84331899999999</v>
+        <v>98.843209</v>
       </c>
       <c r="N472" s="6" t="n">
         <v>100.905822</v>
@@ -38952,7 +38952,7 @@
         <v>101.201261</v>
       </c>
       <c r="M473" s="9" t="n">
-        <v>99.007141</v>
+        <v>99.007234</v>
       </c>
       <c r="N473" s="9" t="n">
         <v>100.807857</v>
@@ -39036,7 +39036,7 @@
         <v>101.194706</v>
       </c>
       <c r="M474" s="6" t="n">
-        <v>99.11803500000001</v>
+        <v>99.118206</v>
       </c>
       <c r="N474" s="6" t="n">
         <v>100.715774</v>
@@ -39120,7 +39120,7 @@
         <v>101.193266</v>
       </c>
       <c r="M475" s="9" t="n">
-        <v>99.19526399999999</v>
+        <v>99.19544</v>
       </c>
       <c r="N475" s="9" t="n">
         <v>100.633468</v>
@@ -39204,7 +39204,7 @@
         <v>101.198558</v>
       </c>
       <c r="M476" s="6" t="n">
-        <v>99.239897</v>
+        <v>99.240047</v>
       </c>
       <c r="N476" s="6" t="n">
         <v>100.563245</v>
@@ -39288,7 +39288,7 @@
         <v>101.209779</v>
       </c>
       <c r="M477" s="9" t="n">
-        <v>99.25556899999999</v>
+        <v>99.25572</v>
       </c>
       <c r="N477" s="9" t="n">
         <v>100.502645</v>
@@ -39372,7 +39372,7 @@
         <v>101.223059</v>
       </c>
       <c r="M478" s="6" t="n">
-        <v>99.261787</v>
+        <v>99.262056</v>
       </c>
       <c r="N478" s="6" t="n">
         <v>100.443481</v>
@@ -39456,7 +39456,7 @@
         <v>101.234141</v>
       </c>
       <c r="M479" s="9" t="n">
-        <v>99.242632</v>
+        <v>99.243066</v>
       </c>
       <c r="N479" s="9" t="n">
         <v>100.383873</v>
@@ -39540,7 +39540,7 @@
         <v>101.237288</v>
       </c>
       <c r="M480" s="6" t="n">
-        <v>99.21308999999999</v>
+        <v>99.213712</v>
       </c>
       <c r="N480" s="6" t="n">
         <v>100.322616</v>
@@ -39624,7 +39624,7 @@
         <v>101.2271</v>
       </c>
       <c r="M481" s="9" t="n">
-        <v>99.189075</v>
+        <v>99.189898</v>
       </c>
       <c r="N481" s="9" t="n">
         <v>100.24474</v>
@@ -39708,7 +39708,7 @@
         <v>101.196117</v>
       </c>
       <c r="M482" s="6" t="n">
-        <v>99.194183</v>
+        <v>99.19521899999999</v>
       </c>
       <c r="N482" s="6" t="n">
         <v>100.141689</v>
@@ -39792,7 +39792,7 @@
         <v>101.130652</v>
       </c>
       <c r="M483" s="9" t="n">
-        <v>99.23823299999999</v>
+        <v>99.23947</v>
       </c>
       <c r="N483" s="9" t="n">
         <v>100.005824</v>
@@ -39876,7 +39876,7 @@
         <v>101.01215</v>
       </c>
       <c r="M484" s="6" t="n">
-        <v>99.324172</v>
+        <v>99.325553</v>
       </c>
       <c r="N484" s="6" t="n">
         <v>99.821956</v>
@@ -39960,7 +39960,7 @@
         <v>100.818869</v>
       </c>
       <c r="M485" s="9" t="n">
-        <v>99.48212100000001</v>
+        <v>99.48364100000001</v>
       </c>
       <c r="N485" s="9" t="n">
         <v>99.57194800000001</v>
@@ -40044,7 +40044,7 @@
         <v>100.530118</v>
       </c>
       <c r="M486" s="6" t="n">
-        <v>99.777096</v>
+        <v>99.77884299999999</v>
       </c>
       <c r="N486" s="6" t="n">
         <v>99.232862</v>
@@ -40128,7 +40128,7 @@
         <v>100.13616</v>
       </c>
       <c r="M487" s="9" t="n">
-        <v>100.2103</v>
+        <v>100.2124</v>
       </c>
       <c r="N487" s="9" t="n">
         <v>98.78703299999999</v>
@@ -40212,7 +40212,7 @@
         <v>99.656261</v>
       </c>
       <c r="M488" s="6" t="n">
-        <v>100.762096</v>
+        <v>100.764709</v>
       </c>
       <c r="N488" s="6" t="n">
         <v>98.253626</v>
@@ -40296,7 +40296,7 @@
         <v>99.134218</v>
       </c>
       <c r="M489" s="9" t="n">
-        <v>101.436864</v>
+        <v>101.440248</v>
       </c>
       <c r="N489" s="9" t="n">
         <v>95.55669399999999</v>
@@ -40380,7 +40380,7 @@
         <v>98.627835</v>
       </c>
       <c r="M490" s="6" t="n">
-        <v>102.118757</v>
+        <v>102.123168</v>
       </c>
       <c r="N490" s="6" t="n">
         <v>93.073734</v>
@@ -40464,7 +40464,7 @@
         <v>98.198143</v>
       </c>
       <c r="M491" s="9" t="n">
-        <v>102.713129</v>
+        <v>102.71858</v>
       </c>
       <c r="N491" s="9" t="n">
         <v>95.743156</v>
@@ -40548,7 +40548,7 @@
         <v>97.875964</v>
       </c>
       <c r="M492" s="6" t="n">
-        <v>103.122046</v>
+        <v>103.128354</v>
       </c>
       <c r="N492" s="6" t="n">
         <v>96.07962499999999</v>
@@ -40632,7 +40632,7 @@
         <v>97.658879</v>
       </c>
       <c r="M493" s="9" t="n">
-        <v>103.334912</v>
+        <v>103.34182</v>
       </c>
       <c r="N493" s="9" t="n">
         <v>97.10638899999999</v>
@@ -40716,7 +40716,7 @@
         <v>97.531682</v>
       </c>
       <c r="M494" s="6" t="n">
-        <v>103.386234</v>
+        <v>103.39348</v>
       </c>
       <c r="N494" s="6" t="n">
         <v>97.453835</v>
@@ -40800,7 +40800,7 @@
         <v>97.47754500000001</v>
       </c>
       <c r="M495" s="9" t="n">
-        <v>103.327991</v>
+        <v>103.335325</v>
       </c>
       <c r="N495" s="9" t="n">
         <v>97.844987</v>
@@ -40884,7 +40884,7 @@
         <v>97.47793</v>
       </c>
       <c r="M496" s="6" t="n">
-        <v>103.218996</v>
+        <v>103.226162</v>
       </c>
       <c r="N496" s="6" t="n">
         <v>98.23362299999999</v>
@@ -40968,7 +40968,7 @@
         <v>97.518314</v>
       </c>
       <c r="M497" s="9" t="n">
-        <v>103.104657</v>
+        <v>103.1115</v>
       </c>
       <c r="N497" s="9" t="n">
         <v>98.57064699999999</v>
@@ -41052,7 +41052,7 @@
         <v>97.594053</v>
       </c>
       <c r="M498" s="6" t="n">
-        <v>103.019589</v>
+        <v>103.026028</v>
       </c>
       <c r="N498" s="6" t="n">
         <v>98.843762</v>
@@ -41136,7 +41136,7 @@
         <v>97.71531299999999</v>
       </c>
       <c r="M499" s="9" t="n">
-        <v>102.905384</v>
+        <v>102.911314</v>
       </c>
       <c r="N499" s="9" t="n">
         <v>99.067261</v>
@@ -41220,7 +41220,7 @@
         <v>97.89507999999999</v>
       </c>
       <c r="M500" s="6" t="n">
-        <v>102.770952</v>
+        <v>102.776357</v>
       </c>
       <c r="N500" s="6" t="n">
         <v>99.284261</v>
@@ -41304,7 +41304,7 @@
         <v>98.13861900000001</v>
       </c>
       <c r="M501" s="9" t="n">
-        <v>102.608069</v>
+        <v>102.613061</v>
       </c>
       <c r="N501" s="9" t="n">
         <v>99.506621</v>
@@ -41388,7 +41388,7 @@
         <v>98.436666</v>
       </c>
       <c r="M502" s="6" t="n">
-        <v>102.41672</v>
+        <v>102.421627</v>
       </c>
       <c r="N502" s="6" t="n">
         <v>99.72223</v>
@@ -41472,7 +41472,7 @@
         <v>98.751597</v>
       </c>
       <c r="M503" s="9" t="n">
-        <v>102.245137</v>
+        <v>102.250178</v>
       </c>
       <c r="N503" s="9" t="n">
         <v>99.910652</v>
@@ -41556,7 +41556,7 @@
         <v>99.04414800000001</v>
       </c>
       <c r="M504" s="6" t="n">
-        <v>102.107648</v>
+        <v>102.112953</v>
       </c>
       <c r="N504" s="6" t="n">
         <v>100.06839</v>
@@ -41640,7 +41640,7 @@
         <v>99.28756799999999</v>
       </c>
       <c r="M505" s="9" t="n">
-        <v>101.984296</v>
+        <v>101.989875</v>
       </c>
       <c r="N505" s="9" t="n">
         <v>100.188481</v>
@@ -41724,7 +41724,7 @@
         <v>99.475399</v>
       </c>
       <c r="M506" s="6" t="n">
-        <v>101.864353</v>
+        <v>101.870117</v>
       </c>
       <c r="N506" s="6" t="n">
         <v>100.300791</v>
@@ -41808,7 +41808,7 @@
         <v>99.61449399999999</v>
       </c>
       <c r="M507" s="9" t="n">
-        <v>101.741478</v>
+        <v>101.747233</v>
       </c>
       <c r="N507" s="9" t="n">
         <v>100.432031</v>
@@ -41892,7 +41892,7 @@
         <v>99.718289</v>
       </c>
       <c r="M508" s="6" t="n">
-        <v>101.619014</v>
+        <v>101.624443</v>
       </c>
       <c r="N508" s="6" t="n">
         <v>100.588669</v>
@@ -41976,7 +41976,7 @@
         <v>99.797732</v>
       </c>
       <c r="M509" s="9" t="n">
-        <v>101.494387</v>
+        <v>101.499258</v>
       </c>
       <c r="N509" s="9" t="n">
         <v>100.764847</v>
@@ -42060,7 +42060,7 @@
         <v>99.860732</v>
       </c>
       <c r="M510" s="6" t="n">
-        <v>101.341838</v>
+        <v>101.345949</v>
       </c>
       <c r="N510" s="6" t="n">
         <v>100.954178</v>
@@ -42144,7 +42144,7 @@
         <v>99.91152700000001</v>
       </c>
       <c r="M511" s="9" t="n">
-        <v>101.131597</v>
+        <v>101.13479</v>
       </c>
       <c r="N511" s="9" t="n">
         <v>101.163991</v>
@@ -42228,7 +42228,7 @@
         <v>99.952749</v>
       </c>
       <c r="M512" s="6" t="n">
-        <v>100.838256</v>
+        <v>100.840457</v>
       </c>
       <c r="N512" s="6" t="n">
         <v>101.365937</v>
@@ -42312,7 +42312,7 @@
         <v>99.988383</v>
       </c>
       <c r="M513" s="9" t="n">
-        <v>100.547023</v>
+        <v>100.548459</v>
       </c>
       <c r="N513" s="9" t="n">
         <v>101.534089</v>
@@ -42396,7 +42396,7 @@
         <v>100.021356</v>
       </c>
       <c r="M514" s="6" t="n">
-        <v>100.317165</v>
+        <v>100.318409</v>
       </c>
       <c r="N514" s="6" t="n">
         <v>101.644665</v>
@@ -42480,7 +42480,7 @@
         <v>100.056195</v>
       </c>
       <c r="M515" s="9" t="n">
-        <v>100.145127</v>
+        <v>100.146546</v>
       </c>
       <c r="N515" s="9" t="n">
         <v>101.681153</v>
@@ -42564,7 +42564,7 @@
         <v>100.094198</v>
       </c>
       <c r="M516" s="6" t="n">
-        <v>100.014042</v>
+        <v>100.015834</v>
       </c>
       <c r="N516" s="6" t="n">
         <v>101.630796</v>
@@ -42648,7 +42648,7 @@
         <v>100.135134</v>
       </c>
       <c r="M517" s="9" t="n">
-        <v>99.919135</v>
+        <v>99.92132599999999</v>
       </c>
       <c r="N517" s="9" t="n">
         <v>101.507476</v>
@@ -42732,7 +42732,7 @@
         <v>100.17799</v>
       </c>
       <c r="M518" s="6" t="n">
-        <v>99.83895099999999</v>
+        <v>99.841396</v>
       </c>
       <c r="N518" s="6" t="n">
         <v>101.343523</v>
@@ -42816,7 +42816,7 @@
         <v>100.220885</v>
       </c>
       <c r="M519" s="9" t="n">
-        <v>99.75003700000001</v>
+        <v>99.75242</v>
       </c>
       <c r="N519" s="9" t="n">
         <v>101.166503</v>
@@ -42900,7 +42900,7 @@
         <v>100.262626</v>
       </c>
       <c r="M520" s="6" t="n">
-        <v>99.61024500000001</v>
+        <v>99.612028</v>
       </c>
       <c r="N520" s="6" t="n">
         <v>101.001868</v>
@@ -42984,7 +42984,7 @@
         <v>100.305645</v>
       </c>
       <c r="M521" s="9" t="n">
-        <v>99.439331</v>
+        <v>99.440119</v>
       </c>
       <c r="N521" s="9" t="n">
         <v>100.870706</v>
@@ -43068,7 +43068,7 @@
         <v>100.351844</v>
       </c>
       <c r="M522" s="6" t="n">
-        <v>99.24552799999999</v>
+        <v>99.24509399999999</v>
       </c>
       <c r="N522" s="6" t="n">
         <v>100.763686</v>
@@ -43152,7 +43152,7 @@
         <v>100.402255</v>
       </c>
       <c r="M523" s="9" t="n">
-        <v>99.067223</v>
+        <v>99.065482</v>
       </c>
       <c r="N523" s="9" t="n">
         <v>100.663368</v>
@@ -43236,7 +43236,7 @@
         <v>100.453242</v>
       </c>
       <c r="M524" s="6" t="n">
-        <v>98.927182</v>
+        <v>98.924232</v>
       </c>
       <c r="N524" s="6" t="n">
         <v>100.567792</v>
@@ -43320,7 +43320,7 @@
         <v>100.497898</v>
       </c>
       <c r="M525" s="9" t="n">
-        <v>98.829159</v>
+        <v>98.825355</v>
       </c>
       <c r="N525" s="9" t="n">
         <v>100.477409</v>
@@ -43404,7 +43404,7 @@
         <v>100.532758</v>
       </c>
       <c r="M526" s="6" t="n">
-        <v>98.743075</v>
+        <v>98.73905000000001</v>
       </c>
       <c r="N526" s="6" t="n">
         <v>100.383687</v>
@@ -43488,7 +43488,7 @@
         <v>100.555063</v>
       </c>
       <c r="M527" s="9" t="n">
-        <v>98.69872100000001</v>
+        <v>98.694999</v>
       </c>
       <c r="N527" s="9" t="n">
         <v>100.290873</v>
@@ -43572,7 +43572,7 @@
         <v>100.565701</v>
       </c>
       <c r="M528" s="6" t="n">
-        <v>98.7244</v>
+        <v>98.72140899999999</v>
       </c>
       <c r="N528" s="6" t="n">
         <v>100.206185</v>
@@ -43656,7 +43656,7 @@
         <v>100.568192</v>
       </c>
       <c r="M529" s="9" t="n">
-        <v>98.791405</v>
+        <v>98.789305</v>
       </c>
       <c r="N529" s="9" t="n">
         <v>100.138378</v>
@@ -43740,7 +43740,7 @@
         <v>100.566838</v>
       </c>
       <c r="M530" s="6" t="n">
-        <v>98.885837</v>
+        <v>98.88441899999999</v>
       </c>
       <c r="N530" s="6" t="n">
         <v>100.084765</v>
@@ -43824,7 +43824,7 @@
         <v>100.564714</v>
       </c>
       <c r="M531" s="9" t="n">
-        <v>98.990784</v>
+        <v>98.989289</v>
       </c>
       <c r="N531" s="9" t="n">
         <v>100.032874</v>
@@ -43908,7 +43908,7 @@
         <v>100.562632</v>
       </c>
       <c r="M532" s="6" t="n">
-        <v>99.086555</v>
+        <v>99.08412</v>
       </c>
       <c r="N532" s="6" t="n">
         <v>99.994353</v>
@@ -43992,7 +43992,7 @@
         <v>100.560597</v>
       </c>
       <c r="M533" s="9" t="n">
-        <v>99.164484</v>
+        <v>99.160549</v>
       </c>
       <c r="N533" s="9" t="n">
         <v>99.982116</v>
@@ -44076,7 +44076,7 @@
         <v>100.559299</v>
       </c>
       <c r="M534" s="6" t="n">
-        <v>99.222487</v>
+        <v>99.216832</v>
       </c>
       <c r="N534" s="6" t="n">
         <v>99.997514</v>
@@ -44160,7 +44160,7 @@
         <v>100.558504</v>
       </c>
       <c r="M535" s="9" t="n">
-        <v>99.26419300000001</v>
+        <v>99.25679700000001</v>
       </c>
       <c r="N535" s="9" t="n">
         <v>100.025173</v>
@@ -44244,7 +44244,7 @@
         <v>100.558039</v>
       </c>
       <c r="M536" s="6" t="n">
-        <v>99.29733</v>
+        <v>99.288444</v>
       </c>
       <c r="N536" s="6" t="n">
         <v>100.027704</v>
@@ -44328,7 +44328,7 @@
         <v>100.558219</v>
       </c>
       <c r="M537" s="9" t="n">
-        <v>99.32158099999999</v>
+        <v>99.31176600000001</v>
       </c>
       <c r="N537" s="9" t="n">
         <v>100.001897</v>
@@ -44412,7 +44412,7 @@
         <v>100.556353</v>
       </c>
       <c r="M538" s="6" t="n">
-        <v>99.34638200000001</v>
+        <v>99.336482</v>
       </c>
       <c r="N538" s="6" t="n">
         <v>99.951207</v>
@@ -44496,7 +44496,7 @@
         <v>100.54897</v>
       </c>
       <c r="M539" s="9" t="n">
-        <v>99.352293</v>
+        <v>99.342917</v>
       </c>
       <c r="N539" s="9" t="n">
         <v>99.884123</v>
@@ -44580,7 +44580,7 @@
         <v>100.534621</v>
       </c>
       <c r="M540" s="6" t="n">
-        <v>99.31580599999999</v>
+        <v>99.30723999999999</v>
       </c>
       <c r="N540" s="6" t="n">
         <v>99.79774500000001</v>
@@ -44664,7 +44664,7 @@
         <v>100.51008</v>
       </c>
       <c r="M541" s="9" t="n">
-        <v>99.24623099999999</v>
+        <v>99.23834600000001</v>
       </c>
       <c r="N541" s="9" t="n">
         <v>99.696808</v>
@@ -44748,7 +44748,7 @@
         <v>100.474732</v>
       </c>
       <c r="M542" s="6" t="n">
-        <v>99.16469499999999</v>
+        <v>99.156924</v>
       </c>
       <c r="N542" s="6" t="n">
         <v>99.585432</v>
@@ -44832,7 +44832,7 @@
         <v>100.42974</v>
       </c>
       <c r="M543" s="9" t="n">
-        <v>99.099536</v>
+        <v>99.09093799999999</v>
       </c>
       <c r="N543" s="9" t="n">
         <v>99.486316</v>
@@ -44916,7 +44916,7 @@
         <v>100.378549</v>
       </c>
       <c r="M544" s="6" t="n">
-        <v>99.09106</v>
+        <v>99.080685</v>
       </c>
       <c r="N544" s="6" t="n">
         <v>99.394492</v>
@@ -45000,7 +45000,7 @@
         <v>100.323723</v>
       </c>
       <c r="M545" s="9" t="n">
-        <v>99.124756</v>
+        <v>99.11204600000001</v>
       </c>
       <c r="N545" s="9" t="n">
         <v>99.298998</v>
@@ -45084,7 +45084,7 @@
         <v>100.26626</v>
       </c>
       <c r="M546" s="6" t="n">
-        <v>99.17992599999999</v>
+        <v>99.16477</v>
       </c>
       <c r="N546" s="6" t="n">
         <v>99.206896</v>
@@ -45168,7 +45168,7 @@
         <v>100.206858</v>
       </c>
       <c r="M547" s="9" t="n">
-        <v>99.239465</v>
+        <v>99.221985</v>
       </c>
       <c r="N547" s="9" t="n">
         <v>99.12917299999999</v>
@@ -45252,7 +45252,7 @@
         <v>100.145668</v>
       </c>
       <c r="M548" s="6" t="n">
-        <v>99.30811199999999</v>
+        <v>99.288764</v>
       </c>
       <c r="N548" s="6" t="n">
         <v>99.080938</v>
@@ -45336,7 +45336,7 @@
         <v>100.081705</v>
       </c>
       <c r="M549" s="9" t="n">
-        <v>99.41411100000001</v>
+        <v>99.39373500000001</v>
       </c>
       <c r="N549" s="9" t="n">
         <v>99.05335599999999</v>
@@ -45420,7 +45420,7 @@
         <v>100.015623</v>
       </c>
       <c r="M550" s="6" t="n">
-        <v>99.522002</v>
+        <v>99.501587</v>
       </c>
       <c r="N550" s="6" t="n">
         <v>99.044051</v>
@@ -45504,7 +45504,7 @@
         <v>99.949878</v>
       </c>
       <c r="M551" s="9" t="n">
-        <v>99.63457099999999</v>
+        <v>99.61484900000001</v>
       </c>
       <c r="N551" s="9" t="n">
         <v>99.06027</v>
@@ -45588,7 +45588,7 @@
         <v>99.887653</v>
       </c>
       <c r="M552" s="6" t="n">
-        <v>99.766857</v>
+        <v>99.74811</v>
       </c>
       <c r="N552" s="6" t="n">
         <v>99.10844299999999</v>
@@ -45672,7 +45672,7 @@
         <v>99.833029</v>
       </c>
       <c r="M553" s="9" t="n">
-        <v>99.930751</v>
+        <v>99.91265</v>
       </c>
       <c r="N553" s="9" t="n">
         <v>99.19386799999999</v>
@@ -45756,7 +45756,7 @@
         <v>99.789569</v>
       </c>
       <c r="M554" s="6" t="n">
-        <v>100.070674</v>
+        <v>100.052241</v>
       </c>
       <c r="N554" s="6" t="n">
         <v>99.30423399999999</v>
@@ -45840,7 +45840,7 @@
         <v>99.75531599999999</v>
       </c>
       <c r="M555" s="9" t="n">
-        <v>100.151774</v>
+        <v>100.131775</v>
       </c>
       <c r="N555" s="9" t="n">
         <v>99.42832</v>
@@ -45924,7 +45924,7 @@
         <v>99.727041</v>
       </c>
       <c r="M556" s="6" t="n">
-        <v>100.216711</v>
+        <v>100.193833</v>
       </c>
       <c r="N556" s="6" t="n">
         <v>99.557726</v>
@@ -46008,7 +46008,7 @@
         <v>99.702732</v>
       </c>
       <c r="M557" s="9" t="n">
-        <v>100.285121</v>
+        <v>100.258551</v>
       </c>
       <c r="N557" s="9" t="n">
         <v>99.698927</v>
@@ -46092,7 +46092,7 @@
         <v>99.680273</v>
       </c>
       <c r="M558" s="6" t="n">
-        <v>100.389843</v>
+        <v>100.359435</v>
       </c>
       <c r="N558" s="6" t="n">
         <v>99.862517</v>
@@ -46176,7 +46176,7 @@
         <v>99.658101</v>
       </c>
       <c r="M559" s="9" t="n">
-        <v>100.515751</v>
+        <v>100.48189</v>
       </c>
       <c r="N559" s="9" t="n">
         <v>100.056753</v>
@@ -46260,7 +46260,7 @@
         <v>99.63489800000001</v>
       </c>
       <c r="M560" s="6" t="n">
-        <v>100.635757</v>
+        <v>100.599603</v>
       </c>
       <c r="N560" s="6" t="n">
         <v>100.282217</v>
@@ -46344,7 +46344,7 @@
         <v>99.611126</v>
       </c>
       <c r="M561" s="9" t="n">
-        <v>100.715535</v>
+        <v>100.679244</v>
       </c>
       <c r="N561" s="9" t="n">
         <v>100.53139</v>
@@ -46428,7 +46428,7 @@
         <v>99.590773</v>
       </c>
       <c r="M562" s="6" t="n">
-        <v>100.746164</v>
+        <v>100.712871</v>
       </c>
       <c r="N562" s="6" t="n">
         <v>100.79495</v>
@@ -46512,7 +46512,7 @@
         <v>99.57714300000001</v>
       </c>
       <c r="M563" s="9" t="n">
-        <v>100.719442</v>
+        <v>100.692966</v>
       </c>
       <c r="N563" s="9" t="n">
         <v>101.069159</v>
@@ -46596,7 +46596,7 @@
         <v>99.568476</v>
       </c>
       <c r="M564" s="6" t="n">
-        <v>100.638019</v>
+        <v>100.62248</v>
       </c>
       <c r="N564" s="6" t="n">
         <v>101.360238</v>
@@ -46672,7 +46672,7 @@
         <v>99.56307200000001</v>
       </c>
       <c r="M565" s="9" t="n">
-        <v>100.528134</v>
+        <v>100.527377</v>
       </c>
       <c r="N565" s="9" t="n">
         <v>101.628724</v>

--- a/downloads/indicadores/SIC/SIC_datos.xlsx
+++ b/downloads/indicadores/SIC/SIC_datos.xlsx
@@ -668,7 +668,7 @@
       <c r="G6" s="7" t="n"/>
       <c r="H6" s="7" t="n"/>
       <c r="I6" s="6" t="n">
-        <v>97.077684</v>
+        <v>97.07626500000001</v>
       </c>
       <c r="J6" s="6" t="n">
         <v>98.586946</v>
@@ -740,7 +740,7 @@
       </c>
       <c r="H7" s="10" t="n"/>
       <c r="I7" s="9" t="n">
-        <v>97.248456</v>
+        <v>97.24711000000001</v>
       </c>
       <c r="J7" s="9" t="n">
         <v>98.619894</v>
@@ -812,7 +812,7 @@
       </c>
       <c r="H8" s="7" t="n"/>
       <c r="I8" s="6" t="n">
-        <v>97.42827800000001</v>
+        <v>97.42701</v>
       </c>
       <c r="J8" s="6" t="n">
         <v>98.655816</v>
@@ -884,7 +884,7 @@
       </c>
       <c r="H9" s="10" t="n"/>
       <c r="I9" s="9" t="n">
-        <v>97.611076</v>
+        <v>97.609886</v>
       </c>
       <c r="J9" s="9" t="n">
         <v>98.700909</v>
@@ -956,7 +956,7 @@
       </c>
       <c r="H10" s="7" t="n"/>
       <c r="I10" s="6" t="n">
-        <v>97.826522</v>
+        <v>97.825424</v>
       </c>
       <c r="J10" s="6" t="n">
         <v>98.768818</v>
@@ -1028,7 +1028,7 @@
       </c>
       <c r="H11" s="10" t="n"/>
       <c r="I11" s="9" t="n">
-        <v>98.09350499999999</v>
+        <v>98.092522</v>
       </c>
       <c r="J11" s="9" t="n">
         <v>98.87081999999999</v>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="H12" s="7" t="n"/>
       <c r="I12" s="6" t="n">
-        <v>98.40176700000001</v>
+        <v>98.400915</v>
       </c>
       <c r="J12" s="6" t="n">
         <v>99.018193</v>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="H13" s="10" t="n"/>
       <c r="I13" s="9" t="n">
-        <v>98.74391900000001</v>
+        <v>98.743213</v>
       </c>
       <c r="J13" s="9" t="n">
         <v>99.22459600000001</v>
@@ -1244,7 +1244,7 @@
       </c>
       <c r="H14" s="7" t="n"/>
       <c r="I14" s="6" t="n">
-        <v>99.11490999999999</v>
+        <v>99.114363</v>
       </c>
       <c r="J14" s="6" t="n">
         <v>99.474411</v>
@@ -1316,7 +1316,7 @@
       </c>
       <c r="H15" s="10" t="n"/>
       <c r="I15" s="9" t="n">
-        <v>99.513266</v>
+        <v>99.512889</v>
       </c>
       <c r="J15" s="9" t="n">
         <v>99.753573</v>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="H16" s="7" t="n"/>
       <c r="I16" s="6" t="n">
-        <v>99.91264099999999</v>
+        <v>99.912435</v>
       </c>
       <c r="J16" s="6" t="n">
         <v>100.040917</v>
@@ -1460,7 +1460,7 @@
       </c>
       <c r="H17" s="10" t="n"/>
       <c r="I17" s="9" t="n">
-        <v>100.294977</v>
+        <v>100.294935</v>
       </c>
       <c r="J17" s="9" t="n">
         <v>100.321753</v>
@@ -1536,7 +1536,7 @@
         <v>2.229739</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>100.670598</v>
+        <v>100.670717</v>
       </c>
       <c r="J18" s="6" t="n">
         <v>100.587918</v>
@@ -1614,7 +1614,7 @@
         <v>2.071459</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>101.023649</v>
+        <v>101.023919</v>
       </c>
       <c r="J19" s="9" t="n">
         <v>100.83802</v>
@@ -1692,7 +1692,7 @@
         <v>1.93452</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>101.34911</v>
+        <v>101.349519</v>
       </c>
       <c r="J20" s="6" t="n">
         <v>101.07342</v>
@@ -1770,7 +1770,7 @@
         <v>1.752148</v>
       </c>
       <c r="I21" s="9" t="n">
-        <v>101.651244</v>
+        <v>101.651782</v>
       </c>
       <c r="J21" s="9" t="n">
         <v>101.289448</v>
@@ -1848,7 +1848,7 @@
         <v>1.421301</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>101.90494</v>
+        <v>101.905587</v>
       </c>
       <c r="J22" s="6" t="n">
         <v>101.481379</v>
@@ -1926,7 +1926,7 @@
         <v>0.9423899999999999</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>102.110513</v>
+        <v>102.111248</v>
       </c>
       <c r="J23" s="9" t="n">
         <v>101.651903</v>
@@ -2004,7 +2004,7 @@
         <v>0.357388</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>102.284513</v>
+        <v>102.285323</v>
       </c>
       <c r="J24" s="6" t="n">
         <v>101.801905</v>
@@ -2082,7 +2082,7 @@
         <v>-0.266288</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>102.435834</v>
+        <v>102.436708</v>
       </c>
       <c r="J25" s="9" t="n">
         <v>101.923296</v>
@@ -2160,7 +2160,7 @@
         <v>-0.847554</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>102.551122</v>
+        <v>102.552047</v>
       </c>
       <c r="J26" s="6" t="n">
         <v>102.008319</v>
@@ -2238,7 +2238,7 @@
         <v>-1.343828</v>
       </c>
       <c r="I27" s="9" t="n">
-        <v>102.623419</v>
+        <v>102.624375</v>
       </c>
       <c r="J27" s="9" t="n">
         <v>102.053862</v>
@@ -2316,7 +2316,7 @@
         <v>-1.799386</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>102.616518</v>
+        <v>102.617471</v>
       </c>
       <c r="J28" s="6" t="n">
         <v>102.067896</v>
@@ -2394,7 +2394,7 @@
         <v>-2.309084</v>
       </c>
       <c r="I29" s="9" t="n">
-        <v>102.510761</v>
+        <v>102.511669</v>
       </c>
       <c r="J29" s="9" t="n">
         <v>102.05766</v>
@@ -2472,7 +2472,7 @@
         <v>-2.979402</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>102.331246</v>
+        <v>102.332077</v>
       </c>
       <c r="J30" s="6" t="n">
         <v>102.028821</v>
@@ -2550,7 +2550,7 @@
         <v>-3.648135</v>
       </c>
       <c r="I31" s="9" t="n">
-        <v>102.131764</v>
+        <v>102.132511</v>
       </c>
       <c r="J31" s="9" t="n">
         <v>101.972547</v>
@@ -2628,7 +2628,7 @@
         <v>-4.414118</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>101.942937</v>
+        <v>101.943603</v>
       </c>
       <c r="J32" s="6" t="n">
         <v>101.879111</v>
@@ -2706,7 +2706,7 @@
         <v>-5.191236</v>
       </c>
       <c r="I33" s="9" t="n">
-        <v>101.786291</v>
+        <v>101.78689</v>
       </c>
       <c r="J33" s="9" t="n">
         <v>101.74295</v>
@@ -2784,7 +2784,7 @@
         <v>-5.84301</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>101.641863</v>
+        <v>101.642401</v>
       </c>
       <c r="J34" s="6" t="n">
         <v>101.562426</v>
@@ -2862,7 +2862,7 @@
         <v>-6.335978</v>
       </c>
       <c r="I35" s="9" t="n">
-        <v>101.477899</v>
+        <v>101.478368</v>
       </c>
       <c r="J35" s="9" t="n">
         <v>101.331778</v>
@@ -2940,7 +2940,7 @@
         <v>-6.623331</v>
       </c>
       <c r="I36" s="6" t="n">
-        <v>101.283369</v>
+        <v>101.283755</v>
       </c>
       <c r="J36" s="6" t="n">
         <v>101.054802</v>
@@ -3018,7 +3018,7 @@
         <v>-6.696779</v>
       </c>
       <c r="I37" s="9" t="n">
-        <v>101.049162</v>
+        <v>101.049448</v>
       </c>
       <c r="J37" s="9" t="n">
         <v>100.743763</v>
@@ -3096,7 +3096,7 @@
         <v>-6.570834</v>
       </c>
       <c r="I38" s="6" t="n">
-        <v>100.761497</v>
+        <v>100.76166</v>
       </c>
       <c r="J38" s="6" t="n">
         <v>100.410754</v>
@@ -3174,7 +3174,7 @@
         <v>-6.276091</v>
       </c>
       <c r="I39" s="9" t="n">
-        <v>100.426977</v>
+        <v>100.426997</v>
       </c>
       <c r="J39" s="9" t="n">
         <v>100.07531</v>
@@ -3252,7 +3252,7 @@
         <v>-5.831309</v>
       </c>
       <c r="I40" s="6" t="n">
-        <v>100.089177</v>
+        <v>100.089054</v>
       </c>
       <c r="J40" s="6" t="n">
         <v>99.760628</v>
@@ -3330,7 +3330,7 @@
         <v>-5.244899</v>
       </c>
       <c r="I41" s="9" t="n">
-        <v>99.77144</v>
+        <v>99.771182</v>
       </c>
       <c r="J41" s="9" t="n">
         <v>99.456295</v>
@@ -3408,7 +3408,7 @@
         <v>-4.453863</v>
       </c>
       <c r="I42" s="6" t="n">
-        <v>99.47217499999999</v>
+        <v>99.471789</v>
       </c>
       <c r="J42" s="6" t="n">
         <v>99.16512299999999</v>
@@ -3486,7 +3486,7 @@
         <v>-3.483857</v>
       </c>
       <c r="I43" s="9" t="n">
-        <v>99.193282</v>
+        <v>99.19277700000001</v>
       </c>
       <c r="J43" s="9" t="n">
         <v>98.898816</v>
@@ -3564,7 +3564,7 @@
         <v>-2.39669</v>
       </c>
       <c r="I44" s="6" t="n">
-        <v>98.93933</v>
+        <v>98.938717</v>
       </c>
       <c r="J44" s="6" t="n">
         <v>98.675723</v>
@@ -3642,7 +3642,7 @@
         <v>-1.266633</v>
       </c>
       <c r="I45" s="9" t="n">
-        <v>98.72855199999999</v>
+        <v>98.72785</v>
       </c>
       <c r="J45" s="9" t="n">
         <v>98.505612</v>
@@ -3720,7 +3720,7 @@
         <v>-0.183968</v>
       </c>
       <c r="I46" s="6" t="n">
-        <v>98.60877000000001</v>
+        <v>98.608017</v>
       </c>
       <c r="J46" s="6" t="n">
         <v>98.385851</v>
@@ -3798,7 +3798,7 @@
         <v>0.820773</v>
       </c>
       <c r="I47" s="9" t="n">
-        <v>98.573397</v>
+        <v>98.57262900000001</v>
       </c>
       <c r="J47" s="9" t="n">
         <v>98.31832799999999</v>
@@ -3876,7 +3876,7 @@
         <v>1.692758</v>
       </c>
       <c r="I48" s="6" t="n">
-        <v>98.60900599999999</v>
+        <v>98.608254</v>
       </c>
       <c r="J48" s="6" t="n">
         <v>98.301321</v>
@@ -3954,7 +3954,7 @@
         <v>2.386011</v>
       </c>
       <c r="I49" s="9" t="n">
-        <v>98.700958</v>
+        <v>98.700245</v>
       </c>
       <c r="J49" s="9" t="n">
         <v>98.33217399999999</v>
@@ -4032,7 +4032,7 @@
         <v>2.906103</v>
       </c>
       <c r="I50" s="6" t="n">
-        <v>98.861086</v>
+        <v>98.86044200000001</v>
       </c>
       <c r="J50" s="6" t="n">
         <v>98.404349</v>
@@ -4110,7 +4110,7 @@
         <v>3.26613</v>
       </c>
       <c r="I51" s="9" t="n">
-        <v>99.074564</v>
+        <v>99.074011</v>
       </c>
       <c r="J51" s="9" t="n">
         <v>98.510688</v>
@@ -4188,7 +4188,7 @@
         <v>3.508114</v>
       </c>
       <c r="I52" s="6" t="n">
-        <v>99.30423</v>
+        <v>99.303776</v>
       </c>
       <c r="J52" s="6" t="n">
         <v>98.64295799999999</v>
@@ -4266,7 +4266,7 @@
         <v>3.693818</v>
       </c>
       <c r="I53" s="9" t="n">
-        <v>99.55011399999999</v>
+        <v>99.54976499999999</v>
       </c>
       <c r="J53" s="9" t="n">
         <v>98.792827</v>
@@ -4344,7 +4344,7 @@
         <v>3.800709</v>
       </c>
       <c r="I54" s="6" t="n">
-        <v>99.781046</v>
+        <v>99.78079700000001</v>
       </c>
       <c r="J54" s="6" t="n">
         <v>98.945533</v>
@@ -4422,7 +4422,7 @@
         <v>3.793813</v>
       </c>
       <c r="I55" s="9" t="n">
-        <v>99.941086</v>
+        <v>99.940905</v>
       </c>
       <c r="J55" s="9" t="n">
         <v>99.100864</v>
@@ -4500,7 +4500,7 @@
         <v>3.685872</v>
       </c>
       <c r="I56" s="6" t="n">
-        <v>100.040716</v>
+        <v>100.040577</v>
       </c>
       <c r="J56" s="6" t="n">
         <v>99.25765199999999</v>
@@ -4578,7 +4578,7 @@
         <v>3.519636</v>
       </c>
       <c r="I57" s="9" t="n">
-        <v>100.101148</v>
+        <v>100.101036</v>
       </c>
       <c r="J57" s="9" t="n">
         <v>99.420682</v>
@@ -4656,7 +4656,7 @@
         <v>3.323388</v>
       </c>
       <c r="I58" s="6" t="n">
-        <v>100.161708</v>
+        <v>100.161622</v>
       </c>
       <c r="J58" s="6" t="n">
         <v>99.595643</v>
@@ -4734,7 +4734,7 @@
         <v>3.085141</v>
       </c>
       <c r="I59" s="9" t="n">
-        <v>100.272424</v>
+        <v>100.272386</v>
       </c>
       <c r="J59" s="9" t="n">
         <v>99.78168700000001</v>
@@ -4812,7 +4812,7 @@
         <v>2.832557</v>
       </c>
       <c r="I60" s="6" t="n">
-        <v>100.412956</v>
+        <v>100.412978</v>
       </c>
       <c r="J60" s="6" t="n">
         <v>99.965689</v>
@@ -4890,7 +4890,7 @@
         <v>2.595285</v>
       </c>
       <c r="I61" s="9" t="n">
-        <v>100.526736</v>
+        <v>100.526807</v>
       </c>
       <c r="J61" s="9" t="n">
         <v>100.135751</v>
@@ -4968,7 +4968,7 @@
         <v>2.318479</v>
       </c>
       <c r="I62" s="6" t="n">
-        <v>100.60814</v>
+        <v>100.608246</v>
       </c>
       <c r="J62" s="6" t="n">
         <v>100.291121</v>
@@ -5046,7 +5046,7 @@
         <v>2.005352</v>
       </c>
       <c r="I63" s="9" t="n">
-        <v>100.660625</v>
+        <v>100.660753</v>
       </c>
       <c r="J63" s="9" t="n">
         <v>100.437705</v>
@@ -5124,7 +5124,7 @@
         <v>1.689436</v>
       </c>
       <c r="I64" s="6" t="n">
-        <v>100.739041</v>
+        <v>100.739204</v>
       </c>
       <c r="J64" s="6" t="n">
         <v>100.603087</v>
@@ -5202,7 +5202,7 @@
         <v>1.408344</v>
       </c>
       <c r="I65" s="9" t="n">
-        <v>100.85617</v>
+        <v>100.856383</v>
       </c>
       <c r="J65" s="9" t="n">
         <v>100.773025</v>
@@ -5280,7 +5280,7 @@
         <v>1.180398</v>
       </c>
       <c r="I66" s="6" t="n">
-        <v>100.98882</v>
+        <v>100.98909</v>
       </c>
       <c r="J66" s="6" t="n">
         <v>100.930358</v>
@@ -5358,7 +5358,7 @@
         <v>1.015536</v>
       </c>
       <c r="I67" s="9" t="n">
-        <v>101.111137</v>
+        <v>101.111459</v>
       </c>
       <c r="J67" s="9" t="n">
         <v>101.06397</v>
@@ -5436,7 +5436,7 @@
         <v>0.848261</v>
       </c>
       <c r="I68" s="6" t="n">
-        <v>101.195283</v>
+        <v>101.195642</v>
       </c>
       <c r="J68" s="6" t="n">
         <v>101.165182</v>
@@ -5514,7 +5514,7 @@
         <v>0.639122</v>
       </c>
       <c r="I69" s="9" t="n">
-        <v>101.252232</v>
+        <v>101.252615</v>
       </c>
       <c r="J69" s="9" t="n">
         <v>101.237809</v>
@@ -5592,7 +5592,7 @@
         <v>0.364845</v>
       </c>
       <c r="I70" s="6" t="n">
-        <v>101.29234</v>
+        <v>101.29274</v>
       </c>
       <c r="J70" s="6" t="n">
         <v>101.301106</v>
@@ -5670,7 +5670,7 @@
         <v>0.060315</v>
       </c>
       <c r="I71" s="9" t="n">
-        <v>101.33056</v>
+        <v>101.330976</v>
       </c>
       <c r="J71" s="9" t="n">
         <v>101.354768</v>
@@ -5748,7 +5748,7 @@
         <v>-0.275626</v>
       </c>
       <c r="I72" s="6" t="n">
-        <v>101.338021</v>
+        <v>101.338441</v>
       </c>
       <c r="J72" s="6" t="n">
         <v>101.38111</v>
@@ -5826,7 +5826,7 @@
         <v>-0.623271</v>
       </c>
       <c r="I73" s="9" t="n">
-        <v>101.310903</v>
+        <v>101.311312</v>
       </c>
       <c r="J73" s="9" t="n">
         <v>101.365559</v>
@@ -5904,7 +5904,7 @@
         <v>-0.889683</v>
       </c>
       <c r="I74" s="6" t="n">
-        <v>101.231927</v>
+        <v>101.232301</v>
       </c>
       <c r="J74" s="6" t="n">
         <v>101.311594</v>
@@ -5982,7 +5982,7 @@
         <v>-1.071488</v>
       </c>
       <c r="I75" s="9" t="n">
-        <v>101.087058</v>
+        <v>101.08737</v>
       </c>
       <c r="J75" s="9" t="n">
         <v>101.222381</v>
@@ -6060,7 +6060,7 @@
         <v>-1.225665</v>
       </c>
       <c r="I76" s="6" t="n">
-        <v>100.894536</v>
+        <v>100.894766</v>
       </c>
       <c r="J76" s="6" t="n">
         <v>101.101502</v>
@@ -6138,7 +6138,7 @@
         <v>-1.425508</v>
       </c>
       <c r="I77" s="9" t="n">
-        <v>100.660475</v>
+        <v>100.660605</v>
       </c>
       <c r="J77" s="9" t="n">
         <v>100.951601</v>
@@ -6216,7 +6216,7 @@
         <v>-1.677614</v>
       </c>
       <c r="I78" s="6" t="n">
-        <v>100.40591</v>
+        <v>100.405931</v>
       </c>
       <c r="J78" s="6" t="n">
         <v>100.777559</v>
@@ -6296,7 +6296,7 @@
         <v>-1.957862</v>
       </c>
       <c r="I79" s="9" t="n">
-        <v>100.200881</v>
+        <v>100.200814</v>
       </c>
       <c r="J79" s="9" t="n">
         <v>100.570453</v>
@@ -6376,7 +6376,7 @@
         <v>-2.20591</v>
       </c>
       <c r="I80" s="6" t="n">
-        <v>100.026697</v>
+        <v>100.026556</v>
       </c>
       <c r="J80" s="6" t="n">
         <v>100.321374</v>
@@ -6456,7 +6456,7 @@
         <v>-2.407231</v>
       </c>
       <c r="I81" s="9" t="n">
-        <v>99.83749899999999</v>
+        <v>99.837276</v>
       </c>
       <c r="J81" s="9" t="n">
         <v>100.034504</v>
@@ -6536,7 +6536,7 @@
         <v>-2.531773</v>
       </c>
       <c r="I82" s="6" t="n">
-        <v>99.643163</v>
+        <v>99.64285700000001</v>
       </c>
       <c r="J82" s="6" t="n">
         <v>99.70409100000001</v>
@@ -6616,7 +6616,7 @@
         <v>-2.553208</v>
       </c>
       <c r="I83" s="9" t="n">
-        <v>99.397147</v>
+        <v>99.396736</v>
       </c>
       <c r="J83" s="9" t="n">
         <v>99.352118</v>
@@ -6696,7 +6696,7 @@
         <v>-2.43673</v>
       </c>
       <c r="I84" s="6" t="n">
-        <v>99.089251</v>
+        <v>99.088707</v>
       </c>
       <c r="J84" s="6" t="n">
         <v>99.02132</v>
@@ -6776,7 +6776,7 @@
         <v>-2.183567</v>
       </c>
       <c r="I85" s="9" t="n">
-        <v>98.80620500000001</v>
+        <v>98.80553999999999</v>
       </c>
       <c r="J85" s="9" t="n">
         <v>98.741837</v>
@@ -6856,7 +6856,7 @@
         <v>-1.855685</v>
       </c>
       <c r="I86" s="6" t="n">
-        <v>98.576689</v>
+        <v>98.575925</v>
       </c>
       <c r="J86" s="6" t="n">
         <v>98.53317</v>
@@ -6936,7 +6936,7 @@
         <v>-1.466768</v>
       </c>
       <c r="I87" s="9" t="n">
-        <v>98.42932</v>
+        <v>98.42849200000001</v>
       </c>
       <c r="J87" s="9" t="n">
         <v>98.401658</v>
@@ -7016,7 +7016,7 @@
         <v>-0.996502</v>
       </c>
       <c r="I88" s="6" t="n">
-        <v>98.37601600000001</v>
+        <v>98.375164</v>
       </c>
       <c r="J88" s="6" t="n">
         <v>98.348884</v>
@@ -7096,7 +7096,7 @@
         <v>-0.408178</v>
       </c>
       <c r="I89" s="9" t="n">
-        <v>98.404894</v>
+        <v>98.404053</v>
       </c>
       <c r="J89" s="9" t="n">
         <v>98.387186</v>
@@ -7176,7 +7176,7 @@
         <v>0.279225</v>
       </c>
       <c r="I90" s="6" t="n">
-        <v>98.522384</v>
+        <v>98.521593</v>
       </c>
       <c r="J90" s="6" t="n">
         <v>98.515604</v>
@@ -7258,7 +7258,7 @@
         <v>1.02696</v>
       </c>
       <c r="I91" s="9" t="n">
-        <v>98.705164</v>
+        <v>98.70444999999999</v>
       </c>
       <c r="J91" s="9" t="n">
         <v>98.71991300000001</v>
@@ -7340,7 +7340,7 @@
         <v>1.79411</v>
       </c>
       <c r="I92" s="6" t="n">
-        <v>98.92668399999999</v>
+        <v>98.926063</v>
       </c>
       <c r="J92" s="6" t="n">
         <v>98.972651</v>
@@ -7422,7 +7422,7 @@
         <v>2.544261</v>
       </c>
       <c r="I93" s="9" t="n">
-        <v>99.172929</v>
+        <v>99.17241199999999</v>
       </c>
       <c r="J93" s="9" t="n">
         <v>99.232417</v>
@@ -7504,7 +7504,7 @@
         <v>3.228662</v>
       </c>
       <c r="I94" s="6" t="n">
-        <v>99.36812999999999</v>
+        <v>99.367694</v>
       </c>
       <c r="J94" s="6" t="n">
         <v>99.465391</v>
@@ -7586,7 +7586,7 @@
         <v>3.732812</v>
       </c>
       <c r="I95" s="9" t="n">
-        <v>99.501212</v>
+        <v>99.500832</v>
       </c>
       <c r="J95" s="9" t="n">
         <v>99.654354</v>
@@ -7668,7 +7668,7 @@
         <v>3.922056</v>
       </c>
       <c r="I96" s="6" t="n">
-        <v>99.58997100000001</v>
+        <v>99.58962699999999</v>
       </c>
       <c r="J96" s="6" t="n">
         <v>99.797794</v>
@@ -7750,7 +7750,7 @@
         <v>3.692184</v>
       </c>
       <c r="I97" s="9" t="n">
-        <v>99.65280199999999</v>
+        <v>99.65248200000001</v>
       </c>
       <c r="J97" s="9" t="n">
         <v>99.89845800000001</v>
@@ -7832,7 +7832,7 @@
         <v>3.025204</v>
       </c>
       <c r="I98" s="6" t="n">
-        <v>99.681888</v>
+        <v>99.681579</v>
       </c>
       <c r="J98" s="6" t="n">
         <v>99.95576199999999</v>
@@ -7914,7 +7914,7 @@
         <v>2.012594</v>
       </c>
       <c r="I99" s="9" t="n">
-        <v>99.68566300000001</v>
+        <v>99.685354</v>
       </c>
       <c r="J99" s="9" t="n">
         <v>99.95500800000001</v>
@@ -7996,7 +7996,7 @@
         <v>0.810656</v>
       </c>
       <c r="I100" s="6" t="n">
-        <v>99.631958</v>
+        <v>99.63162199999999</v>
       </c>
       <c r="J100" s="6" t="n">
         <v>99.899019</v>
@@ -8078,7 +8078,7 @@
         <v>-0.365422</v>
       </c>
       <c r="I101" s="9" t="n">
-        <v>99.51013</v>
+        <v>99.50973999999999</v>
       </c>
       <c r="J101" s="9" t="n">
         <v>99.795023</v>
@@ -8160,7 +8160,7 @@
         <v>-1.348641</v>
       </c>
       <c r="I102" s="6" t="n">
-        <v>99.346661</v>
+        <v>99.346199</v>
       </c>
       <c r="J102" s="6" t="n">
         <v>99.652359</v>
@@ -8242,7 +8242,7 @@
         <v>-2.076067</v>
       </c>
       <c r="I103" s="9" t="n">
-        <v>99.173152</v>
+        <v>99.172613</v>
       </c>
       <c r="J103" s="9" t="n">
         <v>99.498048</v>
@@ -8324,7 +8324,7 @@
         <v>-2.552085</v>
       </c>
       <c r="I104" s="6" t="n">
-        <v>99.026126</v>
+        <v>99.025521</v>
       </c>
       <c r="J104" s="6" t="n">
         <v>99.34424799999999</v>
@@ -8406,7 +8406,7 @@
         <v>-2.80954</v>
       </c>
       <c r="I105" s="9" t="n">
-        <v>98.912353</v>
+        <v>98.91169600000001</v>
       </c>
       <c r="J105" s="9" t="n">
         <v>99.21383899999999</v>
@@ -8488,7 +8488,7 @@
         <v>-2.908628</v>
       </c>
       <c r="I106" s="6" t="n">
-        <v>98.82204900000001</v>
+        <v>98.82135</v>
       </c>
       <c r="J106" s="6" t="n">
         <v>99.126107</v>
@@ -8570,7 +8570,7 @@
         <v>-2.85245</v>
       </c>
       <c r="I107" s="9" t="n">
-        <v>98.74914800000001</v>
+        <v>98.74841499999999</v>
       </c>
       <c r="J107" s="9" t="n">
         <v>99.093529</v>
@@ -8652,7 +8652,7 @@
         <v>-2.608995</v>
       </c>
       <c r="I108" s="6" t="n">
-        <v>98.702493</v>
+        <v>98.70173699999999</v>
       </c>
       <c r="J108" s="6" t="n">
         <v>99.11807899999999</v>
@@ -8734,7 +8734,7 @@
         <v>-2.128623</v>
       </c>
       <c r="I109" s="9" t="n">
-        <v>98.706485</v>
+        <v>98.705726</v>
       </c>
       <c r="J109" s="9" t="n">
         <v>99.22349699999999</v>
@@ -8816,7 +8816,7 @@
         <v>-1.397249</v>
       </c>
       <c r="I110" s="6" t="n">
-        <v>98.787453</v>
+        <v>98.78672400000001</v>
       </c>
       <c r="J110" s="6" t="n">
         <v>99.37839200000001</v>
@@ -8898,7 +8898,7 @@
         <v>-0.481154</v>
       </c>
       <c r="I111" s="9" t="n">
-        <v>98.93053</v>
+        <v>98.92985899999999</v>
       </c>
       <c r="J111" s="9" t="n">
         <v>99.566131</v>
@@ -8980,7 +8980,7 @@
         <v>0.485589</v>
       </c>
       <c r="I112" s="6" t="n">
-        <v>99.08313</v>
+        <v>99.082519</v>
       </c>
       <c r="J112" s="6" t="n">
         <v>99.756495</v>
@@ -9062,7 +9062,7 @@
         <v>1.283595</v>
       </c>
       <c r="I113" s="9" t="n">
-        <v>99.249621</v>
+        <v>99.249077</v>
       </c>
       <c r="J113" s="9" t="n">
         <v>99.911468</v>
@@ -9144,7 +9144,7 @@
         <v>1.802279</v>
       </c>
       <c r="I114" s="6" t="n">
-        <v>99.41645</v>
+        <v>99.415972</v>
       </c>
       <c r="J114" s="6" t="n">
         <v>100.021312</v>
@@ -9226,7 +9226,7 @@
         <v>2.050574</v>
       </c>
       <c r="I115" s="9" t="n">
-        <v>99.561543</v>
+        <v>99.561122</v>
       </c>
       <c r="J115" s="9" t="n">
         <v>100.091356</v>
@@ -9308,7 +9308,7 @@
         <v>2.071205</v>
       </c>
       <c r="I116" s="6" t="n">
-        <v>99.67402199999999</v>
+        <v>99.673644</v>
       </c>
       <c r="J116" s="6" t="n">
         <v>100.135609</v>
@@ -9390,7 +9390,7 @@
         <v>1.91657</v>
       </c>
       <c r="I117" s="9" t="n">
-        <v>99.749515</v>
+        <v>99.74916399999999</v>
       </c>
       <c r="J117" s="9" t="n">
         <v>100.164723</v>
@@ -9472,7 +9472,7 @@
         <v>1.66489</v>
       </c>
       <c r="I118" s="6" t="n">
-        <v>99.79264999999999</v>
+        <v>99.792312</v>
       </c>
       <c r="J118" s="6" t="n">
         <v>100.171398</v>
@@ -9554,7 +9554,7 @@
         <v>1.377927</v>
       </c>
       <c r="I119" s="9" t="n">
-        <v>99.805074</v>
+        <v>99.80473499999999</v>
       </c>
       <c r="J119" s="9" t="n">
         <v>100.14881</v>
@@ -9636,7 +9636,7 @@
         <v>1.098579</v>
       </c>
       <c r="I120" s="6" t="n">
-        <v>99.77128999999999</v>
+        <v>99.770931</v>
       </c>
       <c r="J120" s="6" t="n">
         <v>100.084549</v>
@@ -9718,7 +9718,7 @@
         <v>0.824611</v>
       </c>
       <c r="I121" s="9" t="n">
-        <v>99.68836899999999</v>
+        <v>99.687968</v>
       </c>
       <c r="J121" s="9" t="n">
         <v>99.99422800000001</v>
@@ -9800,7 +9800,7 @@
         <v>0.560129</v>
       </c>
       <c r="I122" s="6" t="n">
-        <v>99.59194100000001</v>
+        <v>99.591493</v>
       </c>
       <c r="J122" s="6" t="n">
         <v>99.894998</v>
@@ -9882,7 +9882,7 @@
         <v>0.315453</v>
       </c>
       <c r="I123" s="9" t="n">
-        <v>99.514264</v>
+        <v>99.51377599999999</v>
       </c>
       <c r="J123" s="9" t="n">
         <v>99.827461</v>
@@ -9964,7 +9964,7 @@
         <v>0.108616</v>
       </c>
       <c r="I124" s="6" t="n">
-        <v>99.497756</v>
+        <v>99.497255</v>
       </c>
       <c r="J124" s="6" t="n">
         <v>99.819624</v>
@@ -10046,7 +10046,7 @@
         <v>-0.024876</v>
       </c>
       <c r="I125" s="9" t="n">
-        <v>99.56820999999999</v>
+        <v>99.56773200000001</v>
       </c>
       <c r="J125" s="9" t="n">
         <v>99.885834</v>
@@ -10128,7 +10128,7 @@
         <v>-0.11377</v>
       </c>
       <c r="I126" s="6" t="n">
-        <v>99.709906</v>
+        <v>99.709481</v>
       </c>
       <c r="J126" s="6" t="n">
         <v>100.022789</v>
@@ -10210,7 +10210,7 @@
         <v>-0.185125</v>
       </c>
       <c r="I127" s="9" t="n">
-        <v>99.885463</v>
+        <v>99.88510599999999</v>
       </c>
       <c r="J127" s="9" t="n">
         <v>100.198667</v>
@@ -10292,7 +10292,7 @@
         <v>-0.235455</v>
       </c>
       <c r="I128" s="6" t="n">
-        <v>100.067996</v>
+        <v>100.06771</v>
       </c>
       <c r="J128" s="6" t="n">
         <v>100.393657</v>
@@ -10374,7 +10374,7 @@
         <v>-0.274571</v>
       </c>
       <c r="I129" s="9" t="n">
-        <v>100.257202</v>
+        <v>100.256988</v>
       </c>
       <c r="J129" s="9" t="n">
         <v>100.564093</v>
@@ -10456,7 +10456,7 @@
         <v>-0.322845</v>
       </c>
       <c r="I130" s="6" t="n">
-        <v>100.394907</v>
+        <v>100.394745</v>
       </c>
       <c r="J130" s="6" t="n">
         <v>100.713018</v>
@@ -10538,7 +10538,7 @@
         <v>-0.421972</v>
       </c>
       <c r="I131" s="9" t="n">
-        <v>100.505843</v>
+        <v>100.505721</v>
       </c>
       <c r="J131" s="9" t="n">
         <v>100.82097</v>
@@ -10620,7 +10620,7 @@
         <v>-0.562422</v>
       </c>
       <c r="I132" s="6" t="n">
-        <v>100.587758</v>
+        <v>100.587662</v>
       </c>
       <c r="J132" s="6" t="n">
         <v>100.88146</v>
@@ -10702,7 +10702,7 @@
         <v>-0.68901</v>
       </c>
       <c r="I133" s="9" t="n">
-        <v>100.645105</v>
+        <v>100.645026</v>
       </c>
       <c r="J133" s="9" t="n">
         <v>100.889203</v>
@@ -10784,7 +10784,7 @@
         <v>-0.75257</v>
       </c>
       <c r="I134" s="6" t="n">
-        <v>100.694602</v>
+        <v>100.694536</v>
       </c>
       <c r="J134" s="6" t="n">
         <v>100.850625</v>
@@ -10866,7 +10866,7 @@
         <v>-0.737611</v>
       </c>
       <c r="I135" s="9" t="n">
-        <v>100.733843</v>
+        <v>100.733786</v>
       </c>
       <c r="J135" s="9" t="n">
         <v>100.777227</v>
@@ -10948,7 +10948,7 @@
         <v>-0.672737</v>
       </c>
       <c r="I136" s="6" t="n">
-        <v>100.761615</v>
+        <v>100.761562</v>
       </c>
       <c r="J136" s="6" t="n">
         <v>100.678754</v>
@@ -11030,7 +11030,7 @@
         <v>-0.560868</v>
       </c>
       <c r="I137" s="9" t="n">
-        <v>100.779053</v>
+        <v>100.778999</v>
       </c>
       <c r="J137" s="9" t="n">
         <v>100.583776</v>
@@ -11112,7 +11112,7 @@
         <v>-0.390058</v>
       </c>
       <c r="I138" s="6" t="n">
-        <v>100.793776</v>
+        <v>100.793722</v>
       </c>
       <c r="J138" s="6" t="n">
         <v>100.516769</v>
@@ -11194,7 +11194,7 @@
         <v>-0.158963</v>
       </c>
       <c r="I139" s="9" t="n">
-        <v>100.844164</v>
+        <v>100.844125</v>
       </c>
       <c r="J139" s="9" t="n">
         <v>100.473621</v>
@@ -11276,7 +11276,7 @@
         <v>0.08562</v>
       </c>
       <c r="I140" s="6" t="n">
-        <v>100.921288</v>
+        <v>100.921276</v>
       </c>
       <c r="J140" s="6" t="n">
         <v>100.448401</v>
@@ -11358,7 +11358,7 @@
         <v>0.317901</v>
       </c>
       <c r="I141" s="9" t="n">
-        <v>100.989016</v>
+        <v>100.989029</v>
       </c>
       <c r="J141" s="9" t="n">
         <v>100.439634</v>
@@ -11440,7 +11440,7 @@
         <v>0.529536</v>
       </c>
       <c r="I142" s="6" t="n">
-        <v>101.03388</v>
+        <v>101.033907</v>
       </c>
       <c r="J142" s="6" t="n">
         <v>100.424116</v>
@@ -11522,7 +11522,7 @@
         <v>0.74738</v>
       </c>
       <c r="I143" s="9" t="n">
-        <v>101.01884</v>
+        <v>101.018855</v>
       </c>
       <c r="J143" s="9" t="n">
         <v>100.399163</v>
@@ -11604,7 +11604,7 @@
         <v>0.978386</v>
       </c>
       <c r="I144" s="6" t="n">
-        <v>100.928647</v>
+        <v>100.928614</v>
       </c>
       <c r="J144" s="6" t="n">
         <v>100.383126</v>
@@ -11686,7 +11686,7 @@
         <v>1.205845</v>
       </c>
       <c r="I145" s="9" t="n">
-        <v>100.850905</v>
+        <v>100.850824</v>
       </c>
       <c r="J145" s="9" t="n">
         <v>100.377542</v>
@@ -11768,7 +11768,7 @@
         <v>1.398013</v>
       </c>
       <c r="I146" s="6" t="n">
-        <v>100.825335</v>
+        <v>100.825218</v>
       </c>
       <c r="J146" s="6" t="n">
         <v>100.394198</v>
@@ -11850,7 +11850,7 @@
         <v>1.540005</v>
       </c>
       <c r="I147" s="9" t="n">
-        <v>100.856851</v>
+        <v>100.856709</v>
       </c>
       <c r="J147" s="9" t="n">
         <v>100.426517</v>
@@ -11932,7 +11932,7 @@
         <v>1.67256</v>
       </c>
       <c r="I148" s="6" t="n">
-        <v>100.90514</v>
+        <v>100.90496</v>
       </c>
       <c r="J148" s="6" t="n">
         <v>100.43304</v>
@@ -12014,7 +12014,7 @@
         <v>1.789315</v>
       </c>
       <c r="I149" s="9" t="n">
-        <v>100.947883</v>
+        <v>100.947646</v>
       </c>
       <c r="J149" s="9" t="n">
         <v>100.436697</v>
@@ -12096,7 +12096,7 @@
         <v>1.853192</v>
       </c>
       <c r="I150" s="6" t="n">
-        <v>100.987057</v>
+        <v>100.986751</v>
       </c>
       <c r="J150" s="6" t="n">
         <v>100.475758</v>
@@ -12178,7 +12178,7 @@
         <v>1.799034</v>
       </c>
       <c r="I151" s="9" t="n">
-        <v>101.037869</v>
+        <v>101.037505</v>
       </c>
       <c r="J151" s="9" t="n">
         <v>100.580672</v>
@@ -12260,7 +12260,7 @@
         <v>1.61457</v>
       </c>
       <c r="I152" s="6" t="n">
-        <v>101.11582</v>
+        <v>101.115454</v>
       </c>
       <c r="J152" s="6" t="n">
         <v>100.719477</v>
@@ -12342,7 +12342,7 @@
         <v>1.317286</v>
       </c>
       <c r="I153" s="9" t="n">
-        <v>101.210437</v>
+        <v>101.210179</v>
       </c>
       <c r="J153" s="9" t="n">
         <v>100.835074</v>
@@ -12424,7 +12424,7 @@
         <v>0.924436</v>
       </c>
       <c r="I154" s="6" t="n">
-        <v>101.26101</v>
+        <v>101.261029</v>
       </c>
       <c r="J154" s="6" t="n">
         <v>100.933444</v>
@@ -12506,7 +12506,7 @@
         <v>0.47135</v>
       </c>
       <c r="I155" s="9" t="n">
-        <v>101.245488</v>
+        <v>101.246048</v>
       </c>
       <c r="J155" s="9" t="n">
         <v>100.984415</v>
@@ -12588,7 +12588,7 @@
         <v>0.014593</v>
       </c>
       <c r="I156" s="6" t="n">
-        <v>101.16644</v>
+        <v>101.167912</v>
       </c>
       <c r="J156" s="6" t="n">
         <v>100.969963</v>
@@ -12670,7 +12670,7 @@
         <v>-0.403665</v>
       </c>
       <c r="I157" s="9" t="n">
-        <v>101.064022</v>
+        <v>101.066862</v>
       </c>
       <c r="J157" s="9" t="n">
         <v>100.897067</v>
@@ -12752,7 +12752,7 @@
         <v>-0.740707</v>
       </c>
       <c r="I158" s="6" t="n">
-        <v>100.968004</v>
+        <v>100.972643</v>
       </c>
       <c r="J158" s="6" t="n">
         <v>100.806436</v>
@@ -12834,7 +12834,7 @@
         <v>-0.986731</v>
       </c>
       <c r="I159" s="9" t="n">
-        <v>100.917017</v>
+        <v>100.923654</v>
       </c>
       <c r="J159" s="9" t="n">
         <v>100.707513</v>
@@ -12916,7 +12916,7 @@
         <v>-1.185722</v>
       </c>
       <c r="I160" s="6" t="n">
-        <v>100.869268</v>
+        <v>100.877502</v>
       </c>
       <c r="J160" s="6" t="n">
         <v>100.622354</v>
@@ -12998,7 +12998,7 @@
         <v>-1.380586</v>
       </c>
       <c r="I161" s="9" t="n">
-        <v>100.815835</v>
+        <v>100.824188</v>
       </c>
       <c r="J161" s="9" t="n">
         <v>100.58554</v>
@@ -13080,7 +13080,7 @@
         <v>-1.566156</v>
       </c>
       <c r="I162" s="6" t="n">
-        <v>100.791382</v>
+        <v>100.796721</v>
       </c>
       <c r="J162" s="6" t="n">
         <v>100.605765</v>
@@ -13162,7 +13162,7 @@
         <v>-1.690856</v>
       </c>
       <c r="I163" s="9" t="n">
-        <v>100.808215</v>
+        <v>100.805129</v>
       </c>
       <c r="J163" s="9" t="n">
         <v>100.669182</v>
@@ -13244,7 +13244,7 @@
         <v>-1.700833</v>
       </c>
       <c r="I164" s="6" t="n">
-        <v>100.821534</v>
+        <v>100.812927</v>
       </c>
       <c r="J164" s="6" t="n">
         <v>100.713813</v>
@@ -13326,7 +13326,7 @@
         <v>-1.586461</v>
       </c>
       <c r="I165" s="9" t="n">
-        <v>100.816181</v>
+        <v>100.80651</v>
       </c>
       <c r="J165" s="9" t="n">
         <v>100.711479</v>
@@ -13408,7 +13408,7 @@
         <v>-1.319657</v>
       </c>
       <c r="I166" s="6" t="n">
-        <v>100.804559</v>
+        <v>100.796721</v>
       </c>
       <c r="J166" s="6" t="n">
         <v>100.67648</v>
@@ -13490,7 +13490,7 @@
         <v>-0.892056</v>
       </c>
       <c r="I167" s="9" t="n">
-        <v>100.776298</v>
+        <v>100.771222</v>
       </c>
       <c r="J167" s="9" t="n">
         <v>100.629585</v>
@@ -13572,7 +13572,7 @@
         <v>-0.37921</v>
       </c>
       <c r="I168" s="6" t="n">
-        <v>100.737375</v>
+        <v>100.734875</v>
       </c>
       <c r="J168" s="6" t="n">
         <v>100.594698</v>
@@ -13654,7 +13654,7 @@
         <v>0.158621</v>
       </c>
       <c r="I169" s="9" t="n">
-        <v>100.67486</v>
+        <v>100.674693</v>
       </c>
       <c r="J169" s="9" t="n">
         <v>100.57889</v>
@@ -13736,7 +13736,7 @@
         <v>0.66266</v>
       </c>
       <c r="I170" s="6" t="n">
-        <v>100.609379</v>
+        <v>100.611636</v>
       </c>
       <c r="J170" s="6" t="n">
         <v>100.59143</v>
@@ -13818,7 +13818,7 @@
         <v>1.098231</v>
       </c>
       <c r="I171" s="9" t="n">
-        <v>100.576673</v>
+        <v>100.581618</v>
       </c>
       <c r="J171" s="9" t="n">
         <v>100.645437</v>
@@ -13900,7 +13900,7 @@
         <v>1.443658</v>
       </c>
       <c r="I172" s="6" t="n">
-        <v>100.6076</v>
+        <v>100.615156</v>
       </c>
       <c r="J172" s="6" t="n">
         <v>100.745986</v>
@@ -13982,7 +13982,7 @@
         <v>1.697455</v>
       </c>
       <c r="I173" s="9" t="n">
-        <v>100.716863</v>
+        <v>100.725985</v>
       </c>
       <c r="J173" s="9" t="n">
         <v>100.891905</v>
@@ -14064,7 +14064,7 @@
         <v>1.84997</v>
       </c>
       <c r="I174" s="6" t="n">
-        <v>100.883616</v>
+        <v>100.891431</v>
       </c>
       <c r="J174" s="6" t="n">
         <v>101.06454</v>
@@ -14146,7 +14146,7 @@
         <v>1.880127</v>
       </c>
       <c r="I175" s="9" t="n">
-        <v>101.093095</v>
+        <v>101.094376</v>
       </c>
       <c r="J175" s="9" t="n">
         <v>101.24947</v>
@@ -14228,7 +14228,7 @@
         <v>1.775975</v>
       </c>
       <c r="I176" s="6" t="n">
-        <v>101.334177</v>
+        <v>101.330232</v>
       </c>
       <c r="J176" s="6" t="n">
         <v>101.436306</v>
@@ -14310,7 +14310,7 @@
         <v>1.571862</v>
       </c>
       <c r="I177" s="9" t="n">
-        <v>101.574337</v>
+        <v>101.568173</v>
       </c>
       <c r="J177" s="9" t="n">
         <v>101.58721</v>
@@ -14392,7 +14392,7 @@
         <v>1.301668</v>
       </c>
       <c r="I178" s="6" t="n">
-        <v>101.76633</v>
+        <v>101.760268</v>
       </c>
       <c r="J178" s="6" t="n">
         <v>101.645436</v>
@@ -14474,7 +14474,7 @@
         <v>0.973898</v>
       </c>
       <c r="I179" s="9" t="n">
-        <v>101.902082</v>
+        <v>101.897252</v>
       </c>
       <c r="J179" s="9" t="n">
         <v>101.646348</v>
@@ -14556,7 +14556,7 @@
         <v>0.623231</v>
       </c>
       <c r="I180" s="6" t="n">
-        <v>101.986594</v>
+        <v>101.983351</v>
       </c>
       <c r="J180" s="6" t="n">
         <v>101.607516</v>
@@ -14638,7 +14638,7 @@
         <v>0.224557</v>
       </c>
       <c r="I181" s="9" t="n">
-        <v>102.025339</v>
+        <v>102.023788</v>
       </c>
       <c r="J181" s="9" t="n">
         <v>101.520731</v>
@@ -14720,7 +14720,7 @@
         <v>-0.300894</v>
       </c>
       <c r="I182" s="6" t="n">
-        <v>101.979362</v>
+        <v>101.979718</v>
       </c>
       <c r="J182" s="6" t="n">
         <v>101.345464</v>
@@ -14802,7 +14802,7 @@
         <v>-1.033128</v>
       </c>
       <c r="I183" s="9" t="n">
-        <v>101.787403</v>
+        <v>101.789952</v>
       </c>
       <c r="J183" s="9" t="n">
         <v>101.039437</v>
@@ -14884,7 +14884,7 @@
         <v>-2.010098</v>
       </c>
       <c r="I184" s="6" t="n">
-        <v>101.388268</v>
+        <v>101.39309</v>
       </c>
       <c r="J184" s="6" t="n">
         <v>100.573974</v>
@@ -14966,7 +14966,7 @@
         <v>-3.183883</v>
       </c>
       <c r="I185" s="9" t="n">
-        <v>100.740003</v>
+        <v>100.746446</v>
       </c>
       <c r="J185" s="9" t="n">
         <v>99.933902</v>
@@ -15048,7 +15048,7 @@
         <v>-4.402223</v>
       </c>
       <c r="I186" s="6" t="n">
-        <v>99.854777</v>
+        <v>99.86084099999999</v>
       </c>
       <c r="J186" s="6" t="n">
         <v>99.137591</v>
@@ -15130,7 +15130,7 @@
         <v>-5.428293</v>
       </c>
       <c r="I187" s="9" t="n">
-        <v>98.803917</v>
+        <v>98.80591</v>
       </c>
       <c r="J187" s="9" t="n">
         <v>98.270338</v>
@@ -15212,7 +15212,7 @@
         <v>-6.039035</v>
       </c>
       <c r="I188" s="6" t="n">
-        <v>97.781021</v>
+        <v>97.779023</v>
       </c>
       <c r="J188" s="6" t="n">
         <v>97.439446</v>
@@ -15294,7 +15294,7 @@
         <v>-6.152976</v>
       </c>
       <c r="I189" s="9" t="n">
-        <v>96.912764</v>
+        <v>96.908151</v>
       </c>
       <c r="J189" s="9" t="n">
         <v>96.731899</v>
@@ -15376,7 +15376,7 @@
         <v>-5.856765</v>
       </c>
       <c r="I190" s="6" t="n">
-        <v>96.304697</v>
+        <v>96.298877</v>
       </c>
       <c r="J190" s="6" t="n">
         <v>96.230408</v>
@@ -15458,7 +15458,7 @@
         <v>-5.308898</v>
       </c>
       <c r="I191" s="9" t="n">
-        <v>95.983831</v>
+        <v>95.977802</v>
       </c>
       <c r="J191" s="9" t="n">
         <v>95.960842</v>
@@ -15540,7 +15540,7 @@
         <v>-4.678465</v>
       </c>
       <c r="I192" s="6" t="n">
-        <v>95.90464900000001</v>
+        <v>95.89903700000001</v>
       </c>
       <c r="J192" s="6" t="n">
         <v>95.908733</v>
@@ -15622,7 +15622,7 @@
         <v>-4.050403</v>
       </c>
       <c r="I193" s="9" t="n">
-        <v>96.005684</v>
+        <v>96.000944</v>
       </c>
       <c r="J193" s="9" t="n">
         <v>96.043942</v>
@@ -15704,7 +15704,7 @@
         <v>-3.402282</v>
       </c>
       <c r="I194" s="6" t="n">
-        <v>96.23366</v>
+        <v>96.230237</v>
       </c>
       <c r="J194" s="6" t="n">
         <v>96.33393100000001</v>
@@ -15786,7 +15786,7 @@
         <v>-2.64907</v>
       </c>
       <c r="I195" s="9" t="n">
-        <v>96.556589</v>
+        <v>96.554963</v>
       </c>
       <c r="J195" s="9" t="n">
         <v>96.73128800000001</v>
@@ -15868,7 +15868,7 @@
         <v>-1.672549</v>
       </c>
       <c r="I196" s="6" t="n">
-        <v>96.971158</v>
+        <v>96.971681</v>
       </c>
       <c r="J196" s="6" t="n">
         <v>97.181674</v>
@@ -15950,7 +15950,7 @@
         <v>-0.449247</v>
       </c>
       <c r="I197" s="9" t="n">
-        <v>97.385548</v>
+        <v>97.38810100000001</v>
       </c>
       <c r="J197" s="9" t="n">
         <v>97.627257</v>
@@ -16032,7 +16032,7 @@
         <v>0.8953100000000001</v>
       </c>
       <c r="I198" s="6" t="n">
-        <v>97.700647</v>
+        <v>97.704125</v>
       </c>
       <c r="J198" s="6" t="n">
         <v>97.97762899999999</v>
@@ -16114,7 +16114,7 @@
         <v>2.126016</v>
       </c>
       <c r="I199" s="9" t="n">
-        <v>97.905906</v>
+        <v>97.908202</v>
       </c>
       <c r="J199" s="9" t="n">
         <v>98.228292</v>
@@ -16196,7 +16196,7 @@
         <v>3.024141</v>
       </c>
       <c r="I200" s="6" t="n">
-        <v>98.041636</v>
+        <v>98.04207</v>
       </c>
       <c r="J200" s="6" t="n">
         <v>98.40825700000001</v>
@@ -16278,7 +16278,7 @@
         <v>3.473318</v>
       </c>
       <c r="I201" s="9" t="n">
-        <v>98.13914200000001</v>
+        <v>98.137851</v>
       </c>
       <c r="J201" s="9" t="n">
         <v>98.53738800000001</v>
@@ -16360,7 +16360,7 @@
         <v>3.486595</v>
       </c>
       <c r="I202" s="6" t="n">
-        <v>98.23297599999999</v>
+        <v>98.230487</v>
       </c>
       <c r="J202" s="6" t="n">
         <v>98.64767399999999</v>
@@ -16442,7 +16442,7 @@
         <v>3.177294</v>
       </c>
       <c r="I203" s="9" t="n">
-        <v>98.324212</v>
+        <v>98.321157</v>
       </c>
       <c r="J203" s="9" t="n">
         <v>98.743802</v>
@@ -16524,7 +16524,7 @@
         <v>2.728927</v>
       </c>
       <c r="I204" s="6" t="n">
-        <v>98.41337300000001</v>
+        <v>98.410352</v>
       </c>
       <c r="J204" s="6" t="n">
         <v>98.82535300000001</v>
@@ -16606,7 +16606,7 @@
         <v>2.303085</v>
       </c>
       <c r="I205" s="9" t="n">
-        <v>98.515066</v>
+        <v>98.51249</v>
       </c>
       <c r="J205" s="9" t="n">
         <v>98.912744</v>
@@ -16688,7 +16688,7 @@
         <v>1.962204</v>
       </c>
       <c r="I206" s="6" t="n">
-        <v>98.641824</v>
+        <v>98.63995</v>
       </c>
       <c r="J206" s="6" t="n">
         <v>99.024647</v>
@@ -16770,7 +16770,7 @@
         <v>1.724518</v>
       </c>
       <c r="I207" s="9" t="n">
-        <v>98.786248</v>
+        <v>98.78519900000001</v>
       </c>
       <c r="J207" s="9" t="n">
         <v>99.16342400000001</v>
@@ -16852,7 +16852,7 @@
         <v>1.565608</v>
       </c>
       <c r="I208" s="6" t="n">
-        <v>98.92958</v>
+        <v>98.92934099999999</v>
       </c>
       <c r="J208" s="6" t="n">
         <v>99.303696</v>
@@ -16934,7 +16934,7 @@
         <v>1.469638</v>
       </c>
       <c r="I209" s="9" t="n">
-        <v>99.05066600000001</v>
+        <v>99.05103800000001</v>
       </c>
       <c r="J209" s="9" t="n">
         <v>99.4211</v>
@@ -17016,7 +17016,7 @@
         <v>1.424535</v>
       </c>
       <c r="I210" s="6" t="n">
-        <v>99.15240900000001</v>
+        <v>99.15291999999999</v>
       </c>
       <c r="J210" s="6" t="n">
         <v>99.50048</v>
@@ -17098,7 +17098,7 @@
         <v>1.421238</v>
       </c>
       <c r="I211" s="9" t="n">
-        <v>99.266676</v>
+        <v>99.266823</v>
       </c>
       <c r="J211" s="9" t="n">
         <v>99.588167</v>
@@ -17180,7 +17180,7 @@
         <v>1.428314</v>
       </c>
       <c r="I212" s="6" t="n">
-        <v>99.413782</v>
+        <v>99.41344599999999</v>
       </c>
       <c r="J212" s="6" t="n">
         <v>99.708342</v>
@@ -17262,7 +17262,7 @@
         <v>1.468908</v>
       </c>
       <c r="I213" s="9" t="n">
-        <v>99.59703</v>
+        <v>99.596323</v>
       </c>
       <c r="J213" s="9" t="n">
         <v>99.867265</v>
@@ -17344,7 +17344,7 @@
         <v>1.581265</v>
       </c>
       <c r="I214" s="6" t="n">
-        <v>99.802103</v>
+        <v>99.80120100000001</v>
       </c>
       <c r="J214" s="6" t="n">
         <v>100.050824</v>
@@ -17426,7 +17426,7 @@
         <v>1.767849</v>
       </c>
       <c r="I215" s="9" t="n">
-        <v>100.012104</v>
+        <v>100.0112</v>
       </c>
       <c r="J215" s="9" t="n">
         <v>100.242871</v>
@@ -17508,7 +17508,7 @@
         <v>1.970497</v>
       </c>
       <c r="I216" s="6" t="n">
-        <v>100.217411</v>
+        <v>100.216668</v>
       </c>
       <c r="J216" s="6" t="n">
         <v>100.429831</v>
@@ -17590,7 +17590,7 @@
         <v>2.127433</v>
       </c>
       <c r="I217" s="9" t="n">
-        <v>100.427568</v>
+        <v>100.427112</v>
       </c>
       <c r="J217" s="9" t="n">
         <v>100.607078</v>
@@ -17672,7 +17672,7 @@
         <v>2.233625</v>
       </c>
       <c r="I218" s="6" t="n">
-        <v>100.643096</v>
+        <v>100.643003</v>
       </c>
       <c r="J218" s="6" t="n">
         <v>100.778066</v>
@@ -17754,7 +17754,7 @@
         <v>2.259755</v>
       </c>
       <c r="I219" s="9" t="n">
-        <v>100.858339</v>
+        <v>100.858657</v>
       </c>
       <c r="J219" s="9" t="n">
         <v>100.951909</v>
@@ -17836,7 +17836,7 @@
         <v>2.188377</v>
       </c>
       <c r="I220" s="6" t="n">
-        <v>101.053014</v>
+        <v>101.053717</v>
       </c>
       <c r="J220" s="6" t="n">
         <v>101.125429</v>
@@ -17918,7 +17918,7 @@
         <v>2.013833</v>
       </c>
       <c r="I221" s="9" t="n">
-        <v>101.217562</v>
+        <v>101.218561</v>
       </c>
       <c r="J221" s="9" t="n">
         <v>101.294647</v>
@@ -18000,7 +18000,7 @@
         <v>1.74565</v>
       </c>
       <c r="I222" s="6" t="n">
-        <v>101.361019</v>
+        <v>101.362091</v>
       </c>
       <c r="J222" s="6" t="n">
         <v>101.453106</v>
@@ -18082,7 +18082,7 @@
         <v>1.421516</v>
       </c>
       <c r="I223" s="9" t="n">
-        <v>101.473835</v>
+        <v>101.474718</v>
       </c>
       <c r="J223" s="9" t="n">
         <v>101.575015</v>
@@ -18164,7 +18164,7 @@
         <v>1.042722</v>
       </c>
       <c r="I224" s="6" t="n">
-        <v>101.529729</v>
+        <v>101.530323</v>
       </c>
       <c r="J224" s="6" t="n">
         <v>101.629263</v>
@@ -18246,7 +18246,7 @@
         <v>0.56193</v>
       </c>
       <c r="I225" s="9" t="n">
-        <v>101.513487</v>
+        <v>101.513796</v>
       </c>
       <c r="J225" s="9" t="n">
         <v>101.606145</v>
@@ -18328,7 +18328,7 @@
         <v>-0.042958</v>
       </c>
       <c r="I226" s="6" t="n">
-        <v>101.436028</v>
+        <v>101.436115</v>
       </c>
       <c r="J226" s="6" t="n">
         <v>101.522112</v>
@@ -18410,7 +18410,7 @@
         <v>-0.74291</v>
       </c>
       <c r="I227" s="9" t="n">
-        <v>101.322242</v>
+        <v>101.32219</v>
       </c>
       <c r="J227" s="9" t="n">
         <v>101.399479</v>
@@ -18492,7 +18492,7 @@
         <v>-1.478119</v>
       </c>
       <c r="I228" s="6" t="n">
-        <v>101.198958</v>
+        <v>101.198866</v>
       </c>
       <c r="J228" s="6" t="n">
         <v>101.27543</v>
@@ -18574,7 +18574,7 @@
         <v>-2.178851</v>
       </c>
       <c r="I229" s="9" t="n">
-        <v>101.071269</v>
+        <v>101.071206</v>
       </c>
       <c r="J229" s="9" t="n">
         <v>101.166822</v>
@@ -18656,7 +18656,7 @@
         <v>-2.725813</v>
       </c>
       <c r="I230" s="6" t="n">
-        <v>100.945175</v>
+        <v>100.945233</v>
       </c>
       <c r="J230" s="6" t="n">
         <v>101.076543</v>
@@ -18738,7 +18738,7 @@
         <v>-3.031556</v>
       </c>
       <c r="I231" s="9" t="n">
-        <v>100.839905</v>
+        <v>100.840135</v>
       </c>
       <c r="J231" s="9" t="n">
         <v>101.009401</v>
@@ -18820,7 +18820,7 @@
         <v>-3.101772</v>
       </c>
       <c r="I232" s="6" t="n">
-        <v>100.76906</v>
+        <v>100.769483</v>
       </c>
       <c r="J232" s="6" t="n">
         <v>100.963615</v>
@@ -18902,7 +18902,7 @@
         <v>-2.977164</v>
       </c>
       <c r="I233" s="9" t="n">
-        <v>100.7314</v>
+        <v>100.73197</v>
       </c>
       <c r="J233" s="9" t="n">
         <v>100.933077</v>
@@ -18984,7 +18984,7 @@
         <v>-2.678502</v>
       </c>
       <c r="I234" s="6" t="n">
-        <v>100.710807</v>
+        <v>100.711427</v>
       </c>
       <c r="J234" s="6" t="n">
         <v>100.900827</v>
@@ -19066,7 +19066,7 @@
         <v>-2.239978</v>
       </c>
       <c r="I235" s="9" t="n">
-        <v>100.688715</v>
+        <v>100.68923</v>
       </c>
       <c r="J235" s="9" t="n">
         <v>100.859093</v>
@@ -19148,7 +19148,7 @@
         <v>-1.682236</v>
       </c>
       <c r="I236" s="6" t="n">
-        <v>100.662718</v>
+        <v>100.66304</v>
       </c>
       <c r="J236" s="6" t="n">
         <v>100.801506</v>
@@ -19230,7 +19230,7 @@
         <v>-1.040581</v>
       </c>
       <c r="I237" s="9" t="n">
-        <v>100.631436</v>
+        <v>100.631543</v>
       </c>
       <c r="J237" s="9" t="n">
         <v>100.724126</v>
@@ -19312,7 +19312,7 @@
         <v>-0.378666</v>
       </c>
       <c r="I238" s="6" t="n">
-        <v>100.598586</v>
+        <v>100.5985</v>
       </c>
       <c r="J238" s="6" t="n">
         <v>100.626731</v>
@@ -19394,7 +19394,7 @@
         <v>0.272381</v>
       </c>
       <c r="I239" s="9" t="n">
-        <v>100.572942</v>
+        <v>100.572752</v>
       </c>
       <c r="J239" s="9" t="n">
         <v>100.537224</v>
@@ -19476,7 +19476,7 @@
         <v>0.918393</v>
       </c>
       <c r="I240" s="6" t="n">
-        <v>100.57487</v>
+        <v>100.574672</v>
       </c>
       <c r="J240" s="6" t="n">
         <v>100.484435</v>
@@ -19558,7 +19558,7 @@
         <v>1.547201</v>
       </c>
       <c r="I241" s="9" t="n">
-        <v>100.610989</v>
+        <v>100.610868</v>
       </c>
       <c r="J241" s="9" t="n">
         <v>100.484262</v>
@@ -19640,7 +19640,7 @@
         <v>2.102219</v>
       </c>
       <c r="I242" s="6" t="n">
-        <v>100.693563</v>
+        <v>100.693582</v>
       </c>
       <c r="J242" s="6" t="n">
         <v>100.542528</v>
@@ -19722,7 +19722,7 @@
         <v>2.535452</v>
       </c>
       <c r="I243" s="9" t="n">
-        <v>100.822833</v>
+        <v>100.823028</v>
       </c>
       <c r="J243" s="9" t="n">
         <v>100.656953</v>
@@ -19804,7 +19804,7 @@
         <v>2.819634</v>
       </c>
       <c r="I244" s="6" t="n">
-        <v>101.006919</v>
+        <v>101.0073</v>
       </c>
       <c r="J244" s="6" t="n">
         <v>100.838987</v>
@@ -19886,7 +19886,7 @@
         <v>2.931161</v>
       </c>
       <c r="I245" s="9" t="n">
-        <v>101.237319</v>
+        <v>101.237885</v>
       </c>
       <c r="J245" s="9" t="n">
         <v>101.079846</v>
@@ -19968,7 +19968,7 @@
         <v>2.859679</v>
       </c>
       <c r="I246" s="6" t="n">
-        <v>101.476854</v>
+        <v>101.477569</v>
       </c>
       <c r="J246" s="6" t="n">
         <v>101.356756</v>
@@ -20050,7 +20050,7 @@
         <v>2.615476</v>
       </c>
       <c r="I247" s="9" t="n">
-        <v>101.669203</v>
+        <v>101.67003</v>
       </c>
       <c r="J247" s="9" t="n">
         <v>101.629364</v>
@@ -20132,7 +20132,7 @@
         <v>2.252237</v>
       </c>
       <c r="I248" s="6" t="n">
-        <v>101.817562</v>
+        <v>101.818391</v>
       </c>
       <c r="J248" s="6" t="n">
         <v>101.859741</v>
@@ -20214,7 +20214,7 @@
         <v>1.827948</v>
       </c>
       <c r="I249" s="9" t="n">
-        <v>101.938496</v>
+        <v>101.939255</v>
       </c>
       <c r="J249" s="9" t="n">
         <v>102.033347</v>
@@ -20296,7 +20296,7 @@
         <v>1.427844</v>
       </c>
       <c r="I250" s="6" t="n">
-        <v>102.037514</v>
+        <v>102.038192</v>
       </c>
       <c r="J250" s="6" t="n">
         <v>102.153983</v>
@@ -20378,7 +20378,7 @@
         <v>1.107829</v>
       </c>
       <c r="I251" s="9" t="n">
-        <v>102.10011</v>
+        <v>102.100712</v>
       </c>
       <c r="J251" s="9" t="n">
         <v>102.207856</v>
@@ -20460,7 +20460,7 @@
         <v>0.819765</v>
       </c>
       <c r="I252" s="6" t="n">
-        <v>102.105857</v>
+        <v>102.106384</v>
       </c>
       <c r="J252" s="6" t="n">
         <v>102.172985</v>
@@ -20542,7 +20542,7 @@
         <v>0.525408</v>
       </c>
       <c r="I253" s="9" t="n">
-        <v>102.04413</v>
+        <v>102.044619</v>
       </c>
       <c r="J253" s="9" t="n">
         <v>102.038678</v>
@@ -20624,7 +20624,7 @@
         <v>0.15148</v>
       </c>
       <c r="I254" s="6" t="n">
-        <v>101.927567</v>
+        <v>101.928044</v>
       </c>
       <c r="J254" s="6" t="n">
         <v>101.830025</v>
@@ -20706,7 +20706,7 @@
         <v>-0.333081</v>
       </c>
       <c r="I255" s="9" t="n">
-        <v>101.76773</v>
+        <v>101.768205</v>
       </c>
       <c r="J255" s="9" t="n">
         <v>101.576864</v>
@@ -20788,7 +20788,7 @@
         <v>-0.873067</v>
       </c>
       <c r="I256" s="6" t="n">
-        <v>101.575308</v>
+        <v>101.575786</v>
       </c>
       <c r="J256" s="6" t="n">
         <v>101.309553</v>
@@ -20870,7 +20870,7 @@
         <v>-1.394467</v>
       </c>
       <c r="I257" s="9" t="n">
-        <v>101.368384</v>
+        <v>101.368872</v>
       </c>
       <c r="J257" s="9" t="n">
         <v>101.067248</v>
@@ -20952,7 +20952,7 @@
         <v>-1.826922</v>
       </c>
       <c r="I258" s="6" t="n">
-        <v>101.166747</v>
+        <v>101.167234</v>
       </c>
       <c r="J258" s="6" t="n">
         <v>100.878459</v>
@@ -21034,7 +21034,7 @@
         <v>-2.124669</v>
       </c>
       <c r="I259" s="9" t="n">
-        <v>100.964793</v>
+        <v>100.96525</v>
       </c>
       <c r="J259" s="9" t="n">
         <v>100.698828</v>
@@ -21116,7 +21116,7 @@
         <v>-2.271757</v>
       </c>
       <c r="I260" s="6" t="n">
-        <v>100.775288</v>
+        <v>100.77562</v>
       </c>
       <c r="J260" s="6" t="n">
         <v>100.521928</v>
@@ -21198,7 +21198,7 @@
         <v>-2.250192</v>
       </c>
       <c r="I261" s="9" t="n">
-        <v>100.605748</v>
+        <v>100.60594</v>
       </c>
       <c r="J261" s="9" t="n">
         <v>100.364414</v>
@@ -21280,7 +21280,7 @@
         <v>-2.098118</v>
       </c>
       <c r="I262" s="6" t="n">
-        <v>100.458358</v>
+        <v>100.458422</v>
       </c>
       <c r="J262" s="6" t="n">
         <v>100.236646</v>
@@ -21362,7 +21362,7 @@
         <v>-1.922347</v>
       </c>
       <c r="I263" s="9" t="n">
-        <v>100.327345</v>
+        <v>100.327304</v>
       </c>
       <c r="J263" s="9" t="n">
         <v>100.122365</v>
@@ -21444,7 +21444,7 @@
         <v>-1.738698</v>
       </c>
       <c r="I264" s="6" t="n">
-        <v>100.199074</v>
+        <v>100.198943</v>
       </c>
       <c r="J264" s="6" t="n">
         <v>100.00604</v>
@@ -21526,7 +21526,7 @@
         <v>-1.541135</v>
       </c>
       <c r="I265" s="9" t="n">
-        <v>100.059166</v>
+        <v>100.058939</v>
       </c>
       <c r="J265" s="9" t="n">
         <v>99.86980200000001</v>
@@ -21608,7 +21608,7 @@
         <v>-1.280844</v>
       </c>
       <c r="I266" s="6" t="n">
-        <v>99.88954099999999</v>
+        <v>99.88920400000001</v>
       </c>
       <c r="J266" s="6" t="n">
         <v>99.699366</v>
@@ -21690,7 +21690,7 @@
         <v>-0.886089</v>
       </c>
       <c r="I267" s="9" t="n">
-        <v>99.692621</v>
+        <v>99.69220199999999</v>
       </c>
       <c r="J267" s="9" t="n">
         <v>99.489704</v>
@@ -21772,7 +21772,7 @@
         <v>-0.397285</v>
       </c>
       <c r="I268" s="6" t="n">
-        <v>99.493555</v>
+        <v>99.49310699999999</v>
       </c>
       <c r="J268" s="6" t="n">
         <v>99.265398</v>
@@ -21854,7 +21854,7 @@
         <v>0.112656</v>
       </c>
       <c r="I269" s="9" t="n">
-        <v>99.305325</v>
+        <v>99.304894</v>
       </c>
       <c r="J269" s="9" t="n">
         <v>99.032257</v>
@@ -21936,7 +21936,7 @@
         <v>0.5478460000000001</v>
       </c>
       <c r="I270" s="6" t="n">
-        <v>99.15286500000001</v>
+        <v>99.152514</v>
       </c>
       <c r="J270" s="6" t="n">
         <v>98.817561</v>
@@ -22018,7 +22018,7 @@
         <v>0.837765</v>
       </c>
       <c r="I271" s="9" t="n">
-        <v>99.07285299999999</v>
+        <v>99.072581</v>
       </c>
       <c r="J271" s="9" t="n">
         <v>98.66233200000001</v>
@@ -22100,7 +22100,7 @@
         <v>0.932845</v>
       </c>
       <c r="I272" s="6" t="n">
-        <v>99.072687</v>
+        <v>99.072367</v>
       </c>
       <c r="J272" s="6" t="n">
         <v>98.60550499999999</v>
@@ -22182,7 +22182,7 @@
         <v>0.783791</v>
       </c>
       <c r="I273" s="9" t="n">
-        <v>99.126738</v>
+        <v>99.12631399999999</v>
       </c>
       <c r="J273" s="9" t="n">
         <v>98.63034500000001</v>
@@ -22264,7 +22264,7 @@
         <v>0.418483</v>
       </c>
       <c r="I274" s="6" t="n">
-        <v>99.203604</v>
+        <v>99.20308199999999</v>
       </c>
       <c r="J274" s="6" t="n">
         <v>98.69931</v>
@@ -22346,7 +22346,7 @@
         <v>-0.055686</v>
       </c>
       <c r="I275" s="9" t="n">
-        <v>99.287351</v>
+        <v>99.28674100000001</v>
       </c>
       <c r="J275" s="9" t="n">
         <v>98.802026</v>
@@ -22428,7 +22428,7 @@
         <v>-0.530034</v>
       </c>
       <c r="I276" s="6" t="n">
-        <v>99.36861500000001</v>
+        <v>99.367966</v>
       </c>
       <c r="J276" s="6" t="n">
         <v>98.924543</v>
@@ -22510,7 +22510,7 @@
         <v>-0.941342</v>
       </c>
       <c r="I277" s="9" t="n">
-        <v>99.430807</v>
+        <v>99.43016799999999</v>
       </c>
       <c r="J277" s="9" t="n">
         <v>99.046228</v>
@@ -22592,7 +22592,7 @@
         <v>-1.301651</v>
       </c>
       <c r="I278" s="6" t="n">
-        <v>99.454221</v>
+        <v>99.45363399999999</v>
       </c>
       <c r="J278" s="6" t="n">
         <v>99.135785</v>
@@ -22674,7 +22674,7 @@
         <v>-1.664956</v>
       </c>
       <c r="I279" s="9" t="n">
-        <v>99.43778399999999</v>
+        <v>99.43727199999999</v>
       </c>
       <c r="J279" s="9" t="n">
         <v>99.174409</v>
@@ -22756,7 +22756,7 @@
         <v>-2.037024</v>
       </c>
       <c r="I280" s="6" t="n">
-        <v>99.38231500000001</v>
+        <v>99.381894</v>
       </c>
       <c r="J280" s="6" t="n">
         <v>99.144828</v>
@@ -22838,7 +22838,7 @@
         <v>-2.405</v>
       </c>
       <c r="I281" s="9" t="n">
-        <v>99.305403</v>
+        <v>99.305072</v>
       </c>
       <c r="J281" s="9" t="n">
         <v>99.059608</v>
@@ -22920,7 +22920,7 @@
         <v>-2.701576</v>
       </c>
       <c r="I282" s="6" t="n">
-        <v>99.216711</v>
+        <v>99.21643299999999</v>
       </c>
       <c r="J282" s="6" t="n">
         <v>98.961314</v>
@@ -23002,7 +23002,7 @@
         <v>-2.832749</v>
       </c>
       <c r="I283" s="9" t="n">
-        <v>99.120822</v>
+        <v>99.12051</v>
       </c>
       <c r="J283" s="9" t="n">
         <v>98.89430900000001</v>
@@ -23084,7 +23084,7 @@
         <v>-2.719545</v>
       </c>
       <c r="I284" s="6" t="n">
-        <v>99.015102</v>
+        <v>99.01464</v>
       </c>
       <c r="J284" s="6" t="n">
         <v>98.847026</v>
@@ -23166,7 +23166,7 @@
         <v>-2.30242</v>
       </c>
       <c r="I285" s="9" t="n">
-        <v>98.914725</v>
+        <v>98.91411100000001</v>
       </c>
       <c r="J285" s="9" t="n">
         <v>98.819878</v>
@@ -23248,7 +23248,7 @@
         <v>-1.646322</v>
       </c>
       <c r="I286" s="6" t="n">
-        <v>98.826447</v>
+        <v>98.82570800000001</v>
       </c>
       <c r="J286" s="6" t="n">
         <v>98.80480300000001</v>
@@ -23330,7 +23330,7 @@
         <v>-0.848732</v>
       </c>
       <c r="I287" s="9" t="n">
-        <v>98.755296</v>
+        <v>98.75447800000001</v>
       </c>
       <c r="J287" s="9" t="n">
         <v>98.79048</v>
@@ -23412,7 +23412,7 @@
         <v>-0.055501</v>
       </c>
       <c r="I288" s="6" t="n">
-        <v>98.69419499999999</v>
+        <v>98.69333899999999</v>
       </c>
       <c r="J288" s="6" t="n">
         <v>98.769066</v>
@@ -23494,7 +23494,7 @@
         <v>0.641625</v>
       </c>
       <c r="I289" s="9" t="n">
-        <v>98.654949</v>
+        <v>98.654096</v>
       </c>
       <c r="J289" s="9" t="n">
         <v>98.752287</v>
@@ -23576,7 +23576,7 @@
         <v>1.2337</v>
       </c>
       <c r="I290" s="6" t="n">
-        <v>98.668381</v>
+        <v>98.667575</v>
       </c>
       <c r="J290" s="6" t="n">
         <v>98.760458</v>
@@ -23658,7 +23658,7 @@
         <v>1.716854</v>
       </c>
       <c r="I291" s="9" t="n">
-        <v>98.745349</v>
+        <v>98.74463900000001</v>
       </c>
       <c r="J291" s="9" t="n">
         <v>98.811789</v>
@@ -23740,7 +23740,7 @@
         <v>2.099951</v>
       </c>
       <c r="I292" s="6" t="n">
-        <v>98.882288</v>
+        <v>98.881702</v>
       </c>
       <c r="J292" s="6" t="n">
         <v>98.910783</v>
@@ -23822,7 +23822,7 @@
         <v>2.408112</v>
       </c>
       <c r="I293" s="9" t="n">
-        <v>99.06447900000001</v>
+        <v>99.064059</v>
       </c>
       <c r="J293" s="9" t="n">
         <v>99.06177</v>
@@ -23904,7 +23904,7 @@
         <v>2.619649</v>
       </c>
       <c r="I294" s="6" t="n">
-        <v>99.25767399999999</v>
+        <v>99.257424</v>
       </c>
       <c r="J294" s="6" t="n">
         <v>99.23747899999999</v>
@@ -23988,7 +23988,7 @@
         <v>2.710678</v>
       </c>
       <c r="I295" s="9" t="n">
-        <v>99.435543</v>
+        <v>99.435406</v>
       </c>
       <c r="J295" s="9" t="n">
         <v>99.416667</v>
@@ -24072,7 +24072,7 @@
         <v>2.610011</v>
       </c>
       <c r="I296" s="6" t="n">
-        <v>99.57784100000001</v>
+        <v>99.577686</v>
       </c>
       <c r="J296" s="6" t="n">
         <v>99.57662000000001</v>
@@ -24156,7 +24156,7 @@
         <v>2.313159</v>
       </c>
       <c r="I297" s="9" t="n">
-        <v>99.66283</v>
+        <v>99.66256799999999</v>
       </c>
       <c r="J297" s="9" t="n">
         <v>99.68022499999999</v>
@@ -24240,7 +24240,7 @@
         <v>1.892023</v>
       </c>
       <c r="I298" s="6" t="n">
-        <v>99.698207</v>
+        <v>99.69778599999999</v>
       </c>
       <c r="J298" s="6" t="n">
         <v>99.725082</v>
@@ -24324,7 +24324,7 @@
         <v>1.421045</v>
       </c>
       <c r="I299" s="9" t="n">
-        <v>99.695364</v>
+        <v>99.69480799999999</v>
       </c>
       <c r="J299" s="9" t="n">
         <v>99.726629</v>
@@ -24408,7 +24408,7 @@
         <v>0.985465</v>
       </c>
       <c r="I300" s="6" t="n">
-        <v>99.66714</v>
+        <v>99.66650300000001</v>
       </c>
       <c r="J300" s="6" t="n">
         <v>99.696996</v>
@@ -24492,7 +24492,7 @@
         <v>0.631534</v>
       </c>
       <c r="I301" s="9" t="n">
-        <v>99.64004199999999</v>
+        <v>99.63942</v>
       </c>
       <c r="J301" s="9" t="n">
         <v>99.659678</v>
@@ -24576,7 +24576,7 @@
         <v>0.359592</v>
       </c>
       <c r="I302" s="6" t="n">
-        <v>99.626394</v>
+        <v>99.625888</v>
       </c>
       <c r="J302" s="6" t="n">
         <v>99.630871</v>
@@ -24660,7 +24660,7 @@
         <v>0.149196</v>
       </c>
       <c r="I303" s="9" t="n">
-        <v>99.62969</v>
+        <v>99.62936500000001</v>
       </c>
       <c r="J303" s="9" t="n">
         <v>99.616765</v>
@@ -24744,7 +24744,7 @@
         <v>-0.004707</v>
       </c>
       <c r="I304" s="6" t="n">
-        <v>99.638194</v>
+        <v>99.63805499999999</v>
       </c>
       <c r="J304" s="6" t="n">
         <v>99.61432499999999</v>
@@ -24828,7 +24828,7 @@
         <v>-0.122263</v>
       </c>
       <c r="I305" s="9" t="n">
-        <v>99.62995100000001</v>
+        <v>99.62995600000001</v>
       </c>
       <c r="J305" s="9" t="n">
         <v>99.619725</v>
@@ -24912,7 +24912,7 @@
         <v>-0.21053</v>
       </c>
       <c r="I306" s="6" t="n">
-        <v>99.600236</v>
+        <v>99.600291</v>
       </c>
       <c r="J306" s="6" t="n">
         <v>99.625196</v>
@@ -24996,7 +24996,7 @@
         <v>-0.314184</v>
       </c>
       <c r="I307" s="9" t="n">
-        <v>99.551689</v>
+        <v>99.551695</v>
       </c>
       <c r="J307" s="9" t="n">
         <v>99.623008</v>
@@ -25080,7 +25080,7 @@
         <v>-0.389532</v>
       </c>
       <c r="I308" s="6" t="n">
-        <v>99.493551</v>
+        <v>99.493397</v>
       </c>
       <c r="J308" s="6" t="n">
         <v>99.608045</v>
@@ -25164,7 +25164,7 @@
         <v>-0.416353</v>
       </c>
       <c r="I309" s="9" t="n">
-        <v>99.445517</v>
+        <v>99.445108</v>
       </c>
       <c r="J309" s="9" t="n">
         <v>99.587181</v>
@@ -25248,7 +25248,7 @@
         <v>-0.369342</v>
       </c>
       <c r="I310" s="6" t="n">
-        <v>99.41868599999999</v>
+        <v>99.41798900000001</v>
       </c>
       <c r="J310" s="6" t="n">
         <v>99.567351</v>
@@ -25332,7 +25332,7 @@
         <v>-0.250815</v>
       </c>
       <c r="I311" s="9" t="n">
-        <v>99.43216099999999</v>
+        <v>99.43122099999999</v>
       </c>
       <c r="J311" s="9" t="n">
         <v>99.56322</v>
@@ -25416,7 +25416,7 @@
         <v>-0.084081</v>
       </c>
       <c r="I312" s="6" t="n">
-        <v>99.51751</v>
+        <v>99.516485</v>
       </c>
       <c r="J312" s="6" t="n">
         <v>99.623222</v>
@@ -25500,7 +25500,7 @@
         <v>0.103705</v>
       </c>
       <c r="I313" s="9" t="n">
-        <v>99.678454</v>
+        <v>99.67756199999999</v>
       </c>
       <c r="J313" s="9" t="n">
         <v>99.784924</v>
@@ -25584,7 +25584,7 @@
         <v>0.284457</v>
       </c>
       <c r="I314" s="6" t="n">
-        <v>99.890883</v>
+        <v>99.89036</v>
       </c>
       <c r="J314" s="6" t="n">
         <v>100.018898</v>
@@ -25668,7 +25668,7 @@
         <v>0.46098</v>
       </c>
       <c r="I315" s="9" t="n">
-        <v>100.135256</v>
+        <v>100.135263</v>
       </c>
       <c r="J315" s="9" t="n">
         <v>100.29486</v>
@@ -25752,7 +25752,7 @@
         <v>0.621958</v>
       </c>
       <c r="I316" s="6" t="n">
-        <v>100.395182</v>
+        <v>100.395809</v>
       </c>
       <c r="J316" s="6" t="n">
         <v>100.586342</v>
@@ -25836,7 +25836,7 @@
         <v>0.770973</v>
       </c>
       <c r="I317" s="9" t="n">
-        <v>100.644594</v>
+        <v>100.645775</v>
       </c>
       <c r="J317" s="9" t="n">
         <v>100.855263</v>
@@ -25920,7 +25920,7 @@
         <v>0.917279</v>
       </c>
       <c r="I318" s="6" t="n">
-        <v>100.85787</v>
+        <v>100.859389</v>
       </c>
       <c r="J318" s="6" t="n">
         <v>101.075482</v>
@@ -26004,7 +26004,7 @@
         <v>1.081921</v>
       </c>
       <c r="I319" s="9" t="n">
-        <v>101.009495</v>
+        <v>101.01097</v>
       </c>
       <c r="J319" s="9" t="n">
         <v>101.250123</v>
@@ -26088,7 +26088,7 @@
         <v>1.236931</v>
       </c>
       <c r="I320" s="6" t="n">
-        <v>101.123711</v>
+        <v>101.124731</v>
       </c>
       <c r="J320" s="6" t="n">
         <v>101.400839</v>
@@ -26172,7 +26172,7 @@
         <v>1.354622</v>
       </c>
       <c r="I321" s="9" t="n">
-        <v>101.21678</v>
+        <v>101.216997</v>
       </c>
       <c r="J321" s="9" t="n">
         <v>101.52941</v>
@@ -26256,7 +26256,7 @@
         <v>1.417111</v>
       </c>
       <c r="I322" s="6" t="n">
-        <v>101.286351</v>
+        <v>101.285622</v>
       </c>
       <c r="J322" s="6" t="n">
         <v>101.634813</v>
@@ -26340,7 +26340,7 @@
         <v>1.424053</v>
       </c>
       <c r="I323" s="9" t="n">
-        <v>101.320251</v>
+        <v>101.318695</v>
       </c>
       <c r="J323" s="9" t="n">
         <v>101.704394</v>
@@ -26424,7 +26424,7 @@
         <v>1.398341</v>
       </c>
       <c r="I324" s="6" t="n">
-        <v>101.324999</v>
+        <v>101.323058</v>
       </c>
       <c r="J324" s="6" t="n">
         <v>101.736751</v>
@@ -26508,7 +26508,7 @@
         <v>1.358989</v>
       </c>
       <c r="I325" s="9" t="n">
-        <v>101.312037</v>
+        <v>101.31054</v>
       </c>
       <c r="J325" s="9" t="n">
         <v>101.736143</v>
@@ -26592,7 +26592,7 @@
         <v>1.316018</v>
       </c>
       <c r="I326" s="6" t="n">
-        <v>101.289823</v>
+        <v>101.28921</v>
       </c>
       <c r="J326" s="6" t="n">
         <v>101.705753</v>
@@ -26676,7 +26676,7 @@
         <v>1.265412</v>
       </c>
       <c r="I327" s="9" t="n">
-        <v>101.269616</v>
+        <v>101.270115</v>
       </c>
       <c r="J327" s="9" t="n">
         <v>101.661041</v>
@@ -26760,7 +26760,7 @@
         <v>1.209236</v>
       </c>
       <c r="I328" s="6" t="n">
-        <v>101.260163</v>
+        <v>101.261775</v>
       </c>
       <c r="J328" s="6" t="n">
         <v>101.617399</v>
@@ -26844,7 +26844,7 @@
         <v>1.158347</v>
       </c>
       <c r="I329" s="9" t="n">
-        <v>101.275097</v>
+        <v>101.2776</v>
       </c>
       <c r="J329" s="9" t="n">
         <v>101.591129</v>
@@ -26928,7 +26928,7 @@
         <v>1.124364</v>
       </c>
       <c r="I330" s="6" t="n">
-        <v>101.315538</v>
+        <v>101.31848</v>
       </c>
       <c r="J330" s="6" t="n">
         <v>101.606839</v>
@@ -27012,7 +27012,7 @@
         <v>1.106862</v>
       </c>
       <c r="I331" s="9" t="n">
-        <v>101.381979</v>
+        <v>101.384717</v>
       </c>
       <c r="J331" s="9" t="n">
         <v>101.663269</v>
@@ -27096,7 +27096,7 @@
         <v>1.10764</v>
       </c>
       <c r="I332" s="6" t="n">
-        <v>101.469961</v>
+        <v>101.471889</v>
       </c>
       <c r="J332" s="6" t="n">
         <v>101.733652</v>
@@ -27180,7 +27180,7 @@
         <v>1.12308</v>
       </c>
       <c r="I333" s="9" t="n">
-        <v>101.563269</v>
+        <v>101.563915</v>
       </c>
       <c r="J333" s="9" t="n">
         <v>101.785554</v>
@@ -27264,7 +27264,7 @@
         <v>1.126861</v>
       </c>
       <c r="I334" s="6" t="n">
-        <v>101.645022</v>
+        <v>101.644169</v>
       </c>
       <c r="J334" s="6" t="n">
         <v>101.81014</v>
@@ -27348,7 +27348,7 @@
         <v>1.116865</v>
       </c>
       <c r="I335" s="9" t="n">
-        <v>101.703883</v>
+        <v>101.701789</v>
       </c>
       <c r="J335" s="9" t="n">
         <v>101.807362</v>
@@ -27432,7 +27432,7 @@
         <v>1.081767</v>
       </c>
       <c r="I336" s="6" t="n">
-        <v>101.732412</v>
+        <v>101.729719</v>
       </c>
       <c r="J336" s="6" t="n">
         <v>101.783489</v>
@@ -27516,7 +27516,7 @@
         <v>1.002841</v>
       </c>
       <c r="I337" s="9" t="n">
-        <v>101.734915</v>
+        <v>101.732965</v>
       </c>
       <c r="J337" s="9" t="n">
         <v>101.748871</v>
@@ -27600,7 +27600,7 @@
         <v>0.885329</v>
       </c>
       <c r="I338" s="6" t="n">
-        <v>101.714332</v>
+        <v>101.713688</v>
       </c>
       <c r="J338" s="6" t="n">
         <v>101.718057</v>
@@ -27684,7 +27684,7 @@
         <v>0.709975</v>
       </c>
       <c r="I339" s="9" t="n">
-        <v>101.677054</v>
+        <v>101.677889</v>
       </c>
       <c r="J339" s="9" t="n">
         <v>101.693356</v>
@@ -27768,7 +27768,7 @@
         <v>0.48019</v>
       </c>
       <c r="I340" s="6" t="n">
-        <v>101.638798</v>
+        <v>101.641017</v>
       </c>
       <c r="J340" s="6" t="n">
         <v>101.686789</v>
@@ -27852,7 +27852,7 @@
         <v>0.213133</v>
       </c>
       <c r="I341" s="9" t="n">
-        <v>101.618118</v>
+        <v>101.621402</v>
       </c>
       <c r="J341" s="9" t="n">
         <v>101.708914</v>
@@ -27936,7 +27936,7 @@
         <v>-0.08151899999999999</v>
       </c>
       <c r="I342" s="6" t="n">
-        <v>101.620766</v>
+        <v>101.624581</v>
       </c>
       <c r="J342" s="6" t="n">
         <v>101.745379</v>
@@ -28020,7 +28020,7 @@
         <v>-0.388818</v>
       </c>
       <c r="I343" s="9" t="n">
-        <v>101.639652</v>
+        <v>101.643121</v>
       </c>
       <c r="J343" s="9" t="n">
         <v>101.776216</v>
@@ -28104,7 +28104,7 @@
         <v>-0.69158</v>
       </c>
       <c r="I344" s="6" t="n">
-        <v>101.673783</v>
+        <v>101.676121</v>
       </c>
       <c r="J344" s="6" t="n">
         <v>101.765782</v>
@@ -28188,7 +28188,7 @@
         <v>-1.009736</v>
       </c>
       <c r="I345" s="9" t="n">
-        <v>101.729031</v>
+        <v>101.729675</v>
       </c>
       <c r="J345" s="9" t="n">
         <v>101.733667</v>
@@ -28272,7 +28272,7 @@
         <v>-1.368634</v>
       </c>
       <c r="I346" s="6" t="n">
-        <v>101.758898</v>
+        <v>101.757584</v>
       </c>
       <c r="J346" s="6" t="n">
         <v>101.675375</v>
@@ -28356,7 +28356,7 @@
         <v>-1.835492</v>
       </c>
       <c r="I347" s="9" t="n">
-        <v>101.731161</v>
+        <v>101.728257</v>
       </c>
       <c r="J347" s="9" t="n">
         <v>101.5661</v>
@@ -28440,7 +28440,7 @@
         <v>-2.446937</v>
       </c>
       <c r="I348" s="6" t="n">
-        <v>101.602005</v>
+        <v>101.59828</v>
       </c>
       <c r="J348" s="6" t="n">
         <v>101.369122</v>
@@ -28524,7 +28524,7 @@
         <v>-3.20879</v>
       </c>
       <c r="I349" s="9" t="n">
-        <v>101.345483</v>
+        <v>101.342747</v>
       </c>
       <c r="J349" s="9" t="n">
         <v>101.081684</v>
@@ -28608,7 +28608,7 @@
         <v>-4.101523</v>
       </c>
       <c r="I350" s="6" t="n">
-        <v>100.95627</v>
+        <v>100.95515</v>
       </c>
       <c r="J350" s="6" t="n">
         <v>100.685709</v>
@@ -28692,7 +28692,7 @@
         <v>-5.005769</v>
       </c>
       <c r="I351" s="9" t="n">
-        <v>100.423675</v>
+        <v>100.424143</v>
       </c>
       <c r="J351" s="9" t="n">
         <v>100.16835</v>
@@ -28776,7 +28776,7 @@
         <v>-5.761422</v>
       </c>
       <c r="I352" s="6" t="n">
-        <v>99.74545999999999</v>
+        <v>99.747167</v>
       </c>
       <c r="J352" s="6" t="n">
         <v>99.522375</v>
@@ -28860,7 +28860,7 @@
         <v>-6.284786</v>
       </c>
       <c r="I353" s="9" t="n">
-        <v>98.966345</v>
+        <v>98.968816</v>
       </c>
       <c r="J353" s="9" t="n">
         <v>98.787548</v>
@@ -28944,7 +28944,7 @@
         <v>-6.544513</v>
       </c>
       <c r="I354" s="6" t="n">
-        <v>98.17129300000001</v>
+        <v>98.173886</v>
       </c>
       <c r="J354" s="6" t="n">
         <v>98.03980199999999</v>
@@ -29028,7 +29028,7 @@
         <v>-6.514938</v>
       </c>
       <c r="I355" s="9" t="n">
-        <v>97.494719</v>
+        <v>97.49649599999999</v>
       </c>
       <c r="J355" s="9" t="n">
         <v>97.406628</v>
@@ -29112,7 +29112,7 @@
         <v>-6.181943</v>
       </c>
       <c r="I356" s="6" t="n">
-        <v>97.00215</v>
+        <v>97.002461</v>
       </c>
       <c r="J356" s="6" t="n">
         <v>96.94768500000001</v>
@@ -29196,7 +29196,7 @@
         <v>-5.557246</v>
       </c>
       <c r="I357" s="9" t="n">
-        <v>96.720716</v>
+        <v>96.719143</v>
       </c>
       <c r="J357" s="9" t="n">
         <v>96.686582</v>
@@ -29280,7 +29280,7 @@
         <v>-4.707167</v>
       </c>
       <c r="I358" s="6" t="n">
-        <v>96.661676</v>
+        <v>96.65818400000001</v>
       </c>
       <c r="J358" s="6" t="n">
         <v>96.61674499999999</v>
@@ -29364,7 +29364,7 @@
         <v>-3.6638</v>
       </c>
       <c r="I359" s="9" t="n">
-        <v>96.803201</v>
+        <v>96.79833000000001</v>
       </c>
       <c r="J359" s="9" t="n">
         <v>96.720698</v>
@@ -29448,7 +29448,7 @@
         <v>-2.461284</v>
       </c>
       <c r="I360" s="6" t="n">
-        <v>97.072547</v>
+        <v>97.067075</v>
       </c>
       <c r="J360" s="6" t="n">
         <v>96.966677</v>
@@ -29532,7 +29532,7 @@
         <v>-1.126835</v>
       </c>
       <c r="I361" s="9" t="n">
-        <v>97.39340199999999</v>
+        <v>97.389253</v>
       </c>
       <c r="J361" s="9" t="n">
         <v>97.29292599999999</v>
@@ -29616,7 +29616,7 @@
         <v>0.291487</v>
       </c>
       <c r="I362" s="6" t="n">
-        <v>97.729226</v>
+        <v>97.727183</v>
       </c>
       <c r="J362" s="6" t="n">
         <v>97.659109</v>
@@ -29700,7 +29700,7 @@
         <v>1.697069</v>
       </c>
       <c r="I363" s="9" t="n">
-        <v>98.04966400000001</v>
+        <v>98.04967000000001</v>
       </c>
       <c r="J363" s="9" t="n">
         <v>98.020214</v>
@@ -29784,7 +29784,7 @@
         <v>2.922179</v>
       </c>
       <c r="I364" s="6" t="n">
-        <v>98.331205</v>
+        <v>98.332864</v>
       </c>
       <c r="J364" s="6" t="n">
         <v>98.34518799999999</v>
@@ -29868,7 +29868,7 @@
         <v>3.886951</v>
       </c>
       <c r="I365" s="9" t="n">
-        <v>98.55943600000001</v>
+        <v>98.562181</v>
       </c>
       <c r="J365" s="9" t="n">
         <v>98.605935</v>
@@ -29952,7 +29952,7 @@
         <v>4.576366</v>
       </c>
       <c r="I366" s="6" t="n">
-        <v>98.74196600000001</v>
+        <v>98.745007</v>
       </c>
       <c r="J366" s="6" t="n">
         <v>98.801265</v>
@@ -30036,7 +30036,7 @@
         <v>4.965863</v>
       </c>
       <c r="I367" s="9" t="n">
-        <v>98.909769</v>
+        <v>98.911929</v>
       </c>
       <c r="J367" s="9" t="n">
         <v>98.95103400000001</v>
@@ -30120,7 +30120,7 @@
         <v>5.0331</v>
       </c>
       <c r="I368" s="6" t="n">
-        <v>99.06503499999999</v>
+        <v>99.065511</v>
       </c>
       <c r="J368" s="6" t="n">
         <v>99.073775</v>
@@ -30204,7 +30204,7 @@
         <v>4.782909</v>
       </c>
       <c r="I369" s="9" t="n">
-        <v>99.195863</v>
+        <v>99.194209</v>
       </c>
       <c r="J369" s="9" t="n">
         <v>99.159145</v>
@@ -30288,7 +30288,7 @@
         <v>4.308617</v>
       </c>
       <c r="I370" s="6" t="n">
-        <v>99.286001</v>
+        <v>99.282279</v>
       </c>
       <c r="J370" s="6" t="n">
         <v>99.195295</v>
@@ -30372,7 +30372,7 @@
         <v>3.728814</v>
       </c>
       <c r="I371" s="9" t="n">
-        <v>99.344471</v>
+        <v>99.339288</v>
       </c>
       <c r="J371" s="9" t="n">
         <v>99.196333</v>
@@ -30456,7 +30456,7 @@
         <v>3.146055</v>
       </c>
       <c r="I372" s="6" t="n">
-        <v>99.385468</v>
+        <v>99.379795</v>
       </c>
       <c r="J372" s="6" t="n">
         <v>99.177138</v>
@@ -30540,7 +30540,7 @@
         <v>2.627698</v>
       </c>
       <c r="I373" s="9" t="n">
-        <v>99.41757699999999</v>
+        <v>99.413466</v>
       </c>
       <c r="J373" s="9" t="n">
         <v>99.151408</v>
@@ -30624,7 +30624,7 @@
         <v>2.212695</v>
       </c>
       <c r="I374" s="6" t="n">
-        <v>99.447481</v>
+        <v>99.44581700000001</v>
       </c>
       <c r="J374" s="6" t="n">
         <v>99.12123099999999</v>
@@ -30708,7 +30708,7 @@
         <v>1.886943</v>
       </c>
       <c r="I375" s="9" t="n">
-        <v>99.481326</v>
+        <v>99.48227300000001</v>
       </c>
       <c r="J375" s="9" t="n">
         <v>99.103025</v>
@@ -30792,7 +30792,7 @@
         <v>1.651139</v>
       </c>
       <c r="I376" s="6" t="n">
-        <v>99.527075</v>
+        <v>99.530304</v>
       </c>
       <c r="J376" s="6" t="n">
         <v>99.107911</v>
@@ -30876,7 +30876,7 @@
         <v>1.477903</v>
       </c>
       <c r="I377" s="9" t="n">
-        <v>99.584295</v>
+        <v>99.589088</v>
       </c>
       <c r="J377" s="9" t="n">
         <v>99.142009</v>
@@ -30960,7 +30960,7 @@
         <v>1.327823</v>
       </c>
       <c r="I378" s="6" t="n">
-        <v>99.64242299999999</v>
+        <v>99.647581</v>
       </c>
       <c r="J378" s="6" t="n">
         <v>99.195933</v>
@@ -31044,7 +31044,7 @@
         <v>1.174703</v>
       </c>
       <c r="I379" s="9" t="n">
-        <v>99.700738</v>
+        <v>99.70450700000001</v>
       </c>
       <c r="J379" s="9" t="n">
         <v>99.26933699999999</v>
@@ -31128,7 +31128,7 @@
         <v>1.004152</v>
       </c>
       <c r="I380" s="6" t="n">
-        <v>99.762776</v>
+        <v>99.764152</v>
       </c>
       <c r="J380" s="6" t="n">
         <v>99.368239</v>
@@ -31212,7 +31212,7 @@
         <v>0.83658</v>
       </c>
       <c r="I381" s="9" t="n">
-        <v>99.834366</v>
+        <v>99.83304200000001</v>
       </c>
       <c r="J381" s="9" t="n">
         <v>99.48851000000001</v>
@@ -31296,7 +31296,7 @@
         <v>0.672216</v>
       </c>
       <c r="I382" s="6" t="n">
-        <v>99.936494</v>
+        <v>99.932923</v>
       </c>
       <c r="J382" s="6" t="n">
         <v>99.62996200000001</v>
@@ -31380,7 +31380,7 @@
         <v>0.482881</v>
       </c>
       <c r="I383" s="9" t="n">
-        <v>100.055366</v>
+        <v>100.05035</v>
       </c>
       <c r="J383" s="9" t="n">
         <v>99.78041399999999</v>
@@ -31464,7 +31464,7 @@
         <v>0.241357</v>
       </c>
       <c r="I384" s="6" t="n">
-        <v>100.18013</v>
+        <v>100.174745</v>
       </c>
       <c r="J384" s="6" t="n">
         <v>99.930651</v>
@@ -31548,7 +31548,7 @@
         <v>-0.053069</v>
       </c>
       <c r="I385" s="9" t="n">
-        <v>100.302255</v>
+        <v>100.298183</v>
       </c>
       <c r="J385" s="9" t="n">
         <v>100.090241</v>
@@ -31632,7 +31632,7 @@
         <v>-0.357242</v>
       </c>
       <c r="I386" s="6" t="n">
-        <v>100.410591</v>
+        <v>100.408686</v>
       </c>
       <c r="J386" s="6" t="n">
         <v>100.264956</v>
@@ -31716,7 +31716,7 @@
         <v>-0.6084889999999999</v>
       </c>
       <c r="I387" s="9" t="n">
-        <v>100.50774</v>
+        <v>100.508327</v>
       </c>
       <c r="J387" s="9" t="n">
         <v>100.456663</v>
@@ -31800,7 +31800,7 @@
         <v>-0.782481</v>
       </c>
       <c r="I388" s="6" t="n">
-        <v>100.599306</v>
+        <v>100.602321</v>
       </c>
       <c r="J388" s="6" t="n">
         <v>100.640929</v>
@@ -31884,7 +31884,7 @@
         <v>-0.8830480000000001</v>
       </c>
       <c r="I389" s="9" t="n">
-        <v>100.681257</v>
+        <v>100.686157</v>
       </c>
       <c r="J389" s="9" t="n">
         <v>100.793069</v>
@@ -31968,7 +31968,7 @@
         <v>-0.912863</v>
       </c>
       <c r="I390" s="6" t="n">
-        <v>100.752972</v>
+        <v>100.758569</v>
       </c>
       <c r="J390" s="6" t="n">
         <v>100.901033</v>
@@ -32052,7 +32052,7 @@
         <v>-0.914785</v>
       </c>
       <c r="I391" s="9" t="n">
-        <v>100.801695</v>
+        <v>100.805854</v>
       </c>
       <c r="J391" s="9" t="n">
         <v>100.968247</v>
@@ -32136,7 +32136,7 @@
         <v>-0.925724</v>
       </c>
       <c r="I392" s="6" t="n">
-        <v>100.823855</v>
+        <v>100.825579</v>
       </c>
       <c r="J392" s="6" t="n">
         <v>101.004862</v>
@@ -32220,7 +32220,7 @@
         <v>-0.944681</v>
       </c>
       <c r="I393" s="9" t="n">
-        <v>100.821764</v>
+        <v>100.820921</v>
       </c>
       <c r="J393" s="9" t="n">
         <v>101.017402</v>
@@ -32304,7 +32304,7 @@
         <v>-0.922122</v>
       </c>
       <c r="I394" s="6" t="n">
-        <v>100.802062</v>
+        <v>100.799194</v>
       </c>
       <c r="J394" s="6" t="n">
         <v>101.004737</v>
@@ -32388,7 +32388,7 @@
         <v>-0.817499</v>
       </c>
       <c r="I395" s="9" t="n">
-        <v>100.777497</v>
+        <v>100.773361</v>
       </c>
       <c r="J395" s="9" t="n">
         <v>100.970436</v>
@@ -32472,7 +32472,7 @@
         <v>-0.627268</v>
       </c>
       <c r="I396" s="6" t="n">
-        <v>100.743601</v>
+        <v>100.739134</v>
       </c>
       <c r="J396" s="6" t="n">
         <v>100.903804</v>
@@ -32556,7 +32556,7 @@
         <v>-0.378812</v>
       </c>
       <c r="I397" s="9" t="n">
-        <v>100.698623</v>
+        <v>100.694974</v>
       </c>
       <c r="J397" s="9" t="n">
         <v>100.795256</v>
@@ -32640,7 +32640,7 @@
         <v>-0.127239</v>
       </c>
       <c r="I398" s="6" t="n">
-        <v>100.653655</v>
+        <v>100.651516</v>
       </c>
       <c r="J398" s="6" t="n">
         <v>100.663653</v>
@@ -32724,7 +32724,7 @@
         <v>0.07849200000000001</v>
       </c>
       <c r="I399" s="9" t="n">
-        <v>100.60564</v>
+        <v>100.605499</v>
       </c>
       <c r="J399" s="9" t="n">
         <v>100.508538</v>
@@ -32808,7 +32808,7 @@
         <v>0.215927</v>
       </c>
       <c r="I400" s="6" t="n">
-        <v>100.548644</v>
+        <v>100.550695</v>
       </c>
       <c r="J400" s="6" t="n">
         <v>100.360567</v>
@@ -32892,7 +32892,7 @@
         <v>0.301299</v>
       </c>
       <c r="I401" s="9" t="n">
-        <v>100.465217</v>
+        <v>100.469193</v>
       </c>
       <c r="J401" s="9" t="n">
         <v>100.219358</v>
@@ -32976,7 +32976,7 @@
         <v>0.321314</v>
       </c>
       <c r="I402" s="6" t="n">
-        <v>100.359909</v>
+        <v>100.364809</v>
       </c>
       <c r="J402" s="6" t="n">
         <v>100.088554</v>
@@ -33060,7 +33060,7 @@
         <v>0.311521</v>
       </c>
       <c r="I403" s="9" t="n">
-        <v>100.243815</v>
+        <v>100.247379</v>
       </c>
       <c r="J403" s="9" t="n">
         <v>99.961204</v>
@@ -33144,7 +33144,7 @@
         <v>0.327646</v>
       </c>
       <c r="I404" s="6" t="n">
-        <v>100.130933</v>
+        <v>100.132358</v>
       </c>
       <c r="J404" s="6" t="n">
         <v>99.829032</v>
@@ -33228,7 +33228,7 @@
         <v>0.375122</v>
       </c>
       <c r="I405" s="9" t="n">
-        <v>100.033482</v>
+        <v>100.032844</v>
       </c>
       <c r="J405" s="9" t="n">
         <v>99.712627</v>
@@ -33312,7 +33312,7 @@
         <v>0.406638</v>
       </c>
       <c r="I406" s="6" t="n">
-        <v>99.95945500000001</v>
+        <v>99.957347</v>
       </c>
       <c r="J406" s="6" t="n">
         <v>99.629347</v>
@@ -33396,7 +33396,7 @@
         <v>0.385068</v>
       </c>
       <c r="I407" s="9" t="n">
-        <v>99.899371</v>
+        <v>99.896433</v>
       </c>
       <c r="J407" s="9" t="n">
         <v>99.564437</v>
@@ -33480,7 +33480,7 @@
         <v>0.33029</v>
       </c>
       <c r="I408" s="6" t="n">
-        <v>99.854653</v>
+        <v>99.85149699999999</v>
       </c>
       <c r="J408" s="6" t="n">
         <v>99.527354</v>
@@ -33564,7 +33564,7 @@
         <v>0.256959</v>
       </c>
       <c r="I409" s="9" t="n">
-        <v>99.822395</v>
+        <v>99.819551</v>
       </c>
       <c r="J409" s="9" t="n">
         <v>99.516019</v>
@@ -33648,7 +33648,7 @@
         <v>0.180948</v>
       </c>
       <c r="I410" s="6" t="n">
-        <v>99.793025</v>
+        <v>99.790925</v>
       </c>
       <c r="J410" s="6" t="n">
         <v>99.520746</v>
@@ -33732,7 +33732,7 @@
         <v>0.10693</v>
       </c>
       <c r="I411" s="9" t="n">
-        <v>99.769323</v>
+        <v>99.768304</v>
       </c>
       <c r="J411" s="9" t="n">
         <v>99.553943</v>
@@ -33816,7 +33816,7 @@
         <v>0.036217</v>
       </c>
       <c r="I412" s="6" t="n">
-        <v>99.75527099999999</v>
+        <v>99.755622</v>
       </c>
       <c r="J412" s="6" t="n">
         <v>99.611103</v>
@@ -33900,7 +33900,7 @@
         <v>-0.057334</v>
       </c>
       <c r="I413" s="9" t="n">
-        <v>99.76277399999999</v>
+        <v>99.76456</v>
       </c>
       <c r="J413" s="9" t="n">
         <v>99.7008</v>
@@ -33984,7 +33984,7 @@
         <v>-0.145795</v>
       </c>
       <c r="I414" s="6" t="n">
-        <v>99.796195</v>
+        <v>99.798813</v>
       </c>
       <c r="J414" s="6" t="n">
         <v>99.82587700000001</v>
@@ -34068,7 +34068,7 @@
         <v>-0.1774</v>
       </c>
       <c r="I415" s="9" t="n">
-        <v>99.86736000000001</v>
+        <v>99.868872</v>
       </c>
       <c r="J415" s="9" t="n">
         <v>99.983197</v>
@@ -34152,7 +34152,7 @@
         <v>-0.132311</v>
       </c>
       <c r="I416" s="6" t="n">
-        <v>99.95337499999999</v>
+        <v>99.953317</v>
       </c>
       <c r="J416" s="6" t="n">
         <v>100.152898</v>
@@ -34236,7 +34236,7 @@
         <v>-0.025502</v>
       </c>
       <c r="I417" s="9" t="n">
-        <v>100.034998</v>
+        <v>100.03365</v>
       </c>
       <c r="J417" s="9" t="n">
         <v>100.294693</v>
@@ -34320,7 +34320,7 @@
         <v>0.136317</v>
       </c>
       <c r="I418" s="6" t="n">
-        <v>100.093756</v>
+        <v>100.091602</v>
       </c>
       <c r="J418" s="6" t="n">
         <v>100.384111</v>
@@ -34404,7 +34404,7 @@
         <v>0.334415</v>
       </c>
       <c r="I419" s="9" t="n">
-        <v>100.116451</v>
+        <v>100.113966</v>
       </c>
       <c r="J419" s="9" t="n">
         <v>100.419001</v>
@@ -34488,7 +34488,7 @@
         <v>0.513053</v>
       </c>
       <c r="I420" s="6" t="n">
-        <v>100.111925</v>
+        <v>100.109504</v>
       </c>
       <c r="J420" s="6" t="n">
         <v>100.411943</v>
@@ -34572,7 +34572,7 @@
         <v>0.640329</v>
       </c>
       <c r="I421" s="9" t="n">
-        <v>100.087493</v>
+        <v>100.085498</v>
       </c>
       <c r="J421" s="9" t="n">
         <v>100.392828</v>
@@ -34656,7 +34656,7 @@
         <v>0.685857</v>
       </c>
       <c r="I422" s="6" t="n">
-        <v>100.066044</v>
+        <v>100.064805</v>
       </c>
       <c r="J422" s="6" t="n">
         <v>100.382712</v>
@@ -34740,7 +34740,7 @@
         <v>0.6447850000000001</v>
       </c>
       <c r="I423" s="9" t="n">
-        <v>100.054218</v>
+        <v>100.054046</v>
       </c>
       <c r="J423" s="9" t="n">
         <v>100.374373</v>
@@ -34824,7 +34824,7 @@
         <v>0.543062</v>
       </c>
       <c r="I424" s="6" t="n">
-        <v>100.04597</v>
+        <v>100.04711</v>
       </c>
       <c r="J424" s="6" t="n">
         <v>100.352348</v>
@@ -34908,7 +34908,7 @@
         <v>0.434832</v>
       </c>
       <c r="I425" s="9" t="n">
-        <v>100.042782</v>
+        <v>100.045248</v>
       </c>
       <c r="J425" s="9" t="n">
         <v>100.321112</v>
@@ -34992,7 +34992,7 @@
         <v>0.352559</v>
       </c>
       <c r="I426" s="6" t="n">
-        <v>100.053675</v>
+        <v>100.056836</v>
       </c>
       <c r="J426" s="6" t="n">
         <v>100.296011</v>
@@ -35076,7 +35076,7 @@
         <v>0.26584</v>
       </c>
       <c r="I427" s="9" t="n">
-        <v>100.084022</v>
+        <v>100.086043</v>
       </c>
       <c r="J427" s="9" t="n">
         <v>100.294382</v>
@@ -35160,7 +35160,7 @@
         <v>0.130135</v>
       </c>
       <c r="I428" s="6" t="n">
-        <v>100.130533</v>
+        <v>100.130862</v>
       </c>
       <c r="J428" s="6" t="n">
         <v>100.319524</v>
@@ -35244,7 +35244,7 @@
         <v>-0.03187</v>
       </c>
       <c r="I429" s="9" t="n">
-        <v>100.186973</v>
+        <v>100.185788</v>
       </c>
       <c r="J429" s="9" t="n">
         <v>100.38189</v>
@@ -35328,7 +35328,7 @@
         <v>-0.212493</v>
       </c>
       <c r="I430" s="6" t="n">
-        <v>100.242303</v>
+        <v>100.240111</v>
       </c>
       <c r="J430" s="6" t="n">
         <v>100.474424</v>
@@ -35412,7 +35412,7 @@
         <v>-0.401396</v>
       </c>
       <c r="I431" s="9" t="n">
-        <v>100.304127</v>
+        <v>100.301521</v>
       </c>
       <c r="J431" s="9" t="n">
         <v>100.604704</v>
@@ -35496,7 +35496,7 @@
         <v>-0.578423</v>
       </c>
       <c r="I432" s="6" t="n">
-        <v>100.36113</v>
+        <v>100.358671</v>
       </c>
       <c r="J432" s="6" t="n">
         <v>100.752647</v>
@@ -35580,7 +35580,7 @@
         <v>-0.723601</v>
       </c>
       <c r="I433" s="9" t="n">
-        <v>100.390851</v>
+        <v>100.388974</v>
       </c>
       <c r="J433" s="9" t="n">
         <v>100.875599</v>
@@ -35664,7 +35664,7 @@
         <v>-0.811018</v>
       </c>
       <c r="I434" s="6" t="n">
-        <v>100.378024</v>
+        <v>100.377062</v>
       </c>
       <c r="J434" s="6" t="n">
         <v>100.935011</v>
@@ -35748,7 +35748,7 @@
         <v>-0.830357</v>
       </c>
       <c r="I435" s="9" t="n">
-        <v>100.30473</v>
+        <v>100.304803</v>
       </c>
       <c r="J435" s="9" t="n">
         <v>100.896788</v>
@@ -35832,7 +35832,7 @@
         <v>-0.819692</v>
       </c>
       <c r="I436" s="6" t="n">
-        <v>100.203707</v>
+        <v>100.204912</v>
       </c>
       <c r="J436" s="6" t="n">
         <v>100.801882</v>
@@ -35916,7 +35916,7 @@
         <v>-0.812696</v>
       </c>
       <c r="I437" s="9" t="n">
-        <v>100.109448</v>
+        <v>100.111679</v>
       </c>
       <c r="J437" s="9" t="n">
         <v>100.687586</v>
@@ -36000,7 +36000,7 @@
         <v>-0.824664</v>
       </c>
       <c r="I438" s="6" t="n">
-        <v>100.033732</v>
+        <v>100.036421</v>
       </c>
       <c r="J438" s="6" t="n">
         <v>100.564559</v>
@@ -36084,7 +36084,7 @@
         <v>-0.8353930000000001</v>
       </c>
       <c r="I439" s="9" t="n">
-        <v>99.97796099999999</v>
+        <v>99.979742</v>
       </c>
       <c r="J439" s="9" t="n">
         <v>100.439677</v>
@@ -36168,7 +36168,7 @@
         <v>-0.8124130000000001</v>
       </c>
       <c r="I440" s="6" t="n">
-        <v>99.93913499999999</v>
+        <v>99.939515</v>
       </c>
       <c r="J440" s="6" t="n">
         <v>100.320142</v>
@@ -36252,7 +36252,7 @@
         <v>-0.771163</v>
       </c>
       <c r="I441" s="9" t="n">
-        <v>99.928348</v>
+        <v>99.927387</v>
       </c>
       <c r="J441" s="9" t="n">
         <v>100.224769</v>
@@ -36336,7 +36336,7 @@
         <v>-0.72736</v>
       </c>
       <c r="I442" s="6" t="n">
-        <v>99.949658</v>
+        <v>99.947729</v>
       </c>
       <c r="J442" s="6" t="n">
         <v>100.162153</v>
@@ -36420,7 +36420,7 @@
         <v>-0.683044</v>
       </c>
       <c r="I443" s="9" t="n">
-        <v>99.998912</v>
+        <v>99.996537</v>
       </c>
       <c r="J443" s="9" t="n">
         <v>100.133762</v>
@@ -36504,7 +36504,7 @@
         <v>-0.650376</v>
       </c>
       <c r="I444" s="6" t="n">
-        <v>100.070386</v>
+        <v>100.068122</v>
       </c>
       <c r="J444" s="6" t="n">
         <v>100.1465</v>
@@ -36588,7 +36588,7 @@
         <v>-0.636497</v>
       </c>
       <c r="I445" s="9" t="n">
-        <v>100.163886</v>
+        <v>100.162223</v>
       </c>
       <c r="J445" s="9" t="n">
         <v>100.202335</v>
@@ -36672,7 +36672,7 @@
         <v>-0.652933</v>
       </c>
       <c r="I446" s="6" t="n">
-        <v>100.270771</v>
+        <v>100.270063</v>
       </c>
       <c r="J446" s="6" t="n">
         <v>100.296623</v>
@@ -36756,7 +36756,7 @@
         <v>-0.697619</v>
       </c>
       <c r="I447" s="9" t="n">
-        <v>100.374695</v>
+        <v>100.375002</v>
       </c>
       <c r="J447" s="9" t="n">
         <v>100.416303</v>
@@ -36840,7 +36840,7 @@
         <v>-0.720552</v>
       </c>
       <c r="I448" s="6" t="n">
-        <v>100.46336</v>
+        <v>100.464756</v>
       </c>
       <c r="J448" s="6" t="n">
         <v>100.545392</v>
@@ -36924,7 +36924,7 @@
         <v>-0.688513</v>
       </c>
       <c r="I449" s="9" t="n">
-        <v>100.526073</v>
+        <v>100.528435</v>
       </c>
       <c r="J449" s="9" t="n">
         <v>100.653184</v>
@@ -37008,7 +37008,7 @@
         <v>-0.57809</v>
       </c>
       <c r="I450" s="6" t="n">
-        <v>100.552497</v>
+        <v>100.555382</v>
       </c>
       <c r="J450" s="6" t="n">
         <v>100.726824</v>
@@ -37092,7 +37092,7 @@
         <v>-0.394525</v>
       </c>
       <c r="I451" s="9" t="n">
-        <v>100.542199</v>
+        <v>100.544745</v>
       </c>
       <c r="J451" s="9" t="n">
         <v>100.751273</v>
@@ -37176,7 +37176,7 @@
         <v>-0.174259</v>
       </c>
       <c r="I452" s="6" t="n">
-        <v>100.509739</v>
+        <v>100.511414</v>
       </c>
       <c r="J452" s="6" t="n">
         <v>100.729694</v>
@@ -37260,7 +37260,7 @@
         <v>0.042446</v>
       </c>
       <c r="I453" s="9" t="n">
-        <v>100.462826</v>
+        <v>100.4634</v>
       </c>
       <c r="J453" s="9" t="n">
         <v>100.664404</v>
@@ -37344,7 +37344,7 @@
         <v>0.248257</v>
       </c>
       <c r="I454" s="6" t="n">
-        <v>100.413059</v>
+        <v>100.412606</v>
       </c>
       <c r="J454" s="6" t="n">
         <v>100.583946</v>
@@ -37428,7 +37428,7 @@
         <v>0.414593</v>
       </c>
       <c r="I455" s="9" t="n">
-        <v>100.374678</v>
+        <v>100.373507</v>
       </c>
       <c r="J455" s="9" t="n">
         <v>100.506393</v>
@@ -37512,7 +37512,7 @@
         <v>0.535173</v>
       </c>
       <c r="I456" s="6" t="n">
-        <v>100.356267</v>
+        <v>100.354819</v>
       </c>
       <c r="J456" s="6" t="n">
         <v>100.446615</v>
@@ -37596,7 +37596,7 @@
         <v>0.6160639999999999</v>
       </c>
       <c r="I457" s="9" t="n">
-        <v>100.379632</v>
+        <v>100.378416</v>
       </c>
       <c r="J457" s="9" t="n">
         <v>100.42486</v>
@@ -37680,7 +37680,7 @@
         <v>0.679284</v>
       </c>
       <c r="I458" s="6" t="n">
-        <v>100.443537</v>
+        <v>100.4429</v>
       </c>
       <c r="J458" s="6" t="n">
         <v>100.441656</v>
@@ -37764,7 +37764,7 @@
         <v>0.74082</v>
       </c>
       <c r="I459" s="9" t="n">
-        <v>100.559666</v>
+        <v>100.559656</v>
       </c>
       <c r="J459" s="9" t="n">
         <v>100.502298</v>
@@ -37848,7 +37848,7 @@
         <v>0.802729</v>
       </c>
       <c r="I460" s="6" t="n">
-        <v>100.698017</v>
+        <v>100.698767</v>
       </c>
       <c r="J460" s="6" t="n">
         <v>100.579637</v>
@@ -37932,7 +37932,7 @@
         <v>0.859114</v>
       </c>
       <c r="I461" s="9" t="n">
-        <v>100.827213</v>
+        <v>100.828788</v>
       </c>
       <c r="J461" s="9" t="n">
         <v>100.651651</v>
@@ -38016,7 +38016,7 @@
         <v>0.853294</v>
       </c>
       <c r="I462" s="6" t="n">
-        <v>100.929826</v>
+        <v>100.932149</v>
       </c>
       <c r="J462" s="6" t="n">
         <v>100.702414</v>
@@ -38100,7 +38100,7 @@
         <v>0.752519</v>
       </c>
       <c r="I463" s="9" t="n">
-        <v>101.01473</v>
+        <v>101.017743</v>
       </c>
       <c r="J463" s="9" t="n">
         <v>100.74405</v>
@@ -38184,7 +38184,7 @@
         <v>0.580939</v>
       </c>
       <c r="I464" s="6" t="n">
-        <v>101.079754</v>
+        <v>101.082954</v>
       </c>
       <c r="J464" s="6" t="n">
         <v>100.780445</v>
@@ -38268,7 +38268,7 @@
         <v>0.382546</v>
       </c>
       <c r="I465" s="9" t="n">
-        <v>101.122948</v>
+        <v>101.125689</v>
       </c>
       <c r="J465" s="9" t="n">
         <v>100.821121</v>
@@ -38352,7 +38352,7 @@
         <v>0.192156</v>
       </c>
       <c r="I466" s="6" t="n">
-        <v>101.16205</v>
+        <v>101.163789</v>
       </c>
       <c r="J466" s="6" t="n">
         <v>100.881561</v>
@@ -38436,7 +38436,7 @@
         <v>0.059288</v>
       </c>
       <c r="I467" s="9" t="n">
-        <v>101.193735</v>
+        <v>101.194215</v>
       </c>
       <c r="J467" s="9" t="n">
         <v>100.931266</v>
@@ -38520,7 +38520,7 @@
         <v>0.000375</v>
       </c>
       <c r="I468" s="6" t="n">
-        <v>101.218068</v>
+        <v>101.217361</v>
       </c>
       <c r="J468" s="6" t="n">
         <v>100.953381</v>
@@ -38604,7 +38604,7 @@
         <v>-0.014898</v>
       </c>
       <c r="I469" s="9" t="n">
-        <v>101.224545</v>
+        <v>101.223052</v>
       </c>
       <c r="J469" s="9" t="n">
         <v>100.935749</v>
@@ -38688,7 +38688,7 @@
         <v>-0.028673</v>
       </c>
       <c r="I470" s="6" t="n">
-        <v>101.202244</v>
+        <v>101.200656</v>
       </c>
       <c r="J470" s="6" t="n">
         <v>100.882407</v>
@@ -38772,7 +38772,7 @@
         <v>-0.072896</v>
       </c>
       <c r="I471" s="9" t="n">
-        <v>101.14791</v>
+        <v>101.147105</v>
       </c>
       <c r="J471" s="9" t="n">
         <v>100.785227</v>
@@ -38856,7 +38856,7 @@
         <v>-0.158069</v>
       </c>
       <c r="I472" s="6" t="n">
-        <v>101.070004</v>
+        <v>101.071068</v>
       </c>
       <c r="J472" s="6" t="n">
         <v>100.669595</v>
@@ -38940,7 +38940,7 @@
         <v>-0.256847</v>
       </c>
       <c r="I473" s="9" t="n">
-        <v>100.986413</v>
+        <v>100.990262</v>
       </c>
       <c r="J473" s="9" t="n">
         <v>100.569196</v>
@@ -39024,7 +39024,7 @@
         <v>-0.322331</v>
       </c>
       <c r="I474" s="6" t="n">
-        <v>100.90861</v>
+        <v>100.915567</v>
       </c>
       <c r="J474" s="6" t="n">
         <v>100.499193</v>
@@ -39108,7 +39108,7 @@
         <v>-0.359202</v>
       </c>
       <c r="I475" s="9" t="n">
-        <v>100.830767</v>
+        <v>100.839942</v>
       </c>
       <c r="J475" s="9" t="n">
         <v>100.45492</v>
@@ -39192,7 +39192,7 @@
         <v>-0.374597</v>
       </c>
       <c r="I476" s="6" t="n">
-        <v>100.75335</v>
+        <v>100.761407</v>
       </c>
       <c r="J476" s="6" t="n">
         <v>100.424351</v>
@@ -39276,7 +39276,7 @@
         <v>-0.379198</v>
       </c>
       <c r="I477" s="9" t="n">
-        <v>100.697059</v>
+        <v>100.702417</v>
       </c>
       <c r="J477" s="9" t="n">
         <v>100.410702</v>
@@ -39360,7 +39360,7 @@
         <v>-0.397224</v>
       </c>
       <c r="I478" s="6" t="n">
-        <v>100.661816</v>
+        <v>100.664007</v>
       </c>
       <c r="J478" s="6" t="n">
         <v>100.390693</v>
@@ -39444,7 +39444,7 @@
         <v>-0.422238</v>
       </c>
       <c r="I479" s="9" t="n">
-        <v>100.646907</v>
+        <v>100.646132</v>
       </c>
       <c r="J479" s="9" t="n">
         <v>100.354062</v>
@@ -39528,7 +39528,7 @@
         <v>-0.440812</v>
       </c>
       <c r="I480" s="6" t="n">
-        <v>100.635819</v>
+        <v>100.63273</v>
       </c>
       <c r="J480" s="6" t="n">
         <v>100.272682</v>
@@ -39612,7 +39612,7 @@
         <v>-0.42913</v>
       </c>
       <c r="I481" s="9" t="n">
-        <v>100.616084</v>
+        <v>100.611683</v>
       </c>
       <c r="J481" s="9" t="n">
         <v>100.140509</v>
@@ -39696,7 +39696,7 @@
         <v>-0.389688</v>
       </c>
       <c r="I482" s="6" t="n">
-        <v>100.570925</v>
+        <v>100.566599</v>
       </c>
       <c r="J482" s="6" t="n">
         <v>99.95886</v>
@@ -39780,7 +39780,7 @@
         <v>-0.321512</v>
       </c>
       <c r="I483" s="9" t="n">
-        <v>100.483885</v>
+        <v>100.481376</v>
       </c>
       <c r="J483" s="9" t="n">
         <v>99.740737</v>
@@ -39864,7 +39864,7 @@
         <v>-0.261897</v>
       </c>
       <c r="I484" s="6" t="n">
-        <v>100.357631</v>
+        <v>100.358942</v>
       </c>
       <c r="J484" s="6" t="n">
         <v>99.521987</v>
@@ -39948,7 +39948,7 @@
         <v>-0.302859</v>
       </c>
       <c r="I485" s="9" t="n">
-        <v>100.18014</v>
+        <v>100.187057</v>
       </c>
       <c r="J485" s="9" t="n">
         <v>99.30245600000001</v>
@@ -40032,7 +40032,7 @@
         <v>-0.500205</v>
       </c>
       <c r="I486" s="6" t="n">
-        <v>99.940834</v>
+        <v>99.95411199999999</v>
       </c>
       <c r="J486" s="6" t="n">
         <v>99.077945</v>
@@ -40116,7 +40116,7 @@
         <v>-0.826951</v>
       </c>
       <c r="I487" s="9" t="n">
-        <v>99.63569099999999</v>
+        <v>99.653817</v>
       </c>
       <c r="J487" s="9" t="n">
         <v>98.828571</v>
@@ -40200,7 +40200,7 @@
         <v>-1.227583</v>
       </c>
       <c r="I488" s="6" t="n">
-        <v>99.315038</v>
+        <v>99.332235</v>
       </c>
       <c r="J488" s="6" t="n">
         <v>98.578856</v>
@@ -40284,7 +40284,7 @@
         <v>-1.559112</v>
       </c>
       <c r="I489" s="9" t="n">
-        <v>87.07612399999999</v>
+        <v>87.063529</v>
       </c>
       <c r="J489" s="9" t="n">
         <v>85.513008</v>
@@ -40368,7 +40368,7 @@
         <v>-1.699334</v>
       </c>
       <c r="I490" s="6" t="n">
-        <v>86.054305</v>
+        <v>86.042699</v>
       </c>
       <c r="J490" s="6" t="n">
         <v>85.472877</v>
@@ -40452,7 +40452,7 @@
         <v>-1.656283</v>
       </c>
       <c r="I491" s="9" t="n">
-        <v>92.067036</v>
+        <v>92.058887</v>
       </c>
       <c r="J491" s="9" t="n">
         <v>93.296547</v>
@@ -40536,7 +40536,7 @@
         <v>-1.476582</v>
       </c>
       <c r="I492" s="6" t="n">
-        <v>93.726494</v>
+        <v>93.719179</v>
       </c>
       <c r="J492" s="6" t="n">
         <v>94.06985899999999</v>
@@ -40620,7 +40620,7 @@
         <v>-1.195123</v>
       </c>
       <c r="I493" s="9" t="n">
-        <v>94.88717800000001</v>
+        <v>94.878761</v>
       </c>
       <c r="J493" s="9" t="n">
         <v>95.36012599999999</v>
@@ -40704,7 +40704,7 @@
         <v>-0.8287409999999999</v>
       </c>
       <c r="I494" s="6" t="n">
-        <v>96.065577</v>
+        <v>96.058018</v>
       </c>
       <c r="J494" s="6" t="n">
         <v>96.57197499999999</v>
@@ -40788,7 +40788,7 @@
         <v>-0.414295</v>
       </c>
       <c r="I495" s="9" t="n">
-        <v>97.067708</v>
+        <v>97.063244</v>
       </c>
       <c r="J495" s="9" t="n">
         <v>97.529372</v>
@@ -40872,7 +40872,7 @@
         <v>0.036567</v>
       </c>
       <c r="I496" s="6" t="n">
-        <v>97.813734</v>
+        <v>97.81474300000001</v>
       </c>
       <c r="J496" s="6" t="n">
         <v>98.169107</v>
@@ -40956,7 +40956,7 @@
         <v>0.538595</v>
       </c>
       <c r="I497" s="9" t="n">
-        <v>98.30518499999999</v>
+        <v>98.31368000000001</v>
       </c>
       <c r="J497" s="9" t="n">
         <v>98.517003</v>
@@ -41040,7 +41040,7 @@
         <v>1.102946</v>
       </c>
       <c r="I498" s="6" t="n">
-        <v>98.599205</v>
+        <v>98.615652</v>
       </c>
       <c r="J498" s="6" t="n">
         <v>98.655096</v>
@@ -41124,7 +41124,7 @@
         <v>1.731072</v>
       </c>
       <c r="I499" s="9" t="n">
-        <v>98.760508</v>
+        <v>98.781779</v>
       </c>
       <c r="J499" s="9" t="n">
         <v>98.678971</v>
@@ -41208,7 +41208,7 @@
         <v>2.393356</v>
       </c>
       <c r="I500" s="6" t="n">
-        <v>98.84008799999999</v>
+        <v>98.85719400000001</v>
       </c>
       <c r="J500" s="6" t="n">
         <v>98.65911800000001</v>
@@ -41292,7 +41292,7 @@
         <v>2.958263</v>
       </c>
       <c r="I501" s="9" t="n">
-        <v>98.83710000000001</v>
+        <v>98.847002</v>
       </c>
       <c r="J501" s="9" t="n">
         <v>98.60088500000001</v>
@@ -41376,7 +41376,7 @@
         <v>3.298747</v>
       </c>
       <c r="I502" s="6" t="n">
-        <v>98.767016</v>
+        <v>98.76991700000001</v>
       </c>
       <c r="J502" s="6" t="n">
         <v>98.523594</v>
@@ -41460,7 +41460,7 @@
         <v>3.38536</v>
       </c>
       <c r="I503" s="9" t="n">
-        <v>98.651916</v>
+        <v>98.649491</v>
       </c>
       <c r="J503" s="9" t="n">
         <v>98.456734</v>
@@ -41544,7 +41544,7 @@
         <v>3.250564</v>
       </c>
       <c r="I504" s="6" t="n">
-        <v>98.52353100000001</v>
+        <v>98.51785099999999</v>
       </c>
       <c r="J504" s="6" t="n">
         <v>98.424458</v>
@@ -41628,7 +41628,7 @@
         <v>2.940998</v>
       </c>
       <c r="I505" s="9" t="n">
-        <v>98.42260400000001</v>
+        <v>98.415745</v>
       </c>
       <c r="J505" s="9" t="n">
         <v>98.44262999999999</v>
@@ -41712,7 +41712,7 @@
         <v>2.512032</v>
       </c>
       <c r="I506" s="6" t="n">
-        <v>98.391453</v>
+        <v>98.385288</v>
       </c>
       <c r="J506" s="6" t="n">
         <v>98.526662</v>
@@ -41796,7 +41796,7 @@
         <v>2.023709</v>
       </c>
       <c r="I507" s="9" t="n">
-        <v>98.44952600000001</v>
+        <v>98.44584500000001</v>
       </c>
       <c r="J507" s="9" t="n">
         <v>98.70104600000001</v>
@@ -41880,7 +41880,7 @@
         <v>1.524263</v>
       </c>
       <c r="I508" s="6" t="n">
-        <v>98.583315</v>
+        <v>98.583872</v>
       </c>
       <c r="J508" s="6" t="n">
         <v>98.952949</v>
@@ -41964,7 +41964,7 @@
         <v>1.047468</v>
       </c>
       <c r="I509" s="9" t="n">
-        <v>98.766127</v>
+        <v>98.77242200000001</v>
       </c>
       <c r="J509" s="9" t="n">
         <v>99.254807</v>
@@ -42048,7 +42048,7 @@
         <v>0.603982</v>
       </c>
       <c r="I510" s="6" t="n">
-        <v>98.970637</v>
+        <v>98.98312900000001</v>
       </c>
       <c r="J510" s="6" t="n">
         <v>99.56235700000001</v>
@@ -42132,7 +42132,7 @@
         <v>0.178809</v>
       </c>
       <c r="I511" s="9" t="n">
-        <v>99.172735</v>
+        <v>99.189588</v>
       </c>
       <c r="J511" s="9" t="n">
         <v>99.83539399999999</v>
@@ -42216,7 +42216,7 @@
         <v>-0.262444</v>
       </c>
       <c r="I512" s="6" t="n">
-        <v>99.35871899999999</v>
+        <v>99.37372000000001</v>
       </c>
       <c r="J512" s="6" t="n">
         <v>100.058233</v>
@@ -42300,7 +42300,7 @@
         <v>-0.708506</v>
       </c>
       <c r="I513" s="9" t="n">
-        <v>99.514899</v>
+        <v>99.525288</v>
       </c>
       <c r="J513" s="9" t="n">
         <v>100.216011</v>
@@ -42384,7 +42384,7 @@
         <v>-1.121131</v>
       </c>
       <c r="I514" s="6" t="n">
-        <v>99.636751</v>
+        <v>99.641194</v>
       </c>
       <c r="J514" s="6" t="n">
         <v>100.310393</v>
@@ -42468,7 +42468,7 @@
         <v>-1.465836</v>
       </c>
       <c r="I515" s="9" t="n">
-        <v>99.739271</v>
+        <v>99.738452</v>
       </c>
       <c r="J515" s="9" t="n">
         <v>100.367013</v>
@@ -42552,7 +42552,7 @@
         <v>-1.719833</v>
       </c>
       <c r="I516" s="6" t="n">
-        <v>99.84506399999999</v>
+        <v>99.84058899999999</v>
       </c>
       <c r="J516" s="6" t="n">
         <v>100.418301</v>
@@ -42636,7 +42636,7 @@
         <v>-1.875094</v>
       </c>
       <c r="I517" s="9" t="n">
-        <v>99.95968999999999</v>
+        <v>99.953378</v>
       </c>
       <c r="J517" s="9" t="n">
         <v>100.476073</v>
@@ -42720,7 +42720,7 @@
         <v>-1.93658</v>
       </c>
       <c r="I518" s="6" t="n">
-        <v>100.081</v>
+        <v>100.074554</v>
       </c>
       <c r="J518" s="6" t="n">
         <v>100.549889</v>
@@ -42804,7 +42804,7 @@
         <v>-1.905906</v>
       </c>
       <c r="I519" s="9" t="n">
-        <v>100.205604</v>
+        <v>100.200525</v>
       </c>
       <c r="J519" s="9" t="n">
         <v>100.655448</v>
@@ -42888,7 +42888,7 @@
         <v>-1.806659</v>
       </c>
       <c r="I520" s="6" t="n">
-        <v>100.322531</v>
+        <v>100.320217</v>
       </c>
       <c r="J520" s="6" t="n">
         <v>100.790567</v>
@@ -42972,7 +42972,7 @@
         <v>-1.650502</v>
       </c>
       <c r="I521" s="9" t="n">
-        <v>100.415127</v>
+        <v>100.416711</v>
       </c>
       <c r="J521" s="9" t="n">
         <v>100.924947</v>
@@ -43056,7 +43056,7 @@
         <v>-1.432887</v>
       </c>
       <c r="I522" s="6" t="n">
-        <v>100.469904</v>
+        <v>100.475879</v>
       </c>
       <c r="J522" s="6" t="n">
         <v>101.028206</v>
@@ -43140,7 +43140,7 @@
         <v>-1.171605</v>
       </c>
       <c r="I523" s="9" t="n">
-        <v>100.498619</v>
+        <v>100.508117</v>
       </c>
       <c r="J523" s="9" t="n">
         <v>101.109661</v>
@@ -43224,7 +43224,7 @@
         <v>-0.872628</v>
       </c>
       <c r="I524" s="6" t="n">
-        <v>100.532422</v>
+        <v>100.542016</v>
       </c>
       <c r="J524" s="6" t="n">
         <v>101.191005</v>
@@ -43308,7 +43308,7 @@
         <v>-0.5532550000000001</v>
       </c>
       <c r="I525" s="9" t="n">
-        <v>100.589925</v>
+        <v>100.597209</v>
       </c>
       <c r="J525" s="9" t="n">
         <v>101.28547</v>
@@ -43392,7 +43392,7 @@
         <v>-0.239132</v>
       </c>
       <c r="I526" s="6" t="n">
-        <v>100.661766</v>
+        <v>100.663885</v>
       </c>
       <c r="J526" s="6" t="n">
         <v>101.389861</v>
@@ -43476,7 +43476,7 @@
         <v>0.050677</v>
       </c>
       <c r="I527" s="9" t="n">
-        <v>100.740786</v>
+        <v>100.73737</v>
       </c>
       <c r="J527" s="9" t="n">
         <v>101.49271</v>
@@ -43560,7 +43560,7 @@
         <v>0.286081</v>
       </c>
       <c r="I528" s="6" t="n">
-        <v>100.818062</v>
+        <v>100.8101</v>
       </c>
       <c r="J528" s="6" t="n">
         <v>101.58194</v>
@@ -43644,7 +43644,7 @@
         <v>0.454366</v>
       </c>
       <c r="I529" s="9" t="n">
-        <v>100.888541</v>
+        <v>100.877641</v>
       </c>
       <c r="J529" s="9" t="n">
         <v>101.650164</v>
@@ -43728,7 +43728,7 @@
         <v>0.568971</v>
       </c>
       <c r="I530" s="6" t="n">
-        <v>100.939658</v>
+        <v>100.927678</v>
       </c>
       <c r="J530" s="6" t="n">
         <v>101.683087</v>
@@ -43812,7 +43812,7 @@
         <v>0.650641</v>
       </c>
       <c r="I531" s="9" t="n">
-        <v>100.955336</v>
+        <v>100.943795</v>
       </c>
       <c r="J531" s="9" t="n">
         <v>101.657057</v>
@@ -43896,7 +43896,7 @@
         <v>0.7345429999999999</v>
       </c>
       <c r="I532" s="6" t="n">
-        <v>100.939924</v>
+        <v>100.92999</v>
       </c>
       <c r="J532" s="6" t="n">
         <v>101.558299</v>
@@ -43980,7 +43980,7 @@
         <v>0.809484</v>
       </c>
       <c r="I533" s="9" t="n">
-        <v>100.913523</v>
+        <v>100.905976</v>
       </c>
       <c r="J533" s="9" t="n">
         <v>101.419006</v>
@@ -44064,7 +44064,7 @@
         <v>0.841351</v>
       </c>
       <c r="I534" s="6" t="n">
-        <v>100.87965</v>
+        <v>100.874823</v>
       </c>
       <c r="J534" s="6" t="n">
         <v>101.257861</v>
@@ -44148,7 +44148,7 @@
         <v>0.823619</v>
       </c>
       <c r="I535" s="9" t="n">
-        <v>100.838947</v>
+        <v>100.836697</v>
       </c>
       <c r="J535" s="9" t="n">
         <v>101.085013</v>
@@ -44232,7 +44232,7 @@
         <v>0.759494</v>
       </c>
       <c r="I536" s="6" t="n">
-        <v>100.788414</v>
+        <v>100.787742</v>
       </c>
       <c r="J536" s="6" t="n">
         <v>100.933128</v>
@@ -44316,7 +44316,7 @@
         <v>0.640055</v>
       </c>
       <c r="I537" s="9" t="n">
-        <v>100.732864</v>
+        <v>100.731507</v>
       </c>
       <c r="J537" s="9" t="n">
         <v>100.807882</v>
@@ -44400,7 +44400,7 @@
         <v>0.474605</v>
       </c>
       <c r="I538" s="6" t="n">
-        <v>100.693866</v>
+        <v>100.687692</v>
       </c>
       <c r="J538" s="6" t="n">
         <v>100.720319</v>
@@ -44484,7 +44484,7 @@
         <v>0.274379</v>
       </c>
       <c r="I539" s="9" t="n">
-        <v>100.658289</v>
+        <v>100.645559</v>
       </c>
       <c r="J539" s="9" t="n">
         <v>100.657102</v>
@@ -44568,7 +44568,7 @@
         <v>0.076115</v>
       </c>
       <c r="I540" s="6" t="n">
-        <v>100.607989</v>
+        <v>100.588685</v>
       </c>
       <c r="J540" s="6" t="n">
         <v>100.591947</v>
@@ -44652,7 +44652,7 @@
         <v>-0.102561</v>
       </c>
       <c r="I541" s="9" t="n">
-        <v>100.524119</v>
+        <v>100.49953</v>
       </c>
       <c r="J541" s="9" t="n">
         <v>100.497531</v>
@@ -44736,7 +44736,7 @@
         <v>-0.267388</v>
       </c>
       <c r="I542" s="6" t="n">
-        <v>100.418188</v>
+        <v>100.391226</v>
       </c>
       <c r="J542" s="6" t="n">
         <v>100.370502</v>
@@ -44820,7 +44820,7 @@
         <v>-0.446421</v>
       </c>
       <c r="I543" s="9" t="n">
-        <v>100.303743</v>
+        <v>100.277009</v>
       </c>
       <c r="J543" s="9" t="n">
         <v>100.213821</v>
@@ -44904,7 +44904,7 @@
         <v>-0.670031</v>
       </c>
       <c r="I544" s="6" t="n">
-        <v>100.208709</v>
+        <v>100.184127</v>
       </c>
       <c r="J544" s="6" t="n">
         <v>100.068431</v>
@@ -44988,7 +44988,7 @@
         <v>-0.918922</v>
       </c>
       <c r="I545" s="9" t="n">
-        <v>100.142715</v>
+        <v>100.121305</v>
       </c>
       <c r="J545" s="9" t="n">
         <v>99.957966</v>
@@ -45072,7 +45072,7 @@
         <v>-1.148989</v>
       </c>
       <c r="I546" s="6" t="n">
-        <v>100.117118</v>
+        <v>100.098966</v>
       </c>
       <c r="J546" s="6" t="n">
         <v>99.904202</v>
@@ -45156,7 +45156,7 @@
         <v>-1.322597</v>
       </c>
       <c r="I547" s="9" t="n">
-        <v>100.109531</v>
+        <v>100.093698</v>
       </c>
       <c r="J547" s="9" t="n">
         <v>99.887636</v>
@@ -45240,7 +45240,7 @@
         <v>-1.407232</v>
       </c>
       <c r="I548" s="6" t="n">
-        <v>100.088978</v>
+        <v>100.073646</v>
       </c>
       <c r="J548" s="6" t="n">
         <v>99.85809999999999</v>
@@ -45324,7 +45324,7 @@
         <v>-1.358171</v>
       </c>
       <c r="I549" s="9" t="n">
-        <v>100.050048</v>
+        <v>100.032556</v>
       </c>
       <c r="J549" s="9" t="n">
         <v>99.80019299999999</v>
@@ -45408,7 +45408,7 @@
         <v>-1.166792</v>
       </c>
       <c r="I550" s="6" t="n">
-        <v>99.99865699999999</v>
+        <v>99.975628</v>
       </c>
       <c r="J550" s="6" t="n">
         <v>99.719556</v>
@@ -45492,7 +45492,7 @@
         <v>-0.873835</v>
       </c>
       <c r="I551" s="9" t="n">
-        <v>99.936921</v>
+        <v>99.905976</v>
       </c>
       <c r="J551" s="9" t="n">
         <v>99.608245</v>
@@ -45576,7 +45576,7 @@
         <v>-0.534716</v>
       </c>
       <c r="I552" s="6" t="n">
-        <v>99.87272299999999</v>
+        <v>99.832745</v>
       </c>
       <c r="J552" s="6" t="n">
         <v>99.485319</v>
@@ -45660,7 +45660,7 @@
         <v>-0.192948</v>
       </c>
       <c r="I553" s="9" t="n">
-        <v>99.826672</v>
+        <v>99.77855099999999</v>
       </c>
       <c r="J553" s="9" t="n">
         <v>99.389957</v>
@@ -45744,7 +45744,7 @@
         <v>0.122701</v>
       </c>
       <c r="I554" s="6" t="n">
-        <v>99.798992</v>
+        <v>99.74658100000001</v>
       </c>
       <c r="J554" s="6" t="n">
         <v>99.346199</v>
@@ -45828,7 +45828,7 @@
         <v>0.401682</v>
       </c>
       <c r="I555" s="9" t="n">
-        <v>99.791175</v>
+        <v>99.737792</v>
       </c>
       <c r="J555" s="9" t="n">
         <v>99.353003</v>
@@ -45912,7 +45912,7 @@
         <v>0.649109</v>
       </c>
       <c r="I556" s="6" t="n">
-        <v>99.78725300000001</v>
+        <v>99.73521100000001</v>
       </c>
       <c r="J556" s="6" t="n">
         <v>99.38487499999999</v>
@@ -45996,7 +45996,7 @@
         <v>0.875324</v>
       </c>
       <c r="I557" s="9" t="n">
-        <v>99.787902</v>
+        <v>99.738479</v>
       </c>
       <c r="J557" s="9" t="n">
         <v>99.420351</v>
@@ -46080,7 +46080,7 @@
         <v>1.071422</v>
       </c>
       <c r="I558" s="6" t="n">
-        <v>99.80225</v>
+        <v>99.756097</v>
       </c>
       <c r="J558" s="6" t="n">
         <v>99.460641</v>
@@ -46164,7 +46164,7 @@
         <v>1.222234</v>
       </c>
       <c r="I559" s="9" t="n">
-        <v>99.85903999999999</v>
+        <v>99.81670699999999</v>
       </c>
       <c r="J559" s="9" t="n">
         <v>99.53000299999999</v>
@@ -46248,7 +46248,7 @@
         <v>1.313967</v>
       </c>
       <c r="I560" s="6" t="n">
-        <v>99.962011</v>
+        <v>99.92457</v>
       </c>
       <c r="J560" s="6" t="n">
         <v>99.635588</v>
@@ -46332,7 +46332,7 @@
         <v>1.330738</v>
       </c>
       <c r="I561" s="9" t="n">
-        <v>100.094416</v>
+        <v>100.064653</v>
       </c>
       <c r="J561" s="9" t="n">
         <v>99.780231</v>
@@ -46416,7 +46416,7 @@
         <v>1.266505</v>
       </c>
       <c r="I562" s="6" t="n">
-        <v>100.225959</v>
+        <v>100.209737</v>
       </c>
       <c r="J562" s="6" t="n">
         <v>99.933437</v>
@@ -46500,7 +46500,7 @@
         <v>1.145639</v>
       </c>
       <c r="I563" s="9" t="n">
-        <v>100.356612</v>
+        <v>100.360928</v>
       </c>
       <c r="J563" s="9" t="n">
         <v>100.098738</v>
@@ -46584,7 +46584,7 @@
         <v>0.999678</v>
       </c>
       <c r="I564" s="6" t="n">
-        <v>100.491865</v>
+        <v>100.524106</v>
       </c>
       <c r="J564" s="6" t="n">
         <v>100.276559</v>
@@ -46661,7 +46661,9 @@
       <c r="H565" s="10" t="n">
         <v>0.856274</v>
       </c>
-      <c r="I565" s="9" t="n"/>
+      <c r="I565" s="9" t="n">
+        <v>100.692757</v>
+      </c>
       <c r="J565" s="9" t="n">
         <v>100.461215</v>
       </c>

--- a/downloads/indicadores/SIC/SIC_datos.xlsx
+++ b/downloads/indicadores/SIC/SIC_datos.xlsx
@@ -679,7 +679,7 @@
       </c>
       <c r="M6" s="6" t="n"/>
       <c r="N6" s="6" t="n">
-        <v>96.01853800000001</v>
+        <v>96.02374399999999</v>
       </c>
       <c r="O6" s="6" t="n">
         <v>100.455586</v>
@@ -751,7 +751,7 @@
       </c>
       <c r="M7" s="9" t="n"/>
       <c r="N7" s="9" t="n">
-        <v>96.648679</v>
+        <v>96.65304999999999</v>
       </c>
       <c r="O7" s="9" t="n">
         <v>100.495876</v>
@@ -823,7 +823,7 @@
       </c>
       <c r="M8" s="6" t="n"/>
       <c r="N8" s="6" t="n">
-        <v>97.279504</v>
+        <v>97.283038</v>
       </c>
       <c r="O8" s="6" t="n">
         <v>100.518536</v>
@@ -895,7 +895,7 @@
       </c>
       <c r="M9" s="9" t="n"/>
       <c r="N9" s="9" t="n">
-        <v>97.915756</v>
+        <v>97.918447</v>
       </c>
       <c r="O9" s="9" t="n">
         <v>100.563989</v>
@@ -967,7 +967,7 @@
       </c>
       <c r="M10" s="6" t="n"/>
       <c r="N10" s="6" t="n">
-        <v>98.558206</v>
+        <v>98.560046</v>
       </c>
       <c r="O10" s="6" t="n">
         <v>100.708463</v>
@@ -1039,7 +1039,7 @@
       </c>
       <c r="M11" s="9" t="n"/>
       <c r="N11" s="9" t="n">
-        <v>99.214552</v>
+        <v>99.21552200000001</v>
       </c>
       <c r="O11" s="9" t="n">
         <v>100.952213</v>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="M12" s="6" t="n"/>
       <c r="N12" s="6" t="n">
-        <v>99.89823800000001</v>
+        <v>99.898301</v>
       </c>
       <c r="O12" s="6" t="n">
         <v>101.226189</v>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="M13" s="9" t="n"/>
       <c r="N13" s="9" t="n">
-        <v>100.597011</v>
+        <v>100.596149</v>
       </c>
       <c r="O13" s="9" t="n">
         <v>101.473115</v>
@@ -1255,7 +1255,7 @@
       </c>
       <c r="M14" s="6" t="n"/>
       <c r="N14" s="6" t="n">
-        <v>101.289255</v>
+        <v>101.287476</v>
       </c>
       <c r="O14" s="6" t="n">
         <v>101.608758</v>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="M15" s="9" t="n"/>
       <c r="N15" s="9" t="n">
-        <v>101.936772</v>
+        <v>101.934136</v>
       </c>
       <c r="O15" s="9" t="n">
         <v>101.579974</v>
@@ -1399,7 +1399,7 @@
       </c>
       <c r="M16" s="6" t="n"/>
       <c r="N16" s="6" t="n">
-        <v>102.504641</v>
+        <v>102.501253</v>
       </c>
       <c r="O16" s="6" t="n">
         <v>101.441421</v>
@@ -1471,7 +1471,7 @@
       </c>
       <c r="M17" s="9" t="n"/>
       <c r="N17" s="9" t="n">
-        <v>102.971084</v>
+        <v>102.967079</v>
       </c>
       <c r="O17" s="9" t="n">
         <v>101.284557</v>
@@ -1547,7 +1547,7 @@
       </c>
       <c r="M18" s="6" t="n"/>
       <c r="N18" s="6" t="n">
-        <v>103.330031</v>
+        <v>103.325551</v>
       </c>
       <c r="O18" s="6" t="n">
         <v>101.19651</v>
@@ -1625,7 +1625,7 @@
       </c>
       <c r="M19" s="9" t="n"/>
       <c r="N19" s="9" t="n">
-        <v>103.583824</v>
+        <v>103.579008</v>
       </c>
       <c r="O19" s="9" t="n">
         <v>101.197183</v>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="M20" s="6" t="n"/>
       <c r="N20" s="6" t="n">
-        <v>103.754</v>
+        <v>103.748957</v>
       </c>
       <c r="O20" s="6" t="n">
         <v>101.30155</v>
@@ -1781,7 +1781,7 @@
       </c>
       <c r="M21" s="9" t="n"/>
       <c r="N21" s="9" t="n">
-        <v>103.850555</v>
+        <v>103.845381</v>
       </c>
       <c r="O21" s="9" t="n">
         <v>101.483924</v>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="M22" s="6" t="n"/>
       <c r="N22" s="6" t="n">
-        <v>103.906068</v>
+        <v>103.900813</v>
       </c>
       <c r="O22" s="6" t="n">
         <v>101.602641</v>
@@ -1937,7 +1937,7 @@
       </c>
       <c r="M23" s="9" t="n"/>
       <c r="N23" s="9" t="n">
-        <v>103.951245</v>
+        <v>103.945918</v>
       </c>
       <c r="O23" s="9" t="n">
         <v>101.630048</v>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="M24" s="6" t="n"/>
       <c r="N24" s="6" t="n">
-        <v>104.017258</v>
+        <v>104.011823</v>
       </c>
       <c r="O24" s="6" t="n">
         <v>101.517795</v>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="M25" s="9" t="n"/>
       <c r="N25" s="9" t="n">
-        <v>104.116691</v>
+        <v>104.111098</v>
       </c>
       <c r="O25" s="9" t="n">
         <v>101.294059</v>
@@ -2171,7 +2171,7 @@
       </c>
       <c r="M26" s="6" t="n"/>
       <c r="N26" s="6" t="n">
-        <v>104.250865</v>
+        <v>104.245063</v>
       </c>
       <c r="O26" s="6" t="n">
         <v>101.043878</v>
@@ -2249,7 +2249,7 @@
       </c>
       <c r="M27" s="9" t="n"/>
       <c r="N27" s="9" t="n">
-        <v>104.384649</v>
+        <v>104.378641</v>
       </c>
       <c r="O27" s="9" t="n">
         <v>100.80307</v>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="M28" s="6" t="n"/>
       <c r="N28" s="6" t="n">
-        <v>104.436256</v>
+        <v>104.430168</v>
       </c>
       <c r="O28" s="6" t="n">
         <v>100.566418</v>
@@ -2405,7 +2405,7 @@
       </c>
       <c r="M29" s="9" t="n"/>
       <c r="N29" s="9" t="n">
-        <v>104.322865</v>
+        <v>104.316911</v>
       </c>
       <c r="O29" s="9" t="n">
         <v>100.300369</v>
@@ -2483,7 +2483,7 @@
       </c>
       <c r="M30" s="6" t="n"/>
       <c r="N30" s="6" t="n">
-        <v>104.021082</v>
+        <v>104.0155</v>
       </c>
       <c r="O30" s="6" t="n">
         <v>99.928353</v>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="M31" s="9" t="n"/>
       <c r="N31" s="9" t="n">
-        <v>103.53688</v>
+        <v>103.531899</v>
       </c>
       <c r="O31" s="9" t="n">
         <v>99.481447</v>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="M32" s="6" t="n"/>
       <c r="N32" s="6" t="n">
-        <v>102.868663</v>
+        <v>102.864529</v>
       </c>
       <c r="O32" s="6" t="n">
         <v>98.97144900000001</v>
@@ -2717,7 +2717,7 @@
       </c>
       <c r="M33" s="9" t="n"/>
       <c r="N33" s="9" t="n">
-        <v>102.049289</v>
+        <v>102.046234</v>
       </c>
       <c r="O33" s="9" t="n">
         <v>98.37693400000001</v>
@@ -2795,7 +2795,7 @@
       </c>
       <c r="M34" s="6" t="n"/>
       <c r="N34" s="6" t="n">
-        <v>101.095145</v>
+        <v>101.093426</v>
       </c>
       <c r="O34" s="6" t="n">
         <v>97.759479</v>
@@ -2873,7 +2873,7 @@
       </c>
       <c r="M35" s="9" t="n"/>
       <c r="N35" s="9" t="n">
-        <v>100.035605</v>
+        <v>100.035508</v>
       </c>
       <c r="O35" s="9" t="n">
         <v>97.094443</v>
@@ -2951,7 +2951,7 @@
       </c>
       <c r="M36" s="6" t="n"/>
       <c r="N36" s="6" t="n">
-        <v>98.9059</v>
+        <v>98.907628</v>
       </c>
       <c r="O36" s="6" t="n">
         <v>96.47264199999999</v>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="M37" s="9" t="n"/>
       <c r="N37" s="9" t="n">
-        <v>97.741972</v>
+        <v>97.74564100000001</v>
       </c>
       <c r="O37" s="9" t="n">
         <v>95.951261</v>
@@ -3107,7 +3107,7 @@
       </c>
       <c r="M38" s="6" t="n"/>
       <c r="N38" s="6" t="n">
-        <v>96.635603</v>
+        <v>96.641143</v>
       </c>
       <c r="O38" s="6" t="n">
         <v>95.566489</v>
@@ -3185,7 +3185,7 @@
       </c>
       <c r="M39" s="9" t="n"/>
       <c r="N39" s="9" t="n">
-        <v>95.67626199999999</v>
+        <v>95.683368</v>
       </c>
       <c r="O39" s="9" t="n">
         <v>95.394738</v>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="M40" s="6" t="n"/>
       <c r="N40" s="6" t="n">
-        <v>94.953543</v>
+        <v>94.961589</v>
       </c>
       <c r="O40" s="6" t="n">
         <v>95.478382</v>
@@ -3341,7 +3341,7 @@
       </c>
       <c r="M41" s="9" t="n"/>
       <c r="N41" s="9" t="n">
-        <v>94.529996</v>
+        <v>94.53845099999999</v>
       </c>
       <c r="O41" s="9" t="n">
         <v>95.739322</v>
@@ -3419,7 +3419,7 @@
       </c>
       <c r="M42" s="6" t="n"/>
       <c r="N42" s="6" t="n">
-        <v>94.40653</v>
+        <v>94.414936</v>
       </c>
       <c r="O42" s="6" t="n">
         <v>96.12897700000001</v>
@@ -3497,7 +3497,7 @@
       </c>
       <c r="M43" s="9" t="n"/>
       <c r="N43" s="9" t="n">
-        <v>94.55947500000001</v>
+        <v>94.56738900000001</v>
       </c>
       <c r="O43" s="9" t="n">
         <v>96.55039499999999</v>
@@ -3575,7 +3575,7 @@
       </c>
       <c r="M44" s="6" t="n"/>
       <c r="N44" s="6" t="n">
-        <v>94.946664</v>
+        <v>94.953795</v>
       </c>
       <c r="O44" s="6" t="n">
         <v>96.93601099999999</v>
@@ -3653,7 +3653,7 @@
       </c>
       <c r="M45" s="9" t="n"/>
       <c r="N45" s="9" t="n">
-        <v>95.4669</v>
+        <v>95.473134</v>
       </c>
       <c r="O45" s="9" t="n">
         <v>97.24065400000001</v>
@@ -3731,7 +3731,7 @@
       </c>
       <c r="M46" s="6" t="n"/>
       <c r="N46" s="6" t="n">
-        <v>96.01516700000001</v>
+        <v>96.020534</v>
       </c>
       <c r="O46" s="6" t="n">
         <v>97.487493</v>
@@ -3809,7 +3809,7 @@
       </c>
       <c r="M47" s="9" t="n"/>
       <c r="N47" s="9" t="n">
-        <v>96.513676</v>
+        <v>96.518294</v>
       </c>
       <c r="O47" s="9" t="n">
         <v>97.761562</v>
@@ -3887,7 +3887,7 @@
       </c>
       <c r="M48" s="6" t="n"/>
       <c r="N48" s="6" t="n">
-        <v>96.919253</v>
+        <v>96.92327400000001</v>
       </c>
       <c r="O48" s="6" t="n">
         <v>98.095491</v>
@@ -3965,7 +3965,7 @@
       </c>
       <c r="M49" s="9" t="n"/>
       <c r="N49" s="9" t="n">
-        <v>97.23245199999999</v>
+        <v>97.235997</v>
       </c>
       <c r="O49" s="9" t="n">
         <v>98.439329</v>
@@ -4043,7 +4043,7 @@
       </c>
       <c r="M50" s="6" t="n"/>
       <c r="N50" s="6" t="n">
-        <v>97.457053</v>
+        <v>97.46021</v>
       </c>
       <c r="O50" s="6" t="n">
         <v>98.816548</v>
@@ -4121,7 +4121,7 @@
       </c>
       <c r="M51" s="9" t="n"/>
       <c r="N51" s="9" t="n">
-        <v>97.60056299999999</v>
+        <v>97.603388</v>
       </c>
       <c r="O51" s="9" t="n">
         <v>99.223665</v>
@@ -4199,7 +4199,7 @@
       </c>
       <c r="M52" s="6" t="n"/>
       <c r="N52" s="6" t="n">
-        <v>97.687847</v>
+        <v>97.690355</v>
       </c>
       <c r="O52" s="6" t="n">
         <v>99.624047</v>
@@ -4277,7 +4277,7 @@
       </c>
       <c r="M53" s="9" t="n"/>
       <c r="N53" s="9" t="n">
-        <v>97.794072</v>
+        <v>97.79619</v>
       </c>
       <c r="O53" s="9" t="n">
         <v>99.99641200000001</v>
@@ -4355,7 +4355,7 @@
       </c>
       <c r="M54" s="6" t="n"/>
       <c r="N54" s="6" t="n">
-        <v>97.966244</v>
+        <v>97.967887</v>
       </c>
       <c r="O54" s="6" t="n">
         <v>100.354708</v>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="M55" s="9" t="n"/>
       <c r="N55" s="9" t="n">
-        <v>98.23016200000001</v>
+        <v>98.231318</v>
       </c>
       <c r="O55" s="9" t="n">
         <v>100.704746</v>
@@ -4511,7 +4511,7 @@
       </c>
       <c r="M56" s="6" t="n"/>
       <c r="N56" s="6" t="n">
-        <v>98.563427</v>
+        <v>98.56429300000001</v>
       </c>
       <c r="O56" s="6" t="n">
         <v>101.105744</v>
@@ -4589,7 +4589,7 @@
       </c>
       <c r="M57" s="9" t="n"/>
       <c r="N57" s="9" t="n">
-        <v>98.93799</v>
+        <v>98.93862300000001</v>
       </c>
       <c r="O57" s="9" t="n">
         <v>101.577774</v>
@@ -4667,7 +4667,7 @@
       </c>
       <c r="M58" s="6" t="n"/>
       <c r="N58" s="6" t="n">
-        <v>99.34953899999999</v>
+        <v>99.34989400000001</v>
       </c>
       <c r="O58" s="6" t="n">
         <v>102.067495</v>
@@ -4745,7 +4745,7 @@
       </c>
       <c r="M59" s="9" t="n"/>
       <c r="N59" s="9" t="n">
-        <v>99.802744</v>
+        <v>99.802719</v>
       </c>
       <c r="O59" s="9" t="n">
         <v>102.460664</v>
@@ -4823,7 +4823,7 @@
       </c>
       <c r="M60" s="6" t="n"/>
       <c r="N60" s="6" t="n">
-        <v>100.258239</v>
+        <v>100.257768</v>
       </c>
       <c r="O60" s="6" t="n">
         <v>102.720971</v>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="M61" s="9" t="n"/>
       <c r="N61" s="9" t="n">
-        <v>100.665427</v>
+        <v>100.664515</v>
       </c>
       <c r="O61" s="9" t="n">
         <v>102.871162</v>
@@ -4979,7 +4979,7 @@
       </c>
       <c r="M62" s="6" t="n"/>
       <c r="N62" s="6" t="n">
-        <v>101.004395</v>
+        <v>101.003087</v>
       </c>
       <c r="O62" s="6" t="n">
         <v>102.887526</v>
@@ -5057,7 +5057,7 @@
       </c>
       <c r="M63" s="9" t="n"/>
       <c r="N63" s="9" t="n">
-        <v>101.272127</v>
+        <v>101.270485</v>
       </c>
       <c r="O63" s="9" t="n">
         <v>102.820769</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="M64" s="6" t="n"/>
       <c r="N64" s="6" t="n">
-        <v>101.483991</v>
+        <v>101.482071</v>
       </c>
       <c r="O64" s="6" t="n">
         <v>102.75384</v>
@@ -5213,7 +5213,7 @@
       </c>
       <c r="M65" s="9" t="n"/>
       <c r="N65" s="9" t="n">
-        <v>101.632015</v>
+        <v>101.629892</v>
       </c>
       <c r="O65" s="9" t="n">
         <v>102.779026</v>
@@ -5291,7 +5291,7 @@
       </c>
       <c r="M66" s="6" t="n"/>
       <c r="N66" s="6" t="n">
-        <v>101.689445</v>
+        <v>101.687236</v>
       </c>
       <c r="O66" s="6" t="n">
         <v>102.870128</v>
@@ -5369,7 +5369,7 @@
       </c>
       <c r="M67" s="9" t="n"/>
       <c r="N67" s="9" t="n">
-        <v>101.639903</v>
+        <v>101.63775</v>
       </c>
       <c r="O67" s="9" t="n">
         <v>102.962627</v>
@@ -5447,7 +5447,7 @@
       </c>
       <c r="M68" s="6" t="n"/>
       <c r="N68" s="6" t="n">
-        <v>101.533699</v>
+        <v>101.53168</v>
       </c>
       <c r="O68" s="6" t="n">
         <v>102.952446</v>
@@ -5525,7 +5525,7 @@
       </c>
       <c r="M69" s="9" t="n"/>
       <c r="N69" s="9" t="n">
-        <v>101.413445</v>
+        <v>101.41158</v>
       </c>
       <c r="O69" s="9" t="n">
         <v>102.849597</v>
@@ -5603,7 +5603,7 @@
       </c>
       <c r="M70" s="6" t="n"/>
       <c r="N70" s="6" t="n">
-        <v>101.294322</v>
+        <v>101.292613</v>
       </c>
       <c r="O70" s="6" t="n">
         <v>102.637772</v>
@@ -5681,7 +5681,7 @@
       </c>
       <c r="M71" s="9" t="n"/>
       <c r="N71" s="9" t="n">
-        <v>101.182899</v>
+        <v>101.181336</v>
       </c>
       <c r="O71" s="9" t="n">
         <v>102.335775</v>
@@ -5759,7 +5759,7 @@
       </c>
       <c r="M72" s="6" t="n"/>
       <c r="N72" s="6" t="n">
-        <v>101.098066</v>
+        <v>101.096615</v>
       </c>
       <c r="O72" s="6" t="n">
         <v>101.931515</v>
@@ -5837,7 +5837,7 @@
       </c>
       <c r="M73" s="9" t="n"/>
       <c r="N73" s="9" t="n">
-        <v>101.055154</v>
+        <v>101.053761</v>
       </c>
       <c r="O73" s="9" t="n">
         <v>101.450228</v>
@@ -5915,7 +5915,7 @@
       </c>
       <c r="M74" s="6" t="n"/>
       <c r="N74" s="6" t="n">
-        <v>101.021534</v>
+        <v>101.020186</v>
       </c>
       <c r="O74" s="6" t="n">
         <v>100.975378</v>
@@ -5993,7 +5993,7 @@
       </c>
       <c r="M75" s="9" t="n"/>
       <c r="N75" s="9" t="n">
-        <v>100.984445</v>
+        <v>100.983146</v>
       </c>
       <c r="O75" s="9" t="n">
         <v>100.492392</v>
@@ -6071,7 +6071,7 @@
       </c>
       <c r="M76" s="6" t="n"/>
       <c r="N76" s="6" t="n">
-        <v>100.920798</v>
+        <v>100.919584</v>
       </c>
       <c r="O76" s="6" t="n">
         <v>100.004756</v>
@@ -6149,7 +6149,7 @@
       </c>
       <c r="M77" s="9" t="n"/>
       <c r="N77" s="9" t="n">
-        <v>100.792046</v>
+        <v>100.791002</v>
       </c>
       <c r="O77" s="9" t="n">
         <v>99.481739</v>
@@ -6229,7 +6229,7 @@
       </c>
       <c r="M78" s="6" t="n"/>
       <c r="N78" s="6" t="n">
-        <v>100.593891</v>
+        <v>100.59311</v>
       </c>
       <c r="O78" s="6" t="n">
         <v>98.959497</v>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="M79" s="9" t="n"/>
       <c r="N79" s="9" t="n">
-        <v>100.321488</v>
+        <v>100.321068</v>
       </c>
       <c r="O79" s="9" t="n">
         <v>98.47816</v>
@@ -6389,7 +6389,7 @@
       </c>
       <c r="M80" s="6" t="n"/>
       <c r="N80" s="6" t="n">
-        <v>99.992313</v>
+        <v>99.992328</v>
       </c>
       <c r="O80" s="6" t="n">
         <v>98.03691499999999</v>
@@ -6469,7 +6469,7 @@
       </c>
       <c r="M81" s="9" t="n"/>
       <c r="N81" s="9" t="n">
-        <v>99.64630099999999</v>
+        <v>99.64677399999999</v>
       </c>
       <c r="O81" s="9" t="n">
         <v>97.60441400000001</v>
@@ -6549,7 +6549,7 @@
       </c>
       <c r="M82" s="6" t="n"/>
       <c r="N82" s="6" t="n">
-        <v>99.277101</v>
+        <v>99.27806200000001</v>
       </c>
       <c r="O82" s="6" t="n">
         <v>97.19315899999999</v>
@@ -6629,7 +6629,7 @@
       </c>
       <c r="M83" s="9" t="n"/>
       <c r="N83" s="9" t="n">
-        <v>98.886428</v>
+        <v>98.887906</v>
       </c>
       <c r="O83" s="9" t="n">
         <v>96.906559</v>
@@ -6709,7 +6709,7 @@
       </c>
       <c r="M84" s="6" t="n"/>
       <c r="N84" s="6" t="n">
-        <v>98.50815299999999</v>
+        <v>98.510132</v>
       </c>
       <c r="O84" s="6" t="n">
         <v>96.837414</v>
@@ -6789,7 +6789,7 @@
       </c>
       <c r="M85" s="9" t="n"/>
       <c r="N85" s="9" t="n">
-        <v>98.180939</v>
+        <v>98.183351</v>
       </c>
       <c r="O85" s="9" t="n">
         <v>97.01312900000001</v>
@@ -6869,7 +6869,7 @@
       </c>
       <c r="M86" s="6" t="n"/>
       <c r="N86" s="6" t="n">
-        <v>97.95077499999999</v>
+        <v>97.953491</v>
       </c>
       <c r="O86" s="6" t="n">
         <v>97.362796</v>
@@ -6949,7 +6949,7 @@
       </c>
       <c r="M87" s="9" t="n"/>
       <c r="N87" s="9" t="n">
-        <v>97.839367</v>
+        <v>97.84223</v>
       </c>
       <c r="O87" s="9" t="n">
         <v>97.799617</v>
@@ -7029,7 +7029,7 @@
       </c>
       <c r="M88" s="6" t="n"/>
       <c r="N88" s="6" t="n">
-        <v>97.81147900000001</v>
+        <v>97.814378</v>
       </c>
       <c r="O88" s="6" t="n">
         <v>98.272766</v>
@@ -7109,7 +7109,7 @@
       </c>
       <c r="M89" s="9" t="n"/>
       <c r="N89" s="9" t="n">
-        <v>97.841663</v>
+        <v>97.844521</v>
       </c>
       <c r="O89" s="9" t="n">
         <v>98.765536</v>
@@ -7191,7 +7191,7 @@
         <v>102.505645</v>
       </c>
       <c r="N90" s="6" t="n">
-        <v>97.892993</v>
+        <v>97.89578299999999</v>
       </c>
       <c r="O90" s="6" t="n">
         <v>99.219624</v>
@@ -7273,7 +7273,7 @@
         <v>102.145931</v>
       </c>
       <c r="N91" s="9" t="n">
-        <v>97.95244</v>
+        <v>97.955151</v>
       </c>
       <c r="O91" s="9" t="n">
         <v>99.615661</v>
@@ -7355,7 +7355,7 @@
         <v>101.748141</v>
       </c>
       <c r="N92" s="6" t="n">
-        <v>98.018962</v>
+        <v>98.021584</v>
       </c>
       <c r="O92" s="6" t="n">
         <v>99.98959499999999</v>
@@ -7437,7 +7437,7 @@
         <v>101.338109</v>
       </c>
       <c r="N93" s="9" t="n">
-        <v>98.086065</v>
+        <v>98.08859699999999</v>
       </c>
       <c r="O93" s="9" t="n">
         <v>100.385082</v>
@@ -7519,7 +7519,7 @@
         <v>100.935514</v>
       </c>
       <c r="N94" s="6" t="n">
-        <v>98.165239</v>
+        <v>98.167666</v>
       </c>
       <c r="O94" s="6" t="n">
         <v>100.837509</v>
@@ -7601,7 +7601,7 @@
         <v>100.594494</v>
       </c>
       <c r="N95" s="9" t="n">
-        <v>98.272392</v>
+        <v>98.274676</v>
       </c>
       <c r="O95" s="9" t="n">
         <v>101.240763</v>
@@ -7683,7 +7683,7 @@
         <v>100.331462</v>
       </c>
       <c r="N96" s="6" t="n">
-        <v>98.412328</v>
+        <v>98.41442600000001</v>
       </c>
       <c r="O96" s="6" t="n">
         <v>101.461014</v>
@@ -7765,7 +7765,7 @@
         <v>100.14944</v>
       </c>
       <c r="N97" s="9" t="n">
-        <v>98.545681</v>
+        <v>98.547602</v>
       </c>
       <c r="O97" s="9" t="n">
         <v>101.453763</v>
@@ -7847,7 +7847,7 @@
         <v>100.048493</v>
       </c>
       <c r="N98" s="6" t="n">
-        <v>98.652556</v>
+        <v>98.65433400000001</v>
       </c>
       <c r="O98" s="6" t="n">
         <v>101.239914</v>
@@ -7929,7 +7929,7 @@
         <v>100.01127</v>
       </c>
       <c r="N99" s="9" t="n">
-        <v>98.745116</v>
+        <v>98.746771</v>
       </c>
       <c r="O99" s="9" t="n">
         <v>100.867646</v>
@@ -8011,7 +8011,7 @@
         <v>100.001253</v>
       </c>
       <c r="N100" s="6" t="n">
-        <v>98.84505799999999</v>
+        <v>98.84658</v>
       </c>
       <c r="O100" s="6" t="n">
         <v>100.352548</v>
@@ -8093,7 +8093,7 @@
         <v>100.034458</v>
       </c>
       <c r="N101" s="9" t="n">
-        <v>98.996773</v>
+        <v>98.998093</v>
       </c>
       <c r="O101" s="9" t="n">
         <v>99.789754</v>
@@ -8175,7 +8175,7 @@
         <v>100.154919</v>
       </c>
       <c r="N102" s="6" t="n">
-        <v>99.241058</v>
+        <v>99.242054</v>
       </c>
       <c r="O102" s="6" t="n">
         <v>99.273549</v>
@@ -8257,7 +8257,7 @@
         <v>100.325688</v>
       </c>
       <c r="N103" s="9" t="n">
-        <v>99.545348</v>
+        <v>99.545941</v>
       </c>
       <c r="O103" s="9" t="n">
         <v>98.863499</v>
@@ -8339,7 +8339,7 @@
         <v>100.516051</v>
       </c>
       <c r="N104" s="6" t="n">
-        <v>99.882403</v>
+        <v>99.882548</v>
       </c>
       <c r="O104" s="6" t="n">
         <v>98.625893</v>
@@ -8421,7 +8421,7 @@
         <v>100.677797</v>
       </c>
       <c r="N105" s="9" t="n">
-        <v>100.22264</v>
+        <v>100.222334</v>
       </c>
       <c r="O105" s="9" t="n">
         <v>98.56365</v>
@@ -8503,7 +8503,7 @@
         <v>100.796935</v>
       </c>
       <c r="N106" s="6" t="n">
-        <v>100.54233</v>
+        <v>100.5416</v>
       </c>
       <c r="O106" s="6" t="n">
         <v>98.63038400000001</v>
@@ -8585,7 +8585,7 @@
         <v>100.869219</v>
       </c>
       <c r="N107" s="9" t="n">
-        <v>100.826539</v>
+        <v>100.825433</v>
       </c>
       <c r="O107" s="9" t="n">
         <v>98.84425400000001</v>
@@ -8667,7 +8667,7 @@
         <v>100.895517</v>
       </c>
       <c r="N108" s="6" t="n">
-        <v>101.0659</v>
+        <v>101.064476</v>
       </c>
       <c r="O108" s="6" t="n">
         <v>99.19525899999999</v>
@@ -8749,7 +8749,7 @@
         <v>100.901976</v>
       </c>
       <c r="N109" s="9" t="n">
-        <v>101.255606</v>
+        <v>101.25393</v>
       </c>
       <c r="O109" s="9" t="n">
         <v>99.65191299999999</v>
@@ -8831,7 +8831,7 @@
         <v>100.912167</v>
       </c>
       <c r="N110" s="6" t="n">
-        <v>101.382544</v>
+        <v>101.380699</v>
       </c>
       <c r="O110" s="6" t="n">
         <v>100.15625</v>
@@ -8913,7 +8913,7 @@
         <v>100.90053</v>
       </c>
       <c r="N111" s="9" t="n">
-        <v>101.453116</v>
+        <v>101.451177</v>
       </c>
       <c r="O111" s="9" t="n">
         <v>100.685793</v>
@@ -8995,7 +8995,7 @@
         <v>100.859848</v>
       </c>
       <c r="N112" s="6" t="n">
-        <v>101.484906</v>
+        <v>101.482924</v>
       </c>
       <c r="O112" s="6" t="n">
         <v>101.220881</v>
@@ -9077,7 +9077,7 @@
         <v>100.759781</v>
       </c>
       <c r="N113" s="9" t="n">
-        <v>101.485166</v>
+        <v>101.483184</v>
       </c>
       <c r="O113" s="9" t="n">
         <v>101.651126</v>
@@ -9159,7 +9159,7 @@
         <v>100.579261</v>
       </c>
       <c r="N114" s="6" t="n">
-        <v>101.472124</v>
+        <v>101.470158</v>
       </c>
       <c r="O114" s="6" t="n">
         <v>101.950193</v>
@@ -9241,7 +9241,7 @@
         <v>100.333537</v>
       </c>
       <c r="N115" s="9" t="n">
-        <v>101.434323</v>
+        <v>101.432406</v>
       </c>
       <c r="O115" s="9" t="n">
         <v>102.125705</v>
@@ -9323,7 +9323,7 @@
         <v>100.078044</v>
       </c>
       <c r="N116" s="6" t="n">
-        <v>101.349857</v>
+        <v>101.348052</v>
       </c>
       <c r="O116" s="6" t="n">
         <v>102.14945</v>
@@ -9405,7 +9405,7 @@
         <v>99.848173</v>
       </c>
       <c r="N117" s="9" t="n">
-        <v>101.217953</v>
+        <v>101.216321</v>
       </c>
       <c r="O117" s="9" t="n">
         <v>102.01987</v>
@@ -9487,7 +9487,7 @@
         <v>99.65935</v>
       </c>
       <c r="N118" s="6" t="n">
-        <v>101.045453</v>
+        <v>101.044049</v>
       </c>
       <c r="O118" s="6" t="n">
         <v>101.78726</v>
@@ -9569,7 +9569,7 @@
         <v>99.49160500000001</v>
       </c>
       <c r="N119" s="9" t="n">
-        <v>100.859876</v>
+        <v>100.858718</v>
       </c>
       <c r="O119" s="9" t="n">
         <v>101.499675</v>
@@ -9651,7 +9651,7 @@
         <v>99.349518</v>
       </c>
       <c r="N120" s="6" t="n">
-        <v>100.673591</v>
+        <v>100.672678</v>
       </c>
       <c r="O120" s="6" t="n">
         <v>101.187001</v>
@@ -9733,7 +9733,7 @@
         <v>99.211206</v>
       </c>
       <c r="N121" s="9" t="n">
-        <v>100.537663</v>
+        <v>100.536931</v>
       </c>
       <c r="O121" s="9" t="n">
         <v>100.842161</v>
@@ -9815,7 +9815,7 @@
         <v>99.051051</v>
       </c>
       <c r="N122" s="6" t="n">
-        <v>100.451146</v>
+        <v>100.450527</v>
       </c>
       <c r="O122" s="6" t="n">
         <v>100.555113</v>
@@ -9897,7 +9897,7 @@
         <v>98.88392899999999</v>
       </c>
       <c r="N123" s="9" t="n">
-        <v>100.374445</v>
+        <v>100.373928</v>
       </c>
       <c r="O123" s="9" t="n">
         <v>100.408638</v>
@@ -9979,7 +9979,7 @@
         <v>98.749235</v>
       </c>
       <c r="N124" s="6" t="n">
-        <v>100.293431</v>
+        <v>100.293021</v>
       </c>
       <c r="O124" s="6" t="n">
         <v>100.406985</v>
@@ -10061,7 +10061,7 @@
         <v>98.653002</v>
       </c>
       <c r="N125" s="9" t="n">
-        <v>100.201901</v>
+        <v>100.201611</v>
       </c>
       <c r="O125" s="9" t="n">
         <v>100.508033</v>
@@ -10143,7 +10143,7 @@
         <v>98.607123</v>
       </c>
       <c r="N126" s="6" t="n">
-        <v>100.117984</v>
+        <v>100.117804</v>
       </c>
       <c r="O126" s="6" t="n">
         <v>100.648218</v>
@@ -10225,7 +10225,7 @@
         <v>98.66306</v>
       </c>
       <c r="N127" s="9" t="n">
-        <v>100.060988</v>
+        <v>100.060884</v>
       </c>
       <c r="O127" s="9" t="n">
         <v>100.779823</v>
@@ -10307,7 +10307,7 @@
         <v>98.838875</v>
       </c>
       <c r="N128" s="6" t="n">
-        <v>100.056448</v>
+        <v>100.056349</v>
       </c>
       <c r="O128" s="6" t="n">
         <v>100.889258</v>
@@ -10389,7 +10389,7 @@
         <v>99.10758199999999</v>
       </c>
       <c r="N129" s="9" t="n">
-        <v>100.110861</v>
+        <v>100.11069</v>
       </c>
       <c r="O129" s="9" t="n">
         <v>100.950111</v>
@@ -10471,7 +10471,7 @@
         <v>99.39531100000001</v>
       </c>
       <c r="N130" s="6" t="n">
-        <v>100.22437</v>
+        <v>100.224048</v>
       </c>
       <c r="O130" s="6" t="n">
         <v>100.974055</v>
@@ -10553,7 +10553,7 @@
         <v>99.637959</v>
       </c>
       <c r="N131" s="9" t="n">
-        <v>100.370938</v>
+        <v>100.370422</v>
       </c>
       <c r="O131" s="9" t="n">
         <v>100.95348</v>
@@ -10635,7 +10635,7 @@
         <v>99.767954</v>
       </c>
       <c r="N132" s="6" t="n">
-        <v>100.523246</v>
+        <v>100.522528</v>
       </c>
       <c r="O132" s="6" t="n">
         <v>100.946231</v>
@@ -10717,7 +10717,7 @@
         <v>99.739744</v>
       </c>
       <c r="N133" s="9" t="n">
-        <v>100.655925</v>
+        <v>100.655031</v>
       </c>
       <c r="O133" s="9" t="n">
         <v>100.999638</v>
@@ -10799,7 +10799,7 @@
         <v>99.622214</v>
       </c>
       <c r="N134" s="6" t="n">
-        <v>100.738316</v>
+        <v>100.737312</v>
       </c>
       <c r="O134" s="6" t="n">
         <v>101.064491</v>
@@ -10881,7 +10881,7 @@
         <v>99.484739</v>
       </c>
       <c r="N135" s="9" t="n">
-        <v>100.757939</v>
+        <v>100.756908</v>
       </c>
       <c r="O135" s="9" t="n">
         <v>101.067416</v>
@@ -10963,7 +10963,7 @@
         <v>99.29418</v>
       </c>
       <c r="N136" s="6" t="n">
-        <v>100.716531</v>
+        <v>100.715554</v>
       </c>
       <c r="O136" s="6" t="n">
         <v>100.933552</v>
@@ -11045,7 +11045,7 @@
         <v>99.098625</v>
       </c>
       <c r="N137" s="9" t="n">
-        <v>100.63709</v>
+        <v>100.636219</v>
       </c>
       <c r="O137" s="9" t="n">
         <v>100.718284</v>
@@ -11127,7 +11127,7 @@
         <v>98.90656799999999</v>
       </c>
       <c r="N138" s="6" t="n">
-        <v>100.528929</v>
+        <v>100.5282</v>
       </c>
       <c r="O138" s="6" t="n">
         <v>100.478603</v>
@@ -11209,7 +11209,7 @@
         <v>98.713013</v>
       </c>
       <c r="N139" s="9" t="n">
-        <v>100.416987</v>
+        <v>100.416406</v>
       </c>
       <c r="O139" s="9" t="n">
         <v>100.282145</v>
@@ -11291,7 +11291,7 @@
         <v>98.529905</v>
       </c>
       <c r="N140" s="6" t="n">
-        <v>100.326247</v>
+        <v>100.325786</v>
       </c>
       <c r="O140" s="6" t="n">
         <v>100.142935</v>
@@ -11373,7 +11373,7 @@
         <v>98.340757</v>
       </c>
       <c r="N141" s="9" t="n">
-        <v>100.276095</v>
+        <v>100.2757</v>
       </c>
       <c r="O141" s="9" t="n">
         <v>100.080943</v>
@@ -11455,7 +11455,7 @@
         <v>98.22070100000001</v>
       </c>
       <c r="N142" s="6" t="n">
-        <v>100.25898</v>
+        <v>100.258608</v>
       </c>
       <c r="O142" s="6" t="n">
         <v>100.088461</v>
@@ -11537,7 +11537,7 @@
         <v>98.264689</v>
       </c>
       <c r="N143" s="9" t="n">
-        <v>100.261962</v>
+        <v>100.261585</v>
       </c>
       <c r="O143" s="9" t="n">
         <v>100.126577</v>
@@ -11619,7 +11619,7 @@
         <v>98.516133</v>
       </c>
       <c r="N144" s="6" t="n">
-        <v>100.283657</v>
+        <v>100.283251</v>
       </c>
       <c r="O144" s="6" t="n">
         <v>100.157223</v>
@@ -11701,7 +11701,7 @@
         <v>98.87304899999999</v>
       </c>
       <c r="N145" s="9" t="n">
-        <v>100.31637</v>
+        <v>100.315921</v>
       </c>
       <c r="O145" s="9" t="n">
         <v>100.16226</v>
@@ -11783,7 +11783,7 @@
         <v>99.17898599999999</v>
       </c>
       <c r="N146" s="6" t="n">
-        <v>100.361433</v>
+        <v>100.360924</v>
       </c>
       <c r="O146" s="6" t="n">
         <v>100.114604</v>
@@ -11865,7 +11865,7 @@
         <v>99.379952</v>
       </c>
       <c r="N147" s="9" t="n">
-        <v>100.425478</v>
+        <v>100.424883</v>
       </c>
       <c r="O147" s="9" t="n">
         <v>99.996458</v>
@@ -11947,7 +11947,7 @@
         <v>99.450188</v>
       </c>
       <c r="N148" s="6" t="n">
-        <v>100.51403</v>
+        <v>100.513318</v>
       </c>
       <c r="O148" s="6" t="n">
         <v>99.90772699999999</v>
@@ -12029,7 +12029,7 @@
         <v>99.414552</v>
       </c>
       <c r="N149" s="9" t="n">
-        <v>100.611543</v>
+        <v>100.610701</v>
       </c>
       <c r="O149" s="9" t="n">
         <v>99.89586199999999</v>
@@ -12111,7 +12111,7 @@
         <v>99.311908</v>
       </c>
       <c r="N150" s="6" t="n">
-        <v>100.732318</v>
+        <v>100.731316</v>
       </c>
       <c r="O150" s="6" t="n">
         <v>99.94376200000001</v>
@@ -12193,7 +12193,7 @@
         <v>99.160231</v>
       </c>
       <c r="N151" s="9" t="n">
-        <v>100.874249</v>
+        <v>100.873057</v>
       </c>
       <c r="O151" s="9" t="n">
         <v>100.004625</v>
@@ -12275,7 +12275,7 @@
         <v>98.96181</v>
       </c>
       <c r="N152" s="6" t="n">
-        <v>101.01343</v>
+        <v>101.012053</v>
       </c>
       <c r="O152" s="6" t="n">
         <v>100.036684</v>
@@ -12357,7 +12357,7 @@
         <v>98.755171</v>
       </c>
       <c r="N153" s="9" t="n">
-        <v>101.11644</v>
+        <v>101.114925</v>
       </c>
       <c r="O153" s="9" t="n">
         <v>100.027131</v>
@@ -12439,7 +12439,7 @@
         <v>98.549961</v>
       </c>
       <c r="N154" s="6" t="n">
-        <v>101.170233</v>
+        <v>101.168646</v>
       </c>
       <c r="O154" s="6" t="n">
         <v>99.931487</v>
@@ -12521,7 +12521,7 @@
         <v>98.335803</v>
       </c>
       <c r="N155" s="9" t="n">
-        <v>101.171436</v>
+        <v>101.169848</v>
       </c>
       <c r="O155" s="9" t="n">
         <v>99.727564</v>
@@ -12603,7 +12603,7 @@
         <v>98.143238</v>
       </c>
       <c r="N156" s="6" t="n">
-        <v>101.127271</v>
+        <v>101.125745</v>
       </c>
       <c r="O156" s="6" t="n">
         <v>99.44500600000001</v>
@@ -12685,7 +12685,7 @@
         <v>98.01733</v>
       </c>
       <c r="N157" s="9" t="n">
-        <v>101.042696</v>
+        <v>101.041289</v>
       </c>
       <c r="O157" s="9" t="n">
         <v>99.103094</v>
@@ -12767,7 +12767,7 @@
         <v>98.045863</v>
       </c>
       <c r="N158" s="6" t="n">
-        <v>100.938767</v>
+        <v>100.93751</v>
       </c>
       <c r="O158" s="6" t="n">
         <v>98.759124</v>
@@ -12849,7 +12849,7 @@
         <v>98.23064599999999</v>
       </c>
       <c r="N159" s="9" t="n">
-        <v>100.824871</v>
+        <v>100.823783</v>
       </c>
       <c r="O159" s="9" t="n">
         <v>98.46948999999999</v>
@@ -12931,7 +12931,7 @@
         <v>98.497737</v>
       </c>
       <c r="N160" s="6" t="n">
-        <v>100.693439</v>
+        <v>100.692551</v>
       </c>
       <c r="O160" s="6" t="n">
         <v>98.273011</v>
@@ -13013,7 +13013,7 @@
         <v>98.748088</v>
       </c>
       <c r="N161" s="9" t="n">
-        <v>100.551053</v>
+        <v>100.550381</v>
       </c>
       <c r="O161" s="9" t="n">
         <v>98.155097</v>
@@ -13095,7 +13095,7 @@
         <v>98.995076</v>
       </c>
       <c r="N162" s="6" t="n">
-        <v>100.412185</v>
+        <v>100.41172</v>
       </c>
       <c r="O162" s="6" t="n">
         <v>98.09733</v>
@@ -13177,7 +13177,7 @@
         <v>99.202899</v>
       </c>
       <c r="N163" s="9" t="n">
-        <v>100.309694</v>
+        <v>100.30937</v>
       </c>
       <c r="O163" s="9" t="n">
         <v>98.07414</v>
@@ -13259,7 +13259,7 @@
         <v>99.33259200000001</v>
       </c>
       <c r="N164" s="6" t="n">
-        <v>100.233917</v>
+        <v>100.233685</v>
       </c>
       <c r="O164" s="6" t="n">
         <v>98.09599</v>
@@ -13341,7 +13341,7 @@
         <v>99.394111</v>
       </c>
       <c r="N165" s="9" t="n">
-        <v>100.175406</v>
+        <v>100.175238</v>
       </c>
       <c r="O165" s="9" t="n">
         <v>98.15438399999999</v>
@@ -13423,7 +13423,7 @@
         <v>99.457899</v>
       </c>
       <c r="N166" s="6" t="n">
-        <v>100.113812</v>
+        <v>100.113713</v>
       </c>
       <c r="O166" s="6" t="n">
         <v>98.264855</v>
@@ -13505,7 +13505,7 @@
         <v>99.53036</v>
       </c>
       <c r="N167" s="9" t="n">
-        <v>100.040858</v>
+        <v>100.040827</v>
       </c>
       <c r="O167" s="9" t="n">
         <v>98.446603</v>
@@ -13587,7 +13587,7 @@
         <v>99.636188</v>
       </c>
       <c r="N168" s="6" t="n">
-        <v>99.94884500000001</v>
+        <v>99.948885</v>
       </c>
       <c r="O168" s="6" t="n">
         <v>98.627031</v>
@@ -13669,7 +13669,7 @@
         <v>99.741989</v>
       </c>
       <c r="N169" s="9" t="n">
-        <v>99.842817</v>
+        <v>99.842955</v>
       </c>
       <c r="O169" s="9" t="n">
         <v>98.78427000000001</v>
@@ -13751,7 +13751,7 @@
         <v>99.785819</v>
       </c>
       <c r="N170" s="6" t="n">
-        <v>99.78045299999999</v>
+        <v>99.780647</v>
       </c>
       <c r="O170" s="6" t="n">
         <v>98.931074</v>
@@ -13833,7 +13833,7 @@
         <v>99.755782</v>
       </c>
       <c r="N171" s="9" t="n">
-        <v>99.774691</v>
+        <v>99.77489199999999</v>
       </c>
       <c r="O171" s="9" t="n">
         <v>99.084312</v>
@@ -13915,7 +13915,7 @@
         <v>99.680899</v>
       </c>
       <c r="N172" s="6" t="n">
-        <v>99.842652</v>
+        <v>99.842769</v>
       </c>
       <c r="O172" s="6" t="n">
         <v>99.23784499999999</v>
@@ -13997,7 +13997,7 @@
         <v>99.561831</v>
       </c>
       <c r="N173" s="9" t="n">
-        <v>100.003455</v>
+        <v>100.00337</v>
       </c>
       <c r="O173" s="9" t="n">
         <v>99.379774</v>
@@ -14079,7 +14079,7 @@
         <v>99.383966</v>
       </c>
       <c r="N174" s="6" t="n">
-        <v>100.21716</v>
+        <v>100.216829</v>
       </c>
       <c r="O174" s="6" t="n">
         <v>99.556181</v>
@@ -14161,7 +14161,7 @@
         <v>99.149326</v>
       </c>
       <c r="N175" s="9" t="n">
-        <v>100.433036</v>
+        <v>100.432461</v>
       </c>
       <c r="O175" s="9" t="n">
         <v>99.763295</v>
@@ -14243,7 +14243,7 @@
         <v>98.895264</v>
       </c>
       <c r="N176" s="6" t="n">
-        <v>100.616494</v>
+        <v>100.615708</v>
       </c>
       <c r="O176" s="6" t="n">
         <v>99.94620999999999</v>
@@ -14325,7 +14325,7 @@
         <v>98.650632</v>
       </c>
       <c r="N177" s="9" t="n">
-        <v>100.771587</v>
+        <v>100.770618</v>
       </c>
       <c r="O177" s="9" t="n">
         <v>100.037318</v>
@@ -14407,7 +14407,7 @@
         <v>98.43951300000001</v>
       </c>
       <c r="N178" s="6" t="n">
-        <v>100.891778</v>
+        <v>100.890647</v>
       </c>
       <c r="O178" s="6" t="n">
         <v>100.024936</v>
@@ -14489,7 +14489,7 @@
         <v>98.319558</v>
       </c>
       <c r="N179" s="9" t="n">
-        <v>100.971814</v>
+        <v>100.970553</v>
       </c>
       <c r="O179" s="9" t="n">
         <v>99.937353</v>
@@ -14571,7 +14571,7 @@
         <v>98.30601</v>
       </c>
       <c r="N180" s="6" t="n">
-        <v>101.001825</v>
+        <v>101.00049</v>
       </c>
       <c r="O180" s="6" t="n">
         <v>99.84246899999999</v>
@@ -14653,7 +14653,7 @@
         <v>98.409738</v>
       </c>
       <c r="N181" s="9" t="n">
-        <v>100.978331</v>
+        <v>100.976986</v>
       </c>
       <c r="O181" s="9" t="n">
         <v>99.76661199999999</v>
@@ -14735,7 +14735,7 @@
         <v>98.65625900000001</v>
       </c>
       <c r="N182" s="6" t="n">
-        <v>100.902762</v>
+        <v>100.901483</v>
       </c>
       <c r="O182" s="6" t="n">
         <v>99.681062</v>
@@ -14817,7 +14817,7 @@
         <v>99.032411</v>
       </c>
       <c r="N183" s="9" t="n">
-        <v>100.763539</v>
+        <v>100.762438</v>
       </c>
       <c r="O183" s="9" t="n">
         <v>99.531655</v>
@@ -14899,7 +14899,7 @@
         <v>99.528628</v>
       </c>
       <c r="N184" s="6" t="n">
-        <v>100.520509</v>
+        <v>100.519734</v>
       </c>
       <c r="O184" s="6" t="n">
         <v>99.233773</v>
@@ -14981,7 +14981,7 @@
         <v>100.139565</v>
       </c>
       <c r="N185" s="9" t="n">
-        <v>100.154459</v>
+        <v>100.15417</v>
       </c>
       <c r="O185" s="9" t="n">
         <v>98.78295</v>
@@ -15063,7 +15063,7 @@
         <v>100.874701</v>
       </c>
       <c r="N186" s="6" t="n">
-        <v>99.688078</v>
+        <v>99.68842600000001</v>
       </c>
       <c r="O186" s="6" t="n">
         <v>98.206176</v>
@@ -15145,7 +15145,7 @@
         <v>101.694512</v>
       </c>
       <c r="N187" s="9" t="n">
-        <v>99.19038999999999</v>
+        <v>99.191416</v>
       </c>
       <c r="O187" s="9" t="n">
         <v>97.607215</v>
@@ -15227,7 +15227,7 @@
         <v>102.522743</v>
       </c>
       <c r="N188" s="6" t="n">
-        <v>98.73393299999999</v>
+        <v>98.735574</v>
       </c>
       <c r="O188" s="6" t="n">
         <v>97.133386</v>
@@ -15309,7 +15309,7 @@
         <v>103.281993</v>
       </c>
       <c r="N189" s="9" t="n">
-        <v>98.35557900000001</v>
+        <v>98.35772900000001</v>
       </c>
       <c r="O189" s="9" t="n">
         <v>96.934489</v>
@@ -15391,7 +15391,7 @@
         <v>103.909397</v>
       </c>
       <c r="N190" s="6" t="n">
-        <v>98.10335600000001</v>
+        <v>98.10583699999999</v>
       </c>
       <c r="O190" s="6" t="n">
         <v>97.057682</v>
@@ -15473,7 +15473,7 @@
         <v>104.360716</v>
       </c>
       <c r="N191" s="9" t="n">
-        <v>97.967546</v>
+        <v>97.970189</v>
       </c>
       <c r="O191" s="9" t="n">
         <v>97.46702999999999</v>
@@ -15555,7 +15555,7 @@
         <v>104.616837</v>
       </c>
       <c r="N192" s="6" t="n">
-        <v>97.926462</v>
+        <v>97.929143</v>
       </c>
       <c r="O192" s="6" t="n">
         <v>98.04333</v>
@@ -15637,7 +15637,7 @@
         <v>104.683472</v>
       </c>
       <c r="N193" s="9" t="n">
-        <v>97.960284</v>
+        <v>97.962918</v>
       </c>
       <c r="O193" s="9" t="n">
         <v>98.69188200000001</v>
@@ -15719,7 +15719,7 @@
         <v>104.574424</v>
       </c>
       <c r="N194" s="6" t="n">
-        <v>98.027846</v>
+        <v>98.03039800000001</v>
       </c>
       <c r="O194" s="6" t="n">
         <v>99.352406</v>
@@ -15801,7 +15801,7 @@
         <v>104.339403</v>
       </c>
       <c r="N195" s="9" t="n">
-        <v>98.11821500000001</v>
+        <v>98.120653</v>
       </c>
       <c r="O195" s="9" t="n">
         <v>99.99030399999999</v>
@@ -15883,7 +15883,7 @@
         <v>104.030338</v>
       </c>
       <c r="N196" s="6" t="n">
-        <v>98.24487000000001</v>
+        <v>98.247152</v>
       </c>
       <c r="O196" s="6" t="n">
         <v>100.595184</v>
@@ -15965,7 +15965,7 @@
         <v>103.680714</v>
       </c>
       <c r="N197" s="9" t="n">
-        <v>98.403447</v>
+        <v>98.405537</v>
       </c>
       <c r="O197" s="9" t="n">
         <v>101.117972</v>
@@ -16047,7 +16047,7 @@
         <v>103.301362</v>
       </c>
       <c r="N198" s="6" t="n">
-        <v>98.576204</v>
+        <v>98.578085</v>
       </c>
       <c r="O198" s="6" t="n">
         <v>101.510859</v>
@@ -16129,7 +16129,7 @@
         <v>102.929043</v>
       </c>
       <c r="N199" s="9" t="n">
-        <v>98.750491</v>
+        <v>98.75215300000001</v>
       </c>
       <c r="O199" s="9" t="n">
         <v>101.757798</v>
@@ -16211,7 +16211,7 @@
         <v>102.591436</v>
       </c>
       <c r="N200" s="6" t="n">
-        <v>98.90775499999999</v>
+        <v>98.909221</v>
       </c>
       <c r="O200" s="6" t="n">
         <v>101.909062</v>
@@ -16293,7 +16293,7 @@
         <v>102.3114</v>
       </c>
       <c r="N201" s="9" t="n">
-        <v>99.04475499999999</v>
+        <v>99.046043</v>
       </c>
       <c r="O201" s="9" t="n">
         <v>101.973943</v>
@@ -16375,7 +16375,7 @@
         <v>102.106223</v>
       </c>
       <c r="N202" s="6" t="n">
-        <v>99.153679</v>
+        <v>99.154827</v>
       </c>
       <c r="O202" s="6" t="n">
         <v>101.949382</v>
@@ -16457,7 +16457,7 @@
         <v>101.993646</v>
       </c>
       <c r="N203" s="9" t="n">
-        <v>99.236716</v>
+        <v>99.23775000000001</v>
       </c>
       <c r="O203" s="9" t="n">
         <v>101.827988</v>
@@ -16539,7 +16539,7 @@
         <v>101.966094</v>
       </c>
       <c r="N204" s="6" t="n">
-        <v>99.32405</v>
+        <v>99.32493700000001</v>
       </c>
       <c r="O204" s="6" t="n">
         <v>101.656758</v>
@@ -16621,7 +16621,7 @@
         <v>102.022975</v>
       </c>
       <c r="N205" s="9" t="n">
-        <v>99.407473</v>
+        <v>99.40821200000001</v>
       </c>
       <c r="O205" s="9" t="n">
         <v>101.459561</v>
@@ -16703,7 +16703,7 @@
         <v>102.145831</v>
       </c>
       <c r="N206" s="6" t="n">
-        <v>99.475847</v>
+        <v>99.47646899999999</v>
       </c>
       <c r="O206" s="6" t="n">
         <v>101.236249</v>
@@ -16785,7 +16785,7 @@
         <v>102.250722</v>
       </c>
       <c r="N207" s="9" t="n">
-        <v>99.52188200000001</v>
+        <v>99.522437</v>
       </c>
       <c r="O207" s="9" t="n">
         <v>101.029187</v>
@@ -16867,7 +16867,7 @@
         <v>102.254282</v>
       </c>
       <c r="N208" s="6" t="n">
-        <v>99.542753</v>
+        <v>99.543284</v>
       </c>
       <c r="O208" s="6" t="n">
         <v>100.893659</v>
@@ -16949,7 +16949,7 @@
         <v>102.142713</v>
       </c>
       <c r="N209" s="9" t="n">
-        <v>99.56228400000001</v>
+        <v>99.562787</v>
       </c>
       <c r="O209" s="9" t="n">
         <v>100.873014</v>
@@ -17031,7 +17031,7 @@
         <v>101.942383</v>
       </c>
       <c r="N210" s="6" t="n">
-        <v>99.618022</v>
+        <v>99.618467</v>
       </c>
       <c r="O210" s="6" t="n">
         <v>100.946766</v>
@@ -17113,7 +17113,7 @@
         <v>101.694818</v>
       </c>
       <c r="N211" s="9" t="n">
-        <v>99.70281900000001</v>
+        <v>99.703171</v>
       </c>
       <c r="O211" s="9" t="n">
         <v>101.075557</v>
@@ -17195,7 +17195,7 @@
         <v>101.449137</v>
       </c>
       <c r="N212" s="6" t="n">
-        <v>99.808397</v>
+        <v>99.808628</v>
       </c>
       <c r="O212" s="6" t="n">
         <v>101.18355</v>
@@ -17277,7 +17277,7 @@
         <v>101.208194</v>
       </c>
       <c r="N213" s="9" t="n">
-        <v>99.920496</v>
+        <v>99.920598</v>
       </c>
       <c r="O213" s="9" t="n">
         <v>101.255403</v>
@@ -17359,7 +17359,7 @@
         <v>100.957131</v>
       </c>
       <c r="N214" s="6" t="n">
-        <v>100.031551</v>
+        <v>100.031516</v>
       </c>
       <c r="O214" s="6" t="n">
         <v>101.292803</v>
@@ -17441,7 +17441,7 @@
         <v>100.691173</v>
       </c>
       <c r="N215" s="9" t="n">
-        <v>100.143371</v>
+        <v>100.143192</v>
       </c>
       <c r="O215" s="9" t="n">
         <v>101.306987</v>
@@ -17523,7 +17523,7 @@
         <v>100.444159</v>
       </c>
       <c r="N216" s="6" t="n">
-        <v>100.245406</v>
+        <v>100.24509</v>
       </c>
       <c r="O216" s="6" t="n">
         <v>101.317731</v>
@@ -17605,7 +17605,7 @@
         <v>100.205953</v>
       </c>
       <c r="N217" s="9" t="n">
-        <v>100.331473</v>
+        <v>100.331042</v>
       </c>
       <c r="O217" s="9" t="n">
         <v>101.365232</v>
@@ -17687,7 +17687,7 @@
         <v>100.013279</v>
       </c>
       <c r="N218" s="6" t="n">
-        <v>100.406185</v>
+        <v>100.405643</v>
       </c>
       <c r="O218" s="6" t="n">
         <v>101.444929</v>
@@ -17769,7 +17769,7 @@
         <v>99.891732</v>
       </c>
       <c r="N219" s="9" t="n">
-        <v>100.472125</v>
+        <v>100.471487</v>
       </c>
       <c r="O219" s="9" t="n">
         <v>101.520116</v>
@@ -17851,7 +17851,7 @@
         <v>99.844444</v>
       </c>
       <c r="N220" s="6" t="n">
-        <v>100.529471</v>
+        <v>100.528748</v>
       </c>
       <c r="O220" s="6" t="n">
         <v>101.561943</v>
@@ -17933,7 +17933,7 @@
         <v>99.846621</v>
       </c>
       <c r="N221" s="9" t="n">
-        <v>100.571143</v>
+        <v>100.570348</v>
       </c>
       <c r="O221" s="9" t="n">
         <v>101.552815</v>
@@ -18015,7 +18015,7 @@
         <v>99.89007700000001</v>
       </c>
       <c r="N222" s="6" t="n">
-        <v>100.597709</v>
+        <v>100.596871</v>
       </c>
       <c r="O222" s="6" t="n">
         <v>101.488278</v>
@@ -18097,7 +18097,7 @@
         <v>99.932492</v>
       </c>
       <c r="N223" s="9" t="n">
-        <v>100.595021</v>
+        <v>100.594183</v>
       </c>
       <c r="O223" s="9" t="n">
         <v>101.388178</v>
@@ -18179,7 +18179,7 @@
         <v>99.95344900000001</v>
       </c>
       <c r="N224" s="6" t="n">
-        <v>100.555884</v>
+        <v>100.555099</v>
       </c>
       <c r="O224" s="6" t="n">
         <v>101.224646</v>
@@ -18261,7 +18261,7 @@
         <v>99.967405</v>
       </c>
       <c r="N225" s="9" t="n">
-        <v>100.474418</v>
+        <v>100.473757</v>
       </c>
       <c r="O225" s="9" t="n">
         <v>100.99528</v>
@@ -18343,7 +18343,7 @@
         <v>100.000069</v>
       </c>
       <c r="N226" s="6" t="n">
-        <v>100.356471</v>
+        <v>100.355994</v>
       </c>
       <c r="O226" s="6" t="n">
         <v>100.766572</v>
@@ -18425,7 +18425,7 @@
         <v>100.026174</v>
       </c>
       <c r="N227" s="9" t="n">
-        <v>100.220202</v>
+        <v>100.219921</v>
       </c>
       <c r="O227" s="9" t="n">
         <v>100.56545</v>
@@ -18507,7 +18507,7 @@
         <v>100.013657</v>
       </c>
       <c r="N228" s="6" t="n">
-        <v>100.089906</v>
+        <v>100.089795</v>
       </c>
       <c r="O228" s="6" t="n">
         <v>100.375216</v>
@@ -18589,7 +18589,7 @@
         <v>99.97425699999999</v>
       </c>
       <c r="N229" s="9" t="n">
-        <v>99.981208</v>
+        <v>99.981236</v>
       </c>
       <c r="O229" s="9" t="n">
         <v>100.170897</v>
@@ -18671,7 +18671,7 @@
         <v>99.924115</v>
       </c>
       <c r="N230" s="6" t="n">
-        <v>99.90106299999999</v>
+        <v>99.90118699999999</v>
       </c>
       <c r="O230" s="6" t="n">
         <v>99.96684999999999</v>
@@ -18753,7 +18753,7 @@
         <v>99.85794300000001</v>
       </c>
       <c r="N231" s="9" t="n">
-        <v>99.841312</v>
+        <v>99.841497</v>
       </c>
       <c r="O231" s="9" t="n">
         <v>99.76700200000001</v>
@@ -18835,7 +18835,7 @@
         <v>99.759507</v>
       </c>
       <c r="N232" s="6" t="n">
-        <v>99.799183</v>
+        <v>99.799404</v>
       </c>
       <c r="O232" s="6" t="n">
         <v>99.570707</v>
@@ -18917,7 +18917,7 @@
         <v>99.63978299999999</v>
       </c>
       <c r="N233" s="9" t="n">
-        <v>99.771214</v>
+        <v>99.771463</v>
       </c>
       <c r="O233" s="9" t="n">
         <v>99.408389</v>
@@ -18999,7 +18999,7 @@
         <v>99.47354</v>
       </c>
       <c r="N234" s="6" t="n">
-        <v>99.77301300000001</v>
+        <v>99.77327099999999</v>
       </c>
       <c r="O234" s="6" t="n">
         <v>99.313047</v>
@@ -19081,7 +19081,7 @@
         <v>99.285849</v>
       </c>
       <c r="N235" s="9" t="n">
-        <v>99.81453500000001</v>
+        <v>99.814745</v>
       </c>
       <c r="O235" s="9" t="n">
         <v>99.309934</v>
@@ -19163,7 +19163,7 @@
         <v>99.063266</v>
       </c>
       <c r="N236" s="6" t="n">
-        <v>99.891158</v>
+        <v>99.891273</v>
       </c>
       <c r="O236" s="6" t="n">
         <v>99.40194</v>
@@ -19327,7 +19327,7 @@
         <v>98.57602300000001</v>
       </c>
       <c r="N238" s="6" t="n">
-        <v>100.093697</v>
+        <v>100.093583</v>
       </c>
       <c r="O238" s="6" t="n">
         <v>99.786002</v>
@@ -19409,7 +19409,7 @@
         <v>98.38342400000001</v>
       </c>
       <c r="N239" s="9" t="n">
-        <v>100.192889</v>
+        <v>100.192662</v>
       </c>
       <c r="O239" s="9" t="n">
         <v>99.961513</v>
@@ -19491,7 +19491,7 @@
         <v>98.203025</v>
       </c>
       <c r="N240" s="6" t="n">
-        <v>100.285093</v>
+        <v>100.284733</v>
       </c>
       <c r="O240" s="6" t="n">
         <v>100.129883</v>
@@ -19573,7 +19573,7 @@
         <v>98.075113</v>
       </c>
       <c r="N241" s="9" t="n">
-        <v>100.377273</v>
+        <v>100.376772</v>
       </c>
       <c r="O241" s="9" t="n">
         <v>100.274099</v>
@@ -19655,7 +19655,7 @@
         <v>97.997096</v>
       </c>
       <c r="N242" s="6" t="n">
-        <v>100.473648</v>
+        <v>100.473005</v>
       </c>
       <c r="O242" s="6" t="n">
         <v>100.420729</v>
@@ -19737,7 +19737,7 @@
         <v>97.98635899999999</v>
       </c>
       <c r="N243" s="9" t="n">
-        <v>100.581864</v>
+        <v>100.581075</v>
       </c>
       <c r="O243" s="9" t="n">
         <v>100.58824</v>
@@ -19819,7 +19819,7 @@
         <v>98.030119</v>
       </c>
       <c r="N244" s="6" t="n">
-        <v>100.702642</v>
+        <v>100.701678</v>
       </c>
       <c r="O244" s="6" t="n">
         <v>100.744343</v>
@@ -19901,7 +19901,7 @@
         <v>98.106086</v>
       </c>
       <c r="N245" s="9" t="n">
-        <v>100.835624</v>
+        <v>100.834466</v>
       </c>
       <c r="O245" s="9" t="n">
         <v>100.880699</v>
@@ -19983,7 +19983,7 @@
         <v>98.192639</v>
       </c>
       <c r="N246" s="6" t="n">
-        <v>100.973945</v>
+        <v>100.972602</v>
       </c>
       <c r="O246" s="6" t="n">
         <v>100.991365</v>
@@ -20065,7 +20065,7 @@
         <v>98.285622</v>
       </c>
       <c r="N247" s="9" t="n">
-        <v>101.100266</v>
+        <v>101.098766</v>
       </c>
       <c r="O247" s="9" t="n">
         <v>101.03665</v>
@@ -20147,7 +20147,7 @@
         <v>98.368903</v>
       </c>
       <c r="N248" s="6" t="n">
-        <v>101.220627</v>
+        <v>101.218977</v>
       </c>
       <c r="O248" s="6" t="n">
         <v>101.057634</v>
@@ -20229,7 +20229,7 @@
         <v>98.43029199999999</v>
       </c>
       <c r="N249" s="9" t="n">
-        <v>101.353368</v>
+        <v>101.351557</v>
       </c>
       <c r="O249" s="9" t="n">
         <v>101.054736</v>
@@ -20311,7 +20311,7 @@
         <v>98.42809699999999</v>
       </c>
       <c r="N250" s="6" t="n">
-        <v>101.491925</v>
+        <v>101.489938</v>
       </c>
       <c r="O250" s="6" t="n">
         <v>101.02227</v>
@@ -20393,7 +20393,7 @@
         <v>98.36959899999999</v>
       </c>
       <c r="N251" s="9" t="n">
-        <v>101.620261</v>
+        <v>101.61811</v>
       </c>
       <c r="O251" s="9" t="n">
         <v>100.98814</v>
@@ -20475,7 +20475,7 @@
         <v>98.304012</v>
       </c>
       <c r="N252" s="6" t="n">
-        <v>101.727241</v>
+        <v>101.724951</v>
       </c>
       <c r="O252" s="6" t="n">
         <v>100.900579</v>
@@ -20557,7 +20557,7 @@
         <v>98.242548</v>
       </c>
       <c r="N253" s="9" t="n">
-        <v>101.795031</v>
+        <v>101.792656</v>
       </c>
       <c r="O253" s="9" t="n">
         <v>100.773598</v>
@@ -20639,7 +20639,7 @@
         <v>98.14287400000001</v>
       </c>
       <c r="N254" s="6" t="n">
-        <v>101.813423</v>
+        <v>101.811027</v>
       </c>
       <c r="O254" s="6" t="n">
         <v>100.594735</v>
@@ -20721,7 +20721,7 @@
         <v>98.03489</v>
       </c>
       <c r="N255" s="9" t="n">
-        <v>101.780165</v>
+        <v>101.777811</v>
       </c>
       <c r="O255" s="9" t="n">
         <v>100.325693</v>
@@ -20803,7 +20803,7 @@
         <v>98.04242000000001</v>
       </c>
       <c r="N256" s="6" t="n">
-        <v>101.691687</v>
+        <v>101.689446</v>
       </c>
       <c r="O256" s="6" t="n">
         <v>100.000222</v>
@@ -20885,7 +20885,7 @@
         <v>98.18418</v>
       </c>
       <c r="N257" s="9" t="n">
-        <v>101.550311</v>
+        <v>101.548248</v>
       </c>
       <c r="O257" s="9" t="n">
         <v>99.615005</v>
@@ -20967,7 +20967,7 @@
         <v>98.40951699999999</v>
       </c>
       <c r="N258" s="6" t="n">
-        <v>101.362216</v>
+        <v>101.360381</v>
       </c>
       <c r="O258" s="6" t="n">
         <v>99.226553</v>
@@ -21049,7 +21049,7 @@
         <v>98.627904</v>
       </c>
       <c r="N259" s="9" t="n">
-        <v>101.155111</v>
+        <v>101.153528</v>
       </c>
       <c r="O259" s="9" t="n">
         <v>98.89233</v>
@@ -21131,7 +21131,7 @@
         <v>98.759429</v>
       </c>
       <c r="N260" s="6" t="n">
-        <v>100.941924</v>
+        <v>100.940611</v>
       </c>
       <c r="O260" s="6" t="n">
         <v>98.62803</v>
@@ -21213,7 +21213,7 @@
         <v>98.83910400000001</v>
       </c>
       <c r="N261" s="9" t="n">
-        <v>100.713381</v>
+        <v>100.712375</v>
       </c>
       <c r="O261" s="9" t="n">
         <v>98.437274</v>
@@ -21295,7 +21295,7 @@
         <v>98.894919</v>
       </c>
       <c r="N262" s="6" t="n">
-        <v>100.471632</v>
+        <v>100.470972</v>
       </c>
       <c r="O262" s="6" t="n">
         <v>98.350855</v>
@@ -21377,7 +21377,7 @@
         <v>98.907971</v>
       </c>
       <c r="N263" s="9" t="n">
-        <v>100.240478</v>
+        <v>100.240152</v>
       </c>
       <c r="O263" s="9" t="n">
         <v>98.330592</v>
@@ -21459,7 +21459,7 @@
         <v>98.923818</v>
       </c>
       <c r="N264" s="6" t="n">
-        <v>100.034526</v>
+        <v>100.034476</v>
       </c>
       <c r="O264" s="6" t="n">
         <v>98.36838400000001</v>
@@ -21541,7 +21541,7 @@
         <v>98.978926</v>
       </c>
       <c r="N265" s="9" t="n">
-        <v>99.86706700000001</v>
+        <v>99.867227</v>
       </c>
       <c r="O265" s="9" t="n">
         <v>98.422907</v>
@@ -21623,7 +21623,7 @@
         <v>99.11685</v>
       </c>
       <c r="N266" s="6" t="n">
-        <v>99.733389</v>
+        <v>99.73371400000001</v>
       </c>
       <c r="O266" s="6" t="n">
         <v>98.46892</v>
@@ -21705,7 +21705,7 @@
         <v>99.317302</v>
       </c>
       <c r="N267" s="9" t="n">
-        <v>99.626424</v>
+        <v>99.626873</v>
       </c>
       <c r="O267" s="9" t="n">
         <v>98.556331</v>
@@ -21787,7 +21787,7 @@
         <v>99.51432699999999</v>
       </c>
       <c r="N268" s="6" t="n">
-        <v>99.548011</v>
+        <v>99.54854899999999</v>
       </c>
       <c r="O268" s="6" t="n">
         <v>98.695598</v>
@@ -21869,7 +21869,7 @@
         <v>99.686216</v>
       </c>
       <c r="N269" s="9" t="n">
-        <v>99.507159</v>
+        <v>99.50775</v>
       </c>
       <c r="O269" s="9" t="n">
         <v>98.90544</v>
@@ -21951,7 +21951,7 @@
         <v>99.78176999999999</v>
       </c>
       <c r="N270" s="6" t="n">
-        <v>99.50595800000001</v>
+        <v>99.506559</v>
       </c>
       <c r="O270" s="6" t="n">
         <v>99.157911</v>
@@ -22033,7 +22033,7 @@
         <v>99.798507</v>
       </c>
       <c r="N271" s="9" t="n">
-        <v>99.547132</v>
+        <v>99.54769400000001</v>
       </c>
       <c r="O271" s="9" t="n">
         <v>99.41578699999999</v>
@@ -22115,7 +22115,7 @@
         <v>99.783028</v>
       </c>
       <c r="N272" s="6" t="n">
-        <v>99.599718</v>
+        <v>99.600229</v>
       </c>
       <c r="O272" s="6" t="n">
         <v>99.614178</v>
@@ -22197,7 +22197,7 @@
         <v>99.737453</v>
       </c>
       <c r="N273" s="9" t="n">
-        <v>99.632903</v>
+        <v>99.633388</v>
       </c>
       <c r="O273" s="9" t="n">
         <v>99.693658</v>
@@ -22279,7 +22279,7 @@
         <v>99.674167</v>
       </c>
       <c r="N274" s="6" t="n">
-        <v>99.640725</v>
+        <v>99.641215</v>
       </c>
       <c r="O274" s="6" t="n">
         <v>99.659221</v>
@@ -22361,7 +22361,7 @@
         <v>99.605881</v>
       </c>
       <c r="N275" s="9" t="n">
-        <v>99.617377</v>
+        <v>99.617907</v>
       </c>
       <c r="O275" s="9" t="n">
         <v>99.514285</v>
@@ -22443,7 +22443,7 @@
         <v>99.559022</v>
       </c>
       <c r="N276" s="6" t="n">
-        <v>99.568095</v>
+        <v>99.568675</v>
       </c>
       <c r="O276" s="6" t="n">
         <v>99.329511</v>
@@ -22525,7 +22525,7 @@
         <v>99.489159</v>
       </c>
       <c r="N277" s="9" t="n">
-        <v>99.4956</v>
+        <v>99.496244</v>
       </c>
       <c r="O277" s="9" t="n">
         <v>99.161208</v>
@@ -22607,7 +22607,7 @@
         <v>99.39760699999999</v>
       </c>
       <c r="N278" s="6" t="n">
-        <v>99.405604</v>
+        <v>99.40633699999999</v>
       </c>
       <c r="O278" s="6" t="n">
         <v>99.03699400000001</v>
@@ -22689,7 +22689,7 @@
         <v>99.28125300000001</v>
       </c>
       <c r="N279" s="9" t="n">
-        <v>99.304765</v>
+        <v>99.30562</v>
       </c>
       <c r="O279" s="9" t="n">
         <v>98.953535</v>
@@ -22771,7 +22771,7 @@
         <v>99.191298</v>
       </c>
       <c r="N280" s="6" t="n">
-        <v>99.2075</v>
+        <v>99.208493</v>
       </c>
       <c r="O280" s="6" t="n">
         <v>98.906184</v>
@@ -22853,7 +22853,7 @@
         <v>99.151517</v>
       </c>
       <c r="N281" s="9" t="n">
-        <v>99.119569</v>
+        <v>99.12068600000001</v>
       </c>
       <c r="O281" s="9" t="n">
         <v>98.858953</v>
@@ -22935,7 +22935,7 @@
         <v>99.210168</v>
       </c>
       <c r="N282" s="6" t="n">
-        <v>99.041619</v>
+        <v>99.04284</v>
       </c>
       <c r="O282" s="6" t="n">
         <v>98.801851</v>
@@ -23017,7 +23017,7 @@
         <v>99.365319</v>
       </c>
       <c r="N283" s="9" t="n">
-        <v>98.96995800000001</v>
+        <v>98.971277</v>
       </c>
       <c r="O283" s="9" t="n">
         <v>98.757936</v>
@@ -23099,7 +23099,7 @@
         <v>99.617497</v>
       </c>
       <c r="N284" s="6" t="n">
-        <v>98.90468</v>
+        <v>98.90609499999999</v>
       </c>
       <c r="O284" s="6" t="n">
         <v>98.733155</v>
@@ -23181,7 +23181,7 @@
         <v>99.94101999999999</v>
       </c>
       <c r="N285" s="9" t="n">
-        <v>98.83648700000001</v>
+        <v>98.838014</v>
       </c>
       <c r="O285" s="9" t="n">
         <v>98.77739</v>
@@ -23263,7 +23263,7 @@
         <v>100.317192</v>
       </c>
       <c r="N286" s="6" t="n">
-        <v>98.76652199999999</v>
+        <v>98.76815499999999</v>
       </c>
       <c r="O286" s="6" t="n">
         <v>98.868092</v>
@@ -23345,7 +23345,7 @@
         <v>100.735094</v>
       </c>
       <c r="N287" s="9" t="n">
-        <v>98.709718</v>
+        <v>98.711443</v>
       </c>
       <c r="O287" s="9" t="n">
         <v>99.040721</v>
@@ -23427,7 +23427,7 @@
         <v>101.125522</v>
       </c>
       <c r="N288" s="6" t="n">
-        <v>98.67411800000001</v>
+        <v>98.675912</v>
       </c>
       <c r="O288" s="6" t="n">
         <v>99.244872</v>
@@ -23509,7 +23509,7 @@
         <v>101.453117</v>
       </c>
       <c r="N289" s="9" t="n">
-        <v>98.66251800000001</v>
+        <v>98.66433600000001</v>
       </c>
       <c r="O289" s="9" t="n">
         <v>99.458702</v>
@@ -23591,7 +23591,7 @@
         <v>101.683551</v>
       </c>
       <c r="N290" s="6" t="n">
-        <v>98.685772</v>
+        <v>98.68754</v>
       </c>
       <c r="O290" s="6" t="n">
         <v>99.69829799999999</v>
@@ -23673,7 +23673,7 @@
         <v>101.82383</v>
       </c>
       <c r="N291" s="9" t="n">
-        <v>98.74519100000001</v>
+        <v>98.74684499999999</v>
       </c>
       <c r="O291" s="9" t="n">
         <v>99.954849</v>
@@ -23755,7 +23755,7 @@
         <v>101.896802</v>
       </c>
       <c r="N292" s="6" t="n">
-        <v>98.83146000000001</v>
+        <v>98.83299700000001</v>
       </c>
       <c r="O292" s="6" t="n">
         <v>100.185682</v>
@@ -23837,7 +23837,7 @@
         <v>101.925545</v>
       </c>
       <c r="N293" s="9" t="n">
-        <v>98.934561</v>
+        <v>98.935968</v>
       </c>
       <c r="O293" s="9" t="n">
         <v>100.398835</v>
@@ -23919,7 +23919,7 @@
         <v>101.958836</v>
       </c>
       <c r="N294" s="6" t="n">
-        <v>99.04898300000001</v>
+        <v>99.050234</v>
       </c>
       <c r="O294" s="6" t="n">
         <v>100.592393</v>
@@ -24003,7 +24003,7 @@
         <v>102.005107</v>
       </c>
       <c r="N295" s="9" t="n">
-        <v>99.17849699999999</v>
+        <v>99.179562</v>
       </c>
       <c r="O295" s="9" t="n">
         <v>100.781812</v>
@@ -24087,7 +24087,7 @@
         <v>102.037852</v>
       </c>
       <c r="N296" s="6" t="n">
-        <v>99.30637400000001</v>
+        <v>99.30725700000001</v>
       </c>
       <c r="O296" s="6" t="n">
         <v>100.960914</v>
@@ -24171,7 +24171,7 @@
         <v>102.034217</v>
       </c>
       <c r="N297" s="9" t="n">
-        <v>99.42188299999999</v>
+        <v>99.422618</v>
       </c>
       <c r="O297" s="9" t="n">
         <v>101.091886</v>
@@ -24255,7 +24255,7 @@
         <v>102.003919</v>
       </c>
       <c r="N298" s="6" t="n">
-        <v>99.517658</v>
+        <v>99.518292</v>
       </c>
       <c r="O298" s="6" t="n">
         <v>101.132925</v>
@@ -24339,7 +24339,7 @@
         <v>101.961228</v>
       </c>
       <c r="N299" s="9" t="n">
-        <v>99.581422</v>
+        <v>99.582002</v>
       </c>
       <c r="O299" s="9" t="n">
         <v>101.081769</v>
@@ -24423,7 +24423,7 @@
         <v>101.885123</v>
       </c>
       <c r="N300" s="6" t="n">
-        <v>99.62473799999999</v>
+        <v>99.62526699999999</v>
       </c>
       <c r="O300" s="6" t="n">
         <v>100.976439</v>
@@ -24507,7 +24507,7 @@
         <v>101.777666</v>
       </c>
       <c r="N301" s="9" t="n">
-        <v>99.657937</v>
+        <v>99.658405</v>
       </c>
       <c r="O301" s="9" t="n">
         <v>100.845339</v>
@@ -24591,7 +24591,7 @@
         <v>101.609484</v>
       </c>
       <c r="N302" s="6" t="n">
-        <v>99.69403200000001</v>
+        <v>99.694413</v>
       </c>
       <c r="O302" s="6" t="n">
         <v>100.711</v>
@@ -24675,7 +24675,7 @@
         <v>101.428204</v>
       </c>
       <c r="N303" s="9" t="n">
-        <v>99.744525</v>
+        <v>99.744777</v>
       </c>
       <c r="O303" s="9" t="n">
         <v>100.572751</v>
@@ -24759,7 +24759,7 @@
         <v>101.273301</v>
       </c>
       <c r="N304" s="6" t="n">
-        <v>99.794731</v>
+        <v>99.794898</v>
       </c>
       <c r="O304" s="6" t="n">
         <v>100.483379</v>
@@ -24843,7 +24843,7 @@
         <v>101.119377</v>
       </c>
       <c r="N305" s="9" t="n">
-        <v>99.82226900000001</v>
+        <v>99.82242100000001</v>
       </c>
       <c r="O305" s="9" t="n">
         <v>100.430824</v>
@@ -24927,7 +24927,7 @@
         <v>100.976029</v>
       </c>
       <c r="N306" s="6" t="n">
-        <v>99.830072</v>
+        <v>99.83024399999999</v>
       </c>
       <c r="O306" s="6" t="n">
         <v>100.383167</v>
@@ -25011,7 +25011,7 @@
         <v>100.845536</v>
       </c>
       <c r="N307" s="9" t="n">
-        <v>99.818237</v>
+        <v>99.818454</v>
       </c>
       <c r="O307" s="9" t="n">
         <v>100.251087</v>
@@ -25095,7 +25095,7 @@
         <v>100.723</v>
       </c>
       <c r="N308" s="6" t="n">
-        <v>99.797618</v>
+        <v>99.79788499999999</v>
       </c>
       <c r="O308" s="6" t="n">
         <v>100.07084</v>
@@ -25179,7 +25179,7 @@
         <v>100.610822</v>
       </c>
       <c r="N309" s="9" t="n">
-        <v>99.78245099999999</v>
+        <v>99.782758</v>
       </c>
       <c r="O309" s="9" t="n">
         <v>99.876687</v>
@@ -25263,7 +25263,7 @@
         <v>100.483077</v>
       </c>
       <c r="N310" s="6" t="n">
-        <v>99.778835</v>
+        <v>99.779149</v>
       </c>
       <c r="O310" s="6" t="n">
         <v>99.730268</v>
@@ -25347,7 +25347,7 @@
         <v>100.321752</v>
       </c>
       <c r="N311" s="9" t="n">
-        <v>99.800089</v>
+        <v>99.80038500000001</v>
       </c>
       <c r="O311" s="9" t="n">
         <v>99.672015</v>
@@ -25431,7 +25431,7 @@
         <v>100.120569</v>
       </c>
       <c r="N312" s="6" t="n">
-        <v>99.84898699999999</v>
+        <v>99.849232</v>
       </c>
       <c r="O312" s="6" t="n">
         <v>99.71995699999999</v>
@@ -25515,7 +25515,7 @@
         <v>99.856549</v>
       </c>
       <c r="N313" s="9" t="n">
-        <v>99.931945</v>
+        <v>99.932069</v>
       </c>
       <c r="O313" s="9" t="n">
         <v>99.863394</v>
@@ -25599,7 +25599,7 @@
         <v>99.582819</v>
       </c>
       <c r="N314" s="6" t="n">
-        <v>100.052675</v>
+        <v>100.052602</v>
       </c>
       <c r="O314" s="6" t="n">
         <v>100.026412</v>
@@ -25683,7 +25683,7 @@
         <v>99.35308000000001</v>
       </c>
       <c r="N315" s="9" t="n">
-        <v>100.205912</v>
+        <v>100.205571</v>
       </c>
       <c r="O315" s="9" t="n">
         <v>100.205086</v>
@@ -25767,7 +25767,7 @@
         <v>99.179491</v>
       </c>
       <c r="N316" s="6" t="n">
-        <v>100.363537</v>
+        <v>100.362985</v>
       </c>
       <c r="O316" s="6" t="n">
         <v>100.353158</v>
@@ -25851,7 +25851,7 @@
         <v>99.09101</v>
       </c>
       <c r="N317" s="9" t="n">
-        <v>100.498237</v>
+        <v>100.497524</v>
       </c>
       <c r="O317" s="9" t="n">
         <v>100.459098</v>
@@ -25935,7 +25935,7 @@
         <v>99.06735</v>
       </c>
       <c r="N318" s="6" t="n">
-        <v>100.595855</v>
+        <v>100.595024</v>
       </c>
       <c r="O318" s="6" t="n">
         <v>100.549525</v>
@@ -26019,7 +26019,7 @@
         <v>99.07811100000001</v>
       </c>
       <c r="N319" s="9" t="n">
-        <v>100.66973</v>
+        <v>100.668803</v>
       </c>
       <c r="O319" s="9" t="n">
         <v>100.672854</v>
@@ -26103,7 +26103,7 @@
         <v>99.096953</v>
       </c>
       <c r="N320" s="6" t="n">
-        <v>100.726671</v>
+        <v>100.725661</v>
       </c>
       <c r="O320" s="6" t="n">
         <v>100.830395</v>
@@ -26187,7 +26187,7 @@
         <v>99.130112</v>
       </c>
       <c r="N321" s="9" t="n">
-        <v>100.767885</v>
+        <v>100.766821</v>
       </c>
       <c r="O321" s="9" t="n">
         <v>101.002921</v>
@@ -26271,7 +26271,7 @@
         <v>99.19046400000001</v>
       </c>
       <c r="N322" s="6" t="n">
-        <v>100.790309</v>
+        <v>100.78921</v>
       </c>
       <c r="O322" s="6" t="n">
         <v>101.16847</v>
@@ -26355,7 +26355,7 @@
         <v>99.284623</v>
       </c>
       <c r="N323" s="9" t="n">
-        <v>100.79069</v>
+        <v>100.789609</v>
       </c>
       <c r="O323" s="9" t="n">
         <v>101.248448</v>
@@ -26439,7 +26439,7 @@
         <v>99.36771400000001</v>
       </c>
       <c r="N324" s="6" t="n">
-        <v>100.777144</v>
+        <v>100.776131</v>
       </c>
       <c r="O324" s="6" t="n">
         <v>101.202129</v>
@@ -26523,7 +26523,7 @@
         <v>99.428893</v>
       </c>
       <c r="N325" s="9" t="n">
-        <v>100.756076</v>
+        <v>100.755151</v>
       </c>
       <c r="O325" s="9" t="n">
         <v>101.068439</v>
@@ -26607,7 +26607,7 @@
         <v>99.494704</v>
       </c>
       <c r="N326" s="6" t="n">
-        <v>100.726864</v>
+        <v>100.726006</v>
       </c>
       <c r="O326" s="6" t="n">
         <v>100.896307</v>
@@ -26691,7 +26691,7 @@
         <v>99.562135</v>
       </c>
       <c r="N327" s="9" t="n">
-        <v>100.688176</v>
+        <v>100.687309</v>
       </c>
       <c r="O327" s="9" t="n">
         <v>100.726436</v>
@@ -26775,7 +26775,7 @@
         <v>99.624752</v>
       </c>
       <c r="N328" s="6" t="n">
-        <v>100.651309</v>
+        <v>100.650464</v>
       </c>
       <c r="O328" s="6" t="n">
         <v>100.574905</v>
@@ -26859,7 +26859,7 @@
         <v>99.660315</v>
       </c>
       <c r="N329" s="9" t="n">
-        <v>100.63399</v>
+        <v>100.633171</v>
       </c>
       <c r="O329" s="9" t="n">
         <v>100.468732</v>
@@ -26943,7 +26943,7 @@
         <v>99.66794899999999</v>
       </c>
       <c r="N330" s="6" t="n">
-        <v>100.640534</v>
+        <v>100.63969</v>
       </c>
       <c r="O330" s="6" t="n">
         <v>100.436874</v>
@@ -27027,7 +27027,7 @@
         <v>99.636107</v>
       </c>
       <c r="N331" s="9" t="n">
-        <v>100.675856</v>
+        <v>100.674936</v>
       </c>
       <c r="O331" s="9" t="n">
         <v>100.485819</v>
@@ -27111,7 +27111,7 @@
         <v>99.548956</v>
       </c>
       <c r="N332" s="6" t="n">
-        <v>100.735903</v>
+        <v>100.73487</v>
       </c>
       <c r="O332" s="6" t="n">
         <v>100.556668</v>
@@ -27195,7 +27195,7 @@
         <v>99.39650899999999</v>
       </c>
       <c r="N333" s="9" t="n">
-        <v>100.813787</v>
+        <v>100.81263</v>
       </c>
       <c r="O333" s="9" t="n">
         <v>100.624279</v>
@@ -27279,7 +27279,7 @@
         <v>99.216894</v>
       </c>
       <c r="N334" s="6" t="n">
-        <v>100.894728</v>
+        <v>100.893468</v>
       </c>
       <c r="O334" s="6" t="n">
         <v>100.664121</v>
@@ -27363,7 +27363,7 @@
         <v>99.045158</v>
       </c>
       <c r="N335" s="9" t="n">
-        <v>100.963076</v>
+        <v>100.961756</v>
       </c>
       <c r="O335" s="9" t="n">
         <v>100.725804</v>
@@ -27447,7 +27447,7 @@
         <v>98.912389</v>
       </c>
       <c r="N336" s="6" t="n">
-        <v>101.01511</v>
+        <v>101.013761</v>
       </c>
       <c r="O336" s="6" t="n">
         <v>100.829693</v>
@@ -27531,7 +27531,7 @@
         <v>98.85366</v>
       </c>
       <c r="N337" s="9" t="n">
-        <v>101.068919</v>
+        <v>101.067542</v>
       </c>
       <c r="O337" s="9" t="n">
         <v>100.937077</v>
@@ -27615,7 +27615,7 @@
         <v>98.848484</v>
       </c>
       <c r="N338" s="6" t="n">
-        <v>101.126517</v>
+        <v>101.125082</v>
       </c>
       <c r="O338" s="6" t="n">
         <v>101.023968</v>
@@ -27699,7 +27699,7 @@
         <v>98.848885</v>
       </c>
       <c r="N339" s="9" t="n">
-        <v>101.190783</v>
+        <v>101.189181</v>
       </c>
       <c r="O339" s="9" t="n">
         <v>101.021686</v>
@@ -27783,7 +27783,7 @@
         <v>98.829064</v>
       </c>
       <c r="N340" s="6" t="n">
-        <v>101.275297</v>
+        <v>101.273519</v>
       </c>
       <c r="O340" s="6" t="n">
         <v>100.961097</v>
@@ -27867,7 +27867,7 @@
         <v>98.787646</v>
       </c>
       <c r="N341" s="9" t="n">
-        <v>101.387716</v>
+        <v>101.385767</v>
       </c>
       <c r="O341" s="9" t="n">
         <v>100.863154</v>
@@ -27951,7 +27951,7 @@
         <v>98.702485</v>
       </c>
       <c r="N342" s="6" t="n">
-        <v>101.523463</v>
+        <v>101.521333</v>
       </c>
       <c r="O342" s="6" t="n">
         <v>100.707109</v>
@@ -28035,7 +28035,7 @@
         <v>98.563294</v>
       </c>
       <c r="N343" s="9" t="n">
-        <v>101.663543</v>
+        <v>101.661238</v>
       </c>
       <c r="O343" s="9" t="n">
         <v>100.477666</v>
@@ -28119,7 +28119,7 @@
         <v>98.399601</v>
       </c>
       <c r="N344" s="6" t="n">
-        <v>101.795039</v>
+        <v>101.792569</v>
       </c>
       <c r="O344" s="6" t="n">
         <v>100.203274</v>
@@ -28203,7 +28203,7 @@
         <v>98.254901</v>
       </c>
       <c r="N345" s="9" t="n">
-        <v>101.904424</v>
+        <v>101.901818</v>
       </c>
       <c r="O345" s="9" t="n">
         <v>99.885807</v>
@@ -28287,7 +28287,7 @@
         <v>98.174121</v>
       </c>
       <c r="N346" s="6" t="n">
-        <v>101.966805</v>
+        <v>101.964113</v>
       </c>
       <c r="O346" s="6" t="n">
         <v>99.542552</v>
@@ -28371,7 +28371,7 @@
         <v>98.19389200000001</v>
       </c>
       <c r="N347" s="9" t="n">
-        <v>101.957807</v>
+        <v>101.955164</v>
       </c>
       <c r="O347" s="9" t="n">
         <v>99.155209</v>
@@ -28455,7 +28455,7 @@
         <v>98.32347300000001</v>
       </c>
       <c r="N348" s="6" t="n">
-        <v>101.836125</v>
+        <v>101.833751</v>
       </c>
       <c r="O348" s="6" t="n">
         <v>98.72685</v>
@@ -28539,7 +28539,7 @@
         <v>98.537925</v>
       </c>
       <c r="N349" s="9" t="n">
-        <v>101.542324</v>
+        <v>101.540477</v>
       </c>
       <c r="O349" s="9" t="n">
         <v>98.23600399999999</v>
@@ -28623,7 +28623,7 @@
         <v>98.836018</v>
       </c>
       <c r="N350" s="6" t="n">
-        <v>101.051415</v>
+        <v>101.050304</v>
       </c>
       <c r="O350" s="6" t="n">
         <v>97.71191899999999</v>
@@ -28707,7 +28707,7 @@
         <v>99.229721</v>
       </c>
       <c r="N351" s="9" t="n">
-        <v>100.379316</v>
+        <v>100.379034</v>
       </c>
       <c r="O351" s="9" t="n">
         <v>97.21533700000001</v>
@@ -28791,7 +28791,7 @@
         <v>99.69058200000001</v>
       </c>
       <c r="N352" s="6" t="n">
-        <v>99.567076</v>
+        <v>99.567786</v>
       </c>
       <c r="O352" s="6" t="n">
         <v>96.81200200000001</v>
@@ -28875,7 +28875,7 @@
         <v>100.1536</v>
       </c>
       <c r="N353" s="9" t="n">
-        <v>98.699679</v>
+        <v>98.701444</v>
       </c>
       <c r="O353" s="9" t="n">
         <v>96.513154</v>
@@ -28959,7 +28959,7 @@
         <v>100.586294</v>
       </c>
       <c r="N354" s="6" t="n">
-        <v>97.914196</v>
+        <v>97.916911</v>
       </c>
       <c r="O354" s="6" t="n">
         <v>96.281989</v>
@@ -29043,7 +29043,7 @@
         <v>100.988994</v>
       </c>
       <c r="N355" s="9" t="n">
-        <v>97.286761</v>
+        <v>97.290245</v>
       </c>
       <c r="O355" s="9" t="n">
         <v>96.154399</v>
@@ -29127,7 +29127,7 @@
         <v>101.351476</v>
       </c>
       <c r="N356" s="6" t="n">
-        <v>96.848017</v>
+        <v>96.852051</v>
       </c>
       <c r="O356" s="6" t="n">
         <v>96.159921</v>
@@ -29211,7 +29211,7 @@
         <v>101.656333</v>
       </c>
       <c r="N357" s="9" t="n">
-        <v>96.61138200000001</v>
+        <v>96.615719</v>
       </c>
       <c r="O357" s="9" t="n">
         <v>96.358328</v>
@@ -29295,7 +29295,7 @@
         <v>101.864059</v>
       </c>
       <c r="N358" s="6" t="n">
-        <v>96.574217</v>
+        <v>96.578613</v>
       </c>
       <c r="O358" s="6" t="n">
         <v>96.74793200000001</v>
@@ -29379,7 +29379,7 @@
         <v>101.96635</v>
       </c>
       <c r="N359" s="9" t="n">
-        <v>96.71358600000001</v>
+        <v>96.717831</v>
       </c>
       <c r="O359" s="9" t="n">
         <v>97.301406</v>
@@ -29463,7 +29463,7 @@
         <v>102.005256</v>
       </c>
       <c r="N360" s="6" t="n">
-        <v>96.969452</v>
+        <v>96.97344699999999</v>
       </c>
       <c r="O360" s="6" t="n">
         <v>97.95477099999999</v>
@@ -29547,7 +29547,7 @@
         <v>101.975205</v>
       </c>
       <c r="N361" s="9" t="n">
-        <v>97.294439</v>
+        <v>97.298132</v>
       </c>
       <c r="O361" s="9" t="n">
         <v>98.652686</v>
@@ -29631,7 +29631,7 @@
         <v>101.867389</v>
       </c>
       <c r="N362" s="6" t="n">
-        <v>97.64972899999999</v>
+        <v>97.653051</v>
       </c>
       <c r="O362" s="6" t="n">
         <v>99.329498</v>
@@ -29715,7 +29715,7 @@
         <v>101.679683</v>
       </c>
       <c r="N363" s="9" t="n">
-        <v>98.006354</v>
+        <v>98.00916599999999</v>
       </c>
       <c r="O363" s="9" t="n">
         <v>99.963708</v>
@@ -29799,7 +29799,7 @@
         <v>101.462034</v>
       </c>
       <c r="N364" s="6" t="n">
-        <v>98.349371</v>
+        <v>98.351634</v>
       </c>
       <c r="O364" s="6" t="n">
         <v>100.459522</v>
@@ -29883,7 +29883,7 @@
         <v>101.275331</v>
       </c>
       <c r="N365" s="9" t="n">
-        <v>98.64978000000001</v>
+        <v>98.651552</v>
       </c>
       <c r="O365" s="9" t="n">
         <v>100.818514</v>
@@ -29967,7 +29967,7 @@
         <v>101.132222</v>
       </c>
       <c r="N366" s="6" t="n">
-        <v>98.909622</v>
+        <v>98.910965</v>
       </c>
       <c r="O366" s="6" t="n">
         <v>101.099589</v>
@@ -30051,7 +30051,7 @@
         <v>100.999057</v>
       </c>
       <c r="N367" s="9" t="n">
-        <v>99.13820200000001</v>
+        <v>99.139178</v>
       </c>
       <c r="O367" s="9" t="n">
         <v>101.308297</v>
@@ -30135,7 +30135,7 @@
         <v>100.893157</v>
       </c>
       <c r="N368" s="6" t="n">
-        <v>99.329008</v>
+        <v>99.329696</v>
       </c>
       <c r="O368" s="6" t="n">
         <v>101.467926</v>
@@ -30219,7 +30219,7 @@
         <v>100.807244</v>
       </c>
       <c r="N369" s="9" t="n">
-        <v>99.46657399999999</v>
+        <v>99.467071</v>
       </c>
       <c r="O369" s="9" t="n">
         <v>101.563309</v>
@@ -30303,7 +30303,7 @@
         <v>100.721744</v>
       </c>
       <c r="N370" s="6" t="n">
-        <v>99.549446</v>
+        <v>99.54984399999999</v>
       </c>
       <c r="O370" s="6" t="n">
         <v>101.584287</v>
@@ -30387,7 +30387,7 @@
         <v>100.63788</v>
       </c>
       <c r="N371" s="9" t="n">
-        <v>99.59773800000001</v>
+        <v>99.59811999999999</v>
       </c>
       <c r="O371" s="9" t="n">
         <v>101.537002</v>
@@ -30471,7 +30471,7 @@
         <v>100.547571</v>
       </c>
       <c r="N372" s="6" t="n">
-        <v>99.649765</v>
+        <v>99.65015099999999</v>
       </c>
       <c r="O372" s="6" t="n">
         <v>101.445804</v>
@@ -30555,7 +30555,7 @@
         <v>100.477664</v>
       </c>
       <c r="N373" s="9" t="n">
-        <v>99.724464</v>
+        <v>99.724844</v>
       </c>
       <c r="O373" s="9" t="n">
         <v>101.33131</v>
@@ -30639,7 +30639,7 @@
         <v>100.462042</v>
       </c>
       <c r="N374" s="6" t="n">
-        <v>99.822796</v>
+        <v>99.823108</v>
       </c>
       <c r="O374" s="6" t="n">
         <v>101.209165</v>
@@ -30723,7 +30723,7 @@
         <v>100.457695</v>
       </c>
       <c r="N375" s="9" t="n">
-        <v>99.947025</v>
+        <v>99.94713</v>
       </c>
       <c r="O375" s="9" t="n">
         <v>101.049888</v>
@@ -30807,7 +30807,7 @@
         <v>100.428043</v>
       </c>
       <c r="N376" s="6" t="n">
-        <v>100.082285</v>
+        <v>100.082096</v>
       </c>
       <c r="O376" s="6" t="n">
         <v>100.901185</v>
@@ -30891,7 +30891,7 @@
         <v>100.352335</v>
       </c>
       <c r="N377" s="9" t="n">
-        <v>100.218999</v>
+        <v>100.218508</v>
       </c>
       <c r="O377" s="9" t="n">
         <v>100.799588</v>
@@ -30975,7 +30975,7 @@
         <v>100.215073</v>
       </c>
       <c r="N378" s="6" t="n">
-        <v>100.346661</v>
+        <v>100.34592</v>
       </c>
       <c r="O378" s="6" t="n">
         <v>100.753267</v>
@@ -31059,7 +31059,7 @@
         <v>100.069349</v>
       </c>
       <c r="N379" s="9" t="n">
-        <v>100.458514</v>
+        <v>100.457612</v>
       </c>
       <c r="O379" s="9" t="n">
         <v>100.763402</v>
@@ -31143,7 +31143,7 @@
         <v>99.953221</v>
       </c>
       <c r="N380" s="6" t="n">
-        <v>100.55405</v>
+        <v>100.553056</v>
       </c>
       <c r="O380" s="6" t="n">
         <v>100.806973</v>
@@ -31227,7 +31227,7 @@
         <v>99.892893</v>
       </c>
       <c r="N381" s="9" t="n">
-        <v>100.63803</v>
+        <v>100.636974</v>
       </c>
       <c r="O381" s="9" t="n">
         <v>100.863752</v>
@@ -31311,7 +31311,7 @@
         <v>99.905143</v>
       </c>
       <c r="N382" s="6" t="n">
-        <v>100.712082</v>
+        <v>100.710956</v>
       </c>
       <c r="O382" s="6" t="n">
         <v>100.914184</v>
@@ -31395,7 +31395,7 @@
         <v>99.925693</v>
       </c>
       <c r="N383" s="9" t="n">
-        <v>100.75947</v>
+        <v>100.758332</v>
       </c>
       <c r="O383" s="9" t="n">
         <v>100.955688</v>
@@ -31479,7 +31479,7 @@
         <v>99.916246</v>
       </c>
       <c r="N384" s="6" t="n">
-        <v>100.769444</v>
+        <v>100.768389</v>
       </c>
       <c r="O384" s="6" t="n">
         <v>100.982817</v>
@@ -31563,7 +31563,7 @@
         <v>99.871948</v>
       </c>
       <c r="N385" s="9" t="n">
-        <v>100.753206</v>
+        <v>100.752269</v>
       </c>
       <c r="O385" s="9" t="n">
         <v>101.019819</v>
@@ -31647,7 +31647,7 @@
         <v>99.810282</v>
       </c>
       <c r="N386" s="6" t="n">
-        <v>100.730717</v>
+        <v>100.729857</v>
       </c>
       <c r="O386" s="6" t="n">
         <v>101.074465</v>
@@ -31731,7 +31731,7 @@
         <v>99.751407</v>
       </c>
       <c r="N387" s="9" t="n">
-        <v>100.706738</v>
+        <v>100.705853</v>
       </c>
       <c r="O387" s="9" t="n">
         <v>101.16615</v>
@@ -31815,7 +31815,7 @@
         <v>99.710025</v>
       </c>
       <c r="N388" s="6" t="n">
-        <v>100.695379</v>
+        <v>100.694388</v>
       </c>
       <c r="O388" s="6" t="n">
         <v>101.292182</v>
@@ -31899,7 +31899,7 @@
         <v>99.69111599999999</v>
       </c>
       <c r="N389" s="9" t="n">
-        <v>100.695622</v>
+        <v>100.69448</v>
       </c>
       <c r="O389" s="9" t="n">
         <v>101.410419</v>
@@ -31983,7 +31983,7 @@
         <v>99.711561</v>
       </c>
       <c r="N390" s="6" t="n">
-        <v>100.697007</v>
+        <v>100.695742</v>
       </c>
       <c r="O390" s="6" t="n">
         <v>101.528913</v>
@@ -32067,7 +32067,7 @@
         <v>99.75391999999999</v>
       </c>
       <c r="N391" s="9" t="n">
-        <v>100.68705</v>
+        <v>100.685739</v>
       </c>
       <c r="O391" s="9" t="n">
         <v>101.59571</v>
@@ -32151,7 +32151,7 @@
         <v>99.765445</v>
       </c>
       <c r="N392" s="6" t="n">
-        <v>100.654299</v>
+        <v>100.653019</v>
       </c>
       <c r="O392" s="6" t="n">
         <v>101.556125</v>
@@ -32235,7 +32235,7 @@
         <v>99.749572</v>
       </c>
       <c r="N393" s="9" t="n">
-        <v>100.605926</v>
+        <v>100.604767</v>
       </c>
       <c r="O393" s="9" t="n">
         <v>101.420716</v>
@@ -32319,7 +32319,7 @@
         <v>99.720951</v>
       </c>
       <c r="N394" s="6" t="n">
-        <v>100.537653</v>
+        <v>100.536707</v>
       </c>
       <c r="O394" s="6" t="n">
         <v>101.267194</v>
@@ -32403,7 +32403,7 @@
         <v>99.683486</v>
       </c>
       <c r="N395" s="9" t="n">
-        <v>100.464907</v>
+        <v>100.464146</v>
       </c>
       <c r="O395" s="9" t="n">
         <v>101.118442</v>
@@ -32487,7 +32487,7 @@
         <v>99.67305899999999</v>
       </c>
       <c r="N396" s="6" t="n">
-        <v>100.415927</v>
+        <v>100.415274</v>
       </c>
       <c r="O396" s="6" t="n">
         <v>100.956772</v>
@@ -32571,7 +32571,7 @@
         <v>99.70900899999999</v>
       </c>
       <c r="N397" s="9" t="n">
-        <v>100.397993</v>
+        <v>100.397382</v>
       </c>
       <c r="O397" s="9" t="n">
         <v>100.794263</v>
@@ -32655,7 +32655,7 @@
         <v>99.784384</v>
       </c>
       <c r="N398" s="6" t="n">
-        <v>100.414017</v>
+        <v>100.413349</v>
       </c>
       <c r="O398" s="6" t="n">
         <v>100.664795</v>
@@ -32739,7 +32739,7 @@
         <v>99.908261</v>
       </c>
       <c r="N399" s="9" t="n">
-        <v>100.449321</v>
+        <v>100.448476</v>
       </c>
       <c r="O399" s="9" t="n">
         <v>100.590856</v>
@@ -32823,7 +32823,7 @@
         <v>100.052841</v>
       </c>
       <c r="N400" s="6" t="n">
-        <v>100.479223</v>
+        <v>100.478193</v>
       </c>
       <c r="O400" s="6" t="n">
         <v>100.53594</v>
@@ -32907,7 +32907,7 @@
         <v>100.175126</v>
       </c>
       <c r="N401" s="9" t="n">
-        <v>100.501792</v>
+        <v>100.500678</v>
       </c>
       <c r="O401" s="9" t="n">
         <v>100.473692</v>
@@ -32991,7 +32991,7 @@
         <v>100.248598</v>
       </c>
       <c r="N402" s="6" t="n">
-        <v>100.519201</v>
+        <v>100.518131</v>
       </c>
       <c r="O402" s="6" t="n">
         <v>100.31421</v>
@@ -33075,7 +33075,7 @@
         <v>100.26208</v>
       </c>
       <c r="N403" s="9" t="n">
-        <v>100.518529</v>
+        <v>100.517553</v>
       </c>
       <c r="O403" s="9" t="n">
         <v>100.059382</v>
@@ -33159,7 +33159,7 @@
         <v>100.239974</v>
       </c>
       <c r="N404" s="6" t="n">
-        <v>100.49299</v>
+        <v>100.492133</v>
       </c>
       <c r="O404" s="6" t="n">
         <v>99.781265</v>
@@ -33243,7 +33243,7 @@
         <v>100.183232</v>
       </c>
       <c r="N405" s="9" t="n">
-        <v>100.441688</v>
+        <v>100.440926</v>
       </c>
       <c r="O405" s="9" t="n">
         <v>99.525713</v>
@@ -33327,7 +33327,7 @@
         <v>100.081637</v>
       </c>
       <c r="N406" s="6" t="n">
-        <v>100.370978</v>
+        <v>100.370295</v>
       </c>
       <c r="O406" s="6" t="n">
         <v>99.29205</v>
@@ -33411,7 +33411,7 @@
         <v>99.98832899999999</v>
       </c>
       <c r="N407" s="9" t="n">
-        <v>100.294936</v>
+        <v>100.294318</v>
       </c>
       <c r="O407" s="9" t="n">
         <v>99.078492</v>
@@ -33495,7 +33495,7 @@
         <v>99.91446000000001</v>
       </c>
       <c r="N408" s="6" t="n">
-        <v>100.216912</v>
+        <v>100.216313</v>
       </c>
       <c r="O408" s="6" t="n">
         <v>98.925603</v>
@@ -33579,7 +33579,7 @@
         <v>99.88247800000001</v>
       </c>
       <c r="N409" s="9" t="n">
-        <v>100.138756</v>
+        <v>100.138181</v>
       </c>
       <c r="O409" s="9" t="n">
         <v>98.83386400000001</v>
@@ -33663,7 +33663,7 @@
         <v>99.90955700000001</v>
       </c>
       <c r="N410" s="6" t="n">
-        <v>100.072091</v>
+        <v>100.071561</v>
       </c>
       <c r="O410" s="6" t="n">
         <v>98.802589</v>
@@ -33747,7 +33747,7 @@
         <v>99.996719</v>
       </c>
       <c r="N411" s="9" t="n">
-        <v>100.029666</v>
+        <v>100.029202</v>
       </c>
       <c r="O411" s="9" t="n">
         <v>98.811201</v>
@@ -33831,7 +33831,7 @@
         <v>100.163279</v>
       </c>
       <c r="N412" s="6" t="n">
-        <v>100.019786</v>
+        <v>100.019295</v>
       </c>
       <c r="O412" s="6" t="n">
         <v>98.832548</v>
@@ -33915,7 +33915,7 @@
         <v>100.41581</v>
       </c>
       <c r="N413" s="9" t="n">
-        <v>100.052249</v>
+        <v>100.051653</v>
       </c>
       <c r="O413" s="9" t="n">
         <v>98.80226500000001</v>
@@ -33999,7 +33999,7 @@
         <v>100.676447</v>
       </c>
       <c r="N414" s="6" t="n">
-        <v>100.123755</v>
+        <v>100.123039</v>
       </c>
       <c r="O414" s="6" t="n">
         <v>98.72873300000001</v>
@@ -34083,7 +34083,7 @@
         <v>100.884864</v>
       </c>
       <c r="N415" s="9" t="n">
-        <v>100.216677</v>
+        <v>100.215902</v>
       </c>
       <c r="O415" s="9" t="n">
         <v>98.68765399999999</v>
@@ -34167,7 +34167,7 @@
         <v>101.049333</v>
       </c>
       <c r="N416" s="6" t="n">
-        <v>100.310077</v>
+        <v>100.309297</v>
       </c>
       <c r="O416" s="6" t="n">
         <v>98.733374</v>
@@ -34251,7 +34251,7 @@
         <v>101.150299</v>
       </c>
       <c r="N417" s="9" t="n">
-        <v>100.389486</v>
+        <v>100.388747</v>
       </c>
       <c r="O417" s="9" t="n">
         <v>98.80347399999999</v>
@@ -34335,7 +34335,7 @@
         <v>101.1804</v>
       </c>
       <c r="N418" s="6" t="n">
-        <v>100.444756</v>
+        <v>100.443959</v>
       </c>
       <c r="O418" s="6" t="n">
         <v>98.85941800000001</v>
@@ -34419,7 +34419,7 @@
         <v>101.165166</v>
       </c>
       <c r="N419" s="9" t="n">
-        <v>100.471961</v>
+        <v>100.471135</v>
       </c>
       <c r="O419" s="9" t="n">
         <v>98.889866</v>
@@ -34503,7 +34503,7 @@
         <v>101.092033</v>
       </c>
       <c r="N420" s="6" t="n">
-        <v>100.474492</v>
+        <v>100.473704</v>
       </c>
       <c r="O420" s="6" t="n">
         <v>98.908968</v>
@@ -34587,7 +34587,7 @@
         <v>100.932091</v>
       </c>
       <c r="N421" s="9" t="n">
-        <v>100.459157</v>
+        <v>100.458379</v>
       </c>
       <c r="O421" s="9" t="n">
         <v>98.93425499999999</v>
@@ -34671,7 +34671,7 @@
         <v>100.721407</v>
       </c>
       <c r="N422" s="6" t="n">
-        <v>100.418398</v>
+        <v>100.417597</v>
       </c>
       <c r="O422" s="6" t="n">
         <v>98.947836</v>
@@ -34755,7 +34755,7 @@
         <v>100.49528</v>
       </c>
       <c r="N423" s="9" t="n">
-        <v>100.368032</v>
+        <v>100.367214</v>
       </c>
       <c r="O423" s="9" t="n">
         <v>98.93785200000001</v>
@@ -34839,7 +34839,7 @@
         <v>100.274736</v>
       </c>
       <c r="N424" s="6" t="n">
-        <v>100.310085</v>
+        <v>100.309283</v>
       </c>
       <c r="O424" s="6" t="n">
         <v>98.929418</v>
@@ -34923,7 +34923,7 @@
         <v>100.106451</v>
       </c>
       <c r="N425" s="9" t="n">
-        <v>100.232938</v>
+        <v>100.232182</v>
       </c>
       <c r="O425" s="9" t="n">
         <v>98.98154599999999</v>
@@ -35007,7 +35007,7 @@
         <v>100.020882</v>
       </c>
       <c r="N426" s="6" t="n">
-        <v>100.155544</v>
+        <v>100.154881</v>
       </c>
       <c r="O426" s="6" t="n">
         <v>99.115207</v>
@@ -35091,7 +35091,7 @@
         <v>99.993723</v>
       </c>
       <c r="N427" s="9" t="n">
-        <v>100.100401</v>
+        <v>100.099901</v>
       </c>
       <c r="O427" s="9" t="n">
         <v>99.279213</v>
@@ -35175,7 +35175,7 @@
         <v>99.998182</v>
       </c>
       <c r="N428" s="6" t="n">
-        <v>100.077033</v>
+        <v>100.076686</v>
       </c>
       <c r="O428" s="6" t="n">
         <v>99.398883</v>
@@ -35259,7 +35259,7 @@
         <v>100.034968</v>
       </c>
       <c r="N429" s="9" t="n">
-        <v>100.07313</v>
+        <v>100.072888</v>
       </c>
       <c r="O429" s="9" t="n">
         <v>99.516049</v>
@@ -35343,7 +35343,7 @@
         <v>100.089443</v>
       </c>
       <c r="N430" s="6" t="n">
-        <v>100.078951</v>
+        <v>100.078685</v>
       </c>
       <c r="O430" s="6" t="n">
         <v>99.643069</v>
@@ -35427,7 +35427,7 @@
         <v>100.132142</v>
       </c>
       <c r="N431" s="9" t="n">
-        <v>100.079464</v>
+        <v>100.079106</v>
       </c>
       <c r="O431" s="9" t="n">
         <v>99.79485</v>
@@ -35511,7 +35511,7 @@
         <v>100.163585</v>
       </c>
       <c r="N432" s="6" t="n">
-        <v>100.052077</v>
+        <v>100.051656</v>
       </c>
       <c r="O432" s="6" t="n">
         <v>99.96868600000001</v>
@@ -35595,7 +35595,7 @@
         <v>100.178385</v>
       </c>
       <c r="N433" s="9" t="n">
-        <v>99.990887</v>
+        <v>99.99049100000001</v>
       </c>
       <c r="O433" s="9" t="n">
         <v>100.13088</v>
@@ -35679,7 +35679,7 @@
         <v>100.180964</v>
       </c>
       <c r="N434" s="6" t="n">
-        <v>99.88988000000001</v>
+        <v>99.889617</v>
       </c>
       <c r="O434" s="6" t="n">
         <v>100.261252</v>
@@ -35763,7 +35763,7 @@
         <v>100.163911</v>
       </c>
       <c r="N435" s="9" t="n">
-        <v>99.76402899999999</v>
+        <v>99.76390000000001</v>
       </c>
       <c r="O435" s="9" t="n">
         <v>100.359718</v>
@@ -35847,7 +35847,7 @@
         <v>100.129547</v>
       </c>
       <c r="N436" s="6" t="n">
-        <v>99.62432</v>
+        <v>99.624416</v>
       </c>
       <c r="O436" s="6" t="n">
         <v>100.415724</v>
@@ -35931,7 +35931,7 @@
         <v>100.113881</v>
       </c>
       <c r="N437" s="9" t="n">
-        <v>99.486923</v>
+        <v>99.487341</v>
       </c>
       <c r="O437" s="9" t="n">
         <v>100.436515</v>
@@ -36015,7 +36015,7 @@
         <v>100.060432</v>
       </c>
       <c r="N438" s="6" t="n">
-        <v>99.37418700000001</v>
+        <v>99.374888</v>
       </c>
       <c r="O438" s="6" t="n">
         <v>100.430038</v>
@@ -36099,7 +36099,7 @@
         <v>99.990843</v>
       </c>
       <c r="N439" s="9" t="n">
-        <v>99.29082200000001</v>
+        <v>99.291809</v>
       </c>
       <c r="O439" s="9" t="n">
         <v>100.388748</v>
@@ -36183,7 +36183,7 @@
         <v>99.91474700000001</v>
       </c>
       <c r="N440" s="6" t="n">
-        <v>99.240371</v>
+        <v>99.241668</v>
       </c>
       <c r="O440" s="6" t="n">
         <v>100.322816</v>
@@ -36267,7 +36267,7 @@
         <v>99.847533</v>
       </c>
       <c r="N441" s="9" t="n">
-        <v>99.22458</v>
+        <v>99.22605799999999</v>
       </c>
       <c r="O441" s="9" t="n">
         <v>100.274831</v>
@@ -36351,7 +36351,7 @@
         <v>99.80473499999999</v>
       </c>
       <c r="N442" s="6" t="n">
-        <v>99.23282</v>
+        <v>99.23426499999999</v>
       </c>
       <c r="O442" s="6" t="n">
         <v>100.245444</v>
@@ -36435,7 +36435,7 @@
         <v>99.76145</v>
       </c>
       <c r="N443" s="9" t="n">
-        <v>99.265654</v>
+        <v>99.26697</v>
       </c>
       <c r="O443" s="9" t="n">
         <v>100.246641</v>
@@ -36519,7 +36519,7 @@
         <v>99.723989</v>
       </c>
       <c r="N444" s="6" t="n">
-        <v>99.317403</v>
+        <v>99.31854</v>
       </c>
       <c r="O444" s="6" t="n">
         <v>100.254928</v>
@@ -36603,7 +36603,7 @@
         <v>99.692137</v>
       </c>
       <c r="N445" s="9" t="n">
-        <v>99.379154</v>
+        <v>99.380088</v>
       </c>
       <c r="O445" s="9" t="n">
         <v>100.268812</v>
@@ -36687,7 +36687,7 @@
         <v>99.631274</v>
       </c>
       <c r="N446" s="6" t="n">
-        <v>99.448081</v>
+        <v>99.44885499999999</v>
       </c>
       <c r="O446" s="6" t="n">
         <v>100.297718</v>
@@ -36771,7 +36771,7 @@
         <v>99.48919100000001</v>
       </c>
       <c r="N447" s="9" t="n">
-        <v>99.515027</v>
+        <v>99.51575800000001</v>
       </c>
       <c r="O447" s="9" t="n">
         <v>100.335448</v>
@@ -36855,7 +36855,7 @@
         <v>99.30237700000001</v>
       </c>
       <c r="N448" s="6" t="n">
-        <v>99.58543299999999</v>
+        <v>99.586242</v>
       </c>
       <c r="O448" s="6" t="n">
         <v>100.402915</v>
@@ -36939,7 +36939,7 @@
         <v>99.082825</v>
       </c>
       <c r="N449" s="9" t="n">
-        <v>99.650679</v>
+        <v>99.651537</v>
       </c>
       <c r="O449" s="9" t="n">
         <v>100.48506</v>
@@ -37023,7 +37023,7 @@
         <v>98.84902099999999</v>
       </c>
       <c r="N450" s="6" t="n">
-        <v>99.70380900000001</v>
+        <v>99.70473</v>
       </c>
       <c r="O450" s="6" t="n">
         <v>100.63214</v>
@@ -37107,7 +37107,7 @@
         <v>98.664529</v>
       </c>
       <c r="N451" s="9" t="n">
-        <v>99.748104</v>
+        <v>99.749144</v>
       </c>
       <c r="O451" s="9" t="n">
         <v>100.852252</v>
@@ -37191,7 +37191,7 @@
         <v>98.575514</v>
       </c>
       <c r="N452" s="6" t="n">
-        <v>99.790616</v>
+        <v>99.791775</v>
       </c>
       <c r="O452" s="6" t="n">
         <v>101.081772</v>
@@ -37275,7 +37275,7 @@
         <v>98.545501</v>
       </c>
       <c r="N453" s="9" t="n">
-        <v>99.840459</v>
+        <v>99.84168099999999</v>
       </c>
       <c r="O453" s="9" t="n">
         <v>101.238397</v>
@@ -37359,7 +37359,7 @@
         <v>98.550822</v>
       </c>
       <c r="N454" s="6" t="n">
-        <v>99.908192</v>
+        <v>99.909279</v>
       </c>
       <c r="O454" s="6" t="n">
         <v>101.304899</v>
@@ -37443,7 +37443,7 @@
         <v>98.59469199999999</v>
       </c>
       <c r="N455" s="9" t="n">
-        <v>99.986108</v>
+        <v>99.987037</v>
       </c>
       <c r="O455" s="9" t="n">
         <v>101.224725</v>
@@ -37527,7 +37527,7 @@
         <v>98.67578899999999</v>
       </c>
       <c r="N456" s="6" t="n">
-        <v>100.071859</v>
+        <v>100.07272</v>
       </c>
       <c r="O456" s="6" t="n">
         <v>101.004863</v>
@@ -37611,7 +37611,7 @@
         <v>98.768801</v>
       </c>
       <c r="N457" s="9" t="n">
-        <v>100.167662</v>
+        <v>100.168551</v>
       </c>
       <c r="O457" s="9" t="n">
         <v>100.701399</v>
@@ -37695,7 +37695,7 @@
         <v>98.843002</v>
       </c>
       <c r="N458" s="6" t="n">
-        <v>100.263737</v>
+        <v>100.264639</v>
       </c>
       <c r="O458" s="6" t="n">
         <v>100.392656</v>
@@ -37779,7 +37779,7 @@
         <v>98.87049</v>
       </c>
       <c r="N459" s="9" t="n">
-        <v>100.362334</v>
+        <v>100.363207</v>
       </c>
       <c r="O459" s="9" t="n">
         <v>100.137233</v>
@@ -37863,7 +37863,7 @@
         <v>98.858771</v>
       </c>
       <c r="N460" s="6" t="n">
-        <v>100.459892</v>
+        <v>100.460761</v>
       </c>
       <c r="O460" s="6" t="n">
         <v>99.96413800000001</v>
@@ -37947,7 +37947,7 @@
         <v>98.83102100000001</v>
       </c>
       <c r="N461" s="9" t="n">
-        <v>100.558842</v>
+        <v>100.55971</v>
       </c>
       <c r="O461" s="9" t="n">
         <v>99.899615</v>
@@ -38031,7 +38031,7 @@
         <v>98.808734</v>
       </c>
       <c r="N462" s="6" t="n">
-        <v>100.646552</v>
+        <v>100.647385</v>
       </c>
       <c r="O462" s="6" t="n">
         <v>99.89067900000001</v>
@@ -38115,7 +38115,7 @@
         <v>98.78897499999999</v>
       </c>
       <c r="N463" s="9" t="n">
-        <v>100.733264</v>
+        <v>100.734093</v>
       </c>
       <c r="O463" s="9" t="n">
         <v>99.92132599999999</v>
@@ -38199,7 +38199,7 @@
         <v>98.769777</v>
       </c>
       <c r="N464" s="6" t="n">
-        <v>100.813605</v>
+        <v>100.814493</v>
       </c>
       <c r="O464" s="6" t="n">
         <v>99.995718</v>
@@ -38283,7 +38283,7 @@
         <v>98.741198</v>
       </c>
       <c r="N465" s="9" t="n">
-        <v>100.881008</v>
+        <v>100.882029</v>
       </c>
       <c r="O465" s="9" t="n">
         <v>100.088421</v>
@@ -38367,7 +38367,7 @@
         <v>98.691909</v>
       </c>
       <c r="N466" s="6" t="n">
-        <v>100.945593</v>
+        <v>100.946706</v>
       </c>
       <c r="O466" s="6" t="n">
         <v>100.188819</v>
@@ -38451,7 +38451,7 @@
         <v>98.65710799999999</v>
       </c>
       <c r="N467" s="9" t="n">
-        <v>100.999612</v>
+        <v>101.000771</v>
       </c>
       <c r="O467" s="9" t="n">
         <v>100.283258</v>
@@ -38535,7 +38535,7 @@
         <v>98.625551</v>
       </c>
       <c r="N468" s="6" t="n">
-        <v>101.033632</v>
+        <v>101.034857</v>
       </c>
       <c r="O468" s="6" t="n">
         <v>100.370237</v>
@@ -38619,7 +38619,7 @@
         <v>98.616364</v>
       </c>
       <c r="N469" s="9" t="n">
-        <v>101.043422</v>
+        <v>101.044763</v>
       </c>
       <c r="O469" s="9" t="n">
         <v>100.451297</v>
@@ -38703,7 +38703,7 @@
         <v>98.629704</v>
       </c>
       <c r="N470" s="6" t="n">
-        <v>101.028239</v>
+        <v>101.029732</v>
       </c>
       <c r="O470" s="6" t="n">
         <v>100.524302</v>
@@ -38787,7 +38787,7 @@
         <v>98.702406</v>
       </c>
       <c r="N471" s="9" t="n">
-        <v>100.983073</v>
+        <v>100.984701</v>
       </c>
       <c r="O471" s="9" t="n">
         <v>100.533258</v>
@@ -38871,7 +38871,7 @@
         <v>98.843209</v>
       </c>
       <c r="N472" s="6" t="n">
-        <v>100.905822</v>
+        <v>100.90768</v>
       </c>
       <c r="O472" s="6" t="n">
         <v>100.421271</v>
@@ -38955,7 +38955,7 @@
         <v>99.007234</v>
       </c>
       <c r="N473" s="9" t="n">
-        <v>100.807857</v>
+        <v>100.810064</v>
       </c>
       <c r="O473" s="9" t="n">
         <v>100.220718</v>
@@ -39039,7 +39039,7 @@
         <v>99.118206</v>
       </c>
       <c r="N474" s="6" t="n">
-        <v>100.715774</v>
+        <v>100.718386</v>
       </c>
       <c r="O474" s="6" t="n">
         <v>99.971486</v>
@@ -39123,7 +39123,7 @@
         <v>99.19544</v>
       </c>
       <c r="N475" s="9" t="n">
-        <v>100.633468</v>
+        <v>100.63642</v>
       </c>
       <c r="O475" s="9" t="n">
         <v>99.68424899999999</v>
@@ -39207,7 +39207,7 @@
         <v>99.240047</v>
       </c>
       <c r="N476" s="6" t="n">
-        <v>100.563245</v>
+        <v>100.566518</v>
       </c>
       <c r="O476" s="6" t="n">
         <v>99.42711</v>
@@ -39291,7 +39291,7 @@
         <v>99.25572</v>
       </c>
       <c r="N477" s="9" t="n">
-        <v>100.502645</v>
+        <v>100.506184</v>
       </c>
       <c r="O477" s="9" t="n">
         <v>99.219936</v>
@@ -39375,7 +39375,7 @@
         <v>99.262056</v>
       </c>
       <c r="N478" s="6" t="n">
-        <v>100.443481</v>
+        <v>100.44719</v>
       </c>
       <c r="O478" s="6" t="n">
         <v>99.055898</v>
@@ -39459,7 +39459,7 @@
         <v>99.243066</v>
       </c>
       <c r="N479" s="9" t="n">
-        <v>100.383873</v>
+        <v>100.387748</v>
       </c>
       <c r="O479" s="9" t="n">
         <v>99.000445</v>
@@ -39543,7 +39543,7 @@
         <v>99.213712</v>
       </c>
       <c r="N480" s="6" t="n">
-        <v>100.322616</v>
+        <v>100.326693</v>
       </c>
       <c r="O480" s="6" t="n">
         <v>99.047498</v>
@@ -39627,7 +39627,7 @@
         <v>99.189898</v>
       </c>
       <c r="N481" s="9" t="n">
-        <v>100.24474</v>
+        <v>100.249096</v>
       </c>
       <c r="O481" s="9" t="n">
         <v>99.13811099999999</v>
@@ -39711,7 +39711,7 @@
         <v>99.19521899999999</v>
       </c>
       <c r="N482" s="6" t="n">
-        <v>100.141689</v>
+        <v>100.146434</v>
       </c>
       <c r="O482" s="6" t="n">
         <v>99.168932</v>
@@ -39795,7 +39795,7 @@
         <v>99.23947</v>
       </c>
       <c r="N483" s="9" t="n">
-        <v>100.005824</v>
+        <v>100.011032</v>
       </c>
       <c r="O483" s="9" t="n">
         <v>99.172121</v>
@@ -39879,7 +39879,7 @@
         <v>99.325553</v>
       </c>
       <c r="N484" s="6" t="n">
-        <v>99.821956</v>
+        <v>99.827665</v>
       </c>
       <c r="O484" s="6" t="n">
         <v>99.17484</v>
@@ -39963,7 +39963,7 @@
         <v>99.48364100000001</v>
       </c>
       <c r="N485" s="9" t="n">
-        <v>99.57194800000001</v>
+        <v>99.578199</v>
       </c>
       <c r="O485" s="9" t="n">
         <v>99.13416599999999</v>
@@ -40047,7 +40047,7 @@
         <v>99.77884299999999</v>
       </c>
       <c r="N486" s="6" t="n">
-        <v>99.232862</v>
+        <v>99.239722</v>
       </c>
       <c r="O486" s="6" t="n">
         <v>99.044944</v>
@@ -40131,7 +40131,7 @@
         <v>100.2124</v>
       </c>
       <c r="N487" s="9" t="n">
-        <v>98.78703299999999</v>
+        <v>98.794578</v>
       </c>
       <c r="O487" s="9" t="n">
         <v>98.941948</v>
@@ -40215,7 +40215,7 @@
         <v>100.764709</v>
       </c>
       <c r="N488" s="6" t="n">
-        <v>98.253626</v>
+        <v>98.261999</v>
       </c>
       <c r="O488" s="6" t="n">
         <v>98.804221</v>
@@ -40299,7 +40299,7 @@
         <v>101.440248</v>
       </c>
       <c r="N489" s="9" t="n">
-        <v>95.55669399999999</v>
+        <v>95.570324</v>
       </c>
       <c r="O489" s="9" t="n">
         <v>98.67305</v>
@@ -40383,7 +40383,7 @@
         <v>102.123168</v>
       </c>
       <c r="N490" s="6" t="n">
-        <v>93.073734</v>
+        <v>93.09028000000001</v>
       </c>
       <c r="O490" s="6" t="n">
         <v>98.59501299999999</v>
@@ -40467,7 +40467,7 @@
         <v>102.71858</v>
       </c>
       <c r="N491" s="9" t="n">
-        <v>95.743156</v>
+        <v>95.753169</v>
       </c>
       <c r="O491" s="9" t="n">
         <v>98.59129299999999</v>
@@ -40551,7 +40551,7 @@
         <v>103.128354</v>
       </c>
       <c r="N492" s="6" t="n">
-        <v>96.07962499999999</v>
+        <v>96.091244</v>
       </c>
       <c r="O492" s="6" t="n">
         <v>98.68841</v>
@@ -40635,7 +40635,7 @@
         <v>103.34182</v>
       </c>
       <c r="N493" s="9" t="n">
-        <v>97.10638899999999</v>
+        <v>97.11473100000001</v>
       </c>
       <c r="O493" s="9" t="n">
         <v>98.88535899999999</v>
@@ -40719,7 +40719,7 @@
         <v>103.39348</v>
       </c>
       <c r="N494" s="6" t="n">
-        <v>97.453835</v>
+        <v>97.464491</v>
       </c>
       <c r="O494" s="6" t="n">
         <v>99.166437</v>
@@ -40803,7 +40803,7 @@
         <v>103.335325</v>
       </c>
       <c r="N495" s="9" t="n">
-        <v>97.844987</v>
+        <v>97.855313</v>
       </c>
       <c r="O495" s="9" t="n">
         <v>99.474293</v>
@@ -40887,7 +40887,7 @@
         <v>103.226162</v>
       </c>
       <c r="N496" s="6" t="n">
-        <v>98.23362299999999</v>
+        <v>98.243629</v>
       </c>
       <c r="O496" s="6" t="n">
         <v>99.771334</v>
@@ -40971,7 +40971,7 @@
         <v>103.1115</v>
       </c>
       <c r="N497" s="9" t="n">
-        <v>98.57064699999999</v>
+        <v>98.580444</v>
       </c>
       <c r="O497" s="9" t="n">
         <v>100.040225</v>
@@ -41055,7 +41055,7 @@
         <v>103.026028</v>
       </c>
       <c r="N498" s="6" t="n">
-        <v>98.843762</v>
+        <v>98.853317</v>
       </c>
       <c r="O498" s="6" t="n">
         <v>100.260968</v>
@@ -41139,7 +41139,7 @@
         <v>102.911314</v>
       </c>
       <c r="N499" s="9" t="n">
-        <v>99.067261</v>
+        <v>99.07641700000001</v>
       </c>
       <c r="O499" s="9" t="n">
         <v>100.439602</v>
@@ -41223,7 +41223,7 @@
         <v>102.776357</v>
       </c>
       <c r="N500" s="6" t="n">
-        <v>99.284261</v>
+        <v>99.29297699999999</v>
       </c>
       <c r="O500" s="6" t="n">
         <v>100.611608</v>
@@ -41307,7 +41307,7 @@
         <v>102.613061</v>
       </c>
       <c r="N501" s="9" t="n">
-        <v>99.506621</v>
+        <v>99.514926</v>
       </c>
       <c r="O501" s="9" t="n">
         <v>100.761999</v>
@@ -41391,7 +41391,7 @@
         <v>102.421627</v>
       </c>
       <c r="N502" s="6" t="n">
-        <v>99.72223</v>
+        <v>99.730238</v>
       </c>
       <c r="O502" s="6" t="n">
         <v>100.858559</v>
@@ -41475,7 +41475,7 @@
         <v>102.250178</v>
       </c>
       <c r="N503" s="9" t="n">
-        <v>99.910652</v>
+        <v>99.918543</v>
       </c>
       <c r="O503" s="9" t="n">
         <v>100.87585</v>
@@ -41559,7 +41559,7 @@
         <v>102.112953</v>
       </c>
       <c r="N504" s="6" t="n">
-        <v>100.06839</v>
+        <v>100.076228</v>
       </c>
       <c r="O504" s="6" t="n">
         <v>100.814893</v>
@@ -41643,7 +41643,7 @@
         <v>101.989875</v>
       </c>
       <c r="N505" s="9" t="n">
-        <v>100.188481</v>
+        <v>100.19632</v>
       </c>
       <c r="O505" s="9" t="n">
         <v>100.695469</v>
@@ -41727,7 +41727,7 @@
         <v>101.870117</v>
       </c>
       <c r="N506" s="6" t="n">
-        <v>100.300791</v>
+        <v>100.308592</v>
       </c>
       <c r="O506" s="6" t="n">
         <v>100.545911</v>
@@ -41811,7 +41811,7 @@
         <v>101.747233</v>
       </c>
       <c r="N507" s="9" t="n">
-        <v>100.432031</v>
+        <v>100.439552</v>
       </c>
       <c r="O507" s="9" t="n">
         <v>100.386218</v>
@@ -41895,7 +41895,7 @@
         <v>101.624443</v>
       </c>
       <c r="N508" s="6" t="n">
-        <v>100.588669</v>
+        <v>100.595745</v>
       </c>
       <c r="O508" s="6" t="n">
         <v>100.256376</v>
@@ -41979,7 +41979,7 @@
         <v>101.499258</v>
       </c>
       <c r="N509" s="9" t="n">
-        <v>100.764847</v>
+        <v>100.771395</v>
       </c>
       <c r="O509" s="9" t="n">
         <v>100.171727</v>
@@ -42063,7 +42063,7 @@
         <v>101.345949</v>
       </c>
       <c r="N510" s="6" t="n">
-        <v>100.954178</v>
+        <v>100.960135</v>
       </c>
       <c r="O510" s="6" t="n">
         <v>100.12999</v>
@@ -42147,7 +42147,7 @@
         <v>101.13479</v>
       </c>
       <c r="N511" s="9" t="n">
-        <v>101.163991</v>
+        <v>101.169229</v>
       </c>
       <c r="O511" s="9" t="n">
         <v>100.120627</v>
@@ -42231,7 +42231,7 @@
         <v>100.840457</v>
       </c>
       <c r="N512" s="6" t="n">
-        <v>101.365937</v>
+        <v>101.370439</v>
       </c>
       <c r="O512" s="6" t="n">
         <v>100.118806</v>
@@ -42315,7 +42315,7 @@
         <v>100.548459</v>
       </c>
       <c r="N513" s="9" t="n">
-        <v>101.534089</v>
+        <v>101.537968</v>
       </c>
       <c r="O513" s="9" t="n">
         <v>100.135434</v>
@@ -42399,7 +42399,7 @@
         <v>100.318409</v>
       </c>
       <c r="N514" s="6" t="n">
-        <v>101.644665</v>
+        <v>101.648132</v>
       </c>
       <c r="O514" s="6" t="n">
         <v>100.189094</v>
@@ -42483,7 +42483,7 @@
         <v>100.146546</v>
       </c>
       <c r="N515" s="9" t="n">
-        <v>101.681153</v>
+        <v>101.684491</v>
       </c>
       <c r="O515" s="9" t="n">
         <v>100.264195</v>
@@ -42567,7 +42567,7 @@
         <v>100.015834</v>
       </c>
       <c r="N516" s="6" t="n">
-        <v>101.630796</v>
+        <v>101.634235</v>
       </c>
       <c r="O516" s="6" t="n">
         <v>100.335159</v>
@@ -42651,7 +42651,7 @@
         <v>99.92132599999999</v>
       </c>
       <c r="N517" s="9" t="n">
-        <v>101.507476</v>
+        <v>101.511001</v>
       </c>
       <c r="O517" s="9" t="n">
         <v>100.383775</v>
@@ -42735,7 +42735,7 @@
         <v>99.841396</v>
       </c>
       <c r="N518" s="6" t="n">
-        <v>101.343523</v>
+        <v>101.347084</v>
       </c>
       <c r="O518" s="6" t="n">
         <v>100.430545</v>
@@ -42819,7 +42819,7 @@
         <v>99.75242</v>
       </c>
       <c r="N519" s="9" t="n">
-        <v>101.166503</v>
+        <v>101.169891</v>
       </c>
       <c r="O519" s="9" t="n">
         <v>100.482495</v>
@@ -42903,7 +42903,7 @@
         <v>99.612028</v>
       </c>
       <c r="N520" s="6" t="n">
-        <v>101.001868</v>
+        <v>101.004937</v>
       </c>
       <c r="O520" s="6" t="n">
         <v>100.524667</v>
@@ -42987,7 +42987,7 @@
         <v>99.440119</v>
       </c>
       <c r="N521" s="9" t="n">
-        <v>100.870706</v>
+        <v>100.873147</v>
       </c>
       <c r="O521" s="9" t="n">
         <v>100.575517</v>
@@ -43071,7 +43071,7 @@
         <v>99.24509399999999</v>
       </c>
       <c r="N522" s="6" t="n">
-        <v>100.763686</v>
+        <v>100.765242</v>
       </c>
       <c r="O522" s="6" t="n">
         <v>100.64361</v>
@@ -43155,7 +43155,7 @@
         <v>99.065482</v>
       </c>
       <c r="N523" s="9" t="n">
-        <v>100.663368</v>
+        <v>100.66373</v>
       </c>
       <c r="O523" s="9" t="n">
         <v>100.714411</v>
@@ -43239,7 +43239,7 @@
         <v>98.924232</v>
       </c>
       <c r="N524" s="6" t="n">
-        <v>100.567792</v>
+        <v>100.566862</v>
       </c>
       <c r="O524" s="6" t="n">
         <v>100.766356</v>
@@ -43323,7 +43323,7 @@
         <v>98.825355</v>
       </c>
       <c r="N525" s="9" t="n">
-        <v>100.477409</v>
+        <v>100.475364</v>
       </c>
       <c r="O525" s="9" t="n">
         <v>100.78027</v>
@@ -43407,7 +43407,7 @@
         <v>98.73905000000001</v>
       </c>
       <c r="N526" s="6" t="n">
-        <v>100.383687</v>
+        <v>100.380796</v>
       </c>
       <c r="O526" s="6" t="n">
         <v>100.744827</v>
@@ -43491,7 +43491,7 @@
         <v>98.694999</v>
       </c>
       <c r="N527" s="9" t="n">
-        <v>100.290873</v>
+        <v>100.287425</v>
       </c>
       <c r="O527" s="9" t="n">
         <v>100.670756</v>
@@ -43575,7 +43575,7 @@
         <v>98.72140899999999</v>
       </c>
       <c r="N528" s="6" t="n">
-        <v>100.206185</v>
+        <v>100.202355</v>
       </c>
       <c r="O528" s="6" t="n">
         <v>100.572192</v>
@@ -43659,7 +43659,7 @@
         <v>98.789305</v>
       </c>
       <c r="N529" s="9" t="n">
-        <v>100.138378</v>
+        <v>100.134079</v>
       </c>
       <c r="O529" s="9" t="n">
         <v>100.469904</v>
@@ -43743,7 +43743,7 @@
         <v>98.88441899999999</v>
       </c>
       <c r="N530" s="6" t="n">
-        <v>100.084765</v>
+        <v>100.07974</v>
       </c>
       <c r="O530" s="6" t="n">
         <v>100.376591</v>
@@ -43827,7 +43827,7 @@
         <v>98.989289</v>
       </c>
       <c r="N531" s="9" t="n">
-        <v>100.032874</v>
+        <v>100.026708</v>
       </c>
       <c r="O531" s="9" t="n">
         <v>100.315029</v>
@@ -43911,7 +43911,7 @@
         <v>99.08412</v>
       </c>
       <c r="N532" s="6" t="n">
-        <v>99.994353</v>
+        <v>99.986761</v>
       </c>
       <c r="O532" s="6" t="n">
         <v>100.30701</v>
@@ -43995,7 +43995,7 @@
         <v>99.160549</v>
       </c>
       <c r="N533" s="9" t="n">
-        <v>99.982116</v>
+        <v>99.972791</v>
       </c>
       <c r="O533" s="9" t="n">
         <v>100.340843</v>
@@ -44079,7 +44079,7 @@
         <v>99.216832</v>
       </c>
       <c r="N534" s="6" t="n">
-        <v>99.997514</v>
+        <v>99.98612</v>
       </c>
       <c r="O534" s="6" t="n">
         <v>100.390247</v>
@@ -44163,7 +44163,7 @@
         <v>99.25679700000001</v>
       </c>
       <c r="N535" s="9" t="n">
-        <v>100.025173</v>
+        <v>100.011392</v>
       </c>
       <c r="O535" s="9" t="n">
         <v>100.428315</v>
@@ -44247,7 +44247,7 @@
         <v>99.288444</v>
       </c>
       <c r="N536" s="6" t="n">
-        <v>100.027704</v>
+        <v>100.011504</v>
       </c>
       <c r="O536" s="6" t="n">
         <v>100.453038</v>
@@ -44331,7 +44331,7 @@
         <v>99.31176600000001</v>
       </c>
       <c r="N537" s="9" t="n">
-        <v>100.001897</v>
+        <v>99.983507</v>
       </c>
       <c r="O537" s="9" t="n">
         <v>100.454715</v>
@@ -44415,7 +44415,7 @@
         <v>99.336482</v>
       </c>
       <c r="N538" s="6" t="n">
-        <v>99.951207</v>
+        <v>99.931022</v>
       </c>
       <c r="O538" s="6" t="n">
         <v>100.429545</v>
@@ -44499,7 +44499,7 @@
         <v>99.342917</v>
       </c>
       <c r="N539" s="9" t="n">
-        <v>99.884123</v>
+        <v>99.862465</v>
       </c>
       <c r="O539" s="9" t="n">
         <v>100.377561</v>
@@ -44583,7 +44583,7 @@
         <v>99.30723999999999</v>
       </c>
       <c r="N540" s="6" t="n">
-        <v>99.79774500000001</v>
+        <v>99.77467799999999</v>
       </c>
       <c r="O540" s="6" t="n">
         <v>100.304682</v>
@@ -44667,7 +44667,7 @@
         <v>99.23834600000001</v>
       </c>
       <c r="N541" s="9" t="n">
-        <v>99.696808</v>
+        <v>99.672084</v>
       </c>
       <c r="O541" s="9" t="n">
         <v>100.228566</v>
@@ -44751,7 +44751,7 @@
         <v>99.156924</v>
       </c>
       <c r="N542" s="6" t="n">
-        <v>99.585432</v>
+        <v>99.558798</v>
       </c>
       <c r="O542" s="6" t="n">
         <v>100.154715</v>
@@ -44835,7 +44835,7 @@
         <v>99.09093799999999</v>
       </c>
       <c r="N543" s="9" t="n">
-        <v>99.486316</v>
+        <v>99.457526</v>
       </c>
       <c r="O543" s="9" t="n">
         <v>100.071439</v>
@@ -44919,7 +44919,7 @@
         <v>99.080685</v>
       </c>
       <c r="N544" s="6" t="n">
-        <v>99.394492</v>
+        <v>99.363257</v>
       </c>
       <c r="O544" s="6" t="n">
         <v>99.96960199999999</v>
@@ -45003,7 +45003,7 @@
         <v>99.11204600000001</v>
       </c>
       <c r="N545" s="9" t="n">
-        <v>99.298998</v>
+        <v>99.264976</v>
       </c>
       <c r="O545" s="9" t="n">
         <v>99.839995</v>
@@ -45087,7 +45087,7 @@
         <v>99.16477</v>
       </c>
       <c r="N546" s="6" t="n">
-        <v>99.206896</v>
+        <v>99.16972</v>
       </c>
       <c r="O546" s="6" t="n">
         <v>99.701699</v>
@@ -45171,7 +45171,7 @@
         <v>99.221985</v>
       </c>
       <c r="N547" s="9" t="n">
-        <v>99.12917299999999</v>
+        <v>99.08845700000001</v>
       </c>
       <c r="O547" s="9" t="n">
         <v>99.558834</v>
@@ -45255,7 +45255,7 @@
         <v>99.288764</v>
       </c>
       <c r="N548" s="6" t="n">
-        <v>99.080938</v>
+        <v>99.03648699999999</v>
       </c>
       <c r="O548" s="6" t="n">
         <v>99.416664</v>
@@ -45339,7 +45339,7 @@
         <v>99.39373500000001</v>
       </c>
       <c r="N549" s="9" t="n">
-        <v>99.05335599999999</v>
+        <v>99.00535600000001</v>
       </c>
       <c r="O549" s="9" t="n">
         <v>99.30459399999999</v>
@@ -45423,7 +45423,7 @@
         <v>99.501587</v>
       </c>
       <c r="N550" s="6" t="n">
-        <v>99.044051</v>
+        <v>98.992859</v>
       </c>
       <c r="O550" s="6" t="n">
         <v>99.23044</v>
@@ -45507,7 +45507,7 @@
         <v>99.61484900000001</v>
       </c>
       <c r="N551" s="9" t="n">
-        <v>99.06027</v>
+        <v>99.006366</v>
       </c>
       <c r="O551" s="9" t="n">
         <v>99.18846499999999</v>
@@ -45591,7 +45591,7 @@
         <v>99.74811</v>
       </c>
       <c r="N552" s="6" t="n">
-        <v>99.10844299999999</v>
+        <v>99.052148</v>
       </c>
       <c r="O552" s="6" t="n">
         <v>99.16442600000001</v>
@@ -45675,7 +45675,7 @@
         <v>99.91265</v>
       </c>
       <c r="N553" s="9" t="n">
-        <v>99.19386799999999</v>
+        <v>99.135034</v>
       </c>
       <c r="O553" s="9" t="n">
         <v>99.149593</v>
@@ -45759,7 +45759,7 @@
         <v>100.052241</v>
       </c>
       <c r="N554" s="6" t="n">
-        <v>99.30423399999999</v>
+        <v>99.242693</v>
       </c>
       <c r="O554" s="6" t="n">
         <v>99.136381</v>
@@ -45843,7 +45843,7 @@
         <v>100.131775</v>
       </c>
       <c r="N555" s="9" t="n">
-        <v>99.42832</v>
+        <v>99.364105</v>
       </c>
       <c r="O555" s="9" t="n">
         <v>99.14503000000001</v>
@@ -45927,7 +45927,7 @@
         <v>100.193833</v>
       </c>
       <c r="N556" s="6" t="n">
-        <v>99.557726</v>
+        <v>99.491095</v>
       </c>
       <c r="O556" s="6" t="n">
         <v>99.182095</v>
@@ -46011,7 +46011,7 @@
         <v>100.258551</v>
       </c>
       <c r="N557" s="9" t="n">
-        <v>99.698927</v>
+        <v>99.630049</v>
       </c>
       <c r="O557" s="9" t="n">
         <v>99.265089</v>
@@ -46095,7 +46095,7 @@
         <v>100.359435</v>
       </c>
       <c r="N558" s="6" t="n">
-        <v>99.862517</v>
+        <v>99.79140099999999</v>
       </c>
       <c r="O558" s="6" t="n">
         <v>99.391604</v>
@@ -46179,7 +46179,7 @@
         <v>100.48189</v>
       </c>
       <c r="N559" s="9" t="n">
-        <v>100.056753</v>
+        <v>99.982955</v>
       </c>
       <c r="O559" s="9" t="n">
         <v>99.546012</v>
@@ -46263,7 +46263,7 @@
         <v>100.599603</v>
       </c>
       <c r="N560" s="6" t="n">
-        <v>100.282217</v>
+        <v>100.204304</v>
       </c>
       <c r="O560" s="6" t="n">
         <v>99.717207</v>
@@ -46347,7 +46347,7 @@
         <v>100.679244</v>
       </c>
       <c r="N561" s="9" t="n">
-        <v>100.53139</v>
+        <v>100.446385</v>
       </c>
       <c r="O561" s="9" t="n">
         <v>99.874979</v>
@@ -46431,7 +46431,7 @@
         <v>100.712871</v>
       </c>
       <c r="N562" s="6" t="n">
-        <v>100.79495</v>
+        <v>100.697343</v>
       </c>
       <c r="O562" s="6" t="n">
         <v>100.023675</v>
@@ -46515,7 +46515,7 @@
         <v>100.692966</v>
       </c>
       <c r="N563" s="9" t="n">
-        <v>101.069159</v>
+        <v>100.949913</v>
       </c>
       <c r="O563" s="9" t="n">
         <v>100.160256</v>
@@ -46599,7 +46599,7 @@
         <v>100.62248</v>
       </c>
       <c r="N564" s="6" t="n">
-        <v>101.360238</v>
+        <v>101.206381</v>
       </c>
       <c r="O564" s="6" t="n">
         <v>100.296868</v>
@@ -46677,7 +46677,7 @@
         <v>100.527377</v>
       </c>
       <c r="N565" s="9" t="n">
-        <v>101.628724</v>
+        <v>101.424331</v>
       </c>
       <c r="O565" s="9" t="n">
         <v>100.427363</v>
